--- a/database/AURE3.xlsx
+++ b/database/AURE3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1083"/>
+  <dimension ref="A1:F1084"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44648</v>
       </c>
       <c r="B2" t="n">
-        <v>12.75723075866699</v>
+        <v>12.75723171234131</v>
       </c>
       <c r="C2" t="n">
-        <v>13.06838243889043</v>
+        <v>13.06838341582507</v>
       </c>
       <c r="D2" t="n">
-        <v>12.02602393921985</v>
+        <v>12.02602483823237</v>
       </c>
       <c r="E2" t="n">
-        <v>13.06838243889043</v>
+        <v>13.06838341582507</v>
       </c>
       <c r="F2" t="n">
         <v>5237900</v>
@@ -472,16 +472,16 @@
         <v>44649</v>
       </c>
       <c r="B3" t="n">
-        <v>12.91281032562256</v>
+        <v>12.91280937194824</v>
       </c>
       <c r="C3" t="n">
-        <v>13.21618309850878</v>
+        <v>13.2161821224289</v>
       </c>
       <c r="D3" t="n">
-        <v>12.6172150483126</v>
+        <v>12.61721411646944</v>
       </c>
       <c r="E3" t="n">
-        <v>12.74945472843788</v>
+        <v>12.74945378682817</v>
       </c>
       <c r="F3" t="n">
         <v>4714100</v>
@@ -492,16 +492,16 @@
         <v>44650</v>
       </c>
       <c r="B4" t="n">
-        <v>12.38385009765625</v>
+        <v>12.38385105133057</v>
       </c>
       <c r="C4" t="n">
-        <v>13.04504841779609</v>
+        <v>13.04504942238897</v>
       </c>
       <c r="D4" t="n">
-        <v>12.30606179816537</v>
+        <v>12.30606274584925</v>
       </c>
       <c r="E4" t="n">
-        <v>12.92836671040398</v>
+        <v>12.92836770601126</v>
       </c>
       <c r="F4" t="n">
         <v>4408600</v>
@@ -512,16 +512,16 @@
         <v>44651</v>
       </c>
       <c r="B5" t="n">
-        <v>12.4383020401001</v>
+        <v>12.43830108642578</v>
       </c>
       <c r="C5" t="n">
-        <v>12.82724207193696</v>
+        <v>12.82724108844168</v>
       </c>
       <c r="D5" t="n">
-        <v>12.05714098694259</v>
+        <v>12.05714006249281</v>
       </c>
       <c r="E5" t="n">
-        <v>12.41496584590627</v>
+        <v>12.4149648940212</v>
       </c>
       <c r="F5" t="n">
         <v>3876100</v>
@@ -532,16 +532,16 @@
         <v>44652</v>
       </c>
       <c r="B6" t="n">
-        <v>12.51609039306641</v>
+        <v>12.51609134674072</v>
       </c>
       <c r="C6" t="n">
-        <v>12.95170281502629</v>
+        <v>12.95170380189247</v>
       </c>
       <c r="D6" t="n">
-        <v>12.31384139766291</v>
+        <v>12.31384233592669</v>
       </c>
       <c r="E6" t="n">
-        <v>12.43830208965145</v>
+        <v>12.43830303739862</v>
       </c>
       <c r="F6" t="n">
         <v>4252000</v>
@@ -572,16 +572,16 @@
         <v>44656</v>
       </c>
       <c r="B8" t="n">
-        <v>12.15826606750488</v>
+        <v>12.15826511383057</v>
       </c>
       <c r="C8" t="n">
-        <v>12.50053298552928</v>
+        <v>12.50053200500811</v>
       </c>
       <c r="D8" t="n">
-        <v>12.05714156535479</v>
+        <v>12.05714061961251</v>
       </c>
       <c r="E8" t="n">
-        <v>12.37607228806586</v>
+        <v>12.37607131730719</v>
       </c>
       <c r="F8" t="n">
         <v>3624900</v>
@@ -592,16 +592,16 @@
         <v>44657</v>
       </c>
       <c r="B9" t="n">
-        <v>12.43052387237549</v>
+        <v>12.43052291870117</v>
       </c>
       <c r="C9" t="n">
-        <v>12.44608183074918</v>
+        <v>12.44608087588125</v>
       </c>
       <c r="D9" t="n">
-        <v>12.01824761944832</v>
+        <v>12.01824669740399</v>
       </c>
       <c r="E9" t="n">
-        <v>12.06492075272512</v>
+        <v>12.06491982710001</v>
       </c>
       <c r="F9" t="n">
         <v>2914800</v>
@@ -612,16 +612,16 @@
         <v>44658</v>
       </c>
       <c r="B10" t="n">
-        <v>12.44608211517334</v>
+        <v>12.44608116149902</v>
       </c>
       <c r="C10" t="n">
-        <v>12.71834045818048</v>
+        <v>12.71833948364451</v>
       </c>
       <c r="D10" t="n">
-        <v>12.20493894778036</v>
+        <v>12.20493801258351</v>
       </c>
       <c r="E10" t="n">
-        <v>12.32162141271669</v>
+        <v>12.32162046857911</v>
       </c>
       <c r="F10" t="n">
         <v>3223900</v>
@@ -632,16 +632,16 @@
         <v>44659</v>
       </c>
       <c r="B11" t="n">
-        <v>12.60943508148193</v>
+        <v>12.60943603515625</v>
       </c>
       <c r="C11" t="n">
-        <v>12.75723270856147</v>
+        <v>12.75723367341398</v>
       </c>
       <c r="D11" t="n">
-        <v>12.33717750513392</v>
+        <v>12.3371784382169</v>
       </c>
       <c r="E11" t="n">
-        <v>12.33717750513392</v>
+        <v>12.3371784382169</v>
       </c>
       <c r="F11" t="n">
         <v>2049800</v>
@@ -672,16 +672,16 @@
         <v>44663</v>
       </c>
       <c r="B13" t="n">
-        <v>12.24383163452148</v>
+        <v>12.2438325881958</v>
       </c>
       <c r="C13" t="n">
-        <v>12.64055063241211</v>
+        <v>12.64055161698694</v>
       </c>
       <c r="D13" t="n">
-        <v>12.21271646263855</v>
+        <v>12.2127174138893</v>
       </c>
       <c r="E13" t="n">
-        <v>12.4849740311532</v>
+        <v>12.48497500361014</v>
       </c>
       <c r="F13" t="n">
         <v>2267700</v>
@@ -712,16 +712,16 @@
         <v>44665</v>
       </c>
       <c r="B15" t="n">
-        <v>12.11159133911133</v>
+        <v>12.11159229278564</v>
       </c>
       <c r="C15" t="n">
-        <v>12.36829167926575</v>
+        <v>12.36829265315281</v>
       </c>
       <c r="D15" t="n">
-        <v>12.0493609985796</v>
+        <v>12.04936194735386</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08047616884546</v>
+        <v>12.08047712006975</v>
       </c>
       <c r="F15" t="n">
         <v>2077400</v>
@@ -732,16 +732,16 @@
         <v>44669</v>
       </c>
       <c r="B16" t="n">
-        <v>12.45386028289795</v>
+        <v>12.45385932922363</v>
       </c>
       <c r="C16" t="n">
-        <v>12.45386028289795</v>
+        <v>12.45385932922363</v>
       </c>
       <c r="D16" t="n">
-        <v>11.92490159008608</v>
+        <v>11.92490067691762</v>
       </c>
       <c r="E16" t="n">
-        <v>12.10381439459067</v>
+        <v>12.10381346772168</v>
       </c>
       <c r="F16" t="n">
         <v>3931100</v>
@@ -772,16 +772,16 @@
         <v>44671</v>
       </c>
       <c r="B18" t="n">
-        <v>12.05714130401611</v>
+        <v>12.0571403503418</v>
       </c>
       <c r="C18" t="n">
-        <v>12.21271717247328</v>
+        <v>12.2127162064935</v>
       </c>
       <c r="D18" t="n">
-        <v>11.95601680405789</v>
+        <v>11.95601585838214</v>
       </c>
       <c r="E18" t="n">
-        <v>12.07269926178396</v>
+        <v>12.07269830687907</v>
       </c>
       <c r="F18" t="n">
         <v>2798400</v>
@@ -792,16 +792,16 @@
         <v>44673</v>
       </c>
       <c r="B19" t="n">
-        <v>12.22049617767334</v>
+        <v>12.22049522399902</v>
       </c>
       <c r="C19" t="n">
-        <v>12.33717789380641</v>
+        <v>12.33717693102638</v>
       </c>
       <c r="D19" t="n">
-        <v>11.80044096101231</v>
+        <v>11.80044004011864</v>
       </c>
       <c r="E19" t="n">
-        <v>12.01824717732137</v>
+        <v>12.01824623943035</v>
       </c>
       <c r="F19" t="n">
         <v>11382300</v>
@@ -812,16 +812,16 @@
         <v>44676</v>
       </c>
       <c r="B20" t="n">
-        <v>12.39163017272949</v>
+        <v>12.39162921905518</v>
       </c>
       <c r="C20" t="n">
-        <v>12.39163017272949</v>
+        <v>12.39162921905518</v>
       </c>
       <c r="D20" t="n">
-        <v>11.90156562298855</v>
+        <v>11.90156470703017</v>
       </c>
       <c r="E20" t="n">
-        <v>12.11937184225865</v>
+        <v>12.11937090953766</v>
       </c>
       <c r="F20" t="n">
         <v>2683100</v>
@@ -832,16 +832,16 @@
         <v>44677</v>
       </c>
       <c r="B21" t="n">
-        <v>11.95601654052734</v>
+        <v>11.95601558685303</v>
       </c>
       <c r="C21" t="n">
-        <v>12.4383020930363</v>
+        <v>12.43830110089237</v>
       </c>
       <c r="D21" t="n">
-        <v>11.86267102151054</v>
+        <v>11.86267007528195</v>
       </c>
       <c r="E21" t="n">
-        <v>12.32939935843881</v>
+        <v>12.32939837498153</v>
       </c>
       <c r="F21" t="n">
         <v>2627000</v>
@@ -852,16 +852,16 @@
         <v>44678</v>
       </c>
       <c r="B22" t="n">
-        <v>12.05714130401611</v>
+        <v>12.0571403503418</v>
       </c>
       <c r="C22" t="n">
-        <v>12.06492028290003</v>
+        <v>12.06491932861043</v>
       </c>
       <c r="D22" t="n">
-        <v>11.83155610929216</v>
+        <v>11.83155517346078</v>
       </c>
       <c r="E22" t="n">
-        <v>12.04936232513219</v>
+        <v>12.04936137207316</v>
       </c>
       <c r="F22" t="n">
         <v>2401400</v>
@@ -872,16 +872,16 @@
         <v>44679</v>
       </c>
       <c r="B23" t="n">
-        <v>11.90934371948242</v>
+        <v>11.90934467315674</v>
       </c>
       <c r="C23" t="n">
-        <v>12.08825577230682</v>
+        <v>12.08825674030803</v>
       </c>
       <c r="D23" t="n">
-        <v>11.49706676482372</v>
+        <v>11.49706768548379</v>
       </c>
       <c r="E23" t="n">
-        <v>12.08825577230682</v>
+        <v>12.08825674030803</v>
       </c>
       <c r="F23" t="n">
         <v>3489600</v>
@@ -892,16 +892,16 @@
         <v>44680</v>
       </c>
       <c r="B24" t="n">
-        <v>11.40372180938721</v>
+        <v>11.40372276306152</v>
       </c>
       <c r="C24" t="n">
-        <v>11.96379567250737</v>
+        <v>11.96379667301973</v>
       </c>
       <c r="D24" t="n">
-        <v>11.40372180938721</v>
+        <v>11.40372276306152</v>
       </c>
       <c r="E24" t="n">
-        <v>11.96379567250737</v>
+        <v>11.96379667301973</v>
       </c>
       <c r="F24" t="n">
         <v>10427400</v>
@@ -932,16 +932,16 @@
         <v>44684</v>
       </c>
       <c r="B26" t="n">
-        <v>11.27148151397705</v>
+        <v>11.27148246765137</v>
       </c>
       <c r="C26" t="n">
-        <v>11.35704879249248</v>
+        <v>11.3570497534066</v>
       </c>
       <c r="D26" t="n">
-        <v>11.01478116211917</v>
+        <v>11.0147820940742</v>
       </c>
       <c r="E26" t="n">
-        <v>11.15479980562136</v>
+        <v>11.1548007494233</v>
       </c>
       <c r="F26" t="n">
         <v>1672900</v>
@@ -972,16 +972,16 @@
         <v>44686</v>
       </c>
       <c r="B28" t="n">
-        <v>11.28714656829834</v>
+        <v>11.28714752197266</v>
       </c>
       <c r="C28" t="n">
-        <v>11.62395965090248</v>
+        <v>11.62396063303483</v>
       </c>
       <c r="D28" t="n">
-        <v>11.14615490637113</v>
+        <v>11.14615584813277</v>
       </c>
       <c r="E28" t="n">
-        <v>11.61612661479554</v>
+        <v>11.61612759626606</v>
       </c>
       <c r="F28" t="n">
         <v>3065700</v>
@@ -992,16 +992,16 @@
         <v>44687</v>
       </c>
       <c r="B29" t="n">
-        <v>11.12265777587891</v>
+        <v>11.12265872955322</v>
       </c>
       <c r="C29" t="n">
-        <v>11.31064618125162</v>
+        <v>11.31064715104436</v>
       </c>
       <c r="D29" t="n">
-        <v>11.05216193711426</v>
+        <v>11.05216288474415</v>
       </c>
       <c r="E29" t="n">
-        <v>11.28714781732991</v>
+        <v>11.28714878510787</v>
       </c>
       <c r="F29" t="n">
         <v>2813300</v>
@@ -1012,16 +1012,16 @@
         <v>44690</v>
       </c>
       <c r="B30" t="n">
-        <v>11.07566070556641</v>
+        <v>11.07566165924072</v>
       </c>
       <c r="C30" t="n">
-        <v>11.13049046868818</v>
+        <v>11.13049142708364</v>
       </c>
       <c r="D30" t="n">
-        <v>10.80934343269006</v>
+        <v>10.80934436343302</v>
       </c>
       <c r="E30" t="n">
-        <v>10.99733183225001</v>
+        <v>10.99733277917979</v>
       </c>
       <c r="F30" t="n">
         <v>1545300</v>
@@ -1032,16 +1032,16 @@
         <v>44691</v>
       </c>
       <c r="B31" t="n">
-        <v>11.12265777587891</v>
+        <v>11.12265872955322</v>
       </c>
       <c r="C31" t="n">
-        <v>11.25581641643446</v>
+        <v>11.25581738152601</v>
       </c>
       <c r="D31" t="n">
-        <v>10.95033469745416</v>
+        <v>10.95033563635322</v>
       </c>
       <c r="E31" t="n">
-        <v>11.11482473890516</v>
+        <v>11.11482569190786</v>
       </c>
       <c r="F31" t="n">
         <v>2338900</v>
@@ -1112,16 +1112,16 @@
         <v>44697</v>
       </c>
       <c r="B35" t="n">
-        <v>11.27931499481201</v>
+        <v>11.27931594848633</v>
       </c>
       <c r="C35" t="n">
-        <v>11.41247363789934</v>
+        <v>11.41247460283231</v>
       </c>
       <c r="D35" t="n">
-        <v>11.11482495023352</v>
+        <v>11.11482589000009</v>
       </c>
       <c r="E35" t="n">
-        <v>11.17748850021538</v>
+        <v>11.1774894452802</v>
       </c>
       <c r="F35" t="n">
         <v>2419100</v>
@@ -1212,16 +1212,16 @@
         <v>44704</v>
       </c>
       <c r="B40" t="n">
-        <v>11.20882034301758</v>
+        <v>11.20881938934326</v>
       </c>
       <c r="C40" t="n">
-        <v>11.4359731995218</v>
+        <v>11.43597222652075</v>
       </c>
       <c r="D40" t="n">
-        <v>11.16182286543069</v>
+        <v>11.16182191575504</v>
       </c>
       <c r="E40" t="n">
-        <v>11.18532123072435</v>
+        <v>11.1853202790494</v>
       </c>
       <c r="F40" t="n">
         <v>1184600</v>
@@ -1292,16 +1292,16 @@
         <v>44708</v>
       </c>
       <c r="B44" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C44" t="n">
-        <v>11.42030698171035</v>
+        <v>11.42030600182509</v>
       </c>
       <c r="D44" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="E44" t="n">
-        <v>11.26364997004757</v>
+        <v>11.26364900360379</v>
       </c>
       <c r="F44" t="n">
         <v>2224600</v>
@@ -1312,16 +1312,16 @@
         <v>44711</v>
       </c>
       <c r="B45" t="n">
-        <v>11.09915828704834</v>
+        <v>11.09916019439697</v>
       </c>
       <c r="C45" t="n">
-        <v>11.271481348008</v>
+        <v>11.27148328496971</v>
       </c>
       <c r="D45" t="n">
-        <v>11.0286624554285</v>
+        <v>11.02866435066269</v>
       </c>
       <c r="E45" t="n">
-        <v>11.15398804630846</v>
+        <v>11.15398996307938</v>
       </c>
       <c r="F45" t="n">
         <v>1940200</v>
@@ -1332,16 +1332,16 @@
         <v>44712</v>
       </c>
       <c r="B46" t="n">
-        <v>10.93466949462891</v>
+        <v>10.93466854095459</v>
       </c>
       <c r="C46" t="n">
-        <v>11.20881981582572</v>
+        <v>11.2088188382412</v>
       </c>
       <c r="D46" t="n">
-        <v>10.82500921675028</v>
+        <v>10.82500827264005</v>
       </c>
       <c r="E46" t="n">
-        <v>11.16965537751195</v>
+        <v>11.16965440334319</v>
       </c>
       <c r="F46" t="n">
         <v>9431500</v>
@@ -1412,16 +1412,16 @@
         <v>44718</v>
       </c>
       <c r="B50" t="n">
-        <v>10.61352252960205</v>
+        <v>10.61352157592773</v>
       </c>
       <c r="C50" t="n">
-        <v>10.91117121735836</v>
+        <v>10.91117023693893</v>
       </c>
       <c r="D50" t="n">
-        <v>10.4568655220986</v>
+        <v>10.45686458250065</v>
       </c>
       <c r="E50" t="n">
-        <v>10.8171770128563</v>
+        <v>10.81717604088268</v>
       </c>
       <c r="F50" t="n">
         <v>3175000</v>
@@ -1432,16 +1432,16 @@
         <v>44719</v>
       </c>
       <c r="B51" t="n">
-        <v>10.8563404083252</v>
+        <v>10.85634136199951</v>
       </c>
       <c r="C51" t="n">
-        <v>10.87983951905932</v>
+        <v>10.87984047479791</v>
       </c>
       <c r="D51" t="n">
-        <v>10.53519336495403</v>
+        <v>10.53519429041721</v>
       </c>
       <c r="E51" t="n">
-        <v>10.59002387633413</v>
+        <v>10.59002480661389</v>
       </c>
       <c r="F51" t="n">
         <v>2760900</v>
@@ -1452,16 +1452,16 @@
         <v>44720</v>
       </c>
       <c r="B52" t="n">
-        <v>11.12265777587891</v>
+        <v>11.12265872955322</v>
       </c>
       <c r="C52" t="n">
-        <v>11.19315361464355</v>
+        <v>11.19315457436229</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73884792815973</v>
+        <v>10.73884884892558</v>
       </c>
       <c r="E52" t="n">
-        <v>10.78584540300267</v>
+        <v>10.78584632779816</v>
       </c>
       <c r="F52" t="n">
         <v>2847500</v>
@@ -1552,16 +1552,16 @@
         <v>44727</v>
       </c>
       <c r="B57" t="n">
-        <v>10.84067440032959</v>
+        <v>10.84067535400391</v>
       </c>
       <c r="C57" t="n">
-        <v>10.84850743674878</v>
+        <v>10.84850839111218</v>
       </c>
       <c r="D57" t="n">
-        <v>10.44119850694474</v>
+        <v>10.44119942547642</v>
       </c>
       <c r="E57" t="n">
-        <v>10.55085877581493</v>
+        <v>10.55085970399363</v>
       </c>
       <c r="F57" t="n">
         <v>3153700</v>
@@ -1592,16 +1592,16 @@
         <v>44732</v>
       </c>
       <c r="B59" t="n">
-        <v>10.59785556793213</v>
+        <v>10.59785652160645</v>
       </c>
       <c r="C59" t="n">
-        <v>10.69968280103267</v>
+        <v>10.69968376387016</v>
       </c>
       <c r="D59" t="n">
-        <v>10.37070273932307</v>
+        <v>10.37070367255648</v>
       </c>
       <c r="E59" t="n">
-        <v>10.47252997242361</v>
+        <v>10.47253091482019</v>
       </c>
       <c r="F59" t="n">
         <v>1649800</v>
@@ -1612,16 +1612,16 @@
         <v>44733</v>
       </c>
       <c r="B60" t="n">
-        <v>10.63702011108398</v>
+        <v>10.6370210647583</v>
       </c>
       <c r="C60" t="n">
-        <v>10.7153489825704</v>
+        <v>10.71534994326738</v>
       </c>
       <c r="D60" t="n">
-        <v>10.51952755085384</v>
+        <v>10.51952849399422</v>
       </c>
       <c r="E60" t="n">
-        <v>10.69184987292479</v>
+        <v>10.69185083151493</v>
       </c>
       <c r="F60" t="n">
         <v>1455700</v>
@@ -1652,16 +1652,16 @@
         <v>44735</v>
       </c>
       <c r="B62" t="n">
-        <v>10.63702011108398</v>
+        <v>10.6370210647583</v>
       </c>
       <c r="C62" t="n">
-        <v>10.89550434118989</v>
+        <v>10.89550531803891</v>
       </c>
       <c r="D62" t="n">
-        <v>10.55085895004851</v>
+        <v>10.55085989599795</v>
       </c>
       <c r="E62" t="n">
-        <v>10.8798390150923</v>
+        <v>10.87983999053682</v>
       </c>
       <c r="F62" t="n">
         <v>3444100</v>
@@ -1672,16 +1672,16 @@
         <v>44736</v>
       </c>
       <c r="B63" t="n">
-        <v>10.48819637298584</v>
+        <v>10.48819732666016</v>
       </c>
       <c r="C63" t="n">
-        <v>10.70751617197673</v>
+        <v>10.70751714559343</v>
       </c>
       <c r="D63" t="n">
-        <v>10.42553357327416</v>
+        <v>10.42553452125065</v>
       </c>
       <c r="E63" t="n">
-        <v>10.70751617197673</v>
+        <v>10.70751714559343</v>
       </c>
       <c r="F63" t="n">
         <v>807500</v>
@@ -1712,16 +1712,16 @@
         <v>44740</v>
       </c>
       <c r="B65" t="n">
-        <v>10.61352252960205</v>
+        <v>10.61352157592773</v>
       </c>
       <c r="C65" t="n">
-        <v>10.86417374160756</v>
+        <v>10.86417276541107</v>
       </c>
       <c r="D65" t="n">
-        <v>10.47253084934918</v>
+        <v>10.47252990834362</v>
       </c>
       <c r="E65" t="n">
-        <v>10.5273606152255</v>
+        <v>10.52735966929324</v>
       </c>
       <c r="F65" t="n">
         <v>5362200</v>
@@ -1732,16 +1732,16 @@
         <v>44741</v>
       </c>
       <c r="B66" t="n">
-        <v>10.68401718139648</v>
+        <v>10.6840181350708</v>
       </c>
       <c r="C66" t="n">
-        <v>10.68401718139648</v>
+        <v>10.6840181350708</v>
       </c>
       <c r="D66" t="n">
-        <v>10.53519248057162</v>
+        <v>10.53519342096158</v>
       </c>
       <c r="E66" t="n">
-        <v>10.62918667461916</v>
+        <v>10.62918762339921</v>
       </c>
       <c r="F66" t="n">
         <v>1613700</v>
@@ -1772,16 +1772,16 @@
         <v>44743</v>
       </c>
       <c r="B68" t="n">
-        <v>10.68401718139648</v>
+        <v>10.6840181350708</v>
       </c>
       <c r="C68" t="n">
-        <v>10.84067417147572</v>
+        <v>10.84067513913352</v>
       </c>
       <c r="D68" t="n">
-        <v>10.54302551682544</v>
+        <v>10.54302645791459</v>
       </c>
       <c r="E68" t="n">
-        <v>10.72318086866671</v>
+        <v>10.72318182583684</v>
       </c>
       <c r="F68" t="n">
         <v>2696600</v>
@@ -1852,16 +1852,16 @@
         <v>44749</v>
       </c>
       <c r="B72" t="n">
-        <v>11.04432964324951</v>
+        <v>11.04433059692383</v>
       </c>
       <c r="C72" t="n">
-        <v>11.16182220981619</v>
+        <v>11.16182317363595</v>
       </c>
       <c r="D72" t="n">
-        <v>10.62135535781014</v>
+        <v>10.62135627496076</v>
       </c>
       <c r="E72" t="n">
-        <v>10.7858453992032</v>
+        <v>10.78584633055749</v>
       </c>
       <c r="F72" t="n">
         <v>2931100</v>
@@ -1912,16 +1912,16 @@
         <v>44754</v>
       </c>
       <c r="B75" t="n">
-        <v>11.14615535736084</v>
+        <v>11.14615631103516</v>
       </c>
       <c r="C75" t="n">
-        <v>11.22448422760069</v>
+        <v>11.22448518797689</v>
       </c>
       <c r="D75" t="n">
-        <v>10.99733140030449</v>
+        <v>10.99733234124531</v>
       </c>
       <c r="E75" t="n">
-        <v>11.10699166924038</v>
+        <v>11.10699261956382</v>
       </c>
       <c r="F75" t="n">
         <v>1673000</v>
@@ -2032,16 +2032,16 @@
         <v>44762</v>
       </c>
       <c r="B81" t="n">
-        <v>11.27931499481201</v>
+        <v>11.27931594848633</v>
       </c>
       <c r="C81" t="n">
-        <v>11.35764387203968</v>
+        <v>11.35764483233677</v>
       </c>
       <c r="D81" t="n">
-        <v>11.0521621472512</v>
+        <v>11.05216308171958</v>
       </c>
       <c r="E81" t="n">
-        <v>11.08349354874236</v>
+        <v>11.08349448585983</v>
       </c>
       <c r="F81" t="n">
         <v>2285400</v>
@@ -2072,16 +2072,16 @@
         <v>44764</v>
       </c>
       <c r="B83" t="n">
-        <v>11.36547565460205</v>
+        <v>11.36547660827637</v>
       </c>
       <c r="C83" t="n">
-        <v>11.37330869086009</v>
+        <v>11.37330964519167</v>
       </c>
       <c r="D83" t="n">
-        <v>11.13048979585711</v>
+        <v>11.13049072981382</v>
       </c>
       <c r="E83" t="n">
-        <v>11.27148146050397</v>
+        <v>11.27148240629125</v>
       </c>
       <c r="F83" t="n">
         <v>1975500</v>
@@ -2152,16 +2152,16 @@
         <v>44770</v>
       </c>
       <c r="B87" t="n">
-        <v>10.96599960327148</v>
+        <v>10.9660005569458</v>
       </c>
       <c r="C87" t="n">
-        <v>11.33414408482687</v>
+        <v>11.33414507051741</v>
       </c>
       <c r="D87" t="n">
-        <v>10.82500794076103</v>
+        <v>10.8250088821738</v>
       </c>
       <c r="E87" t="n">
-        <v>11.31064497640883</v>
+        <v>11.31064596005574</v>
       </c>
       <c r="F87" t="n">
         <v>2911900</v>
@@ -2172,16 +2172,16 @@
         <v>44771</v>
       </c>
       <c r="B88" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C88" t="n">
-        <v>11.33414581204571</v>
+        <v>11.33414483955325</v>
       </c>
       <c r="D88" t="n">
-        <v>10.51952860439969</v>
+        <v>10.51952770180302</v>
       </c>
       <c r="E88" t="n">
-        <v>10.96600127438851</v>
+        <v>10.96600033348359</v>
       </c>
       <c r="F88" t="n">
         <v>13059200</v>
@@ -2272,16 +2272,16 @@
         <v>44778</v>
       </c>
       <c r="B93" t="n">
-        <v>10.96599960327148</v>
+        <v>10.9660005569458</v>
       </c>
       <c r="C93" t="n">
-        <v>11.16965406089782</v>
+        <v>11.16965503228325</v>
       </c>
       <c r="D93" t="n">
-        <v>10.93466820571354</v>
+        <v>10.93466915666308</v>
       </c>
       <c r="E93" t="n">
-        <v>11.16965406089782</v>
+        <v>11.16965503228325</v>
       </c>
       <c r="F93" t="n">
         <v>1948700</v>
@@ -2292,16 +2292,16 @@
         <v>44781</v>
       </c>
       <c r="B94" t="n">
-        <v>10.97383403778076</v>
+        <v>10.97383308410645</v>
       </c>
       <c r="C94" t="n">
-        <v>11.10699268111997</v>
+        <v>11.10699171587358</v>
       </c>
       <c r="D94" t="n">
-        <v>10.87200679599199</v>
+        <v>10.8720058511669</v>
       </c>
       <c r="E94" t="n">
-        <v>11.02866380374413</v>
+        <v>11.02866284530486</v>
       </c>
       <c r="F94" t="n">
         <v>2949000</v>
@@ -2312,16 +2312,16 @@
         <v>44782</v>
       </c>
       <c r="B95" t="n">
-        <v>10.92683696746826</v>
+        <v>10.92683601379395</v>
       </c>
       <c r="C95" t="n">
-        <v>11.0599956157492</v>
+        <v>11.05999465045304</v>
       </c>
       <c r="D95" t="n">
-        <v>10.67618574576276</v>
+        <v>10.67618481396482</v>
       </c>
       <c r="E95" t="n">
-        <v>10.98166748246601</v>
+        <v>10.98166652400619</v>
       </c>
       <c r="F95" t="n">
         <v>1743500</v>
@@ -2412,16 +2412,16 @@
         <v>44789</v>
       </c>
       <c r="B100" t="n">
-        <v>11.04432964324951</v>
+        <v>11.04433059692383</v>
       </c>
       <c r="C100" t="n">
-        <v>11.29498085032484</v>
+        <v>11.2949818256428</v>
       </c>
       <c r="D100" t="n">
-        <v>10.94250240362528</v>
+        <v>10.94250334850685</v>
       </c>
       <c r="E100" t="n">
-        <v>11.25581641246944</v>
+        <v>11.25581738440557</v>
       </c>
       <c r="F100" t="n">
         <v>1185300</v>
@@ -2472,16 +2472,16 @@
         <v>44792</v>
       </c>
       <c r="B103" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C103" t="n">
-        <v>11.16182272571687</v>
+        <v>11.16182176801008</v>
       </c>
       <c r="D103" t="n">
-        <v>10.98166734905456</v>
+        <v>10.98166640680546</v>
       </c>
       <c r="E103" t="n">
-        <v>11.16182272571687</v>
+        <v>11.16182176801008</v>
       </c>
       <c r="F103" t="n">
         <v>1667800</v>
@@ -2552,16 +2552,16 @@
         <v>44798</v>
       </c>
       <c r="B107" t="n">
-        <v>11.04432964324951</v>
+        <v>11.04433059692383</v>
       </c>
       <c r="C107" t="n">
-        <v>11.22448501158502</v>
+        <v>11.22448598081569</v>
       </c>
       <c r="D107" t="n">
-        <v>10.95033469359675</v>
+        <v>10.95033563915463</v>
       </c>
       <c r="E107" t="n">
-        <v>11.20881968464257</v>
+        <v>11.20882065252055</v>
       </c>
       <c r="F107" t="n">
         <v>2435800</v>
@@ -2592,16 +2592,16 @@
         <v>44802</v>
       </c>
       <c r="B109" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C109" t="n">
-        <v>11.20882020271549</v>
+        <v>11.20881924097621</v>
       </c>
       <c r="D109" t="n">
-        <v>10.93466987205595</v>
+        <v>10.93466893383933</v>
       </c>
       <c r="E109" t="n">
-        <v>11.02083104172059</v>
+        <v>11.02083009611117</v>
       </c>
       <c r="F109" t="n">
         <v>3615600</v>
@@ -2672,16 +2672,16 @@
         <v>44806</v>
       </c>
       <c r="B113" t="n">
-        <v>11.74145412445068</v>
+        <v>11.74145317077637</v>
       </c>
       <c r="C113" t="n">
-        <v>11.79628463916563</v>
+        <v>11.79628368103782</v>
       </c>
       <c r="D113" t="n">
-        <v>11.56129874652895</v>
+        <v>11.56129780748737</v>
       </c>
       <c r="E113" t="n">
-        <v>11.74145412445068</v>
+        <v>11.74145317077637</v>
       </c>
       <c r="F113" t="n">
         <v>3674700</v>
@@ -2752,16 +2752,16 @@
         <v>44813</v>
       </c>
       <c r="B117" t="n">
-        <v>11.31847953796387</v>
+        <v>11.31847858428955</v>
       </c>
       <c r="C117" t="n">
-        <v>11.51430098584213</v>
+        <v>11.51430001566826</v>
       </c>
       <c r="D117" t="n">
-        <v>11.16965556625618</v>
+        <v>11.1696546251215</v>
       </c>
       <c r="E117" t="n">
-        <v>11.51430098584213</v>
+        <v>11.51430001566826</v>
       </c>
       <c r="F117" t="n">
         <v>2426300</v>
@@ -2772,16 +2772,16 @@
         <v>44816</v>
       </c>
       <c r="B118" t="n">
-        <v>11.41247367858887</v>
+        <v>11.41247272491455</v>
       </c>
       <c r="C118" t="n">
-        <v>11.64745956411016</v>
+        <v>11.64745859079944</v>
       </c>
       <c r="D118" t="n">
-        <v>11.35764391253373</v>
+        <v>11.35764296344122</v>
       </c>
       <c r="E118" t="n">
-        <v>11.3968083512872</v>
+        <v>11.39680739892195</v>
       </c>
       <c r="F118" t="n">
         <v>2097200</v>
@@ -2812,16 +2812,16 @@
         <v>44818</v>
       </c>
       <c r="B120" t="n">
-        <v>11.20882034301758</v>
+        <v>11.20881938934326</v>
       </c>
       <c r="C120" t="n">
-        <v>11.42030712465965</v>
+        <v>11.42030615299151</v>
       </c>
       <c r="D120" t="n">
-        <v>11.02866421710068</v>
+        <v>11.02866327875449</v>
       </c>
       <c r="E120" t="n">
-        <v>11.2009873055865</v>
+        <v>11.20098635257864</v>
       </c>
       <c r="F120" t="n">
         <v>1856400</v>
@@ -2852,16 +2852,16 @@
         <v>44820</v>
       </c>
       <c r="B122" t="n">
-        <v>11.16965484619141</v>
+        <v>11.16965579986572</v>
       </c>
       <c r="C122" t="n">
-        <v>11.35764324475576</v>
+        <v>11.35764421448068</v>
       </c>
       <c r="D122" t="n">
-        <v>11.02866317376839</v>
+        <v>11.02866411540472</v>
       </c>
       <c r="E122" t="n">
-        <v>11.2244846090228</v>
+        <v>11.22448556737853</v>
       </c>
       <c r="F122" t="n">
         <v>3523100</v>
@@ -2872,16 +2872,16 @@
         <v>44823</v>
       </c>
       <c r="B123" t="n">
-        <v>11.28714656829834</v>
+        <v>11.28714752197266</v>
       </c>
       <c r="C123" t="n">
-        <v>11.43597126633249</v>
+        <v>11.43597223258132</v>
       </c>
       <c r="D123" t="n">
-        <v>11.1148235089428</v>
+        <v>11.11482444805718</v>
       </c>
       <c r="E123" t="n">
-        <v>11.1148235089428</v>
+        <v>11.11482444805718</v>
       </c>
       <c r="F123" t="n">
         <v>1858600</v>
@@ -2892,16 +2892,16 @@
         <v>44824</v>
       </c>
       <c r="B124" t="n">
-        <v>11.13049125671387</v>
+        <v>11.13049030303955</v>
       </c>
       <c r="C124" t="n">
-        <v>11.35764410901417</v>
+        <v>11.35764313587711</v>
       </c>
       <c r="D124" t="n">
-        <v>11.08349377999676</v>
+        <v>11.08349283034925</v>
       </c>
       <c r="E124" t="n">
-        <v>11.28714826743829</v>
+        <v>11.28714730034141</v>
       </c>
       <c r="F124" t="n">
         <v>1310600</v>
@@ -3012,16 +3012,16 @@
         <v>44832</v>
       </c>
       <c r="B130" t="n">
-        <v>10.74668121337891</v>
+        <v>10.74668025970459</v>
       </c>
       <c r="C130" t="n">
-        <v>11.03649686510639</v>
+        <v>11.03649588571345</v>
       </c>
       <c r="D130" t="n">
-        <v>10.72318210191485</v>
+        <v>10.72318115032588</v>
       </c>
       <c r="E130" t="n">
-        <v>10.95816798755862</v>
+        <v>10.95816701511669</v>
       </c>
       <c r="F130" t="n">
         <v>4249200</v>
@@ -3032,16 +3032,16 @@
         <v>44833</v>
       </c>
       <c r="B131" t="n">
-        <v>10.70751571655273</v>
+        <v>10.70751667022705</v>
       </c>
       <c r="C131" t="n">
-        <v>10.83284131064561</v>
+        <v>10.83284227548216</v>
       </c>
       <c r="D131" t="n">
-        <v>10.6448529195063</v>
+        <v>10.6448538675995</v>
       </c>
       <c r="E131" t="n">
-        <v>10.69184964379139</v>
+        <v>10.6918505960704</v>
       </c>
       <c r="F131" t="n">
         <v>2222600</v>
@@ -3052,16 +3052,16 @@
         <v>44834</v>
       </c>
       <c r="B132" t="n">
-        <v>10.61352252960205</v>
+        <v>10.61352157592773</v>
       </c>
       <c r="C132" t="n">
-        <v>10.74668117272986</v>
+        <v>10.74668020709063</v>
       </c>
       <c r="D132" t="n">
-        <v>10.59785645535194</v>
+        <v>10.59785550308529</v>
       </c>
       <c r="E132" t="n">
-        <v>10.70751673410412</v>
+        <v>10.70751577198399</v>
       </c>
       <c r="F132" t="n">
         <v>4019300</v>
@@ -3092,16 +3092,16 @@
         <v>44838</v>
       </c>
       <c r="B134" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C134" t="n">
-        <v>11.32631277471268</v>
+        <v>11.32631180289231</v>
       </c>
       <c r="D134" t="n">
-        <v>11.07566155605223</v>
+        <v>11.07566060573824</v>
       </c>
       <c r="E134" t="n">
-        <v>11.20882020271549</v>
+        <v>11.20881924097621</v>
       </c>
       <c r="F134" t="n">
         <v>2406500</v>
@@ -3112,16 +3112,16 @@
         <v>44839</v>
       </c>
       <c r="B135" t="n">
-        <v>10.97383403778076</v>
+        <v>10.97383308410645</v>
       </c>
       <c r="C135" t="n">
-        <v>11.20881992290874</v>
+        <v>11.20881894881312</v>
       </c>
       <c r="D135" t="n">
-        <v>10.85634072171701</v>
+        <v>10.85633977825337</v>
       </c>
       <c r="E135" t="n">
-        <v>11.20881992290874</v>
+        <v>11.20881894881312</v>
       </c>
       <c r="F135" t="n">
         <v>5244200</v>
@@ -3172,16 +3172,16 @@
         <v>44844</v>
       </c>
       <c r="B138" t="n">
-        <v>11.07566070556641</v>
+        <v>11.07566165924072</v>
       </c>
       <c r="C138" t="n">
-        <v>11.35764330490633</v>
+        <v>11.35764428286087</v>
       </c>
       <c r="D138" t="n">
-        <v>11.01299790571309</v>
+        <v>11.0129988539918</v>
       </c>
       <c r="E138" t="n">
-        <v>11.07566070556641</v>
+        <v>11.07566165924072</v>
       </c>
       <c r="F138" t="n">
         <v>2000500</v>
@@ -3332,16 +3332,16 @@
         <v>44855</v>
       </c>
       <c r="B146" t="n">
-        <v>11.16965484619141</v>
+        <v>11.16965579986572</v>
       </c>
       <c r="C146" t="n">
-        <v>11.16965484619141</v>
+        <v>11.16965579986572</v>
       </c>
       <c r="D146" t="n">
-        <v>10.75451286561242</v>
+        <v>10.75451378384157</v>
       </c>
       <c r="E146" t="n">
-        <v>10.75451286561242</v>
+        <v>10.75451378384157</v>
       </c>
       <c r="F146" t="n">
         <v>9489900</v>
@@ -3452,16 +3452,16 @@
         <v>44865</v>
       </c>
       <c r="B152" t="n">
-        <v>11.68662357330322</v>
+        <v>11.68662452697754</v>
       </c>
       <c r="C152" t="n">
-        <v>11.72578801061714</v>
+        <v>11.72578896748743</v>
       </c>
       <c r="D152" t="n">
-        <v>11.16182205549541</v>
+        <v>11.16182296634386</v>
       </c>
       <c r="E152" t="n">
-        <v>11.23231789326056</v>
+        <v>11.23231880986175</v>
       </c>
       <c r="F152" t="n">
         <v>2644000</v>
@@ -3472,16 +3472,16 @@
         <v>44866</v>
       </c>
       <c r="B153" t="n">
-        <v>11.56913089752197</v>
+        <v>11.56913185119629</v>
       </c>
       <c r="C153" t="n">
-        <v>11.80411602515518</v>
+        <v>11.80411699819995</v>
       </c>
       <c r="D153" t="n">
-        <v>11.34981034946504</v>
+        <v>11.34981128506018</v>
       </c>
       <c r="E153" t="n">
-        <v>11.67879042455094</v>
+        <v>11.67879138726478</v>
       </c>
       <c r="F153" t="n">
         <v>3576300</v>
@@ -3492,16 +3492,16 @@
         <v>44868</v>
       </c>
       <c r="B154" t="n">
-        <v>11.68662357330322</v>
+        <v>11.68662452697754</v>
       </c>
       <c r="C154" t="n">
-        <v>11.74928637420569</v>
+        <v>11.74928733299354</v>
       </c>
       <c r="D154" t="n">
-        <v>11.36547653192819</v>
+        <v>11.36547745939565</v>
       </c>
       <c r="E154" t="n">
-        <v>11.49863517059581</v>
+        <v>11.49863610892954</v>
       </c>
       <c r="F154" t="n">
         <v>2959500</v>
@@ -3552,16 +3552,16 @@
         <v>44873</v>
       </c>
       <c r="B157" t="n">
-        <v>11.12265777587891</v>
+        <v>11.12265872955322</v>
       </c>
       <c r="C157" t="n">
-        <v>11.27148249038195</v>
+        <v>11.27148345681673</v>
       </c>
       <c r="D157" t="n">
-        <v>11.02083053621881</v>
+        <v>11.02083148116229</v>
       </c>
       <c r="E157" t="n">
-        <v>11.11482473890516</v>
+        <v>11.11482569190786</v>
       </c>
       <c r="F157" t="n">
         <v>2450400</v>
@@ -3572,16 +3572,16 @@
         <v>44874</v>
       </c>
       <c r="B158" t="n">
-        <v>11.12265777587891</v>
+        <v>11.12265872955322</v>
       </c>
       <c r="C158" t="n">
-        <v>11.21665197856526</v>
+        <v>11.21665294029879</v>
       </c>
       <c r="D158" t="n">
-        <v>11.04432964714004</v>
+        <v>11.04433059409837</v>
       </c>
       <c r="E158" t="n">
-        <v>11.14615613980062</v>
+        <v>11.14615709548972</v>
       </c>
       <c r="F158" t="n">
         <v>1977800</v>
@@ -3592,16 +3592,16 @@
         <v>44875</v>
       </c>
       <c r="B159" t="n">
-        <v>10.70751571655273</v>
+        <v>10.70751667022705</v>
       </c>
       <c r="C159" t="n">
-        <v>11.10699160797338</v>
+        <v>11.10699259722736</v>
       </c>
       <c r="D159" t="n">
-        <v>10.49602821627141</v>
+        <v>10.4960291511094</v>
       </c>
       <c r="E159" t="n">
-        <v>11.04432881092694</v>
+        <v>11.04432979459981</v>
       </c>
       <c r="F159" t="n">
         <v>4341400</v>
@@ -3612,16 +3612,16 @@
         <v>44876</v>
       </c>
       <c r="B160" t="n">
-        <v>10.79367828369141</v>
+        <v>10.79367637634277</v>
       </c>
       <c r="C160" t="n">
-        <v>10.85634108891171</v>
+        <v>10.85633917048995</v>
       </c>
       <c r="D160" t="n">
-        <v>10.53519402540776</v>
+        <v>10.53519216373583</v>
       </c>
       <c r="E160" t="n">
-        <v>10.78584599328854</v>
+        <v>10.78584408732395</v>
       </c>
       <c r="F160" t="n">
         <v>3291200</v>
@@ -3672,16 +3672,16 @@
         <v>44882</v>
       </c>
       <c r="B163" t="n">
-        <v>10.74668121337891</v>
+        <v>10.74668025970459</v>
       </c>
       <c r="C163" t="n">
-        <v>10.80151097946262</v>
+        <v>10.80151002092264</v>
       </c>
       <c r="D163" t="n">
-        <v>10.50386229058046</v>
+        <v>10.50386135845421</v>
       </c>
       <c r="E163" t="n">
-        <v>10.69185070029565</v>
+        <v>10.69184975148707</v>
       </c>
       <c r="F163" t="n">
         <v>5834900</v>
@@ -3712,16 +3712,16 @@
         <v>44886</v>
       </c>
       <c r="B165" t="n">
-        <v>11.27931499481201</v>
+        <v>11.27931594848633</v>
       </c>
       <c r="C165" t="n">
-        <v>11.32631247054852</v>
+        <v>11.32631342819651</v>
       </c>
       <c r="D165" t="n">
-        <v>10.80934397244457</v>
+        <v>10.8093448863825</v>
       </c>
       <c r="E165" t="n">
-        <v>10.84067537393573</v>
+        <v>10.84067629052275</v>
       </c>
       <c r="F165" t="n">
         <v>4939800</v>
@@ -3812,16 +3812,16 @@
         <v>44893</v>
       </c>
       <c r="B170" t="n">
-        <v>10.97383403778076</v>
+        <v>10.97383308410645</v>
       </c>
       <c r="C170" t="n">
-        <v>11.09915964398247</v>
+        <v>11.09915867941681</v>
       </c>
       <c r="D170" t="n">
-        <v>10.68401838668942</v>
+        <v>10.68401745820135</v>
       </c>
       <c r="E170" t="n">
-        <v>10.84067539444156</v>
+        <v>10.84067445233931</v>
       </c>
       <c r="F170" t="n">
         <v>4990000</v>
@@ -3832,16 +3832,16 @@
         <v>44894</v>
       </c>
       <c r="B171" t="n">
-        <v>11.16965484619141</v>
+        <v>11.16965579986572</v>
       </c>
       <c r="C171" t="n">
-        <v>11.26364904547358</v>
+        <v>11.2636500071732</v>
       </c>
       <c r="D171" t="n">
-        <v>10.99733177400767</v>
+        <v>10.9973327129689</v>
       </c>
       <c r="E171" t="n">
-        <v>11.01299784738778</v>
+        <v>11.01299878768659</v>
       </c>
       <c r="F171" t="n">
         <v>1705300</v>
@@ -3872,16 +3872,16 @@
         <v>44896</v>
       </c>
       <c r="B173" t="n">
-        <v>10.92683696746826</v>
+        <v>10.92683601379395</v>
       </c>
       <c r="C173" t="n">
-        <v>11.02083117560783</v>
+        <v>11.02083021372987</v>
       </c>
       <c r="D173" t="n">
-        <v>10.69185107361957</v>
+        <v>10.69185014045439</v>
       </c>
       <c r="E173" t="n">
-        <v>10.76234691647413</v>
+        <v>10.76234597715621</v>
       </c>
       <c r="F173" t="n">
         <v>1944500</v>
@@ -3932,16 +3932,16 @@
         <v>44901</v>
       </c>
       <c r="B176" t="n">
-        <v>10.47253036499023</v>
+        <v>10.47253131866455</v>
       </c>
       <c r="C176" t="n">
-        <v>10.58219063867058</v>
+        <v>10.58219160233104</v>
       </c>
       <c r="D176" t="n">
-        <v>10.41770060164981</v>
+        <v>10.41770155033109</v>
       </c>
       <c r="E176" t="n">
-        <v>10.51952783856738</v>
+        <v>10.51952879652149</v>
       </c>
       <c r="F176" t="n">
         <v>1647500</v>
@@ -4132,16 +4132,16 @@
         <v>44915</v>
       </c>
       <c r="B186" t="n">
-        <v>11.27931499481201</v>
+        <v>11.27931594848633</v>
       </c>
       <c r="C186" t="n">
-        <v>11.56129835523201</v>
+        <v>11.56129933274823</v>
       </c>
       <c r="D186" t="n">
-        <v>11.16965546309271</v>
+        <v>11.16965640749523</v>
       </c>
       <c r="E186" t="n">
-        <v>11.35764387203968</v>
+        <v>11.35764483233677</v>
       </c>
       <c r="F186" t="n">
         <v>4148100</v>
@@ -4312,16 +4312,16 @@
         <v>44929</v>
       </c>
       <c r="B195" t="n">
-        <v>11.13832473754883</v>
+        <v>11.13832378387451</v>
       </c>
       <c r="C195" t="n">
-        <v>11.32631315790418</v>
+        <v>11.32631218813412</v>
       </c>
       <c r="D195" t="n">
-        <v>11.05999585556764</v>
+        <v>11.05999490859992</v>
       </c>
       <c r="E195" t="n">
-        <v>11.30281479210966</v>
+        <v>11.30281382435154</v>
       </c>
       <c r="F195" t="n">
         <v>1562800</v>
@@ -4352,16 +4352,16 @@
         <v>44931</v>
       </c>
       <c r="B197" t="n">
-        <v>11.41247367858887</v>
+        <v>11.41247272491455</v>
       </c>
       <c r="C197" t="n">
-        <v>11.41247367858887</v>
+        <v>11.41247272491455</v>
       </c>
       <c r="D197" t="n">
-        <v>11.08349358825896</v>
+        <v>11.08349266207561</v>
       </c>
       <c r="E197" t="n">
-        <v>11.31064643662965</v>
+        <v>11.31064549146445</v>
       </c>
       <c r="F197" t="n">
         <v>4358300</v>
@@ -4372,16 +4372,16 @@
         <v>44932</v>
       </c>
       <c r="B198" t="n">
-        <v>11.42030620574951</v>
+        <v>11.4203052520752</v>
       </c>
       <c r="C198" t="n">
-        <v>11.53779876976359</v>
+        <v>11.53779780627784</v>
       </c>
       <c r="D198" t="n">
-        <v>11.31847896833754</v>
+        <v>11.3184780231665</v>
       </c>
       <c r="E198" t="n">
-        <v>11.4124731689487</v>
+        <v>11.4124722159285</v>
       </c>
       <c r="F198" t="n">
         <v>2864500</v>
@@ -4412,16 +4412,16 @@
         <v>44936</v>
       </c>
       <c r="B200" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C200" t="n">
-        <v>11.1853210907164</v>
+        <v>11.1853201309934</v>
       </c>
       <c r="D200" t="n">
-        <v>10.69185094372897</v>
+        <v>10.6918500263467</v>
       </c>
       <c r="E200" t="n">
-        <v>11.08349384638571</v>
+        <v>11.08349289539969</v>
       </c>
       <c r="F200" t="n">
         <v>5832500</v>
@@ -4512,16 +4512,16 @@
         <v>44943</v>
       </c>
       <c r="B205" t="n">
-        <v>11.74928569793701</v>
+        <v>11.74928665161133</v>
       </c>
       <c r="C205" t="n">
-        <v>11.93727408982413</v>
+        <v>11.93727505875722</v>
       </c>
       <c r="D205" t="n">
-        <v>11.60829403052194</v>
+        <v>11.60829497275214</v>
       </c>
       <c r="E205" t="n">
-        <v>11.81194849523272</v>
+        <v>11.81194945399329</v>
       </c>
       <c r="F205" t="n">
         <v>2676600</v>
@@ -4532,16 +4532,16 @@
         <v>44944</v>
       </c>
       <c r="B206" t="n">
-        <v>11.41247367858887</v>
+        <v>11.41247272491455</v>
       </c>
       <c r="C206" t="n">
-        <v>11.89027848678206</v>
+        <v>11.89027749318036</v>
       </c>
       <c r="D206" t="n">
-        <v>11.41247367858887</v>
+        <v>11.41247272491455</v>
       </c>
       <c r="E206" t="n">
-        <v>11.87461241248085</v>
+        <v>11.87461142018828</v>
       </c>
       <c r="F206" t="n">
         <v>3532000</v>
@@ -4552,16 +4552,16 @@
         <v>44945</v>
       </c>
       <c r="B207" t="n">
-        <v>11.66312599182129</v>
+        <v>11.66312694549561</v>
       </c>
       <c r="C207" t="n">
-        <v>11.68662435698559</v>
+        <v>11.68662531258133</v>
       </c>
       <c r="D207" t="n">
-        <v>11.27931537680668</v>
+        <v>11.27931629909744</v>
       </c>
       <c r="E207" t="n">
-        <v>11.3419781819112</v>
+        <v>11.34197910932579</v>
       </c>
       <c r="F207" t="n">
         <v>1847800</v>
@@ -4592,16 +4592,16 @@
         <v>44949</v>
       </c>
       <c r="B209" t="n">
-        <v>11.52213382720947</v>
+        <v>11.52213478088379</v>
       </c>
       <c r="C209" t="n">
-        <v>11.64745943220163</v>
+        <v>11.64746039624901</v>
       </c>
       <c r="D209" t="n">
-        <v>11.34981074684549</v>
+        <v>11.34981168625682</v>
       </c>
       <c r="E209" t="n">
-        <v>11.59262966676744</v>
+        <v>11.59263062627662</v>
       </c>
       <c r="F209" t="n">
         <v>1770800</v>
@@ -4612,16 +4612,16 @@
         <v>44950</v>
       </c>
       <c r="B210" t="n">
-        <v>11.68662357330322</v>
+        <v>11.68662452697754</v>
       </c>
       <c r="C210" t="n">
-        <v>11.80411613824548</v>
+        <v>11.80411710150764</v>
       </c>
       <c r="D210" t="n">
-        <v>11.32631209461427</v>
+        <v>11.32631301888575</v>
       </c>
       <c r="E210" t="n">
-        <v>11.52996657104705</v>
+        <v>11.52996751193754</v>
       </c>
       <c r="F210" t="n">
         <v>5839900</v>
@@ -4672,16 +4672,16 @@
         <v>44953</v>
       </c>
       <c r="B213" t="n">
-        <v>11.98427295684814</v>
+        <v>11.98427104949951</v>
       </c>
       <c r="C213" t="n">
-        <v>12.23492417521897</v>
+        <v>12.23492222797812</v>
       </c>
       <c r="D213" t="n">
-        <v>11.92161015225544</v>
+        <v>11.92160825487986</v>
       </c>
       <c r="E213" t="n">
-        <v>11.96860688220019</v>
+        <v>11.96860497734488</v>
       </c>
       <c r="F213" t="n">
         <v>4160800</v>
@@ -4692,16 +4692,16 @@
         <v>44956</v>
       </c>
       <c r="B214" t="n">
-        <v>11.84328079223633</v>
+        <v>11.84327983856201</v>
       </c>
       <c r="C214" t="n">
-        <v>11.97643943334014</v>
+        <v>11.97643846894329</v>
       </c>
       <c r="D214" t="n">
-        <v>11.74928658916297</v>
+        <v>11.74928564305749</v>
       </c>
       <c r="E214" t="n">
-        <v>11.86677915625479</v>
+        <v>11.86677820068828</v>
       </c>
       <c r="F214" t="n">
         <v>3859300</v>
@@ -4712,16 +4712,16 @@
         <v>44957</v>
       </c>
       <c r="B215" t="n">
-        <v>12.07043266296387</v>
+        <v>12.0704345703125</v>
       </c>
       <c r="C215" t="n">
-        <v>12.14092849633346</v>
+        <v>12.14093041482172</v>
       </c>
       <c r="D215" t="n">
-        <v>11.8276145113569</v>
+        <v>11.82761638033583</v>
       </c>
       <c r="E215" t="n">
-        <v>11.84327983710599</v>
+        <v>11.84328170856034</v>
       </c>
       <c r="F215" t="n">
         <v>5446800</v>
@@ -4772,16 +4772,16 @@
         <v>44960</v>
       </c>
       <c r="B218" t="n">
-        <v>11.92161083221436</v>
+        <v>11.92160892486572</v>
       </c>
       <c r="C218" t="n">
-        <v>12.17226206488128</v>
+        <v>12.17226011743074</v>
       </c>
       <c r="D218" t="n">
-        <v>11.80411750665204</v>
+        <v>11.80411561810126</v>
       </c>
       <c r="E218" t="n">
-        <v>11.99993896892297</v>
+        <v>11.99993704904255</v>
       </c>
       <c r="F218" t="n">
         <v>3073100</v>
@@ -4812,16 +4812,16 @@
         <v>44964</v>
       </c>
       <c r="B220" t="n">
-        <v>11.60046291351318</v>
+        <v>11.60046195983887</v>
       </c>
       <c r="C220" t="n">
-        <v>12.02343721150694</v>
+        <v>12.02343622305989</v>
       </c>
       <c r="D220" t="n">
-        <v>11.49080263366312</v>
+        <v>11.49080168900398</v>
       </c>
       <c r="E220" t="n">
-        <v>12.02343721150694</v>
+        <v>12.02343622305989</v>
       </c>
       <c r="F220" t="n">
         <v>5199600</v>
@@ -4832,16 +4832,16 @@
         <v>44965</v>
       </c>
       <c r="B221" t="n">
-        <v>11.71012210845947</v>
+        <v>11.71012306213379</v>
       </c>
       <c r="C221" t="n">
-        <v>11.78845098423493</v>
+        <v>11.78845194428836</v>
       </c>
       <c r="D221" t="n">
-        <v>11.54563206693063</v>
+        <v>11.54563300720885</v>
       </c>
       <c r="E221" t="n">
-        <v>11.68662374452664</v>
+        <v>11.68662469628725</v>
       </c>
       <c r="F221" t="n">
         <v>3697100</v>
@@ -4852,16 +4852,16 @@
         <v>44966</v>
       </c>
       <c r="B222" t="n">
-        <v>11.66312599182129</v>
+        <v>11.66312694549561</v>
       </c>
       <c r="C222" t="n">
-        <v>11.78845160203032</v>
+        <v>11.7884525659523</v>
       </c>
       <c r="D222" t="n">
-        <v>11.55346570938861</v>
+        <v>11.55346665409618</v>
       </c>
       <c r="E222" t="n">
-        <v>11.7101227221499</v>
+        <v>11.71012367966706</v>
       </c>
       <c r="F222" t="n">
         <v>2260100</v>
@@ -4872,16 +4872,16 @@
         <v>44967</v>
       </c>
       <c r="B223" t="n">
-        <v>11.72578811645508</v>
+        <v>11.72578907012939</v>
       </c>
       <c r="C223" t="n">
-        <v>11.88244512012525</v>
+        <v>11.88244608654069</v>
       </c>
       <c r="D223" t="n">
-        <v>11.62396087731959</v>
+        <v>11.62396182271216</v>
       </c>
       <c r="E223" t="n">
-        <v>11.62396087731959</v>
+        <v>11.62396182271216</v>
       </c>
       <c r="F223" t="n">
         <v>6075300</v>
@@ -4912,16 +4912,16 @@
         <v>44971</v>
       </c>
       <c r="B225" t="n">
-        <v>11.71795558929443</v>
+        <v>11.71795463562012</v>
       </c>
       <c r="C225" t="n">
-        <v>11.8824456370539</v>
+        <v>11.88244466999244</v>
       </c>
       <c r="D225" t="n">
-        <v>11.51430110216375</v>
+        <v>11.51430016506401</v>
       </c>
       <c r="E225" t="n">
-        <v>11.78061839348856</v>
+        <v>11.78061743471438</v>
       </c>
       <c r="F225" t="n">
         <v>2141000</v>
@@ -4972,16 +4972,16 @@
         <v>44974</v>
       </c>
       <c r="B228" t="n">
-        <v>11.72578811645508</v>
+        <v>11.72578907012939</v>
       </c>
       <c r="C228" t="n">
-        <v>12.13309632599753</v>
+        <v>12.13309731279878</v>
       </c>
       <c r="D228" t="n">
-        <v>11.55346503891813</v>
+        <v>11.55346597857718</v>
       </c>
       <c r="E228" t="n">
-        <v>11.94510792159332</v>
+        <v>11.94510889310522</v>
       </c>
       <c r="F228" t="n">
         <v>9428300</v>
@@ -4992,16 +4992,16 @@
         <v>44979</v>
       </c>
       <c r="B229" t="n">
-        <v>11.71795558929443</v>
+        <v>11.71795463562012</v>
       </c>
       <c r="C229" t="n">
-        <v>11.95294147852217</v>
+        <v>11.95294050572336</v>
       </c>
       <c r="D229" t="n">
-        <v>11.66312582237446</v>
+        <v>11.66312487316251</v>
       </c>
       <c r="E229" t="n">
-        <v>11.89811096460265</v>
+        <v>11.89810999626626</v>
       </c>
       <c r="F229" t="n">
         <v>6185800</v>
@@ -5012,16 +5012,16 @@
         <v>44980</v>
       </c>
       <c r="B230" t="n">
-        <v>11.67879009246826</v>
+        <v>11.67879104614258</v>
       </c>
       <c r="C230" t="n">
-        <v>11.8511131618989</v>
+        <v>11.85111412964489</v>
       </c>
       <c r="D230" t="n">
-        <v>11.61612729394793</v>
+        <v>11.61612824250529</v>
       </c>
       <c r="E230" t="n">
-        <v>11.79628339994349</v>
+        <v>11.79628436321215</v>
       </c>
       <c r="F230" t="n">
         <v>3218000</v>
@@ -5032,16 +5032,16 @@
         <v>44981</v>
       </c>
       <c r="B231" t="n">
-        <v>11.67879009246826</v>
+        <v>11.67879104614258</v>
       </c>
       <c r="C231" t="n">
-        <v>11.89810988728941</v>
+        <v>11.89811085887308</v>
       </c>
       <c r="D231" t="n">
-        <v>11.51430005960253</v>
+        <v>11.51430099984482</v>
       </c>
       <c r="E231" t="n">
-        <v>11.72578756485825</v>
+        <v>11.72578852237032</v>
       </c>
       <c r="F231" t="n">
         <v>4705500</v>
@@ -5052,16 +5052,16 @@
         <v>44984</v>
       </c>
       <c r="B232" t="n">
-        <v>11.64745998382568</v>
+        <v>11.64745903015137</v>
       </c>
       <c r="C232" t="n">
-        <v>11.85894751251565</v>
+        <v>11.85894654152509</v>
       </c>
       <c r="D232" t="n">
-        <v>11.56129881306286</v>
+        <v>11.56129786644328</v>
       </c>
       <c r="E232" t="n">
-        <v>11.7336211545885</v>
+        <v>11.73362019385946</v>
       </c>
       <c r="F232" t="n">
         <v>3412900</v>
@@ -5252,16 +5252,16 @@
         <v>44998</v>
       </c>
       <c r="B242" t="n">
-        <v>11.66312599182129</v>
+        <v>11.66312694549561</v>
       </c>
       <c r="C242" t="n">
-        <v>11.74145412470215</v>
+        <v>11.74145508478123</v>
       </c>
       <c r="D242" t="n">
-        <v>11.45947150173183</v>
+        <v>11.45947243875366</v>
       </c>
       <c r="E242" t="n">
-        <v>11.52213430683635</v>
+        <v>11.52213524898201</v>
       </c>
       <c r="F242" t="n">
         <v>3223500</v>
@@ -5292,16 +5292,16 @@
         <v>45000</v>
       </c>
       <c r="B244" t="n">
-        <v>11.74928569793701</v>
+        <v>11.74928665161133</v>
       </c>
       <c r="C244" t="n">
-        <v>11.89027736535209</v>
+        <v>11.89027833047051</v>
       </c>
       <c r="D244" t="n">
-        <v>11.61612706693377</v>
+        <v>11.61612800979977</v>
       </c>
       <c r="E244" t="n">
-        <v>11.71795429928916</v>
+        <v>11.71795525042035</v>
       </c>
       <c r="F244" t="n">
         <v>4602600</v>
@@ -5352,16 +5352,16 @@
         <v>45005</v>
       </c>
       <c r="B247" t="n">
-        <v>11.31847953796387</v>
+        <v>11.31847858428955</v>
       </c>
       <c r="C247" t="n">
-        <v>11.51430098584213</v>
+        <v>11.51430001566826</v>
       </c>
       <c r="D247" t="n">
-        <v>11.24798369720776</v>
+        <v>11.2479827494733</v>
       </c>
       <c r="E247" t="n">
-        <v>11.45163818228105</v>
+        <v>11.45163721738703</v>
       </c>
       <c r="F247" t="n">
         <v>2892000</v>
@@ -5412,16 +5412,16 @@
         <v>45008</v>
       </c>
       <c r="B250" t="n">
-        <v>11.18532180786133</v>
+        <v>11.18532085418701</v>
       </c>
       <c r="C250" t="n">
-        <v>11.47513748476884</v>
+        <v>11.47513650638449</v>
       </c>
       <c r="D250" t="n">
-        <v>11.05999619049587</v>
+        <v>11.05999524750697</v>
       </c>
       <c r="E250" t="n">
-        <v>11.39680934741524</v>
+        <v>11.39680837570923</v>
       </c>
       <c r="F250" t="n">
         <v>4422500</v>
@@ -5432,16 +5432,16 @@
         <v>45009</v>
       </c>
       <c r="B251" t="n">
-        <v>11.30281352996826</v>
+        <v>11.30281448364258</v>
       </c>
       <c r="C251" t="n">
-        <v>11.39680772964997</v>
+        <v>11.39680869125504</v>
       </c>
       <c r="D251" t="n">
-        <v>11.11482438360535</v>
+        <v>11.11482532141809</v>
       </c>
       <c r="E251" t="n">
-        <v>11.20881933028655</v>
+        <v>11.20882027603011</v>
       </c>
       <c r="F251" t="n">
         <v>3265300</v>
@@ -5452,16 +5452,16 @@
         <v>45012</v>
       </c>
       <c r="B252" t="n">
-        <v>11.28714656829834</v>
+        <v>11.28714752197266</v>
       </c>
       <c r="C252" t="n">
-        <v>11.42030519411861</v>
+        <v>11.42030615904377</v>
       </c>
       <c r="D252" t="n">
-        <v>11.19315237601335</v>
+        <v>11.1931533217459</v>
       </c>
       <c r="E252" t="n">
-        <v>11.39680683279722</v>
+        <v>11.39680779573696</v>
       </c>
       <c r="F252" t="n">
         <v>2288800</v>
@@ -5472,16 +5472,16 @@
         <v>45013</v>
       </c>
       <c r="B253" t="n">
-        <v>11.42030620574951</v>
+        <v>11.4203052520752</v>
       </c>
       <c r="C253" t="n">
-        <v>11.45163760595323</v>
+        <v>11.45163664966253</v>
       </c>
       <c r="D253" t="n">
-        <v>11.25581616793009</v>
+        <v>11.25581522799183</v>
       </c>
       <c r="E253" t="n">
-        <v>11.31064593153673</v>
+        <v>11.3106449870198</v>
       </c>
       <c r="F253" t="n">
         <v>3302900</v>
@@ -5492,16 +5492,16 @@
         <v>45014</v>
       </c>
       <c r="B254" t="n">
-        <v>11.36547565460205</v>
+        <v>11.36547660827637</v>
       </c>
       <c r="C254" t="n">
-        <v>11.47513517421676</v>
+        <v>11.47513613709258</v>
       </c>
       <c r="D254" t="n">
-        <v>11.1931525919225</v>
+        <v>11.19315353113723</v>
       </c>
       <c r="E254" t="n">
-        <v>11.43597148692548</v>
+        <v>11.43597244651508</v>
       </c>
       <c r="F254" t="n">
         <v>2326000</v>
@@ -5632,16 +5632,16 @@
         <v>45026</v>
       </c>
       <c r="B261" t="n">
-        <v>11.71795558929443</v>
+        <v>11.71795463562012</v>
       </c>
       <c r="C261" t="n">
-        <v>11.85111423495683</v>
+        <v>11.85111327044531</v>
       </c>
       <c r="D261" t="n">
-        <v>11.45947133524378</v>
+        <v>11.4594704026064</v>
       </c>
       <c r="E261" t="n">
-        <v>11.53779946698666</v>
+        <v>11.53779852797449</v>
       </c>
       <c r="F261" t="n">
         <v>3430500</v>
@@ -5712,16 +5712,16 @@
         <v>45030</v>
       </c>
       <c r="B265" t="n">
-        <v>11.97643852233887</v>
+        <v>11.97643947601318</v>
       </c>
       <c r="C265" t="n">
-        <v>12.10176411690365</v>
+        <v>12.10176508055754</v>
       </c>
       <c r="D265" t="n">
-        <v>11.83544685495376</v>
+        <v>11.83544779740101</v>
       </c>
       <c r="E265" t="n">
-        <v>12.01560295739023</v>
+        <v>12.01560391418318</v>
       </c>
       <c r="F265" t="n">
         <v>3392800</v>
@@ -5792,16 +5792,16 @@
         <v>45036</v>
       </c>
       <c r="B269" t="n">
-        <v>12.09393119812012</v>
+        <v>12.09393215179443</v>
       </c>
       <c r="C269" t="n">
-        <v>12.14092867003875</v>
+        <v>12.14092962741908</v>
       </c>
       <c r="D269" t="n">
-        <v>12.00777003776868</v>
+        <v>12.00777098464871</v>
       </c>
       <c r="E269" t="n">
-        <v>12.06259979917419</v>
+        <v>12.06260075037785</v>
       </c>
       <c r="F269" t="n">
         <v>4813100</v>
@@ -5812,16 +5812,16 @@
         <v>45040</v>
       </c>
       <c r="B270" t="n">
-        <v>12.10959815979004</v>
+        <v>12.10959911346436</v>
       </c>
       <c r="C270" t="n">
-        <v>12.17226096228058</v>
+        <v>12.17226192088982</v>
       </c>
       <c r="D270" t="n">
-        <v>12.0312692831771</v>
+        <v>12.03127023068273</v>
       </c>
       <c r="E270" t="n">
-        <v>12.10176512272884</v>
+        <v>12.10176607578628</v>
       </c>
       <c r="F270" t="n">
         <v>2389300</v>
@@ -5892,16 +5892,16 @@
         <v>45044</v>
       </c>
       <c r="B274" t="n">
-        <v>12.36024856567383</v>
+        <v>12.36024951934814</v>
       </c>
       <c r="C274" t="n">
-        <v>12.45424276329498</v>
+        <v>12.45424372422157</v>
       </c>
       <c r="D274" t="n">
-        <v>12.01560317439626</v>
+        <v>12.01560410147892</v>
       </c>
       <c r="E274" t="n">
-        <v>12.11743040856905</v>
+        <v>12.11743134350835</v>
       </c>
       <c r="F274" t="n">
         <v>8419400</v>
@@ -5952,16 +5952,16 @@
         <v>45050</v>
       </c>
       <c r="B277" t="n">
-        <v>12.33675193786621</v>
+        <v>12.33675098419189</v>
       </c>
       <c r="C277" t="n">
-        <v>12.43857918635839</v>
+        <v>12.43857822481247</v>
       </c>
       <c r="D277" t="n">
-        <v>12.25842305533389</v>
+        <v>12.25842210771467</v>
       </c>
       <c r="E277" t="n">
-        <v>12.43074614870524</v>
+        <v>12.43074518776484</v>
       </c>
       <c r="F277" t="n">
         <v>8184400</v>
@@ -5972,16 +5972,16 @@
         <v>45051</v>
       </c>
       <c r="B278" t="n">
-        <v>12.50989818572998</v>
+        <v>12.50989723205566</v>
       </c>
       <c r="C278" t="n">
-        <v>12.59647220699179</v>
+        <v>12.59647124671763</v>
       </c>
       <c r="D278" t="n">
-        <v>12.15494618469247</v>
+        <v>12.15494525807742</v>
       </c>
       <c r="E278" t="n">
-        <v>12.34540853608981</v>
+        <v>12.34540759495513</v>
       </c>
       <c r="F278" t="n">
         <v>9400800</v>
@@ -6112,16 +6112,16 @@
         <v>45062</v>
       </c>
       <c r="B285" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="C285" t="n">
-        <v>12.30212031805942</v>
+        <v>12.30212128603885</v>
       </c>
       <c r="D285" t="n">
-        <v>12.08568611177803</v>
+        <v>12.08568706272756</v>
       </c>
       <c r="E285" t="n">
-        <v>12.18091686531469</v>
+        <v>12.18091782375736</v>
       </c>
       <c r="F285" t="n">
         <v>2907500</v>
@@ -6132,16 +6132,16 @@
         <v>45063</v>
       </c>
       <c r="B286" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="C286" t="n">
-        <v>12.24151939290137</v>
+        <v>12.24152036724783</v>
       </c>
       <c r="D286" t="n">
-        <v>11.94716873091856</v>
+        <v>11.9471696818366</v>
       </c>
       <c r="E286" t="n">
-        <v>12.12897350298847</v>
+        <v>12.128974468377</v>
       </c>
       <c r="F286" t="n">
         <v>4330800</v>
@@ -6152,16 +6152,16 @@
         <v>45064</v>
       </c>
       <c r="B287" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="C287" t="n">
-        <v>12.05971462083146</v>
+        <v>12.05971558070743</v>
       </c>
       <c r="D287" t="n">
-        <v>11.82596527432829</v>
+        <v>11.82596621559931</v>
       </c>
       <c r="E287" t="n">
-        <v>12.01642761307558</v>
+        <v>12.01642856950617</v>
       </c>
       <c r="F287" t="n">
         <v>4680600</v>
@@ -6172,16 +6172,16 @@
         <v>45065</v>
       </c>
       <c r="B288" t="n">
-        <v>12.09434413909912</v>
+        <v>12.09434509277344</v>
       </c>
       <c r="C288" t="n">
-        <v>12.18091732953242</v>
+        <v>12.18091829003328</v>
       </c>
       <c r="D288" t="n">
-        <v>11.93851124043578</v>
+        <v>11.93851218182222</v>
       </c>
       <c r="E288" t="n">
-        <v>11.99911255630219</v>
+        <v>11.99911350246722</v>
       </c>
       <c r="F288" t="n">
         <v>2962700</v>
@@ -6252,16 +6252,16 @@
         <v>45071</v>
       </c>
       <c r="B292" t="n">
-        <v>12.29346370697021</v>
+        <v>12.29346466064453</v>
       </c>
       <c r="C292" t="n">
-        <v>12.39735203498263</v>
+        <v>12.39735299671616</v>
       </c>
       <c r="D292" t="n">
-        <v>12.20689051310872</v>
+        <v>12.20689146006706</v>
       </c>
       <c r="E292" t="n">
-        <v>12.28480613989475</v>
+        <v>12.28480709289745</v>
       </c>
       <c r="F292" t="n">
         <v>2204600</v>
@@ -6292,16 +6292,16 @@
         <v>45075</v>
       </c>
       <c r="B294" t="n">
-        <v>12.28480625152588</v>
+        <v>12.28480529785156</v>
       </c>
       <c r="C294" t="n">
-        <v>12.34540839597375</v>
+        <v>12.34540743759487</v>
       </c>
       <c r="D294" t="n">
-        <v>12.16360361389222</v>
+        <v>12.16360266962691</v>
       </c>
       <c r="E294" t="n">
-        <v>12.16360361389222</v>
+        <v>12.16360266962691</v>
       </c>
       <c r="F294" t="n">
         <v>1431900</v>
@@ -6312,16 +6312,16 @@
         <v>45076</v>
       </c>
       <c r="B295" t="n">
-        <v>12.26749134063721</v>
+        <v>12.26749229431152</v>
       </c>
       <c r="C295" t="n">
-        <v>12.3800372312229</v>
+        <v>12.38003819364653</v>
       </c>
       <c r="D295" t="n">
-        <v>12.25017620717894</v>
+        <v>12.25017715950718</v>
       </c>
       <c r="E295" t="n">
-        <v>12.37137966449377</v>
+        <v>12.37138062624436</v>
       </c>
       <c r="F295" t="n">
         <v>1829100</v>
@@ -6332,16 +6332,16 @@
         <v>45077</v>
       </c>
       <c r="B296" t="n">
-        <v>12.1895751953125</v>
+        <v>12.18957614898682</v>
       </c>
       <c r="C296" t="n">
-        <v>12.31077865564981</v>
+        <v>12.31077961880671</v>
       </c>
       <c r="D296" t="n">
-        <v>12.16360332010844</v>
+        <v>12.1636042717508</v>
       </c>
       <c r="E296" t="n">
-        <v>12.27614921350073</v>
+        <v>12.27615017394832</v>
       </c>
       <c r="F296" t="n">
         <v>3816500</v>
@@ -6372,16 +6372,16 @@
         <v>45079</v>
       </c>
       <c r="B298" t="n">
-        <v>12.17226028442383</v>
+        <v>12.17226123809814</v>
       </c>
       <c r="C298" t="n">
-        <v>12.3367499200806</v>
+        <v>12.33675088664238</v>
       </c>
       <c r="D298" t="n">
-        <v>12.07702870400534</v>
+        <v>12.07702965021844</v>
       </c>
       <c r="E298" t="n">
-        <v>12.31077804616237</v>
+        <v>12.3107790106893</v>
       </c>
       <c r="F298" t="n">
         <v>5725100</v>
@@ -6392,16 +6392,16 @@
         <v>45082</v>
       </c>
       <c r="B299" t="n">
-        <v>12.0683708190918</v>
+        <v>12.06837177276611</v>
       </c>
       <c r="C299" t="n">
-        <v>12.19823183651883</v>
+        <v>12.1982328004551</v>
       </c>
       <c r="D299" t="n">
-        <v>11.97314006681674</v>
+        <v>11.97314101296568</v>
       </c>
       <c r="E299" t="n">
-        <v>12.17225996328581</v>
+        <v>12.17226092516972</v>
       </c>
       <c r="F299" t="n">
         <v>3442900</v>
@@ -6432,16 +6432,16 @@
         <v>45084</v>
       </c>
       <c r="B301" t="n">
-        <v>12.22420501708984</v>
+        <v>12.22420597076416</v>
       </c>
       <c r="C301" t="n">
-        <v>12.46661111966148</v>
+        <v>12.46661209224716</v>
       </c>
       <c r="D301" t="n">
-        <v>12.21554744987595</v>
+        <v>12.21554840287484</v>
       </c>
       <c r="E301" t="n">
-        <v>12.3800379244157</v>
+        <v>12.38003889024736</v>
       </c>
       <c r="F301" t="n">
         <v>3154600</v>
@@ -6472,16 +6472,16 @@
         <v>45089</v>
       </c>
       <c r="B303" t="n">
-        <v>12.45795440673828</v>
+        <v>12.45795345306396</v>
       </c>
       <c r="C303" t="n">
-        <v>12.45795440673828</v>
+        <v>12.45795345306396</v>
       </c>
       <c r="D303" t="n">
-        <v>12.25883448851593</v>
+        <v>12.25883355008453</v>
       </c>
       <c r="E303" t="n">
-        <v>12.3800379528961</v>
+        <v>12.3800370051864</v>
       </c>
       <c r="F303" t="n">
         <v>2572800</v>
@@ -6492,16 +6492,16 @@
         <v>45090</v>
       </c>
       <c r="B304" t="n">
-        <v>12.3107795715332</v>
+        <v>12.31077861785889</v>
       </c>
       <c r="C304" t="n">
-        <v>12.5012411047074</v>
+        <v>12.50124013627868</v>
       </c>
       <c r="D304" t="n">
-        <v>12.29346443635495</v>
+        <v>12.29346348402198</v>
       </c>
       <c r="E304" t="n">
-        <v>12.46661165998199</v>
+        <v>12.46661069423589</v>
       </c>
       <c r="F304" t="n">
         <v>1312000</v>
@@ -6532,16 +6532,16 @@
         <v>45092</v>
       </c>
       <c r="B306" t="n">
-        <v>12.4666109085083</v>
+        <v>12.46661186218262</v>
       </c>
       <c r="C306" t="n">
-        <v>12.49258360971007</v>
+        <v>12.49258456537125</v>
       </c>
       <c r="D306" t="n">
-        <v>12.36272258059435</v>
+        <v>12.36272352632139</v>
       </c>
       <c r="E306" t="n">
-        <v>12.45795416707208</v>
+        <v>12.45795512008417</v>
       </c>
       <c r="F306" t="n">
         <v>1266000</v>
@@ -6552,16 +6552,16 @@
         <v>45093</v>
       </c>
       <c r="B307" t="n">
-        <v>12.62244415283203</v>
+        <v>12.62244319915771</v>
       </c>
       <c r="C307" t="n">
-        <v>12.83022081425066</v>
+        <v>12.83021984487801</v>
       </c>
       <c r="D307" t="n">
-        <v>12.44063936768297</v>
+        <v>12.4406384277447</v>
       </c>
       <c r="E307" t="n">
-        <v>12.46661124395253</v>
+        <v>12.46661030205199</v>
       </c>
       <c r="F307" t="n">
         <v>5319000</v>
@@ -6572,16 +6572,16 @@
         <v>45096</v>
       </c>
       <c r="B308" t="n">
-        <v>12.6137866973877</v>
+        <v>12.61378574371338</v>
       </c>
       <c r="C308" t="n">
-        <v>12.80424905152594</v>
+        <v>12.80424808345158</v>
       </c>
       <c r="D308" t="n">
-        <v>12.38869572500366</v>
+        <v>12.38869478834751</v>
       </c>
       <c r="E308" t="n">
-        <v>12.80424905152594</v>
+        <v>12.80424808345158</v>
       </c>
       <c r="F308" t="n">
         <v>3301400</v>
@@ -6612,16 +6612,16 @@
         <v>45098</v>
       </c>
       <c r="B310" t="n">
-        <v>12.86485004425049</v>
+        <v>12.86484909057617</v>
       </c>
       <c r="C310" t="n">
-        <v>12.90813705440186</v>
+        <v>12.90813609751867</v>
       </c>
       <c r="D310" t="n">
-        <v>12.63975907759925</v>
+        <v>12.63975814061098</v>
       </c>
       <c r="E310" t="n">
-        <v>12.75230414810935</v>
+        <v>12.75230320277808</v>
       </c>
       <c r="F310" t="n">
         <v>5022600</v>
@@ -6692,16 +6692,16 @@
         <v>45104</v>
       </c>
       <c r="B314" t="n">
-        <v>12.50123977661133</v>
+        <v>12.50124073028564</v>
       </c>
       <c r="C314" t="n">
-        <v>12.83887744603771</v>
+        <v>12.83887842546918</v>
       </c>
       <c r="D314" t="n">
-        <v>12.3973514534719</v>
+        <v>12.39735239922096</v>
       </c>
       <c r="E314" t="n">
-        <v>12.76961856394476</v>
+        <v>12.76961953809272</v>
       </c>
       <c r="F314" t="n">
         <v>3014700</v>
@@ -6872,16 +6872,16 @@
         <v>45117</v>
       </c>
       <c r="B323" t="n">
-        <v>12.38869571685791</v>
+        <v>12.38869476318359</v>
       </c>
       <c r="C323" t="n">
-        <v>12.45795460456609</v>
+        <v>12.45795364556026</v>
       </c>
       <c r="D323" t="n">
-        <v>12.31077926177845</v>
+        <v>12.31077831410209</v>
       </c>
       <c r="E323" t="n">
-        <v>12.38003814948662</v>
+        <v>12.38003719647876</v>
       </c>
       <c r="F323" t="n">
         <v>1514600</v>
@@ -6912,16 +6912,16 @@
         <v>45119</v>
       </c>
       <c r="B325" t="n">
-        <v>12.38869571685791</v>
+        <v>12.38869476318359</v>
       </c>
       <c r="C325" t="n">
-        <v>12.45795460456609</v>
+        <v>12.45795364556026</v>
       </c>
       <c r="D325" t="n">
-        <v>12.28480655966458</v>
+        <v>12.28480561398759</v>
       </c>
       <c r="E325" t="n">
-        <v>12.37138058211533</v>
+        <v>12.37137962977392</v>
       </c>
       <c r="F325" t="n">
         <v>1842800</v>
@@ -7052,16 +7052,16 @@
         <v>45128</v>
       </c>
       <c r="B332" t="n">
-        <v>12.38869571685791</v>
+        <v>12.38869476318359</v>
       </c>
       <c r="C332" t="n">
-        <v>12.38869571685791</v>
+        <v>12.38869476318359</v>
       </c>
       <c r="D332" t="n">
-        <v>12.2242052393277</v>
+        <v>12.22420429831576</v>
       </c>
       <c r="E332" t="n">
-        <v>12.27614981792436</v>
+        <v>12.27614887291376</v>
       </c>
       <c r="F332" t="n">
         <v>2631400</v>
@@ -7092,16 +7092,16 @@
         <v>45132</v>
       </c>
       <c r="B334" t="n">
-        <v>12.17226028442383</v>
+        <v>12.17226123809814</v>
       </c>
       <c r="C334" t="n">
-        <v>12.47526768181915</v>
+        <v>12.47526865923354</v>
       </c>
       <c r="D334" t="n">
-        <v>12.16360271790742</v>
+        <v>12.16360367090343</v>
       </c>
       <c r="E334" t="n">
-        <v>12.41466636746628</v>
+        <v>12.41466734013267</v>
       </c>
       <c r="F334" t="n">
         <v>2710400</v>
@@ -7152,16 +7152,16 @@
         <v>45135</v>
       </c>
       <c r="B337" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="C337" t="n">
-        <v>12.22420387169716</v>
+        <v>12.22420483354582</v>
       </c>
       <c r="D337" t="n">
-        <v>12.05971423820094</v>
+        <v>12.0597151871069</v>
       </c>
       <c r="E337" t="n">
-        <v>12.14628742533491</v>
+        <v>12.14628838105279</v>
       </c>
       <c r="F337" t="n">
         <v>1506100</v>
@@ -7172,16 +7172,16 @@
         <v>45138</v>
       </c>
       <c r="B338" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="C338" t="n">
-        <v>12.20688956452276</v>
+        <v>12.20689052500906</v>
       </c>
       <c r="D338" t="n">
-        <v>12.10300041895243</v>
+        <v>12.10300137126433</v>
       </c>
       <c r="E338" t="n">
-        <v>12.20688956452276</v>
+        <v>12.20689052500906</v>
       </c>
       <c r="F338" t="n">
         <v>1549400</v>
@@ -7192,16 +7192,16 @@
         <v>45139</v>
       </c>
       <c r="B339" t="n">
-        <v>12.12897491455078</v>
+        <v>12.12897396087646</v>
       </c>
       <c r="C339" t="n">
-        <v>12.38003859799633</v>
+        <v>12.38003762458143</v>
       </c>
       <c r="D339" t="n">
-        <v>12.08568790175718</v>
+        <v>12.08568695148643</v>
       </c>
       <c r="E339" t="n">
-        <v>12.12031734686584</v>
+        <v>12.12031639387225</v>
       </c>
       <c r="F339" t="n">
         <v>5884200</v>
@@ -7212,16 +7212,16 @@
         <v>45140</v>
       </c>
       <c r="B340" t="n">
-        <v>12.22420501708984</v>
+        <v>12.22420597076416</v>
       </c>
       <c r="C340" t="n">
-        <v>12.23286258430374</v>
+        <v>12.23286353865348</v>
       </c>
       <c r="D340" t="n">
-        <v>12.12897425463018</v>
+        <v>12.12897520087505</v>
       </c>
       <c r="E340" t="n">
-        <v>12.13763182184407</v>
+        <v>12.13763276876436</v>
       </c>
       <c r="F340" t="n">
         <v>1697600</v>
@@ -7412,16 +7412,16 @@
         <v>45154</v>
       </c>
       <c r="B350" t="n">
-        <v>11.6874475479126</v>
+        <v>11.68744850158691</v>
       </c>
       <c r="C350" t="n">
-        <v>11.91253932846828</v>
+        <v>11.91254030050967</v>
       </c>
       <c r="D350" t="n">
-        <v>11.64416054001635</v>
+        <v>11.64416149015853</v>
       </c>
       <c r="E350" t="n">
-        <v>11.88656662835193</v>
+        <v>11.886567598274</v>
       </c>
       <c r="F350" t="n">
         <v>3946200</v>
@@ -7432,16 +7432,16 @@
         <v>45155</v>
       </c>
       <c r="B351" t="n">
-        <v>11.71341896057129</v>
+        <v>11.71342086791992</v>
       </c>
       <c r="C351" t="n">
-        <v>11.7826778402222</v>
+        <v>11.78267975884857</v>
       </c>
       <c r="D351" t="n">
-        <v>11.66147521364859</v>
+        <v>11.66147711253899</v>
       </c>
       <c r="E351" t="n">
-        <v>11.7307340932995</v>
+        <v>11.73073600346764</v>
       </c>
       <c r="F351" t="n">
         <v>2345000</v>
@@ -7452,16 +7452,16 @@
         <v>45156</v>
       </c>
       <c r="B352" t="n">
-        <v>11.77402210235596</v>
+        <v>11.77402114868164</v>
       </c>
       <c r="C352" t="n">
-        <v>11.80865154513102</v>
+        <v>11.80865058865178</v>
       </c>
       <c r="D352" t="n">
-        <v>11.65281863982772</v>
+        <v>11.65281769597066</v>
       </c>
       <c r="E352" t="n">
-        <v>11.71341995827632</v>
+        <v>11.71341900951066</v>
       </c>
       <c r="F352" t="n">
         <v>3061800</v>
@@ -7512,16 +7512,16 @@
         <v>45161</v>
       </c>
       <c r="B355" t="n">
-        <v>11.87791061401367</v>
+        <v>11.87790966033936</v>
       </c>
       <c r="C355" t="n">
-        <v>11.89522492285292</v>
+        <v>11.89522396778845</v>
       </c>
       <c r="D355" t="n">
-        <v>11.79133659292425</v>
+        <v>11.79133564620093</v>
       </c>
       <c r="E355" t="n">
-        <v>11.86059547954337</v>
+        <v>11.86059452725928</v>
       </c>
       <c r="F355" t="n">
         <v>2615000</v>
@@ -7532,16 +7532,16 @@
         <v>45162</v>
       </c>
       <c r="B356" t="n">
-        <v>11.97314167022705</v>
+        <v>11.97314071655273</v>
       </c>
       <c r="C356" t="n">
-        <v>11.99911354693815</v>
+        <v>11.99911259119515</v>
       </c>
       <c r="D356" t="n">
-        <v>11.89522521446267</v>
+        <v>11.89522426699448</v>
       </c>
       <c r="E356" t="n">
-        <v>11.90388278191006</v>
+        <v>11.90388183375229</v>
       </c>
       <c r="F356" t="n">
         <v>2322800</v>
@@ -7592,16 +7592,16 @@
         <v>45167</v>
       </c>
       <c r="B359" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="C359" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="D359" t="n">
-        <v>11.97314022543599</v>
+        <v>11.97314116752997</v>
       </c>
       <c r="E359" t="n">
-        <v>11.98179779183868</v>
+        <v>11.98179873461387</v>
       </c>
       <c r="F359" t="n">
         <v>1776800</v>
@@ -7652,16 +7652,16 @@
         <v>45170</v>
       </c>
       <c r="B362" t="n">
-        <v>12.04240036010742</v>
+        <v>12.04239940643311</v>
       </c>
       <c r="C362" t="n">
-        <v>12.04240036010742</v>
+        <v>12.04239940643311</v>
       </c>
       <c r="D362" t="n">
-        <v>11.89522501845123</v>
+        <v>11.89522407643217</v>
       </c>
       <c r="E362" t="n">
-        <v>11.90388258575596</v>
+        <v>11.90388164305129</v>
       </c>
       <c r="F362" t="n">
         <v>3740800</v>
@@ -7732,16 +7732,16 @@
         <v>45177</v>
       </c>
       <c r="B366" t="n">
-        <v>11.92985439300537</v>
+        <v>11.92985343933105</v>
       </c>
       <c r="C366" t="n">
-        <v>12.07702973380992</v>
+        <v>12.07702876837038</v>
       </c>
       <c r="D366" t="n">
-        <v>11.88656738236326</v>
+        <v>11.88656643214931</v>
       </c>
       <c r="E366" t="n">
-        <v>11.93851196026</v>
+        <v>11.9385110058936</v>
       </c>
       <c r="F366" t="n">
         <v>3462800</v>
@@ -7772,16 +7772,16 @@
         <v>45181</v>
       </c>
       <c r="B368" t="n">
-        <v>12.0683708190918</v>
+        <v>12.06837177276611</v>
       </c>
       <c r="C368" t="n">
-        <v>12.15494483070982</v>
+        <v>12.15494579122544</v>
       </c>
       <c r="D368" t="n">
-        <v>11.98179763310474</v>
+        <v>11.98179857993782</v>
       </c>
       <c r="E368" t="n">
-        <v>12.03374137957078</v>
+        <v>12.03374233050859</v>
       </c>
       <c r="F368" t="n">
         <v>2215400</v>
@@ -7792,16 +7792,16 @@
         <v>45182</v>
       </c>
       <c r="B369" t="n">
-        <v>12.0683708190918</v>
+        <v>12.06837177276611</v>
       </c>
       <c r="C369" t="n">
-        <v>12.19823183651883</v>
+        <v>12.1982328004551</v>
       </c>
       <c r="D369" t="n">
-        <v>12.03374137957078</v>
+        <v>12.03374233050859</v>
       </c>
       <c r="E369" t="n">
-        <v>12.07702838537979</v>
+        <v>12.07702933973825</v>
       </c>
       <c r="F369" t="n">
         <v>1684100</v>
@@ -7812,16 +7812,16 @@
         <v>45183</v>
       </c>
       <c r="B370" t="n">
-        <v>12.21554756164551</v>
+        <v>12.21554660797119</v>
       </c>
       <c r="C370" t="n">
-        <v>12.25017700518688</v>
+        <v>12.25017604880902</v>
       </c>
       <c r="D370" t="n">
-        <v>12.09434492206624</v>
+        <v>12.09434397785428</v>
       </c>
       <c r="E370" t="n">
-        <v>12.09434492206624</v>
+        <v>12.09434397785428</v>
       </c>
       <c r="F370" t="n">
         <v>2498700</v>
@@ -7892,16 +7892,16 @@
         <v>45189</v>
       </c>
       <c r="B374" t="n">
-        <v>12.0683708190918</v>
+        <v>12.06837177276611</v>
       </c>
       <c r="C374" t="n">
-        <v>12.14628726442182</v>
+        <v>12.1462882242533</v>
       </c>
       <c r="D374" t="n">
-        <v>11.97314006681674</v>
+        <v>11.97314101296568</v>
       </c>
       <c r="E374" t="n">
-        <v>12.08568595166779</v>
+        <v>12.08568690671039</v>
       </c>
       <c r="F374" t="n">
         <v>2998000</v>
@@ -8092,16 +8092,16 @@
         <v>45203</v>
       </c>
       <c r="B384" t="n">
-        <v>11.77402210235596</v>
+        <v>11.77402114868164</v>
       </c>
       <c r="C384" t="n">
-        <v>11.86059529647809</v>
+        <v>11.86059433579151</v>
       </c>
       <c r="D384" t="n">
-        <v>11.74804940105138</v>
+        <v>11.7480484494808</v>
       </c>
       <c r="E384" t="n">
-        <v>11.80865154513102</v>
+        <v>11.80865058865178</v>
       </c>
       <c r="F384" t="n">
         <v>4367600</v>
@@ -8132,16 +8132,16 @@
         <v>45205</v>
       </c>
       <c r="B386" t="n">
-        <v>11.67879009246826</v>
+        <v>11.67879104614258</v>
       </c>
       <c r="C386" t="n">
-        <v>11.70476279283205</v>
+        <v>11.70476374862726</v>
       </c>
       <c r="D386" t="n">
-        <v>11.61818877621478</v>
+        <v>11.61818972494048</v>
       </c>
       <c r="E386" t="n">
-        <v>11.68744765925619</v>
+        <v>11.68744861363747</v>
       </c>
       <c r="F386" t="n">
         <v>3573900</v>
@@ -8192,16 +8192,16 @@
         <v>45210</v>
       </c>
       <c r="B389" t="n">
-        <v>12.09434413909912</v>
+        <v>12.09434509277344</v>
       </c>
       <c r="C389" t="n">
-        <v>12.18957489626505</v>
+        <v>12.18957585744859</v>
       </c>
       <c r="D389" t="n">
-        <v>12.00777012303482</v>
+        <v>12.00777106988252</v>
       </c>
       <c r="E389" t="n">
-        <v>12.09434413909912</v>
+        <v>12.09434509277344</v>
       </c>
       <c r="F389" t="n">
         <v>3458500</v>
@@ -8232,16 +8232,16 @@
         <v>45215</v>
       </c>
       <c r="B391" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="C391" t="n">
-        <v>12.12031593631109</v>
+        <v>12.12031690101054</v>
       </c>
       <c r="D391" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="E391" t="n">
-        <v>12.05971462083146</v>
+        <v>12.05971558070743</v>
       </c>
       <c r="F391" t="n">
         <v>3983600</v>
@@ -8272,16 +8272,16 @@
         <v>45217</v>
       </c>
       <c r="B393" t="n">
-        <v>11.66147518157959</v>
+        <v>11.66147613525391</v>
       </c>
       <c r="C393" t="n">
-        <v>11.955825832102</v>
+        <v>11.95582680984828</v>
       </c>
       <c r="D393" t="n">
-        <v>11.66147518157959</v>
+        <v>11.66147613525391</v>
       </c>
       <c r="E393" t="n">
-        <v>11.955825832102</v>
+        <v>11.95582680984828</v>
       </c>
       <c r="F393" t="n">
         <v>13737300</v>
@@ -8292,16 +8292,16 @@
         <v>45218</v>
       </c>
       <c r="B394" t="n">
-        <v>11.67013359069824</v>
+        <v>11.67013263702393</v>
       </c>
       <c r="C394" t="n">
-        <v>11.75670761521626</v>
+        <v>11.75670665446719</v>
       </c>
       <c r="D394" t="n">
-        <v>11.62684740407032</v>
+        <v>11.62684645393332</v>
       </c>
       <c r="E394" t="n">
-        <v>11.66147684875131</v>
+        <v>11.66147589578441</v>
       </c>
       <c r="F394" t="n">
         <v>3066300</v>
@@ -8312,16 +8312,16 @@
         <v>45219</v>
       </c>
       <c r="B395" t="n">
-        <v>11.7653636932373</v>
+        <v>11.76536464691162</v>
       </c>
       <c r="C395" t="n">
-        <v>11.91253902090612</v>
+        <v>11.91253998651014</v>
       </c>
       <c r="D395" t="n">
-        <v>11.67013211319808</v>
+        <v>11.67013305915314</v>
       </c>
       <c r="E395" t="n">
-        <v>11.67013211319808</v>
+        <v>11.67013305915314</v>
       </c>
       <c r="F395" t="n">
         <v>6261200</v>
@@ -8332,16 +8332,16 @@
         <v>45222</v>
       </c>
       <c r="B396" t="n">
-        <v>11.72207832336426</v>
+        <v>11.72207736968994</v>
       </c>
       <c r="C396" t="n">
-        <v>11.90388311671755</v>
+        <v>11.90388214825212</v>
       </c>
       <c r="D396" t="n">
-        <v>11.72207832336426</v>
+        <v>11.72207736968994</v>
       </c>
       <c r="E396" t="n">
-        <v>11.77402290387853</v>
+        <v>11.77402194597815</v>
       </c>
       <c r="F396" t="n">
         <v>3068100</v>
@@ -8352,16 +8352,16 @@
         <v>45223</v>
       </c>
       <c r="B397" t="n">
-        <v>11.6355037689209</v>
+        <v>11.63550281524658</v>
       </c>
       <c r="C397" t="n">
-        <v>11.81730855401174</v>
+        <v>11.81730758543626</v>
       </c>
       <c r="D397" t="n">
-        <v>11.54893057283972</v>
+        <v>11.54892962626116</v>
       </c>
       <c r="E397" t="n">
-        <v>11.80865181234537</v>
+        <v>11.80865084447942</v>
       </c>
       <c r="F397" t="n">
         <v>3637500</v>
@@ -8392,16 +8392,16 @@
         <v>45225</v>
       </c>
       <c r="B399" t="n">
-        <v>11.67879009246826</v>
+        <v>11.67879104614258</v>
       </c>
       <c r="C399" t="n">
-        <v>11.73073466756482</v>
+        <v>11.73073562548086</v>
       </c>
       <c r="D399" t="n">
-        <v>11.54892989317337</v>
+        <v>11.54893083624348</v>
       </c>
       <c r="E399" t="n">
-        <v>11.54892989317337</v>
+        <v>11.54893083624348</v>
       </c>
       <c r="F399" t="n">
         <v>2627000</v>
@@ -8432,16 +8432,16 @@
         <v>45229</v>
       </c>
       <c r="B401" t="n">
-        <v>11.49698638916016</v>
+        <v>11.49698543548584</v>
       </c>
       <c r="C401" t="n">
-        <v>11.64416173574207</v>
+        <v>11.64416076985956</v>
       </c>
       <c r="D401" t="n">
-        <v>11.47101451200779</v>
+        <v>11.47101356048784</v>
       </c>
       <c r="E401" t="n">
-        <v>11.57490284624835</v>
+        <v>11.57490188611087</v>
       </c>
       <c r="F401" t="n">
         <v>4549600</v>
@@ -8452,16 +8452,16 @@
         <v>45230</v>
       </c>
       <c r="B402" t="n">
-        <v>11.61818981170654</v>
+        <v>11.61818885803223</v>
       </c>
       <c r="C402" t="n">
-        <v>11.66147682387321</v>
+        <v>11.6614758666457</v>
       </c>
       <c r="D402" t="n">
-        <v>11.52295904544475</v>
+        <v>11.52295809958741</v>
       </c>
       <c r="E402" t="n">
-        <v>11.52295904544475</v>
+        <v>11.52295809958741</v>
       </c>
       <c r="F402" t="n">
         <v>3290000</v>
@@ -8472,16 +8472,16 @@
         <v>45231</v>
       </c>
       <c r="B403" t="n">
-        <v>11.66147518157959</v>
+        <v>11.66147613525391</v>
       </c>
       <c r="C403" t="n">
-        <v>11.74804836808967</v>
+        <v>11.74804932884394</v>
       </c>
       <c r="D403" t="n">
-        <v>11.28055051891613</v>
+        <v>11.28055144143846</v>
       </c>
       <c r="E403" t="n">
-        <v>11.55758686238891</v>
+        <v>11.55758780756725</v>
       </c>
       <c r="F403" t="n">
         <v>7182500</v>
@@ -8632,16 +8632,16 @@
         <v>45244</v>
       </c>
       <c r="B411" t="n">
-        <v>12.1895751953125</v>
+        <v>12.18957614898682</v>
       </c>
       <c r="C411" t="n">
-        <v>12.25017651266564</v>
+        <v>12.25017747108122</v>
       </c>
       <c r="D411" t="n">
-        <v>11.86059508208067</v>
+        <v>11.86059601001661</v>
       </c>
       <c r="E411" t="n">
-        <v>11.86059508208067</v>
+        <v>11.86059601001661</v>
       </c>
       <c r="F411" t="n">
         <v>3963500</v>
@@ -8712,16 +8712,16 @@
         <v>45251</v>
       </c>
       <c r="B415" t="n">
-        <v>11.97314167022705</v>
+        <v>11.97314071655273</v>
       </c>
       <c r="C415" t="n">
-        <v>12.09434513759732</v>
+        <v>12.09434417426901</v>
       </c>
       <c r="D415" t="n">
-        <v>11.91254034935745</v>
+        <v>11.9125394005101</v>
       </c>
       <c r="E415" t="n">
-        <v>12.08568757014993</v>
+        <v>12.0856866075112</v>
       </c>
       <c r="F415" t="n">
         <v>2713400</v>
@@ -8732,16 +8732,16 @@
         <v>45252</v>
       </c>
       <c r="B416" t="n">
-        <v>12.4666109085083</v>
+        <v>12.46661186218262</v>
       </c>
       <c r="C416" t="n">
-        <v>12.94276636400384</v>
+        <v>12.94276735410323</v>
       </c>
       <c r="D416" t="n">
-        <v>12.44063903293757</v>
+        <v>12.44063998462508</v>
       </c>
       <c r="E416" t="n">
-        <v>12.81290616051917</v>
+        <v>12.81290714068447</v>
       </c>
       <c r="F416" t="n">
         <v>20875500</v>
@@ -8872,16 +8872,16 @@
         <v>45261</v>
       </c>
       <c r="B423" t="n">
-        <v>12.86485004425049</v>
+        <v>12.86484909057617</v>
       </c>
       <c r="C423" t="n">
-        <v>12.96873837323515</v>
+        <v>12.96873741185957</v>
       </c>
       <c r="D423" t="n">
-        <v>12.70901796358902</v>
+        <v>12.70901702146657</v>
       </c>
       <c r="E423" t="n">
-        <v>12.72633227227094</v>
+        <v>12.72633132886498</v>
       </c>
       <c r="F423" t="n">
         <v>6458300</v>
@@ -8932,16 +8932,16 @@
         <v>45266</v>
       </c>
       <c r="B426" t="n">
-        <v>13.07262802124023</v>
+        <v>13.07262706756592</v>
       </c>
       <c r="C426" t="n">
-        <v>13.27174711956826</v>
+        <v>13.2717461513678</v>
       </c>
       <c r="D426" t="n">
-        <v>13.04665531879052</v>
+        <v>13.04665436701096</v>
       </c>
       <c r="E426" t="n">
-        <v>13.21114579844774</v>
+        <v>13.21114483466828</v>
       </c>
       <c r="F426" t="n">
         <v>5861300</v>
@@ -8952,16 +8952,16 @@
         <v>45267</v>
       </c>
       <c r="B427" t="n">
-        <v>13.11591339111328</v>
+        <v>13.1159143447876</v>
       </c>
       <c r="C427" t="n">
-        <v>13.15054283325996</v>
+        <v>13.15054378945223</v>
       </c>
       <c r="D427" t="n">
-        <v>12.97739562252655</v>
+        <v>12.97739656612907</v>
       </c>
       <c r="E427" t="n">
-        <v>13.10725664979988</v>
+        <v>13.10725760284475</v>
       </c>
       <c r="F427" t="n">
         <v>6196000</v>
@@ -9052,16 +9052,16 @@
         <v>45274</v>
       </c>
       <c r="B432" t="n">
-        <v>12.94470119476318</v>
+        <v>12.94470024108887</v>
       </c>
       <c r="C432" t="n">
-        <v>12.9831984112191</v>
+        <v>12.98319745470858</v>
       </c>
       <c r="D432" t="n">
-        <v>12.71371789602766</v>
+        <v>12.71371695937057</v>
       </c>
       <c r="E432" t="n">
-        <v>12.71371789602766</v>
+        <v>12.71371695937057</v>
       </c>
       <c r="F432" t="n">
         <v>5480800</v>
@@ -9092,16 +9092,16 @@
         <v>45278</v>
       </c>
       <c r="B434" t="n">
-        <v>12.8484582901001</v>
+        <v>12.84845733642578</v>
       </c>
       <c r="C434" t="n">
-        <v>13.08906611637279</v>
+        <v>13.0890651448394</v>
       </c>
       <c r="D434" t="n">
-        <v>12.8484582901001</v>
+        <v>12.84845733642578</v>
       </c>
       <c r="E434" t="n">
-        <v>12.98319808539135</v>
+        <v>12.983197121716</v>
       </c>
       <c r="F434" t="n">
         <v>3314300</v>
@@ -9112,16 +9112,16 @@
         <v>45279</v>
       </c>
       <c r="B435" t="n">
-        <v>12.86770534515381</v>
+        <v>12.86770629882812</v>
       </c>
       <c r="C435" t="n">
-        <v>12.94469976958878</v>
+        <v>12.94470072896945</v>
       </c>
       <c r="D435" t="n">
-        <v>12.79071092071883</v>
+        <v>12.7907118686868</v>
       </c>
       <c r="E435" t="n">
-        <v>12.87732987766966</v>
+        <v>12.87733083205729</v>
       </c>
       <c r="F435" t="n">
         <v>4780200</v>
@@ -9232,16 +9232,16 @@
         <v>45288</v>
       </c>
       <c r="B441" t="n">
-        <v>12.80996131896973</v>
+        <v>12.80996036529541</v>
       </c>
       <c r="C441" t="n">
-        <v>12.88695575141803</v>
+        <v>12.88695479201164</v>
       </c>
       <c r="D441" t="n">
-        <v>12.76183956922803</v>
+        <v>12.76183861913627</v>
       </c>
       <c r="E441" t="n">
-        <v>12.88695575141803</v>
+        <v>12.88695479201164</v>
       </c>
       <c r="F441" t="n">
         <v>3487000</v>
@@ -9332,16 +9332,16 @@
         <v>45299</v>
       </c>
       <c r="B446" t="n">
-        <v>13.01207160949707</v>
+        <v>13.01207065582275</v>
       </c>
       <c r="C446" t="n">
-        <v>13.09868965545936</v>
+        <v>13.09868869543668</v>
       </c>
       <c r="D446" t="n">
-        <v>12.88695543042352</v>
+        <v>12.88695448591916</v>
       </c>
       <c r="E446" t="n">
-        <v>12.9543253276762</v>
+        <v>12.95432437823419</v>
       </c>
       <c r="F446" t="n">
         <v>3738800</v>
@@ -9392,16 +9392,16 @@
         <v>45302</v>
       </c>
       <c r="B449" t="n">
-        <v>12.8484582901001</v>
+        <v>12.84845733642578</v>
       </c>
       <c r="C449" t="n">
-        <v>12.94470086990156</v>
+        <v>12.94469990908366</v>
       </c>
       <c r="D449" t="n">
-        <v>12.74259025911866</v>
+        <v>12.74258931330238</v>
       </c>
       <c r="E449" t="n">
-        <v>12.94470086990156</v>
+        <v>12.94469990908366</v>
       </c>
       <c r="F449" t="n">
         <v>4814200</v>
@@ -9412,16 +9412,16 @@
         <v>45303</v>
       </c>
       <c r="B450" t="n">
-        <v>12.77146339416504</v>
+        <v>12.77146434783936</v>
       </c>
       <c r="C450" t="n">
-        <v>12.88695503642984</v>
+        <v>12.88695599872818</v>
       </c>
       <c r="D450" t="n">
-        <v>12.74258979521435</v>
+        <v>12.74259074673261</v>
       </c>
       <c r="E450" t="n">
-        <v>12.84845782234157</v>
+        <v>12.84845878176524</v>
       </c>
       <c r="F450" t="n">
         <v>4041800</v>
@@ -9432,16 +9432,16 @@
         <v>45306</v>
       </c>
       <c r="B451" t="n">
-        <v>12.80996131896973</v>
+        <v>12.80996036529541</v>
       </c>
       <c r="C451" t="n">
-        <v>12.84845853519388</v>
+        <v>12.84845757865353</v>
       </c>
       <c r="D451" t="n">
-        <v>12.74259050219293</v>
+        <v>12.74258955353423</v>
       </c>
       <c r="E451" t="n">
-        <v>12.77146410274557</v>
+        <v>12.77146315193729</v>
       </c>
       <c r="F451" t="n">
         <v>1955800</v>
@@ -9492,16 +9492,16 @@
         <v>45309</v>
       </c>
       <c r="B454" t="n">
-        <v>12.55972862243652</v>
+        <v>12.55972766876221</v>
       </c>
       <c r="C454" t="n">
-        <v>12.77146376499286</v>
+        <v>12.77146279524125</v>
       </c>
       <c r="D454" t="n">
-        <v>12.51160687396745</v>
+        <v>12.51160592394707</v>
       </c>
       <c r="E454" t="n">
-        <v>12.76183923172984</v>
+        <v>12.76183826270904</v>
       </c>
       <c r="F454" t="n">
         <v>6534900</v>
@@ -9532,16 +9532,16 @@
         <v>45313</v>
       </c>
       <c r="B456" t="n">
-        <v>12.61747455596924</v>
+        <v>12.61747360229492</v>
       </c>
       <c r="C456" t="n">
-        <v>12.65597177291335</v>
+        <v>12.65597081632927</v>
       </c>
       <c r="D456" t="n">
-        <v>12.56935372317364</v>
+        <v>12.56935277313647</v>
       </c>
       <c r="E456" t="n">
-        <v>12.60785094011775</v>
+        <v>12.60784998717082</v>
       </c>
       <c r="F456" t="n">
         <v>4490300</v>
@@ -9572,16 +9572,16 @@
         <v>45315</v>
       </c>
       <c r="B458" t="n">
-        <v>12.79071140289307</v>
+        <v>12.79071235656738</v>
       </c>
       <c r="C458" t="n">
-        <v>12.82920861656179</v>
+        <v>12.82920957310646</v>
       </c>
       <c r="D458" t="n">
-        <v>12.64634708109684</v>
+        <v>12.64634802400737</v>
       </c>
       <c r="E458" t="n">
-        <v>12.65597069612954</v>
+        <v>12.6559716397576</v>
       </c>
       <c r="F458" t="n">
         <v>3333600</v>
@@ -9652,16 +9652,16 @@
         <v>45321</v>
       </c>
       <c r="B462" t="n">
-        <v>12.51160621643066</v>
+        <v>12.51160717010498</v>
       </c>
       <c r="C462" t="n">
-        <v>12.63672238873649</v>
+        <v>12.63672335194755</v>
       </c>
       <c r="D462" t="n">
-        <v>12.51160621643066</v>
+        <v>12.51160717010498</v>
       </c>
       <c r="E462" t="n">
-        <v>12.58860064279641</v>
+        <v>12.58860160233948</v>
       </c>
       <c r="F462" t="n">
         <v>3463200</v>
@@ -9672,16 +9672,16 @@
         <v>45322</v>
       </c>
       <c r="B463" t="n">
-        <v>12.68484497070312</v>
+        <v>12.68484401702881</v>
       </c>
       <c r="C463" t="n">
-        <v>12.79071208447197</v>
+        <v>12.79071112283833</v>
       </c>
       <c r="D463" t="n">
-        <v>12.53085610782262</v>
+        <v>12.53085516572552</v>
       </c>
       <c r="E463" t="n">
-        <v>12.57897693908826</v>
+        <v>12.57897599337333</v>
       </c>
       <c r="F463" t="n">
         <v>3755000</v>
@@ -9812,16 +9812,16 @@
         <v>45331</v>
       </c>
       <c r="B470" t="n">
-        <v>12.48273372650146</v>
+        <v>12.48273468017578</v>
       </c>
       <c r="C470" t="n">
-        <v>12.62709804867886</v>
+        <v>12.62709901338253</v>
       </c>
       <c r="D470" t="n">
-        <v>12.36724208519036</v>
+        <v>12.36724303004117</v>
       </c>
       <c r="E470" t="n">
-        <v>12.36724208519036</v>
+        <v>12.36724303004117</v>
       </c>
       <c r="F470" t="n">
         <v>4943200</v>
@@ -9852,16 +9852,16 @@
         <v>45337</v>
       </c>
       <c r="B472" t="n">
-        <v>12.50198173522949</v>
+        <v>12.50198268890381</v>
       </c>
       <c r="C472" t="n">
-        <v>12.58860069470964</v>
+        <v>12.58860165499141</v>
       </c>
       <c r="D472" t="n">
-        <v>12.41536277574934</v>
+        <v>12.4153637228162</v>
       </c>
       <c r="E472" t="n">
-        <v>12.46348452188787</v>
+        <v>12.46348547262554</v>
       </c>
       <c r="F472" t="n">
         <v>4740900</v>
@@ -9892,16 +9892,16 @@
         <v>45341</v>
       </c>
       <c r="B474" t="n">
-        <v>12.77146339416504</v>
+        <v>12.77146434783936</v>
       </c>
       <c r="C474" t="n">
-        <v>12.85808143747915</v>
+        <v>12.85808239762144</v>
       </c>
       <c r="D474" t="n">
-        <v>12.53085557665187</v>
+        <v>12.53085651235945</v>
       </c>
       <c r="E474" t="n">
-        <v>12.54047919178945</v>
+        <v>12.54048012821565</v>
       </c>
       <c r="F474" t="n">
         <v>4786000</v>
@@ -9972,16 +9972,16 @@
         <v>45345</v>
       </c>
       <c r="B478" t="n">
-        <v>12.41536235809326</v>
+        <v>12.41536331176758</v>
       </c>
       <c r="C478" t="n">
-        <v>12.55010305917923</v>
+        <v>12.55010402320352</v>
       </c>
       <c r="D478" t="n">
-        <v>12.41536235809326</v>
+        <v>12.41536331176758</v>
       </c>
       <c r="E478" t="n">
-        <v>12.52123037960578</v>
+        <v>12.52123134141225</v>
       </c>
       <c r="F478" t="n">
         <v>4574300</v>
@@ -9992,16 +9992,16 @@
         <v>45348</v>
       </c>
       <c r="B479" t="n">
-        <v>12.35761833190918</v>
+        <v>12.35761737823486</v>
       </c>
       <c r="C479" t="n">
-        <v>12.48273451401776</v>
+        <v>12.48273355068785</v>
       </c>
       <c r="D479" t="n">
-        <v>12.33836926488661</v>
+        <v>12.3383683126978</v>
       </c>
       <c r="E479" t="n">
-        <v>12.45386091348391</v>
+        <v>12.45385995238227</v>
       </c>
       <c r="F479" t="n">
         <v>6964500</v>
@@ -22072,19 +22072,39 @@
         <v>46230</v>
       </c>
       <c r="B1083" t="n">
-        <v>11.32</v>
+        <v>11.31999969482422</v>
       </c>
       <c r="C1083" t="n">
-        <v>11.37</v>
+        <v>11.36999988555908</v>
       </c>
       <c r="D1083" t="n">
-        <v>11.16</v>
+        <v>11.15999984741211</v>
       </c>
       <c r="E1083" t="n">
         <v>11.25</v>
       </c>
       <c r="F1083" t="n">
         <v>1323600</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B1084" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="C1084" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="D1084" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="E1084" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="F1084" t="n">
+        <v>295000</v>
       </c>
     </row>
   </sheetData>

--- a/database/AURE3.xlsx
+++ b/database/AURE3.xlsx
@@ -472,16 +472,16 @@
         <v>44649</v>
       </c>
       <c r="B3" t="n">
-        <v>12.91280937194824</v>
+        <v>12.91280841827393</v>
       </c>
       <c r="C3" t="n">
-        <v>13.2161821224289</v>
+        <v>13.21618114634902</v>
       </c>
       <c r="D3" t="n">
-        <v>12.61721411646944</v>
+        <v>12.61721318462629</v>
       </c>
       <c r="E3" t="n">
-        <v>12.74945378682817</v>
+        <v>12.74945284521847</v>
       </c>
       <c r="F3" t="n">
         <v>4714100</v>
@@ -512,16 +512,16 @@
         <v>44651</v>
       </c>
       <c r="B5" t="n">
-        <v>12.43830108642578</v>
+        <v>12.4383020401001</v>
       </c>
       <c r="C5" t="n">
-        <v>12.82724108844168</v>
+        <v>12.82724207193696</v>
       </c>
       <c r="D5" t="n">
-        <v>12.05714006249281</v>
+        <v>12.05714098694259</v>
       </c>
       <c r="E5" t="n">
-        <v>12.4149648940212</v>
+        <v>12.41496584590627</v>
       </c>
       <c r="F5" t="n">
         <v>3876100</v>
@@ -532,16 +532,16 @@
         <v>44652</v>
       </c>
       <c r="B6" t="n">
-        <v>12.51609134674072</v>
+        <v>12.51609039306641</v>
       </c>
       <c r="C6" t="n">
-        <v>12.95170380189247</v>
+        <v>12.95170281502629</v>
       </c>
       <c r="D6" t="n">
-        <v>12.31384233592669</v>
+        <v>12.31384139766291</v>
       </c>
       <c r="E6" t="n">
-        <v>12.43830303739862</v>
+        <v>12.43830208965145</v>
       </c>
       <c r="F6" t="n">
         <v>4252000</v>
@@ -552,16 +552,16 @@
         <v>44655</v>
       </c>
       <c r="B7" t="n">
-        <v>12.42274475097656</v>
+        <v>12.42274379730225</v>
       </c>
       <c r="C7" t="n">
-        <v>12.7338972197089</v>
+        <v>12.73389624214791</v>
       </c>
       <c r="D7" t="n">
-        <v>12.33717746969916</v>
+        <v>12.3371765225937</v>
       </c>
       <c r="E7" t="n">
-        <v>12.54720469988757</v>
+        <v>12.54720373665866</v>
       </c>
       <c r="F7" t="n">
         <v>2842400</v>
@@ -592,16 +592,16 @@
         <v>44657</v>
       </c>
       <c r="B9" t="n">
-        <v>12.43052291870117</v>
+        <v>12.43052387237549</v>
       </c>
       <c r="C9" t="n">
-        <v>12.44608087588125</v>
+        <v>12.44608183074918</v>
       </c>
       <c r="D9" t="n">
-        <v>12.01824669740399</v>
+        <v>12.01824761944832</v>
       </c>
       <c r="E9" t="n">
-        <v>12.06491982710001</v>
+        <v>12.06492075272512</v>
       </c>
       <c r="F9" t="n">
         <v>2914800</v>
@@ -772,16 +772,16 @@
         <v>44671</v>
       </c>
       <c r="B18" t="n">
-        <v>12.0571403503418</v>
+        <v>12.05714130401611</v>
       </c>
       <c r="C18" t="n">
-        <v>12.2127162064935</v>
+        <v>12.21271717247328</v>
       </c>
       <c r="D18" t="n">
-        <v>11.95601585838214</v>
+        <v>11.95601680405789</v>
       </c>
       <c r="E18" t="n">
-        <v>12.07269830687907</v>
+        <v>12.07269926178396</v>
       </c>
       <c r="F18" t="n">
         <v>2798400</v>
@@ -852,16 +852,16 @@
         <v>44678</v>
       </c>
       <c r="B22" t="n">
-        <v>12.0571403503418</v>
+        <v>12.05714130401611</v>
       </c>
       <c r="C22" t="n">
-        <v>12.06491932861043</v>
+        <v>12.06492028290003</v>
       </c>
       <c r="D22" t="n">
-        <v>11.83155517346078</v>
+        <v>11.83155610929216</v>
       </c>
       <c r="E22" t="n">
-        <v>12.04936137207316</v>
+        <v>12.04936232513219</v>
       </c>
       <c r="F22" t="n">
         <v>2401400</v>
@@ -872,16 +872,16 @@
         <v>44679</v>
       </c>
       <c r="B23" t="n">
-        <v>11.90934467315674</v>
+        <v>11.90934371948242</v>
       </c>
       <c r="C23" t="n">
-        <v>12.08825674030803</v>
+        <v>12.08825577230682</v>
       </c>
       <c r="D23" t="n">
-        <v>11.49706768548379</v>
+        <v>11.49706676482372</v>
       </c>
       <c r="E23" t="n">
-        <v>12.08825674030803</v>
+        <v>12.08825577230682</v>
       </c>
       <c r="F23" t="n">
         <v>3489600</v>
@@ -892,16 +892,16 @@
         <v>44680</v>
       </c>
       <c r="B24" t="n">
-        <v>11.40372276306152</v>
+        <v>11.40372180938721</v>
       </c>
       <c r="C24" t="n">
-        <v>11.96379667301973</v>
+        <v>11.96379567250737</v>
       </c>
       <c r="D24" t="n">
-        <v>11.40372276306152</v>
+        <v>11.40372180938721</v>
       </c>
       <c r="E24" t="n">
-        <v>11.96379667301973</v>
+        <v>11.96379567250737</v>
       </c>
       <c r="F24" t="n">
         <v>10427400</v>
@@ -932,16 +932,16 @@
         <v>44684</v>
       </c>
       <c r="B26" t="n">
-        <v>11.27148246765137</v>
+        <v>11.27148151397705</v>
       </c>
       <c r="C26" t="n">
-        <v>11.3570497534066</v>
+        <v>11.35704879249248</v>
       </c>
       <c r="D26" t="n">
-        <v>11.0147820940742</v>
+        <v>11.01478116211917</v>
       </c>
       <c r="E26" t="n">
-        <v>11.1548007494233</v>
+        <v>11.15479980562136</v>
       </c>
       <c r="F26" t="n">
         <v>1672900</v>
@@ -1012,16 +1012,16 @@
         <v>44690</v>
       </c>
       <c r="B30" t="n">
-        <v>11.07566165924072</v>
+        <v>11.07566070556641</v>
       </c>
       <c r="C30" t="n">
-        <v>11.13049142708364</v>
+        <v>11.13049046868818</v>
       </c>
       <c r="D30" t="n">
-        <v>10.80934436343302</v>
+        <v>10.80934343269006</v>
       </c>
       <c r="E30" t="n">
-        <v>10.99733277917979</v>
+        <v>10.99733183225001</v>
       </c>
       <c r="F30" t="n">
         <v>1545300</v>
@@ -1072,16 +1072,16 @@
         <v>44693</v>
       </c>
       <c r="B33" t="n">
-        <v>11.1539888381958</v>
+        <v>11.15398979187012</v>
       </c>
       <c r="C33" t="n">
-        <v>11.27931443797336</v>
+        <v>11.27931540236311</v>
       </c>
       <c r="D33" t="n">
-        <v>10.85634016522435</v>
+        <v>10.85634109344948</v>
       </c>
       <c r="E33" t="n">
-        <v>10.99733183847385</v>
+        <v>10.99733277875388</v>
       </c>
       <c r="F33" t="n">
         <v>1884700</v>
@@ -1092,16 +1092,16 @@
         <v>44694</v>
       </c>
       <c r="B34" t="n">
-        <v>11.32631301879883</v>
+        <v>11.32631206512451</v>
       </c>
       <c r="C34" t="n">
-        <v>11.38114278731251</v>
+        <v>11.38114182902154</v>
       </c>
       <c r="D34" t="n">
-        <v>11.11482548824677</v>
+        <v>11.11482455237968</v>
       </c>
       <c r="E34" t="n">
-        <v>11.18532133176413</v>
+        <v>11.18532038996129</v>
       </c>
       <c r="F34" t="n">
         <v>1333500</v>
@@ -1172,16 +1172,16 @@
         <v>44700</v>
       </c>
       <c r="B38" t="n">
-        <v>11.22448444366455</v>
+        <v>11.22448539733887</v>
       </c>
       <c r="C38" t="n">
-        <v>11.25581584296371</v>
+        <v>11.25581679930005</v>
       </c>
       <c r="D38" t="n">
-        <v>10.97383324927132</v>
+        <v>10.97383418164937</v>
       </c>
       <c r="E38" t="n">
-        <v>11.11482417261777</v>
+        <v>11.11482511697494</v>
       </c>
       <c r="F38" t="n">
         <v>2127500</v>
@@ -1252,16 +1252,16 @@
         <v>44706</v>
       </c>
       <c r="B42" t="n">
-        <v>11.32631301879883</v>
+        <v>11.32631206512451</v>
       </c>
       <c r="C42" t="n">
-        <v>11.39680886231618</v>
+        <v>11.39680790270612</v>
       </c>
       <c r="D42" t="n">
-        <v>11.13832460075227</v>
+        <v>11.13832366290656</v>
       </c>
       <c r="E42" t="n">
-        <v>11.17748904126186</v>
+        <v>11.17748810011851</v>
       </c>
       <c r="F42" t="n">
         <v>821700</v>
@@ -1272,16 +1272,16 @@
         <v>44707</v>
       </c>
       <c r="B43" t="n">
-        <v>11.25581645965576</v>
+        <v>11.25581550598145</v>
       </c>
       <c r="C43" t="n">
-        <v>11.44380486575034</v>
+        <v>11.44380389614828</v>
       </c>
       <c r="D43" t="n">
-        <v>11.20881973163188</v>
+        <v>11.20881878193947</v>
       </c>
       <c r="E43" t="n">
-        <v>11.33414533569493</v>
+        <v>11.33414437538402</v>
       </c>
       <c r="F43" t="n">
         <v>1248800</v>
@@ -1432,16 +1432,16 @@
         <v>44719</v>
       </c>
       <c r="B51" t="n">
-        <v>10.85634136199951</v>
+        <v>10.8563404083252</v>
       </c>
       <c r="C51" t="n">
-        <v>10.87984047479791</v>
+        <v>10.87983951905932</v>
       </c>
       <c r="D51" t="n">
-        <v>10.53519429041721</v>
+        <v>10.53519336495403</v>
       </c>
       <c r="E51" t="n">
-        <v>10.59002480661389</v>
+        <v>10.59002387633413</v>
       </c>
       <c r="F51" t="n">
         <v>2760900</v>
@@ -1592,16 +1592,16 @@
         <v>44732</v>
       </c>
       <c r="B59" t="n">
-        <v>10.59785652160645</v>
+        <v>10.59785747528076</v>
       </c>
       <c r="C59" t="n">
-        <v>10.69968376387016</v>
+        <v>10.69968472670765</v>
       </c>
       <c r="D59" t="n">
-        <v>10.37070367255648</v>
+        <v>10.37070460578988</v>
       </c>
       <c r="E59" t="n">
-        <v>10.47253091482019</v>
+        <v>10.47253185721677</v>
       </c>
       <c r="F59" t="n">
         <v>1649800</v>
@@ -1632,16 +1632,16 @@
         <v>44734</v>
       </c>
       <c r="B61" t="n">
-        <v>10.73884868621826</v>
+        <v>10.73884773254395</v>
       </c>
       <c r="C61" t="n">
-        <v>10.8328428955397</v>
+        <v>10.83284193351813</v>
       </c>
       <c r="D61" t="n">
-        <v>10.43336694567391</v>
+        <v>10.43336601912821</v>
       </c>
       <c r="E61" t="n">
-        <v>10.53519419252203</v>
+        <v>10.53519325693346</v>
       </c>
       <c r="F61" t="n">
         <v>1196200</v>
@@ -1672,16 +1672,16 @@
         <v>44736</v>
       </c>
       <c r="B63" t="n">
-        <v>10.48819732666016</v>
+        <v>10.48819637298584</v>
       </c>
       <c r="C63" t="n">
-        <v>10.70751714559343</v>
+        <v>10.70751617197673</v>
       </c>
       <c r="D63" t="n">
-        <v>10.42553452125065</v>
+        <v>10.42553357327416</v>
       </c>
       <c r="E63" t="n">
-        <v>10.70751714559343</v>
+        <v>10.70751617197673</v>
       </c>
       <c r="F63" t="n">
         <v>807500</v>
@@ -1732,16 +1732,16 @@
         <v>44741</v>
       </c>
       <c r="B66" t="n">
-        <v>10.6840181350708</v>
+        <v>10.68401718139648</v>
       </c>
       <c r="C66" t="n">
-        <v>10.6840181350708</v>
+        <v>10.68401718139648</v>
       </c>
       <c r="D66" t="n">
-        <v>10.53519342096158</v>
+        <v>10.53519248057162</v>
       </c>
       <c r="E66" t="n">
-        <v>10.62918762339921</v>
+        <v>10.62918667461916</v>
       </c>
       <c r="F66" t="n">
         <v>1613700</v>
@@ -1772,16 +1772,16 @@
         <v>44743</v>
       </c>
       <c r="B68" t="n">
-        <v>10.6840181350708</v>
+        <v>10.68401718139648</v>
       </c>
       <c r="C68" t="n">
-        <v>10.84067513913352</v>
+        <v>10.84067417147572</v>
       </c>
       <c r="D68" t="n">
-        <v>10.54302645791459</v>
+        <v>10.54302551682544</v>
       </c>
       <c r="E68" t="n">
-        <v>10.72318182583684</v>
+        <v>10.72318086866671</v>
       </c>
       <c r="F68" t="n">
         <v>2696600</v>
@@ -1792,16 +1792,16 @@
         <v>44746</v>
       </c>
       <c r="B69" t="n">
-        <v>10.65268707275391</v>
+        <v>10.65268611907959</v>
       </c>
       <c r="C69" t="n">
-        <v>10.7858457171883</v>
+        <v>10.78584475159305</v>
       </c>
       <c r="D69" t="n">
-        <v>10.52736071852189</v>
+        <v>10.52735977606733</v>
       </c>
       <c r="E69" t="n">
-        <v>10.68401847456203</v>
+        <v>10.68401751808279</v>
       </c>
       <c r="F69" t="n">
         <v>1437100</v>
@@ -1852,16 +1852,16 @@
         <v>44749</v>
       </c>
       <c r="B72" t="n">
-        <v>11.04433059692383</v>
+        <v>11.04432964324951</v>
       </c>
       <c r="C72" t="n">
-        <v>11.16182317363595</v>
+        <v>11.16182220981619</v>
       </c>
       <c r="D72" t="n">
-        <v>10.62135627496076</v>
+        <v>10.62135535781014</v>
       </c>
       <c r="E72" t="n">
-        <v>10.78584633055749</v>
+        <v>10.7858453992032</v>
       </c>
       <c r="F72" t="n">
         <v>2931100</v>
@@ -1872,16 +1872,16 @@
         <v>44750</v>
       </c>
       <c r="B73" t="n">
-        <v>11.1539888381958</v>
+        <v>11.15398979187012</v>
       </c>
       <c r="C73" t="n">
-        <v>11.31064583791775</v>
+        <v>11.31064680498636</v>
       </c>
       <c r="D73" t="n">
-        <v>11.00516487520982</v>
+        <v>11.00516581615958</v>
       </c>
       <c r="E73" t="n">
-        <v>11.00516487520982</v>
+        <v>11.00516581615958</v>
       </c>
       <c r="F73" t="n">
         <v>1922000</v>
@@ -1912,16 +1912,16 @@
         <v>44754</v>
       </c>
       <c r="B75" t="n">
-        <v>11.14615631103516</v>
+        <v>11.14615535736084</v>
       </c>
       <c r="C75" t="n">
-        <v>11.22448518797689</v>
+        <v>11.22448422760069</v>
       </c>
       <c r="D75" t="n">
-        <v>10.99733234124531</v>
+        <v>10.99733140030449</v>
       </c>
       <c r="E75" t="n">
-        <v>11.10699261956382</v>
+        <v>11.10699166924038</v>
       </c>
       <c r="F75" t="n">
         <v>1673000</v>
@@ -1972,16 +1972,16 @@
         <v>44757</v>
       </c>
       <c r="B78" t="n">
-        <v>10.8093433380127</v>
+        <v>10.80934238433838</v>
       </c>
       <c r="C78" t="n">
-        <v>10.98166640959971</v>
+        <v>10.98166544072187</v>
       </c>
       <c r="D78" t="n">
-        <v>10.60568886677345</v>
+        <v>10.60568793106692</v>
       </c>
       <c r="E78" t="n">
-        <v>10.97383337293678</v>
+        <v>10.97383240475003</v>
       </c>
       <c r="F78" t="n">
         <v>2342600</v>
@@ -2112,16 +2112,16 @@
         <v>44768</v>
       </c>
       <c r="B85" t="n">
-        <v>11.27148246765137</v>
+        <v>11.27148151397705</v>
       </c>
       <c r="C85" t="n">
-        <v>11.38114199706455</v>
+        <v>11.38114103411199</v>
       </c>
       <c r="D85" t="n">
-        <v>11.16965522819662</v>
+        <v>11.16965428313785</v>
       </c>
       <c r="E85" t="n">
-        <v>11.19315359207094</v>
+        <v>11.19315264502399</v>
       </c>
       <c r="F85" t="n">
         <v>1661400</v>
@@ -2292,16 +2292,16 @@
         <v>44781</v>
       </c>
       <c r="B94" t="n">
-        <v>10.97383308410645</v>
+        <v>10.97383403778076</v>
       </c>
       <c r="C94" t="n">
-        <v>11.10699171587358</v>
+        <v>11.10699268111997</v>
       </c>
       <c r="D94" t="n">
-        <v>10.8720058511669</v>
+        <v>10.87200679599199</v>
       </c>
       <c r="E94" t="n">
-        <v>11.02866284530486</v>
+        <v>11.02866380374413</v>
       </c>
       <c r="F94" t="n">
         <v>2949000</v>
@@ -2332,16 +2332,16 @@
         <v>44783</v>
       </c>
       <c r="B96" t="n">
-        <v>11.05216217041016</v>
+        <v>11.05216121673584</v>
       </c>
       <c r="C96" t="n">
-        <v>11.16965548649786</v>
+        <v>11.16965452268523</v>
       </c>
       <c r="D96" t="n">
-        <v>10.88767212548699</v>
+        <v>10.88767118600627</v>
       </c>
       <c r="E96" t="n">
-        <v>10.9268365641829</v>
+        <v>10.92683562132274</v>
       </c>
       <c r="F96" t="n">
         <v>2933600</v>
@@ -2352,16 +2352,16 @@
         <v>44784</v>
       </c>
       <c r="B97" t="n">
-        <v>10.89550495147705</v>
+        <v>10.89550399780273</v>
       </c>
       <c r="C97" t="n">
-        <v>11.10699246813669</v>
+        <v>11.10699149595105</v>
       </c>
       <c r="D97" t="n">
-        <v>10.83284214957779</v>
+        <v>10.8328412013883</v>
       </c>
       <c r="E97" t="n">
-        <v>11.05999499321249</v>
+        <v>11.0599940251405</v>
       </c>
       <c r="F97" t="n">
         <v>1665400</v>
@@ -2412,16 +2412,16 @@
         <v>44789</v>
       </c>
       <c r="B100" t="n">
-        <v>11.04433059692383</v>
+        <v>11.04432964324951</v>
       </c>
       <c r="C100" t="n">
-        <v>11.2949818256428</v>
+        <v>11.29498085032484</v>
       </c>
       <c r="D100" t="n">
-        <v>10.94250334850685</v>
+        <v>10.94250240362528</v>
       </c>
       <c r="E100" t="n">
-        <v>11.25581738440557</v>
+        <v>11.25581641246944</v>
       </c>
       <c r="F100" t="n">
         <v>1185300</v>
@@ -2512,16 +2512,16 @@
         <v>44796</v>
       </c>
       <c r="B105" t="n">
-        <v>11.22448444366455</v>
+        <v>11.22448539733887</v>
       </c>
       <c r="C105" t="n">
-        <v>11.27148191611302</v>
+        <v>11.27148287378042</v>
       </c>
       <c r="D105" t="n">
-        <v>10.98949857542116</v>
+        <v>10.98949950913019</v>
       </c>
       <c r="E105" t="n">
-        <v>10.98949857542116</v>
+        <v>10.98949950913019</v>
       </c>
       <c r="F105" t="n">
         <v>2361000</v>
@@ -2552,16 +2552,16 @@
         <v>44798</v>
       </c>
       <c r="B107" t="n">
-        <v>11.04433059692383</v>
+        <v>11.04432964324951</v>
       </c>
       <c r="C107" t="n">
-        <v>11.22448598081569</v>
+        <v>11.22448501158502</v>
       </c>
       <c r="D107" t="n">
-        <v>10.95033563915463</v>
+        <v>10.95033469359675</v>
       </c>
       <c r="E107" t="n">
-        <v>11.20882065252055</v>
+        <v>11.20881968464257</v>
       </c>
       <c r="F107" t="n">
         <v>2435800</v>
@@ -2572,16 +2572,16 @@
         <v>44799</v>
       </c>
       <c r="B108" t="n">
-        <v>11.05216217041016</v>
+        <v>11.05216121673584</v>
       </c>
       <c r="C108" t="n">
-        <v>11.17748852363695</v>
+        <v>11.17748755914842</v>
       </c>
       <c r="D108" t="n">
-        <v>10.95816796573971</v>
+        <v>10.95816702017601</v>
       </c>
       <c r="E108" t="n">
-        <v>11.05216217041016</v>
+        <v>11.05216121673584</v>
       </c>
       <c r="F108" t="n">
         <v>1356300</v>
@@ -2612,16 +2612,16 @@
         <v>44803</v>
       </c>
       <c r="B110" t="n">
-        <v>11.0129976272583</v>
+        <v>11.01299858093262</v>
       </c>
       <c r="C110" t="n">
-        <v>11.16182158639716</v>
+        <v>11.16182255295894</v>
       </c>
       <c r="D110" t="n">
-        <v>10.93466875592239</v>
+        <v>10.93466970281379</v>
       </c>
       <c r="E110" t="n">
-        <v>11.11482411419572</v>
+        <v>11.11482507668773</v>
       </c>
       <c r="F110" t="n">
         <v>1284900</v>
@@ -2692,16 +2692,16 @@
         <v>44809</v>
       </c>
       <c r="B114" t="n">
-        <v>11.85894680023193</v>
+        <v>11.85894584655762</v>
       </c>
       <c r="C114" t="n">
-        <v>11.92160960193201</v>
+        <v>11.92160864321847</v>
       </c>
       <c r="D114" t="n">
-        <v>11.60829484643211</v>
+        <v>11.60829391291476</v>
       </c>
       <c r="E114" t="n">
-        <v>11.76495259768182</v>
+        <v>11.76495165156634</v>
       </c>
       <c r="F114" t="n">
         <v>1899700</v>
@@ -2712,16 +2712,16 @@
         <v>44810</v>
       </c>
       <c r="B115" t="n">
-        <v>11.58479690551758</v>
+        <v>11.58479785919189</v>
       </c>
       <c r="C115" t="n">
-        <v>11.90594396270576</v>
+        <v>11.90594494281729</v>
       </c>
       <c r="D115" t="n">
-        <v>11.49863573678402</v>
+        <v>11.49863668336545</v>
       </c>
       <c r="E115" t="n">
-        <v>11.89811092545738</v>
+        <v>11.89811190492408</v>
       </c>
       <c r="F115" t="n">
         <v>1316500</v>
@@ -2832,16 +2832,16 @@
         <v>44819</v>
       </c>
       <c r="B121" t="n">
-        <v>11.22448444366455</v>
+        <v>11.22448539733887</v>
       </c>
       <c r="C121" t="n">
-        <v>11.27148191611302</v>
+        <v>11.27148287378042</v>
       </c>
       <c r="D121" t="n">
-        <v>11.11482417261777</v>
+        <v>11.11482511697494</v>
       </c>
       <c r="E121" t="n">
-        <v>11.16182164506624</v>
+        <v>11.16182259341649</v>
       </c>
       <c r="F121" t="n">
         <v>1523500</v>
@@ -2992,16 +2992,16 @@
         <v>44831</v>
       </c>
       <c r="B129" t="n">
-        <v>10.9033374786377</v>
+        <v>10.90333843231201</v>
       </c>
       <c r="C129" t="n">
-        <v>11.04432914981819</v>
+        <v>11.04433011582452</v>
       </c>
       <c r="D129" t="n">
-        <v>10.77017884407822</v>
+        <v>10.77017978610565</v>
       </c>
       <c r="E129" t="n">
-        <v>11.04432914981819</v>
+        <v>11.04433011582452</v>
       </c>
       <c r="F129" t="n">
         <v>2130200</v>
@@ -3112,16 +3112,16 @@
         <v>44839</v>
       </c>
       <c r="B135" t="n">
-        <v>10.97383308410645</v>
+        <v>10.97383403778076</v>
       </c>
       <c r="C135" t="n">
-        <v>11.20881894881312</v>
+        <v>11.20881992290874</v>
       </c>
       <c r="D135" t="n">
-        <v>10.85633977825337</v>
+        <v>10.85634072171701</v>
       </c>
       <c r="E135" t="n">
-        <v>11.20881894881312</v>
+        <v>11.20881992290874</v>
       </c>
       <c r="F135" t="n">
         <v>5244200</v>
@@ -3152,16 +3152,16 @@
         <v>44841</v>
       </c>
       <c r="B137" t="n">
-        <v>11.02866363525391</v>
+        <v>11.02866458892822</v>
       </c>
       <c r="C137" t="n">
-        <v>11.15398923954096</v>
+        <v>11.15399020405247</v>
       </c>
       <c r="D137" t="n">
-        <v>10.94250246905644</v>
+        <v>10.9425034152802</v>
       </c>
       <c r="E137" t="n">
-        <v>10.98166690714602</v>
+        <v>10.98166785675642</v>
       </c>
       <c r="F137" t="n">
         <v>7588600</v>
@@ -3172,16 +3172,16 @@
         <v>44844</v>
       </c>
       <c r="B138" t="n">
-        <v>11.07566165924072</v>
+        <v>11.07566070556641</v>
       </c>
       <c r="C138" t="n">
-        <v>11.35764428286087</v>
+        <v>11.35764330490633</v>
       </c>
       <c r="D138" t="n">
-        <v>11.0129988539918</v>
+        <v>11.01299790571309</v>
       </c>
       <c r="E138" t="n">
-        <v>11.07566165924072</v>
+        <v>11.07566070556641</v>
       </c>
       <c r="F138" t="n">
         <v>2000500</v>
@@ -3192,16 +3192,16 @@
         <v>44845</v>
       </c>
       <c r="B139" t="n">
-        <v>11.22448444366455</v>
+        <v>11.22448539733887</v>
       </c>
       <c r="C139" t="n">
-        <v>11.31847864156201</v>
+        <v>11.31847960322243</v>
       </c>
       <c r="D139" t="n">
-        <v>10.99733161199581</v>
+        <v>10.99733254637037</v>
       </c>
       <c r="E139" t="n">
-        <v>11.04432908444429</v>
+        <v>11.04433002281193</v>
       </c>
       <c r="F139" t="n">
         <v>1834300</v>
@@ -3252,16 +3252,16 @@
         <v>44851</v>
       </c>
       <c r="B142" t="n">
-        <v>11.1539888381958</v>
+        <v>11.15398979187012</v>
       </c>
       <c r="C142" t="n">
-        <v>11.20098631161214</v>
+        <v>11.20098726930477</v>
       </c>
       <c r="D142" t="n">
-        <v>10.78584507559909</v>
+        <v>10.78584599779684</v>
       </c>
       <c r="E142" t="n">
-        <v>10.86417320196032</v>
+        <v>10.86417413085518</v>
       </c>
       <c r="F142" t="n">
         <v>6971700</v>
@@ -3272,16 +3272,16 @@
         <v>44852</v>
       </c>
       <c r="B143" t="n">
-        <v>11.27148246765137</v>
+        <v>11.27148151397705</v>
       </c>
       <c r="C143" t="n">
-        <v>11.37330970710612</v>
+        <v>11.37330874481625</v>
       </c>
       <c r="D143" t="n">
-        <v>11.06782798874186</v>
+        <v>11.06782705229865</v>
       </c>
       <c r="E143" t="n">
-        <v>11.20881966598683</v>
+        <v>11.20881871761438</v>
       </c>
       <c r="F143" t="n">
         <v>2646800</v>
@@ -3452,16 +3452,16 @@
         <v>44865</v>
       </c>
       <c r="B152" t="n">
-        <v>11.68662452697754</v>
+        <v>11.68662357330322</v>
       </c>
       <c r="C152" t="n">
-        <v>11.72578896748743</v>
+        <v>11.72578801061714</v>
       </c>
       <c r="D152" t="n">
-        <v>11.16182296634386</v>
+        <v>11.16182205549541</v>
       </c>
       <c r="E152" t="n">
-        <v>11.23231880986175</v>
+        <v>11.23231789326056</v>
       </c>
       <c r="F152" t="n">
         <v>2644000</v>
@@ -3492,16 +3492,16 @@
         <v>44868</v>
       </c>
       <c r="B154" t="n">
-        <v>11.68662452697754</v>
+        <v>11.68662357330322</v>
       </c>
       <c r="C154" t="n">
-        <v>11.74928733299354</v>
+        <v>11.74928637420569</v>
       </c>
       <c r="D154" t="n">
-        <v>11.36547745939565</v>
+        <v>11.36547653192819</v>
       </c>
       <c r="E154" t="n">
-        <v>11.49863610892954</v>
+        <v>11.49863517059581</v>
       </c>
       <c r="F154" t="n">
         <v>2959500</v>
@@ -3612,16 +3612,16 @@
         <v>44876</v>
       </c>
       <c r="B160" t="n">
-        <v>10.79367637634277</v>
+        <v>10.79367733001709</v>
       </c>
       <c r="C160" t="n">
-        <v>10.85633917048995</v>
+        <v>10.85634012970083</v>
       </c>
       <c r="D160" t="n">
-        <v>10.53519216373583</v>
+        <v>10.5351930945718</v>
       </c>
       <c r="E160" t="n">
-        <v>10.78584408732395</v>
+        <v>10.78584504030624</v>
       </c>
       <c r="F160" t="n">
         <v>3291200</v>
@@ -3652,16 +3652,16 @@
         <v>44881</v>
       </c>
       <c r="B162" t="n">
-        <v>10.9033374786377</v>
+        <v>10.90333843231201</v>
       </c>
       <c r="C162" t="n">
-        <v>10.9033374786377</v>
+        <v>10.90333843231201</v>
       </c>
       <c r="D162" t="n">
-        <v>10.59785577341312</v>
+        <v>10.59785670036809</v>
       </c>
       <c r="E162" t="n">
-        <v>10.86417304253206</v>
+        <v>10.86417399278081</v>
       </c>
       <c r="F162" t="n">
         <v>5270300</v>
@@ -3752,16 +3752,16 @@
         <v>44888</v>
       </c>
       <c r="B167" t="n">
-        <v>10.56652450561523</v>
+        <v>10.56652545928955</v>
       </c>
       <c r="C167" t="n">
-        <v>10.8171764516154</v>
+        <v>10.81717742791213</v>
       </c>
       <c r="D167" t="n">
-        <v>10.51952777930236</v>
+        <v>10.51952872873502</v>
       </c>
       <c r="E167" t="n">
-        <v>10.80934341489675</v>
+        <v>10.80934439048652</v>
       </c>
       <c r="F167" t="n">
         <v>4669400</v>
@@ -3812,16 +3812,16 @@
         <v>44893</v>
       </c>
       <c r="B170" t="n">
-        <v>10.97383308410645</v>
+        <v>10.97383403778076</v>
       </c>
       <c r="C170" t="n">
-        <v>11.09915867941681</v>
+        <v>11.09915964398247</v>
       </c>
       <c r="D170" t="n">
-        <v>10.68401745820135</v>
+        <v>10.68401838668942</v>
       </c>
       <c r="E170" t="n">
-        <v>10.84067445233931</v>
+        <v>10.84067539444156</v>
       </c>
       <c r="F170" t="n">
         <v>4990000</v>
@@ -3952,16 +3952,16 @@
         <v>44902</v>
       </c>
       <c r="B177" t="n">
-        <v>10.65268707275391</v>
+        <v>10.65268611907959</v>
       </c>
       <c r="C177" t="n">
-        <v>10.80151104459258</v>
+        <v>10.80151007759491</v>
       </c>
       <c r="D177" t="n">
-        <v>10.42553422289516</v>
+        <v>10.42553328955654</v>
       </c>
       <c r="E177" t="n">
-        <v>10.42553422289516</v>
+        <v>10.42553328955654</v>
       </c>
       <c r="F177" t="n">
         <v>2865300</v>
@@ -4052,16 +4052,16 @@
         <v>44909</v>
       </c>
       <c r="B182" t="n">
-        <v>10.99733257293701</v>
+        <v>10.99733352661133</v>
       </c>
       <c r="C182" t="n">
-        <v>11.13832425560273</v>
+        <v>11.13832522150366</v>
       </c>
       <c r="D182" t="n">
-        <v>10.7388483193829</v>
+        <v>10.7388492506418</v>
       </c>
       <c r="E182" t="n">
-        <v>11.01299864745522</v>
+        <v>11.01299960248808</v>
       </c>
       <c r="F182" t="n">
         <v>3892800</v>
@@ -4072,16 +4072,16 @@
         <v>44910</v>
       </c>
       <c r="B183" t="n">
-        <v>11.05216217041016</v>
+        <v>11.05216121673584</v>
       </c>
       <c r="C183" t="n">
-        <v>11.17748852363695</v>
+        <v>11.17748755914842</v>
       </c>
       <c r="D183" t="n">
-        <v>10.86417376106927</v>
+        <v>10.86417282361618</v>
       </c>
       <c r="E183" t="n">
-        <v>10.95033492860062</v>
+        <v>10.95033398371283</v>
       </c>
       <c r="F183" t="n">
         <v>3824700</v>
@@ -4112,16 +4112,16 @@
         <v>44914</v>
       </c>
       <c r="B185" t="n">
-        <v>11.37330913543701</v>
+        <v>11.37331008911133</v>
       </c>
       <c r="C185" t="n">
-        <v>11.5221330951599</v>
+        <v>11.5221340613134</v>
       </c>
       <c r="D185" t="n">
-        <v>11.18531999289299</v>
+        <v>11.18532093080405</v>
       </c>
       <c r="E185" t="n">
-        <v>11.23231746527886</v>
+        <v>11.23231840713075</v>
       </c>
       <c r="F185" t="n">
         <v>3838800</v>
@@ -4152,16 +4152,16 @@
         <v>44916</v>
       </c>
       <c r="B187" t="n">
-        <v>11.58479690551758</v>
+        <v>11.58479785919189</v>
       </c>
       <c r="C187" t="n">
-        <v>11.75711998998425</v>
+        <v>11.7571209578444</v>
       </c>
       <c r="D187" t="n">
-        <v>11.15398956785069</v>
+        <v>11.15399048606043</v>
       </c>
       <c r="E187" t="n">
-        <v>11.42813989554768</v>
+        <v>11.4281408363258</v>
       </c>
       <c r="F187" t="n">
         <v>6348400</v>
@@ -4212,16 +4212,16 @@
         <v>44921</v>
       </c>
       <c r="B190" t="n">
-        <v>11.57696342468262</v>
+        <v>11.5769624710083</v>
       </c>
       <c r="C190" t="n">
-        <v>11.82761537802995</v>
+        <v>11.8276144037077</v>
       </c>
       <c r="D190" t="n">
-        <v>11.51430062309566</v>
+        <v>11.51429967458331</v>
       </c>
       <c r="E190" t="n">
-        <v>11.77278486639172</v>
+        <v>11.77278389658625</v>
       </c>
       <c r="F190" t="n">
         <v>1646600</v>
@@ -4252,16 +4252,16 @@
         <v>44923</v>
       </c>
       <c r="B192" t="n">
-        <v>11.58479690551758</v>
+        <v>11.58479785919189</v>
       </c>
       <c r="C192" t="n">
-        <v>11.69445718599628</v>
+        <v>11.69445814869797</v>
       </c>
       <c r="D192" t="n">
-        <v>11.49863573678402</v>
+        <v>11.49863668336545</v>
       </c>
       <c r="E192" t="n">
-        <v>11.5769638682692</v>
+        <v>11.57696482129869</v>
       </c>
       <c r="F192" t="n">
         <v>2005900</v>
@@ -4372,16 +4372,16 @@
         <v>44932</v>
       </c>
       <c r="B198" t="n">
-        <v>11.4203052520752</v>
+        <v>11.42030620574951</v>
       </c>
       <c r="C198" t="n">
-        <v>11.53779780627784</v>
+        <v>11.53779876976359</v>
       </c>
       <c r="D198" t="n">
-        <v>11.3184780231665</v>
+        <v>11.31847896833754</v>
       </c>
       <c r="E198" t="n">
-        <v>11.4124722159285</v>
+        <v>11.4124731689487</v>
       </c>
       <c r="F198" t="n">
         <v>2864500</v>
@@ -4472,16 +4472,16 @@
         <v>44939</v>
       </c>
       <c r="B203" t="n">
-        <v>11.58479690551758</v>
+        <v>11.58479785919189</v>
       </c>
       <c r="C203" t="n">
-        <v>11.78845139197822</v>
+        <v>11.78845236241762</v>
       </c>
       <c r="D203" t="n">
-        <v>11.44380522304489</v>
+        <v>11.4438061651126</v>
       </c>
       <c r="E203" t="n">
-        <v>11.74928695273586</v>
+        <v>11.7492879199512</v>
       </c>
       <c r="F203" t="n">
         <v>2269100</v>
@@ -4552,16 +4552,16 @@
         <v>44945</v>
       </c>
       <c r="B207" t="n">
-        <v>11.66312694549561</v>
+        <v>11.66312599182129</v>
       </c>
       <c r="C207" t="n">
-        <v>11.68662531258133</v>
+        <v>11.68662435698559</v>
       </c>
       <c r="D207" t="n">
-        <v>11.27931629909744</v>
+        <v>11.27931537680668</v>
       </c>
       <c r="E207" t="n">
-        <v>11.34197910932579</v>
+        <v>11.3419781819112</v>
       </c>
       <c r="F207" t="n">
         <v>1847800</v>
@@ -4572,16 +4572,16 @@
         <v>44946</v>
       </c>
       <c r="B208" t="n">
-        <v>11.58479690551758</v>
+        <v>11.58479785919189</v>
       </c>
       <c r="C208" t="n">
-        <v>11.6866241487479</v>
+        <v>11.68662511080476</v>
       </c>
       <c r="D208" t="n">
-        <v>11.48296966228726</v>
+        <v>11.48297060757903</v>
       </c>
       <c r="E208" t="n">
-        <v>11.65529274675392</v>
+        <v>11.65529370623154</v>
       </c>
       <c r="F208" t="n">
         <v>2012100</v>
@@ -4612,16 +4612,16 @@
         <v>44950</v>
       </c>
       <c r="B210" t="n">
-        <v>11.68662452697754</v>
+        <v>11.68662357330322</v>
       </c>
       <c r="C210" t="n">
-        <v>11.80411710150764</v>
+        <v>11.80411613824548</v>
       </c>
       <c r="D210" t="n">
-        <v>11.32631301888575</v>
+        <v>11.32631209461427</v>
       </c>
       <c r="E210" t="n">
-        <v>11.52996751193754</v>
+        <v>11.52996657104705</v>
       </c>
       <c r="F210" t="n">
         <v>5839900</v>
@@ -4632,16 +4632,16 @@
         <v>44951</v>
       </c>
       <c r="B211" t="n">
-        <v>11.89027881622314</v>
+        <v>11.89027786254883</v>
       </c>
       <c r="C211" t="n">
-        <v>12.07043419368129</v>
+        <v>12.07043322555739</v>
       </c>
       <c r="D211" t="n">
-        <v>11.62396152172019</v>
+        <v>11.62396058940618</v>
       </c>
       <c r="E211" t="n">
-        <v>11.67879128929448</v>
+        <v>11.67879035258278</v>
       </c>
       <c r="F211" t="n">
         <v>10764800</v>
@@ -4712,16 +4712,16 @@
         <v>44957</v>
       </c>
       <c r="B215" t="n">
-        <v>12.0704345703125</v>
+        <v>12.07043361663818</v>
       </c>
       <c r="C215" t="n">
-        <v>12.14093041482172</v>
+        <v>12.14092945557759</v>
       </c>
       <c r="D215" t="n">
-        <v>11.82761638033583</v>
+        <v>11.82761544584636</v>
       </c>
       <c r="E215" t="n">
-        <v>11.84328170856034</v>
+        <v>11.84328077283316</v>
       </c>
       <c r="F215" t="n">
         <v>5446800</v>
@@ -4812,16 +4812,16 @@
         <v>44964</v>
       </c>
       <c r="B220" t="n">
-        <v>11.60046195983887</v>
+        <v>11.60046291351318</v>
       </c>
       <c r="C220" t="n">
-        <v>12.02343622305989</v>
+        <v>12.02343721150694</v>
       </c>
       <c r="D220" t="n">
-        <v>11.49080168900398</v>
+        <v>11.49080263366312</v>
       </c>
       <c r="E220" t="n">
-        <v>12.02343622305989</v>
+        <v>12.02343721150694</v>
       </c>
       <c r="F220" t="n">
         <v>5199600</v>
@@ -4852,16 +4852,16 @@
         <v>44966</v>
       </c>
       <c r="B222" t="n">
-        <v>11.66312694549561</v>
+        <v>11.66312599182129</v>
       </c>
       <c r="C222" t="n">
-        <v>11.7884525659523</v>
+        <v>11.78845160203032</v>
       </c>
       <c r="D222" t="n">
-        <v>11.55346665409618</v>
+        <v>11.55346570938861</v>
       </c>
       <c r="E222" t="n">
-        <v>11.71012367966706</v>
+        <v>11.7101227221499</v>
       </c>
       <c r="F222" t="n">
         <v>2260100</v>
@@ -4952,16 +4952,16 @@
         <v>44973</v>
       </c>
       <c r="B227" t="n">
-        <v>11.89027881622314</v>
+        <v>11.89027786254883</v>
       </c>
       <c r="C227" t="n">
-        <v>11.9764399862684</v>
+        <v>11.97643902568342</v>
       </c>
       <c r="D227" t="n">
-        <v>11.57696404451397</v>
+        <v>11.57696311596945</v>
       </c>
       <c r="E227" t="n">
-        <v>11.7649532063393</v>
+        <v>11.76495226271687</v>
       </c>
       <c r="F227" t="n">
         <v>4461000</v>
@@ -5052,16 +5052,16 @@
         <v>44984</v>
       </c>
       <c r="B232" t="n">
-        <v>11.64745903015137</v>
+        <v>11.64745998382568</v>
       </c>
       <c r="C232" t="n">
-        <v>11.85894654152509</v>
+        <v>11.85894751251565</v>
       </c>
       <c r="D232" t="n">
-        <v>11.56129786644328</v>
+        <v>11.56129881306286</v>
       </c>
       <c r="E232" t="n">
-        <v>11.73362019385946</v>
+        <v>11.7336211545885</v>
       </c>
       <c r="F232" t="n">
         <v>3412900</v>
@@ -5212,16 +5212,16 @@
         <v>44994</v>
       </c>
       <c r="B240" t="n">
-        <v>11.57696342468262</v>
+        <v>11.5769624710083</v>
       </c>
       <c r="C240" t="n">
-        <v>11.70228902785652</v>
+        <v>11.70228806385827</v>
       </c>
       <c r="D240" t="n">
-        <v>11.51430062309566</v>
+        <v>11.51429967458331</v>
       </c>
       <c r="E240" t="n">
-        <v>11.62396089937259</v>
+        <v>11.62395994182677</v>
       </c>
       <c r="F240" t="n">
         <v>2514900</v>
@@ -5232,16 +5232,16 @@
         <v>44995</v>
       </c>
       <c r="B241" t="n">
-        <v>11.57696342468262</v>
+        <v>11.5769624710083</v>
       </c>
       <c r="C241" t="n">
-        <v>11.63179393632084</v>
+        <v>11.63179297812976</v>
       </c>
       <c r="D241" t="n">
-        <v>11.44380478456046</v>
+        <v>11.44380384185534</v>
       </c>
       <c r="E241" t="n">
-        <v>11.57696342468262</v>
+        <v>11.5769624710083</v>
       </c>
       <c r="F241" t="n">
         <v>3626000</v>
@@ -5252,16 +5252,16 @@
         <v>44998</v>
       </c>
       <c r="B242" t="n">
-        <v>11.66312694549561</v>
+        <v>11.66312599182129</v>
       </c>
       <c r="C242" t="n">
-        <v>11.74145508478123</v>
+        <v>11.74145412470215</v>
       </c>
       <c r="D242" t="n">
-        <v>11.45947243875366</v>
+        <v>11.45947150173183</v>
       </c>
       <c r="E242" t="n">
-        <v>11.52213524898201</v>
+        <v>11.52213430683635</v>
       </c>
       <c r="F242" t="n">
         <v>3223500</v>
@@ -5332,16 +5332,16 @@
         <v>45002</v>
       </c>
       <c r="B246" t="n">
-        <v>11.40464115142822</v>
+        <v>11.40464210510254</v>
       </c>
       <c r="C246" t="n">
-        <v>11.66312539603</v>
+        <v>11.66312637131919</v>
       </c>
       <c r="D246" t="n">
-        <v>11.37330975047648</v>
+        <v>11.37331070153081</v>
       </c>
       <c r="E246" t="n">
-        <v>11.66312539603</v>
+        <v>11.66312637131919</v>
       </c>
       <c r="F246" t="n">
         <v>6196900</v>
@@ -5432,16 +5432,16 @@
         <v>45009</v>
       </c>
       <c r="B251" t="n">
-        <v>11.30281448364258</v>
+        <v>11.30281352996826</v>
       </c>
       <c r="C251" t="n">
-        <v>11.39680869125504</v>
+        <v>11.39680772964997</v>
       </c>
       <c r="D251" t="n">
-        <v>11.11482532141809</v>
+        <v>11.11482438360535</v>
       </c>
       <c r="E251" t="n">
-        <v>11.20882027603011</v>
+        <v>11.20881933028655</v>
       </c>
       <c r="F251" t="n">
         <v>3265300</v>
@@ -5472,16 +5472,16 @@
         <v>45013</v>
       </c>
       <c r="B253" t="n">
-        <v>11.4203052520752</v>
+        <v>11.42030620574951</v>
       </c>
       <c r="C253" t="n">
-        <v>11.45163664966253</v>
+        <v>11.45163760595323</v>
       </c>
       <c r="D253" t="n">
-        <v>11.25581522799183</v>
+        <v>11.25581616793009</v>
       </c>
       <c r="E253" t="n">
-        <v>11.3106449870198</v>
+        <v>11.31064593153673</v>
       </c>
       <c r="F253" t="n">
         <v>3302900</v>
@@ -5512,16 +5512,16 @@
         <v>45015</v>
       </c>
       <c r="B255" t="n">
-        <v>11.40464115142822</v>
+        <v>11.40464210510254</v>
       </c>
       <c r="C255" t="n">
-        <v>11.50646764427175</v>
+        <v>11.50646860646096</v>
       </c>
       <c r="D255" t="n">
-        <v>11.12265779586299</v>
+        <v>11.12265872595741</v>
       </c>
       <c r="E255" t="n">
-        <v>11.42030647840433</v>
+        <v>11.42030743338861</v>
       </c>
       <c r="F255" t="n">
         <v>3320400</v>
@@ -5672,16 +5672,16 @@
         <v>45028</v>
       </c>
       <c r="B263" t="n">
-        <v>11.80411624908447</v>
+        <v>11.80411720275879</v>
       </c>
       <c r="C263" t="n">
-        <v>12.01560376436578</v>
+        <v>12.01560473512652</v>
       </c>
       <c r="D263" t="n">
-        <v>11.74928648452985</v>
+        <v>11.74928743377437</v>
       </c>
       <c r="E263" t="n">
-        <v>11.82761535989319</v>
+        <v>11.82761631546603</v>
       </c>
       <c r="F263" t="n">
         <v>2987000</v>
@@ -5832,16 +5832,16 @@
         <v>45041</v>
       </c>
       <c r="B271" t="n">
-        <v>12.06260108947754</v>
+        <v>12.06260013580322</v>
       </c>
       <c r="C271" t="n">
-        <v>12.14092996872072</v>
+        <v>12.14092900885369</v>
       </c>
       <c r="D271" t="n">
-        <v>11.96860688258545</v>
+        <v>11.96860593634236</v>
       </c>
       <c r="E271" t="n">
-        <v>12.11743160374759</v>
+        <v>12.11743064573835</v>
       </c>
       <c r="F271" t="n">
         <v>2381100</v>
@@ -5912,16 +5912,16 @@
         <v>45048</v>
       </c>
       <c r="B275" t="n">
-        <v>12.39158058166504</v>
+        <v>12.39158153533936</v>
       </c>
       <c r="C275" t="n">
-        <v>12.650064824739</v>
+        <v>12.65006579830664</v>
       </c>
       <c r="D275" t="n">
-        <v>12.2505896517153</v>
+        <v>12.25059059453875</v>
       </c>
       <c r="E275" t="n">
-        <v>12.5325722586143</v>
+        <v>12.53257322313954</v>
       </c>
       <c r="F275" t="n">
         <v>5999300</v>
@@ -5932,16 +5932,16 @@
         <v>45049</v>
       </c>
       <c r="B276" t="n">
-        <v>12.28975391387939</v>
+        <v>12.28975296020508</v>
       </c>
       <c r="C276" t="n">
-        <v>12.48557536452565</v>
+        <v>12.48557439565576</v>
       </c>
       <c r="D276" t="n">
-        <v>12.2819216235732</v>
+        <v>12.28192067050667</v>
       </c>
       <c r="E276" t="n">
-        <v>12.48557536452565</v>
+        <v>12.48557439565576</v>
       </c>
       <c r="F276" t="n">
         <v>6661600</v>
@@ -22092,19 +22092,19 @@
         <v>46231</v>
       </c>
       <c r="B1084" t="n">
-        <v>11.55</v>
+        <v>11.42</v>
       </c>
       <c r="C1084" t="n">
         <v>11.72</v>
       </c>
       <c r="D1084" t="n">
-        <v>11.53</v>
+        <v>11.41</v>
       </c>
       <c r="E1084" t="n">
         <v>11.53</v>
       </c>
       <c r="F1084" t="n">
-        <v>295000</v>
+        <v>896400</v>
       </c>
     </row>
   </sheetData>

--- a/database/AURE3.xlsx
+++ b/database/AURE3.xlsx
@@ -452,16 +452,16 @@
         <v>44648</v>
       </c>
       <c r="B2" t="n">
-        <v>12.75723171234131</v>
+        <v>12.75723266601562</v>
       </c>
       <c r="C2" t="n">
-        <v>13.06838341582507</v>
+        <v>13.06838439275972</v>
       </c>
       <c r="D2" t="n">
-        <v>12.02602483823237</v>
+        <v>12.02602573724489</v>
       </c>
       <c r="E2" t="n">
-        <v>13.06838341582507</v>
+        <v>13.06838439275972</v>
       </c>
       <c r="F2" t="n">
         <v>5237900</v>
@@ -472,16 +472,16 @@
         <v>44649</v>
       </c>
       <c r="B3" t="n">
-        <v>12.91280841827393</v>
+        <v>12.91280937194824</v>
       </c>
       <c r="C3" t="n">
-        <v>13.21618114634902</v>
+        <v>13.2161821224289</v>
       </c>
       <c r="D3" t="n">
-        <v>12.61721318462629</v>
+        <v>12.61721411646944</v>
       </c>
       <c r="E3" t="n">
-        <v>12.74945284521847</v>
+        <v>12.74945378682817</v>
       </c>
       <c r="F3" t="n">
         <v>4714100</v>
@@ -552,16 +552,16 @@
         <v>44655</v>
       </c>
       <c r="B7" t="n">
-        <v>12.42274379730225</v>
+        <v>12.42274475097656</v>
       </c>
       <c r="C7" t="n">
-        <v>12.73389624214791</v>
+        <v>12.7338972197089</v>
       </c>
       <c r="D7" t="n">
-        <v>12.3371765225937</v>
+        <v>12.33717746969916</v>
       </c>
       <c r="E7" t="n">
-        <v>12.54720373665866</v>
+        <v>12.54720469988757</v>
       </c>
       <c r="F7" t="n">
         <v>2842400</v>
@@ -592,16 +592,16 @@
         <v>44657</v>
       </c>
       <c r="B9" t="n">
-        <v>12.43052387237549</v>
+        <v>12.43052291870117</v>
       </c>
       <c r="C9" t="n">
-        <v>12.44608183074918</v>
+        <v>12.44608087588125</v>
       </c>
       <c r="D9" t="n">
-        <v>12.01824761944832</v>
+        <v>12.01824669740399</v>
       </c>
       <c r="E9" t="n">
-        <v>12.06492075272512</v>
+        <v>12.06491982710001</v>
       </c>
       <c r="F9" t="n">
         <v>2914800</v>
@@ -612,16 +612,16 @@
         <v>44658</v>
       </c>
       <c r="B10" t="n">
-        <v>12.44608116149902</v>
+        <v>12.44608020782471</v>
       </c>
       <c r="C10" t="n">
-        <v>12.71833948364451</v>
+        <v>12.71833850910855</v>
       </c>
       <c r="D10" t="n">
-        <v>12.20493801258351</v>
+        <v>12.20493707738666</v>
       </c>
       <c r="E10" t="n">
-        <v>12.32162046857911</v>
+        <v>12.32161952444153</v>
       </c>
       <c r="F10" t="n">
         <v>3223900</v>
@@ -652,16 +652,16 @@
         <v>44662</v>
       </c>
       <c r="B12" t="n">
-        <v>12.37607097625732</v>
+        <v>12.37607192993164</v>
       </c>
       <c r="C12" t="n">
-        <v>12.89725064802586</v>
+        <v>12.8972516418612</v>
       </c>
       <c r="D12" t="n">
-        <v>12.37607097625732</v>
+        <v>12.37607192993164</v>
       </c>
       <c r="E12" t="n">
-        <v>12.59387791557601</v>
+        <v>12.59387888603408</v>
       </c>
       <c r="F12" t="n">
         <v>2119500</v>
@@ -672,16 +672,16 @@
         <v>44663</v>
       </c>
       <c r="B13" t="n">
-        <v>12.2438325881958</v>
+        <v>12.24383354187012</v>
       </c>
       <c r="C13" t="n">
-        <v>12.64055161698694</v>
+        <v>12.64055260156177</v>
       </c>
       <c r="D13" t="n">
-        <v>12.2127174138893</v>
+        <v>12.21271836514005</v>
       </c>
       <c r="E13" t="n">
-        <v>12.48497500361014</v>
+        <v>12.48497597606709</v>
       </c>
       <c r="F13" t="n">
         <v>2267700</v>
@@ -692,16 +692,16 @@
         <v>44664</v>
       </c>
       <c r="B14" t="n">
-        <v>12.10381412506104</v>
+        <v>12.10381317138672</v>
       </c>
       <c r="C14" t="n">
-        <v>12.55498376109398</v>
+        <v>12.55498277187146</v>
       </c>
       <c r="D14" t="n">
-        <v>12.08825616769219</v>
+        <v>12.0882552152437</v>
       </c>
       <c r="E14" t="n">
-        <v>12.39162965978653</v>
+        <v>12.39162868343488</v>
       </c>
       <c r="F14" t="n">
         <v>4421300</v>
@@ -712,16 +712,16 @@
         <v>44665</v>
       </c>
       <c r="B15" t="n">
-        <v>12.11159229278564</v>
+        <v>12.11159324645996</v>
       </c>
       <c r="C15" t="n">
-        <v>12.36829265315281</v>
+        <v>12.36829362703988</v>
       </c>
       <c r="D15" t="n">
-        <v>12.04936194735386</v>
+        <v>12.04936289612812</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08047712006975</v>
+        <v>12.08047807129404</v>
       </c>
       <c r="F15" t="n">
         <v>2077400</v>
@@ -732,16 +732,16 @@
         <v>44669</v>
       </c>
       <c r="B16" t="n">
-        <v>12.45385932922363</v>
+        <v>12.45386028289795</v>
       </c>
       <c r="C16" t="n">
-        <v>12.45385932922363</v>
+        <v>12.45386028289795</v>
       </c>
       <c r="D16" t="n">
-        <v>11.92490067691762</v>
+        <v>11.92490159008608</v>
       </c>
       <c r="E16" t="n">
-        <v>12.10381346772168</v>
+        <v>12.10381439459067</v>
       </c>
       <c r="F16" t="n">
         <v>3931100</v>
@@ -752,16 +752,16 @@
         <v>44670</v>
       </c>
       <c r="B17" t="n">
-        <v>12.10381412506104</v>
+        <v>12.10381317138672</v>
       </c>
       <c r="C17" t="n">
-        <v>12.60165763320052</v>
+        <v>12.60165664030051</v>
       </c>
       <c r="D17" t="n">
-        <v>12.00268962769625</v>
+        <v>12.00268868198966</v>
       </c>
       <c r="E17" t="n">
-        <v>12.4383020482046</v>
+        <v>12.43830106817557</v>
       </c>
       <c r="F17" t="n">
         <v>3118100</v>
@@ -772,16 +772,16 @@
         <v>44671</v>
       </c>
       <c r="B18" t="n">
-        <v>12.05714130401611</v>
+        <v>12.0571403503418</v>
       </c>
       <c r="C18" t="n">
-        <v>12.21271717247328</v>
+        <v>12.2127162064935</v>
       </c>
       <c r="D18" t="n">
-        <v>11.95601680405789</v>
+        <v>11.95601585838214</v>
       </c>
       <c r="E18" t="n">
-        <v>12.07269926178396</v>
+        <v>12.07269830687907</v>
       </c>
       <c r="F18" t="n">
         <v>2798400</v>
@@ -792,16 +792,16 @@
         <v>44673</v>
       </c>
       <c r="B19" t="n">
-        <v>12.22049522399902</v>
+        <v>12.22049617767334</v>
       </c>
       <c r="C19" t="n">
-        <v>12.33717693102638</v>
+        <v>12.33717789380641</v>
       </c>
       <c r="D19" t="n">
-        <v>11.80044004011864</v>
+        <v>11.80044096101231</v>
       </c>
       <c r="E19" t="n">
-        <v>12.01824623943035</v>
+        <v>12.01824717732137</v>
       </c>
       <c r="F19" t="n">
         <v>11382300</v>
@@ -812,16 +812,16 @@
         <v>44676</v>
       </c>
       <c r="B20" t="n">
-        <v>12.39162921905518</v>
+        <v>12.39162826538086</v>
       </c>
       <c r="C20" t="n">
-        <v>12.39162921905518</v>
+        <v>12.39162826538086</v>
       </c>
       <c r="D20" t="n">
-        <v>11.90156470703017</v>
+        <v>11.90156379107179</v>
       </c>
       <c r="E20" t="n">
-        <v>12.11937090953766</v>
+        <v>12.11936997681666</v>
       </c>
       <c r="F20" t="n">
         <v>2683100</v>
@@ -832,16 +832,16 @@
         <v>44677</v>
       </c>
       <c r="B21" t="n">
-        <v>11.95601558685303</v>
+        <v>11.95601654052734</v>
       </c>
       <c r="C21" t="n">
-        <v>12.43830110089237</v>
+        <v>12.4383020930363</v>
       </c>
       <c r="D21" t="n">
-        <v>11.86267007528195</v>
+        <v>11.86267102151054</v>
       </c>
       <c r="E21" t="n">
-        <v>12.32939837498153</v>
+        <v>12.32939935843881</v>
       </c>
       <c r="F21" t="n">
         <v>2627000</v>
@@ -852,16 +852,16 @@
         <v>44678</v>
       </c>
       <c r="B22" t="n">
-        <v>12.05714130401611</v>
+        <v>12.0571403503418</v>
       </c>
       <c r="C22" t="n">
-        <v>12.06492028290003</v>
+        <v>12.06491932861043</v>
       </c>
       <c r="D22" t="n">
-        <v>11.83155610929216</v>
+        <v>11.83155517346078</v>
       </c>
       <c r="E22" t="n">
-        <v>12.04936232513219</v>
+        <v>12.04936137207316</v>
       </c>
       <c r="F22" t="n">
         <v>2401400</v>
@@ -992,16 +992,16 @@
         <v>44687</v>
       </c>
       <c r="B29" t="n">
-        <v>11.12265872955322</v>
+        <v>11.12265777587891</v>
       </c>
       <c r="C29" t="n">
-        <v>11.31064715104436</v>
+        <v>11.31064618125162</v>
       </c>
       <c r="D29" t="n">
-        <v>11.05216288474415</v>
+        <v>11.05216193711426</v>
       </c>
       <c r="E29" t="n">
-        <v>11.28714878510787</v>
+        <v>11.28714781732991</v>
       </c>
       <c r="F29" t="n">
         <v>2813300</v>
@@ -1032,16 +1032,16 @@
         <v>44691</v>
       </c>
       <c r="B31" t="n">
-        <v>11.12265872955322</v>
+        <v>11.12265777587891</v>
       </c>
       <c r="C31" t="n">
-        <v>11.25581738152601</v>
+        <v>11.25581641643446</v>
       </c>
       <c r="D31" t="n">
-        <v>10.95033563635322</v>
+        <v>10.95033469745416</v>
       </c>
       <c r="E31" t="n">
-        <v>11.11482569190786</v>
+        <v>11.11482473890516</v>
       </c>
       <c r="F31" t="n">
         <v>2338900</v>
@@ -1112,16 +1112,16 @@
         <v>44697</v>
       </c>
       <c r="B35" t="n">
-        <v>11.27931594848633</v>
+        <v>11.27931499481201</v>
       </c>
       <c r="C35" t="n">
-        <v>11.41247460283231</v>
+        <v>11.41247363789934</v>
       </c>
       <c r="D35" t="n">
-        <v>11.11482589000009</v>
+        <v>11.11482495023352</v>
       </c>
       <c r="E35" t="n">
-        <v>11.1774894452802</v>
+        <v>11.17748850021538</v>
       </c>
       <c r="F35" t="n">
         <v>2419100</v>
@@ -1212,16 +1212,16 @@
         <v>44704</v>
       </c>
       <c r="B40" t="n">
-        <v>11.20881938934326</v>
+        <v>11.20882034301758</v>
       </c>
       <c r="C40" t="n">
-        <v>11.43597222652075</v>
+        <v>11.4359731995218</v>
       </c>
       <c r="D40" t="n">
-        <v>11.16182191575504</v>
+        <v>11.16182286543069</v>
       </c>
       <c r="E40" t="n">
-        <v>11.1853202790494</v>
+        <v>11.18532123072435</v>
       </c>
       <c r="F40" t="n">
         <v>1184600</v>
@@ -1292,16 +1292,16 @@
         <v>44708</v>
       </c>
       <c r="B44" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C44" t="n">
-        <v>11.42030600182509</v>
+        <v>11.42030698171035</v>
       </c>
       <c r="D44" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="E44" t="n">
-        <v>11.26364900360379</v>
+        <v>11.26364997004757</v>
       </c>
       <c r="F44" t="n">
         <v>2224600</v>
@@ -1312,16 +1312,16 @@
         <v>44711</v>
       </c>
       <c r="B45" t="n">
-        <v>11.09916019439697</v>
+        <v>11.09915924072266</v>
       </c>
       <c r="C45" t="n">
-        <v>11.27148328496971</v>
+        <v>11.27148231648886</v>
       </c>
       <c r="D45" t="n">
-        <v>11.02866435066269</v>
+        <v>11.0286634030456</v>
       </c>
       <c r="E45" t="n">
-        <v>11.15398996307938</v>
+        <v>11.15398900469392</v>
       </c>
       <c r="F45" t="n">
         <v>1940200</v>
@@ -1412,16 +1412,16 @@
         <v>44718</v>
       </c>
       <c r="B50" t="n">
-        <v>10.61352157592773</v>
+        <v>10.61352252960205</v>
       </c>
       <c r="C50" t="n">
-        <v>10.91117023693893</v>
+        <v>10.91117121735836</v>
       </c>
       <c r="D50" t="n">
-        <v>10.45686458250065</v>
+        <v>10.4568655220986</v>
       </c>
       <c r="E50" t="n">
-        <v>10.81717604088268</v>
+        <v>10.8171770128563</v>
       </c>
       <c r="F50" t="n">
         <v>3175000</v>
@@ -1452,16 +1452,16 @@
         <v>44720</v>
       </c>
       <c r="B52" t="n">
-        <v>11.12265872955322</v>
+        <v>11.12265777587891</v>
       </c>
       <c r="C52" t="n">
-        <v>11.19315457436229</v>
+        <v>11.19315361464355</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73884884892558</v>
+        <v>10.73884792815973</v>
       </c>
       <c r="E52" t="n">
-        <v>10.78584632779816</v>
+        <v>10.78584540300267</v>
       </c>
       <c r="F52" t="n">
         <v>2847500</v>
@@ -1492,16 +1492,16 @@
         <v>44722</v>
       </c>
       <c r="B54" t="n">
-        <v>10.4803638458252</v>
+        <v>10.48036289215088</v>
       </c>
       <c r="C54" t="n">
-        <v>10.98949930498655</v>
+        <v>10.98949830498279</v>
       </c>
       <c r="D54" t="n">
-        <v>10.39420267878237</v>
+        <v>10.3942017329484</v>
       </c>
       <c r="E54" t="n">
-        <v>10.98949930498655</v>
+        <v>10.98949830498279</v>
       </c>
       <c r="F54" t="n">
         <v>4538500</v>
@@ -1552,16 +1552,16 @@
         <v>44727</v>
       </c>
       <c r="B57" t="n">
-        <v>10.84067535400391</v>
+        <v>10.84067440032959</v>
       </c>
       <c r="C57" t="n">
-        <v>10.84850839111218</v>
+        <v>10.84850743674878</v>
       </c>
       <c r="D57" t="n">
-        <v>10.44119942547642</v>
+        <v>10.44119850694474</v>
       </c>
       <c r="E57" t="n">
-        <v>10.55085970399363</v>
+        <v>10.55085877581493</v>
       </c>
       <c r="F57" t="n">
         <v>3153700</v>
@@ -1592,16 +1592,16 @@
         <v>44732</v>
       </c>
       <c r="B59" t="n">
-        <v>10.59785747528076</v>
+        <v>10.59785652160645</v>
       </c>
       <c r="C59" t="n">
-        <v>10.69968472670765</v>
+        <v>10.69968376387016</v>
       </c>
       <c r="D59" t="n">
-        <v>10.37070460578988</v>
+        <v>10.37070367255648</v>
       </c>
       <c r="E59" t="n">
-        <v>10.47253185721677</v>
+        <v>10.47253091482019</v>
       </c>
       <c r="F59" t="n">
         <v>1649800</v>
@@ -1672,16 +1672,16 @@
         <v>44736</v>
       </c>
       <c r="B63" t="n">
-        <v>10.48819637298584</v>
+        <v>10.48819732666016</v>
       </c>
       <c r="C63" t="n">
-        <v>10.70751617197673</v>
+        <v>10.70751714559343</v>
       </c>
       <c r="D63" t="n">
-        <v>10.42553357327416</v>
+        <v>10.42553452125065</v>
       </c>
       <c r="E63" t="n">
-        <v>10.70751617197673</v>
+        <v>10.70751714559343</v>
       </c>
       <c r="F63" t="n">
         <v>807500</v>
@@ -1712,16 +1712,16 @@
         <v>44740</v>
       </c>
       <c r="B65" t="n">
-        <v>10.61352157592773</v>
+        <v>10.61352252960205</v>
       </c>
       <c r="C65" t="n">
-        <v>10.86417276541107</v>
+        <v>10.86417374160756</v>
       </c>
       <c r="D65" t="n">
-        <v>10.47252990834362</v>
+        <v>10.47253084934918</v>
       </c>
       <c r="E65" t="n">
-        <v>10.52735966929324</v>
+        <v>10.5273606152255</v>
       </c>
       <c r="F65" t="n">
         <v>5362200</v>
@@ -1792,16 +1792,16 @@
         <v>44746</v>
       </c>
       <c r="B69" t="n">
-        <v>10.65268611907959</v>
+        <v>10.65268707275391</v>
       </c>
       <c r="C69" t="n">
-        <v>10.78584475159305</v>
+        <v>10.7858457171883</v>
       </c>
       <c r="D69" t="n">
-        <v>10.52735977606733</v>
+        <v>10.52736071852189</v>
       </c>
       <c r="E69" t="n">
-        <v>10.68401751808279</v>
+        <v>10.68401847456203</v>
       </c>
       <c r="F69" t="n">
         <v>1437100</v>
@@ -1932,16 +1932,16 @@
         <v>44755</v>
       </c>
       <c r="B76" t="n">
-        <v>11.17748737335205</v>
+        <v>11.17748832702637</v>
       </c>
       <c r="C76" t="n">
-        <v>11.23231713368402</v>
+        <v>11.23231809203646</v>
       </c>
       <c r="D76" t="n">
-        <v>11.0129973453567</v>
+        <v>11.01299828499656</v>
       </c>
       <c r="E76" t="n">
-        <v>11.18531966268557</v>
+        <v>11.18532061702815</v>
       </c>
       <c r="F76" t="n">
         <v>2559400</v>
@@ -1972,16 +1972,16 @@
         <v>44757</v>
       </c>
       <c r="B78" t="n">
-        <v>10.80934238433838</v>
+        <v>10.8093433380127</v>
       </c>
       <c r="C78" t="n">
-        <v>10.98166544072187</v>
+        <v>10.98166640959971</v>
       </c>
       <c r="D78" t="n">
-        <v>10.60568793106692</v>
+        <v>10.60568886677345</v>
       </c>
       <c r="E78" t="n">
-        <v>10.97383240475003</v>
+        <v>10.97383337293678</v>
       </c>
       <c r="F78" t="n">
         <v>2342600</v>
@@ -2032,16 +2032,16 @@
         <v>44762</v>
       </c>
       <c r="B81" t="n">
-        <v>11.27931594848633</v>
+        <v>11.27931499481201</v>
       </c>
       <c r="C81" t="n">
-        <v>11.35764483233677</v>
+        <v>11.35764387203968</v>
       </c>
       <c r="D81" t="n">
-        <v>11.05216308171958</v>
+        <v>11.0521621472512</v>
       </c>
       <c r="E81" t="n">
-        <v>11.08349448585983</v>
+        <v>11.08349354874236</v>
       </c>
       <c r="F81" t="n">
         <v>2285400</v>
@@ -2112,16 +2112,16 @@
         <v>44768</v>
       </c>
       <c r="B85" t="n">
-        <v>11.27148151397705</v>
+        <v>11.27148246765137</v>
       </c>
       <c r="C85" t="n">
-        <v>11.38114103411199</v>
+        <v>11.38114199706455</v>
       </c>
       <c r="D85" t="n">
-        <v>11.16965428313785</v>
+        <v>11.16965522819662</v>
       </c>
       <c r="E85" t="n">
-        <v>11.19315264502399</v>
+        <v>11.19315359207094</v>
       </c>
       <c r="F85" t="n">
         <v>1661400</v>
@@ -2152,16 +2152,16 @@
         <v>44770</v>
       </c>
       <c r="B87" t="n">
-        <v>10.9660005569458</v>
+        <v>10.96599960327148</v>
       </c>
       <c r="C87" t="n">
-        <v>11.33414507051741</v>
+        <v>11.33414408482687</v>
       </c>
       <c r="D87" t="n">
-        <v>10.8250088821738</v>
+        <v>10.82500794076103</v>
       </c>
       <c r="E87" t="n">
-        <v>11.31064596005574</v>
+        <v>11.31064497640883</v>
       </c>
       <c r="F87" t="n">
         <v>2911900</v>
@@ -2172,16 +2172,16 @@
         <v>44771</v>
       </c>
       <c r="B88" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C88" t="n">
-        <v>11.33414483955325</v>
+        <v>11.33414581204571</v>
       </c>
       <c r="D88" t="n">
-        <v>10.51952770180302</v>
+        <v>10.51952860439969</v>
       </c>
       <c r="E88" t="n">
-        <v>10.96600033348359</v>
+        <v>10.96600127438851</v>
       </c>
       <c r="F88" t="n">
         <v>13059200</v>
@@ -2192,16 +2192,16 @@
         <v>44774</v>
       </c>
       <c r="B89" t="n">
-        <v>10.9503345489502</v>
+        <v>10.95033550262451</v>
       </c>
       <c r="C89" t="n">
-        <v>11.20881953658161</v>
+        <v>11.20882051276761</v>
       </c>
       <c r="D89" t="n">
-        <v>10.78584525672945</v>
+        <v>10.78584619607824</v>
       </c>
       <c r="E89" t="n">
-        <v>11.05999482409687</v>
+        <v>11.0599957873216</v>
       </c>
       <c r="F89" t="n">
         <v>3205600</v>
@@ -2272,16 +2272,16 @@
         <v>44778</v>
       </c>
       <c r="B93" t="n">
-        <v>10.9660005569458</v>
+        <v>10.96599960327148</v>
       </c>
       <c r="C93" t="n">
-        <v>11.16965503228325</v>
+        <v>11.16965406089782</v>
       </c>
       <c r="D93" t="n">
-        <v>10.93466915666308</v>
+        <v>10.93466820571354</v>
       </c>
       <c r="E93" t="n">
-        <v>11.16965503228325</v>
+        <v>11.16965406089782</v>
       </c>
       <c r="F93" t="n">
         <v>1948700</v>
@@ -2312,16 +2312,16 @@
         <v>44782</v>
       </c>
       <c r="B95" t="n">
-        <v>10.92683601379395</v>
+        <v>10.92683696746826</v>
       </c>
       <c r="C95" t="n">
-        <v>11.05999465045304</v>
+        <v>11.0599956157492</v>
       </c>
       <c r="D95" t="n">
-        <v>10.67618481396482</v>
+        <v>10.67618574576276</v>
       </c>
       <c r="E95" t="n">
-        <v>10.98166652400619</v>
+        <v>10.98166748246601</v>
       </c>
       <c r="F95" t="n">
         <v>1743500</v>
@@ -2472,16 +2472,16 @@
         <v>44792</v>
       </c>
       <c r="B103" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C103" t="n">
-        <v>11.16182176801008</v>
+        <v>11.16182272571687</v>
       </c>
       <c r="D103" t="n">
-        <v>10.98166640680546</v>
+        <v>10.98166734905456</v>
       </c>
       <c r="E103" t="n">
-        <v>11.16182176801008</v>
+        <v>11.16182272571687</v>
       </c>
       <c r="F103" t="n">
         <v>1667800</v>
@@ -2492,16 +2492,16 @@
         <v>44795</v>
       </c>
       <c r="B104" t="n">
-        <v>11.05999565124512</v>
+        <v>11.0599946975708</v>
       </c>
       <c r="C104" t="n">
-        <v>11.22448570276716</v>
+        <v>11.2244847349093</v>
       </c>
       <c r="D104" t="n">
-        <v>10.98166751771054</v>
+        <v>10.98166657079026</v>
       </c>
       <c r="E104" t="n">
-        <v>11.05999565124512</v>
+        <v>11.0599946975708</v>
       </c>
       <c r="F104" t="n">
         <v>1703300</v>
@@ -2592,16 +2592,16 @@
         <v>44802</v>
       </c>
       <c r="B109" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C109" t="n">
-        <v>11.20881924097621</v>
+        <v>11.20882020271549</v>
       </c>
       <c r="D109" t="n">
-        <v>10.93466893383933</v>
+        <v>10.93466987205595</v>
       </c>
       <c r="E109" t="n">
-        <v>11.02083009611117</v>
+        <v>11.02083104172059</v>
       </c>
       <c r="F109" t="n">
         <v>3615600</v>
@@ -2692,16 +2692,16 @@
         <v>44809</v>
       </c>
       <c r="B114" t="n">
-        <v>11.85894584655762</v>
+        <v>11.85894680023193</v>
       </c>
       <c r="C114" t="n">
-        <v>11.92160864321847</v>
+        <v>11.92160960193201</v>
       </c>
       <c r="D114" t="n">
-        <v>11.60829391291476</v>
+        <v>11.60829484643211</v>
       </c>
       <c r="E114" t="n">
-        <v>11.76495165156634</v>
+        <v>11.76495259768182</v>
       </c>
       <c r="F114" t="n">
         <v>1899700</v>
@@ -2712,16 +2712,16 @@
         <v>44810</v>
       </c>
       <c r="B115" t="n">
-        <v>11.58479785919189</v>
+        <v>11.58479690551758</v>
       </c>
       <c r="C115" t="n">
-        <v>11.90594494281729</v>
+        <v>11.90594396270576</v>
       </c>
       <c r="D115" t="n">
-        <v>11.49863668336545</v>
+        <v>11.49863573678402</v>
       </c>
       <c r="E115" t="n">
-        <v>11.89811190492408</v>
+        <v>11.89811092545738</v>
       </c>
       <c r="F115" t="n">
         <v>1316500</v>
@@ -2752,16 +2752,16 @@
         <v>44813</v>
       </c>
       <c r="B117" t="n">
-        <v>11.31847858428955</v>
+        <v>11.31847953796387</v>
       </c>
       <c r="C117" t="n">
-        <v>11.51430001566826</v>
+        <v>11.51430098584213</v>
       </c>
       <c r="D117" t="n">
-        <v>11.1696546251215</v>
+        <v>11.16965556625618</v>
       </c>
       <c r="E117" t="n">
-        <v>11.51430001566826</v>
+        <v>11.51430098584213</v>
       </c>
       <c r="F117" t="n">
         <v>2426300</v>
@@ -2812,16 +2812,16 @@
         <v>44818</v>
       </c>
       <c r="B120" t="n">
-        <v>11.20881938934326</v>
+        <v>11.20882034301758</v>
       </c>
       <c r="C120" t="n">
-        <v>11.42030615299151</v>
+        <v>11.42030712465965</v>
       </c>
       <c r="D120" t="n">
-        <v>11.02866327875449</v>
+        <v>11.02866421710068</v>
       </c>
       <c r="E120" t="n">
-        <v>11.20098635257864</v>
+        <v>11.2009873055865</v>
       </c>
       <c r="F120" t="n">
         <v>1856400</v>
@@ -3012,16 +3012,16 @@
         <v>44832</v>
       </c>
       <c r="B130" t="n">
-        <v>10.74668025970459</v>
+        <v>10.74668121337891</v>
       </c>
       <c r="C130" t="n">
-        <v>11.03649588571345</v>
+        <v>11.03649686510639</v>
       </c>
       <c r="D130" t="n">
-        <v>10.72318115032588</v>
+        <v>10.72318210191485</v>
       </c>
       <c r="E130" t="n">
-        <v>10.95816701511669</v>
+        <v>10.95816798755862</v>
       </c>
       <c r="F130" t="n">
         <v>4249200</v>
@@ -3052,16 +3052,16 @@
         <v>44834</v>
       </c>
       <c r="B132" t="n">
-        <v>10.61352157592773</v>
+        <v>10.61352252960205</v>
       </c>
       <c r="C132" t="n">
-        <v>10.74668020709063</v>
+        <v>10.74668117272986</v>
       </c>
       <c r="D132" t="n">
-        <v>10.59785550308529</v>
+        <v>10.59785645535194</v>
       </c>
       <c r="E132" t="n">
-        <v>10.70751577198399</v>
+        <v>10.70751673410412</v>
       </c>
       <c r="F132" t="n">
         <v>4019300</v>
@@ -3092,16 +3092,16 @@
         <v>44838</v>
       </c>
       <c r="B134" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C134" t="n">
-        <v>11.32631180289231</v>
+        <v>11.32631277471268</v>
       </c>
       <c r="D134" t="n">
-        <v>11.07566060573824</v>
+        <v>11.07566155605223</v>
       </c>
       <c r="E134" t="n">
-        <v>11.20881924097621</v>
+        <v>11.20882020271549</v>
       </c>
       <c r="F134" t="n">
         <v>2406500</v>
@@ -3272,16 +3272,16 @@
         <v>44852</v>
       </c>
       <c r="B143" t="n">
-        <v>11.27148151397705</v>
+        <v>11.27148246765137</v>
       </c>
       <c r="C143" t="n">
-        <v>11.37330874481625</v>
+        <v>11.37330970710612</v>
       </c>
       <c r="D143" t="n">
-        <v>11.06782705229865</v>
+        <v>11.06782798874186</v>
       </c>
       <c r="E143" t="n">
-        <v>11.20881871761438</v>
+        <v>11.20881966598683</v>
       </c>
       <c r="F143" t="n">
         <v>2646800</v>
@@ -3312,16 +3312,16 @@
         <v>44854</v>
       </c>
       <c r="B145" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C145" t="n">
-        <v>10.98166658413194</v>
+        <v>10.98166755090811</v>
       </c>
       <c r="D145" t="n">
-        <v>10.39420227106638</v>
+        <v>10.39420318612486</v>
       </c>
       <c r="E145" t="n">
-        <v>10.57435763518006</v>
+        <v>10.5743585660986</v>
       </c>
       <c r="F145" t="n">
         <v>7194300</v>
@@ -3552,16 +3552,16 @@
         <v>44873</v>
       </c>
       <c r="B157" t="n">
-        <v>11.12265872955322</v>
+        <v>11.12265777587891</v>
       </c>
       <c r="C157" t="n">
-        <v>11.27148345681673</v>
+        <v>11.27148249038195</v>
       </c>
       <c r="D157" t="n">
-        <v>11.02083148116229</v>
+        <v>11.02083053621881</v>
       </c>
       <c r="E157" t="n">
-        <v>11.11482569190786</v>
+        <v>11.11482473890516</v>
       </c>
       <c r="F157" t="n">
         <v>2450400</v>
@@ -3572,16 +3572,16 @@
         <v>44874</v>
       </c>
       <c r="B158" t="n">
-        <v>11.12265872955322</v>
+        <v>11.12265777587891</v>
       </c>
       <c r="C158" t="n">
-        <v>11.21665294029879</v>
+        <v>11.21665197856526</v>
       </c>
       <c r="D158" t="n">
-        <v>11.04433059409837</v>
+        <v>11.04432964714004</v>
       </c>
       <c r="E158" t="n">
-        <v>11.14615709548972</v>
+        <v>11.14615613980062</v>
       </c>
       <c r="F158" t="n">
         <v>1977800</v>
@@ -3612,16 +3612,16 @@
         <v>44876</v>
       </c>
       <c r="B160" t="n">
-        <v>10.79367733001709</v>
+        <v>10.79367828369141</v>
       </c>
       <c r="C160" t="n">
-        <v>10.85634012970083</v>
+        <v>10.85634108891171</v>
       </c>
       <c r="D160" t="n">
-        <v>10.5351930945718</v>
+        <v>10.53519402540776</v>
       </c>
       <c r="E160" t="n">
-        <v>10.78584504030624</v>
+        <v>10.78584599328854</v>
       </c>
       <c r="F160" t="n">
         <v>3291200</v>
@@ -3632,16 +3632,16 @@
         <v>44879</v>
       </c>
       <c r="B161" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C161" t="n">
-        <v>10.9660005105571</v>
+        <v>10.9660014759541</v>
       </c>
       <c r="D161" t="n">
-        <v>10.71534930935563</v>
+        <v>10.71535025268644</v>
       </c>
       <c r="E161" t="n">
-        <v>10.94250214719434</v>
+        <v>10.94250311052265</v>
       </c>
       <c r="F161" t="n">
         <v>1203700</v>
@@ -3672,16 +3672,16 @@
         <v>44882</v>
       </c>
       <c r="B163" t="n">
-        <v>10.74668025970459</v>
+        <v>10.74668121337891</v>
       </c>
       <c r="C163" t="n">
-        <v>10.80151002092264</v>
+        <v>10.80151097946262</v>
       </c>
       <c r="D163" t="n">
-        <v>10.50386135845421</v>
+        <v>10.50386229058046</v>
       </c>
       <c r="E163" t="n">
-        <v>10.69184975148707</v>
+        <v>10.69185070029565</v>
       </c>
       <c r="F163" t="n">
         <v>5834900</v>
@@ -3712,16 +3712,16 @@
         <v>44886</v>
       </c>
       <c r="B165" t="n">
-        <v>11.27931594848633</v>
+        <v>11.27931499481201</v>
       </c>
       <c r="C165" t="n">
-        <v>11.32631342819651</v>
+        <v>11.32631247054852</v>
       </c>
       <c r="D165" t="n">
-        <v>10.8093448863825</v>
+        <v>10.80934397244457</v>
       </c>
       <c r="E165" t="n">
-        <v>10.84067629052275</v>
+        <v>10.84067537393573</v>
       </c>
       <c r="F165" t="n">
         <v>4939800</v>
@@ -3772,16 +3772,16 @@
         <v>44889</v>
       </c>
       <c r="B168" t="n">
-        <v>10.9503345489502</v>
+        <v>10.95033550262451</v>
       </c>
       <c r="C168" t="n">
-        <v>11.09132622456742</v>
+        <v>11.09132719052083</v>
       </c>
       <c r="D168" t="n">
-        <v>10.56652470643609</v>
+        <v>10.56652562668407</v>
       </c>
       <c r="E168" t="n">
-        <v>10.56652470643609</v>
+        <v>10.56652562668407</v>
       </c>
       <c r="F168" t="n">
         <v>1852400</v>
@@ -3792,16 +3792,16 @@
         <v>44890</v>
       </c>
       <c r="B169" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C169" t="n">
-        <v>11.03649634764489</v>
+        <v>11.03649731924802</v>
       </c>
       <c r="D169" t="n">
-        <v>10.71534930935563</v>
+        <v>10.71535025268644</v>
       </c>
       <c r="E169" t="n">
-        <v>10.95033443698226</v>
+        <v>10.95033540100009</v>
       </c>
       <c r="F169" t="n">
         <v>1631500</v>
@@ -3852,16 +3852,16 @@
         <v>44895</v>
       </c>
       <c r="B172" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C172" t="n">
-        <v>11.20881942197064</v>
+        <v>11.20882040874432</v>
       </c>
       <c r="D172" t="n">
-        <v>10.69185019899337</v>
+        <v>10.69185114025542</v>
       </c>
       <c r="E172" t="n">
-        <v>11.20881942197064</v>
+        <v>11.20882040874432</v>
       </c>
       <c r="F172" t="n">
         <v>4586400</v>
@@ -3872,16 +3872,16 @@
         <v>44896</v>
       </c>
       <c r="B173" t="n">
-        <v>10.92683601379395</v>
+        <v>10.92683696746826</v>
       </c>
       <c r="C173" t="n">
-        <v>11.02083021372987</v>
+        <v>11.02083117560783</v>
       </c>
       <c r="D173" t="n">
-        <v>10.69185014045439</v>
+        <v>10.69185107361957</v>
       </c>
       <c r="E173" t="n">
-        <v>10.76234597715621</v>
+        <v>10.76234691647413</v>
       </c>
       <c r="F173" t="n">
         <v>1944500</v>
@@ -3952,16 +3952,16 @@
         <v>44902</v>
       </c>
       <c r="B177" t="n">
-        <v>10.65268611907959</v>
+        <v>10.65268707275391</v>
       </c>
       <c r="C177" t="n">
-        <v>10.80151007759491</v>
+        <v>10.80151104459258</v>
       </c>
       <c r="D177" t="n">
-        <v>10.42553328955654</v>
+        <v>10.42553422289516</v>
       </c>
       <c r="E177" t="n">
-        <v>10.42553328955654</v>
+        <v>10.42553422289516</v>
       </c>
       <c r="F177" t="n">
         <v>2865300</v>
@@ -3992,16 +3992,16 @@
         <v>44904</v>
       </c>
       <c r="B179" t="n">
-        <v>11.17748737335205</v>
+        <v>11.17748832702637</v>
       </c>
       <c r="C179" t="n">
-        <v>11.5691302260077</v>
+        <v>11.56913121309737</v>
       </c>
       <c r="D179" t="n">
-        <v>11.04432874368917</v>
+        <v>11.04432968600226</v>
       </c>
       <c r="E179" t="n">
-        <v>11.29497993034896</v>
+        <v>11.29498089404786</v>
       </c>
       <c r="F179" t="n">
         <v>7204400</v>
@@ -4052,16 +4052,16 @@
         <v>44909</v>
       </c>
       <c r="B182" t="n">
-        <v>10.99733352661133</v>
+        <v>10.99733257293701</v>
       </c>
       <c r="C182" t="n">
-        <v>11.13832522150366</v>
+        <v>11.13832425560273</v>
       </c>
       <c r="D182" t="n">
-        <v>10.7388492506418</v>
+        <v>10.7388483193829</v>
       </c>
       <c r="E182" t="n">
-        <v>11.01299960248808</v>
+        <v>11.01299864745522</v>
       </c>
       <c r="F182" t="n">
         <v>3892800</v>
@@ -4132,16 +4132,16 @@
         <v>44915</v>
       </c>
       <c r="B186" t="n">
-        <v>11.27931594848633</v>
+        <v>11.27931499481201</v>
       </c>
       <c r="C186" t="n">
-        <v>11.56129933274823</v>
+        <v>11.56129835523201</v>
       </c>
       <c r="D186" t="n">
-        <v>11.16965640749523</v>
+        <v>11.16965546309271</v>
       </c>
       <c r="E186" t="n">
-        <v>11.35764483233677</v>
+        <v>11.35764387203968</v>
       </c>
       <c r="F186" t="n">
         <v>4148100</v>
@@ -4152,16 +4152,16 @@
         <v>44916</v>
       </c>
       <c r="B187" t="n">
-        <v>11.58479785919189</v>
+        <v>11.58479690551758</v>
       </c>
       <c r="C187" t="n">
-        <v>11.7571209578444</v>
+        <v>11.75711998998425</v>
       </c>
       <c r="D187" t="n">
-        <v>11.15399048606043</v>
+        <v>11.15398956785069</v>
       </c>
       <c r="E187" t="n">
-        <v>11.4281408363258</v>
+        <v>11.42813989554768</v>
       </c>
       <c r="F187" t="n">
         <v>6348400</v>
@@ -4212,16 +4212,16 @@
         <v>44921</v>
       </c>
       <c r="B190" t="n">
-        <v>11.5769624710083</v>
+        <v>11.57696342468262</v>
       </c>
       <c r="C190" t="n">
-        <v>11.8276144037077</v>
+        <v>11.82761537802995</v>
       </c>
       <c r="D190" t="n">
-        <v>11.51429967458331</v>
+        <v>11.51430062309566</v>
       </c>
       <c r="E190" t="n">
-        <v>11.77278389658625</v>
+        <v>11.77278486639172</v>
       </c>
       <c r="F190" t="n">
         <v>1646600</v>
@@ -4252,16 +4252,16 @@
         <v>44923</v>
       </c>
       <c r="B192" t="n">
-        <v>11.58479785919189</v>
+        <v>11.58479690551758</v>
       </c>
       <c r="C192" t="n">
-        <v>11.69445814869797</v>
+        <v>11.69445718599628</v>
       </c>
       <c r="D192" t="n">
-        <v>11.49863668336545</v>
+        <v>11.49863573678402</v>
       </c>
       <c r="E192" t="n">
-        <v>11.57696482129869</v>
+        <v>11.5769638682692</v>
       </c>
       <c r="F192" t="n">
         <v>2005900</v>
@@ -4312,16 +4312,16 @@
         <v>44929</v>
       </c>
       <c r="B195" t="n">
-        <v>11.13832378387451</v>
+        <v>11.13832473754883</v>
       </c>
       <c r="C195" t="n">
-        <v>11.32631218813412</v>
+        <v>11.32631315790418</v>
       </c>
       <c r="D195" t="n">
-        <v>11.05999490859992</v>
+        <v>11.05999585556764</v>
       </c>
       <c r="E195" t="n">
-        <v>11.30281382435154</v>
+        <v>11.30281479210966</v>
       </c>
       <c r="F195" t="n">
         <v>1562800</v>
@@ -4372,16 +4372,16 @@
         <v>44932</v>
       </c>
       <c r="B198" t="n">
-        <v>11.42030620574951</v>
+        <v>11.42030715942383</v>
       </c>
       <c r="C198" t="n">
-        <v>11.53779876976359</v>
+        <v>11.53779973324935</v>
       </c>
       <c r="D198" t="n">
-        <v>11.31847896833754</v>
+        <v>11.31847991350858</v>
       </c>
       <c r="E198" t="n">
-        <v>11.4124731689487</v>
+        <v>11.41247412196891</v>
       </c>
       <c r="F198" t="n">
         <v>2864500</v>
@@ -4412,16 +4412,16 @@
         <v>44936</v>
       </c>
       <c r="B200" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C200" t="n">
-        <v>11.1853201309934</v>
+        <v>11.1853210907164</v>
       </c>
       <c r="D200" t="n">
-        <v>10.6918500263467</v>
+        <v>10.69185094372897</v>
       </c>
       <c r="E200" t="n">
-        <v>11.08349289539969</v>
+        <v>11.08349384638571</v>
       </c>
       <c r="F200" t="n">
         <v>5832500</v>
@@ -4472,16 +4472,16 @@
         <v>44939</v>
       </c>
       <c r="B203" t="n">
-        <v>11.58479785919189</v>
+        <v>11.58479690551758</v>
       </c>
       <c r="C203" t="n">
-        <v>11.78845236241762</v>
+        <v>11.78845139197822</v>
       </c>
       <c r="D203" t="n">
-        <v>11.4438061651126</v>
+        <v>11.44380522304489</v>
       </c>
       <c r="E203" t="n">
-        <v>11.7492879199512</v>
+        <v>11.74928695273586</v>
       </c>
       <c r="F203" t="n">
         <v>2269100</v>
@@ -4512,16 +4512,16 @@
         <v>44943</v>
       </c>
       <c r="B205" t="n">
-        <v>11.74928665161133</v>
+        <v>11.74928569793701</v>
       </c>
       <c r="C205" t="n">
-        <v>11.93727505875722</v>
+        <v>11.93727408982413</v>
       </c>
       <c r="D205" t="n">
-        <v>11.60829497275214</v>
+        <v>11.60829403052194</v>
       </c>
       <c r="E205" t="n">
-        <v>11.81194945399329</v>
+        <v>11.81194849523272</v>
       </c>
       <c r="F205" t="n">
         <v>2676600</v>
@@ -4572,16 +4572,16 @@
         <v>44946</v>
       </c>
       <c r="B208" t="n">
-        <v>11.58479785919189</v>
+        <v>11.58479690551758</v>
       </c>
       <c r="C208" t="n">
-        <v>11.68662511080476</v>
+        <v>11.6866241487479</v>
       </c>
       <c r="D208" t="n">
-        <v>11.48297060757903</v>
+        <v>11.48296966228726</v>
       </c>
       <c r="E208" t="n">
-        <v>11.65529370623154</v>
+        <v>11.65529274675392</v>
       </c>
       <c r="F208" t="n">
         <v>2012100</v>
@@ -4592,16 +4592,16 @@
         <v>44949</v>
       </c>
       <c r="B209" t="n">
-        <v>11.52213478088379</v>
+        <v>11.52213382720947</v>
       </c>
       <c r="C209" t="n">
-        <v>11.64746039624901</v>
+        <v>11.64745943220163</v>
       </c>
       <c r="D209" t="n">
-        <v>11.34981168625682</v>
+        <v>11.34981074684549</v>
       </c>
       <c r="E209" t="n">
-        <v>11.59263062627662</v>
+        <v>11.59262966676744</v>
       </c>
       <c r="F209" t="n">
         <v>1770800</v>
@@ -4672,16 +4672,16 @@
         <v>44953</v>
       </c>
       <c r="B213" t="n">
-        <v>11.98427104949951</v>
+        <v>11.98427200317383</v>
       </c>
       <c r="C213" t="n">
-        <v>12.23492222797812</v>
+        <v>12.23492320159854</v>
       </c>
       <c r="D213" t="n">
-        <v>11.92160825487986</v>
+        <v>11.92160920356765</v>
       </c>
       <c r="E213" t="n">
-        <v>11.96860497734488</v>
+        <v>11.96860592977254</v>
       </c>
       <c r="F213" t="n">
         <v>4160800</v>
@@ -4772,16 +4772,16 @@
         <v>44960</v>
       </c>
       <c r="B218" t="n">
-        <v>11.92160892486572</v>
+        <v>11.92160987854004</v>
       </c>
       <c r="C218" t="n">
-        <v>12.17226011743074</v>
+        <v>12.17226109115601</v>
       </c>
       <c r="D218" t="n">
-        <v>11.80411561810126</v>
+        <v>11.80411656237665</v>
       </c>
       <c r="E218" t="n">
-        <v>11.99993704904255</v>
+        <v>11.99993800898276</v>
       </c>
       <c r="F218" t="n">
         <v>3073100</v>
@@ -4872,16 +4872,16 @@
         <v>44967</v>
       </c>
       <c r="B223" t="n">
-        <v>11.72578907012939</v>
+        <v>11.72578811645508</v>
       </c>
       <c r="C223" t="n">
-        <v>11.88244608654069</v>
+        <v>11.88244512012525</v>
       </c>
       <c r="D223" t="n">
-        <v>11.62396182271216</v>
+        <v>11.62396087731959</v>
       </c>
       <c r="E223" t="n">
-        <v>11.62396182271216</v>
+        <v>11.62396087731959</v>
       </c>
       <c r="F223" t="n">
         <v>6075300</v>
@@ -4932,16 +4932,16 @@
         <v>44972</v>
       </c>
       <c r="B226" t="n">
-        <v>11.75711917877197</v>
+        <v>11.75712013244629</v>
       </c>
       <c r="C226" t="n">
-        <v>11.92944150434928</v>
+        <v>11.92944247200145</v>
       </c>
       <c r="D226" t="n">
-        <v>11.63179357944321</v>
+        <v>11.63179452295179</v>
       </c>
       <c r="E226" t="n">
-        <v>11.6631249792754</v>
+        <v>11.66312592532541</v>
       </c>
       <c r="F226" t="n">
         <v>3961900</v>
@@ -4972,16 +4972,16 @@
         <v>44974</v>
       </c>
       <c r="B228" t="n">
-        <v>11.72578907012939</v>
+        <v>11.72578811645508</v>
       </c>
       <c r="C228" t="n">
-        <v>12.13309731279878</v>
+        <v>12.13309632599753</v>
       </c>
       <c r="D228" t="n">
-        <v>11.55346597857718</v>
+        <v>11.55346503891813</v>
       </c>
       <c r="E228" t="n">
-        <v>11.94510889310522</v>
+        <v>11.94510792159332</v>
       </c>
       <c r="F228" t="n">
         <v>9428300</v>
@@ -5052,16 +5052,16 @@
         <v>44984</v>
       </c>
       <c r="B232" t="n">
-        <v>11.64745998382568</v>
+        <v>11.64745903015137</v>
       </c>
       <c r="C232" t="n">
-        <v>11.85894751251565</v>
+        <v>11.85894654152509</v>
       </c>
       <c r="D232" t="n">
-        <v>11.56129881306286</v>
+        <v>11.56129786644328</v>
       </c>
       <c r="E232" t="n">
-        <v>11.7336211545885</v>
+        <v>11.73362019385946</v>
       </c>
       <c r="F232" t="n">
         <v>3412900</v>
@@ -5212,16 +5212,16 @@
         <v>44994</v>
       </c>
       <c r="B240" t="n">
-        <v>11.5769624710083</v>
+        <v>11.57696342468262</v>
       </c>
       <c r="C240" t="n">
-        <v>11.70228806385827</v>
+        <v>11.70228902785652</v>
       </c>
       <c r="D240" t="n">
-        <v>11.51429967458331</v>
+        <v>11.51430062309566</v>
       </c>
       <c r="E240" t="n">
-        <v>11.62395994182677</v>
+        <v>11.62396089937259</v>
       </c>
       <c r="F240" t="n">
         <v>2514900</v>
@@ -5232,16 +5232,16 @@
         <v>44995</v>
       </c>
       <c r="B241" t="n">
-        <v>11.5769624710083</v>
+        <v>11.57696342468262</v>
       </c>
       <c r="C241" t="n">
-        <v>11.63179297812976</v>
+        <v>11.63179393632084</v>
       </c>
       <c r="D241" t="n">
-        <v>11.44380384185534</v>
+        <v>11.44380478456046</v>
       </c>
       <c r="E241" t="n">
-        <v>11.5769624710083</v>
+        <v>11.57696342468262</v>
       </c>
       <c r="F241" t="n">
         <v>3626000</v>
@@ -5272,16 +5272,16 @@
         <v>44999</v>
       </c>
       <c r="B243" t="n">
-        <v>11.75711917877197</v>
+        <v>11.75712013244629</v>
       </c>
       <c r="C243" t="n">
-        <v>11.82761501514428</v>
+        <v>11.82761597453684</v>
       </c>
       <c r="D243" t="n">
-        <v>11.63962586915163</v>
+        <v>11.63962681329553</v>
       </c>
       <c r="E243" t="n">
-        <v>11.69445637910759</v>
+        <v>11.69445732769904</v>
       </c>
       <c r="F243" t="n">
         <v>2520000</v>
@@ -5292,16 +5292,16 @@
         <v>45000</v>
       </c>
       <c r="B244" t="n">
-        <v>11.74928665161133</v>
+        <v>11.74928569793701</v>
       </c>
       <c r="C244" t="n">
-        <v>11.89027833047051</v>
+        <v>11.89027736535209</v>
       </c>
       <c r="D244" t="n">
-        <v>11.61612800979977</v>
+        <v>11.61612706693377</v>
       </c>
       <c r="E244" t="n">
-        <v>11.71795525042035</v>
+        <v>11.71795429928916</v>
       </c>
       <c r="F244" t="n">
         <v>4602600</v>
@@ -5332,16 +5332,16 @@
         <v>45002</v>
       </c>
       <c r="B246" t="n">
-        <v>11.40464210510254</v>
+        <v>11.40464115142822</v>
       </c>
       <c r="C246" t="n">
-        <v>11.66312637131919</v>
+        <v>11.66312539603</v>
       </c>
       <c r="D246" t="n">
-        <v>11.37331070153081</v>
+        <v>11.37330975047648</v>
       </c>
       <c r="E246" t="n">
-        <v>11.66312637131919</v>
+        <v>11.66312539603</v>
       </c>
       <c r="F246" t="n">
         <v>6196900</v>
@@ -5352,16 +5352,16 @@
         <v>45005</v>
       </c>
       <c r="B247" t="n">
-        <v>11.31847858428955</v>
+        <v>11.31847953796387</v>
       </c>
       <c r="C247" t="n">
-        <v>11.51430001566826</v>
+        <v>11.51430098584213</v>
       </c>
       <c r="D247" t="n">
-        <v>11.2479827494733</v>
+        <v>11.24798369720776</v>
       </c>
       <c r="E247" t="n">
-        <v>11.45163721738703</v>
+        <v>11.45163818228105</v>
       </c>
       <c r="F247" t="n">
         <v>2892000</v>
@@ -5472,16 +5472,16 @@
         <v>45013</v>
       </c>
       <c r="B253" t="n">
-        <v>11.42030620574951</v>
+        <v>11.42030715942383</v>
       </c>
       <c r="C253" t="n">
-        <v>11.45163760595323</v>
+        <v>11.45163856224394</v>
       </c>
       <c r="D253" t="n">
-        <v>11.25581616793009</v>
+        <v>11.25581710786836</v>
       </c>
       <c r="E253" t="n">
-        <v>11.31064593153673</v>
+        <v>11.31064687605366</v>
       </c>
       <c r="F253" t="n">
         <v>3302900</v>
@@ -5512,16 +5512,16 @@
         <v>45015</v>
       </c>
       <c r="B255" t="n">
-        <v>11.40464210510254</v>
+        <v>11.40464115142822</v>
       </c>
       <c r="C255" t="n">
-        <v>11.50646860646096</v>
+        <v>11.50646764427175</v>
       </c>
       <c r="D255" t="n">
-        <v>11.12265872595741</v>
+        <v>11.12265779586299</v>
       </c>
       <c r="E255" t="n">
-        <v>11.42030743338861</v>
+        <v>11.42030647840433</v>
       </c>
       <c r="F255" t="n">
         <v>3320400</v>
@@ -5672,16 +5672,16 @@
         <v>45028</v>
       </c>
       <c r="B263" t="n">
-        <v>11.80411720275879</v>
+        <v>11.80411624908447</v>
       </c>
       <c r="C263" t="n">
-        <v>12.01560473512652</v>
+        <v>12.01560376436578</v>
       </c>
       <c r="D263" t="n">
-        <v>11.74928743377437</v>
+        <v>11.74928648452985</v>
       </c>
       <c r="E263" t="n">
-        <v>11.82761631546603</v>
+        <v>11.82761535989319</v>
       </c>
       <c r="F263" t="n">
         <v>2987000</v>
@@ -5812,16 +5812,16 @@
         <v>45040</v>
       </c>
       <c r="B270" t="n">
-        <v>12.10959911346436</v>
+        <v>12.10959815979004</v>
       </c>
       <c r="C270" t="n">
-        <v>12.17226192088982</v>
+        <v>12.17226096228058</v>
       </c>
       <c r="D270" t="n">
-        <v>12.03127023068273</v>
+        <v>12.0312692831771</v>
       </c>
       <c r="E270" t="n">
-        <v>12.10176607578628</v>
+        <v>12.10176512272884</v>
       </c>
       <c r="F270" t="n">
         <v>2389300</v>
@@ -5912,16 +5912,16 @@
         <v>45048</v>
       </c>
       <c r="B275" t="n">
-        <v>12.39158153533936</v>
+        <v>12.39158058166504</v>
       </c>
       <c r="C275" t="n">
-        <v>12.65006579830664</v>
+        <v>12.650064824739</v>
       </c>
       <c r="D275" t="n">
-        <v>12.25059059453875</v>
+        <v>12.2505896517153</v>
       </c>
       <c r="E275" t="n">
-        <v>12.53257322313954</v>
+        <v>12.5325722586143</v>
       </c>
       <c r="F275" t="n">
         <v>5999300</v>
@@ -5972,16 +5972,16 @@
         <v>45051</v>
       </c>
       <c r="B278" t="n">
-        <v>12.50989723205566</v>
+        <v>12.50989818572998</v>
       </c>
       <c r="C278" t="n">
-        <v>12.59647124671763</v>
+        <v>12.59647220699179</v>
       </c>
       <c r="D278" t="n">
-        <v>12.15494525807742</v>
+        <v>12.15494618469247</v>
       </c>
       <c r="E278" t="n">
-        <v>12.34540759495513</v>
+        <v>12.34540853608981</v>
       </c>
       <c r="F278" t="n">
         <v>9400800</v>
@@ -6032,16 +6032,16 @@
         <v>45056</v>
       </c>
       <c r="B281" t="n">
-        <v>11.86925315856934</v>
+        <v>11.86925220489502</v>
       </c>
       <c r="C281" t="n">
-        <v>12.05105794406462</v>
+        <v>12.0510569757826</v>
       </c>
       <c r="D281" t="n">
-        <v>11.69610594039075</v>
+        <v>11.69610500062852</v>
       </c>
       <c r="E281" t="n">
-        <v>12.0164285004289</v>
+        <v>12.0164275349293</v>
       </c>
       <c r="F281" t="n">
         <v>5308900</v>
@@ -6112,16 +6112,16 @@
         <v>45062</v>
       </c>
       <c r="B285" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="C285" t="n">
-        <v>12.30212128603885</v>
+        <v>12.30212031805942</v>
       </c>
       <c r="D285" t="n">
-        <v>12.08568706272756</v>
+        <v>12.08568611177803</v>
       </c>
       <c r="E285" t="n">
-        <v>12.18091782375736</v>
+        <v>12.18091686531469</v>
       </c>
       <c r="F285" t="n">
         <v>2907500</v>
@@ -6132,16 +6132,16 @@
         <v>45063</v>
       </c>
       <c r="B286" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="C286" t="n">
-        <v>12.24152036724783</v>
+        <v>12.24151939290137</v>
       </c>
       <c r="D286" t="n">
-        <v>11.9471696818366</v>
+        <v>11.94716873091856</v>
       </c>
       <c r="E286" t="n">
-        <v>12.128974468377</v>
+        <v>12.12897350298847</v>
       </c>
       <c r="F286" t="n">
         <v>4330800</v>
@@ -6152,16 +6152,16 @@
         <v>45064</v>
       </c>
       <c r="B287" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="C287" t="n">
-        <v>12.05971558070743</v>
+        <v>12.05971462083146</v>
       </c>
       <c r="D287" t="n">
-        <v>11.82596621559931</v>
+        <v>11.82596527432829</v>
       </c>
       <c r="E287" t="n">
-        <v>12.01642856950617</v>
+        <v>12.01642761307558</v>
       </c>
       <c r="F287" t="n">
         <v>4680600</v>
@@ -6172,16 +6172,16 @@
         <v>45065</v>
       </c>
       <c r="B288" t="n">
-        <v>12.09434509277344</v>
+        <v>12.09434413909912</v>
       </c>
       <c r="C288" t="n">
-        <v>12.18091829003328</v>
+        <v>12.18091732953242</v>
       </c>
       <c r="D288" t="n">
-        <v>11.93851218182222</v>
+        <v>11.93851124043578</v>
       </c>
       <c r="E288" t="n">
-        <v>11.99911350246722</v>
+        <v>11.99911255630219</v>
       </c>
       <c r="F288" t="n">
         <v>2962700</v>
@@ -6252,16 +6252,16 @@
         <v>45071</v>
       </c>
       <c r="B292" t="n">
-        <v>12.29346466064453</v>
+        <v>12.29346370697021</v>
       </c>
       <c r="C292" t="n">
-        <v>12.39735299671616</v>
+        <v>12.39735203498263</v>
       </c>
       <c r="D292" t="n">
-        <v>12.20689146006706</v>
+        <v>12.20689051310872</v>
       </c>
       <c r="E292" t="n">
-        <v>12.28480709289745</v>
+        <v>12.28480613989475</v>
       </c>
       <c r="F292" t="n">
         <v>2204600</v>
@@ -6292,16 +6292,16 @@
         <v>45075</v>
       </c>
       <c r="B294" t="n">
-        <v>12.28480529785156</v>
+        <v>12.28480625152588</v>
       </c>
       <c r="C294" t="n">
-        <v>12.34540743759487</v>
+        <v>12.34540839597375</v>
       </c>
       <c r="D294" t="n">
-        <v>12.16360266962691</v>
+        <v>12.16360361389222</v>
       </c>
       <c r="E294" t="n">
-        <v>12.16360266962691</v>
+        <v>12.16360361389222</v>
       </c>
       <c r="F294" t="n">
         <v>1431900</v>
@@ -6312,16 +6312,16 @@
         <v>45076</v>
       </c>
       <c r="B295" t="n">
-        <v>12.26749229431152</v>
+        <v>12.26749134063721</v>
       </c>
       <c r="C295" t="n">
-        <v>12.38003819364653</v>
+        <v>12.3800372312229</v>
       </c>
       <c r="D295" t="n">
-        <v>12.25017715950718</v>
+        <v>12.25017620717894</v>
       </c>
       <c r="E295" t="n">
-        <v>12.37138062624436</v>
+        <v>12.37137966449377</v>
       </c>
       <c r="F295" t="n">
         <v>1829100</v>
@@ -6392,16 +6392,16 @@
         <v>45082</v>
       </c>
       <c r="B299" t="n">
-        <v>12.06837177276611</v>
+        <v>12.0683708190918</v>
       </c>
       <c r="C299" t="n">
-        <v>12.1982328004551</v>
+        <v>12.19823183651883</v>
       </c>
       <c r="D299" t="n">
-        <v>11.97314101296568</v>
+        <v>11.97314006681674</v>
       </c>
       <c r="E299" t="n">
-        <v>12.17226092516972</v>
+        <v>12.17225996328581</v>
       </c>
       <c r="F299" t="n">
         <v>3442900</v>
@@ -6432,16 +6432,16 @@
         <v>45084</v>
       </c>
       <c r="B301" t="n">
-        <v>12.22420597076416</v>
+        <v>12.22420501708984</v>
       </c>
       <c r="C301" t="n">
-        <v>12.46661209224716</v>
+        <v>12.46661111966148</v>
       </c>
       <c r="D301" t="n">
-        <v>12.21554840287484</v>
+        <v>12.21554744987595</v>
       </c>
       <c r="E301" t="n">
-        <v>12.38003889024736</v>
+        <v>12.3800379244157</v>
       </c>
       <c r="F301" t="n">
         <v>3154600</v>
@@ -6472,16 +6472,16 @@
         <v>45089</v>
       </c>
       <c r="B303" t="n">
-        <v>12.45795345306396</v>
+        <v>12.45795440673828</v>
       </c>
       <c r="C303" t="n">
-        <v>12.45795345306396</v>
+        <v>12.45795440673828</v>
       </c>
       <c r="D303" t="n">
-        <v>12.25883355008453</v>
+        <v>12.25883448851593</v>
       </c>
       <c r="E303" t="n">
-        <v>12.3800370051864</v>
+        <v>12.3800379528961</v>
       </c>
       <c r="F303" t="n">
         <v>2572800</v>
@@ -6492,16 +6492,16 @@
         <v>45090</v>
       </c>
       <c r="B304" t="n">
-        <v>12.31077861785889</v>
+        <v>12.3107795715332</v>
       </c>
       <c r="C304" t="n">
-        <v>12.50124013627868</v>
+        <v>12.5012411047074</v>
       </c>
       <c r="D304" t="n">
-        <v>12.29346348402198</v>
+        <v>12.29346443635495</v>
       </c>
       <c r="E304" t="n">
-        <v>12.46661069423589</v>
+        <v>12.46661165998199</v>
       </c>
       <c r="F304" t="n">
         <v>1312000</v>
@@ -6532,16 +6532,16 @@
         <v>45092</v>
       </c>
       <c r="B306" t="n">
-        <v>12.46661186218262</v>
+        <v>12.4666109085083</v>
       </c>
       <c r="C306" t="n">
-        <v>12.49258456537125</v>
+        <v>12.49258360971007</v>
       </c>
       <c r="D306" t="n">
-        <v>12.36272352632139</v>
+        <v>12.36272258059435</v>
       </c>
       <c r="E306" t="n">
-        <v>12.45795512008417</v>
+        <v>12.45795416707208</v>
       </c>
       <c r="F306" t="n">
         <v>1266000</v>
@@ -6552,16 +6552,16 @@
         <v>45093</v>
       </c>
       <c r="B307" t="n">
-        <v>12.62244319915771</v>
+        <v>12.62244415283203</v>
       </c>
       <c r="C307" t="n">
-        <v>12.83021984487801</v>
+        <v>12.83022081425066</v>
       </c>
       <c r="D307" t="n">
-        <v>12.4406384277447</v>
+        <v>12.44063936768297</v>
       </c>
       <c r="E307" t="n">
-        <v>12.46661030205199</v>
+        <v>12.46661124395253</v>
       </c>
       <c r="F307" t="n">
         <v>5319000</v>
@@ -6612,16 +6612,16 @@
         <v>45098</v>
       </c>
       <c r="B310" t="n">
-        <v>12.86484909057617</v>
+        <v>12.86485004425049</v>
       </c>
       <c r="C310" t="n">
-        <v>12.90813609751867</v>
+        <v>12.90813705440186</v>
       </c>
       <c r="D310" t="n">
-        <v>12.63975814061098</v>
+        <v>12.63975907759925</v>
       </c>
       <c r="E310" t="n">
-        <v>12.75230320277808</v>
+        <v>12.75230414810935</v>
       </c>
       <c r="F310" t="n">
         <v>5022600</v>
@@ -6692,16 +6692,16 @@
         <v>45104</v>
       </c>
       <c r="B314" t="n">
-        <v>12.50124073028564</v>
+        <v>12.50123977661133</v>
       </c>
       <c r="C314" t="n">
-        <v>12.83887842546918</v>
+        <v>12.83887744603771</v>
       </c>
       <c r="D314" t="n">
-        <v>12.39735239922096</v>
+        <v>12.3973514534719</v>
       </c>
       <c r="E314" t="n">
-        <v>12.76961953809272</v>
+        <v>12.76961856394476</v>
       </c>
       <c r="F314" t="n">
         <v>3014700</v>
@@ -6872,16 +6872,16 @@
         <v>45117</v>
       </c>
       <c r="B323" t="n">
-        <v>12.38869476318359</v>
+        <v>12.38869571685791</v>
       </c>
       <c r="C323" t="n">
-        <v>12.45795364556026</v>
+        <v>12.45795460456609</v>
       </c>
       <c r="D323" t="n">
-        <v>12.31077831410209</v>
+        <v>12.31077926177845</v>
       </c>
       <c r="E323" t="n">
-        <v>12.38003719647876</v>
+        <v>12.38003814948662</v>
       </c>
       <c r="F323" t="n">
         <v>1514600</v>
@@ -6912,16 +6912,16 @@
         <v>45119</v>
       </c>
       <c r="B325" t="n">
-        <v>12.38869476318359</v>
+        <v>12.38869571685791</v>
       </c>
       <c r="C325" t="n">
-        <v>12.45795364556026</v>
+        <v>12.45795460456609</v>
       </c>
       <c r="D325" t="n">
-        <v>12.28480561398759</v>
+        <v>12.28480655966458</v>
       </c>
       <c r="E325" t="n">
-        <v>12.37137962977392</v>
+        <v>12.37138058211533</v>
       </c>
       <c r="F325" t="n">
         <v>1842800</v>
@@ -7052,16 +7052,16 @@
         <v>45128</v>
       </c>
       <c r="B332" t="n">
-        <v>12.38869476318359</v>
+        <v>12.38869571685791</v>
       </c>
       <c r="C332" t="n">
-        <v>12.38869476318359</v>
+        <v>12.38869571685791</v>
       </c>
       <c r="D332" t="n">
-        <v>12.22420429831576</v>
+        <v>12.2242052393277</v>
       </c>
       <c r="E332" t="n">
-        <v>12.27614887291376</v>
+        <v>12.27614981792436</v>
       </c>
       <c r="F332" t="n">
         <v>2631400</v>
@@ -7152,16 +7152,16 @@
         <v>45135</v>
       </c>
       <c r="B337" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="C337" t="n">
-        <v>12.22420483354582</v>
+        <v>12.22420387169716</v>
       </c>
       <c r="D337" t="n">
-        <v>12.0597151871069</v>
+        <v>12.05971423820094</v>
       </c>
       <c r="E337" t="n">
-        <v>12.14628838105279</v>
+        <v>12.14628742533491</v>
       </c>
       <c r="F337" t="n">
         <v>1506100</v>
@@ -7172,16 +7172,16 @@
         <v>45138</v>
       </c>
       <c r="B338" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="C338" t="n">
-        <v>12.20689052500906</v>
+        <v>12.20688956452276</v>
       </c>
       <c r="D338" t="n">
-        <v>12.10300137126433</v>
+        <v>12.10300041895243</v>
       </c>
       <c r="E338" t="n">
-        <v>12.20689052500906</v>
+        <v>12.20688956452276</v>
       </c>
       <c r="F338" t="n">
         <v>1549400</v>
@@ -7212,16 +7212,16 @@
         <v>45140</v>
       </c>
       <c r="B340" t="n">
-        <v>12.22420597076416</v>
+        <v>12.22420501708984</v>
       </c>
       <c r="C340" t="n">
-        <v>12.23286353865348</v>
+        <v>12.23286258430374</v>
       </c>
       <c r="D340" t="n">
-        <v>12.12897520087505</v>
+        <v>12.12897425463018</v>
       </c>
       <c r="E340" t="n">
-        <v>12.13763276876436</v>
+        <v>12.13763182184407</v>
       </c>
       <c r="F340" t="n">
         <v>1697600</v>
@@ -7332,16 +7332,16 @@
         <v>45148</v>
       </c>
       <c r="B346" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C346" t="n">
-        <v>12.09434549372545</v>
+        <v>12.09434452900206</v>
       </c>
       <c r="D346" t="n">
-        <v>11.88656799702522</v>
+        <v>11.88656704887551</v>
       </c>
       <c r="E346" t="n">
-        <v>12.01642903566675</v>
+        <v>12.01642807715848</v>
       </c>
       <c r="F346" t="n">
         <v>2835300</v>
@@ -7412,16 +7412,16 @@
         <v>45154</v>
       </c>
       <c r="B350" t="n">
-        <v>11.68744850158691</v>
+        <v>11.6874475479126</v>
       </c>
       <c r="C350" t="n">
-        <v>11.91254030050967</v>
+        <v>11.91253932846828</v>
       </c>
       <c r="D350" t="n">
-        <v>11.64416149015853</v>
+        <v>11.64416054001635</v>
       </c>
       <c r="E350" t="n">
-        <v>11.886567598274</v>
+        <v>11.88656662835193</v>
       </c>
       <c r="F350" t="n">
         <v>3946200</v>
@@ -7432,16 +7432,16 @@
         <v>45155</v>
       </c>
       <c r="B351" t="n">
-        <v>11.71342086791992</v>
+        <v>11.71341991424561</v>
       </c>
       <c r="C351" t="n">
-        <v>11.78267975884857</v>
+        <v>11.78267879953539</v>
       </c>
       <c r="D351" t="n">
-        <v>11.66147711253899</v>
+        <v>11.66147616309379</v>
       </c>
       <c r="E351" t="n">
-        <v>11.73073600346764</v>
+        <v>11.73073504838357</v>
       </c>
       <c r="F351" t="n">
         <v>2345000</v>
@@ -7452,16 +7452,16 @@
         <v>45156</v>
       </c>
       <c r="B352" t="n">
-        <v>11.77402114868164</v>
+        <v>11.77402210235596</v>
       </c>
       <c r="C352" t="n">
-        <v>11.80865058865178</v>
+        <v>11.80865154513102</v>
       </c>
       <c r="D352" t="n">
-        <v>11.65281769597066</v>
+        <v>11.65281863982772</v>
       </c>
       <c r="E352" t="n">
-        <v>11.71341900951066</v>
+        <v>11.71341995827632</v>
       </c>
       <c r="F352" t="n">
         <v>3061800</v>
@@ -7512,16 +7512,16 @@
         <v>45161</v>
       </c>
       <c r="B355" t="n">
-        <v>11.87790966033936</v>
+        <v>11.87791061401367</v>
       </c>
       <c r="C355" t="n">
-        <v>11.89522396778845</v>
+        <v>11.89522492285292</v>
       </c>
       <c r="D355" t="n">
-        <v>11.79133564620093</v>
+        <v>11.79133659292425</v>
       </c>
       <c r="E355" t="n">
-        <v>11.86059452725928</v>
+        <v>11.86059547954337</v>
       </c>
       <c r="F355" t="n">
         <v>2615000</v>
@@ -7532,16 +7532,16 @@
         <v>45162</v>
       </c>
       <c r="B356" t="n">
-        <v>11.97314071655273</v>
+        <v>11.97314167022705</v>
       </c>
       <c r="C356" t="n">
-        <v>11.99911259119515</v>
+        <v>11.99911354693815</v>
       </c>
       <c r="D356" t="n">
-        <v>11.89522426699448</v>
+        <v>11.89522521446267</v>
       </c>
       <c r="E356" t="n">
-        <v>11.90388183375229</v>
+        <v>11.90388278191006</v>
       </c>
       <c r="F356" t="n">
         <v>2322800</v>
@@ -7592,16 +7592,16 @@
         <v>45167</v>
       </c>
       <c r="B359" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="C359" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="D359" t="n">
-        <v>11.97314116752997</v>
+        <v>11.97314022543599</v>
       </c>
       <c r="E359" t="n">
-        <v>11.98179873461387</v>
+        <v>11.98179779183868</v>
       </c>
       <c r="F359" t="n">
         <v>1776800</v>
@@ -7632,16 +7632,16 @@
         <v>45169</v>
       </c>
       <c r="B361" t="n">
-        <v>11.78267955780029</v>
+        <v>11.78267860412598</v>
       </c>
       <c r="C361" t="n">
-        <v>12.12031726453966</v>
+        <v>12.1203162835374</v>
       </c>
       <c r="D361" t="n">
-        <v>11.78267955780029</v>
+        <v>11.78267860412598</v>
       </c>
       <c r="E361" t="n">
-        <v>12.12031726453966</v>
+        <v>12.1203162835374</v>
       </c>
       <c r="F361" t="n">
         <v>3236500</v>
@@ -7712,16 +7712,16 @@
         <v>45175</v>
       </c>
       <c r="B365" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C365" t="n">
-        <v>12.02508660336907</v>
+        <v>12.02508564417022</v>
       </c>
       <c r="D365" t="n">
-        <v>11.81730910666884</v>
+        <v>11.81730816404367</v>
       </c>
       <c r="E365" t="n">
-        <v>11.93851257760805</v>
+        <v>11.9385116253149</v>
       </c>
       <c r="F365" t="n">
         <v>2473500</v>
@@ -7732,16 +7732,16 @@
         <v>45177</v>
       </c>
       <c r="B366" t="n">
-        <v>11.92985343933105</v>
+        <v>11.92985439300537</v>
       </c>
       <c r="C366" t="n">
-        <v>12.07702876837038</v>
+        <v>12.07702973380992</v>
       </c>
       <c r="D366" t="n">
-        <v>11.88656643214931</v>
+        <v>11.88656738236326</v>
       </c>
       <c r="E366" t="n">
-        <v>11.9385110058936</v>
+        <v>11.93851196026</v>
       </c>
       <c r="F366" t="n">
         <v>3462800</v>
@@ -7772,16 +7772,16 @@
         <v>45181</v>
       </c>
       <c r="B368" t="n">
-        <v>12.06837177276611</v>
+        <v>12.0683708190918</v>
       </c>
       <c r="C368" t="n">
-        <v>12.15494579122544</v>
+        <v>12.15494483070982</v>
       </c>
       <c r="D368" t="n">
-        <v>11.98179857993782</v>
+        <v>11.98179763310474</v>
       </c>
       <c r="E368" t="n">
-        <v>12.03374233050859</v>
+        <v>12.03374137957078</v>
       </c>
       <c r="F368" t="n">
         <v>2215400</v>
@@ -7792,16 +7792,16 @@
         <v>45182</v>
       </c>
       <c r="B369" t="n">
-        <v>12.06837177276611</v>
+        <v>12.0683708190918</v>
       </c>
       <c r="C369" t="n">
-        <v>12.1982328004551</v>
+        <v>12.19823183651883</v>
       </c>
       <c r="D369" t="n">
-        <v>12.03374233050859</v>
+        <v>12.03374137957078</v>
       </c>
       <c r="E369" t="n">
-        <v>12.07702933973825</v>
+        <v>12.07702838537979</v>
       </c>
       <c r="F369" t="n">
         <v>1684100</v>
@@ -7892,16 +7892,16 @@
         <v>45189</v>
       </c>
       <c r="B374" t="n">
-        <v>12.06837177276611</v>
+        <v>12.0683708190918</v>
       </c>
       <c r="C374" t="n">
-        <v>12.1462882242533</v>
+        <v>12.14628726442182</v>
       </c>
       <c r="D374" t="n">
-        <v>11.97314101296568</v>
+        <v>11.97314006681674</v>
       </c>
       <c r="E374" t="n">
-        <v>12.08568690671039</v>
+        <v>12.08568595166779</v>
       </c>
       <c r="F374" t="n">
         <v>2998000</v>
@@ -7912,16 +7912,16 @@
         <v>45190</v>
       </c>
       <c r="B375" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C375" t="n">
-        <v>12.0337433454403</v>
+        <v>12.03374238555092</v>
       </c>
       <c r="D375" t="n">
-        <v>11.877911254954</v>
+        <v>11.8779103074948</v>
       </c>
       <c r="E375" t="n">
-        <v>12.02508660336907</v>
+        <v>12.02508564417022</v>
       </c>
       <c r="F375" t="n">
         <v>4405700</v>
@@ -7932,16 +7932,16 @@
         <v>45191</v>
       </c>
       <c r="B376" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C376" t="n">
-        <v>12.10300223579667</v>
+        <v>12.10300127038276</v>
       </c>
       <c r="D376" t="n">
-        <v>11.92985500990573</v>
+        <v>11.92985405830317</v>
       </c>
       <c r="E376" t="n">
-        <v>12.02508660336907</v>
+        <v>12.02508564417022</v>
       </c>
       <c r="F376" t="n">
         <v>2812600</v>
@@ -8012,16 +8012,16 @@
         <v>45197</v>
       </c>
       <c r="B380" t="n">
-        <v>11.78267955780029</v>
+        <v>11.78267860412598</v>
       </c>
       <c r="C380" t="n">
-        <v>11.86059601517331</v>
+        <v>11.86059505519254</v>
       </c>
       <c r="D380" t="n">
-        <v>11.73073580330568</v>
+        <v>11.73073485383562</v>
       </c>
       <c r="E380" t="n">
-        <v>11.85193844754717</v>
+        <v>11.85193748826714</v>
       </c>
       <c r="F380" t="n">
         <v>2404900</v>
@@ -8092,16 +8092,16 @@
         <v>45203</v>
       </c>
       <c r="B384" t="n">
-        <v>11.77402114868164</v>
+        <v>11.77402210235596</v>
       </c>
       <c r="C384" t="n">
-        <v>11.86059433579151</v>
+        <v>11.86059529647809</v>
       </c>
       <c r="D384" t="n">
-        <v>11.7480484494808</v>
+        <v>11.74804940105138</v>
       </c>
       <c r="E384" t="n">
-        <v>11.80865058865178</v>
+        <v>11.80865154513102</v>
       </c>
       <c r="F384" t="n">
         <v>4367600</v>
@@ -8192,16 +8192,16 @@
         <v>45210</v>
       </c>
       <c r="B389" t="n">
-        <v>12.09434509277344</v>
+        <v>12.09434413909912</v>
       </c>
       <c r="C389" t="n">
-        <v>12.18957585744859</v>
+        <v>12.18957489626505</v>
       </c>
       <c r="D389" t="n">
-        <v>12.00777106988252</v>
+        <v>12.00777012303482</v>
       </c>
       <c r="E389" t="n">
-        <v>12.09434509277344</v>
+        <v>12.09434413909912</v>
       </c>
       <c r="F389" t="n">
         <v>3458500</v>
@@ -8232,16 +8232,16 @@
         <v>45215</v>
       </c>
       <c r="B391" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="C391" t="n">
-        <v>12.12031690101054</v>
+        <v>12.12031593631109</v>
       </c>
       <c r="D391" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="E391" t="n">
-        <v>12.05971558070743</v>
+        <v>12.05971462083146</v>
       </c>
       <c r="F391" t="n">
         <v>3983600</v>
@@ -8252,16 +8252,16 @@
         <v>45216</v>
       </c>
       <c r="B392" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C392" t="n">
-        <v>12.10300223579667</v>
+        <v>12.10300127038276</v>
       </c>
       <c r="D392" t="n">
-        <v>11.88656799702522</v>
+        <v>11.88656704887551</v>
       </c>
       <c r="E392" t="n">
-        <v>11.97314202278624</v>
+        <v>11.97314106773082</v>
       </c>
       <c r="F392" t="n">
         <v>5165000</v>
@@ -8292,16 +8292,16 @@
         <v>45218</v>
       </c>
       <c r="B394" t="n">
-        <v>11.67013263702393</v>
+        <v>11.67013359069824</v>
       </c>
       <c r="C394" t="n">
-        <v>11.75670665446719</v>
+        <v>11.75670761521626</v>
       </c>
       <c r="D394" t="n">
-        <v>11.62684645393332</v>
+        <v>11.62684740407032</v>
       </c>
       <c r="E394" t="n">
-        <v>11.66147589578441</v>
+        <v>11.66147684875131</v>
       </c>
       <c r="F394" t="n">
         <v>3066300</v>
@@ -8452,16 +8452,16 @@
         <v>45230</v>
       </c>
       <c r="B402" t="n">
-        <v>11.61818885803223</v>
+        <v>11.61818981170654</v>
       </c>
       <c r="C402" t="n">
-        <v>11.6614758666457</v>
+        <v>11.66147682387321</v>
       </c>
       <c r="D402" t="n">
-        <v>11.52295809958741</v>
+        <v>11.52295904544475</v>
       </c>
       <c r="E402" t="n">
-        <v>11.52295809958741</v>
+        <v>11.52295904544475</v>
       </c>
       <c r="F402" t="n">
         <v>3290000</v>
@@ -8592,16 +8592,16 @@
         <v>45240</v>
       </c>
       <c r="B409" t="n">
-        <v>11.78267955780029</v>
+        <v>11.78267860412598</v>
       </c>
       <c r="C409" t="n">
-        <v>11.86059601517331</v>
+        <v>11.86059505519254</v>
       </c>
       <c r="D409" t="n">
-        <v>11.69610635843224</v>
+        <v>11.69610541176504</v>
       </c>
       <c r="E409" t="n">
-        <v>11.69610635843224</v>
+        <v>11.69610541176504</v>
       </c>
       <c r="F409" t="n">
         <v>3430000</v>
@@ -8712,16 +8712,16 @@
         <v>45251</v>
       </c>
       <c r="B415" t="n">
-        <v>11.97314071655273</v>
+        <v>11.97314167022705</v>
       </c>
       <c r="C415" t="n">
-        <v>12.09434417426901</v>
+        <v>12.09434513759732</v>
       </c>
       <c r="D415" t="n">
-        <v>11.9125394005101</v>
+        <v>11.91254034935745</v>
       </c>
       <c r="E415" t="n">
-        <v>12.0856866075112</v>
+        <v>12.08568757014993</v>
       </c>
       <c r="F415" t="n">
         <v>2713400</v>
@@ -8732,16 +8732,16 @@
         <v>45252</v>
       </c>
       <c r="B416" t="n">
-        <v>12.46661186218262</v>
+        <v>12.4666109085083</v>
       </c>
       <c r="C416" t="n">
-        <v>12.94276735410323</v>
+        <v>12.94276636400384</v>
       </c>
       <c r="D416" t="n">
-        <v>12.44063998462508</v>
+        <v>12.44063903293757</v>
       </c>
       <c r="E416" t="n">
-        <v>12.81290714068447</v>
+        <v>12.81290616051917</v>
       </c>
       <c r="F416" t="n">
         <v>20875500</v>
@@ -8752,16 +8752,16 @@
         <v>45253</v>
       </c>
       <c r="B417" t="n">
-        <v>12.56184196472168</v>
+        <v>12.561842918396</v>
       </c>
       <c r="C417" t="n">
-        <v>12.76961861177884</v>
+        <v>12.76961958122722</v>
       </c>
       <c r="D417" t="n">
-        <v>12.46661038226389</v>
+        <v>12.46661132870839</v>
       </c>
       <c r="E417" t="n">
-        <v>12.76961861177884</v>
+        <v>12.76961958122722</v>
       </c>
       <c r="F417" t="n">
         <v>9122900</v>
@@ -8832,16 +8832,16 @@
         <v>45259</v>
       </c>
       <c r="B421" t="n">
-        <v>12.56184196472168</v>
+        <v>12.561842918396</v>
       </c>
       <c r="C421" t="n">
-        <v>12.75230347837524</v>
+        <v>12.75230444650908</v>
       </c>
       <c r="D421" t="n">
-        <v>12.56184196472168</v>
+        <v>12.561842918396</v>
       </c>
       <c r="E421" t="n">
-        <v>12.72633160390085</v>
+        <v>12.72633257006295</v>
       </c>
       <c r="F421" t="n">
         <v>5869600</v>
@@ -8872,16 +8872,16 @@
         <v>45261</v>
       </c>
       <c r="B423" t="n">
-        <v>12.86484909057617</v>
+        <v>12.86485004425049</v>
       </c>
       <c r="C423" t="n">
-        <v>12.96873741185957</v>
+        <v>12.96873837323515</v>
       </c>
       <c r="D423" t="n">
-        <v>12.70901702146657</v>
+        <v>12.70901796358902</v>
       </c>
       <c r="E423" t="n">
-        <v>12.72633132886498</v>
+        <v>12.72633227227094</v>
       </c>
       <c r="F423" t="n">
         <v>6458300</v>
@@ -8912,16 +8912,16 @@
         <v>45265</v>
       </c>
       <c r="B425" t="n">
-        <v>13.15920066833496</v>
+        <v>13.15919971466064</v>
       </c>
       <c r="C425" t="n">
-        <v>13.20248767830808</v>
+        <v>13.20248672149667</v>
       </c>
       <c r="D425" t="n">
-        <v>12.92545213548978</v>
+        <v>12.9254511987557</v>
       </c>
       <c r="E425" t="n">
-        <v>12.96008157834207</v>
+        <v>12.96008063909832</v>
       </c>
       <c r="F425" t="n">
         <v>6696500</v>
@@ -8952,16 +8952,16 @@
         <v>45267</v>
       </c>
       <c r="B427" t="n">
-        <v>13.1159143447876</v>
+        <v>13.11591339111328</v>
       </c>
       <c r="C427" t="n">
-        <v>13.15054378945223</v>
+        <v>13.15054283325996</v>
       </c>
       <c r="D427" t="n">
-        <v>12.97739656612907</v>
+        <v>12.97739562252655</v>
       </c>
       <c r="E427" t="n">
-        <v>13.10725760284475</v>
+        <v>13.10725664979988</v>
       </c>
       <c r="F427" t="n">
         <v>6196000</v>
@@ -9052,16 +9052,16 @@
         <v>45274</v>
       </c>
       <c r="B432" t="n">
-        <v>12.94470024108887</v>
+        <v>12.94470119476318</v>
       </c>
       <c r="C432" t="n">
-        <v>12.98319745470858</v>
+        <v>12.9831984112191</v>
       </c>
       <c r="D432" t="n">
-        <v>12.71371695937057</v>
+        <v>12.71371789602766</v>
       </c>
       <c r="E432" t="n">
-        <v>12.71371695937057</v>
+        <v>12.71371789602766</v>
       </c>
       <c r="F432" t="n">
         <v>5480800</v>
@@ -9092,16 +9092,16 @@
         <v>45278</v>
       </c>
       <c r="B434" t="n">
-        <v>12.84845733642578</v>
+        <v>12.8484582901001</v>
       </c>
       <c r="C434" t="n">
-        <v>13.0890651448394</v>
+        <v>13.08906611637279</v>
       </c>
       <c r="D434" t="n">
-        <v>12.84845733642578</v>
+        <v>12.8484582901001</v>
       </c>
       <c r="E434" t="n">
-        <v>12.983197121716</v>
+        <v>12.98319808539135</v>
       </c>
       <c r="F434" t="n">
         <v>3314300</v>
@@ -9112,16 +9112,16 @@
         <v>45279</v>
       </c>
       <c r="B435" t="n">
-        <v>12.86770629882812</v>
+        <v>12.86770534515381</v>
       </c>
       <c r="C435" t="n">
-        <v>12.94470072896945</v>
+        <v>12.94469976958878</v>
       </c>
       <c r="D435" t="n">
-        <v>12.7907118686868</v>
+        <v>12.79071092071883</v>
       </c>
       <c r="E435" t="n">
-        <v>12.87733083205729</v>
+        <v>12.87732987766966</v>
       </c>
       <c r="F435" t="n">
         <v>4780200</v>
@@ -9232,16 +9232,16 @@
         <v>45288</v>
       </c>
       <c r="B441" t="n">
-        <v>12.80996036529541</v>
+        <v>12.80996131896973</v>
       </c>
       <c r="C441" t="n">
-        <v>12.88695479201164</v>
+        <v>12.88695575141803</v>
       </c>
       <c r="D441" t="n">
-        <v>12.76183861913627</v>
+        <v>12.76183956922803</v>
       </c>
       <c r="E441" t="n">
-        <v>12.88695479201164</v>
+        <v>12.88695575141803</v>
       </c>
       <c r="F441" t="n">
         <v>3487000</v>
@@ -9332,16 +9332,16 @@
         <v>45299</v>
       </c>
       <c r="B446" t="n">
-        <v>13.01207065582275</v>
+        <v>13.01207160949707</v>
       </c>
       <c r="C446" t="n">
-        <v>13.09868869543668</v>
+        <v>13.09868965545936</v>
       </c>
       <c r="D446" t="n">
-        <v>12.88695448591916</v>
+        <v>12.88695543042352</v>
       </c>
       <c r="E446" t="n">
-        <v>12.95432437823419</v>
+        <v>12.9543253276762</v>
       </c>
       <c r="F446" t="n">
         <v>3738800</v>
@@ -9392,16 +9392,16 @@
         <v>45302</v>
       </c>
       <c r="B449" t="n">
-        <v>12.84845733642578</v>
+        <v>12.8484582901001</v>
       </c>
       <c r="C449" t="n">
-        <v>12.94469990908366</v>
+        <v>12.94470086990156</v>
       </c>
       <c r="D449" t="n">
-        <v>12.74258931330238</v>
+        <v>12.74259025911866</v>
       </c>
       <c r="E449" t="n">
-        <v>12.94469990908366</v>
+        <v>12.94470086990156</v>
       </c>
       <c r="F449" t="n">
         <v>4814200</v>
@@ -9412,16 +9412,16 @@
         <v>45303</v>
       </c>
       <c r="B450" t="n">
-        <v>12.77146434783936</v>
+        <v>12.77146339416504</v>
       </c>
       <c r="C450" t="n">
-        <v>12.88695599872818</v>
+        <v>12.88695503642984</v>
       </c>
       <c r="D450" t="n">
-        <v>12.74259074673261</v>
+        <v>12.74258979521435</v>
       </c>
       <c r="E450" t="n">
-        <v>12.84845878176524</v>
+        <v>12.84845782234157</v>
       </c>
       <c r="F450" t="n">
         <v>4041800</v>
@@ -9432,16 +9432,16 @@
         <v>45306</v>
       </c>
       <c r="B451" t="n">
-        <v>12.80996036529541</v>
+        <v>12.80996131896973</v>
       </c>
       <c r="C451" t="n">
-        <v>12.84845757865353</v>
+        <v>12.84845853519388</v>
       </c>
       <c r="D451" t="n">
-        <v>12.74258955353423</v>
+        <v>12.74259050219293</v>
       </c>
       <c r="E451" t="n">
-        <v>12.77146315193729</v>
+        <v>12.77146410274557</v>
       </c>
       <c r="F451" t="n">
         <v>1955800</v>
@@ -9492,16 +9492,16 @@
         <v>45309</v>
       </c>
       <c r="B454" t="n">
-        <v>12.55972766876221</v>
+        <v>12.55972862243652</v>
       </c>
       <c r="C454" t="n">
-        <v>12.77146279524125</v>
+        <v>12.77146376499286</v>
       </c>
       <c r="D454" t="n">
-        <v>12.51160592394707</v>
+        <v>12.51160687396745</v>
       </c>
       <c r="E454" t="n">
-        <v>12.76183826270904</v>
+        <v>12.76183923172984</v>
       </c>
       <c r="F454" t="n">
         <v>6534900</v>
@@ -9532,16 +9532,16 @@
         <v>45313</v>
       </c>
       <c r="B456" t="n">
-        <v>12.61747360229492</v>
+        <v>12.61747455596924</v>
       </c>
       <c r="C456" t="n">
-        <v>12.65597081632927</v>
+        <v>12.65597177291335</v>
       </c>
       <c r="D456" t="n">
-        <v>12.56935277313647</v>
+        <v>12.56935372317364</v>
       </c>
       <c r="E456" t="n">
-        <v>12.60784998717082</v>
+        <v>12.60785094011775</v>
       </c>
       <c r="F456" t="n">
         <v>4490300</v>
@@ -9572,16 +9572,16 @@
         <v>45315</v>
       </c>
       <c r="B458" t="n">
-        <v>12.79071235656738</v>
+        <v>12.79071140289307</v>
       </c>
       <c r="C458" t="n">
-        <v>12.82920957310646</v>
+        <v>12.82920861656179</v>
       </c>
       <c r="D458" t="n">
-        <v>12.64634802400737</v>
+        <v>12.64634708109684</v>
       </c>
       <c r="E458" t="n">
-        <v>12.6559716397576</v>
+        <v>12.65597069612954</v>
       </c>
       <c r="F458" t="n">
         <v>3333600</v>
@@ -9652,16 +9652,16 @@
         <v>45321</v>
       </c>
       <c r="B462" t="n">
-        <v>12.51160717010498</v>
+        <v>12.51160621643066</v>
       </c>
       <c r="C462" t="n">
-        <v>12.63672335194755</v>
+        <v>12.63672238873649</v>
       </c>
       <c r="D462" t="n">
-        <v>12.51160717010498</v>
+        <v>12.51160621643066</v>
       </c>
       <c r="E462" t="n">
-        <v>12.58860160233948</v>
+        <v>12.58860064279641</v>
       </c>
       <c r="F462" t="n">
         <v>3463200</v>
@@ -9672,16 +9672,16 @@
         <v>45322</v>
       </c>
       <c r="B463" t="n">
-        <v>12.68484401702881</v>
+        <v>12.68484497070312</v>
       </c>
       <c r="C463" t="n">
-        <v>12.79071112283833</v>
+        <v>12.79071208447197</v>
       </c>
       <c r="D463" t="n">
-        <v>12.53085516572552</v>
+        <v>12.53085610782262</v>
       </c>
       <c r="E463" t="n">
-        <v>12.57897599337333</v>
+        <v>12.57897693908826</v>
       </c>
       <c r="F463" t="n">
         <v>3755000</v>
@@ -9812,16 +9812,16 @@
         <v>45331</v>
       </c>
       <c r="B470" t="n">
-        <v>12.48273468017578</v>
+        <v>12.48273372650146</v>
       </c>
       <c r="C470" t="n">
-        <v>12.62709901338253</v>
+        <v>12.62709804867886</v>
       </c>
       <c r="D470" t="n">
-        <v>12.36724303004117</v>
+        <v>12.36724208519036</v>
       </c>
       <c r="E470" t="n">
-        <v>12.36724303004117</v>
+        <v>12.36724208519036</v>
       </c>
       <c r="F470" t="n">
         <v>4943200</v>
@@ -9852,16 +9852,16 @@
         <v>45337</v>
       </c>
       <c r="B472" t="n">
-        <v>12.50198268890381</v>
+        <v>12.50198173522949</v>
       </c>
       <c r="C472" t="n">
-        <v>12.58860165499141</v>
+        <v>12.58860069470964</v>
       </c>
       <c r="D472" t="n">
-        <v>12.4153637228162</v>
+        <v>12.41536277574934</v>
       </c>
       <c r="E472" t="n">
-        <v>12.46348547262554</v>
+        <v>12.46348452188787</v>
       </c>
       <c r="F472" t="n">
         <v>4740900</v>
@@ -9892,16 +9892,16 @@
         <v>45341</v>
       </c>
       <c r="B474" t="n">
-        <v>12.77146434783936</v>
+        <v>12.77146339416504</v>
       </c>
       <c r="C474" t="n">
-        <v>12.85808239762144</v>
+        <v>12.85808143747915</v>
       </c>
       <c r="D474" t="n">
-        <v>12.53085651235945</v>
+        <v>12.53085557665187</v>
       </c>
       <c r="E474" t="n">
-        <v>12.54048012821565</v>
+        <v>12.54047919178945</v>
       </c>
       <c r="F474" t="n">
         <v>4786000</v>
@@ -9972,16 +9972,16 @@
         <v>45345</v>
       </c>
       <c r="B478" t="n">
-        <v>12.41536331176758</v>
+        <v>12.41536235809326</v>
       </c>
       <c r="C478" t="n">
-        <v>12.55010402320352</v>
+        <v>12.55010305917923</v>
       </c>
       <c r="D478" t="n">
-        <v>12.41536331176758</v>
+        <v>12.41536235809326</v>
       </c>
       <c r="E478" t="n">
-        <v>12.52123134141225</v>
+        <v>12.52123037960578</v>
       </c>
       <c r="F478" t="n">
         <v>4574300</v>
@@ -9992,16 +9992,16 @@
         <v>45348</v>
       </c>
       <c r="B479" t="n">
-        <v>12.35761737823486</v>
+        <v>12.35761833190918</v>
       </c>
       <c r="C479" t="n">
-        <v>12.48273355068785</v>
+        <v>12.48273451401776</v>
       </c>
       <c r="D479" t="n">
-        <v>12.3383683126978</v>
+        <v>12.33836926488661</v>
       </c>
       <c r="E479" t="n">
-        <v>12.45385995238227</v>
+        <v>12.45386091348391</v>
       </c>
       <c r="F479" t="n">
         <v>6964500</v>
@@ -22092,19 +22092,19 @@
         <v>46231</v>
       </c>
       <c r="B1084" t="n">
-        <v>11.42</v>
+        <v>11.45</v>
       </c>
       <c r="C1084" t="n">
         <v>11.72</v>
       </c>
       <c r="D1084" t="n">
-        <v>11.41</v>
+        <v>11.38</v>
       </c>
       <c r="E1084" t="n">
         <v>11.53</v>
       </c>
       <c r="F1084" t="n">
-        <v>896400</v>
+        <v>1564600</v>
       </c>
     </row>
   </sheetData>

--- a/database/AURE3.xlsx
+++ b/database/AURE3.xlsx
@@ -452,16 +452,16 @@
         <v>44648</v>
       </c>
       <c r="B2" t="n">
-        <v>12.75723266601562</v>
+        <v>12.75723171234131</v>
       </c>
       <c r="C2" t="n">
-        <v>13.06838439275972</v>
+        <v>13.06838341582507</v>
       </c>
       <c r="D2" t="n">
-        <v>12.02602573724489</v>
+        <v>12.02602483823237</v>
       </c>
       <c r="E2" t="n">
-        <v>13.06838439275972</v>
+        <v>13.06838341582507</v>
       </c>
       <c r="F2" t="n">
         <v>5237900</v>
@@ -492,16 +492,16 @@
         <v>44650</v>
       </c>
       <c r="B4" t="n">
-        <v>12.38385105133057</v>
+        <v>12.38384914398193</v>
       </c>
       <c r="C4" t="n">
-        <v>13.04504942238897</v>
+        <v>13.04504741320321</v>
       </c>
       <c r="D4" t="n">
-        <v>12.30606274584925</v>
+        <v>12.3060608504815</v>
       </c>
       <c r="E4" t="n">
-        <v>12.92836770601126</v>
+        <v>12.9283657147967</v>
       </c>
       <c r="F4" t="n">
         <v>4408600</v>
@@ -612,16 +612,16 @@
         <v>44658</v>
       </c>
       <c r="B10" t="n">
-        <v>12.44608020782471</v>
+        <v>12.44608116149902</v>
       </c>
       <c r="C10" t="n">
-        <v>12.71833850910855</v>
+        <v>12.71833948364451</v>
       </c>
       <c r="D10" t="n">
-        <v>12.20493707738666</v>
+        <v>12.20493801258351</v>
       </c>
       <c r="E10" t="n">
-        <v>12.32161952444153</v>
+        <v>12.32162046857911</v>
       </c>
       <c r="F10" t="n">
         <v>3223900</v>
@@ -672,16 +672,16 @@
         <v>44663</v>
       </c>
       <c r="B13" t="n">
-        <v>12.24383354187012</v>
+        <v>12.24383163452148</v>
       </c>
       <c r="C13" t="n">
-        <v>12.64055260156177</v>
+        <v>12.64055063241211</v>
       </c>
       <c r="D13" t="n">
-        <v>12.21271836514005</v>
+        <v>12.21271646263855</v>
       </c>
       <c r="E13" t="n">
-        <v>12.48497597606709</v>
+        <v>12.4849740311532</v>
       </c>
       <c r="F13" t="n">
         <v>2267700</v>
@@ -732,16 +732,16 @@
         <v>44669</v>
       </c>
       <c r="B16" t="n">
-        <v>12.45386028289795</v>
+        <v>12.45385932922363</v>
       </c>
       <c r="C16" t="n">
-        <v>12.45386028289795</v>
+        <v>12.45385932922363</v>
       </c>
       <c r="D16" t="n">
-        <v>11.92490159008608</v>
+        <v>11.92490067691762</v>
       </c>
       <c r="E16" t="n">
-        <v>12.10381439459067</v>
+        <v>12.10381346772168</v>
       </c>
       <c r="F16" t="n">
         <v>3931100</v>
@@ -772,16 +772,16 @@
         <v>44671</v>
       </c>
       <c r="B18" t="n">
-        <v>12.0571403503418</v>
+        <v>12.05714130401611</v>
       </c>
       <c r="C18" t="n">
-        <v>12.2127162064935</v>
+        <v>12.21271717247328</v>
       </c>
       <c r="D18" t="n">
-        <v>11.95601585838214</v>
+        <v>11.95601680405789</v>
       </c>
       <c r="E18" t="n">
-        <v>12.07269830687907</v>
+        <v>12.07269926178396</v>
       </c>
       <c r="F18" t="n">
         <v>2798400</v>
@@ -812,16 +812,16 @@
         <v>44676</v>
       </c>
       <c r="B20" t="n">
-        <v>12.39162826538086</v>
+        <v>12.39162921905518</v>
       </c>
       <c r="C20" t="n">
-        <v>12.39162826538086</v>
+        <v>12.39162921905518</v>
       </c>
       <c r="D20" t="n">
-        <v>11.90156379107179</v>
+        <v>11.90156470703017</v>
       </c>
       <c r="E20" t="n">
-        <v>12.11936997681666</v>
+        <v>12.11937090953766</v>
       </c>
       <c r="F20" t="n">
         <v>2683100</v>
@@ -832,16 +832,16 @@
         <v>44677</v>
       </c>
       <c r="B21" t="n">
-        <v>11.95601654052734</v>
+        <v>11.95601558685303</v>
       </c>
       <c r="C21" t="n">
-        <v>12.4383020930363</v>
+        <v>12.43830110089237</v>
       </c>
       <c r="D21" t="n">
-        <v>11.86267102151054</v>
+        <v>11.86267007528195</v>
       </c>
       <c r="E21" t="n">
-        <v>12.32939935843881</v>
+        <v>12.32939837498153</v>
       </c>
       <c r="F21" t="n">
         <v>2627000</v>
@@ -852,16 +852,16 @@
         <v>44678</v>
       </c>
       <c r="B22" t="n">
-        <v>12.0571403503418</v>
+        <v>12.05714130401611</v>
       </c>
       <c r="C22" t="n">
-        <v>12.06491932861043</v>
+        <v>12.06492028290003</v>
       </c>
       <c r="D22" t="n">
-        <v>11.83155517346078</v>
+        <v>11.83155610929216</v>
       </c>
       <c r="E22" t="n">
-        <v>12.04936137207316</v>
+        <v>12.04936232513219</v>
       </c>
       <c r="F22" t="n">
         <v>2401400</v>
@@ -912,16 +912,16 @@
         <v>44683</v>
       </c>
       <c r="B25" t="n">
-        <v>11.1703577041626</v>
+        <v>11.17035675048828</v>
       </c>
       <c r="C25" t="n">
-        <v>11.47373120303561</v>
+        <v>11.47373022346064</v>
       </c>
       <c r="D25" t="n">
-        <v>10.96033046789994</v>
+        <v>10.96032953215679</v>
       </c>
       <c r="E25" t="n">
-        <v>11.42705807173043</v>
+        <v>11.4270570961402</v>
       </c>
       <c r="F25" t="n">
         <v>2883200</v>
@@ -972,16 +972,16 @@
         <v>44686</v>
       </c>
       <c r="B28" t="n">
-        <v>11.28714752197266</v>
+        <v>11.28714847564697</v>
       </c>
       <c r="C28" t="n">
-        <v>11.62396063303483</v>
+        <v>11.62396161516718</v>
       </c>
       <c r="D28" t="n">
-        <v>11.14615584813277</v>
+        <v>11.14615678989441</v>
       </c>
       <c r="E28" t="n">
-        <v>11.61612759626606</v>
+        <v>11.61612857773658</v>
       </c>
       <c r="F28" t="n">
         <v>3065700</v>
@@ -1012,16 +1012,16 @@
         <v>44690</v>
       </c>
       <c r="B30" t="n">
-        <v>11.07566070556641</v>
+        <v>11.07566165924072</v>
       </c>
       <c r="C30" t="n">
-        <v>11.13049046868818</v>
+        <v>11.13049142708364</v>
       </c>
       <c r="D30" t="n">
-        <v>10.80934343269006</v>
+        <v>10.80934436343302</v>
       </c>
       <c r="E30" t="n">
-        <v>10.99733183225001</v>
+        <v>10.99733277917979</v>
       </c>
       <c r="F30" t="n">
         <v>1545300</v>
@@ -1072,16 +1072,16 @@
         <v>44693</v>
       </c>
       <c r="B33" t="n">
-        <v>11.15398979187012</v>
+        <v>11.1539888381958</v>
       </c>
       <c r="C33" t="n">
-        <v>11.27931540236311</v>
+        <v>11.27931443797336</v>
       </c>
       <c r="D33" t="n">
-        <v>10.85634109344948</v>
+        <v>10.85634016522435</v>
       </c>
       <c r="E33" t="n">
-        <v>10.99733277875388</v>
+        <v>10.99733183847385</v>
       </c>
       <c r="F33" t="n">
         <v>1884700</v>
@@ -1132,16 +1132,16 @@
         <v>44698</v>
       </c>
       <c r="B36" t="n">
-        <v>11.56129741668701</v>
+        <v>11.56129837036133</v>
       </c>
       <c r="C36" t="n">
-        <v>11.74928581037311</v>
+        <v>11.74928677955431</v>
       </c>
       <c r="D36" t="n">
-        <v>11.35764295002734</v>
+        <v>11.3576438869025</v>
       </c>
       <c r="E36" t="n">
-        <v>11.35764295002734</v>
+        <v>11.3576438869025</v>
       </c>
       <c r="F36" t="n">
         <v>1389700</v>
@@ -1152,16 +1152,16 @@
         <v>44699</v>
       </c>
       <c r="B37" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C37" t="n">
-        <v>11.5926298208571</v>
+        <v>11.59262882548476</v>
       </c>
       <c r="D37" t="n">
-        <v>11.03649688106261</v>
+        <v>11.03649593344125</v>
       </c>
       <c r="E37" t="n">
-        <v>11.51430094319608</v>
+        <v>11.51429995454926</v>
       </c>
       <c r="F37" t="n">
         <v>1959900</v>
@@ -1192,16 +1192,16 @@
         <v>44701</v>
       </c>
       <c r="B39" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C39" t="n">
-        <v>11.34197786054158</v>
+        <v>11.34197688669085</v>
       </c>
       <c r="D39" t="n">
-        <v>10.86417379840811</v>
+        <v>10.86417286558284</v>
       </c>
       <c r="E39" t="n">
-        <v>11.34197786054158</v>
+        <v>11.34197688669085</v>
       </c>
       <c r="F39" t="n">
         <v>1777400</v>
@@ -1212,16 +1212,16 @@
         <v>44704</v>
       </c>
       <c r="B40" t="n">
-        <v>11.20882034301758</v>
+        <v>11.20881938934326</v>
       </c>
       <c r="C40" t="n">
-        <v>11.4359731995218</v>
+        <v>11.43597222652075</v>
       </c>
       <c r="D40" t="n">
-        <v>11.16182286543069</v>
+        <v>11.16182191575504</v>
       </c>
       <c r="E40" t="n">
-        <v>11.18532123072435</v>
+        <v>11.1853202790494</v>
       </c>
       <c r="F40" t="n">
         <v>1184600</v>
@@ -1232,16 +1232,16 @@
         <v>44705</v>
       </c>
       <c r="B41" t="n">
-        <v>11.21665191650391</v>
+        <v>11.21665096282959</v>
       </c>
       <c r="C41" t="n">
-        <v>11.22448495343431</v>
+        <v>11.22448399909401</v>
       </c>
       <c r="D41" t="n">
-        <v>11.00516514837963</v>
+        <v>11.00516421268657</v>
       </c>
       <c r="E41" t="n">
-        <v>11.09132631361552</v>
+        <v>11.09132537059677</v>
       </c>
       <c r="F41" t="n">
         <v>792900</v>
@@ -1272,16 +1272,16 @@
         <v>44707</v>
       </c>
       <c r="B43" t="n">
-        <v>11.25581550598145</v>
+        <v>11.25581645965576</v>
       </c>
       <c r="C43" t="n">
-        <v>11.44380389614828</v>
+        <v>11.44380486575034</v>
       </c>
       <c r="D43" t="n">
-        <v>11.20881878193947</v>
+        <v>11.20881973163188</v>
       </c>
       <c r="E43" t="n">
-        <v>11.33414437538402</v>
+        <v>11.33414533569493</v>
       </c>
       <c r="F43" t="n">
         <v>1248800</v>
@@ -1332,16 +1332,16 @@
         <v>44712</v>
       </c>
       <c r="B46" t="n">
-        <v>10.93466854095459</v>
+        <v>10.93466949462891</v>
       </c>
       <c r="C46" t="n">
-        <v>11.2088188382412</v>
+        <v>11.20881981582572</v>
       </c>
       <c r="D46" t="n">
-        <v>10.82500827264005</v>
+        <v>10.82500921675028</v>
       </c>
       <c r="E46" t="n">
-        <v>11.16965440334319</v>
+        <v>11.16965537751195</v>
       </c>
       <c r="F46" t="n">
         <v>9431500</v>
@@ -1352,16 +1352,16 @@
         <v>44713</v>
       </c>
       <c r="B47" t="n">
-        <v>10.73101425170898</v>
+        <v>10.7310152053833</v>
       </c>
       <c r="C47" t="n">
-        <v>10.94250175540008</v>
+        <v>10.94250272786947</v>
       </c>
       <c r="D47" t="n">
-        <v>10.66051841714529</v>
+        <v>10.66051936455458</v>
       </c>
       <c r="E47" t="n">
-        <v>10.94250175540008</v>
+        <v>10.94250272786947</v>
       </c>
       <c r="F47" t="n">
         <v>6323900</v>
@@ -1412,16 +1412,16 @@
         <v>44718</v>
       </c>
       <c r="B50" t="n">
-        <v>10.61352252960205</v>
+        <v>10.61352157592773</v>
       </c>
       <c r="C50" t="n">
-        <v>10.91117121735836</v>
+        <v>10.91117023693893</v>
       </c>
       <c r="D50" t="n">
-        <v>10.4568655220986</v>
+        <v>10.45686458250065</v>
       </c>
       <c r="E50" t="n">
-        <v>10.8171770128563</v>
+        <v>10.81717604088268</v>
       </c>
       <c r="F50" t="n">
         <v>3175000</v>
@@ -1492,16 +1492,16 @@
         <v>44722</v>
       </c>
       <c r="B54" t="n">
-        <v>10.48036289215088</v>
+        <v>10.4803638458252</v>
       </c>
       <c r="C54" t="n">
-        <v>10.98949830498279</v>
+        <v>10.98949930498655</v>
       </c>
       <c r="D54" t="n">
-        <v>10.3942017329484</v>
+        <v>10.39420267878237</v>
       </c>
       <c r="E54" t="n">
-        <v>10.98949830498279</v>
+        <v>10.98949930498655</v>
       </c>
       <c r="F54" t="n">
         <v>4538500</v>
@@ -1552,16 +1552,16 @@
         <v>44727</v>
       </c>
       <c r="B57" t="n">
-        <v>10.84067440032959</v>
+        <v>10.84067630767822</v>
       </c>
       <c r="C57" t="n">
-        <v>10.84850743674878</v>
+        <v>10.84850934547558</v>
       </c>
       <c r="D57" t="n">
-        <v>10.44119850694474</v>
+        <v>10.44120034400809</v>
       </c>
       <c r="E57" t="n">
-        <v>10.55085877581493</v>
+        <v>10.55086063217233</v>
       </c>
       <c r="F57" t="n">
         <v>3153700</v>
@@ -1712,16 +1712,16 @@
         <v>44740</v>
       </c>
       <c r="B65" t="n">
-        <v>10.61352252960205</v>
+        <v>10.61352157592773</v>
       </c>
       <c r="C65" t="n">
-        <v>10.86417374160756</v>
+        <v>10.86417276541107</v>
       </c>
       <c r="D65" t="n">
-        <v>10.47253084934918</v>
+        <v>10.47252990834362</v>
       </c>
       <c r="E65" t="n">
-        <v>10.5273606152255</v>
+        <v>10.52735966929324</v>
       </c>
       <c r="F65" t="n">
         <v>5362200</v>
@@ -1732,16 +1732,16 @@
         <v>44741</v>
       </c>
       <c r="B66" t="n">
-        <v>10.68401718139648</v>
+        <v>10.6840181350708</v>
       </c>
       <c r="C66" t="n">
-        <v>10.68401718139648</v>
+        <v>10.6840181350708</v>
       </c>
       <c r="D66" t="n">
-        <v>10.53519248057162</v>
+        <v>10.53519342096158</v>
       </c>
       <c r="E66" t="n">
-        <v>10.62918667461916</v>
+        <v>10.62918762339921</v>
       </c>
       <c r="F66" t="n">
         <v>1613700</v>
@@ -1772,16 +1772,16 @@
         <v>44743</v>
       </c>
       <c r="B68" t="n">
-        <v>10.68401718139648</v>
+        <v>10.6840181350708</v>
       </c>
       <c r="C68" t="n">
-        <v>10.84067417147572</v>
+        <v>10.84067513913352</v>
       </c>
       <c r="D68" t="n">
-        <v>10.54302551682544</v>
+        <v>10.54302645791459</v>
       </c>
       <c r="E68" t="n">
-        <v>10.72318086866671</v>
+        <v>10.72318182583684</v>
       </c>
       <c r="F68" t="n">
         <v>2696600</v>
@@ -1852,16 +1852,16 @@
         <v>44749</v>
       </c>
       <c r="B72" t="n">
-        <v>11.04432964324951</v>
+        <v>11.04433059692383</v>
       </c>
       <c r="C72" t="n">
-        <v>11.16182220981619</v>
+        <v>11.16182317363595</v>
       </c>
       <c r="D72" t="n">
-        <v>10.62135535781014</v>
+        <v>10.62135627496076</v>
       </c>
       <c r="E72" t="n">
-        <v>10.7858453992032</v>
+        <v>10.78584633055749</v>
       </c>
       <c r="F72" t="n">
         <v>2931100</v>
@@ -1872,16 +1872,16 @@
         <v>44750</v>
       </c>
       <c r="B73" t="n">
-        <v>11.15398979187012</v>
+        <v>11.1539888381958</v>
       </c>
       <c r="C73" t="n">
-        <v>11.31064680498636</v>
+        <v>11.31064583791775</v>
       </c>
       <c r="D73" t="n">
-        <v>11.00516581615958</v>
+        <v>11.00516487520982</v>
       </c>
       <c r="E73" t="n">
-        <v>11.00516581615958</v>
+        <v>11.00516487520982</v>
       </c>
       <c r="F73" t="n">
         <v>1922000</v>
@@ -1892,16 +1892,16 @@
         <v>44753</v>
       </c>
       <c r="B74" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C74" t="n">
-        <v>11.18532085221909</v>
+        <v>11.18531989181933</v>
       </c>
       <c r="D74" t="n">
-        <v>10.83284239674361</v>
+        <v>10.83284146660853</v>
       </c>
       <c r="E74" t="n">
-        <v>11.0599952455611</v>
+        <v>11.05999429592211</v>
       </c>
       <c r="F74" t="n">
         <v>1881000</v>
@@ -1912,16 +1912,16 @@
         <v>44754</v>
       </c>
       <c r="B75" t="n">
-        <v>11.14615535736084</v>
+        <v>11.14615631103516</v>
       </c>
       <c r="C75" t="n">
-        <v>11.22448422760069</v>
+        <v>11.22448518797689</v>
       </c>
       <c r="D75" t="n">
-        <v>10.99733140030449</v>
+        <v>10.99733234124531</v>
       </c>
       <c r="E75" t="n">
-        <v>11.10699166924038</v>
+        <v>11.10699261956382</v>
       </c>
       <c r="F75" t="n">
         <v>1673000</v>
@@ -1992,16 +1992,16 @@
         <v>44760</v>
       </c>
       <c r="B79" t="n">
-        <v>10.73101425170898</v>
+        <v>10.7310152053833</v>
       </c>
       <c r="C79" t="n">
-        <v>11.00516455345681</v>
+        <v>11.0051655314951</v>
       </c>
       <c r="D79" t="n">
-        <v>10.59002332958107</v>
+        <v>10.5900242707254</v>
       </c>
       <c r="E79" t="n">
-        <v>10.80934312277964</v>
+        <v>10.80934408341511</v>
       </c>
       <c r="F79" t="n">
         <v>1463400</v>
@@ -2112,16 +2112,16 @@
         <v>44768</v>
       </c>
       <c r="B85" t="n">
-        <v>11.27148246765137</v>
+        <v>11.27148342132568</v>
       </c>
       <c r="C85" t="n">
-        <v>11.38114199706455</v>
+        <v>11.3811429600171</v>
       </c>
       <c r="D85" t="n">
-        <v>11.16965522819662</v>
+        <v>11.16965617325538</v>
       </c>
       <c r="E85" t="n">
-        <v>11.19315359207094</v>
+        <v>11.19315453911789</v>
       </c>
       <c r="F85" t="n">
         <v>1661400</v>
@@ -2152,16 +2152,16 @@
         <v>44770</v>
       </c>
       <c r="B87" t="n">
-        <v>10.96599960327148</v>
+        <v>10.9660005569458</v>
       </c>
       <c r="C87" t="n">
-        <v>11.33414408482687</v>
+        <v>11.33414507051741</v>
       </c>
       <c r="D87" t="n">
-        <v>10.82500794076103</v>
+        <v>10.8250088821738</v>
       </c>
       <c r="E87" t="n">
-        <v>11.31064497640883</v>
+        <v>11.31064596005574</v>
       </c>
       <c r="F87" t="n">
         <v>2911900</v>
@@ -2192,16 +2192,16 @@
         <v>44774</v>
       </c>
       <c r="B89" t="n">
-        <v>10.95033550262451</v>
+        <v>10.9503345489502</v>
       </c>
       <c r="C89" t="n">
-        <v>11.20882051276761</v>
+        <v>11.20881953658161</v>
       </c>
       <c r="D89" t="n">
-        <v>10.78584619607824</v>
+        <v>10.78584525672945</v>
       </c>
       <c r="E89" t="n">
-        <v>11.0599957873216</v>
+        <v>11.05999482409687</v>
       </c>
       <c r="F89" t="n">
         <v>3205600</v>
@@ -2232,16 +2232,16 @@
         <v>44776</v>
       </c>
       <c r="B91" t="n">
-        <v>10.88767147064209</v>
+        <v>10.88767242431641</v>
       </c>
       <c r="C91" t="n">
-        <v>11.02083010599954</v>
+        <v>11.02083107133751</v>
       </c>
       <c r="D91" t="n">
-        <v>10.70751610927583</v>
+        <v>10.70751704716995</v>
       </c>
       <c r="E91" t="n">
-        <v>10.83284170796531</v>
+        <v>10.83284265683698</v>
       </c>
       <c r="F91" t="n">
         <v>3133200</v>
@@ -2272,16 +2272,16 @@
         <v>44778</v>
       </c>
       <c r="B93" t="n">
-        <v>10.96599960327148</v>
+        <v>10.9660005569458</v>
       </c>
       <c r="C93" t="n">
-        <v>11.16965406089782</v>
+        <v>11.16965503228325</v>
       </c>
       <c r="D93" t="n">
-        <v>10.93466820571354</v>
+        <v>10.93466915666308</v>
       </c>
       <c r="E93" t="n">
-        <v>11.16965406089782</v>
+        <v>11.16965503228325</v>
       </c>
       <c r="F93" t="n">
         <v>1948700</v>
@@ -2292,16 +2292,16 @@
         <v>44781</v>
       </c>
       <c r="B94" t="n">
-        <v>10.97383403778076</v>
+        <v>10.97383308410645</v>
       </c>
       <c r="C94" t="n">
-        <v>11.10699268111997</v>
+        <v>11.10699171587358</v>
       </c>
       <c r="D94" t="n">
-        <v>10.87200679599199</v>
+        <v>10.8720058511669</v>
       </c>
       <c r="E94" t="n">
-        <v>11.02866380374413</v>
+        <v>11.02866284530486</v>
       </c>
       <c r="F94" t="n">
         <v>2949000</v>
@@ -2312,16 +2312,16 @@
         <v>44782</v>
       </c>
       <c r="B95" t="n">
-        <v>10.92683696746826</v>
+        <v>10.92683601379395</v>
       </c>
       <c r="C95" t="n">
-        <v>11.0599956157492</v>
+        <v>11.05999465045304</v>
       </c>
       <c r="D95" t="n">
-        <v>10.67618574576276</v>
+        <v>10.67618481396482</v>
       </c>
       <c r="E95" t="n">
-        <v>10.98166748246601</v>
+        <v>10.98166652400619</v>
       </c>
       <c r="F95" t="n">
         <v>1743500</v>
@@ -2332,16 +2332,16 @@
         <v>44783</v>
       </c>
       <c r="B96" t="n">
-        <v>11.05216121673584</v>
+        <v>11.05216217041016</v>
       </c>
       <c r="C96" t="n">
-        <v>11.16965452268523</v>
+        <v>11.16965548649786</v>
       </c>
       <c r="D96" t="n">
-        <v>10.88767118600627</v>
+        <v>10.88767212548699</v>
       </c>
       <c r="E96" t="n">
-        <v>10.92683562132274</v>
+        <v>10.9268365641829</v>
       </c>
       <c r="F96" t="n">
         <v>2933600</v>
@@ -2352,16 +2352,16 @@
         <v>44784</v>
       </c>
       <c r="B97" t="n">
-        <v>10.89550399780273</v>
+        <v>10.89550590515137</v>
       </c>
       <c r="C97" t="n">
-        <v>11.10699149595105</v>
+        <v>11.10699344032233</v>
       </c>
       <c r="D97" t="n">
-        <v>10.8328412013883</v>
+        <v>10.83284309776729</v>
       </c>
       <c r="E97" t="n">
-        <v>11.0599940251405</v>
+        <v>11.05999596128448</v>
       </c>
       <c r="F97" t="n">
         <v>1665400</v>
@@ -2392,16 +2392,16 @@
         <v>44788</v>
       </c>
       <c r="B99" t="n">
-        <v>11.21665191650391</v>
+        <v>11.21665096282959</v>
       </c>
       <c r="C99" t="n">
-        <v>11.3106461186702</v>
+        <v>11.3106451570042</v>
       </c>
       <c r="D99" t="n">
-        <v>10.92683627307463</v>
+        <v>10.92683534404133</v>
       </c>
       <c r="E99" t="n">
-        <v>10.99733211144923</v>
+        <v>10.99733117642216</v>
       </c>
       <c r="F99" t="n">
         <v>3450900</v>
@@ -2412,16 +2412,16 @@
         <v>44789</v>
       </c>
       <c r="B100" t="n">
-        <v>11.04432964324951</v>
+        <v>11.04433059692383</v>
       </c>
       <c r="C100" t="n">
-        <v>11.29498085032484</v>
+        <v>11.2949818256428</v>
       </c>
       <c r="D100" t="n">
-        <v>10.94250240362528</v>
+        <v>10.94250334850685</v>
       </c>
       <c r="E100" t="n">
-        <v>11.25581641246944</v>
+        <v>11.25581738440557</v>
       </c>
       <c r="F100" t="n">
         <v>1185300</v>
@@ -2452,16 +2452,16 @@
         <v>44791</v>
       </c>
       <c r="B102" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="C102" t="n">
-        <v>11.37330994384684</v>
+        <v>11.37330897550059</v>
       </c>
       <c r="D102" t="n">
-        <v>11.09915962060828</v>
+        <v>11.09915867560374</v>
       </c>
       <c r="E102" t="n">
-        <v>11.27931499239396</v>
+        <v>11.27931403205064</v>
       </c>
       <c r="F102" t="n">
         <v>2180500</v>
@@ -2532,16 +2532,16 @@
         <v>44797</v>
       </c>
       <c r="B106" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C106" t="n">
-        <v>11.3968083737041</v>
+        <v>11.39680739514549</v>
       </c>
       <c r="D106" t="n">
-        <v>11.09915968439161</v>
+        <v>11.09915873138986</v>
       </c>
       <c r="E106" t="n">
-        <v>11.2244852910496</v>
+        <v>11.22448432728707</v>
       </c>
       <c r="F106" t="n">
         <v>2116800</v>
@@ -2552,16 +2552,16 @@
         <v>44798</v>
       </c>
       <c r="B107" t="n">
-        <v>11.04432964324951</v>
+        <v>11.04433059692383</v>
       </c>
       <c r="C107" t="n">
-        <v>11.22448501158502</v>
+        <v>11.22448598081569</v>
       </c>
       <c r="D107" t="n">
-        <v>10.95033469359675</v>
+        <v>10.95033563915463</v>
       </c>
       <c r="E107" t="n">
-        <v>11.20881968464257</v>
+        <v>11.20882065252055</v>
       </c>
       <c r="F107" t="n">
         <v>2435800</v>
@@ -2572,16 +2572,16 @@
         <v>44799</v>
       </c>
       <c r="B108" t="n">
-        <v>11.05216121673584</v>
+        <v>11.05216217041016</v>
       </c>
       <c r="C108" t="n">
-        <v>11.17748755914842</v>
+        <v>11.17748852363695</v>
       </c>
       <c r="D108" t="n">
-        <v>10.95816702017601</v>
+        <v>10.95816796573971</v>
       </c>
       <c r="E108" t="n">
-        <v>11.05216121673584</v>
+        <v>11.05216217041016</v>
       </c>
       <c r="F108" t="n">
         <v>1356300</v>
@@ -2612,16 +2612,16 @@
         <v>44803</v>
       </c>
       <c r="B110" t="n">
-        <v>11.01299858093262</v>
+        <v>11.0129976272583</v>
       </c>
       <c r="C110" t="n">
-        <v>11.16182255295894</v>
+        <v>11.16182158639716</v>
       </c>
       <c r="D110" t="n">
-        <v>10.93466970281379</v>
+        <v>10.93466875592239</v>
       </c>
       <c r="E110" t="n">
-        <v>11.11482507668773</v>
+        <v>11.11482411419572</v>
       </c>
       <c r="F110" t="n">
         <v>1284900</v>
@@ -2812,16 +2812,16 @@
         <v>44818</v>
       </c>
       <c r="B120" t="n">
-        <v>11.20882034301758</v>
+        <v>11.20881938934326</v>
       </c>
       <c r="C120" t="n">
-        <v>11.42030712465965</v>
+        <v>11.42030615299151</v>
       </c>
       <c r="D120" t="n">
-        <v>11.02866421710068</v>
+        <v>11.02866327875449</v>
       </c>
       <c r="E120" t="n">
-        <v>11.2009873055865</v>
+        <v>11.20098635257864</v>
       </c>
       <c r="F120" t="n">
         <v>1856400</v>
@@ -2852,16 +2852,16 @@
         <v>44820</v>
       </c>
       <c r="B122" t="n">
-        <v>11.16965579986572</v>
+        <v>11.16965484619141</v>
       </c>
       <c r="C122" t="n">
-        <v>11.35764421448068</v>
+        <v>11.35764324475576</v>
       </c>
       <c r="D122" t="n">
-        <v>11.02866411540472</v>
+        <v>11.02866317376839</v>
       </c>
       <c r="E122" t="n">
-        <v>11.22448556737853</v>
+        <v>11.2244846090228</v>
       </c>
       <c r="F122" t="n">
         <v>3523100</v>
@@ -2872,16 +2872,16 @@
         <v>44823</v>
       </c>
       <c r="B123" t="n">
-        <v>11.28714752197266</v>
+        <v>11.28714847564697</v>
       </c>
       <c r="C123" t="n">
-        <v>11.43597223258132</v>
+        <v>11.43597319883014</v>
       </c>
       <c r="D123" t="n">
-        <v>11.11482444805718</v>
+        <v>11.11482538717157</v>
       </c>
       <c r="E123" t="n">
-        <v>11.11482444805718</v>
+        <v>11.11482538717157</v>
       </c>
       <c r="F123" t="n">
         <v>1858600</v>
@@ -2892,16 +2892,16 @@
         <v>44824</v>
       </c>
       <c r="B124" t="n">
-        <v>11.13049030303955</v>
+        <v>11.13049125671387</v>
       </c>
       <c r="C124" t="n">
-        <v>11.35764313587711</v>
+        <v>11.35764410901417</v>
       </c>
       <c r="D124" t="n">
-        <v>11.08349283034925</v>
+        <v>11.08349377999676</v>
       </c>
       <c r="E124" t="n">
-        <v>11.28714730034141</v>
+        <v>11.28714826743829</v>
       </c>
       <c r="F124" t="n">
         <v>1310600</v>
@@ -2952,16 +2952,16 @@
         <v>44827</v>
       </c>
       <c r="B127" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="C127" t="n">
-        <v>11.30281410375695</v>
+        <v>11.30281314141286</v>
       </c>
       <c r="D127" t="n">
-        <v>11.07566125624483</v>
+        <v>11.07566031324099</v>
       </c>
       <c r="E127" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="F127" t="n">
         <v>2444100</v>
@@ -2992,16 +2992,16 @@
         <v>44831</v>
       </c>
       <c r="B129" t="n">
-        <v>10.90333843231201</v>
+        <v>10.9033374786377</v>
       </c>
       <c r="C129" t="n">
-        <v>11.04433011582452</v>
+        <v>11.04432914981819</v>
       </c>
       <c r="D129" t="n">
-        <v>10.77017978610565</v>
+        <v>10.77017884407822</v>
       </c>
       <c r="E129" t="n">
-        <v>11.04433011582452</v>
+        <v>11.04432914981819</v>
       </c>
       <c r="F129" t="n">
         <v>2130200</v>
@@ -3052,16 +3052,16 @@
         <v>44834</v>
       </c>
       <c r="B132" t="n">
-        <v>10.61352252960205</v>
+        <v>10.61352157592773</v>
       </c>
       <c r="C132" t="n">
-        <v>10.74668117272986</v>
+        <v>10.74668020709063</v>
       </c>
       <c r="D132" t="n">
-        <v>10.59785645535194</v>
+        <v>10.59785550308529</v>
       </c>
       <c r="E132" t="n">
-        <v>10.70751673410412</v>
+        <v>10.70751577198399</v>
       </c>
       <c r="F132" t="n">
         <v>4019300</v>
@@ -3072,16 +3072,16 @@
         <v>44837</v>
       </c>
       <c r="B133" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="C133" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="D133" t="n">
-        <v>10.62918785134206</v>
+        <v>10.62918694635185</v>
       </c>
       <c r="E133" t="n">
-        <v>10.74668116715839</v>
+        <v>10.74668025216456</v>
       </c>
       <c r="F133" t="n">
         <v>2250700</v>
@@ -3112,16 +3112,16 @@
         <v>44839</v>
       </c>
       <c r="B135" t="n">
-        <v>10.97383403778076</v>
+        <v>10.97383308410645</v>
       </c>
       <c r="C135" t="n">
-        <v>11.20881992290874</v>
+        <v>11.20881894881312</v>
       </c>
       <c r="D135" t="n">
-        <v>10.85634072171701</v>
+        <v>10.85633977825337</v>
       </c>
       <c r="E135" t="n">
-        <v>11.20881992290874</v>
+        <v>11.20881894881312</v>
       </c>
       <c r="F135" t="n">
         <v>5244200</v>
@@ -3152,16 +3152,16 @@
         <v>44841</v>
       </c>
       <c r="B137" t="n">
-        <v>11.02866458892822</v>
+        <v>11.02866363525391</v>
       </c>
       <c r="C137" t="n">
-        <v>11.15399020405247</v>
+        <v>11.15398923954096</v>
       </c>
       <c r="D137" t="n">
-        <v>10.9425034152802</v>
+        <v>10.94250246905644</v>
       </c>
       <c r="E137" t="n">
-        <v>10.98166785675642</v>
+        <v>10.98166690714602</v>
       </c>
       <c r="F137" t="n">
         <v>7588600</v>
@@ -3172,16 +3172,16 @@
         <v>44844</v>
       </c>
       <c r="B138" t="n">
-        <v>11.07566070556641</v>
+        <v>11.07566165924072</v>
       </c>
       <c r="C138" t="n">
-        <v>11.35764330490633</v>
+        <v>11.35764428286087</v>
       </c>
       <c r="D138" t="n">
-        <v>11.01299790571309</v>
+        <v>11.0129988539918</v>
       </c>
       <c r="E138" t="n">
-        <v>11.07566070556641</v>
+        <v>11.07566165924072</v>
       </c>
       <c r="F138" t="n">
         <v>2000500</v>
@@ -3252,16 +3252,16 @@
         <v>44851</v>
       </c>
       <c r="B142" t="n">
-        <v>11.15398979187012</v>
+        <v>11.1539888381958</v>
       </c>
       <c r="C142" t="n">
-        <v>11.20098726930477</v>
+        <v>11.20098631161214</v>
       </c>
       <c r="D142" t="n">
-        <v>10.78584599779684</v>
+        <v>10.78584507559909</v>
       </c>
       <c r="E142" t="n">
-        <v>10.86417413085518</v>
+        <v>10.86417320196032</v>
       </c>
       <c r="F142" t="n">
         <v>6971700</v>
@@ -3272,16 +3272,16 @@
         <v>44852</v>
       </c>
       <c r="B143" t="n">
-        <v>11.27148246765137</v>
+        <v>11.27148342132568</v>
       </c>
       <c r="C143" t="n">
-        <v>11.37330970710612</v>
+        <v>11.37331066939599</v>
       </c>
       <c r="D143" t="n">
-        <v>11.06782798874186</v>
+        <v>11.06782892518508</v>
       </c>
       <c r="E143" t="n">
-        <v>11.20881966598683</v>
+        <v>11.20882061435928</v>
       </c>
       <c r="F143" t="n">
         <v>2646800</v>
@@ -3312,16 +3312,16 @@
         <v>44854</v>
       </c>
       <c r="B145" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C145" t="n">
-        <v>10.98166755090811</v>
+        <v>10.98166658413194</v>
       </c>
       <c r="D145" t="n">
-        <v>10.39420318612486</v>
+        <v>10.39420227106638</v>
       </c>
       <c r="E145" t="n">
-        <v>10.5743585660986</v>
+        <v>10.57435763518006</v>
       </c>
       <c r="F145" t="n">
         <v>7194300</v>
@@ -3332,16 +3332,16 @@
         <v>44855</v>
       </c>
       <c r="B146" t="n">
-        <v>11.16965579986572</v>
+        <v>11.16965484619141</v>
       </c>
       <c r="C146" t="n">
-        <v>11.16965579986572</v>
+        <v>11.16965484619141</v>
       </c>
       <c r="D146" t="n">
-        <v>10.75451378384157</v>
+        <v>10.75451286561242</v>
       </c>
       <c r="E146" t="n">
-        <v>10.75451378384157</v>
+        <v>10.75451286561242</v>
       </c>
       <c r="F146" t="n">
         <v>9489900</v>
@@ -3412,16 +3412,16 @@
         <v>44861</v>
       </c>
       <c r="B150" t="n">
-        <v>11.35764312744141</v>
+        <v>11.35764408111572</v>
       </c>
       <c r="C150" t="n">
-        <v>11.63179343276565</v>
+        <v>11.63179440945972</v>
       </c>
       <c r="D150" t="n">
-        <v>11.27148196573925</v>
+        <v>11.27148291217882</v>
       </c>
       <c r="E150" t="n">
-        <v>11.42813896292475</v>
+        <v>11.42813992251844</v>
       </c>
       <c r="F150" t="n">
         <v>4207900</v>
@@ -3432,16 +3432,16 @@
         <v>44862</v>
       </c>
       <c r="B151" t="n">
-        <v>11.49080181121826</v>
+        <v>11.49080276489258</v>
       </c>
       <c r="C151" t="n">
-        <v>11.63962577243467</v>
+        <v>11.63962673846057</v>
       </c>
       <c r="D151" t="n">
-        <v>11.2244845413578</v>
+        <v>11.22448547292922</v>
       </c>
       <c r="E151" t="n">
-        <v>11.32631177671618</v>
+        <v>11.32631271673871</v>
       </c>
       <c r="F151" t="n">
         <v>2887600</v>
@@ -3472,16 +3472,16 @@
         <v>44866</v>
       </c>
       <c r="B153" t="n">
-        <v>11.56913185119629</v>
+        <v>11.56913089752197</v>
       </c>
       <c r="C153" t="n">
-        <v>11.80411699819995</v>
+        <v>11.80411602515518</v>
       </c>
       <c r="D153" t="n">
-        <v>11.34981128506018</v>
+        <v>11.34981034946504</v>
       </c>
       <c r="E153" t="n">
-        <v>11.67879138726478</v>
+        <v>11.67879042455094</v>
       </c>
       <c r="F153" t="n">
         <v>3576300</v>
@@ -3512,16 +3512,16 @@
         <v>44869</v>
       </c>
       <c r="B155" t="n">
-        <v>11.67095756530762</v>
+        <v>11.67095851898193</v>
       </c>
       <c r="C155" t="n">
-        <v>11.87461204288736</v>
+        <v>11.87461301320299</v>
       </c>
       <c r="D155" t="n">
-        <v>11.64745920158673</v>
+        <v>11.64746015334091</v>
       </c>
       <c r="E155" t="n">
-        <v>11.7492864403766</v>
+        <v>11.74928740045144</v>
       </c>
       <c r="F155" t="n">
         <v>2161500</v>
@@ -3532,16 +3532,16 @@
         <v>44872</v>
       </c>
       <c r="B156" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="C156" t="n">
-        <v>11.65529255720685</v>
+        <v>11.65529156485204</v>
       </c>
       <c r="D156" t="n">
-        <v>11.12265798497174</v>
+        <v>11.1226570379665</v>
       </c>
       <c r="E156" t="n">
-        <v>11.60829508148041</v>
+        <v>11.60829409312706</v>
       </c>
       <c r="F156" t="n">
         <v>3276500</v>
@@ -3612,16 +3612,16 @@
         <v>44876</v>
       </c>
       <c r="B160" t="n">
-        <v>10.79367828369141</v>
+        <v>10.79367733001709</v>
       </c>
       <c r="C160" t="n">
-        <v>10.85634108891171</v>
+        <v>10.85634012970083</v>
       </c>
       <c r="D160" t="n">
-        <v>10.53519402540776</v>
+        <v>10.5351930945718</v>
       </c>
       <c r="E160" t="n">
-        <v>10.78584599328854</v>
+        <v>10.78584504030624</v>
       </c>
       <c r="F160" t="n">
         <v>3291200</v>
@@ -3632,16 +3632,16 @@
         <v>44879</v>
       </c>
       <c r="B161" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C161" t="n">
-        <v>10.9660014759541</v>
+        <v>10.9660005105571</v>
       </c>
       <c r="D161" t="n">
-        <v>10.71535025268644</v>
+        <v>10.71534930935563</v>
       </c>
       <c r="E161" t="n">
-        <v>10.94250311052265</v>
+        <v>10.94250214719434</v>
       </c>
       <c r="F161" t="n">
         <v>1203700</v>
@@ -3652,16 +3652,16 @@
         <v>44881</v>
       </c>
       <c r="B162" t="n">
-        <v>10.90333843231201</v>
+        <v>10.9033374786377</v>
       </c>
       <c r="C162" t="n">
-        <v>10.90333843231201</v>
+        <v>10.9033374786377</v>
       </c>
       <c r="D162" t="n">
-        <v>10.59785670036809</v>
+        <v>10.59785577341312</v>
       </c>
       <c r="E162" t="n">
-        <v>10.86417399278081</v>
+        <v>10.86417304253206</v>
       </c>
       <c r="F162" t="n">
         <v>5270300</v>
@@ -3752,16 +3752,16 @@
         <v>44888</v>
       </c>
       <c r="B167" t="n">
-        <v>10.56652545928955</v>
+        <v>10.56652450561523</v>
       </c>
       <c r="C167" t="n">
-        <v>10.81717742791213</v>
+        <v>10.8171764516154</v>
       </c>
       <c r="D167" t="n">
-        <v>10.51952872873502</v>
+        <v>10.51952777930236</v>
       </c>
       <c r="E167" t="n">
-        <v>10.80934439048652</v>
+        <v>10.80934341489675</v>
       </c>
       <c r="F167" t="n">
         <v>4669400</v>
@@ -3772,16 +3772,16 @@
         <v>44889</v>
       </c>
       <c r="B168" t="n">
-        <v>10.95033550262451</v>
+        <v>10.9503345489502</v>
       </c>
       <c r="C168" t="n">
-        <v>11.09132719052083</v>
+        <v>11.09132622456742</v>
       </c>
       <c r="D168" t="n">
-        <v>10.56652562668407</v>
+        <v>10.56652470643609</v>
       </c>
       <c r="E168" t="n">
-        <v>10.56652562668407</v>
+        <v>10.56652470643609</v>
       </c>
       <c r="F168" t="n">
         <v>1852400</v>
@@ -3792,16 +3792,16 @@
         <v>44890</v>
       </c>
       <c r="B169" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C169" t="n">
-        <v>11.03649731924802</v>
+        <v>11.03649634764489</v>
       </c>
       <c r="D169" t="n">
-        <v>10.71535025268644</v>
+        <v>10.71534930935563</v>
       </c>
       <c r="E169" t="n">
-        <v>10.95033540100009</v>
+        <v>10.95033443698226</v>
       </c>
       <c r="F169" t="n">
         <v>1631500</v>
@@ -3812,16 +3812,16 @@
         <v>44893</v>
       </c>
       <c r="B170" t="n">
-        <v>10.97383403778076</v>
+        <v>10.97383308410645</v>
       </c>
       <c r="C170" t="n">
-        <v>11.09915964398247</v>
+        <v>11.09915867941681</v>
       </c>
       <c r="D170" t="n">
-        <v>10.68401838668942</v>
+        <v>10.68401745820135</v>
       </c>
       <c r="E170" t="n">
-        <v>10.84067539444156</v>
+        <v>10.84067445233931</v>
       </c>
       <c r="F170" t="n">
         <v>4990000</v>
@@ -3832,16 +3832,16 @@
         <v>44894</v>
       </c>
       <c r="B171" t="n">
-        <v>11.16965579986572</v>
+        <v>11.16965484619141</v>
       </c>
       <c r="C171" t="n">
-        <v>11.2636500071732</v>
+        <v>11.26364904547358</v>
       </c>
       <c r="D171" t="n">
-        <v>10.9973327129689</v>
+        <v>10.99733177400767</v>
       </c>
       <c r="E171" t="n">
-        <v>11.01299878768659</v>
+        <v>11.01299784738778</v>
       </c>
       <c r="F171" t="n">
         <v>1705300</v>
@@ -3852,16 +3852,16 @@
         <v>44895</v>
       </c>
       <c r="B172" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C172" t="n">
-        <v>11.20882040874432</v>
+        <v>11.20881942197064</v>
       </c>
       <c r="D172" t="n">
-        <v>10.69185114025542</v>
+        <v>10.69185019899337</v>
       </c>
       <c r="E172" t="n">
-        <v>11.20882040874432</v>
+        <v>11.20881942197064</v>
       </c>
       <c r="F172" t="n">
         <v>4586400</v>
@@ -3872,16 +3872,16 @@
         <v>44896</v>
       </c>
       <c r="B173" t="n">
-        <v>10.92683696746826</v>
+        <v>10.92683601379395</v>
       </c>
       <c r="C173" t="n">
-        <v>11.02083117560783</v>
+        <v>11.02083021372987</v>
       </c>
       <c r="D173" t="n">
-        <v>10.69185107361957</v>
+        <v>10.69185014045439</v>
       </c>
       <c r="E173" t="n">
-        <v>10.76234691647413</v>
+        <v>10.76234597715621</v>
       </c>
       <c r="F173" t="n">
         <v>1944500</v>
@@ -3912,16 +3912,16 @@
         <v>44900</v>
       </c>
       <c r="B175" t="n">
-        <v>10.51952838897705</v>
+        <v>10.51952743530273</v>
       </c>
       <c r="C175" t="n">
-        <v>10.80151100419552</v>
+        <v>10.80151002495736</v>
       </c>
       <c r="D175" t="n">
-        <v>10.50386231463181</v>
+        <v>10.50386136237774</v>
       </c>
       <c r="E175" t="n">
-        <v>10.7780126396772</v>
+        <v>10.77801166256934</v>
       </c>
       <c r="F175" t="n">
         <v>1355000</v>
@@ -3932,16 +3932,16 @@
         <v>44901</v>
       </c>
       <c r="B176" t="n">
-        <v>10.47253131866455</v>
+        <v>10.47253036499023</v>
       </c>
       <c r="C176" t="n">
-        <v>10.58219160233104</v>
+        <v>10.58219063867058</v>
       </c>
       <c r="D176" t="n">
-        <v>10.41770155033109</v>
+        <v>10.41770060164981</v>
       </c>
       <c r="E176" t="n">
-        <v>10.51952879652149</v>
+        <v>10.51952783856738</v>
       </c>
       <c r="F176" t="n">
         <v>1647500</v>
@@ -4072,16 +4072,16 @@
         <v>44910</v>
       </c>
       <c r="B183" t="n">
-        <v>11.05216121673584</v>
+        <v>11.05216217041016</v>
       </c>
       <c r="C183" t="n">
-        <v>11.17748755914842</v>
+        <v>11.17748852363695</v>
       </c>
       <c r="D183" t="n">
-        <v>10.86417282361618</v>
+        <v>10.86417376106927</v>
       </c>
       <c r="E183" t="n">
-        <v>10.95033398371283</v>
+        <v>10.95033492860062</v>
       </c>
       <c r="F183" t="n">
         <v>3824700</v>
@@ -4112,16 +4112,16 @@
         <v>44914</v>
       </c>
       <c r="B185" t="n">
-        <v>11.37331008911133</v>
+        <v>11.37330913543701</v>
       </c>
       <c r="C185" t="n">
-        <v>11.5221340613134</v>
+        <v>11.5221330951599</v>
       </c>
       <c r="D185" t="n">
-        <v>11.18532093080405</v>
+        <v>11.18531999289299</v>
       </c>
       <c r="E185" t="n">
-        <v>11.23231840713075</v>
+        <v>11.23231746527886</v>
       </c>
       <c r="F185" t="n">
         <v>3838800</v>
@@ -4192,16 +4192,16 @@
         <v>44918</v>
       </c>
       <c r="B189" t="n">
-        <v>11.78845119476318</v>
+        <v>11.78845024108887</v>
       </c>
       <c r="C189" t="n">
-        <v>12.09393217234406</v>
+        <v>12.09393119395663</v>
       </c>
       <c r="D189" t="n">
-        <v>11.57696367459224</v>
+        <v>11.57696273802706</v>
       </c>
       <c r="E189" t="n">
-        <v>11.67879091611904</v>
+        <v>11.67878997131614</v>
       </c>
       <c r="F189" t="n">
         <v>5656000</v>
@@ -4212,16 +4212,16 @@
         <v>44921</v>
       </c>
       <c r="B190" t="n">
-        <v>11.57696342468262</v>
+        <v>11.57696437835693</v>
       </c>
       <c r="C190" t="n">
-        <v>11.82761537802995</v>
+        <v>11.82761635235219</v>
       </c>
       <c r="D190" t="n">
-        <v>11.51430062309566</v>
+        <v>11.51430157160801</v>
       </c>
       <c r="E190" t="n">
-        <v>11.77278486639172</v>
+        <v>11.7727858361972</v>
       </c>
       <c r="F190" t="n">
         <v>1646600</v>
@@ -4232,16 +4232,16 @@
         <v>44922</v>
       </c>
       <c r="B191" t="n">
-        <v>11.52996730804443</v>
+        <v>11.52996635437012</v>
       </c>
       <c r="C191" t="n">
-        <v>11.60829544067951</v>
+        <v>11.60829448052647</v>
       </c>
       <c r="D191" t="n">
-        <v>11.34197814632122</v>
+        <v>11.34197720819598</v>
       </c>
       <c r="E191" t="n">
-        <v>11.60829544067951</v>
+        <v>11.60829448052647</v>
       </c>
       <c r="F191" t="n">
         <v>1633000</v>
@@ -4272,16 +4272,16 @@
         <v>44924</v>
       </c>
       <c r="B193" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="C193" t="n">
-        <v>11.73362032145083</v>
+        <v>11.73362129131107</v>
       </c>
       <c r="D193" t="n">
-        <v>11.4751360805163</v>
+        <v>11.47513702901113</v>
       </c>
       <c r="E193" t="n">
-        <v>11.62396079317528</v>
+        <v>11.62396175397144</v>
       </c>
       <c r="F193" t="n">
         <v>2424800</v>
@@ -4332,16 +4332,16 @@
         <v>44930</v>
       </c>
       <c r="B196" t="n">
-        <v>11.35764312744141</v>
+        <v>11.35764408111572</v>
       </c>
       <c r="C196" t="n">
-        <v>11.35764312744141</v>
+        <v>11.35764408111572</v>
       </c>
       <c r="D196" t="n">
-        <v>10.96600026097791</v>
+        <v>10.9660011817669</v>
       </c>
       <c r="E196" t="n">
-        <v>11.1696547308188</v>
+        <v>11.16965566870818</v>
       </c>
       <c r="F196" t="n">
         <v>2937400</v>
@@ -4372,16 +4372,16 @@
         <v>44932</v>
       </c>
       <c r="B198" t="n">
-        <v>11.42030715942383</v>
+        <v>11.42030620574951</v>
       </c>
       <c r="C198" t="n">
-        <v>11.53779973324935</v>
+        <v>11.53779876976359</v>
       </c>
       <c r="D198" t="n">
-        <v>11.31847991350858</v>
+        <v>11.31847896833754</v>
       </c>
       <c r="E198" t="n">
-        <v>11.41247412196891</v>
+        <v>11.4124731689487</v>
       </c>
       <c r="F198" t="n">
         <v>2864500</v>
@@ -4452,16 +4452,16 @@
         <v>44938</v>
       </c>
       <c r="B202" t="n">
-        <v>11.79628372192383</v>
+        <v>11.79628276824951</v>
       </c>
       <c r="C202" t="n">
-        <v>11.97643908583725</v>
+        <v>11.97643811759822</v>
       </c>
       <c r="D202" t="n">
-        <v>11.49863504732819</v>
+        <v>11.49863411771738</v>
       </c>
       <c r="E202" t="n">
-        <v>11.49863504732819</v>
+        <v>11.49863411771738</v>
       </c>
       <c r="F202" t="n">
         <v>5662900</v>
@@ -4492,16 +4492,16 @@
         <v>44942</v>
       </c>
       <c r="B204" t="n">
-        <v>11.78845119476318</v>
+        <v>11.78845024108887</v>
       </c>
       <c r="C204" t="n">
-        <v>11.80411652199833</v>
+        <v>11.8041155670567</v>
       </c>
       <c r="D204" t="n">
-        <v>11.39680830289065</v>
+        <v>11.39680738089987</v>
       </c>
       <c r="E204" t="n">
-        <v>11.49080250730011</v>
+        <v>11.49080157770529</v>
       </c>
       <c r="F204" t="n">
         <v>3279700</v>
@@ -4552,16 +4552,16 @@
         <v>44945</v>
       </c>
       <c r="B207" t="n">
-        <v>11.66312599182129</v>
+        <v>11.66312503814697</v>
       </c>
       <c r="C207" t="n">
-        <v>11.68662435698559</v>
+        <v>11.68662340138985</v>
       </c>
       <c r="D207" t="n">
-        <v>11.27931537680668</v>
+        <v>11.27931445451592</v>
       </c>
       <c r="E207" t="n">
-        <v>11.3419781819112</v>
+        <v>11.3419772544966</v>
       </c>
       <c r="F207" t="n">
         <v>1847800</v>
@@ -4632,16 +4632,16 @@
         <v>44951</v>
       </c>
       <c r="B211" t="n">
-        <v>11.89027786254883</v>
+        <v>11.89027881622314</v>
       </c>
       <c r="C211" t="n">
-        <v>12.07043322555739</v>
+        <v>12.07043419368129</v>
       </c>
       <c r="D211" t="n">
-        <v>11.62396058940618</v>
+        <v>11.62396152172019</v>
       </c>
       <c r="E211" t="n">
-        <v>11.67879035258278</v>
+        <v>11.67879128929448</v>
       </c>
       <c r="F211" t="n">
         <v>10764800</v>
@@ -4692,16 +4692,16 @@
         <v>44956</v>
       </c>
       <c r="B214" t="n">
-        <v>11.84327983856201</v>
+        <v>11.84328079223633</v>
       </c>
       <c r="C214" t="n">
-        <v>11.97643846894329</v>
+        <v>11.97643943334014</v>
       </c>
       <c r="D214" t="n">
-        <v>11.74928564305749</v>
+        <v>11.74928658916297</v>
       </c>
       <c r="E214" t="n">
-        <v>11.86677820068828</v>
+        <v>11.86677915625479</v>
       </c>
       <c r="F214" t="n">
         <v>3859300</v>
@@ -4712,16 +4712,16 @@
         <v>44957</v>
       </c>
       <c r="B215" t="n">
-        <v>12.07043361663818</v>
+        <v>12.0704345703125</v>
       </c>
       <c r="C215" t="n">
-        <v>12.14092945557759</v>
+        <v>12.14093041482172</v>
       </c>
       <c r="D215" t="n">
-        <v>11.82761544584636</v>
+        <v>11.82761638033583</v>
       </c>
       <c r="E215" t="n">
-        <v>11.84328077283316</v>
+        <v>11.84328170856034</v>
       </c>
       <c r="F215" t="n">
         <v>5446800</v>
@@ -4732,16 +4732,16 @@
         <v>44958</v>
       </c>
       <c r="B216" t="n">
-        <v>12.07826709747314</v>
+        <v>12.07826614379883</v>
       </c>
       <c r="C216" t="n">
-        <v>12.19575966868999</v>
+        <v>12.19575870573871</v>
       </c>
       <c r="D216" t="n">
-        <v>11.93727541441329</v>
+        <v>11.93727447187138</v>
       </c>
       <c r="E216" t="n">
-        <v>12.08610013475415</v>
+        <v>12.08609918046135</v>
       </c>
       <c r="F216" t="n">
         <v>3741600</v>
@@ -4792,16 +4792,16 @@
         <v>44963</v>
       </c>
       <c r="B219" t="n">
-        <v>11.91377639770508</v>
+        <v>11.91377735137939</v>
       </c>
       <c r="C219" t="n">
-        <v>11.96077387182007</v>
+        <v>11.96077482925644</v>
       </c>
       <c r="D219" t="n">
-        <v>11.75711939565429</v>
+        <v>11.75712033678852</v>
       </c>
       <c r="E219" t="n">
-        <v>11.92160943455749</v>
+        <v>11.92161038885883</v>
       </c>
       <c r="F219" t="n">
         <v>3421200</v>
@@ -4852,16 +4852,16 @@
         <v>44966</v>
       </c>
       <c r="B222" t="n">
-        <v>11.66312599182129</v>
+        <v>11.66312503814697</v>
       </c>
       <c r="C222" t="n">
-        <v>11.78845160203032</v>
+        <v>11.78845063810834</v>
       </c>
       <c r="D222" t="n">
-        <v>11.55346570938861</v>
+        <v>11.55346476468103</v>
       </c>
       <c r="E222" t="n">
-        <v>11.7101227221499</v>
+        <v>11.71012176463273</v>
       </c>
       <c r="F222" t="n">
         <v>2260100</v>
@@ -4892,16 +4892,16 @@
         <v>44970</v>
       </c>
       <c r="B224" t="n">
-        <v>11.79628372192383</v>
+        <v>11.79628276824951</v>
       </c>
       <c r="C224" t="n">
-        <v>11.87461184871247</v>
+        <v>11.87461088870569</v>
       </c>
       <c r="D224" t="n">
-        <v>11.63179368456833</v>
+        <v>11.63179274419227</v>
       </c>
       <c r="E224" t="n">
-        <v>11.74145321147233</v>
+        <v>11.7414522622308</v>
       </c>
       <c r="F224" t="n">
         <v>2704300</v>
@@ -4912,16 +4912,16 @@
         <v>44971</v>
       </c>
       <c r="B225" t="n">
-        <v>11.71795463562012</v>
+        <v>11.71795558929443</v>
       </c>
       <c r="C225" t="n">
-        <v>11.88244466999244</v>
+        <v>11.8824456370539</v>
       </c>
       <c r="D225" t="n">
-        <v>11.51430016506401</v>
+        <v>11.51430110216375</v>
       </c>
       <c r="E225" t="n">
-        <v>11.78061743471438</v>
+        <v>11.78061839348856</v>
       </c>
       <c r="F225" t="n">
         <v>2141000</v>
@@ -4952,16 +4952,16 @@
         <v>44973</v>
       </c>
       <c r="B227" t="n">
-        <v>11.89027786254883</v>
+        <v>11.89027881622314</v>
       </c>
       <c r="C227" t="n">
-        <v>11.97643902568342</v>
+        <v>11.9764399862684</v>
       </c>
       <c r="D227" t="n">
-        <v>11.57696311596945</v>
+        <v>11.57696404451397</v>
       </c>
       <c r="E227" t="n">
-        <v>11.76495226271687</v>
+        <v>11.7649532063393</v>
       </c>
       <c r="F227" t="n">
         <v>4461000</v>
@@ -4992,16 +4992,16 @@
         <v>44979</v>
       </c>
       <c r="B229" t="n">
-        <v>11.71795463562012</v>
+        <v>11.71795558929443</v>
       </c>
       <c r="C229" t="n">
-        <v>11.95294050572336</v>
+        <v>11.95294147852217</v>
       </c>
       <c r="D229" t="n">
-        <v>11.66312487316251</v>
+        <v>11.66312582237446</v>
       </c>
       <c r="E229" t="n">
-        <v>11.89810999626626</v>
+        <v>11.89811096460265</v>
       </c>
       <c r="F229" t="n">
         <v>6185800</v>
@@ -5072,16 +5072,16 @@
         <v>44985</v>
       </c>
       <c r="B233" t="n">
-        <v>11.59262943267822</v>
+        <v>11.59262847900391</v>
       </c>
       <c r="C233" t="n">
-        <v>11.82761531079323</v>
+        <v>11.82761433778766</v>
       </c>
       <c r="D233" t="n">
-        <v>11.54563195825542</v>
+        <v>11.54563100844737</v>
       </c>
       <c r="E233" t="n">
-        <v>11.67095756071688</v>
+        <v>11.67095660059886</v>
       </c>
       <c r="F233" t="n">
         <v>7018700</v>
@@ -5092,16 +5092,16 @@
         <v>44986</v>
       </c>
       <c r="B234" t="n">
-        <v>11.52996730804443</v>
+        <v>11.52996635437012</v>
       </c>
       <c r="C234" t="n">
-        <v>11.6552929178602</v>
+        <v>11.65529195381987</v>
       </c>
       <c r="D234" t="n">
-        <v>11.31847978123065</v>
+        <v>11.31847884504903</v>
       </c>
       <c r="E234" t="n">
-        <v>11.6004631503157</v>
+        <v>11.60046219081048</v>
       </c>
       <c r="F234" t="n">
         <v>8005300</v>
@@ -5112,16 +5112,16 @@
         <v>44987</v>
       </c>
       <c r="B235" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="C235" t="n">
-        <v>11.67879055731306</v>
+        <v>11.67879152264125</v>
       </c>
       <c r="D235" t="n">
-        <v>11.45947075376244</v>
+        <v>11.45947170096243</v>
       </c>
       <c r="E235" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="F235" t="n">
         <v>2250800</v>
@@ -5132,16 +5132,16 @@
         <v>44988</v>
       </c>
       <c r="B236" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="C236" t="n">
-        <v>11.64745915680582</v>
+        <v>11.64746011954428</v>
       </c>
       <c r="D236" t="n">
-        <v>11.45947075376244</v>
+        <v>11.45947170096243</v>
       </c>
       <c r="E236" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="F236" t="n">
         <v>1727100</v>
@@ -5172,16 +5172,16 @@
         <v>44992</v>
       </c>
       <c r="B238" t="n">
-        <v>11.61612796783447</v>
+        <v>11.61612701416016</v>
       </c>
       <c r="C238" t="n">
-        <v>11.6239610048538</v>
+        <v>11.6239600505364</v>
       </c>
       <c r="D238" t="n">
-        <v>11.3889751232706</v>
+        <v>11.38897418824534</v>
       </c>
       <c r="E238" t="n">
-        <v>11.52996680162043</v>
+        <v>11.52996585501987</v>
       </c>
       <c r="F238" t="n">
         <v>3776700</v>
@@ -5212,16 +5212,16 @@
         <v>44994</v>
       </c>
       <c r="B240" t="n">
-        <v>11.57696342468262</v>
+        <v>11.57696437835693</v>
       </c>
       <c r="C240" t="n">
-        <v>11.70228902785652</v>
+        <v>11.70228999185477</v>
       </c>
       <c r="D240" t="n">
-        <v>11.51430062309566</v>
+        <v>11.51430157160801</v>
       </c>
       <c r="E240" t="n">
-        <v>11.62396089937259</v>
+        <v>11.62396185691841</v>
       </c>
       <c r="F240" t="n">
         <v>2514900</v>
@@ -5232,16 +5232,16 @@
         <v>44995</v>
       </c>
       <c r="B241" t="n">
-        <v>11.57696342468262</v>
+        <v>11.57696437835693</v>
       </c>
       <c r="C241" t="n">
-        <v>11.63179393632084</v>
+        <v>11.63179489451192</v>
       </c>
       <c r="D241" t="n">
-        <v>11.44380478456046</v>
+        <v>11.44380572726558</v>
       </c>
       <c r="E241" t="n">
-        <v>11.57696342468262</v>
+        <v>11.57696437835693</v>
       </c>
       <c r="F241" t="n">
         <v>3626000</v>
@@ -5252,16 +5252,16 @@
         <v>44998</v>
       </c>
       <c r="B242" t="n">
-        <v>11.66312599182129</v>
+        <v>11.66312503814697</v>
       </c>
       <c r="C242" t="n">
-        <v>11.74145412470215</v>
+        <v>11.74145316462308</v>
       </c>
       <c r="D242" t="n">
-        <v>11.45947150173183</v>
+        <v>11.45947056471</v>
       </c>
       <c r="E242" t="n">
-        <v>11.52213430683635</v>
+        <v>11.52213336469069</v>
       </c>
       <c r="F242" t="n">
         <v>3223500</v>
@@ -5312,16 +5312,16 @@
         <v>45001</v>
       </c>
       <c r="B245" t="n">
-        <v>11.67095756530762</v>
+        <v>11.67095851898193</v>
       </c>
       <c r="C245" t="n">
-        <v>11.81194924163198</v>
+        <v>11.81195020682722</v>
       </c>
       <c r="D245" t="n">
-        <v>11.63962616467993</v>
+        <v>11.63962711579405</v>
       </c>
       <c r="E245" t="n">
-        <v>11.81194924163198</v>
+        <v>11.81195020682722</v>
       </c>
       <c r="F245" t="n">
         <v>5495800</v>
@@ -5392,16 +5392,16 @@
         <v>45007</v>
       </c>
       <c r="B249" t="n">
-        <v>11.33414459228516</v>
+        <v>11.33414554595947</v>
       </c>
       <c r="C249" t="n">
-        <v>11.45947018812806</v>
+        <v>11.45947115234749</v>
       </c>
       <c r="D249" t="n">
-        <v>11.21665128593282</v>
+        <v>11.21665222972105</v>
       </c>
       <c r="E249" t="n">
-        <v>11.36547599124588</v>
+        <v>11.36547694755648</v>
       </c>
       <c r="F249" t="n">
         <v>3006300</v>
@@ -5452,16 +5452,16 @@
         <v>45012</v>
       </c>
       <c r="B252" t="n">
-        <v>11.28714752197266</v>
+        <v>11.28714847564697</v>
       </c>
       <c r="C252" t="n">
-        <v>11.42030615904377</v>
+        <v>11.42030712396893</v>
       </c>
       <c r="D252" t="n">
-        <v>11.1931533217459</v>
+        <v>11.19315426747845</v>
       </c>
       <c r="E252" t="n">
-        <v>11.39680779573696</v>
+        <v>11.39680875867669</v>
       </c>
       <c r="F252" t="n">
         <v>2288800</v>
@@ -5472,16 +5472,16 @@
         <v>45013</v>
       </c>
       <c r="B253" t="n">
-        <v>11.42030715942383</v>
+        <v>11.42030620574951</v>
       </c>
       <c r="C253" t="n">
-        <v>11.45163856224394</v>
+        <v>11.45163760595323</v>
       </c>
       <c r="D253" t="n">
-        <v>11.25581710786836</v>
+        <v>11.25581616793009</v>
       </c>
       <c r="E253" t="n">
-        <v>11.31064687605366</v>
+        <v>11.31064593153673</v>
       </c>
       <c r="F253" t="n">
         <v>3302900</v>
@@ -5532,16 +5532,16 @@
         <v>45016</v>
       </c>
       <c r="B256" t="n">
-        <v>11.49080181121826</v>
+        <v>11.49080276489258</v>
       </c>
       <c r="C256" t="n">
-        <v>11.61612740950566</v>
+        <v>11.61612837358132</v>
       </c>
       <c r="D256" t="n">
-        <v>11.30281341378716</v>
+        <v>11.30281435185946</v>
       </c>
       <c r="E256" t="n">
-        <v>11.42813901207456</v>
+        <v>11.42813996054821</v>
       </c>
       <c r="F256" t="n">
         <v>5155800</v>
@@ -5592,16 +5592,16 @@
         <v>45021</v>
       </c>
       <c r="B259" t="n">
-        <v>11.49080181121826</v>
+        <v>11.49080276489258</v>
       </c>
       <c r="C259" t="n">
-        <v>11.56913068364763</v>
+        <v>11.56913164382282</v>
       </c>
       <c r="D259" t="n">
-        <v>11.27931430385866</v>
+        <v>11.27931523998066</v>
       </c>
       <c r="E259" t="n">
-        <v>11.55346461036196</v>
+        <v>11.55346556923695</v>
       </c>
       <c r="F259" t="n">
         <v>4689800</v>
@@ -5612,16 +5612,16 @@
         <v>45022</v>
       </c>
       <c r="B260" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="C260" t="n">
-        <v>11.6631252305592</v>
+        <v>11.66312619459255</v>
       </c>
       <c r="D260" t="n">
-        <v>11.4751360805163</v>
+        <v>11.47513702901113</v>
       </c>
       <c r="E260" t="n">
-        <v>11.49080215426967</v>
+        <v>11.4908031040594</v>
       </c>
       <c r="F260" t="n">
         <v>4653400</v>
@@ -5632,16 +5632,16 @@
         <v>45026</v>
       </c>
       <c r="B261" t="n">
-        <v>11.71795463562012</v>
+        <v>11.71795558929443</v>
       </c>
       <c r="C261" t="n">
-        <v>11.85111327044531</v>
+        <v>11.85111423495683</v>
       </c>
       <c r="D261" t="n">
-        <v>11.4594704026064</v>
+        <v>11.45947133524378</v>
       </c>
       <c r="E261" t="n">
-        <v>11.53779852797449</v>
+        <v>11.53779946698666</v>
       </c>
       <c r="F261" t="n">
         <v>3430500</v>
@@ -5692,16 +5692,16 @@
         <v>45029</v>
       </c>
       <c r="B264" t="n">
-        <v>11.91377639770508</v>
+        <v>11.91377735137939</v>
       </c>
       <c r="C264" t="n">
-        <v>11.99993756208313</v>
+        <v>11.99993852265448</v>
       </c>
       <c r="D264" t="n">
-        <v>11.77278472235961</v>
+        <v>11.77278566474782</v>
       </c>
       <c r="E264" t="n">
-        <v>11.82761523332702</v>
+        <v>11.82761618010431</v>
       </c>
       <c r="F264" t="n">
         <v>3337400</v>
@@ -5832,16 +5832,16 @@
         <v>45041</v>
       </c>
       <c r="B271" t="n">
-        <v>12.06260013580322</v>
+        <v>12.06260108947754</v>
       </c>
       <c r="C271" t="n">
-        <v>12.14092900885369</v>
+        <v>12.14092996872072</v>
       </c>
       <c r="D271" t="n">
-        <v>11.96860593634236</v>
+        <v>11.96860688258545</v>
       </c>
       <c r="E271" t="n">
-        <v>12.11743064573835</v>
+        <v>12.11743160374759</v>
       </c>
       <c r="F271" t="n">
         <v>2381100</v>
@@ -5872,16 +5872,16 @@
         <v>45043</v>
       </c>
       <c r="B273" t="n">
-        <v>12.07826709747314</v>
+        <v>12.07826614379883</v>
       </c>
       <c r="C273" t="n">
-        <v>12.0939324250356</v>
+        <v>12.09393147012438</v>
       </c>
       <c r="D273" t="n">
-        <v>11.95294148897529</v>
+        <v>11.95294054519642</v>
       </c>
       <c r="E273" t="n">
-        <v>12.01560429322422</v>
+        <v>12.01560334449763</v>
       </c>
       <c r="F273" t="n">
         <v>2919600</v>
@@ -5932,16 +5932,16 @@
         <v>45049</v>
       </c>
       <c r="B276" t="n">
-        <v>12.28975296020508</v>
+        <v>12.28975391387939</v>
       </c>
       <c r="C276" t="n">
-        <v>12.48557439565576</v>
+        <v>12.48557536452565</v>
       </c>
       <c r="D276" t="n">
-        <v>12.28192067050667</v>
+        <v>12.2819216235732</v>
       </c>
       <c r="E276" t="n">
-        <v>12.48557439565576</v>
+        <v>12.48557536452565</v>
       </c>
       <c r="F276" t="n">
         <v>6661600</v>
@@ -5972,16 +5972,16 @@
         <v>45051</v>
       </c>
       <c r="B278" t="n">
-        <v>12.50989818572998</v>
+        <v>12.50989723205566</v>
       </c>
       <c r="C278" t="n">
-        <v>12.59647220699179</v>
+        <v>12.59647124671763</v>
       </c>
       <c r="D278" t="n">
-        <v>12.15494618469247</v>
+        <v>12.15494525807742</v>
       </c>
       <c r="E278" t="n">
-        <v>12.34540853608981</v>
+        <v>12.34540759495513</v>
       </c>
       <c r="F278" t="n">
         <v>9400800</v>
@@ -6032,16 +6032,16 @@
         <v>45056</v>
       </c>
       <c r="B281" t="n">
-        <v>11.86925220489502</v>
+        <v>11.86925315856934</v>
       </c>
       <c r="C281" t="n">
-        <v>12.0510569757826</v>
+        <v>12.05105794406462</v>
       </c>
       <c r="D281" t="n">
-        <v>11.69610500062852</v>
+        <v>11.69610594039075</v>
       </c>
       <c r="E281" t="n">
-        <v>12.0164275349293</v>
+        <v>12.0164285004289</v>
       </c>
       <c r="F281" t="n">
         <v>5308900</v>
@@ -6112,16 +6112,16 @@
         <v>45062</v>
       </c>
       <c r="B285" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="C285" t="n">
-        <v>12.30212031805942</v>
+        <v>12.30212128603885</v>
       </c>
       <c r="D285" t="n">
-        <v>12.08568611177803</v>
+        <v>12.08568706272756</v>
       </c>
       <c r="E285" t="n">
-        <v>12.18091686531469</v>
+        <v>12.18091782375736</v>
       </c>
       <c r="F285" t="n">
         <v>2907500</v>
@@ -6132,16 +6132,16 @@
         <v>45063</v>
       </c>
       <c r="B286" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="C286" t="n">
-        <v>12.24151939290137</v>
+        <v>12.24152036724783</v>
       </c>
       <c r="D286" t="n">
-        <v>11.94716873091856</v>
+        <v>11.9471696818366</v>
       </c>
       <c r="E286" t="n">
-        <v>12.12897350298847</v>
+        <v>12.128974468377</v>
       </c>
       <c r="F286" t="n">
         <v>4330800</v>
@@ -6152,16 +6152,16 @@
         <v>45064</v>
       </c>
       <c r="B287" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="C287" t="n">
-        <v>12.05971462083146</v>
+        <v>12.05971558070743</v>
       </c>
       <c r="D287" t="n">
-        <v>11.82596527432829</v>
+        <v>11.82596621559931</v>
       </c>
       <c r="E287" t="n">
-        <v>12.01642761307558</v>
+        <v>12.01642856950617</v>
       </c>
       <c r="F287" t="n">
         <v>4680600</v>
@@ -6172,16 +6172,16 @@
         <v>45065</v>
       </c>
       <c r="B288" t="n">
-        <v>12.09434413909912</v>
+        <v>12.09434509277344</v>
       </c>
       <c r="C288" t="n">
-        <v>12.18091732953242</v>
+        <v>12.18091829003328</v>
       </c>
       <c r="D288" t="n">
-        <v>11.93851124043578</v>
+        <v>11.93851218182222</v>
       </c>
       <c r="E288" t="n">
-        <v>11.99911255630219</v>
+        <v>11.99911350246722</v>
       </c>
       <c r="F288" t="n">
         <v>2962700</v>
@@ -6252,16 +6252,16 @@
         <v>45071</v>
       </c>
       <c r="B292" t="n">
-        <v>12.29346370697021</v>
+        <v>12.29346466064453</v>
       </c>
       <c r="C292" t="n">
-        <v>12.39735203498263</v>
+        <v>12.39735299671616</v>
       </c>
       <c r="D292" t="n">
-        <v>12.20689051310872</v>
+        <v>12.20689146006706</v>
       </c>
       <c r="E292" t="n">
-        <v>12.28480613989475</v>
+        <v>12.28480709289745</v>
       </c>
       <c r="F292" t="n">
         <v>2204600</v>
@@ -6292,16 +6292,16 @@
         <v>45075</v>
       </c>
       <c r="B294" t="n">
-        <v>12.28480625152588</v>
+        <v>12.28480529785156</v>
       </c>
       <c r="C294" t="n">
-        <v>12.34540839597375</v>
+        <v>12.34540743759487</v>
       </c>
       <c r="D294" t="n">
-        <v>12.16360361389222</v>
+        <v>12.16360266962691</v>
       </c>
       <c r="E294" t="n">
-        <v>12.16360361389222</v>
+        <v>12.16360266962691</v>
       </c>
       <c r="F294" t="n">
         <v>1431900</v>
@@ -6312,16 +6312,16 @@
         <v>45076</v>
       </c>
       <c r="B295" t="n">
-        <v>12.26749134063721</v>
+        <v>12.26749229431152</v>
       </c>
       <c r="C295" t="n">
-        <v>12.3800372312229</v>
+        <v>12.38003819364653</v>
       </c>
       <c r="D295" t="n">
-        <v>12.25017620717894</v>
+        <v>12.25017715950718</v>
       </c>
       <c r="E295" t="n">
-        <v>12.37137966449377</v>
+        <v>12.37138062624436</v>
       </c>
       <c r="F295" t="n">
         <v>1829100</v>
@@ -6392,16 +6392,16 @@
         <v>45082</v>
       </c>
       <c r="B299" t="n">
-        <v>12.0683708190918</v>
+        <v>12.06837177276611</v>
       </c>
       <c r="C299" t="n">
-        <v>12.19823183651883</v>
+        <v>12.1982328004551</v>
       </c>
       <c r="D299" t="n">
-        <v>11.97314006681674</v>
+        <v>11.97314101296568</v>
       </c>
       <c r="E299" t="n">
-        <v>12.17225996328581</v>
+        <v>12.17226092516972</v>
       </c>
       <c r="F299" t="n">
         <v>3442900</v>
@@ -6432,16 +6432,16 @@
         <v>45084</v>
       </c>
       <c r="B301" t="n">
-        <v>12.22420501708984</v>
+        <v>12.22420597076416</v>
       </c>
       <c r="C301" t="n">
-        <v>12.46661111966148</v>
+        <v>12.46661209224716</v>
       </c>
       <c r="D301" t="n">
-        <v>12.21554744987595</v>
+        <v>12.21554840287484</v>
       </c>
       <c r="E301" t="n">
-        <v>12.3800379244157</v>
+        <v>12.38003889024736</v>
       </c>
       <c r="F301" t="n">
         <v>3154600</v>
@@ -6472,16 +6472,16 @@
         <v>45089</v>
       </c>
       <c r="B303" t="n">
-        <v>12.45795440673828</v>
+        <v>12.45795345306396</v>
       </c>
       <c r="C303" t="n">
-        <v>12.45795440673828</v>
+        <v>12.45795345306396</v>
       </c>
       <c r="D303" t="n">
-        <v>12.25883448851593</v>
+        <v>12.25883355008453</v>
       </c>
       <c r="E303" t="n">
-        <v>12.3800379528961</v>
+        <v>12.3800370051864</v>
       </c>
       <c r="F303" t="n">
         <v>2572800</v>
@@ -6492,16 +6492,16 @@
         <v>45090</v>
       </c>
       <c r="B304" t="n">
-        <v>12.3107795715332</v>
+        <v>12.31077861785889</v>
       </c>
       <c r="C304" t="n">
-        <v>12.5012411047074</v>
+        <v>12.50124013627868</v>
       </c>
       <c r="D304" t="n">
-        <v>12.29346443635495</v>
+        <v>12.29346348402198</v>
       </c>
       <c r="E304" t="n">
-        <v>12.46661165998199</v>
+        <v>12.46661069423589</v>
       </c>
       <c r="F304" t="n">
         <v>1312000</v>
@@ -6532,16 +6532,16 @@
         <v>45092</v>
       </c>
       <c r="B306" t="n">
-        <v>12.4666109085083</v>
+        <v>12.46661186218262</v>
       </c>
       <c r="C306" t="n">
-        <v>12.49258360971007</v>
+        <v>12.49258456537125</v>
       </c>
       <c r="D306" t="n">
-        <v>12.36272258059435</v>
+        <v>12.36272352632139</v>
       </c>
       <c r="E306" t="n">
-        <v>12.45795416707208</v>
+        <v>12.45795512008417</v>
       </c>
       <c r="F306" t="n">
         <v>1266000</v>
@@ -6552,16 +6552,16 @@
         <v>45093</v>
       </c>
       <c r="B307" t="n">
-        <v>12.62244415283203</v>
+        <v>12.62244319915771</v>
       </c>
       <c r="C307" t="n">
-        <v>12.83022081425066</v>
+        <v>12.83021984487801</v>
       </c>
       <c r="D307" t="n">
-        <v>12.44063936768297</v>
+        <v>12.4406384277447</v>
       </c>
       <c r="E307" t="n">
-        <v>12.46661124395253</v>
+        <v>12.46661030205199</v>
       </c>
       <c r="F307" t="n">
         <v>5319000</v>
@@ -6612,16 +6612,16 @@
         <v>45098</v>
       </c>
       <c r="B310" t="n">
-        <v>12.86485004425049</v>
+        <v>12.86484909057617</v>
       </c>
       <c r="C310" t="n">
-        <v>12.90813705440186</v>
+        <v>12.90813609751867</v>
       </c>
       <c r="D310" t="n">
-        <v>12.63975907759925</v>
+        <v>12.63975814061098</v>
       </c>
       <c r="E310" t="n">
-        <v>12.75230414810935</v>
+        <v>12.75230320277808</v>
       </c>
       <c r="F310" t="n">
         <v>5022600</v>
@@ -6692,16 +6692,16 @@
         <v>45104</v>
       </c>
       <c r="B314" t="n">
-        <v>12.50123977661133</v>
+        <v>12.50124073028564</v>
       </c>
       <c r="C314" t="n">
-        <v>12.83887744603771</v>
+        <v>12.83887842546918</v>
       </c>
       <c r="D314" t="n">
-        <v>12.3973514534719</v>
+        <v>12.39735239922096</v>
       </c>
       <c r="E314" t="n">
-        <v>12.76961856394476</v>
+        <v>12.76961953809272</v>
       </c>
       <c r="F314" t="n">
         <v>3014700</v>
@@ -6872,16 +6872,16 @@
         <v>45117</v>
       </c>
       <c r="B323" t="n">
-        <v>12.38869571685791</v>
+        <v>12.38869476318359</v>
       </c>
       <c r="C323" t="n">
-        <v>12.45795460456609</v>
+        <v>12.45795364556026</v>
       </c>
       <c r="D323" t="n">
-        <v>12.31077926177845</v>
+        <v>12.31077831410209</v>
       </c>
       <c r="E323" t="n">
-        <v>12.38003814948662</v>
+        <v>12.38003719647876</v>
       </c>
       <c r="F323" t="n">
         <v>1514600</v>
@@ -6912,16 +6912,16 @@
         <v>45119</v>
       </c>
       <c r="B325" t="n">
-        <v>12.38869571685791</v>
+        <v>12.38869476318359</v>
       </c>
       <c r="C325" t="n">
-        <v>12.45795460456609</v>
+        <v>12.45795364556026</v>
       </c>
       <c r="D325" t="n">
-        <v>12.28480655966458</v>
+        <v>12.28480561398759</v>
       </c>
       <c r="E325" t="n">
-        <v>12.37138058211533</v>
+        <v>12.37137962977392</v>
       </c>
       <c r="F325" t="n">
         <v>1842800</v>
@@ -7052,16 +7052,16 @@
         <v>45128</v>
       </c>
       <c r="B332" t="n">
-        <v>12.38869571685791</v>
+        <v>12.38869476318359</v>
       </c>
       <c r="C332" t="n">
-        <v>12.38869571685791</v>
+        <v>12.38869476318359</v>
       </c>
       <c r="D332" t="n">
-        <v>12.2242052393277</v>
+        <v>12.22420429831576</v>
       </c>
       <c r="E332" t="n">
-        <v>12.27614981792436</v>
+        <v>12.27614887291376</v>
       </c>
       <c r="F332" t="n">
         <v>2631400</v>
@@ -7152,16 +7152,16 @@
         <v>45135</v>
       </c>
       <c r="B337" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="C337" t="n">
-        <v>12.22420387169716</v>
+        <v>12.22420483354582</v>
       </c>
       <c r="D337" t="n">
-        <v>12.05971423820094</v>
+        <v>12.0597151871069</v>
       </c>
       <c r="E337" t="n">
-        <v>12.14628742533491</v>
+        <v>12.14628838105279</v>
       </c>
       <c r="F337" t="n">
         <v>1506100</v>
@@ -7172,16 +7172,16 @@
         <v>45138</v>
       </c>
       <c r="B338" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="C338" t="n">
-        <v>12.20688956452276</v>
+        <v>12.20689052500906</v>
       </c>
       <c r="D338" t="n">
-        <v>12.10300041895243</v>
+        <v>12.10300137126433</v>
       </c>
       <c r="E338" t="n">
-        <v>12.20688956452276</v>
+        <v>12.20689052500906</v>
       </c>
       <c r="F338" t="n">
         <v>1549400</v>
@@ -7212,16 +7212,16 @@
         <v>45140</v>
       </c>
       <c r="B340" t="n">
-        <v>12.22420501708984</v>
+        <v>12.22420597076416</v>
       </c>
       <c r="C340" t="n">
-        <v>12.23286258430374</v>
+        <v>12.23286353865348</v>
       </c>
       <c r="D340" t="n">
-        <v>12.12897425463018</v>
+        <v>12.12897520087505</v>
       </c>
       <c r="E340" t="n">
-        <v>12.13763182184407</v>
+        <v>12.13763276876436</v>
       </c>
       <c r="F340" t="n">
         <v>1697600</v>
@@ -7332,16 +7332,16 @@
         <v>45148</v>
       </c>
       <c r="B346" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C346" t="n">
-        <v>12.09434452900206</v>
+        <v>12.09434549372545</v>
       </c>
       <c r="D346" t="n">
-        <v>11.88656704887551</v>
+        <v>11.88656799702522</v>
       </c>
       <c r="E346" t="n">
-        <v>12.01642807715848</v>
+        <v>12.01642903566675</v>
       </c>
       <c r="F346" t="n">
         <v>2835300</v>
@@ -7412,16 +7412,16 @@
         <v>45154</v>
       </c>
       <c r="B350" t="n">
-        <v>11.6874475479126</v>
+        <v>11.68744850158691</v>
       </c>
       <c r="C350" t="n">
-        <v>11.91253932846828</v>
+        <v>11.91254030050967</v>
       </c>
       <c r="D350" t="n">
-        <v>11.64416054001635</v>
+        <v>11.64416149015853</v>
       </c>
       <c r="E350" t="n">
-        <v>11.88656662835193</v>
+        <v>11.886567598274</v>
       </c>
       <c r="F350" t="n">
         <v>3946200</v>
@@ -7432,16 +7432,16 @@
         <v>45155</v>
       </c>
       <c r="B351" t="n">
-        <v>11.71341991424561</v>
+        <v>11.71342086791992</v>
       </c>
       <c r="C351" t="n">
-        <v>11.78267879953539</v>
+        <v>11.78267975884857</v>
       </c>
       <c r="D351" t="n">
-        <v>11.66147616309379</v>
+        <v>11.66147711253899</v>
       </c>
       <c r="E351" t="n">
-        <v>11.73073504838357</v>
+        <v>11.73073600346764</v>
       </c>
       <c r="F351" t="n">
         <v>2345000</v>
@@ -7452,16 +7452,16 @@
         <v>45156</v>
       </c>
       <c r="B352" t="n">
-        <v>11.77402210235596</v>
+        <v>11.77402114868164</v>
       </c>
       <c r="C352" t="n">
-        <v>11.80865154513102</v>
+        <v>11.80865058865178</v>
       </c>
       <c r="D352" t="n">
-        <v>11.65281863982772</v>
+        <v>11.65281769597066</v>
       </c>
       <c r="E352" t="n">
-        <v>11.71341995827632</v>
+        <v>11.71341900951066</v>
       </c>
       <c r="F352" t="n">
         <v>3061800</v>
@@ -7512,16 +7512,16 @@
         <v>45161</v>
       </c>
       <c r="B355" t="n">
-        <v>11.87791061401367</v>
+        <v>11.87790966033936</v>
       </c>
       <c r="C355" t="n">
-        <v>11.89522492285292</v>
+        <v>11.89522396778845</v>
       </c>
       <c r="D355" t="n">
-        <v>11.79133659292425</v>
+        <v>11.79133564620093</v>
       </c>
       <c r="E355" t="n">
-        <v>11.86059547954337</v>
+        <v>11.86059452725928</v>
       </c>
       <c r="F355" t="n">
         <v>2615000</v>
@@ -7532,16 +7532,16 @@
         <v>45162</v>
       </c>
       <c r="B356" t="n">
-        <v>11.97314167022705</v>
+        <v>11.97314071655273</v>
       </c>
       <c r="C356" t="n">
-        <v>11.99911354693815</v>
+        <v>11.99911259119515</v>
       </c>
       <c r="D356" t="n">
-        <v>11.89522521446267</v>
+        <v>11.89522426699448</v>
       </c>
       <c r="E356" t="n">
-        <v>11.90388278191006</v>
+        <v>11.90388183375229</v>
       </c>
       <c r="F356" t="n">
         <v>2322800</v>
@@ -7592,16 +7592,16 @@
         <v>45167</v>
       </c>
       <c r="B359" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="C359" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="D359" t="n">
-        <v>11.97314022543599</v>
+        <v>11.97314116752997</v>
       </c>
       <c r="E359" t="n">
-        <v>11.98179779183868</v>
+        <v>11.98179873461387</v>
       </c>
       <c r="F359" t="n">
         <v>1776800</v>
@@ -7632,16 +7632,16 @@
         <v>45169</v>
       </c>
       <c r="B361" t="n">
-        <v>11.78267860412598</v>
+        <v>11.78267955780029</v>
       </c>
       <c r="C361" t="n">
-        <v>12.1203162835374</v>
+        <v>12.12031726453966</v>
       </c>
       <c r="D361" t="n">
-        <v>11.78267860412598</v>
+        <v>11.78267955780029</v>
       </c>
       <c r="E361" t="n">
-        <v>12.1203162835374</v>
+        <v>12.12031726453966</v>
       </c>
       <c r="F361" t="n">
         <v>3236500</v>
@@ -7712,16 +7712,16 @@
         <v>45175</v>
       </c>
       <c r="B365" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C365" t="n">
-        <v>12.02508564417022</v>
+        <v>12.02508660336907</v>
       </c>
       <c r="D365" t="n">
-        <v>11.81730816404367</v>
+        <v>11.81730910666884</v>
       </c>
       <c r="E365" t="n">
-        <v>11.9385116253149</v>
+        <v>11.93851257760805</v>
       </c>
       <c r="F365" t="n">
         <v>2473500</v>
@@ -7732,16 +7732,16 @@
         <v>45177</v>
       </c>
       <c r="B366" t="n">
-        <v>11.92985439300537</v>
+        <v>11.92985343933105</v>
       </c>
       <c r="C366" t="n">
-        <v>12.07702973380992</v>
+        <v>12.07702876837038</v>
       </c>
       <c r="D366" t="n">
-        <v>11.88656738236326</v>
+        <v>11.88656643214931</v>
       </c>
       <c r="E366" t="n">
-        <v>11.93851196026</v>
+        <v>11.9385110058936</v>
       </c>
       <c r="F366" t="n">
         <v>3462800</v>
@@ -7772,16 +7772,16 @@
         <v>45181</v>
       </c>
       <c r="B368" t="n">
-        <v>12.0683708190918</v>
+        <v>12.06837177276611</v>
       </c>
       <c r="C368" t="n">
-        <v>12.15494483070982</v>
+        <v>12.15494579122544</v>
       </c>
       <c r="D368" t="n">
-        <v>11.98179763310474</v>
+        <v>11.98179857993782</v>
       </c>
       <c r="E368" t="n">
-        <v>12.03374137957078</v>
+        <v>12.03374233050859</v>
       </c>
       <c r="F368" t="n">
         <v>2215400</v>
@@ -7792,16 +7792,16 @@
         <v>45182</v>
       </c>
       <c r="B369" t="n">
-        <v>12.0683708190918</v>
+        <v>12.06837177276611</v>
       </c>
       <c r="C369" t="n">
-        <v>12.19823183651883</v>
+        <v>12.1982328004551</v>
       </c>
       <c r="D369" t="n">
-        <v>12.03374137957078</v>
+        <v>12.03374233050859</v>
       </c>
       <c r="E369" t="n">
-        <v>12.07702838537979</v>
+        <v>12.07702933973825</v>
       </c>
       <c r="F369" t="n">
         <v>1684100</v>
@@ -7892,16 +7892,16 @@
         <v>45189</v>
       </c>
       <c r="B374" t="n">
-        <v>12.0683708190918</v>
+        <v>12.06837177276611</v>
       </c>
       <c r="C374" t="n">
-        <v>12.14628726442182</v>
+        <v>12.1462882242533</v>
       </c>
       <c r="D374" t="n">
-        <v>11.97314006681674</v>
+        <v>11.97314101296568</v>
       </c>
       <c r="E374" t="n">
-        <v>12.08568595166779</v>
+        <v>12.08568690671039</v>
       </c>
       <c r="F374" t="n">
         <v>2998000</v>
@@ -7912,16 +7912,16 @@
         <v>45190</v>
       </c>
       <c r="B375" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C375" t="n">
-        <v>12.03374238555092</v>
+        <v>12.0337433454403</v>
       </c>
       <c r="D375" t="n">
-        <v>11.8779103074948</v>
+        <v>11.877911254954</v>
       </c>
       <c r="E375" t="n">
-        <v>12.02508564417022</v>
+        <v>12.02508660336907</v>
       </c>
       <c r="F375" t="n">
         <v>4405700</v>
@@ -7932,16 +7932,16 @@
         <v>45191</v>
       </c>
       <c r="B376" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C376" t="n">
-        <v>12.10300127038276</v>
+        <v>12.10300223579667</v>
       </c>
       <c r="D376" t="n">
-        <v>11.92985405830317</v>
+        <v>11.92985500990573</v>
       </c>
       <c r="E376" t="n">
-        <v>12.02508564417022</v>
+        <v>12.02508660336907</v>
       </c>
       <c r="F376" t="n">
         <v>2812600</v>
@@ -8012,16 +8012,16 @@
         <v>45197</v>
       </c>
       <c r="B380" t="n">
-        <v>11.78267860412598</v>
+        <v>11.78267955780029</v>
       </c>
       <c r="C380" t="n">
-        <v>11.86059505519254</v>
+        <v>11.86059601517331</v>
       </c>
       <c r="D380" t="n">
-        <v>11.73073485383562</v>
+        <v>11.73073580330568</v>
       </c>
       <c r="E380" t="n">
-        <v>11.85193748826714</v>
+        <v>11.85193844754717</v>
       </c>
       <c r="F380" t="n">
         <v>2404900</v>
@@ -8092,16 +8092,16 @@
         <v>45203</v>
       </c>
       <c r="B384" t="n">
-        <v>11.77402210235596</v>
+        <v>11.77402114868164</v>
       </c>
       <c r="C384" t="n">
-        <v>11.86059529647809</v>
+        <v>11.86059433579151</v>
       </c>
       <c r="D384" t="n">
-        <v>11.74804940105138</v>
+        <v>11.7480484494808</v>
       </c>
       <c r="E384" t="n">
-        <v>11.80865154513102</v>
+        <v>11.80865058865178</v>
       </c>
       <c r="F384" t="n">
         <v>4367600</v>
@@ -8192,16 +8192,16 @@
         <v>45210</v>
       </c>
       <c r="B389" t="n">
-        <v>12.09434413909912</v>
+        <v>12.09434509277344</v>
       </c>
       <c r="C389" t="n">
-        <v>12.18957489626505</v>
+        <v>12.18957585744859</v>
       </c>
       <c r="D389" t="n">
-        <v>12.00777012303482</v>
+        <v>12.00777106988252</v>
       </c>
       <c r="E389" t="n">
-        <v>12.09434413909912</v>
+        <v>12.09434509277344</v>
       </c>
       <c r="F389" t="n">
         <v>3458500</v>
@@ -8232,16 +8232,16 @@
         <v>45215</v>
       </c>
       <c r="B391" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="C391" t="n">
-        <v>12.12031593631109</v>
+        <v>12.12031690101054</v>
       </c>
       <c r="D391" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="E391" t="n">
-        <v>12.05971462083146</v>
+        <v>12.05971558070743</v>
       </c>
       <c r="F391" t="n">
         <v>3983600</v>
@@ -8252,16 +8252,16 @@
         <v>45216</v>
       </c>
       <c r="B392" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C392" t="n">
-        <v>12.10300127038276</v>
+        <v>12.10300223579667</v>
       </c>
       <c r="D392" t="n">
-        <v>11.88656704887551</v>
+        <v>11.88656799702522</v>
       </c>
       <c r="E392" t="n">
-        <v>11.97314106773082</v>
+        <v>11.97314202278624</v>
       </c>
       <c r="F392" t="n">
         <v>5165000</v>
@@ -8292,16 +8292,16 @@
         <v>45218</v>
       </c>
       <c r="B394" t="n">
-        <v>11.67013359069824</v>
+        <v>11.67013263702393</v>
       </c>
       <c r="C394" t="n">
-        <v>11.75670761521626</v>
+        <v>11.75670665446719</v>
       </c>
       <c r="D394" t="n">
-        <v>11.62684740407032</v>
+        <v>11.62684645393332</v>
       </c>
       <c r="E394" t="n">
-        <v>11.66147684875131</v>
+        <v>11.66147589578441</v>
       </c>
       <c r="F394" t="n">
         <v>3066300</v>
@@ -8452,16 +8452,16 @@
         <v>45230</v>
       </c>
       <c r="B402" t="n">
-        <v>11.61818981170654</v>
+        <v>11.61818885803223</v>
       </c>
       <c r="C402" t="n">
-        <v>11.66147682387321</v>
+        <v>11.6614758666457</v>
       </c>
       <c r="D402" t="n">
-        <v>11.52295904544475</v>
+        <v>11.52295809958741</v>
       </c>
       <c r="E402" t="n">
-        <v>11.52295904544475</v>
+        <v>11.52295809958741</v>
       </c>
       <c r="F402" t="n">
         <v>3290000</v>
@@ -8592,16 +8592,16 @@
         <v>45240</v>
       </c>
       <c r="B409" t="n">
-        <v>11.78267860412598</v>
+        <v>11.78267955780029</v>
       </c>
       <c r="C409" t="n">
-        <v>11.86059505519254</v>
+        <v>11.86059601517331</v>
       </c>
       <c r="D409" t="n">
-        <v>11.69610541176504</v>
+        <v>11.69610635843224</v>
       </c>
       <c r="E409" t="n">
-        <v>11.69610541176504</v>
+        <v>11.69610635843224</v>
       </c>
       <c r="F409" t="n">
         <v>3430000</v>
@@ -8712,16 +8712,16 @@
         <v>45251</v>
       </c>
       <c r="B415" t="n">
-        <v>11.97314167022705</v>
+        <v>11.97314071655273</v>
       </c>
       <c r="C415" t="n">
-        <v>12.09434513759732</v>
+        <v>12.09434417426901</v>
       </c>
       <c r="D415" t="n">
-        <v>11.91254034935745</v>
+        <v>11.9125394005101</v>
       </c>
       <c r="E415" t="n">
-        <v>12.08568757014993</v>
+        <v>12.0856866075112</v>
       </c>
       <c r="F415" t="n">
         <v>2713400</v>
@@ -8732,16 +8732,16 @@
         <v>45252</v>
       </c>
       <c r="B416" t="n">
-        <v>12.4666109085083</v>
+        <v>12.46661186218262</v>
       </c>
       <c r="C416" t="n">
-        <v>12.94276636400384</v>
+        <v>12.94276735410323</v>
       </c>
       <c r="D416" t="n">
-        <v>12.44063903293757</v>
+        <v>12.44063998462508</v>
       </c>
       <c r="E416" t="n">
-        <v>12.81290616051917</v>
+        <v>12.81290714068447</v>
       </c>
       <c r="F416" t="n">
         <v>20875500</v>
@@ -8752,16 +8752,16 @@
         <v>45253</v>
       </c>
       <c r="B417" t="n">
-        <v>12.561842918396</v>
+        <v>12.56184196472168</v>
       </c>
       <c r="C417" t="n">
-        <v>12.76961958122722</v>
+        <v>12.76961861177884</v>
       </c>
       <c r="D417" t="n">
-        <v>12.46661132870839</v>
+        <v>12.46661038226389</v>
       </c>
       <c r="E417" t="n">
-        <v>12.76961958122722</v>
+        <v>12.76961861177884</v>
       </c>
       <c r="F417" t="n">
         <v>9122900</v>
@@ -8832,16 +8832,16 @@
         <v>45259</v>
       </c>
       <c r="B421" t="n">
-        <v>12.561842918396</v>
+        <v>12.56184196472168</v>
       </c>
       <c r="C421" t="n">
-        <v>12.75230444650908</v>
+        <v>12.75230347837524</v>
       </c>
       <c r="D421" t="n">
-        <v>12.561842918396</v>
+        <v>12.56184196472168</v>
       </c>
       <c r="E421" t="n">
-        <v>12.72633257006295</v>
+        <v>12.72633160390085</v>
       </c>
       <c r="F421" t="n">
         <v>5869600</v>
@@ -8872,16 +8872,16 @@
         <v>45261</v>
       </c>
       <c r="B423" t="n">
-        <v>12.86485004425049</v>
+        <v>12.86484909057617</v>
       </c>
       <c r="C423" t="n">
-        <v>12.96873837323515</v>
+        <v>12.96873741185957</v>
       </c>
       <c r="D423" t="n">
-        <v>12.70901796358902</v>
+        <v>12.70901702146657</v>
       </c>
       <c r="E423" t="n">
-        <v>12.72633227227094</v>
+        <v>12.72633132886498</v>
       </c>
       <c r="F423" t="n">
         <v>6458300</v>
@@ -8912,16 +8912,16 @@
         <v>45265</v>
       </c>
       <c r="B425" t="n">
-        <v>13.15919971466064</v>
+        <v>13.15920066833496</v>
       </c>
       <c r="C425" t="n">
-        <v>13.20248672149667</v>
+        <v>13.20248767830808</v>
       </c>
       <c r="D425" t="n">
-        <v>12.9254511987557</v>
+        <v>12.92545213548978</v>
       </c>
       <c r="E425" t="n">
-        <v>12.96008063909832</v>
+        <v>12.96008157834207</v>
       </c>
       <c r="F425" t="n">
         <v>6696500</v>
@@ -8952,16 +8952,16 @@
         <v>45267</v>
       </c>
       <c r="B427" t="n">
-        <v>13.11591339111328</v>
+        <v>13.1159143447876</v>
       </c>
       <c r="C427" t="n">
-        <v>13.15054283325996</v>
+        <v>13.15054378945223</v>
       </c>
       <c r="D427" t="n">
-        <v>12.97739562252655</v>
+        <v>12.97739656612907</v>
       </c>
       <c r="E427" t="n">
-        <v>13.10725664979988</v>
+        <v>13.10725760284475</v>
       </c>
       <c r="F427" t="n">
         <v>6196000</v>
@@ -9052,16 +9052,16 @@
         <v>45274</v>
       </c>
       <c r="B432" t="n">
-        <v>12.94470119476318</v>
+        <v>12.94470024108887</v>
       </c>
       <c r="C432" t="n">
-        <v>12.9831984112191</v>
+        <v>12.98319745470858</v>
       </c>
       <c r="D432" t="n">
-        <v>12.71371789602766</v>
+        <v>12.71371695937057</v>
       </c>
       <c r="E432" t="n">
-        <v>12.71371789602766</v>
+        <v>12.71371695937057</v>
       </c>
       <c r="F432" t="n">
         <v>5480800</v>
@@ -9092,16 +9092,16 @@
         <v>45278</v>
       </c>
       <c r="B434" t="n">
-        <v>12.8484582901001</v>
+        <v>12.84845733642578</v>
       </c>
       <c r="C434" t="n">
-        <v>13.08906611637279</v>
+        <v>13.0890651448394</v>
       </c>
       <c r="D434" t="n">
-        <v>12.8484582901001</v>
+        <v>12.84845733642578</v>
       </c>
       <c r="E434" t="n">
-        <v>12.98319808539135</v>
+        <v>12.983197121716</v>
       </c>
       <c r="F434" t="n">
         <v>3314300</v>
@@ -9112,16 +9112,16 @@
         <v>45279</v>
       </c>
       <c r="B435" t="n">
-        <v>12.86770534515381</v>
+        <v>12.86770629882812</v>
       </c>
       <c r="C435" t="n">
-        <v>12.94469976958878</v>
+        <v>12.94470072896945</v>
       </c>
       <c r="D435" t="n">
-        <v>12.79071092071883</v>
+        <v>12.7907118686868</v>
       </c>
       <c r="E435" t="n">
-        <v>12.87732987766966</v>
+        <v>12.87733083205729</v>
       </c>
       <c r="F435" t="n">
         <v>4780200</v>
@@ -9232,16 +9232,16 @@
         <v>45288</v>
       </c>
       <c r="B441" t="n">
-        <v>12.80996131896973</v>
+        <v>12.80996036529541</v>
       </c>
       <c r="C441" t="n">
-        <v>12.88695575141803</v>
+        <v>12.88695479201164</v>
       </c>
       <c r="D441" t="n">
-        <v>12.76183956922803</v>
+        <v>12.76183861913627</v>
       </c>
       <c r="E441" t="n">
-        <v>12.88695575141803</v>
+        <v>12.88695479201164</v>
       </c>
       <c r="F441" t="n">
         <v>3487000</v>
@@ -9332,16 +9332,16 @@
         <v>45299</v>
       </c>
       <c r="B446" t="n">
-        <v>13.01207160949707</v>
+        <v>13.01207065582275</v>
       </c>
       <c r="C446" t="n">
-        <v>13.09868965545936</v>
+        <v>13.09868869543668</v>
       </c>
       <c r="D446" t="n">
-        <v>12.88695543042352</v>
+        <v>12.88695448591916</v>
       </c>
       <c r="E446" t="n">
-        <v>12.9543253276762</v>
+        <v>12.95432437823419</v>
       </c>
       <c r="F446" t="n">
         <v>3738800</v>
@@ -9392,16 +9392,16 @@
         <v>45302</v>
       </c>
       <c r="B449" t="n">
-        <v>12.8484582901001</v>
+        <v>12.84845733642578</v>
       </c>
       <c r="C449" t="n">
-        <v>12.94470086990156</v>
+        <v>12.94469990908366</v>
       </c>
       <c r="D449" t="n">
-        <v>12.74259025911866</v>
+        <v>12.74258931330238</v>
       </c>
       <c r="E449" t="n">
-        <v>12.94470086990156</v>
+        <v>12.94469990908366</v>
       </c>
       <c r="F449" t="n">
         <v>4814200</v>
@@ -9412,16 +9412,16 @@
         <v>45303</v>
       </c>
       <c r="B450" t="n">
-        <v>12.77146339416504</v>
+        <v>12.77146434783936</v>
       </c>
       <c r="C450" t="n">
-        <v>12.88695503642984</v>
+        <v>12.88695599872818</v>
       </c>
       <c r="D450" t="n">
-        <v>12.74258979521435</v>
+        <v>12.74259074673261</v>
       </c>
       <c r="E450" t="n">
-        <v>12.84845782234157</v>
+        <v>12.84845878176524</v>
       </c>
       <c r="F450" t="n">
         <v>4041800</v>
@@ -9432,16 +9432,16 @@
         <v>45306</v>
       </c>
       <c r="B451" t="n">
-        <v>12.80996131896973</v>
+        <v>12.80996036529541</v>
       </c>
       <c r="C451" t="n">
-        <v>12.84845853519388</v>
+        <v>12.84845757865353</v>
       </c>
       <c r="D451" t="n">
-        <v>12.74259050219293</v>
+        <v>12.74258955353423</v>
       </c>
       <c r="E451" t="n">
-        <v>12.77146410274557</v>
+        <v>12.77146315193729</v>
       </c>
       <c r="F451" t="n">
         <v>1955800</v>
@@ -9492,16 +9492,16 @@
         <v>45309</v>
       </c>
       <c r="B454" t="n">
-        <v>12.55972862243652</v>
+        <v>12.55972766876221</v>
       </c>
       <c r="C454" t="n">
-        <v>12.77146376499286</v>
+        <v>12.77146279524125</v>
       </c>
       <c r="D454" t="n">
-        <v>12.51160687396745</v>
+        <v>12.51160592394707</v>
       </c>
       <c r="E454" t="n">
-        <v>12.76183923172984</v>
+        <v>12.76183826270904</v>
       </c>
       <c r="F454" t="n">
         <v>6534900</v>
@@ -9532,16 +9532,16 @@
         <v>45313</v>
       </c>
       <c r="B456" t="n">
-        <v>12.61747455596924</v>
+        <v>12.61747360229492</v>
       </c>
       <c r="C456" t="n">
-        <v>12.65597177291335</v>
+        <v>12.65597081632927</v>
       </c>
       <c r="D456" t="n">
-        <v>12.56935372317364</v>
+        <v>12.56935277313647</v>
       </c>
       <c r="E456" t="n">
-        <v>12.60785094011775</v>
+        <v>12.60784998717082</v>
       </c>
       <c r="F456" t="n">
         <v>4490300</v>
@@ -9572,16 +9572,16 @@
         <v>45315</v>
       </c>
       <c r="B458" t="n">
-        <v>12.79071140289307</v>
+        <v>12.79071235656738</v>
       </c>
       <c r="C458" t="n">
-        <v>12.82920861656179</v>
+        <v>12.82920957310646</v>
       </c>
       <c r="D458" t="n">
-        <v>12.64634708109684</v>
+        <v>12.64634802400737</v>
       </c>
       <c r="E458" t="n">
-        <v>12.65597069612954</v>
+        <v>12.6559716397576</v>
       </c>
       <c r="F458" t="n">
         <v>3333600</v>
@@ -9652,16 +9652,16 @@
         <v>45321</v>
       </c>
       <c r="B462" t="n">
-        <v>12.51160621643066</v>
+        <v>12.51160717010498</v>
       </c>
       <c r="C462" t="n">
-        <v>12.63672238873649</v>
+        <v>12.63672335194755</v>
       </c>
       <c r="D462" t="n">
-        <v>12.51160621643066</v>
+        <v>12.51160717010498</v>
       </c>
       <c r="E462" t="n">
-        <v>12.58860064279641</v>
+        <v>12.58860160233948</v>
       </c>
       <c r="F462" t="n">
         <v>3463200</v>
@@ -9672,16 +9672,16 @@
         <v>45322</v>
       </c>
       <c r="B463" t="n">
-        <v>12.68484497070312</v>
+        <v>12.68484401702881</v>
       </c>
       <c r="C463" t="n">
-        <v>12.79071208447197</v>
+        <v>12.79071112283833</v>
       </c>
       <c r="D463" t="n">
-        <v>12.53085610782262</v>
+        <v>12.53085516572552</v>
       </c>
       <c r="E463" t="n">
-        <v>12.57897693908826</v>
+        <v>12.57897599337333</v>
       </c>
       <c r="F463" t="n">
         <v>3755000</v>
@@ -9812,16 +9812,16 @@
         <v>45331</v>
       </c>
       <c r="B470" t="n">
-        <v>12.48273372650146</v>
+        <v>12.48273468017578</v>
       </c>
       <c r="C470" t="n">
-        <v>12.62709804867886</v>
+        <v>12.62709901338253</v>
       </c>
       <c r="D470" t="n">
-        <v>12.36724208519036</v>
+        <v>12.36724303004117</v>
       </c>
       <c r="E470" t="n">
-        <v>12.36724208519036</v>
+        <v>12.36724303004117</v>
       </c>
       <c r="F470" t="n">
         <v>4943200</v>
@@ -9852,16 +9852,16 @@
         <v>45337</v>
       </c>
       <c r="B472" t="n">
-        <v>12.50198173522949</v>
+        <v>12.50198268890381</v>
       </c>
       <c r="C472" t="n">
-        <v>12.58860069470964</v>
+        <v>12.58860165499141</v>
       </c>
       <c r="D472" t="n">
-        <v>12.41536277574934</v>
+        <v>12.4153637228162</v>
       </c>
       <c r="E472" t="n">
-        <v>12.46348452188787</v>
+        <v>12.46348547262554</v>
       </c>
       <c r="F472" t="n">
         <v>4740900</v>
@@ -9892,16 +9892,16 @@
         <v>45341</v>
       </c>
       <c r="B474" t="n">
-        <v>12.77146339416504</v>
+        <v>12.77146434783936</v>
       </c>
       <c r="C474" t="n">
-        <v>12.85808143747915</v>
+        <v>12.85808239762144</v>
       </c>
       <c r="D474" t="n">
-        <v>12.53085557665187</v>
+        <v>12.53085651235945</v>
       </c>
       <c r="E474" t="n">
-        <v>12.54047919178945</v>
+        <v>12.54048012821565</v>
       </c>
       <c r="F474" t="n">
         <v>4786000</v>
@@ -9972,16 +9972,16 @@
         <v>45345</v>
       </c>
       <c r="B478" t="n">
-        <v>12.41536235809326</v>
+        <v>12.41536331176758</v>
       </c>
       <c r="C478" t="n">
-        <v>12.55010305917923</v>
+        <v>12.55010402320352</v>
       </c>
       <c r="D478" t="n">
-        <v>12.41536235809326</v>
+        <v>12.41536331176758</v>
       </c>
       <c r="E478" t="n">
-        <v>12.52123037960578</v>
+        <v>12.52123134141225</v>
       </c>
       <c r="F478" t="n">
         <v>4574300</v>
@@ -9992,16 +9992,16 @@
         <v>45348</v>
       </c>
       <c r="B479" t="n">
-        <v>12.35761833190918</v>
+        <v>12.35761737823486</v>
       </c>
       <c r="C479" t="n">
-        <v>12.48273451401776</v>
+        <v>12.48273355068785</v>
       </c>
       <c r="D479" t="n">
-        <v>12.33836926488661</v>
+        <v>12.3383683126978</v>
       </c>
       <c r="E479" t="n">
-        <v>12.45386091348391</v>
+        <v>12.45385995238227</v>
       </c>
       <c r="F479" t="n">
         <v>6964500</v>
@@ -22092,16 +22092,16 @@
         <v>46231</v>
       </c>
       <c r="B1084" t="n">
-        <v>11.45</v>
+        <v>11.44999980926514</v>
       </c>
       <c r="C1084" t="n">
-        <v>11.72</v>
+        <v>11.72000026702881</v>
       </c>
       <c r="D1084" t="n">
-        <v>11.38</v>
+        <v>11.38000011444092</v>
       </c>
       <c r="E1084" t="n">
-        <v>11.53</v>
+        <v>11.52999973297119</v>
       </c>
       <c r="F1084" t="n">
         <v>1564600</v>

--- a/database/AURE3.xlsx
+++ b/database/AURE3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1084"/>
+  <dimension ref="A1:F1085"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44648</v>
       </c>
       <c r="B2" t="n">
-        <v>12.75723171234131</v>
+        <v>12.75723266601562</v>
       </c>
       <c r="C2" t="n">
-        <v>13.06838341582507</v>
+        <v>13.06838439275972</v>
       </c>
       <c r="D2" t="n">
-        <v>12.02602483823237</v>
+        <v>12.02602573724489</v>
       </c>
       <c r="E2" t="n">
-        <v>13.06838341582507</v>
+        <v>13.06838439275972</v>
       </c>
       <c r="F2" t="n">
         <v>5237900</v>
@@ -492,16 +492,16 @@
         <v>44650</v>
       </c>
       <c r="B4" t="n">
-        <v>12.38384914398193</v>
+        <v>12.38385105133057</v>
       </c>
       <c r="C4" t="n">
-        <v>13.04504741320321</v>
+        <v>13.04504942238897</v>
       </c>
       <c r="D4" t="n">
-        <v>12.3060608504815</v>
+        <v>12.30606274584925</v>
       </c>
       <c r="E4" t="n">
-        <v>12.9283657147967</v>
+        <v>12.92836770601126</v>
       </c>
       <c r="F4" t="n">
         <v>4408600</v>
@@ -512,16 +512,16 @@
         <v>44651</v>
       </c>
       <c r="B5" t="n">
-        <v>12.4383020401001</v>
+        <v>12.43830299377441</v>
       </c>
       <c r="C5" t="n">
-        <v>12.82724207193696</v>
+        <v>12.82724305543223</v>
       </c>
       <c r="D5" t="n">
-        <v>12.05714098694259</v>
+        <v>12.05714191139238</v>
       </c>
       <c r="E5" t="n">
-        <v>12.41496584590627</v>
+        <v>12.41496679779135</v>
       </c>
       <c r="F5" t="n">
         <v>3876100</v>
@@ -532,16 +532,16 @@
         <v>44652</v>
       </c>
       <c r="B6" t="n">
-        <v>12.51609039306641</v>
+        <v>12.51609134674072</v>
       </c>
       <c r="C6" t="n">
-        <v>12.95170281502629</v>
+        <v>12.95170380189247</v>
       </c>
       <c r="D6" t="n">
-        <v>12.31384139766291</v>
+        <v>12.31384233592669</v>
       </c>
       <c r="E6" t="n">
-        <v>12.43830208965145</v>
+        <v>12.43830303739862</v>
       </c>
       <c r="F6" t="n">
         <v>4252000</v>
@@ -632,16 +632,16 @@
         <v>44659</v>
       </c>
       <c r="B11" t="n">
-        <v>12.60943603515625</v>
+        <v>12.60943508148193</v>
       </c>
       <c r="C11" t="n">
-        <v>12.75723367341398</v>
+        <v>12.75723270856147</v>
       </c>
       <c r="D11" t="n">
-        <v>12.3371784382169</v>
+        <v>12.33717750513392</v>
       </c>
       <c r="E11" t="n">
-        <v>12.3371784382169</v>
+        <v>12.33717750513392</v>
       </c>
       <c r="F11" t="n">
         <v>2049800</v>
@@ -672,16 +672,16 @@
         <v>44663</v>
       </c>
       <c r="B13" t="n">
-        <v>12.24383163452148</v>
+        <v>12.2438325881958</v>
       </c>
       <c r="C13" t="n">
-        <v>12.64055063241211</v>
+        <v>12.64055161698694</v>
       </c>
       <c r="D13" t="n">
-        <v>12.21271646263855</v>
+        <v>12.2127174138893</v>
       </c>
       <c r="E13" t="n">
-        <v>12.4849740311532</v>
+        <v>12.48497500361014</v>
       </c>
       <c r="F13" t="n">
         <v>2267700</v>
@@ -692,16 +692,16 @@
         <v>44664</v>
       </c>
       <c r="B14" t="n">
-        <v>12.10381317138672</v>
+        <v>12.10381412506104</v>
       </c>
       <c r="C14" t="n">
-        <v>12.55498277187146</v>
+        <v>12.55498376109398</v>
       </c>
       <c r="D14" t="n">
-        <v>12.0882552152437</v>
+        <v>12.08825616769219</v>
       </c>
       <c r="E14" t="n">
-        <v>12.39162868343488</v>
+        <v>12.39162965978653</v>
       </c>
       <c r="F14" t="n">
         <v>4421300</v>
@@ -732,16 +732,16 @@
         <v>44669</v>
       </c>
       <c r="B16" t="n">
-        <v>12.45385932922363</v>
+        <v>12.45386028289795</v>
       </c>
       <c r="C16" t="n">
-        <v>12.45385932922363</v>
+        <v>12.45386028289795</v>
       </c>
       <c r="D16" t="n">
-        <v>11.92490067691762</v>
+        <v>11.92490159008608</v>
       </c>
       <c r="E16" t="n">
-        <v>12.10381346772168</v>
+        <v>12.10381439459067</v>
       </c>
       <c r="F16" t="n">
         <v>3931100</v>
@@ -752,16 +752,16 @@
         <v>44670</v>
       </c>
       <c r="B17" t="n">
-        <v>12.10381317138672</v>
+        <v>12.10381412506104</v>
       </c>
       <c r="C17" t="n">
-        <v>12.60165664030051</v>
+        <v>12.60165763320052</v>
       </c>
       <c r="D17" t="n">
-        <v>12.00268868198966</v>
+        <v>12.00268962769625</v>
       </c>
       <c r="E17" t="n">
-        <v>12.43830106817557</v>
+        <v>12.4383020482046</v>
       </c>
       <c r="F17" t="n">
         <v>3118100</v>
@@ -832,16 +832,16 @@
         <v>44677</v>
       </c>
       <c r="B21" t="n">
-        <v>11.95601558685303</v>
+        <v>11.95601654052734</v>
       </c>
       <c r="C21" t="n">
-        <v>12.43830110089237</v>
+        <v>12.4383020930363</v>
       </c>
       <c r="D21" t="n">
-        <v>11.86267007528195</v>
+        <v>11.86267102151054</v>
       </c>
       <c r="E21" t="n">
-        <v>12.32939837498153</v>
+        <v>12.32939935843881</v>
       </c>
       <c r="F21" t="n">
         <v>2627000</v>
@@ -892,16 +892,16 @@
         <v>44680</v>
       </c>
       <c r="B24" t="n">
-        <v>11.40372180938721</v>
+        <v>11.40372085571289</v>
       </c>
       <c r="C24" t="n">
-        <v>11.96379567250737</v>
+        <v>11.963794671995</v>
       </c>
       <c r="D24" t="n">
-        <v>11.40372180938721</v>
+        <v>11.40372085571289</v>
       </c>
       <c r="E24" t="n">
-        <v>11.96379567250737</v>
+        <v>11.963794671995</v>
       </c>
       <c r="F24" t="n">
         <v>10427400</v>
@@ -912,16 +912,16 @@
         <v>44683</v>
       </c>
       <c r="B25" t="n">
-        <v>11.17035675048828</v>
+        <v>11.1703577041626</v>
       </c>
       <c r="C25" t="n">
-        <v>11.47373022346064</v>
+        <v>11.47373120303561</v>
       </c>
       <c r="D25" t="n">
-        <v>10.96032953215679</v>
+        <v>10.96033046789994</v>
       </c>
       <c r="E25" t="n">
-        <v>11.4270570961402</v>
+        <v>11.42705807173043</v>
       </c>
       <c r="F25" t="n">
         <v>2883200</v>
@@ -972,16 +972,16 @@
         <v>44686</v>
       </c>
       <c r="B28" t="n">
-        <v>11.28714847564697</v>
+        <v>11.28714752197266</v>
       </c>
       <c r="C28" t="n">
-        <v>11.62396161516718</v>
+        <v>11.62396063303483</v>
       </c>
       <c r="D28" t="n">
-        <v>11.14615678989441</v>
+        <v>11.14615584813277</v>
       </c>
       <c r="E28" t="n">
-        <v>11.61612857773658</v>
+        <v>11.61612759626606</v>
       </c>
       <c r="F28" t="n">
         <v>3065700</v>
@@ -1012,16 +1012,16 @@
         <v>44690</v>
       </c>
       <c r="B30" t="n">
-        <v>11.07566165924072</v>
+        <v>11.07565975189209</v>
       </c>
       <c r="C30" t="n">
-        <v>11.13049142708364</v>
+        <v>11.13048951029273</v>
       </c>
       <c r="D30" t="n">
-        <v>10.80934436343302</v>
+        <v>10.8093425019471</v>
       </c>
       <c r="E30" t="n">
-        <v>10.99733277917979</v>
+        <v>10.99733088532023</v>
       </c>
       <c r="F30" t="n">
         <v>1545300</v>
@@ -1152,16 +1152,16 @@
         <v>44699</v>
       </c>
       <c r="B37" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C37" t="n">
-        <v>11.59262882548476</v>
+        <v>11.5926298208571</v>
       </c>
       <c r="D37" t="n">
-        <v>11.03649593344125</v>
+        <v>11.03649688106261</v>
       </c>
       <c r="E37" t="n">
-        <v>11.51429995454926</v>
+        <v>11.51430094319608</v>
       </c>
       <c r="F37" t="n">
         <v>1959900</v>
@@ -1192,16 +1192,16 @@
         <v>44701</v>
       </c>
       <c r="B39" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C39" t="n">
-        <v>11.34197688669085</v>
+        <v>11.34197786054158</v>
       </c>
       <c r="D39" t="n">
-        <v>10.86417286558284</v>
+        <v>10.86417379840811</v>
       </c>
       <c r="E39" t="n">
-        <v>11.34197688669085</v>
+        <v>11.34197786054158</v>
       </c>
       <c r="F39" t="n">
         <v>1777400</v>
@@ -1212,16 +1212,16 @@
         <v>44704</v>
       </c>
       <c r="B40" t="n">
-        <v>11.20881938934326</v>
+        <v>11.20882034301758</v>
       </c>
       <c r="C40" t="n">
-        <v>11.43597222652075</v>
+        <v>11.4359731995218</v>
       </c>
       <c r="D40" t="n">
-        <v>11.16182191575504</v>
+        <v>11.16182286543069</v>
       </c>
       <c r="E40" t="n">
-        <v>11.1853202790494</v>
+        <v>11.18532123072435</v>
       </c>
       <c r="F40" t="n">
         <v>1184600</v>
@@ -1232,16 +1232,16 @@
         <v>44705</v>
       </c>
       <c r="B41" t="n">
-        <v>11.21665096282959</v>
+        <v>11.21665191650391</v>
       </c>
       <c r="C41" t="n">
-        <v>11.22448399909401</v>
+        <v>11.22448495343431</v>
       </c>
       <c r="D41" t="n">
-        <v>11.00516421268657</v>
+        <v>11.00516514837963</v>
       </c>
       <c r="E41" t="n">
-        <v>11.09132537059677</v>
+        <v>11.09132631361552</v>
       </c>
       <c r="F41" t="n">
         <v>792900</v>
@@ -1272,16 +1272,16 @@
         <v>44707</v>
       </c>
       <c r="B43" t="n">
-        <v>11.25581645965576</v>
+        <v>11.25581550598145</v>
       </c>
       <c r="C43" t="n">
-        <v>11.44380486575034</v>
+        <v>11.44380389614828</v>
       </c>
       <c r="D43" t="n">
-        <v>11.20881973163188</v>
+        <v>11.20881878193947</v>
       </c>
       <c r="E43" t="n">
-        <v>11.33414533569493</v>
+        <v>11.33414437538402</v>
       </c>
       <c r="F43" t="n">
         <v>1248800</v>
@@ -1312,16 +1312,16 @@
         <v>44711</v>
       </c>
       <c r="B45" t="n">
-        <v>11.09915924072266</v>
+        <v>11.09916019439697</v>
       </c>
       <c r="C45" t="n">
-        <v>11.27148231648886</v>
+        <v>11.27148328496971</v>
       </c>
       <c r="D45" t="n">
-        <v>11.0286634030456</v>
+        <v>11.02866435066269</v>
       </c>
       <c r="E45" t="n">
-        <v>11.15398900469392</v>
+        <v>11.15398996307938</v>
       </c>
       <c r="F45" t="n">
         <v>1940200</v>
@@ -1552,16 +1552,16 @@
         <v>44727</v>
       </c>
       <c r="B57" t="n">
-        <v>10.84067630767822</v>
+        <v>10.84067440032959</v>
       </c>
       <c r="C57" t="n">
-        <v>10.84850934547558</v>
+        <v>10.84850743674878</v>
       </c>
       <c r="D57" t="n">
-        <v>10.44120034400809</v>
+        <v>10.44119850694474</v>
       </c>
       <c r="E57" t="n">
-        <v>10.55086063217233</v>
+        <v>10.55085877581493</v>
       </c>
       <c r="F57" t="n">
         <v>3153700</v>
@@ -1572,16 +1572,16 @@
         <v>44729</v>
       </c>
       <c r="B58" t="n">
-        <v>10.45686531066895</v>
+        <v>10.45686626434326</v>
       </c>
       <c r="C58" t="n">
-        <v>10.80151072020806</v>
+        <v>10.80151170531431</v>
       </c>
       <c r="D58" t="n">
-        <v>10.42553390980175</v>
+        <v>10.42553486061862</v>
       </c>
       <c r="E58" t="n">
-        <v>10.74668095544036</v>
+        <v>10.74668193554609</v>
       </c>
       <c r="F58" t="n">
         <v>8202900</v>
@@ -1672,16 +1672,16 @@
         <v>44736</v>
       </c>
       <c r="B63" t="n">
-        <v>10.48819732666016</v>
+        <v>10.48819637298584</v>
       </c>
       <c r="C63" t="n">
-        <v>10.70751714559343</v>
+        <v>10.70751617197673</v>
       </c>
       <c r="D63" t="n">
-        <v>10.42553452125065</v>
+        <v>10.42553357327416</v>
       </c>
       <c r="E63" t="n">
-        <v>10.70751714559343</v>
+        <v>10.70751617197673</v>
       </c>
       <c r="F63" t="n">
         <v>807500</v>
@@ -1692,16 +1692,16 @@
         <v>44739</v>
       </c>
       <c r="B64" t="n">
-        <v>10.45686531066895</v>
+        <v>10.45686626434326</v>
       </c>
       <c r="C64" t="n">
-        <v>10.55085951327052</v>
+        <v>10.55086047551718</v>
       </c>
       <c r="D64" t="n">
-        <v>10.33153896020065</v>
+        <v>10.33153990244511</v>
       </c>
       <c r="E64" t="n">
-        <v>10.4960290015033</v>
+        <v>10.49602995874937</v>
       </c>
       <c r="F64" t="n">
         <v>1661400</v>
@@ -1732,16 +1732,16 @@
         <v>44741</v>
       </c>
       <c r="B66" t="n">
-        <v>10.6840181350708</v>
+        <v>10.68401718139648</v>
       </c>
       <c r="C66" t="n">
-        <v>10.6840181350708</v>
+        <v>10.68401718139648</v>
       </c>
       <c r="D66" t="n">
-        <v>10.53519342096158</v>
+        <v>10.53519248057162</v>
       </c>
       <c r="E66" t="n">
-        <v>10.62918762339921</v>
+        <v>10.62918667461916</v>
       </c>
       <c r="F66" t="n">
         <v>1613700</v>
@@ -1772,16 +1772,16 @@
         <v>44743</v>
       </c>
       <c r="B68" t="n">
-        <v>10.6840181350708</v>
+        <v>10.68401718139648</v>
       </c>
       <c r="C68" t="n">
-        <v>10.84067513913352</v>
+        <v>10.84067417147572</v>
       </c>
       <c r="D68" t="n">
-        <v>10.54302645791459</v>
+        <v>10.54302551682544</v>
       </c>
       <c r="E68" t="n">
-        <v>10.72318182583684</v>
+        <v>10.72318086866671</v>
       </c>
       <c r="F68" t="n">
         <v>2696600</v>
@@ -1832,16 +1832,16 @@
         <v>44748</v>
       </c>
       <c r="B71" t="n">
-        <v>10.67618560791016</v>
+        <v>10.67618465423584</v>
       </c>
       <c r="C71" t="n">
-        <v>10.71535004754583</v>
+        <v>10.71534909037307</v>
       </c>
       <c r="D71" t="n">
-        <v>10.49602948438586</v>
+        <v>10.49602854680439</v>
       </c>
       <c r="E71" t="n">
-        <v>10.57435836365721</v>
+        <v>10.57435741907885</v>
       </c>
       <c r="F71" t="n">
         <v>1826800</v>
@@ -1852,16 +1852,16 @@
         <v>44749</v>
       </c>
       <c r="B72" t="n">
-        <v>11.04433059692383</v>
+        <v>11.04432964324951</v>
       </c>
       <c r="C72" t="n">
-        <v>11.16182317363595</v>
+        <v>11.16182220981619</v>
       </c>
       <c r="D72" t="n">
-        <v>10.62135627496076</v>
+        <v>10.62135535781014</v>
       </c>
       <c r="E72" t="n">
-        <v>10.78584633055749</v>
+        <v>10.7858453992032</v>
       </c>
       <c r="F72" t="n">
         <v>2931100</v>
@@ -1892,16 +1892,16 @@
         <v>44753</v>
       </c>
       <c r="B74" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C74" t="n">
-        <v>11.18531989181933</v>
+        <v>11.18532085221909</v>
       </c>
       <c r="D74" t="n">
-        <v>10.83284146660853</v>
+        <v>10.83284239674361</v>
       </c>
       <c r="E74" t="n">
-        <v>11.05999429592211</v>
+        <v>11.0599952455611</v>
       </c>
       <c r="F74" t="n">
         <v>1881000</v>
@@ -1912,16 +1912,16 @@
         <v>44754</v>
       </c>
       <c r="B75" t="n">
-        <v>11.14615631103516</v>
+        <v>11.14615535736084</v>
       </c>
       <c r="C75" t="n">
-        <v>11.22448518797689</v>
+        <v>11.22448422760069</v>
       </c>
       <c r="D75" t="n">
-        <v>10.99733234124531</v>
+        <v>10.99733140030449</v>
       </c>
       <c r="E75" t="n">
-        <v>11.10699261956382</v>
+        <v>11.10699166924038</v>
       </c>
       <c r="F75" t="n">
         <v>1673000</v>
@@ -2052,16 +2052,16 @@
         <v>44763</v>
       </c>
       <c r="B82" t="n">
-        <v>11.24798393249512</v>
+        <v>11.2479829788208</v>
       </c>
       <c r="C82" t="n">
-        <v>11.27931533493105</v>
+        <v>11.27931437860027</v>
       </c>
       <c r="D82" t="n">
-        <v>11.0599955178795</v>
+        <v>11.05999458014401</v>
       </c>
       <c r="E82" t="n">
-        <v>11.22448556741805</v>
+        <v>11.22448461573608</v>
       </c>
       <c r="F82" t="n">
         <v>1092700</v>
@@ -2112,16 +2112,16 @@
         <v>44768</v>
       </c>
       <c r="B85" t="n">
-        <v>11.27148342132568</v>
+        <v>11.27148246765137</v>
       </c>
       <c r="C85" t="n">
-        <v>11.3811429600171</v>
+        <v>11.38114199706455</v>
       </c>
       <c r="D85" t="n">
-        <v>11.16965617325538</v>
+        <v>11.16965522819662</v>
       </c>
       <c r="E85" t="n">
-        <v>11.19315453911789</v>
+        <v>11.19315359207094</v>
       </c>
       <c r="F85" t="n">
         <v>1661400</v>
@@ -2232,16 +2232,16 @@
         <v>44776</v>
       </c>
       <c r="B91" t="n">
-        <v>10.88767242431641</v>
+        <v>10.88767147064209</v>
       </c>
       <c r="C91" t="n">
-        <v>11.02083107133751</v>
+        <v>11.02083010599954</v>
       </c>
       <c r="D91" t="n">
-        <v>10.70751704716995</v>
+        <v>10.70751610927583</v>
       </c>
       <c r="E91" t="n">
-        <v>10.83284265683698</v>
+        <v>10.83284170796531</v>
       </c>
       <c r="F91" t="n">
         <v>3133200</v>
@@ -2292,16 +2292,16 @@
         <v>44781</v>
       </c>
       <c r="B94" t="n">
-        <v>10.97383308410645</v>
+        <v>10.97383403778076</v>
       </c>
       <c r="C94" t="n">
-        <v>11.10699171587358</v>
+        <v>11.10699268111997</v>
       </c>
       <c r="D94" t="n">
-        <v>10.8720058511669</v>
+        <v>10.87200679599199</v>
       </c>
       <c r="E94" t="n">
-        <v>11.02866284530486</v>
+        <v>11.02866380374413</v>
       </c>
       <c r="F94" t="n">
         <v>2949000</v>
@@ -2312,16 +2312,16 @@
         <v>44782</v>
       </c>
       <c r="B95" t="n">
-        <v>10.92683601379395</v>
+        <v>10.92683696746826</v>
       </c>
       <c r="C95" t="n">
-        <v>11.05999465045304</v>
+        <v>11.0599956157492</v>
       </c>
       <c r="D95" t="n">
-        <v>10.67618481396482</v>
+        <v>10.67618574576276</v>
       </c>
       <c r="E95" t="n">
-        <v>10.98166652400619</v>
+        <v>10.98166748246601</v>
       </c>
       <c r="F95" t="n">
         <v>1743500</v>
@@ -2352,16 +2352,16 @@
         <v>44784</v>
       </c>
       <c r="B97" t="n">
-        <v>10.89550590515137</v>
+        <v>10.89550495147705</v>
       </c>
       <c r="C97" t="n">
-        <v>11.10699344032233</v>
+        <v>11.10699246813669</v>
       </c>
       <c r="D97" t="n">
-        <v>10.83284309776729</v>
+        <v>10.83284214957779</v>
       </c>
       <c r="E97" t="n">
-        <v>11.05999596128448</v>
+        <v>11.05999499321249</v>
       </c>
       <c r="F97" t="n">
         <v>1665400</v>
@@ -2372,16 +2372,16 @@
         <v>44785</v>
       </c>
       <c r="B98" t="n">
-        <v>11.08349323272705</v>
+        <v>11.08349418640137</v>
       </c>
       <c r="C98" t="n">
-        <v>11.13049070712356</v>
+        <v>11.13049166484175</v>
       </c>
       <c r="D98" t="n">
-        <v>10.78584530054738</v>
+        <v>10.78584622861072</v>
       </c>
       <c r="E98" t="n">
-        <v>10.89550482914005</v>
+        <v>10.89550576663898</v>
       </c>
       <c r="F98" t="n">
         <v>2648400</v>
@@ -2392,16 +2392,16 @@
         <v>44788</v>
       </c>
       <c r="B99" t="n">
-        <v>11.21665096282959</v>
+        <v>11.21665191650391</v>
       </c>
       <c r="C99" t="n">
-        <v>11.3106451570042</v>
+        <v>11.3106461186702</v>
       </c>
       <c r="D99" t="n">
-        <v>10.92683534404133</v>
+        <v>10.92683627307463</v>
       </c>
       <c r="E99" t="n">
-        <v>10.99733117642216</v>
+        <v>10.99733211144923</v>
       </c>
       <c r="F99" t="n">
         <v>3450900</v>
@@ -2412,16 +2412,16 @@
         <v>44789</v>
       </c>
       <c r="B100" t="n">
-        <v>11.04433059692383</v>
+        <v>11.04432964324951</v>
       </c>
       <c r="C100" t="n">
-        <v>11.2949818256428</v>
+        <v>11.29498085032484</v>
       </c>
       <c r="D100" t="n">
-        <v>10.94250334850685</v>
+        <v>10.94250240362528</v>
       </c>
       <c r="E100" t="n">
-        <v>11.25581738440557</v>
+        <v>11.25581641246944</v>
       </c>
       <c r="F100" t="n">
         <v>1185300</v>
@@ -2452,16 +2452,16 @@
         <v>44791</v>
       </c>
       <c r="B102" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="C102" t="n">
-        <v>11.37330897550059</v>
+        <v>11.37330994384684</v>
       </c>
       <c r="D102" t="n">
-        <v>11.09915867560374</v>
+        <v>11.09915962060828</v>
       </c>
       <c r="E102" t="n">
-        <v>11.27931403205064</v>
+        <v>11.27931499239396</v>
       </c>
       <c r="F102" t="n">
         <v>2180500</v>
@@ -2532,16 +2532,16 @@
         <v>44797</v>
       </c>
       <c r="B106" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C106" t="n">
-        <v>11.39680739514549</v>
+        <v>11.3968083737041</v>
       </c>
       <c r="D106" t="n">
-        <v>11.09915873138986</v>
+        <v>11.09915968439161</v>
       </c>
       <c r="E106" t="n">
-        <v>11.22448432728707</v>
+        <v>11.2244852910496</v>
       </c>
       <c r="F106" t="n">
         <v>2116800</v>
@@ -2552,16 +2552,16 @@
         <v>44798</v>
       </c>
       <c r="B107" t="n">
-        <v>11.04433059692383</v>
+        <v>11.04432964324951</v>
       </c>
       <c r="C107" t="n">
-        <v>11.22448598081569</v>
+        <v>11.22448501158502</v>
       </c>
       <c r="D107" t="n">
-        <v>10.95033563915463</v>
+        <v>10.95033469359675</v>
       </c>
       <c r="E107" t="n">
-        <v>11.20882065252055</v>
+        <v>11.20881968464257</v>
       </c>
       <c r="F107" t="n">
         <v>2435800</v>
@@ -2612,16 +2612,16 @@
         <v>44803</v>
       </c>
       <c r="B110" t="n">
-        <v>11.0129976272583</v>
+        <v>11.01299858093262</v>
       </c>
       <c r="C110" t="n">
-        <v>11.16182158639716</v>
+        <v>11.16182255295894</v>
       </c>
       <c r="D110" t="n">
-        <v>10.93466875592239</v>
+        <v>10.93466970281379</v>
       </c>
       <c r="E110" t="n">
-        <v>11.11482411419572</v>
+        <v>11.11482507668773</v>
       </c>
       <c r="F110" t="n">
         <v>1284900</v>
@@ -2652,16 +2652,16 @@
         <v>44805</v>
       </c>
       <c r="B112" t="n">
-        <v>11.65529251098633</v>
+        <v>11.65529346466064</v>
       </c>
       <c r="C112" t="n">
-        <v>12.15659567974902</v>
+        <v>12.1565966744416</v>
       </c>
       <c r="D112" t="n">
-        <v>11.42030662728508</v>
+        <v>11.42030756173208</v>
       </c>
       <c r="E112" t="n">
-        <v>12.14092960556915</v>
+        <v>12.14093059897989</v>
       </c>
       <c r="F112" t="n">
         <v>4716400</v>
@@ -2732,16 +2732,16 @@
         <v>44812</v>
       </c>
       <c r="B116" t="n">
-        <v>11.43597221374512</v>
+        <v>11.4359712600708</v>
       </c>
       <c r="C116" t="n">
-        <v>11.63962594040124</v>
+        <v>11.63962496974372</v>
       </c>
       <c r="D116" t="n">
-        <v>11.37330941369716</v>
+        <v>11.37330846524845</v>
       </c>
       <c r="E116" t="n">
-        <v>11.623960613889</v>
+        <v>11.62395964453786</v>
       </c>
       <c r="F116" t="n">
         <v>2598100</v>
@@ -2812,16 +2812,16 @@
         <v>44818</v>
       </c>
       <c r="B120" t="n">
-        <v>11.20881938934326</v>
+        <v>11.20882034301758</v>
       </c>
       <c r="C120" t="n">
-        <v>11.42030615299151</v>
+        <v>11.42030712465965</v>
       </c>
       <c r="D120" t="n">
-        <v>11.02866327875449</v>
+        <v>11.02866421710068</v>
       </c>
       <c r="E120" t="n">
-        <v>11.20098635257864</v>
+        <v>11.2009873055865</v>
       </c>
       <c r="F120" t="n">
         <v>1856400</v>
@@ -2872,16 +2872,16 @@
         <v>44823</v>
       </c>
       <c r="B123" t="n">
-        <v>11.28714847564697</v>
+        <v>11.28714752197266</v>
       </c>
       <c r="C123" t="n">
-        <v>11.43597319883014</v>
+        <v>11.43597223258132</v>
       </c>
       <c r="D123" t="n">
-        <v>11.11482538717157</v>
+        <v>11.11482444805718</v>
       </c>
       <c r="E123" t="n">
-        <v>11.11482538717157</v>
+        <v>11.11482444805718</v>
       </c>
       <c r="F123" t="n">
         <v>1858600</v>
@@ -2952,16 +2952,16 @@
         <v>44827</v>
       </c>
       <c r="B127" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="C127" t="n">
-        <v>11.30281314141286</v>
+        <v>11.30281410375695</v>
       </c>
       <c r="D127" t="n">
-        <v>11.07566031324099</v>
+        <v>11.07566125624483</v>
       </c>
       <c r="E127" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="F127" t="n">
         <v>2444100</v>
@@ -2992,16 +2992,16 @@
         <v>44831</v>
       </c>
       <c r="B129" t="n">
-        <v>10.9033374786377</v>
+        <v>10.90333843231201</v>
       </c>
       <c r="C129" t="n">
-        <v>11.04432914981819</v>
+        <v>11.04433011582452</v>
       </c>
       <c r="D129" t="n">
-        <v>10.77017884407822</v>
+        <v>10.77017978610565</v>
       </c>
       <c r="E129" t="n">
-        <v>11.04432914981819</v>
+        <v>11.04433011582452</v>
       </c>
       <c r="F129" t="n">
         <v>2130200</v>
@@ -3032,16 +3032,16 @@
         <v>44833</v>
       </c>
       <c r="B131" t="n">
-        <v>10.70751667022705</v>
+        <v>10.70751571655273</v>
       </c>
       <c r="C131" t="n">
-        <v>10.83284227548216</v>
+        <v>10.83284131064561</v>
       </c>
       <c r="D131" t="n">
-        <v>10.6448538675995</v>
+        <v>10.6448529195063</v>
       </c>
       <c r="E131" t="n">
-        <v>10.6918505960704</v>
+        <v>10.69184964379139</v>
       </c>
       <c r="F131" t="n">
         <v>2222600</v>
@@ -3072,16 +3072,16 @@
         <v>44837</v>
       </c>
       <c r="B133" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="C133" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="D133" t="n">
-        <v>10.62918694635185</v>
+        <v>10.62918785134206</v>
       </c>
       <c r="E133" t="n">
-        <v>10.74668025216456</v>
+        <v>10.74668116715839</v>
       </c>
       <c r="F133" t="n">
         <v>2250700</v>
@@ -3112,16 +3112,16 @@
         <v>44839</v>
       </c>
       <c r="B135" t="n">
-        <v>10.97383308410645</v>
+        <v>10.97383403778076</v>
       </c>
       <c r="C135" t="n">
-        <v>11.20881894881312</v>
+        <v>11.20881992290874</v>
       </c>
       <c r="D135" t="n">
-        <v>10.85633977825337</v>
+        <v>10.85634072171701</v>
       </c>
       <c r="E135" t="n">
-        <v>11.20881894881312</v>
+        <v>11.20881992290874</v>
       </c>
       <c r="F135" t="n">
         <v>5244200</v>
@@ -3152,16 +3152,16 @@
         <v>44841</v>
       </c>
       <c r="B137" t="n">
-        <v>11.02866363525391</v>
+        <v>11.02866458892822</v>
       </c>
       <c r="C137" t="n">
-        <v>11.15398923954096</v>
+        <v>11.15399020405247</v>
       </c>
       <c r="D137" t="n">
-        <v>10.94250246905644</v>
+        <v>10.9425034152802</v>
       </c>
       <c r="E137" t="n">
-        <v>10.98166690714602</v>
+        <v>10.98166785675642</v>
       </c>
       <c r="F137" t="n">
         <v>7588600</v>
@@ -3172,16 +3172,16 @@
         <v>44844</v>
       </c>
       <c r="B138" t="n">
-        <v>11.07566165924072</v>
+        <v>11.07565975189209</v>
       </c>
       <c r="C138" t="n">
-        <v>11.35764428286087</v>
+        <v>11.35764232695178</v>
       </c>
       <c r="D138" t="n">
-        <v>11.0129988539918</v>
+        <v>11.01299695743438</v>
       </c>
       <c r="E138" t="n">
-        <v>11.07566165924072</v>
+        <v>11.07565975189209</v>
       </c>
       <c r="F138" t="n">
         <v>2000500</v>
@@ -3232,16 +3232,16 @@
         <v>44848</v>
       </c>
       <c r="B141" t="n">
-        <v>10.82500839233398</v>
+        <v>10.8250093460083</v>
       </c>
       <c r="C141" t="n">
-        <v>11.16182149038183</v>
+        <v>11.1618224737291</v>
       </c>
       <c r="D141" t="n">
-        <v>10.82500839233398</v>
+        <v>10.8250093460083</v>
       </c>
       <c r="E141" t="n">
-        <v>10.97383309719211</v>
+        <v>10.97383406397776</v>
       </c>
       <c r="F141" t="n">
         <v>3601200</v>
@@ -3272,16 +3272,16 @@
         <v>44852</v>
       </c>
       <c r="B143" t="n">
-        <v>11.27148342132568</v>
+        <v>11.27148246765137</v>
       </c>
       <c r="C143" t="n">
-        <v>11.37331066939599</v>
+        <v>11.37330970710612</v>
       </c>
       <c r="D143" t="n">
-        <v>11.06782892518508</v>
+        <v>11.06782798874186</v>
       </c>
       <c r="E143" t="n">
-        <v>11.20882061435928</v>
+        <v>11.20881966598683</v>
       </c>
       <c r="F143" t="n">
         <v>2646800</v>
@@ -3312,16 +3312,16 @@
         <v>44854</v>
       </c>
       <c r="B145" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C145" t="n">
-        <v>10.98166658413194</v>
+        <v>10.98166755090811</v>
       </c>
       <c r="D145" t="n">
-        <v>10.39420227106638</v>
+        <v>10.39420318612486</v>
       </c>
       <c r="E145" t="n">
-        <v>10.57435763518006</v>
+        <v>10.5743585660986</v>
       </c>
       <c r="F145" t="n">
         <v>7194300</v>
@@ -3352,16 +3352,16 @@
         <v>44858</v>
       </c>
       <c r="B147" t="n">
-        <v>11.24798393249512</v>
+        <v>11.2479829788208</v>
       </c>
       <c r="C147" t="n">
-        <v>11.45163842182848</v>
+        <v>11.45163745088707</v>
       </c>
       <c r="D147" t="n">
-        <v>11.10699299503318</v>
+        <v>11.10699205331296</v>
       </c>
       <c r="E147" t="n">
-        <v>11.10699299503318</v>
+        <v>11.10699205331296</v>
       </c>
       <c r="F147" t="n">
         <v>2219500</v>
@@ -3392,16 +3392,16 @@
         <v>44860</v>
       </c>
       <c r="B149" t="n">
-        <v>11.34197807312012</v>
+        <v>11.3419771194458</v>
       </c>
       <c r="C149" t="n">
-        <v>11.45163835450095</v>
+        <v>11.451637391606</v>
       </c>
       <c r="D149" t="n">
-        <v>11.20098713648711</v>
+        <v>11.20098619466782</v>
       </c>
       <c r="E149" t="n">
-        <v>11.43597302687486</v>
+        <v>11.43597206529711</v>
       </c>
       <c r="F149" t="n">
         <v>4386900</v>
@@ -3412,16 +3412,16 @@
         <v>44861</v>
       </c>
       <c r="B150" t="n">
-        <v>11.35764408111572</v>
+        <v>11.35764312744141</v>
       </c>
       <c r="C150" t="n">
-        <v>11.63179440945972</v>
+        <v>11.63179343276565</v>
       </c>
       <c r="D150" t="n">
-        <v>11.27148291217882</v>
+        <v>11.27148196573925</v>
       </c>
       <c r="E150" t="n">
-        <v>11.42813992251844</v>
+        <v>11.42813896292475</v>
       </c>
       <c r="F150" t="n">
         <v>4207900</v>
@@ -3432,16 +3432,16 @@
         <v>44862</v>
       </c>
       <c r="B151" t="n">
-        <v>11.49080276489258</v>
+        <v>11.49080181121826</v>
       </c>
       <c r="C151" t="n">
-        <v>11.63962673846057</v>
+        <v>11.63962577243467</v>
       </c>
       <c r="D151" t="n">
-        <v>11.22448547292922</v>
+        <v>11.2244845413578</v>
       </c>
       <c r="E151" t="n">
-        <v>11.32631271673871</v>
+        <v>11.32631177671618</v>
       </c>
       <c r="F151" t="n">
         <v>2887600</v>
@@ -3512,16 +3512,16 @@
         <v>44869</v>
       </c>
       <c r="B155" t="n">
-        <v>11.67095851898193</v>
+        <v>11.67095756530762</v>
       </c>
       <c r="C155" t="n">
-        <v>11.87461301320299</v>
+        <v>11.87461204288736</v>
       </c>
       <c r="D155" t="n">
-        <v>11.64746015334091</v>
+        <v>11.64745920158673</v>
       </c>
       <c r="E155" t="n">
-        <v>11.74928740045144</v>
+        <v>11.7492864403766</v>
       </c>
       <c r="F155" t="n">
         <v>2161500</v>
@@ -3532,16 +3532,16 @@
         <v>44872</v>
       </c>
       <c r="B156" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="C156" t="n">
-        <v>11.65529156485204</v>
+        <v>11.65529255720685</v>
       </c>
       <c r="D156" t="n">
-        <v>11.1226570379665</v>
+        <v>11.12265798497174</v>
       </c>
       <c r="E156" t="n">
-        <v>11.60829409312706</v>
+        <v>11.60829508148041</v>
       </c>
       <c r="F156" t="n">
         <v>3276500</v>
@@ -3592,16 +3592,16 @@
         <v>44875</v>
       </c>
       <c r="B159" t="n">
-        <v>10.70751667022705</v>
+        <v>10.70751571655273</v>
       </c>
       <c r="C159" t="n">
-        <v>11.10699259722736</v>
+        <v>11.10699160797338</v>
       </c>
       <c r="D159" t="n">
-        <v>10.4960291511094</v>
+        <v>10.49602821627141</v>
       </c>
       <c r="E159" t="n">
-        <v>11.04432979459981</v>
+        <v>11.04432881092694</v>
       </c>
       <c r="F159" t="n">
         <v>4341400</v>
@@ -3612,16 +3612,16 @@
         <v>44876</v>
       </c>
       <c r="B160" t="n">
-        <v>10.79367733001709</v>
+        <v>10.79367828369141</v>
       </c>
       <c r="C160" t="n">
-        <v>10.85634012970083</v>
+        <v>10.85634108891171</v>
       </c>
       <c r="D160" t="n">
-        <v>10.5351930945718</v>
+        <v>10.53519402540776</v>
       </c>
       <c r="E160" t="n">
-        <v>10.78584504030624</v>
+        <v>10.78584599328854</v>
       </c>
       <c r="F160" t="n">
         <v>3291200</v>
@@ -3632,16 +3632,16 @@
         <v>44879</v>
       </c>
       <c r="B161" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C161" t="n">
-        <v>10.9660005105571</v>
+        <v>10.9660014759541</v>
       </c>
       <c r="D161" t="n">
-        <v>10.71534930935563</v>
+        <v>10.71535025268644</v>
       </c>
       <c r="E161" t="n">
-        <v>10.94250214719434</v>
+        <v>10.94250311052265</v>
       </c>
       <c r="F161" t="n">
         <v>1203700</v>
@@ -3652,16 +3652,16 @@
         <v>44881</v>
       </c>
       <c r="B162" t="n">
-        <v>10.9033374786377</v>
+        <v>10.90333843231201</v>
       </c>
       <c r="C162" t="n">
-        <v>10.9033374786377</v>
+        <v>10.90333843231201</v>
       </c>
       <c r="D162" t="n">
-        <v>10.59785577341312</v>
+        <v>10.59785670036809</v>
       </c>
       <c r="E162" t="n">
-        <v>10.86417304253206</v>
+        <v>10.86417399278081</v>
       </c>
       <c r="F162" t="n">
         <v>5270300</v>
@@ -3692,16 +3692,16 @@
         <v>44883</v>
       </c>
       <c r="B164" t="n">
-        <v>10.78584575653076</v>
+        <v>10.78584480285645</v>
       </c>
       <c r="C164" t="n">
-        <v>10.98949949552661</v>
+        <v>10.98949852384542</v>
       </c>
       <c r="D164" t="n">
-        <v>10.57435823330488</v>
+        <v>10.57435729833009</v>
       </c>
       <c r="E164" t="n">
-        <v>10.80934412122268</v>
+        <v>10.80934316547066</v>
       </c>
       <c r="F164" t="n">
         <v>3568700</v>
@@ -3752,16 +3752,16 @@
         <v>44888</v>
       </c>
       <c r="B167" t="n">
-        <v>10.56652450561523</v>
+        <v>10.56652545928955</v>
       </c>
       <c r="C167" t="n">
-        <v>10.8171764516154</v>
+        <v>10.81717742791213</v>
       </c>
       <c r="D167" t="n">
-        <v>10.51952777930236</v>
+        <v>10.51952872873502</v>
       </c>
       <c r="E167" t="n">
-        <v>10.80934341489675</v>
+        <v>10.80934439048652</v>
       </c>
       <c r="F167" t="n">
         <v>4669400</v>
@@ -3792,16 +3792,16 @@
         <v>44890</v>
       </c>
       <c r="B169" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C169" t="n">
-        <v>11.03649634764489</v>
+        <v>11.03649731924802</v>
       </c>
       <c r="D169" t="n">
-        <v>10.71534930935563</v>
+        <v>10.71535025268644</v>
       </c>
       <c r="E169" t="n">
-        <v>10.95033443698226</v>
+        <v>10.95033540100009</v>
       </c>
       <c r="F169" t="n">
         <v>1631500</v>
@@ -3812,16 +3812,16 @@
         <v>44893</v>
       </c>
       <c r="B170" t="n">
-        <v>10.97383308410645</v>
+        <v>10.97383403778076</v>
       </c>
       <c r="C170" t="n">
-        <v>11.09915867941681</v>
+        <v>11.09915964398247</v>
       </c>
       <c r="D170" t="n">
-        <v>10.68401745820135</v>
+        <v>10.68401838668942</v>
       </c>
       <c r="E170" t="n">
-        <v>10.84067445233931</v>
+        <v>10.84067539444156</v>
       </c>
       <c r="F170" t="n">
         <v>4990000</v>
@@ -3852,16 +3852,16 @@
         <v>44895</v>
       </c>
       <c r="B172" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C172" t="n">
-        <v>11.20881942197064</v>
+        <v>11.20882040874432</v>
       </c>
       <c r="D172" t="n">
-        <v>10.69185019899337</v>
+        <v>10.69185114025542</v>
       </c>
       <c r="E172" t="n">
-        <v>11.20881942197064</v>
+        <v>11.20882040874432</v>
       </c>
       <c r="F172" t="n">
         <v>4586400</v>
@@ -3872,16 +3872,16 @@
         <v>44896</v>
       </c>
       <c r="B173" t="n">
-        <v>10.92683601379395</v>
+        <v>10.92683696746826</v>
       </c>
       <c r="C173" t="n">
-        <v>11.02083021372987</v>
+        <v>11.02083117560783</v>
       </c>
       <c r="D173" t="n">
-        <v>10.69185014045439</v>
+        <v>10.69185107361957</v>
       </c>
       <c r="E173" t="n">
-        <v>10.76234597715621</v>
+        <v>10.76234691647413</v>
       </c>
       <c r="F173" t="n">
         <v>1944500</v>
@@ -4032,16 +4032,16 @@
         <v>44908</v>
       </c>
       <c r="B181" t="n">
-        <v>11.08349323272705</v>
+        <v>11.08349418640137</v>
       </c>
       <c r="C181" t="n">
-        <v>11.3028137839114</v>
+        <v>11.30281475645706</v>
       </c>
       <c r="D181" t="n">
-        <v>10.99733206783289</v>
+        <v>10.9973330140935</v>
       </c>
       <c r="E181" t="n">
-        <v>11.00516510473222</v>
+        <v>11.00516605166683</v>
       </c>
       <c r="F181" t="n">
         <v>3594700</v>
@@ -4092,16 +4092,16 @@
         <v>44911</v>
       </c>
       <c r="B184" t="n">
-        <v>11.24798393249512</v>
+        <v>11.2479829788208</v>
       </c>
       <c r="C184" t="n">
-        <v>11.24798393249512</v>
+        <v>11.2479829788208</v>
       </c>
       <c r="D184" t="n">
-        <v>10.90333850569981</v>
+        <v>10.90333758124669</v>
       </c>
       <c r="E184" t="n">
-        <v>11.04433019016131</v>
+        <v>11.04432925375403</v>
       </c>
       <c r="F184" t="n">
         <v>3365900</v>
@@ -4112,16 +4112,16 @@
         <v>44914</v>
       </c>
       <c r="B185" t="n">
-        <v>11.37330913543701</v>
+        <v>11.37331008911133</v>
       </c>
       <c r="C185" t="n">
-        <v>11.5221330951599</v>
+        <v>11.5221340613134</v>
       </c>
       <c r="D185" t="n">
-        <v>11.18531999289299</v>
+        <v>11.18532093080405</v>
       </c>
       <c r="E185" t="n">
-        <v>11.23231746527886</v>
+        <v>11.23231840713075</v>
       </c>
       <c r="F185" t="n">
         <v>3838800</v>
@@ -4192,16 +4192,16 @@
         <v>44918</v>
       </c>
       <c r="B189" t="n">
-        <v>11.78845024108887</v>
+        <v>11.78845119476318</v>
       </c>
       <c r="C189" t="n">
-        <v>12.09393119395663</v>
+        <v>12.09393217234406</v>
       </c>
       <c r="D189" t="n">
-        <v>11.57696273802706</v>
+        <v>11.57696367459224</v>
       </c>
       <c r="E189" t="n">
-        <v>11.67878997131614</v>
+        <v>11.67879091611904</v>
       </c>
       <c r="F189" t="n">
         <v>5656000</v>
@@ -4212,16 +4212,16 @@
         <v>44921</v>
       </c>
       <c r="B190" t="n">
-        <v>11.57696437835693</v>
+        <v>11.57696342468262</v>
       </c>
       <c r="C190" t="n">
-        <v>11.82761635235219</v>
+        <v>11.82761537802995</v>
       </c>
       <c r="D190" t="n">
-        <v>11.51430157160801</v>
+        <v>11.51430062309566</v>
       </c>
       <c r="E190" t="n">
-        <v>11.7727858361972</v>
+        <v>11.77278486639172</v>
       </c>
       <c r="F190" t="n">
         <v>1646600</v>
@@ -4232,16 +4232,16 @@
         <v>44922</v>
       </c>
       <c r="B191" t="n">
-        <v>11.52996635437012</v>
+        <v>11.52996730804443</v>
       </c>
       <c r="C191" t="n">
-        <v>11.60829448052647</v>
+        <v>11.60829544067951</v>
       </c>
       <c r="D191" t="n">
-        <v>11.34197720819598</v>
+        <v>11.34197814632122</v>
       </c>
       <c r="E191" t="n">
-        <v>11.60829448052647</v>
+        <v>11.60829544067951</v>
       </c>
       <c r="F191" t="n">
         <v>1633000</v>
@@ -4272,16 +4272,16 @@
         <v>44924</v>
       </c>
       <c r="B193" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="C193" t="n">
-        <v>11.73362129131107</v>
+        <v>11.73362032145083</v>
       </c>
       <c r="D193" t="n">
-        <v>11.47513702901113</v>
+        <v>11.4751360805163</v>
       </c>
       <c r="E193" t="n">
-        <v>11.62396175397144</v>
+        <v>11.62396079317528</v>
       </c>
       <c r="F193" t="n">
         <v>2424800</v>
@@ -4292,16 +4292,16 @@
         <v>44928</v>
       </c>
       <c r="B194" t="n">
-        <v>11.34197807312012</v>
+        <v>11.3419771194458</v>
       </c>
       <c r="C194" t="n">
-        <v>11.46730442912659</v>
+        <v>11.46730346491438</v>
       </c>
       <c r="D194" t="n">
-        <v>11.1774887715482</v>
+        <v>11.17748783170473</v>
       </c>
       <c r="E194" t="n">
-        <v>11.38897554999749</v>
+        <v>11.38897459237146</v>
       </c>
       <c r="F194" t="n">
         <v>1018800</v>
@@ -4312,16 +4312,16 @@
         <v>44929</v>
       </c>
       <c r="B195" t="n">
-        <v>11.13832473754883</v>
+        <v>11.13832378387451</v>
       </c>
       <c r="C195" t="n">
-        <v>11.32631315790418</v>
+        <v>11.32631218813412</v>
       </c>
       <c r="D195" t="n">
-        <v>11.05999585556764</v>
+        <v>11.05999490859992</v>
       </c>
       <c r="E195" t="n">
-        <v>11.30281479210966</v>
+        <v>11.30281382435154</v>
       </c>
       <c r="F195" t="n">
         <v>1562800</v>
@@ -4332,16 +4332,16 @@
         <v>44930</v>
       </c>
       <c r="B196" t="n">
-        <v>11.35764408111572</v>
+        <v>11.35764312744141</v>
       </c>
       <c r="C196" t="n">
-        <v>11.35764408111572</v>
+        <v>11.35764312744141</v>
       </c>
       <c r="D196" t="n">
-        <v>10.9660011817669</v>
+        <v>10.96600026097791</v>
       </c>
       <c r="E196" t="n">
-        <v>11.16965566870818</v>
+        <v>11.1696547308188</v>
       </c>
       <c r="F196" t="n">
         <v>2937400</v>
@@ -4372,16 +4372,16 @@
         <v>44932</v>
       </c>
       <c r="B198" t="n">
-        <v>11.42030620574951</v>
+        <v>11.42030715942383</v>
       </c>
       <c r="C198" t="n">
-        <v>11.53779876976359</v>
+        <v>11.53779973324935</v>
       </c>
       <c r="D198" t="n">
-        <v>11.31847896833754</v>
+        <v>11.31847991350858</v>
       </c>
       <c r="E198" t="n">
-        <v>11.4124731689487</v>
+        <v>11.41247412196891</v>
       </c>
       <c r="F198" t="n">
         <v>2864500</v>
@@ -4432,16 +4432,16 @@
         <v>44937</v>
       </c>
       <c r="B201" t="n">
-        <v>11.49863529205322</v>
+        <v>11.49863624572754</v>
       </c>
       <c r="C201" t="n">
-        <v>11.61612785823652</v>
+        <v>11.61612882165544</v>
       </c>
       <c r="D201" t="n">
-        <v>11.06782797104859</v>
+        <v>11.0678288889926</v>
       </c>
       <c r="E201" t="n">
-        <v>11.09132633488535</v>
+        <v>11.09132725477826</v>
       </c>
       <c r="F201" t="n">
         <v>4499200</v>
@@ -4452,16 +4452,16 @@
         <v>44938</v>
       </c>
       <c r="B202" t="n">
-        <v>11.79628276824951</v>
+        <v>11.79628372192383</v>
       </c>
       <c r="C202" t="n">
-        <v>11.97643811759822</v>
+        <v>11.97643908583725</v>
       </c>
       <c r="D202" t="n">
-        <v>11.49863411771738</v>
+        <v>11.49863504732819</v>
       </c>
       <c r="E202" t="n">
-        <v>11.49863411771738</v>
+        <v>11.49863504732819</v>
       </c>
       <c r="F202" t="n">
         <v>5662900</v>
@@ -4492,16 +4492,16 @@
         <v>44942</v>
       </c>
       <c r="B204" t="n">
-        <v>11.78845024108887</v>
+        <v>11.78845119476318</v>
       </c>
       <c r="C204" t="n">
-        <v>11.8041155670567</v>
+        <v>11.80411652199833</v>
       </c>
       <c r="D204" t="n">
-        <v>11.39680738089987</v>
+        <v>11.39680830289065</v>
       </c>
       <c r="E204" t="n">
-        <v>11.49080157770529</v>
+        <v>11.49080250730011</v>
       </c>
       <c r="F204" t="n">
         <v>3279700</v>
@@ -4512,16 +4512,16 @@
         <v>44943</v>
       </c>
       <c r="B205" t="n">
-        <v>11.74928569793701</v>
+        <v>11.74928665161133</v>
       </c>
       <c r="C205" t="n">
-        <v>11.93727408982413</v>
+        <v>11.93727505875722</v>
       </c>
       <c r="D205" t="n">
-        <v>11.60829403052194</v>
+        <v>11.60829497275214</v>
       </c>
       <c r="E205" t="n">
-        <v>11.81194849523272</v>
+        <v>11.81194945399329</v>
       </c>
       <c r="F205" t="n">
         <v>2676600</v>
@@ -4552,16 +4552,16 @@
         <v>44945</v>
       </c>
       <c r="B207" t="n">
-        <v>11.66312503814697</v>
+        <v>11.66312599182129</v>
       </c>
       <c r="C207" t="n">
-        <v>11.68662340138985</v>
+        <v>11.68662435698559</v>
       </c>
       <c r="D207" t="n">
-        <v>11.27931445451592</v>
+        <v>11.27931537680668</v>
       </c>
       <c r="E207" t="n">
-        <v>11.3419772544966</v>
+        <v>11.3419781819112</v>
       </c>
       <c r="F207" t="n">
         <v>1847800</v>
@@ -4592,16 +4592,16 @@
         <v>44949</v>
       </c>
       <c r="B209" t="n">
-        <v>11.52213382720947</v>
+        <v>11.52213287353516</v>
       </c>
       <c r="C209" t="n">
-        <v>11.64745943220163</v>
+        <v>11.64745846815425</v>
       </c>
       <c r="D209" t="n">
-        <v>11.34981074684549</v>
+        <v>11.34980980743417</v>
       </c>
       <c r="E209" t="n">
-        <v>11.59262966676744</v>
+        <v>11.59262870725826</v>
       </c>
       <c r="F209" t="n">
         <v>1770800</v>
@@ -4652,16 +4652,16 @@
         <v>44952</v>
       </c>
       <c r="B212" t="n">
-        <v>11.96860599517822</v>
+        <v>11.96860504150391</v>
       </c>
       <c r="C212" t="n">
-        <v>12.09393159507546</v>
+        <v>12.09393063141503</v>
       </c>
       <c r="D212" t="n">
-        <v>11.79628366881928</v>
+        <v>11.79628272887583</v>
       </c>
       <c r="E212" t="n">
-        <v>11.91377623197306</v>
+        <v>11.91377528266765</v>
       </c>
       <c r="F212" t="n">
         <v>8143300</v>
@@ -4712,16 +4712,16 @@
         <v>44957</v>
       </c>
       <c r="B215" t="n">
-        <v>12.0704345703125</v>
+        <v>12.07043266296387</v>
       </c>
       <c r="C215" t="n">
-        <v>12.14093041482172</v>
+        <v>12.14092849633346</v>
       </c>
       <c r="D215" t="n">
-        <v>11.82761638033583</v>
+        <v>11.8276145113569</v>
       </c>
       <c r="E215" t="n">
-        <v>11.84328170856034</v>
+        <v>11.84327983710599</v>
       </c>
       <c r="F215" t="n">
         <v>5446800</v>
@@ -4792,16 +4792,16 @@
         <v>44963</v>
       </c>
       <c r="B219" t="n">
-        <v>11.91377735137939</v>
+        <v>11.91377639770508</v>
       </c>
       <c r="C219" t="n">
-        <v>11.96077482925644</v>
+        <v>11.96077387182007</v>
       </c>
       <c r="D219" t="n">
-        <v>11.75712033678852</v>
+        <v>11.75711939565429</v>
       </c>
       <c r="E219" t="n">
-        <v>11.92161038885883</v>
+        <v>11.92160943455749</v>
       </c>
       <c r="F219" t="n">
         <v>3421200</v>
@@ -4832,16 +4832,16 @@
         <v>44965</v>
       </c>
       <c r="B221" t="n">
-        <v>11.71012306213379</v>
+        <v>11.71012210845947</v>
       </c>
       <c r="C221" t="n">
-        <v>11.78845194428836</v>
+        <v>11.78845098423493</v>
       </c>
       <c r="D221" t="n">
-        <v>11.54563300720885</v>
+        <v>11.54563206693063</v>
       </c>
       <c r="E221" t="n">
-        <v>11.68662469628725</v>
+        <v>11.68662374452664</v>
       </c>
       <c r="F221" t="n">
         <v>3697100</v>
@@ -4852,16 +4852,16 @@
         <v>44966</v>
       </c>
       <c r="B222" t="n">
-        <v>11.66312503814697</v>
+        <v>11.66312599182129</v>
       </c>
       <c r="C222" t="n">
-        <v>11.78845063810834</v>
+        <v>11.78845160203032</v>
       </c>
       <c r="D222" t="n">
-        <v>11.55346476468103</v>
+        <v>11.55346570938861</v>
       </c>
       <c r="E222" t="n">
-        <v>11.71012176463273</v>
+        <v>11.7101227221499</v>
       </c>
       <c r="F222" t="n">
         <v>2260100</v>
@@ -4872,16 +4872,16 @@
         <v>44967</v>
       </c>
       <c r="B223" t="n">
-        <v>11.72578811645508</v>
+        <v>11.72578907012939</v>
       </c>
       <c r="C223" t="n">
-        <v>11.88244512012525</v>
+        <v>11.88244608654069</v>
       </c>
       <c r="D223" t="n">
-        <v>11.62396087731959</v>
+        <v>11.62396182271216</v>
       </c>
       <c r="E223" t="n">
-        <v>11.62396087731959</v>
+        <v>11.62396182271216</v>
       </c>
       <c r="F223" t="n">
         <v>6075300</v>
@@ -4892,16 +4892,16 @@
         <v>44970</v>
       </c>
       <c r="B224" t="n">
-        <v>11.79628276824951</v>
+        <v>11.79628372192383</v>
       </c>
       <c r="C224" t="n">
-        <v>11.87461088870569</v>
+        <v>11.87461184871247</v>
       </c>
       <c r="D224" t="n">
-        <v>11.63179274419227</v>
+        <v>11.63179368456833</v>
       </c>
       <c r="E224" t="n">
-        <v>11.7414522622308</v>
+        <v>11.74145321147233</v>
       </c>
       <c r="F224" t="n">
         <v>2704300</v>
@@ -4912,16 +4912,16 @@
         <v>44971</v>
       </c>
       <c r="B225" t="n">
-        <v>11.71795558929443</v>
+        <v>11.71795463562012</v>
       </c>
       <c r="C225" t="n">
-        <v>11.8824456370539</v>
+        <v>11.88244466999244</v>
       </c>
       <c r="D225" t="n">
-        <v>11.51430110216375</v>
+        <v>11.51430016506401</v>
       </c>
       <c r="E225" t="n">
-        <v>11.78061839348856</v>
+        <v>11.78061743471438</v>
       </c>
       <c r="F225" t="n">
         <v>2141000</v>
@@ -4932,16 +4932,16 @@
         <v>44972</v>
       </c>
       <c r="B226" t="n">
-        <v>11.75712013244629</v>
+        <v>11.75711917877197</v>
       </c>
       <c r="C226" t="n">
-        <v>11.92944247200145</v>
+        <v>11.92944150434928</v>
       </c>
       <c r="D226" t="n">
-        <v>11.63179452295179</v>
+        <v>11.63179357944321</v>
       </c>
       <c r="E226" t="n">
-        <v>11.66312592532541</v>
+        <v>11.6631249792754</v>
       </c>
       <c r="F226" t="n">
         <v>3961900</v>
@@ -4972,16 +4972,16 @@
         <v>44974</v>
       </c>
       <c r="B228" t="n">
-        <v>11.72578811645508</v>
+        <v>11.72578907012939</v>
       </c>
       <c r="C228" t="n">
-        <v>12.13309632599753</v>
+        <v>12.13309731279878</v>
       </c>
       <c r="D228" t="n">
-        <v>11.55346503891813</v>
+        <v>11.55346597857718</v>
       </c>
       <c r="E228" t="n">
-        <v>11.94510792159332</v>
+        <v>11.94510889310522</v>
       </c>
       <c r="F228" t="n">
         <v>9428300</v>
@@ -4992,16 +4992,16 @@
         <v>44979</v>
       </c>
       <c r="B229" t="n">
-        <v>11.71795558929443</v>
+        <v>11.71795463562012</v>
       </c>
       <c r="C229" t="n">
-        <v>11.95294147852217</v>
+        <v>11.95294050572336</v>
       </c>
       <c r="D229" t="n">
-        <v>11.66312582237446</v>
+        <v>11.66312487316251</v>
       </c>
       <c r="E229" t="n">
-        <v>11.89811096460265</v>
+        <v>11.89810999626626</v>
       </c>
       <c r="F229" t="n">
         <v>6185800</v>
@@ -5012,16 +5012,16 @@
         <v>44980</v>
       </c>
       <c r="B230" t="n">
-        <v>11.67879104614258</v>
+        <v>11.67879009246826</v>
       </c>
       <c r="C230" t="n">
-        <v>11.85111412964489</v>
+        <v>11.8511131618989</v>
       </c>
       <c r="D230" t="n">
-        <v>11.61612824250529</v>
+        <v>11.61612729394793</v>
       </c>
       <c r="E230" t="n">
-        <v>11.79628436321215</v>
+        <v>11.79628339994349</v>
       </c>
       <c r="F230" t="n">
         <v>3218000</v>
@@ -5032,16 +5032,16 @@
         <v>44981</v>
       </c>
       <c r="B231" t="n">
-        <v>11.67879104614258</v>
+        <v>11.67879009246826</v>
       </c>
       <c r="C231" t="n">
-        <v>11.89811085887308</v>
+        <v>11.89810988728941</v>
       </c>
       <c r="D231" t="n">
-        <v>11.51430099984482</v>
+        <v>11.51430005960253</v>
       </c>
       <c r="E231" t="n">
-        <v>11.72578852237032</v>
+        <v>11.72578756485825</v>
       </c>
       <c r="F231" t="n">
         <v>4705500</v>
@@ -5072,16 +5072,16 @@
         <v>44985</v>
       </c>
       <c r="B233" t="n">
-        <v>11.59262847900391</v>
+        <v>11.59262943267822</v>
       </c>
       <c r="C233" t="n">
-        <v>11.82761433778766</v>
+        <v>11.82761531079323</v>
       </c>
       <c r="D233" t="n">
-        <v>11.54563100844737</v>
+        <v>11.54563195825542</v>
       </c>
       <c r="E233" t="n">
-        <v>11.67095660059886</v>
+        <v>11.67095756071688</v>
       </c>
       <c r="F233" t="n">
         <v>7018700</v>
@@ -5092,16 +5092,16 @@
         <v>44986</v>
       </c>
       <c r="B234" t="n">
-        <v>11.52996635437012</v>
+        <v>11.52996730804443</v>
       </c>
       <c r="C234" t="n">
-        <v>11.65529195381987</v>
+        <v>11.6552929178602</v>
       </c>
       <c r="D234" t="n">
-        <v>11.31847884504903</v>
+        <v>11.31847978123065</v>
       </c>
       <c r="E234" t="n">
-        <v>11.60046219081048</v>
+        <v>11.6004631503157</v>
       </c>
       <c r="F234" t="n">
         <v>8005300</v>
@@ -5112,16 +5112,16 @@
         <v>44987</v>
       </c>
       <c r="B235" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="C235" t="n">
-        <v>11.67879152264125</v>
+        <v>11.67879055731306</v>
       </c>
       <c r="D235" t="n">
-        <v>11.45947170096243</v>
+        <v>11.45947075376244</v>
       </c>
       <c r="E235" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="F235" t="n">
         <v>2250800</v>
@@ -5132,16 +5132,16 @@
         <v>44988</v>
       </c>
       <c r="B236" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="C236" t="n">
-        <v>11.64746011954428</v>
+        <v>11.64745915680582</v>
       </c>
       <c r="D236" t="n">
-        <v>11.45947170096243</v>
+        <v>11.45947075376244</v>
       </c>
       <c r="E236" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="F236" t="n">
         <v>1727100</v>
@@ -5172,16 +5172,16 @@
         <v>44992</v>
       </c>
       <c r="B238" t="n">
-        <v>11.61612701416016</v>
+        <v>11.61612796783447</v>
       </c>
       <c r="C238" t="n">
-        <v>11.6239600505364</v>
+        <v>11.6239610048538</v>
       </c>
       <c r="D238" t="n">
-        <v>11.38897418824534</v>
+        <v>11.3889751232706</v>
       </c>
       <c r="E238" t="n">
-        <v>11.52996585501987</v>
+        <v>11.52996680162043</v>
       </c>
       <c r="F238" t="n">
         <v>3776700</v>
@@ -5212,16 +5212,16 @@
         <v>44994</v>
       </c>
       <c r="B240" t="n">
-        <v>11.57696437835693</v>
+        <v>11.57696342468262</v>
       </c>
       <c r="C240" t="n">
-        <v>11.70228999185477</v>
+        <v>11.70228902785652</v>
       </c>
       <c r="D240" t="n">
-        <v>11.51430157160801</v>
+        <v>11.51430062309566</v>
       </c>
       <c r="E240" t="n">
-        <v>11.62396185691841</v>
+        <v>11.62396089937259</v>
       </c>
       <c r="F240" t="n">
         <v>2514900</v>
@@ -5232,16 +5232,16 @@
         <v>44995</v>
       </c>
       <c r="B241" t="n">
-        <v>11.57696437835693</v>
+        <v>11.57696342468262</v>
       </c>
       <c r="C241" t="n">
-        <v>11.63179489451192</v>
+        <v>11.63179393632084</v>
       </c>
       <c r="D241" t="n">
-        <v>11.44380572726558</v>
+        <v>11.44380478456046</v>
       </c>
       <c r="E241" t="n">
-        <v>11.57696437835693</v>
+        <v>11.57696342468262</v>
       </c>
       <c r="F241" t="n">
         <v>3626000</v>
@@ -5252,16 +5252,16 @@
         <v>44998</v>
       </c>
       <c r="B242" t="n">
-        <v>11.66312503814697</v>
+        <v>11.66312599182129</v>
       </c>
       <c r="C242" t="n">
-        <v>11.74145316462308</v>
+        <v>11.74145412470215</v>
       </c>
       <c r="D242" t="n">
-        <v>11.45947056471</v>
+        <v>11.45947150173183</v>
       </c>
       <c r="E242" t="n">
-        <v>11.52213336469069</v>
+        <v>11.52213430683635</v>
       </c>
       <c r="F242" t="n">
         <v>3223500</v>
@@ -5272,16 +5272,16 @@
         <v>44999</v>
       </c>
       <c r="B243" t="n">
-        <v>11.75712013244629</v>
+        <v>11.75711917877197</v>
       </c>
       <c r="C243" t="n">
-        <v>11.82761597453684</v>
+        <v>11.82761501514428</v>
       </c>
       <c r="D243" t="n">
-        <v>11.63962681329553</v>
+        <v>11.63962586915163</v>
       </c>
       <c r="E243" t="n">
-        <v>11.69445732769904</v>
+        <v>11.69445637910759</v>
       </c>
       <c r="F243" t="n">
         <v>2520000</v>
@@ -5292,16 +5292,16 @@
         <v>45000</v>
       </c>
       <c r="B244" t="n">
-        <v>11.74928569793701</v>
+        <v>11.74928665161133</v>
       </c>
       <c r="C244" t="n">
-        <v>11.89027736535209</v>
+        <v>11.89027833047051</v>
       </c>
       <c r="D244" t="n">
-        <v>11.61612706693377</v>
+        <v>11.61612800979977</v>
       </c>
       <c r="E244" t="n">
-        <v>11.71795429928916</v>
+        <v>11.71795525042035</v>
       </c>
       <c r="F244" t="n">
         <v>4602600</v>
@@ -5312,16 +5312,16 @@
         <v>45001</v>
       </c>
       <c r="B245" t="n">
-        <v>11.67095851898193</v>
+        <v>11.67095756530762</v>
       </c>
       <c r="C245" t="n">
-        <v>11.81195020682722</v>
+        <v>11.81194924163198</v>
       </c>
       <c r="D245" t="n">
-        <v>11.63962711579405</v>
+        <v>11.63962616467993</v>
       </c>
       <c r="E245" t="n">
-        <v>11.81195020682722</v>
+        <v>11.81194924163198</v>
       </c>
       <c r="F245" t="n">
         <v>5495800</v>
@@ -5372,16 +5372,16 @@
         <v>45006</v>
       </c>
       <c r="B248" t="n">
-        <v>11.34197807312012</v>
+        <v>11.3419771194458</v>
       </c>
       <c r="C248" t="n">
-        <v>11.42030695224922</v>
+        <v>11.42030599198873</v>
       </c>
       <c r="D248" t="n">
-        <v>11.27931526861666</v>
+        <v>11.27931432021125</v>
       </c>
       <c r="E248" t="n">
-        <v>11.36547718505858</v>
+        <v>11.36547622940837</v>
       </c>
       <c r="F248" t="n">
         <v>2410300</v>
@@ -5452,16 +5452,16 @@
         <v>45012</v>
       </c>
       <c r="B252" t="n">
-        <v>11.28714847564697</v>
+        <v>11.28714752197266</v>
       </c>
       <c r="C252" t="n">
-        <v>11.42030712396893</v>
+        <v>11.42030615904377</v>
       </c>
       <c r="D252" t="n">
-        <v>11.19315426747845</v>
+        <v>11.1931533217459</v>
       </c>
       <c r="E252" t="n">
-        <v>11.39680875867669</v>
+        <v>11.39680779573696</v>
       </c>
       <c r="F252" t="n">
         <v>2288800</v>
@@ -5472,16 +5472,16 @@
         <v>45013</v>
       </c>
       <c r="B253" t="n">
-        <v>11.42030620574951</v>
+        <v>11.42030715942383</v>
       </c>
       <c r="C253" t="n">
-        <v>11.45163760595323</v>
+        <v>11.45163856224394</v>
       </c>
       <c r="D253" t="n">
-        <v>11.25581616793009</v>
+        <v>11.25581710786836</v>
       </c>
       <c r="E253" t="n">
-        <v>11.31064593153673</v>
+        <v>11.31064687605366</v>
       </c>
       <c r="F253" t="n">
         <v>3302900</v>
@@ -5532,16 +5532,16 @@
         <v>45016</v>
       </c>
       <c r="B256" t="n">
-        <v>11.49080276489258</v>
+        <v>11.49080181121826</v>
       </c>
       <c r="C256" t="n">
-        <v>11.61612837358132</v>
+        <v>11.61612740950566</v>
       </c>
       <c r="D256" t="n">
-        <v>11.30281435185946</v>
+        <v>11.30281341378716</v>
       </c>
       <c r="E256" t="n">
-        <v>11.42813996054821</v>
+        <v>11.42813901207456</v>
       </c>
       <c r="F256" t="n">
         <v>5155800</v>
@@ -5552,16 +5552,16 @@
         <v>45019</v>
       </c>
       <c r="B257" t="n">
-        <v>11.34197807312012</v>
+        <v>11.3419771194458</v>
       </c>
       <c r="C257" t="n">
-        <v>11.58479700082069</v>
+        <v>11.58479602672929</v>
       </c>
       <c r="D257" t="n">
-        <v>11.24798386636493</v>
+        <v>11.24798292059398</v>
       </c>
       <c r="E257" t="n">
-        <v>11.58479700082069</v>
+        <v>11.58479602672929</v>
       </c>
       <c r="F257" t="n">
         <v>6471200</v>
@@ -5572,16 +5572,16 @@
         <v>45020</v>
       </c>
       <c r="B258" t="n">
-        <v>11.43597221374512</v>
+        <v>11.4359712600708</v>
       </c>
       <c r="C258" t="n">
-        <v>11.49863501379308</v>
+        <v>11.49863405489315</v>
       </c>
       <c r="D258" t="n">
-        <v>11.24798306660174</v>
+        <v>11.24798212860431</v>
       </c>
       <c r="E258" t="n">
-        <v>11.35764334018542</v>
+        <v>11.35764239304314</v>
       </c>
       <c r="F258" t="n">
         <v>5230100</v>
@@ -5592,16 +5592,16 @@
         <v>45021</v>
       </c>
       <c r="B259" t="n">
-        <v>11.49080276489258</v>
+        <v>11.49080181121826</v>
       </c>
       <c r="C259" t="n">
-        <v>11.56913164382282</v>
+        <v>11.56913068364763</v>
       </c>
       <c r="D259" t="n">
-        <v>11.27931523998066</v>
+        <v>11.27931430385866</v>
       </c>
       <c r="E259" t="n">
-        <v>11.55346556923695</v>
+        <v>11.55346461036196</v>
       </c>
       <c r="F259" t="n">
         <v>4689800</v>
@@ -5612,16 +5612,16 @@
         <v>45022</v>
       </c>
       <c r="B260" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="C260" t="n">
-        <v>11.66312619459255</v>
+        <v>11.6631252305592</v>
       </c>
       <c r="D260" t="n">
-        <v>11.47513702901113</v>
+        <v>11.4751360805163</v>
       </c>
       <c r="E260" t="n">
-        <v>11.4908031040594</v>
+        <v>11.49080215426967</v>
       </c>
       <c r="F260" t="n">
         <v>4653400</v>
@@ -5632,16 +5632,16 @@
         <v>45026</v>
       </c>
       <c r="B261" t="n">
-        <v>11.71795558929443</v>
+        <v>11.71795463562012</v>
       </c>
       <c r="C261" t="n">
-        <v>11.85111423495683</v>
+        <v>11.85111327044531</v>
       </c>
       <c r="D261" t="n">
-        <v>11.45947133524378</v>
+        <v>11.4594704026064</v>
       </c>
       <c r="E261" t="n">
-        <v>11.53779946698666</v>
+        <v>11.53779852797449</v>
       </c>
       <c r="F261" t="n">
         <v>3430500</v>
@@ -5652,16 +5652,16 @@
         <v>45027</v>
       </c>
       <c r="B262" t="n">
-        <v>11.76495265960693</v>
+        <v>11.76495361328125</v>
       </c>
       <c r="C262" t="n">
-        <v>12.01560386772655</v>
+        <v>12.0156048417188</v>
       </c>
       <c r="D262" t="n">
-        <v>11.71012214758113</v>
+        <v>11.71012309681085</v>
       </c>
       <c r="E262" t="n">
-        <v>11.82761546163684</v>
+        <v>11.82761642039064</v>
       </c>
       <c r="F262" t="n">
         <v>2622300</v>
@@ -5672,16 +5672,16 @@
         <v>45028</v>
       </c>
       <c r="B263" t="n">
-        <v>11.80411624908447</v>
+        <v>11.80411529541016</v>
       </c>
       <c r="C263" t="n">
-        <v>12.01560376436578</v>
+        <v>12.01560279360503</v>
       </c>
       <c r="D263" t="n">
-        <v>11.74928648452985</v>
+        <v>11.74928553528532</v>
       </c>
       <c r="E263" t="n">
-        <v>11.82761535989319</v>
+        <v>11.82761440432034</v>
       </c>
       <c r="F263" t="n">
         <v>2987000</v>
@@ -5692,16 +5692,16 @@
         <v>45029</v>
       </c>
       <c r="B264" t="n">
-        <v>11.91377735137939</v>
+        <v>11.91377639770508</v>
       </c>
       <c r="C264" t="n">
-        <v>11.99993852265448</v>
+        <v>11.99993756208313</v>
       </c>
       <c r="D264" t="n">
-        <v>11.77278566474782</v>
+        <v>11.77278472235961</v>
       </c>
       <c r="E264" t="n">
-        <v>11.82761618010431</v>
+        <v>11.82761523332702</v>
       </c>
       <c r="F264" t="n">
         <v>3337400</v>
@@ -5752,16 +5752,16 @@
         <v>45034</v>
       </c>
       <c r="B267" t="n">
-        <v>11.96860599517822</v>
+        <v>11.96860504150391</v>
       </c>
       <c r="C267" t="n">
-        <v>12.16442743176752</v>
+        <v>12.1644264624899</v>
       </c>
       <c r="D267" t="n">
-        <v>11.94510763194737</v>
+        <v>11.94510668014543</v>
       </c>
       <c r="E267" t="n">
-        <v>12.14092906853667</v>
+        <v>12.14092810113142</v>
       </c>
       <c r="F267" t="n">
         <v>3259600</v>
@@ -5832,16 +5832,16 @@
         <v>45041</v>
       </c>
       <c r="B271" t="n">
-        <v>12.06260108947754</v>
+        <v>12.06260013580322</v>
       </c>
       <c r="C271" t="n">
-        <v>12.14092996872072</v>
+        <v>12.14092900885369</v>
       </c>
       <c r="D271" t="n">
-        <v>11.96860688258545</v>
+        <v>11.96860593634236</v>
       </c>
       <c r="E271" t="n">
-        <v>12.11743160374759</v>
+        <v>12.11743064573835</v>
       </c>
       <c r="F271" t="n">
         <v>2381100</v>
@@ -5912,16 +5912,16 @@
         <v>45048</v>
       </c>
       <c r="B275" t="n">
-        <v>12.39158058166504</v>
+        <v>12.39158153533936</v>
       </c>
       <c r="C275" t="n">
-        <v>12.650064824739</v>
+        <v>12.65006579830664</v>
       </c>
       <c r="D275" t="n">
-        <v>12.2505896517153</v>
+        <v>12.25059059453875</v>
       </c>
       <c r="E275" t="n">
-        <v>12.5325722586143</v>
+        <v>12.53257322313954</v>
       </c>
       <c r="F275" t="n">
         <v>5999300</v>
@@ -5972,16 +5972,16 @@
         <v>45051</v>
       </c>
       <c r="B278" t="n">
-        <v>12.50989723205566</v>
+        <v>12.50989818572998</v>
       </c>
       <c r="C278" t="n">
-        <v>12.59647124671763</v>
+        <v>12.59647220699179</v>
       </c>
       <c r="D278" t="n">
-        <v>12.15494525807742</v>
+        <v>12.15494618469247</v>
       </c>
       <c r="E278" t="n">
-        <v>12.34540759495513</v>
+        <v>12.34540853608981</v>
       </c>
       <c r="F278" t="n">
         <v>9400800</v>
@@ -6072,16 +6072,16 @@
         <v>45058</v>
       </c>
       <c r="B283" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C283" t="n">
-        <v>12.25017632493442</v>
+        <v>12.25017729158851</v>
       </c>
       <c r="D283" t="n">
-        <v>11.99911266679329</v>
+        <v>11.9991136136361</v>
       </c>
       <c r="E283" t="n">
-        <v>12.04239967522403</v>
+        <v>12.0424006254826</v>
       </c>
       <c r="F283" t="n">
         <v>3087800</v>
@@ -6132,16 +6132,16 @@
         <v>45063</v>
       </c>
       <c r="B286" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="C286" t="n">
-        <v>12.24152036724783</v>
+        <v>12.24151939290137</v>
       </c>
       <c r="D286" t="n">
-        <v>11.9471696818366</v>
+        <v>11.94716873091856</v>
       </c>
       <c r="E286" t="n">
-        <v>12.128974468377</v>
+        <v>12.12897350298847</v>
       </c>
       <c r="F286" t="n">
         <v>4330800</v>
@@ -6152,16 +6152,16 @@
         <v>45064</v>
       </c>
       <c r="B287" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="C287" t="n">
-        <v>12.05971558070743</v>
+        <v>12.05971462083146</v>
       </c>
       <c r="D287" t="n">
-        <v>11.82596621559931</v>
+        <v>11.82596527432829</v>
       </c>
       <c r="E287" t="n">
-        <v>12.01642856950617</v>
+        <v>12.01642761307558</v>
       </c>
       <c r="F287" t="n">
         <v>4680600</v>
@@ -6172,16 +6172,16 @@
         <v>45065</v>
       </c>
       <c r="B288" t="n">
-        <v>12.09434509277344</v>
+        <v>12.09434413909912</v>
       </c>
       <c r="C288" t="n">
-        <v>12.18091829003328</v>
+        <v>12.18091732953242</v>
       </c>
       <c r="D288" t="n">
-        <v>11.93851218182222</v>
+        <v>11.93851124043578</v>
       </c>
       <c r="E288" t="n">
-        <v>11.99911350246722</v>
+        <v>11.99911255630219</v>
       </c>
       <c r="F288" t="n">
         <v>2962700</v>
@@ -6232,16 +6232,16 @@
         <v>45070</v>
       </c>
       <c r="B291" t="n">
-        <v>12.25017642974854</v>
+        <v>12.25017738342285</v>
       </c>
       <c r="C291" t="n">
-        <v>12.30212100543608</v>
+        <v>12.30212196315428</v>
       </c>
       <c r="D291" t="n">
-        <v>12.18091754591915</v>
+        <v>12.18091849420168</v>
       </c>
       <c r="E291" t="n">
-        <v>12.26749156352139</v>
+        <v>12.26749251854369</v>
       </c>
       <c r="F291" t="n">
         <v>1846000</v>
@@ -6252,16 +6252,16 @@
         <v>45071</v>
       </c>
       <c r="B292" t="n">
-        <v>12.29346466064453</v>
+        <v>12.29346370697021</v>
       </c>
       <c r="C292" t="n">
-        <v>12.39735299671616</v>
+        <v>12.39735203498263</v>
       </c>
       <c r="D292" t="n">
-        <v>12.20689146006706</v>
+        <v>12.20689051310872</v>
       </c>
       <c r="E292" t="n">
-        <v>12.28480709289745</v>
+        <v>12.28480613989475</v>
       </c>
       <c r="F292" t="n">
         <v>2204600</v>
@@ -6292,16 +6292,16 @@
         <v>45075</v>
       </c>
       <c r="B294" t="n">
-        <v>12.28480529785156</v>
+        <v>12.28480625152588</v>
       </c>
       <c r="C294" t="n">
-        <v>12.34540743759487</v>
+        <v>12.34540839597375</v>
       </c>
       <c r="D294" t="n">
-        <v>12.16360266962691</v>
+        <v>12.16360361389222</v>
       </c>
       <c r="E294" t="n">
-        <v>12.16360266962691</v>
+        <v>12.16360361389222</v>
       </c>
       <c r="F294" t="n">
         <v>1431900</v>
@@ -6352,16 +6352,16 @@
         <v>45078</v>
       </c>
       <c r="B297" t="n">
-        <v>12.24151992797852</v>
+        <v>12.2415189743042</v>
       </c>
       <c r="C297" t="n">
-        <v>12.30212124610704</v>
+        <v>12.30212028771158</v>
       </c>
       <c r="D297" t="n">
-        <v>12.1636034757384</v>
+        <v>12.16360252813415</v>
       </c>
       <c r="E297" t="n">
-        <v>12.26749180351488</v>
+        <v>12.26749084781722</v>
       </c>
       <c r="F297" t="n">
         <v>2308800</v>
@@ -6412,16 +6412,16 @@
         <v>45083</v>
       </c>
       <c r="B300" t="n">
-        <v>12.32809352874756</v>
+        <v>12.32809257507324</v>
       </c>
       <c r="C300" t="n">
-        <v>12.41466755090237</v>
+        <v>12.41466659053087</v>
       </c>
       <c r="D300" t="n">
-        <v>12.0770298552559</v>
+        <v>12.07702892100332</v>
       </c>
       <c r="E300" t="n">
-        <v>12.08568742259759</v>
+        <v>12.08568648767528</v>
       </c>
       <c r="F300" t="n">
         <v>7376500</v>
@@ -6432,16 +6432,16 @@
         <v>45084</v>
       </c>
       <c r="B301" t="n">
-        <v>12.22420597076416</v>
+        <v>12.22420501708984</v>
       </c>
       <c r="C301" t="n">
-        <v>12.46661209224716</v>
+        <v>12.46661111966148</v>
       </c>
       <c r="D301" t="n">
-        <v>12.21554840287484</v>
+        <v>12.21554744987595</v>
       </c>
       <c r="E301" t="n">
-        <v>12.38003889024736</v>
+        <v>12.3800379244157</v>
       </c>
       <c r="F301" t="n">
         <v>3154600</v>
@@ -6452,16 +6452,16 @@
         <v>45086</v>
       </c>
       <c r="B302" t="n">
-        <v>12.37137985229492</v>
+        <v>12.37138080596924</v>
       </c>
       <c r="C302" t="n">
-        <v>12.42332442782724</v>
+        <v>12.42332538550581</v>
       </c>
       <c r="D302" t="n">
-        <v>12.26749152686131</v>
+        <v>12.26749247252717</v>
       </c>
       <c r="E302" t="n">
-        <v>12.29346340181196</v>
+        <v>12.29346434947992</v>
       </c>
       <c r="F302" t="n">
         <v>4999400</v>
@@ -6472,16 +6472,16 @@
         <v>45089</v>
       </c>
       <c r="B303" t="n">
-        <v>12.45795345306396</v>
+        <v>12.45795440673828</v>
       </c>
       <c r="C303" t="n">
-        <v>12.45795345306396</v>
+        <v>12.45795440673828</v>
       </c>
       <c r="D303" t="n">
-        <v>12.25883355008453</v>
+        <v>12.25883448851593</v>
       </c>
       <c r="E303" t="n">
-        <v>12.3800370051864</v>
+        <v>12.3800379528961</v>
       </c>
       <c r="F303" t="n">
         <v>2572800</v>
@@ -6532,16 +6532,16 @@
         <v>45092</v>
       </c>
       <c r="B306" t="n">
-        <v>12.46661186218262</v>
+        <v>12.4666109085083</v>
       </c>
       <c r="C306" t="n">
-        <v>12.49258456537125</v>
+        <v>12.49258360971007</v>
       </c>
       <c r="D306" t="n">
-        <v>12.36272352632139</v>
+        <v>12.36272258059435</v>
       </c>
       <c r="E306" t="n">
-        <v>12.45795512008417</v>
+        <v>12.45795416707208</v>
       </c>
       <c r="F306" t="n">
         <v>1266000</v>
@@ -6552,16 +6552,16 @@
         <v>45093</v>
       </c>
       <c r="B307" t="n">
-        <v>12.62244319915771</v>
+        <v>12.62244415283203</v>
       </c>
       <c r="C307" t="n">
-        <v>12.83021984487801</v>
+        <v>12.83022081425066</v>
       </c>
       <c r="D307" t="n">
-        <v>12.4406384277447</v>
+        <v>12.44063936768297</v>
       </c>
       <c r="E307" t="n">
-        <v>12.46661030205199</v>
+        <v>12.46661124395253</v>
       </c>
       <c r="F307" t="n">
         <v>5319000</v>
@@ -6612,16 +6612,16 @@
         <v>45098</v>
       </c>
       <c r="B310" t="n">
-        <v>12.86484909057617</v>
+        <v>12.86485004425049</v>
       </c>
       <c r="C310" t="n">
-        <v>12.90813609751867</v>
+        <v>12.90813705440186</v>
       </c>
       <c r="D310" t="n">
-        <v>12.63975814061098</v>
+        <v>12.63975907759925</v>
       </c>
       <c r="E310" t="n">
-        <v>12.75230320277808</v>
+        <v>12.75230414810935</v>
       </c>
       <c r="F310" t="n">
         <v>5022600</v>
@@ -6632,16 +6632,16 @@
         <v>45099</v>
       </c>
       <c r="B311" t="n">
-        <v>12.7869348526001</v>
+        <v>12.78693389892578</v>
       </c>
       <c r="C311" t="n">
-        <v>12.84753617349909</v>
+        <v>12.84753521530501</v>
       </c>
       <c r="D311" t="n">
-        <v>12.64841625026786</v>
+        <v>12.64841530692453</v>
       </c>
       <c r="E311" t="n">
-        <v>12.7869348526001</v>
+        <v>12.78693389892578</v>
       </c>
       <c r="F311" t="n">
         <v>2039700</v>
@@ -6652,16 +6652,16 @@
         <v>45100</v>
       </c>
       <c r="B312" t="n">
-        <v>12.94276714324951</v>
+        <v>12.9427661895752</v>
       </c>
       <c r="C312" t="n">
-        <v>13.07262818018377</v>
+        <v>13.07262721694078</v>
       </c>
       <c r="D312" t="n">
-        <v>12.76096235204642</v>
+        <v>12.7609614117682</v>
       </c>
       <c r="E312" t="n">
-        <v>12.81290693194634</v>
+        <v>12.81290598784064</v>
       </c>
       <c r="F312" t="n">
         <v>2959500</v>
@@ -6672,16 +6672,16 @@
         <v>45103</v>
       </c>
       <c r="B313" t="n">
-        <v>12.71767520904541</v>
+        <v>12.71767425537109</v>
       </c>
       <c r="C313" t="n">
-        <v>13.01202589898095</v>
+        <v>13.01202492323384</v>
       </c>
       <c r="D313" t="n">
-        <v>12.66573145531036</v>
+        <v>12.66573050553121</v>
       </c>
       <c r="E313" t="n">
-        <v>12.94276701024684</v>
+        <v>12.94276603969331</v>
       </c>
       <c r="F313" t="n">
         <v>2677600</v>
@@ -6692,16 +6692,16 @@
         <v>45104</v>
       </c>
       <c r="B314" t="n">
-        <v>12.50124073028564</v>
+        <v>12.50123977661133</v>
       </c>
       <c r="C314" t="n">
-        <v>12.83887842546918</v>
+        <v>12.83887744603771</v>
       </c>
       <c r="D314" t="n">
-        <v>12.39735239922096</v>
+        <v>12.3973514534719</v>
       </c>
       <c r="E314" t="n">
-        <v>12.76961953809272</v>
+        <v>12.76961856394476</v>
       </c>
       <c r="F314" t="n">
         <v>3014700</v>
@@ -6792,16 +6792,16 @@
         <v>45111</v>
       </c>
       <c r="B319" t="n">
-        <v>12.34540843963623</v>
+        <v>12.34540748596191</v>
       </c>
       <c r="C319" t="n">
-        <v>12.40600975866739</v>
+        <v>12.40600880031166</v>
       </c>
       <c r="D319" t="n">
-        <v>12.23286254312761</v>
+        <v>12.23286159814739</v>
       </c>
       <c r="E319" t="n">
-        <v>12.38869544992894</v>
+        <v>12.38869449291073</v>
       </c>
       <c r="F319" t="n">
         <v>2230100</v>
@@ -6832,16 +6832,16 @@
         <v>45113</v>
       </c>
       <c r="B321" t="n">
-        <v>12.32809352874756</v>
+        <v>12.32809257507324</v>
       </c>
       <c r="C321" t="n">
-        <v>12.48392643837378</v>
+        <v>12.48392547264458</v>
       </c>
       <c r="D321" t="n">
-        <v>12.25017707393445</v>
+        <v>12.25017612628758</v>
       </c>
       <c r="E321" t="n">
-        <v>12.43198185995469</v>
+        <v>12.4319808982438</v>
       </c>
       <c r="F321" t="n">
         <v>2081000</v>
@@ -6852,16 +6852,16 @@
         <v>45114</v>
       </c>
       <c r="B322" t="n">
-        <v>12.34540843963623</v>
+        <v>12.34540748596191</v>
       </c>
       <c r="C322" t="n">
-        <v>12.48392621206805</v>
+        <v>12.48392524769333</v>
       </c>
       <c r="D322" t="n">
-        <v>12.25883441905082</v>
+        <v>12.25883347206429</v>
       </c>
       <c r="E322" t="n">
-        <v>12.42332489303689</v>
+        <v>12.42332393334358</v>
       </c>
       <c r="F322" t="n">
         <v>2149700</v>
@@ -6872,16 +6872,16 @@
         <v>45117</v>
       </c>
       <c r="B323" t="n">
-        <v>12.38869476318359</v>
+        <v>12.38869571685791</v>
       </c>
       <c r="C323" t="n">
-        <v>12.45795364556026</v>
+        <v>12.45795460456609</v>
       </c>
       <c r="D323" t="n">
-        <v>12.31077831410209</v>
+        <v>12.31077926177845</v>
       </c>
       <c r="E323" t="n">
-        <v>12.38003719647876</v>
+        <v>12.38003814948662</v>
       </c>
       <c r="F323" t="n">
         <v>1514600</v>
@@ -6892,16 +6892,16 @@
         <v>45118</v>
       </c>
       <c r="B324" t="n">
-        <v>12.34540843963623</v>
+        <v>12.34540748596191</v>
       </c>
       <c r="C324" t="n">
-        <v>12.39735219148264</v>
+        <v>12.3973512337957</v>
       </c>
       <c r="D324" t="n">
-        <v>12.23286254312761</v>
+        <v>12.23286159814739</v>
       </c>
       <c r="E324" t="n">
-        <v>12.38869544992894</v>
+        <v>12.38869449291073</v>
       </c>
       <c r="F324" t="n">
         <v>1919200</v>
@@ -6912,16 +6912,16 @@
         <v>45119</v>
       </c>
       <c r="B325" t="n">
-        <v>12.38869476318359</v>
+        <v>12.38869571685791</v>
       </c>
       <c r="C325" t="n">
-        <v>12.45795364556026</v>
+        <v>12.45795460456609</v>
       </c>
       <c r="D325" t="n">
-        <v>12.28480561398759</v>
+        <v>12.28480655966458</v>
       </c>
       <c r="E325" t="n">
-        <v>12.37137962977392</v>
+        <v>12.37138058211533</v>
       </c>
       <c r="F325" t="n">
         <v>1842800</v>
@@ -7052,16 +7052,16 @@
         <v>45128</v>
       </c>
       <c r="B332" t="n">
-        <v>12.38869476318359</v>
+        <v>12.38869571685791</v>
       </c>
       <c r="C332" t="n">
-        <v>12.38869476318359</v>
+        <v>12.38869571685791</v>
       </c>
       <c r="D332" t="n">
-        <v>12.22420429831576</v>
+        <v>12.2242052393277</v>
       </c>
       <c r="E332" t="n">
-        <v>12.27614887291376</v>
+        <v>12.27614981792436</v>
       </c>
       <c r="F332" t="n">
         <v>2631400</v>
@@ -7072,16 +7072,16 @@
         <v>45131</v>
       </c>
       <c r="B333" t="n">
-        <v>12.34540843963623</v>
+        <v>12.34540748596191</v>
       </c>
       <c r="C333" t="n">
-        <v>12.42332489303689</v>
+        <v>12.42332393334358</v>
       </c>
       <c r="D333" t="n">
-        <v>12.31943573808198</v>
+        <v>12.31943478641403</v>
       </c>
       <c r="E333" t="n">
-        <v>12.42332489303689</v>
+        <v>12.42332393334358</v>
       </c>
       <c r="F333" t="n">
         <v>1347200</v>
@@ -7132,16 +7132,16 @@
         <v>45134</v>
       </c>
       <c r="B336" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C336" t="n">
-        <v>12.22420445012837</v>
+        <v>12.22420541473304</v>
       </c>
       <c r="D336" t="n">
-        <v>12.03374210841168</v>
+        <v>12.03374305798708</v>
       </c>
       <c r="E336" t="n">
-        <v>12.18091744169762</v>
+        <v>12.18091840288654</v>
       </c>
       <c r="F336" t="n">
         <v>2852900</v>
@@ -7212,16 +7212,16 @@
         <v>45140</v>
       </c>
       <c r="B340" t="n">
-        <v>12.22420597076416</v>
+        <v>12.22420501708984</v>
       </c>
       <c r="C340" t="n">
-        <v>12.23286353865348</v>
+        <v>12.23286258430374</v>
       </c>
       <c r="D340" t="n">
-        <v>12.12897520087505</v>
+        <v>12.12897425463018</v>
       </c>
       <c r="E340" t="n">
-        <v>12.13763276876436</v>
+        <v>12.13763182184407</v>
       </c>
       <c r="F340" t="n">
         <v>1697600</v>
@@ -7292,16 +7292,16 @@
         <v>45146</v>
       </c>
       <c r="B344" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C344" t="n">
-        <v>12.15494556689158</v>
+        <v>12.15494652603107</v>
       </c>
       <c r="D344" t="n">
-        <v>11.92985378355649</v>
+        <v>11.92985472493413</v>
       </c>
       <c r="E344" t="n">
-        <v>11.99045592561195</v>
+        <v>11.99045687177166</v>
       </c>
       <c r="F344" t="n">
         <v>2176400</v>
@@ -7332,16 +7332,16 @@
         <v>45148</v>
       </c>
       <c r="B346" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C346" t="n">
-        <v>12.09434549372545</v>
+        <v>12.09434452900206</v>
       </c>
       <c r="D346" t="n">
-        <v>11.88656799702522</v>
+        <v>11.88656704887551</v>
       </c>
       <c r="E346" t="n">
-        <v>12.01642903566675</v>
+        <v>12.01642807715848</v>
       </c>
       <c r="F346" t="n">
         <v>2835300</v>
@@ -7352,16 +7352,16 @@
         <v>45149</v>
       </c>
       <c r="B347" t="n">
-        <v>11.92119789123535</v>
+        <v>11.92119693756104</v>
       </c>
       <c r="C347" t="n">
-        <v>11.97314164454614</v>
+        <v>11.97314068671642</v>
       </c>
       <c r="D347" t="n">
-        <v>11.83462386820927</v>
+        <v>11.83462292146072</v>
       </c>
       <c r="E347" t="n">
-        <v>11.97314164454614</v>
+        <v>11.97314068671642</v>
       </c>
       <c r="F347" t="n">
         <v>2472600</v>
@@ -7392,16 +7392,16 @@
         <v>45153</v>
       </c>
       <c r="B349" t="n">
-        <v>11.86059474945068</v>
+        <v>11.860595703125</v>
       </c>
       <c r="C349" t="n">
-        <v>11.9991125141623</v>
+        <v>11.99911347897441</v>
       </c>
       <c r="D349" t="n">
-        <v>11.85193718274846</v>
+        <v>11.85193813572664</v>
       </c>
       <c r="E349" t="n">
-        <v>11.91253932403304</v>
+        <v>11.91254028188406</v>
       </c>
       <c r="F349" t="n">
         <v>2713800</v>
@@ -7412,16 +7412,16 @@
         <v>45154</v>
       </c>
       <c r="B350" t="n">
-        <v>11.68744850158691</v>
+        <v>11.6874475479126</v>
       </c>
       <c r="C350" t="n">
-        <v>11.91254030050967</v>
+        <v>11.91253932846828</v>
       </c>
       <c r="D350" t="n">
-        <v>11.64416149015853</v>
+        <v>11.64416054001635</v>
       </c>
       <c r="E350" t="n">
-        <v>11.886567598274</v>
+        <v>11.88656662835193</v>
       </c>
       <c r="F350" t="n">
         <v>3946200</v>
@@ -7432,16 +7432,16 @@
         <v>45155</v>
       </c>
       <c r="B351" t="n">
-        <v>11.71342086791992</v>
+        <v>11.71341991424561</v>
       </c>
       <c r="C351" t="n">
-        <v>11.78267975884857</v>
+        <v>11.78267879953539</v>
       </c>
       <c r="D351" t="n">
-        <v>11.66147711253899</v>
+        <v>11.66147616309379</v>
       </c>
       <c r="E351" t="n">
-        <v>11.73073600346764</v>
+        <v>11.73073504838357</v>
       </c>
       <c r="F351" t="n">
         <v>2345000</v>
@@ -7452,16 +7452,16 @@
         <v>45156</v>
       </c>
       <c r="B352" t="n">
-        <v>11.77402114868164</v>
+        <v>11.77402210235596</v>
       </c>
       <c r="C352" t="n">
-        <v>11.80865058865178</v>
+        <v>11.80865154513102</v>
       </c>
       <c r="D352" t="n">
-        <v>11.65281769597066</v>
+        <v>11.65281863982772</v>
       </c>
       <c r="E352" t="n">
-        <v>11.71341900951066</v>
+        <v>11.71341995827632</v>
       </c>
       <c r="F352" t="n">
         <v>3061800</v>
@@ -7492,16 +7492,16 @@
         <v>45160</v>
       </c>
       <c r="B354" t="n">
-        <v>11.79999446868896</v>
+        <v>11.79999351501465</v>
       </c>
       <c r="C354" t="n">
-        <v>11.86925335711897</v>
+        <v>11.86925239784715</v>
       </c>
       <c r="D354" t="n">
-        <v>11.73073558025896</v>
+        <v>11.73073463218214</v>
       </c>
       <c r="E354" t="n">
-        <v>11.79133690122745</v>
+        <v>11.79133594825283</v>
       </c>
       <c r="F354" t="n">
         <v>2231700</v>
@@ -7512,16 +7512,16 @@
         <v>45161</v>
       </c>
       <c r="B355" t="n">
-        <v>11.87790966033936</v>
+        <v>11.87791061401367</v>
       </c>
       <c r="C355" t="n">
-        <v>11.89522396778845</v>
+        <v>11.89522492285292</v>
       </c>
       <c r="D355" t="n">
-        <v>11.79133564620093</v>
+        <v>11.79133659292425</v>
       </c>
       <c r="E355" t="n">
-        <v>11.86059452725928</v>
+        <v>11.86059547954337</v>
       </c>
       <c r="F355" t="n">
         <v>2615000</v>
@@ -7532,16 +7532,16 @@
         <v>45162</v>
       </c>
       <c r="B356" t="n">
-        <v>11.97314071655273</v>
+        <v>11.97314167022705</v>
       </c>
       <c r="C356" t="n">
-        <v>11.99911259119515</v>
+        <v>11.99911354693815</v>
       </c>
       <c r="D356" t="n">
-        <v>11.89522426699448</v>
+        <v>11.89522521446267</v>
       </c>
       <c r="E356" t="n">
-        <v>11.90388183375229</v>
+        <v>11.90388278191006</v>
       </c>
       <c r="F356" t="n">
         <v>2322800</v>
@@ -7572,16 +7572,16 @@
         <v>45166</v>
       </c>
       <c r="B358" t="n">
-        <v>11.9644832611084</v>
+        <v>11.96448421478271</v>
       </c>
       <c r="C358" t="n">
-        <v>11.9991127028308</v>
+        <v>11.99911365926539</v>
       </c>
       <c r="D358" t="n">
-        <v>11.8432806278955</v>
+        <v>11.84328157190891</v>
       </c>
       <c r="E358" t="n">
-        <v>11.95582651990106</v>
+        <v>11.95582747288536</v>
       </c>
       <c r="F358" t="n">
         <v>2184700</v>
@@ -7652,16 +7652,16 @@
         <v>45170</v>
       </c>
       <c r="B362" t="n">
-        <v>12.04239940643311</v>
+        <v>12.04240036010742</v>
       </c>
       <c r="C362" t="n">
-        <v>12.04239940643311</v>
+        <v>12.04240036010742</v>
       </c>
       <c r="D362" t="n">
-        <v>11.89522407643217</v>
+        <v>11.89522501845123</v>
       </c>
       <c r="E362" t="n">
-        <v>11.90388164305129</v>
+        <v>11.90388258575596</v>
       </c>
       <c r="F362" t="n">
         <v>3740800</v>
@@ -7692,16 +7692,16 @@
         <v>45174</v>
       </c>
       <c r="B364" t="n">
-        <v>11.92119789123535</v>
+        <v>11.92119693756104</v>
       </c>
       <c r="C364" t="n">
-        <v>12.06837240936998</v>
+        <v>12.06837144392197</v>
       </c>
       <c r="D364" t="n">
-        <v>11.91254032380653</v>
+        <v>11.9125393708248</v>
       </c>
       <c r="E364" t="n">
-        <v>12.04240053271458</v>
+        <v>12.04239956934427</v>
       </c>
       <c r="F364" t="n">
         <v>3869600</v>
@@ -7712,16 +7712,16 @@
         <v>45175</v>
       </c>
       <c r="B365" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C365" t="n">
-        <v>12.02508660336907</v>
+        <v>12.02508564417022</v>
       </c>
       <c r="D365" t="n">
-        <v>11.81730910666884</v>
+        <v>11.81730816404367</v>
       </c>
       <c r="E365" t="n">
-        <v>11.93851257760805</v>
+        <v>11.9385116253149</v>
       </c>
       <c r="F365" t="n">
         <v>2473500</v>
@@ -7732,16 +7732,16 @@
         <v>45177</v>
       </c>
       <c r="B366" t="n">
-        <v>11.92985343933105</v>
+        <v>11.92985439300537</v>
       </c>
       <c r="C366" t="n">
-        <v>12.07702876837038</v>
+        <v>12.07702973380992</v>
       </c>
       <c r="D366" t="n">
-        <v>11.88656643214931</v>
+        <v>11.88656738236326</v>
       </c>
       <c r="E366" t="n">
-        <v>11.9385110058936</v>
+        <v>11.93851196026</v>
       </c>
       <c r="F366" t="n">
         <v>3462800</v>
@@ -7812,16 +7812,16 @@
         <v>45183</v>
       </c>
       <c r="B370" t="n">
-        <v>12.21554660797119</v>
+        <v>12.21554756164551</v>
       </c>
       <c r="C370" t="n">
-        <v>12.25017604880902</v>
+        <v>12.25017700518688</v>
       </c>
       <c r="D370" t="n">
-        <v>12.09434397785428</v>
+        <v>12.09434492206624</v>
       </c>
       <c r="E370" t="n">
-        <v>12.09434397785428</v>
+        <v>12.09434492206624</v>
       </c>
       <c r="F370" t="n">
         <v>2498700</v>
@@ -7912,16 +7912,16 @@
         <v>45190</v>
       </c>
       <c r="B375" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C375" t="n">
-        <v>12.0337433454403</v>
+        <v>12.03374238555092</v>
       </c>
       <c r="D375" t="n">
-        <v>11.877911254954</v>
+        <v>11.8779103074948</v>
       </c>
       <c r="E375" t="n">
-        <v>12.02508660336907</v>
+        <v>12.02508564417022</v>
       </c>
       <c r="F375" t="n">
         <v>4405700</v>
@@ -7932,16 +7932,16 @@
         <v>45191</v>
       </c>
       <c r="B376" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C376" t="n">
-        <v>12.10300223579667</v>
+        <v>12.10300127038276</v>
       </c>
       <c r="D376" t="n">
-        <v>11.92985500990573</v>
+        <v>11.92985405830317</v>
       </c>
       <c r="E376" t="n">
-        <v>12.02508660336907</v>
+        <v>12.02508564417022</v>
       </c>
       <c r="F376" t="n">
         <v>2812600</v>
@@ -7972,16 +7972,16 @@
         <v>45195</v>
       </c>
       <c r="B378" t="n">
-        <v>11.83462333679199</v>
+        <v>11.83462238311768</v>
       </c>
       <c r="C378" t="n">
-        <v>12.06837186745655</v>
+        <v>12.06837089494598</v>
       </c>
       <c r="D378" t="n">
-        <v>11.78267876018263</v>
+        <v>11.78267781069418</v>
       </c>
       <c r="E378" t="n">
-        <v>11.80865146130283</v>
+        <v>11.80865050972141</v>
       </c>
       <c r="F378" t="n">
         <v>7795500</v>
@@ -8092,16 +8092,16 @@
         <v>45203</v>
       </c>
       <c r="B384" t="n">
-        <v>11.77402114868164</v>
+        <v>11.77402210235596</v>
       </c>
       <c r="C384" t="n">
-        <v>11.86059433579151</v>
+        <v>11.86059529647809</v>
       </c>
       <c r="D384" t="n">
-        <v>11.7480484494808</v>
+        <v>11.74804940105138</v>
       </c>
       <c r="E384" t="n">
-        <v>11.80865058865178</v>
+        <v>11.80865154513102</v>
       </c>
       <c r="F384" t="n">
         <v>4367600</v>
@@ -8172,16 +8172,16 @@
         <v>45209</v>
       </c>
       <c r="B388" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C388" t="n">
-        <v>12.16360313370393</v>
+        <v>12.16360409352659</v>
       </c>
       <c r="D388" t="n">
-        <v>11.9125394755628</v>
+        <v>11.91254041557417</v>
       </c>
       <c r="E388" t="n">
-        <v>11.92985378355649</v>
+        <v>11.92985472493413</v>
       </c>
       <c r="F388" t="n">
         <v>3643400</v>
@@ -8192,16 +8192,16 @@
         <v>45210</v>
       </c>
       <c r="B389" t="n">
-        <v>12.09434509277344</v>
+        <v>12.09434413909912</v>
       </c>
       <c r="C389" t="n">
-        <v>12.18957585744859</v>
+        <v>12.18957489626505</v>
       </c>
       <c r="D389" t="n">
-        <v>12.00777106988252</v>
+        <v>12.00777012303482</v>
       </c>
       <c r="E389" t="n">
-        <v>12.09434509277344</v>
+        <v>12.09434413909912</v>
       </c>
       <c r="F389" t="n">
         <v>3458500</v>
@@ -8212,16 +8212,16 @@
         <v>45212</v>
       </c>
       <c r="B390" t="n">
-        <v>12.02508640289307</v>
+        <v>12.02508544921875</v>
       </c>
       <c r="C390" t="n">
-        <v>12.19823362589739</v>
+        <v>12.19823265849127</v>
       </c>
       <c r="D390" t="n">
-        <v>12.02508640289307</v>
+        <v>12.02508544921875</v>
       </c>
       <c r="E390" t="n">
-        <v>12.0943452920948</v>
+        <v>12.09434433292776</v>
       </c>
       <c r="F390" t="n">
         <v>4555500</v>
@@ -8232,16 +8232,16 @@
         <v>45215</v>
       </c>
       <c r="B391" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="C391" t="n">
-        <v>12.12031690101054</v>
+        <v>12.12031593631109</v>
       </c>
       <c r="D391" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="E391" t="n">
-        <v>12.05971558070743</v>
+        <v>12.05971462083146</v>
       </c>
       <c r="F391" t="n">
         <v>3983600</v>
@@ -8252,16 +8252,16 @@
         <v>45216</v>
       </c>
       <c r="B392" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C392" t="n">
-        <v>12.10300223579667</v>
+        <v>12.10300127038276</v>
       </c>
       <c r="D392" t="n">
-        <v>11.88656799702522</v>
+        <v>11.88656704887551</v>
       </c>
       <c r="E392" t="n">
-        <v>11.97314202278624</v>
+        <v>11.97314106773082</v>
       </c>
       <c r="F392" t="n">
         <v>5165000</v>
@@ -8292,16 +8292,16 @@
         <v>45218</v>
       </c>
       <c r="B394" t="n">
-        <v>11.67013263702393</v>
+        <v>11.67013359069824</v>
       </c>
       <c r="C394" t="n">
-        <v>11.75670665446719</v>
+        <v>11.75670761521626</v>
       </c>
       <c r="D394" t="n">
-        <v>11.62684645393332</v>
+        <v>11.62684740407032</v>
       </c>
       <c r="E394" t="n">
-        <v>11.66147589578441</v>
+        <v>11.66147684875131</v>
       </c>
       <c r="F394" t="n">
         <v>3066300</v>
@@ -8352,16 +8352,16 @@
         <v>45223</v>
       </c>
       <c r="B397" t="n">
-        <v>11.63550281524658</v>
+        <v>11.6355037689209</v>
       </c>
       <c r="C397" t="n">
-        <v>11.81730758543626</v>
+        <v>11.81730855401174</v>
       </c>
       <c r="D397" t="n">
-        <v>11.54892962626116</v>
+        <v>11.54893057283972</v>
       </c>
       <c r="E397" t="n">
-        <v>11.80865084447942</v>
+        <v>11.80865181234537</v>
       </c>
       <c r="F397" t="n">
         <v>3637500</v>
@@ -8432,16 +8432,16 @@
         <v>45229</v>
       </c>
       <c r="B401" t="n">
-        <v>11.49698543548584</v>
+        <v>11.49698638916016</v>
       </c>
       <c r="C401" t="n">
-        <v>11.64416076985956</v>
+        <v>11.64416173574207</v>
       </c>
       <c r="D401" t="n">
-        <v>11.47101356048784</v>
+        <v>11.47101451200779</v>
       </c>
       <c r="E401" t="n">
-        <v>11.57490188611087</v>
+        <v>11.57490284624835</v>
       </c>
       <c r="F401" t="n">
         <v>4549600</v>
@@ -8492,16 +8492,16 @@
         <v>45233</v>
       </c>
       <c r="B404" t="n">
-        <v>11.9644832611084</v>
+        <v>11.96448421478271</v>
       </c>
       <c r="C404" t="n">
-        <v>12.02508540334586</v>
+        <v>12.0250863618507</v>
       </c>
       <c r="D404" t="n">
-        <v>11.65281828560679</v>
+        <v>11.65281921443867</v>
       </c>
       <c r="E404" t="n">
-        <v>11.74804904393564</v>
+        <v>11.74804998035825</v>
       </c>
       <c r="F404" t="n">
         <v>4830800</v>
@@ -8512,16 +8512,16 @@
         <v>45236</v>
       </c>
       <c r="B405" t="n">
-        <v>12.02508640289307</v>
+        <v>12.02508544921875</v>
       </c>
       <c r="C405" t="n">
-        <v>12.07703015697882</v>
+        <v>12.077029199185</v>
       </c>
       <c r="D405" t="n">
-        <v>11.81730890965679</v>
+        <v>11.8173079724607</v>
       </c>
       <c r="E405" t="n">
-        <v>11.94716994613335</v>
+        <v>11.94716899863836</v>
       </c>
       <c r="F405" t="n">
         <v>2982900</v>
@@ -8672,16 +8672,16 @@
         <v>45247</v>
       </c>
       <c r="B413" t="n">
-        <v>12.25017642974854</v>
+        <v>12.25017738342285</v>
       </c>
       <c r="C413" t="n">
-        <v>12.48392578189597</v>
+        <v>12.48392675376763</v>
       </c>
       <c r="D413" t="n">
-        <v>12.14628810400446</v>
+        <v>12.14628904959109</v>
       </c>
       <c r="E413" t="n">
-        <v>12.48392578189597</v>
+        <v>12.48392675376763</v>
       </c>
       <c r="F413" t="n">
         <v>3124800</v>
@@ -8692,16 +8692,16 @@
         <v>45250</v>
       </c>
       <c r="B414" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C414" t="n">
-        <v>12.23286201694073</v>
+        <v>12.23286298222856</v>
       </c>
       <c r="D414" t="n">
-        <v>11.99045592561195</v>
+        <v>11.99045687177166</v>
       </c>
       <c r="E414" t="n">
-        <v>12.20689014213468</v>
+        <v>12.20689110537309</v>
       </c>
       <c r="F414" t="n">
         <v>3248400</v>
@@ -8712,16 +8712,16 @@
         <v>45251</v>
       </c>
       <c r="B415" t="n">
-        <v>11.97314071655273</v>
+        <v>11.97314167022705</v>
       </c>
       <c r="C415" t="n">
-        <v>12.09434417426901</v>
+        <v>12.09434513759732</v>
       </c>
       <c r="D415" t="n">
-        <v>11.9125394005101</v>
+        <v>11.91254034935745</v>
       </c>
       <c r="E415" t="n">
-        <v>12.0856866075112</v>
+        <v>12.08568757014993</v>
       </c>
       <c r="F415" t="n">
         <v>2713400</v>
@@ -8732,16 +8732,16 @@
         <v>45252</v>
       </c>
       <c r="B416" t="n">
-        <v>12.46661186218262</v>
+        <v>12.4666109085083</v>
       </c>
       <c r="C416" t="n">
-        <v>12.94276735410323</v>
+        <v>12.94276636400384</v>
       </c>
       <c r="D416" t="n">
-        <v>12.44063998462508</v>
+        <v>12.44063903293757</v>
       </c>
       <c r="E416" t="n">
-        <v>12.81290714068447</v>
+        <v>12.81290616051917</v>
       </c>
       <c r="F416" t="n">
         <v>20875500</v>
@@ -8752,16 +8752,16 @@
         <v>45253</v>
       </c>
       <c r="B417" t="n">
-        <v>12.56184196472168</v>
+        <v>12.561842918396</v>
       </c>
       <c r="C417" t="n">
-        <v>12.76961861177884</v>
+        <v>12.76961958122722</v>
       </c>
       <c r="D417" t="n">
-        <v>12.46661038226389</v>
+        <v>12.46661132870839</v>
       </c>
       <c r="E417" t="n">
-        <v>12.76961861177884</v>
+        <v>12.76961958122722</v>
       </c>
       <c r="F417" t="n">
         <v>9122900</v>
@@ -8812,16 +8812,16 @@
         <v>45258</v>
       </c>
       <c r="B420" t="n">
-        <v>12.6397590637207</v>
+        <v>12.63975811004639</v>
       </c>
       <c r="C420" t="n">
-        <v>12.76961926840118</v>
+        <v>12.76961830492886</v>
       </c>
       <c r="D420" t="n">
-        <v>12.57050017780698</v>
+        <v>12.57049922935827</v>
       </c>
       <c r="E420" t="n">
-        <v>12.57915691932291</v>
+        <v>12.57915597022104</v>
       </c>
       <c r="F420" t="n">
         <v>5941200</v>
@@ -8832,16 +8832,16 @@
         <v>45259</v>
       </c>
       <c r="B421" t="n">
-        <v>12.56184196472168</v>
+        <v>12.561842918396</v>
       </c>
       <c r="C421" t="n">
-        <v>12.75230347837524</v>
+        <v>12.75230444650908</v>
       </c>
       <c r="D421" t="n">
-        <v>12.56184196472168</v>
+        <v>12.561842918396</v>
       </c>
       <c r="E421" t="n">
-        <v>12.72633160390085</v>
+        <v>12.72633257006295</v>
       </c>
       <c r="F421" t="n">
         <v>5869600</v>
@@ -8852,16 +8852,16 @@
         <v>45260</v>
       </c>
       <c r="B422" t="n">
-        <v>12.71767520904541</v>
+        <v>12.71767425537109</v>
       </c>
       <c r="C422" t="n">
-        <v>12.71767520904541</v>
+        <v>12.71767425537109</v>
       </c>
       <c r="D422" t="n">
-        <v>12.58781499907671</v>
+        <v>12.58781405514036</v>
       </c>
       <c r="E422" t="n">
-        <v>12.6311020109433</v>
+        <v>12.63110106376094</v>
       </c>
       <c r="F422" t="n">
         <v>4162000</v>
@@ -8872,16 +8872,16 @@
         <v>45261</v>
       </c>
       <c r="B423" t="n">
-        <v>12.86484909057617</v>
+        <v>12.86485004425049</v>
       </c>
       <c r="C423" t="n">
-        <v>12.96873741185957</v>
+        <v>12.96873837323515</v>
       </c>
       <c r="D423" t="n">
-        <v>12.70901702146657</v>
+        <v>12.70901796358902</v>
       </c>
       <c r="E423" t="n">
-        <v>12.72633132886498</v>
+        <v>12.72633227227094</v>
       </c>
       <c r="F423" t="n">
         <v>6458300</v>
@@ -8932,16 +8932,16 @@
         <v>45266</v>
       </c>
       <c r="B426" t="n">
-        <v>13.07262706756592</v>
+        <v>13.07262802124023</v>
       </c>
       <c r="C426" t="n">
-        <v>13.2717461513678</v>
+        <v>13.27174711956826</v>
       </c>
       <c r="D426" t="n">
-        <v>13.04665436701096</v>
+        <v>13.04665531879052</v>
       </c>
       <c r="E426" t="n">
-        <v>13.21114483466828</v>
+        <v>13.21114579844774</v>
       </c>
       <c r="F426" t="n">
         <v>5861300</v>
@@ -9052,16 +9052,16 @@
         <v>45274</v>
       </c>
       <c r="B432" t="n">
-        <v>12.94470024108887</v>
+        <v>12.94470119476318</v>
       </c>
       <c r="C432" t="n">
-        <v>12.98319745470858</v>
+        <v>12.9831984112191</v>
       </c>
       <c r="D432" t="n">
-        <v>12.71371695937057</v>
+        <v>12.71371789602766</v>
       </c>
       <c r="E432" t="n">
-        <v>12.71371695937057</v>
+        <v>12.71371789602766</v>
       </c>
       <c r="F432" t="n">
         <v>5480800</v>
@@ -9092,16 +9092,16 @@
         <v>45278</v>
       </c>
       <c r="B434" t="n">
-        <v>12.84845733642578</v>
+        <v>12.8484582901001</v>
       </c>
       <c r="C434" t="n">
-        <v>13.0890651448394</v>
+        <v>13.08906611637279</v>
       </c>
       <c r="D434" t="n">
-        <v>12.84845733642578</v>
+        <v>12.8484582901001</v>
       </c>
       <c r="E434" t="n">
-        <v>12.983197121716</v>
+        <v>12.98319808539135</v>
       </c>
       <c r="F434" t="n">
         <v>3314300</v>
@@ -9112,16 +9112,16 @@
         <v>45279</v>
       </c>
       <c r="B435" t="n">
-        <v>12.86770629882812</v>
+        <v>12.86770534515381</v>
       </c>
       <c r="C435" t="n">
-        <v>12.94470072896945</v>
+        <v>12.94469976958878</v>
       </c>
       <c r="D435" t="n">
-        <v>12.7907118686868</v>
+        <v>12.79071092071883</v>
       </c>
       <c r="E435" t="n">
-        <v>12.87733083205729</v>
+        <v>12.87732987766966</v>
       </c>
       <c r="F435" t="n">
         <v>4780200</v>
@@ -9232,16 +9232,16 @@
         <v>45288</v>
       </c>
       <c r="B441" t="n">
-        <v>12.80996036529541</v>
+        <v>12.80996131896973</v>
       </c>
       <c r="C441" t="n">
-        <v>12.88695479201164</v>
+        <v>12.88695575141803</v>
       </c>
       <c r="D441" t="n">
-        <v>12.76183861913627</v>
+        <v>12.76183956922803</v>
       </c>
       <c r="E441" t="n">
-        <v>12.88695479201164</v>
+        <v>12.88695575141803</v>
       </c>
       <c r="F441" t="n">
         <v>3487000</v>
@@ -9332,16 +9332,16 @@
         <v>45299</v>
       </c>
       <c r="B446" t="n">
-        <v>13.01207065582275</v>
+        <v>13.01207160949707</v>
       </c>
       <c r="C446" t="n">
-        <v>13.09868869543668</v>
+        <v>13.09868965545936</v>
       </c>
       <c r="D446" t="n">
-        <v>12.88695448591916</v>
+        <v>12.88695543042352</v>
       </c>
       <c r="E446" t="n">
-        <v>12.95432437823419</v>
+        <v>12.9543253276762</v>
       </c>
       <c r="F446" t="n">
         <v>3738800</v>
@@ -9392,16 +9392,16 @@
         <v>45302</v>
       </c>
       <c r="B449" t="n">
-        <v>12.84845733642578</v>
+        <v>12.8484582901001</v>
       </c>
       <c r="C449" t="n">
-        <v>12.94469990908366</v>
+        <v>12.94470086990156</v>
       </c>
       <c r="D449" t="n">
-        <v>12.74258931330238</v>
+        <v>12.74259025911866</v>
       </c>
       <c r="E449" t="n">
-        <v>12.94469990908366</v>
+        <v>12.94470086990156</v>
       </c>
       <c r="F449" t="n">
         <v>4814200</v>
@@ -9412,16 +9412,16 @@
         <v>45303</v>
       </c>
       <c r="B450" t="n">
-        <v>12.77146434783936</v>
+        <v>12.77146339416504</v>
       </c>
       <c r="C450" t="n">
-        <v>12.88695599872818</v>
+        <v>12.88695503642984</v>
       </c>
       <c r="D450" t="n">
-        <v>12.74259074673261</v>
+        <v>12.74258979521435</v>
       </c>
       <c r="E450" t="n">
-        <v>12.84845878176524</v>
+        <v>12.84845782234157</v>
       </c>
       <c r="F450" t="n">
         <v>4041800</v>
@@ -9432,16 +9432,16 @@
         <v>45306</v>
       </c>
       <c r="B451" t="n">
-        <v>12.80996036529541</v>
+        <v>12.80996131896973</v>
       </c>
       <c r="C451" t="n">
-        <v>12.84845757865353</v>
+        <v>12.84845853519388</v>
       </c>
       <c r="D451" t="n">
-        <v>12.74258955353423</v>
+        <v>12.74259050219293</v>
       </c>
       <c r="E451" t="n">
-        <v>12.77146315193729</v>
+        <v>12.77146410274557</v>
       </c>
       <c r="F451" t="n">
         <v>1955800</v>
@@ -9492,16 +9492,16 @@
         <v>45309</v>
       </c>
       <c r="B454" t="n">
-        <v>12.55972766876221</v>
+        <v>12.55972862243652</v>
       </c>
       <c r="C454" t="n">
-        <v>12.77146279524125</v>
+        <v>12.77146376499286</v>
       </c>
       <c r="D454" t="n">
-        <v>12.51160592394707</v>
+        <v>12.51160687396745</v>
       </c>
       <c r="E454" t="n">
-        <v>12.76183826270904</v>
+        <v>12.76183923172984</v>
       </c>
       <c r="F454" t="n">
         <v>6534900</v>
@@ -9532,16 +9532,16 @@
         <v>45313</v>
       </c>
       <c r="B456" t="n">
-        <v>12.61747360229492</v>
+        <v>12.61747455596924</v>
       </c>
       <c r="C456" t="n">
-        <v>12.65597081632927</v>
+        <v>12.65597177291335</v>
       </c>
       <c r="D456" t="n">
-        <v>12.56935277313647</v>
+        <v>12.56935372317364</v>
       </c>
       <c r="E456" t="n">
-        <v>12.60784998717082</v>
+        <v>12.60785094011775</v>
       </c>
       <c r="F456" t="n">
         <v>4490300</v>
@@ -9572,16 +9572,16 @@
         <v>45315</v>
       </c>
       <c r="B458" t="n">
-        <v>12.79071235656738</v>
+        <v>12.79071140289307</v>
       </c>
       <c r="C458" t="n">
-        <v>12.82920957310646</v>
+        <v>12.82920861656179</v>
       </c>
       <c r="D458" t="n">
-        <v>12.64634802400737</v>
+        <v>12.64634708109684</v>
       </c>
       <c r="E458" t="n">
-        <v>12.6559716397576</v>
+        <v>12.65597069612954</v>
       </c>
       <c r="F458" t="n">
         <v>3333600</v>
@@ -9652,16 +9652,16 @@
         <v>45321</v>
       </c>
       <c r="B462" t="n">
-        <v>12.51160717010498</v>
+        <v>12.51160621643066</v>
       </c>
       <c r="C462" t="n">
-        <v>12.63672335194755</v>
+        <v>12.63672238873649</v>
       </c>
       <c r="D462" t="n">
-        <v>12.51160717010498</v>
+        <v>12.51160621643066</v>
       </c>
       <c r="E462" t="n">
-        <v>12.58860160233948</v>
+        <v>12.58860064279641</v>
       </c>
       <c r="F462" t="n">
         <v>3463200</v>
@@ -9672,16 +9672,16 @@
         <v>45322</v>
       </c>
       <c r="B463" t="n">
-        <v>12.68484401702881</v>
+        <v>12.68484497070312</v>
       </c>
       <c r="C463" t="n">
-        <v>12.79071112283833</v>
+        <v>12.79071208447197</v>
       </c>
       <c r="D463" t="n">
-        <v>12.53085516572552</v>
+        <v>12.53085610782262</v>
       </c>
       <c r="E463" t="n">
-        <v>12.57897599337333</v>
+        <v>12.57897693908826</v>
       </c>
       <c r="F463" t="n">
         <v>3755000</v>
@@ -9812,16 +9812,16 @@
         <v>45331</v>
       </c>
       <c r="B470" t="n">
-        <v>12.48273468017578</v>
+        <v>12.48273372650146</v>
       </c>
       <c r="C470" t="n">
-        <v>12.62709901338253</v>
+        <v>12.62709804867886</v>
       </c>
       <c r="D470" t="n">
-        <v>12.36724303004117</v>
+        <v>12.36724208519036</v>
       </c>
       <c r="E470" t="n">
-        <v>12.36724303004117</v>
+        <v>12.36724208519036</v>
       </c>
       <c r="F470" t="n">
         <v>4943200</v>
@@ -9852,16 +9852,16 @@
         <v>45337</v>
       </c>
       <c r="B472" t="n">
-        <v>12.50198268890381</v>
+        <v>12.50198173522949</v>
       </c>
       <c r="C472" t="n">
-        <v>12.58860165499141</v>
+        <v>12.58860069470964</v>
       </c>
       <c r="D472" t="n">
-        <v>12.4153637228162</v>
+        <v>12.41536277574934</v>
       </c>
       <c r="E472" t="n">
-        <v>12.46348547262554</v>
+        <v>12.46348452188787</v>
       </c>
       <c r="F472" t="n">
         <v>4740900</v>
@@ -9892,16 +9892,16 @@
         <v>45341</v>
       </c>
       <c r="B474" t="n">
-        <v>12.77146434783936</v>
+        <v>12.77146339416504</v>
       </c>
       <c r="C474" t="n">
-        <v>12.85808239762144</v>
+        <v>12.85808143747915</v>
       </c>
       <c r="D474" t="n">
-        <v>12.53085651235945</v>
+        <v>12.53085557665187</v>
       </c>
       <c r="E474" t="n">
-        <v>12.54048012821565</v>
+        <v>12.54047919178945</v>
       </c>
       <c r="F474" t="n">
         <v>4786000</v>
@@ -9972,16 +9972,16 @@
         <v>45345</v>
       </c>
       <c r="B478" t="n">
-        <v>12.41536331176758</v>
+        <v>12.41536235809326</v>
       </c>
       <c r="C478" t="n">
-        <v>12.55010402320352</v>
+        <v>12.55010305917923</v>
       </c>
       <c r="D478" t="n">
-        <v>12.41536331176758</v>
+        <v>12.41536235809326</v>
       </c>
       <c r="E478" t="n">
-        <v>12.52123134141225</v>
+        <v>12.52123037960578</v>
       </c>
       <c r="F478" t="n">
         <v>4574300</v>
@@ -9992,16 +9992,16 @@
         <v>45348</v>
       </c>
       <c r="B479" t="n">
-        <v>12.35761737823486</v>
+        <v>12.35761833190918</v>
       </c>
       <c r="C479" t="n">
-        <v>12.48273355068785</v>
+        <v>12.48273451401776</v>
       </c>
       <c r="D479" t="n">
-        <v>12.3383683126978</v>
+        <v>12.33836926488661</v>
       </c>
       <c r="E479" t="n">
-        <v>12.45385995238227</v>
+        <v>12.45386091348391</v>
       </c>
       <c r="F479" t="n">
         <v>6964500</v>
@@ -22105,6 +22105,26 @@
       </c>
       <c r="F1084" t="n">
         <v>1564600</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B1085" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="C1085" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="D1085" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E1085" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="F1085" t="n">
+        <v>1250900</v>
       </c>
     </row>
   </sheetData>

--- a/database/AURE3.xlsx
+++ b/database/AURE3.xlsx
@@ -492,16 +492,16 @@
         <v>44650</v>
       </c>
       <c r="B4" t="n">
-        <v>12.38385105133057</v>
+        <v>12.38385009765625</v>
       </c>
       <c r="C4" t="n">
-        <v>13.04504942238897</v>
+        <v>13.04504841779609</v>
       </c>
       <c r="D4" t="n">
-        <v>12.30606274584925</v>
+        <v>12.30606179816537</v>
       </c>
       <c r="E4" t="n">
-        <v>12.92836770601126</v>
+        <v>12.92836671040398</v>
       </c>
       <c r="F4" t="n">
         <v>4408600</v>
@@ -512,16 +512,16 @@
         <v>44651</v>
       </c>
       <c r="B5" t="n">
-        <v>12.43830299377441</v>
+        <v>12.4383020401001</v>
       </c>
       <c r="C5" t="n">
-        <v>12.82724305543223</v>
+        <v>12.82724207193696</v>
       </c>
       <c r="D5" t="n">
-        <v>12.05714191139238</v>
+        <v>12.05714098694259</v>
       </c>
       <c r="E5" t="n">
-        <v>12.41496679779135</v>
+        <v>12.41496584590627</v>
       </c>
       <c r="F5" t="n">
         <v>3876100</v>
@@ -532,16 +532,16 @@
         <v>44652</v>
       </c>
       <c r="B6" t="n">
-        <v>12.51609134674072</v>
+        <v>12.51609039306641</v>
       </c>
       <c r="C6" t="n">
-        <v>12.95170380189247</v>
+        <v>12.95170281502629</v>
       </c>
       <c r="D6" t="n">
-        <v>12.31384233592669</v>
+        <v>12.31384139766291</v>
       </c>
       <c r="E6" t="n">
-        <v>12.43830303739862</v>
+        <v>12.43830208965145</v>
       </c>
       <c r="F6" t="n">
         <v>4252000</v>
@@ -592,16 +592,16 @@
         <v>44657</v>
       </c>
       <c r="B9" t="n">
-        <v>12.43052291870117</v>
+        <v>12.43052387237549</v>
       </c>
       <c r="C9" t="n">
-        <v>12.44608087588125</v>
+        <v>12.44608183074918</v>
       </c>
       <c r="D9" t="n">
-        <v>12.01824669740399</v>
+        <v>12.01824761944832</v>
       </c>
       <c r="E9" t="n">
-        <v>12.06491982710001</v>
+        <v>12.06492075272512</v>
       </c>
       <c r="F9" t="n">
         <v>2914800</v>
@@ -672,16 +672,16 @@
         <v>44663</v>
       </c>
       <c r="B13" t="n">
-        <v>12.2438325881958</v>
+        <v>12.24383163452148</v>
       </c>
       <c r="C13" t="n">
-        <v>12.64055161698694</v>
+        <v>12.64055063241211</v>
       </c>
       <c r="D13" t="n">
-        <v>12.2127174138893</v>
+        <v>12.21271646263855</v>
       </c>
       <c r="E13" t="n">
-        <v>12.48497500361014</v>
+        <v>12.4849740311532</v>
       </c>
       <c r="F13" t="n">
         <v>2267700</v>
@@ -772,16 +772,16 @@
         <v>44671</v>
       </c>
       <c r="B18" t="n">
-        <v>12.05714130401611</v>
+        <v>12.0571403503418</v>
       </c>
       <c r="C18" t="n">
-        <v>12.21271717247328</v>
+        <v>12.2127162064935</v>
       </c>
       <c r="D18" t="n">
-        <v>11.95601680405789</v>
+        <v>11.95601585838214</v>
       </c>
       <c r="E18" t="n">
-        <v>12.07269926178396</v>
+        <v>12.07269830687907</v>
       </c>
       <c r="F18" t="n">
         <v>2798400</v>
@@ -832,16 +832,16 @@
         <v>44677</v>
       </c>
       <c r="B21" t="n">
-        <v>11.95601654052734</v>
+        <v>11.95601558685303</v>
       </c>
       <c r="C21" t="n">
-        <v>12.4383020930363</v>
+        <v>12.43830110089237</v>
       </c>
       <c r="D21" t="n">
-        <v>11.86267102151054</v>
+        <v>11.86267007528195</v>
       </c>
       <c r="E21" t="n">
-        <v>12.32939935843881</v>
+        <v>12.32939837498153</v>
       </c>
       <c r="F21" t="n">
         <v>2627000</v>
@@ -852,16 +852,16 @@
         <v>44678</v>
       </c>
       <c r="B22" t="n">
-        <v>12.05714130401611</v>
+        <v>12.0571403503418</v>
       </c>
       <c r="C22" t="n">
-        <v>12.06492028290003</v>
+        <v>12.06491932861043</v>
       </c>
       <c r="D22" t="n">
-        <v>11.83155610929216</v>
+        <v>11.83155517346078</v>
       </c>
       <c r="E22" t="n">
-        <v>12.04936232513219</v>
+        <v>12.04936137207316</v>
       </c>
       <c r="F22" t="n">
         <v>2401400</v>
@@ -892,16 +892,16 @@
         <v>44680</v>
       </c>
       <c r="B24" t="n">
-        <v>11.40372085571289</v>
+        <v>11.40372180938721</v>
       </c>
       <c r="C24" t="n">
-        <v>11.963794671995</v>
+        <v>11.96379567250737</v>
       </c>
       <c r="D24" t="n">
-        <v>11.40372085571289</v>
+        <v>11.40372180938721</v>
       </c>
       <c r="E24" t="n">
-        <v>11.963794671995</v>
+        <v>11.96379567250737</v>
       </c>
       <c r="F24" t="n">
         <v>10427400</v>
@@ -932,16 +932,16 @@
         <v>44684</v>
       </c>
       <c r="B26" t="n">
-        <v>11.27148151397705</v>
+        <v>11.27148056030273</v>
       </c>
       <c r="C26" t="n">
-        <v>11.35704879249248</v>
+        <v>11.35704783157836</v>
       </c>
       <c r="D26" t="n">
-        <v>11.01478116211917</v>
+        <v>11.01478023016414</v>
       </c>
       <c r="E26" t="n">
-        <v>11.15479980562136</v>
+        <v>11.15479886181943</v>
       </c>
       <c r="F26" t="n">
         <v>1672900</v>
@@ -952,16 +952,16 @@
         <v>44685</v>
       </c>
       <c r="B27" t="n">
-        <v>11.69445705413818</v>
+        <v>11.69445610046387</v>
       </c>
       <c r="C27" t="n">
-        <v>11.69445705413818</v>
+        <v>11.69445610046387</v>
       </c>
       <c r="D27" t="n">
-        <v>11.03649687268372</v>
+        <v>11.03649597266557</v>
       </c>
       <c r="E27" t="n">
-        <v>11.2088199552074</v>
+        <v>11.20881904113643</v>
       </c>
       <c r="F27" t="n">
         <v>4400300</v>
@@ -1012,16 +1012,16 @@
         <v>44690</v>
       </c>
       <c r="B30" t="n">
-        <v>11.07565975189209</v>
+        <v>11.07566165924072</v>
       </c>
       <c r="C30" t="n">
-        <v>11.13048951029273</v>
+        <v>11.13049142708364</v>
       </c>
       <c r="D30" t="n">
-        <v>10.8093425019471</v>
+        <v>10.80934436343302</v>
       </c>
       <c r="E30" t="n">
-        <v>10.99733088532023</v>
+        <v>10.99733277917979</v>
       </c>
       <c r="F30" t="n">
         <v>1545300</v>
@@ -1092,16 +1092,16 @@
         <v>44694</v>
       </c>
       <c r="B34" t="n">
-        <v>11.32631206512451</v>
+        <v>11.32631301879883</v>
       </c>
       <c r="C34" t="n">
-        <v>11.38114182902154</v>
+        <v>11.38114278731251</v>
       </c>
       <c r="D34" t="n">
-        <v>11.11482455237968</v>
+        <v>11.11482548824677</v>
       </c>
       <c r="E34" t="n">
-        <v>11.18532038996129</v>
+        <v>11.18532133176413</v>
       </c>
       <c r="F34" t="n">
         <v>1333500</v>
@@ -1152,16 +1152,16 @@
         <v>44699</v>
       </c>
       <c r="B37" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C37" t="n">
-        <v>11.5926298208571</v>
+        <v>11.59262882548476</v>
       </c>
       <c r="D37" t="n">
-        <v>11.03649688106261</v>
+        <v>11.03649593344125</v>
       </c>
       <c r="E37" t="n">
-        <v>11.51430094319608</v>
+        <v>11.51429995454926</v>
       </c>
       <c r="F37" t="n">
         <v>1959900</v>
@@ -1192,16 +1192,16 @@
         <v>44701</v>
       </c>
       <c r="B39" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C39" t="n">
-        <v>11.34197786054158</v>
+        <v>11.34197688669085</v>
       </c>
       <c r="D39" t="n">
-        <v>10.86417379840811</v>
+        <v>10.86417286558284</v>
       </c>
       <c r="E39" t="n">
-        <v>11.34197786054158</v>
+        <v>11.34197688669085</v>
       </c>
       <c r="F39" t="n">
         <v>1777400</v>
@@ -1212,16 +1212,16 @@
         <v>44704</v>
       </c>
       <c r="B40" t="n">
-        <v>11.20882034301758</v>
+        <v>11.20881938934326</v>
       </c>
       <c r="C40" t="n">
-        <v>11.4359731995218</v>
+        <v>11.43597222652075</v>
       </c>
       <c r="D40" t="n">
-        <v>11.16182286543069</v>
+        <v>11.16182191575504</v>
       </c>
       <c r="E40" t="n">
-        <v>11.18532123072435</v>
+        <v>11.1853202790494</v>
       </c>
       <c r="F40" t="n">
         <v>1184600</v>
@@ -1252,16 +1252,16 @@
         <v>44706</v>
       </c>
       <c r="B42" t="n">
-        <v>11.32631206512451</v>
+        <v>11.32631301879883</v>
       </c>
       <c r="C42" t="n">
-        <v>11.39680790270612</v>
+        <v>11.39680886231618</v>
       </c>
       <c r="D42" t="n">
-        <v>11.13832366290656</v>
+        <v>11.13832460075227</v>
       </c>
       <c r="E42" t="n">
-        <v>11.17748810011851</v>
+        <v>11.17748904126186</v>
       </c>
       <c r="F42" t="n">
         <v>821700</v>
@@ -1272,16 +1272,16 @@
         <v>44707</v>
       </c>
       <c r="B43" t="n">
-        <v>11.25581550598145</v>
+        <v>11.25581645965576</v>
       </c>
       <c r="C43" t="n">
-        <v>11.44380389614828</v>
+        <v>11.44380486575034</v>
       </c>
       <c r="D43" t="n">
-        <v>11.20881878193947</v>
+        <v>11.20881973163188</v>
       </c>
       <c r="E43" t="n">
-        <v>11.33414437538402</v>
+        <v>11.33414533569493</v>
       </c>
       <c r="F43" t="n">
         <v>1248800</v>
@@ -1312,16 +1312,16 @@
         <v>44711</v>
       </c>
       <c r="B45" t="n">
-        <v>11.09916019439697</v>
+        <v>11.09915924072266</v>
       </c>
       <c r="C45" t="n">
-        <v>11.27148328496971</v>
+        <v>11.27148231648886</v>
       </c>
       <c r="D45" t="n">
-        <v>11.02866435066269</v>
+        <v>11.0286634030456</v>
       </c>
       <c r="E45" t="n">
-        <v>11.15398996307938</v>
+        <v>11.15398900469392</v>
       </c>
       <c r="F45" t="n">
         <v>1940200</v>
@@ -1372,16 +1372,16 @@
         <v>44714</v>
       </c>
       <c r="B48" t="n">
-        <v>10.86417388916016</v>
+        <v>10.86417293548584</v>
       </c>
       <c r="C48" t="n">
-        <v>10.98949949686503</v>
+        <v>10.98949853218943</v>
       </c>
       <c r="D48" t="n">
-        <v>10.68401851483428</v>
+        <v>10.68401757697429</v>
       </c>
       <c r="E48" t="n">
-        <v>10.75451360891862</v>
+        <v>10.75451266487045</v>
       </c>
       <c r="F48" t="n">
         <v>3275400</v>
@@ -1412,16 +1412,16 @@
         <v>44718</v>
       </c>
       <c r="B50" t="n">
-        <v>10.61352157592773</v>
+        <v>10.61352252960205</v>
       </c>
       <c r="C50" t="n">
-        <v>10.91117023693893</v>
+        <v>10.91117121735836</v>
       </c>
       <c r="D50" t="n">
-        <v>10.45686458250065</v>
+        <v>10.4568655220986</v>
       </c>
       <c r="E50" t="n">
-        <v>10.81717604088268</v>
+        <v>10.8171770128563</v>
       </c>
       <c r="F50" t="n">
         <v>3175000</v>
@@ -1532,16 +1532,16 @@
         <v>44726</v>
       </c>
       <c r="B56" t="n">
-        <v>10.39420223236084</v>
+        <v>10.39420318603516</v>
       </c>
       <c r="C56" t="n">
-        <v>10.47253035894487</v>
+        <v>10.47253131980584</v>
       </c>
       <c r="D56" t="n">
-        <v>10.01822468495919</v>
+        <v>10.01822560413734</v>
       </c>
       <c r="E56" t="n">
-        <v>10.01822468495919</v>
+        <v>10.01822560413734</v>
       </c>
       <c r="F56" t="n">
         <v>4085600</v>
@@ -1552,16 +1552,16 @@
         <v>44727</v>
       </c>
       <c r="B57" t="n">
-        <v>10.84067440032959</v>
+        <v>10.84067535400391</v>
       </c>
       <c r="C57" t="n">
-        <v>10.84850743674878</v>
+        <v>10.84850839111218</v>
       </c>
       <c r="D57" t="n">
-        <v>10.44119850694474</v>
+        <v>10.44119942547642</v>
       </c>
       <c r="E57" t="n">
-        <v>10.55085877581493</v>
+        <v>10.55085970399363</v>
       </c>
       <c r="F57" t="n">
         <v>3153700</v>
@@ -1572,16 +1572,16 @@
         <v>44729</v>
       </c>
       <c r="B58" t="n">
-        <v>10.45686626434326</v>
+        <v>10.45686531066895</v>
       </c>
       <c r="C58" t="n">
-        <v>10.80151170531431</v>
+        <v>10.80151072020806</v>
       </c>
       <c r="D58" t="n">
-        <v>10.42553486061862</v>
+        <v>10.42553390980175</v>
       </c>
       <c r="E58" t="n">
-        <v>10.74668193554609</v>
+        <v>10.74668095544036</v>
       </c>
       <c r="F58" t="n">
         <v>8202900</v>
@@ -1692,16 +1692,16 @@
         <v>44739</v>
       </c>
       <c r="B64" t="n">
-        <v>10.45686626434326</v>
+        <v>10.45686531066895</v>
       </c>
       <c r="C64" t="n">
-        <v>10.55086047551718</v>
+        <v>10.55085951327052</v>
       </c>
       <c r="D64" t="n">
-        <v>10.33153990244511</v>
+        <v>10.33153896020065</v>
       </c>
       <c r="E64" t="n">
-        <v>10.49602995874937</v>
+        <v>10.4960290015033</v>
       </c>
       <c r="F64" t="n">
         <v>1661400</v>
@@ -1712,16 +1712,16 @@
         <v>44740</v>
       </c>
       <c r="B65" t="n">
-        <v>10.61352157592773</v>
+        <v>10.61352252960205</v>
       </c>
       <c r="C65" t="n">
-        <v>10.86417276541107</v>
+        <v>10.86417374160756</v>
       </c>
       <c r="D65" t="n">
-        <v>10.47252990834362</v>
+        <v>10.47253084934918</v>
       </c>
       <c r="E65" t="n">
-        <v>10.52735966929324</v>
+        <v>10.5273606152255</v>
       </c>
       <c r="F65" t="n">
         <v>5362200</v>
@@ -1732,16 +1732,16 @@
         <v>44741</v>
       </c>
       <c r="B66" t="n">
-        <v>10.68401718139648</v>
+        <v>10.6840181350708</v>
       </c>
       <c r="C66" t="n">
-        <v>10.68401718139648</v>
+        <v>10.6840181350708</v>
       </c>
       <c r="D66" t="n">
-        <v>10.53519248057162</v>
+        <v>10.53519342096158</v>
       </c>
       <c r="E66" t="n">
-        <v>10.62918667461916</v>
+        <v>10.62918762339921</v>
       </c>
       <c r="F66" t="n">
         <v>1613700</v>
@@ -1772,16 +1772,16 @@
         <v>44743</v>
       </c>
       <c r="B68" t="n">
-        <v>10.68401718139648</v>
+        <v>10.6840181350708</v>
       </c>
       <c r="C68" t="n">
-        <v>10.84067417147572</v>
+        <v>10.84067513913352</v>
       </c>
       <c r="D68" t="n">
-        <v>10.54302551682544</v>
+        <v>10.54302645791459</v>
       </c>
       <c r="E68" t="n">
-        <v>10.72318086866671</v>
+        <v>10.72318182583684</v>
       </c>
       <c r="F68" t="n">
         <v>2696600</v>
@@ -1832,16 +1832,16 @@
         <v>44748</v>
       </c>
       <c r="B71" t="n">
-        <v>10.67618465423584</v>
+        <v>10.67618560791016</v>
       </c>
       <c r="C71" t="n">
-        <v>10.71534909037307</v>
+        <v>10.71535004754583</v>
       </c>
       <c r="D71" t="n">
-        <v>10.49602854680439</v>
+        <v>10.49602948438586</v>
       </c>
       <c r="E71" t="n">
-        <v>10.57435741907885</v>
+        <v>10.57435836365721</v>
       </c>
       <c r="F71" t="n">
         <v>1826800</v>
@@ -1892,16 +1892,16 @@
         <v>44753</v>
       </c>
       <c r="B74" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C74" t="n">
-        <v>11.18532085221909</v>
+        <v>11.18531989181933</v>
       </c>
       <c r="D74" t="n">
-        <v>10.83284239674361</v>
+        <v>10.83284146660853</v>
       </c>
       <c r="E74" t="n">
-        <v>11.0599952455611</v>
+        <v>11.05999429592211</v>
       </c>
       <c r="F74" t="n">
         <v>1881000</v>
@@ -1912,16 +1912,16 @@
         <v>44754</v>
       </c>
       <c r="B75" t="n">
-        <v>11.14615535736084</v>
+        <v>11.14615631103516</v>
       </c>
       <c r="C75" t="n">
-        <v>11.22448422760069</v>
+        <v>11.22448518797689</v>
       </c>
       <c r="D75" t="n">
-        <v>10.99733140030449</v>
+        <v>10.99733234124531</v>
       </c>
       <c r="E75" t="n">
-        <v>11.10699166924038</v>
+        <v>11.10699261956382</v>
       </c>
       <c r="F75" t="n">
         <v>1673000</v>
@@ -1932,16 +1932,16 @@
         <v>44755</v>
       </c>
       <c r="B76" t="n">
-        <v>11.17748832702637</v>
+        <v>11.17748737335205</v>
       </c>
       <c r="C76" t="n">
-        <v>11.23231809203646</v>
+        <v>11.23231713368402</v>
       </c>
       <c r="D76" t="n">
-        <v>11.01299828499656</v>
+        <v>11.0129973453567</v>
       </c>
       <c r="E76" t="n">
-        <v>11.18532061702815</v>
+        <v>11.18531966268557</v>
       </c>
       <c r="F76" t="n">
         <v>2559400</v>
@@ -1952,16 +1952,16 @@
         <v>44756</v>
       </c>
       <c r="B77" t="n">
-        <v>10.91117095947266</v>
+        <v>10.91117000579834</v>
       </c>
       <c r="C77" t="n">
-        <v>11.17748823943387</v>
+        <v>11.1774872624825</v>
       </c>
       <c r="D77" t="n">
-        <v>10.84850815795232</v>
+        <v>10.84850720975495</v>
       </c>
       <c r="E77" t="n">
-        <v>11.04432959945326</v>
+        <v>11.04432863414042</v>
       </c>
       <c r="F77" t="n">
         <v>1968500</v>
@@ -1972,16 +1972,16 @@
         <v>44757</v>
       </c>
       <c r="B78" t="n">
-        <v>10.8093433380127</v>
+        <v>10.80934429168701</v>
       </c>
       <c r="C78" t="n">
-        <v>10.98166640959971</v>
+        <v>10.98166737847755</v>
       </c>
       <c r="D78" t="n">
-        <v>10.60568886677345</v>
+        <v>10.60568980247997</v>
       </c>
       <c r="E78" t="n">
-        <v>10.97383337293678</v>
+        <v>10.97383434112354</v>
       </c>
       <c r="F78" t="n">
         <v>2342600</v>
@@ -2012,16 +2012,16 @@
         <v>44761</v>
       </c>
       <c r="B80" t="n">
-        <v>11.09132671356201</v>
+        <v>11.0913257598877</v>
       </c>
       <c r="C80" t="n">
-        <v>11.09132671356201</v>
+        <v>11.0913257598877</v>
       </c>
       <c r="D80" t="n">
-        <v>10.78584573225599</v>
+        <v>10.78584480484809</v>
       </c>
       <c r="E80" t="n">
-        <v>10.87200690059879</v>
+        <v>10.87200596578243</v>
       </c>
       <c r="F80" t="n">
         <v>2890800</v>
@@ -2052,16 +2052,16 @@
         <v>44763</v>
       </c>
       <c r="B82" t="n">
-        <v>11.2479829788208</v>
+        <v>11.24798393249512</v>
       </c>
       <c r="C82" t="n">
-        <v>11.27931437860027</v>
+        <v>11.27931533493105</v>
       </c>
       <c r="D82" t="n">
-        <v>11.05999458014401</v>
+        <v>11.0599955178795</v>
       </c>
       <c r="E82" t="n">
-        <v>11.22448461573608</v>
+        <v>11.22448556741805</v>
       </c>
       <c r="F82" t="n">
         <v>1092700</v>
@@ -2112,16 +2112,16 @@
         <v>44768</v>
       </c>
       <c r="B85" t="n">
-        <v>11.27148246765137</v>
+        <v>11.27148342132568</v>
       </c>
       <c r="C85" t="n">
-        <v>11.38114199706455</v>
+        <v>11.3811429600171</v>
       </c>
       <c r="D85" t="n">
-        <v>11.16965522819662</v>
+        <v>11.16965617325538</v>
       </c>
       <c r="E85" t="n">
-        <v>11.19315359207094</v>
+        <v>11.19315453911789</v>
       </c>
       <c r="F85" t="n">
         <v>1661400</v>
@@ -2132,16 +2132,16 @@
         <v>44769</v>
       </c>
       <c r="B86" t="n">
-        <v>11.24015045166016</v>
+        <v>11.24015140533447</v>
       </c>
       <c r="C86" t="n">
-        <v>11.49080164460048</v>
+        <v>11.49080261954139</v>
       </c>
       <c r="D86" t="n">
-        <v>11.15398854383731</v>
+        <v>11.15398949020119</v>
       </c>
       <c r="E86" t="n">
-        <v>11.28714717683673</v>
+        <v>11.2871481344985</v>
       </c>
       <c r="F86" t="n">
         <v>3096400</v>
@@ -2212,16 +2212,16 @@
         <v>44775</v>
       </c>
       <c r="B90" t="n">
-        <v>10.86417388916016</v>
+        <v>10.86417293548584</v>
       </c>
       <c r="C90" t="n">
-        <v>11.06782837518035</v>
+        <v>11.06782740362892</v>
       </c>
       <c r="D90" t="n">
-        <v>10.7231822069924</v>
+        <v>10.72318126569455</v>
       </c>
       <c r="E90" t="n">
-        <v>10.93466973024404</v>
+        <v>10.93466877038148</v>
       </c>
       <c r="F90" t="n">
         <v>2371400</v>
@@ -2292,16 +2292,16 @@
         <v>44781</v>
       </c>
       <c r="B94" t="n">
-        <v>10.97383403778076</v>
+        <v>10.97383308410645</v>
       </c>
       <c r="C94" t="n">
-        <v>11.10699268111997</v>
+        <v>11.10699171587358</v>
       </c>
       <c r="D94" t="n">
-        <v>10.87200679599199</v>
+        <v>10.8720058511669</v>
       </c>
       <c r="E94" t="n">
-        <v>11.02866380374413</v>
+        <v>11.02866284530486</v>
       </c>
       <c r="F94" t="n">
         <v>2949000</v>
@@ -2352,16 +2352,16 @@
         <v>44784</v>
       </c>
       <c r="B97" t="n">
-        <v>10.89550495147705</v>
+        <v>10.89550590515137</v>
       </c>
       <c r="C97" t="n">
-        <v>11.10699246813669</v>
+        <v>11.10699344032233</v>
       </c>
       <c r="D97" t="n">
-        <v>10.83284214957779</v>
+        <v>10.83284309776729</v>
       </c>
       <c r="E97" t="n">
-        <v>11.05999499321249</v>
+        <v>11.05999596128448</v>
       </c>
       <c r="F97" t="n">
         <v>1665400</v>
@@ -2372,16 +2372,16 @@
         <v>44785</v>
       </c>
       <c r="B98" t="n">
-        <v>11.08349418640137</v>
+        <v>11.08349323272705</v>
       </c>
       <c r="C98" t="n">
-        <v>11.13049166484175</v>
+        <v>11.13049070712356</v>
       </c>
       <c r="D98" t="n">
-        <v>10.78584622861072</v>
+        <v>10.78584530054738</v>
       </c>
       <c r="E98" t="n">
-        <v>10.89550576663898</v>
+        <v>10.89550482914005</v>
       </c>
       <c r="F98" t="n">
         <v>2648400</v>
@@ -2432,16 +2432,16 @@
         <v>44790</v>
       </c>
       <c r="B101" t="n">
-        <v>11.24015045166016</v>
+        <v>11.24015140533447</v>
       </c>
       <c r="C101" t="n">
-        <v>11.25581577771919</v>
+        <v>11.25581673272263</v>
       </c>
       <c r="D101" t="n">
-        <v>10.91117038742624</v>
+        <v>10.91117131318813</v>
       </c>
       <c r="E101" t="n">
-        <v>10.98949851172035</v>
+        <v>10.98949944412802</v>
       </c>
       <c r="F101" t="n">
         <v>4396400</v>
@@ -2452,16 +2452,16 @@
         <v>44791</v>
       </c>
       <c r="B102" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="C102" t="n">
-        <v>11.37330994384684</v>
+        <v>11.37330897550059</v>
       </c>
       <c r="D102" t="n">
-        <v>11.09915962060828</v>
+        <v>11.09915867560374</v>
       </c>
       <c r="E102" t="n">
-        <v>11.27931499239396</v>
+        <v>11.27931403205064</v>
       </c>
       <c r="F102" t="n">
         <v>2180500</v>
@@ -2532,16 +2532,16 @@
         <v>44797</v>
       </c>
       <c r="B106" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C106" t="n">
-        <v>11.3968083737041</v>
+        <v>11.39680739514549</v>
       </c>
       <c r="D106" t="n">
-        <v>11.09915968439161</v>
+        <v>11.09915873138986</v>
       </c>
       <c r="E106" t="n">
-        <v>11.2244852910496</v>
+        <v>11.22448432728707</v>
       </c>
       <c r="F106" t="n">
         <v>2116800</v>
@@ -2652,16 +2652,16 @@
         <v>44805</v>
       </c>
       <c r="B112" t="n">
-        <v>11.65529346466064</v>
+        <v>11.65529251098633</v>
       </c>
       <c r="C112" t="n">
-        <v>12.1565966744416</v>
+        <v>12.15659567974902</v>
       </c>
       <c r="D112" t="n">
-        <v>11.42030756173208</v>
+        <v>11.42030662728508</v>
       </c>
       <c r="E112" t="n">
-        <v>12.14093059897989</v>
+        <v>12.14092960556915</v>
       </c>
       <c r="F112" t="n">
         <v>4716400</v>
@@ -2712,16 +2712,16 @@
         <v>44810</v>
       </c>
       <c r="B115" t="n">
-        <v>11.58479690551758</v>
+        <v>11.58479785919189</v>
       </c>
       <c r="C115" t="n">
-        <v>11.90594396270576</v>
+        <v>11.90594494281729</v>
       </c>
       <c r="D115" t="n">
-        <v>11.49863573678402</v>
+        <v>11.49863668336545</v>
       </c>
       <c r="E115" t="n">
-        <v>11.89811092545738</v>
+        <v>11.89811190492408</v>
       </c>
       <c r="F115" t="n">
         <v>1316500</v>
@@ -2732,16 +2732,16 @@
         <v>44812</v>
       </c>
       <c r="B116" t="n">
-        <v>11.4359712600708</v>
+        <v>11.43597221374512</v>
       </c>
       <c r="C116" t="n">
-        <v>11.63962496974372</v>
+        <v>11.63962594040124</v>
       </c>
       <c r="D116" t="n">
-        <v>11.37330846524845</v>
+        <v>11.37330941369716</v>
       </c>
       <c r="E116" t="n">
-        <v>11.62395964453786</v>
+        <v>11.623960613889</v>
       </c>
       <c r="F116" t="n">
         <v>2598100</v>
@@ -2772,16 +2772,16 @@
         <v>44816</v>
       </c>
       <c r="B118" t="n">
-        <v>11.41247272491455</v>
+        <v>11.41247367858887</v>
       </c>
       <c r="C118" t="n">
-        <v>11.64745859079944</v>
+        <v>11.64745956411016</v>
       </c>
       <c r="D118" t="n">
-        <v>11.35764296344122</v>
+        <v>11.35764391253373</v>
       </c>
       <c r="E118" t="n">
-        <v>11.39680739892195</v>
+        <v>11.3968083512872</v>
       </c>
       <c r="F118" t="n">
         <v>2097200</v>
@@ -2792,16 +2792,16 @@
         <v>44817</v>
       </c>
       <c r="B119" t="n">
-        <v>11.24015045166016</v>
+        <v>11.24015140533447</v>
       </c>
       <c r="C119" t="n">
-        <v>11.43597188289466</v>
+        <v>11.43597285318351</v>
       </c>
       <c r="D119" t="n">
-        <v>11.16965461689582</v>
+        <v>11.16965556458889</v>
       </c>
       <c r="E119" t="n">
-        <v>11.30281324989524</v>
+        <v>11.3028142088862</v>
       </c>
       <c r="F119" t="n">
         <v>1768400</v>
@@ -2812,16 +2812,16 @@
         <v>44818</v>
       </c>
       <c r="B120" t="n">
-        <v>11.20882034301758</v>
+        <v>11.20881938934326</v>
       </c>
       <c r="C120" t="n">
-        <v>11.42030712465965</v>
+        <v>11.42030615299151</v>
       </c>
       <c r="D120" t="n">
-        <v>11.02866421710068</v>
+        <v>11.02866327875449</v>
       </c>
       <c r="E120" t="n">
-        <v>11.2009873055865</v>
+        <v>11.20098635257864</v>
       </c>
       <c r="F120" t="n">
         <v>1856400</v>
@@ -2912,16 +2912,16 @@
         <v>44825</v>
       </c>
       <c r="B125" t="n">
-        <v>11.09132671356201</v>
+        <v>11.0913257598877</v>
       </c>
       <c r="C125" t="n">
-        <v>11.23231839539528</v>
+        <v>11.23231742959796</v>
       </c>
       <c r="D125" t="n">
-        <v>10.93466970430257</v>
+        <v>10.93466876409822</v>
       </c>
       <c r="E125" t="n">
-        <v>11.13049115262676</v>
+        <v>11.13049019558493</v>
       </c>
       <c r="F125" t="n">
         <v>2825100</v>
@@ -2952,16 +2952,16 @@
         <v>44827</v>
       </c>
       <c r="B127" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="C127" t="n">
-        <v>11.30281410375695</v>
+        <v>11.30281314141286</v>
       </c>
       <c r="D127" t="n">
-        <v>11.07566125624483</v>
+        <v>11.07566031324099</v>
       </c>
       <c r="E127" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="F127" t="n">
         <v>2444100</v>
@@ -2992,16 +2992,16 @@
         <v>44831</v>
       </c>
       <c r="B129" t="n">
-        <v>10.90333843231201</v>
+        <v>10.9033374786377</v>
       </c>
       <c r="C129" t="n">
-        <v>11.04433011582452</v>
+        <v>11.04432914981819</v>
       </c>
       <c r="D129" t="n">
-        <v>10.77017978610565</v>
+        <v>10.77017884407822</v>
       </c>
       <c r="E129" t="n">
-        <v>11.04433011582452</v>
+        <v>11.04432914981819</v>
       </c>
       <c r="F129" t="n">
         <v>2130200</v>
@@ -3052,16 +3052,16 @@
         <v>44834</v>
       </c>
       <c r="B132" t="n">
-        <v>10.61352157592773</v>
+        <v>10.61352252960205</v>
       </c>
       <c r="C132" t="n">
-        <v>10.74668020709063</v>
+        <v>10.74668117272986</v>
       </c>
       <c r="D132" t="n">
-        <v>10.59785550308529</v>
+        <v>10.59785645535194</v>
       </c>
       <c r="E132" t="n">
-        <v>10.70751577198399</v>
+        <v>10.70751673410412</v>
       </c>
       <c r="F132" t="n">
         <v>4019300</v>
@@ -3072,16 +3072,16 @@
         <v>44837</v>
       </c>
       <c r="B133" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="C133" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="D133" t="n">
-        <v>10.62918785134206</v>
+        <v>10.62918694635185</v>
       </c>
       <c r="E133" t="n">
-        <v>10.74668116715839</v>
+        <v>10.74668025216456</v>
       </c>
       <c r="F133" t="n">
         <v>2250700</v>
@@ -3112,16 +3112,16 @@
         <v>44839</v>
       </c>
       <c r="B135" t="n">
-        <v>10.97383403778076</v>
+        <v>10.97383308410645</v>
       </c>
       <c r="C135" t="n">
-        <v>11.20881992290874</v>
+        <v>11.20881894881312</v>
       </c>
       <c r="D135" t="n">
-        <v>10.85634072171701</v>
+        <v>10.85633977825337</v>
       </c>
       <c r="E135" t="n">
-        <v>11.20881992290874</v>
+        <v>11.20881894881312</v>
       </c>
       <c r="F135" t="n">
         <v>5244200</v>
@@ -3132,16 +3132,16 @@
         <v>44840</v>
       </c>
       <c r="B136" t="n">
-        <v>10.98949909210205</v>
+        <v>10.98950004577637</v>
       </c>
       <c r="C136" t="n">
-        <v>11.1226577321339</v>
+        <v>11.12265869736379</v>
       </c>
       <c r="D136" t="n">
-        <v>10.88767185284243</v>
+        <v>10.88767279768013</v>
       </c>
       <c r="E136" t="n">
-        <v>11.02866352981721</v>
+        <v>11.02866448689024</v>
       </c>
       <c r="F136" t="n">
         <v>3101100</v>
@@ -3152,16 +3152,16 @@
         <v>44841</v>
       </c>
       <c r="B137" t="n">
-        <v>11.02866458892822</v>
+        <v>11.02866363525391</v>
       </c>
       <c r="C137" t="n">
-        <v>11.15399020405247</v>
+        <v>11.15398923954096</v>
       </c>
       <c r="D137" t="n">
-        <v>10.9425034152802</v>
+        <v>10.94250246905644</v>
       </c>
       <c r="E137" t="n">
-        <v>10.98166785675642</v>
+        <v>10.98166690714602</v>
       </c>
       <c r="F137" t="n">
         <v>7588600</v>
@@ -3172,16 +3172,16 @@
         <v>44844</v>
       </c>
       <c r="B138" t="n">
-        <v>11.07565975189209</v>
+        <v>11.07566165924072</v>
       </c>
       <c r="C138" t="n">
-        <v>11.35764232695178</v>
+        <v>11.35764428286087</v>
       </c>
       <c r="D138" t="n">
-        <v>11.01299695743438</v>
+        <v>11.0129988539918</v>
       </c>
       <c r="E138" t="n">
-        <v>11.07565975189209</v>
+        <v>11.07566165924072</v>
       </c>
       <c r="F138" t="n">
         <v>2000500</v>
@@ -3212,16 +3212,16 @@
         <v>44847</v>
       </c>
       <c r="B140" t="n">
-        <v>10.91117095947266</v>
+        <v>10.91117000579834</v>
       </c>
       <c r="C140" t="n">
-        <v>11.20098660325412</v>
+        <v>11.20098562424891</v>
       </c>
       <c r="D140" t="n">
-        <v>10.87200652177256</v>
+        <v>10.87200557152136</v>
       </c>
       <c r="E140" t="n">
-        <v>11.12265772785393</v>
+        <v>11.12265675569494</v>
       </c>
       <c r="F140" t="n">
         <v>3739400</v>
@@ -3232,16 +3232,16 @@
         <v>44848</v>
       </c>
       <c r="B141" t="n">
-        <v>10.8250093460083</v>
+        <v>10.82500839233398</v>
       </c>
       <c r="C141" t="n">
-        <v>11.1618224737291</v>
+        <v>11.16182149038183</v>
       </c>
       <c r="D141" t="n">
-        <v>10.8250093460083</v>
+        <v>10.82500839233398</v>
       </c>
       <c r="E141" t="n">
-        <v>10.97383406397776</v>
+        <v>10.97383309719211</v>
       </c>
       <c r="F141" t="n">
         <v>3601200</v>
@@ -3272,16 +3272,16 @@
         <v>44852</v>
       </c>
       <c r="B143" t="n">
-        <v>11.27148246765137</v>
+        <v>11.27148342132568</v>
       </c>
       <c r="C143" t="n">
-        <v>11.37330970710612</v>
+        <v>11.37331066939599</v>
       </c>
       <c r="D143" t="n">
-        <v>11.06782798874186</v>
+        <v>11.06782892518508</v>
       </c>
       <c r="E143" t="n">
-        <v>11.20881966598683</v>
+        <v>11.20882061435928</v>
       </c>
       <c r="F143" t="n">
         <v>2646800</v>
@@ -3312,16 +3312,16 @@
         <v>44854</v>
       </c>
       <c r="B145" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C145" t="n">
-        <v>10.98166755090811</v>
+        <v>10.98166658413194</v>
       </c>
       <c r="D145" t="n">
-        <v>10.39420318612486</v>
+        <v>10.39420227106638</v>
       </c>
       <c r="E145" t="n">
-        <v>10.5743585660986</v>
+        <v>10.57435763518006</v>
       </c>
       <c r="F145" t="n">
         <v>7194300</v>
@@ -3352,16 +3352,16 @@
         <v>44858</v>
       </c>
       <c r="B147" t="n">
-        <v>11.2479829788208</v>
+        <v>11.24798393249512</v>
       </c>
       <c r="C147" t="n">
-        <v>11.45163745088707</v>
+        <v>11.45163842182848</v>
       </c>
       <c r="D147" t="n">
-        <v>11.10699205331296</v>
+        <v>11.10699299503318</v>
       </c>
       <c r="E147" t="n">
-        <v>11.10699205331296</v>
+        <v>11.10699299503318</v>
       </c>
       <c r="F147" t="n">
         <v>2219500</v>
@@ -3372,16 +3372,16 @@
         <v>44859</v>
       </c>
       <c r="B148" t="n">
-        <v>11.38897514343262</v>
+        <v>11.38897609710693</v>
       </c>
       <c r="C148" t="n">
-        <v>11.50646771093245</v>
+        <v>11.5064686744452</v>
       </c>
       <c r="D148" t="n">
-        <v>11.18532066256667</v>
+        <v>11.18532159918765</v>
       </c>
       <c r="E148" t="n">
-        <v>11.24015117479952</v>
+        <v>11.24015211601182</v>
       </c>
       <c r="F148" t="n">
         <v>2935500</v>
@@ -3392,16 +3392,16 @@
         <v>44860</v>
       </c>
       <c r="B149" t="n">
-        <v>11.3419771194458</v>
+        <v>11.34197807312012</v>
       </c>
       <c r="C149" t="n">
-        <v>11.451637391606</v>
+        <v>11.45163835450095</v>
       </c>
       <c r="D149" t="n">
-        <v>11.20098619466782</v>
+        <v>11.20098713648711</v>
       </c>
       <c r="E149" t="n">
-        <v>11.43597206529711</v>
+        <v>11.43597302687486</v>
       </c>
       <c r="F149" t="n">
         <v>4386900</v>
@@ -3412,16 +3412,16 @@
         <v>44861</v>
       </c>
       <c r="B150" t="n">
-        <v>11.35764312744141</v>
+        <v>11.35764408111572</v>
       </c>
       <c r="C150" t="n">
-        <v>11.63179343276565</v>
+        <v>11.63179440945972</v>
       </c>
       <c r="D150" t="n">
-        <v>11.27148196573925</v>
+        <v>11.27148291217882</v>
       </c>
       <c r="E150" t="n">
-        <v>11.42813896292475</v>
+        <v>11.42813992251844</v>
       </c>
       <c r="F150" t="n">
         <v>4207900</v>
@@ -3512,16 +3512,16 @@
         <v>44869</v>
       </c>
       <c r="B155" t="n">
-        <v>11.67095756530762</v>
+        <v>11.67095851898193</v>
       </c>
       <c r="C155" t="n">
-        <v>11.87461204288736</v>
+        <v>11.87461301320299</v>
       </c>
       <c r="D155" t="n">
-        <v>11.64745920158673</v>
+        <v>11.64746015334091</v>
       </c>
       <c r="E155" t="n">
-        <v>11.7492864403766</v>
+        <v>11.74928740045144</v>
       </c>
       <c r="F155" t="n">
         <v>2161500</v>
@@ -3532,16 +3532,16 @@
         <v>44872</v>
       </c>
       <c r="B156" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="C156" t="n">
-        <v>11.65529255720685</v>
+        <v>11.65529156485204</v>
       </c>
       <c r="D156" t="n">
-        <v>11.12265798497174</v>
+        <v>11.1226570379665</v>
       </c>
       <c r="E156" t="n">
-        <v>11.60829508148041</v>
+        <v>11.60829409312706</v>
       </c>
       <c r="F156" t="n">
         <v>3276500</v>
@@ -3632,16 +3632,16 @@
         <v>44879</v>
       </c>
       <c r="B161" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C161" t="n">
-        <v>10.9660014759541</v>
+        <v>10.9660005105571</v>
       </c>
       <c r="D161" t="n">
-        <v>10.71535025268644</v>
+        <v>10.71534930935563</v>
       </c>
       <c r="E161" t="n">
-        <v>10.94250311052265</v>
+        <v>10.94250214719434</v>
       </c>
       <c r="F161" t="n">
         <v>1203700</v>
@@ -3652,16 +3652,16 @@
         <v>44881</v>
       </c>
       <c r="B162" t="n">
-        <v>10.90333843231201</v>
+        <v>10.9033374786377</v>
       </c>
       <c r="C162" t="n">
-        <v>10.90333843231201</v>
+        <v>10.9033374786377</v>
       </c>
       <c r="D162" t="n">
-        <v>10.59785670036809</v>
+        <v>10.59785577341312</v>
       </c>
       <c r="E162" t="n">
-        <v>10.86417399278081</v>
+        <v>10.86417304253206</v>
       </c>
       <c r="F162" t="n">
         <v>5270300</v>
@@ -3692,16 +3692,16 @@
         <v>44883</v>
       </c>
       <c r="B164" t="n">
-        <v>10.78584480285645</v>
+        <v>10.78584671020508</v>
       </c>
       <c r="C164" t="n">
-        <v>10.98949852384542</v>
+        <v>10.9895004672078</v>
       </c>
       <c r="D164" t="n">
-        <v>10.57435729833009</v>
+        <v>10.57435916827967</v>
       </c>
       <c r="E164" t="n">
-        <v>10.80934316547066</v>
+        <v>10.8093450769747</v>
       </c>
       <c r="F164" t="n">
         <v>3568700</v>
@@ -3752,16 +3752,16 @@
         <v>44888</v>
       </c>
       <c r="B167" t="n">
-        <v>10.56652545928955</v>
+        <v>10.56652450561523</v>
       </c>
       <c r="C167" t="n">
-        <v>10.81717742791213</v>
+        <v>10.8171764516154</v>
       </c>
       <c r="D167" t="n">
-        <v>10.51952872873502</v>
+        <v>10.51952777930236</v>
       </c>
       <c r="E167" t="n">
-        <v>10.80934439048652</v>
+        <v>10.80934341489675</v>
       </c>
       <c r="F167" t="n">
         <v>4669400</v>
@@ -3792,16 +3792,16 @@
         <v>44890</v>
       </c>
       <c r="B169" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C169" t="n">
-        <v>11.03649731924802</v>
+        <v>11.03649634764489</v>
       </c>
       <c r="D169" t="n">
-        <v>10.71535025268644</v>
+        <v>10.71534930935563</v>
       </c>
       <c r="E169" t="n">
-        <v>10.95033540100009</v>
+        <v>10.95033443698226</v>
       </c>
       <c r="F169" t="n">
         <v>1631500</v>
@@ -3812,16 +3812,16 @@
         <v>44893</v>
       </c>
       <c r="B170" t="n">
-        <v>10.97383403778076</v>
+        <v>10.97383308410645</v>
       </c>
       <c r="C170" t="n">
-        <v>11.09915964398247</v>
+        <v>11.09915867941681</v>
       </c>
       <c r="D170" t="n">
-        <v>10.68401838668942</v>
+        <v>10.68401745820135</v>
       </c>
       <c r="E170" t="n">
-        <v>10.84067539444156</v>
+        <v>10.84067445233931</v>
       </c>
       <c r="F170" t="n">
         <v>4990000</v>
@@ -3852,16 +3852,16 @@
         <v>44895</v>
       </c>
       <c r="B172" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C172" t="n">
-        <v>11.20882040874432</v>
+        <v>11.20881942197064</v>
       </c>
       <c r="D172" t="n">
-        <v>10.69185114025542</v>
+        <v>10.69185019899337</v>
       </c>
       <c r="E172" t="n">
-        <v>11.20882040874432</v>
+        <v>11.20881942197064</v>
       </c>
       <c r="F172" t="n">
         <v>4586400</v>
@@ -3972,16 +3972,16 @@
         <v>44903</v>
       </c>
       <c r="B178" t="n">
-        <v>11.26364994049072</v>
+        <v>11.26364898681641</v>
       </c>
       <c r="C178" t="n">
-        <v>11.81194985337145</v>
+        <v>11.8119488532735</v>
       </c>
       <c r="D178" t="n">
-        <v>11.15398965911476</v>
+        <v>11.15398871472519</v>
       </c>
       <c r="E178" t="n">
-        <v>11.74928704887077</v>
+        <v>11.74928605407837</v>
       </c>
       <c r="F178" t="n">
         <v>12105700</v>
@@ -3992,16 +3992,16 @@
         <v>44904</v>
       </c>
       <c r="B179" t="n">
-        <v>11.17748832702637</v>
+        <v>11.17748737335205</v>
       </c>
       <c r="C179" t="n">
-        <v>11.56913121309737</v>
+        <v>11.5691302260077</v>
       </c>
       <c r="D179" t="n">
-        <v>11.04432968600226</v>
+        <v>11.04432874368917</v>
       </c>
       <c r="E179" t="n">
-        <v>11.29498089404786</v>
+        <v>11.29497993034896</v>
       </c>
       <c r="F179" t="n">
         <v>7204400</v>
@@ -4032,16 +4032,16 @@
         <v>44908</v>
       </c>
       <c r="B181" t="n">
-        <v>11.08349418640137</v>
+        <v>11.08349323272705</v>
       </c>
       <c r="C181" t="n">
-        <v>11.30281475645706</v>
+        <v>11.3028137839114</v>
       </c>
       <c r="D181" t="n">
-        <v>10.9973330140935</v>
+        <v>10.99733206783289</v>
       </c>
       <c r="E181" t="n">
-        <v>11.00516605166683</v>
+        <v>11.00516510473222</v>
       </c>
       <c r="F181" t="n">
         <v>3594700</v>
@@ -4092,16 +4092,16 @@
         <v>44911</v>
       </c>
       <c r="B184" t="n">
-        <v>11.2479829788208</v>
+        <v>11.24798393249512</v>
       </c>
       <c r="C184" t="n">
-        <v>11.2479829788208</v>
+        <v>11.24798393249512</v>
       </c>
       <c r="D184" t="n">
-        <v>10.90333758124669</v>
+        <v>10.90333850569981</v>
       </c>
       <c r="E184" t="n">
-        <v>11.04432925375403</v>
+        <v>11.04433019016131</v>
       </c>
       <c r="F184" t="n">
         <v>3365900</v>
@@ -4112,16 +4112,16 @@
         <v>44914</v>
       </c>
       <c r="B185" t="n">
-        <v>11.37331008911133</v>
+        <v>11.37330913543701</v>
       </c>
       <c r="C185" t="n">
-        <v>11.5221340613134</v>
+        <v>11.5221330951599</v>
       </c>
       <c r="D185" t="n">
-        <v>11.18532093080405</v>
+        <v>11.18531999289299</v>
       </c>
       <c r="E185" t="n">
-        <v>11.23231840713075</v>
+        <v>11.23231746527886</v>
       </c>
       <c r="F185" t="n">
         <v>3838800</v>
@@ -4152,16 +4152,16 @@
         <v>44916</v>
       </c>
       <c r="B187" t="n">
-        <v>11.58479690551758</v>
+        <v>11.58479785919189</v>
       </c>
       <c r="C187" t="n">
-        <v>11.75711998998425</v>
+        <v>11.7571209578444</v>
       </c>
       <c r="D187" t="n">
-        <v>11.15398956785069</v>
+        <v>11.15399048606043</v>
       </c>
       <c r="E187" t="n">
-        <v>11.42813989554768</v>
+        <v>11.4281408363258</v>
       </c>
       <c r="F187" t="n">
         <v>6348400</v>
@@ -4252,16 +4252,16 @@
         <v>44923</v>
       </c>
       <c r="B192" t="n">
-        <v>11.58479690551758</v>
+        <v>11.58479785919189</v>
       </c>
       <c r="C192" t="n">
-        <v>11.69445718599628</v>
+        <v>11.69445814869797</v>
       </c>
       <c r="D192" t="n">
-        <v>11.49863573678402</v>
+        <v>11.49863668336545</v>
       </c>
       <c r="E192" t="n">
-        <v>11.5769638682692</v>
+        <v>11.57696482129869</v>
       </c>
       <c r="F192" t="n">
         <v>2005900</v>
@@ -4272,16 +4272,16 @@
         <v>44924</v>
       </c>
       <c r="B193" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="C193" t="n">
-        <v>11.73362032145083</v>
+        <v>11.73362129131107</v>
       </c>
       <c r="D193" t="n">
-        <v>11.4751360805163</v>
+        <v>11.47513702901113</v>
       </c>
       <c r="E193" t="n">
-        <v>11.62396079317528</v>
+        <v>11.62396175397144</v>
       </c>
       <c r="F193" t="n">
         <v>2424800</v>
@@ -4292,16 +4292,16 @@
         <v>44928</v>
       </c>
       <c r="B194" t="n">
-        <v>11.3419771194458</v>
+        <v>11.34197807312012</v>
       </c>
       <c r="C194" t="n">
-        <v>11.46730346491438</v>
+        <v>11.46730442912659</v>
       </c>
       <c r="D194" t="n">
-        <v>11.17748783170473</v>
+        <v>11.1774887715482</v>
       </c>
       <c r="E194" t="n">
-        <v>11.38897459237146</v>
+        <v>11.38897554999749</v>
       </c>
       <c r="F194" t="n">
         <v>1018800</v>
@@ -4312,16 +4312,16 @@
         <v>44929</v>
       </c>
       <c r="B195" t="n">
-        <v>11.13832378387451</v>
+        <v>11.13832473754883</v>
       </c>
       <c r="C195" t="n">
-        <v>11.32631218813412</v>
+        <v>11.32631315790418</v>
       </c>
       <c r="D195" t="n">
-        <v>11.05999490859992</v>
+        <v>11.05999585556764</v>
       </c>
       <c r="E195" t="n">
-        <v>11.30281382435154</v>
+        <v>11.30281479210966</v>
       </c>
       <c r="F195" t="n">
         <v>1562800</v>
@@ -4332,16 +4332,16 @@
         <v>44930</v>
       </c>
       <c r="B196" t="n">
-        <v>11.35764312744141</v>
+        <v>11.35764408111572</v>
       </c>
       <c r="C196" t="n">
-        <v>11.35764312744141</v>
+        <v>11.35764408111572</v>
       </c>
       <c r="D196" t="n">
-        <v>10.96600026097791</v>
+        <v>10.9660011817669</v>
       </c>
       <c r="E196" t="n">
-        <v>11.1696547308188</v>
+        <v>11.16965566870818</v>
       </c>
       <c r="F196" t="n">
         <v>2937400</v>
@@ -4352,16 +4352,16 @@
         <v>44931</v>
       </c>
       <c r="B197" t="n">
-        <v>11.41247272491455</v>
+        <v>11.41247367858887</v>
       </c>
       <c r="C197" t="n">
-        <v>11.41247272491455</v>
+        <v>11.41247367858887</v>
       </c>
       <c r="D197" t="n">
-        <v>11.08349266207561</v>
+        <v>11.08349358825896</v>
       </c>
       <c r="E197" t="n">
-        <v>11.31064549146445</v>
+        <v>11.31064643662965</v>
       </c>
       <c r="F197" t="n">
         <v>4358300</v>
@@ -4372,16 +4372,16 @@
         <v>44932</v>
       </c>
       <c r="B198" t="n">
-        <v>11.42030715942383</v>
+        <v>11.42030620574951</v>
       </c>
       <c r="C198" t="n">
-        <v>11.53779973324935</v>
+        <v>11.53779876976359</v>
       </c>
       <c r="D198" t="n">
-        <v>11.31847991350858</v>
+        <v>11.31847896833754</v>
       </c>
       <c r="E198" t="n">
-        <v>11.41247412196891</v>
+        <v>11.4124731689487</v>
       </c>
       <c r="F198" t="n">
         <v>2864500</v>
@@ -4432,16 +4432,16 @@
         <v>44937</v>
       </c>
       <c r="B201" t="n">
-        <v>11.49863624572754</v>
+        <v>11.49863529205322</v>
       </c>
       <c r="C201" t="n">
-        <v>11.61612882165544</v>
+        <v>11.61612785823652</v>
       </c>
       <c r="D201" t="n">
-        <v>11.0678288889926</v>
+        <v>11.06782797104859</v>
       </c>
       <c r="E201" t="n">
-        <v>11.09132725477826</v>
+        <v>11.09132633488535</v>
       </c>
       <c r="F201" t="n">
         <v>4499200</v>
@@ -4472,16 +4472,16 @@
         <v>44939</v>
       </c>
       <c r="B203" t="n">
-        <v>11.58479690551758</v>
+        <v>11.58479785919189</v>
       </c>
       <c r="C203" t="n">
-        <v>11.78845139197822</v>
+        <v>11.78845236241762</v>
       </c>
       <c r="D203" t="n">
-        <v>11.44380522304489</v>
+        <v>11.4438061651126</v>
       </c>
       <c r="E203" t="n">
-        <v>11.74928695273586</v>
+        <v>11.7492879199512</v>
       </c>
       <c r="F203" t="n">
         <v>2269100</v>
@@ -4512,16 +4512,16 @@
         <v>44943</v>
       </c>
       <c r="B205" t="n">
-        <v>11.74928665161133</v>
+        <v>11.74928569793701</v>
       </c>
       <c r="C205" t="n">
-        <v>11.93727505875722</v>
+        <v>11.93727408982413</v>
       </c>
       <c r="D205" t="n">
-        <v>11.60829497275214</v>
+        <v>11.60829403052194</v>
       </c>
       <c r="E205" t="n">
-        <v>11.81194945399329</v>
+        <v>11.81194849523272</v>
       </c>
       <c r="F205" t="n">
         <v>2676600</v>
@@ -4532,16 +4532,16 @@
         <v>44944</v>
       </c>
       <c r="B206" t="n">
-        <v>11.41247272491455</v>
+        <v>11.41247367858887</v>
       </c>
       <c r="C206" t="n">
-        <v>11.89027749318036</v>
+        <v>11.89027848678206</v>
       </c>
       <c r="D206" t="n">
-        <v>11.41247272491455</v>
+        <v>11.41247367858887</v>
       </c>
       <c r="E206" t="n">
-        <v>11.87461142018828</v>
+        <v>11.87461241248085</v>
       </c>
       <c r="F206" t="n">
         <v>3532000</v>
@@ -4552,16 +4552,16 @@
         <v>44945</v>
       </c>
       <c r="B207" t="n">
-        <v>11.66312599182129</v>
+        <v>11.66312503814697</v>
       </c>
       <c r="C207" t="n">
-        <v>11.68662435698559</v>
+        <v>11.68662340138985</v>
       </c>
       <c r="D207" t="n">
-        <v>11.27931537680668</v>
+        <v>11.27931445451592</v>
       </c>
       <c r="E207" t="n">
-        <v>11.3419781819112</v>
+        <v>11.3419772544966</v>
       </c>
       <c r="F207" t="n">
         <v>1847800</v>
@@ -4572,16 +4572,16 @@
         <v>44946</v>
       </c>
       <c r="B208" t="n">
-        <v>11.58479690551758</v>
+        <v>11.58479785919189</v>
       </c>
       <c r="C208" t="n">
-        <v>11.6866241487479</v>
+        <v>11.68662511080476</v>
       </c>
       <c r="D208" t="n">
-        <v>11.48296966228726</v>
+        <v>11.48297060757903</v>
       </c>
       <c r="E208" t="n">
-        <v>11.65529274675392</v>
+        <v>11.65529370623154</v>
       </c>
       <c r="F208" t="n">
         <v>2012100</v>
@@ -4592,16 +4592,16 @@
         <v>44949</v>
       </c>
       <c r="B209" t="n">
-        <v>11.52213287353516</v>
+        <v>11.52213382720947</v>
       </c>
       <c r="C209" t="n">
-        <v>11.64745846815425</v>
+        <v>11.64745943220163</v>
       </c>
       <c r="D209" t="n">
-        <v>11.34980980743417</v>
+        <v>11.34981074684549</v>
       </c>
       <c r="E209" t="n">
-        <v>11.59262870725826</v>
+        <v>11.59262966676744</v>
       </c>
       <c r="F209" t="n">
         <v>1770800</v>
@@ -4632,16 +4632,16 @@
         <v>44951</v>
       </c>
       <c r="B211" t="n">
-        <v>11.89027881622314</v>
+        <v>11.89027786254883</v>
       </c>
       <c r="C211" t="n">
-        <v>12.07043419368129</v>
+        <v>12.07043322555739</v>
       </c>
       <c r="D211" t="n">
-        <v>11.62396152172019</v>
+        <v>11.62396058940618</v>
       </c>
       <c r="E211" t="n">
-        <v>11.67879128929448</v>
+        <v>11.67879035258278</v>
       </c>
       <c r="F211" t="n">
         <v>10764800</v>
@@ -4652,16 +4652,16 @@
         <v>44952</v>
       </c>
       <c r="B212" t="n">
-        <v>11.96860504150391</v>
+        <v>11.96860599517822</v>
       </c>
       <c r="C212" t="n">
-        <v>12.09393063141503</v>
+        <v>12.09393159507546</v>
       </c>
       <c r="D212" t="n">
-        <v>11.79628272887583</v>
+        <v>11.79628366881928</v>
       </c>
       <c r="E212" t="n">
-        <v>11.91377528266765</v>
+        <v>11.91377623197306</v>
       </c>
       <c r="F212" t="n">
         <v>8143300</v>
@@ -4712,16 +4712,16 @@
         <v>44957</v>
       </c>
       <c r="B215" t="n">
-        <v>12.07043266296387</v>
+        <v>12.07043361663818</v>
       </c>
       <c r="C215" t="n">
-        <v>12.14092849633346</v>
+        <v>12.14092945557759</v>
       </c>
       <c r="D215" t="n">
-        <v>11.8276145113569</v>
+        <v>11.82761544584636</v>
       </c>
       <c r="E215" t="n">
-        <v>11.84327983710599</v>
+        <v>11.84328077283316</v>
       </c>
       <c r="F215" t="n">
         <v>5446800</v>
@@ -4852,16 +4852,16 @@
         <v>44966</v>
       </c>
       <c r="B222" t="n">
-        <v>11.66312599182129</v>
+        <v>11.66312503814697</v>
       </c>
       <c r="C222" t="n">
-        <v>11.78845160203032</v>
+        <v>11.78845063810834</v>
       </c>
       <c r="D222" t="n">
-        <v>11.55346570938861</v>
+        <v>11.55346476468103</v>
       </c>
       <c r="E222" t="n">
-        <v>11.7101227221499</v>
+        <v>11.71012176463273</v>
       </c>
       <c r="F222" t="n">
         <v>2260100</v>
@@ -4872,16 +4872,16 @@
         <v>44967</v>
       </c>
       <c r="B223" t="n">
-        <v>11.72578907012939</v>
+        <v>11.72578811645508</v>
       </c>
       <c r="C223" t="n">
-        <v>11.88244608654069</v>
+        <v>11.88244512012525</v>
       </c>
       <c r="D223" t="n">
-        <v>11.62396182271216</v>
+        <v>11.62396087731959</v>
       </c>
       <c r="E223" t="n">
-        <v>11.62396182271216</v>
+        <v>11.62396087731959</v>
       </c>
       <c r="F223" t="n">
         <v>6075300</v>
@@ -4912,16 +4912,16 @@
         <v>44971</v>
       </c>
       <c r="B225" t="n">
-        <v>11.71795463562012</v>
+        <v>11.71795558929443</v>
       </c>
       <c r="C225" t="n">
-        <v>11.88244466999244</v>
+        <v>11.8824456370539</v>
       </c>
       <c r="D225" t="n">
-        <v>11.51430016506401</v>
+        <v>11.51430110216375</v>
       </c>
       <c r="E225" t="n">
-        <v>11.78061743471438</v>
+        <v>11.78061839348856</v>
       </c>
       <c r="F225" t="n">
         <v>2141000</v>
@@ -4932,16 +4932,16 @@
         <v>44972</v>
       </c>
       <c r="B226" t="n">
-        <v>11.75711917877197</v>
+        <v>11.75712013244629</v>
       </c>
       <c r="C226" t="n">
-        <v>11.92944150434928</v>
+        <v>11.92944247200145</v>
       </c>
       <c r="D226" t="n">
-        <v>11.63179357944321</v>
+        <v>11.63179452295179</v>
       </c>
       <c r="E226" t="n">
-        <v>11.6631249792754</v>
+        <v>11.66312592532541</v>
       </c>
       <c r="F226" t="n">
         <v>3961900</v>
@@ -4952,16 +4952,16 @@
         <v>44973</v>
       </c>
       <c r="B227" t="n">
-        <v>11.89027881622314</v>
+        <v>11.89027786254883</v>
       </c>
       <c r="C227" t="n">
-        <v>11.9764399862684</v>
+        <v>11.97643902568342</v>
       </c>
       <c r="D227" t="n">
-        <v>11.57696404451397</v>
+        <v>11.57696311596945</v>
       </c>
       <c r="E227" t="n">
-        <v>11.7649532063393</v>
+        <v>11.76495226271687</v>
       </c>
       <c r="F227" t="n">
         <v>4461000</v>
@@ -4972,16 +4972,16 @@
         <v>44974</v>
       </c>
       <c r="B228" t="n">
-        <v>11.72578907012939</v>
+        <v>11.72578811645508</v>
       </c>
       <c r="C228" t="n">
-        <v>12.13309731279878</v>
+        <v>12.13309632599753</v>
       </c>
       <c r="D228" t="n">
-        <v>11.55346597857718</v>
+        <v>11.55346503891813</v>
       </c>
       <c r="E228" t="n">
-        <v>11.94510889310522</v>
+        <v>11.94510792159332</v>
       </c>
       <c r="F228" t="n">
         <v>9428300</v>
@@ -4992,16 +4992,16 @@
         <v>44979</v>
       </c>
       <c r="B229" t="n">
-        <v>11.71795463562012</v>
+        <v>11.71795558929443</v>
       </c>
       <c r="C229" t="n">
-        <v>11.95294050572336</v>
+        <v>11.95294147852217</v>
       </c>
       <c r="D229" t="n">
-        <v>11.66312487316251</v>
+        <v>11.66312582237446</v>
       </c>
       <c r="E229" t="n">
-        <v>11.89810999626626</v>
+        <v>11.89811096460265</v>
       </c>
       <c r="F229" t="n">
         <v>6185800</v>
@@ -5012,16 +5012,16 @@
         <v>44980</v>
       </c>
       <c r="B230" t="n">
-        <v>11.67879009246826</v>
+        <v>11.67879104614258</v>
       </c>
       <c r="C230" t="n">
-        <v>11.8511131618989</v>
+        <v>11.85111412964489</v>
       </c>
       <c r="D230" t="n">
-        <v>11.61612729394793</v>
+        <v>11.61612824250529</v>
       </c>
       <c r="E230" t="n">
-        <v>11.79628339994349</v>
+        <v>11.79628436321215</v>
       </c>
       <c r="F230" t="n">
         <v>3218000</v>
@@ -5032,16 +5032,16 @@
         <v>44981</v>
       </c>
       <c r="B231" t="n">
-        <v>11.67879009246826</v>
+        <v>11.67879104614258</v>
       </c>
       <c r="C231" t="n">
-        <v>11.89810988728941</v>
+        <v>11.89811085887308</v>
       </c>
       <c r="D231" t="n">
-        <v>11.51430005960253</v>
+        <v>11.51430099984482</v>
       </c>
       <c r="E231" t="n">
-        <v>11.72578756485825</v>
+        <v>11.72578852237032</v>
       </c>
       <c r="F231" t="n">
         <v>4705500</v>
@@ -5052,16 +5052,16 @@
         <v>44984</v>
       </c>
       <c r="B232" t="n">
-        <v>11.64745903015137</v>
+        <v>11.64745998382568</v>
       </c>
       <c r="C232" t="n">
-        <v>11.85894654152509</v>
+        <v>11.85894751251565</v>
       </c>
       <c r="D232" t="n">
-        <v>11.56129786644328</v>
+        <v>11.56129881306286</v>
       </c>
       <c r="E232" t="n">
-        <v>11.73362019385946</v>
+        <v>11.7336211545885</v>
       </c>
       <c r="F232" t="n">
         <v>3412900</v>
@@ -5112,16 +5112,16 @@
         <v>44987</v>
       </c>
       <c r="B235" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="C235" t="n">
-        <v>11.67879055731306</v>
+        <v>11.67879152264125</v>
       </c>
       <c r="D235" t="n">
-        <v>11.45947075376244</v>
+        <v>11.45947170096243</v>
       </c>
       <c r="E235" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="F235" t="n">
         <v>2250800</v>
@@ -5132,16 +5132,16 @@
         <v>44988</v>
       </c>
       <c r="B236" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="C236" t="n">
-        <v>11.64745915680582</v>
+        <v>11.64746011954428</v>
       </c>
       <c r="D236" t="n">
-        <v>11.45947075376244</v>
+        <v>11.45947170096243</v>
       </c>
       <c r="E236" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="F236" t="n">
         <v>1727100</v>
@@ -5252,16 +5252,16 @@
         <v>44998</v>
       </c>
       <c r="B242" t="n">
-        <v>11.66312599182129</v>
+        <v>11.66312503814697</v>
       </c>
       <c r="C242" t="n">
-        <v>11.74145412470215</v>
+        <v>11.74145316462308</v>
       </c>
       <c r="D242" t="n">
-        <v>11.45947150173183</v>
+        <v>11.45947056471</v>
       </c>
       <c r="E242" t="n">
-        <v>11.52213430683635</v>
+        <v>11.52213336469069</v>
       </c>
       <c r="F242" t="n">
         <v>3223500</v>
@@ -5272,16 +5272,16 @@
         <v>44999</v>
       </c>
       <c r="B243" t="n">
-        <v>11.75711917877197</v>
+        <v>11.75712013244629</v>
       </c>
       <c r="C243" t="n">
-        <v>11.82761501514428</v>
+        <v>11.82761597453684</v>
       </c>
       <c r="D243" t="n">
-        <v>11.63962586915163</v>
+        <v>11.63962681329553</v>
       </c>
       <c r="E243" t="n">
-        <v>11.69445637910759</v>
+        <v>11.69445732769904</v>
       </c>
       <c r="F243" t="n">
         <v>2520000</v>
@@ -5292,16 +5292,16 @@
         <v>45000</v>
       </c>
       <c r="B244" t="n">
-        <v>11.74928665161133</v>
+        <v>11.74928569793701</v>
       </c>
       <c r="C244" t="n">
-        <v>11.89027833047051</v>
+        <v>11.89027736535209</v>
       </c>
       <c r="D244" t="n">
-        <v>11.61612800979977</v>
+        <v>11.61612706693377</v>
       </c>
       <c r="E244" t="n">
-        <v>11.71795525042035</v>
+        <v>11.71795429928916</v>
       </c>
       <c r="F244" t="n">
         <v>4602600</v>
@@ -5312,16 +5312,16 @@
         <v>45001</v>
       </c>
       <c r="B245" t="n">
-        <v>11.67095756530762</v>
+        <v>11.67095851898193</v>
       </c>
       <c r="C245" t="n">
-        <v>11.81194924163198</v>
+        <v>11.81195020682722</v>
       </c>
       <c r="D245" t="n">
-        <v>11.63962616467993</v>
+        <v>11.63962711579405</v>
       </c>
       <c r="E245" t="n">
-        <v>11.81194924163198</v>
+        <v>11.81195020682722</v>
       </c>
       <c r="F245" t="n">
         <v>5495800</v>
@@ -5372,16 +5372,16 @@
         <v>45006</v>
       </c>
       <c r="B248" t="n">
-        <v>11.3419771194458</v>
+        <v>11.34197807312012</v>
       </c>
       <c r="C248" t="n">
-        <v>11.42030599198873</v>
+        <v>11.42030695224922</v>
       </c>
       <c r="D248" t="n">
-        <v>11.27931432021125</v>
+        <v>11.27931526861666</v>
       </c>
       <c r="E248" t="n">
-        <v>11.36547622940837</v>
+        <v>11.36547718505858</v>
       </c>
       <c r="F248" t="n">
         <v>2410300</v>
@@ -5412,16 +5412,16 @@
         <v>45008</v>
       </c>
       <c r="B250" t="n">
-        <v>11.18532085418701</v>
+        <v>11.18532180786133</v>
       </c>
       <c r="C250" t="n">
-        <v>11.47513650638449</v>
+        <v>11.47513748476884</v>
       </c>
       <c r="D250" t="n">
-        <v>11.05999524750697</v>
+        <v>11.05999619049587</v>
       </c>
       <c r="E250" t="n">
-        <v>11.39680837570923</v>
+        <v>11.39680934741524</v>
       </c>
       <c r="F250" t="n">
         <v>4422500</v>
@@ -5472,16 +5472,16 @@
         <v>45013</v>
       </c>
       <c r="B253" t="n">
-        <v>11.42030715942383</v>
+        <v>11.42030620574951</v>
       </c>
       <c r="C253" t="n">
-        <v>11.45163856224394</v>
+        <v>11.45163760595323</v>
       </c>
       <c r="D253" t="n">
-        <v>11.25581710786836</v>
+        <v>11.25581616793009</v>
       </c>
       <c r="E253" t="n">
-        <v>11.31064687605366</v>
+        <v>11.31064593153673</v>
       </c>
       <c r="F253" t="n">
         <v>3302900</v>
@@ -5552,16 +5552,16 @@
         <v>45019</v>
       </c>
       <c r="B257" t="n">
-        <v>11.3419771194458</v>
+        <v>11.34197807312012</v>
       </c>
       <c r="C257" t="n">
-        <v>11.58479602672929</v>
+        <v>11.58479700082069</v>
       </c>
       <c r="D257" t="n">
-        <v>11.24798292059398</v>
+        <v>11.24798386636493</v>
       </c>
       <c r="E257" t="n">
-        <v>11.58479602672929</v>
+        <v>11.58479700082069</v>
       </c>
       <c r="F257" t="n">
         <v>6471200</v>
@@ -5572,16 +5572,16 @@
         <v>45020</v>
       </c>
       <c r="B258" t="n">
-        <v>11.4359712600708</v>
+        <v>11.43597221374512</v>
       </c>
       <c r="C258" t="n">
-        <v>11.49863405489315</v>
+        <v>11.49863501379308</v>
       </c>
       <c r="D258" t="n">
-        <v>11.24798212860431</v>
+        <v>11.24798306660174</v>
       </c>
       <c r="E258" t="n">
-        <v>11.35764239304314</v>
+        <v>11.35764334018542</v>
       </c>
       <c r="F258" t="n">
         <v>5230100</v>
@@ -5612,16 +5612,16 @@
         <v>45022</v>
       </c>
       <c r="B260" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="C260" t="n">
-        <v>11.6631252305592</v>
+        <v>11.66312619459255</v>
       </c>
       <c r="D260" t="n">
-        <v>11.4751360805163</v>
+        <v>11.47513702901113</v>
       </c>
       <c r="E260" t="n">
-        <v>11.49080215426967</v>
+        <v>11.4908031040594</v>
       </c>
       <c r="F260" t="n">
         <v>4653400</v>
@@ -5632,16 +5632,16 @@
         <v>45026</v>
       </c>
       <c r="B261" t="n">
-        <v>11.71795463562012</v>
+        <v>11.71795558929443</v>
       </c>
       <c r="C261" t="n">
-        <v>11.85111327044531</v>
+        <v>11.85111423495683</v>
       </c>
       <c r="D261" t="n">
-        <v>11.4594704026064</v>
+        <v>11.45947133524378</v>
       </c>
       <c r="E261" t="n">
-        <v>11.53779852797449</v>
+        <v>11.53779946698666</v>
       </c>
       <c r="F261" t="n">
         <v>3430500</v>
@@ -5652,16 +5652,16 @@
         <v>45027</v>
       </c>
       <c r="B262" t="n">
-        <v>11.76495361328125</v>
+        <v>11.76495265960693</v>
       </c>
       <c r="C262" t="n">
-        <v>12.0156048417188</v>
+        <v>12.01560386772655</v>
       </c>
       <c r="D262" t="n">
-        <v>11.71012309681085</v>
+        <v>11.71012214758113</v>
       </c>
       <c r="E262" t="n">
-        <v>11.82761642039064</v>
+        <v>11.82761546163684</v>
       </c>
       <c r="F262" t="n">
         <v>2622300</v>
@@ -5672,16 +5672,16 @@
         <v>45028</v>
       </c>
       <c r="B263" t="n">
-        <v>11.80411529541016</v>
+        <v>11.80411624908447</v>
       </c>
       <c r="C263" t="n">
-        <v>12.01560279360503</v>
+        <v>12.01560376436578</v>
       </c>
       <c r="D263" t="n">
-        <v>11.74928553528532</v>
+        <v>11.74928648452985</v>
       </c>
       <c r="E263" t="n">
-        <v>11.82761440432034</v>
+        <v>11.82761535989319</v>
       </c>
       <c r="F263" t="n">
         <v>2987000</v>
@@ -5752,16 +5752,16 @@
         <v>45034</v>
       </c>
       <c r="B267" t="n">
-        <v>11.96860504150391</v>
+        <v>11.96860599517822</v>
       </c>
       <c r="C267" t="n">
-        <v>12.1644264624899</v>
+        <v>12.16442743176752</v>
       </c>
       <c r="D267" t="n">
-        <v>11.94510668014543</v>
+        <v>11.94510763194737</v>
       </c>
       <c r="E267" t="n">
-        <v>12.14092810113142</v>
+        <v>12.14092906853667</v>
       </c>
       <c r="F267" t="n">
         <v>3259600</v>
@@ -5792,16 +5792,16 @@
         <v>45036</v>
       </c>
       <c r="B269" t="n">
-        <v>12.09393215179443</v>
+        <v>12.09393119812012</v>
       </c>
       <c r="C269" t="n">
-        <v>12.14092962741908</v>
+        <v>12.14092867003875</v>
       </c>
       <c r="D269" t="n">
-        <v>12.00777098464871</v>
+        <v>12.00777003776868</v>
       </c>
       <c r="E269" t="n">
-        <v>12.06260075037785</v>
+        <v>12.06259979917419</v>
       </c>
       <c r="F269" t="n">
         <v>4813100</v>
@@ -5832,16 +5832,16 @@
         <v>45041</v>
       </c>
       <c r="B271" t="n">
-        <v>12.06260013580322</v>
+        <v>12.06260108947754</v>
       </c>
       <c r="C271" t="n">
-        <v>12.14092900885369</v>
+        <v>12.14092996872072</v>
       </c>
       <c r="D271" t="n">
-        <v>11.96860593634236</v>
+        <v>11.96860688258545</v>
       </c>
       <c r="E271" t="n">
-        <v>12.11743064573835</v>
+        <v>12.11743160374759</v>
       </c>
       <c r="F271" t="n">
         <v>2381100</v>
@@ -5932,16 +5932,16 @@
         <v>45049</v>
       </c>
       <c r="B276" t="n">
-        <v>12.28975391387939</v>
+        <v>12.28975296020508</v>
       </c>
       <c r="C276" t="n">
-        <v>12.48557536452565</v>
+        <v>12.48557439565576</v>
       </c>
       <c r="D276" t="n">
-        <v>12.2819216235732</v>
+        <v>12.28192067050667</v>
       </c>
       <c r="E276" t="n">
-        <v>12.48557536452565</v>
+        <v>12.48557439565576</v>
       </c>
       <c r="F276" t="n">
         <v>6661600</v>
@@ -6032,16 +6032,16 @@
         <v>45056</v>
       </c>
       <c r="B281" t="n">
-        <v>11.86925315856934</v>
+        <v>11.86925220489502</v>
       </c>
       <c r="C281" t="n">
-        <v>12.05105794406462</v>
+        <v>12.0510569757826</v>
       </c>
       <c r="D281" t="n">
-        <v>11.69610594039075</v>
+        <v>11.69610500062852</v>
       </c>
       <c r="E281" t="n">
-        <v>12.0164285004289</v>
+        <v>12.0164275349293</v>
       </c>
       <c r="F281" t="n">
         <v>5308900</v>
@@ -6072,16 +6072,16 @@
         <v>45058</v>
       </c>
       <c r="B283" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C283" t="n">
-        <v>12.25017729158851</v>
+        <v>12.25017632493442</v>
       </c>
       <c r="D283" t="n">
-        <v>11.9991136136361</v>
+        <v>11.99911266679329</v>
       </c>
       <c r="E283" t="n">
-        <v>12.0424006254826</v>
+        <v>12.04239967522403</v>
       </c>
       <c r="F283" t="n">
         <v>3087800</v>
@@ -6112,16 +6112,16 @@
         <v>45062</v>
       </c>
       <c r="B285" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="C285" t="n">
-        <v>12.30212128603885</v>
+        <v>12.30212031805942</v>
       </c>
       <c r="D285" t="n">
-        <v>12.08568706272756</v>
+        <v>12.08568611177803</v>
       </c>
       <c r="E285" t="n">
-        <v>12.18091782375736</v>
+        <v>12.18091686531469</v>
       </c>
       <c r="F285" t="n">
         <v>2907500</v>
@@ -6232,16 +6232,16 @@
         <v>45070</v>
       </c>
       <c r="B291" t="n">
-        <v>12.25017738342285</v>
+        <v>12.25017642974854</v>
       </c>
       <c r="C291" t="n">
-        <v>12.30212196315428</v>
+        <v>12.30212100543608</v>
       </c>
       <c r="D291" t="n">
-        <v>12.18091849420168</v>
+        <v>12.18091754591915</v>
       </c>
       <c r="E291" t="n">
-        <v>12.26749251854369</v>
+        <v>12.26749156352139</v>
       </c>
       <c r="F291" t="n">
         <v>1846000</v>
@@ -6312,16 +6312,16 @@
         <v>45076</v>
       </c>
       <c r="B295" t="n">
-        <v>12.26749229431152</v>
+        <v>12.26749134063721</v>
       </c>
       <c r="C295" t="n">
-        <v>12.38003819364653</v>
+        <v>12.3800372312229</v>
       </c>
       <c r="D295" t="n">
-        <v>12.25017715950718</v>
+        <v>12.25017620717894</v>
       </c>
       <c r="E295" t="n">
-        <v>12.37138062624436</v>
+        <v>12.37137966449377</v>
       </c>
       <c r="F295" t="n">
         <v>1829100</v>
@@ -6352,16 +6352,16 @@
         <v>45078</v>
       </c>
       <c r="B297" t="n">
-        <v>12.2415189743042</v>
+        <v>12.24151992797852</v>
       </c>
       <c r="C297" t="n">
-        <v>12.30212028771158</v>
+        <v>12.30212124610704</v>
       </c>
       <c r="D297" t="n">
-        <v>12.16360252813415</v>
+        <v>12.1636034757384</v>
       </c>
       <c r="E297" t="n">
-        <v>12.26749084781722</v>
+        <v>12.26749180351488</v>
       </c>
       <c r="F297" t="n">
         <v>2308800</v>
@@ -6392,16 +6392,16 @@
         <v>45082</v>
       </c>
       <c r="B299" t="n">
-        <v>12.06837177276611</v>
+        <v>12.0683708190918</v>
       </c>
       <c r="C299" t="n">
-        <v>12.1982328004551</v>
+        <v>12.19823183651883</v>
       </c>
       <c r="D299" t="n">
-        <v>11.97314101296568</v>
+        <v>11.97314006681674</v>
       </c>
       <c r="E299" t="n">
-        <v>12.17226092516972</v>
+        <v>12.17225996328581</v>
       </c>
       <c r="F299" t="n">
         <v>3442900</v>
@@ -6412,16 +6412,16 @@
         <v>45083</v>
       </c>
       <c r="B300" t="n">
-        <v>12.32809257507324</v>
+        <v>12.32809352874756</v>
       </c>
       <c r="C300" t="n">
-        <v>12.41466659053087</v>
+        <v>12.41466755090237</v>
       </c>
       <c r="D300" t="n">
-        <v>12.07702892100332</v>
+        <v>12.0770298552559</v>
       </c>
       <c r="E300" t="n">
-        <v>12.08568648767528</v>
+        <v>12.08568742259759</v>
       </c>
       <c r="F300" t="n">
         <v>7376500</v>
@@ -6452,16 +6452,16 @@
         <v>45086</v>
       </c>
       <c r="B302" t="n">
-        <v>12.37138080596924</v>
+        <v>12.37137985229492</v>
       </c>
       <c r="C302" t="n">
-        <v>12.42332538550581</v>
+        <v>12.42332442782724</v>
       </c>
       <c r="D302" t="n">
-        <v>12.26749247252717</v>
+        <v>12.26749152686131</v>
       </c>
       <c r="E302" t="n">
-        <v>12.29346434947992</v>
+        <v>12.29346340181196</v>
       </c>
       <c r="F302" t="n">
         <v>4999400</v>
@@ -6492,16 +6492,16 @@
         <v>45090</v>
       </c>
       <c r="B304" t="n">
-        <v>12.31077861785889</v>
+        <v>12.3107795715332</v>
       </c>
       <c r="C304" t="n">
-        <v>12.50124013627868</v>
+        <v>12.5012411047074</v>
       </c>
       <c r="D304" t="n">
-        <v>12.29346348402198</v>
+        <v>12.29346443635495</v>
       </c>
       <c r="E304" t="n">
-        <v>12.46661069423589</v>
+        <v>12.46661165998199</v>
       </c>
       <c r="F304" t="n">
         <v>1312000</v>
@@ -6632,16 +6632,16 @@
         <v>45099</v>
       </c>
       <c r="B311" t="n">
-        <v>12.78693389892578</v>
+        <v>12.7869348526001</v>
       </c>
       <c r="C311" t="n">
-        <v>12.84753521530501</v>
+        <v>12.84753617349909</v>
       </c>
       <c r="D311" t="n">
-        <v>12.64841530692453</v>
+        <v>12.64841625026786</v>
       </c>
       <c r="E311" t="n">
-        <v>12.78693389892578</v>
+        <v>12.7869348526001</v>
       </c>
       <c r="F311" t="n">
         <v>2039700</v>
@@ -6652,16 +6652,16 @@
         <v>45100</v>
       </c>
       <c r="B312" t="n">
-        <v>12.9427661895752</v>
+        <v>12.94276714324951</v>
       </c>
       <c r="C312" t="n">
-        <v>13.07262721694078</v>
+        <v>13.07262818018377</v>
       </c>
       <c r="D312" t="n">
-        <v>12.7609614117682</v>
+        <v>12.76096235204642</v>
       </c>
       <c r="E312" t="n">
-        <v>12.81290598784064</v>
+        <v>12.81290693194634</v>
       </c>
       <c r="F312" t="n">
         <v>2959500</v>
@@ -6672,16 +6672,16 @@
         <v>45103</v>
       </c>
       <c r="B313" t="n">
-        <v>12.71767425537109</v>
+        <v>12.71767520904541</v>
       </c>
       <c r="C313" t="n">
-        <v>13.01202492323384</v>
+        <v>13.01202589898095</v>
       </c>
       <c r="D313" t="n">
-        <v>12.66573050553121</v>
+        <v>12.66573145531036</v>
       </c>
       <c r="E313" t="n">
-        <v>12.94276603969331</v>
+        <v>12.94276701024684</v>
       </c>
       <c r="F313" t="n">
         <v>2677600</v>
@@ -6792,16 +6792,16 @@
         <v>45111</v>
       </c>
       <c r="B319" t="n">
-        <v>12.34540748596191</v>
+        <v>12.34540843963623</v>
       </c>
       <c r="C319" t="n">
-        <v>12.40600880031166</v>
+        <v>12.40600975866739</v>
       </c>
       <c r="D319" t="n">
-        <v>12.23286159814739</v>
+        <v>12.23286254312761</v>
       </c>
       <c r="E319" t="n">
-        <v>12.38869449291073</v>
+        <v>12.38869544992894</v>
       </c>
       <c r="F319" t="n">
         <v>2230100</v>
@@ -6832,16 +6832,16 @@
         <v>45113</v>
       </c>
       <c r="B321" t="n">
-        <v>12.32809257507324</v>
+        <v>12.32809352874756</v>
       </c>
       <c r="C321" t="n">
-        <v>12.48392547264458</v>
+        <v>12.48392643837378</v>
       </c>
       <c r="D321" t="n">
-        <v>12.25017612628758</v>
+        <v>12.25017707393445</v>
       </c>
       <c r="E321" t="n">
-        <v>12.4319808982438</v>
+        <v>12.43198185995469</v>
       </c>
       <c r="F321" t="n">
         <v>2081000</v>
@@ -6852,16 +6852,16 @@
         <v>45114</v>
       </c>
       <c r="B322" t="n">
-        <v>12.34540748596191</v>
+        <v>12.34540843963623</v>
       </c>
       <c r="C322" t="n">
-        <v>12.48392524769333</v>
+        <v>12.48392621206805</v>
       </c>
       <c r="D322" t="n">
-        <v>12.25883347206429</v>
+        <v>12.25883441905082</v>
       </c>
       <c r="E322" t="n">
-        <v>12.42332393334358</v>
+        <v>12.42332489303689</v>
       </c>
       <c r="F322" t="n">
         <v>2149700</v>
@@ -6892,16 +6892,16 @@
         <v>45118</v>
       </c>
       <c r="B324" t="n">
-        <v>12.34540748596191</v>
+        <v>12.34540843963623</v>
       </c>
       <c r="C324" t="n">
-        <v>12.3973512337957</v>
+        <v>12.39735219148264</v>
       </c>
       <c r="D324" t="n">
-        <v>12.23286159814739</v>
+        <v>12.23286254312761</v>
       </c>
       <c r="E324" t="n">
-        <v>12.38869449291073</v>
+        <v>12.38869544992894</v>
       </c>
       <c r="F324" t="n">
         <v>1919200</v>
@@ -7072,16 +7072,16 @@
         <v>45131</v>
       </c>
       <c r="B333" t="n">
-        <v>12.34540748596191</v>
+        <v>12.34540843963623</v>
       </c>
       <c r="C333" t="n">
-        <v>12.42332393334358</v>
+        <v>12.42332489303689</v>
       </c>
       <c r="D333" t="n">
-        <v>12.31943478641403</v>
+        <v>12.31943573808198</v>
       </c>
       <c r="E333" t="n">
-        <v>12.42332393334358</v>
+        <v>12.42332489303689</v>
       </c>
       <c r="F333" t="n">
         <v>1347200</v>
@@ -7132,16 +7132,16 @@
         <v>45134</v>
       </c>
       <c r="B336" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C336" t="n">
-        <v>12.22420541473304</v>
+        <v>12.22420445012837</v>
       </c>
       <c r="D336" t="n">
-        <v>12.03374305798708</v>
+        <v>12.03374210841168</v>
       </c>
       <c r="E336" t="n">
-        <v>12.18091840288654</v>
+        <v>12.18091744169762</v>
       </c>
       <c r="F336" t="n">
         <v>2852900</v>
@@ -7152,16 +7152,16 @@
         <v>45135</v>
       </c>
       <c r="B337" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="C337" t="n">
-        <v>12.22420483354582</v>
+        <v>12.22420387169716</v>
       </c>
       <c r="D337" t="n">
-        <v>12.0597151871069</v>
+        <v>12.05971423820094</v>
       </c>
       <c r="E337" t="n">
-        <v>12.14628838105279</v>
+        <v>12.14628742533491</v>
       </c>
       <c r="F337" t="n">
         <v>1506100</v>
@@ -7172,16 +7172,16 @@
         <v>45138</v>
       </c>
       <c r="B338" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="C338" t="n">
-        <v>12.20689052500906</v>
+        <v>12.20688956452276</v>
       </c>
       <c r="D338" t="n">
-        <v>12.10300137126433</v>
+        <v>12.10300041895243</v>
       </c>
       <c r="E338" t="n">
-        <v>12.20689052500906</v>
+        <v>12.20688956452276</v>
       </c>
       <c r="F338" t="n">
         <v>1549400</v>
@@ -7292,16 +7292,16 @@
         <v>45146</v>
       </c>
       <c r="B344" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C344" t="n">
-        <v>12.15494652603107</v>
+        <v>12.15494556689158</v>
       </c>
       <c r="D344" t="n">
-        <v>11.92985472493413</v>
+        <v>11.92985378355649</v>
       </c>
       <c r="E344" t="n">
-        <v>11.99045687177166</v>
+        <v>11.99045592561195</v>
       </c>
       <c r="F344" t="n">
         <v>2176400</v>
@@ -7352,16 +7352,16 @@
         <v>45149</v>
       </c>
       <c r="B347" t="n">
-        <v>11.92119693756104</v>
+        <v>11.92119789123535</v>
       </c>
       <c r="C347" t="n">
-        <v>11.97314068671642</v>
+        <v>11.97314164454614</v>
       </c>
       <c r="D347" t="n">
-        <v>11.83462292146072</v>
+        <v>11.83462386820927</v>
       </c>
       <c r="E347" t="n">
-        <v>11.97314068671642</v>
+        <v>11.97314164454614</v>
       </c>
       <c r="F347" t="n">
         <v>2472600</v>
@@ -7392,16 +7392,16 @@
         <v>45153</v>
       </c>
       <c r="B349" t="n">
-        <v>11.860595703125</v>
+        <v>11.86059474945068</v>
       </c>
       <c r="C349" t="n">
-        <v>11.99911347897441</v>
+        <v>11.9991125141623</v>
       </c>
       <c r="D349" t="n">
-        <v>11.85193813572664</v>
+        <v>11.85193718274846</v>
       </c>
       <c r="E349" t="n">
-        <v>11.91254028188406</v>
+        <v>11.91253932403304</v>
       </c>
       <c r="F349" t="n">
         <v>2713800</v>
@@ -7492,16 +7492,16 @@
         <v>45160</v>
       </c>
       <c r="B354" t="n">
-        <v>11.79999351501465</v>
+        <v>11.79999446868896</v>
       </c>
       <c r="C354" t="n">
-        <v>11.86925239784715</v>
+        <v>11.86925335711897</v>
       </c>
       <c r="D354" t="n">
-        <v>11.73073463218214</v>
+        <v>11.73073558025896</v>
       </c>
       <c r="E354" t="n">
-        <v>11.79133594825283</v>
+        <v>11.79133690122745</v>
       </c>
       <c r="F354" t="n">
         <v>2231700</v>
@@ -7572,16 +7572,16 @@
         <v>45166</v>
       </c>
       <c r="B358" t="n">
-        <v>11.96448421478271</v>
+        <v>11.9644832611084</v>
       </c>
       <c r="C358" t="n">
-        <v>11.99911365926539</v>
+        <v>11.9991127028308</v>
       </c>
       <c r="D358" t="n">
-        <v>11.84328157190891</v>
+        <v>11.8432806278955</v>
       </c>
       <c r="E358" t="n">
-        <v>11.95582747288536</v>
+        <v>11.95582651990106</v>
       </c>
       <c r="F358" t="n">
         <v>2184700</v>
@@ -7592,16 +7592,16 @@
         <v>45167</v>
       </c>
       <c r="B359" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="C359" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="D359" t="n">
-        <v>11.97314116752997</v>
+        <v>11.97314022543599</v>
       </c>
       <c r="E359" t="n">
-        <v>11.98179873461387</v>
+        <v>11.98179779183868</v>
       </c>
       <c r="F359" t="n">
         <v>1776800</v>
@@ -7632,16 +7632,16 @@
         <v>45169</v>
       </c>
       <c r="B361" t="n">
-        <v>11.78267955780029</v>
+        <v>11.78267860412598</v>
       </c>
       <c r="C361" t="n">
-        <v>12.12031726453966</v>
+        <v>12.1203162835374</v>
       </c>
       <c r="D361" t="n">
-        <v>11.78267955780029</v>
+        <v>11.78267860412598</v>
       </c>
       <c r="E361" t="n">
-        <v>12.12031726453966</v>
+        <v>12.1203162835374</v>
       </c>
       <c r="F361" t="n">
         <v>3236500</v>
@@ -7652,16 +7652,16 @@
         <v>45170</v>
       </c>
       <c r="B362" t="n">
-        <v>12.04240036010742</v>
+        <v>12.04239940643311</v>
       </c>
       <c r="C362" t="n">
-        <v>12.04240036010742</v>
+        <v>12.04239940643311</v>
       </c>
       <c r="D362" t="n">
-        <v>11.89522501845123</v>
+        <v>11.89522407643217</v>
       </c>
       <c r="E362" t="n">
-        <v>11.90388258575596</v>
+        <v>11.90388164305129</v>
       </c>
       <c r="F362" t="n">
         <v>3740800</v>
@@ -7692,16 +7692,16 @@
         <v>45174</v>
       </c>
       <c r="B364" t="n">
-        <v>11.92119693756104</v>
+        <v>11.92119789123535</v>
       </c>
       <c r="C364" t="n">
-        <v>12.06837144392197</v>
+        <v>12.06837240936998</v>
       </c>
       <c r="D364" t="n">
-        <v>11.9125393708248</v>
+        <v>11.91254032380653</v>
       </c>
       <c r="E364" t="n">
-        <v>12.04239956934427</v>
+        <v>12.04240053271458</v>
       </c>
       <c r="F364" t="n">
         <v>3869600</v>
@@ -7772,16 +7772,16 @@
         <v>45181</v>
       </c>
       <c r="B368" t="n">
-        <v>12.06837177276611</v>
+        <v>12.0683708190918</v>
       </c>
       <c r="C368" t="n">
-        <v>12.15494579122544</v>
+        <v>12.15494483070982</v>
       </c>
       <c r="D368" t="n">
-        <v>11.98179857993782</v>
+        <v>11.98179763310474</v>
       </c>
       <c r="E368" t="n">
-        <v>12.03374233050859</v>
+        <v>12.03374137957078</v>
       </c>
       <c r="F368" t="n">
         <v>2215400</v>
@@ -7792,16 +7792,16 @@
         <v>45182</v>
       </c>
       <c r="B369" t="n">
-        <v>12.06837177276611</v>
+        <v>12.0683708190918</v>
       </c>
       <c r="C369" t="n">
-        <v>12.1982328004551</v>
+        <v>12.19823183651883</v>
       </c>
       <c r="D369" t="n">
-        <v>12.03374233050859</v>
+        <v>12.03374137957078</v>
       </c>
       <c r="E369" t="n">
-        <v>12.07702933973825</v>
+        <v>12.07702838537979</v>
       </c>
       <c r="F369" t="n">
         <v>1684100</v>
@@ -7812,16 +7812,16 @@
         <v>45183</v>
       </c>
       <c r="B370" t="n">
-        <v>12.21554756164551</v>
+        <v>12.21554660797119</v>
       </c>
       <c r="C370" t="n">
-        <v>12.25017700518688</v>
+        <v>12.25017604880902</v>
       </c>
       <c r="D370" t="n">
-        <v>12.09434492206624</v>
+        <v>12.09434397785428</v>
       </c>
       <c r="E370" t="n">
-        <v>12.09434492206624</v>
+        <v>12.09434397785428</v>
       </c>
       <c r="F370" t="n">
         <v>2498700</v>
@@ -7892,16 +7892,16 @@
         <v>45189</v>
       </c>
       <c r="B374" t="n">
-        <v>12.06837177276611</v>
+        <v>12.0683708190918</v>
       </c>
       <c r="C374" t="n">
-        <v>12.1462882242533</v>
+        <v>12.14628726442182</v>
       </c>
       <c r="D374" t="n">
-        <v>11.97314101296568</v>
+        <v>11.97314006681674</v>
       </c>
       <c r="E374" t="n">
-        <v>12.08568690671039</v>
+        <v>12.08568595166779</v>
       </c>
       <c r="F374" t="n">
         <v>2998000</v>
@@ -7972,16 +7972,16 @@
         <v>45195</v>
       </c>
       <c r="B378" t="n">
-        <v>11.83462238311768</v>
+        <v>11.83462333679199</v>
       </c>
       <c r="C378" t="n">
-        <v>12.06837089494598</v>
+        <v>12.06837186745655</v>
       </c>
       <c r="D378" t="n">
-        <v>11.78267781069418</v>
+        <v>11.78267876018263</v>
       </c>
       <c r="E378" t="n">
-        <v>11.80865050972141</v>
+        <v>11.80865146130283</v>
       </c>
       <c r="F378" t="n">
         <v>7795500</v>
@@ -8012,16 +8012,16 @@
         <v>45197</v>
       </c>
       <c r="B380" t="n">
-        <v>11.78267955780029</v>
+        <v>11.78267860412598</v>
       </c>
       <c r="C380" t="n">
-        <v>11.86059601517331</v>
+        <v>11.86059505519254</v>
       </c>
       <c r="D380" t="n">
-        <v>11.73073580330568</v>
+        <v>11.73073485383562</v>
       </c>
       <c r="E380" t="n">
-        <v>11.85193844754717</v>
+        <v>11.85193748826714</v>
       </c>
       <c r="F380" t="n">
         <v>2404900</v>
@@ -8172,16 +8172,16 @@
         <v>45209</v>
       </c>
       <c r="B388" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C388" t="n">
-        <v>12.16360409352659</v>
+        <v>12.16360313370393</v>
       </c>
       <c r="D388" t="n">
-        <v>11.91254041557417</v>
+        <v>11.9125394755628</v>
       </c>
       <c r="E388" t="n">
-        <v>11.92985472493413</v>
+        <v>11.92985378355649</v>
       </c>
       <c r="F388" t="n">
         <v>3643400</v>
@@ -8212,16 +8212,16 @@
         <v>45212</v>
       </c>
       <c r="B390" t="n">
-        <v>12.02508544921875</v>
+        <v>12.02508640289307</v>
       </c>
       <c r="C390" t="n">
-        <v>12.19823265849127</v>
+        <v>12.19823362589739</v>
       </c>
       <c r="D390" t="n">
-        <v>12.02508544921875</v>
+        <v>12.02508640289307</v>
       </c>
       <c r="E390" t="n">
-        <v>12.09434433292776</v>
+        <v>12.0943452920948</v>
       </c>
       <c r="F390" t="n">
         <v>4555500</v>
@@ -8352,16 +8352,16 @@
         <v>45223</v>
       </c>
       <c r="B397" t="n">
-        <v>11.6355037689209</v>
+        <v>11.63550281524658</v>
       </c>
       <c r="C397" t="n">
-        <v>11.81730855401174</v>
+        <v>11.81730758543626</v>
       </c>
       <c r="D397" t="n">
-        <v>11.54893057283972</v>
+        <v>11.54892962626116</v>
       </c>
       <c r="E397" t="n">
-        <v>11.80865181234537</v>
+        <v>11.80865084447942</v>
       </c>
       <c r="F397" t="n">
         <v>3637500</v>
@@ -8432,16 +8432,16 @@
         <v>45229</v>
       </c>
       <c r="B401" t="n">
-        <v>11.49698638916016</v>
+        <v>11.49698543548584</v>
       </c>
       <c r="C401" t="n">
-        <v>11.64416173574207</v>
+        <v>11.64416076985956</v>
       </c>
       <c r="D401" t="n">
-        <v>11.47101451200779</v>
+        <v>11.47101356048784</v>
       </c>
       <c r="E401" t="n">
-        <v>11.57490284624835</v>
+        <v>11.57490188611087</v>
       </c>
       <c r="F401" t="n">
         <v>4549600</v>
@@ -8452,16 +8452,16 @@
         <v>45230</v>
       </c>
       <c r="B402" t="n">
-        <v>11.61818885803223</v>
+        <v>11.61818981170654</v>
       </c>
       <c r="C402" t="n">
-        <v>11.6614758666457</v>
+        <v>11.66147682387321</v>
       </c>
       <c r="D402" t="n">
-        <v>11.52295809958741</v>
+        <v>11.52295904544475</v>
       </c>
       <c r="E402" t="n">
-        <v>11.52295809958741</v>
+        <v>11.52295904544475</v>
       </c>
       <c r="F402" t="n">
         <v>3290000</v>
@@ -8492,16 +8492,16 @@
         <v>45233</v>
       </c>
       <c r="B404" t="n">
-        <v>11.96448421478271</v>
+        <v>11.9644832611084</v>
       </c>
       <c r="C404" t="n">
-        <v>12.0250863618507</v>
+        <v>12.02508540334586</v>
       </c>
       <c r="D404" t="n">
-        <v>11.65281921443867</v>
+        <v>11.65281828560679</v>
       </c>
       <c r="E404" t="n">
-        <v>11.74804998035825</v>
+        <v>11.74804904393564</v>
       </c>
       <c r="F404" t="n">
         <v>4830800</v>
@@ -8512,16 +8512,16 @@
         <v>45236</v>
       </c>
       <c r="B405" t="n">
-        <v>12.02508544921875</v>
+        <v>12.02508640289307</v>
       </c>
       <c r="C405" t="n">
-        <v>12.077029199185</v>
+        <v>12.07703015697882</v>
       </c>
       <c r="D405" t="n">
-        <v>11.8173079724607</v>
+        <v>11.81730890965679</v>
       </c>
       <c r="E405" t="n">
-        <v>11.94716899863836</v>
+        <v>11.94716994613335</v>
       </c>
       <c r="F405" t="n">
         <v>2982900</v>
@@ -8592,16 +8592,16 @@
         <v>45240</v>
       </c>
       <c r="B409" t="n">
-        <v>11.78267955780029</v>
+        <v>11.78267860412598</v>
       </c>
       <c r="C409" t="n">
-        <v>11.86059601517331</v>
+        <v>11.86059505519254</v>
       </c>
       <c r="D409" t="n">
-        <v>11.69610635843224</v>
+        <v>11.69610541176504</v>
       </c>
       <c r="E409" t="n">
-        <v>11.69610635843224</v>
+        <v>11.69610541176504</v>
       </c>
       <c r="F409" t="n">
         <v>3430000</v>
@@ -8672,16 +8672,16 @@
         <v>45247</v>
       </c>
       <c r="B413" t="n">
-        <v>12.25017738342285</v>
+        <v>12.25017642974854</v>
       </c>
       <c r="C413" t="n">
-        <v>12.48392675376763</v>
+        <v>12.48392578189597</v>
       </c>
       <c r="D413" t="n">
-        <v>12.14628904959109</v>
+        <v>12.14628810400446</v>
       </c>
       <c r="E413" t="n">
-        <v>12.48392675376763</v>
+        <v>12.48392578189597</v>
       </c>
       <c r="F413" t="n">
         <v>3124800</v>
@@ -8692,16 +8692,16 @@
         <v>45250</v>
       </c>
       <c r="B414" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C414" t="n">
-        <v>12.23286298222856</v>
+        <v>12.23286201694073</v>
       </c>
       <c r="D414" t="n">
-        <v>11.99045687177166</v>
+        <v>11.99045592561195</v>
       </c>
       <c r="E414" t="n">
-        <v>12.20689110537309</v>
+        <v>12.20689014213468</v>
       </c>
       <c r="F414" t="n">
         <v>3248400</v>
@@ -8812,16 +8812,16 @@
         <v>45258</v>
       </c>
       <c r="B420" t="n">
-        <v>12.63975811004639</v>
+        <v>12.6397590637207</v>
       </c>
       <c r="C420" t="n">
-        <v>12.76961830492886</v>
+        <v>12.76961926840118</v>
       </c>
       <c r="D420" t="n">
-        <v>12.57049922935827</v>
+        <v>12.57050017780698</v>
       </c>
       <c r="E420" t="n">
-        <v>12.57915597022104</v>
+        <v>12.57915691932291</v>
       </c>
       <c r="F420" t="n">
         <v>5941200</v>
@@ -8852,16 +8852,16 @@
         <v>45260</v>
       </c>
       <c r="B422" t="n">
-        <v>12.71767425537109</v>
+        <v>12.71767520904541</v>
       </c>
       <c r="C422" t="n">
-        <v>12.71767425537109</v>
+        <v>12.71767520904541</v>
       </c>
       <c r="D422" t="n">
-        <v>12.58781405514036</v>
+        <v>12.58781499907671</v>
       </c>
       <c r="E422" t="n">
-        <v>12.63110106376094</v>
+        <v>12.6311020109433</v>
       </c>
       <c r="F422" t="n">
         <v>4162000</v>
@@ -8912,16 +8912,16 @@
         <v>45265</v>
       </c>
       <c r="B425" t="n">
-        <v>13.15920066833496</v>
+        <v>13.15919971466064</v>
       </c>
       <c r="C425" t="n">
-        <v>13.20248767830808</v>
+        <v>13.20248672149667</v>
       </c>
       <c r="D425" t="n">
-        <v>12.92545213548978</v>
+        <v>12.9254511987557</v>
       </c>
       <c r="E425" t="n">
-        <v>12.96008157834207</v>
+        <v>12.96008063909832</v>
       </c>
       <c r="F425" t="n">
         <v>6696500</v>
@@ -8932,16 +8932,16 @@
         <v>45266</v>
       </c>
       <c r="B426" t="n">
-        <v>13.07262802124023</v>
+        <v>13.07262706756592</v>
       </c>
       <c r="C426" t="n">
-        <v>13.27174711956826</v>
+        <v>13.2717461513678</v>
       </c>
       <c r="D426" t="n">
-        <v>13.04665531879052</v>
+        <v>13.04665436701096</v>
       </c>
       <c r="E426" t="n">
-        <v>13.21114579844774</v>
+        <v>13.21114483466828</v>
       </c>
       <c r="F426" t="n">
         <v>5861300</v>
@@ -8952,16 +8952,16 @@
         <v>45267</v>
       </c>
       <c r="B427" t="n">
-        <v>13.1159143447876</v>
+        <v>13.11591339111328</v>
       </c>
       <c r="C427" t="n">
-        <v>13.15054378945223</v>
+        <v>13.15054283325996</v>
       </c>
       <c r="D427" t="n">
-        <v>12.97739656612907</v>
+        <v>12.97739562252655</v>
       </c>
       <c r="E427" t="n">
-        <v>13.10725760284475</v>
+        <v>13.10725664979988</v>
       </c>
       <c r="F427" t="n">
         <v>6196000</v>
@@ -22118,13 +22118,13 @@
         <v>11.47</v>
       </c>
       <c r="D1085" t="n">
-        <v>11.1</v>
+        <v>11.08</v>
       </c>
       <c r="E1085" t="n">
         <v>11.45</v>
       </c>
       <c r="F1085" t="n">
-        <v>1250900</v>
+        <v>2114700</v>
       </c>
     </row>
   </sheetData>

--- a/database/AURE3.xlsx
+++ b/database/AURE3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1085"/>
+  <dimension ref="A1:F1086"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>44649</v>
       </c>
       <c r="B3" t="n">
-        <v>12.91280937194824</v>
+        <v>12.91280841827393</v>
       </c>
       <c r="C3" t="n">
-        <v>13.2161821224289</v>
+        <v>13.21618114634902</v>
       </c>
       <c r="D3" t="n">
-        <v>12.61721411646944</v>
+        <v>12.61721318462629</v>
       </c>
       <c r="E3" t="n">
-        <v>12.74945378682817</v>
+        <v>12.74945284521847</v>
       </c>
       <c r="F3" t="n">
         <v>4714100</v>
@@ -492,16 +492,16 @@
         <v>44650</v>
       </c>
       <c r="B4" t="n">
-        <v>12.38385009765625</v>
+        <v>12.38385105133057</v>
       </c>
       <c r="C4" t="n">
-        <v>13.04504841779609</v>
+        <v>13.04504942238897</v>
       </c>
       <c r="D4" t="n">
-        <v>12.30606179816537</v>
+        <v>12.30606274584925</v>
       </c>
       <c r="E4" t="n">
-        <v>12.92836671040398</v>
+        <v>12.92836770601126</v>
       </c>
       <c r="F4" t="n">
         <v>4408600</v>
@@ -512,16 +512,16 @@
         <v>44651</v>
       </c>
       <c r="B5" t="n">
-        <v>12.4383020401001</v>
+        <v>12.43830299377441</v>
       </c>
       <c r="C5" t="n">
-        <v>12.82724207193696</v>
+        <v>12.82724305543223</v>
       </c>
       <c r="D5" t="n">
-        <v>12.05714098694259</v>
+        <v>12.05714191139238</v>
       </c>
       <c r="E5" t="n">
-        <v>12.41496584590627</v>
+        <v>12.41496679779135</v>
       </c>
       <c r="F5" t="n">
         <v>3876100</v>
@@ -592,16 +592,16 @@
         <v>44657</v>
       </c>
       <c r="B9" t="n">
-        <v>12.43052387237549</v>
+        <v>12.43052291870117</v>
       </c>
       <c r="C9" t="n">
-        <v>12.44608183074918</v>
+        <v>12.44608087588125</v>
       </c>
       <c r="D9" t="n">
-        <v>12.01824761944832</v>
+        <v>12.01824669740399</v>
       </c>
       <c r="E9" t="n">
-        <v>12.06492075272512</v>
+        <v>12.06491982710001</v>
       </c>
       <c r="F9" t="n">
         <v>2914800</v>
@@ -692,16 +692,16 @@
         <v>44664</v>
       </c>
       <c r="B14" t="n">
-        <v>12.10381412506104</v>
+        <v>12.10381317138672</v>
       </c>
       <c r="C14" t="n">
-        <v>12.55498376109398</v>
+        <v>12.55498277187146</v>
       </c>
       <c r="D14" t="n">
-        <v>12.08825616769219</v>
+        <v>12.0882552152437</v>
       </c>
       <c r="E14" t="n">
-        <v>12.39162965978653</v>
+        <v>12.39162868343488</v>
       </c>
       <c r="F14" t="n">
         <v>4421300</v>
@@ -712,16 +712,16 @@
         <v>44665</v>
       </c>
       <c r="B15" t="n">
-        <v>12.11159324645996</v>
+        <v>12.11159229278564</v>
       </c>
       <c r="C15" t="n">
-        <v>12.36829362703988</v>
+        <v>12.36829265315281</v>
       </c>
       <c r="D15" t="n">
-        <v>12.04936289612812</v>
+        <v>12.04936194735386</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08047807129404</v>
+        <v>12.08047712006975</v>
       </c>
       <c r="F15" t="n">
         <v>2077400</v>
@@ -732,16 +732,16 @@
         <v>44669</v>
       </c>
       <c r="B16" t="n">
-        <v>12.45386028289795</v>
+        <v>12.45385932922363</v>
       </c>
       <c r="C16" t="n">
-        <v>12.45386028289795</v>
+        <v>12.45385932922363</v>
       </c>
       <c r="D16" t="n">
-        <v>11.92490159008608</v>
+        <v>11.92490067691762</v>
       </c>
       <c r="E16" t="n">
-        <v>12.10381439459067</v>
+        <v>12.10381346772168</v>
       </c>
       <c r="F16" t="n">
         <v>3931100</v>
@@ -752,16 +752,16 @@
         <v>44670</v>
       </c>
       <c r="B17" t="n">
-        <v>12.10381412506104</v>
+        <v>12.10381317138672</v>
       </c>
       <c r="C17" t="n">
-        <v>12.60165763320052</v>
+        <v>12.60165664030051</v>
       </c>
       <c r="D17" t="n">
-        <v>12.00268962769625</v>
+        <v>12.00268868198966</v>
       </c>
       <c r="E17" t="n">
-        <v>12.4383020482046</v>
+        <v>12.43830106817557</v>
       </c>
       <c r="F17" t="n">
         <v>3118100</v>
@@ -832,16 +832,16 @@
         <v>44677</v>
       </c>
       <c r="B21" t="n">
-        <v>11.95601558685303</v>
+        <v>11.95601654052734</v>
       </c>
       <c r="C21" t="n">
-        <v>12.43830110089237</v>
+        <v>12.4383020930363</v>
       </c>
       <c r="D21" t="n">
-        <v>11.86267007528195</v>
+        <v>11.86267102151054</v>
       </c>
       <c r="E21" t="n">
-        <v>12.32939837498153</v>
+        <v>12.32939935843881</v>
       </c>
       <c r="F21" t="n">
         <v>2627000</v>
@@ -932,16 +932,16 @@
         <v>44684</v>
       </c>
       <c r="B26" t="n">
-        <v>11.27148056030273</v>
+        <v>11.27148151397705</v>
       </c>
       <c r="C26" t="n">
-        <v>11.35704783157836</v>
+        <v>11.35704879249248</v>
       </c>
       <c r="D26" t="n">
-        <v>11.01478023016414</v>
+        <v>11.01478116211917</v>
       </c>
       <c r="E26" t="n">
-        <v>11.15479886181943</v>
+        <v>11.15479980562136</v>
       </c>
       <c r="F26" t="n">
         <v>1672900</v>
@@ -952,16 +952,16 @@
         <v>44685</v>
       </c>
       <c r="B27" t="n">
-        <v>11.69445610046387</v>
+        <v>11.69445705413818</v>
       </c>
       <c r="C27" t="n">
-        <v>11.69445610046387</v>
+        <v>11.69445705413818</v>
       </c>
       <c r="D27" t="n">
-        <v>11.03649597266557</v>
+        <v>11.03649687268372</v>
       </c>
       <c r="E27" t="n">
-        <v>11.20881904113643</v>
+        <v>11.2088199552074</v>
       </c>
       <c r="F27" t="n">
         <v>4400300</v>
@@ -1092,16 +1092,16 @@
         <v>44694</v>
       </c>
       <c r="B34" t="n">
-        <v>11.32631301879883</v>
+        <v>11.32631206512451</v>
       </c>
       <c r="C34" t="n">
-        <v>11.38114278731251</v>
+        <v>11.38114182902154</v>
       </c>
       <c r="D34" t="n">
-        <v>11.11482548824677</v>
+        <v>11.11482455237968</v>
       </c>
       <c r="E34" t="n">
-        <v>11.18532133176413</v>
+        <v>11.18532038996129</v>
       </c>
       <c r="F34" t="n">
         <v>1333500</v>
@@ -1112,16 +1112,16 @@
         <v>44697</v>
       </c>
       <c r="B35" t="n">
-        <v>11.27931499481201</v>
+        <v>11.2793140411377</v>
       </c>
       <c r="C35" t="n">
-        <v>11.41247363789934</v>
+        <v>11.41247267296636</v>
       </c>
       <c r="D35" t="n">
-        <v>11.11482495023352</v>
+        <v>11.11482401046696</v>
       </c>
       <c r="E35" t="n">
-        <v>11.17748850021538</v>
+        <v>11.17748755515057</v>
       </c>
       <c r="F35" t="n">
         <v>2419100</v>
@@ -1212,16 +1212,16 @@
         <v>44704</v>
       </c>
       <c r="B40" t="n">
-        <v>11.20881938934326</v>
+        <v>11.20882034301758</v>
       </c>
       <c r="C40" t="n">
-        <v>11.43597222652075</v>
+        <v>11.4359731995218</v>
       </c>
       <c r="D40" t="n">
-        <v>11.16182191575504</v>
+        <v>11.16182286543069</v>
       </c>
       <c r="E40" t="n">
-        <v>11.1853202790494</v>
+        <v>11.18532123072435</v>
       </c>
       <c r="F40" t="n">
         <v>1184600</v>
@@ -1252,16 +1252,16 @@
         <v>44706</v>
       </c>
       <c r="B42" t="n">
-        <v>11.32631301879883</v>
+        <v>11.32631206512451</v>
       </c>
       <c r="C42" t="n">
-        <v>11.39680886231618</v>
+        <v>11.39680790270612</v>
       </c>
       <c r="D42" t="n">
-        <v>11.13832460075227</v>
+        <v>11.13832366290656</v>
       </c>
       <c r="E42" t="n">
-        <v>11.17748904126186</v>
+        <v>11.17748810011851</v>
       </c>
       <c r="F42" t="n">
         <v>821700</v>
@@ -1292,16 +1292,16 @@
         <v>44708</v>
       </c>
       <c r="B44" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482620239258</v>
       </c>
       <c r="C44" t="n">
-        <v>11.42030698171035</v>
+        <v>11.42030796159561</v>
       </c>
       <c r="D44" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482620239258</v>
       </c>
       <c r="E44" t="n">
-        <v>11.26364997004757</v>
+        <v>11.26365093649135</v>
       </c>
       <c r="F44" t="n">
         <v>2224600</v>
@@ -1372,16 +1372,16 @@
         <v>44714</v>
       </c>
       <c r="B48" t="n">
-        <v>10.86417293548584</v>
+        <v>10.86417388916016</v>
       </c>
       <c r="C48" t="n">
-        <v>10.98949853218943</v>
+        <v>10.98949949686503</v>
       </c>
       <c r="D48" t="n">
-        <v>10.68401757697429</v>
+        <v>10.68401851483428</v>
       </c>
       <c r="E48" t="n">
-        <v>10.75451266487045</v>
+        <v>10.75451360891862</v>
       </c>
       <c r="F48" t="n">
         <v>3275400</v>
@@ -1432,16 +1432,16 @@
         <v>44719</v>
       </c>
       <c r="B51" t="n">
-        <v>10.8563404083252</v>
+        <v>10.85634136199951</v>
       </c>
       <c r="C51" t="n">
-        <v>10.87983951905932</v>
+        <v>10.87984047479791</v>
       </c>
       <c r="D51" t="n">
-        <v>10.53519336495403</v>
+        <v>10.53519429041721</v>
       </c>
       <c r="E51" t="n">
-        <v>10.59002387633413</v>
+        <v>10.59002480661389</v>
       </c>
       <c r="F51" t="n">
         <v>2760900</v>
@@ -1532,16 +1532,16 @@
         <v>44726</v>
       </c>
       <c r="B56" t="n">
-        <v>10.39420318603516</v>
+        <v>10.39420223236084</v>
       </c>
       <c r="C56" t="n">
-        <v>10.47253131980584</v>
+        <v>10.47253035894487</v>
       </c>
       <c r="D56" t="n">
-        <v>10.01822560413734</v>
+        <v>10.01822468495919</v>
       </c>
       <c r="E56" t="n">
-        <v>10.01822560413734</v>
+        <v>10.01822468495919</v>
       </c>
       <c r="F56" t="n">
         <v>4085600</v>
@@ -1572,16 +1572,16 @@
         <v>44729</v>
       </c>
       <c r="B58" t="n">
-        <v>10.45686531066895</v>
+        <v>10.45686626434326</v>
       </c>
       <c r="C58" t="n">
-        <v>10.80151072020806</v>
+        <v>10.80151170531431</v>
       </c>
       <c r="D58" t="n">
-        <v>10.42553390980175</v>
+        <v>10.42553486061862</v>
       </c>
       <c r="E58" t="n">
-        <v>10.74668095544036</v>
+        <v>10.74668193554609</v>
       </c>
       <c r="F58" t="n">
         <v>8202900</v>
@@ -1612,16 +1612,16 @@
         <v>44733</v>
       </c>
       <c r="B60" t="n">
-        <v>10.6370210647583</v>
+        <v>10.63702011108398</v>
       </c>
       <c r="C60" t="n">
-        <v>10.71534994326738</v>
+        <v>10.7153489825704</v>
       </c>
       <c r="D60" t="n">
-        <v>10.51952849399422</v>
+        <v>10.51952755085384</v>
       </c>
       <c r="E60" t="n">
-        <v>10.69185083151493</v>
+        <v>10.69184987292479</v>
       </c>
       <c r="F60" t="n">
         <v>1455700</v>
@@ -1652,16 +1652,16 @@
         <v>44735</v>
       </c>
       <c r="B62" t="n">
-        <v>10.6370210647583</v>
+        <v>10.63702011108398</v>
       </c>
       <c r="C62" t="n">
-        <v>10.89550531803891</v>
+        <v>10.89550434118989</v>
       </c>
       <c r="D62" t="n">
-        <v>10.55085989599795</v>
+        <v>10.55085895004851</v>
       </c>
       <c r="E62" t="n">
-        <v>10.87983999053682</v>
+        <v>10.8798390150923</v>
       </c>
       <c r="F62" t="n">
         <v>3444100</v>
@@ -1672,16 +1672,16 @@
         <v>44736</v>
       </c>
       <c r="B63" t="n">
-        <v>10.48819637298584</v>
+        <v>10.48819732666016</v>
       </c>
       <c r="C63" t="n">
-        <v>10.70751617197673</v>
+        <v>10.70751714559343</v>
       </c>
       <c r="D63" t="n">
-        <v>10.42553357327416</v>
+        <v>10.42553452125065</v>
       </c>
       <c r="E63" t="n">
-        <v>10.70751617197673</v>
+        <v>10.70751714559343</v>
       </c>
       <c r="F63" t="n">
         <v>807500</v>
@@ -1692,16 +1692,16 @@
         <v>44739</v>
       </c>
       <c r="B64" t="n">
-        <v>10.45686531066895</v>
+        <v>10.45686626434326</v>
       </c>
       <c r="C64" t="n">
-        <v>10.55085951327052</v>
+        <v>10.55086047551718</v>
       </c>
       <c r="D64" t="n">
-        <v>10.33153896020065</v>
+        <v>10.33153990244511</v>
       </c>
       <c r="E64" t="n">
-        <v>10.4960290015033</v>
+        <v>10.49602995874937</v>
       </c>
       <c r="F64" t="n">
         <v>1661400</v>
@@ -1792,16 +1792,16 @@
         <v>44746</v>
       </c>
       <c r="B69" t="n">
-        <v>10.65268707275391</v>
+        <v>10.65268611907959</v>
       </c>
       <c r="C69" t="n">
-        <v>10.7858457171883</v>
+        <v>10.78584475159305</v>
       </c>
       <c r="D69" t="n">
-        <v>10.52736071852189</v>
+        <v>10.52735977606733</v>
       </c>
       <c r="E69" t="n">
-        <v>10.68401847456203</v>
+        <v>10.68401751808279</v>
       </c>
       <c r="F69" t="n">
         <v>1437100</v>
@@ -1812,16 +1812,16 @@
         <v>44747</v>
       </c>
       <c r="B70" t="n">
-        <v>10.6213550567627</v>
+        <v>10.62135601043701</v>
       </c>
       <c r="C70" t="n">
-        <v>10.6213550567627</v>
+        <v>10.62135601043701</v>
       </c>
       <c r="D70" t="n">
-        <v>10.49602870977771</v>
+        <v>10.49602965219918</v>
       </c>
       <c r="E70" t="n">
-        <v>10.58219062001736</v>
+        <v>10.58219157017516</v>
       </c>
       <c r="F70" t="n">
         <v>1722600</v>
@@ -1852,16 +1852,16 @@
         <v>44749</v>
       </c>
       <c r="B72" t="n">
-        <v>11.04432964324951</v>
+        <v>11.0443286895752</v>
       </c>
       <c r="C72" t="n">
-        <v>11.16182220981619</v>
+        <v>11.16182124599643</v>
       </c>
       <c r="D72" t="n">
-        <v>10.62135535781014</v>
+        <v>10.62135444065952</v>
       </c>
       <c r="E72" t="n">
-        <v>10.7858453992032</v>
+        <v>10.78584446784892</v>
       </c>
       <c r="F72" t="n">
         <v>2931100</v>
@@ -1912,16 +1912,16 @@
         <v>44754</v>
       </c>
       <c r="B75" t="n">
-        <v>11.14615631103516</v>
+        <v>11.14615535736084</v>
       </c>
       <c r="C75" t="n">
-        <v>11.22448518797689</v>
+        <v>11.22448422760069</v>
       </c>
       <c r="D75" t="n">
-        <v>10.99733234124531</v>
+        <v>10.99733140030449</v>
       </c>
       <c r="E75" t="n">
-        <v>11.10699261956382</v>
+        <v>11.10699166924038</v>
       </c>
       <c r="F75" t="n">
         <v>1673000</v>
@@ -2032,16 +2032,16 @@
         <v>44762</v>
       </c>
       <c r="B81" t="n">
-        <v>11.27931499481201</v>
+        <v>11.2793140411377</v>
       </c>
       <c r="C81" t="n">
-        <v>11.35764387203968</v>
+        <v>11.35764291174261</v>
       </c>
       <c r="D81" t="n">
-        <v>11.0521621472512</v>
+        <v>11.05216121278282</v>
       </c>
       <c r="E81" t="n">
-        <v>11.08349354874236</v>
+        <v>11.08349261162489</v>
       </c>
       <c r="F81" t="n">
         <v>2285400</v>
@@ -2112,16 +2112,16 @@
         <v>44768</v>
       </c>
       <c r="B85" t="n">
-        <v>11.27148342132568</v>
+        <v>11.27148246765137</v>
       </c>
       <c r="C85" t="n">
-        <v>11.3811429600171</v>
+        <v>11.38114199706455</v>
       </c>
       <c r="D85" t="n">
-        <v>11.16965617325538</v>
+        <v>11.16965522819662</v>
       </c>
       <c r="E85" t="n">
-        <v>11.19315453911789</v>
+        <v>11.19315359207094</v>
       </c>
       <c r="F85" t="n">
         <v>1661400</v>
@@ -2132,16 +2132,16 @@
         <v>44769</v>
       </c>
       <c r="B86" t="n">
-        <v>11.24015140533447</v>
+        <v>11.24015045166016</v>
       </c>
       <c r="C86" t="n">
-        <v>11.49080261954139</v>
+        <v>11.49080164460048</v>
       </c>
       <c r="D86" t="n">
-        <v>11.15398949020119</v>
+        <v>11.15398854383731</v>
       </c>
       <c r="E86" t="n">
-        <v>11.2871481344985</v>
+        <v>11.28714717683673</v>
       </c>
       <c r="F86" t="n">
         <v>3096400</v>
@@ -2172,16 +2172,16 @@
         <v>44771</v>
       </c>
       <c r="B88" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482620239258</v>
       </c>
       <c r="C88" t="n">
-        <v>11.33414581204571</v>
+        <v>11.33414678453817</v>
       </c>
       <c r="D88" t="n">
-        <v>10.51952860439969</v>
+        <v>10.51952950699636</v>
       </c>
       <c r="E88" t="n">
-        <v>10.96600127438851</v>
+        <v>10.96600221529343</v>
       </c>
       <c r="F88" t="n">
         <v>13059200</v>
@@ -2212,16 +2212,16 @@
         <v>44775</v>
       </c>
       <c r="B90" t="n">
-        <v>10.86417293548584</v>
+        <v>10.86417388916016</v>
       </c>
       <c r="C90" t="n">
-        <v>11.06782740362892</v>
+        <v>11.06782837518035</v>
       </c>
       <c r="D90" t="n">
-        <v>10.72318126569455</v>
+        <v>10.7231822069924</v>
       </c>
       <c r="E90" t="n">
-        <v>10.93466877038148</v>
+        <v>10.93466973024404</v>
       </c>
       <c r="F90" t="n">
         <v>2371400</v>
@@ -2292,16 +2292,16 @@
         <v>44781</v>
       </c>
       <c r="B94" t="n">
-        <v>10.97383308410645</v>
+        <v>10.97383403778076</v>
       </c>
       <c r="C94" t="n">
-        <v>11.10699171587358</v>
+        <v>11.10699268111997</v>
       </c>
       <c r="D94" t="n">
-        <v>10.8720058511669</v>
+        <v>10.87200679599199</v>
       </c>
       <c r="E94" t="n">
-        <v>11.02866284530486</v>
+        <v>11.02866380374413</v>
       </c>
       <c r="F94" t="n">
         <v>2949000</v>
@@ -2352,16 +2352,16 @@
         <v>44784</v>
       </c>
       <c r="B97" t="n">
-        <v>10.89550590515137</v>
+        <v>10.89550495147705</v>
       </c>
       <c r="C97" t="n">
-        <v>11.10699344032233</v>
+        <v>11.10699246813669</v>
       </c>
       <c r="D97" t="n">
-        <v>10.83284309776729</v>
+        <v>10.83284214957779</v>
       </c>
       <c r="E97" t="n">
-        <v>11.05999596128448</v>
+        <v>11.05999499321249</v>
       </c>
       <c r="F97" t="n">
         <v>1665400</v>
@@ -2412,16 +2412,16 @@
         <v>44789</v>
       </c>
       <c r="B100" t="n">
-        <v>11.04432964324951</v>
+        <v>11.0443286895752</v>
       </c>
       <c r="C100" t="n">
-        <v>11.29498085032484</v>
+        <v>11.29497987500687</v>
       </c>
       <c r="D100" t="n">
-        <v>10.94250240362528</v>
+        <v>10.94250145874372</v>
       </c>
       <c r="E100" t="n">
-        <v>11.25581641246944</v>
+        <v>11.25581544053331</v>
       </c>
       <c r="F100" t="n">
         <v>1185300</v>
@@ -2432,16 +2432,16 @@
         <v>44790</v>
       </c>
       <c r="B101" t="n">
-        <v>11.24015140533447</v>
+        <v>11.24015045166016</v>
       </c>
       <c r="C101" t="n">
-        <v>11.25581673272263</v>
+        <v>11.25581577771919</v>
       </c>
       <c r="D101" t="n">
-        <v>10.91117131318813</v>
+        <v>10.91117038742624</v>
       </c>
       <c r="E101" t="n">
-        <v>10.98949944412802</v>
+        <v>10.98949851172035</v>
       </c>
       <c r="F101" t="n">
         <v>4396400</v>
@@ -2452,16 +2452,16 @@
         <v>44791</v>
       </c>
       <c r="B102" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="C102" t="n">
-        <v>11.37330897550059</v>
+        <v>11.37330994384684</v>
       </c>
       <c r="D102" t="n">
-        <v>11.09915867560374</v>
+        <v>11.09915962060828</v>
       </c>
       <c r="E102" t="n">
-        <v>11.27931403205064</v>
+        <v>11.27931499239396</v>
       </c>
       <c r="F102" t="n">
         <v>2180500</v>
@@ -2472,16 +2472,16 @@
         <v>44792</v>
       </c>
       <c r="B103" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482620239258</v>
       </c>
       <c r="C103" t="n">
-        <v>11.16182272571687</v>
+        <v>11.16182368342367</v>
       </c>
       <c r="D103" t="n">
-        <v>10.98166734905456</v>
+        <v>10.98166829130366</v>
       </c>
       <c r="E103" t="n">
-        <v>11.16182272571687</v>
+        <v>11.16182368342367</v>
       </c>
       <c r="F103" t="n">
         <v>1667800</v>
@@ -2492,16 +2492,16 @@
         <v>44795</v>
       </c>
       <c r="B104" t="n">
-        <v>11.0599946975708</v>
+        <v>11.05999565124512</v>
       </c>
       <c r="C104" t="n">
-        <v>11.2244847349093</v>
+        <v>11.22448570276716</v>
       </c>
       <c r="D104" t="n">
-        <v>10.98166657079026</v>
+        <v>10.98166751771054</v>
       </c>
       <c r="E104" t="n">
-        <v>11.0599946975708</v>
+        <v>11.05999565124512</v>
       </c>
       <c r="F104" t="n">
         <v>1703300</v>
@@ -2552,16 +2552,16 @@
         <v>44798</v>
       </c>
       <c r="B107" t="n">
-        <v>11.04432964324951</v>
+        <v>11.0443286895752</v>
       </c>
       <c r="C107" t="n">
-        <v>11.22448501158502</v>
+        <v>11.22448404235435</v>
       </c>
       <c r="D107" t="n">
-        <v>10.95033469359675</v>
+        <v>10.95033374803886</v>
       </c>
       <c r="E107" t="n">
-        <v>11.20881968464257</v>
+        <v>11.2088187167646</v>
       </c>
       <c r="F107" t="n">
         <v>2435800</v>
@@ -2592,16 +2592,16 @@
         <v>44802</v>
       </c>
       <c r="B109" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482620239258</v>
       </c>
       <c r="C109" t="n">
-        <v>11.20882020271549</v>
+        <v>11.20882116445476</v>
       </c>
       <c r="D109" t="n">
-        <v>10.93466987205595</v>
+        <v>10.93467081027257</v>
       </c>
       <c r="E109" t="n">
-        <v>11.02083104172059</v>
+        <v>11.02083198733002</v>
       </c>
       <c r="F109" t="n">
         <v>3615600</v>
@@ -2612,16 +2612,16 @@
         <v>44803</v>
       </c>
       <c r="B110" t="n">
-        <v>11.01299858093262</v>
+        <v>11.0129976272583</v>
       </c>
       <c r="C110" t="n">
-        <v>11.16182255295894</v>
+        <v>11.16182158639716</v>
       </c>
       <c r="D110" t="n">
-        <v>10.93466970281379</v>
+        <v>10.93466875592239</v>
       </c>
       <c r="E110" t="n">
-        <v>11.11482507668773</v>
+        <v>11.11482411419572</v>
       </c>
       <c r="F110" t="n">
         <v>1284900</v>
@@ -2672,16 +2672,16 @@
         <v>44806</v>
       </c>
       <c r="B113" t="n">
-        <v>11.74145317077637</v>
+        <v>11.74145412445068</v>
       </c>
       <c r="C113" t="n">
-        <v>11.79628368103782</v>
+        <v>11.79628463916563</v>
       </c>
       <c r="D113" t="n">
-        <v>11.56129780748737</v>
+        <v>11.56129874652895</v>
       </c>
       <c r="E113" t="n">
-        <v>11.74145317077637</v>
+        <v>11.74145412445068</v>
       </c>
       <c r="F113" t="n">
         <v>3674700</v>
@@ -2712,16 +2712,16 @@
         <v>44810</v>
       </c>
       <c r="B115" t="n">
-        <v>11.58479785919189</v>
+        <v>11.58479690551758</v>
       </c>
       <c r="C115" t="n">
-        <v>11.90594494281729</v>
+        <v>11.90594396270576</v>
       </c>
       <c r="D115" t="n">
-        <v>11.49863668336545</v>
+        <v>11.49863573678402</v>
       </c>
       <c r="E115" t="n">
-        <v>11.89811190492408</v>
+        <v>11.89811092545738</v>
       </c>
       <c r="F115" t="n">
         <v>1316500</v>
@@ -2772,16 +2772,16 @@
         <v>44816</v>
       </c>
       <c r="B118" t="n">
-        <v>11.41247367858887</v>
+        <v>11.41247272491455</v>
       </c>
       <c r="C118" t="n">
-        <v>11.64745956411016</v>
+        <v>11.64745859079944</v>
       </c>
       <c r="D118" t="n">
-        <v>11.35764391253373</v>
+        <v>11.35764296344122</v>
       </c>
       <c r="E118" t="n">
-        <v>11.3968083512872</v>
+        <v>11.39680739892195</v>
       </c>
       <c r="F118" t="n">
         <v>2097200</v>
@@ -2792,16 +2792,16 @@
         <v>44817</v>
       </c>
       <c r="B119" t="n">
-        <v>11.24015140533447</v>
+        <v>11.24015045166016</v>
       </c>
       <c r="C119" t="n">
-        <v>11.43597285318351</v>
+        <v>11.43597188289466</v>
       </c>
       <c r="D119" t="n">
-        <v>11.16965556458889</v>
+        <v>11.16965461689582</v>
       </c>
       <c r="E119" t="n">
-        <v>11.3028142088862</v>
+        <v>11.30281324989524</v>
       </c>
       <c r="F119" t="n">
         <v>1768400</v>
@@ -2812,16 +2812,16 @@
         <v>44818</v>
       </c>
       <c r="B120" t="n">
-        <v>11.20881938934326</v>
+        <v>11.20882034301758</v>
       </c>
       <c r="C120" t="n">
-        <v>11.42030615299151</v>
+        <v>11.42030712465965</v>
       </c>
       <c r="D120" t="n">
-        <v>11.02866327875449</v>
+        <v>11.02866421710068</v>
       </c>
       <c r="E120" t="n">
-        <v>11.20098635257864</v>
+        <v>11.2009873055865</v>
       </c>
       <c r="F120" t="n">
         <v>1856400</v>
@@ -2892,16 +2892,16 @@
         <v>44824</v>
       </c>
       <c r="B124" t="n">
-        <v>11.13049125671387</v>
+        <v>11.13049030303955</v>
       </c>
       <c r="C124" t="n">
-        <v>11.35764410901417</v>
+        <v>11.35764313587711</v>
       </c>
       <c r="D124" t="n">
-        <v>11.08349377999676</v>
+        <v>11.08349283034925</v>
       </c>
       <c r="E124" t="n">
-        <v>11.28714826743829</v>
+        <v>11.28714730034141</v>
       </c>
       <c r="F124" t="n">
         <v>1310600</v>
@@ -2952,16 +2952,16 @@
         <v>44827</v>
       </c>
       <c r="B127" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="C127" t="n">
-        <v>11.30281314141286</v>
+        <v>11.30281410375695</v>
       </c>
       <c r="D127" t="n">
-        <v>11.07566031324099</v>
+        <v>11.07566125624483</v>
       </c>
       <c r="E127" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="F127" t="n">
         <v>2444100</v>
@@ -3032,16 +3032,16 @@
         <v>44833</v>
       </c>
       <c r="B131" t="n">
-        <v>10.70751571655273</v>
+        <v>10.70751667022705</v>
       </c>
       <c r="C131" t="n">
-        <v>10.83284131064561</v>
+        <v>10.83284227548216</v>
       </c>
       <c r="D131" t="n">
-        <v>10.6448529195063</v>
+        <v>10.6448538675995</v>
       </c>
       <c r="E131" t="n">
-        <v>10.69184964379139</v>
+        <v>10.6918505960704</v>
       </c>
       <c r="F131" t="n">
         <v>2222600</v>
@@ -3072,16 +3072,16 @@
         <v>44837</v>
       </c>
       <c r="B133" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="C133" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="D133" t="n">
-        <v>10.62918694635185</v>
+        <v>10.62918785134206</v>
       </c>
       <c r="E133" t="n">
-        <v>10.74668025216456</v>
+        <v>10.74668116715839</v>
       </c>
       <c r="F133" t="n">
         <v>2250700</v>
@@ -3092,16 +3092,16 @@
         <v>44838</v>
       </c>
       <c r="B134" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482620239258</v>
       </c>
       <c r="C134" t="n">
-        <v>11.32631277471268</v>
+        <v>11.32631374653305</v>
       </c>
       <c r="D134" t="n">
-        <v>11.07566155605223</v>
+        <v>11.07566250636622</v>
       </c>
       <c r="E134" t="n">
-        <v>11.20882020271549</v>
+        <v>11.20882116445476</v>
       </c>
       <c r="F134" t="n">
         <v>2406500</v>
@@ -3112,16 +3112,16 @@
         <v>44839</v>
       </c>
       <c r="B135" t="n">
-        <v>10.97383308410645</v>
+        <v>10.97383403778076</v>
       </c>
       <c r="C135" t="n">
-        <v>11.20881894881312</v>
+        <v>11.20881992290874</v>
       </c>
       <c r="D135" t="n">
-        <v>10.85633977825337</v>
+        <v>10.85634072171701</v>
       </c>
       <c r="E135" t="n">
-        <v>11.20881894881312</v>
+        <v>11.20881992290874</v>
       </c>
       <c r="F135" t="n">
         <v>5244200</v>
@@ -3272,16 +3272,16 @@
         <v>44852</v>
       </c>
       <c r="B143" t="n">
-        <v>11.27148342132568</v>
+        <v>11.27148246765137</v>
       </c>
       <c r="C143" t="n">
-        <v>11.37331066939599</v>
+        <v>11.37330970710612</v>
       </c>
       <c r="D143" t="n">
-        <v>11.06782892518508</v>
+        <v>11.06782798874186</v>
       </c>
       <c r="E143" t="n">
-        <v>11.20882061435928</v>
+        <v>11.20881966598683</v>
       </c>
       <c r="F143" t="n">
         <v>2646800</v>
@@ -3372,16 +3372,16 @@
         <v>44859</v>
       </c>
       <c r="B148" t="n">
-        <v>11.38897609710693</v>
+        <v>11.38897514343262</v>
       </c>
       <c r="C148" t="n">
-        <v>11.5064686744452</v>
+        <v>11.50646771093245</v>
       </c>
       <c r="D148" t="n">
-        <v>11.18532159918765</v>
+        <v>11.18532066256667</v>
       </c>
       <c r="E148" t="n">
-        <v>11.24015211601182</v>
+        <v>11.24015117479952</v>
       </c>
       <c r="F148" t="n">
         <v>2935500</v>
@@ -3432,16 +3432,16 @@
         <v>44862</v>
       </c>
       <c r="B151" t="n">
-        <v>11.49080181121826</v>
+        <v>11.49080276489258</v>
       </c>
       <c r="C151" t="n">
-        <v>11.63962577243467</v>
+        <v>11.63962673846057</v>
       </c>
       <c r="D151" t="n">
-        <v>11.2244845413578</v>
+        <v>11.22448547292922</v>
       </c>
       <c r="E151" t="n">
-        <v>11.32631177671618</v>
+        <v>11.32631271673871</v>
       </c>
       <c r="F151" t="n">
         <v>2887600</v>
@@ -3452,16 +3452,16 @@
         <v>44865</v>
       </c>
       <c r="B152" t="n">
-        <v>11.68662357330322</v>
+        <v>11.68662452697754</v>
       </c>
       <c r="C152" t="n">
-        <v>11.72578801061714</v>
+        <v>11.72578896748743</v>
       </c>
       <c r="D152" t="n">
-        <v>11.16182205549541</v>
+        <v>11.16182296634386</v>
       </c>
       <c r="E152" t="n">
-        <v>11.23231789326056</v>
+        <v>11.23231880986175</v>
       </c>
       <c r="F152" t="n">
         <v>2644000</v>
@@ -3492,16 +3492,16 @@
         <v>44868</v>
       </c>
       <c r="B154" t="n">
-        <v>11.68662357330322</v>
+        <v>11.68662452697754</v>
       </c>
       <c r="C154" t="n">
-        <v>11.74928637420569</v>
+        <v>11.74928733299354</v>
       </c>
       <c r="D154" t="n">
-        <v>11.36547653192819</v>
+        <v>11.36547745939565</v>
       </c>
       <c r="E154" t="n">
-        <v>11.49863517059581</v>
+        <v>11.49863610892954</v>
       </c>
       <c r="F154" t="n">
         <v>2959500</v>
@@ -3512,16 +3512,16 @@
         <v>44869</v>
       </c>
       <c r="B155" t="n">
-        <v>11.67095851898193</v>
+        <v>11.67095756530762</v>
       </c>
       <c r="C155" t="n">
-        <v>11.87461301320299</v>
+        <v>11.87461204288736</v>
       </c>
       <c r="D155" t="n">
-        <v>11.64746015334091</v>
+        <v>11.64745920158673</v>
       </c>
       <c r="E155" t="n">
-        <v>11.74928740045144</v>
+        <v>11.7492864403766</v>
       </c>
       <c r="F155" t="n">
         <v>2161500</v>
@@ -3532,16 +3532,16 @@
         <v>44872</v>
       </c>
       <c r="B156" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="C156" t="n">
-        <v>11.65529156485204</v>
+        <v>11.65529255720685</v>
       </c>
       <c r="D156" t="n">
-        <v>11.1226570379665</v>
+        <v>11.12265798497174</v>
       </c>
       <c r="E156" t="n">
-        <v>11.60829409312706</v>
+        <v>11.60829508148041</v>
       </c>
       <c r="F156" t="n">
         <v>3276500</v>
@@ -3592,16 +3592,16 @@
         <v>44875</v>
       </c>
       <c r="B159" t="n">
-        <v>10.70751571655273</v>
+        <v>10.70751667022705</v>
       </c>
       <c r="C159" t="n">
-        <v>11.10699160797338</v>
+        <v>11.10699259722736</v>
       </c>
       <c r="D159" t="n">
-        <v>10.49602821627141</v>
+        <v>10.4960291511094</v>
       </c>
       <c r="E159" t="n">
-        <v>11.04432881092694</v>
+        <v>11.04432979459981</v>
       </c>
       <c r="F159" t="n">
         <v>4341400</v>
@@ -3692,16 +3692,16 @@
         <v>44883</v>
       </c>
       <c r="B164" t="n">
-        <v>10.78584671020508</v>
+        <v>10.78584575653076</v>
       </c>
       <c r="C164" t="n">
-        <v>10.9895004672078</v>
+        <v>10.98949949552661</v>
       </c>
       <c r="D164" t="n">
-        <v>10.57435916827967</v>
+        <v>10.57435823330488</v>
       </c>
       <c r="E164" t="n">
-        <v>10.8093450769747</v>
+        <v>10.80934412122268</v>
       </c>
       <c r="F164" t="n">
         <v>3568700</v>
@@ -3712,16 +3712,16 @@
         <v>44886</v>
       </c>
       <c r="B165" t="n">
-        <v>11.27931499481201</v>
+        <v>11.2793140411377</v>
       </c>
       <c r="C165" t="n">
-        <v>11.32631247054852</v>
+        <v>11.32631151290053</v>
       </c>
       <c r="D165" t="n">
-        <v>10.80934397244457</v>
+        <v>10.80934305850665</v>
       </c>
       <c r="E165" t="n">
-        <v>10.84067537393573</v>
+        <v>10.84067445734872</v>
       </c>
       <c r="F165" t="n">
         <v>4939800</v>
@@ -3812,16 +3812,16 @@
         <v>44893</v>
       </c>
       <c r="B170" t="n">
-        <v>10.97383308410645</v>
+        <v>10.97383403778076</v>
       </c>
       <c r="C170" t="n">
-        <v>11.09915867941681</v>
+        <v>11.09915964398247</v>
       </c>
       <c r="D170" t="n">
-        <v>10.68401745820135</v>
+        <v>10.68401838668942</v>
       </c>
       <c r="E170" t="n">
-        <v>10.84067445233931</v>
+        <v>10.84067539444156</v>
       </c>
       <c r="F170" t="n">
         <v>4990000</v>
@@ -3952,16 +3952,16 @@
         <v>44902</v>
       </c>
       <c r="B177" t="n">
-        <v>10.65268707275391</v>
+        <v>10.65268611907959</v>
       </c>
       <c r="C177" t="n">
-        <v>10.80151104459258</v>
+        <v>10.80151007759491</v>
       </c>
       <c r="D177" t="n">
-        <v>10.42553422289516</v>
+        <v>10.42553328955654</v>
       </c>
       <c r="E177" t="n">
-        <v>10.42553422289516</v>
+        <v>10.42553328955654</v>
       </c>
       <c r="F177" t="n">
         <v>2865300</v>
@@ -4052,16 +4052,16 @@
         <v>44909</v>
       </c>
       <c r="B182" t="n">
-        <v>10.99733257293701</v>
+        <v>10.9973316192627</v>
       </c>
       <c r="C182" t="n">
-        <v>11.13832425560273</v>
+        <v>11.13832328970179</v>
       </c>
       <c r="D182" t="n">
-        <v>10.7388483193829</v>
+        <v>10.738847388124</v>
       </c>
       <c r="E182" t="n">
-        <v>11.01299864745522</v>
+        <v>11.01299769242237</v>
       </c>
       <c r="F182" t="n">
         <v>3892800</v>
@@ -4132,16 +4132,16 @@
         <v>44915</v>
       </c>
       <c r="B186" t="n">
-        <v>11.27931499481201</v>
+        <v>11.2793140411377</v>
       </c>
       <c r="C186" t="n">
-        <v>11.56129835523201</v>
+        <v>11.56129737771579</v>
       </c>
       <c r="D186" t="n">
-        <v>11.16965546309271</v>
+        <v>11.16965451869019</v>
       </c>
       <c r="E186" t="n">
-        <v>11.35764387203968</v>
+        <v>11.35764291174261</v>
       </c>
       <c r="F186" t="n">
         <v>4148100</v>
@@ -4152,16 +4152,16 @@
         <v>44916</v>
       </c>
       <c r="B187" t="n">
-        <v>11.58479785919189</v>
+        <v>11.58479690551758</v>
       </c>
       <c r="C187" t="n">
-        <v>11.7571209578444</v>
+        <v>11.75711998998425</v>
       </c>
       <c r="D187" t="n">
-        <v>11.15399048606043</v>
+        <v>11.15398956785069</v>
       </c>
       <c r="E187" t="n">
-        <v>11.4281408363258</v>
+        <v>11.42813989554768</v>
       </c>
       <c r="F187" t="n">
         <v>6348400</v>
@@ -4172,16 +4172,16 @@
         <v>44917</v>
       </c>
       <c r="B188" t="n">
-        <v>11.63179397583008</v>
+        <v>11.63179302215576</v>
       </c>
       <c r="C188" t="n">
-        <v>11.74928654245482</v>
+        <v>11.74928557914745</v>
       </c>
       <c r="D188" t="n">
-        <v>11.50646762523096</v>
+        <v>11.50646668183198</v>
       </c>
       <c r="E188" t="n">
-        <v>11.60046257493018</v>
+        <v>11.60046162382468</v>
       </c>
       <c r="F188" t="n">
         <v>2577900</v>
@@ -4232,16 +4232,16 @@
         <v>44922</v>
       </c>
       <c r="B191" t="n">
-        <v>11.52996730804443</v>
+        <v>11.52996635437012</v>
       </c>
       <c r="C191" t="n">
-        <v>11.60829544067951</v>
+        <v>11.60829448052647</v>
       </c>
       <c r="D191" t="n">
-        <v>11.34197814632122</v>
+        <v>11.34197720819598</v>
       </c>
       <c r="E191" t="n">
-        <v>11.60829544067951</v>
+        <v>11.60829448052647</v>
       </c>
       <c r="F191" t="n">
         <v>1633000</v>
@@ -4252,16 +4252,16 @@
         <v>44923</v>
       </c>
       <c r="B192" t="n">
-        <v>11.58479785919189</v>
+        <v>11.58479690551758</v>
       </c>
       <c r="C192" t="n">
-        <v>11.69445814869797</v>
+        <v>11.69445718599628</v>
       </c>
       <c r="D192" t="n">
-        <v>11.49863668336545</v>
+        <v>11.49863573678402</v>
       </c>
       <c r="E192" t="n">
-        <v>11.57696482129869</v>
+        <v>11.5769638682692</v>
       </c>
       <c r="F192" t="n">
         <v>2005900</v>
@@ -4272,16 +4272,16 @@
         <v>44924</v>
       </c>
       <c r="B193" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="C193" t="n">
-        <v>11.73362129131107</v>
+        <v>11.73362032145083</v>
       </c>
       <c r="D193" t="n">
-        <v>11.47513702901113</v>
+        <v>11.4751360805163</v>
       </c>
       <c r="E193" t="n">
-        <v>11.62396175397144</v>
+        <v>11.62396079317528</v>
       </c>
       <c r="F193" t="n">
         <v>2424800</v>
@@ -4312,16 +4312,16 @@
         <v>44929</v>
       </c>
       <c r="B195" t="n">
-        <v>11.13832473754883</v>
+        <v>11.13832378387451</v>
       </c>
       <c r="C195" t="n">
-        <v>11.32631315790418</v>
+        <v>11.32631218813412</v>
       </c>
       <c r="D195" t="n">
-        <v>11.05999585556764</v>
+        <v>11.05999490859992</v>
       </c>
       <c r="E195" t="n">
-        <v>11.30281479210966</v>
+        <v>11.30281382435154</v>
       </c>
       <c r="F195" t="n">
         <v>1562800</v>
@@ -4352,16 +4352,16 @@
         <v>44931</v>
       </c>
       <c r="B197" t="n">
-        <v>11.41247367858887</v>
+        <v>11.41247272491455</v>
       </c>
       <c r="C197" t="n">
-        <v>11.41247367858887</v>
+        <v>11.41247272491455</v>
       </c>
       <c r="D197" t="n">
-        <v>11.08349358825896</v>
+        <v>11.08349266207561</v>
       </c>
       <c r="E197" t="n">
-        <v>11.31064643662965</v>
+        <v>11.31064549146445</v>
       </c>
       <c r="F197" t="n">
         <v>4358300</v>
@@ -4412,16 +4412,16 @@
         <v>44936</v>
       </c>
       <c r="B200" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482620239258</v>
       </c>
       <c r="C200" t="n">
-        <v>11.1853210907164</v>
+        <v>11.1853220504394</v>
       </c>
       <c r="D200" t="n">
-        <v>10.69185094372897</v>
+        <v>10.69185186111124</v>
       </c>
       <c r="E200" t="n">
-        <v>11.08349384638571</v>
+        <v>11.08349479737172</v>
       </c>
       <c r="F200" t="n">
         <v>5832500</v>
@@ -4432,16 +4432,16 @@
         <v>44937</v>
       </c>
       <c r="B201" t="n">
-        <v>11.49863529205322</v>
+        <v>11.49863433837891</v>
       </c>
       <c r="C201" t="n">
-        <v>11.61612785823652</v>
+        <v>11.6161268948176</v>
       </c>
       <c r="D201" t="n">
-        <v>11.06782797104859</v>
+        <v>11.06782705310459</v>
       </c>
       <c r="E201" t="n">
-        <v>11.09132633488535</v>
+        <v>11.09132541499244</v>
       </c>
       <c r="F201" t="n">
         <v>4499200</v>
@@ -4472,16 +4472,16 @@
         <v>44939</v>
       </c>
       <c r="B203" t="n">
-        <v>11.58479785919189</v>
+        <v>11.58479690551758</v>
       </c>
       <c r="C203" t="n">
-        <v>11.78845236241762</v>
+        <v>11.78845139197822</v>
       </c>
       <c r="D203" t="n">
-        <v>11.4438061651126</v>
+        <v>11.44380522304489</v>
       </c>
       <c r="E203" t="n">
-        <v>11.7492879199512</v>
+        <v>11.74928695273586</v>
       </c>
       <c r="F203" t="n">
         <v>2269100</v>
@@ -4532,16 +4532,16 @@
         <v>44944</v>
       </c>
       <c r="B206" t="n">
-        <v>11.41247367858887</v>
+        <v>11.41247272491455</v>
       </c>
       <c r="C206" t="n">
-        <v>11.89027848678206</v>
+        <v>11.89027749318036</v>
       </c>
       <c r="D206" t="n">
-        <v>11.41247367858887</v>
+        <v>11.41247272491455</v>
       </c>
       <c r="E206" t="n">
-        <v>11.87461241248085</v>
+        <v>11.87461142018828</v>
       </c>
       <c r="F206" t="n">
         <v>3532000</v>
@@ -4572,16 +4572,16 @@
         <v>44946</v>
       </c>
       <c r="B208" t="n">
-        <v>11.58479785919189</v>
+        <v>11.58479690551758</v>
       </c>
       <c r="C208" t="n">
-        <v>11.68662511080476</v>
+        <v>11.6866241487479</v>
       </c>
       <c r="D208" t="n">
-        <v>11.48297060757903</v>
+        <v>11.48296966228726</v>
       </c>
       <c r="E208" t="n">
-        <v>11.65529370623154</v>
+        <v>11.65529274675392</v>
       </c>
       <c r="F208" t="n">
         <v>2012100</v>
@@ -4612,16 +4612,16 @@
         <v>44950</v>
       </c>
       <c r="B210" t="n">
-        <v>11.68662357330322</v>
+        <v>11.68662452697754</v>
       </c>
       <c r="C210" t="n">
-        <v>11.80411613824548</v>
+        <v>11.80411710150764</v>
       </c>
       <c r="D210" t="n">
-        <v>11.32631209461427</v>
+        <v>11.32631301888575</v>
       </c>
       <c r="E210" t="n">
-        <v>11.52996657104705</v>
+        <v>11.52996751193754</v>
       </c>
       <c r="F210" t="n">
         <v>5839900</v>
@@ -4672,16 +4672,16 @@
         <v>44953</v>
       </c>
       <c r="B213" t="n">
-        <v>11.98427200317383</v>
+        <v>11.98427295684814</v>
       </c>
       <c r="C213" t="n">
-        <v>12.23492320159854</v>
+        <v>12.23492417521897</v>
       </c>
       <c r="D213" t="n">
-        <v>11.92160920356765</v>
+        <v>11.92161015225544</v>
       </c>
       <c r="E213" t="n">
-        <v>11.96860592977254</v>
+        <v>11.96860688220019</v>
       </c>
       <c r="F213" t="n">
         <v>4160800</v>
@@ -4812,16 +4812,16 @@
         <v>44964</v>
       </c>
       <c r="B220" t="n">
-        <v>11.60046291351318</v>
+        <v>11.6004638671875</v>
       </c>
       <c r="C220" t="n">
-        <v>12.02343721150694</v>
+        <v>12.02343819995398</v>
       </c>
       <c r="D220" t="n">
-        <v>11.49080263366312</v>
+        <v>11.49080357832226</v>
       </c>
       <c r="E220" t="n">
-        <v>12.02343721150694</v>
+        <v>12.02343819995398</v>
       </c>
       <c r="F220" t="n">
         <v>5199600</v>
@@ -4932,16 +4932,16 @@
         <v>44972</v>
       </c>
       <c r="B226" t="n">
-        <v>11.75712013244629</v>
+        <v>11.75711917877197</v>
       </c>
       <c r="C226" t="n">
-        <v>11.92944247200145</v>
+        <v>11.92944150434928</v>
       </c>
       <c r="D226" t="n">
-        <v>11.63179452295179</v>
+        <v>11.63179357944321</v>
       </c>
       <c r="E226" t="n">
-        <v>11.66312592532541</v>
+        <v>11.6631249792754</v>
       </c>
       <c r="F226" t="n">
         <v>3961900</v>
@@ -5012,16 +5012,16 @@
         <v>44980</v>
       </c>
       <c r="B230" t="n">
-        <v>11.67879104614258</v>
+        <v>11.67879009246826</v>
       </c>
       <c r="C230" t="n">
-        <v>11.85111412964489</v>
+        <v>11.8511131618989</v>
       </c>
       <c r="D230" t="n">
-        <v>11.61612824250529</v>
+        <v>11.61612729394793</v>
       </c>
       <c r="E230" t="n">
-        <v>11.79628436321215</v>
+        <v>11.79628339994349</v>
       </c>
       <c r="F230" t="n">
         <v>3218000</v>
@@ -5032,16 +5032,16 @@
         <v>44981</v>
       </c>
       <c r="B231" t="n">
-        <v>11.67879104614258</v>
+        <v>11.67879009246826</v>
       </c>
       <c r="C231" t="n">
-        <v>11.89811085887308</v>
+        <v>11.89810988728941</v>
       </c>
       <c r="D231" t="n">
-        <v>11.51430099984482</v>
+        <v>11.51430005960253</v>
       </c>
       <c r="E231" t="n">
-        <v>11.72578852237032</v>
+        <v>11.72578756485825</v>
       </c>
       <c r="F231" t="n">
         <v>4705500</v>
@@ -5092,16 +5092,16 @@
         <v>44986</v>
       </c>
       <c r="B234" t="n">
-        <v>11.52996730804443</v>
+        <v>11.52996635437012</v>
       </c>
       <c r="C234" t="n">
-        <v>11.6552929178602</v>
+        <v>11.65529195381987</v>
       </c>
       <c r="D234" t="n">
-        <v>11.31847978123065</v>
+        <v>11.31847884504903</v>
       </c>
       <c r="E234" t="n">
-        <v>11.6004631503157</v>
+        <v>11.60046219081048</v>
       </c>
       <c r="F234" t="n">
         <v>8005300</v>
@@ -5112,16 +5112,16 @@
         <v>44987</v>
       </c>
       <c r="B235" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="C235" t="n">
-        <v>11.67879152264125</v>
+        <v>11.67879055731306</v>
       </c>
       <c r="D235" t="n">
-        <v>11.45947170096243</v>
+        <v>11.45947075376244</v>
       </c>
       <c r="E235" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="F235" t="n">
         <v>2250800</v>
@@ -5132,16 +5132,16 @@
         <v>44988</v>
       </c>
       <c r="B236" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="C236" t="n">
-        <v>11.64746011954428</v>
+        <v>11.64745915680582</v>
       </c>
       <c r="D236" t="n">
-        <v>11.45947170096243</v>
+        <v>11.45947075376244</v>
       </c>
       <c r="E236" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="F236" t="n">
         <v>1727100</v>
@@ -5192,16 +5192,16 @@
         <v>44993</v>
       </c>
       <c r="B239" t="n">
-        <v>11.63179397583008</v>
+        <v>11.63179302215576</v>
       </c>
       <c r="C239" t="n">
-        <v>11.63962626580541</v>
+        <v>11.63962531148894</v>
       </c>
       <c r="D239" t="n">
-        <v>11.48296926130592</v>
+        <v>11.48296831983353</v>
       </c>
       <c r="E239" t="n">
-        <v>11.62396093885522</v>
+        <v>11.62395998582313</v>
       </c>
       <c r="F239" t="n">
         <v>2946500</v>
@@ -5272,16 +5272,16 @@
         <v>44999</v>
       </c>
       <c r="B243" t="n">
-        <v>11.75712013244629</v>
+        <v>11.75711917877197</v>
       </c>
       <c r="C243" t="n">
-        <v>11.82761597453684</v>
+        <v>11.82761501514428</v>
       </c>
       <c r="D243" t="n">
-        <v>11.63962681329553</v>
+        <v>11.63962586915163</v>
       </c>
       <c r="E243" t="n">
-        <v>11.69445732769904</v>
+        <v>11.69445637910759</v>
       </c>
       <c r="F243" t="n">
         <v>2520000</v>
@@ -5312,16 +5312,16 @@
         <v>45001</v>
       </c>
       <c r="B245" t="n">
-        <v>11.67095851898193</v>
+        <v>11.67095756530762</v>
       </c>
       <c r="C245" t="n">
-        <v>11.81195020682722</v>
+        <v>11.81194924163198</v>
       </c>
       <c r="D245" t="n">
-        <v>11.63962711579405</v>
+        <v>11.63962616467993</v>
       </c>
       <c r="E245" t="n">
-        <v>11.81195020682722</v>
+        <v>11.81194924163198</v>
       </c>
       <c r="F245" t="n">
         <v>5495800</v>
@@ -5412,16 +5412,16 @@
         <v>45008</v>
       </c>
       <c r="B250" t="n">
-        <v>11.18532180786133</v>
+        <v>11.18532085418701</v>
       </c>
       <c r="C250" t="n">
-        <v>11.47513748476884</v>
+        <v>11.47513650638449</v>
       </c>
       <c r="D250" t="n">
-        <v>11.05999619049587</v>
+        <v>11.05999524750697</v>
       </c>
       <c r="E250" t="n">
-        <v>11.39680934741524</v>
+        <v>11.39680837570923</v>
       </c>
       <c r="F250" t="n">
         <v>4422500</v>
@@ -5532,16 +5532,16 @@
         <v>45016</v>
       </c>
       <c r="B256" t="n">
-        <v>11.49080181121826</v>
+        <v>11.49080276489258</v>
       </c>
       <c r="C256" t="n">
-        <v>11.61612740950566</v>
+        <v>11.61612837358132</v>
       </c>
       <c r="D256" t="n">
-        <v>11.30281341378716</v>
+        <v>11.30281435185946</v>
       </c>
       <c r="E256" t="n">
-        <v>11.42813901207456</v>
+        <v>11.42813996054821</v>
       </c>
       <c r="F256" t="n">
         <v>5155800</v>
@@ -5592,16 +5592,16 @@
         <v>45021</v>
       </c>
       <c r="B259" t="n">
-        <v>11.49080181121826</v>
+        <v>11.49080276489258</v>
       </c>
       <c r="C259" t="n">
-        <v>11.56913068364763</v>
+        <v>11.56913164382282</v>
       </c>
       <c r="D259" t="n">
-        <v>11.27931430385866</v>
+        <v>11.27931523998066</v>
       </c>
       <c r="E259" t="n">
-        <v>11.55346461036196</v>
+        <v>11.55346556923695</v>
       </c>
       <c r="F259" t="n">
         <v>4689800</v>
@@ -5612,16 +5612,16 @@
         <v>45022</v>
       </c>
       <c r="B260" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="C260" t="n">
-        <v>11.66312619459255</v>
+        <v>11.6631252305592</v>
       </c>
       <c r="D260" t="n">
-        <v>11.47513702901113</v>
+        <v>11.4751360805163</v>
       </c>
       <c r="E260" t="n">
-        <v>11.4908031040594</v>
+        <v>11.49080215426967</v>
       </c>
       <c r="F260" t="n">
         <v>4653400</v>
@@ -5652,16 +5652,16 @@
         <v>45027</v>
       </c>
       <c r="B262" t="n">
-        <v>11.76495265960693</v>
+        <v>11.76495170593262</v>
       </c>
       <c r="C262" t="n">
-        <v>12.01560386772655</v>
+        <v>12.01560289373429</v>
       </c>
       <c r="D262" t="n">
-        <v>11.71012214758113</v>
+        <v>11.7101211983514</v>
       </c>
       <c r="E262" t="n">
-        <v>11.82761546163684</v>
+        <v>11.82761450288304</v>
       </c>
       <c r="F262" t="n">
         <v>2622300</v>
@@ -5792,16 +5792,16 @@
         <v>45036</v>
       </c>
       <c r="B269" t="n">
-        <v>12.09393119812012</v>
+        <v>12.09393215179443</v>
       </c>
       <c r="C269" t="n">
-        <v>12.14092867003875</v>
+        <v>12.14092962741908</v>
       </c>
       <c r="D269" t="n">
-        <v>12.00777003776868</v>
+        <v>12.00777098464871</v>
       </c>
       <c r="E269" t="n">
-        <v>12.06259979917419</v>
+        <v>12.06260075037785</v>
       </c>
       <c r="F269" t="n">
         <v>4813100</v>
@@ -5912,16 +5912,16 @@
         <v>45048</v>
       </c>
       <c r="B275" t="n">
-        <v>12.39158153533936</v>
+        <v>12.39158058166504</v>
       </c>
       <c r="C275" t="n">
-        <v>12.65006579830664</v>
+        <v>12.650064824739</v>
       </c>
       <c r="D275" t="n">
-        <v>12.25059059453875</v>
+        <v>12.2505896517153</v>
       </c>
       <c r="E275" t="n">
-        <v>12.53257322313954</v>
+        <v>12.5325722586143</v>
       </c>
       <c r="F275" t="n">
         <v>5999300</v>
@@ -6032,16 +6032,16 @@
         <v>45056</v>
       </c>
       <c r="B281" t="n">
-        <v>11.86925220489502</v>
+        <v>11.86925315856934</v>
       </c>
       <c r="C281" t="n">
-        <v>12.0510569757826</v>
+        <v>12.05105794406462</v>
       </c>
       <c r="D281" t="n">
-        <v>11.69610500062852</v>
+        <v>11.69610594039075</v>
       </c>
       <c r="E281" t="n">
-        <v>12.0164275349293</v>
+        <v>12.0164285004289</v>
       </c>
       <c r="F281" t="n">
         <v>5308900</v>
@@ -6332,16 +6332,16 @@
         <v>45077</v>
       </c>
       <c r="B296" t="n">
-        <v>12.18957614898682</v>
+        <v>12.1895751953125</v>
       </c>
       <c r="C296" t="n">
-        <v>12.31077961880671</v>
+        <v>12.31077865564981</v>
       </c>
       <c r="D296" t="n">
-        <v>12.1636042717508</v>
+        <v>12.16360332010844</v>
       </c>
       <c r="E296" t="n">
-        <v>12.27615017394832</v>
+        <v>12.27614921350073</v>
       </c>
       <c r="F296" t="n">
         <v>3816500</v>
@@ -6372,16 +6372,16 @@
         <v>45079</v>
       </c>
       <c r="B298" t="n">
-        <v>12.17226123809814</v>
+        <v>12.17226028442383</v>
       </c>
       <c r="C298" t="n">
-        <v>12.33675088664238</v>
+        <v>12.3367499200806</v>
       </c>
       <c r="D298" t="n">
-        <v>12.07702965021844</v>
+        <v>12.07702870400534</v>
       </c>
       <c r="E298" t="n">
-        <v>12.3107790106893</v>
+        <v>12.31077804616237</v>
       </c>
       <c r="F298" t="n">
         <v>5725100</v>
@@ -6572,16 +6572,16 @@
         <v>45096</v>
       </c>
       <c r="B308" t="n">
-        <v>12.61378574371338</v>
+        <v>12.6137866973877</v>
       </c>
       <c r="C308" t="n">
-        <v>12.80424808345158</v>
+        <v>12.80424905152594</v>
       </c>
       <c r="D308" t="n">
-        <v>12.38869478834751</v>
+        <v>12.38869572500366</v>
       </c>
       <c r="E308" t="n">
-        <v>12.80424808345158</v>
+        <v>12.80424905152594</v>
       </c>
       <c r="F308" t="n">
         <v>3301400</v>
@@ -7092,16 +7092,16 @@
         <v>45132</v>
       </c>
       <c r="B334" t="n">
-        <v>12.17226123809814</v>
+        <v>12.17226028442383</v>
       </c>
       <c r="C334" t="n">
-        <v>12.47526865923354</v>
+        <v>12.47526768181915</v>
       </c>
       <c r="D334" t="n">
-        <v>12.16360367090343</v>
+        <v>12.16360271790742</v>
       </c>
       <c r="E334" t="n">
-        <v>12.41466734013267</v>
+        <v>12.41466636746628</v>
       </c>
       <c r="F334" t="n">
         <v>2710400</v>
@@ -7192,16 +7192,16 @@
         <v>45139</v>
       </c>
       <c r="B339" t="n">
-        <v>12.12897396087646</v>
+        <v>12.12897491455078</v>
       </c>
       <c r="C339" t="n">
-        <v>12.38003762458143</v>
+        <v>12.38003859799633</v>
       </c>
       <c r="D339" t="n">
-        <v>12.08568695148643</v>
+        <v>12.08568790175718</v>
       </c>
       <c r="E339" t="n">
-        <v>12.12031639387225</v>
+        <v>12.12031734686584</v>
       </c>
       <c r="F339" t="n">
         <v>5884200</v>
@@ -7332,16 +7332,16 @@
         <v>45148</v>
       </c>
       <c r="B346" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C346" t="n">
-        <v>12.09434452900206</v>
+        <v>12.09434549372545</v>
       </c>
       <c r="D346" t="n">
-        <v>11.88656704887551</v>
+        <v>11.88656799702522</v>
       </c>
       <c r="E346" t="n">
-        <v>12.01642807715848</v>
+        <v>12.01642903566675</v>
       </c>
       <c r="F346" t="n">
         <v>2835300</v>
@@ -7432,16 +7432,16 @@
         <v>45155</v>
       </c>
       <c r="B351" t="n">
-        <v>11.71341991424561</v>
+        <v>11.71341896057129</v>
       </c>
       <c r="C351" t="n">
-        <v>11.78267879953539</v>
+        <v>11.7826778402222</v>
       </c>
       <c r="D351" t="n">
-        <v>11.66147616309379</v>
+        <v>11.66147521364859</v>
       </c>
       <c r="E351" t="n">
-        <v>11.73073504838357</v>
+        <v>11.7307340932995</v>
       </c>
       <c r="F351" t="n">
         <v>2345000</v>
@@ -7632,16 +7632,16 @@
         <v>45169</v>
       </c>
       <c r="B361" t="n">
-        <v>11.78267860412598</v>
+        <v>11.78267955780029</v>
       </c>
       <c r="C361" t="n">
-        <v>12.1203162835374</v>
+        <v>12.12031726453966</v>
       </c>
       <c r="D361" t="n">
-        <v>11.78267860412598</v>
+        <v>11.78267955780029</v>
       </c>
       <c r="E361" t="n">
-        <v>12.1203162835374</v>
+        <v>12.12031726453966</v>
       </c>
       <c r="F361" t="n">
         <v>3236500</v>
@@ -7652,16 +7652,16 @@
         <v>45170</v>
       </c>
       <c r="B362" t="n">
-        <v>12.04239940643311</v>
+        <v>12.04240036010742</v>
       </c>
       <c r="C362" t="n">
-        <v>12.04239940643311</v>
+        <v>12.04240036010742</v>
       </c>
       <c r="D362" t="n">
-        <v>11.89522407643217</v>
+        <v>11.89522501845123</v>
       </c>
       <c r="E362" t="n">
-        <v>11.90388164305129</v>
+        <v>11.90388258575596</v>
       </c>
       <c r="F362" t="n">
         <v>3740800</v>
@@ -7712,16 +7712,16 @@
         <v>45175</v>
       </c>
       <c r="B365" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C365" t="n">
-        <v>12.02508564417022</v>
+        <v>12.02508660336907</v>
       </c>
       <c r="D365" t="n">
-        <v>11.81730816404367</v>
+        <v>11.81730910666884</v>
       </c>
       <c r="E365" t="n">
-        <v>11.9385116253149</v>
+        <v>11.93851257760805</v>
       </c>
       <c r="F365" t="n">
         <v>2473500</v>
@@ -7812,16 +7812,16 @@
         <v>45183</v>
       </c>
       <c r="B370" t="n">
-        <v>12.21554660797119</v>
+        <v>12.21554756164551</v>
       </c>
       <c r="C370" t="n">
-        <v>12.25017604880902</v>
+        <v>12.25017700518688</v>
       </c>
       <c r="D370" t="n">
-        <v>12.09434397785428</v>
+        <v>12.09434492206624</v>
       </c>
       <c r="E370" t="n">
-        <v>12.09434397785428</v>
+        <v>12.09434492206624</v>
       </c>
       <c r="F370" t="n">
         <v>2498700</v>
@@ -7912,16 +7912,16 @@
         <v>45190</v>
       </c>
       <c r="B375" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C375" t="n">
-        <v>12.03374238555092</v>
+        <v>12.0337433454403</v>
       </c>
       <c r="D375" t="n">
-        <v>11.8779103074948</v>
+        <v>11.877911254954</v>
       </c>
       <c r="E375" t="n">
-        <v>12.02508564417022</v>
+        <v>12.02508660336907</v>
       </c>
       <c r="F375" t="n">
         <v>4405700</v>
@@ -7932,16 +7932,16 @@
         <v>45191</v>
       </c>
       <c r="B376" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C376" t="n">
-        <v>12.10300127038276</v>
+        <v>12.10300223579667</v>
       </c>
       <c r="D376" t="n">
-        <v>11.92985405830317</v>
+        <v>11.92985500990573</v>
       </c>
       <c r="E376" t="n">
-        <v>12.02508564417022</v>
+        <v>12.02508660336907</v>
       </c>
       <c r="F376" t="n">
         <v>2812600</v>
@@ -8012,16 +8012,16 @@
         <v>45197</v>
       </c>
       <c r="B380" t="n">
-        <v>11.78267860412598</v>
+        <v>11.78267955780029</v>
       </c>
       <c r="C380" t="n">
-        <v>11.86059505519254</v>
+        <v>11.86059601517331</v>
       </c>
       <c r="D380" t="n">
-        <v>11.73073485383562</v>
+        <v>11.73073580330568</v>
       </c>
       <c r="E380" t="n">
-        <v>11.85193748826714</v>
+        <v>11.85193844754717</v>
       </c>
       <c r="F380" t="n">
         <v>2404900</v>
@@ -8132,16 +8132,16 @@
         <v>45205</v>
       </c>
       <c r="B386" t="n">
-        <v>11.67879104614258</v>
+        <v>11.67879009246826</v>
       </c>
       <c r="C386" t="n">
-        <v>11.70476374862726</v>
+        <v>11.70476279283205</v>
       </c>
       <c r="D386" t="n">
-        <v>11.61818972494048</v>
+        <v>11.61818877621478</v>
       </c>
       <c r="E386" t="n">
-        <v>11.68744861363747</v>
+        <v>11.68744765925619</v>
       </c>
       <c r="F386" t="n">
         <v>3573900</v>
@@ -8252,16 +8252,16 @@
         <v>45216</v>
       </c>
       <c r="B392" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C392" t="n">
-        <v>12.10300127038276</v>
+        <v>12.10300223579667</v>
       </c>
       <c r="D392" t="n">
-        <v>11.88656704887551</v>
+        <v>11.88656799702522</v>
       </c>
       <c r="E392" t="n">
-        <v>11.97314106773082</v>
+        <v>11.97314202278624</v>
       </c>
       <c r="F392" t="n">
         <v>5165000</v>
@@ -8272,16 +8272,16 @@
         <v>45217</v>
       </c>
       <c r="B393" t="n">
-        <v>11.66147613525391</v>
+        <v>11.66147518157959</v>
       </c>
       <c r="C393" t="n">
-        <v>11.95582680984828</v>
+        <v>11.955825832102</v>
       </c>
       <c r="D393" t="n">
-        <v>11.66147613525391</v>
+        <v>11.66147518157959</v>
       </c>
       <c r="E393" t="n">
-        <v>11.95582680984828</v>
+        <v>11.955825832102</v>
       </c>
       <c r="F393" t="n">
         <v>13737300</v>
@@ -8312,16 +8312,16 @@
         <v>45219</v>
       </c>
       <c r="B395" t="n">
-        <v>11.76536464691162</v>
+        <v>11.7653636932373</v>
       </c>
       <c r="C395" t="n">
-        <v>11.91253998651014</v>
+        <v>11.91253902090612</v>
       </c>
       <c r="D395" t="n">
-        <v>11.67013305915314</v>
+        <v>11.67013211319808</v>
       </c>
       <c r="E395" t="n">
-        <v>11.67013305915314</v>
+        <v>11.67013211319808</v>
       </c>
       <c r="F395" t="n">
         <v>6261200</v>
@@ -8332,16 +8332,16 @@
         <v>45222</v>
       </c>
       <c r="B396" t="n">
-        <v>11.72207736968994</v>
+        <v>11.72207832336426</v>
       </c>
       <c r="C396" t="n">
-        <v>11.90388214825212</v>
+        <v>11.90388311671755</v>
       </c>
       <c r="D396" t="n">
-        <v>11.72207736968994</v>
+        <v>11.72207832336426</v>
       </c>
       <c r="E396" t="n">
-        <v>11.77402194597815</v>
+        <v>11.77402290387853</v>
       </c>
       <c r="F396" t="n">
         <v>3068100</v>
@@ -8352,16 +8352,16 @@
         <v>45223</v>
       </c>
       <c r="B397" t="n">
-        <v>11.63550281524658</v>
+        <v>11.6355037689209</v>
       </c>
       <c r="C397" t="n">
-        <v>11.81730758543626</v>
+        <v>11.81730855401174</v>
       </c>
       <c r="D397" t="n">
-        <v>11.54892962626116</v>
+        <v>11.54893057283972</v>
       </c>
       <c r="E397" t="n">
-        <v>11.80865084447942</v>
+        <v>11.80865181234537</v>
       </c>
       <c r="F397" t="n">
         <v>3637500</v>
@@ -8392,16 +8392,16 @@
         <v>45225</v>
       </c>
       <c r="B399" t="n">
-        <v>11.67879104614258</v>
+        <v>11.67879009246826</v>
       </c>
       <c r="C399" t="n">
-        <v>11.73073562548086</v>
+        <v>11.73073466756482</v>
       </c>
       <c r="D399" t="n">
-        <v>11.54893083624348</v>
+        <v>11.54892989317337</v>
       </c>
       <c r="E399" t="n">
-        <v>11.54893083624348</v>
+        <v>11.54892989317337</v>
       </c>
       <c r="F399" t="n">
         <v>2627000</v>
@@ -8432,16 +8432,16 @@
         <v>45229</v>
       </c>
       <c r="B401" t="n">
-        <v>11.49698543548584</v>
+        <v>11.49698638916016</v>
       </c>
       <c r="C401" t="n">
-        <v>11.64416076985956</v>
+        <v>11.64416173574207</v>
       </c>
       <c r="D401" t="n">
-        <v>11.47101356048784</v>
+        <v>11.47101451200779</v>
       </c>
       <c r="E401" t="n">
-        <v>11.57490188611087</v>
+        <v>11.57490284624835</v>
       </c>
       <c r="F401" t="n">
         <v>4549600</v>
@@ -8472,16 +8472,16 @@
         <v>45231</v>
       </c>
       <c r="B403" t="n">
-        <v>11.66147613525391</v>
+        <v>11.66147518157959</v>
       </c>
       <c r="C403" t="n">
-        <v>11.74804932884394</v>
+        <v>11.74804836808967</v>
       </c>
       <c r="D403" t="n">
-        <v>11.28055144143846</v>
+        <v>11.28055051891613</v>
       </c>
       <c r="E403" t="n">
-        <v>11.55758780756725</v>
+        <v>11.55758686238891</v>
       </c>
       <c r="F403" t="n">
         <v>7182500</v>
@@ -8592,16 +8592,16 @@
         <v>45240</v>
       </c>
       <c r="B409" t="n">
-        <v>11.78267860412598</v>
+        <v>11.78267955780029</v>
       </c>
       <c r="C409" t="n">
-        <v>11.86059505519254</v>
+        <v>11.86059601517331</v>
       </c>
       <c r="D409" t="n">
-        <v>11.69610541176504</v>
+        <v>11.69610635843224</v>
       </c>
       <c r="E409" t="n">
-        <v>11.69610541176504</v>
+        <v>11.69610635843224</v>
       </c>
       <c r="F409" t="n">
         <v>3430000</v>
@@ -8632,16 +8632,16 @@
         <v>45244</v>
       </c>
       <c r="B411" t="n">
-        <v>12.18957614898682</v>
+        <v>12.1895751953125</v>
       </c>
       <c r="C411" t="n">
-        <v>12.25017747108122</v>
+        <v>12.25017651266564</v>
       </c>
       <c r="D411" t="n">
-        <v>11.86059601001661</v>
+        <v>11.86059508208067</v>
       </c>
       <c r="E411" t="n">
-        <v>11.86059601001661</v>
+        <v>11.86059508208067</v>
       </c>
       <c r="F411" t="n">
         <v>3963500</v>
@@ -8752,16 +8752,16 @@
         <v>45253</v>
       </c>
       <c r="B417" t="n">
-        <v>12.561842918396</v>
+        <v>12.56184196472168</v>
       </c>
       <c r="C417" t="n">
-        <v>12.76961958122722</v>
+        <v>12.76961861177884</v>
       </c>
       <c r="D417" t="n">
-        <v>12.46661132870839</v>
+        <v>12.46661038226389</v>
       </c>
       <c r="E417" t="n">
-        <v>12.76961958122722</v>
+        <v>12.76961861177884</v>
       </c>
       <c r="F417" t="n">
         <v>9122900</v>
@@ -8832,16 +8832,16 @@
         <v>45259</v>
       </c>
       <c r="B421" t="n">
-        <v>12.561842918396</v>
+        <v>12.56184196472168</v>
       </c>
       <c r="C421" t="n">
-        <v>12.75230444650908</v>
+        <v>12.75230347837524</v>
       </c>
       <c r="D421" t="n">
-        <v>12.561842918396</v>
+        <v>12.56184196472168</v>
       </c>
       <c r="E421" t="n">
-        <v>12.72633257006295</v>
+        <v>12.72633160390085</v>
       </c>
       <c r="F421" t="n">
         <v>5869600</v>
@@ -8912,16 +8912,16 @@
         <v>45265</v>
       </c>
       <c r="B425" t="n">
-        <v>13.15919971466064</v>
+        <v>13.15920066833496</v>
       </c>
       <c r="C425" t="n">
-        <v>13.20248672149667</v>
+        <v>13.20248767830808</v>
       </c>
       <c r="D425" t="n">
-        <v>12.9254511987557</v>
+        <v>12.92545213548978</v>
       </c>
       <c r="E425" t="n">
-        <v>12.96008063909832</v>
+        <v>12.96008157834207</v>
       </c>
       <c r="F425" t="n">
         <v>6696500</v>
@@ -8932,16 +8932,16 @@
         <v>45266</v>
       </c>
       <c r="B426" t="n">
-        <v>13.07262706756592</v>
+        <v>13.07262802124023</v>
       </c>
       <c r="C426" t="n">
-        <v>13.2717461513678</v>
+        <v>13.27174711956826</v>
       </c>
       <c r="D426" t="n">
-        <v>13.04665436701096</v>
+        <v>13.04665531879052</v>
       </c>
       <c r="E426" t="n">
-        <v>13.21114483466828</v>
+        <v>13.21114579844774</v>
       </c>
       <c r="F426" t="n">
         <v>5861300</v>
@@ -22112,19 +22112,39 @@
         <v>46232</v>
       </c>
       <c r="B1085" t="n">
-        <v>11.11</v>
+        <v>11.10999965667725</v>
       </c>
       <c r="C1085" t="n">
-        <v>11.47</v>
+        <v>11.47000026702881</v>
       </c>
       <c r="D1085" t="n">
-        <v>11.08</v>
+        <v>11.07999992370605</v>
       </c>
       <c r="E1085" t="n">
-        <v>11.45</v>
+        <v>11.44999980926514</v>
       </c>
       <c r="F1085" t="n">
         <v>2114700</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B1086" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="C1086" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="D1086" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="E1086" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="F1086" t="n">
+        <v>2543000</v>
       </c>
     </row>
   </sheetData>

--- a/database/AURE3.xlsx
+++ b/database/AURE3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1086"/>
+  <dimension ref="A1:F1087"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>44649</v>
       </c>
       <c r="B3" t="n">
-        <v>12.91280841827393</v>
+        <v>12.91280937194824</v>
       </c>
       <c r="C3" t="n">
-        <v>13.21618114634902</v>
+        <v>13.2161821224289</v>
       </c>
       <c r="D3" t="n">
-        <v>12.61721318462629</v>
+        <v>12.61721411646944</v>
       </c>
       <c r="E3" t="n">
-        <v>12.74945284521847</v>
+        <v>12.74945378682817</v>
       </c>
       <c r="F3" t="n">
         <v>4714100</v>
@@ -512,16 +512,16 @@
         <v>44651</v>
       </c>
       <c r="B5" t="n">
-        <v>12.43830299377441</v>
+        <v>12.4383020401001</v>
       </c>
       <c r="C5" t="n">
-        <v>12.82724305543223</v>
+        <v>12.82724207193696</v>
       </c>
       <c r="D5" t="n">
-        <v>12.05714191139238</v>
+        <v>12.05714098694259</v>
       </c>
       <c r="E5" t="n">
-        <v>12.41496679779135</v>
+        <v>12.41496584590627</v>
       </c>
       <c r="F5" t="n">
         <v>3876100</v>
@@ -552,16 +552,16 @@
         <v>44655</v>
       </c>
       <c r="B7" t="n">
-        <v>12.42274475097656</v>
+        <v>12.42274379730225</v>
       </c>
       <c r="C7" t="n">
-        <v>12.7338972197089</v>
+        <v>12.73389624214791</v>
       </c>
       <c r="D7" t="n">
-        <v>12.33717746969916</v>
+        <v>12.3371765225937</v>
       </c>
       <c r="E7" t="n">
-        <v>12.54720469988757</v>
+        <v>12.54720373665866</v>
       </c>
       <c r="F7" t="n">
         <v>2842400</v>
@@ -692,16 +692,16 @@
         <v>44664</v>
       </c>
       <c r="B14" t="n">
-        <v>12.10381317138672</v>
+        <v>12.10381412506104</v>
       </c>
       <c r="C14" t="n">
-        <v>12.55498277187146</v>
+        <v>12.55498376109398</v>
       </c>
       <c r="D14" t="n">
-        <v>12.0882552152437</v>
+        <v>12.08825616769219</v>
       </c>
       <c r="E14" t="n">
-        <v>12.39162868343488</v>
+        <v>12.39162965978653</v>
       </c>
       <c r="F14" t="n">
         <v>4421300</v>
@@ -712,16 +712,16 @@
         <v>44665</v>
       </c>
       <c r="B15" t="n">
-        <v>12.11159229278564</v>
+        <v>12.11159324645996</v>
       </c>
       <c r="C15" t="n">
-        <v>12.36829265315281</v>
+        <v>12.36829362703988</v>
       </c>
       <c r="D15" t="n">
-        <v>12.04936194735386</v>
+        <v>12.04936289612812</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08047712006975</v>
+        <v>12.08047807129404</v>
       </c>
       <c r="F15" t="n">
         <v>2077400</v>
@@ -752,16 +752,16 @@
         <v>44670</v>
       </c>
       <c r="B17" t="n">
-        <v>12.10381317138672</v>
+        <v>12.10381412506104</v>
       </c>
       <c r="C17" t="n">
-        <v>12.60165664030051</v>
+        <v>12.60165763320052</v>
       </c>
       <c r="D17" t="n">
-        <v>12.00268868198966</v>
+        <v>12.00268962769625</v>
       </c>
       <c r="E17" t="n">
-        <v>12.43830106817557</v>
+        <v>12.4383020482046</v>
       </c>
       <c r="F17" t="n">
         <v>3118100</v>
@@ -792,16 +792,16 @@
         <v>44673</v>
       </c>
       <c r="B19" t="n">
-        <v>12.22049617767334</v>
+        <v>12.22049522399902</v>
       </c>
       <c r="C19" t="n">
-        <v>12.33717789380641</v>
+        <v>12.33717693102638</v>
       </c>
       <c r="D19" t="n">
-        <v>11.80044096101231</v>
+        <v>11.80044004011864</v>
       </c>
       <c r="E19" t="n">
-        <v>12.01824717732137</v>
+        <v>12.01824623943035</v>
       </c>
       <c r="F19" t="n">
         <v>11382300</v>
@@ -812,16 +812,16 @@
         <v>44676</v>
       </c>
       <c r="B20" t="n">
-        <v>12.39162921905518</v>
+        <v>12.39163017272949</v>
       </c>
       <c r="C20" t="n">
-        <v>12.39162921905518</v>
+        <v>12.39163017272949</v>
       </c>
       <c r="D20" t="n">
-        <v>11.90156470703017</v>
+        <v>11.90156562298855</v>
       </c>
       <c r="E20" t="n">
-        <v>12.11937090953766</v>
+        <v>12.11937184225865</v>
       </c>
       <c r="F20" t="n">
         <v>2683100</v>
@@ -832,16 +832,16 @@
         <v>44677</v>
       </c>
       <c r="B21" t="n">
-        <v>11.95601654052734</v>
+        <v>11.95601558685303</v>
       </c>
       <c r="C21" t="n">
-        <v>12.4383020930363</v>
+        <v>12.43830110089237</v>
       </c>
       <c r="D21" t="n">
-        <v>11.86267102151054</v>
+        <v>11.86267007528195</v>
       </c>
       <c r="E21" t="n">
-        <v>12.32939935843881</v>
+        <v>12.32939837498153</v>
       </c>
       <c r="F21" t="n">
         <v>2627000</v>
@@ -872,16 +872,16 @@
         <v>44679</v>
       </c>
       <c r="B23" t="n">
-        <v>11.90934371948242</v>
+        <v>11.90934276580811</v>
       </c>
       <c r="C23" t="n">
-        <v>12.08825577230682</v>
+        <v>12.08825480430562</v>
       </c>
       <c r="D23" t="n">
-        <v>11.49706676482372</v>
+        <v>11.49706584416364</v>
       </c>
       <c r="E23" t="n">
-        <v>12.08825577230682</v>
+        <v>12.08825480430562</v>
       </c>
       <c r="F23" t="n">
         <v>3489600</v>
@@ -912,16 +912,16 @@
         <v>44683</v>
       </c>
       <c r="B25" t="n">
-        <v>11.1703577041626</v>
+        <v>11.17035675048828</v>
       </c>
       <c r="C25" t="n">
-        <v>11.47373120303561</v>
+        <v>11.47373022346064</v>
       </c>
       <c r="D25" t="n">
-        <v>10.96033046789994</v>
+        <v>10.96032953215679</v>
       </c>
       <c r="E25" t="n">
-        <v>11.42705807173043</v>
+        <v>11.4270570961402</v>
       </c>
       <c r="F25" t="n">
         <v>2883200</v>
@@ -1012,16 +1012,16 @@
         <v>44690</v>
       </c>
       <c r="B30" t="n">
-        <v>11.07566165924072</v>
+        <v>11.07565975189209</v>
       </c>
       <c r="C30" t="n">
-        <v>11.13049142708364</v>
+        <v>11.13048951029273</v>
       </c>
       <c r="D30" t="n">
-        <v>10.80934436343302</v>
+        <v>10.8093425019471</v>
       </c>
       <c r="E30" t="n">
-        <v>10.99733277917979</v>
+        <v>10.99733088532023</v>
       </c>
       <c r="F30" t="n">
         <v>1545300</v>
@@ -1112,16 +1112,16 @@
         <v>44697</v>
       </c>
       <c r="B35" t="n">
-        <v>11.2793140411377</v>
+        <v>11.27931499481201</v>
       </c>
       <c r="C35" t="n">
-        <v>11.41247267296636</v>
+        <v>11.41247363789934</v>
       </c>
       <c r="D35" t="n">
-        <v>11.11482401046696</v>
+        <v>11.11482495023352</v>
       </c>
       <c r="E35" t="n">
-        <v>11.17748755515057</v>
+        <v>11.17748850021538</v>
       </c>
       <c r="F35" t="n">
         <v>2419100</v>
@@ -1152,16 +1152,16 @@
         <v>44699</v>
       </c>
       <c r="B37" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C37" t="n">
-        <v>11.59262882548476</v>
+        <v>11.5926298208571</v>
       </c>
       <c r="D37" t="n">
-        <v>11.03649593344125</v>
+        <v>11.03649688106261</v>
       </c>
       <c r="E37" t="n">
-        <v>11.51429995454926</v>
+        <v>11.51430094319608</v>
       </c>
       <c r="F37" t="n">
         <v>1959900</v>
@@ -1192,16 +1192,16 @@
         <v>44701</v>
       </c>
       <c r="B39" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C39" t="n">
-        <v>11.34197688669085</v>
+        <v>11.34197786054158</v>
       </c>
       <c r="D39" t="n">
-        <v>10.86417286558284</v>
+        <v>10.86417379840811</v>
       </c>
       <c r="E39" t="n">
-        <v>11.34197688669085</v>
+        <v>11.34197786054158</v>
       </c>
       <c r="F39" t="n">
         <v>1777400</v>
@@ -1272,16 +1272,16 @@
         <v>44707</v>
       </c>
       <c r="B43" t="n">
-        <v>11.25581645965576</v>
+        <v>11.25581550598145</v>
       </c>
       <c r="C43" t="n">
-        <v>11.44380486575034</v>
+        <v>11.44380389614828</v>
       </c>
       <c r="D43" t="n">
-        <v>11.20881973163188</v>
+        <v>11.20881878193947</v>
       </c>
       <c r="E43" t="n">
-        <v>11.33414533569493</v>
+        <v>11.33414437538402</v>
       </c>
       <c r="F43" t="n">
         <v>1248800</v>
@@ -1292,16 +1292,16 @@
         <v>44708</v>
       </c>
       <c r="B44" t="n">
-        <v>11.11482620239258</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C44" t="n">
-        <v>11.42030796159561</v>
+        <v>11.42030698171035</v>
       </c>
       <c r="D44" t="n">
-        <v>11.11482620239258</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="E44" t="n">
-        <v>11.26365093649135</v>
+        <v>11.26364997004757</v>
       </c>
       <c r="F44" t="n">
         <v>2224600</v>
@@ -1312,16 +1312,16 @@
         <v>44711</v>
       </c>
       <c r="B45" t="n">
-        <v>11.09915924072266</v>
+        <v>11.09916019439697</v>
       </c>
       <c r="C45" t="n">
-        <v>11.27148231648886</v>
+        <v>11.27148328496971</v>
       </c>
       <c r="D45" t="n">
-        <v>11.0286634030456</v>
+        <v>11.02866435066269</v>
       </c>
       <c r="E45" t="n">
-        <v>11.15398900469392</v>
+        <v>11.15398996307938</v>
       </c>
       <c r="F45" t="n">
         <v>1940200</v>
@@ -1412,16 +1412,16 @@
         <v>44718</v>
       </c>
       <c r="B50" t="n">
-        <v>10.61352252960205</v>
+        <v>10.61352157592773</v>
       </c>
       <c r="C50" t="n">
-        <v>10.91117121735836</v>
+        <v>10.91117023693893</v>
       </c>
       <c r="D50" t="n">
-        <v>10.4568655220986</v>
+        <v>10.45686458250065</v>
       </c>
       <c r="E50" t="n">
-        <v>10.8171770128563</v>
+        <v>10.81717604088268</v>
       </c>
       <c r="F50" t="n">
         <v>3175000</v>
@@ -1432,16 +1432,16 @@
         <v>44719</v>
       </c>
       <c r="B51" t="n">
-        <v>10.85634136199951</v>
+        <v>10.8563404083252</v>
       </c>
       <c r="C51" t="n">
-        <v>10.87984047479791</v>
+        <v>10.87983951905932</v>
       </c>
       <c r="D51" t="n">
-        <v>10.53519429041721</v>
+        <v>10.53519336495403</v>
       </c>
       <c r="E51" t="n">
-        <v>10.59002480661389</v>
+        <v>10.59002387633413</v>
       </c>
       <c r="F51" t="n">
         <v>2760900</v>
@@ -1552,16 +1552,16 @@
         <v>44727</v>
       </c>
       <c r="B57" t="n">
-        <v>10.84067535400391</v>
+        <v>10.84067440032959</v>
       </c>
       <c r="C57" t="n">
-        <v>10.84850839111218</v>
+        <v>10.84850743674878</v>
       </c>
       <c r="D57" t="n">
-        <v>10.44119942547642</v>
+        <v>10.44119850694474</v>
       </c>
       <c r="E57" t="n">
-        <v>10.55085970399363</v>
+        <v>10.55085877581493</v>
       </c>
       <c r="F57" t="n">
         <v>3153700</v>
@@ -1612,16 +1612,16 @@
         <v>44733</v>
       </c>
       <c r="B60" t="n">
-        <v>10.63702011108398</v>
+        <v>10.6370210647583</v>
       </c>
       <c r="C60" t="n">
-        <v>10.7153489825704</v>
+        <v>10.71534994326738</v>
       </c>
       <c r="D60" t="n">
-        <v>10.51952755085384</v>
+        <v>10.51952849399422</v>
       </c>
       <c r="E60" t="n">
-        <v>10.69184987292479</v>
+        <v>10.69185083151493</v>
       </c>
       <c r="F60" t="n">
         <v>1455700</v>
@@ -1652,16 +1652,16 @@
         <v>44735</v>
       </c>
       <c r="B62" t="n">
-        <v>10.63702011108398</v>
+        <v>10.6370210647583</v>
       </c>
       <c r="C62" t="n">
-        <v>10.89550434118989</v>
+        <v>10.89550531803891</v>
       </c>
       <c r="D62" t="n">
-        <v>10.55085895004851</v>
+        <v>10.55085989599795</v>
       </c>
       <c r="E62" t="n">
-        <v>10.8798390150923</v>
+        <v>10.87983999053682</v>
       </c>
       <c r="F62" t="n">
         <v>3444100</v>
@@ -1672,16 +1672,16 @@
         <v>44736</v>
       </c>
       <c r="B63" t="n">
-        <v>10.48819732666016</v>
+        <v>10.48819637298584</v>
       </c>
       <c r="C63" t="n">
-        <v>10.70751714559343</v>
+        <v>10.70751617197673</v>
       </c>
       <c r="D63" t="n">
-        <v>10.42553452125065</v>
+        <v>10.42553357327416</v>
       </c>
       <c r="E63" t="n">
-        <v>10.70751714559343</v>
+        <v>10.70751617197673</v>
       </c>
       <c r="F63" t="n">
         <v>807500</v>
@@ -1712,16 +1712,16 @@
         <v>44740</v>
       </c>
       <c r="B65" t="n">
-        <v>10.61352252960205</v>
+        <v>10.61352157592773</v>
       </c>
       <c r="C65" t="n">
-        <v>10.86417374160756</v>
+        <v>10.86417276541107</v>
       </c>
       <c r="D65" t="n">
-        <v>10.47253084934918</v>
+        <v>10.47252990834362</v>
       </c>
       <c r="E65" t="n">
-        <v>10.5273606152255</v>
+        <v>10.52735966929324</v>
       </c>
       <c r="F65" t="n">
         <v>5362200</v>
@@ -1732,16 +1732,16 @@
         <v>44741</v>
       </c>
       <c r="B66" t="n">
-        <v>10.6840181350708</v>
+        <v>10.68401718139648</v>
       </c>
       <c r="C66" t="n">
-        <v>10.6840181350708</v>
+        <v>10.68401718139648</v>
       </c>
       <c r="D66" t="n">
-        <v>10.53519342096158</v>
+        <v>10.53519248057162</v>
       </c>
       <c r="E66" t="n">
-        <v>10.62918762339921</v>
+        <v>10.62918667461916</v>
       </c>
       <c r="F66" t="n">
         <v>1613700</v>
@@ -1772,16 +1772,16 @@
         <v>44743</v>
       </c>
       <c r="B68" t="n">
-        <v>10.6840181350708</v>
+        <v>10.68401718139648</v>
       </c>
       <c r="C68" t="n">
-        <v>10.84067513913352</v>
+        <v>10.84067417147572</v>
       </c>
       <c r="D68" t="n">
-        <v>10.54302645791459</v>
+        <v>10.54302551682544</v>
       </c>
       <c r="E68" t="n">
-        <v>10.72318182583684</v>
+        <v>10.72318086866671</v>
       </c>
       <c r="F68" t="n">
         <v>2696600</v>
@@ -1792,16 +1792,16 @@
         <v>44746</v>
       </c>
       <c r="B69" t="n">
-        <v>10.65268611907959</v>
+        <v>10.65268707275391</v>
       </c>
       <c r="C69" t="n">
-        <v>10.78584475159305</v>
+        <v>10.7858457171883</v>
       </c>
       <c r="D69" t="n">
-        <v>10.52735977606733</v>
+        <v>10.52736071852189</v>
       </c>
       <c r="E69" t="n">
-        <v>10.68401751808279</v>
+        <v>10.68401847456203</v>
       </c>
       <c r="F69" t="n">
         <v>1437100</v>
@@ -1812,16 +1812,16 @@
         <v>44747</v>
       </c>
       <c r="B70" t="n">
-        <v>10.62135601043701</v>
+        <v>10.6213550567627</v>
       </c>
       <c r="C70" t="n">
-        <v>10.62135601043701</v>
+        <v>10.6213550567627</v>
       </c>
       <c r="D70" t="n">
-        <v>10.49602965219918</v>
+        <v>10.49602870977771</v>
       </c>
       <c r="E70" t="n">
-        <v>10.58219157017516</v>
+        <v>10.58219062001736</v>
       </c>
       <c r="F70" t="n">
         <v>1722600</v>
@@ -1832,16 +1832,16 @@
         <v>44748</v>
       </c>
       <c r="B71" t="n">
-        <v>10.67618560791016</v>
+        <v>10.67618465423584</v>
       </c>
       <c r="C71" t="n">
-        <v>10.71535004754583</v>
+        <v>10.71534909037307</v>
       </c>
       <c r="D71" t="n">
-        <v>10.49602948438586</v>
+        <v>10.49602854680439</v>
       </c>
       <c r="E71" t="n">
-        <v>10.57435836365721</v>
+        <v>10.57435741907885</v>
       </c>
       <c r="F71" t="n">
         <v>1826800</v>
@@ -1852,16 +1852,16 @@
         <v>44749</v>
       </c>
       <c r="B72" t="n">
-        <v>11.0443286895752</v>
+        <v>11.04432964324951</v>
       </c>
       <c r="C72" t="n">
-        <v>11.16182124599643</v>
+        <v>11.16182220981619</v>
       </c>
       <c r="D72" t="n">
-        <v>10.62135444065952</v>
+        <v>10.62135535781014</v>
       </c>
       <c r="E72" t="n">
-        <v>10.78584446784892</v>
+        <v>10.7858453992032</v>
       </c>
       <c r="F72" t="n">
         <v>2931100</v>
@@ -1892,16 +1892,16 @@
         <v>44753</v>
       </c>
       <c r="B74" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C74" t="n">
-        <v>11.18531989181933</v>
+        <v>11.18532085221909</v>
       </c>
       <c r="D74" t="n">
-        <v>10.83284146660853</v>
+        <v>10.83284239674361</v>
       </c>
       <c r="E74" t="n">
-        <v>11.05999429592211</v>
+        <v>11.0599952455611</v>
       </c>
       <c r="F74" t="n">
         <v>1881000</v>
@@ -1932,16 +1932,16 @@
         <v>44755</v>
       </c>
       <c r="B76" t="n">
-        <v>11.17748737335205</v>
+        <v>11.17748832702637</v>
       </c>
       <c r="C76" t="n">
-        <v>11.23231713368402</v>
+        <v>11.23231809203646</v>
       </c>
       <c r="D76" t="n">
-        <v>11.0129973453567</v>
+        <v>11.01299828499656</v>
       </c>
       <c r="E76" t="n">
-        <v>11.18531966268557</v>
+        <v>11.18532061702815</v>
       </c>
       <c r="F76" t="n">
         <v>2559400</v>
@@ -1952,16 +1952,16 @@
         <v>44756</v>
       </c>
       <c r="B77" t="n">
-        <v>10.91117000579834</v>
+        <v>10.91117095947266</v>
       </c>
       <c r="C77" t="n">
-        <v>11.1774872624825</v>
+        <v>11.17748823943387</v>
       </c>
       <c r="D77" t="n">
-        <v>10.84850720975495</v>
+        <v>10.84850815795232</v>
       </c>
       <c r="E77" t="n">
-        <v>11.04432863414042</v>
+        <v>11.04432959945326</v>
       </c>
       <c r="F77" t="n">
         <v>1968500</v>
@@ -1972,16 +1972,16 @@
         <v>44757</v>
       </c>
       <c r="B78" t="n">
-        <v>10.80934429168701</v>
+        <v>10.8093433380127</v>
       </c>
       <c r="C78" t="n">
-        <v>10.98166737847755</v>
+        <v>10.98166640959971</v>
       </c>
       <c r="D78" t="n">
-        <v>10.60568980247997</v>
+        <v>10.60568886677345</v>
       </c>
       <c r="E78" t="n">
-        <v>10.97383434112354</v>
+        <v>10.97383337293678</v>
       </c>
       <c r="F78" t="n">
         <v>2342600</v>
@@ -2012,16 +2012,16 @@
         <v>44761</v>
       </c>
       <c r="B80" t="n">
-        <v>11.0913257598877</v>
+        <v>11.09132671356201</v>
       </c>
       <c r="C80" t="n">
-        <v>11.0913257598877</v>
+        <v>11.09132671356201</v>
       </c>
       <c r="D80" t="n">
-        <v>10.78584480484809</v>
+        <v>10.78584573225599</v>
       </c>
       <c r="E80" t="n">
-        <v>10.87200596578243</v>
+        <v>10.87200690059879</v>
       </c>
       <c r="F80" t="n">
         <v>2890800</v>
@@ -2032,16 +2032,16 @@
         <v>44762</v>
       </c>
       <c r="B81" t="n">
-        <v>11.2793140411377</v>
+        <v>11.27931499481201</v>
       </c>
       <c r="C81" t="n">
-        <v>11.35764291174261</v>
+        <v>11.35764387203968</v>
       </c>
       <c r="D81" t="n">
-        <v>11.05216121278282</v>
+        <v>11.0521621472512</v>
       </c>
       <c r="E81" t="n">
-        <v>11.08349261162489</v>
+        <v>11.08349354874236</v>
       </c>
       <c r="F81" t="n">
         <v>2285400</v>
@@ -2052,16 +2052,16 @@
         <v>44763</v>
       </c>
       <c r="B82" t="n">
-        <v>11.24798393249512</v>
+        <v>11.2479829788208</v>
       </c>
       <c r="C82" t="n">
-        <v>11.27931533493105</v>
+        <v>11.27931437860027</v>
       </c>
       <c r="D82" t="n">
-        <v>11.0599955178795</v>
+        <v>11.05999458014401</v>
       </c>
       <c r="E82" t="n">
-        <v>11.22448556741805</v>
+        <v>11.22448461573608</v>
       </c>
       <c r="F82" t="n">
         <v>1092700</v>
@@ -2172,16 +2172,16 @@
         <v>44771</v>
       </c>
       <c r="B88" t="n">
-        <v>11.11482620239258</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C88" t="n">
-        <v>11.33414678453817</v>
+        <v>11.33414581204571</v>
       </c>
       <c r="D88" t="n">
-        <v>10.51952950699636</v>
+        <v>10.51952860439969</v>
       </c>
       <c r="E88" t="n">
-        <v>10.96600221529343</v>
+        <v>10.96600127438851</v>
       </c>
       <c r="F88" t="n">
         <v>13059200</v>
@@ -2372,16 +2372,16 @@
         <v>44785</v>
       </c>
       <c r="B98" t="n">
-        <v>11.08349323272705</v>
+        <v>11.08349418640137</v>
       </c>
       <c r="C98" t="n">
-        <v>11.13049070712356</v>
+        <v>11.13049166484175</v>
       </c>
       <c r="D98" t="n">
-        <v>10.78584530054738</v>
+        <v>10.78584622861072</v>
       </c>
       <c r="E98" t="n">
-        <v>10.89550482914005</v>
+        <v>10.89550576663898</v>
       </c>
       <c r="F98" t="n">
         <v>2648400</v>
@@ -2412,16 +2412,16 @@
         <v>44789</v>
       </c>
       <c r="B100" t="n">
-        <v>11.0443286895752</v>
+        <v>11.04432964324951</v>
       </c>
       <c r="C100" t="n">
-        <v>11.29497987500687</v>
+        <v>11.29498085032484</v>
       </c>
       <c r="D100" t="n">
-        <v>10.94250145874372</v>
+        <v>10.94250240362528</v>
       </c>
       <c r="E100" t="n">
-        <v>11.25581544053331</v>
+        <v>11.25581641246944</v>
       </c>
       <c r="F100" t="n">
         <v>1185300</v>
@@ -2472,16 +2472,16 @@
         <v>44792</v>
       </c>
       <c r="B103" t="n">
-        <v>11.11482620239258</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C103" t="n">
-        <v>11.16182368342367</v>
+        <v>11.16182272571687</v>
       </c>
       <c r="D103" t="n">
-        <v>10.98166829130366</v>
+        <v>10.98166734905456</v>
       </c>
       <c r="E103" t="n">
-        <v>11.16182368342367</v>
+        <v>11.16182272571687</v>
       </c>
       <c r="F103" t="n">
         <v>1667800</v>
@@ -2492,16 +2492,16 @@
         <v>44795</v>
       </c>
       <c r="B104" t="n">
-        <v>11.05999565124512</v>
+        <v>11.0599946975708</v>
       </c>
       <c r="C104" t="n">
-        <v>11.22448570276716</v>
+        <v>11.2244847349093</v>
       </c>
       <c r="D104" t="n">
-        <v>10.98166751771054</v>
+        <v>10.98166657079026</v>
       </c>
       <c r="E104" t="n">
-        <v>11.05999565124512</v>
+        <v>11.0599946975708</v>
       </c>
       <c r="F104" t="n">
         <v>1703300</v>
@@ -2532,16 +2532,16 @@
         <v>44797</v>
       </c>
       <c r="B106" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C106" t="n">
-        <v>11.39680739514549</v>
+        <v>11.3968083737041</v>
       </c>
       <c r="D106" t="n">
-        <v>11.09915873138986</v>
+        <v>11.09915968439161</v>
       </c>
       <c r="E106" t="n">
-        <v>11.22448432728707</v>
+        <v>11.2244852910496</v>
       </c>
       <c r="F106" t="n">
         <v>2116800</v>
@@ -2552,16 +2552,16 @@
         <v>44798</v>
       </c>
       <c r="B107" t="n">
-        <v>11.0443286895752</v>
+        <v>11.04432964324951</v>
       </c>
       <c r="C107" t="n">
-        <v>11.22448404235435</v>
+        <v>11.22448501158502</v>
       </c>
       <c r="D107" t="n">
-        <v>10.95033374803886</v>
+        <v>10.95033469359675</v>
       </c>
       <c r="E107" t="n">
-        <v>11.2088187167646</v>
+        <v>11.20881968464257</v>
       </c>
       <c r="F107" t="n">
         <v>2435800</v>
@@ -2592,16 +2592,16 @@
         <v>44802</v>
       </c>
       <c r="B109" t="n">
-        <v>11.11482620239258</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C109" t="n">
-        <v>11.20882116445476</v>
+        <v>11.20882020271549</v>
       </c>
       <c r="D109" t="n">
-        <v>10.93467081027257</v>
+        <v>10.93466987205595</v>
       </c>
       <c r="E109" t="n">
-        <v>11.02083198733002</v>
+        <v>11.02083104172059</v>
       </c>
       <c r="F109" t="n">
         <v>3615600</v>
@@ -2612,16 +2612,16 @@
         <v>44803</v>
       </c>
       <c r="B110" t="n">
-        <v>11.0129976272583</v>
+        <v>11.01299858093262</v>
       </c>
       <c r="C110" t="n">
-        <v>11.16182158639716</v>
+        <v>11.16182255295894</v>
       </c>
       <c r="D110" t="n">
-        <v>10.93466875592239</v>
+        <v>10.93466970281379</v>
       </c>
       <c r="E110" t="n">
-        <v>11.11482411419572</v>
+        <v>11.11482507668773</v>
       </c>
       <c r="F110" t="n">
         <v>1284900</v>
@@ -2652,16 +2652,16 @@
         <v>44805</v>
       </c>
       <c r="B112" t="n">
-        <v>11.65529251098633</v>
+        <v>11.65529346466064</v>
       </c>
       <c r="C112" t="n">
-        <v>12.15659567974902</v>
+        <v>12.1565966744416</v>
       </c>
       <c r="D112" t="n">
-        <v>11.42030662728508</v>
+        <v>11.42030756173208</v>
       </c>
       <c r="E112" t="n">
-        <v>12.14092960556915</v>
+        <v>12.14093059897989</v>
       </c>
       <c r="F112" t="n">
         <v>4716400</v>
@@ -2672,16 +2672,16 @@
         <v>44806</v>
       </c>
       <c r="B113" t="n">
-        <v>11.74145412445068</v>
+        <v>11.74145317077637</v>
       </c>
       <c r="C113" t="n">
-        <v>11.79628463916563</v>
+        <v>11.79628368103782</v>
       </c>
       <c r="D113" t="n">
-        <v>11.56129874652895</v>
+        <v>11.56129780748737</v>
       </c>
       <c r="E113" t="n">
-        <v>11.74145412445068</v>
+        <v>11.74145317077637</v>
       </c>
       <c r="F113" t="n">
         <v>3674700</v>
@@ -2732,16 +2732,16 @@
         <v>44812</v>
       </c>
       <c r="B116" t="n">
-        <v>11.43597221374512</v>
+        <v>11.4359712600708</v>
       </c>
       <c r="C116" t="n">
-        <v>11.63962594040124</v>
+        <v>11.63962496974372</v>
       </c>
       <c r="D116" t="n">
-        <v>11.37330941369716</v>
+        <v>11.37330846524845</v>
       </c>
       <c r="E116" t="n">
-        <v>11.623960613889</v>
+        <v>11.62395964453786</v>
       </c>
       <c r="F116" t="n">
         <v>2598100</v>
@@ -2892,16 +2892,16 @@
         <v>44824</v>
       </c>
       <c r="B124" t="n">
-        <v>11.13049030303955</v>
+        <v>11.13049125671387</v>
       </c>
       <c r="C124" t="n">
-        <v>11.35764313587711</v>
+        <v>11.35764410901417</v>
       </c>
       <c r="D124" t="n">
-        <v>11.08349283034925</v>
+        <v>11.08349377999676</v>
       </c>
       <c r="E124" t="n">
-        <v>11.28714730034141</v>
+        <v>11.28714826743829</v>
       </c>
       <c r="F124" t="n">
         <v>1310600</v>
@@ -2912,16 +2912,16 @@
         <v>44825</v>
       </c>
       <c r="B125" t="n">
-        <v>11.0913257598877</v>
+        <v>11.09132671356201</v>
       </c>
       <c r="C125" t="n">
-        <v>11.23231742959796</v>
+        <v>11.23231839539528</v>
       </c>
       <c r="D125" t="n">
-        <v>10.93466876409822</v>
+        <v>10.93466970430257</v>
       </c>
       <c r="E125" t="n">
-        <v>11.13049019558493</v>
+        <v>11.13049115262676</v>
       </c>
       <c r="F125" t="n">
         <v>2825100</v>
@@ -2992,16 +2992,16 @@
         <v>44831</v>
       </c>
       <c r="B129" t="n">
-        <v>10.9033374786377</v>
+        <v>10.90333843231201</v>
       </c>
       <c r="C129" t="n">
-        <v>11.04432914981819</v>
+        <v>11.04433011582452</v>
       </c>
       <c r="D129" t="n">
-        <v>10.77017884407822</v>
+        <v>10.77017978610565</v>
       </c>
       <c r="E129" t="n">
-        <v>11.04432914981819</v>
+        <v>11.04433011582452</v>
       </c>
       <c r="F129" t="n">
         <v>2130200</v>
@@ -3032,16 +3032,16 @@
         <v>44833</v>
       </c>
       <c r="B131" t="n">
-        <v>10.70751667022705</v>
+        <v>10.70751571655273</v>
       </c>
       <c r="C131" t="n">
-        <v>10.83284227548216</v>
+        <v>10.83284131064561</v>
       </c>
       <c r="D131" t="n">
-        <v>10.6448538675995</v>
+        <v>10.6448529195063</v>
       </c>
       <c r="E131" t="n">
-        <v>10.6918505960704</v>
+        <v>10.69184964379139</v>
       </c>
       <c r="F131" t="n">
         <v>2222600</v>
@@ -3052,16 +3052,16 @@
         <v>44834</v>
       </c>
       <c r="B132" t="n">
-        <v>10.61352252960205</v>
+        <v>10.61352157592773</v>
       </c>
       <c r="C132" t="n">
-        <v>10.74668117272986</v>
+        <v>10.74668020709063</v>
       </c>
       <c r="D132" t="n">
-        <v>10.59785645535194</v>
+        <v>10.59785550308529</v>
       </c>
       <c r="E132" t="n">
-        <v>10.70751673410412</v>
+        <v>10.70751577198399</v>
       </c>
       <c r="F132" t="n">
         <v>4019300</v>
@@ -3092,16 +3092,16 @@
         <v>44838</v>
       </c>
       <c r="B134" t="n">
-        <v>11.11482620239258</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C134" t="n">
-        <v>11.32631374653305</v>
+        <v>11.32631277471268</v>
       </c>
       <c r="D134" t="n">
-        <v>11.07566250636622</v>
+        <v>11.07566155605223</v>
       </c>
       <c r="E134" t="n">
-        <v>11.20882116445476</v>
+        <v>11.20882020271549</v>
       </c>
       <c r="F134" t="n">
         <v>2406500</v>
@@ -3132,16 +3132,16 @@
         <v>44840</v>
       </c>
       <c r="B136" t="n">
-        <v>10.98950004577637</v>
+        <v>10.98949909210205</v>
       </c>
       <c r="C136" t="n">
-        <v>11.12265869736379</v>
+        <v>11.1226577321339</v>
       </c>
       <c r="D136" t="n">
-        <v>10.88767279768013</v>
+        <v>10.88767185284243</v>
       </c>
       <c r="E136" t="n">
-        <v>11.02866448689024</v>
+        <v>11.02866352981721</v>
       </c>
       <c r="F136" t="n">
         <v>3101100</v>
@@ -3152,16 +3152,16 @@
         <v>44841</v>
       </c>
       <c r="B137" t="n">
-        <v>11.02866363525391</v>
+        <v>11.02866458892822</v>
       </c>
       <c r="C137" t="n">
-        <v>11.15398923954096</v>
+        <v>11.15399020405247</v>
       </c>
       <c r="D137" t="n">
-        <v>10.94250246905644</v>
+        <v>10.9425034152802</v>
       </c>
       <c r="E137" t="n">
-        <v>10.98166690714602</v>
+        <v>10.98166785675642</v>
       </c>
       <c r="F137" t="n">
         <v>7588600</v>
@@ -3172,16 +3172,16 @@
         <v>44844</v>
       </c>
       <c r="B138" t="n">
-        <v>11.07566165924072</v>
+        <v>11.07565975189209</v>
       </c>
       <c r="C138" t="n">
-        <v>11.35764428286087</v>
+        <v>11.35764232695178</v>
       </c>
       <c r="D138" t="n">
-        <v>11.0129988539918</v>
+        <v>11.01299695743438</v>
       </c>
       <c r="E138" t="n">
-        <v>11.07566165924072</v>
+        <v>11.07565975189209</v>
       </c>
       <c r="F138" t="n">
         <v>2000500</v>
@@ -3212,16 +3212,16 @@
         <v>44847</v>
       </c>
       <c r="B140" t="n">
-        <v>10.91117000579834</v>
+        <v>10.91117095947266</v>
       </c>
       <c r="C140" t="n">
-        <v>11.20098562424891</v>
+        <v>11.20098660325412</v>
       </c>
       <c r="D140" t="n">
-        <v>10.87200557152136</v>
+        <v>10.87200652177256</v>
       </c>
       <c r="E140" t="n">
-        <v>11.12265675569494</v>
+        <v>11.12265772785393</v>
       </c>
       <c r="F140" t="n">
         <v>3739400</v>
@@ -3232,16 +3232,16 @@
         <v>44848</v>
       </c>
       <c r="B141" t="n">
-        <v>10.82500839233398</v>
+        <v>10.8250093460083</v>
       </c>
       <c r="C141" t="n">
-        <v>11.16182149038183</v>
+        <v>11.1618224737291</v>
       </c>
       <c r="D141" t="n">
-        <v>10.82500839233398</v>
+        <v>10.8250093460083</v>
       </c>
       <c r="E141" t="n">
-        <v>10.97383309719211</v>
+        <v>10.97383406397776</v>
       </c>
       <c r="F141" t="n">
         <v>3601200</v>
@@ -3312,16 +3312,16 @@
         <v>44854</v>
       </c>
       <c r="B145" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C145" t="n">
-        <v>10.98166658413194</v>
+        <v>10.98166755090811</v>
       </c>
       <c r="D145" t="n">
-        <v>10.39420227106638</v>
+        <v>10.39420318612486</v>
       </c>
       <c r="E145" t="n">
-        <v>10.57435763518006</v>
+        <v>10.5743585660986</v>
       </c>
       <c r="F145" t="n">
         <v>7194300</v>
@@ -3352,16 +3352,16 @@
         <v>44858</v>
       </c>
       <c r="B147" t="n">
-        <v>11.24798393249512</v>
+        <v>11.2479829788208</v>
       </c>
       <c r="C147" t="n">
-        <v>11.45163842182848</v>
+        <v>11.45163745088707</v>
       </c>
       <c r="D147" t="n">
-        <v>11.10699299503318</v>
+        <v>11.10699205331296</v>
       </c>
       <c r="E147" t="n">
-        <v>11.10699299503318</v>
+        <v>11.10699205331296</v>
       </c>
       <c r="F147" t="n">
         <v>2219500</v>
@@ -3392,16 +3392,16 @@
         <v>44860</v>
       </c>
       <c r="B149" t="n">
-        <v>11.34197807312012</v>
+        <v>11.3419771194458</v>
       </c>
       <c r="C149" t="n">
-        <v>11.45163835450095</v>
+        <v>11.451637391606</v>
       </c>
       <c r="D149" t="n">
-        <v>11.20098713648711</v>
+        <v>11.20098619466782</v>
       </c>
       <c r="E149" t="n">
-        <v>11.43597302687486</v>
+        <v>11.43597206529711</v>
       </c>
       <c r="F149" t="n">
         <v>4386900</v>
@@ -3412,16 +3412,16 @@
         <v>44861</v>
       </c>
       <c r="B150" t="n">
-        <v>11.35764408111572</v>
+        <v>11.35764312744141</v>
       </c>
       <c r="C150" t="n">
-        <v>11.63179440945972</v>
+        <v>11.63179343276565</v>
       </c>
       <c r="D150" t="n">
-        <v>11.27148291217882</v>
+        <v>11.27148196573925</v>
       </c>
       <c r="E150" t="n">
-        <v>11.42813992251844</v>
+        <v>11.42813896292475</v>
       </c>
       <c r="F150" t="n">
         <v>4207900</v>
@@ -3432,16 +3432,16 @@
         <v>44862</v>
       </c>
       <c r="B151" t="n">
-        <v>11.49080276489258</v>
+        <v>11.49080181121826</v>
       </c>
       <c r="C151" t="n">
-        <v>11.63962673846057</v>
+        <v>11.63962577243467</v>
       </c>
       <c r="D151" t="n">
-        <v>11.22448547292922</v>
+        <v>11.2244845413578</v>
       </c>
       <c r="E151" t="n">
-        <v>11.32631271673871</v>
+        <v>11.32631177671618</v>
       </c>
       <c r="F151" t="n">
         <v>2887600</v>
@@ -3452,16 +3452,16 @@
         <v>44865</v>
       </c>
       <c r="B152" t="n">
-        <v>11.68662452697754</v>
+        <v>11.68662357330322</v>
       </c>
       <c r="C152" t="n">
-        <v>11.72578896748743</v>
+        <v>11.72578801061714</v>
       </c>
       <c r="D152" t="n">
-        <v>11.16182296634386</v>
+        <v>11.16182205549541</v>
       </c>
       <c r="E152" t="n">
-        <v>11.23231880986175</v>
+        <v>11.23231789326056</v>
       </c>
       <c r="F152" t="n">
         <v>2644000</v>
@@ -3492,16 +3492,16 @@
         <v>44868</v>
       </c>
       <c r="B154" t="n">
-        <v>11.68662452697754</v>
+        <v>11.68662357330322</v>
       </c>
       <c r="C154" t="n">
-        <v>11.74928733299354</v>
+        <v>11.74928637420569</v>
       </c>
       <c r="D154" t="n">
-        <v>11.36547745939565</v>
+        <v>11.36547653192819</v>
       </c>
       <c r="E154" t="n">
-        <v>11.49863610892954</v>
+        <v>11.49863517059581</v>
       </c>
       <c r="F154" t="n">
         <v>2959500</v>
@@ -3592,16 +3592,16 @@
         <v>44875</v>
       </c>
       <c r="B159" t="n">
-        <v>10.70751667022705</v>
+        <v>10.70751571655273</v>
       </c>
       <c r="C159" t="n">
-        <v>11.10699259722736</v>
+        <v>11.10699160797338</v>
       </c>
       <c r="D159" t="n">
-        <v>10.4960291511094</v>
+        <v>10.49602821627141</v>
       </c>
       <c r="E159" t="n">
-        <v>11.04432979459981</v>
+        <v>11.04432881092694</v>
       </c>
       <c r="F159" t="n">
         <v>4341400</v>
@@ -3632,16 +3632,16 @@
         <v>44879</v>
       </c>
       <c r="B161" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C161" t="n">
-        <v>10.9660005105571</v>
+        <v>10.9660014759541</v>
       </c>
       <c r="D161" t="n">
-        <v>10.71534930935563</v>
+        <v>10.71535025268644</v>
       </c>
       <c r="E161" t="n">
-        <v>10.94250214719434</v>
+        <v>10.94250311052265</v>
       </c>
       <c r="F161" t="n">
         <v>1203700</v>
@@ -3652,16 +3652,16 @@
         <v>44881</v>
       </c>
       <c r="B162" t="n">
-        <v>10.9033374786377</v>
+        <v>10.90333843231201</v>
       </c>
       <c r="C162" t="n">
-        <v>10.9033374786377</v>
+        <v>10.90333843231201</v>
       </c>
       <c r="D162" t="n">
-        <v>10.59785577341312</v>
+        <v>10.59785670036809</v>
       </c>
       <c r="E162" t="n">
-        <v>10.86417304253206</v>
+        <v>10.86417399278081</v>
       </c>
       <c r="F162" t="n">
         <v>5270300</v>
@@ -3692,16 +3692,16 @@
         <v>44883</v>
       </c>
       <c r="B164" t="n">
-        <v>10.78584575653076</v>
+        <v>10.78584480285645</v>
       </c>
       <c r="C164" t="n">
-        <v>10.98949949552661</v>
+        <v>10.98949852384542</v>
       </c>
       <c r="D164" t="n">
-        <v>10.57435823330488</v>
+        <v>10.57435729833009</v>
       </c>
       <c r="E164" t="n">
-        <v>10.80934412122268</v>
+        <v>10.80934316547066</v>
       </c>
       <c r="F164" t="n">
         <v>3568700</v>
@@ -3712,16 +3712,16 @@
         <v>44886</v>
       </c>
       <c r="B165" t="n">
-        <v>11.2793140411377</v>
+        <v>11.27931499481201</v>
       </c>
       <c r="C165" t="n">
-        <v>11.32631151290053</v>
+        <v>11.32631247054852</v>
       </c>
       <c r="D165" t="n">
-        <v>10.80934305850665</v>
+        <v>10.80934397244457</v>
       </c>
       <c r="E165" t="n">
-        <v>10.84067445734872</v>
+        <v>10.84067537393573</v>
       </c>
       <c r="F165" t="n">
         <v>4939800</v>
@@ -3752,16 +3752,16 @@
         <v>44888</v>
       </c>
       <c r="B167" t="n">
-        <v>10.56652450561523</v>
+        <v>10.56652545928955</v>
       </c>
       <c r="C167" t="n">
-        <v>10.8171764516154</v>
+        <v>10.81717742791213</v>
       </c>
       <c r="D167" t="n">
-        <v>10.51952777930236</v>
+        <v>10.51952872873502</v>
       </c>
       <c r="E167" t="n">
-        <v>10.80934341489675</v>
+        <v>10.80934439048652</v>
       </c>
       <c r="F167" t="n">
         <v>4669400</v>
@@ -3792,16 +3792,16 @@
         <v>44890</v>
       </c>
       <c r="B169" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C169" t="n">
-        <v>11.03649634764489</v>
+        <v>11.03649731924802</v>
       </c>
       <c r="D169" t="n">
-        <v>10.71534930935563</v>
+        <v>10.71535025268644</v>
       </c>
       <c r="E169" t="n">
-        <v>10.95033443698226</v>
+        <v>10.95033540100009</v>
       </c>
       <c r="F169" t="n">
         <v>1631500</v>
@@ -3852,16 +3852,16 @@
         <v>44895</v>
       </c>
       <c r="B172" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C172" t="n">
-        <v>11.20881942197064</v>
+        <v>11.20882040874432</v>
       </c>
       <c r="D172" t="n">
-        <v>10.69185019899337</v>
+        <v>10.69185114025542</v>
       </c>
       <c r="E172" t="n">
-        <v>11.20881942197064</v>
+        <v>11.20882040874432</v>
       </c>
       <c r="F172" t="n">
         <v>4586400</v>
@@ -3952,16 +3952,16 @@
         <v>44902</v>
       </c>
       <c r="B177" t="n">
-        <v>10.65268611907959</v>
+        <v>10.65268707275391</v>
       </c>
       <c r="C177" t="n">
-        <v>10.80151007759491</v>
+        <v>10.80151104459258</v>
       </c>
       <c r="D177" t="n">
-        <v>10.42553328955654</v>
+        <v>10.42553422289516</v>
       </c>
       <c r="E177" t="n">
-        <v>10.42553328955654</v>
+        <v>10.42553422289516</v>
       </c>
       <c r="F177" t="n">
         <v>2865300</v>
@@ -3972,16 +3972,16 @@
         <v>44903</v>
       </c>
       <c r="B178" t="n">
-        <v>11.26364898681641</v>
+        <v>11.26364994049072</v>
       </c>
       <c r="C178" t="n">
-        <v>11.8119488532735</v>
+        <v>11.81194985337145</v>
       </c>
       <c r="D178" t="n">
-        <v>11.15398871472519</v>
+        <v>11.15398965911476</v>
       </c>
       <c r="E178" t="n">
-        <v>11.74928605407837</v>
+        <v>11.74928704887077</v>
       </c>
       <c r="F178" t="n">
         <v>12105700</v>
@@ -3992,16 +3992,16 @@
         <v>44904</v>
       </c>
       <c r="B179" t="n">
-        <v>11.17748737335205</v>
+        <v>11.17748832702637</v>
       </c>
       <c r="C179" t="n">
-        <v>11.5691302260077</v>
+        <v>11.56913121309737</v>
       </c>
       <c r="D179" t="n">
-        <v>11.04432874368917</v>
+        <v>11.04432968600226</v>
       </c>
       <c r="E179" t="n">
-        <v>11.29497993034896</v>
+        <v>11.29498089404786</v>
       </c>
       <c r="F179" t="n">
         <v>7204400</v>
@@ -4032,16 +4032,16 @@
         <v>44908</v>
       </c>
       <c r="B181" t="n">
-        <v>11.08349323272705</v>
+        <v>11.08349418640137</v>
       </c>
       <c r="C181" t="n">
-        <v>11.3028137839114</v>
+        <v>11.30281475645706</v>
       </c>
       <c r="D181" t="n">
-        <v>10.99733206783289</v>
+        <v>10.9973330140935</v>
       </c>
       <c r="E181" t="n">
-        <v>11.00516510473222</v>
+        <v>11.00516605166683</v>
       </c>
       <c r="F181" t="n">
         <v>3594700</v>
@@ -4052,16 +4052,16 @@
         <v>44909</v>
       </c>
       <c r="B182" t="n">
-        <v>10.9973316192627</v>
+        <v>10.99733257293701</v>
       </c>
       <c r="C182" t="n">
-        <v>11.13832328970179</v>
+        <v>11.13832425560273</v>
       </c>
       <c r="D182" t="n">
-        <v>10.738847388124</v>
+        <v>10.7388483193829</v>
       </c>
       <c r="E182" t="n">
-        <v>11.01299769242237</v>
+        <v>11.01299864745522</v>
       </c>
       <c r="F182" t="n">
         <v>3892800</v>
@@ -4092,16 +4092,16 @@
         <v>44911</v>
       </c>
       <c r="B184" t="n">
-        <v>11.24798393249512</v>
+        <v>11.2479829788208</v>
       </c>
       <c r="C184" t="n">
-        <v>11.24798393249512</v>
+        <v>11.2479829788208</v>
       </c>
       <c r="D184" t="n">
-        <v>10.90333850569981</v>
+        <v>10.90333758124669</v>
       </c>
       <c r="E184" t="n">
-        <v>11.04433019016131</v>
+        <v>11.04432925375403</v>
       </c>
       <c r="F184" t="n">
         <v>3365900</v>
@@ -4112,16 +4112,16 @@
         <v>44914</v>
       </c>
       <c r="B185" t="n">
-        <v>11.37330913543701</v>
+        <v>11.37331008911133</v>
       </c>
       <c r="C185" t="n">
-        <v>11.5221330951599</v>
+        <v>11.5221340613134</v>
       </c>
       <c r="D185" t="n">
-        <v>11.18531999289299</v>
+        <v>11.18532093080405</v>
       </c>
       <c r="E185" t="n">
-        <v>11.23231746527886</v>
+        <v>11.23231840713075</v>
       </c>
       <c r="F185" t="n">
         <v>3838800</v>
@@ -4132,16 +4132,16 @@
         <v>44915</v>
       </c>
       <c r="B186" t="n">
-        <v>11.2793140411377</v>
+        <v>11.27931499481201</v>
       </c>
       <c r="C186" t="n">
-        <v>11.56129737771579</v>
+        <v>11.56129835523201</v>
       </c>
       <c r="D186" t="n">
-        <v>11.16965451869019</v>
+        <v>11.16965546309271</v>
       </c>
       <c r="E186" t="n">
-        <v>11.35764291174261</v>
+        <v>11.35764387203968</v>
       </c>
       <c r="F186" t="n">
         <v>4148100</v>
@@ -4172,16 +4172,16 @@
         <v>44917</v>
       </c>
       <c r="B188" t="n">
-        <v>11.63179302215576</v>
+        <v>11.63179397583008</v>
       </c>
       <c r="C188" t="n">
-        <v>11.74928557914745</v>
+        <v>11.74928654245482</v>
       </c>
       <c r="D188" t="n">
-        <v>11.50646668183198</v>
+        <v>11.50646762523096</v>
       </c>
       <c r="E188" t="n">
-        <v>11.60046162382468</v>
+        <v>11.60046257493018</v>
       </c>
       <c r="F188" t="n">
         <v>2577900</v>
@@ -4232,16 +4232,16 @@
         <v>44922</v>
       </c>
       <c r="B191" t="n">
-        <v>11.52996635437012</v>
+        <v>11.52996730804443</v>
       </c>
       <c r="C191" t="n">
-        <v>11.60829448052647</v>
+        <v>11.60829544067951</v>
       </c>
       <c r="D191" t="n">
-        <v>11.34197720819598</v>
+        <v>11.34197814632122</v>
       </c>
       <c r="E191" t="n">
-        <v>11.60829448052647</v>
+        <v>11.60829544067951</v>
       </c>
       <c r="F191" t="n">
         <v>1633000</v>
@@ -4292,16 +4292,16 @@
         <v>44928</v>
       </c>
       <c r="B194" t="n">
-        <v>11.34197807312012</v>
+        <v>11.3419771194458</v>
       </c>
       <c r="C194" t="n">
-        <v>11.46730442912659</v>
+        <v>11.46730346491438</v>
       </c>
       <c r="D194" t="n">
-        <v>11.1774887715482</v>
+        <v>11.17748783170473</v>
       </c>
       <c r="E194" t="n">
-        <v>11.38897554999749</v>
+        <v>11.38897459237146</v>
       </c>
       <c r="F194" t="n">
         <v>1018800</v>
@@ -4332,16 +4332,16 @@
         <v>44930</v>
       </c>
       <c r="B196" t="n">
-        <v>11.35764408111572</v>
+        <v>11.35764312744141</v>
       </c>
       <c r="C196" t="n">
-        <v>11.35764408111572</v>
+        <v>11.35764312744141</v>
       </c>
       <c r="D196" t="n">
-        <v>10.9660011817669</v>
+        <v>10.96600026097791</v>
       </c>
       <c r="E196" t="n">
-        <v>11.16965566870818</v>
+        <v>11.1696547308188</v>
       </c>
       <c r="F196" t="n">
         <v>2937400</v>
@@ -4372,16 +4372,16 @@
         <v>44932</v>
       </c>
       <c r="B198" t="n">
-        <v>11.42030620574951</v>
+        <v>11.42030715942383</v>
       </c>
       <c r="C198" t="n">
-        <v>11.53779876976359</v>
+        <v>11.53779973324935</v>
       </c>
       <c r="D198" t="n">
-        <v>11.31847896833754</v>
+        <v>11.31847991350858</v>
       </c>
       <c r="E198" t="n">
-        <v>11.4124731689487</v>
+        <v>11.41247412196891</v>
       </c>
       <c r="F198" t="n">
         <v>2864500</v>
@@ -4412,16 +4412,16 @@
         <v>44936</v>
       </c>
       <c r="B200" t="n">
-        <v>11.11482620239258</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C200" t="n">
-        <v>11.1853220504394</v>
+        <v>11.1853210907164</v>
       </c>
       <c r="D200" t="n">
-        <v>10.69185186111124</v>
+        <v>10.69185094372897</v>
       </c>
       <c r="E200" t="n">
-        <v>11.08349479737172</v>
+        <v>11.08349384638571</v>
       </c>
       <c r="F200" t="n">
         <v>5832500</v>
@@ -4432,16 +4432,16 @@
         <v>44937</v>
       </c>
       <c r="B201" t="n">
-        <v>11.49863433837891</v>
+        <v>11.49863624572754</v>
       </c>
       <c r="C201" t="n">
-        <v>11.6161268948176</v>
+        <v>11.61612882165544</v>
       </c>
       <c r="D201" t="n">
-        <v>11.06782705310459</v>
+        <v>11.0678288889926</v>
       </c>
       <c r="E201" t="n">
-        <v>11.09132541499244</v>
+        <v>11.09132725477826</v>
       </c>
       <c r="F201" t="n">
         <v>4499200</v>
@@ -4512,16 +4512,16 @@
         <v>44943</v>
       </c>
       <c r="B205" t="n">
-        <v>11.74928569793701</v>
+        <v>11.74928665161133</v>
       </c>
       <c r="C205" t="n">
-        <v>11.93727408982413</v>
+        <v>11.93727505875722</v>
       </c>
       <c r="D205" t="n">
-        <v>11.60829403052194</v>
+        <v>11.60829497275214</v>
       </c>
       <c r="E205" t="n">
-        <v>11.81194849523272</v>
+        <v>11.81194945399329</v>
       </c>
       <c r="F205" t="n">
         <v>2676600</v>
@@ -4552,16 +4552,16 @@
         <v>44945</v>
       </c>
       <c r="B207" t="n">
-        <v>11.66312503814697</v>
+        <v>11.66312599182129</v>
       </c>
       <c r="C207" t="n">
-        <v>11.68662340138985</v>
+        <v>11.68662435698559</v>
       </c>
       <c r="D207" t="n">
-        <v>11.27931445451592</v>
+        <v>11.27931537680668</v>
       </c>
       <c r="E207" t="n">
-        <v>11.3419772544966</v>
+        <v>11.3419781819112</v>
       </c>
       <c r="F207" t="n">
         <v>1847800</v>
@@ -4592,16 +4592,16 @@
         <v>44949</v>
       </c>
       <c r="B209" t="n">
-        <v>11.52213382720947</v>
+        <v>11.52213287353516</v>
       </c>
       <c r="C209" t="n">
-        <v>11.64745943220163</v>
+        <v>11.64745846815425</v>
       </c>
       <c r="D209" t="n">
-        <v>11.34981074684549</v>
+        <v>11.34980980743417</v>
       </c>
       <c r="E209" t="n">
-        <v>11.59262966676744</v>
+        <v>11.59262870725826</v>
       </c>
       <c r="F209" t="n">
         <v>1770800</v>
@@ -4612,16 +4612,16 @@
         <v>44950</v>
       </c>
       <c r="B210" t="n">
-        <v>11.68662452697754</v>
+        <v>11.68662357330322</v>
       </c>
       <c r="C210" t="n">
-        <v>11.80411710150764</v>
+        <v>11.80411613824548</v>
       </c>
       <c r="D210" t="n">
-        <v>11.32631301888575</v>
+        <v>11.32631209461427</v>
       </c>
       <c r="E210" t="n">
-        <v>11.52996751193754</v>
+        <v>11.52996657104705</v>
       </c>
       <c r="F210" t="n">
         <v>5839900</v>
@@ -4632,16 +4632,16 @@
         <v>44951</v>
       </c>
       <c r="B211" t="n">
-        <v>11.89027786254883</v>
+        <v>11.89027881622314</v>
       </c>
       <c r="C211" t="n">
-        <v>12.07043322555739</v>
+        <v>12.07043419368129</v>
       </c>
       <c r="D211" t="n">
-        <v>11.62396058940618</v>
+        <v>11.62396152172019</v>
       </c>
       <c r="E211" t="n">
-        <v>11.67879035258278</v>
+        <v>11.67879128929448</v>
       </c>
       <c r="F211" t="n">
         <v>10764800</v>
@@ -4652,16 +4652,16 @@
         <v>44952</v>
       </c>
       <c r="B212" t="n">
-        <v>11.96860599517822</v>
+        <v>11.96860504150391</v>
       </c>
       <c r="C212" t="n">
-        <v>12.09393159507546</v>
+        <v>12.09393063141503</v>
       </c>
       <c r="D212" t="n">
-        <v>11.79628366881928</v>
+        <v>11.79628272887583</v>
       </c>
       <c r="E212" t="n">
-        <v>11.91377623197306</v>
+        <v>11.91377528266765</v>
       </c>
       <c r="F212" t="n">
         <v>8143300</v>
@@ -4672,16 +4672,16 @@
         <v>44953</v>
       </c>
       <c r="B213" t="n">
-        <v>11.98427295684814</v>
+        <v>11.98427200317383</v>
       </c>
       <c r="C213" t="n">
-        <v>12.23492417521897</v>
+        <v>12.23492320159854</v>
       </c>
       <c r="D213" t="n">
-        <v>11.92161015225544</v>
+        <v>11.92160920356765</v>
       </c>
       <c r="E213" t="n">
-        <v>11.96860688220019</v>
+        <v>11.96860592977254</v>
       </c>
       <c r="F213" t="n">
         <v>4160800</v>
@@ -4712,16 +4712,16 @@
         <v>44957</v>
       </c>
       <c r="B215" t="n">
-        <v>12.07043361663818</v>
+        <v>12.07043266296387</v>
       </c>
       <c r="C215" t="n">
-        <v>12.14092945557759</v>
+        <v>12.14092849633346</v>
       </c>
       <c r="D215" t="n">
-        <v>11.82761544584636</v>
+        <v>11.8276145113569</v>
       </c>
       <c r="E215" t="n">
-        <v>11.84328077283316</v>
+        <v>11.84327983710599</v>
       </c>
       <c r="F215" t="n">
         <v>5446800</v>
@@ -4812,16 +4812,16 @@
         <v>44964</v>
       </c>
       <c r="B220" t="n">
-        <v>11.6004638671875</v>
+        <v>11.60046291351318</v>
       </c>
       <c r="C220" t="n">
-        <v>12.02343819995398</v>
+        <v>12.02343721150694</v>
       </c>
       <c r="D220" t="n">
-        <v>11.49080357832226</v>
+        <v>11.49080263366312</v>
       </c>
       <c r="E220" t="n">
-        <v>12.02343819995398</v>
+        <v>12.02343721150694</v>
       </c>
       <c r="F220" t="n">
         <v>5199600</v>
@@ -4852,16 +4852,16 @@
         <v>44966</v>
       </c>
       <c r="B222" t="n">
-        <v>11.66312503814697</v>
+        <v>11.66312599182129</v>
       </c>
       <c r="C222" t="n">
-        <v>11.78845063810834</v>
+        <v>11.78845160203032</v>
       </c>
       <c r="D222" t="n">
-        <v>11.55346476468103</v>
+        <v>11.55346570938861</v>
       </c>
       <c r="E222" t="n">
-        <v>11.71012176463273</v>
+        <v>11.7101227221499</v>
       </c>
       <c r="F222" t="n">
         <v>2260100</v>
@@ -4872,16 +4872,16 @@
         <v>44967</v>
       </c>
       <c r="B223" t="n">
-        <v>11.72578811645508</v>
+        <v>11.72578907012939</v>
       </c>
       <c r="C223" t="n">
-        <v>11.88244512012525</v>
+        <v>11.88244608654069</v>
       </c>
       <c r="D223" t="n">
-        <v>11.62396087731959</v>
+        <v>11.62396182271216</v>
       </c>
       <c r="E223" t="n">
-        <v>11.62396087731959</v>
+        <v>11.62396182271216</v>
       </c>
       <c r="F223" t="n">
         <v>6075300</v>
@@ -4912,16 +4912,16 @@
         <v>44971</v>
       </c>
       <c r="B225" t="n">
-        <v>11.71795558929443</v>
+        <v>11.71795463562012</v>
       </c>
       <c r="C225" t="n">
-        <v>11.8824456370539</v>
+        <v>11.88244466999244</v>
       </c>
       <c r="D225" t="n">
-        <v>11.51430110216375</v>
+        <v>11.51430016506401</v>
       </c>
       <c r="E225" t="n">
-        <v>11.78061839348856</v>
+        <v>11.78061743471438</v>
       </c>
       <c r="F225" t="n">
         <v>2141000</v>
@@ -4952,16 +4952,16 @@
         <v>44973</v>
       </c>
       <c r="B227" t="n">
-        <v>11.89027786254883</v>
+        <v>11.89027881622314</v>
       </c>
       <c r="C227" t="n">
-        <v>11.97643902568342</v>
+        <v>11.9764399862684</v>
       </c>
       <c r="D227" t="n">
-        <v>11.57696311596945</v>
+        <v>11.57696404451397</v>
       </c>
       <c r="E227" t="n">
-        <v>11.76495226271687</v>
+        <v>11.7649532063393</v>
       </c>
       <c r="F227" t="n">
         <v>4461000</v>
@@ -4972,16 +4972,16 @@
         <v>44974</v>
       </c>
       <c r="B228" t="n">
-        <v>11.72578811645508</v>
+        <v>11.72578907012939</v>
       </c>
       <c r="C228" t="n">
-        <v>12.13309632599753</v>
+        <v>12.13309731279878</v>
       </c>
       <c r="D228" t="n">
-        <v>11.55346503891813</v>
+        <v>11.55346597857718</v>
       </c>
       <c r="E228" t="n">
-        <v>11.94510792159332</v>
+        <v>11.94510889310522</v>
       </c>
       <c r="F228" t="n">
         <v>9428300</v>
@@ -4992,16 +4992,16 @@
         <v>44979</v>
       </c>
       <c r="B229" t="n">
-        <v>11.71795558929443</v>
+        <v>11.71795463562012</v>
       </c>
       <c r="C229" t="n">
-        <v>11.95294147852217</v>
+        <v>11.95294050572336</v>
       </c>
       <c r="D229" t="n">
-        <v>11.66312582237446</v>
+        <v>11.66312487316251</v>
       </c>
       <c r="E229" t="n">
-        <v>11.89811096460265</v>
+        <v>11.89810999626626</v>
       </c>
       <c r="F229" t="n">
         <v>6185800</v>
@@ -5052,16 +5052,16 @@
         <v>44984</v>
       </c>
       <c r="B232" t="n">
-        <v>11.64745998382568</v>
+        <v>11.64745903015137</v>
       </c>
       <c r="C232" t="n">
-        <v>11.85894751251565</v>
+        <v>11.85894654152509</v>
       </c>
       <c r="D232" t="n">
-        <v>11.56129881306286</v>
+        <v>11.56129786644328</v>
       </c>
       <c r="E232" t="n">
-        <v>11.7336211545885</v>
+        <v>11.73362019385946</v>
       </c>
       <c r="F232" t="n">
         <v>3412900</v>
@@ -5092,16 +5092,16 @@
         <v>44986</v>
       </c>
       <c r="B234" t="n">
-        <v>11.52996635437012</v>
+        <v>11.52996730804443</v>
       </c>
       <c r="C234" t="n">
-        <v>11.65529195381987</v>
+        <v>11.6552929178602</v>
       </c>
       <c r="D234" t="n">
-        <v>11.31847884504903</v>
+        <v>11.31847978123065</v>
       </c>
       <c r="E234" t="n">
-        <v>11.60046219081048</v>
+        <v>11.6004631503157</v>
       </c>
       <c r="F234" t="n">
         <v>8005300</v>
@@ -5192,16 +5192,16 @@
         <v>44993</v>
       </c>
       <c r="B239" t="n">
-        <v>11.63179302215576</v>
+        <v>11.63179397583008</v>
       </c>
       <c r="C239" t="n">
-        <v>11.63962531148894</v>
+        <v>11.63962626580541</v>
       </c>
       <c r="D239" t="n">
-        <v>11.48296831983353</v>
+        <v>11.48296926130592</v>
       </c>
       <c r="E239" t="n">
-        <v>11.62395998582313</v>
+        <v>11.62396093885522</v>
       </c>
       <c r="F239" t="n">
         <v>2946500</v>
@@ -5252,16 +5252,16 @@
         <v>44998</v>
       </c>
       <c r="B242" t="n">
-        <v>11.66312503814697</v>
+        <v>11.66312599182129</v>
       </c>
       <c r="C242" t="n">
-        <v>11.74145316462308</v>
+        <v>11.74145412470215</v>
       </c>
       <c r="D242" t="n">
-        <v>11.45947056471</v>
+        <v>11.45947150173183</v>
       </c>
       <c r="E242" t="n">
-        <v>11.52213336469069</v>
+        <v>11.52213430683635</v>
       </c>
       <c r="F242" t="n">
         <v>3223500</v>
@@ -5292,16 +5292,16 @@
         <v>45000</v>
       </c>
       <c r="B244" t="n">
-        <v>11.74928569793701</v>
+        <v>11.74928665161133</v>
       </c>
       <c r="C244" t="n">
-        <v>11.89027736535209</v>
+        <v>11.89027833047051</v>
       </c>
       <c r="D244" t="n">
-        <v>11.61612706693377</v>
+        <v>11.61612800979977</v>
       </c>
       <c r="E244" t="n">
-        <v>11.71795429928916</v>
+        <v>11.71795525042035</v>
       </c>
       <c r="F244" t="n">
         <v>4602600</v>
@@ -5372,16 +5372,16 @@
         <v>45006</v>
       </c>
       <c r="B248" t="n">
-        <v>11.34197807312012</v>
+        <v>11.3419771194458</v>
       </c>
       <c r="C248" t="n">
-        <v>11.42030695224922</v>
+        <v>11.42030599198873</v>
       </c>
       <c r="D248" t="n">
-        <v>11.27931526861666</v>
+        <v>11.27931432021125</v>
       </c>
       <c r="E248" t="n">
-        <v>11.36547718505858</v>
+        <v>11.36547622940837</v>
       </c>
       <c r="F248" t="n">
         <v>2410300</v>
@@ -5472,16 +5472,16 @@
         <v>45013</v>
       </c>
       <c r="B253" t="n">
-        <v>11.42030620574951</v>
+        <v>11.42030715942383</v>
       </c>
       <c r="C253" t="n">
-        <v>11.45163760595323</v>
+        <v>11.45163856224394</v>
       </c>
       <c r="D253" t="n">
-        <v>11.25581616793009</v>
+        <v>11.25581710786836</v>
       </c>
       <c r="E253" t="n">
-        <v>11.31064593153673</v>
+        <v>11.31064687605366</v>
       </c>
       <c r="F253" t="n">
         <v>3302900</v>
@@ -5532,16 +5532,16 @@
         <v>45016</v>
       </c>
       <c r="B256" t="n">
-        <v>11.49080276489258</v>
+        <v>11.49080181121826</v>
       </c>
       <c r="C256" t="n">
-        <v>11.61612837358132</v>
+        <v>11.61612740950566</v>
       </c>
       <c r="D256" t="n">
-        <v>11.30281435185946</v>
+        <v>11.30281341378716</v>
       </c>
       <c r="E256" t="n">
-        <v>11.42813996054821</v>
+        <v>11.42813901207456</v>
       </c>
       <c r="F256" t="n">
         <v>5155800</v>
@@ -5552,16 +5552,16 @@
         <v>45019</v>
       </c>
       <c r="B257" t="n">
-        <v>11.34197807312012</v>
+        <v>11.3419771194458</v>
       </c>
       <c r="C257" t="n">
-        <v>11.58479700082069</v>
+        <v>11.58479602672929</v>
       </c>
       <c r="D257" t="n">
-        <v>11.24798386636493</v>
+        <v>11.24798292059398</v>
       </c>
       <c r="E257" t="n">
-        <v>11.58479700082069</v>
+        <v>11.58479602672929</v>
       </c>
       <c r="F257" t="n">
         <v>6471200</v>
@@ -5572,16 +5572,16 @@
         <v>45020</v>
       </c>
       <c r="B258" t="n">
-        <v>11.43597221374512</v>
+        <v>11.4359712600708</v>
       </c>
       <c r="C258" t="n">
-        <v>11.49863501379308</v>
+        <v>11.49863405489315</v>
       </c>
       <c r="D258" t="n">
-        <v>11.24798306660174</v>
+        <v>11.24798212860431</v>
       </c>
       <c r="E258" t="n">
-        <v>11.35764334018542</v>
+        <v>11.35764239304314</v>
       </c>
       <c r="F258" t="n">
         <v>5230100</v>
@@ -5592,16 +5592,16 @@
         <v>45021</v>
       </c>
       <c r="B259" t="n">
-        <v>11.49080276489258</v>
+        <v>11.49080181121826</v>
       </c>
       <c r="C259" t="n">
-        <v>11.56913164382282</v>
+        <v>11.56913068364763</v>
       </c>
       <c r="D259" t="n">
-        <v>11.27931523998066</v>
+        <v>11.27931430385866</v>
       </c>
       <c r="E259" t="n">
-        <v>11.55346556923695</v>
+        <v>11.55346461036196</v>
       </c>
       <c r="F259" t="n">
         <v>4689800</v>
@@ -5632,16 +5632,16 @@
         <v>45026</v>
       </c>
       <c r="B261" t="n">
-        <v>11.71795558929443</v>
+        <v>11.71795463562012</v>
       </c>
       <c r="C261" t="n">
-        <v>11.85111423495683</v>
+        <v>11.85111327044531</v>
       </c>
       <c r="D261" t="n">
-        <v>11.45947133524378</v>
+        <v>11.4594704026064</v>
       </c>
       <c r="E261" t="n">
-        <v>11.53779946698666</v>
+        <v>11.53779852797449</v>
       </c>
       <c r="F261" t="n">
         <v>3430500</v>
@@ -5652,16 +5652,16 @@
         <v>45027</v>
       </c>
       <c r="B262" t="n">
-        <v>11.76495170593262</v>
+        <v>11.76495361328125</v>
       </c>
       <c r="C262" t="n">
-        <v>12.01560289373429</v>
+        <v>12.0156048417188</v>
       </c>
       <c r="D262" t="n">
-        <v>11.7101211983514</v>
+        <v>11.71012309681085</v>
       </c>
       <c r="E262" t="n">
-        <v>11.82761450288304</v>
+        <v>11.82761642039064</v>
       </c>
       <c r="F262" t="n">
         <v>2622300</v>
@@ -5672,16 +5672,16 @@
         <v>45028</v>
       </c>
       <c r="B263" t="n">
-        <v>11.80411624908447</v>
+        <v>11.80411529541016</v>
       </c>
       <c r="C263" t="n">
-        <v>12.01560376436578</v>
+        <v>12.01560279360503</v>
       </c>
       <c r="D263" t="n">
-        <v>11.74928648452985</v>
+        <v>11.74928553528532</v>
       </c>
       <c r="E263" t="n">
-        <v>11.82761535989319</v>
+        <v>11.82761440432034</v>
       </c>
       <c r="F263" t="n">
         <v>2987000</v>
@@ -5752,16 +5752,16 @@
         <v>45034</v>
       </c>
       <c r="B267" t="n">
-        <v>11.96860599517822</v>
+        <v>11.96860504150391</v>
       </c>
       <c r="C267" t="n">
-        <v>12.16442743176752</v>
+        <v>12.1644264624899</v>
       </c>
       <c r="D267" t="n">
-        <v>11.94510763194737</v>
+        <v>11.94510668014543</v>
       </c>
       <c r="E267" t="n">
-        <v>12.14092906853667</v>
+        <v>12.14092810113142</v>
       </c>
       <c r="F267" t="n">
         <v>3259600</v>
@@ -5832,16 +5832,16 @@
         <v>45041</v>
       </c>
       <c r="B271" t="n">
-        <v>12.06260108947754</v>
+        <v>12.06260013580322</v>
       </c>
       <c r="C271" t="n">
-        <v>12.14092996872072</v>
+        <v>12.14092900885369</v>
       </c>
       <c r="D271" t="n">
-        <v>11.96860688258545</v>
+        <v>11.96860593634236</v>
       </c>
       <c r="E271" t="n">
-        <v>12.11743160374759</v>
+        <v>12.11743064573835</v>
       </c>
       <c r="F271" t="n">
         <v>2381100</v>
@@ -5912,16 +5912,16 @@
         <v>45048</v>
       </c>
       <c r="B275" t="n">
-        <v>12.39158058166504</v>
+        <v>12.39158153533936</v>
       </c>
       <c r="C275" t="n">
-        <v>12.650064824739</v>
+        <v>12.65006579830664</v>
       </c>
       <c r="D275" t="n">
-        <v>12.2505896517153</v>
+        <v>12.25059059453875</v>
       </c>
       <c r="E275" t="n">
-        <v>12.5325722586143</v>
+        <v>12.53257322313954</v>
       </c>
       <c r="F275" t="n">
         <v>5999300</v>
@@ -5932,16 +5932,16 @@
         <v>45049</v>
       </c>
       <c r="B276" t="n">
-        <v>12.28975296020508</v>
+        <v>12.28975391387939</v>
       </c>
       <c r="C276" t="n">
-        <v>12.48557439565576</v>
+        <v>12.48557536452565</v>
       </c>
       <c r="D276" t="n">
-        <v>12.28192067050667</v>
+        <v>12.2819216235732</v>
       </c>
       <c r="E276" t="n">
-        <v>12.48557439565576</v>
+        <v>12.48557536452565</v>
       </c>
       <c r="F276" t="n">
         <v>6661600</v>
@@ -6072,16 +6072,16 @@
         <v>45058</v>
       </c>
       <c r="B283" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C283" t="n">
-        <v>12.25017632493442</v>
+        <v>12.25017729158851</v>
       </c>
       <c r="D283" t="n">
-        <v>11.99911266679329</v>
+        <v>11.9991136136361</v>
       </c>
       <c r="E283" t="n">
-        <v>12.04239967522403</v>
+        <v>12.0424006254826</v>
       </c>
       <c r="F283" t="n">
         <v>3087800</v>
@@ -6112,16 +6112,16 @@
         <v>45062</v>
       </c>
       <c r="B285" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="C285" t="n">
-        <v>12.30212031805942</v>
+        <v>12.30212128603885</v>
       </c>
       <c r="D285" t="n">
-        <v>12.08568611177803</v>
+        <v>12.08568706272756</v>
       </c>
       <c r="E285" t="n">
-        <v>12.18091686531469</v>
+        <v>12.18091782375736</v>
       </c>
       <c r="F285" t="n">
         <v>2907500</v>
@@ -6232,16 +6232,16 @@
         <v>45070</v>
       </c>
       <c r="B291" t="n">
-        <v>12.25017642974854</v>
+        <v>12.25017738342285</v>
       </c>
       <c r="C291" t="n">
-        <v>12.30212100543608</v>
+        <v>12.30212196315428</v>
       </c>
       <c r="D291" t="n">
-        <v>12.18091754591915</v>
+        <v>12.18091849420168</v>
       </c>
       <c r="E291" t="n">
-        <v>12.26749156352139</v>
+        <v>12.26749251854369</v>
       </c>
       <c r="F291" t="n">
         <v>1846000</v>
@@ -6312,16 +6312,16 @@
         <v>45076</v>
       </c>
       <c r="B295" t="n">
-        <v>12.26749134063721</v>
+        <v>12.26749229431152</v>
       </c>
       <c r="C295" t="n">
-        <v>12.3800372312229</v>
+        <v>12.38003819364653</v>
       </c>
       <c r="D295" t="n">
-        <v>12.25017620717894</v>
+        <v>12.25017715950718</v>
       </c>
       <c r="E295" t="n">
-        <v>12.37137966449377</v>
+        <v>12.37138062624436</v>
       </c>
       <c r="F295" t="n">
         <v>1829100</v>
@@ -6332,16 +6332,16 @@
         <v>45077</v>
       </c>
       <c r="B296" t="n">
-        <v>12.1895751953125</v>
+        <v>12.18957614898682</v>
       </c>
       <c r="C296" t="n">
-        <v>12.31077865564981</v>
+        <v>12.31077961880671</v>
       </c>
       <c r="D296" t="n">
-        <v>12.16360332010844</v>
+        <v>12.1636042717508</v>
       </c>
       <c r="E296" t="n">
-        <v>12.27614921350073</v>
+        <v>12.27615017394832</v>
       </c>
       <c r="F296" t="n">
         <v>3816500</v>
@@ -6352,16 +6352,16 @@
         <v>45078</v>
       </c>
       <c r="B297" t="n">
-        <v>12.24151992797852</v>
+        <v>12.2415189743042</v>
       </c>
       <c r="C297" t="n">
-        <v>12.30212124610704</v>
+        <v>12.30212028771158</v>
       </c>
       <c r="D297" t="n">
-        <v>12.1636034757384</v>
+        <v>12.16360252813415</v>
       </c>
       <c r="E297" t="n">
-        <v>12.26749180351488</v>
+        <v>12.26749084781722</v>
       </c>
       <c r="F297" t="n">
         <v>2308800</v>
@@ -6372,16 +6372,16 @@
         <v>45079</v>
       </c>
       <c r="B298" t="n">
-        <v>12.17226028442383</v>
+        <v>12.17226123809814</v>
       </c>
       <c r="C298" t="n">
-        <v>12.3367499200806</v>
+        <v>12.33675088664238</v>
       </c>
       <c r="D298" t="n">
-        <v>12.07702870400534</v>
+        <v>12.07702965021844</v>
       </c>
       <c r="E298" t="n">
-        <v>12.31077804616237</v>
+        <v>12.3107790106893</v>
       </c>
       <c r="F298" t="n">
         <v>5725100</v>
@@ -6392,16 +6392,16 @@
         <v>45082</v>
       </c>
       <c r="B299" t="n">
-        <v>12.0683708190918</v>
+        <v>12.06837177276611</v>
       </c>
       <c r="C299" t="n">
-        <v>12.19823183651883</v>
+        <v>12.1982328004551</v>
       </c>
       <c r="D299" t="n">
-        <v>11.97314006681674</v>
+        <v>11.97314101296568</v>
       </c>
       <c r="E299" t="n">
-        <v>12.17225996328581</v>
+        <v>12.17226092516972</v>
       </c>
       <c r="F299" t="n">
         <v>3442900</v>
@@ -6412,16 +6412,16 @@
         <v>45083</v>
       </c>
       <c r="B300" t="n">
-        <v>12.32809352874756</v>
+        <v>12.32809257507324</v>
       </c>
       <c r="C300" t="n">
-        <v>12.41466755090237</v>
+        <v>12.41466659053087</v>
       </c>
       <c r="D300" t="n">
-        <v>12.0770298552559</v>
+        <v>12.07702892100332</v>
       </c>
       <c r="E300" t="n">
-        <v>12.08568742259759</v>
+        <v>12.08568648767528</v>
       </c>
       <c r="F300" t="n">
         <v>7376500</v>
@@ -6452,16 +6452,16 @@
         <v>45086</v>
       </c>
       <c r="B302" t="n">
-        <v>12.37137985229492</v>
+        <v>12.37138080596924</v>
       </c>
       <c r="C302" t="n">
-        <v>12.42332442782724</v>
+        <v>12.42332538550581</v>
       </c>
       <c r="D302" t="n">
-        <v>12.26749152686131</v>
+        <v>12.26749247252717</v>
       </c>
       <c r="E302" t="n">
-        <v>12.29346340181196</v>
+        <v>12.29346434947992</v>
       </c>
       <c r="F302" t="n">
         <v>4999400</v>
@@ -6492,16 +6492,16 @@
         <v>45090</v>
       </c>
       <c r="B304" t="n">
-        <v>12.3107795715332</v>
+        <v>12.31077861785889</v>
       </c>
       <c r="C304" t="n">
-        <v>12.5012411047074</v>
+        <v>12.50124013627868</v>
       </c>
       <c r="D304" t="n">
-        <v>12.29346443635495</v>
+        <v>12.29346348402198</v>
       </c>
       <c r="E304" t="n">
-        <v>12.46661165998199</v>
+        <v>12.46661069423589</v>
       </c>
       <c r="F304" t="n">
         <v>1312000</v>
@@ -6572,16 +6572,16 @@
         <v>45096</v>
       </c>
       <c r="B308" t="n">
-        <v>12.6137866973877</v>
+        <v>12.61378574371338</v>
       </c>
       <c r="C308" t="n">
-        <v>12.80424905152594</v>
+        <v>12.80424808345158</v>
       </c>
       <c r="D308" t="n">
-        <v>12.38869572500366</v>
+        <v>12.38869478834751</v>
       </c>
       <c r="E308" t="n">
-        <v>12.80424905152594</v>
+        <v>12.80424808345158</v>
       </c>
       <c r="F308" t="n">
         <v>3301400</v>
@@ -6632,16 +6632,16 @@
         <v>45099</v>
       </c>
       <c r="B311" t="n">
-        <v>12.7869348526001</v>
+        <v>12.78693389892578</v>
       </c>
       <c r="C311" t="n">
-        <v>12.84753617349909</v>
+        <v>12.84753521530501</v>
       </c>
       <c r="D311" t="n">
-        <v>12.64841625026786</v>
+        <v>12.64841530692453</v>
       </c>
       <c r="E311" t="n">
-        <v>12.7869348526001</v>
+        <v>12.78693389892578</v>
       </c>
       <c r="F311" t="n">
         <v>2039700</v>
@@ -6652,16 +6652,16 @@
         <v>45100</v>
       </c>
       <c r="B312" t="n">
-        <v>12.94276714324951</v>
+        <v>12.9427661895752</v>
       </c>
       <c r="C312" t="n">
-        <v>13.07262818018377</v>
+        <v>13.07262721694078</v>
       </c>
       <c r="D312" t="n">
-        <v>12.76096235204642</v>
+        <v>12.7609614117682</v>
       </c>
       <c r="E312" t="n">
-        <v>12.81290693194634</v>
+        <v>12.81290598784064</v>
       </c>
       <c r="F312" t="n">
         <v>2959500</v>
@@ -6672,16 +6672,16 @@
         <v>45103</v>
       </c>
       <c r="B313" t="n">
-        <v>12.71767520904541</v>
+        <v>12.71767425537109</v>
       </c>
       <c r="C313" t="n">
-        <v>13.01202589898095</v>
+        <v>13.01202492323384</v>
       </c>
       <c r="D313" t="n">
-        <v>12.66573145531036</v>
+        <v>12.66573050553121</v>
       </c>
       <c r="E313" t="n">
-        <v>12.94276701024684</v>
+        <v>12.94276603969331</v>
       </c>
       <c r="F313" t="n">
         <v>2677600</v>
@@ -6792,16 +6792,16 @@
         <v>45111</v>
       </c>
       <c r="B319" t="n">
-        <v>12.34540843963623</v>
+        <v>12.34540748596191</v>
       </c>
       <c r="C319" t="n">
-        <v>12.40600975866739</v>
+        <v>12.40600880031166</v>
       </c>
       <c r="D319" t="n">
-        <v>12.23286254312761</v>
+        <v>12.23286159814739</v>
       </c>
       <c r="E319" t="n">
-        <v>12.38869544992894</v>
+        <v>12.38869449291073</v>
       </c>
       <c r="F319" t="n">
         <v>2230100</v>
@@ -6832,16 +6832,16 @@
         <v>45113</v>
       </c>
       <c r="B321" t="n">
-        <v>12.32809352874756</v>
+        <v>12.32809257507324</v>
       </c>
       <c r="C321" t="n">
-        <v>12.48392643837378</v>
+        <v>12.48392547264458</v>
       </c>
       <c r="D321" t="n">
-        <v>12.25017707393445</v>
+        <v>12.25017612628758</v>
       </c>
       <c r="E321" t="n">
-        <v>12.43198185995469</v>
+        <v>12.4319808982438</v>
       </c>
       <c r="F321" t="n">
         <v>2081000</v>
@@ -6852,16 +6852,16 @@
         <v>45114</v>
       </c>
       <c r="B322" t="n">
-        <v>12.34540843963623</v>
+        <v>12.34540748596191</v>
       </c>
       <c r="C322" t="n">
-        <v>12.48392621206805</v>
+        <v>12.48392524769333</v>
       </c>
       <c r="D322" t="n">
-        <v>12.25883441905082</v>
+        <v>12.25883347206429</v>
       </c>
       <c r="E322" t="n">
-        <v>12.42332489303689</v>
+        <v>12.42332393334358</v>
       </c>
       <c r="F322" t="n">
         <v>2149700</v>
@@ -6892,16 +6892,16 @@
         <v>45118</v>
       </c>
       <c r="B324" t="n">
-        <v>12.34540843963623</v>
+        <v>12.34540748596191</v>
       </c>
       <c r="C324" t="n">
-        <v>12.39735219148264</v>
+        <v>12.3973512337957</v>
       </c>
       <c r="D324" t="n">
-        <v>12.23286254312761</v>
+        <v>12.23286159814739</v>
       </c>
       <c r="E324" t="n">
-        <v>12.38869544992894</v>
+        <v>12.38869449291073</v>
       </c>
       <c r="F324" t="n">
         <v>1919200</v>
@@ -7072,16 +7072,16 @@
         <v>45131</v>
       </c>
       <c r="B333" t="n">
-        <v>12.34540843963623</v>
+        <v>12.34540748596191</v>
       </c>
       <c r="C333" t="n">
-        <v>12.42332489303689</v>
+        <v>12.42332393334358</v>
       </c>
       <c r="D333" t="n">
-        <v>12.31943573808198</v>
+        <v>12.31943478641403</v>
       </c>
       <c r="E333" t="n">
-        <v>12.42332489303689</v>
+        <v>12.42332393334358</v>
       </c>
       <c r="F333" t="n">
         <v>1347200</v>
@@ -7092,16 +7092,16 @@
         <v>45132</v>
       </c>
       <c r="B334" t="n">
-        <v>12.17226028442383</v>
+        <v>12.17226123809814</v>
       </c>
       <c r="C334" t="n">
-        <v>12.47526768181915</v>
+        <v>12.47526865923354</v>
       </c>
       <c r="D334" t="n">
-        <v>12.16360271790742</v>
+        <v>12.16360367090343</v>
       </c>
       <c r="E334" t="n">
-        <v>12.41466636746628</v>
+        <v>12.41466734013267</v>
       </c>
       <c r="F334" t="n">
         <v>2710400</v>
@@ -7132,16 +7132,16 @@
         <v>45134</v>
       </c>
       <c r="B336" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C336" t="n">
-        <v>12.22420445012837</v>
+        <v>12.22420541473304</v>
       </c>
       <c r="D336" t="n">
-        <v>12.03374210841168</v>
+        <v>12.03374305798708</v>
       </c>
       <c r="E336" t="n">
-        <v>12.18091744169762</v>
+        <v>12.18091840288654</v>
       </c>
       <c r="F336" t="n">
         <v>2852900</v>
@@ -7152,16 +7152,16 @@
         <v>45135</v>
       </c>
       <c r="B337" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="C337" t="n">
-        <v>12.22420387169716</v>
+        <v>12.22420483354582</v>
       </c>
       <c r="D337" t="n">
-        <v>12.05971423820094</v>
+        <v>12.0597151871069</v>
       </c>
       <c r="E337" t="n">
-        <v>12.14628742533491</v>
+        <v>12.14628838105279</v>
       </c>
       <c r="F337" t="n">
         <v>1506100</v>
@@ -7172,16 +7172,16 @@
         <v>45138</v>
       </c>
       <c r="B338" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="C338" t="n">
-        <v>12.20688956452276</v>
+        <v>12.20689052500906</v>
       </c>
       <c r="D338" t="n">
-        <v>12.10300041895243</v>
+        <v>12.10300137126433</v>
       </c>
       <c r="E338" t="n">
-        <v>12.20688956452276</v>
+        <v>12.20689052500906</v>
       </c>
       <c r="F338" t="n">
         <v>1549400</v>
@@ -7192,16 +7192,16 @@
         <v>45139</v>
       </c>
       <c r="B339" t="n">
-        <v>12.12897491455078</v>
+        <v>12.12897396087646</v>
       </c>
       <c r="C339" t="n">
-        <v>12.38003859799633</v>
+        <v>12.38003762458143</v>
       </c>
       <c r="D339" t="n">
-        <v>12.08568790175718</v>
+        <v>12.08568695148643</v>
       </c>
       <c r="E339" t="n">
-        <v>12.12031734686584</v>
+        <v>12.12031639387225</v>
       </c>
       <c r="F339" t="n">
         <v>5884200</v>
@@ -7292,16 +7292,16 @@
         <v>45146</v>
       </c>
       <c r="B344" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C344" t="n">
-        <v>12.15494556689158</v>
+        <v>12.15494652603107</v>
       </c>
       <c r="D344" t="n">
-        <v>11.92985378355649</v>
+        <v>11.92985472493413</v>
       </c>
       <c r="E344" t="n">
-        <v>11.99045592561195</v>
+        <v>11.99045687177166</v>
       </c>
       <c r="F344" t="n">
         <v>2176400</v>
@@ -7332,16 +7332,16 @@
         <v>45148</v>
       </c>
       <c r="B346" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C346" t="n">
-        <v>12.09434549372545</v>
+        <v>12.09434452900206</v>
       </c>
       <c r="D346" t="n">
-        <v>11.88656799702522</v>
+        <v>11.88656704887551</v>
       </c>
       <c r="E346" t="n">
-        <v>12.01642903566675</v>
+        <v>12.01642807715848</v>
       </c>
       <c r="F346" t="n">
         <v>2835300</v>
@@ -7352,16 +7352,16 @@
         <v>45149</v>
       </c>
       <c r="B347" t="n">
-        <v>11.92119789123535</v>
+        <v>11.92119693756104</v>
       </c>
       <c r="C347" t="n">
-        <v>11.97314164454614</v>
+        <v>11.97314068671642</v>
       </c>
       <c r="D347" t="n">
-        <v>11.83462386820927</v>
+        <v>11.83462292146072</v>
       </c>
       <c r="E347" t="n">
-        <v>11.97314164454614</v>
+        <v>11.97314068671642</v>
       </c>
       <c r="F347" t="n">
         <v>2472600</v>
@@ -7392,16 +7392,16 @@
         <v>45153</v>
       </c>
       <c r="B349" t="n">
-        <v>11.86059474945068</v>
+        <v>11.860595703125</v>
       </c>
       <c r="C349" t="n">
-        <v>11.9991125141623</v>
+        <v>11.99911347897441</v>
       </c>
       <c r="D349" t="n">
-        <v>11.85193718274846</v>
+        <v>11.85193813572664</v>
       </c>
       <c r="E349" t="n">
-        <v>11.91253932403304</v>
+        <v>11.91254028188406</v>
       </c>
       <c r="F349" t="n">
         <v>2713800</v>
@@ -7432,16 +7432,16 @@
         <v>45155</v>
       </c>
       <c r="B351" t="n">
-        <v>11.71341896057129</v>
+        <v>11.71341991424561</v>
       </c>
       <c r="C351" t="n">
-        <v>11.7826778402222</v>
+        <v>11.78267879953539</v>
       </c>
       <c r="D351" t="n">
-        <v>11.66147521364859</v>
+        <v>11.66147616309379</v>
       </c>
       <c r="E351" t="n">
-        <v>11.7307340932995</v>
+        <v>11.73073504838357</v>
       </c>
       <c r="F351" t="n">
         <v>2345000</v>
@@ -7492,16 +7492,16 @@
         <v>45160</v>
       </c>
       <c r="B354" t="n">
-        <v>11.79999446868896</v>
+        <v>11.79999351501465</v>
       </c>
       <c r="C354" t="n">
-        <v>11.86925335711897</v>
+        <v>11.86925239784715</v>
       </c>
       <c r="D354" t="n">
-        <v>11.73073558025896</v>
+        <v>11.73073463218214</v>
       </c>
       <c r="E354" t="n">
-        <v>11.79133690122745</v>
+        <v>11.79133594825283</v>
       </c>
       <c r="F354" t="n">
         <v>2231700</v>
@@ -7572,16 +7572,16 @@
         <v>45166</v>
       </c>
       <c r="B358" t="n">
-        <v>11.9644832611084</v>
+        <v>11.96448421478271</v>
       </c>
       <c r="C358" t="n">
-        <v>11.9991127028308</v>
+        <v>11.99911365926539</v>
       </c>
       <c r="D358" t="n">
-        <v>11.8432806278955</v>
+        <v>11.84328157190891</v>
       </c>
       <c r="E358" t="n">
-        <v>11.95582651990106</v>
+        <v>11.95582747288536</v>
       </c>
       <c r="F358" t="n">
         <v>2184700</v>
@@ -7592,16 +7592,16 @@
         <v>45167</v>
       </c>
       <c r="B359" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="C359" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="D359" t="n">
-        <v>11.97314022543599</v>
+        <v>11.97314116752997</v>
       </c>
       <c r="E359" t="n">
-        <v>11.98179779183868</v>
+        <v>11.98179873461387</v>
       </c>
       <c r="F359" t="n">
         <v>1776800</v>
@@ -7692,16 +7692,16 @@
         <v>45174</v>
       </c>
       <c r="B364" t="n">
-        <v>11.92119789123535</v>
+        <v>11.92119693756104</v>
       </c>
       <c r="C364" t="n">
-        <v>12.06837240936998</v>
+        <v>12.06837144392197</v>
       </c>
       <c r="D364" t="n">
-        <v>11.91254032380653</v>
+        <v>11.9125393708248</v>
       </c>
       <c r="E364" t="n">
-        <v>12.04240053271458</v>
+        <v>12.04239956934427</v>
       </c>
       <c r="F364" t="n">
         <v>3869600</v>
@@ -7712,16 +7712,16 @@
         <v>45175</v>
       </c>
       <c r="B365" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C365" t="n">
-        <v>12.02508660336907</v>
+        <v>12.02508564417022</v>
       </c>
       <c r="D365" t="n">
-        <v>11.81730910666884</v>
+        <v>11.81730816404367</v>
       </c>
       <c r="E365" t="n">
-        <v>11.93851257760805</v>
+        <v>11.9385116253149</v>
       </c>
       <c r="F365" t="n">
         <v>2473500</v>
@@ -7772,16 +7772,16 @@
         <v>45181</v>
       </c>
       <c r="B368" t="n">
-        <v>12.0683708190918</v>
+        <v>12.06837177276611</v>
       </c>
       <c r="C368" t="n">
-        <v>12.15494483070982</v>
+        <v>12.15494579122544</v>
       </c>
       <c r="D368" t="n">
-        <v>11.98179763310474</v>
+        <v>11.98179857993782</v>
       </c>
       <c r="E368" t="n">
-        <v>12.03374137957078</v>
+        <v>12.03374233050859</v>
       </c>
       <c r="F368" t="n">
         <v>2215400</v>
@@ -7792,16 +7792,16 @@
         <v>45182</v>
       </c>
       <c r="B369" t="n">
-        <v>12.0683708190918</v>
+        <v>12.06837177276611</v>
       </c>
       <c r="C369" t="n">
-        <v>12.19823183651883</v>
+        <v>12.1982328004551</v>
       </c>
       <c r="D369" t="n">
-        <v>12.03374137957078</v>
+        <v>12.03374233050859</v>
       </c>
       <c r="E369" t="n">
-        <v>12.07702838537979</v>
+        <v>12.07702933973825</v>
       </c>
       <c r="F369" t="n">
         <v>1684100</v>
@@ -7892,16 +7892,16 @@
         <v>45189</v>
       </c>
       <c r="B374" t="n">
-        <v>12.0683708190918</v>
+        <v>12.06837177276611</v>
       </c>
       <c r="C374" t="n">
-        <v>12.14628726442182</v>
+        <v>12.1462882242533</v>
       </c>
       <c r="D374" t="n">
-        <v>11.97314006681674</v>
+        <v>11.97314101296568</v>
       </c>
       <c r="E374" t="n">
-        <v>12.08568595166779</v>
+        <v>12.08568690671039</v>
       </c>
       <c r="F374" t="n">
         <v>2998000</v>
@@ -7912,16 +7912,16 @@
         <v>45190</v>
       </c>
       <c r="B375" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C375" t="n">
-        <v>12.0337433454403</v>
+        <v>12.03374238555092</v>
       </c>
       <c r="D375" t="n">
-        <v>11.877911254954</v>
+        <v>11.8779103074948</v>
       </c>
       <c r="E375" t="n">
-        <v>12.02508660336907</v>
+        <v>12.02508564417022</v>
       </c>
       <c r="F375" t="n">
         <v>4405700</v>
@@ -7932,16 +7932,16 @@
         <v>45191</v>
       </c>
       <c r="B376" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C376" t="n">
-        <v>12.10300223579667</v>
+        <v>12.10300127038276</v>
       </c>
       <c r="D376" t="n">
-        <v>11.92985500990573</v>
+        <v>11.92985405830317</v>
       </c>
       <c r="E376" t="n">
-        <v>12.02508660336907</v>
+        <v>12.02508564417022</v>
       </c>
       <c r="F376" t="n">
         <v>2812600</v>
@@ -7972,16 +7972,16 @@
         <v>45195</v>
       </c>
       <c r="B378" t="n">
-        <v>11.83462333679199</v>
+        <v>11.83462238311768</v>
       </c>
       <c r="C378" t="n">
-        <v>12.06837186745655</v>
+        <v>12.06837089494598</v>
       </c>
       <c r="D378" t="n">
-        <v>11.78267876018263</v>
+        <v>11.78267781069418</v>
       </c>
       <c r="E378" t="n">
-        <v>11.80865146130283</v>
+        <v>11.80865050972141</v>
       </c>
       <c r="F378" t="n">
         <v>7795500</v>
@@ -8132,16 +8132,16 @@
         <v>45205</v>
       </c>
       <c r="B386" t="n">
-        <v>11.67879009246826</v>
+        <v>11.67879104614258</v>
       </c>
       <c r="C386" t="n">
-        <v>11.70476279283205</v>
+        <v>11.70476374862726</v>
       </c>
       <c r="D386" t="n">
-        <v>11.61818877621478</v>
+        <v>11.61818972494048</v>
       </c>
       <c r="E386" t="n">
-        <v>11.68744765925619</v>
+        <v>11.68744861363747</v>
       </c>
       <c r="F386" t="n">
         <v>3573900</v>
@@ -8172,16 +8172,16 @@
         <v>45209</v>
       </c>
       <c r="B388" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C388" t="n">
-        <v>12.16360313370393</v>
+        <v>12.16360409352659</v>
       </c>
       <c r="D388" t="n">
-        <v>11.9125394755628</v>
+        <v>11.91254041557417</v>
       </c>
       <c r="E388" t="n">
-        <v>11.92985378355649</v>
+        <v>11.92985472493413</v>
       </c>
       <c r="F388" t="n">
         <v>3643400</v>
@@ -8212,16 +8212,16 @@
         <v>45212</v>
       </c>
       <c r="B390" t="n">
-        <v>12.02508640289307</v>
+        <v>12.02508544921875</v>
       </c>
       <c r="C390" t="n">
-        <v>12.19823362589739</v>
+        <v>12.19823265849127</v>
       </c>
       <c r="D390" t="n">
-        <v>12.02508640289307</v>
+        <v>12.02508544921875</v>
       </c>
       <c r="E390" t="n">
-        <v>12.0943452920948</v>
+        <v>12.09434433292776</v>
       </c>
       <c r="F390" t="n">
         <v>4555500</v>
@@ -8252,16 +8252,16 @@
         <v>45216</v>
       </c>
       <c r="B392" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C392" t="n">
-        <v>12.10300223579667</v>
+        <v>12.10300127038276</v>
       </c>
       <c r="D392" t="n">
-        <v>11.88656799702522</v>
+        <v>11.88656704887551</v>
       </c>
       <c r="E392" t="n">
-        <v>11.97314202278624</v>
+        <v>11.97314106773082</v>
       </c>
       <c r="F392" t="n">
         <v>5165000</v>
@@ -8272,16 +8272,16 @@
         <v>45217</v>
       </c>
       <c r="B393" t="n">
-        <v>11.66147518157959</v>
+        <v>11.66147613525391</v>
       </c>
       <c r="C393" t="n">
-        <v>11.955825832102</v>
+        <v>11.95582680984828</v>
       </c>
       <c r="D393" t="n">
-        <v>11.66147518157959</v>
+        <v>11.66147613525391</v>
       </c>
       <c r="E393" t="n">
-        <v>11.955825832102</v>
+        <v>11.95582680984828</v>
       </c>
       <c r="F393" t="n">
         <v>13737300</v>
@@ -8312,16 +8312,16 @@
         <v>45219</v>
       </c>
       <c r="B395" t="n">
-        <v>11.7653636932373</v>
+        <v>11.76536464691162</v>
       </c>
       <c r="C395" t="n">
-        <v>11.91253902090612</v>
+        <v>11.91253998651014</v>
       </c>
       <c r="D395" t="n">
-        <v>11.67013211319808</v>
+        <v>11.67013305915314</v>
       </c>
       <c r="E395" t="n">
-        <v>11.67013211319808</v>
+        <v>11.67013305915314</v>
       </c>
       <c r="F395" t="n">
         <v>6261200</v>
@@ -8332,16 +8332,16 @@
         <v>45222</v>
       </c>
       <c r="B396" t="n">
-        <v>11.72207832336426</v>
+        <v>11.72207736968994</v>
       </c>
       <c r="C396" t="n">
-        <v>11.90388311671755</v>
+        <v>11.90388214825212</v>
       </c>
       <c r="D396" t="n">
-        <v>11.72207832336426</v>
+        <v>11.72207736968994</v>
       </c>
       <c r="E396" t="n">
-        <v>11.77402290387853</v>
+        <v>11.77402194597815</v>
       </c>
       <c r="F396" t="n">
         <v>3068100</v>
@@ -8392,16 +8392,16 @@
         <v>45225</v>
       </c>
       <c r="B399" t="n">
-        <v>11.67879009246826</v>
+        <v>11.67879104614258</v>
       </c>
       <c r="C399" t="n">
-        <v>11.73073466756482</v>
+        <v>11.73073562548086</v>
       </c>
       <c r="D399" t="n">
-        <v>11.54892989317337</v>
+        <v>11.54893083624348</v>
       </c>
       <c r="E399" t="n">
-        <v>11.54892989317337</v>
+        <v>11.54893083624348</v>
       </c>
       <c r="F399" t="n">
         <v>2627000</v>
@@ -8452,16 +8452,16 @@
         <v>45230</v>
       </c>
       <c r="B402" t="n">
-        <v>11.61818981170654</v>
+        <v>11.61818885803223</v>
       </c>
       <c r="C402" t="n">
-        <v>11.66147682387321</v>
+        <v>11.6614758666457</v>
       </c>
       <c r="D402" t="n">
-        <v>11.52295904544475</v>
+        <v>11.52295809958741</v>
       </c>
       <c r="E402" t="n">
-        <v>11.52295904544475</v>
+        <v>11.52295809958741</v>
       </c>
       <c r="F402" t="n">
         <v>3290000</v>
@@ -8472,16 +8472,16 @@
         <v>45231</v>
       </c>
       <c r="B403" t="n">
-        <v>11.66147518157959</v>
+        <v>11.66147613525391</v>
       </c>
       <c r="C403" t="n">
-        <v>11.74804836808967</v>
+        <v>11.74804932884394</v>
       </c>
       <c r="D403" t="n">
-        <v>11.28055051891613</v>
+        <v>11.28055144143846</v>
       </c>
       <c r="E403" t="n">
-        <v>11.55758686238891</v>
+        <v>11.55758780756725</v>
       </c>
       <c r="F403" t="n">
         <v>7182500</v>
@@ -8492,16 +8492,16 @@
         <v>45233</v>
       </c>
       <c r="B404" t="n">
-        <v>11.9644832611084</v>
+        <v>11.96448421478271</v>
       </c>
       <c r="C404" t="n">
-        <v>12.02508540334586</v>
+        <v>12.0250863618507</v>
       </c>
       <c r="D404" t="n">
-        <v>11.65281828560679</v>
+        <v>11.65281921443867</v>
       </c>
       <c r="E404" t="n">
-        <v>11.74804904393564</v>
+        <v>11.74804998035825</v>
       </c>
       <c r="F404" t="n">
         <v>4830800</v>
@@ -8512,16 +8512,16 @@
         <v>45236</v>
       </c>
       <c r="B405" t="n">
-        <v>12.02508640289307</v>
+        <v>12.02508544921875</v>
       </c>
       <c r="C405" t="n">
-        <v>12.07703015697882</v>
+        <v>12.077029199185</v>
       </c>
       <c r="D405" t="n">
-        <v>11.81730890965679</v>
+        <v>11.8173079724607</v>
       </c>
       <c r="E405" t="n">
-        <v>11.94716994613335</v>
+        <v>11.94716899863836</v>
       </c>
       <c r="F405" t="n">
         <v>2982900</v>
@@ -8632,16 +8632,16 @@
         <v>45244</v>
       </c>
       <c r="B411" t="n">
-        <v>12.1895751953125</v>
+        <v>12.18957614898682</v>
       </c>
       <c r="C411" t="n">
-        <v>12.25017651266564</v>
+        <v>12.25017747108122</v>
       </c>
       <c r="D411" t="n">
-        <v>11.86059508208067</v>
+        <v>11.86059601001661</v>
       </c>
       <c r="E411" t="n">
-        <v>11.86059508208067</v>
+        <v>11.86059601001661</v>
       </c>
       <c r="F411" t="n">
         <v>3963500</v>
@@ -8672,16 +8672,16 @@
         <v>45247</v>
       </c>
       <c r="B413" t="n">
-        <v>12.25017642974854</v>
+        <v>12.25017738342285</v>
       </c>
       <c r="C413" t="n">
-        <v>12.48392578189597</v>
+        <v>12.48392675376763</v>
       </c>
       <c r="D413" t="n">
-        <v>12.14628810400446</v>
+        <v>12.14628904959109</v>
       </c>
       <c r="E413" t="n">
-        <v>12.48392578189597</v>
+        <v>12.48392675376763</v>
       </c>
       <c r="F413" t="n">
         <v>3124800</v>
@@ -8692,16 +8692,16 @@
         <v>45250</v>
       </c>
       <c r="B414" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C414" t="n">
-        <v>12.23286201694073</v>
+        <v>12.23286298222856</v>
       </c>
       <c r="D414" t="n">
-        <v>11.99045592561195</v>
+        <v>11.99045687177166</v>
       </c>
       <c r="E414" t="n">
-        <v>12.20689014213468</v>
+        <v>12.20689110537309</v>
       </c>
       <c r="F414" t="n">
         <v>3248400</v>
@@ -8752,16 +8752,16 @@
         <v>45253</v>
       </c>
       <c r="B417" t="n">
-        <v>12.56184196472168</v>
+        <v>12.561842918396</v>
       </c>
       <c r="C417" t="n">
-        <v>12.76961861177884</v>
+        <v>12.76961958122722</v>
       </c>
       <c r="D417" t="n">
-        <v>12.46661038226389</v>
+        <v>12.46661132870839</v>
       </c>
       <c r="E417" t="n">
-        <v>12.76961861177884</v>
+        <v>12.76961958122722</v>
       </c>
       <c r="F417" t="n">
         <v>9122900</v>
@@ -8812,16 +8812,16 @@
         <v>45258</v>
       </c>
       <c r="B420" t="n">
-        <v>12.6397590637207</v>
+        <v>12.63975811004639</v>
       </c>
       <c r="C420" t="n">
-        <v>12.76961926840118</v>
+        <v>12.76961830492886</v>
       </c>
       <c r="D420" t="n">
-        <v>12.57050017780698</v>
+        <v>12.57049922935827</v>
       </c>
       <c r="E420" t="n">
-        <v>12.57915691932291</v>
+        <v>12.57915597022104</v>
       </c>
       <c r="F420" t="n">
         <v>5941200</v>
@@ -8832,16 +8832,16 @@
         <v>45259</v>
       </c>
       <c r="B421" t="n">
-        <v>12.56184196472168</v>
+        <v>12.561842918396</v>
       </c>
       <c r="C421" t="n">
-        <v>12.75230347837524</v>
+        <v>12.75230444650908</v>
       </c>
       <c r="D421" t="n">
-        <v>12.56184196472168</v>
+        <v>12.561842918396</v>
       </c>
       <c r="E421" t="n">
-        <v>12.72633160390085</v>
+        <v>12.72633257006295</v>
       </c>
       <c r="F421" t="n">
         <v>5869600</v>
@@ -8852,16 +8852,16 @@
         <v>45260</v>
       </c>
       <c r="B422" t="n">
-        <v>12.71767520904541</v>
+        <v>12.71767425537109</v>
       </c>
       <c r="C422" t="n">
-        <v>12.71767520904541</v>
+        <v>12.71767425537109</v>
       </c>
       <c r="D422" t="n">
-        <v>12.58781499907671</v>
+        <v>12.58781405514036</v>
       </c>
       <c r="E422" t="n">
-        <v>12.6311020109433</v>
+        <v>12.63110106376094</v>
       </c>
       <c r="F422" t="n">
         <v>4162000</v>
@@ -8952,16 +8952,16 @@
         <v>45267</v>
       </c>
       <c r="B427" t="n">
-        <v>13.11591339111328</v>
+        <v>13.1159143447876</v>
       </c>
       <c r="C427" t="n">
-        <v>13.15054283325996</v>
+        <v>13.15054378945223</v>
       </c>
       <c r="D427" t="n">
-        <v>12.97739562252655</v>
+        <v>12.97739656612907</v>
       </c>
       <c r="E427" t="n">
-        <v>13.10725664979988</v>
+        <v>13.10725760284475</v>
       </c>
       <c r="F427" t="n">
         <v>6196000</v>
@@ -22132,19 +22132,39 @@
         <v>46233</v>
       </c>
       <c r="B1086" t="n">
-        <v>11.2</v>
+        <v>11.19999980926514</v>
       </c>
       <c r="C1086" t="n">
-        <v>11.31</v>
+        <v>11.3100004196167</v>
       </c>
       <c r="D1086" t="n">
-        <v>11.09</v>
+        <v>11.09000015258789</v>
       </c>
       <c r="E1086" t="n">
-        <v>11.18</v>
+        <v>11.18000030517578</v>
       </c>
       <c r="F1086" t="n">
         <v>2543000</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B1087" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="C1087" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="D1087" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="E1087" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F1087" t="n">
+        <v>5442500</v>
       </c>
     </row>
   </sheetData>

--- a/database/AURE3.xlsx
+++ b/database/AURE3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1087"/>
+  <dimension ref="A1:F1088"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,16 +492,16 @@
         <v>44650</v>
       </c>
       <c r="B4" t="n">
-        <v>12.38385105133057</v>
+        <v>12.38385009765625</v>
       </c>
       <c r="C4" t="n">
-        <v>13.04504942238897</v>
+        <v>13.04504841779609</v>
       </c>
       <c r="D4" t="n">
-        <v>12.30606274584925</v>
+        <v>12.30606179816537</v>
       </c>
       <c r="E4" t="n">
-        <v>12.92836770601126</v>
+        <v>12.92836671040398</v>
       </c>
       <c r="F4" t="n">
         <v>4408600</v>
@@ -552,16 +552,16 @@
         <v>44655</v>
       </c>
       <c r="B7" t="n">
-        <v>12.42274379730225</v>
+        <v>12.42274570465088</v>
       </c>
       <c r="C7" t="n">
-        <v>12.73389624214791</v>
+        <v>12.7338981972699</v>
       </c>
       <c r="D7" t="n">
-        <v>12.3371765225937</v>
+        <v>12.33717841680461</v>
       </c>
       <c r="E7" t="n">
-        <v>12.54720373665866</v>
+        <v>12.54720566311648</v>
       </c>
       <c r="F7" t="n">
         <v>2842400</v>
@@ -592,16 +592,16 @@
         <v>44657</v>
       </c>
       <c r="B9" t="n">
-        <v>12.43052291870117</v>
+        <v>12.43052387237549</v>
       </c>
       <c r="C9" t="n">
-        <v>12.44608087588125</v>
+        <v>12.44608183074918</v>
       </c>
       <c r="D9" t="n">
-        <v>12.01824669740399</v>
+        <v>12.01824761944832</v>
       </c>
       <c r="E9" t="n">
-        <v>12.06491982710001</v>
+        <v>12.06492075272512</v>
       </c>
       <c r="F9" t="n">
         <v>2914800</v>
@@ -692,16 +692,16 @@
         <v>44664</v>
       </c>
       <c r="B14" t="n">
-        <v>12.10381412506104</v>
+        <v>12.10381317138672</v>
       </c>
       <c r="C14" t="n">
-        <v>12.55498376109398</v>
+        <v>12.55498277187146</v>
       </c>
       <c r="D14" t="n">
-        <v>12.08825616769219</v>
+        <v>12.0882552152437</v>
       </c>
       <c r="E14" t="n">
-        <v>12.39162965978653</v>
+        <v>12.39162868343488</v>
       </c>
       <c r="F14" t="n">
         <v>4421300</v>
@@ -712,16 +712,16 @@
         <v>44665</v>
       </c>
       <c r="B15" t="n">
-        <v>12.11159324645996</v>
+        <v>12.11159229278564</v>
       </c>
       <c r="C15" t="n">
-        <v>12.36829362703988</v>
+        <v>12.36829265315281</v>
       </c>
       <c r="D15" t="n">
-        <v>12.04936289612812</v>
+        <v>12.04936194735386</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08047807129404</v>
+        <v>12.08047712006975</v>
       </c>
       <c r="F15" t="n">
         <v>2077400</v>
@@ -732,16 +732,16 @@
         <v>44669</v>
       </c>
       <c r="B16" t="n">
-        <v>12.45385932922363</v>
+        <v>12.45386028289795</v>
       </c>
       <c r="C16" t="n">
-        <v>12.45385932922363</v>
+        <v>12.45386028289795</v>
       </c>
       <c r="D16" t="n">
-        <v>11.92490067691762</v>
+        <v>11.92490159008608</v>
       </c>
       <c r="E16" t="n">
-        <v>12.10381346772168</v>
+        <v>12.10381439459067</v>
       </c>
       <c r="F16" t="n">
         <v>3931100</v>
@@ -752,16 +752,16 @@
         <v>44670</v>
       </c>
       <c r="B17" t="n">
-        <v>12.10381412506104</v>
+        <v>12.10381317138672</v>
       </c>
       <c r="C17" t="n">
-        <v>12.60165763320052</v>
+        <v>12.60165664030051</v>
       </c>
       <c r="D17" t="n">
-        <v>12.00268962769625</v>
+        <v>12.00268868198966</v>
       </c>
       <c r="E17" t="n">
-        <v>12.4383020482046</v>
+        <v>12.43830106817557</v>
       </c>
       <c r="F17" t="n">
         <v>3118100</v>
@@ -772,16 +772,16 @@
         <v>44671</v>
       </c>
       <c r="B18" t="n">
-        <v>12.0571403503418</v>
+        <v>12.05714130401611</v>
       </c>
       <c r="C18" t="n">
-        <v>12.2127162064935</v>
+        <v>12.21271717247328</v>
       </c>
       <c r="D18" t="n">
-        <v>11.95601585838214</v>
+        <v>11.95601680405789</v>
       </c>
       <c r="E18" t="n">
-        <v>12.07269830687907</v>
+        <v>12.07269926178396</v>
       </c>
       <c r="F18" t="n">
         <v>2798400</v>
@@ -792,16 +792,16 @@
         <v>44673</v>
       </c>
       <c r="B19" t="n">
-        <v>12.22049522399902</v>
+        <v>12.22049617767334</v>
       </c>
       <c r="C19" t="n">
-        <v>12.33717693102638</v>
+        <v>12.33717789380641</v>
       </c>
       <c r="D19" t="n">
-        <v>11.80044004011864</v>
+        <v>11.80044096101231</v>
       </c>
       <c r="E19" t="n">
-        <v>12.01824623943035</v>
+        <v>12.01824717732137</v>
       </c>
       <c r="F19" t="n">
         <v>11382300</v>
@@ -812,16 +812,16 @@
         <v>44676</v>
       </c>
       <c r="B20" t="n">
-        <v>12.39163017272949</v>
+        <v>12.39162826538086</v>
       </c>
       <c r="C20" t="n">
-        <v>12.39163017272949</v>
+        <v>12.39162826538086</v>
       </c>
       <c r="D20" t="n">
-        <v>11.90156562298855</v>
+        <v>11.90156379107179</v>
       </c>
       <c r="E20" t="n">
-        <v>12.11937184225865</v>
+        <v>12.11936997681666</v>
       </c>
       <c r="F20" t="n">
         <v>2683100</v>
@@ -852,16 +852,16 @@
         <v>44678</v>
       </c>
       <c r="B22" t="n">
-        <v>12.0571403503418</v>
+        <v>12.05714130401611</v>
       </c>
       <c r="C22" t="n">
-        <v>12.06491932861043</v>
+        <v>12.06492028290003</v>
       </c>
       <c r="D22" t="n">
-        <v>11.83155517346078</v>
+        <v>11.83155610929216</v>
       </c>
       <c r="E22" t="n">
-        <v>12.04936137207316</v>
+        <v>12.04936232513219</v>
       </c>
       <c r="F22" t="n">
         <v>2401400</v>
@@ -872,16 +872,16 @@
         <v>44679</v>
       </c>
       <c r="B23" t="n">
-        <v>11.90934276580811</v>
+        <v>11.90934371948242</v>
       </c>
       <c r="C23" t="n">
-        <v>12.08825480430562</v>
+        <v>12.08825577230682</v>
       </c>
       <c r="D23" t="n">
-        <v>11.49706584416364</v>
+        <v>11.49706676482372</v>
       </c>
       <c r="E23" t="n">
-        <v>12.08825480430562</v>
+        <v>12.08825577230682</v>
       </c>
       <c r="F23" t="n">
         <v>3489600</v>
@@ -912,16 +912,16 @@
         <v>44683</v>
       </c>
       <c r="B25" t="n">
-        <v>11.17035675048828</v>
+        <v>11.1703577041626</v>
       </c>
       <c r="C25" t="n">
-        <v>11.47373022346064</v>
+        <v>11.47373120303561</v>
       </c>
       <c r="D25" t="n">
-        <v>10.96032953215679</v>
+        <v>10.96033046789994</v>
       </c>
       <c r="E25" t="n">
-        <v>11.4270570961402</v>
+        <v>11.42705807173043</v>
       </c>
       <c r="F25" t="n">
         <v>2883200</v>
@@ -952,16 +952,16 @@
         <v>44685</v>
       </c>
       <c r="B27" t="n">
-        <v>11.69445705413818</v>
+        <v>11.69445610046387</v>
       </c>
       <c r="C27" t="n">
-        <v>11.69445705413818</v>
+        <v>11.69445610046387</v>
       </c>
       <c r="D27" t="n">
-        <v>11.03649687268372</v>
+        <v>11.03649597266557</v>
       </c>
       <c r="E27" t="n">
-        <v>11.2088199552074</v>
+        <v>11.20881904113643</v>
       </c>
       <c r="F27" t="n">
         <v>4400300</v>
@@ -1012,16 +1012,16 @@
         <v>44690</v>
       </c>
       <c r="B30" t="n">
-        <v>11.07565975189209</v>
+        <v>11.07566165924072</v>
       </c>
       <c r="C30" t="n">
-        <v>11.13048951029273</v>
+        <v>11.13049142708364</v>
       </c>
       <c r="D30" t="n">
-        <v>10.8093425019471</v>
+        <v>10.80934436343302</v>
       </c>
       <c r="E30" t="n">
-        <v>10.99733088532023</v>
+        <v>10.99733277917979</v>
       </c>
       <c r="F30" t="n">
         <v>1545300</v>
@@ -1092,16 +1092,16 @@
         <v>44694</v>
       </c>
       <c r="B34" t="n">
-        <v>11.32631206512451</v>
+        <v>11.32631301879883</v>
       </c>
       <c r="C34" t="n">
-        <v>11.38114182902154</v>
+        <v>11.38114278731251</v>
       </c>
       <c r="D34" t="n">
-        <v>11.11482455237968</v>
+        <v>11.11482548824677</v>
       </c>
       <c r="E34" t="n">
-        <v>11.18532038996129</v>
+        <v>11.18532133176413</v>
       </c>
       <c r="F34" t="n">
         <v>1333500</v>
@@ -1152,16 +1152,16 @@
         <v>44699</v>
       </c>
       <c r="B37" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C37" t="n">
-        <v>11.5926298208571</v>
+        <v>11.59262882548476</v>
       </c>
       <c r="D37" t="n">
-        <v>11.03649688106261</v>
+        <v>11.03649593344125</v>
       </c>
       <c r="E37" t="n">
-        <v>11.51430094319608</v>
+        <v>11.51429995454926</v>
       </c>
       <c r="F37" t="n">
         <v>1959900</v>
@@ -1192,16 +1192,16 @@
         <v>44701</v>
       </c>
       <c r="B39" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C39" t="n">
-        <v>11.34197786054158</v>
+        <v>11.34197688669085</v>
       </c>
       <c r="D39" t="n">
-        <v>10.86417379840811</v>
+        <v>10.86417286558284</v>
       </c>
       <c r="E39" t="n">
-        <v>11.34197786054158</v>
+        <v>11.34197688669085</v>
       </c>
       <c r="F39" t="n">
         <v>1777400</v>
@@ -1212,16 +1212,16 @@
         <v>44704</v>
       </c>
       <c r="B40" t="n">
-        <v>11.20882034301758</v>
+        <v>11.20881938934326</v>
       </c>
       <c r="C40" t="n">
-        <v>11.4359731995218</v>
+        <v>11.43597222652075</v>
       </c>
       <c r="D40" t="n">
-        <v>11.16182286543069</v>
+        <v>11.16182191575504</v>
       </c>
       <c r="E40" t="n">
-        <v>11.18532123072435</v>
+        <v>11.1853202790494</v>
       </c>
       <c r="F40" t="n">
         <v>1184600</v>
@@ -1252,16 +1252,16 @@
         <v>44706</v>
       </c>
       <c r="B42" t="n">
-        <v>11.32631206512451</v>
+        <v>11.32631301879883</v>
       </c>
       <c r="C42" t="n">
-        <v>11.39680790270612</v>
+        <v>11.39680886231618</v>
       </c>
       <c r="D42" t="n">
-        <v>11.13832366290656</v>
+        <v>11.13832460075227</v>
       </c>
       <c r="E42" t="n">
-        <v>11.17748810011851</v>
+        <v>11.17748904126186</v>
       </c>
       <c r="F42" t="n">
         <v>821700</v>
@@ -1272,16 +1272,16 @@
         <v>44707</v>
       </c>
       <c r="B43" t="n">
-        <v>11.25581550598145</v>
+        <v>11.25581645965576</v>
       </c>
       <c r="C43" t="n">
-        <v>11.44380389614828</v>
+        <v>11.44380486575034</v>
       </c>
       <c r="D43" t="n">
-        <v>11.20881878193947</v>
+        <v>11.20881973163188</v>
       </c>
       <c r="E43" t="n">
-        <v>11.33414437538402</v>
+        <v>11.33414533569493</v>
       </c>
       <c r="F43" t="n">
         <v>1248800</v>
@@ -1312,16 +1312,16 @@
         <v>44711</v>
       </c>
       <c r="B45" t="n">
-        <v>11.09916019439697</v>
+        <v>11.09915924072266</v>
       </c>
       <c r="C45" t="n">
-        <v>11.27148328496971</v>
+        <v>11.27148231648886</v>
       </c>
       <c r="D45" t="n">
-        <v>11.02866435066269</v>
+        <v>11.0286634030456</v>
       </c>
       <c r="E45" t="n">
-        <v>11.15398996307938</v>
+        <v>11.15398900469392</v>
       </c>
       <c r="F45" t="n">
         <v>1940200</v>
@@ -1372,16 +1372,16 @@
         <v>44714</v>
       </c>
       <c r="B48" t="n">
-        <v>10.86417388916016</v>
+        <v>10.86417293548584</v>
       </c>
       <c r="C48" t="n">
-        <v>10.98949949686503</v>
+        <v>10.98949853218943</v>
       </c>
       <c r="D48" t="n">
-        <v>10.68401851483428</v>
+        <v>10.68401757697429</v>
       </c>
       <c r="E48" t="n">
-        <v>10.75451360891862</v>
+        <v>10.75451266487045</v>
       </c>
       <c r="F48" t="n">
         <v>3275400</v>
@@ -1412,16 +1412,16 @@
         <v>44718</v>
       </c>
       <c r="B50" t="n">
-        <v>10.61352157592773</v>
+        <v>10.61352252960205</v>
       </c>
       <c r="C50" t="n">
-        <v>10.91117023693893</v>
+        <v>10.91117121735836</v>
       </c>
       <c r="D50" t="n">
-        <v>10.45686458250065</v>
+        <v>10.4568655220986</v>
       </c>
       <c r="E50" t="n">
-        <v>10.81717604088268</v>
+        <v>10.8171770128563</v>
       </c>
       <c r="F50" t="n">
         <v>3175000</v>
@@ -1532,16 +1532,16 @@
         <v>44726</v>
       </c>
       <c r="B56" t="n">
-        <v>10.39420223236084</v>
+        <v>10.39420318603516</v>
       </c>
       <c r="C56" t="n">
-        <v>10.47253035894487</v>
+        <v>10.47253131980584</v>
       </c>
       <c r="D56" t="n">
-        <v>10.01822468495919</v>
+        <v>10.01822560413734</v>
       </c>
       <c r="E56" t="n">
-        <v>10.01822468495919</v>
+        <v>10.01822560413734</v>
       </c>
       <c r="F56" t="n">
         <v>4085600</v>
@@ -1552,16 +1552,16 @@
         <v>44727</v>
       </c>
       <c r="B57" t="n">
-        <v>10.84067440032959</v>
+        <v>10.84067535400391</v>
       </c>
       <c r="C57" t="n">
-        <v>10.84850743674878</v>
+        <v>10.84850839111218</v>
       </c>
       <c r="D57" t="n">
-        <v>10.44119850694474</v>
+        <v>10.44119942547642</v>
       </c>
       <c r="E57" t="n">
-        <v>10.55085877581493</v>
+        <v>10.55085970399363</v>
       </c>
       <c r="F57" t="n">
         <v>3153700</v>
@@ -1572,16 +1572,16 @@
         <v>44729</v>
       </c>
       <c r="B58" t="n">
-        <v>10.45686626434326</v>
+        <v>10.45686531066895</v>
       </c>
       <c r="C58" t="n">
-        <v>10.80151170531431</v>
+        <v>10.80151072020806</v>
       </c>
       <c r="D58" t="n">
-        <v>10.42553486061862</v>
+        <v>10.42553390980175</v>
       </c>
       <c r="E58" t="n">
-        <v>10.74668193554609</v>
+        <v>10.74668095544036</v>
       </c>
       <c r="F58" t="n">
         <v>8202900</v>
@@ -1692,16 +1692,16 @@
         <v>44739</v>
       </c>
       <c r="B64" t="n">
-        <v>10.45686626434326</v>
+        <v>10.45686531066895</v>
       </c>
       <c r="C64" t="n">
-        <v>10.55086047551718</v>
+        <v>10.55085951327052</v>
       </c>
       <c r="D64" t="n">
-        <v>10.33153990244511</v>
+        <v>10.33153896020065</v>
       </c>
       <c r="E64" t="n">
-        <v>10.49602995874937</v>
+        <v>10.4960290015033</v>
       </c>
       <c r="F64" t="n">
         <v>1661400</v>
@@ -1712,16 +1712,16 @@
         <v>44740</v>
       </c>
       <c r="B65" t="n">
-        <v>10.61352157592773</v>
+        <v>10.61352252960205</v>
       </c>
       <c r="C65" t="n">
-        <v>10.86417276541107</v>
+        <v>10.86417374160756</v>
       </c>
       <c r="D65" t="n">
-        <v>10.47252990834362</v>
+        <v>10.47253084934918</v>
       </c>
       <c r="E65" t="n">
-        <v>10.52735966929324</v>
+        <v>10.5273606152255</v>
       </c>
       <c r="F65" t="n">
         <v>5362200</v>
@@ -1732,16 +1732,16 @@
         <v>44741</v>
       </c>
       <c r="B66" t="n">
-        <v>10.68401718139648</v>
+        <v>10.6840181350708</v>
       </c>
       <c r="C66" t="n">
-        <v>10.68401718139648</v>
+        <v>10.6840181350708</v>
       </c>
       <c r="D66" t="n">
-        <v>10.53519248057162</v>
+        <v>10.53519342096158</v>
       </c>
       <c r="E66" t="n">
-        <v>10.62918667461916</v>
+        <v>10.62918762339921</v>
       </c>
       <c r="F66" t="n">
         <v>1613700</v>
@@ -1772,16 +1772,16 @@
         <v>44743</v>
       </c>
       <c r="B68" t="n">
-        <v>10.68401718139648</v>
+        <v>10.6840181350708</v>
       </c>
       <c r="C68" t="n">
-        <v>10.84067417147572</v>
+        <v>10.84067513913352</v>
       </c>
       <c r="D68" t="n">
-        <v>10.54302551682544</v>
+        <v>10.54302645791459</v>
       </c>
       <c r="E68" t="n">
-        <v>10.72318086866671</v>
+        <v>10.72318182583684</v>
       </c>
       <c r="F68" t="n">
         <v>2696600</v>
@@ -1832,16 +1832,16 @@
         <v>44748</v>
       </c>
       <c r="B71" t="n">
-        <v>10.67618465423584</v>
+        <v>10.67618560791016</v>
       </c>
       <c r="C71" t="n">
-        <v>10.71534909037307</v>
+        <v>10.71535004754583</v>
       </c>
       <c r="D71" t="n">
-        <v>10.49602854680439</v>
+        <v>10.49602948438586</v>
       </c>
       <c r="E71" t="n">
-        <v>10.57435741907885</v>
+        <v>10.57435836365721</v>
       </c>
       <c r="F71" t="n">
         <v>1826800</v>
@@ -1892,16 +1892,16 @@
         <v>44753</v>
       </c>
       <c r="B74" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C74" t="n">
-        <v>11.18532085221909</v>
+        <v>11.18531989181933</v>
       </c>
       <c r="D74" t="n">
-        <v>10.83284239674361</v>
+        <v>10.83284146660853</v>
       </c>
       <c r="E74" t="n">
-        <v>11.0599952455611</v>
+        <v>11.05999429592211</v>
       </c>
       <c r="F74" t="n">
         <v>1881000</v>
@@ -1912,16 +1912,16 @@
         <v>44754</v>
       </c>
       <c r="B75" t="n">
-        <v>11.14615535736084</v>
+        <v>11.14615631103516</v>
       </c>
       <c r="C75" t="n">
-        <v>11.22448422760069</v>
+        <v>11.22448518797689</v>
       </c>
       <c r="D75" t="n">
-        <v>10.99733140030449</v>
+        <v>10.99733234124531</v>
       </c>
       <c r="E75" t="n">
-        <v>11.10699166924038</v>
+        <v>11.10699261956382</v>
       </c>
       <c r="F75" t="n">
         <v>1673000</v>
@@ -1932,16 +1932,16 @@
         <v>44755</v>
       </c>
       <c r="B76" t="n">
-        <v>11.17748832702637</v>
+        <v>11.17748737335205</v>
       </c>
       <c r="C76" t="n">
-        <v>11.23231809203646</v>
+        <v>11.23231713368402</v>
       </c>
       <c r="D76" t="n">
-        <v>11.01299828499656</v>
+        <v>11.0129973453567</v>
       </c>
       <c r="E76" t="n">
-        <v>11.18532061702815</v>
+        <v>11.18531966268557</v>
       </c>
       <c r="F76" t="n">
         <v>2559400</v>
@@ -1952,16 +1952,16 @@
         <v>44756</v>
       </c>
       <c r="B77" t="n">
-        <v>10.91117095947266</v>
+        <v>10.91117000579834</v>
       </c>
       <c r="C77" t="n">
-        <v>11.17748823943387</v>
+        <v>11.1774872624825</v>
       </c>
       <c r="D77" t="n">
-        <v>10.84850815795232</v>
+        <v>10.84850720975495</v>
       </c>
       <c r="E77" t="n">
-        <v>11.04432959945326</v>
+        <v>11.04432863414042</v>
       </c>
       <c r="F77" t="n">
         <v>1968500</v>
@@ -1972,16 +1972,16 @@
         <v>44757</v>
       </c>
       <c r="B78" t="n">
-        <v>10.8093433380127</v>
+        <v>10.80934429168701</v>
       </c>
       <c r="C78" t="n">
-        <v>10.98166640959971</v>
+        <v>10.98166737847755</v>
       </c>
       <c r="D78" t="n">
-        <v>10.60568886677345</v>
+        <v>10.60568980247997</v>
       </c>
       <c r="E78" t="n">
-        <v>10.97383337293678</v>
+        <v>10.97383434112354</v>
       </c>
       <c r="F78" t="n">
         <v>2342600</v>
@@ -2012,16 +2012,16 @@
         <v>44761</v>
       </c>
       <c r="B80" t="n">
-        <v>11.09132671356201</v>
+        <v>11.0913257598877</v>
       </c>
       <c r="C80" t="n">
-        <v>11.09132671356201</v>
+        <v>11.0913257598877</v>
       </c>
       <c r="D80" t="n">
-        <v>10.78584573225599</v>
+        <v>10.78584480484809</v>
       </c>
       <c r="E80" t="n">
-        <v>10.87200690059879</v>
+        <v>10.87200596578243</v>
       </c>
       <c r="F80" t="n">
         <v>2890800</v>
@@ -2052,16 +2052,16 @@
         <v>44763</v>
       </c>
       <c r="B82" t="n">
-        <v>11.2479829788208</v>
+        <v>11.24798393249512</v>
       </c>
       <c r="C82" t="n">
-        <v>11.27931437860027</v>
+        <v>11.27931533493105</v>
       </c>
       <c r="D82" t="n">
-        <v>11.05999458014401</v>
+        <v>11.0599955178795</v>
       </c>
       <c r="E82" t="n">
-        <v>11.22448461573608</v>
+        <v>11.22448556741805</v>
       </c>
       <c r="F82" t="n">
         <v>1092700</v>
@@ -2112,16 +2112,16 @@
         <v>44768</v>
       </c>
       <c r="B85" t="n">
-        <v>11.27148246765137</v>
+        <v>11.27148342132568</v>
       </c>
       <c r="C85" t="n">
-        <v>11.38114199706455</v>
+        <v>11.3811429600171</v>
       </c>
       <c r="D85" t="n">
-        <v>11.16965522819662</v>
+        <v>11.16965617325538</v>
       </c>
       <c r="E85" t="n">
-        <v>11.19315359207094</v>
+        <v>11.19315453911789</v>
       </c>
       <c r="F85" t="n">
         <v>1661400</v>
@@ -2132,16 +2132,16 @@
         <v>44769</v>
       </c>
       <c r="B86" t="n">
-        <v>11.24015045166016</v>
+        <v>11.24015140533447</v>
       </c>
       <c r="C86" t="n">
-        <v>11.49080164460048</v>
+        <v>11.49080261954139</v>
       </c>
       <c r="D86" t="n">
-        <v>11.15398854383731</v>
+        <v>11.15398949020119</v>
       </c>
       <c r="E86" t="n">
-        <v>11.28714717683673</v>
+        <v>11.2871481344985</v>
       </c>
       <c r="F86" t="n">
         <v>3096400</v>
@@ -2212,16 +2212,16 @@
         <v>44775</v>
       </c>
       <c r="B90" t="n">
-        <v>10.86417388916016</v>
+        <v>10.86417293548584</v>
       </c>
       <c r="C90" t="n">
-        <v>11.06782837518035</v>
+        <v>11.06782740362892</v>
       </c>
       <c r="D90" t="n">
-        <v>10.7231822069924</v>
+        <v>10.72318126569455</v>
       </c>
       <c r="E90" t="n">
-        <v>10.93466973024404</v>
+        <v>10.93466877038148</v>
       </c>
       <c r="F90" t="n">
         <v>2371400</v>
@@ -2292,16 +2292,16 @@
         <v>44781</v>
       </c>
       <c r="B94" t="n">
-        <v>10.97383403778076</v>
+        <v>10.97383308410645</v>
       </c>
       <c r="C94" t="n">
-        <v>11.10699268111997</v>
+        <v>11.10699171587358</v>
       </c>
       <c r="D94" t="n">
-        <v>10.87200679599199</v>
+        <v>10.8720058511669</v>
       </c>
       <c r="E94" t="n">
-        <v>11.02866380374413</v>
+        <v>11.02866284530486</v>
       </c>
       <c r="F94" t="n">
         <v>2949000</v>
@@ -2352,16 +2352,16 @@
         <v>44784</v>
       </c>
       <c r="B97" t="n">
-        <v>10.89550495147705</v>
+        <v>10.89550590515137</v>
       </c>
       <c r="C97" t="n">
-        <v>11.10699246813669</v>
+        <v>11.10699344032233</v>
       </c>
       <c r="D97" t="n">
-        <v>10.83284214957779</v>
+        <v>10.83284309776729</v>
       </c>
       <c r="E97" t="n">
-        <v>11.05999499321249</v>
+        <v>11.05999596128448</v>
       </c>
       <c r="F97" t="n">
         <v>1665400</v>
@@ -2372,16 +2372,16 @@
         <v>44785</v>
       </c>
       <c r="B98" t="n">
-        <v>11.08349418640137</v>
+        <v>11.08349323272705</v>
       </c>
       <c r="C98" t="n">
-        <v>11.13049166484175</v>
+        <v>11.13049070712356</v>
       </c>
       <c r="D98" t="n">
-        <v>10.78584622861072</v>
+        <v>10.78584530054738</v>
       </c>
       <c r="E98" t="n">
-        <v>10.89550576663898</v>
+        <v>10.89550482914005</v>
       </c>
       <c r="F98" t="n">
         <v>2648400</v>
@@ -2432,16 +2432,16 @@
         <v>44790</v>
       </c>
       <c r="B101" t="n">
-        <v>11.24015045166016</v>
+        <v>11.24015140533447</v>
       </c>
       <c r="C101" t="n">
-        <v>11.25581577771919</v>
+        <v>11.25581673272263</v>
       </c>
       <c r="D101" t="n">
-        <v>10.91117038742624</v>
+        <v>10.91117131318813</v>
       </c>
       <c r="E101" t="n">
-        <v>10.98949851172035</v>
+        <v>10.98949944412802</v>
       </c>
       <c r="F101" t="n">
         <v>4396400</v>
@@ -2452,16 +2452,16 @@
         <v>44791</v>
       </c>
       <c r="B102" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="C102" t="n">
-        <v>11.37330994384684</v>
+        <v>11.37330897550059</v>
       </c>
       <c r="D102" t="n">
-        <v>11.09915962060828</v>
+        <v>11.09915867560374</v>
       </c>
       <c r="E102" t="n">
-        <v>11.27931499239396</v>
+        <v>11.27931403205064</v>
       </c>
       <c r="F102" t="n">
         <v>2180500</v>
@@ -2532,16 +2532,16 @@
         <v>44797</v>
       </c>
       <c r="B106" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C106" t="n">
-        <v>11.3968083737041</v>
+        <v>11.39680739514549</v>
       </c>
       <c r="D106" t="n">
-        <v>11.09915968439161</v>
+        <v>11.09915873138986</v>
       </c>
       <c r="E106" t="n">
-        <v>11.2244852910496</v>
+        <v>11.22448432728707</v>
       </c>
       <c r="F106" t="n">
         <v>2116800</v>
@@ -2652,16 +2652,16 @@
         <v>44805</v>
       </c>
       <c r="B112" t="n">
-        <v>11.65529346466064</v>
+        <v>11.65529251098633</v>
       </c>
       <c r="C112" t="n">
-        <v>12.1565966744416</v>
+        <v>12.15659567974902</v>
       </c>
       <c r="D112" t="n">
-        <v>11.42030756173208</v>
+        <v>11.42030662728508</v>
       </c>
       <c r="E112" t="n">
-        <v>12.14093059897989</v>
+        <v>12.14092960556915</v>
       </c>
       <c r="F112" t="n">
         <v>4716400</v>
@@ -2712,16 +2712,16 @@
         <v>44810</v>
       </c>
       <c r="B115" t="n">
-        <v>11.58479690551758</v>
+        <v>11.58479785919189</v>
       </c>
       <c r="C115" t="n">
-        <v>11.90594396270576</v>
+        <v>11.90594494281729</v>
       </c>
       <c r="D115" t="n">
-        <v>11.49863573678402</v>
+        <v>11.49863668336545</v>
       </c>
       <c r="E115" t="n">
-        <v>11.89811092545738</v>
+        <v>11.89811190492408</v>
       </c>
       <c r="F115" t="n">
         <v>1316500</v>
@@ -2732,16 +2732,16 @@
         <v>44812</v>
       </c>
       <c r="B116" t="n">
-        <v>11.4359712600708</v>
+        <v>11.43597221374512</v>
       </c>
       <c r="C116" t="n">
-        <v>11.63962496974372</v>
+        <v>11.63962594040124</v>
       </c>
       <c r="D116" t="n">
-        <v>11.37330846524845</v>
+        <v>11.37330941369716</v>
       </c>
       <c r="E116" t="n">
-        <v>11.62395964453786</v>
+        <v>11.623960613889</v>
       </c>
       <c r="F116" t="n">
         <v>2598100</v>
@@ -2772,16 +2772,16 @@
         <v>44816</v>
       </c>
       <c r="B118" t="n">
-        <v>11.41247272491455</v>
+        <v>11.41247367858887</v>
       </c>
       <c r="C118" t="n">
-        <v>11.64745859079944</v>
+        <v>11.64745956411016</v>
       </c>
       <c r="D118" t="n">
-        <v>11.35764296344122</v>
+        <v>11.35764391253373</v>
       </c>
       <c r="E118" t="n">
-        <v>11.39680739892195</v>
+        <v>11.3968083512872</v>
       </c>
       <c r="F118" t="n">
         <v>2097200</v>
@@ -2792,16 +2792,16 @@
         <v>44817</v>
       </c>
       <c r="B119" t="n">
-        <v>11.24015045166016</v>
+        <v>11.24015140533447</v>
       </c>
       <c r="C119" t="n">
-        <v>11.43597188289466</v>
+        <v>11.43597285318351</v>
       </c>
       <c r="D119" t="n">
-        <v>11.16965461689582</v>
+        <v>11.16965556458889</v>
       </c>
       <c r="E119" t="n">
-        <v>11.30281324989524</v>
+        <v>11.3028142088862</v>
       </c>
       <c r="F119" t="n">
         <v>1768400</v>
@@ -2812,16 +2812,16 @@
         <v>44818</v>
       </c>
       <c r="B120" t="n">
-        <v>11.20882034301758</v>
+        <v>11.20881938934326</v>
       </c>
       <c r="C120" t="n">
-        <v>11.42030712465965</v>
+        <v>11.42030615299151</v>
       </c>
       <c r="D120" t="n">
-        <v>11.02866421710068</v>
+        <v>11.02866327875449</v>
       </c>
       <c r="E120" t="n">
-        <v>11.2009873055865</v>
+        <v>11.20098635257864</v>
       </c>
       <c r="F120" t="n">
         <v>1856400</v>
@@ -2912,16 +2912,16 @@
         <v>44825</v>
       </c>
       <c r="B125" t="n">
-        <v>11.09132671356201</v>
+        <v>11.0913257598877</v>
       </c>
       <c r="C125" t="n">
-        <v>11.23231839539528</v>
+        <v>11.23231742959796</v>
       </c>
       <c r="D125" t="n">
-        <v>10.93466970430257</v>
+        <v>10.93466876409822</v>
       </c>
       <c r="E125" t="n">
-        <v>11.13049115262676</v>
+        <v>11.13049019558493</v>
       </c>
       <c r="F125" t="n">
         <v>2825100</v>
@@ -2952,16 +2952,16 @@
         <v>44827</v>
       </c>
       <c r="B127" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="C127" t="n">
-        <v>11.30281410375695</v>
+        <v>11.30281314141286</v>
       </c>
       <c r="D127" t="n">
-        <v>11.07566125624483</v>
+        <v>11.07566031324099</v>
       </c>
       <c r="E127" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="F127" t="n">
         <v>2444100</v>
@@ -2992,16 +2992,16 @@
         <v>44831</v>
       </c>
       <c r="B129" t="n">
-        <v>10.90333843231201</v>
+        <v>10.9033374786377</v>
       </c>
       <c r="C129" t="n">
-        <v>11.04433011582452</v>
+        <v>11.04432914981819</v>
       </c>
       <c r="D129" t="n">
-        <v>10.77017978610565</v>
+        <v>10.77017884407822</v>
       </c>
       <c r="E129" t="n">
-        <v>11.04433011582452</v>
+        <v>11.04432914981819</v>
       </c>
       <c r="F129" t="n">
         <v>2130200</v>
@@ -3052,16 +3052,16 @@
         <v>44834</v>
       </c>
       <c r="B132" t="n">
-        <v>10.61352157592773</v>
+        <v>10.61352252960205</v>
       </c>
       <c r="C132" t="n">
-        <v>10.74668020709063</v>
+        <v>10.74668117272986</v>
       </c>
       <c r="D132" t="n">
-        <v>10.59785550308529</v>
+        <v>10.59785645535194</v>
       </c>
       <c r="E132" t="n">
-        <v>10.70751577198399</v>
+        <v>10.70751673410412</v>
       </c>
       <c r="F132" t="n">
         <v>4019300</v>
@@ -3072,16 +3072,16 @@
         <v>44837</v>
       </c>
       <c r="B133" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="C133" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="D133" t="n">
-        <v>10.62918785134206</v>
+        <v>10.62918694635185</v>
       </c>
       <c r="E133" t="n">
-        <v>10.74668116715839</v>
+        <v>10.74668025216456</v>
       </c>
       <c r="F133" t="n">
         <v>2250700</v>
@@ -3112,16 +3112,16 @@
         <v>44839</v>
       </c>
       <c r="B135" t="n">
-        <v>10.97383403778076</v>
+        <v>10.97383308410645</v>
       </c>
       <c r="C135" t="n">
-        <v>11.20881992290874</v>
+        <v>11.20881894881312</v>
       </c>
       <c r="D135" t="n">
-        <v>10.85634072171701</v>
+        <v>10.85633977825337</v>
       </c>
       <c r="E135" t="n">
-        <v>11.20881992290874</v>
+        <v>11.20881894881312</v>
       </c>
       <c r="F135" t="n">
         <v>5244200</v>
@@ -3132,16 +3132,16 @@
         <v>44840</v>
       </c>
       <c r="B136" t="n">
-        <v>10.98949909210205</v>
+        <v>10.98950004577637</v>
       </c>
       <c r="C136" t="n">
-        <v>11.1226577321339</v>
+        <v>11.12265869736379</v>
       </c>
       <c r="D136" t="n">
-        <v>10.88767185284243</v>
+        <v>10.88767279768013</v>
       </c>
       <c r="E136" t="n">
-        <v>11.02866352981721</v>
+        <v>11.02866448689024</v>
       </c>
       <c r="F136" t="n">
         <v>3101100</v>
@@ -3152,16 +3152,16 @@
         <v>44841</v>
       </c>
       <c r="B137" t="n">
-        <v>11.02866458892822</v>
+        <v>11.02866363525391</v>
       </c>
       <c r="C137" t="n">
-        <v>11.15399020405247</v>
+        <v>11.15398923954096</v>
       </c>
       <c r="D137" t="n">
-        <v>10.9425034152802</v>
+        <v>10.94250246905644</v>
       </c>
       <c r="E137" t="n">
-        <v>10.98166785675642</v>
+        <v>10.98166690714602</v>
       </c>
       <c r="F137" t="n">
         <v>7588600</v>
@@ -3172,16 +3172,16 @@
         <v>44844</v>
       </c>
       <c r="B138" t="n">
-        <v>11.07565975189209</v>
+        <v>11.07566165924072</v>
       </c>
       <c r="C138" t="n">
-        <v>11.35764232695178</v>
+        <v>11.35764428286087</v>
       </c>
       <c r="D138" t="n">
-        <v>11.01299695743438</v>
+        <v>11.0129988539918</v>
       </c>
       <c r="E138" t="n">
-        <v>11.07565975189209</v>
+        <v>11.07566165924072</v>
       </c>
       <c r="F138" t="n">
         <v>2000500</v>
@@ -3212,16 +3212,16 @@
         <v>44847</v>
       </c>
       <c r="B140" t="n">
-        <v>10.91117095947266</v>
+        <v>10.91117000579834</v>
       </c>
       <c r="C140" t="n">
-        <v>11.20098660325412</v>
+        <v>11.20098562424891</v>
       </c>
       <c r="D140" t="n">
-        <v>10.87200652177256</v>
+        <v>10.87200557152136</v>
       </c>
       <c r="E140" t="n">
-        <v>11.12265772785393</v>
+        <v>11.12265675569494</v>
       </c>
       <c r="F140" t="n">
         <v>3739400</v>
@@ -3232,16 +3232,16 @@
         <v>44848</v>
       </c>
       <c r="B141" t="n">
-        <v>10.8250093460083</v>
+        <v>10.82500839233398</v>
       </c>
       <c r="C141" t="n">
-        <v>11.1618224737291</v>
+        <v>11.16182149038183</v>
       </c>
       <c r="D141" t="n">
-        <v>10.8250093460083</v>
+        <v>10.82500839233398</v>
       </c>
       <c r="E141" t="n">
-        <v>10.97383406397776</v>
+        <v>10.97383309719211</v>
       </c>
       <c r="F141" t="n">
         <v>3601200</v>
@@ -3272,16 +3272,16 @@
         <v>44852</v>
       </c>
       <c r="B143" t="n">
-        <v>11.27148246765137</v>
+        <v>11.27148342132568</v>
       </c>
       <c r="C143" t="n">
-        <v>11.37330970710612</v>
+        <v>11.37331066939599</v>
       </c>
       <c r="D143" t="n">
-        <v>11.06782798874186</v>
+        <v>11.06782892518508</v>
       </c>
       <c r="E143" t="n">
-        <v>11.20881966598683</v>
+        <v>11.20882061435928</v>
       </c>
       <c r="F143" t="n">
         <v>2646800</v>
@@ -3312,16 +3312,16 @@
         <v>44854</v>
       </c>
       <c r="B145" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C145" t="n">
-        <v>10.98166755090811</v>
+        <v>10.98166658413194</v>
       </c>
       <c r="D145" t="n">
-        <v>10.39420318612486</v>
+        <v>10.39420227106638</v>
       </c>
       <c r="E145" t="n">
-        <v>10.5743585660986</v>
+        <v>10.57435763518006</v>
       </c>
       <c r="F145" t="n">
         <v>7194300</v>
@@ -3352,16 +3352,16 @@
         <v>44858</v>
       </c>
       <c r="B147" t="n">
-        <v>11.2479829788208</v>
+        <v>11.24798393249512</v>
       </c>
       <c r="C147" t="n">
-        <v>11.45163745088707</v>
+        <v>11.45163842182848</v>
       </c>
       <c r="D147" t="n">
-        <v>11.10699205331296</v>
+        <v>11.10699299503318</v>
       </c>
       <c r="E147" t="n">
-        <v>11.10699205331296</v>
+        <v>11.10699299503318</v>
       </c>
       <c r="F147" t="n">
         <v>2219500</v>
@@ -3372,16 +3372,16 @@
         <v>44859</v>
       </c>
       <c r="B148" t="n">
-        <v>11.38897514343262</v>
+        <v>11.38897609710693</v>
       </c>
       <c r="C148" t="n">
-        <v>11.50646771093245</v>
+        <v>11.5064686744452</v>
       </c>
       <c r="D148" t="n">
-        <v>11.18532066256667</v>
+        <v>11.18532159918765</v>
       </c>
       <c r="E148" t="n">
-        <v>11.24015117479952</v>
+        <v>11.24015211601182</v>
       </c>
       <c r="F148" t="n">
         <v>2935500</v>
@@ -3392,16 +3392,16 @@
         <v>44860</v>
       </c>
       <c r="B149" t="n">
-        <v>11.3419771194458</v>
+        <v>11.34197807312012</v>
       </c>
       <c r="C149" t="n">
-        <v>11.451637391606</v>
+        <v>11.45163835450095</v>
       </c>
       <c r="D149" t="n">
-        <v>11.20098619466782</v>
+        <v>11.20098713648711</v>
       </c>
       <c r="E149" t="n">
-        <v>11.43597206529711</v>
+        <v>11.43597302687486</v>
       </c>
       <c r="F149" t="n">
         <v>4386900</v>
@@ -3412,16 +3412,16 @@
         <v>44861</v>
       </c>
       <c r="B150" t="n">
-        <v>11.35764312744141</v>
+        <v>11.35764408111572</v>
       </c>
       <c r="C150" t="n">
-        <v>11.63179343276565</v>
+        <v>11.63179440945972</v>
       </c>
       <c r="D150" t="n">
-        <v>11.27148196573925</v>
+        <v>11.27148291217882</v>
       </c>
       <c r="E150" t="n">
-        <v>11.42813896292475</v>
+        <v>11.42813992251844</v>
       </c>
       <c r="F150" t="n">
         <v>4207900</v>
@@ -3512,16 +3512,16 @@
         <v>44869</v>
       </c>
       <c r="B155" t="n">
-        <v>11.67095756530762</v>
+        <v>11.67095851898193</v>
       </c>
       <c r="C155" t="n">
-        <v>11.87461204288736</v>
+        <v>11.87461301320299</v>
       </c>
       <c r="D155" t="n">
-        <v>11.64745920158673</v>
+        <v>11.64746015334091</v>
       </c>
       <c r="E155" t="n">
-        <v>11.7492864403766</v>
+        <v>11.74928740045144</v>
       </c>
       <c r="F155" t="n">
         <v>2161500</v>
@@ -3532,16 +3532,16 @@
         <v>44872</v>
       </c>
       <c r="B156" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="C156" t="n">
-        <v>11.65529255720685</v>
+        <v>11.65529156485204</v>
       </c>
       <c r="D156" t="n">
-        <v>11.12265798497174</v>
+        <v>11.1226570379665</v>
       </c>
       <c r="E156" t="n">
-        <v>11.60829508148041</v>
+        <v>11.60829409312706</v>
       </c>
       <c r="F156" t="n">
         <v>3276500</v>
@@ -3632,16 +3632,16 @@
         <v>44879</v>
       </c>
       <c r="B161" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C161" t="n">
-        <v>10.9660014759541</v>
+        <v>10.9660005105571</v>
       </c>
       <c r="D161" t="n">
-        <v>10.71535025268644</v>
+        <v>10.71534930935563</v>
       </c>
       <c r="E161" t="n">
-        <v>10.94250311052265</v>
+        <v>10.94250214719434</v>
       </c>
       <c r="F161" t="n">
         <v>1203700</v>
@@ -3652,16 +3652,16 @@
         <v>44881</v>
       </c>
       <c r="B162" t="n">
-        <v>10.90333843231201</v>
+        <v>10.9033374786377</v>
       </c>
       <c r="C162" t="n">
-        <v>10.90333843231201</v>
+        <v>10.9033374786377</v>
       </c>
       <c r="D162" t="n">
-        <v>10.59785670036809</v>
+        <v>10.59785577341312</v>
       </c>
       <c r="E162" t="n">
-        <v>10.86417399278081</v>
+        <v>10.86417304253206</v>
       </c>
       <c r="F162" t="n">
         <v>5270300</v>
@@ -3692,16 +3692,16 @@
         <v>44883</v>
       </c>
       <c r="B164" t="n">
-        <v>10.78584480285645</v>
+        <v>10.78584671020508</v>
       </c>
       <c r="C164" t="n">
-        <v>10.98949852384542</v>
+        <v>10.9895004672078</v>
       </c>
       <c r="D164" t="n">
-        <v>10.57435729833009</v>
+        <v>10.57435916827967</v>
       </c>
       <c r="E164" t="n">
-        <v>10.80934316547066</v>
+        <v>10.8093450769747</v>
       </c>
       <c r="F164" t="n">
         <v>3568700</v>
@@ -3752,16 +3752,16 @@
         <v>44888</v>
       </c>
       <c r="B167" t="n">
-        <v>10.56652545928955</v>
+        <v>10.56652450561523</v>
       </c>
       <c r="C167" t="n">
-        <v>10.81717742791213</v>
+        <v>10.8171764516154</v>
       </c>
       <c r="D167" t="n">
-        <v>10.51952872873502</v>
+        <v>10.51952777930236</v>
       </c>
       <c r="E167" t="n">
-        <v>10.80934439048652</v>
+        <v>10.80934341489675</v>
       </c>
       <c r="F167" t="n">
         <v>4669400</v>
@@ -3792,16 +3792,16 @@
         <v>44890</v>
       </c>
       <c r="B169" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C169" t="n">
-        <v>11.03649731924802</v>
+        <v>11.03649634764489</v>
       </c>
       <c r="D169" t="n">
-        <v>10.71535025268644</v>
+        <v>10.71534930935563</v>
       </c>
       <c r="E169" t="n">
-        <v>10.95033540100009</v>
+        <v>10.95033443698226</v>
       </c>
       <c r="F169" t="n">
         <v>1631500</v>
@@ -3812,16 +3812,16 @@
         <v>44893</v>
       </c>
       <c r="B170" t="n">
-        <v>10.97383403778076</v>
+        <v>10.97383308410645</v>
       </c>
       <c r="C170" t="n">
-        <v>11.09915964398247</v>
+        <v>11.09915867941681</v>
       </c>
       <c r="D170" t="n">
-        <v>10.68401838668942</v>
+        <v>10.68401745820135</v>
       </c>
       <c r="E170" t="n">
-        <v>10.84067539444156</v>
+        <v>10.84067445233931</v>
       </c>
       <c r="F170" t="n">
         <v>4990000</v>
@@ -3852,16 +3852,16 @@
         <v>44895</v>
       </c>
       <c r="B172" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C172" t="n">
-        <v>11.20882040874432</v>
+        <v>11.20881942197064</v>
       </c>
       <c r="D172" t="n">
-        <v>10.69185114025542</v>
+        <v>10.69185019899337</v>
       </c>
       <c r="E172" t="n">
-        <v>11.20882040874432</v>
+        <v>11.20881942197064</v>
       </c>
       <c r="F172" t="n">
         <v>4586400</v>
@@ -3972,16 +3972,16 @@
         <v>44903</v>
       </c>
       <c r="B178" t="n">
-        <v>11.26364994049072</v>
+        <v>11.26364898681641</v>
       </c>
       <c r="C178" t="n">
-        <v>11.81194985337145</v>
+        <v>11.8119488532735</v>
       </c>
       <c r="D178" t="n">
-        <v>11.15398965911476</v>
+        <v>11.15398871472519</v>
       </c>
       <c r="E178" t="n">
-        <v>11.74928704887077</v>
+        <v>11.74928605407837</v>
       </c>
       <c r="F178" t="n">
         <v>12105700</v>
@@ -3992,16 +3992,16 @@
         <v>44904</v>
       </c>
       <c r="B179" t="n">
-        <v>11.17748832702637</v>
+        <v>11.17748737335205</v>
       </c>
       <c r="C179" t="n">
-        <v>11.56913121309737</v>
+        <v>11.5691302260077</v>
       </c>
       <c r="D179" t="n">
-        <v>11.04432968600226</v>
+        <v>11.04432874368917</v>
       </c>
       <c r="E179" t="n">
-        <v>11.29498089404786</v>
+        <v>11.29497993034896</v>
       </c>
       <c r="F179" t="n">
         <v>7204400</v>
@@ -4032,16 +4032,16 @@
         <v>44908</v>
       </c>
       <c r="B181" t="n">
-        <v>11.08349418640137</v>
+        <v>11.08349323272705</v>
       </c>
       <c r="C181" t="n">
-        <v>11.30281475645706</v>
+        <v>11.3028137839114</v>
       </c>
       <c r="D181" t="n">
-        <v>10.9973330140935</v>
+        <v>10.99733206783289</v>
       </c>
       <c r="E181" t="n">
-        <v>11.00516605166683</v>
+        <v>11.00516510473222</v>
       </c>
       <c r="F181" t="n">
         <v>3594700</v>
@@ -4092,16 +4092,16 @@
         <v>44911</v>
       </c>
       <c r="B184" t="n">
-        <v>11.2479829788208</v>
+        <v>11.24798393249512</v>
       </c>
       <c r="C184" t="n">
-        <v>11.2479829788208</v>
+        <v>11.24798393249512</v>
       </c>
       <c r="D184" t="n">
-        <v>10.90333758124669</v>
+        <v>10.90333850569981</v>
       </c>
       <c r="E184" t="n">
-        <v>11.04432925375403</v>
+        <v>11.04433019016131</v>
       </c>
       <c r="F184" t="n">
         <v>3365900</v>
@@ -4112,16 +4112,16 @@
         <v>44914</v>
       </c>
       <c r="B185" t="n">
-        <v>11.37331008911133</v>
+        <v>11.37330913543701</v>
       </c>
       <c r="C185" t="n">
-        <v>11.5221340613134</v>
+        <v>11.5221330951599</v>
       </c>
       <c r="D185" t="n">
-        <v>11.18532093080405</v>
+        <v>11.18531999289299</v>
       </c>
       <c r="E185" t="n">
-        <v>11.23231840713075</v>
+        <v>11.23231746527886</v>
       </c>
       <c r="F185" t="n">
         <v>3838800</v>
@@ -4152,16 +4152,16 @@
         <v>44916</v>
       </c>
       <c r="B187" t="n">
-        <v>11.58479690551758</v>
+        <v>11.58479785919189</v>
       </c>
       <c r="C187" t="n">
-        <v>11.75711998998425</v>
+        <v>11.7571209578444</v>
       </c>
       <c r="D187" t="n">
-        <v>11.15398956785069</v>
+        <v>11.15399048606043</v>
       </c>
       <c r="E187" t="n">
-        <v>11.42813989554768</v>
+        <v>11.4281408363258</v>
       </c>
       <c r="F187" t="n">
         <v>6348400</v>
@@ -4252,16 +4252,16 @@
         <v>44923</v>
       </c>
       <c r="B192" t="n">
-        <v>11.58479690551758</v>
+        <v>11.58479785919189</v>
       </c>
       <c r="C192" t="n">
-        <v>11.69445718599628</v>
+        <v>11.69445814869797</v>
       </c>
       <c r="D192" t="n">
-        <v>11.49863573678402</v>
+        <v>11.49863668336545</v>
       </c>
       <c r="E192" t="n">
-        <v>11.5769638682692</v>
+        <v>11.57696482129869</v>
       </c>
       <c r="F192" t="n">
         <v>2005900</v>
@@ -4272,16 +4272,16 @@
         <v>44924</v>
       </c>
       <c r="B193" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="C193" t="n">
-        <v>11.73362032145083</v>
+        <v>11.73362129131107</v>
       </c>
       <c r="D193" t="n">
-        <v>11.4751360805163</v>
+        <v>11.47513702901113</v>
       </c>
       <c r="E193" t="n">
-        <v>11.62396079317528</v>
+        <v>11.62396175397144</v>
       </c>
       <c r="F193" t="n">
         <v>2424800</v>
@@ -4292,16 +4292,16 @@
         <v>44928</v>
       </c>
       <c r="B194" t="n">
-        <v>11.3419771194458</v>
+        <v>11.34197807312012</v>
       </c>
       <c r="C194" t="n">
-        <v>11.46730346491438</v>
+        <v>11.46730442912659</v>
       </c>
       <c r="D194" t="n">
-        <v>11.17748783170473</v>
+        <v>11.1774887715482</v>
       </c>
       <c r="E194" t="n">
-        <v>11.38897459237146</v>
+        <v>11.38897554999749</v>
       </c>
       <c r="F194" t="n">
         <v>1018800</v>
@@ -4312,16 +4312,16 @@
         <v>44929</v>
       </c>
       <c r="B195" t="n">
-        <v>11.13832378387451</v>
+        <v>11.13832473754883</v>
       </c>
       <c r="C195" t="n">
-        <v>11.32631218813412</v>
+        <v>11.32631315790418</v>
       </c>
       <c r="D195" t="n">
-        <v>11.05999490859992</v>
+        <v>11.05999585556764</v>
       </c>
       <c r="E195" t="n">
-        <v>11.30281382435154</v>
+        <v>11.30281479210966</v>
       </c>
       <c r="F195" t="n">
         <v>1562800</v>
@@ -4332,16 +4332,16 @@
         <v>44930</v>
       </c>
       <c r="B196" t="n">
-        <v>11.35764312744141</v>
+        <v>11.35764408111572</v>
       </c>
       <c r="C196" t="n">
-        <v>11.35764312744141</v>
+        <v>11.35764408111572</v>
       </c>
       <c r="D196" t="n">
-        <v>10.96600026097791</v>
+        <v>10.9660011817669</v>
       </c>
       <c r="E196" t="n">
-        <v>11.1696547308188</v>
+        <v>11.16965566870818</v>
       </c>
       <c r="F196" t="n">
         <v>2937400</v>
@@ -4352,16 +4352,16 @@
         <v>44931</v>
       </c>
       <c r="B197" t="n">
-        <v>11.41247272491455</v>
+        <v>11.41247367858887</v>
       </c>
       <c r="C197" t="n">
-        <v>11.41247272491455</v>
+        <v>11.41247367858887</v>
       </c>
       <c r="D197" t="n">
-        <v>11.08349266207561</v>
+        <v>11.08349358825896</v>
       </c>
       <c r="E197" t="n">
-        <v>11.31064549146445</v>
+        <v>11.31064643662965</v>
       </c>
       <c r="F197" t="n">
         <v>4358300</v>
@@ -4372,16 +4372,16 @@
         <v>44932</v>
       </c>
       <c r="B198" t="n">
-        <v>11.42030715942383</v>
+        <v>11.42030620574951</v>
       </c>
       <c r="C198" t="n">
-        <v>11.53779973324935</v>
+        <v>11.53779876976359</v>
       </c>
       <c r="D198" t="n">
-        <v>11.31847991350858</v>
+        <v>11.31847896833754</v>
       </c>
       <c r="E198" t="n">
-        <v>11.41247412196891</v>
+        <v>11.4124731689487</v>
       </c>
       <c r="F198" t="n">
         <v>2864500</v>
@@ -4432,16 +4432,16 @@
         <v>44937</v>
       </c>
       <c r="B201" t="n">
-        <v>11.49863624572754</v>
+        <v>11.49863529205322</v>
       </c>
       <c r="C201" t="n">
-        <v>11.61612882165544</v>
+        <v>11.61612785823652</v>
       </c>
       <c r="D201" t="n">
-        <v>11.0678288889926</v>
+        <v>11.06782797104859</v>
       </c>
       <c r="E201" t="n">
-        <v>11.09132725477826</v>
+        <v>11.09132633488535</v>
       </c>
       <c r="F201" t="n">
         <v>4499200</v>
@@ -4472,16 +4472,16 @@
         <v>44939</v>
       </c>
       <c r="B203" t="n">
-        <v>11.58479690551758</v>
+        <v>11.58479785919189</v>
       </c>
       <c r="C203" t="n">
-        <v>11.78845139197822</v>
+        <v>11.78845236241762</v>
       </c>
       <c r="D203" t="n">
-        <v>11.44380522304489</v>
+        <v>11.4438061651126</v>
       </c>
       <c r="E203" t="n">
-        <v>11.74928695273586</v>
+        <v>11.7492879199512</v>
       </c>
       <c r="F203" t="n">
         <v>2269100</v>
@@ -4512,16 +4512,16 @@
         <v>44943</v>
       </c>
       <c r="B205" t="n">
-        <v>11.74928665161133</v>
+        <v>11.74928569793701</v>
       </c>
       <c r="C205" t="n">
-        <v>11.93727505875722</v>
+        <v>11.93727408982413</v>
       </c>
       <c r="D205" t="n">
-        <v>11.60829497275214</v>
+        <v>11.60829403052194</v>
       </c>
       <c r="E205" t="n">
-        <v>11.81194945399329</v>
+        <v>11.81194849523272</v>
       </c>
       <c r="F205" t="n">
         <v>2676600</v>
@@ -4532,16 +4532,16 @@
         <v>44944</v>
       </c>
       <c r="B206" t="n">
-        <v>11.41247272491455</v>
+        <v>11.41247367858887</v>
       </c>
       <c r="C206" t="n">
-        <v>11.89027749318036</v>
+        <v>11.89027848678206</v>
       </c>
       <c r="D206" t="n">
-        <v>11.41247272491455</v>
+        <v>11.41247367858887</v>
       </c>
       <c r="E206" t="n">
-        <v>11.87461142018828</v>
+        <v>11.87461241248085</v>
       </c>
       <c r="F206" t="n">
         <v>3532000</v>
@@ -4552,16 +4552,16 @@
         <v>44945</v>
       </c>
       <c r="B207" t="n">
-        <v>11.66312599182129</v>
+        <v>11.66312503814697</v>
       </c>
       <c r="C207" t="n">
-        <v>11.68662435698559</v>
+        <v>11.68662340138985</v>
       </c>
       <c r="D207" t="n">
-        <v>11.27931537680668</v>
+        <v>11.27931445451592</v>
       </c>
       <c r="E207" t="n">
-        <v>11.3419781819112</v>
+        <v>11.3419772544966</v>
       </c>
       <c r="F207" t="n">
         <v>1847800</v>
@@ -4572,16 +4572,16 @@
         <v>44946</v>
       </c>
       <c r="B208" t="n">
-        <v>11.58479690551758</v>
+        <v>11.58479785919189</v>
       </c>
       <c r="C208" t="n">
-        <v>11.6866241487479</v>
+        <v>11.68662511080476</v>
       </c>
       <c r="D208" t="n">
-        <v>11.48296966228726</v>
+        <v>11.48297060757903</v>
       </c>
       <c r="E208" t="n">
-        <v>11.65529274675392</v>
+        <v>11.65529370623154</v>
       </c>
       <c r="F208" t="n">
         <v>2012100</v>
@@ -4592,16 +4592,16 @@
         <v>44949</v>
       </c>
       <c r="B209" t="n">
-        <v>11.52213287353516</v>
+        <v>11.52213382720947</v>
       </c>
       <c r="C209" t="n">
-        <v>11.64745846815425</v>
+        <v>11.64745943220163</v>
       </c>
       <c r="D209" t="n">
-        <v>11.34980980743417</v>
+        <v>11.34981074684549</v>
       </c>
       <c r="E209" t="n">
-        <v>11.59262870725826</v>
+        <v>11.59262966676744</v>
       </c>
       <c r="F209" t="n">
         <v>1770800</v>
@@ -4632,16 +4632,16 @@
         <v>44951</v>
       </c>
       <c r="B211" t="n">
-        <v>11.89027881622314</v>
+        <v>11.89027786254883</v>
       </c>
       <c r="C211" t="n">
-        <v>12.07043419368129</v>
+        <v>12.07043322555739</v>
       </c>
       <c r="D211" t="n">
-        <v>11.62396152172019</v>
+        <v>11.62396058940618</v>
       </c>
       <c r="E211" t="n">
-        <v>11.67879128929448</v>
+        <v>11.67879035258278</v>
       </c>
       <c r="F211" t="n">
         <v>10764800</v>
@@ -4652,16 +4652,16 @@
         <v>44952</v>
       </c>
       <c r="B212" t="n">
-        <v>11.96860504150391</v>
+        <v>11.96860599517822</v>
       </c>
       <c r="C212" t="n">
-        <v>12.09393063141503</v>
+        <v>12.09393159507546</v>
       </c>
       <c r="D212" t="n">
-        <v>11.79628272887583</v>
+        <v>11.79628366881928</v>
       </c>
       <c r="E212" t="n">
-        <v>11.91377528266765</v>
+        <v>11.91377623197306</v>
       </c>
       <c r="F212" t="n">
         <v>8143300</v>
@@ -4712,16 +4712,16 @@
         <v>44957</v>
       </c>
       <c r="B215" t="n">
-        <v>12.07043266296387</v>
+        <v>12.07043361663818</v>
       </c>
       <c r="C215" t="n">
-        <v>12.14092849633346</v>
+        <v>12.14092945557759</v>
       </c>
       <c r="D215" t="n">
-        <v>11.8276145113569</v>
+        <v>11.82761544584636</v>
       </c>
       <c r="E215" t="n">
-        <v>11.84327983710599</v>
+        <v>11.84328077283316</v>
       </c>
       <c r="F215" t="n">
         <v>5446800</v>
@@ -4852,16 +4852,16 @@
         <v>44966</v>
       </c>
       <c r="B222" t="n">
-        <v>11.66312599182129</v>
+        <v>11.66312503814697</v>
       </c>
       <c r="C222" t="n">
-        <v>11.78845160203032</v>
+        <v>11.78845063810834</v>
       </c>
       <c r="D222" t="n">
-        <v>11.55346570938861</v>
+        <v>11.55346476468103</v>
       </c>
       <c r="E222" t="n">
-        <v>11.7101227221499</v>
+        <v>11.71012176463273</v>
       </c>
       <c r="F222" t="n">
         <v>2260100</v>
@@ -4872,16 +4872,16 @@
         <v>44967</v>
       </c>
       <c r="B223" t="n">
-        <v>11.72578907012939</v>
+        <v>11.72578811645508</v>
       </c>
       <c r="C223" t="n">
-        <v>11.88244608654069</v>
+        <v>11.88244512012525</v>
       </c>
       <c r="D223" t="n">
-        <v>11.62396182271216</v>
+        <v>11.62396087731959</v>
       </c>
       <c r="E223" t="n">
-        <v>11.62396182271216</v>
+        <v>11.62396087731959</v>
       </c>
       <c r="F223" t="n">
         <v>6075300</v>
@@ -4912,16 +4912,16 @@
         <v>44971</v>
       </c>
       <c r="B225" t="n">
-        <v>11.71795463562012</v>
+        <v>11.71795558929443</v>
       </c>
       <c r="C225" t="n">
-        <v>11.88244466999244</v>
+        <v>11.8824456370539</v>
       </c>
       <c r="D225" t="n">
-        <v>11.51430016506401</v>
+        <v>11.51430110216375</v>
       </c>
       <c r="E225" t="n">
-        <v>11.78061743471438</v>
+        <v>11.78061839348856</v>
       </c>
       <c r="F225" t="n">
         <v>2141000</v>
@@ -4932,16 +4932,16 @@
         <v>44972</v>
       </c>
       <c r="B226" t="n">
-        <v>11.75711917877197</v>
+        <v>11.75712013244629</v>
       </c>
       <c r="C226" t="n">
-        <v>11.92944150434928</v>
+        <v>11.92944247200145</v>
       </c>
       <c r="D226" t="n">
-        <v>11.63179357944321</v>
+        <v>11.63179452295179</v>
       </c>
       <c r="E226" t="n">
-        <v>11.6631249792754</v>
+        <v>11.66312592532541</v>
       </c>
       <c r="F226" t="n">
         <v>3961900</v>
@@ -4952,16 +4952,16 @@
         <v>44973</v>
       </c>
       <c r="B227" t="n">
-        <v>11.89027881622314</v>
+        <v>11.89027786254883</v>
       </c>
       <c r="C227" t="n">
-        <v>11.9764399862684</v>
+        <v>11.97643902568342</v>
       </c>
       <c r="D227" t="n">
-        <v>11.57696404451397</v>
+        <v>11.57696311596945</v>
       </c>
       <c r="E227" t="n">
-        <v>11.7649532063393</v>
+        <v>11.76495226271687</v>
       </c>
       <c r="F227" t="n">
         <v>4461000</v>
@@ -4972,16 +4972,16 @@
         <v>44974</v>
       </c>
       <c r="B228" t="n">
-        <v>11.72578907012939</v>
+        <v>11.72578811645508</v>
       </c>
       <c r="C228" t="n">
-        <v>12.13309731279878</v>
+        <v>12.13309632599753</v>
       </c>
       <c r="D228" t="n">
-        <v>11.55346597857718</v>
+        <v>11.55346503891813</v>
       </c>
       <c r="E228" t="n">
-        <v>11.94510889310522</v>
+        <v>11.94510792159332</v>
       </c>
       <c r="F228" t="n">
         <v>9428300</v>
@@ -4992,16 +4992,16 @@
         <v>44979</v>
       </c>
       <c r="B229" t="n">
-        <v>11.71795463562012</v>
+        <v>11.71795558929443</v>
       </c>
       <c r="C229" t="n">
-        <v>11.95294050572336</v>
+        <v>11.95294147852217</v>
       </c>
       <c r="D229" t="n">
-        <v>11.66312487316251</v>
+        <v>11.66312582237446</v>
       </c>
       <c r="E229" t="n">
-        <v>11.89810999626626</v>
+        <v>11.89811096460265</v>
       </c>
       <c r="F229" t="n">
         <v>6185800</v>
@@ -5012,16 +5012,16 @@
         <v>44980</v>
       </c>
       <c r="B230" t="n">
-        <v>11.67879009246826</v>
+        <v>11.67879104614258</v>
       </c>
       <c r="C230" t="n">
-        <v>11.8511131618989</v>
+        <v>11.85111412964489</v>
       </c>
       <c r="D230" t="n">
-        <v>11.61612729394793</v>
+        <v>11.61612824250529</v>
       </c>
       <c r="E230" t="n">
-        <v>11.79628339994349</v>
+        <v>11.79628436321215</v>
       </c>
       <c r="F230" t="n">
         <v>3218000</v>
@@ -5032,16 +5032,16 @@
         <v>44981</v>
       </c>
       <c r="B231" t="n">
-        <v>11.67879009246826</v>
+        <v>11.67879104614258</v>
       </c>
       <c r="C231" t="n">
-        <v>11.89810988728941</v>
+        <v>11.89811085887308</v>
       </c>
       <c r="D231" t="n">
-        <v>11.51430005960253</v>
+        <v>11.51430099984482</v>
       </c>
       <c r="E231" t="n">
-        <v>11.72578756485825</v>
+        <v>11.72578852237032</v>
       </c>
       <c r="F231" t="n">
         <v>4705500</v>
@@ -5052,16 +5052,16 @@
         <v>44984</v>
       </c>
       <c r="B232" t="n">
-        <v>11.64745903015137</v>
+        <v>11.64745998382568</v>
       </c>
       <c r="C232" t="n">
-        <v>11.85894654152509</v>
+        <v>11.85894751251565</v>
       </c>
       <c r="D232" t="n">
-        <v>11.56129786644328</v>
+        <v>11.56129881306286</v>
       </c>
       <c r="E232" t="n">
-        <v>11.73362019385946</v>
+        <v>11.7336211545885</v>
       </c>
       <c r="F232" t="n">
         <v>3412900</v>
@@ -5112,16 +5112,16 @@
         <v>44987</v>
       </c>
       <c r="B235" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="C235" t="n">
-        <v>11.67879055731306</v>
+        <v>11.67879152264125</v>
       </c>
       <c r="D235" t="n">
-        <v>11.45947075376244</v>
+        <v>11.45947170096243</v>
       </c>
       <c r="E235" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="F235" t="n">
         <v>2250800</v>
@@ -5132,16 +5132,16 @@
         <v>44988</v>
       </c>
       <c r="B236" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="C236" t="n">
-        <v>11.64745915680582</v>
+        <v>11.64746011954428</v>
       </c>
       <c r="D236" t="n">
-        <v>11.45947075376244</v>
+        <v>11.45947170096243</v>
       </c>
       <c r="E236" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="F236" t="n">
         <v>1727100</v>
@@ -5252,16 +5252,16 @@
         <v>44998</v>
       </c>
       <c r="B242" t="n">
-        <v>11.66312599182129</v>
+        <v>11.66312503814697</v>
       </c>
       <c r="C242" t="n">
-        <v>11.74145412470215</v>
+        <v>11.74145316462308</v>
       </c>
       <c r="D242" t="n">
-        <v>11.45947150173183</v>
+        <v>11.45947056471</v>
       </c>
       <c r="E242" t="n">
-        <v>11.52213430683635</v>
+        <v>11.52213336469069</v>
       </c>
       <c r="F242" t="n">
         <v>3223500</v>
@@ -5272,16 +5272,16 @@
         <v>44999</v>
       </c>
       <c r="B243" t="n">
-        <v>11.75711917877197</v>
+        <v>11.75712013244629</v>
       </c>
       <c r="C243" t="n">
-        <v>11.82761501514428</v>
+        <v>11.82761597453684</v>
       </c>
       <c r="D243" t="n">
-        <v>11.63962586915163</v>
+        <v>11.63962681329553</v>
       </c>
       <c r="E243" t="n">
-        <v>11.69445637910759</v>
+        <v>11.69445732769904</v>
       </c>
       <c r="F243" t="n">
         <v>2520000</v>
@@ -5292,16 +5292,16 @@
         <v>45000</v>
       </c>
       <c r="B244" t="n">
-        <v>11.74928665161133</v>
+        <v>11.74928569793701</v>
       </c>
       <c r="C244" t="n">
-        <v>11.89027833047051</v>
+        <v>11.89027736535209</v>
       </c>
       <c r="D244" t="n">
-        <v>11.61612800979977</v>
+        <v>11.61612706693377</v>
       </c>
       <c r="E244" t="n">
-        <v>11.71795525042035</v>
+        <v>11.71795429928916</v>
       </c>
       <c r="F244" t="n">
         <v>4602600</v>
@@ -5312,16 +5312,16 @@
         <v>45001</v>
       </c>
       <c r="B245" t="n">
-        <v>11.67095756530762</v>
+        <v>11.67095851898193</v>
       </c>
       <c r="C245" t="n">
-        <v>11.81194924163198</v>
+        <v>11.81195020682722</v>
       </c>
       <c r="D245" t="n">
-        <v>11.63962616467993</v>
+        <v>11.63962711579405</v>
       </c>
       <c r="E245" t="n">
-        <v>11.81194924163198</v>
+        <v>11.81195020682722</v>
       </c>
       <c r="F245" t="n">
         <v>5495800</v>
@@ -5372,16 +5372,16 @@
         <v>45006</v>
       </c>
       <c r="B248" t="n">
-        <v>11.3419771194458</v>
+        <v>11.34197807312012</v>
       </c>
       <c r="C248" t="n">
-        <v>11.42030599198873</v>
+        <v>11.42030695224922</v>
       </c>
       <c r="D248" t="n">
-        <v>11.27931432021125</v>
+        <v>11.27931526861666</v>
       </c>
       <c r="E248" t="n">
-        <v>11.36547622940837</v>
+        <v>11.36547718505858</v>
       </c>
       <c r="F248" t="n">
         <v>2410300</v>
@@ -5412,16 +5412,16 @@
         <v>45008</v>
       </c>
       <c r="B250" t="n">
-        <v>11.18532085418701</v>
+        <v>11.18532180786133</v>
       </c>
       <c r="C250" t="n">
-        <v>11.47513650638449</v>
+        <v>11.47513748476884</v>
       </c>
       <c r="D250" t="n">
-        <v>11.05999524750697</v>
+        <v>11.05999619049587</v>
       </c>
       <c r="E250" t="n">
-        <v>11.39680837570923</v>
+        <v>11.39680934741524</v>
       </c>
       <c r="F250" t="n">
         <v>4422500</v>
@@ -5472,16 +5472,16 @@
         <v>45013</v>
       </c>
       <c r="B253" t="n">
-        <v>11.42030715942383</v>
+        <v>11.42030620574951</v>
       </c>
       <c r="C253" t="n">
-        <v>11.45163856224394</v>
+        <v>11.45163760595323</v>
       </c>
       <c r="D253" t="n">
-        <v>11.25581710786836</v>
+        <v>11.25581616793009</v>
       </c>
       <c r="E253" t="n">
-        <v>11.31064687605366</v>
+        <v>11.31064593153673</v>
       </c>
       <c r="F253" t="n">
         <v>3302900</v>
@@ -5552,16 +5552,16 @@
         <v>45019</v>
       </c>
       <c r="B257" t="n">
-        <v>11.3419771194458</v>
+        <v>11.34197807312012</v>
       </c>
       <c r="C257" t="n">
-        <v>11.58479602672929</v>
+        <v>11.58479700082069</v>
       </c>
       <c r="D257" t="n">
-        <v>11.24798292059398</v>
+        <v>11.24798386636493</v>
       </c>
       <c r="E257" t="n">
-        <v>11.58479602672929</v>
+        <v>11.58479700082069</v>
       </c>
       <c r="F257" t="n">
         <v>6471200</v>
@@ -5572,16 +5572,16 @@
         <v>45020</v>
       </c>
       <c r="B258" t="n">
-        <v>11.4359712600708</v>
+        <v>11.43597221374512</v>
       </c>
       <c r="C258" t="n">
-        <v>11.49863405489315</v>
+        <v>11.49863501379308</v>
       </c>
       <c r="D258" t="n">
-        <v>11.24798212860431</v>
+        <v>11.24798306660174</v>
       </c>
       <c r="E258" t="n">
-        <v>11.35764239304314</v>
+        <v>11.35764334018542</v>
       </c>
       <c r="F258" t="n">
         <v>5230100</v>
@@ -5612,16 +5612,16 @@
         <v>45022</v>
       </c>
       <c r="B260" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="C260" t="n">
-        <v>11.6631252305592</v>
+        <v>11.66312619459255</v>
       </c>
       <c r="D260" t="n">
-        <v>11.4751360805163</v>
+        <v>11.47513702901113</v>
       </c>
       <c r="E260" t="n">
-        <v>11.49080215426967</v>
+        <v>11.4908031040594</v>
       </c>
       <c r="F260" t="n">
         <v>4653400</v>
@@ -5632,16 +5632,16 @@
         <v>45026</v>
       </c>
       <c r="B261" t="n">
-        <v>11.71795463562012</v>
+        <v>11.71795558929443</v>
       </c>
       <c r="C261" t="n">
-        <v>11.85111327044531</v>
+        <v>11.85111423495683</v>
       </c>
       <c r="D261" t="n">
-        <v>11.4594704026064</v>
+        <v>11.45947133524378</v>
       </c>
       <c r="E261" t="n">
-        <v>11.53779852797449</v>
+        <v>11.53779946698666</v>
       </c>
       <c r="F261" t="n">
         <v>3430500</v>
@@ -5652,16 +5652,16 @@
         <v>45027</v>
       </c>
       <c r="B262" t="n">
-        <v>11.76495361328125</v>
+        <v>11.76495265960693</v>
       </c>
       <c r="C262" t="n">
-        <v>12.0156048417188</v>
+        <v>12.01560386772655</v>
       </c>
       <c r="D262" t="n">
-        <v>11.71012309681085</v>
+        <v>11.71012214758113</v>
       </c>
       <c r="E262" t="n">
-        <v>11.82761642039064</v>
+        <v>11.82761546163684</v>
       </c>
       <c r="F262" t="n">
         <v>2622300</v>
@@ -5672,16 +5672,16 @@
         <v>45028</v>
       </c>
       <c r="B263" t="n">
-        <v>11.80411529541016</v>
+        <v>11.80411624908447</v>
       </c>
       <c r="C263" t="n">
-        <v>12.01560279360503</v>
+        <v>12.01560376436578</v>
       </c>
       <c r="D263" t="n">
-        <v>11.74928553528532</v>
+        <v>11.74928648452985</v>
       </c>
       <c r="E263" t="n">
-        <v>11.82761440432034</v>
+        <v>11.82761535989319</v>
       </c>
       <c r="F263" t="n">
         <v>2987000</v>
@@ -5752,16 +5752,16 @@
         <v>45034</v>
       </c>
       <c r="B267" t="n">
-        <v>11.96860504150391</v>
+        <v>11.96860599517822</v>
       </c>
       <c r="C267" t="n">
-        <v>12.1644264624899</v>
+        <v>12.16442743176752</v>
       </c>
       <c r="D267" t="n">
-        <v>11.94510668014543</v>
+        <v>11.94510763194737</v>
       </c>
       <c r="E267" t="n">
-        <v>12.14092810113142</v>
+        <v>12.14092906853667</v>
       </c>
       <c r="F267" t="n">
         <v>3259600</v>
@@ -5792,16 +5792,16 @@
         <v>45036</v>
       </c>
       <c r="B269" t="n">
-        <v>12.09393215179443</v>
+        <v>12.09393119812012</v>
       </c>
       <c r="C269" t="n">
-        <v>12.14092962741908</v>
+        <v>12.14092867003875</v>
       </c>
       <c r="D269" t="n">
-        <v>12.00777098464871</v>
+        <v>12.00777003776868</v>
       </c>
       <c r="E269" t="n">
-        <v>12.06260075037785</v>
+        <v>12.06259979917419</v>
       </c>
       <c r="F269" t="n">
         <v>4813100</v>
@@ -5832,16 +5832,16 @@
         <v>45041</v>
       </c>
       <c r="B271" t="n">
-        <v>12.06260013580322</v>
+        <v>12.06260108947754</v>
       </c>
       <c r="C271" t="n">
-        <v>12.14092900885369</v>
+        <v>12.14092996872072</v>
       </c>
       <c r="D271" t="n">
-        <v>11.96860593634236</v>
+        <v>11.96860688258545</v>
       </c>
       <c r="E271" t="n">
-        <v>12.11743064573835</v>
+        <v>12.11743160374759</v>
       </c>
       <c r="F271" t="n">
         <v>2381100</v>
@@ -5932,16 +5932,16 @@
         <v>45049</v>
       </c>
       <c r="B276" t="n">
-        <v>12.28975391387939</v>
+        <v>12.28975296020508</v>
       </c>
       <c r="C276" t="n">
-        <v>12.48557536452565</v>
+        <v>12.48557439565576</v>
       </c>
       <c r="D276" t="n">
-        <v>12.2819216235732</v>
+        <v>12.28192067050667</v>
       </c>
       <c r="E276" t="n">
-        <v>12.48557536452565</v>
+        <v>12.48557439565576</v>
       </c>
       <c r="F276" t="n">
         <v>6661600</v>
@@ -6032,16 +6032,16 @@
         <v>45056</v>
       </c>
       <c r="B281" t="n">
-        <v>11.86925315856934</v>
+        <v>11.86925220489502</v>
       </c>
       <c r="C281" t="n">
-        <v>12.05105794406462</v>
+        <v>12.0510569757826</v>
       </c>
       <c r="D281" t="n">
-        <v>11.69610594039075</v>
+        <v>11.69610500062852</v>
       </c>
       <c r="E281" t="n">
-        <v>12.0164285004289</v>
+        <v>12.0164275349293</v>
       </c>
       <c r="F281" t="n">
         <v>5308900</v>
@@ -6072,16 +6072,16 @@
         <v>45058</v>
       </c>
       <c r="B283" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C283" t="n">
-        <v>12.25017729158851</v>
+        <v>12.25017632493442</v>
       </c>
       <c r="D283" t="n">
-        <v>11.9991136136361</v>
+        <v>11.99911266679329</v>
       </c>
       <c r="E283" t="n">
-        <v>12.0424006254826</v>
+        <v>12.04239967522403</v>
       </c>
       <c r="F283" t="n">
         <v>3087800</v>
@@ -6112,16 +6112,16 @@
         <v>45062</v>
       </c>
       <c r="B285" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="C285" t="n">
-        <v>12.30212128603885</v>
+        <v>12.30212031805942</v>
       </c>
       <c r="D285" t="n">
-        <v>12.08568706272756</v>
+        <v>12.08568611177803</v>
       </c>
       <c r="E285" t="n">
-        <v>12.18091782375736</v>
+        <v>12.18091686531469</v>
       </c>
       <c r="F285" t="n">
         <v>2907500</v>
@@ -6232,16 +6232,16 @@
         <v>45070</v>
       </c>
       <c r="B291" t="n">
-        <v>12.25017738342285</v>
+        <v>12.25017642974854</v>
       </c>
       <c r="C291" t="n">
-        <v>12.30212196315428</v>
+        <v>12.30212100543608</v>
       </c>
       <c r="D291" t="n">
-        <v>12.18091849420168</v>
+        <v>12.18091754591915</v>
       </c>
       <c r="E291" t="n">
-        <v>12.26749251854369</v>
+        <v>12.26749156352139</v>
       </c>
       <c r="F291" t="n">
         <v>1846000</v>
@@ -6312,16 +6312,16 @@
         <v>45076</v>
       </c>
       <c r="B295" t="n">
-        <v>12.26749229431152</v>
+        <v>12.26749134063721</v>
       </c>
       <c r="C295" t="n">
-        <v>12.38003819364653</v>
+        <v>12.3800372312229</v>
       </c>
       <c r="D295" t="n">
-        <v>12.25017715950718</v>
+        <v>12.25017620717894</v>
       </c>
       <c r="E295" t="n">
-        <v>12.37138062624436</v>
+        <v>12.37137966449377</v>
       </c>
       <c r="F295" t="n">
         <v>1829100</v>
@@ -6352,16 +6352,16 @@
         <v>45078</v>
       </c>
       <c r="B297" t="n">
-        <v>12.2415189743042</v>
+        <v>12.24151992797852</v>
       </c>
       <c r="C297" t="n">
-        <v>12.30212028771158</v>
+        <v>12.30212124610704</v>
       </c>
       <c r="D297" t="n">
-        <v>12.16360252813415</v>
+        <v>12.1636034757384</v>
       </c>
       <c r="E297" t="n">
-        <v>12.26749084781722</v>
+        <v>12.26749180351488</v>
       </c>
       <c r="F297" t="n">
         <v>2308800</v>
@@ -6392,16 +6392,16 @@
         <v>45082</v>
       </c>
       <c r="B299" t="n">
-        <v>12.06837177276611</v>
+        <v>12.0683708190918</v>
       </c>
       <c r="C299" t="n">
-        <v>12.1982328004551</v>
+        <v>12.19823183651883</v>
       </c>
       <c r="D299" t="n">
-        <v>11.97314101296568</v>
+        <v>11.97314006681674</v>
       </c>
       <c r="E299" t="n">
-        <v>12.17226092516972</v>
+        <v>12.17225996328581</v>
       </c>
       <c r="F299" t="n">
         <v>3442900</v>
@@ -6412,16 +6412,16 @@
         <v>45083</v>
       </c>
       <c r="B300" t="n">
-        <v>12.32809257507324</v>
+        <v>12.32809352874756</v>
       </c>
       <c r="C300" t="n">
-        <v>12.41466659053087</v>
+        <v>12.41466755090237</v>
       </c>
       <c r="D300" t="n">
-        <v>12.07702892100332</v>
+        <v>12.0770298552559</v>
       </c>
       <c r="E300" t="n">
-        <v>12.08568648767528</v>
+        <v>12.08568742259759</v>
       </c>
       <c r="F300" t="n">
         <v>7376500</v>
@@ -6452,16 +6452,16 @@
         <v>45086</v>
       </c>
       <c r="B302" t="n">
-        <v>12.37138080596924</v>
+        <v>12.37137985229492</v>
       </c>
       <c r="C302" t="n">
-        <v>12.42332538550581</v>
+        <v>12.42332442782724</v>
       </c>
       <c r="D302" t="n">
-        <v>12.26749247252717</v>
+        <v>12.26749152686131</v>
       </c>
       <c r="E302" t="n">
-        <v>12.29346434947992</v>
+        <v>12.29346340181196</v>
       </c>
       <c r="F302" t="n">
         <v>4999400</v>
@@ -6492,16 +6492,16 @@
         <v>45090</v>
       </c>
       <c r="B304" t="n">
-        <v>12.31077861785889</v>
+        <v>12.3107795715332</v>
       </c>
       <c r="C304" t="n">
-        <v>12.50124013627868</v>
+        <v>12.5012411047074</v>
       </c>
       <c r="D304" t="n">
-        <v>12.29346348402198</v>
+        <v>12.29346443635495</v>
       </c>
       <c r="E304" t="n">
-        <v>12.46661069423589</v>
+        <v>12.46661165998199</v>
       </c>
       <c r="F304" t="n">
         <v>1312000</v>
@@ -6632,16 +6632,16 @@
         <v>45099</v>
       </c>
       <c r="B311" t="n">
-        <v>12.78693389892578</v>
+        <v>12.7869348526001</v>
       </c>
       <c r="C311" t="n">
-        <v>12.84753521530501</v>
+        <v>12.84753617349909</v>
       </c>
       <c r="D311" t="n">
-        <v>12.64841530692453</v>
+        <v>12.64841625026786</v>
       </c>
       <c r="E311" t="n">
-        <v>12.78693389892578</v>
+        <v>12.7869348526001</v>
       </c>
       <c r="F311" t="n">
         <v>2039700</v>
@@ -6652,16 +6652,16 @@
         <v>45100</v>
       </c>
       <c r="B312" t="n">
-        <v>12.9427661895752</v>
+        <v>12.94276714324951</v>
       </c>
       <c r="C312" t="n">
-        <v>13.07262721694078</v>
+        <v>13.07262818018377</v>
       </c>
       <c r="D312" t="n">
-        <v>12.7609614117682</v>
+        <v>12.76096235204642</v>
       </c>
       <c r="E312" t="n">
-        <v>12.81290598784064</v>
+        <v>12.81290693194634</v>
       </c>
       <c r="F312" t="n">
         <v>2959500</v>
@@ -6672,16 +6672,16 @@
         <v>45103</v>
       </c>
       <c r="B313" t="n">
-        <v>12.71767425537109</v>
+        <v>12.71767520904541</v>
       </c>
       <c r="C313" t="n">
-        <v>13.01202492323384</v>
+        <v>13.01202589898095</v>
       </c>
       <c r="D313" t="n">
-        <v>12.66573050553121</v>
+        <v>12.66573145531036</v>
       </c>
       <c r="E313" t="n">
-        <v>12.94276603969331</v>
+        <v>12.94276701024684</v>
       </c>
       <c r="F313" t="n">
         <v>2677600</v>
@@ -6792,16 +6792,16 @@
         <v>45111</v>
       </c>
       <c r="B319" t="n">
-        <v>12.34540748596191</v>
+        <v>12.34540843963623</v>
       </c>
       <c r="C319" t="n">
-        <v>12.40600880031166</v>
+        <v>12.40600975866739</v>
       </c>
       <c r="D319" t="n">
-        <v>12.23286159814739</v>
+        <v>12.23286254312761</v>
       </c>
       <c r="E319" t="n">
-        <v>12.38869449291073</v>
+        <v>12.38869544992894</v>
       </c>
       <c r="F319" t="n">
         <v>2230100</v>
@@ -6832,16 +6832,16 @@
         <v>45113</v>
       </c>
       <c r="B321" t="n">
-        <v>12.32809257507324</v>
+        <v>12.32809352874756</v>
       </c>
       <c r="C321" t="n">
-        <v>12.48392547264458</v>
+        <v>12.48392643837378</v>
       </c>
       <c r="D321" t="n">
-        <v>12.25017612628758</v>
+        <v>12.25017707393445</v>
       </c>
       <c r="E321" t="n">
-        <v>12.4319808982438</v>
+        <v>12.43198185995469</v>
       </c>
       <c r="F321" t="n">
         <v>2081000</v>
@@ -6852,16 +6852,16 @@
         <v>45114</v>
       </c>
       <c r="B322" t="n">
-        <v>12.34540748596191</v>
+        <v>12.34540843963623</v>
       </c>
       <c r="C322" t="n">
-        <v>12.48392524769333</v>
+        <v>12.48392621206805</v>
       </c>
       <c r="D322" t="n">
-        <v>12.25883347206429</v>
+        <v>12.25883441905082</v>
       </c>
       <c r="E322" t="n">
-        <v>12.42332393334358</v>
+        <v>12.42332489303689</v>
       </c>
       <c r="F322" t="n">
         <v>2149700</v>
@@ -6892,16 +6892,16 @@
         <v>45118</v>
       </c>
       <c r="B324" t="n">
-        <v>12.34540748596191</v>
+        <v>12.34540843963623</v>
       </c>
       <c r="C324" t="n">
-        <v>12.3973512337957</v>
+        <v>12.39735219148264</v>
       </c>
       <c r="D324" t="n">
-        <v>12.23286159814739</v>
+        <v>12.23286254312761</v>
       </c>
       <c r="E324" t="n">
-        <v>12.38869449291073</v>
+        <v>12.38869544992894</v>
       </c>
       <c r="F324" t="n">
         <v>1919200</v>
@@ -7072,16 +7072,16 @@
         <v>45131</v>
       </c>
       <c r="B333" t="n">
-        <v>12.34540748596191</v>
+        <v>12.34540843963623</v>
       </c>
       <c r="C333" t="n">
-        <v>12.42332393334358</v>
+        <v>12.42332489303689</v>
       </c>
       <c r="D333" t="n">
-        <v>12.31943478641403</v>
+        <v>12.31943573808198</v>
       </c>
       <c r="E333" t="n">
-        <v>12.42332393334358</v>
+        <v>12.42332489303689</v>
       </c>
       <c r="F333" t="n">
         <v>1347200</v>
@@ -7132,16 +7132,16 @@
         <v>45134</v>
       </c>
       <c r="B336" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C336" t="n">
-        <v>12.22420541473304</v>
+        <v>12.22420445012837</v>
       </c>
       <c r="D336" t="n">
-        <v>12.03374305798708</v>
+        <v>12.03374210841168</v>
       </c>
       <c r="E336" t="n">
-        <v>12.18091840288654</v>
+        <v>12.18091744169762</v>
       </c>
       <c r="F336" t="n">
         <v>2852900</v>
@@ -7152,16 +7152,16 @@
         <v>45135</v>
       </c>
       <c r="B337" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="C337" t="n">
-        <v>12.22420483354582</v>
+        <v>12.22420387169716</v>
       </c>
       <c r="D337" t="n">
-        <v>12.0597151871069</v>
+        <v>12.05971423820094</v>
       </c>
       <c r="E337" t="n">
-        <v>12.14628838105279</v>
+        <v>12.14628742533491</v>
       </c>
       <c r="F337" t="n">
         <v>1506100</v>
@@ -7172,16 +7172,16 @@
         <v>45138</v>
       </c>
       <c r="B338" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="C338" t="n">
-        <v>12.20689052500906</v>
+        <v>12.20688956452276</v>
       </c>
       <c r="D338" t="n">
-        <v>12.10300137126433</v>
+        <v>12.10300041895243</v>
       </c>
       <c r="E338" t="n">
-        <v>12.20689052500906</v>
+        <v>12.20688956452276</v>
       </c>
       <c r="F338" t="n">
         <v>1549400</v>
@@ -7292,16 +7292,16 @@
         <v>45146</v>
       </c>
       <c r="B344" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C344" t="n">
-        <v>12.15494652603107</v>
+        <v>12.15494556689158</v>
       </c>
       <c r="D344" t="n">
-        <v>11.92985472493413</v>
+        <v>11.92985378355649</v>
       </c>
       <c r="E344" t="n">
-        <v>11.99045687177166</v>
+        <v>11.99045592561195</v>
       </c>
       <c r="F344" t="n">
         <v>2176400</v>
@@ -7352,16 +7352,16 @@
         <v>45149</v>
       </c>
       <c r="B347" t="n">
-        <v>11.92119693756104</v>
+        <v>11.92119789123535</v>
       </c>
       <c r="C347" t="n">
-        <v>11.97314068671642</v>
+        <v>11.97314164454614</v>
       </c>
       <c r="D347" t="n">
-        <v>11.83462292146072</v>
+        <v>11.83462386820927</v>
       </c>
       <c r="E347" t="n">
-        <v>11.97314068671642</v>
+        <v>11.97314164454614</v>
       </c>
       <c r="F347" t="n">
         <v>2472600</v>
@@ -7392,16 +7392,16 @@
         <v>45153</v>
       </c>
       <c r="B349" t="n">
-        <v>11.860595703125</v>
+        <v>11.86059474945068</v>
       </c>
       <c r="C349" t="n">
-        <v>11.99911347897441</v>
+        <v>11.9991125141623</v>
       </c>
       <c r="D349" t="n">
-        <v>11.85193813572664</v>
+        <v>11.85193718274846</v>
       </c>
       <c r="E349" t="n">
-        <v>11.91254028188406</v>
+        <v>11.91253932403304</v>
       </c>
       <c r="F349" t="n">
         <v>2713800</v>
@@ -7492,16 +7492,16 @@
         <v>45160</v>
       </c>
       <c r="B354" t="n">
-        <v>11.79999351501465</v>
+        <v>11.79999446868896</v>
       </c>
       <c r="C354" t="n">
-        <v>11.86925239784715</v>
+        <v>11.86925335711897</v>
       </c>
       <c r="D354" t="n">
-        <v>11.73073463218214</v>
+        <v>11.73073558025896</v>
       </c>
       <c r="E354" t="n">
-        <v>11.79133594825283</v>
+        <v>11.79133690122745</v>
       </c>
       <c r="F354" t="n">
         <v>2231700</v>
@@ -7572,16 +7572,16 @@
         <v>45166</v>
       </c>
       <c r="B358" t="n">
-        <v>11.96448421478271</v>
+        <v>11.9644832611084</v>
       </c>
       <c r="C358" t="n">
-        <v>11.99911365926539</v>
+        <v>11.9991127028308</v>
       </c>
       <c r="D358" t="n">
-        <v>11.84328157190891</v>
+        <v>11.8432806278955</v>
       </c>
       <c r="E358" t="n">
-        <v>11.95582747288536</v>
+        <v>11.95582651990106</v>
       </c>
       <c r="F358" t="n">
         <v>2184700</v>
@@ -7592,16 +7592,16 @@
         <v>45167</v>
       </c>
       <c r="B359" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="C359" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="D359" t="n">
-        <v>11.97314116752997</v>
+        <v>11.97314022543599</v>
       </c>
       <c r="E359" t="n">
-        <v>11.98179873461387</v>
+        <v>11.98179779183868</v>
       </c>
       <c r="F359" t="n">
         <v>1776800</v>
@@ -7632,16 +7632,16 @@
         <v>45169</v>
       </c>
       <c r="B361" t="n">
-        <v>11.78267955780029</v>
+        <v>11.78267860412598</v>
       </c>
       <c r="C361" t="n">
-        <v>12.12031726453966</v>
+        <v>12.1203162835374</v>
       </c>
       <c r="D361" t="n">
-        <v>11.78267955780029</v>
+        <v>11.78267860412598</v>
       </c>
       <c r="E361" t="n">
-        <v>12.12031726453966</v>
+        <v>12.1203162835374</v>
       </c>
       <c r="F361" t="n">
         <v>3236500</v>
@@ -7652,16 +7652,16 @@
         <v>45170</v>
       </c>
       <c r="B362" t="n">
-        <v>12.04240036010742</v>
+        <v>12.04239940643311</v>
       </c>
       <c r="C362" t="n">
-        <v>12.04240036010742</v>
+        <v>12.04239940643311</v>
       </c>
       <c r="D362" t="n">
-        <v>11.89522501845123</v>
+        <v>11.89522407643217</v>
       </c>
       <c r="E362" t="n">
-        <v>11.90388258575596</v>
+        <v>11.90388164305129</v>
       </c>
       <c r="F362" t="n">
         <v>3740800</v>
@@ -7692,16 +7692,16 @@
         <v>45174</v>
       </c>
       <c r="B364" t="n">
-        <v>11.92119693756104</v>
+        <v>11.92119789123535</v>
       </c>
       <c r="C364" t="n">
-        <v>12.06837144392197</v>
+        <v>12.06837240936998</v>
       </c>
       <c r="D364" t="n">
-        <v>11.9125393708248</v>
+        <v>11.91254032380653</v>
       </c>
       <c r="E364" t="n">
-        <v>12.04239956934427</v>
+        <v>12.04240053271458</v>
       </c>
       <c r="F364" t="n">
         <v>3869600</v>
@@ -7772,16 +7772,16 @@
         <v>45181</v>
       </c>
       <c r="B368" t="n">
-        <v>12.06837177276611</v>
+        <v>12.0683708190918</v>
       </c>
       <c r="C368" t="n">
-        <v>12.15494579122544</v>
+        <v>12.15494483070982</v>
       </c>
       <c r="D368" t="n">
-        <v>11.98179857993782</v>
+        <v>11.98179763310474</v>
       </c>
       <c r="E368" t="n">
-        <v>12.03374233050859</v>
+        <v>12.03374137957078</v>
       </c>
       <c r="F368" t="n">
         <v>2215400</v>
@@ -7792,16 +7792,16 @@
         <v>45182</v>
       </c>
       <c r="B369" t="n">
-        <v>12.06837177276611</v>
+        <v>12.0683708190918</v>
       </c>
       <c r="C369" t="n">
-        <v>12.1982328004551</v>
+        <v>12.19823183651883</v>
       </c>
       <c r="D369" t="n">
-        <v>12.03374233050859</v>
+        <v>12.03374137957078</v>
       </c>
       <c r="E369" t="n">
-        <v>12.07702933973825</v>
+        <v>12.07702838537979</v>
       </c>
       <c r="F369" t="n">
         <v>1684100</v>
@@ -7812,16 +7812,16 @@
         <v>45183</v>
       </c>
       <c r="B370" t="n">
-        <v>12.21554756164551</v>
+        <v>12.21554660797119</v>
       </c>
       <c r="C370" t="n">
-        <v>12.25017700518688</v>
+        <v>12.25017604880902</v>
       </c>
       <c r="D370" t="n">
-        <v>12.09434492206624</v>
+        <v>12.09434397785428</v>
       </c>
       <c r="E370" t="n">
-        <v>12.09434492206624</v>
+        <v>12.09434397785428</v>
       </c>
       <c r="F370" t="n">
         <v>2498700</v>
@@ -7892,16 +7892,16 @@
         <v>45189</v>
       </c>
       <c r="B374" t="n">
-        <v>12.06837177276611</v>
+        <v>12.0683708190918</v>
       </c>
       <c r="C374" t="n">
-        <v>12.1462882242533</v>
+        <v>12.14628726442182</v>
       </c>
       <c r="D374" t="n">
-        <v>11.97314101296568</v>
+        <v>11.97314006681674</v>
       </c>
       <c r="E374" t="n">
-        <v>12.08568690671039</v>
+        <v>12.08568595166779</v>
       </c>
       <c r="F374" t="n">
         <v>2998000</v>
@@ -7972,16 +7972,16 @@
         <v>45195</v>
       </c>
       <c r="B378" t="n">
-        <v>11.83462238311768</v>
+        <v>11.83462333679199</v>
       </c>
       <c r="C378" t="n">
-        <v>12.06837089494598</v>
+        <v>12.06837186745655</v>
       </c>
       <c r="D378" t="n">
-        <v>11.78267781069418</v>
+        <v>11.78267876018263</v>
       </c>
       <c r="E378" t="n">
-        <v>11.80865050972141</v>
+        <v>11.80865146130283</v>
       </c>
       <c r="F378" t="n">
         <v>7795500</v>
@@ -8012,16 +8012,16 @@
         <v>45197</v>
       </c>
       <c r="B380" t="n">
-        <v>11.78267955780029</v>
+        <v>11.78267860412598</v>
       </c>
       <c r="C380" t="n">
-        <v>11.86059601517331</v>
+        <v>11.86059505519254</v>
       </c>
       <c r="D380" t="n">
-        <v>11.73073580330568</v>
+        <v>11.73073485383562</v>
       </c>
       <c r="E380" t="n">
-        <v>11.85193844754717</v>
+        <v>11.85193748826714</v>
       </c>
       <c r="F380" t="n">
         <v>2404900</v>
@@ -8172,16 +8172,16 @@
         <v>45209</v>
       </c>
       <c r="B388" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C388" t="n">
-        <v>12.16360409352659</v>
+        <v>12.16360313370393</v>
       </c>
       <c r="D388" t="n">
-        <v>11.91254041557417</v>
+        <v>11.9125394755628</v>
       </c>
       <c r="E388" t="n">
-        <v>11.92985472493413</v>
+        <v>11.92985378355649</v>
       </c>
       <c r="F388" t="n">
         <v>3643400</v>
@@ -8212,16 +8212,16 @@
         <v>45212</v>
       </c>
       <c r="B390" t="n">
-        <v>12.02508544921875</v>
+        <v>12.02508640289307</v>
       </c>
       <c r="C390" t="n">
-        <v>12.19823265849127</v>
+        <v>12.19823362589739</v>
       </c>
       <c r="D390" t="n">
-        <v>12.02508544921875</v>
+        <v>12.02508640289307</v>
       </c>
       <c r="E390" t="n">
-        <v>12.09434433292776</v>
+        <v>12.0943452920948</v>
       </c>
       <c r="F390" t="n">
         <v>4555500</v>
@@ -8352,16 +8352,16 @@
         <v>45223</v>
       </c>
       <c r="B397" t="n">
-        <v>11.6355037689209</v>
+        <v>11.63550281524658</v>
       </c>
       <c r="C397" t="n">
-        <v>11.81730855401174</v>
+        <v>11.81730758543626</v>
       </c>
       <c r="D397" t="n">
-        <v>11.54893057283972</v>
+        <v>11.54892962626116</v>
       </c>
       <c r="E397" t="n">
-        <v>11.80865181234537</v>
+        <v>11.80865084447942</v>
       </c>
       <c r="F397" t="n">
         <v>3637500</v>
@@ -8432,16 +8432,16 @@
         <v>45229</v>
       </c>
       <c r="B401" t="n">
-        <v>11.49698638916016</v>
+        <v>11.49698543548584</v>
       </c>
       <c r="C401" t="n">
-        <v>11.64416173574207</v>
+        <v>11.64416076985956</v>
       </c>
       <c r="D401" t="n">
-        <v>11.47101451200779</v>
+        <v>11.47101356048784</v>
       </c>
       <c r="E401" t="n">
-        <v>11.57490284624835</v>
+        <v>11.57490188611087</v>
       </c>
       <c r="F401" t="n">
         <v>4549600</v>
@@ -8452,16 +8452,16 @@
         <v>45230</v>
       </c>
       <c r="B402" t="n">
-        <v>11.61818885803223</v>
+        <v>11.61818981170654</v>
       </c>
       <c r="C402" t="n">
-        <v>11.6614758666457</v>
+        <v>11.66147682387321</v>
       </c>
       <c r="D402" t="n">
-        <v>11.52295809958741</v>
+        <v>11.52295904544475</v>
       </c>
       <c r="E402" t="n">
-        <v>11.52295809958741</v>
+        <v>11.52295904544475</v>
       </c>
       <c r="F402" t="n">
         <v>3290000</v>
@@ -8492,16 +8492,16 @@
         <v>45233</v>
       </c>
       <c r="B404" t="n">
-        <v>11.96448421478271</v>
+        <v>11.9644832611084</v>
       </c>
       <c r="C404" t="n">
-        <v>12.0250863618507</v>
+        <v>12.02508540334586</v>
       </c>
       <c r="D404" t="n">
-        <v>11.65281921443867</v>
+        <v>11.65281828560679</v>
       </c>
       <c r="E404" t="n">
-        <v>11.74804998035825</v>
+        <v>11.74804904393564</v>
       </c>
       <c r="F404" t="n">
         <v>4830800</v>
@@ -8512,16 +8512,16 @@
         <v>45236</v>
       </c>
       <c r="B405" t="n">
-        <v>12.02508544921875</v>
+        <v>12.02508640289307</v>
       </c>
       <c r="C405" t="n">
-        <v>12.077029199185</v>
+        <v>12.07703015697882</v>
       </c>
       <c r="D405" t="n">
-        <v>11.8173079724607</v>
+        <v>11.81730890965679</v>
       </c>
       <c r="E405" t="n">
-        <v>11.94716899863836</v>
+        <v>11.94716994613335</v>
       </c>
       <c r="F405" t="n">
         <v>2982900</v>
@@ -8592,16 +8592,16 @@
         <v>45240</v>
       </c>
       <c r="B409" t="n">
-        <v>11.78267955780029</v>
+        <v>11.78267860412598</v>
       </c>
       <c r="C409" t="n">
-        <v>11.86059601517331</v>
+        <v>11.86059505519254</v>
       </c>
       <c r="D409" t="n">
-        <v>11.69610635843224</v>
+        <v>11.69610541176504</v>
       </c>
       <c r="E409" t="n">
-        <v>11.69610635843224</v>
+        <v>11.69610541176504</v>
       </c>
       <c r="F409" t="n">
         <v>3430000</v>
@@ -8672,16 +8672,16 @@
         <v>45247</v>
       </c>
       <c r="B413" t="n">
-        <v>12.25017738342285</v>
+        <v>12.25017642974854</v>
       </c>
       <c r="C413" t="n">
-        <v>12.48392675376763</v>
+        <v>12.48392578189597</v>
       </c>
       <c r="D413" t="n">
-        <v>12.14628904959109</v>
+        <v>12.14628810400446</v>
       </c>
       <c r="E413" t="n">
-        <v>12.48392675376763</v>
+        <v>12.48392578189597</v>
       </c>
       <c r="F413" t="n">
         <v>3124800</v>
@@ -8692,16 +8692,16 @@
         <v>45250</v>
       </c>
       <c r="B414" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C414" t="n">
-        <v>12.23286298222856</v>
+        <v>12.23286201694073</v>
       </c>
       <c r="D414" t="n">
-        <v>11.99045687177166</v>
+        <v>11.99045592561195</v>
       </c>
       <c r="E414" t="n">
-        <v>12.20689110537309</v>
+        <v>12.20689014213468</v>
       </c>
       <c r="F414" t="n">
         <v>3248400</v>
@@ -8812,16 +8812,16 @@
         <v>45258</v>
       </c>
       <c r="B420" t="n">
-        <v>12.63975811004639</v>
+        <v>12.6397590637207</v>
       </c>
       <c r="C420" t="n">
-        <v>12.76961830492886</v>
+        <v>12.76961926840118</v>
       </c>
       <c r="D420" t="n">
-        <v>12.57049922935827</v>
+        <v>12.57050017780698</v>
       </c>
       <c r="E420" t="n">
-        <v>12.57915597022104</v>
+        <v>12.57915691932291</v>
       </c>
       <c r="F420" t="n">
         <v>5941200</v>
@@ -8852,16 +8852,16 @@
         <v>45260</v>
       </c>
       <c r="B422" t="n">
-        <v>12.71767425537109</v>
+        <v>12.71767520904541</v>
       </c>
       <c r="C422" t="n">
-        <v>12.71767425537109</v>
+        <v>12.71767520904541</v>
       </c>
       <c r="D422" t="n">
-        <v>12.58781405514036</v>
+        <v>12.58781499907671</v>
       </c>
       <c r="E422" t="n">
-        <v>12.63110106376094</v>
+        <v>12.6311020109433</v>
       </c>
       <c r="F422" t="n">
         <v>4162000</v>
@@ -8912,16 +8912,16 @@
         <v>45265</v>
       </c>
       <c r="B425" t="n">
-        <v>13.15920066833496</v>
+        <v>13.15919971466064</v>
       </c>
       <c r="C425" t="n">
-        <v>13.20248767830808</v>
+        <v>13.20248672149667</v>
       </c>
       <c r="D425" t="n">
-        <v>12.92545213548978</v>
+        <v>12.9254511987557</v>
       </c>
       <c r="E425" t="n">
-        <v>12.96008157834207</v>
+        <v>12.96008063909832</v>
       </c>
       <c r="F425" t="n">
         <v>6696500</v>
@@ -8932,16 +8932,16 @@
         <v>45266</v>
       </c>
       <c r="B426" t="n">
-        <v>13.07262802124023</v>
+        <v>13.07262706756592</v>
       </c>
       <c r="C426" t="n">
-        <v>13.27174711956826</v>
+        <v>13.2717461513678</v>
       </c>
       <c r="D426" t="n">
-        <v>13.04665531879052</v>
+        <v>13.04665436701096</v>
       </c>
       <c r="E426" t="n">
-        <v>13.21114579844774</v>
+        <v>13.21114483466828</v>
       </c>
       <c r="F426" t="n">
         <v>5861300</v>
@@ -8952,16 +8952,16 @@
         <v>45267</v>
       </c>
       <c r="B427" t="n">
-        <v>13.1159143447876</v>
+        <v>13.11591339111328</v>
       </c>
       <c r="C427" t="n">
-        <v>13.15054378945223</v>
+        <v>13.15054283325996</v>
       </c>
       <c r="D427" t="n">
-        <v>12.97739656612907</v>
+        <v>12.97739562252655</v>
       </c>
       <c r="E427" t="n">
-        <v>13.10725760284475</v>
+        <v>13.10725664979988</v>
       </c>
       <c r="F427" t="n">
         <v>6196000</v>
@@ -22152,19 +22152,39 @@
         <v>46234</v>
       </c>
       <c r="B1087" t="n">
-        <v>10.98</v>
+        <v>10.97999954223633</v>
       </c>
       <c r="C1087" t="n">
-        <v>11.28</v>
+        <v>11.27999973297119</v>
       </c>
       <c r="D1087" t="n">
-        <v>10.91</v>
+        <v>10.90999984741211</v>
       </c>
       <c r="E1087" t="n">
-        <v>11.2</v>
+        <v>11.19999980926514</v>
       </c>
       <c r="F1087" t="n">
         <v>5442500</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B1088" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="C1088" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="D1088" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="E1088" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>4621900</v>
       </c>
     </row>
   </sheetData>

--- a/database/AURE3.xlsx
+++ b/database/AURE3.xlsx
@@ -552,16 +552,16 @@
         <v>44655</v>
       </c>
       <c r="B7" t="n">
-        <v>12.42274570465088</v>
+        <v>12.42274475097656</v>
       </c>
       <c r="C7" t="n">
-        <v>12.7338981972699</v>
+        <v>12.7338972197089</v>
       </c>
       <c r="D7" t="n">
-        <v>12.33717841680461</v>
+        <v>12.33717746969916</v>
       </c>
       <c r="E7" t="n">
-        <v>12.54720566311648</v>
+        <v>12.54720469988757</v>
       </c>
       <c r="F7" t="n">
         <v>2842400</v>
@@ -572,16 +572,16 @@
         <v>44656</v>
       </c>
       <c r="B8" t="n">
-        <v>12.15826511383057</v>
+        <v>12.15826606750488</v>
       </c>
       <c r="C8" t="n">
-        <v>12.50053200500811</v>
+        <v>12.50053298552928</v>
       </c>
       <c r="D8" t="n">
-        <v>12.05714061961251</v>
+        <v>12.05714156535479</v>
       </c>
       <c r="E8" t="n">
-        <v>12.37607131730719</v>
+        <v>12.37607228806586</v>
       </c>
       <c r="F8" t="n">
         <v>3624900</v>
@@ -592,16 +592,16 @@
         <v>44657</v>
       </c>
       <c r="B9" t="n">
-        <v>12.43052387237549</v>
+        <v>12.43052291870117</v>
       </c>
       <c r="C9" t="n">
-        <v>12.44608183074918</v>
+        <v>12.44608087588125</v>
       </c>
       <c r="D9" t="n">
-        <v>12.01824761944832</v>
+        <v>12.01824669740399</v>
       </c>
       <c r="E9" t="n">
-        <v>12.06492075272512</v>
+        <v>12.06491982710001</v>
       </c>
       <c r="F9" t="n">
         <v>2914800</v>
@@ -672,16 +672,16 @@
         <v>44663</v>
       </c>
       <c r="B13" t="n">
-        <v>12.24383163452148</v>
+        <v>12.2438325881958</v>
       </c>
       <c r="C13" t="n">
-        <v>12.64055063241211</v>
+        <v>12.64055161698694</v>
       </c>
       <c r="D13" t="n">
-        <v>12.21271646263855</v>
+        <v>12.2127174138893</v>
       </c>
       <c r="E13" t="n">
-        <v>12.4849740311532</v>
+        <v>12.48497500361014</v>
       </c>
       <c r="F13" t="n">
         <v>2267700</v>
@@ -712,16 +712,16 @@
         <v>44665</v>
       </c>
       <c r="B15" t="n">
-        <v>12.11159229278564</v>
+        <v>12.11159133911133</v>
       </c>
       <c r="C15" t="n">
-        <v>12.36829265315281</v>
+        <v>12.36829167926575</v>
       </c>
       <c r="D15" t="n">
-        <v>12.04936194735386</v>
+        <v>12.0493609985796</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08047712006975</v>
+        <v>12.08047616884546</v>
       </c>
       <c r="F15" t="n">
         <v>2077400</v>
@@ -772,16 +772,16 @@
         <v>44671</v>
       </c>
       <c r="B18" t="n">
-        <v>12.05714130401611</v>
+        <v>12.0571403503418</v>
       </c>
       <c r="C18" t="n">
-        <v>12.21271717247328</v>
+        <v>12.2127162064935</v>
       </c>
       <c r="D18" t="n">
-        <v>11.95601680405789</v>
+        <v>11.95601585838214</v>
       </c>
       <c r="E18" t="n">
-        <v>12.07269926178396</v>
+        <v>12.07269830687907</v>
       </c>
       <c r="F18" t="n">
         <v>2798400</v>
@@ -812,16 +812,16 @@
         <v>44676</v>
       </c>
       <c r="B20" t="n">
-        <v>12.39162826538086</v>
+        <v>12.39163017272949</v>
       </c>
       <c r="C20" t="n">
-        <v>12.39162826538086</v>
+        <v>12.39163017272949</v>
       </c>
       <c r="D20" t="n">
-        <v>11.90156379107179</v>
+        <v>11.90156562298855</v>
       </c>
       <c r="E20" t="n">
-        <v>12.11936997681666</v>
+        <v>12.11937184225865</v>
       </c>
       <c r="F20" t="n">
         <v>2683100</v>
@@ -832,16 +832,16 @@
         <v>44677</v>
       </c>
       <c r="B21" t="n">
-        <v>11.95601558685303</v>
+        <v>11.95601654052734</v>
       </c>
       <c r="C21" t="n">
-        <v>12.43830110089237</v>
+        <v>12.4383020930363</v>
       </c>
       <c r="D21" t="n">
-        <v>11.86267007528195</v>
+        <v>11.86267102151054</v>
       </c>
       <c r="E21" t="n">
-        <v>12.32939837498153</v>
+        <v>12.32939935843881</v>
       </c>
       <c r="F21" t="n">
         <v>2627000</v>
@@ -852,16 +852,16 @@
         <v>44678</v>
       </c>
       <c r="B22" t="n">
-        <v>12.05714130401611</v>
+        <v>12.0571403503418</v>
       </c>
       <c r="C22" t="n">
-        <v>12.06492028290003</v>
+        <v>12.06491932861043</v>
       </c>
       <c r="D22" t="n">
-        <v>11.83155610929216</v>
+        <v>11.83155517346078</v>
       </c>
       <c r="E22" t="n">
-        <v>12.04936232513219</v>
+        <v>12.04936137207316</v>
       </c>
       <c r="F22" t="n">
         <v>2401400</v>
@@ -912,16 +912,16 @@
         <v>44683</v>
       </c>
       <c r="B25" t="n">
-        <v>11.1703577041626</v>
+        <v>11.17035675048828</v>
       </c>
       <c r="C25" t="n">
-        <v>11.47373120303561</v>
+        <v>11.47373022346064</v>
       </c>
       <c r="D25" t="n">
-        <v>10.96033046789994</v>
+        <v>10.96032953215679</v>
       </c>
       <c r="E25" t="n">
-        <v>11.42705807173043</v>
+        <v>11.4270570961402</v>
       </c>
       <c r="F25" t="n">
         <v>2883200</v>
@@ -952,16 +952,16 @@
         <v>44685</v>
       </c>
       <c r="B27" t="n">
-        <v>11.69445610046387</v>
+        <v>11.69445705413818</v>
       </c>
       <c r="C27" t="n">
-        <v>11.69445610046387</v>
+        <v>11.69445705413818</v>
       </c>
       <c r="D27" t="n">
-        <v>11.03649597266557</v>
+        <v>11.03649687268372</v>
       </c>
       <c r="E27" t="n">
-        <v>11.20881904113643</v>
+        <v>11.2088199552074</v>
       </c>
       <c r="F27" t="n">
         <v>4400300</v>
@@ -1092,16 +1092,16 @@
         <v>44694</v>
       </c>
       <c r="B34" t="n">
-        <v>11.32631301879883</v>
+        <v>11.32631206512451</v>
       </c>
       <c r="C34" t="n">
-        <v>11.38114278731251</v>
+        <v>11.38114182902154</v>
       </c>
       <c r="D34" t="n">
-        <v>11.11482548824677</v>
+        <v>11.11482455237968</v>
       </c>
       <c r="E34" t="n">
-        <v>11.18532133176413</v>
+        <v>11.18532038996129</v>
       </c>
       <c r="F34" t="n">
         <v>1333500</v>
@@ -1132,16 +1132,16 @@
         <v>44698</v>
       </c>
       <c r="B36" t="n">
-        <v>11.56129837036133</v>
+        <v>11.56129741668701</v>
       </c>
       <c r="C36" t="n">
-        <v>11.74928677955431</v>
+        <v>11.74928581037311</v>
       </c>
       <c r="D36" t="n">
-        <v>11.3576438869025</v>
+        <v>11.35764295002734</v>
       </c>
       <c r="E36" t="n">
-        <v>11.3576438869025</v>
+        <v>11.35764295002734</v>
       </c>
       <c r="F36" t="n">
         <v>1389700</v>
@@ -1252,16 +1252,16 @@
         <v>44706</v>
       </c>
       <c r="B42" t="n">
-        <v>11.32631301879883</v>
+        <v>11.32631206512451</v>
       </c>
       <c r="C42" t="n">
-        <v>11.39680886231618</v>
+        <v>11.39680790270612</v>
       </c>
       <c r="D42" t="n">
-        <v>11.13832460075227</v>
+        <v>11.13832366290656</v>
       </c>
       <c r="E42" t="n">
-        <v>11.17748904126186</v>
+        <v>11.17748810011851</v>
       </c>
       <c r="F42" t="n">
         <v>821700</v>
@@ -1292,16 +1292,16 @@
         <v>44708</v>
       </c>
       <c r="B44" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C44" t="n">
-        <v>11.42030698171035</v>
+        <v>11.42030600182509</v>
       </c>
       <c r="D44" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="E44" t="n">
-        <v>11.26364997004757</v>
+        <v>11.26364900360379</v>
       </c>
       <c r="F44" t="n">
         <v>2224600</v>
@@ -1352,16 +1352,16 @@
         <v>44713</v>
       </c>
       <c r="B47" t="n">
-        <v>10.7310152053833</v>
+        <v>10.73101425170898</v>
       </c>
       <c r="C47" t="n">
-        <v>10.94250272786947</v>
+        <v>10.94250175540008</v>
       </c>
       <c r="D47" t="n">
-        <v>10.66051936455458</v>
+        <v>10.66051841714529</v>
       </c>
       <c r="E47" t="n">
-        <v>10.94250272786947</v>
+        <v>10.94250175540008</v>
       </c>
       <c r="F47" t="n">
         <v>6323900</v>
@@ -1532,16 +1532,16 @@
         <v>44726</v>
       </c>
       <c r="B56" t="n">
-        <v>10.39420318603516</v>
+        <v>10.39420223236084</v>
       </c>
       <c r="C56" t="n">
-        <v>10.47253131980584</v>
+        <v>10.47253035894487</v>
       </c>
       <c r="D56" t="n">
-        <v>10.01822560413734</v>
+        <v>10.01822468495919</v>
       </c>
       <c r="E56" t="n">
-        <v>10.01822560413734</v>
+        <v>10.01822468495919</v>
       </c>
       <c r="F56" t="n">
         <v>4085600</v>
@@ -1552,16 +1552,16 @@
         <v>44727</v>
       </c>
       <c r="B57" t="n">
-        <v>10.84067535400391</v>
+        <v>10.84067440032959</v>
       </c>
       <c r="C57" t="n">
-        <v>10.84850839111218</v>
+        <v>10.84850743674878</v>
       </c>
       <c r="D57" t="n">
-        <v>10.44119942547642</v>
+        <v>10.44119850694474</v>
       </c>
       <c r="E57" t="n">
-        <v>10.55085970399363</v>
+        <v>10.55085877581493</v>
       </c>
       <c r="F57" t="n">
         <v>3153700</v>
@@ -1632,16 +1632,16 @@
         <v>44734</v>
       </c>
       <c r="B61" t="n">
-        <v>10.73884773254395</v>
+        <v>10.73884868621826</v>
       </c>
       <c r="C61" t="n">
-        <v>10.83284193351813</v>
+        <v>10.8328428955397</v>
       </c>
       <c r="D61" t="n">
-        <v>10.43336601912821</v>
+        <v>10.43336694567391</v>
       </c>
       <c r="E61" t="n">
-        <v>10.53519325693346</v>
+        <v>10.53519419252203</v>
       </c>
       <c r="F61" t="n">
         <v>1196200</v>
@@ -1912,16 +1912,16 @@
         <v>44754</v>
       </c>
       <c r="B75" t="n">
-        <v>11.14615631103516</v>
+        <v>11.14615726470947</v>
       </c>
       <c r="C75" t="n">
-        <v>11.22448518797689</v>
+        <v>11.22448614835309</v>
       </c>
       <c r="D75" t="n">
-        <v>10.99733234124531</v>
+        <v>10.99733328218612</v>
       </c>
       <c r="E75" t="n">
-        <v>11.10699261956382</v>
+        <v>11.10699356988726</v>
       </c>
       <c r="F75" t="n">
         <v>1673000</v>
@@ -1952,16 +1952,16 @@
         <v>44756</v>
       </c>
       <c r="B77" t="n">
-        <v>10.91117000579834</v>
+        <v>10.91117095947266</v>
       </c>
       <c r="C77" t="n">
-        <v>11.1774872624825</v>
+        <v>11.17748823943387</v>
       </c>
       <c r="D77" t="n">
-        <v>10.84850720975495</v>
+        <v>10.84850815795232</v>
       </c>
       <c r="E77" t="n">
-        <v>11.04432863414042</v>
+        <v>11.04432959945326</v>
       </c>
       <c r="F77" t="n">
         <v>1968500</v>
@@ -1992,16 +1992,16 @@
         <v>44760</v>
       </c>
       <c r="B79" t="n">
-        <v>10.7310152053833</v>
+        <v>10.73101425170898</v>
       </c>
       <c r="C79" t="n">
-        <v>11.0051655314951</v>
+        <v>11.00516455345681</v>
       </c>
       <c r="D79" t="n">
-        <v>10.5900242707254</v>
+        <v>10.59002332958107</v>
       </c>
       <c r="E79" t="n">
-        <v>10.80934408341511</v>
+        <v>10.80934312277964</v>
       </c>
       <c r="F79" t="n">
         <v>1463400</v>
@@ -2052,16 +2052,16 @@
         <v>44763</v>
       </c>
       <c r="B82" t="n">
-        <v>11.24798393249512</v>
+        <v>11.24798202514648</v>
       </c>
       <c r="C82" t="n">
-        <v>11.27931533493105</v>
+        <v>11.27931342226948</v>
       </c>
       <c r="D82" t="n">
-        <v>11.0599955178795</v>
+        <v>11.05999364240853</v>
       </c>
       <c r="E82" t="n">
-        <v>11.22448556741805</v>
+        <v>11.2244836640541</v>
       </c>
       <c r="F82" t="n">
         <v>1092700</v>
@@ -2112,16 +2112,16 @@
         <v>44768</v>
       </c>
       <c r="B85" t="n">
-        <v>11.27148342132568</v>
+        <v>11.27148246765137</v>
       </c>
       <c r="C85" t="n">
-        <v>11.3811429600171</v>
+        <v>11.38114199706455</v>
       </c>
       <c r="D85" t="n">
-        <v>11.16965617325538</v>
+        <v>11.16965522819662</v>
       </c>
       <c r="E85" t="n">
-        <v>11.19315453911789</v>
+        <v>11.19315359207094</v>
       </c>
       <c r="F85" t="n">
         <v>1661400</v>
@@ -2172,16 +2172,16 @@
         <v>44771</v>
       </c>
       <c r="B88" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C88" t="n">
-        <v>11.33414581204571</v>
+        <v>11.33414483955325</v>
       </c>
       <c r="D88" t="n">
-        <v>10.51952860439969</v>
+        <v>10.51952770180302</v>
       </c>
       <c r="E88" t="n">
-        <v>10.96600127438851</v>
+        <v>10.96600033348359</v>
       </c>
       <c r="F88" t="n">
         <v>13059200</v>
@@ -2292,16 +2292,16 @@
         <v>44781</v>
       </c>
       <c r="B94" t="n">
-        <v>10.97383308410645</v>
+        <v>10.97383403778076</v>
       </c>
       <c r="C94" t="n">
-        <v>11.10699171587358</v>
+        <v>11.10699268111997</v>
       </c>
       <c r="D94" t="n">
-        <v>10.8720058511669</v>
+        <v>10.87200679599199</v>
       </c>
       <c r="E94" t="n">
-        <v>11.02866284530486</v>
+        <v>11.02866380374413</v>
       </c>
       <c r="F94" t="n">
         <v>2949000</v>
@@ -2352,16 +2352,16 @@
         <v>44784</v>
       </c>
       <c r="B97" t="n">
-        <v>10.89550590515137</v>
+        <v>10.89550495147705</v>
       </c>
       <c r="C97" t="n">
-        <v>11.10699344032233</v>
+        <v>11.10699246813669</v>
       </c>
       <c r="D97" t="n">
-        <v>10.83284309776729</v>
+        <v>10.83284214957779</v>
       </c>
       <c r="E97" t="n">
-        <v>11.05999596128448</v>
+        <v>11.05999499321249</v>
       </c>
       <c r="F97" t="n">
         <v>1665400</v>
@@ -2452,16 +2452,16 @@
         <v>44791</v>
       </c>
       <c r="B102" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="C102" t="n">
-        <v>11.37330897550059</v>
+        <v>11.37330994384684</v>
       </c>
       <c r="D102" t="n">
-        <v>11.09915867560374</v>
+        <v>11.09915962060828</v>
       </c>
       <c r="E102" t="n">
-        <v>11.27931403205064</v>
+        <v>11.27931499239396</v>
       </c>
       <c r="F102" t="n">
         <v>2180500</v>
@@ -2472,16 +2472,16 @@
         <v>44792</v>
       </c>
       <c r="B103" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C103" t="n">
-        <v>11.16182272571687</v>
+        <v>11.16182176801008</v>
       </c>
       <c r="D103" t="n">
-        <v>10.98166734905456</v>
+        <v>10.98166640680546</v>
       </c>
       <c r="E103" t="n">
-        <v>11.16182272571687</v>
+        <v>11.16182176801008</v>
       </c>
       <c r="F103" t="n">
         <v>1667800</v>
@@ -2492,16 +2492,16 @@
         <v>44795</v>
       </c>
       <c r="B104" t="n">
-        <v>11.0599946975708</v>
+        <v>11.05999565124512</v>
       </c>
       <c r="C104" t="n">
-        <v>11.2244847349093</v>
+        <v>11.22448570276716</v>
       </c>
       <c r="D104" t="n">
-        <v>10.98166657079026</v>
+        <v>10.98166751771054</v>
       </c>
       <c r="E104" t="n">
-        <v>11.0599946975708</v>
+        <v>11.05999565124512</v>
       </c>
       <c r="F104" t="n">
         <v>1703300</v>
@@ -2592,16 +2592,16 @@
         <v>44802</v>
       </c>
       <c r="B109" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C109" t="n">
-        <v>11.20882020271549</v>
+        <v>11.20881924097621</v>
       </c>
       <c r="D109" t="n">
-        <v>10.93466987205595</v>
+        <v>10.93466893383933</v>
       </c>
       <c r="E109" t="n">
-        <v>11.02083104172059</v>
+        <v>11.02083009611117</v>
       </c>
       <c r="F109" t="n">
         <v>3615600</v>
@@ -2632,16 +2632,16 @@
         <v>44804</v>
       </c>
       <c r="B111" t="n">
-        <v>12.03910160064697</v>
+        <v>12.03910255432129</v>
       </c>
       <c r="C111" t="n">
-        <v>12.07826603661254</v>
+        <v>12.07826699338926</v>
       </c>
       <c r="D111" t="n">
-        <v>10.96600023838756</v>
+        <v>10.96600110705643</v>
       </c>
       <c r="E111" t="n">
-        <v>11.02083000053966</v>
+        <v>11.02083087355185</v>
       </c>
       <c r="F111" t="n">
         <v>16560000</v>
@@ -2652,16 +2652,16 @@
         <v>44805</v>
       </c>
       <c r="B112" t="n">
-        <v>11.65529251098633</v>
+        <v>11.65529155731201</v>
       </c>
       <c r="C112" t="n">
-        <v>12.15659567974902</v>
+        <v>12.15659468505643</v>
       </c>
       <c r="D112" t="n">
-        <v>11.42030662728508</v>
+        <v>11.42030569283808</v>
       </c>
       <c r="E112" t="n">
-        <v>12.14092960556915</v>
+        <v>12.14092861215841</v>
       </c>
       <c r="F112" t="n">
         <v>4716400</v>
@@ -2692,16 +2692,16 @@
         <v>44809</v>
       </c>
       <c r="B114" t="n">
-        <v>11.85894680023193</v>
+        <v>11.85894775390625</v>
       </c>
       <c r="C114" t="n">
-        <v>11.92160960193201</v>
+        <v>11.92161056064555</v>
       </c>
       <c r="D114" t="n">
-        <v>11.60829484643211</v>
+        <v>11.60829577994947</v>
       </c>
       <c r="E114" t="n">
-        <v>11.76495259768182</v>
+        <v>11.7649535437973</v>
       </c>
       <c r="F114" t="n">
         <v>1899700</v>
@@ -2712,16 +2712,16 @@
         <v>44810</v>
       </c>
       <c r="B115" t="n">
-        <v>11.58479785919189</v>
+        <v>11.58479595184326</v>
       </c>
       <c r="C115" t="n">
-        <v>11.90594494281729</v>
+        <v>11.90594298259424</v>
       </c>
       <c r="D115" t="n">
-        <v>11.49863668336545</v>
+        <v>11.49863479020259</v>
       </c>
       <c r="E115" t="n">
-        <v>11.89811190492408</v>
+        <v>11.89810994599068</v>
       </c>
       <c r="F115" t="n">
         <v>1316500</v>
@@ -2732,16 +2732,16 @@
         <v>44812</v>
       </c>
       <c r="B116" t="n">
-        <v>11.43597221374512</v>
+        <v>11.43597316741943</v>
       </c>
       <c r="C116" t="n">
-        <v>11.63962594040124</v>
+        <v>11.63962691105875</v>
       </c>
       <c r="D116" t="n">
-        <v>11.37330941369716</v>
+        <v>11.37331036214587</v>
       </c>
       <c r="E116" t="n">
-        <v>11.623960613889</v>
+        <v>11.62396158324014</v>
       </c>
       <c r="F116" t="n">
         <v>2598100</v>
@@ -2892,16 +2892,16 @@
         <v>44824</v>
       </c>
       <c r="B124" t="n">
-        <v>11.13049125671387</v>
+        <v>11.13049030303955</v>
       </c>
       <c r="C124" t="n">
-        <v>11.35764410901417</v>
+        <v>11.35764313587711</v>
       </c>
       <c r="D124" t="n">
-        <v>11.08349377999676</v>
+        <v>11.08349283034925</v>
       </c>
       <c r="E124" t="n">
-        <v>11.28714826743829</v>
+        <v>11.28714730034141</v>
       </c>
       <c r="F124" t="n">
         <v>1310600</v>
@@ -2952,16 +2952,16 @@
         <v>44827</v>
       </c>
       <c r="B127" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="C127" t="n">
-        <v>11.30281314141286</v>
+        <v>11.30281410375695</v>
       </c>
       <c r="D127" t="n">
-        <v>11.07566031324099</v>
+        <v>11.07566125624483</v>
       </c>
       <c r="E127" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="F127" t="n">
         <v>2444100</v>
@@ -2972,16 +2972,16 @@
         <v>44830</v>
       </c>
       <c r="B128" t="n">
-        <v>11.00516510009766</v>
+        <v>11.00516605377197</v>
       </c>
       <c r="C128" t="n">
-        <v>11.20881957739757</v>
+        <v>11.20882054871997</v>
       </c>
       <c r="D128" t="n">
-        <v>10.88767178765562</v>
+        <v>10.88767273114832</v>
       </c>
       <c r="E128" t="n">
-        <v>11.20098654050153</v>
+        <v>11.20098751114514</v>
       </c>
       <c r="F128" t="n">
         <v>1884300</v>
@@ -2992,16 +2992,16 @@
         <v>44831</v>
       </c>
       <c r="B129" t="n">
-        <v>10.9033374786377</v>
+        <v>10.90333843231201</v>
       </c>
       <c r="C129" t="n">
-        <v>11.04432914981819</v>
+        <v>11.04433011582452</v>
       </c>
       <c r="D129" t="n">
-        <v>10.77017884407822</v>
+        <v>10.77017978610565</v>
       </c>
       <c r="E129" t="n">
-        <v>11.04432914981819</v>
+        <v>11.04433011582452</v>
       </c>
       <c r="F129" t="n">
         <v>2130200</v>
@@ -3072,16 +3072,16 @@
         <v>44837</v>
       </c>
       <c r="B133" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="C133" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="D133" t="n">
-        <v>10.62918694635185</v>
+        <v>10.62918785134206</v>
       </c>
       <c r="E133" t="n">
-        <v>10.74668025216456</v>
+        <v>10.74668116715839</v>
       </c>
       <c r="F133" t="n">
         <v>2250700</v>
@@ -3092,16 +3092,16 @@
         <v>44838</v>
       </c>
       <c r="B134" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C134" t="n">
-        <v>11.32631277471268</v>
+        <v>11.32631180289231</v>
       </c>
       <c r="D134" t="n">
-        <v>11.07566155605223</v>
+        <v>11.07566060573824</v>
       </c>
       <c r="E134" t="n">
-        <v>11.20882020271549</v>
+        <v>11.20881924097621</v>
       </c>
       <c r="F134" t="n">
         <v>2406500</v>
@@ -3112,16 +3112,16 @@
         <v>44839</v>
       </c>
       <c r="B135" t="n">
-        <v>10.97383308410645</v>
+        <v>10.97383403778076</v>
       </c>
       <c r="C135" t="n">
-        <v>11.20881894881312</v>
+        <v>11.20881992290874</v>
       </c>
       <c r="D135" t="n">
-        <v>10.85633977825337</v>
+        <v>10.85634072171701</v>
       </c>
       <c r="E135" t="n">
-        <v>11.20881894881312</v>
+        <v>11.20881992290874</v>
       </c>
       <c r="F135" t="n">
         <v>5244200</v>
@@ -3212,16 +3212,16 @@
         <v>44847</v>
       </c>
       <c r="B140" t="n">
-        <v>10.91117000579834</v>
+        <v>10.91117095947266</v>
       </c>
       <c r="C140" t="n">
-        <v>11.20098562424891</v>
+        <v>11.20098660325412</v>
       </c>
       <c r="D140" t="n">
-        <v>10.87200557152136</v>
+        <v>10.87200652177256</v>
       </c>
       <c r="E140" t="n">
-        <v>11.12265675569494</v>
+        <v>11.12265772785393</v>
       </c>
       <c r="F140" t="n">
         <v>3739400</v>
@@ -3232,16 +3232,16 @@
         <v>44848</v>
       </c>
       <c r="B141" t="n">
-        <v>10.82500839233398</v>
+        <v>10.8250093460083</v>
       </c>
       <c r="C141" t="n">
-        <v>11.16182149038183</v>
+        <v>11.1618224737291</v>
       </c>
       <c r="D141" t="n">
-        <v>10.82500839233398</v>
+        <v>10.8250093460083</v>
       </c>
       <c r="E141" t="n">
-        <v>10.97383309719211</v>
+        <v>10.97383406397776</v>
       </c>
       <c r="F141" t="n">
         <v>3601200</v>
@@ -3272,16 +3272,16 @@
         <v>44852</v>
       </c>
       <c r="B143" t="n">
-        <v>11.27148342132568</v>
+        <v>11.27148246765137</v>
       </c>
       <c r="C143" t="n">
-        <v>11.37331066939599</v>
+        <v>11.37330970710612</v>
       </c>
       <c r="D143" t="n">
-        <v>11.06782892518508</v>
+        <v>11.06782798874186</v>
       </c>
       <c r="E143" t="n">
-        <v>11.20882061435928</v>
+        <v>11.20881966598683</v>
       </c>
       <c r="F143" t="n">
         <v>2646800</v>
@@ -3312,16 +3312,16 @@
         <v>44854</v>
       </c>
       <c r="B145" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C145" t="n">
-        <v>10.98166658413194</v>
+        <v>10.98166755090811</v>
       </c>
       <c r="D145" t="n">
-        <v>10.39420227106638</v>
+        <v>10.39420318612486</v>
       </c>
       <c r="E145" t="n">
-        <v>10.57435763518006</v>
+        <v>10.5743585660986</v>
       </c>
       <c r="F145" t="n">
         <v>7194300</v>
@@ -3352,16 +3352,16 @@
         <v>44858</v>
       </c>
       <c r="B147" t="n">
-        <v>11.24798393249512</v>
+        <v>11.24798202514648</v>
       </c>
       <c r="C147" t="n">
-        <v>11.45163842182848</v>
+        <v>11.45163647994565</v>
       </c>
       <c r="D147" t="n">
-        <v>11.10699299503318</v>
+        <v>11.10699111159273</v>
       </c>
       <c r="E147" t="n">
-        <v>11.10699299503318</v>
+        <v>11.10699111159273</v>
       </c>
       <c r="F147" t="n">
         <v>2219500</v>
@@ -3372,16 +3372,16 @@
         <v>44859</v>
       </c>
       <c r="B148" t="n">
-        <v>11.38897609710693</v>
+        <v>11.38897514343262</v>
       </c>
       <c r="C148" t="n">
-        <v>11.5064686744452</v>
+        <v>11.50646771093245</v>
       </c>
       <c r="D148" t="n">
-        <v>11.18532159918765</v>
+        <v>11.18532066256667</v>
       </c>
       <c r="E148" t="n">
-        <v>11.24015211601182</v>
+        <v>11.24015117479952</v>
       </c>
       <c r="F148" t="n">
         <v>2935500</v>
@@ -3512,16 +3512,16 @@
         <v>44869</v>
       </c>
       <c r="B155" t="n">
-        <v>11.67095851898193</v>
+        <v>11.67095756530762</v>
       </c>
       <c r="C155" t="n">
-        <v>11.87461301320299</v>
+        <v>11.87461204288736</v>
       </c>
       <c r="D155" t="n">
-        <v>11.64746015334091</v>
+        <v>11.64745920158673</v>
       </c>
       <c r="E155" t="n">
-        <v>11.74928740045144</v>
+        <v>11.7492864403766</v>
       </c>
       <c r="F155" t="n">
         <v>2161500</v>
@@ -3532,16 +3532,16 @@
         <v>44872</v>
       </c>
       <c r="B156" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="C156" t="n">
-        <v>11.65529156485204</v>
+        <v>11.65529255720685</v>
       </c>
       <c r="D156" t="n">
-        <v>11.1226570379665</v>
+        <v>11.12265798497174</v>
       </c>
       <c r="E156" t="n">
-        <v>11.60829409312706</v>
+        <v>11.60829508148041</v>
       </c>
       <c r="F156" t="n">
         <v>3276500</v>
@@ -3612,16 +3612,16 @@
         <v>44876</v>
       </c>
       <c r="B160" t="n">
-        <v>10.79367828369141</v>
+        <v>10.79367733001709</v>
       </c>
       <c r="C160" t="n">
-        <v>10.85634108891171</v>
+        <v>10.85634012970083</v>
       </c>
       <c r="D160" t="n">
-        <v>10.53519402540776</v>
+        <v>10.5351930945718</v>
       </c>
       <c r="E160" t="n">
-        <v>10.78584599328854</v>
+        <v>10.78584504030624</v>
       </c>
       <c r="F160" t="n">
         <v>3291200</v>
@@ -3632,16 +3632,16 @@
         <v>44879</v>
       </c>
       <c r="B161" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C161" t="n">
-        <v>10.9660005105571</v>
+        <v>10.9660014759541</v>
       </c>
       <c r="D161" t="n">
-        <v>10.71534930935563</v>
+        <v>10.71535025268644</v>
       </c>
       <c r="E161" t="n">
-        <v>10.94250214719434</v>
+        <v>10.94250311052265</v>
       </c>
       <c r="F161" t="n">
         <v>1203700</v>
@@ -3652,16 +3652,16 @@
         <v>44881</v>
       </c>
       <c r="B162" t="n">
-        <v>10.9033374786377</v>
+        <v>10.90333843231201</v>
       </c>
       <c r="C162" t="n">
-        <v>10.9033374786377</v>
+        <v>10.90333843231201</v>
       </c>
       <c r="D162" t="n">
-        <v>10.59785577341312</v>
+        <v>10.59785670036809</v>
       </c>
       <c r="E162" t="n">
-        <v>10.86417304253206</v>
+        <v>10.86417399278081</v>
       </c>
       <c r="F162" t="n">
         <v>5270300</v>
@@ -3692,16 +3692,16 @@
         <v>44883</v>
       </c>
       <c r="B164" t="n">
-        <v>10.78584671020508</v>
+        <v>10.78584480285645</v>
       </c>
       <c r="C164" t="n">
-        <v>10.9895004672078</v>
+        <v>10.98949852384542</v>
       </c>
       <c r="D164" t="n">
-        <v>10.57435916827967</v>
+        <v>10.57435729833009</v>
       </c>
       <c r="E164" t="n">
-        <v>10.8093450769747</v>
+        <v>10.80934316547066</v>
       </c>
       <c r="F164" t="n">
         <v>3568700</v>
@@ -3752,16 +3752,16 @@
         <v>44888</v>
       </c>
       <c r="B167" t="n">
-        <v>10.56652450561523</v>
+        <v>10.56652545928955</v>
       </c>
       <c r="C167" t="n">
-        <v>10.8171764516154</v>
+        <v>10.81717742791213</v>
       </c>
       <c r="D167" t="n">
-        <v>10.51952777930236</v>
+        <v>10.51952872873502</v>
       </c>
       <c r="E167" t="n">
-        <v>10.80934341489675</v>
+        <v>10.80934439048652</v>
       </c>
       <c r="F167" t="n">
         <v>4669400</v>
@@ -3792,16 +3792,16 @@
         <v>44890</v>
       </c>
       <c r="B169" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C169" t="n">
-        <v>11.03649634764489</v>
+        <v>11.03649731924802</v>
       </c>
       <c r="D169" t="n">
-        <v>10.71534930935563</v>
+        <v>10.71535025268644</v>
       </c>
       <c r="E169" t="n">
-        <v>10.95033443698226</v>
+        <v>10.95033540100009</v>
       </c>
       <c r="F169" t="n">
         <v>1631500</v>
@@ -3812,16 +3812,16 @@
         <v>44893</v>
       </c>
       <c r="B170" t="n">
-        <v>10.97383308410645</v>
+        <v>10.97383403778076</v>
       </c>
       <c r="C170" t="n">
-        <v>11.09915867941681</v>
+        <v>11.09915964398247</v>
       </c>
       <c r="D170" t="n">
-        <v>10.68401745820135</v>
+        <v>10.68401838668942</v>
       </c>
       <c r="E170" t="n">
-        <v>10.84067445233931</v>
+        <v>10.84067539444156</v>
       </c>
       <c r="F170" t="n">
         <v>4990000</v>
@@ -3852,16 +3852,16 @@
         <v>44895</v>
       </c>
       <c r="B172" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C172" t="n">
-        <v>11.20881942197064</v>
+        <v>11.20882040874432</v>
       </c>
       <c r="D172" t="n">
-        <v>10.69185019899337</v>
+        <v>10.69185114025542</v>
       </c>
       <c r="E172" t="n">
-        <v>11.20881942197064</v>
+        <v>11.20882040874432</v>
       </c>
       <c r="F172" t="n">
         <v>4586400</v>
@@ -3912,16 +3912,16 @@
         <v>44900</v>
       </c>
       <c r="B175" t="n">
-        <v>10.51952743530273</v>
+        <v>10.51952838897705</v>
       </c>
       <c r="C175" t="n">
-        <v>10.80151002495736</v>
+        <v>10.80151100419552</v>
       </c>
       <c r="D175" t="n">
-        <v>10.50386136237774</v>
+        <v>10.50386231463181</v>
       </c>
       <c r="E175" t="n">
-        <v>10.77801166256934</v>
+        <v>10.7780126396772</v>
       </c>
       <c r="F175" t="n">
         <v>1355000</v>
@@ -3932,16 +3932,16 @@
         <v>44901</v>
       </c>
       <c r="B176" t="n">
-        <v>10.47253036499023</v>
+        <v>10.47253131866455</v>
       </c>
       <c r="C176" t="n">
-        <v>10.58219063867058</v>
+        <v>10.58219160233104</v>
       </c>
       <c r="D176" t="n">
-        <v>10.41770060164981</v>
+        <v>10.41770155033109</v>
       </c>
       <c r="E176" t="n">
-        <v>10.51952783856738</v>
+        <v>10.51952879652149</v>
       </c>
       <c r="F176" t="n">
         <v>1647500</v>
@@ -4012,16 +4012,16 @@
         <v>44907</v>
       </c>
       <c r="B180" t="n">
-        <v>11.00516510009766</v>
+        <v>11.00516605377197</v>
       </c>
       <c r="C180" t="n">
-        <v>11.26364934167081</v>
+        <v>11.26365031774459</v>
       </c>
       <c r="D180" t="n">
-        <v>10.7466808585245</v>
+        <v>10.74668178979936</v>
       </c>
       <c r="E180" t="n">
-        <v>11.17748817681293</v>
+        <v>11.17748914542024</v>
       </c>
       <c r="F180" t="n">
         <v>4004300</v>
@@ -4052,16 +4052,16 @@
         <v>44909</v>
       </c>
       <c r="B182" t="n">
-        <v>10.99733257293701</v>
+        <v>10.9973316192627</v>
       </c>
       <c r="C182" t="n">
-        <v>11.13832425560273</v>
+        <v>11.13832328970179</v>
       </c>
       <c r="D182" t="n">
-        <v>10.7388483193829</v>
+        <v>10.738847388124</v>
       </c>
       <c r="E182" t="n">
-        <v>11.01299864745522</v>
+        <v>11.01299769242237</v>
       </c>
       <c r="F182" t="n">
         <v>3892800</v>
@@ -4092,16 +4092,16 @@
         <v>44911</v>
       </c>
       <c r="B184" t="n">
-        <v>11.24798393249512</v>
+        <v>11.24798202514648</v>
       </c>
       <c r="C184" t="n">
-        <v>11.24798393249512</v>
+        <v>11.24798202514648</v>
       </c>
       <c r="D184" t="n">
-        <v>10.90333850569981</v>
+        <v>10.90333665679356</v>
       </c>
       <c r="E184" t="n">
-        <v>11.04433019016131</v>
+        <v>11.04432831734674</v>
       </c>
       <c r="F184" t="n">
         <v>3365900</v>
@@ -4152,16 +4152,16 @@
         <v>44916</v>
       </c>
       <c r="B187" t="n">
-        <v>11.58479785919189</v>
+        <v>11.58479595184326</v>
       </c>
       <c r="C187" t="n">
-        <v>11.7571209578444</v>
+        <v>11.75711902212409</v>
       </c>
       <c r="D187" t="n">
-        <v>11.15399048606043</v>
+        <v>11.15398864964095</v>
       </c>
       <c r="E187" t="n">
-        <v>11.4281408363258</v>
+        <v>11.42813895476955</v>
       </c>
       <c r="F187" t="n">
         <v>6348400</v>
@@ -4172,16 +4172,16 @@
         <v>44917</v>
       </c>
       <c r="B188" t="n">
-        <v>11.63179397583008</v>
+        <v>11.63179492950439</v>
       </c>
       <c r="C188" t="n">
-        <v>11.74928654245482</v>
+        <v>11.74928750576218</v>
       </c>
       <c r="D188" t="n">
-        <v>11.50646762523096</v>
+        <v>11.50646856862995</v>
       </c>
       <c r="E188" t="n">
-        <v>11.60046257493018</v>
+        <v>11.60046352603568</v>
       </c>
       <c r="F188" t="n">
         <v>2577900</v>
@@ -4212,16 +4212,16 @@
         <v>44921</v>
       </c>
       <c r="B190" t="n">
-        <v>11.57696342468262</v>
+        <v>11.5769624710083</v>
       </c>
       <c r="C190" t="n">
-        <v>11.82761537802995</v>
+        <v>11.8276144037077</v>
       </c>
       <c r="D190" t="n">
-        <v>11.51430062309566</v>
+        <v>11.51429967458331</v>
       </c>
       <c r="E190" t="n">
-        <v>11.77278486639172</v>
+        <v>11.77278389658625</v>
       </c>
       <c r="F190" t="n">
         <v>1646600</v>
@@ -4232,16 +4232,16 @@
         <v>44922</v>
       </c>
       <c r="B191" t="n">
-        <v>11.52996730804443</v>
+        <v>11.52996635437012</v>
       </c>
       <c r="C191" t="n">
-        <v>11.60829544067951</v>
+        <v>11.60829448052647</v>
       </c>
       <c r="D191" t="n">
-        <v>11.34197814632122</v>
+        <v>11.34197720819598</v>
       </c>
       <c r="E191" t="n">
-        <v>11.60829544067951</v>
+        <v>11.60829448052647</v>
       </c>
       <c r="F191" t="n">
         <v>1633000</v>
@@ -4252,16 +4252,16 @@
         <v>44923</v>
       </c>
       <c r="B192" t="n">
-        <v>11.58479785919189</v>
+        <v>11.58479595184326</v>
       </c>
       <c r="C192" t="n">
-        <v>11.69445814869797</v>
+        <v>11.6944562232946</v>
       </c>
       <c r="D192" t="n">
-        <v>11.49863668336545</v>
+        <v>11.49863479020259</v>
       </c>
       <c r="E192" t="n">
-        <v>11.57696482129869</v>
+        <v>11.5769629152397</v>
       </c>
       <c r="F192" t="n">
         <v>2005900</v>
@@ -4272,16 +4272,16 @@
         <v>44924</v>
       </c>
       <c r="B193" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="C193" t="n">
-        <v>11.73362129131107</v>
+        <v>11.73362032145083</v>
       </c>
       <c r="D193" t="n">
-        <v>11.47513702901113</v>
+        <v>11.4751360805163</v>
       </c>
       <c r="E193" t="n">
-        <v>11.62396175397144</v>
+        <v>11.62396079317528</v>
       </c>
       <c r="F193" t="n">
         <v>2424800</v>
@@ -4312,16 +4312,16 @@
         <v>44929</v>
       </c>
       <c r="B195" t="n">
-        <v>11.13832473754883</v>
+        <v>11.13832378387451</v>
       </c>
       <c r="C195" t="n">
-        <v>11.32631315790418</v>
+        <v>11.32631218813412</v>
       </c>
       <c r="D195" t="n">
-        <v>11.05999585556764</v>
+        <v>11.05999490859992</v>
       </c>
       <c r="E195" t="n">
-        <v>11.30281479210966</v>
+        <v>11.30281382435154</v>
       </c>
       <c r="F195" t="n">
         <v>1562800</v>
@@ -4412,16 +4412,16 @@
         <v>44936</v>
       </c>
       <c r="B200" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C200" t="n">
-        <v>11.1853210907164</v>
+        <v>11.1853201309934</v>
       </c>
       <c r="D200" t="n">
-        <v>10.69185094372897</v>
+        <v>10.6918500263467</v>
       </c>
       <c r="E200" t="n">
-        <v>11.08349384638571</v>
+        <v>11.08349289539969</v>
       </c>
       <c r="F200" t="n">
         <v>5832500</v>
@@ -4472,16 +4472,16 @@
         <v>44939</v>
       </c>
       <c r="B203" t="n">
-        <v>11.58479785919189</v>
+        <v>11.58479595184326</v>
       </c>
       <c r="C203" t="n">
-        <v>11.78845236241762</v>
+        <v>11.78845042153883</v>
       </c>
       <c r="D203" t="n">
-        <v>11.4438061651126</v>
+        <v>11.44380428097718</v>
       </c>
       <c r="E203" t="n">
-        <v>11.7492879199512</v>
+        <v>11.74928598552053</v>
       </c>
       <c r="F203" t="n">
         <v>2269100</v>
@@ -4512,16 +4512,16 @@
         <v>44943</v>
       </c>
       <c r="B205" t="n">
-        <v>11.74928569793701</v>
+        <v>11.74928665161133</v>
       </c>
       <c r="C205" t="n">
-        <v>11.93727408982413</v>
+        <v>11.93727505875722</v>
       </c>
       <c r="D205" t="n">
-        <v>11.60829403052194</v>
+        <v>11.60829497275214</v>
       </c>
       <c r="E205" t="n">
-        <v>11.81194849523272</v>
+        <v>11.81194945399329</v>
       </c>
       <c r="F205" t="n">
         <v>2676600</v>
@@ -4572,16 +4572,16 @@
         <v>44946</v>
       </c>
       <c r="B208" t="n">
-        <v>11.58479785919189</v>
+        <v>11.58479595184326</v>
       </c>
       <c r="C208" t="n">
-        <v>11.68662511080476</v>
+        <v>11.68662318669104</v>
       </c>
       <c r="D208" t="n">
-        <v>11.48297060757903</v>
+        <v>11.48296871699548</v>
       </c>
       <c r="E208" t="n">
-        <v>11.65529370623154</v>
+        <v>11.6552917872763</v>
       </c>
       <c r="F208" t="n">
         <v>2012100</v>
@@ -4752,16 +4752,16 @@
         <v>44959</v>
       </c>
       <c r="B217" t="n">
-        <v>12.03910160064697</v>
+        <v>12.03910255432129</v>
       </c>
       <c r="C217" t="n">
-        <v>12.19575859750976</v>
+        <v>12.19575956359362</v>
       </c>
       <c r="D217" t="n">
-        <v>11.85111320441163</v>
+        <v>11.8511141431945</v>
       </c>
       <c r="E217" t="n">
-        <v>12.07043300001953</v>
+        <v>12.07043395617575</v>
       </c>
       <c r="F217" t="n">
         <v>3404900</v>
@@ -4812,16 +4812,16 @@
         <v>44964</v>
       </c>
       <c r="B220" t="n">
-        <v>11.60046291351318</v>
+        <v>11.60046195983887</v>
       </c>
       <c r="C220" t="n">
-        <v>12.02343721150694</v>
+        <v>12.02343622305989</v>
       </c>
       <c r="D220" t="n">
-        <v>11.49080263366312</v>
+        <v>11.49080168900398</v>
       </c>
       <c r="E220" t="n">
-        <v>12.02343721150694</v>
+        <v>12.02343622305989</v>
       </c>
       <c r="F220" t="n">
         <v>5199600</v>
@@ -4912,16 +4912,16 @@
         <v>44971</v>
       </c>
       <c r="B225" t="n">
-        <v>11.71795558929443</v>
+        <v>11.71795463562012</v>
       </c>
       <c r="C225" t="n">
-        <v>11.8824456370539</v>
+        <v>11.88244466999244</v>
       </c>
       <c r="D225" t="n">
-        <v>11.51430110216375</v>
+        <v>11.51430016506401</v>
       </c>
       <c r="E225" t="n">
-        <v>11.78061839348856</v>
+        <v>11.78061743471438</v>
       </c>
       <c r="F225" t="n">
         <v>2141000</v>
@@ -4932,16 +4932,16 @@
         <v>44972</v>
       </c>
       <c r="B226" t="n">
-        <v>11.75712013244629</v>
+        <v>11.75711917877197</v>
       </c>
       <c r="C226" t="n">
-        <v>11.92944247200145</v>
+        <v>11.92944150434928</v>
       </c>
       <c r="D226" t="n">
-        <v>11.63179452295179</v>
+        <v>11.63179357944321</v>
       </c>
       <c r="E226" t="n">
-        <v>11.66312592532541</v>
+        <v>11.6631249792754</v>
       </c>
       <c r="F226" t="n">
         <v>3961900</v>
@@ -4992,16 +4992,16 @@
         <v>44979</v>
       </c>
       <c r="B229" t="n">
-        <v>11.71795558929443</v>
+        <v>11.71795463562012</v>
       </c>
       <c r="C229" t="n">
-        <v>11.95294147852217</v>
+        <v>11.95294050572336</v>
       </c>
       <c r="D229" t="n">
-        <v>11.66312582237446</v>
+        <v>11.66312487316251</v>
       </c>
       <c r="E229" t="n">
-        <v>11.89811096460265</v>
+        <v>11.89810999626626</v>
       </c>
       <c r="F229" t="n">
         <v>6185800</v>
@@ -5052,16 +5052,16 @@
         <v>44984</v>
       </c>
       <c r="B232" t="n">
-        <v>11.64745998382568</v>
+        <v>11.64745903015137</v>
       </c>
       <c r="C232" t="n">
-        <v>11.85894751251565</v>
+        <v>11.85894654152509</v>
       </c>
       <c r="D232" t="n">
-        <v>11.56129881306286</v>
+        <v>11.56129786644328</v>
       </c>
       <c r="E232" t="n">
-        <v>11.7336211545885</v>
+        <v>11.73362019385946</v>
       </c>
       <c r="F232" t="n">
         <v>3412900</v>
@@ -5072,16 +5072,16 @@
         <v>44985</v>
       </c>
       <c r="B233" t="n">
-        <v>11.59262943267822</v>
+        <v>11.59263038635254</v>
       </c>
       <c r="C233" t="n">
-        <v>11.82761531079323</v>
+        <v>11.82761628379879</v>
       </c>
       <c r="D233" t="n">
-        <v>11.54563195825542</v>
+        <v>11.54563290806346</v>
       </c>
       <c r="E233" t="n">
-        <v>11.67095756071688</v>
+        <v>11.67095852083491</v>
       </c>
       <c r="F233" t="n">
         <v>7018700</v>
@@ -5092,16 +5092,16 @@
         <v>44986</v>
       </c>
       <c r="B234" t="n">
-        <v>11.52996730804443</v>
+        <v>11.52996635437012</v>
       </c>
       <c r="C234" t="n">
-        <v>11.6552929178602</v>
+        <v>11.65529195381987</v>
       </c>
       <c r="D234" t="n">
-        <v>11.31847978123065</v>
+        <v>11.31847884504903</v>
       </c>
       <c r="E234" t="n">
-        <v>11.6004631503157</v>
+        <v>11.60046219081048</v>
       </c>
       <c r="F234" t="n">
         <v>8005300</v>
@@ -5112,16 +5112,16 @@
         <v>44987</v>
       </c>
       <c r="B235" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="C235" t="n">
-        <v>11.67879152264125</v>
+        <v>11.67879055731306</v>
       </c>
       <c r="D235" t="n">
-        <v>11.45947170096243</v>
+        <v>11.45947075376244</v>
       </c>
       <c r="E235" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="F235" t="n">
         <v>2250800</v>
@@ -5132,16 +5132,16 @@
         <v>44988</v>
       </c>
       <c r="B236" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="C236" t="n">
-        <v>11.64746011954428</v>
+        <v>11.64745915680582</v>
       </c>
       <c r="D236" t="n">
-        <v>11.45947170096243</v>
+        <v>11.45947075376244</v>
       </c>
       <c r="E236" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="F236" t="n">
         <v>1727100</v>
@@ -5192,16 +5192,16 @@
         <v>44993</v>
       </c>
       <c r="B239" t="n">
-        <v>11.63179397583008</v>
+        <v>11.63179492950439</v>
       </c>
       <c r="C239" t="n">
-        <v>11.63962626580541</v>
+        <v>11.63962722012189</v>
       </c>
       <c r="D239" t="n">
-        <v>11.48296926130592</v>
+        <v>11.48297020277831</v>
       </c>
       <c r="E239" t="n">
-        <v>11.62396093885522</v>
+        <v>11.62396189188732</v>
       </c>
       <c r="F239" t="n">
         <v>2946500</v>
@@ -5212,16 +5212,16 @@
         <v>44994</v>
       </c>
       <c r="B240" t="n">
-        <v>11.57696342468262</v>
+        <v>11.5769624710083</v>
       </c>
       <c r="C240" t="n">
-        <v>11.70228902785652</v>
+        <v>11.70228806385827</v>
       </c>
       <c r="D240" t="n">
-        <v>11.51430062309566</v>
+        <v>11.51429967458331</v>
       </c>
       <c r="E240" t="n">
-        <v>11.62396089937259</v>
+        <v>11.62395994182677</v>
       </c>
       <c r="F240" t="n">
         <v>2514900</v>
@@ -5232,16 +5232,16 @@
         <v>44995</v>
       </c>
       <c r="B241" t="n">
-        <v>11.57696342468262</v>
+        <v>11.5769624710083</v>
       </c>
       <c r="C241" t="n">
-        <v>11.63179393632084</v>
+        <v>11.63179297812976</v>
       </c>
       <c r="D241" t="n">
-        <v>11.44380478456046</v>
+        <v>11.44380384185534</v>
       </c>
       <c r="E241" t="n">
-        <v>11.57696342468262</v>
+        <v>11.5769624710083</v>
       </c>
       <c r="F241" t="n">
         <v>3626000</v>
@@ -5272,16 +5272,16 @@
         <v>44999</v>
       </c>
       <c r="B243" t="n">
-        <v>11.75712013244629</v>
+        <v>11.75711917877197</v>
       </c>
       <c r="C243" t="n">
-        <v>11.82761597453684</v>
+        <v>11.82761501514428</v>
       </c>
       <c r="D243" t="n">
-        <v>11.63962681329553</v>
+        <v>11.63962586915163</v>
       </c>
       <c r="E243" t="n">
-        <v>11.69445732769904</v>
+        <v>11.69445637910759</v>
       </c>
       <c r="F243" t="n">
         <v>2520000</v>
@@ -5292,16 +5292,16 @@
         <v>45000</v>
       </c>
       <c r="B244" t="n">
-        <v>11.74928569793701</v>
+        <v>11.74928665161133</v>
       </c>
       <c r="C244" t="n">
-        <v>11.89027736535209</v>
+        <v>11.89027833047051</v>
       </c>
       <c r="D244" t="n">
-        <v>11.61612706693377</v>
+        <v>11.61612800979977</v>
       </c>
       <c r="E244" t="n">
-        <v>11.71795429928916</v>
+        <v>11.71795525042035</v>
       </c>
       <c r="F244" t="n">
         <v>4602600</v>
@@ -5312,16 +5312,16 @@
         <v>45001</v>
       </c>
       <c r="B245" t="n">
-        <v>11.67095851898193</v>
+        <v>11.67095756530762</v>
       </c>
       <c r="C245" t="n">
-        <v>11.81195020682722</v>
+        <v>11.81194924163198</v>
       </c>
       <c r="D245" t="n">
-        <v>11.63962711579405</v>
+        <v>11.63962616467993</v>
       </c>
       <c r="E245" t="n">
-        <v>11.81195020682722</v>
+        <v>11.81194924163198</v>
       </c>
       <c r="F245" t="n">
         <v>5495800</v>
@@ -5332,16 +5332,16 @@
         <v>45002</v>
       </c>
       <c r="B246" t="n">
-        <v>11.40464115142822</v>
+        <v>11.40464019775391</v>
       </c>
       <c r="C246" t="n">
-        <v>11.66312539603</v>
+        <v>11.66312442074082</v>
       </c>
       <c r="D246" t="n">
-        <v>11.37330975047648</v>
+        <v>11.37330879942214</v>
       </c>
       <c r="E246" t="n">
-        <v>11.66312539603</v>
+        <v>11.66312442074082</v>
       </c>
       <c r="F246" t="n">
         <v>6196900</v>
@@ -5392,16 +5392,16 @@
         <v>45007</v>
       </c>
       <c r="B249" t="n">
-        <v>11.33414554595947</v>
+        <v>11.33414459228516</v>
       </c>
       <c r="C249" t="n">
-        <v>11.45947115234749</v>
+        <v>11.45947018812806</v>
       </c>
       <c r="D249" t="n">
-        <v>11.21665222972105</v>
+        <v>11.21665128593282</v>
       </c>
       <c r="E249" t="n">
-        <v>11.36547694755648</v>
+        <v>11.36547599124588</v>
       </c>
       <c r="F249" t="n">
         <v>3006300</v>
@@ -5412,16 +5412,16 @@
         <v>45008</v>
       </c>
       <c r="B250" t="n">
-        <v>11.18532180786133</v>
+        <v>11.18532085418701</v>
       </c>
       <c r="C250" t="n">
-        <v>11.47513748476884</v>
+        <v>11.47513650638449</v>
       </c>
       <c r="D250" t="n">
-        <v>11.05999619049587</v>
+        <v>11.05999524750697</v>
       </c>
       <c r="E250" t="n">
-        <v>11.39680934741524</v>
+        <v>11.39680837570923</v>
       </c>
       <c r="F250" t="n">
         <v>4422500</v>
@@ -5432,16 +5432,16 @@
         <v>45009</v>
       </c>
       <c r="B251" t="n">
-        <v>11.30281352996826</v>
+        <v>11.30281448364258</v>
       </c>
       <c r="C251" t="n">
-        <v>11.39680772964997</v>
+        <v>11.39680869125504</v>
       </c>
       <c r="D251" t="n">
-        <v>11.11482438360535</v>
+        <v>11.11482532141809</v>
       </c>
       <c r="E251" t="n">
-        <v>11.20881933028655</v>
+        <v>11.20882027603011</v>
       </c>
       <c r="F251" t="n">
         <v>3265300</v>
@@ -5512,16 +5512,16 @@
         <v>45015</v>
       </c>
       <c r="B255" t="n">
-        <v>11.40464115142822</v>
+        <v>11.40464019775391</v>
       </c>
       <c r="C255" t="n">
-        <v>11.50646764427175</v>
+        <v>11.50646668208254</v>
       </c>
       <c r="D255" t="n">
-        <v>11.12265779586299</v>
+        <v>11.12265686576857</v>
       </c>
       <c r="E255" t="n">
-        <v>11.42030647840433</v>
+        <v>11.42030552342006</v>
       </c>
       <c r="F255" t="n">
         <v>3320400</v>
@@ -5572,16 +5572,16 @@
         <v>45020</v>
       </c>
       <c r="B258" t="n">
-        <v>11.43597221374512</v>
+        <v>11.43597316741943</v>
       </c>
       <c r="C258" t="n">
-        <v>11.49863501379308</v>
+        <v>11.498635972693</v>
       </c>
       <c r="D258" t="n">
-        <v>11.24798306660174</v>
+        <v>11.24798400459917</v>
       </c>
       <c r="E258" t="n">
-        <v>11.35764334018542</v>
+        <v>11.35764428732769</v>
       </c>
       <c r="F258" t="n">
         <v>5230100</v>
@@ -5612,16 +5612,16 @@
         <v>45022</v>
       </c>
       <c r="B260" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="C260" t="n">
-        <v>11.66312619459255</v>
+        <v>11.6631252305592</v>
       </c>
       <c r="D260" t="n">
-        <v>11.47513702901113</v>
+        <v>11.4751360805163</v>
       </c>
       <c r="E260" t="n">
-        <v>11.4908031040594</v>
+        <v>11.49080215426967</v>
       </c>
       <c r="F260" t="n">
         <v>4653400</v>
@@ -5632,16 +5632,16 @@
         <v>45026</v>
       </c>
       <c r="B261" t="n">
-        <v>11.71795558929443</v>
+        <v>11.71795463562012</v>
       </c>
       <c r="C261" t="n">
-        <v>11.85111423495683</v>
+        <v>11.85111327044531</v>
       </c>
       <c r="D261" t="n">
-        <v>11.45947133524378</v>
+        <v>11.4594704026064</v>
       </c>
       <c r="E261" t="n">
-        <v>11.53779946698666</v>
+        <v>11.53779852797449</v>
       </c>
       <c r="F261" t="n">
         <v>3430500</v>
@@ -5772,16 +5772,16 @@
         <v>45035</v>
       </c>
       <c r="B268" t="n">
-        <v>12.03910160064697</v>
+        <v>12.03910255432129</v>
       </c>
       <c r="C268" t="n">
-        <v>12.06259996342652</v>
+        <v>12.06260091896225</v>
       </c>
       <c r="D268" t="n">
-        <v>11.86677853059817</v>
+        <v>11.86677947062196</v>
       </c>
       <c r="E268" t="n">
-        <v>11.96860576530885</v>
+        <v>11.96860671339886</v>
       </c>
       <c r="F268" t="n">
         <v>3098200</v>
@@ -5792,16 +5792,16 @@
         <v>45036</v>
       </c>
       <c r="B269" t="n">
-        <v>12.09393119812012</v>
+        <v>12.09393215179443</v>
       </c>
       <c r="C269" t="n">
-        <v>12.14092867003875</v>
+        <v>12.14092962741908</v>
       </c>
       <c r="D269" t="n">
-        <v>12.00777003776868</v>
+        <v>12.00777098464871</v>
       </c>
       <c r="E269" t="n">
-        <v>12.06259979917419</v>
+        <v>12.06260075037785</v>
       </c>
       <c r="F269" t="n">
         <v>4813100</v>
@@ -5832,16 +5832,16 @@
         <v>45041</v>
       </c>
       <c r="B271" t="n">
-        <v>12.06260108947754</v>
+        <v>12.06260013580322</v>
       </c>
       <c r="C271" t="n">
-        <v>12.14092996872072</v>
+        <v>12.14092900885369</v>
       </c>
       <c r="D271" t="n">
-        <v>11.96860688258545</v>
+        <v>11.96860593634236</v>
       </c>
       <c r="E271" t="n">
-        <v>12.11743160374759</v>
+        <v>12.11743064573835</v>
       </c>
       <c r="F271" t="n">
         <v>2381100</v>
@@ -5892,16 +5892,16 @@
         <v>45044</v>
       </c>
       <c r="B274" t="n">
-        <v>12.36024951934814</v>
+        <v>12.36024856567383</v>
       </c>
       <c r="C274" t="n">
-        <v>12.45424372422157</v>
+        <v>12.45424276329498</v>
       </c>
       <c r="D274" t="n">
-        <v>12.01560410147892</v>
+        <v>12.01560317439626</v>
       </c>
       <c r="E274" t="n">
-        <v>12.11743134350835</v>
+        <v>12.11743040856905</v>
       </c>
       <c r="F274" t="n">
         <v>8419400</v>
@@ -5912,16 +5912,16 @@
         <v>45048</v>
       </c>
       <c r="B275" t="n">
-        <v>12.39158153533936</v>
+        <v>12.39158058166504</v>
       </c>
       <c r="C275" t="n">
-        <v>12.65006579830664</v>
+        <v>12.650064824739</v>
       </c>
       <c r="D275" t="n">
-        <v>12.25059059453875</v>
+        <v>12.2505896517153</v>
       </c>
       <c r="E275" t="n">
-        <v>12.53257322313954</v>
+        <v>12.5325722586143</v>
       </c>
       <c r="F275" t="n">
         <v>5999300</v>
@@ -5992,16 +5992,16 @@
         <v>45054</v>
       </c>
       <c r="B279" t="n">
-        <v>12.11165904998779</v>
+        <v>12.11165809631348</v>
       </c>
       <c r="C279" t="n">
-        <v>12.58781451078781</v>
+        <v>12.58781351962092</v>
       </c>
       <c r="D279" t="n">
-        <v>12.05105773110397</v>
+        <v>12.05105678220141</v>
       </c>
       <c r="E279" t="n">
-        <v>12.54452750060035</v>
+        <v>12.54452651284189</v>
       </c>
       <c r="F279" t="n">
         <v>5826000</v>
@@ -6032,16 +6032,16 @@
         <v>45056</v>
       </c>
       <c r="B281" t="n">
-        <v>11.86925220489502</v>
+        <v>11.86925315856934</v>
       </c>
       <c r="C281" t="n">
-        <v>12.0510569757826</v>
+        <v>12.05105794406462</v>
       </c>
       <c r="D281" t="n">
-        <v>11.69610500062852</v>
+        <v>11.69610594039075</v>
       </c>
       <c r="E281" t="n">
-        <v>12.0164275349293</v>
+        <v>12.0164285004289</v>
       </c>
       <c r="F281" t="n">
         <v>5308900</v>
@@ -6052,16 +6052,16 @@
         <v>45057</v>
       </c>
       <c r="B282" t="n">
-        <v>12.05971527099609</v>
+        <v>12.05971622467041</v>
       </c>
       <c r="C282" t="n">
-        <v>12.11165902259875</v>
+        <v>12.11165998038074</v>
       </c>
       <c r="D282" t="n">
-        <v>11.7393927173429</v>
+        <v>11.73939364568632</v>
       </c>
       <c r="E282" t="n">
-        <v>11.79133646894556</v>
+        <v>11.79133740139665</v>
       </c>
       <c r="F282" t="n">
         <v>3678200</v>
@@ -6072,16 +6072,16 @@
         <v>45058</v>
       </c>
       <c r="B283" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C283" t="n">
-        <v>12.25017632493442</v>
+        <v>12.25017729158851</v>
       </c>
       <c r="D283" t="n">
-        <v>11.99911266679329</v>
+        <v>11.9991136136361</v>
       </c>
       <c r="E283" t="n">
-        <v>12.04239967522403</v>
+        <v>12.0424006254826</v>
       </c>
       <c r="F283" t="n">
         <v>3087800</v>
@@ -6112,16 +6112,16 @@
         <v>45062</v>
       </c>
       <c r="B285" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="C285" t="n">
-        <v>12.30212031805942</v>
+        <v>12.30212128603885</v>
       </c>
       <c r="D285" t="n">
-        <v>12.08568611177803</v>
+        <v>12.08568706272756</v>
       </c>
       <c r="E285" t="n">
-        <v>12.18091686531469</v>
+        <v>12.18091782375736</v>
       </c>
       <c r="F285" t="n">
         <v>2907500</v>
@@ -6232,16 +6232,16 @@
         <v>45070</v>
       </c>
       <c r="B291" t="n">
-        <v>12.25017642974854</v>
+        <v>12.25017738342285</v>
       </c>
       <c r="C291" t="n">
-        <v>12.30212100543608</v>
+        <v>12.30212196315428</v>
       </c>
       <c r="D291" t="n">
-        <v>12.18091754591915</v>
+        <v>12.18091849420168</v>
       </c>
       <c r="E291" t="n">
-        <v>12.26749156352139</v>
+        <v>12.26749251854369</v>
       </c>
       <c r="F291" t="n">
         <v>1846000</v>
@@ -6312,16 +6312,16 @@
         <v>45076</v>
       </c>
       <c r="B295" t="n">
-        <v>12.26749134063721</v>
+        <v>12.26749229431152</v>
       </c>
       <c r="C295" t="n">
-        <v>12.3800372312229</v>
+        <v>12.38003819364653</v>
       </c>
       <c r="D295" t="n">
-        <v>12.25017620717894</v>
+        <v>12.25017715950718</v>
       </c>
       <c r="E295" t="n">
-        <v>12.37137966449377</v>
+        <v>12.37138062624436</v>
       </c>
       <c r="F295" t="n">
         <v>1829100</v>
@@ -6352,16 +6352,16 @@
         <v>45078</v>
       </c>
       <c r="B297" t="n">
-        <v>12.24151992797852</v>
+        <v>12.2415189743042</v>
       </c>
       <c r="C297" t="n">
-        <v>12.30212124610704</v>
+        <v>12.30212028771158</v>
       </c>
       <c r="D297" t="n">
-        <v>12.1636034757384</v>
+        <v>12.16360252813415</v>
       </c>
       <c r="E297" t="n">
-        <v>12.26749180351488</v>
+        <v>12.26749084781722</v>
       </c>
       <c r="F297" t="n">
         <v>2308800</v>
@@ -6372,16 +6372,16 @@
         <v>45079</v>
       </c>
       <c r="B298" t="n">
-        <v>12.17226123809814</v>
+        <v>12.17226219177246</v>
       </c>
       <c r="C298" t="n">
-        <v>12.33675088664238</v>
+        <v>12.33675185320416</v>
       </c>
       <c r="D298" t="n">
-        <v>12.07702965021844</v>
+        <v>12.07703059643153</v>
       </c>
       <c r="E298" t="n">
-        <v>12.3107790106893</v>
+        <v>12.31077997521623</v>
       </c>
       <c r="F298" t="n">
         <v>5725100</v>
@@ -6392,16 +6392,16 @@
         <v>45082</v>
       </c>
       <c r="B299" t="n">
-        <v>12.0683708190918</v>
+        <v>12.06837177276611</v>
       </c>
       <c r="C299" t="n">
-        <v>12.19823183651883</v>
+        <v>12.1982328004551</v>
       </c>
       <c r="D299" t="n">
-        <v>11.97314006681674</v>
+        <v>11.97314101296568</v>
       </c>
       <c r="E299" t="n">
-        <v>12.17225996328581</v>
+        <v>12.17226092516972</v>
       </c>
       <c r="F299" t="n">
         <v>3442900</v>
@@ -6412,16 +6412,16 @@
         <v>45083</v>
       </c>
       <c r="B300" t="n">
-        <v>12.32809352874756</v>
+        <v>12.32809257507324</v>
       </c>
       <c r="C300" t="n">
-        <v>12.41466755090237</v>
+        <v>12.41466659053087</v>
       </c>
       <c r="D300" t="n">
-        <v>12.0770298552559</v>
+        <v>12.07702892100332</v>
       </c>
       <c r="E300" t="n">
-        <v>12.08568742259759</v>
+        <v>12.08568648767528</v>
       </c>
       <c r="F300" t="n">
         <v>7376500</v>
@@ -6432,16 +6432,16 @@
         <v>45084</v>
       </c>
       <c r="B301" t="n">
-        <v>12.22420501708984</v>
+        <v>12.22420406341553</v>
       </c>
       <c r="C301" t="n">
-        <v>12.46661111966148</v>
+        <v>12.46661014707579</v>
       </c>
       <c r="D301" t="n">
-        <v>12.21554744987595</v>
+        <v>12.21554649687706</v>
       </c>
       <c r="E301" t="n">
-        <v>12.3800379244157</v>
+        <v>12.38003695858405</v>
       </c>
       <c r="F301" t="n">
         <v>3154600</v>
@@ -6492,16 +6492,16 @@
         <v>45090</v>
       </c>
       <c r="B304" t="n">
-        <v>12.3107795715332</v>
+        <v>12.31077861785889</v>
       </c>
       <c r="C304" t="n">
-        <v>12.5012411047074</v>
+        <v>12.50124013627868</v>
       </c>
       <c r="D304" t="n">
-        <v>12.29346443635495</v>
+        <v>12.29346348402198</v>
       </c>
       <c r="E304" t="n">
-        <v>12.46661165998199</v>
+        <v>12.46661069423589</v>
       </c>
       <c r="F304" t="n">
         <v>1312000</v>
@@ -6532,16 +6532,16 @@
         <v>45092</v>
       </c>
       <c r="B306" t="n">
-        <v>12.4666109085083</v>
+        <v>12.46661186218262</v>
       </c>
       <c r="C306" t="n">
-        <v>12.49258360971007</v>
+        <v>12.49258456537125</v>
       </c>
       <c r="D306" t="n">
-        <v>12.36272258059435</v>
+        <v>12.36272352632139</v>
       </c>
       <c r="E306" t="n">
-        <v>12.45795416707208</v>
+        <v>12.45795512008417</v>
       </c>
       <c r="F306" t="n">
         <v>1266000</v>
@@ -6572,16 +6572,16 @@
         <v>45096</v>
       </c>
       <c r="B308" t="n">
-        <v>12.61378574371338</v>
+        <v>12.6137866973877</v>
       </c>
       <c r="C308" t="n">
-        <v>12.80424808345158</v>
+        <v>12.80424905152594</v>
       </c>
       <c r="D308" t="n">
-        <v>12.38869478834751</v>
+        <v>12.38869572500366</v>
       </c>
       <c r="E308" t="n">
-        <v>12.80424808345158</v>
+        <v>12.80424905152594</v>
       </c>
       <c r="F308" t="n">
         <v>3301400</v>
@@ -6592,16 +6592,16 @@
         <v>45097</v>
       </c>
       <c r="B309" t="n">
-        <v>12.72633171081543</v>
+        <v>12.72633266448975</v>
       </c>
       <c r="C309" t="n">
-        <v>12.89947891815102</v>
+        <v>12.89947988480048</v>
       </c>
       <c r="D309" t="n">
-        <v>12.64841526110666</v>
+        <v>12.64841620894215</v>
       </c>
       <c r="E309" t="n">
-        <v>12.69170226934831</v>
+        <v>12.6917032204276</v>
       </c>
       <c r="F309" t="n">
         <v>3568000</v>
@@ -6652,16 +6652,16 @@
         <v>45100</v>
       </c>
       <c r="B312" t="n">
-        <v>12.94276714324951</v>
+        <v>12.9427661895752</v>
       </c>
       <c r="C312" t="n">
-        <v>13.07262818018377</v>
+        <v>13.07262721694078</v>
       </c>
       <c r="D312" t="n">
-        <v>12.76096235204642</v>
+        <v>12.7609614117682</v>
       </c>
       <c r="E312" t="n">
-        <v>12.81290693194634</v>
+        <v>12.81290598784064</v>
       </c>
       <c r="F312" t="n">
         <v>2959500</v>
@@ -6672,16 +6672,16 @@
         <v>45103</v>
       </c>
       <c r="B313" t="n">
-        <v>12.71767520904541</v>
+        <v>12.71767425537109</v>
       </c>
       <c r="C313" t="n">
-        <v>13.01202589898095</v>
+        <v>13.01202492323384</v>
       </c>
       <c r="D313" t="n">
-        <v>12.66573145531036</v>
+        <v>12.66573050553121</v>
       </c>
       <c r="E313" t="n">
-        <v>12.94276701024684</v>
+        <v>12.94276603969331</v>
       </c>
       <c r="F313" t="n">
         <v>2677600</v>
@@ -6792,16 +6792,16 @@
         <v>45111</v>
       </c>
       <c r="B319" t="n">
-        <v>12.34540843963623</v>
+        <v>12.34540748596191</v>
       </c>
       <c r="C319" t="n">
-        <v>12.40600975866739</v>
+        <v>12.40600880031166</v>
       </c>
       <c r="D319" t="n">
-        <v>12.23286254312761</v>
+        <v>12.23286159814739</v>
       </c>
       <c r="E319" t="n">
-        <v>12.38869544992894</v>
+        <v>12.38869449291073</v>
       </c>
       <c r="F319" t="n">
         <v>2230100</v>
@@ -6832,16 +6832,16 @@
         <v>45113</v>
       </c>
       <c r="B321" t="n">
-        <v>12.32809352874756</v>
+        <v>12.32809257507324</v>
       </c>
       <c r="C321" t="n">
-        <v>12.48392643837378</v>
+        <v>12.48392547264458</v>
       </c>
       <c r="D321" t="n">
-        <v>12.25017707393445</v>
+        <v>12.25017612628758</v>
       </c>
       <c r="E321" t="n">
-        <v>12.43198185995469</v>
+        <v>12.4319808982438</v>
       </c>
       <c r="F321" t="n">
         <v>2081000</v>
@@ -6852,16 +6852,16 @@
         <v>45114</v>
       </c>
       <c r="B322" t="n">
-        <v>12.34540843963623</v>
+        <v>12.34540748596191</v>
       </c>
       <c r="C322" t="n">
-        <v>12.48392621206805</v>
+        <v>12.48392524769333</v>
       </c>
       <c r="D322" t="n">
-        <v>12.25883441905082</v>
+        <v>12.25883347206429</v>
       </c>
       <c r="E322" t="n">
-        <v>12.42332489303689</v>
+        <v>12.42332393334358</v>
       </c>
       <c r="F322" t="n">
         <v>2149700</v>
@@ -6872,16 +6872,16 @@
         <v>45117</v>
       </c>
       <c r="B323" t="n">
-        <v>12.38869571685791</v>
+        <v>12.38869476318359</v>
       </c>
       <c r="C323" t="n">
-        <v>12.45795460456609</v>
+        <v>12.45795364556026</v>
       </c>
       <c r="D323" t="n">
-        <v>12.31077926177845</v>
+        <v>12.31077831410209</v>
       </c>
       <c r="E323" t="n">
-        <v>12.38003814948662</v>
+        <v>12.38003719647876</v>
       </c>
       <c r="F323" t="n">
         <v>1514600</v>
@@ -6892,16 +6892,16 @@
         <v>45118</v>
       </c>
       <c r="B324" t="n">
-        <v>12.34540843963623</v>
+        <v>12.34540748596191</v>
       </c>
       <c r="C324" t="n">
-        <v>12.39735219148264</v>
+        <v>12.3973512337957</v>
       </c>
       <c r="D324" t="n">
-        <v>12.23286254312761</v>
+        <v>12.23286159814739</v>
       </c>
       <c r="E324" t="n">
-        <v>12.38869544992894</v>
+        <v>12.38869449291073</v>
       </c>
       <c r="F324" t="n">
         <v>1919200</v>
@@ -6912,16 +6912,16 @@
         <v>45119</v>
       </c>
       <c r="B325" t="n">
-        <v>12.38869571685791</v>
+        <v>12.38869476318359</v>
       </c>
       <c r="C325" t="n">
-        <v>12.45795460456609</v>
+        <v>12.45795364556026</v>
       </c>
       <c r="D325" t="n">
-        <v>12.28480655966458</v>
+        <v>12.28480561398759</v>
       </c>
       <c r="E325" t="n">
-        <v>12.37138058211533</v>
+        <v>12.37137962977392</v>
       </c>
       <c r="F325" t="n">
         <v>1842800</v>
@@ -7052,16 +7052,16 @@
         <v>45128</v>
       </c>
       <c r="B332" t="n">
-        <v>12.38869571685791</v>
+        <v>12.38869476318359</v>
       </c>
       <c r="C332" t="n">
-        <v>12.38869571685791</v>
+        <v>12.38869476318359</v>
       </c>
       <c r="D332" t="n">
-        <v>12.2242052393277</v>
+        <v>12.22420429831576</v>
       </c>
       <c r="E332" t="n">
-        <v>12.27614981792436</v>
+        <v>12.27614887291376</v>
       </c>
       <c r="F332" t="n">
         <v>2631400</v>
@@ -7072,16 +7072,16 @@
         <v>45131</v>
       </c>
       <c r="B333" t="n">
-        <v>12.34540843963623</v>
+        <v>12.34540748596191</v>
       </c>
       <c r="C333" t="n">
-        <v>12.42332489303689</v>
+        <v>12.42332393334358</v>
       </c>
       <c r="D333" t="n">
-        <v>12.31943573808198</v>
+        <v>12.31943478641403</v>
       </c>
       <c r="E333" t="n">
-        <v>12.42332489303689</v>
+        <v>12.42332393334358</v>
       </c>
       <c r="F333" t="n">
         <v>1347200</v>
@@ -7092,16 +7092,16 @@
         <v>45132</v>
       </c>
       <c r="B334" t="n">
-        <v>12.17226123809814</v>
+        <v>12.17226219177246</v>
       </c>
       <c r="C334" t="n">
-        <v>12.47526865923354</v>
+        <v>12.47526963664793</v>
       </c>
       <c r="D334" t="n">
-        <v>12.16360367090343</v>
+        <v>12.16360462389945</v>
       </c>
       <c r="E334" t="n">
-        <v>12.41466734013267</v>
+        <v>12.41466831279906</v>
       </c>
       <c r="F334" t="n">
         <v>2710400</v>
@@ -7132,16 +7132,16 @@
         <v>45134</v>
       </c>
       <c r="B336" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C336" t="n">
-        <v>12.22420445012837</v>
+        <v>12.22420541473304</v>
       </c>
       <c r="D336" t="n">
-        <v>12.03374210841168</v>
+        <v>12.03374305798708</v>
       </c>
       <c r="E336" t="n">
-        <v>12.18091744169762</v>
+        <v>12.18091840288654</v>
       </c>
       <c r="F336" t="n">
         <v>2852900</v>
@@ -7152,16 +7152,16 @@
         <v>45135</v>
       </c>
       <c r="B337" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="C337" t="n">
-        <v>12.22420387169716</v>
+        <v>12.22420483354582</v>
       </c>
       <c r="D337" t="n">
-        <v>12.05971423820094</v>
+        <v>12.0597151871069</v>
       </c>
       <c r="E337" t="n">
-        <v>12.14628742533491</v>
+        <v>12.14628838105279</v>
       </c>
       <c r="F337" t="n">
         <v>1506100</v>
@@ -7172,16 +7172,16 @@
         <v>45138</v>
       </c>
       <c r="B338" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="C338" t="n">
-        <v>12.20688956452276</v>
+        <v>12.20689052500906</v>
       </c>
       <c r="D338" t="n">
-        <v>12.10300041895243</v>
+        <v>12.10300137126433</v>
       </c>
       <c r="E338" t="n">
-        <v>12.20688956452276</v>
+        <v>12.20689052500906</v>
       </c>
       <c r="F338" t="n">
         <v>1549400</v>
@@ -7212,16 +7212,16 @@
         <v>45140</v>
       </c>
       <c r="B340" t="n">
-        <v>12.22420501708984</v>
+        <v>12.22420406341553</v>
       </c>
       <c r="C340" t="n">
-        <v>12.23286258430374</v>
+        <v>12.232861629954</v>
       </c>
       <c r="D340" t="n">
-        <v>12.12897425463018</v>
+        <v>12.12897330838532</v>
       </c>
       <c r="E340" t="n">
-        <v>12.13763182184407</v>
+        <v>12.13763087492379</v>
       </c>
       <c r="F340" t="n">
         <v>1697600</v>
@@ -7292,16 +7292,16 @@
         <v>45146</v>
       </c>
       <c r="B344" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C344" t="n">
-        <v>12.15494556689158</v>
+        <v>12.15494652603107</v>
       </c>
       <c r="D344" t="n">
-        <v>11.92985378355649</v>
+        <v>11.92985472493413</v>
       </c>
       <c r="E344" t="n">
-        <v>11.99045592561195</v>
+        <v>11.99045687177166</v>
       </c>
       <c r="F344" t="n">
         <v>2176400</v>
@@ -7352,16 +7352,16 @@
         <v>45149</v>
       </c>
       <c r="B347" t="n">
-        <v>11.92119789123535</v>
+        <v>11.92119693756104</v>
       </c>
       <c r="C347" t="n">
-        <v>11.97314164454614</v>
+        <v>11.97314068671642</v>
       </c>
       <c r="D347" t="n">
-        <v>11.83462386820927</v>
+        <v>11.83462292146072</v>
       </c>
       <c r="E347" t="n">
-        <v>11.97314164454614</v>
+        <v>11.97314068671642</v>
       </c>
       <c r="F347" t="n">
         <v>2472600</v>
@@ -7372,16 +7372,16 @@
         <v>45152</v>
       </c>
       <c r="B348" t="n">
-        <v>11.9125394821167</v>
+        <v>11.91254043579102</v>
       </c>
       <c r="C348" t="n">
-        <v>11.96448323175737</v>
+        <v>11.96448418959011</v>
       </c>
       <c r="D348" t="n">
-        <v>11.82596546520757</v>
+        <v>11.82596641195109</v>
       </c>
       <c r="E348" t="n">
-        <v>11.92119704893382</v>
+        <v>11.92119800330122</v>
       </c>
       <c r="F348" t="n">
         <v>1369900</v>
@@ -7392,16 +7392,16 @@
         <v>45153</v>
       </c>
       <c r="B349" t="n">
-        <v>11.86059474945068</v>
+        <v>11.860595703125</v>
       </c>
       <c r="C349" t="n">
-        <v>11.9991125141623</v>
+        <v>11.99911347897441</v>
       </c>
       <c r="D349" t="n">
-        <v>11.85193718274846</v>
+        <v>11.85193813572664</v>
       </c>
       <c r="E349" t="n">
-        <v>11.91253932403304</v>
+        <v>11.91254028188406</v>
       </c>
       <c r="F349" t="n">
         <v>2713800</v>
@@ -7492,16 +7492,16 @@
         <v>45160</v>
       </c>
       <c r="B354" t="n">
-        <v>11.79999446868896</v>
+        <v>11.79999351501465</v>
       </c>
       <c r="C354" t="n">
-        <v>11.86925335711897</v>
+        <v>11.86925239784715</v>
       </c>
       <c r="D354" t="n">
-        <v>11.73073558025896</v>
+        <v>11.73073463218214</v>
       </c>
       <c r="E354" t="n">
-        <v>11.79133690122745</v>
+        <v>11.79133594825283</v>
       </c>
       <c r="F354" t="n">
         <v>2231700</v>
@@ -7592,16 +7592,16 @@
         <v>45167</v>
       </c>
       <c r="B359" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="C359" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="D359" t="n">
-        <v>11.97314022543599</v>
+        <v>11.97314116752997</v>
       </c>
       <c r="E359" t="n">
-        <v>11.98179779183868</v>
+        <v>11.98179873461387</v>
       </c>
       <c r="F359" t="n">
         <v>1776800</v>
@@ -7612,16 +7612,16 @@
         <v>45168</v>
       </c>
       <c r="B360" t="n">
-        <v>12.11165904998779</v>
+        <v>12.11165809631348</v>
       </c>
       <c r="C360" t="n">
-        <v>12.19823307036272</v>
+        <v>12.19823210987155</v>
       </c>
       <c r="D360" t="n">
-        <v>12.05971529826767</v>
+        <v>12.05971434868342</v>
       </c>
       <c r="E360" t="n">
-        <v>12.17226119450266</v>
+        <v>12.17226023605652</v>
       </c>
       <c r="F360" t="n">
         <v>1998700</v>
@@ -7632,16 +7632,16 @@
         <v>45169</v>
       </c>
       <c r="B361" t="n">
-        <v>11.78267860412598</v>
+        <v>11.78267955780029</v>
       </c>
       <c r="C361" t="n">
-        <v>12.1203162835374</v>
+        <v>12.12031726453966</v>
       </c>
       <c r="D361" t="n">
-        <v>11.78267860412598</v>
+        <v>11.78267955780029</v>
       </c>
       <c r="E361" t="n">
-        <v>12.1203162835374</v>
+        <v>12.12031726453966</v>
       </c>
       <c r="F361" t="n">
         <v>3236500</v>
@@ -7652,16 +7652,16 @@
         <v>45170</v>
       </c>
       <c r="B362" t="n">
-        <v>12.04239940643311</v>
+        <v>12.04240036010742</v>
       </c>
       <c r="C362" t="n">
-        <v>12.04239940643311</v>
+        <v>12.04240036010742</v>
       </c>
       <c r="D362" t="n">
-        <v>11.89522407643217</v>
+        <v>11.89522501845123</v>
       </c>
       <c r="E362" t="n">
-        <v>11.90388164305129</v>
+        <v>11.90388258575596</v>
       </c>
       <c r="F362" t="n">
         <v>3740800</v>
@@ -7692,16 +7692,16 @@
         <v>45174</v>
       </c>
       <c r="B364" t="n">
-        <v>11.92119789123535</v>
+        <v>11.92119693756104</v>
       </c>
       <c r="C364" t="n">
-        <v>12.06837240936998</v>
+        <v>12.06837144392197</v>
       </c>
       <c r="D364" t="n">
-        <v>11.91254032380653</v>
+        <v>11.9125393708248</v>
       </c>
       <c r="E364" t="n">
-        <v>12.04240053271458</v>
+        <v>12.04239956934427</v>
       </c>
       <c r="F364" t="n">
         <v>3869600</v>
@@ -7772,16 +7772,16 @@
         <v>45181</v>
       </c>
       <c r="B368" t="n">
-        <v>12.0683708190918</v>
+        <v>12.06837177276611</v>
       </c>
       <c r="C368" t="n">
-        <v>12.15494483070982</v>
+        <v>12.15494579122544</v>
       </c>
       <c r="D368" t="n">
-        <v>11.98179763310474</v>
+        <v>11.98179857993782</v>
       </c>
       <c r="E368" t="n">
-        <v>12.03374137957078</v>
+        <v>12.03374233050859</v>
       </c>
       <c r="F368" t="n">
         <v>2215400</v>
@@ -7792,16 +7792,16 @@
         <v>45182</v>
       </c>
       <c r="B369" t="n">
-        <v>12.0683708190918</v>
+        <v>12.06837177276611</v>
       </c>
       <c r="C369" t="n">
-        <v>12.19823183651883</v>
+        <v>12.1982328004551</v>
       </c>
       <c r="D369" t="n">
-        <v>12.03374137957078</v>
+        <v>12.03374233050859</v>
       </c>
       <c r="E369" t="n">
-        <v>12.07702838537979</v>
+        <v>12.07702933973825</v>
       </c>
       <c r="F369" t="n">
         <v>1684100</v>
@@ -7812,16 +7812,16 @@
         <v>45183</v>
       </c>
       <c r="B370" t="n">
-        <v>12.21554660797119</v>
+        <v>12.21554756164551</v>
       </c>
       <c r="C370" t="n">
-        <v>12.25017604880902</v>
+        <v>12.25017700518688</v>
       </c>
       <c r="D370" t="n">
-        <v>12.09434397785428</v>
+        <v>12.09434492206624</v>
       </c>
       <c r="E370" t="n">
-        <v>12.09434397785428</v>
+        <v>12.09434492206624</v>
       </c>
       <c r="F370" t="n">
         <v>2498700</v>
@@ -7852,16 +7852,16 @@
         <v>45187</v>
       </c>
       <c r="B372" t="n">
-        <v>12.05971527099609</v>
+        <v>12.05971622467041</v>
       </c>
       <c r="C372" t="n">
-        <v>12.24152005286748</v>
+        <v>12.2415210209188</v>
       </c>
       <c r="D372" t="n">
-        <v>11.99911312661827</v>
+        <v>11.99911407550021</v>
       </c>
       <c r="E372" t="n">
-        <v>12.21554735143511</v>
+        <v>12.21554831743252</v>
       </c>
       <c r="F372" t="n">
         <v>3188500</v>
@@ -7892,16 +7892,16 @@
         <v>45189</v>
       </c>
       <c r="B374" t="n">
-        <v>12.0683708190918</v>
+        <v>12.06837177276611</v>
       </c>
       <c r="C374" t="n">
-        <v>12.14628726442182</v>
+        <v>12.1462882242533</v>
       </c>
       <c r="D374" t="n">
-        <v>11.97314006681674</v>
+        <v>11.97314101296568</v>
       </c>
       <c r="E374" t="n">
-        <v>12.08568595166779</v>
+        <v>12.08568690671039</v>
       </c>
       <c r="F374" t="n">
         <v>2998000</v>
@@ -7952,16 +7952,16 @@
         <v>45194</v>
       </c>
       <c r="B377" t="n">
-        <v>11.80865097045898</v>
+        <v>11.8086519241333</v>
       </c>
       <c r="C377" t="n">
-        <v>11.97314060922783</v>
+        <v>11.97314157618643</v>
       </c>
       <c r="D377" t="n">
-        <v>11.80865097045898</v>
+        <v>11.8086519241333</v>
       </c>
       <c r="E377" t="n">
-        <v>11.95582630149842</v>
+        <v>11.95582726705872</v>
       </c>
       <c r="F377" t="n">
         <v>3691700</v>
@@ -7972,16 +7972,16 @@
         <v>45195</v>
       </c>
       <c r="B378" t="n">
-        <v>11.83462333679199</v>
+        <v>11.83462238311768</v>
       </c>
       <c r="C378" t="n">
-        <v>12.06837186745655</v>
+        <v>12.06837089494598</v>
       </c>
       <c r="D378" t="n">
-        <v>11.78267876018263</v>
+        <v>11.78267781069418</v>
       </c>
       <c r="E378" t="n">
-        <v>11.80865146130283</v>
+        <v>11.80865050972141</v>
       </c>
       <c r="F378" t="n">
         <v>7795500</v>
@@ -8012,16 +8012,16 @@
         <v>45197</v>
       </c>
       <c r="B380" t="n">
-        <v>11.78267860412598</v>
+        <v>11.78267955780029</v>
       </c>
       <c r="C380" t="n">
-        <v>11.86059505519254</v>
+        <v>11.86059601517331</v>
       </c>
       <c r="D380" t="n">
-        <v>11.73073485383562</v>
+        <v>11.73073580330568</v>
       </c>
       <c r="E380" t="n">
-        <v>11.85193748826714</v>
+        <v>11.85193844754717</v>
       </c>
       <c r="F380" t="n">
         <v>2404900</v>
@@ -8072,16 +8072,16 @@
         <v>45202</v>
       </c>
       <c r="B383" t="n">
-        <v>11.80865097045898</v>
+        <v>11.8086519241333</v>
       </c>
       <c r="C383" t="n">
-        <v>11.91253929372841</v>
+        <v>11.91254025579282</v>
       </c>
       <c r="D383" t="n">
-        <v>11.75670639600877</v>
+        <v>11.75670734548801</v>
       </c>
       <c r="E383" t="n">
-        <v>11.8605947192782</v>
+        <v>11.86059567714752</v>
       </c>
       <c r="F383" t="n">
         <v>2809600</v>
@@ -8152,16 +8152,16 @@
         <v>45208</v>
       </c>
       <c r="B387" t="n">
-        <v>11.9125394821167</v>
+        <v>11.91254043579102</v>
       </c>
       <c r="C387" t="n">
-        <v>11.92985379011992</v>
+        <v>11.92985474518035</v>
       </c>
       <c r="D387" t="n">
-        <v>11.61818881538288</v>
+        <v>11.61818974549255</v>
       </c>
       <c r="E387" t="n">
-        <v>11.61818881538288</v>
+        <v>11.61818974549255</v>
       </c>
       <c r="F387" t="n">
         <v>4118900</v>
@@ -8172,16 +8172,16 @@
         <v>45209</v>
       </c>
       <c r="B388" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C388" t="n">
-        <v>12.16360313370393</v>
+        <v>12.16360409352659</v>
       </c>
       <c r="D388" t="n">
-        <v>11.9125394755628</v>
+        <v>11.91254041557417</v>
       </c>
       <c r="E388" t="n">
-        <v>11.92985378355649</v>
+        <v>11.92985472493413</v>
       </c>
       <c r="F388" t="n">
         <v>3643400</v>
@@ -8212,16 +8212,16 @@
         <v>45212</v>
       </c>
       <c r="B390" t="n">
-        <v>12.02508640289307</v>
+        <v>12.02508544921875</v>
       </c>
       <c r="C390" t="n">
-        <v>12.19823362589739</v>
+        <v>12.19823265849127</v>
       </c>
       <c r="D390" t="n">
-        <v>12.02508640289307</v>
+        <v>12.02508544921875</v>
       </c>
       <c r="E390" t="n">
-        <v>12.0943452920948</v>
+        <v>12.09434433292776</v>
       </c>
       <c r="F390" t="n">
         <v>4555500</v>
@@ -8292,16 +8292,16 @@
         <v>45218</v>
       </c>
       <c r="B394" t="n">
-        <v>11.67013359069824</v>
+        <v>11.67013263702393</v>
       </c>
       <c r="C394" t="n">
-        <v>11.75670761521626</v>
+        <v>11.75670665446719</v>
       </c>
       <c r="D394" t="n">
-        <v>11.62684740407032</v>
+        <v>11.62684645393332</v>
       </c>
       <c r="E394" t="n">
-        <v>11.66147684875131</v>
+        <v>11.66147589578441</v>
       </c>
       <c r="F394" t="n">
         <v>3066300</v>
@@ -8312,16 +8312,16 @@
         <v>45219</v>
       </c>
       <c r="B395" t="n">
-        <v>11.76536464691162</v>
+        <v>11.76536560058594</v>
       </c>
       <c r="C395" t="n">
-        <v>11.91253998651014</v>
+        <v>11.91254095211416</v>
       </c>
       <c r="D395" t="n">
-        <v>11.67013305915314</v>
+        <v>11.67013400510819</v>
       </c>
       <c r="E395" t="n">
-        <v>11.67013305915314</v>
+        <v>11.67013400510819</v>
       </c>
       <c r="F395" t="n">
         <v>6261200</v>
@@ -8352,16 +8352,16 @@
         <v>45223</v>
       </c>
       <c r="B397" t="n">
-        <v>11.63550281524658</v>
+        <v>11.6355037689209</v>
       </c>
       <c r="C397" t="n">
-        <v>11.81730758543626</v>
+        <v>11.81730855401174</v>
       </c>
       <c r="D397" t="n">
-        <v>11.54892962626116</v>
+        <v>11.54893057283972</v>
       </c>
       <c r="E397" t="n">
-        <v>11.80865084447942</v>
+        <v>11.80865181234537</v>
       </c>
       <c r="F397" t="n">
         <v>3637500</v>
@@ -8452,16 +8452,16 @@
         <v>45230</v>
       </c>
       <c r="B402" t="n">
-        <v>11.61818981170654</v>
+        <v>11.61818885803223</v>
       </c>
       <c r="C402" t="n">
-        <v>11.66147682387321</v>
+        <v>11.6614758666457</v>
       </c>
       <c r="D402" t="n">
-        <v>11.52295904544475</v>
+        <v>11.52295809958741</v>
       </c>
       <c r="E402" t="n">
-        <v>11.52295904544475</v>
+        <v>11.52295809958741</v>
       </c>
       <c r="F402" t="n">
         <v>3290000</v>
@@ -8512,16 +8512,16 @@
         <v>45236</v>
       </c>
       <c r="B405" t="n">
-        <v>12.02508640289307</v>
+        <v>12.02508544921875</v>
       </c>
       <c r="C405" t="n">
-        <v>12.07703015697882</v>
+        <v>12.077029199185</v>
       </c>
       <c r="D405" t="n">
-        <v>11.81730890965679</v>
+        <v>11.8173079724607</v>
       </c>
       <c r="E405" t="n">
-        <v>11.94716994613335</v>
+        <v>11.94716899863836</v>
       </c>
       <c r="F405" t="n">
         <v>2982900</v>
@@ -8552,16 +8552,16 @@
         <v>45238</v>
       </c>
       <c r="B407" t="n">
-        <v>11.81730842590332</v>
+        <v>11.817307472229</v>
       </c>
       <c r="C407" t="n">
-        <v>11.96448376583999</v>
+        <v>11.96448280028841</v>
       </c>
       <c r="D407" t="n">
-        <v>11.73073523076066</v>
+        <v>11.73073428407293</v>
       </c>
       <c r="E407" t="n">
-        <v>11.9385118898603</v>
+        <v>11.93851092640469</v>
       </c>
       <c r="F407" t="n">
         <v>5488500</v>
@@ -8592,16 +8592,16 @@
         <v>45240</v>
       </c>
       <c r="B409" t="n">
-        <v>11.78267860412598</v>
+        <v>11.78267955780029</v>
       </c>
       <c r="C409" t="n">
-        <v>11.86059505519254</v>
+        <v>11.86059601517331</v>
       </c>
       <c r="D409" t="n">
-        <v>11.69610541176504</v>
+        <v>11.69610635843224</v>
       </c>
       <c r="E409" t="n">
-        <v>11.69610541176504</v>
+        <v>11.69610635843224</v>
       </c>
       <c r="F409" t="n">
         <v>3430000</v>
@@ -8652,16 +8652,16 @@
         <v>45246</v>
       </c>
       <c r="B412" t="n">
-        <v>12.49258327484131</v>
+        <v>12.49258422851562</v>
       </c>
       <c r="C412" t="n">
-        <v>12.49258327484131</v>
+        <v>12.49258422851562</v>
       </c>
       <c r="D412" t="n">
-        <v>12.12897372407367</v>
+        <v>12.12897464999031</v>
       </c>
       <c r="E412" t="n">
-        <v>12.12897372407367</v>
+        <v>12.12897464999031</v>
       </c>
       <c r="F412" t="n">
         <v>6741500</v>
@@ -8672,16 +8672,16 @@
         <v>45247</v>
       </c>
       <c r="B413" t="n">
-        <v>12.25017642974854</v>
+        <v>12.25017738342285</v>
       </c>
       <c r="C413" t="n">
-        <v>12.48392578189597</v>
+        <v>12.48392675376763</v>
       </c>
       <c r="D413" t="n">
-        <v>12.14628810400446</v>
+        <v>12.14628904959109</v>
       </c>
       <c r="E413" t="n">
-        <v>12.48392578189597</v>
+        <v>12.48392675376763</v>
       </c>
       <c r="F413" t="n">
         <v>3124800</v>
@@ -8692,16 +8692,16 @@
         <v>45250</v>
       </c>
       <c r="B414" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C414" t="n">
-        <v>12.23286201694073</v>
+        <v>12.23286298222856</v>
       </c>
       <c r="D414" t="n">
-        <v>11.99045592561195</v>
+        <v>11.99045687177166</v>
       </c>
       <c r="E414" t="n">
-        <v>12.20689014213468</v>
+        <v>12.20689110537309</v>
       </c>
       <c r="F414" t="n">
         <v>3248400</v>
@@ -8732,16 +8732,16 @@
         <v>45252</v>
       </c>
       <c r="B416" t="n">
-        <v>12.4666109085083</v>
+        <v>12.46661186218262</v>
       </c>
       <c r="C416" t="n">
-        <v>12.94276636400384</v>
+        <v>12.94276735410323</v>
       </c>
       <c r="D416" t="n">
-        <v>12.44063903293757</v>
+        <v>12.44063998462508</v>
       </c>
       <c r="E416" t="n">
-        <v>12.81290616051917</v>
+        <v>12.81290714068447</v>
       </c>
       <c r="F416" t="n">
         <v>20875500</v>
@@ -8852,16 +8852,16 @@
         <v>45260</v>
       </c>
       <c r="B422" t="n">
-        <v>12.71767520904541</v>
+        <v>12.71767425537109</v>
       </c>
       <c r="C422" t="n">
-        <v>12.71767520904541</v>
+        <v>12.71767425537109</v>
       </c>
       <c r="D422" t="n">
-        <v>12.58781499907671</v>
+        <v>12.58781405514036</v>
       </c>
       <c r="E422" t="n">
-        <v>12.6311020109433</v>
+        <v>12.63110106376094</v>
       </c>
       <c r="F422" t="n">
         <v>4162000</v>
@@ -8892,16 +8892,16 @@
         <v>45264</v>
       </c>
       <c r="B424" t="n">
-        <v>12.89947891235352</v>
+        <v>12.89947986602783</v>
       </c>
       <c r="C424" t="n">
-        <v>12.98605292879791</v>
+        <v>12.98605388887275</v>
       </c>
       <c r="D424" t="n">
-        <v>12.86484947090196</v>
+        <v>12.86485042201608</v>
       </c>
       <c r="E424" t="n">
-        <v>12.94276592057571</v>
+        <v>12.94276687745029</v>
       </c>
       <c r="F424" t="n">
         <v>7048400</v>
@@ -8912,16 +8912,16 @@
         <v>45265</v>
       </c>
       <c r="B425" t="n">
-        <v>13.15919971466064</v>
+        <v>13.15920066833496</v>
       </c>
       <c r="C425" t="n">
-        <v>13.20248672149667</v>
+        <v>13.20248767830808</v>
       </c>
       <c r="D425" t="n">
-        <v>12.9254511987557</v>
+        <v>12.92545213548978</v>
       </c>
       <c r="E425" t="n">
-        <v>12.96008063909832</v>
+        <v>12.96008157834207</v>
       </c>
       <c r="F425" t="n">
         <v>6696500</v>
@@ -8972,16 +8972,16 @@
         <v>45268</v>
       </c>
       <c r="B428" t="n">
-        <v>12.92545223236084</v>
+        <v>12.92545127868652</v>
       </c>
       <c r="C428" t="n">
-        <v>13.15920076695787</v>
+        <v>13.15919979603697</v>
       </c>
       <c r="D428" t="n">
-        <v>12.86485008769187</v>
+        <v>12.86484913848894</v>
       </c>
       <c r="E428" t="n">
-        <v>13.15920076695787</v>
+        <v>13.15919979603697</v>
       </c>
       <c r="F428" t="n">
         <v>10990100</v>
@@ -9052,16 +9052,16 @@
         <v>45274</v>
       </c>
       <c r="B432" t="n">
-        <v>12.94470119476318</v>
+        <v>12.94470024108887</v>
       </c>
       <c r="C432" t="n">
-        <v>12.9831984112191</v>
+        <v>12.98319745470858</v>
       </c>
       <c r="D432" t="n">
-        <v>12.71371789602766</v>
+        <v>12.71371695937057</v>
       </c>
       <c r="E432" t="n">
-        <v>12.71371789602766</v>
+        <v>12.71371695937057</v>
       </c>
       <c r="F432" t="n">
         <v>5480800</v>
@@ -9092,16 +9092,16 @@
         <v>45278</v>
       </c>
       <c r="B434" t="n">
-        <v>12.8484582901001</v>
+        <v>12.84845733642578</v>
       </c>
       <c r="C434" t="n">
-        <v>13.08906611637279</v>
+        <v>13.0890651448394</v>
       </c>
       <c r="D434" t="n">
-        <v>12.8484582901001</v>
+        <v>12.84845733642578</v>
       </c>
       <c r="E434" t="n">
-        <v>12.98319808539135</v>
+        <v>12.983197121716</v>
       </c>
       <c r="F434" t="n">
         <v>3314300</v>
@@ -9112,16 +9112,16 @@
         <v>45279</v>
       </c>
       <c r="B435" t="n">
-        <v>12.86770534515381</v>
+        <v>12.86770629882812</v>
       </c>
       <c r="C435" t="n">
-        <v>12.94469976958878</v>
+        <v>12.94470072896945</v>
       </c>
       <c r="D435" t="n">
-        <v>12.79071092071883</v>
+        <v>12.7907118686868</v>
       </c>
       <c r="E435" t="n">
-        <v>12.87732987766966</v>
+        <v>12.87733083205729</v>
       </c>
       <c r="F435" t="n">
         <v>4780200</v>
@@ -9232,16 +9232,16 @@
         <v>45288</v>
       </c>
       <c r="B441" t="n">
-        <v>12.80996131896973</v>
+        <v>12.80996036529541</v>
       </c>
       <c r="C441" t="n">
-        <v>12.88695575141803</v>
+        <v>12.88695479201164</v>
       </c>
       <c r="D441" t="n">
-        <v>12.76183956922803</v>
+        <v>12.76183861913627</v>
       </c>
       <c r="E441" t="n">
-        <v>12.88695575141803</v>
+        <v>12.88695479201164</v>
       </c>
       <c r="F441" t="n">
         <v>3487000</v>
@@ -9332,16 +9332,16 @@
         <v>45299</v>
       </c>
       <c r="B446" t="n">
-        <v>13.01207160949707</v>
+        <v>13.01207065582275</v>
       </c>
       <c r="C446" t="n">
-        <v>13.09868965545936</v>
+        <v>13.09868869543668</v>
       </c>
       <c r="D446" t="n">
-        <v>12.88695543042352</v>
+        <v>12.88695448591916</v>
       </c>
       <c r="E446" t="n">
-        <v>12.9543253276762</v>
+        <v>12.95432437823419</v>
       </c>
       <c r="F446" t="n">
         <v>3738800</v>
@@ -9392,16 +9392,16 @@
         <v>45302</v>
       </c>
       <c r="B449" t="n">
-        <v>12.8484582901001</v>
+        <v>12.84845733642578</v>
       </c>
       <c r="C449" t="n">
-        <v>12.94470086990156</v>
+        <v>12.94469990908366</v>
       </c>
       <c r="D449" t="n">
-        <v>12.74259025911866</v>
+        <v>12.74258931330238</v>
       </c>
       <c r="E449" t="n">
-        <v>12.94470086990156</v>
+        <v>12.94469990908366</v>
       </c>
       <c r="F449" t="n">
         <v>4814200</v>
@@ -9412,16 +9412,16 @@
         <v>45303</v>
       </c>
       <c r="B450" t="n">
-        <v>12.77146339416504</v>
+        <v>12.77146434783936</v>
       </c>
       <c r="C450" t="n">
-        <v>12.88695503642984</v>
+        <v>12.88695599872818</v>
       </c>
       <c r="D450" t="n">
-        <v>12.74258979521435</v>
+        <v>12.74259074673261</v>
       </c>
       <c r="E450" t="n">
-        <v>12.84845782234157</v>
+        <v>12.84845878176524</v>
       </c>
       <c r="F450" t="n">
         <v>4041800</v>
@@ -9432,16 +9432,16 @@
         <v>45306</v>
       </c>
       <c r="B451" t="n">
-        <v>12.80996131896973</v>
+        <v>12.80996036529541</v>
       </c>
       <c r="C451" t="n">
-        <v>12.84845853519388</v>
+        <v>12.84845757865353</v>
       </c>
       <c r="D451" t="n">
-        <v>12.74259050219293</v>
+        <v>12.74258955353423</v>
       </c>
       <c r="E451" t="n">
-        <v>12.77146410274557</v>
+        <v>12.77146315193729</v>
       </c>
       <c r="F451" t="n">
         <v>1955800</v>
@@ -9492,16 +9492,16 @@
         <v>45309</v>
       </c>
       <c r="B454" t="n">
-        <v>12.55972862243652</v>
+        <v>12.55972766876221</v>
       </c>
       <c r="C454" t="n">
-        <v>12.77146376499286</v>
+        <v>12.77146279524125</v>
       </c>
       <c r="D454" t="n">
-        <v>12.51160687396745</v>
+        <v>12.51160592394707</v>
       </c>
       <c r="E454" t="n">
-        <v>12.76183923172984</v>
+        <v>12.76183826270904</v>
       </c>
       <c r="F454" t="n">
         <v>6534900</v>
@@ -9532,16 +9532,16 @@
         <v>45313</v>
       </c>
       <c r="B456" t="n">
-        <v>12.61747455596924</v>
+        <v>12.61747360229492</v>
       </c>
       <c r="C456" t="n">
-        <v>12.65597177291335</v>
+        <v>12.65597081632927</v>
       </c>
       <c r="D456" t="n">
-        <v>12.56935372317364</v>
+        <v>12.56935277313647</v>
       </c>
       <c r="E456" t="n">
-        <v>12.60785094011775</v>
+        <v>12.60784998717082</v>
       </c>
       <c r="F456" t="n">
         <v>4490300</v>
@@ -9572,16 +9572,16 @@
         <v>45315</v>
       </c>
       <c r="B458" t="n">
-        <v>12.79071140289307</v>
+        <v>12.79071235656738</v>
       </c>
       <c r="C458" t="n">
-        <v>12.82920861656179</v>
+        <v>12.82920957310646</v>
       </c>
       <c r="D458" t="n">
-        <v>12.64634708109684</v>
+        <v>12.64634802400737</v>
       </c>
       <c r="E458" t="n">
-        <v>12.65597069612954</v>
+        <v>12.6559716397576</v>
       </c>
       <c r="F458" t="n">
         <v>3333600</v>
@@ -9652,16 +9652,16 @@
         <v>45321</v>
       </c>
       <c r="B462" t="n">
-        <v>12.51160621643066</v>
+        <v>12.51160717010498</v>
       </c>
       <c r="C462" t="n">
-        <v>12.63672238873649</v>
+        <v>12.63672335194755</v>
       </c>
       <c r="D462" t="n">
-        <v>12.51160621643066</v>
+        <v>12.51160717010498</v>
       </c>
       <c r="E462" t="n">
-        <v>12.58860064279641</v>
+        <v>12.58860160233948</v>
       </c>
       <c r="F462" t="n">
         <v>3463200</v>
@@ -9672,16 +9672,16 @@
         <v>45322</v>
       </c>
       <c r="B463" t="n">
-        <v>12.68484497070312</v>
+        <v>12.68484401702881</v>
       </c>
       <c r="C463" t="n">
-        <v>12.79071208447197</v>
+        <v>12.79071112283833</v>
       </c>
       <c r="D463" t="n">
-        <v>12.53085610782262</v>
+        <v>12.53085516572552</v>
       </c>
       <c r="E463" t="n">
-        <v>12.57897693908826</v>
+        <v>12.57897599337333</v>
       </c>
       <c r="F463" t="n">
         <v>3755000</v>
@@ -9812,16 +9812,16 @@
         <v>45331</v>
       </c>
       <c r="B470" t="n">
-        <v>12.48273372650146</v>
+        <v>12.48273468017578</v>
       </c>
       <c r="C470" t="n">
-        <v>12.62709804867886</v>
+        <v>12.62709901338253</v>
       </c>
       <c r="D470" t="n">
-        <v>12.36724208519036</v>
+        <v>12.36724303004117</v>
       </c>
       <c r="E470" t="n">
-        <v>12.36724208519036</v>
+        <v>12.36724303004117</v>
       </c>
       <c r="F470" t="n">
         <v>4943200</v>
@@ -9852,16 +9852,16 @@
         <v>45337</v>
       </c>
       <c r="B472" t="n">
-        <v>12.50198173522949</v>
+        <v>12.50198268890381</v>
       </c>
       <c r="C472" t="n">
-        <v>12.58860069470964</v>
+        <v>12.58860165499141</v>
       </c>
       <c r="D472" t="n">
-        <v>12.41536277574934</v>
+        <v>12.4153637228162</v>
       </c>
       <c r="E472" t="n">
-        <v>12.46348452188787</v>
+        <v>12.46348547262554</v>
       </c>
       <c r="F472" t="n">
         <v>4740900</v>
@@ -9892,16 +9892,16 @@
         <v>45341</v>
       </c>
       <c r="B474" t="n">
-        <v>12.77146339416504</v>
+        <v>12.77146434783936</v>
       </c>
       <c r="C474" t="n">
-        <v>12.85808143747915</v>
+        <v>12.85808239762144</v>
       </c>
       <c r="D474" t="n">
-        <v>12.53085557665187</v>
+        <v>12.53085651235945</v>
       </c>
       <c r="E474" t="n">
-        <v>12.54047919178945</v>
+        <v>12.54048012821565</v>
       </c>
       <c r="F474" t="n">
         <v>4786000</v>
@@ -9972,16 +9972,16 @@
         <v>45345</v>
       </c>
       <c r="B478" t="n">
-        <v>12.41536235809326</v>
+        <v>12.41536331176758</v>
       </c>
       <c r="C478" t="n">
-        <v>12.55010305917923</v>
+        <v>12.55010402320352</v>
       </c>
       <c r="D478" t="n">
-        <v>12.41536235809326</v>
+        <v>12.41536331176758</v>
       </c>
       <c r="E478" t="n">
-        <v>12.52123037960578</v>
+        <v>12.52123134141225</v>
       </c>
       <c r="F478" t="n">
         <v>4574300</v>
@@ -9992,16 +9992,16 @@
         <v>45348</v>
       </c>
       <c r="B479" t="n">
-        <v>12.35761833190918</v>
+        <v>12.35761737823486</v>
       </c>
       <c r="C479" t="n">
-        <v>12.48273451401776</v>
+        <v>12.48273355068785</v>
       </c>
       <c r="D479" t="n">
-        <v>12.33836926488661</v>
+        <v>12.3383683126978</v>
       </c>
       <c r="E479" t="n">
-        <v>12.45386091348391</v>
+        <v>12.45385995238227</v>
       </c>
       <c r="F479" t="n">
         <v>6964500</v>
@@ -22149,42 +22149,42 @@
     </row>
     <row r="1087">
       <c r="A1087" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B1087" t="n">
-        <v>10.97999954223633</v>
+        <v>11.19999980926514</v>
       </c>
       <c r="C1087" t="n">
-        <v>11.27999973297119</v>
+        <v>11.21000003814697</v>
       </c>
       <c r="D1087" t="n">
-        <v>10.90999984741211</v>
+        <v>10.84000015258789</v>
       </c>
       <c r="E1087" t="n">
-        <v>11.19999980926514</v>
+        <v>11.03999996185303</v>
       </c>
       <c r="F1087" t="n">
-        <v>5442500</v>
+        <v>4621900</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B1088" t="n">
-        <v>11.2</v>
+        <v>11.28</v>
       </c>
       <c r="C1088" t="n">
-        <v>11.21</v>
+        <v>11.57</v>
       </c>
       <c r="D1088" t="n">
-        <v>10.84</v>
+        <v>11.13</v>
       </c>
       <c r="E1088" t="n">
-        <v>11.04</v>
+        <v>11.33</v>
       </c>
       <c r="F1088" t="n">
-        <v>4621900</v>
+        <v>4289500</v>
       </c>
     </row>
   </sheetData>

--- a/database/AURE3.xlsx
+++ b/database/AURE3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1088"/>
+  <dimension ref="A1:F1090"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44648</v>
       </c>
       <c r="B2" t="n">
-        <v>12.75723266601562</v>
+        <v>12.75723171234131</v>
       </c>
       <c r="C2" t="n">
-        <v>13.06838439275972</v>
+        <v>13.06838341582507</v>
       </c>
       <c r="D2" t="n">
-        <v>12.02602573724489</v>
+        <v>12.02602483823237</v>
       </c>
       <c r="E2" t="n">
-        <v>13.06838439275972</v>
+        <v>13.06838341582507</v>
       </c>
       <c r="F2" t="n">
         <v>5237900</v>
@@ -492,16 +492,16 @@
         <v>44650</v>
       </c>
       <c r="B4" t="n">
-        <v>12.38385009765625</v>
+        <v>12.38385105133057</v>
       </c>
       <c r="C4" t="n">
-        <v>13.04504841779609</v>
+        <v>13.04504942238897</v>
       </c>
       <c r="D4" t="n">
-        <v>12.30606179816537</v>
+        <v>12.30606274584925</v>
       </c>
       <c r="E4" t="n">
-        <v>12.92836671040398</v>
+        <v>12.92836770601126</v>
       </c>
       <c r="F4" t="n">
         <v>4408600</v>
@@ -512,16 +512,16 @@
         <v>44651</v>
       </c>
       <c r="B5" t="n">
-        <v>12.4383020401001</v>
+        <v>12.43830108642578</v>
       </c>
       <c r="C5" t="n">
-        <v>12.82724207193696</v>
+        <v>12.82724108844168</v>
       </c>
       <c r="D5" t="n">
-        <v>12.05714098694259</v>
+        <v>12.05714006249281</v>
       </c>
       <c r="E5" t="n">
-        <v>12.41496584590627</v>
+        <v>12.4149648940212</v>
       </c>
       <c r="F5" t="n">
         <v>3876100</v>
@@ -572,16 +572,16 @@
         <v>44656</v>
       </c>
       <c r="B8" t="n">
-        <v>12.15826606750488</v>
+        <v>12.15826511383057</v>
       </c>
       <c r="C8" t="n">
-        <v>12.50053298552928</v>
+        <v>12.50053200500811</v>
       </c>
       <c r="D8" t="n">
-        <v>12.05714156535479</v>
+        <v>12.05714061961251</v>
       </c>
       <c r="E8" t="n">
-        <v>12.37607228806586</v>
+        <v>12.37607131730719</v>
       </c>
       <c r="F8" t="n">
         <v>3624900</v>
@@ -712,16 +712,16 @@
         <v>44665</v>
       </c>
       <c r="B15" t="n">
-        <v>12.11159133911133</v>
+        <v>12.11159229278564</v>
       </c>
       <c r="C15" t="n">
-        <v>12.36829167926575</v>
+        <v>12.36829265315281</v>
       </c>
       <c r="D15" t="n">
-        <v>12.0493609985796</v>
+        <v>12.04936194735386</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08047616884546</v>
+        <v>12.08047712006975</v>
       </c>
       <c r="F15" t="n">
         <v>2077400</v>
@@ -732,16 +732,16 @@
         <v>44669</v>
       </c>
       <c r="B16" t="n">
-        <v>12.45386028289795</v>
+        <v>12.45386123657227</v>
       </c>
       <c r="C16" t="n">
-        <v>12.45386028289795</v>
+        <v>12.45386123657227</v>
       </c>
       <c r="D16" t="n">
-        <v>11.92490159008608</v>
+        <v>11.92490250325453</v>
       </c>
       <c r="E16" t="n">
-        <v>12.10381439459067</v>
+        <v>12.10381532145966</v>
       </c>
       <c r="F16" t="n">
         <v>3931100</v>
@@ -812,16 +812,16 @@
         <v>44676</v>
       </c>
       <c r="B20" t="n">
-        <v>12.39163017272949</v>
+        <v>12.39162921905518</v>
       </c>
       <c r="C20" t="n">
-        <v>12.39163017272949</v>
+        <v>12.39162921905518</v>
       </c>
       <c r="D20" t="n">
-        <v>11.90156562298855</v>
+        <v>11.90156470703017</v>
       </c>
       <c r="E20" t="n">
-        <v>12.11937184225865</v>
+        <v>12.11937090953766</v>
       </c>
       <c r="F20" t="n">
         <v>2683100</v>
@@ -832,16 +832,16 @@
         <v>44677</v>
       </c>
       <c r="B21" t="n">
-        <v>11.95601654052734</v>
+        <v>11.95601749420166</v>
       </c>
       <c r="C21" t="n">
-        <v>12.4383020930363</v>
+        <v>12.43830308518023</v>
       </c>
       <c r="D21" t="n">
-        <v>11.86267102151054</v>
+        <v>11.86267196773913</v>
       </c>
       <c r="E21" t="n">
-        <v>12.32939935843881</v>
+        <v>12.32940034189609</v>
       </c>
       <c r="F21" t="n">
         <v>2627000</v>
@@ -912,16 +912,16 @@
         <v>44683</v>
       </c>
       <c r="B25" t="n">
-        <v>11.17035675048828</v>
+        <v>11.1703577041626</v>
       </c>
       <c r="C25" t="n">
-        <v>11.47373022346064</v>
+        <v>11.47373120303561</v>
       </c>
       <c r="D25" t="n">
-        <v>10.96032953215679</v>
+        <v>10.96033046789994</v>
       </c>
       <c r="E25" t="n">
-        <v>11.4270570961402</v>
+        <v>11.42705807173043</v>
       </c>
       <c r="F25" t="n">
         <v>2883200</v>
@@ -932,16 +932,16 @@
         <v>44684</v>
       </c>
       <c r="B26" t="n">
-        <v>11.27148151397705</v>
+        <v>11.27148056030273</v>
       </c>
       <c r="C26" t="n">
-        <v>11.35704879249248</v>
+        <v>11.35704783157836</v>
       </c>
       <c r="D26" t="n">
-        <v>11.01478116211917</v>
+        <v>11.01478023016414</v>
       </c>
       <c r="E26" t="n">
-        <v>11.15479980562136</v>
+        <v>11.15479886181943</v>
       </c>
       <c r="F26" t="n">
         <v>1672900</v>
@@ -992,16 +992,16 @@
         <v>44687</v>
       </c>
       <c r="B29" t="n">
-        <v>11.12265777587891</v>
+        <v>11.12265872955322</v>
       </c>
       <c r="C29" t="n">
-        <v>11.31064618125162</v>
+        <v>11.31064715104436</v>
       </c>
       <c r="D29" t="n">
-        <v>11.05216193711426</v>
+        <v>11.05216288474415</v>
       </c>
       <c r="E29" t="n">
-        <v>11.28714781732991</v>
+        <v>11.28714878510787</v>
       </c>
       <c r="F29" t="n">
         <v>2813300</v>
@@ -1012,16 +1012,16 @@
         <v>44690</v>
       </c>
       <c r="B30" t="n">
-        <v>11.07566165924072</v>
+        <v>11.07566070556641</v>
       </c>
       <c r="C30" t="n">
-        <v>11.13049142708364</v>
+        <v>11.13049046868818</v>
       </c>
       <c r="D30" t="n">
-        <v>10.80934436343302</v>
+        <v>10.80934343269006</v>
       </c>
       <c r="E30" t="n">
-        <v>10.99733277917979</v>
+        <v>10.99733183225001</v>
       </c>
       <c r="F30" t="n">
         <v>1545300</v>
@@ -1032,16 +1032,16 @@
         <v>44691</v>
       </c>
       <c r="B31" t="n">
-        <v>11.12265777587891</v>
+        <v>11.12265872955322</v>
       </c>
       <c r="C31" t="n">
-        <v>11.25581641643446</v>
+        <v>11.25581738152601</v>
       </c>
       <c r="D31" t="n">
-        <v>10.95033469745416</v>
+        <v>10.95033563635322</v>
       </c>
       <c r="E31" t="n">
-        <v>11.11482473890516</v>
+        <v>11.11482569190786</v>
       </c>
       <c r="F31" t="n">
         <v>2338900</v>
@@ -1072,16 +1072,16 @@
         <v>44693</v>
       </c>
       <c r="B33" t="n">
-        <v>11.1539888381958</v>
+        <v>11.15398979187012</v>
       </c>
       <c r="C33" t="n">
-        <v>11.27931443797336</v>
+        <v>11.27931540236311</v>
       </c>
       <c r="D33" t="n">
-        <v>10.85634016522435</v>
+        <v>10.85634109344948</v>
       </c>
       <c r="E33" t="n">
-        <v>10.99733183847385</v>
+        <v>10.99733277875388</v>
       </c>
       <c r="F33" t="n">
         <v>1884700</v>
@@ -1112,16 +1112,16 @@
         <v>44697</v>
       </c>
       <c r="B35" t="n">
-        <v>11.27931499481201</v>
+        <v>11.27931594848633</v>
       </c>
       <c r="C35" t="n">
-        <v>11.41247363789934</v>
+        <v>11.41247460283231</v>
       </c>
       <c r="D35" t="n">
-        <v>11.11482495023352</v>
+        <v>11.11482589000009</v>
       </c>
       <c r="E35" t="n">
-        <v>11.17748850021538</v>
+        <v>11.1774894452802</v>
       </c>
       <c r="F35" t="n">
         <v>2419100</v>
@@ -1152,16 +1152,16 @@
         <v>44699</v>
       </c>
       <c r="B37" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C37" t="n">
-        <v>11.59262882548476</v>
+        <v>11.5926298208571</v>
       </c>
       <c r="D37" t="n">
-        <v>11.03649593344125</v>
+        <v>11.03649688106261</v>
       </c>
       <c r="E37" t="n">
-        <v>11.51429995454926</v>
+        <v>11.51430094319608</v>
       </c>
       <c r="F37" t="n">
         <v>1959900</v>
@@ -1192,16 +1192,16 @@
         <v>44701</v>
       </c>
       <c r="B39" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C39" t="n">
-        <v>11.34197688669085</v>
+        <v>11.34197786054158</v>
       </c>
       <c r="D39" t="n">
-        <v>10.86417286558284</v>
+        <v>10.86417379840811</v>
       </c>
       <c r="E39" t="n">
-        <v>11.34197688669085</v>
+        <v>11.34197786054158</v>
       </c>
       <c r="F39" t="n">
         <v>1777400</v>
@@ -1272,16 +1272,16 @@
         <v>44707</v>
       </c>
       <c r="B43" t="n">
-        <v>11.25581645965576</v>
+        <v>11.25581550598145</v>
       </c>
       <c r="C43" t="n">
-        <v>11.44380486575034</v>
+        <v>11.44380389614828</v>
       </c>
       <c r="D43" t="n">
-        <v>11.20881973163188</v>
+        <v>11.20881878193947</v>
       </c>
       <c r="E43" t="n">
-        <v>11.33414533569493</v>
+        <v>11.33414437538402</v>
       </c>
       <c r="F43" t="n">
         <v>1248800</v>
@@ -1312,16 +1312,16 @@
         <v>44711</v>
       </c>
       <c r="B45" t="n">
-        <v>11.09915924072266</v>
+        <v>11.09916019439697</v>
       </c>
       <c r="C45" t="n">
-        <v>11.27148231648886</v>
+        <v>11.27148328496971</v>
       </c>
       <c r="D45" t="n">
-        <v>11.0286634030456</v>
+        <v>11.02866435066269</v>
       </c>
       <c r="E45" t="n">
-        <v>11.15398900469392</v>
+        <v>11.15398996307938</v>
       </c>
       <c r="F45" t="n">
         <v>1940200</v>
@@ -1332,16 +1332,16 @@
         <v>44712</v>
       </c>
       <c r="B46" t="n">
-        <v>10.93466949462891</v>
+        <v>10.93466854095459</v>
       </c>
       <c r="C46" t="n">
-        <v>11.20881981582572</v>
+        <v>11.2088188382412</v>
       </c>
       <c r="D46" t="n">
-        <v>10.82500921675028</v>
+        <v>10.82500827264005</v>
       </c>
       <c r="E46" t="n">
-        <v>11.16965537751195</v>
+        <v>11.16965440334319</v>
       </c>
       <c r="F46" t="n">
         <v>9431500</v>
@@ -1372,16 +1372,16 @@
         <v>44714</v>
       </c>
       <c r="B48" t="n">
-        <v>10.86417293548584</v>
+        <v>10.86417388916016</v>
       </c>
       <c r="C48" t="n">
-        <v>10.98949853218943</v>
+        <v>10.98949949686503</v>
       </c>
       <c r="D48" t="n">
-        <v>10.68401757697429</v>
+        <v>10.68401851483428</v>
       </c>
       <c r="E48" t="n">
-        <v>10.75451266487045</v>
+        <v>10.75451360891862</v>
       </c>
       <c r="F48" t="n">
         <v>3275400</v>
@@ -1412,16 +1412,16 @@
         <v>44718</v>
       </c>
       <c r="B50" t="n">
-        <v>10.61352252960205</v>
+        <v>10.61352157592773</v>
       </c>
       <c r="C50" t="n">
-        <v>10.91117121735836</v>
+        <v>10.91117023693893</v>
       </c>
       <c r="D50" t="n">
-        <v>10.4568655220986</v>
+        <v>10.45686458250065</v>
       </c>
       <c r="E50" t="n">
-        <v>10.8171770128563</v>
+        <v>10.81717604088268</v>
       </c>
       <c r="F50" t="n">
         <v>3175000</v>
@@ -1452,16 +1452,16 @@
         <v>44720</v>
       </c>
       <c r="B52" t="n">
-        <v>11.12265777587891</v>
+        <v>11.12265872955322</v>
       </c>
       <c r="C52" t="n">
-        <v>11.19315361464355</v>
+        <v>11.19315457436229</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73884792815973</v>
+        <v>10.73884884892558</v>
       </c>
       <c r="E52" t="n">
-        <v>10.78584540300267</v>
+        <v>10.78584632779816</v>
       </c>
       <c r="F52" t="n">
         <v>2847500</v>
@@ -1552,16 +1552,16 @@
         <v>44727</v>
       </c>
       <c r="B57" t="n">
-        <v>10.84067440032959</v>
+        <v>10.84067535400391</v>
       </c>
       <c r="C57" t="n">
-        <v>10.84850743674878</v>
+        <v>10.84850839111218</v>
       </c>
       <c r="D57" t="n">
-        <v>10.44119850694474</v>
+        <v>10.44119942547642</v>
       </c>
       <c r="E57" t="n">
-        <v>10.55085877581493</v>
+        <v>10.55085970399363</v>
       </c>
       <c r="F57" t="n">
         <v>3153700</v>
@@ -1592,16 +1592,16 @@
         <v>44732</v>
       </c>
       <c r="B59" t="n">
-        <v>10.59785652160645</v>
+        <v>10.59785747528076</v>
       </c>
       <c r="C59" t="n">
-        <v>10.69968376387016</v>
+        <v>10.69968472670765</v>
       </c>
       <c r="D59" t="n">
-        <v>10.37070367255648</v>
+        <v>10.37070460578988</v>
       </c>
       <c r="E59" t="n">
-        <v>10.47253091482019</v>
+        <v>10.47253185721677</v>
       </c>
       <c r="F59" t="n">
         <v>1649800</v>
@@ -1632,16 +1632,16 @@
         <v>44734</v>
       </c>
       <c r="B61" t="n">
-        <v>10.73884868621826</v>
+        <v>10.73884773254395</v>
       </c>
       <c r="C61" t="n">
-        <v>10.8328428955397</v>
+        <v>10.83284193351813</v>
       </c>
       <c r="D61" t="n">
-        <v>10.43336694567391</v>
+        <v>10.43336601912821</v>
       </c>
       <c r="E61" t="n">
-        <v>10.53519419252203</v>
+        <v>10.53519325693346</v>
       </c>
       <c r="F61" t="n">
         <v>1196200</v>
@@ -1712,16 +1712,16 @@
         <v>44740</v>
       </c>
       <c r="B65" t="n">
-        <v>10.61352252960205</v>
+        <v>10.61352157592773</v>
       </c>
       <c r="C65" t="n">
-        <v>10.86417374160756</v>
+        <v>10.86417276541107</v>
       </c>
       <c r="D65" t="n">
-        <v>10.47253084934918</v>
+        <v>10.47252990834362</v>
       </c>
       <c r="E65" t="n">
-        <v>10.5273606152255</v>
+        <v>10.52735966929324</v>
       </c>
       <c r="F65" t="n">
         <v>5362200</v>
@@ -1732,16 +1732,16 @@
         <v>44741</v>
       </c>
       <c r="B66" t="n">
-        <v>10.6840181350708</v>
+        <v>10.68401718139648</v>
       </c>
       <c r="C66" t="n">
-        <v>10.6840181350708</v>
+        <v>10.68401718139648</v>
       </c>
       <c r="D66" t="n">
-        <v>10.53519342096158</v>
+        <v>10.53519248057162</v>
       </c>
       <c r="E66" t="n">
-        <v>10.62918762339921</v>
+        <v>10.62918667461916</v>
       </c>
       <c r="F66" t="n">
         <v>1613700</v>
@@ -1772,16 +1772,16 @@
         <v>44743</v>
       </c>
       <c r="B68" t="n">
-        <v>10.6840181350708</v>
+        <v>10.68401718139648</v>
       </c>
       <c r="C68" t="n">
-        <v>10.84067513913352</v>
+        <v>10.84067417147572</v>
       </c>
       <c r="D68" t="n">
-        <v>10.54302645791459</v>
+        <v>10.54302551682544</v>
       </c>
       <c r="E68" t="n">
-        <v>10.72318182583684</v>
+        <v>10.72318086866671</v>
       </c>
       <c r="F68" t="n">
         <v>2696600</v>
@@ -1792,16 +1792,16 @@
         <v>44746</v>
       </c>
       <c r="B69" t="n">
-        <v>10.65268707275391</v>
+        <v>10.65268611907959</v>
       </c>
       <c r="C69" t="n">
-        <v>10.7858457171883</v>
+        <v>10.78584475159305</v>
       </c>
       <c r="D69" t="n">
-        <v>10.52736071852189</v>
+        <v>10.52735977606733</v>
       </c>
       <c r="E69" t="n">
-        <v>10.68401847456203</v>
+        <v>10.68401751808279</v>
       </c>
       <c r="F69" t="n">
         <v>1437100</v>
@@ -1872,16 +1872,16 @@
         <v>44750</v>
       </c>
       <c r="B73" t="n">
-        <v>11.1539888381958</v>
+        <v>11.15398979187012</v>
       </c>
       <c r="C73" t="n">
-        <v>11.31064583791775</v>
+        <v>11.31064680498636</v>
       </c>
       <c r="D73" t="n">
-        <v>11.00516487520982</v>
+        <v>11.00516581615958</v>
       </c>
       <c r="E73" t="n">
-        <v>11.00516487520982</v>
+        <v>11.00516581615958</v>
       </c>
       <c r="F73" t="n">
         <v>1922000</v>
@@ -1892,16 +1892,16 @@
         <v>44753</v>
       </c>
       <c r="B74" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C74" t="n">
-        <v>11.18531989181933</v>
+        <v>11.18532085221909</v>
       </c>
       <c r="D74" t="n">
-        <v>10.83284146660853</v>
+        <v>10.83284239674361</v>
       </c>
       <c r="E74" t="n">
-        <v>11.05999429592211</v>
+        <v>11.0599952455611</v>
       </c>
       <c r="F74" t="n">
         <v>1881000</v>
@@ -1912,16 +1912,16 @@
         <v>44754</v>
       </c>
       <c r="B75" t="n">
-        <v>11.14615726470947</v>
+        <v>11.14615535736084</v>
       </c>
       <c r="C75" t="n">
-        <v>11.22448614835309</v>
+        <v>11.22448422760069</v>
       </c>
       <c r="D75" t="n">
-        <v>10.99733328218612</v>
+        <v>10.99733140030449</v>
       </c>
       <c r="E75" t="n">
-        <v>11.10699356988726</v>
+        <v>11.10699166924038</v>
       </c>
       <c r="F75" t="n">
         <v>1673000</v>
@@ -1972,16 +1972,16 @@
         <v>44757</v>
       </c>
       <c r="B78" t="n">
-        <v>10.80934429168701</v>
+        <v>10.80934238433838</v>
       </c>
       <c r="C78" t="n">
-        <v>10.98166737847755</v>
+        <v>10.98166544072187</v>
       </c>
       <c r="D78" t="n">
-        <v>10.60568980247997</v>
+        <v>10.60568793106692</v>
       </c>
       <c r="E78" t="n">
-        <v>10.97383434112354</v>
+        <v>10.97383240475003</v>
       </c>
       <c r="F78" t="n">
         <v>2342600</v>
@@ -2012,16 +2012,16 @@
         <v>44761</v>
       </c>
       <c r="B80" t="n">
-        <v>11.0913257598877</v>
+        <v>11.09132671356201</v>
       </c>
       <c r="C80" t="n">
-        <v>11.0913257598877</v>
+        <v>11.09132671356201</v>
       </c>
       <c r="D80" t="n">
-        <v>10.78584480484809</v>
+        <v>10.78584573225599</v>
       </c>
       <c r="E80" t="n">
-        <v>10.87200596578243</v>
+        <v>10.87200690059879</v>
       </c>
       <c r="F80" t="n">
         <v>2890800</v>
@@ -2032,16 +2032,16 @@
         <v>44762</v>
       </c>
       <c r="B81" t="n">
-        <v>11.27931499481201</v>
+        <v>11.27931594848633</v>
       </c>
       <c r="C81" t="n">
-        <v>11.35764387203968</v>
+        <v>11.35764483233677</v>
       </c>
       <c r="D81" t="n">
-        <v>11.0521621472512</v>
+        <v>11.05216308171958</v>
       </c>
       <c r="E81" t="n">
-        <v>11.08349354874236</v>
+        <v>11.08349448585983</v>
       </c>
       <c r="F81" t="n">
         <v>2285400</v>
@@ -2052,16 +2052,16 @@
         <v>44763</v>
       </c>
       <c r="B82" t="n">
-        <v>11.24798202514648</v>
+        <v>11.24798393249512</v>
       </c>
       <c r="C82" t="n">
-        <v>11.27931342226948</v>
+        <v>11.27931533493105</v>
       </c>
       <c r="D82" t="n">
-        <v>11.05999364240853</v>
+        <v>11.0599955178795</v>
       </c>
       <c r="E82" t="n">
-        <v>11.2244836640541</v>
+        <v>11.22448556741805</v>
       </c>
       <c r="F82" t="n">
         <v>1092700</v>
@@ -2112,16 +2112,16 @@
         <v>44768</v>
       </c>
       <c r="B85" t="n">
-        <v>11.27148246765137</v>
+        <v>11.27148151397705</v>
       </c>
       <c r="C85" t="n">
-        <v>11.38114199706455</v>
+        <v>11.38114103411199</v>
       </c>
       <c r="D85" t="n">
-        <v>11.16965522819662</v>
+        <v>11.16965428313785</v>
       </c>
       <c r="E85" t="n">
-        <v>11.19315359207094</v>
+        <v>11.19315264502399</v>
       </c>
       <c r="F85" t="n">
         <v>1661400</v>
@@ -2132,16 +2132,16 @@
         <v>44769</v>
       </c>
       <c r="B86" t="n">
-        <v>11.24015140533447</v>
+        <v>11.24015045166016</v>
       </c>
       <c r="C86" t="n">
-        <v>11.49080261954139</v>
+        <v>11.49080164460048</v>
       </c>
       <c r="D86" t="n">
-        <v>11.15398949020119</v>
+        <v>11.15398854383731</v>
       </c>
       <c r="E86" t="n">
-        <v>11.2871481344985</v>
+        <v>11.28714717683673</v>
       </c>
       <c r="F86" t="n">
         <v>3096400</v>
@@ -2212,16 +2212,16 @@
         <v>44775</v>
       </c>
       <c r="B90" t="n">
-        <v>10.86417293548584</v>
+        <v>10.86417388916016</v>
       </c>
       <c r="C90" t="n">
-        <v>11.06782740362892</v>
+        <v>11.06782837518035</v>
       </c>
       <c r="D90" t="n">
-        <v>10.72318126569455</v>
+        <v>10.7231822069924</v>
       </c>
       <c r="E90" t="n">
-        <v>10.93466877038148</v>
+        <v>10.93466973024404</v>
       </c>
       <c r="F90" t="n">
         <v>2371400</v>
@@ -2312,16 +2312,16 @@
         <v>44782</v>
       </c>
       <c r="B95" t="n">
-        <v>10.92683696746826</v>
+        <v>10.92683601379395</v>
       </c>
       <c r="C95" t="n">
-        <v>11.0599956157492</v>
+        <v>11.05999465045304</v>
       </c>
       <c r="D95" t="n">
-        <v>10.67618574576276</v>
+        <v>10.67618481396482</v>
       </c>
       <c r="E95" t="n">
-        <v>10.98166748246601</v>
+        <v>10.98166652400619</v>
       </c>
       <c r="F95" t="n">
         <v>1743500</v>
@@ -2332,16 +2332,16 @@
         <v>44783</v>
       </c>
       <c r="B96" t="n">
-        <v>11.05216217041016</v>
+        <v>11.05216121673584</v>
       </c>
       <c r="C96" t="n">
-        <v>11.16965548649786</v>
+        <v>11.16965452268523</v>
       </c>
       <c r="D96" t="n">
-        <v>10.88767212548699</v>
+        <v>10.88767118600627</v>
       </c>
       <c r="E96" t="n">
-        <v>10.9268365641829</v>
+        <v>10.92683562132274</v>
       </c>
       <c r="F96" t="n">
         <v>2933600</v>
@@ -2352,16 +2352,16 @@
         <v>44784</v>
       </c>
       <c r="B97" t="n">
-        <v>10.89550495147705</v>
+        <v>10.89550399780273</v>
       </c>
       <c r="C97" t="n">
-        <v>11.10699246813669</v>
+        <v>11.10699149595105</v>
       </c>
       <c r="D97" t="n">
-        <v>10.83284214957779</v>
+        <v>10.8328412013883</v>
       </c>
       <c r="E97" t="n">
-        <v>11.05999499321249</v>
+        <v>11.0599940251405</v>
       </c>
       <c r="F97" t="n">
         <v>1665400</v>
@@ -2432,16 +2432,16 @@
         <v>44790</v>
       </c>
       <c r="B101" t="n">
-        <v>11.24015140533447</v>
+        <v>11.24015045166016</v>
       </c>
       <c r="C101" t="n">
-        <v>11.25581673272263</v>
+        <v>11.25581577771919</v>
       </c>
       <c r="D101" t="n">
-        <v>10.91117131318813</v>
+        <v>10.91117038742624</v>
       </c>
       <c r="E101" t="n">
-        <v>10.98949944412802</v>
+        <v>10.98949851172035</v>
       </c>
       <c r="F101" t="n">
         <v>4396400</v>
@@ -2532,16 +2532,16 @@
         <v>44797</v>
       </c>
       <c r="B106" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C106" t="n">
-        <v>11.39680739514549</v>
+        <v>11.3968083737041</v>
       </c>
       <c r="D106" t="n">
-        <v>11.09915873138986</v>
+        <v>11.09915968439161</v>
       </c>
       <c r="E106" t="n">
-        <v>11.22448432728707</v>
+        <v>11.2244852910496</v>
       </c>
       <c r="F106" t="n">
         <v>2116800</v>
@@ -2572,16 +2572,16 @@
         <v>44799</v>
       </c>
       <c r="B108" t="n">
-        <v>11.05216217041016</v>
+        <v>11.05216121673584</v>
       </c>
       <c r="C108" t="n">
-        <v>11.17748852363695</v>
+        <v>11.17748755914842</v>
       </c>
       <c r="D108" t="n">
-        <v>10.95816796573971</v>
+        <v>10.95816702017601</v>
       </c>
       <c r="E108" t="n">
-        <v>11.05216217041016</v>
+        <v>11.05216121673584</v>
       </c>
       <c r="F108" t="n">
         <v>1356300</v>
@@ -2632,16 +2632,16 @@
         <v>44804</v>
       </c>
       <c r="B111" t="n">
-        <v>12.03910255432129</v>
+        <v>12.03910160064697</v>
       </c>
       <c r="C111" t="n">
-        <v>12.07826699338926</v>
+        <v>12.07826603661254</v>
       </c>
       <c r="D111" t="n">
-        <v>10.96600110705643</v>
+        <v>10.96600023838756</v>
       </c>
       <c r="E111" t="n">
-        <v>11.02083087355185</v>
+        <v>11.02083000053966</v>
       </c>
       <c r="F111" t="n">
         <v>16560000</v>
@@ -2652,16 +2652,16 @@
         <v>44805</v>
       </c>
       <c r="B112" t="n">
-        <v>11.65529155731201</v>
+        <v>11.65529251098633</v>
       </c>
       <c r="C112" t="n">
-        <v>12.15659468505643</v>
+        <v>12.15659567974902</v>
       </c>
       <c r="D112" t="n">
-        <v>11.42030569283808</v>
+        <v>11.42030662728508</v>
       </c>
       <c r="E112" t="n">
-        <v>12.14092861215841</v>
+        <v>12.14092960556915</v>
       </c>
       <c r="F112" t="n">
         <v>4716400</v>
@@ -2692,16 +2692,16 @@
         <v>44809</v>
       </c>
       <c r="B114" t="n">
-        <v>11.85894775390625</v>
+        <v>11.85894584655762</v>
       </c>
       <c r="C114" t="n">
-        <v>11.92161056064555</v>
+        <v>11.92160864321847</v>
       </c>
       <c r="D114" t="n">
-        <v>11.60829577994947</v>
+        <v>11.60829391291476</v>
       </c>
       <c r="E114" t="n">
-        <v>11.7649535437973</v>
+        <v>11.76495165156634</v>
       </c>
       <c r="F114" t="n">
         <v>1899700</v>
@@ -2712,16 +2712,16 @@
         <v>44810</v>
       </c>
       <c r="B115" t="n">
-        <v>11.58479595184326</v>
+        <v>11.58479785919189</v>
       </c>
       <c r="C115" t="n">
-        <v>11.90594298259424</v>
+        <v>11.90594494281729</v>
       </c>
       <c r="D115" t="n">
-        <v>11.49863479020259</v>
+        <v>11.49863668336545</v>
       </c>
       <c r="E115" t="n">
-        <v>11.89810994599068</v>
+        <v>11.89811190492408</v>
       </c>
       <c r="F115" t="n">
         <v>1316500</v>
@@ -2732,16 +2732,16 @@
         <v>44812</v>
       </c>
       <c r="B116" t="n">
-        <v>11.43597316741943</v>
+        <v>11.43597221374512</v>
       </c>
       <c r="C116" t="n">
-        <v>11.63962691105875</v>
+        <v>11.63962594040124</v>
       </c>
       <c r="D116" t="n">
-        <v>11.37331036214587</v>
+        <v>11.37330941369716</v>
       </c>
       <c r="E116" t="n">
-        <v>11.62396158324014</v>
+        <v>11.623960613889</v>
       </c>
       <c r="F116" t="n">
         <v>2598100</v>
@@ -2752,16 +2752,16 @@
         <v>44813</v>
       </c>
       <c r="B117" t="n">
-        <v>11.31847953796387</v>
+        <v>11.31847858428955</v>
       </c>
       <c r="C117" t="n">
-        <v>11.51430098584213</v>
+        <v>11.51430001566826</v>
       </c>
       <c r="D117" t="n">
-        <v>11.16965556625618</v>
+        <v>11.1696546251215</v>
       </c>
       <c r="E117" t="n">
-        <v>11.51430098584213</v>
+        <v>11.51430001566826</v>
       </c>
       <c r="F117" t="n">
         <v>2426300</v>
@@ -2772,16 +2772,16 @@
         <v>44816</v>
       </c>
       <c r="B118" t="n">
-        <v>11.41247367858887</v>
+        <v>11.41247272491455</v>
       </c>
       <c r="C118" t="n">
-        <v>11.64745956411016</v>
+        <v>11.64745859079944</v>
       </c>
       <c r="D118" t="n">
-        <v>11.35764391253373</v>
+        <v>11.35764296344122</v>
       </c>
       <c r="E118" t="n">
-        <v>11.3968083512872</v>
+        <v>11.39680739892195</v>
       </c>
       <c r="F118" t="n">
         <v>2097200</v>
@@ -2792,16 +2792,16 @@
         <v>44817</v>
       </c>
       <c r="B119" t="n">
-        <v>11.24015140533447</v>
+        <v>11.24015045166016</v>
       </c>
       <c r="C119" t="n">
-        <v>11.43597285318351</v>
+        <v>11.43597188289466</v>
       </c>
       <c r="D119" t="n">
-        <v>11.16965556458889</v>
+        <v>11.16965461689582</v>
       </c>
       <c r="E119" t="n">
-        <v>11.3028142088862</v>
+        <v>11.30281324989524</v>
       </c>
       <c r="F119" t="n">
         <v>1768400</v>
@@ -2852,16 +2852,16 @@
         <v>44820</v>
       </c>
       <c r="B122" t="n">
-        <v>11.16965484619141</v>
+        <v>11.16965579986572</v>
       </c>
       <c r="C122" t="n">
-        <v>11.35764324475576</v>
+        <v>11.35764421448068</v>
       </c>
       <c r="D122" t="n">
-        <v>11.02866317376839</v>
+        <v>11.02866411540472</v>
       </c>
       <c r="E122" t="n">
-        <v>11.2244846090228</v>
+        <v>11.22448556737853</v>
       </c>
       <c r="F122" t="n">
         <v>3523100</v>
@@ -2912,16 +2912,16 @@
         <v>44825</v>
       </c>
       <c r="B125" t="n">
-        <v>11.0913257598877</v>
+        <v>11.09132671356201</v>
       </c>
       <c r="C125" t="n">
-        <v>11.23231742959796</v>
+        <v>11.23231839539528</v>
       </c>
       <c r="D125" t="n">
-        <v>10.93466876409822</v>
+        <v>10.93466970430257</v>
       </c>
       <c r="E125" t="n">
-        <v>11.13049019558493</v>
+        <v>11.13049115262676</v>
       </c>
       <c r="F125" t="n">
         <v>2825100</v>
@@ -2972,16 +2972,16 @@
         <v>44830</v>
       </c>
       <c r="B128" t="n">
-        <v>11.00516605377197</v>
+        <v>11.00516510009766</v>
       </c>
       <c r="C128" t="n">
-        <v>11.20882054871997</v>
+        <v>11.20881957739757</v>
       </c>
       <c r="D128" t="n">
-        <v>10.88767273114832</v>
+        <v>10.88767178765562</v>
       </c>
       <c r="E128" t="n">
-        <v>11.20098751114514</v>
+        <v>11.20098654050153</v>
       </c>
       <c r="F128" t="n">
         <v>1884300</v>
@@ -3012,16 +3012,16 @@
         <v>44832</v>
       </c>
       <c r="B130" t="n">
-        <v>10.74668121337891</v>
+        <v>10.74668025970459</v>
       </c>
       <c r="C130" t="n">
-        <v>11.03649686510639</v>
+        <v>11.03649588571345</v>
       </c>
       <c r="D130" t="n">
-        <v>10.72318210191485</v>
+        <v>10.72318115032588</v>
       </c>
       <c r="E130" t="n">
-        <v>10.95816798755862</v>
+        <v>10.95816701511669</v>
       </c>
       <c r="F130" t="n">
         <v>4249200</v>
@@ -3032,16 +3032,16 @@
         <v>44833</v>
       </c>
       <c r="B131" t="n">
-        <v>10.70751571655273</v>
+        <v>10.70751667022705</v>
       </c>
       <c r="C131" t="n">
-        <v>10.83284131064561</v>
+        <v>10.83284227548216</v>
       </c>
       <c r="D131" t="n">
-        <v>10.6448529195063</v>
+        <v>10.6448538675995</v>
       </c>
       <c r="E131" t="n">
-        <v>10.69184964379139</v>
+        <v>10.6918505960704</v>
       </c>
       <c r="F131" t="n">
         <v>2222600</v>
@@ -3052,16 +3052,16 @@
         <v>44834</v>
       </c>
       <c r="B132" t="n">
-        <v>10.61352252960205</v>
+        <v>10.61352157592773</v>
       </c>
       <c r="C132" t="n">
-        <v>10.74668117272986</v>
+        <v>10.74668020709063</v>
       </c>
       <c r="D132" t="n">
-        <v>10.59785645535194</v>
+        <v>10.59785550308529</v>
       </c>
       <c r="E132" t="n">
-        <v>10.70751673410412</v>
+        <v>10.70751577198399</v>
       </c>
       <c r="F132" t="n">
         <v>4019300</v>
@@ -3132,16 +3132,16 @@
         <v>44840</v>
       </c>
       <c r="B136" t="n">
-        <v>10.98950004577637</v>
+        <v>10.98949909210205</v>
       </c>
       <c r="C136" t="n">
-        <v>11.12265869736379</v>
+        <v>11.1226577321339</v>
       </c>
       <c r="D136" t="n">
-        <v>10.88767279768013</v>
+        <v>10.88767185284243</v>
       </c>
       <c r="E136" t="n">
-        <v>11.02866448689024</v>
+        <v>11.02866352981721</v>
       </c>
       <c r="F136" t="n">
         <v>3101100</v>
@@ -3152,16 +3152,16 @@
         <v>44841</v>
       </c>
       <c r="B137" t="n">
-        <v>11.02866363525391</v>
+        <v>11.02866458892822</v>
       </c>
       <c r="C137" t="n">
-        <v>11.15398923954096</v>
+        <v>11.15399020405247</v>
       </c>
       <c r="D137" t="n">
-        <v>10.94250246905644</v>
+        <v>10.9425034152802</v>
       </c>
       <c r="E137" t="n">
-        <v>10.98166690714602</v>
+        <v>10.98166785675642</v>
       </c>
       <c r="F137" t="n">
         <v>7588600</v>
@@ -3172,16 +3172,16 @@
         <v>44844</v>
       </c>
       <c r="B138" t="n">
-        <v>11.07566165924072</v>
+        <v>11.07566070556641</v>
       </c>
       <c r="C138" t="n">
-        <v>11.35764428286087</v>
+        <v>11.35764330490633</v>
       </c>
       <c r="D138" t="n">
-        <v>11.0129988539918</v>
+        <v>11.01299790571309</v>
       </c>
       <c r="E138" t="n">
-        <v>11.07566165924072</v>
+        <v>11.07566070556641</v>
       </c>
       <c r="F138" t="n">
         <v>2000500</v>
@@ -3232,16 +3232,16 @@
         <v>44848</v>
       </c>
       <c r="B141" t="n">
-        <v>10.8250093460083</v>
+        <v>10.82500839233398</v>
       </c>
       <c r="C141" t="n">
-        <v>11.1618224737291</v>
+        <v>11.16182149038183</v>
       </c>
       <c r="D141" t="n">
-        <v>10.8250093460083</v>
+        <v>10.82500839233398</v>
       </c>
       <c r="E141" t="n">
-        <v>10.97383406397776</v>
+        <v>10.97383309719211</v>
       </c>
       <c r="F141" t="n">
         <v>3601200</v>
@@ -3252,16 +3252,16 @@
         <v>44851</v>
       </c>
       <c r="B142" t="n">
-        <v>11.1539888381958</v>
+        <v>11.15398979187012</v>
       </c>
       <c r="C142" t="n">
-        <v>11.20098631161214</v>
+        <v>11.20098726930477</v>
       </c>
       <c r="D142" t="n">
-        <v>10.78584507559909</v>
+        <v>10.78584599779684</v>
       </c>
       <c r="E142" t="n">
-        <v>10.86417320196032</v>
+        <v>10.86417413085518</v>
       </c>
       <c r="F142" t="n">
         <v>6971700</v>
@@ -3272,16 +3272,16 @@
         <v>44852</v>
       </c>
       <c r="B143" t="n">
-        <v>11.27148246765137</v>
+        <v>11.27148151397705</v>
       </c>
       <c r="C143" t="n">
-        <v>11.37330970710612</v>
+        <v>11.37330874481625</v>
       </c>
       <c r="D143" t="n">
-        <v>11.06782798874186</v>
+        <v>11.06782705229865</v>
       </c>
       <c r="E143" t="n">
-        <v>11.20881966598683</v>
+        <v>11.20881871761438</v>
       </c>
       <c r="F143" t="n">
         <v>2646800</v>
@@ -3312,16 +3312,16 @@
         <v>44854</v>
       </c>
       <c r="B145" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C145" t="n">
-        <v>10.98166755090811</v>
+        <v>10.98166658413194</v>
       </c>
       <c r="D145" t="n">
-        <v>10.39420318612486</v>
+        <v>10.39420227106638</v>
       </c>
       <c r="E145" t="n">
-        <v>10.5743585660986</v>
+        <v>10.57435763518006</v>
       </c>
       <c r="F145" t="n">
         <v>7194300</v>
@@ -3332,16 +3332,16 @@
         <v>44855</v>
       </c>
       <c r="B146" t="n">
-        <v>11.16965484619141</v>
+        <v>11.16965579986572</v>
       </c>
       <c r="C146" t="n">
-        <v>11.16965484619141</v>
+        <v>11.16965579986572</v>
       </c>
       <c r="D146" t="n">
-        <v>10.75451286561242</v>
+        <v>10.75451378384157</v>
       </c>
       <c r="E146" t="n">
-        <v>10.75451286561242</v>
+        <v>10.75451378384157</v>
       </c>
       <c r="F146" t="n">
         <v>9489900</v>
@@ -3352,16 +3352,16 @@
         <v>44858</v>
       </c>
       <c r="B147" t="n">
-        <v>11.24798202514648</v>
+        <v>11.24798393249512</v>
       </c>
       <c r="C147" t="n">
-        <v>11.45163647994565</v>
+        <v>11.45163842182848</v>
       </c>
       <c r="D147" t="n">
-        <v>11.10699111159273</v>
+        <v>11.10699299503318</v>
       </c>
       <c r="E147" t="n">
-        <v>11.10699111159273</v>
+        <v>11.10699299503318</v>
       </c>
       <c r="F147" t="n">
         <v>2219500</v>
@@ -3412,16 +3412,16 @@
         <v>44861</v>
       </c>
       <c r="B150" t="n">
-        <v>11.35764408111572</v>
+        <v>11.35764312744141</v>
       </c>
       <c r="C150" t="n">
-        <v>11.63179440945972</v>
+        <v>11.63179343276565</v>
       </c>
       <c r="D150" t="n">
-        <v>11.27148291217882</v>
+        <v>11.27148196573925</v>
       </c>
       <c r="E150" t="n">
-        <v>11.42813992251844</v>
+        <v>11.42813896292475</v>
       </c>
       <c r="F150" t="n">
         <v>4207900</v>
@@ -3472,16 +3472,16 @@
         <v>44866</v>
       </c>
       <c r="B153" t="n">
-        <v>11.56913089752197</v>
+        <v>11.56913185119629</v>
       </c>
       <c r="C153" t="n">
-        <v>11.80411602515518</v>
+        <v>11.80411699819995</v>
       </c>
       <c r="D153" t="n">
-        <v>11.34981034946504</v>
+        <v>11.34981128506018</v>
       </c>
       <c r="E153" t="n">
-        <v>11.67879042455094</v>
+        <v>11.67879138726478</v>
       </c>
       <c r="F153" t="n">
         <v>3576300</v>
@@ -3552,16 +3552,16 @@
         <v>44873</v>
       </c>
       <c r="B157" t="n">
-        <v>11.12265777587891</v>
+        <v>11.12265872955322</v>
       </c>
       <c r="C157" t="n">
-        <v>11.27148249038195</v>
+        <v>11.27148345681673</v>
       </c>
       <c r="D157" t="n">
-        <v>11.02083053621881</v>
+        <v>11.02083148116229</v>
       </c>
       <c r="E157" t="n">
-        <v>11.11482473890516</v>
+        <v>11.11482569190786</v>
       </c>
       <c r="F157" t="n">
         <v>2450400</v>
@@ -3572,16 +3572,16 @@
         <v>44874</v>
       </c>
       <c r="B158" t="n">
-        <v>11.12265777587891</v>
+        <v>11.12265872955322</v>
       </c>
       <c r="C158" t="n">
-        <v>11.21665197856526</v>
+        <v>11.21665294029879</v>
       </c>
       <c r="D158" t="n">
-        <v>11.04432964714004</v>
+        <v>11.04433059409837</v>
       </c>
       <c r="E158" t="n">
-        <v>11.14615613980062</v>
+        <v>11.14615709548972</v>
       </c>
       <c r="F158" t="n">
         <v>1977800</v>
@@ -3592,16 +3592,16 @@
         <v>44875</v>
       </c>
       <c r="B159" t="n">
-        <v>10.70751571655273</v>
+        <v>10.70751667022705</v>
       </c>
       <c r="C159" t="n">
-        <v>11.10699160797338</v>
+        <v>11.10699259722736</v>
       </c>
       <c r="D159" t="n">
-        <v>10.49602821627141</v>
+        <v>10.4960291511094</v>
       </c>
       <c r="E159" t="n">
-        <v>11.04432881092694</v>
+        <v>11.04432979459981</v>
       </c>
       <c r="F159" t="n">
         <v>4341400</v>
@@ -3632,16 +3632,16 @@
         <v>44879</v>
       </c>
       <c r="B161" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C161" t="n">
-        <v>10.9660014759541</v>
+        <v>10.9660005105571</v>
       </c>
       <c r="D161" t="n">
-        <v>10.71535025268644</v>
+        <v>10.71534930935563</v>
       </c>
       <c r="E161" t="n">
-        <v>10.94250311052265</v>
+        <v>10.94250214719434</v>
       </c>
       <c r="F161" t="n">
         <v>1203700</v>
@@ -3672,16 +3672,16 @@
         <v>44882</v>
       </c>
       <c r="B163" t="n">
-        <v>10.74668121337891</v>
+        <v>10.74668025970459</v>
       </c>
       <c r="C163" t="n">
-        <v>10.80151097946262</v>
+        <v>10.80151002092264</v>
       </c>
       <c r="D163" t="n">
-        <v>10.50386229058046</v>
+        <v>10.50386135845421</v>
       </c>
       <c r="E163" t="n">
-        <v>10.69185070029565</v>
+        <v>10.69184975148707</v>
       </c>
       <c r="F163" t="n">
         <v>5834900</v>
@@ -3692,16 +3692,16 @@
         <v>44883</v>
       </c>
       <c r="B164" t="n">
-        <v>10.78584480285645</v>
+        <v>10.78584575653076</v>
       </c>
       <c r="C164" t="n">
-        <v>10.98949852384542</v>
+        <v>10.98949949552661</v>
       </c>
       <c r="D164" t="n">
-        <v>10.57435729833009</v>
+        <v>10.57435823330488</v>
       </c>
       <c r="E164" t="n">
-        <v>10.80934316547066</v>
+        <v>10.80934412122268</v>
       </c>
       <c r="F164" t="n">
         <v>3568700</v>
@@ -3712,16 +3712,16 @@
         <v>44886</v>
       </c>
       <c r="B165" t="n">
-        <v>11.27931499481201</v>
+        <v>11.27931594848633</v>
       </c>
       <c r="C165" t="n">
-        <v>11.32631247054852</v>
+        <v>11.32631342819651</v>
       </c>
       <c r="D165" t="n">
-        <v>10.80934397244457</v>
+        <v>10.8093448863825</v>
       </c>
       <c r="E165" t="n">
-        <v>10.84067537393573</v>
+        <v>10.84067629052275</v>
       </c>
       <c r="F165" t="n">
         <v>4939800</v>
@@ -3792,16 +3792,16 @@
         <v>44890</v>
       </c>
       <c r="B169" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C169" t="n">
-        <v>11.03649731924802</v>
+        <v>11.03649634764489</v>
       </c>
       <c r="D169" t="n">
-        <v>10.71535025268644</v>
+        <v>10.71534930935563</v>
       </c>
       <c r="E169" t="n">
-        <v>10.95033540100009</v>
+        <v>10.95033443698226</v>
       </c>
       <c r="F169" t="n">
         <v>1631500</v>
@@ -3832,16 +3832,16 @@
         <v>44894</v>
       </c>
       <c r="B171" t="n">
-        <v>11.16965484619141</v>
+        <v>11.16965579986572</v>
       </c>
       <c r="C171" t="n">
-        <v>11.26364904547358</v>
+        <v>11.2636500071732</v>
       </c>
       <c r="D171" t="n">
-        <v>10.99733177400767</v>
+        <v>10.9973327129689</v>
       </c>
       <c r="E171" t="n">
-        <v>11.01299784738778</v>
+        <v>11.01299878768659</v>
       </c>
       <c r="F171" t="n">
         <v>1705300</v>
@@ -3852,16 +3852,16 @@
         <v>44895</v>
       </c>
       <c r="B172" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C172" t="n">
-        <v>11.20882040874432</v>
+        <v>11.20881942197064</v>
       </c>
       <c r="D172" t="n">
-        <v>10.69185114025542</v>
+        <v>10.69185019899337</v>
       </c>
       <c r="E172" t="n">
-        <v>11.20882040874432</v>
+        <v>11.20881942197064</v>
       </c>
       <c r="F172" t="n">
         <v>4586400</v>
@@ -3872,16 +3872,16 @@
         <v>44896</v>
       </c>
       <c r="B173" t="n">
-        <v>10.92683696746826</v>
+        <v>10.92683601379395</v>
       </c>
       <c r="C173" t="n">
-        <v>11.02083117560783</v>
+        <v>11.02083021372987</v>
       </c>
       <c r="D173" t="n">
-        <v>10.69185107361957</v>
+        <v>10.69185014045439</v>
       </c>
       <c r="E173" t="n">
-        <v>10.76234691647413</v>
+        <v>10.76234597715621</v>
       </c>
       <c r="F173" t="n">
         <v>1944500</v>
@@ -3952,16 +3952,16 @@
         <v>44902</v>
       </c>
       <c r="B177" t="n">
-        <v>10.65268707275391</v>
+        <v>10.65268611907959</v>
       </c>
       <c r="C177" t="n">
-        <v>10.80151104459258</v>
+        <v>10.80151007759491</v>
       </c>
       <c r="D177" t="n">
-        <v>10.42553422289516</v>
+        <v>10.42553328955654</v>
       </c>
       <c r="E177" t="n">
-        <v>10.42553422289516</v>
+        <v>10.42553328955654</v>
       </c>
       <c r="F177" t="n">
         <v>2865300</v>
@@ -3972,16 +3972,16 @@
         <v>44903</v>
       </c>
       <c r="B178" t="n">
-        <v>11.26364898681641</v>
+        <v>11.26364994049072</v>
       </c>
       <c r="C178" t="n">
-        <v>11.8119488532735</v>
+        <v>11.81194985337145</v>
       </c>
       <c r="D178" t="n">
-        <v>11.15398871472519</v>
+        <v>11.15398965911476</v>
       </c>
       <c r="E178" t="n">
-        <v>11.74928605407837</v>
+        <v>11.74928704887077</v>
       </c>
       <c r="F178" t="n">
         <v>12105700</v>
@@ -4012,16 +4012,16 @@
         <v>44907</v>
       </c>
       <c r="B180" t="n">
-        <v>11.00516605377197</v>
+        <v>11.00516510009766</v>
       </c>
       <c r="C180" t="n">
-        <v>11.26365031774459</v>
+        <v>11.26364934167081</v>
       </c>
       <c r="D180" t="n">
-        <v>10.74668178979936</v>
+        <v>10.7466808585245</v>
       </c>
       <c r="E180" t="n">
-        <v>11.17748914542024</v>
+        <v>11.17748817681293</v>
       </c>
       <c r="F180" t="n">
         <v>4004300</v>
@@ -4052,16 +4052,16 @@
         <v>44909</v>
       </c>
       <c r="B182" t="n">
-        <v>10.9973316192627</v>
+        <v>10.99733352661133</v>
       </c>
       <c r="C182" t="n">
-        <v>11.13832328970179</v>
+        <v>11.13832522150366</v>
       </c>
       <c r="D182" t="n">
-        <v>10.738847388124</v>
+        <v>10.7388492506418</v>
       </c>
       <c r="E182" t="n">
-        <v>11.01299769242237</v>
+        <v>11.01299960248808</v>
       </c>
       <c r="F182" t="n">
         <v>3892800</v>
@@ -4072,16 +4072,16 @@
         <v>44910</v>
       </c>
       <c r="B183" t="n">
-        <v>11.05216217041016</v>
+        <v>11.05216121673584</v>
       </c>
       <c r="C183" t="n">
-        <v>11.17748852363695</v>
+        <v>11.17748755914842</v>
       </c>
       <c r="D183" t="n">
-        <v>10.86417376106927</v>
+        <v>10.86417282361618</v>
       </c>
       <c r="E183" t="n">
-        <v>10.95033492860062</v>
+        <v>10.95033398371283</v>
       </c>
       <c r="F183" t="n">
         <v>3824700</v>
@@ -4092,16 +4092,16 @@
         <v>44911</v>
       </c>
       <c r="B184" t="n">
-        <v>11.24798202514648</v>
+        <v>11.24798393249512</v>
       </c>
       <c r="C184" t="n">
-        <v>11.24798202514648</v>
+        <v>11.24798393249512</v>
       </c>
       <c r="D184" t="n">
-        <v>10.90333665679356</v>
+        <v>10.90333850569981</v>
       </c>
       <c r="E184" t="n">
-        <v>11.04432831734674</v>
+        <v>11.04433019016131</v>
       </c>
       <c r="F184" t="n">
         <v>3365900</v>
@@ -4112,16 +4112,16 @@
         <v>44914</v>
       </c>
       <c r="B185" t="n">
-        <v>11.37330913543701</v>
+        <v>11.37331008911133</v>
       </c>
       <c r="C185" t="n">
-        <v>11.5221330951599</v>
+        <v>11.5221340613134</v>
       </c>
       <c r="D185" t="n">
-        <v>11.18531999289299</v>
+        <v>11.18532093080405</v>
       </c>
       <c r="E185" t="n">
-        <v>11.23231746527886</v>
+        <v>11.23231840713075</v>
       </c>
       <c r="F185" t="n">
         <v>3838800</v>
@@ -4132,16 +4132,16 @@
         <v>44915</v>
       </c>
       <c r="B186" t="n">
-        <v>11.27931499481201</v>
+        <v>11.27931594848633</v>
       </c>
       <c r="C186" t="n">
-        <v>11.56129835523201</v>
+        <v>11.56129933274823</v>
       </c>
       <c r="D186" t="n">
-        <v>11.16965546309271</v>
+        <v>11.16965640749523</v>
       </c>
       <c r="E186" t="n">
-        <v>11.35764387203968</v>
+        <v>11.35764483233677</v>
       </c>
       <c r="F186" t="n">
         <v>4148100</v>
@@ -4152,16 +4152,16 @@
         <v>44916</v>
       </c>
       <c r="B187" t="n">
-        <v>11.58479595184326</v>
+        <v>11.58479785919189</v>
       </c>
       <c r="C187" t="n">
-        <v>11.75711902212409</v>
+        <v>11.7571209578444</v>
       </c>
       <c r="D187" t="n">
-        <v>11.15398864964095</v>
+        <v>11.15399048606043</v>
       </c>
       <c r="E187" t="n">
-        <v>11.42813895476955</v>
+        <v>11.4281408363258</v>
       </c>
       <c r="F187" t="n">
         <v>6348400</v>
@@ -4172,16 +4172,16 @@
         <v>44917</v>
       </c>
       <c r="B188" t="n">
-        <v>11.63179492950439</v>
+        <v>11.63179397583008</v>
       </c>
       <c r="C188" t="n">
-        <v>11.74928750576218</v>
+        <v>11.74928654245482</v>
       </c>
       <c r="D188" t="n">
-        <v>11.50646856862995</v>
+        <v>11.50646762523096</v>
       </c>
       <c r="E188" t="n">
-        <v>11.60046352603568</v>
+        <v>11.60046257493018</v>
       </c>
       <c r="F188" t="n">
         <v>2577900</v>
@@ -4232,16 +4232,16 @@
         <v>44922</v>
       </c>
       <c r="B191" t="n">
-        <v>11.52996635437012</v>
+        <v>11.52996730804443</v>
       </c>
       <c r="C191" t="n">
-        <v>11.60829448052647</v>
+        <v>11.60829544067951</v>
       </c>
       <c r="D191" t="n">
-        <v>11.34197720819598</v>
+        <v>11.34197814632122</v>
       </c>
       <c r="E191" t="n">
-        <v>11.60829448052647</v>
+        <v>11.60829544067951</v>
       </c>
       <c r="F191" t="n">
         <v>1633000</v>
@@ -4252,16 +4252,16 @@
         <v>44923</v>
       </c>
       <c r="B192" t="n">
-        <v>11.58479595184326</v>
+        <v>11.58479785919189</v>
       </c>
       <c r="C192" t="n">
-        <v>11.6944562232946</v>
+        <v>11.69445814869797</v>
       </c>
       <c r="D192" t="n">
-        <v>11.49863479020259</v>
+        <v>11.49863668336545</v>
       </c>
       <c r="E192" t="n">
-        <v>11.5769629152397</v>
+        <v>11.57696482129869</v>
       </c>
       <c r="F192" t="n">
         <v>2005900</v>
@@ -4332,16 +4332,16 @@
         <v>44930</v>
       </c>
       <c r="B196" t="n">
-        <v>11.35764408111572</v>
+        <v>11.35764312744141</v>
       </c>
       <c r="C196" t="n">
-        <v>11.35764408111572</v>
+        <v>11.35764312744141</v>
       </c>
       <c r="D196" t="n">
-        <v>10.9660011817669</v>
+        <v>10.96600026097791</v>
       </c>
       <c r="E196" t="n">
-        <v>11.16965566870818</v>
+        <v>11.1696547308188</v>
       </c>
       <c r="F196" t="n">
         <v>2937400</v>
@@ -4352,16 +4352,16 @@
         <v>44931</v>
       </c>
       <c r="B197" t="n">
-        <v>11.41247367858887</v>
+        <v>11.41247272491455</v>
       </c>
       <c r="C197" t="n">
-        <v>11.41247367858887</v>
+        <v>11.41247272491455</v>
       </c>
       <c r="D197" t="n">
-        <v>11.08349358825896</v>
+        <v>11.08349266207561</v>
       </c>
       <c r="E197" t="n">
-        <v>11.31064643662965</v>
+        <v>11.31064549146445</v>
       </c>
       <c r="F197" t="n">
         <v>4358300</v>
@@ -4472,16 +4472,16 @@
         <v>44939</v>
       </c>
       <c r="B203" t="n">
-        <v>11.58479595184326</v>
+        <v>11.58479785919189</v>
       </c>
       <c r="C203" t="n">
-        <v>11.78845042153883</v>
+        <v>11.78845236241762</v>
       </c>
       <c r="D203" t="n">
-        <v>11.44380428097718</v>
+        <v>11.4438061651126</v>
       </c>
       <c r="E203" t="n">
-        <v>11.74928598552053</v>
+        <v>11.7492879199512</v>
       </c>
       <c r="F203" t="n">
         <v>2269100</v>
@@ -4532,16 +4532,16 @@
         <v>44944</v>
       </c>
       <c r="B206" t="n">
-        <v>11.41247367858887</v>
+        <v>11.41247272491455</v>
       </c>
       <c r="C206" t="n">
-        <v>11.89027848678206</v>
+        <v>11.89027749318036</v>
       </c>
       <c r="D206" t="n">
-        <v>11.41247367858887</v>
+        <v>11.41247272491455</v>
       </c>
       <c r="E206" t="n">
-        <v>11.87461241248085</v>
+        <v>11.87461142018828</v>
       </c>
       <c r="F206" t="n">
         <v>3532000</v>
@@ -4552,16 +4552,16 @@
         <v>44945</v>
       </c>
       <c r="B207" t="n">
-        <v>11.66312503814697</v>
+        <v>11.66312599182129</v>
       </c>
       <c r="C207" t="n">
-        <v>11.68662340138985</v>
+        <v>11.68662435698559</v>
       </c>
       <c r="D207" t="n">
-        <v>11.27931445451592</v>
+        <v>11.27931537680668</v>
       </c>
       <c r="E207" t="n">
-        <v>11.3419772544966</v>
+        <v>11.3419781819112</v>
       </c>
       <c r="F207" t="n">
         <v>1847800</v>
@@ -4572,16 +4572,16 @@
         <v>44946</v>
       </c>
       <c r="B208" t="n">
-        <v>11.58479595184326</v>
+        <v>11.58479785919189</v>
       </c>
       <c r="C208" t="n">
-        <v>11.68662318669104</v>
+        <v>11.68662511080476</v>
       </c>
       <c r="D208" t="n">
-        <v>11.48296871699548</v>
+        <v>11.48297060757903</v>
       </c>
       <c r="E208" t="n">
-        <v>11.6552917872763</v>
+        <v>11.65529370623154</v>
       </c>
       <c r="F208" t="n">
         <v>2012100</v>
@@ -4592,16 +4592,16 @@
         <v>44949</v>
       </c>
       <c r="B209" t="n">
-        <v>11.52213382720947</v>
+        <v>11.52213478088379</v>
       </c>
       <c r="C209" t="n">
-        <v>11.64745943220163</v>
+        <v>11.64746039624901</v>
       </c>
       <c r="D209" t="n">
-        <v>11.34981074684549</v>
+        <v>11.34981168625682</v>
       </c>
       <c r="E209" t="n">
-        <v>11.59262966676744</v>
+        <v>11.59263062627662</v>
       </c>
       <c r="F209" t="n">
         <v>1770800</v>
@@ -4672,16 +4672,16 @@
         <v>44953</v>
       </c>
       <c r="B213" t="n">
-        <v>11.98427200317383</v>
+        <v>11.98427104949951</v>
       </c>
       <c r="C213" t="n">
-        <v>12.23492320159854</v>
+        <v>12.23492222797812</v>
       </c>
       <c r="D213" t="n">
-        <v>11.92160920356765</v>
+        <v>11.92160825487986</v>
       </c>
       <c r="E213" t="n">
-        <v>11.96860592977254</v>
+        <v>11.96860497734488</v>
       </c>
       <c r="F213" t="n">
         <v>4160800</v>
@@ -4692,16 +4692,16 @@
         <v>44956</v>
       </c>
       <c r="B214" t="n">
-        <v>11.84328079223633</v>
+        <v>11.84327983856201</v>
       </c>
       <c r="C214" t="n">
-        <v>11.97643943334014</v>
+        <v>11.97643846894329</v>
       </c>
       <c r="D214" t="n">
-        <v>11.74928658916297</v>
+        <v>11.74928564305749</v>
       </c>
       <c r="E214" t="n">
-        <v>11.86677915625479</v>
+        <v>11.86677820068828</v>
       </c>
       <c r="F214" t="n">
         <v>3859300</v>
@@ -4732,16 +4732,16 @@
         <v>44958</v>
       </c>
       <c r="B216" t="n">
-        <v>12.07826614379883</v>
+        <v>12.07826709747314</v>
       </c>
       <c r="C216" t="n">
-        <v>12.19575870573871</v>
+        <v>12.19575966868999</v>
       </c>
       <c r="D216" t="n">
-        <v>11.93727447187138</v>
+        <v>11.93727541441329</v>
       </c>
       <c r="E216" t="n">
-        <v>12.08609918046135</v>
+        <v>12.08610013475415</v>
       </c>
       <c r="F216" t="n">
         <v>3741600</v>
@@ -4752,16 +4752,16 @@
         <v>44959</v>
       </c>
       <c r="B217" t="n">
-        <v>12.03910255432129</v>
+        <v>12.03910160064697</v>
       </c>
       <c r="C217" t="n">
-        <v>12.19575956359362</v>
+        <v>12.19575859750976</v>
       </c>
       <c r="D217" t="n">
-        <v>11.8511141431945</v>
+        <v>11.85111320441163</v>
       </c>
       <c r="E217" t="n">
-        <v>12.07043395617575</v>
+        <v>12.07043300001953</v>
       </c>
       <c r="F217" t="n">
         <v>3404900</v>
@@ -4772,16 +4772,16 @@
         <v>44960</v>
       </c>
       <c r="B218" t="n">
-        <v>11.92160987854004</v>
+        <v>11.92160892486572</v>
       </c>
       <c r="C218" t="n">
-        <v>12.17226109115601</v>
+        <v>12.17226011743074</v>
       </c>
       <c r="D218" t="n">
-        <v>11.80411656237665</v>
+        <v>11.80411561810126</v>
       </c>
       <c r="E218" t="n">
-        <v>11.99993800898276</v>
+        <v>11.99993704904255</v>
       </c>
       <c r="F218" t="n">
         <v>3073100</v>
@@ -4812,16 +4812,16 @@
         <v>44964</v>
       </c>
       <c r="B220" t="n">
-        <v>11.60046195983887</v>
+        <v>11.60046291351318</v>
       </c>
       <c r="C220" t="n">
-        <v>12.02343622305989</v>
+        <v>12.02343721150694</v>
       </c>
       <c r="D220" t="n">
-        <v>11.49080168900398</v>
+        <v>11.49080263366312</v>
       </c>
       <c r="E220" t="n">
-        <v>12.02343622305989</v>
+        <v>12.02343721150694</v>
       </c>
       <c r="F220" t="n">
         <v>5199600</v>
@@ -4832,16 +4832,16 @@
         <v>44965</v>
       </c>
       <c r="B221" t="n">
-        <v>11.71012210845947</v>
+        <v>11.71012306213379</v>
       </c>
       <c r="C221" t="n">
-        <v>11.78845098423493</v>
+        <v>11.78845194428836</v>
       </c>
       <c r="D221" t="n">
-        <v>11.54563206693063</v>
+        <v>11.54563300720885</v>
       </c>
       <c r="E221" t="n">
-        <v>11.68662374452664</v>
+        <v>11.68662469628725</v>
       </c>
       <c r="F221" t="n">
         <v>3697100</v>
@@ -4852,16 +4852,16 @@
         <v>44966</v>
       </c>
       <c r="B222" t="n">
-        <v>11.66312503814697</v>
+        <v>11.66312599182129</v>
       </c>
       <c r="C222" t="n">
-        <v>11.78845063810834</v>
+        <v>11.78845160203032</v>
       </c>
       <c r="D222" t="n">
-        <v>11.55346476468103</v>
+        <v>11.55346570938861</v>
       </c>
       <c r="E222" t="n">
-        <v>11.71012176463273</v>
+        <v>11.7101227221499</v>
       </c>
       <c r="F222" t="n">
         <v>2260100</v>
@@ -4872,16 +4872,16 @@
         <v>44967</v>
       </c>
       <c r="B223" t="n">
-        <v>11.72578811645508</v>
+        <v>11.72578907012939</v>
       </c>
       <c r="C223" t="n">
-        <v>11.88244512012525</v>
+        <v>11.88244608654069</v>
       </c>
       <c r="D223" t="n">
-        <v>11.62396087731959</v>
+        <v>11.62396182271216</v>
       </c>
       <c r="E223" t="n">
-        <v>11.62396087731959</v>
+        <v>11.62396182271216</v>
       </c>
       <c r="F223" t="n">
         <v>6075300</v>
@@ -4972,16 +4972,16 @@
         <v>44974</v>
       </c>
       <c r="B228" t="n">
-        <v>11.72578811645508</v>
+        <v>11.72578907012939</v>
       </c>
       <c r="C228" t="n">
-        <v>12.13309632599753</v>
+        <v>12.13309731279878</v>
       </c>
       <c r="D228" t="n">
-        <v>11.55346503891813</v>
+        <v>11.55346597857718</v>
       </c>
       <c r="E228" t="n">
-        <v>11.94510792159332</v>
+        <v>11.94510889310522</v>
       </c>
       <c r="F228" t="n">
         <v>9428300</v>
@@ -5052,16 +5052,16 @@
         <v>44984</v>
       </c>
       <c r="B232" t="n">
-        <v>11.64745903015137</v>
+        <v>11.64745998382568</v>
       </c>
       <c r="C232" t="n">
-        <v>11.85894654152509</v>
+        <v>11.85894751251565</v>
       </c>
       <c r="D232" t="n">
-        <v>11.56129786644328</v>
+        <v>11.56129881306286</v>
       </c>
       <c r="E232" t="n">
-        <v>11.73362019385946</v>
+        <v>11.7336211545885</v>
       </c>
       <c r="F232" t="n">
         <v>3412900</v>
@@ -5072,16 +5072,16 @@
         <v>44985</v>
       </c>
       <c r="B233" t="n">
-        <v>11.59263038635254</v>
+        <v>11.59262943267822</v>
       </c>
       <c r="C233" t="n">
-        <v>11.82761628379879</v>
+        <v>11.82761531079323</v>
       </c>
       <c r="D233" t="n">
-        <v>11.54563290806346</v>
+        <v>11.54563195825542</v>
       </c>
       <c r="E233" t="n">
-        <v>11.67095852083491</v>
+        <v>11.67095756071688</v>
       </c>
       <c r="F233" t="n">
         <v>7018700</v>
@@ -5092,16 +5092,16 @@
         <v>44986</v>
       </c>
       <c r="B234" t="n">
-        <v>11.52996635437012</v>
+        <v>11.52996730804443</v>
       </c>
       <c r="C234" t="n">
-        <v>11.65529195381987</v>
+        <v>11.6552929178602</v>
       </c>
       <c r="D234" t="n">
-        <v>11.31847884504903</v>
+        <v>11.31847978123065</v>
       </c>
       <c r="E234" t="n">
-        <v>11.60046219081048</v>
+        <v>11.6004631503157</v>
       </c>
       <c r="F234" t="n">
         <v>8005300</v>
@@ -5192,16 +5192,16 @@
         <v>44993</v>
       </c>
       <c r="B239" t="n">
-        <v>11.63179492950439</v>
+        <v>11.63179397583008</v>
       </c>
       <c r="C239" t="n">
-        <v>11.63962722012189</v>
+        <v>11.63962626580541</v>
       </c>
       <c r="D239" t="n">
-        <v>11.48297020277831</v>
+        <v>11.48296926130592</v>
       </c>
       <c r="E239" t="n">
-        <v>11.62396189188732</v>
+        <v>11.62396093885522</v>
       </c>
       <c r="F239" t="n">
         <v>2946500</v>
@@ -5252,16 +5252,16 @@
         <v>44998</v>
       </c>
       <c r="B242" t="n">
-        <v>11.66312503814697</v>
+        <v>11.66312599182129</v>
       </c>
       <c r="C242" t="n">
-        <v>11.74145316462308</v>
+        <v>11.74145412470215</v>
       </c>
       <c r="D242" t="n">
-        <v>11.45947056471</v>
+        <v>11.45947150173183</v>
       </c>
       <c r="E242" t="n">
-        <v>11.52213336469069</v>
+        <v>11.52213430683635</v>
       </c>
       <c r="F242" t="n">
         <v>3223500</v>
@@ -5332,16 +5332,16 @@
         <v>45002</v>
       </c>
       <c r="B246" t="n">
-        <v>11.40464019775391</v>
+        <v>11.40464210510254</v>
       </c>
       <c r="C246" t="n">
-        <v>11.66312442074082</v>
+        <v>11.66312637131919</v>
       </c>
       <c r="D246" t="n">
-        <v>11.37330879942214</v>
+        <v>11.37331070153081</v>
       </c>
       <c r="E246" t="n">
-        <v>11.66312442074082</v>
+        <v>11.66312637131919</v>
       </c>
       <c r="F246" t="n">
         <v>6196900</v>
@@ -5352,16 +5352,16 @@
         <v>45005</v>
       </c>
       <c r="B247" t="n">
-        <v>11.31847953796387</v>
+        <v>11.31847858428955</v>
       </c>
       <c r="C247" t="n">
-        <v>11.51430098584213</v>
+        <v>11.51430001566826</v>
       </c>
       <c r="D247" t="n">
-        <v>11.24798369720776</v>
+        <v>11.2479827494733</v>
       </c>
       <c r="E247" t="n">
-        <v>11.45163818228105</v>
+        <v>11.45163721738703</v>
       </c>
       <c r="F247" t="n">
         <v>2892000</v>
@@ -5432,16 +5432,16 @@
         <v>45009</v>
       </c>
       <c r="B251" t="n">
-        <v>11.30281448364258</v>
+        <v>11.30281352996826</v>
       </c>
       <c r="C251" t="n">
-        <v>11.39680869125504</v>
+        <v>11.39680772964997</v>
       </c>
       <c r="D251" t="n">
-        <v>11.11482532141809</v>
+        <v>11.11482438360535</v>
       </c>
       <c r="E251" t="n">
-        <v>11.20882027603011</v>
+        <v>11.20881933028655</v>
       </c>
       <c r="F251" t="n">
         <v>3265300</v>
@@ -5512,16 +5512,16 @@
         <v>45015</v>
       </c>
       <c r="B255" t="n">
-        <v>11.40464019775391</v>
+        <v>11.40464210510254</v>
       </c>
       <c r="C255" t="n">
-        <v>11.50646668208254</v>
+        <v>11.50646860646096</v>
       </c>
       <c r="D255" t="n">
-        <v>11.12265686576857</v>
+        <v>11.12265872595741</v>
       </c>
       <c r="E255" t="n">
-        <v>11.42030552342006</v>
+        <v>11.42030743338861</v>
       </c>
       <c r="F255" t="n">
         <v>3320400</v>
@@ -5572,16 +5572,16 @@
         <v>45020</v>
       </c>
       <c r="B258" t="n">
-        <v>11.43597316741943</v>
+        <v>11.43597221374512</v>
       </c>
       <c r="C258" t="n">
-        <v>11.498635972693</v>
+        <v>11.49863501379308</v>
       </c>
       <c r="D258" t="n">
-        <v>11.24798400459917</v>
+        <v>11.24798306660174</v>
       </c>
       <c r="E258" t="n">
-        <v>11.35764428732769</v>
+        <v>11.35764334018542</v>
       </c>
       <c r="F258" t="n">
         <v>5230100</v>
@@ -5672,16 +5672,16 @@
         <v>45028</v>
       </c>
       <c r="B263" t="n">
-        <v>11.80411624908447</v>
+        <v>11.80411720275879</v>
       </c>
       <c r="C263" t="n">
-        <v>12.01560376436578</v>
+        <v>12.01560473512652</v>
       </c>
       <c r="D263" t="n">
-        <v>11.74928648452985</v>
+        <v>11.74928743377437</v>
       </c>
       <c r="E263" t="n">
-        <v>11.82761535989319</v>
+        <v>11.82761631546603</v>
       </c>
       <c r="F263" t="n">
         <v>2987000</v>
@@ -5772,16 +5772,16 @@
         <v>45035</v>
       </c>
       <c r="B268" t="n">
-        <v>12.03910255432129</v>
+        <v>12.03910160064697</v>
       </c>
       <c r="C268" t="n">
-        <v>12.06260091896225</v>
+        <v>12.06259996342652</v>
       </c>
       <c r="D268" t="n">
-        <v>11.86677947062196</v>
+        <v>11.86677853059817</v>
       </c>
       <c r="E268" t="n">
-        <v>11.96860671339886</v>
+        <v>11.96860576530885</v>
       </c>
       <c r="F268" t="n">
         <v>3098200</v>
@@ -5812,16 +5812,16 @@
         <v>45040</v>
       </c>
       <c r="B270" t="n">
-        <v>12.10959815979004</v>
+        <v>12.10959911346436</v>
       </c>
       <c r="C270" t="n">
-        <v>12.17226096228058</v>
+        <v>12.17226192088982</v>
       </c>
       <c r="D270" t="n">
-        <v>12.0312692831771</v>
+        <v>12.03127023068273</v>
       </c>
       <c r="E270" t="n">
-        <v>12.10176512272884</v>
+        <v>12.10176607578628</v>
       </c>
       <c r="F270" t="n">
         <v>2389300</v>
@@ -5872,16 +5872,16 @@
         <v>45043</v>
       </c>
       <c r="B273" t="n">
-        <v>12.07826614379883</v>
+        <v>12.07826709747314</v>
       </c>
       <c r="C273" t="n">
-        <v>12.09393147012438</v>
+        <v>12.0939324250356</v>
       </c>
       <c r="D273" t="n">
-        <v>11.95294054519642</v>
+        <v>11.95294148897529</v>
       </c>
       <c r="E273" t="n">
-        <v>12.01560334449763</v>
+        <v>12.01560429322422</v>
       </c>
       <c r="F273" t="n">
         <v>2919600</v>
@@ -5892,16 +5892,16 @@
         <v>45044</v>
       </c>
       <c r="B274" t="n">
-        <v>12.36024856567383</v>
+        <v>12.36024951934814</v>
       </c>
       <c r="C274" t="n">
-        <v>12.45424276329498</v>
+        <v>12.45424372422157</v>
       </c>
       <c r="D274" t="n">
-        <v>12.01560317439626</v>
+        <v>12.01560410147892</v>
       </c>
       <c r="E274" t="n">
-        <v>12.11743040856905</v>
+        <v>12.11743134350835</v>
       </c>
       <c r="F274" t="n">
         <v>8419400</v>
@@ -5912,16 +5912,16 @@
         <v>45048</v>
       </c>
       <c r="B275" t="n">
-        <v>12.39158058166504</v>
+        <v>12.39158153533936</v>
       </c>
       <c r="C275" t="n">
-        <v>12.650064824739</v>
+        <v>12.65006579830664</v>
       </c>
       <c r="D275" t="n">
-        <v>12.2505896517153</v>
+        <v>12.25059059453875</v>
       </c>
       <c r="E275" t="n">
-        <v>12.5325722586143</v>
+        <v>12.53257322313954</v>
       </c>
       <c r="F275" t="n">
         <v>5999300</v>
@@ -5972,16 +5972,16 @@
         <v>45051</v>
       </c>
       <c r="B278" t="n">
-        <v>12.50989818572998</v>
+        <v>12.50989723205566</v>
       </c>
       <c r="C278" t="n">
-        <v>12.59647220699179</v>
+        <v>12.59647124671763</v>
       </c>
       <c r="D278" t="n">
-        <v>12.15494618469247</v>
+        <v>12.15494525807742</v>
       </c>
       <c r="E278" t="n">
-        <v>12.34540853608981</v>
+        <v>12.34540759495513</v>
       </c>
       <c r="F278" t="n">
         <v>9400800</v>
@@ -5992,16 +5992,16 @@
         <v>45054</v>
       </c>
       <c r="B279" t="n">
-        <v>12.11165809631348</v>
+        <v>12.11165904998779</v>
       </c>
       <c r="C279" t="n">
-        <v>12.58781351962092</v>
+        <v>12.58781451078781</v>
       </c>
       <c r="D279" t="n">
-        <v>12.05105678220141</v>
+        <v>12.05105773110397</v>
       </c>
       <c r="E279" t="n">
-        <v>12.54452651284189</v>
+        <v>12.54452750060035</v>
       </c>
       <c r="F279" t="n">
         <v>5826000</v>
@@ -6052,16 +6052,16 @@
         <v>45057</v>
       </c>
       <c r="B282" t="n">
-        <v>12.05971622467041</v>
+        <v>12.05971527099609</v>
       </c>
       <c r="C282" t="n">
-        <v>12.11165998038074</v>
+        <v>12.11165902259875</v>
       </c>
       <c r="D282" t="n">
-        <v>11.73939364568632</v>
+        <v>11.7393927173429</v>
       </c>
       <c r="E282" t="n">
-        <v>11.79133740139665</v>
+        <v>11.79133646894556</v>
       </c>
       <c r="F282" t="n">
         <v>3678200</v>
@@ -6072,16 +6072,16 @@
         <v>45058</v>
       </c>
       <c r="B283" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C283" t="n">
-        <v>12.25017729158851</v>
+        <v>12.25017632493442</v>
       </c>
       <c r="D283" t="n">
-        <v>11.9991136136361</v>
+        <v>11.99911266679329</v>
       </c>
       <c r="E283" t="n">
-        <v>12.0424006254826</v>
+        <v>12.04239967522403</v>
       </c>
       <c r="F283" t="n">
         <v>3087800</v>
@@ -6132,16 +6132,16 @@
         <v>45063</v>
       </c>
       <c r="B286" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="C286" t="n">
-        <v>12.24151939290137</v>
+        <v>12.24152036724783</v>
       </c>
       <c r="D286" t="n">
-        <v>11.94716873091856</v>
+        <v>11.9471696818366</v>
       </c>
       <c r="E286" t="n">
-        <v>12.12897350298847</v>
+        <v>12.128974468377</v>
       </c>
       <c r="F286" t="n">
         <v>4330800</v>
@@ -6152,16 +6152,16 @@
         <v>45064</v>
       </c>
       <c r="B287" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="C287" t="n">
-        <v>12.05971462083146</v>
+        <v>12.05971558070743</v>
       </c>
       <c r="D287" t="n">
-        <v>11.82596527432829</v>
+        <v>11.82596621559931</v>
       </c>
       <c r="E287" t="n">
-        <v>12.01642761307558</v>
+        <v>12.01642856950617</v>
       </c>
       <c r="F287" t="n">
         <v>4680600</v>
@@ -6172,16 +6172,16 @@
         <v>45065</v>
       </c>
       <c r="B288" t="n">
-        <v>12.09434413909912</v>
+        <v>12.09434509277344</v>
       </c>
       <c r="C288" t="n">
-        <v>12.18091732953242</v>
+        <v>12.18091829003328</v>
       </c>
       <c r="D288" t="n">
-        <v>11.93851124043578</v>
+        <v>11.93851218182222</v>
       </c>
       <c r="E288" t="n">
-        <v>11.99911255630219</v>
+        <v>11.99911350246722</v>
       </c>
       <c r="F288" t="n">
         <v>2962700</v>
@@ -6232,16 +6232,16 @@
         <v>45070</v>
       </c>
       <c r="B291" t="n">
-        <v>12.25017738342285</v>
+        <v>12.25017642974854</v>
       </c>
       <c r="C291" t="n">
-        <v>12.30212196315428</v>
+        <v>12.30212100543608</v>
       </c>
       <c r="D291" t="n">
-        <v>12.18091849420168</v>
+        <v>12.18091754591915</v>
       </c>
       <c r="E291" t="n">
-        <v>12.26749251854369</v>
+        <v>12.26749156352139</v>
       </c>
       <c r="F291" t="n">
         <v>1846000</v>
@@ -6252,16 +6252,16 @@
         <v>45071</v>
       </c>
       <c r="B292" t="n">
-        <v>12.29346370697021</v>
+        <v>12.29346466064453</v>
       </c>
       <c r="C292" t="n">
-        <v>12.39735203498263</v>
+        <v>12.39735299671616</v>
       </c>
       <c r="D292" t="n">
-        <v>12.20689051310872</v>
+        <v>12.20689146006706</v>
       </c>
       <c r="E292" t="n">
-        <v>12.28480613989475</v>
+        <v>12.28480709289745</v>
       </c>
       <c r="F292" t="n">
         <v>2204600</v>
@@ -6292,16 +6292,16 @@
         <v>45075</v>
       </c>
       <c r="B294" t="n">
-        <v>12.28480625152588</v>
+        <v>12.28480529785156</v>
       </c>
       <c r="C294" t="n">
-        <v>12.34540839597375</v>
+        <v>12.34540743759487</v>
       </c>
       <c r="D294" t="n">
-        <v>12.16360361389222</v>
+        <v>12.16360266962691</v>
       </c>
       <c r="E294" t="n">
-        <v>12.16360361389222</v>
+        <v>12.16360266962691</v>
       </c>
       <c r="F294" t="n">
         <v>1431900</v>
@@ -6352,16 +6352,16 @@
         <v>45078</v>
       </c>
       <c r="B297" t="n">
-        <v>12.2415189743042</v>
+        <v>12.24151992797852</v>
       </c>
       <c r="C297" t="n">
-        <v>12.30212028771158</v>
+        <v>12.30212124610704</v>
       </c>
       <c r="D297" t="n">
-        <v>12.16360252813415</v>
+        <v>12.1636034757384</v>
       </c>
       <c r="E297" t="n">
-        <v>12.26749084781722</v>
+        <v>12.26749180351488</v>
       </c>
       <c r="F297" t="n">
         <v>2308800</v>
@@ -6372,16 +6372,16 @@
         <v>45079</v>
       </c>
       <c r="B298" t="n">
-        <v>12.17226219177246</v>
+        <v>12.17226123809814</v>
       </c>
       <c r="C298" t="n">
-        <v>12.33675185320416</v>
+        <v>12.33675088664238</v>
       </c>
       <c r="D298" t="n">
-        <v>12.07703059643153</v>
+        <v>12.07702965021844</v>
       </c>
       <c r="E298" t="n">
-        <v>12.31077997521623</v>
+        <v>12.3107790106893</v>
       </c>
       <c r="F298" t="n">
         <v>5725100</v>
@@ -6412,16 +6412,16 @@
         <v>45083</v>
       </c>
       <c r="B300" t="n">
-        <v>12.32809257507324</v>
+        <v>12.32809352874756</v>
       </c>
       <c r="C300" t="n">
-        <v>12.41466659053087</v>
+        <v>12.41466755090237</v>
       </c>
       <c r="D300" t="n">
-        <v>12.07702892100332</v>
+        <v>12.0770298552559</v>
       </c>
       <c r="E300" t="n">
-        <v>12.08568648767528</v>
+        <v>12.08568742259759</v>
       </c>
       <c r="F300" t="n">
         <v>7376500</v>
@@ -6432,16 +6432,16 @@
         <v>45084</v>
       </c>
       <c r="B301" t="n">
-        <v>12.22420406341553</v>
+        <v>12.22420597076416</v>
       </c>
       <c r="C301" t="n">
-        <v>12.46661014707579</v>
+        <v>12.46661209224716</v>
       </c>
       <c r="D301" t="n">
-        <v>12.21554649687706</v>
+        <v>12.21554840287484</v>
       </c>
       <c r="E301" t="n">
-        <v>12.38003695858405</v>
+        <v>12.38003889024736</v>
       </c>
       <c r="F301" t="n">
         <v>3154600</v>
@@ -6472,16 +6472,16 @@
         <v>45089</v>
       </c>
       <c r="B303" t="n">
-        <v>12.45795440673828</v>
+        <v>12.45795345306396</v>
       </c>
       <c r="C303" t="n">
-        <v>12.45795440673828</v>
+        <v>12.45795345306396</v>
       </c>
       <c r="D303" t="n">
-        <v>12.25883448851593</v>
+        <v>12.25883355008453</v>
       </c>
       <c r="E303" t="n">
-        <v>12.3800379528961</v>
+        <v>12.3800370051864</v>
       </c>
       <c r="F303" t="n">
         <v>2572800</v>
@@ -6552,16 +6552,16 @@
         <v>45093</v>
       </c>
       <c r="B307" t="n">
-        <v>12.62244415283203</v>
+        <v>12.62244319915771</v>
       </c>
       <c r="C307" t="n">
-        <v>12.83022081425066</v>
+        <v>12.83021984487801</v>
       </c>
       <c r="D307" t="n">
-        <v>12.44063936768297</v>
+        <v>12.4406384277447</v>
       </c>
       <c r="E307" t="n">
-        <v>12.46661124395253</v>
+        <v>12.46661030205199</v>
       </c>
       <c r="F307" t="n">
         <v>5319000</v>
@@ -6572,16 +6572,16 @@
         <v>45096</v>
       </c>
       <c r="B308" t="n">
-        <v>12.6137866973877</v>
+        <v>12.61378574371338</v>
       </c>
       <c r="C308" t="n">
-        <v>12.80424905152594</v>
+        <v>12.80424808345158</v>
       </c>
       <c r="D308" t="n">
-        <v>12.38869572500366</v>
+        <v>12.38869478834751</v>
       </c>
       <c r="E308" t="n">
-        <v>12.80424905152594</v>
+        <v>12.80424808345158</v>
       </c>
       <c r="F308" t="n">
         <v>3301400</v>
@@ -6592,16 +6592,16 @@
         <v>45097</v>
       </c>
       <c r="B309" t="n">
-        <v>12.72633266448975</v>
+        <v>12.72633171081543</v>
       </c>
       <c r="C309" t="n">
-        <v>12.89947988480048</v>
+        <v>12.89947891815102</v>
       </c>
       <c r="D309" t="n">
-        <v>12.64841620894215</v>
+        <v>12.64841526110666</v>
       </c>
       <c r="E309" t="n">
-        <v>12.6917032204276</v>
+        <v>12.69170226934831</v>
       </c>
       <c r="F309" t="n">
         <v>3568000</v>
@@ -6612,16 +6612,16 @@
         <v>45098</v>
       </c>
       <c r="B310" t="n">
-        <v>12.86485004425049</v>
+        <v>12.86484909057617</v>
       </c>
       <c r="C310" t="n">
-        <v>12.90813705440186</v>
+        <v>12.90813609751867</v>
       </c>
       <c r="D310" t="n">
-        <v>12.63975907759925</v>
+        <v>12.63975814061098</v>
       </c>
       <c r="E310" t="n">
-        <v>12.75230414810935</v>
+        <v>12.75230320277808</v>
       </c>
       <c r="F310" t="n">
         <v>5022600</v>
@@ -6652,16 +6652,16 @@
         <v>45100</v>
       </c>
       <c r="B312" t="n">
-        <v>12.9427661895752</v>
+        <v>12.94276714324951</v>
       </c>
       <c r="C312" t="n">
-        <v>13.07262721694078</v>
+        <v>13.07262818018377</v>
       </c>
       <c r="D312" t="n">
-        <v>12.7609614117682</v>
+        <v>12.76096235204642</v>
       </c>
       <c r="E312" t="n">
-        <v>12.81290598784064</v>
+        <v>12.81290693194634</v>
       </c>
       <c r="F312" t="n">
         <v>2959500</v>
@@ -6672,16 +6672,16 @@
         <v>45103</v>
       </c>
       <c r="B313" t="n">
-        <v>12.71767425537109</v>
+        <v>12.71767520904541</v>
       </c>
       <c r="C313" t="n">
-        <v>13.01202492323384</v>
+        <v>13.01202589898095</v>
       </c>
       <c r="D313" t="n">
-        <v>12.66573050553121</v>
+        <v>12.66573145531036</v>
       </c>
       <c r="E313" t="n">
-        <v>12.94276603969331</v>
+        <v>12.94276701024684</v>
       </c>
       <c r="F313" t="n">
         <v>2677600</v>
@@ -6692,16 +6692,16 @@
         <v>45104</v>
       </c>
       <c r="B314" t="n">
-        <v>12.50123977661133</v>
+        <v>12.50124073028564</v>
       </c>
       <c r="C314" t="n">
-        <v>12.83887744603771</v>
+        <v>12.83887842546918</v>
       </c>
       <c r="D314" t="n">
-        <v>12.3973514534719</v>
+        <v>12.39735239922096</v>
       </c>
       <c r="E314" t="n">
-        <v>12.76961856394476</v>
+        <v>12.76961953809272</v>
       </c>
       <c r="F314" t="n">
         <v>3014700</v>
@@ -6792,16 +6792,16 @@
         <v>45111</v>
       </c>
       <c r="B319" t="n">
-        <v>12.34540748596191</v>
+        <v>12.34540843963623</v>
       </c>
       <c r="C319" t="n">
-        <v>12.40600880031166</v>
+        <v>12.40600975866739</v>
       </c>
       <c r="D319" t="n">
-        <v>12.23286159814739</v>
+        <v>12.23286254312761</v>
       </c>
       <c r="E319" t="n">
-        <v>12.38869449291073</v>
+        <v>12.38869544992894</v>
       </c>
       <c r="F319" t="n">
         <v>2230100</v>
@@ -6832,16 +6832,16 @@
         <v>45113</v>
       </c>
       <c r="B321" t="n">
-        <v>12.32809257507324</v>
+        <v>12.32809352874756</v>
       </c>
       <c r="C321" t="n">
-        <v>12.48392547264458</v>
+        <v>12.48392643837378</v>
       </c>
       <c r="D321" t="n">
-        <v>12.25017612628758</v>
+        <v>12.25017707393445</v>
       </c>
       <c r="E321" t="n">
-        <v>12.4319808982438</v>
+        <v>12.43198185995469</v>
       </c>
       <c r="F321" t="n">
         <v>2081000</v>
@@ -6852,16 +6852,16 @@
         <v>45114</v>
       </c>
       <c r="B322" t="n">
-        <v>12.34540748596191</v>
+        <v>12.34540843963623</v>
       </c>
       <c r="C322" t="n">
-        <v>12.48392524769333</v>
+        <v>12.48392621206805</v>
       </c>
       <c r="D322" t="n">
-        <v>12.25883347206429</v>
+        <v>12.25883441905082</v>
       </c>
       <c r="E322" t="n">
-        <v>12.42332393334358</v>
+        <v>12.42332489303689</v>
       </c>
       <c r="F322" t="n">
         <v>2149700</v>
@@ -6892,16 +6892,16 @@
         <v>45118</v>
       </c>
       <c r="B324" t="n">
-        <v>12.34540748596191</v>
+        <v>12.34540843963623</v>
       </c>
       <c r="C324" t="n">
-        <v>12.3973512337957</v>
+        <v>12.39735219148264</v>
       </c>
       <c r="D324" t="n">
-        <v>12.23286159814739</v>
+        <v>12.23286254312761</v>
       </c>
       <c r="E324" t="n">
-        <v>12.38869449291073</v>
+        <v>12.38869544992894</v>
       </c>
       <c r="F324" t="n">
         <v>1919200</v>
@@ -7072,16 +7072,16 @@
         <v>45131</v>
       </c>
       <c r="B333" t="n">
-        <v>12.34540748596191</v>
+        <v>12.34540843963623</v>
       </c>
       <c r="C333" t="n">
-        <v>12.42332393334358</v>
+        <v>12.42332489303689</v>
       </c>
       <c r="D333" t="n">
-        <v>12.31943478641403</v>
+        <v>12.31943573808198</v>
       </c>
       <c r="E333" t="n">
-        <v>12.42332393334358</v>
+        <v>12.42332489303689</v>
       </c>
       <c r="F333" t="n">
         <v>1347200</v>
@@ -7092,16 +7092,16 @@
         <v>45132</v>
       </c>
       <c r="B334" t="n">
-        <v>12.17226219177246</v>
+        <v>12.17226123809814</v>
       </c>
       <c r="C334" t="n">
-        <v>12.47526963664793</v>
+        <v>12.47526865923354</v>
       </c>
       <c r="D334" t="n">
-        <v>12.16360462389945</v>
+        <v>12.16360367090343</v>
       </c>
       <c r="E334" t="n">
-        <v>12.41466831279906</v>
+        <v>12.41466734013267</v>
       </c>
       <c r="F334" t="n">
         <v>2710400</v>
@@ -7132,16 +7132,16 @@
         <v>45134</v>
       </c>
       <c r="B336" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C336" t="n">
-        <v>12.22420541473304</v>
+        <v>12.22420445012837</v>
       </c>
       <c r="D336" t="n">
-        <v>12.03374305798708</v>
+        <v>12.03374210841168</v>
       </c>
       <c r="E336" t="n">
-        <v>12.18091840288654</v>
+        <v>12.18091744169762</v>
       </c>
       <c r="F336" t="n">
         <v>2852900</v>
@@ -7212,16 +7212,16 @@
         <v>45140</v>
       </c>
       <c r="B340" t="n">
-        <v>12.22420406341553</v>
+        <v>12.22420597076416</v>
       </c>
       <c r="C340" t="n">
-        <v>12.232861629954</v>
+        <v>12.23286353865348</v>
       </c>
       <c r="D340" t="n">
-        <v>12.12897330838532</v>
+        <v>12.12897520087505</v>
       </c>
       <c r="E340" t="n">
-        <v>12.13763087492379</v>
+        <v>12.13763276876436</v>
       </c>
       <c r="F340" t="n">
         <v>1697600</v>
@@ -7292,16 +7292,16 @@
         <v>45146</v>
       </c>
       <c r="B344" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C344" t="n">
-        <v>12.15494652603107</v>
+        <v>12.15494556689158</v>
       </c>
       <c r="D344" t="n">
-        <v>11.92985472493413</v>
+        <v>11.92985378355649</v>
       </c>
       <c r="E344" t="n">
-        <v>11.99045687177166</v>
+        <v>11.99045592561195</v>
       </c>
       <c r="F344" t="n">
         <v>2176400</v>
@@ -7332,16 +7332,16 @@
         <v>45148</v>
       </c>
       <c r="B346" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C346" t="n">
-        <v>12.09434452900206</v>
+        <v>12.09434549372545</v>
       </c>
       <c r="D346" t="n">
-        <v>11.88656704887551</v>
+        <v>11.88656799702522</v>
       </c>
       <c r="E346" t="n">
-        <v>12.01642807715848</v>
+        <v>12.01642903566675</v>
       </c>
       <c r="F346" t="n">
         <v>2835300</v>
@@ -7352,16 +7352,16 @@
         <v>45149</v>
       </c>
       <c r="B347" t="n">
-        <v>11.92119693756104</v>
+        <v>11.92119789123535</v>
       </c>
       <c r="C347" t="n">
-        <v>11.97314068671642</v>
+        <v>11.97314164454614</v>
       </c>
       <c r="D347" t="n">
-        <v>11.83462292146072</v>
+        <v>11.83462386820927</v>
       </c>
       <c r="E347" t="n">
-        <v>11.97314068671642</v>
+        <v>11.97314164454614</v>
       </c>
       <c r="F347" t="n">
         <v>2472600</v>
@@ -7372,16 +7372,16 @@
         <v>45152</v>
       </c>
       <c r="B348" t="n">
-        <v>11.91254043579102</v>
+        <v>11.9125394821167</v>
       </c>
       <c r="C348" t="n">
-        <v>11.96448418959011</v>
+        <v>11.96448323175737</v>
       </c>
       <c r="D348" t="n">
-        <v>11.82596641195109</v>
+        <v>11.82596546520757</v>
       </c>
       <c r="E348" t="n">
-        <v>11.92119800330122</v>
+        <v>11.92119704893382</v>
       </c>
       <c r="F348" t="n">
         <v>1369900</v>
@@ -7392,16 +7392,16 @@
         <v>45153</v>
       </c>
       <c r="B349" t="n">
-        <v>11.860595703125</v>
+        <v>11.86059474945068</v>
       </c>
       <c r="C349" t="n">
-        <v>11.99911347897441</v>
+        <v>11.9991125141623</v>
       </c>
       <c r="D349" t="n">
-        <v>11.85193813572664</v>
+        <v>11.85193718274846</v>
       </c>
       <c r="E349" t="n">
-        <v>11.91254028188406</v>
+        <v>11.91253932403304</v>
       </c>
       <c r="F349" t="n">
         <v>2713800</v>
@@ -7412,16 +7412,16 @@
         <v>45154</v>
       </c>
       <c r="B350" t="n">
-        <v>11.6874475479126</v>
+        <v>11.68744850158691</v>
       </c>
       <c r="C350" t="n">
-        <v>11.91253932846828</v>
+        <v>11.91254030050967</v>
       </c>
       <c r="D350" t="n">
-        <v>11.64416054001635</v>
+        <v>11.64416149015853</v>
       </c>
       <c r="E350" t="n">
-        <v>11.88656662835193</v>
+        <v>11.886567598274</v>
       </c>
       <c r="F350" t="n">
         <v>3946200</v>
@@ -7432,16 +7432,16 @@
         <v>45155</v>
       </c>
       <c r="B351" t="n">
-        <v>11.71341991424561</v>
+        <v>11.71342086791992</v>
       </c>
       <c r="C351" t="n">
-        <v>11.78267879953539</v>
+        <v>11.78267975884857</v>
       </c>
       <c r="D351" t="n">
-        <v>11.66147616309379</v>
+        <v>11.66147711253899</v>
       </c>
       <c r="E351" t="n">
-        <v>11.73073504838357</v>
+        <v>11.73073600346764</v>
       </c>
       <c r="F351" t="n">
         <v>2345000</v>
@@ -7452,16 +7452,16 @@
         <v>45156</v>
       </c>
       <c r="B352" t="n">
-        <v>11.77402210235596</v>
+        <v>11.77402114868164</v>
       </c>
       <c r="C352" t="n">
-        <v>11.80865154513102</v>
+        <v>11.80865058865178</v>
       </c>
       <c r="D352" t="n">
-        <v>11.65281863982772</v>
+        <v>11.65281769597066</v>
       </c>
       <c r="E352" t="n">
-        <v>11.71341995827632</v>
+        <v>11.71341900951066</v>
       </c>
       <c r="F352" t="n">
         <v>3061800</v>
@@ -7492,16 +7492,16 @@
         <v>45160</v>
       </c>
       <c r="B354" t="n">
-        <v>11.79999351501465</v>
+        <v>11.79999446868896</v>
       </c>
       <c r="C354" t="n">
-        <v>11.86925239784715</v>
+        <v>11.86925335711897</v>
       </c>
       <c r="D354" t="n">
-        <v>11.73073463218214</v>
+        <v>11.73073558025896</v>
       </c>
       <c r="E354" t="n">
-        <v>11.79133594825283</v>
+        <v>11.79133690122745</v>
       </c>
       <c r="F354" t="n">
         <v>2231700</v>
@@ -7512,16 +7512,16 @@
         <v>45161</v>
       </c>
       <c r="B355" t="n">
-        <v>11.87791061401367</v>
+        <v>11.87790966033936</v>
       </c>
       <c r="C355" t="n">
-        <v>11.89522492285292</v>
+        <v>11.89522396778845</v>
       </c>
       <c r="D355" t="n">
-        <v>11.79133659292425</v>
+        <v>11.79133564620093</v>
       </c>
       <c r="E355" t="n">
-        <v>11.86059547954337</v>
+        <v>11.86059452725928</v>
       </c>
       <c r="F355" t="n">
         <v>2615000</v>
@@ -7532,16 +7532,16 @@
         <v>45162</v>
       </c>
       <c r="B356" t="n">
-        <v>11.97314167022705</v>
+        <v>11.97314071655273</v>
       </c>
       <c r="C356" t="n">
-        <v>11.99911354693815</v>
+        <v>11.99911259119515</v>
       </c>
       <c r="D356" t="n">
-        <v>11.89522521446267</v>
+        <v>11.89522426699448</v>
       </c>
       <c r="E356" t="n">
-        <v>11.90388278191006</v>
+        <v>11.90388183375229</v>
       </c>
       <c r="F356" t="n">
         <v>2322800</v>
@@ -7612,16 +7612,16 @@
         <v>45168</v>
       </c>
       <c r="B360" t="n">
-        <v>12.11165809631348</v>
+        <v>12.11165904998779</v>
       </c>
       <c r="C360" t="n">
-        <v>12.19823210987155</v>
+        <v>12.19823307036272</v>
       </c>
       <c r="D360" t="n">
-        <v>12.05971434868342</v>
+        <v>12.05971529826767</v>
       </c>
       <c r="E360" t="n">
-        <v>12.17226023605652</v>
+        <v>12.17226119450266</v>
       </c>
       <c r="F360" t="n">
         <v>1998700</v>
@@ -7652,16 +7652,16 @@
         <v>45170</v>
       </c>
       <c r="B362" t="n">
-        <v>12.04240036010742</v>
+        <v>12.04239940643311</v>
       </c>
       <c r="C362" t="n">
-        <v>12.04240036010742</v>
+        <v>12.04239940643311</v>
       </c>
       <c r="D362" t="n">
-        <v>11.89522501845123</v>
+        <v>11.89522407643217</v>
       </c>
       <c r="E362" t="n">
-        <v>11.90388258575596</v>
+        <v>11.90388164305129</v>
       </c>
       <c r="F362" t="n">
         <v>3740800</v>
@@ -7692,16 +7692,16 @@
         <v>45174</v>
       </c>
       <c r="B364" t="n">
-        <v>11.92119693756104</v>
+        <v>11.92119789123535</v>
       </c>
       <c r="C364" t="n">
-        <v>12.06837144392197</v>
+        <v>12.06837240936998</v>
       </c>
       <c r="D364" t="n">
-        <v>11.9125393708248</v>
+        <v>11.91254032380653</v>
       </c>
       <c r="E364" t="n">
-        <v>12.04239956934427</v>
+        <v>12.04240053271458</v>
       </c>
       <c r="F364" t="n">
         <v>3869600</v>
@@ -7712,16 +7712,16 @@
         <v>45175</v>
       </c>
       <c r="B365" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C365" t="n">
-        <v>12.02508564417022</v>
+        <v>12.02508660336907</v>
       </c>
       <c r="D365" t="n">
-        <v>11.81730816404367</v>
+        <v>11.81730910666884</v>
       </c>
       <c r="E365" t="n">
-        <v>11.9385116253149</v>
+        <v>11.93851257760805</v>
       </c>
       <c r="F365" t="n">
         <v>2473500</v>
@@ -7732,16 +7732,16 @@
         <v>45177</v>
       </c>
       <c r="B366" t="n">
-        <v>11.92985439300537</v>
+        <v>11.92985343933105</v>
       </c>
       <c r="C366" t="n">
-        <v>12.07702973380992</v>
+        <v>12.07702876837038</v>
       </c>
       <c r="D366" t="n">
-        <v>11.88656738236326</v>
+        <v>11.88656643214931</v>
       </c>
       <c r="E366" t="n">
-        <v>11.93851196026</v>
+        <v>11.9385110058936</v>
       </c>
       <c r="F366" t="n">
         <v>3462800</v>
@@ -7812,16 +7812,16 @@
         <v>45183</v>
       </c>
       <c r="B370" t="n">
-        <v>12.21554756164551</v>
+        <v>12.21554660797119</v>
       </c>
       <c r="C370" t="n">
-        <v>12.25017700518688</v>
+        <v>12.25017604880902</v>
       </c>
       <c r="D370" t="n">
-        <v>12.09434492206624</v>
+        <v>12.09434397785428</v>
       </c>
       <c r="E370" t="n">
-        <v>12.09434492206624</v>
+        <v>12.09434397785428</v>
       </c>
       <c r="F370" t="n">
         <v>2498700</v>
@@ -7852,16 +7852,16 @@
         <v>45187</v>
       </c>
       <c r="B372" t="n">
-        <v>12.05971622467041</v>
+        <v>12.05971527099609</v>
       </c>
       <c r="C372" t="n">
-        <v>12.2415210209188</v>
+        <v>12.24152005286748</v>
       </c>
       <c r="D372" t="n">
-        <v>11.99911407550021</v>
+        <v>11.99911312661827</v>
       </c>
       <c r="E372" t="n">
-        <v>12.21554831743252</v>
+        <v>12.21554735143511</v>
       </c>
       <c r="F372" t="n">
         <v>3188500</v>
@@ -7912,16 +7912,16 @@
         <v>45190</v>
       </c>
       <c r="B375" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C375" t="n">
-        <v>12.03374238555092</v>
+        <v>12.0337433454403</v>
       </c>
       <c r="D375" t="n">
-        <v>11.8779103074948</v>
+        <v>11.877911254954</v>
       </c>
       <c r="E375" t="n">
-        <v>12.02508564417022</v>
+        <v>12.02508660336907</v>
       </c>
       <c r="F375" t="n">
         <v>4405700</v>
@@ -7932,16 +7932,16 @@
         <v>45191</v>
       </c>
       <c r="B376" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C376" t="n">
-        <v>12.10300127038276</v>
+        <v>12.10300223579667</v>
       </c>
       <c r="D376" t="n">
-        <v>11.92985405830317</v>
+        <v>11.92985500990573</v>
       </c>
       <c r="E376" t="n">
-        <v>12.02508564417022</v>
+        <v>12.02508660336907</v>
       </c>
       <c r="F376" t="n">
         <v>2812600</v>
@@ -7952,16 +7952,16 @@
         <v>45194</v>
       </c>
       <c r="B377" t="n">
-        <v>11.8086519241333</v>
+        <v>11.80865097045898</v>
       </c>
       <c r="C377" t="n">
-        <v>11.97314157618643</v>
+        <v>11.97314060922783</v>
       </c>
       <c r="D377" t="n">
-        <v>11.8086519241333</v>
+        <v>11.80865097045898</v>
       </c>
       <c r="E377" t="n">
-        <v>11.95582726705872</v>
+        <v>11.95582630149842</v>
       </c>
       <c r="F377" t="n">
         <v>3691700</v>
@@ -7972,16 +7972,16 @@
         <v>45195</v>
       </c>
       <c r="B378" t="n">
-        <v>11.83462238311768</v>
+        <v>11.83462333679199</v>
       </c>
       <c r="C378" t="n">
-        <v>12.06837089494598</v>
+        <v>12.06837186745655</v>
       </c>
       <c r="D378" t="n">
-        <v>11.78267781069418</v>
+        <v>11.78267876018263</v>
       </c>
       <c r="E378" t="n">
-        <v>11.80865050972141</v>
+        <v>11.80865146130283</v>
       </c>
       <c r="F378" t="n">
         <v>7795500</v>
@@ -8072,16 +8072,16 @@
         <v>45202</v>
       </c>
       <c r="B383" t="n">
-        <v>11.8086519241333</v>
+        <v>11.80865097045898</v>
       </c>
       <c r="C383" t="n">
-        <v>11.91254025579282</v>
+        <v>11.91253929372841</v>
       </c>
       <c r="D383" t="n">
-        <v>11.75670734548801</v>
+        <v>11.75670639600877</v>
       </c>
       <c r="E383" t="n">
-        <v>11.86059567714752</v>
+        <v>11.8605947192782</v>
       </c>
       <c r="F383" t="n">
         <v>2809600</v>
@@ -8092,16 +8092,16 @@
         <v>45203</v>
       </c>
       <c r="B384" t="n">
-        <v>11.77402210235596</v>
+        <v>11.77402114868164</v>
       </c>
       <c r="C384" t="n">
-        <v>11.86059529647809</v>
+        <v>11.86059433579151</v>
       </c>
       <c r="D384" t="n">
-        <v>11.74804940105138</v>
+        <v>11.7480484494808</v>
       </c>
       <c r="E384" t="n">
-        <v>11.80865154513102</v>
+        <v>11.80865058865178</v>
       </c>
       <c r="F384" t="n">
         <v>4367600</v>
@@ -8152,16 +8152,16 @@
         <v>45208</v>
       </c>
       <c r="B387" t="n">
-        <v>11.91254043579102</v>
+        <v>11.9125394821167</v>
       </c>
       <c r="C387" t="n">
-        <v>11.92985474518035</v>
+        <v>11.92985379011992</v>
       </c>
       <c r="D387" t="n">
-        <v>11.61818974549255</v>
+        <v>11.61818881538288</v>
       </c>
       <c r="E387" t="n">
-        <v>11.61818974549255</v>
+        <v>11.61818881538288</v>
       </c>
       <c r="F387" t="n">
         <v>4118900</v>
@@ -8172,16 +8172,16 @@
         <v>45209</v>
       </c>
       <c r="B388" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C388" t="n">
-        <v>12.16360409352659</v>
+        <v>12.16360313370393</v>
       </c>
       <c r="D388" t="n">
-        <v>11.91254041557417</v>
+        <v>11.9125394755628</v>
       </c>
       <c r="E388" t="n">
-        <v>11.92985472493413</v>
+        <v>11.92985378355649</v>
       </c>
       <c r="F388" t="n">
         <v>3643400</v>
@@ -8192,16 +8192,16 @@
         <v>45210</v>
       </c>
       <c r="B389" t="n">
-        <v>12.09434413909912</v>
+        <v>12.09434509277344</v>
       </c>
       <c r="C389" t="n">
-        <v>12.18957489626505</v>
+        <v>12.18957585744859</v>
       </c>
       <c r="D389" t="n">
-        <v>12.00777012303482</v>
+        <v>12.00777106988252</v>
       </c>
       <c r="E389" t="n">
-        <v>12.09434413909912</v>
+        <v>12.09434509277344</v>
       </c>
       <c r="F389" t="n">
         <v>3458500</v>
@@ -8212,16 +8212,16 @@
         <v>45212</v>
       </c>
       <c r="B390" t="n">
-        <v>12.02508544921875</v>
+        <v>12.02508640289307</v>
       </c>
       <c r="C390" t="n">
-        <v>12.19823265849127</v>
+        <v>12.19823362589739</v>
       </c>
       <c r="D390" t="n">
-        <v>12.02508544921875</v>
+        <v>12.02508640289307</v>
       </c>
       <c r="E390" t="n">
-        <v>12.09434433292776</v>
+        <v>12.0943452920948</v>
       </c>
       <c r="F390" t="n">
         <v>4555500</v>
@@ -8232,16 +8232,16 @@
         <v>45215</v>
       </c>
       <c r="B391" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="C391" t="n">
-        <v>12.12031593631109</v>
+        <v>12.12031690101054</v>
       </c>
       <c r="D391" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="E391" t="n">
-        <v>12.05971462083146</v>
+        <v>12.05971558070743</v>
       </c>
       <c r="F391" t="n">
         <v>3983600</v>
@@ -8252,16 +8252,16 @@
         <v>45216</v>
       </c>
       <c r="B392" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C392" t="n">
-        <v>12.10300127038276</v>
+        <v>12.10300223579667</v>
       </c>
       <c r="D392" t="n">
-        <v>11.88656704887551</v>
+        <v>11.88656799702522</v>
       </c>
       <c r="E392" t="n">
-        <v>11.97314106773082</v>
+        <v>11.97314202278624</v>
       </c>
       <c r="F392" t="n">
         <v>5165000</v>
@@ -8312,16 +8312,16 @@
         <v>45219</v>
       </c>
       <c r="B395" t="n">
-        <v>11.76536560058594</v>
+        <v>11.76536464691162</v>
       </c>
       <c r="C395" t="n">
-        <v>11.91254095211416</v>
+        <v>11.91253998651014</v>
       </c>
       <c r="D395" t="n">
-        <v>11.67013400510819</v>
+        <v>11.67013305915314</v>
       </c>
       <c r="E395" t="n">
-        <v>11.67013400510819</v>
+        <v>11.67013305915314</v>
       </c>
       <c r="F395" t="n">
         <v>6261200</v>
@@ -8352,16 +8352,16 @@
         <v>45223</v>
       </c>
       <c r="B397" t="n">
-        <v>11.6355037689209</v>
+        <v>11.63550281524658</v>
       </c>
       <c r="C397" t="n">
-        <v>11.81730855401174</v>
+        <v>11.81730758543626</v>
       </c>
       <c r="D397" t="n">
-        <v>11.54893057283972</v>
+        <v>11.54892962626116</v>
       </c>
       <c r="E397" t="n">
-        <v>11.80865181234537</v>
+        <v>11.80865084447942</v>
       </c>
       <c r="F397" t="n">
         <v>3637500</v>
@@ -8512,16 +8512,16 @@
         <v>45236</v>
       </c>
       <c r="B405" t="n">
-        <v>12.02508544921875</v>
+        <v>12.02508640289307</v>
       </c>
       <c r="C405" t="n">
-        <v>12.077029199185</v>
+        <v>12.07703015697882</v>
       </c>
       <c r="D405" t="n">
-        <v>11.8173079724607</v>
+        <v>11.81730890965679</v>
       </c>
       <c r="E405" t="n">
-        <v>11.94716899863836</v>
+        <v>11.94716994613335</v>
       </c>
       <c r="F405" t="n">
         <v>2982900</v>
@@ -8552,16 +8552,16 @@
         <v>45238</v>
       </c>
       <c r="B407" t="n">
-        <v>11.817307472229</v>
+        <v>11.81730842590332</v>
       </c>
       <c r="C407" t="n">
-        <v>11.96448280028841</v>
+        <v>11.96448376583999</v>
       </c>
       <c r="D407" t="n">
-        <v>11.73073428407293</v>
+        <v>11.73073523076066</v>
       </c>
       <c r="E407" t="n">
-        <v>11.93851092640469</v>
+        <v>11.9385118898603</v>
       </c>
       <c r="F407" t="n">
         <v>5488500</v>
@@ -8652,16 +8652,16 @@
         <v>45246</v>
       </c>
       <c r="B412" t="n">
-        <v>12.49258422851562</v>
+        <v>12.49258327484131</v>
       </c>
       <c r="C412" t="n">
-        <v>12.49258422851562</v>
+        <v>12.49258327484131</v>
       </c>
       <c r="D412" t="n">
-        <v>12.12897464999031</v>
+        <v>12.12897372407367</v>
       </c>
       <c r="E412" t="n">
-        <v>12.12897464999031</v>
+        <v>12.12897372407367</v>
       </c>
       <c r="F412" t="n">
         <v>6741500</v>
@@ -8672,16 +8672,16 @@
         <v>45247</v>
       </c>
       <c r="B413" t="n">
-        <v>12.25017738342285</v>
+        <v>12.25017642974854</v>
       </c>
       <c r="C413" t="n">
-        <v>12.48392675376763</v>
+        <v>12.48392578189597</v>
       </c>
       <c r="D413" t="n">
-        <v>12.14628904959109</v>
+        <v>12.14628810400446</v>
       </c>
       <c r="E413" t="n">
-        <v>12.48392675376763</v>
+        <v>12.48392578189597</v>
       </c>
       <c r="F413" t="n">
         <v>3124800</v>
@@ -8692,16 +8692,16 @@
         <v>45250</v>
       </c>
       <c r="B414" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C414" t="n">
-        <v>12.23286298222856</v>
+        <v>12.23286201694073</v>
       </c>
       <c r="D414" t="n">
-        <v>11.99045687177166</v>
+        <v>11.99045592561195</v>
       </c>
       <c r="E414" t="n">
-        <v>12.20689110537309</v>
+        <v>12.20689014213468</v>
       </c>
       <c r="F414" t="n">
         <v>3248400</v>
@@ -8712,16 +8712,16 @@
         <v>45251</v>
       </c>
       <c r="B415" t="n">
-        <v>11.97314167022705</v>
+        <v>11.97314071655273</v>
       </c>
       <c r="C415" t="n">
-        <v>12.09434513759732</v>
+        <v>12.09434417426901</v>
       </c>
       <c r="D415" t="n">
-        <v>11.91254034935745</v>
+        <v>11.9125394005101</v>
       </c>
       <c r="E415" t="n">
-        <v>12.08568757014993</v>
+        <v>12.0856866075112</v>
       </c>
       <c r="F415" t="n">
         <v>2713400</v>
@@ -8752,16 +8752,16 @@
         <v>45253</v>
       </c>
       <c r="B417" t="n">
-        <v>12.561842918396</v>
+        <v>12.56184196472168</v>
       </c>
       <c r="C417" t="n">
-        <v>12.76961958122722</v>
+        <v>12.76961861177884</v>
       </c>
       <c r="D417" t="n">
-        <v>12.46661132870839</v>
+        <v>12.46661038226389</v>
       </c>
       <c r="E417" t="n">
-        <v>12.76961958122722</v>
+        <v>12.76961861177884</v>
       </c>
       <c r="F417" t="n">
         <v>9122900</v>
@@ -8832,16 +8832,16 @@
         <v>45259</v>
       </c>
       <c r="B421" t="n">
-        <v>12.561842918396</v>
+        <v>12.56184196472168</v>
       </c>
       <c r="C421" t="n">
-        <v>12.75230444650908</v>
+        <v>12.75230347837524</v>
       </c>
       <c r="D421" t="n">
-        <v>12.561842918396</v>
+        <v>12.56184196472168</v>
       </c>
       <c r="E421" t="n">
-        <v>12.72633257006295</v>
+        <v>12.72633160390085</v>
       </c>
       <c r="F421" t="n">
         <v>5869600</v>
@@ -8852,16 +8852,16 @@
         <v>45260</v>
       </c>
       <c r="B422" t="n">
-        <v>12.71767425537109</v>
+        <v>12.71767520904541</v>
       </c>
       <c r="C422" t="n">
-        <v>12.71767425537109</v>
+        <v>12.71767520904541</v>
       </c>
       <c r="D422" t="n">
-        <v>12.58781405514036</v>
+        <v>12.58781499907671</v>
       </c>
       <c r="E422" t="n">
-        <v>12.63110106376094</v>
+        <v>12.6311020109433</v>
       </c>
       <c r="F422" t="n">
         <v>4162000</v>
@@ -8872,16 +8872,16 @@
         <v>45261</v>
       </c>
       <c r="B423" t="n">
-        <v>12.86485004425049</v>
+        <v>12.86484909057617</v>
       </c>
       <c r="C423" t="n">
-        <v>12.96873837323515</v>
+        <v>12.96873741185957</v>
       </c>
       <c r="D423" t="n">
-        <v>12.70901796358902</v>
+        <v>12.70901702146657</v>
       </c>
       <c r="E423" t="n">
-        <v>12.72633227227094</v>
+        <v>12.72633132886498</v>
       </c>
       <c r="F423" t="n">
         <v>6458300</v>
@@ -8892,16 +8892,16 @@
         <v>45264</v>
       </c>
       <c r="B424" t="n">
-        <v>12.89947986602783</v>
+        <v>12.89947891235352</v>
       </c>
       <c r="C424" t="n">
-        <v>12.98605388887275</v>
+        <v>12.98605292879791</v>
       </c>
       <c r="D424" t="n">
-        <v>12.86485042201608</v>
+        <v>12.86484947090196</v>
       </c>
       <c r="E424" t="n">
-        <v>12.94276687745029</v>
+        <v>12.94276592057571</v>
       </c>
       <c r="F424" t="n">
         <v>7048400</v>
@@ -8952,16 +8952,16 @@
         <v>45267</v>
       </c>
       <c r="B427" t="n">
-        <v>13.11591339111328</v>
+        <v>13.1159143447876</v>
       </c>
       <c r="C427" t="n">
-        <v>13.15054283325996</v>
+        <v>13.15054378945223</v>
       </c>
       <c r="D427" t="n">
-        <v>12.97739562252655</v>
+        <v>12.97739656612907</v>
       </c>
       <c r="E427" t="n">
-        <v>13.10725664979988</v>
+        <v>13.10725760284475</v>
       </c>
       <c r="F427" t="n">
         <v>6196000</v>
@@ -8972,16 +8972,16 @@
         <v>45268</v>
       </c>
       <c r="B428" t="n">
-        <v>12.92545127868652</v>
+        <v>12.92545223236084</v>
       </c>
       <c r="C428" t="n">
-        <v>13.15919979603697</v>
+        <v>13.15920076695787</v>
       </c>
       <c r="D428" t="n">
-        <v>12.86484913848894</v>
+        <v>12.86485008769187</v>
       </c>
       <c r="E428" t="n">
-        <v>13.15919979603697</v>
+        <v>13.15920076695787</v>
       </c>
       <c r="F428" t="n">
         <v>10990100</v>
@@ -22149,42 +22149,82 @@
     </row>
     <row r="1087">
       <c r="A1087" s="1" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B1087" t="n">
+        <v>10.97999954223633</v>
+      </c>
+      <c r="C1087" t="n">
+        <v>11.27999973297119</v>
+      </c>
+      <c r="D1087" t="n">
+        <v>10.90999984741211</v>
+      </c>
+      <c r="E1087" t="n">
         <v>11.19999980926514</v>
       </c>
-      <c r="C1087" t="n">
-        <v>11.21000003814697</v>
-      </c>
-      <c r="D1087" t="n">
-        <v>10.84000015258789</v>
-      </c>
-      <c r="E1087" t="n">
-        <v>11.03999996185303</v>
-      </c>
       <c r="F1087" t="n">
-        <v>4621900</v>
+        <v>5442500</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B1088" t="n">
+        <v>11.19999980926514</v>
+      </c>
+      <c r="C1088" t="n">
+        <v>11.21000003814697</v>
+      </c>
+      <c r="D1088" t="n">
+        <v>10.84000015258789</v>
+      </c>
+      <c r="E1088" t="n">
+        <v>11.03999996185303</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>4621900</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="1" t="n">
         <v>46238</v>
       </c>
-      <c r="B1088" t="n">
-        <v>11.28</v>
-      </c>
-      <c r="C1088" t="n">
-        <v>11.57</v>
-      </c>
-      <c r="D1088" t="n">
-        <v>11.13</v>
-      </c>
-      <c r="E1088" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="F1088" t="n">
+      <c r="B1089" t="n">
+        <v>11.27999973297119</v>
+      </c>
+      <c r="C1089" t="n">
+        <v>11.56999969482422</v>
+      </c>
+      <c r="D1089" t="n">
+        <v>11.13000011444092</v>
+      </c>
+      <c r="E1089" t="n">
+        <v>11.32999992370605</v>
+      </c>
+      <c r="F1089" t="n">
         <v>4289500</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B1090" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="C1090" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="D1090" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="E1090" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="F1090" t="n">
+        <v>5192700</v>
       </c>
     </row>
   </sheetData>

--- a/database/AURE3.xlsx
+++ b/database/AURE3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1090"/>
+  <dimension ref="A1:F1091"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,16 +492,16 @@
         <v>44650</v>
       </c>
       <c r="B4" t="n">
-        <v>12.38385105133057</v>
+        <v>12.38384914398193</v>
       </c>
       <c r="C4" t="n">
-        <v>13.04504942238897</v>
+        <v>13.04504741320321</v>
       </c>
       <c r="D4" t="n">
-        <v>12.30606274584925</v>
+        <v>12.3060608504815</v>
       </c>
       <c r="E4" t="n">
-        <v>12.92836770601126</v>
+        <v>12.9283657147967</v>
       </c>
       <c r="F4" t="n">
         <v>4408600</v>
@@ -512,16 +512,16 @@
         <v>44651</v>
       </c>
       <c r="B5" t="n">
-        <v>12.43830108642578</v>
+        <v>12.4383020401001</v>
       </c>
       <c r="C5" t="n">
-        <v>12.82724108844168</v>
+        <v>12.82724207193696</v>
       </c>
       <c r="D5" t="n">
-        <v>12.05714006249281</v>
+        <v>12.05714098694259</v>
       </c>
       <c r="E5" t="n">
-        <v>12.4149648940212</v>
+        <v>12.41496584590627</v>
       </c>
       <c r="F5" t="n">
         <v>3876100</v>
@@ -552,16 +552,16 @@
         <v>44655</v>
       </c>
       <c r="B7" t="n">
-        <v>12.42274475097656</v>
+        <v>12.42274570465088</v>
       </c>
       <c r="C7" t="n">
-        <v>12.7338972197089</v>
+        <v>12.7338981972699</v>
       </c>
       <c r="D7" t="n">
-        <v>12.33717746969916</v>
+        <v>12.33717841680461</v>
       </c>
       <c r="E7" t="n">
-        <v>12.54720469988757</v>
+        <v>12.54720566311648</v>
       </c>
       <c r="F7" t="n">
         <v>2842400</v>
@@ -672,16 +672,16 @@
         <v>44663</v>
       </c>
       <c r="B13" t="n">
-        <v>12.2438325881958</v>
+        <v>12.24383163452148</v>
       </c>
       <c r="C13" t="n">
-        <v>12.64055161698694</v>
+        <v>12.64055063241211</v>
       </c>
       <c r="D13" t="n">
-        <v>12.2127174138893</v>
+        <v>12.21271646263855</v>
       </c>
       <c r="E13" t="n">
-        <v>12.48497500361014</v>
+        <v>12.4849740311532</v>
       </c>
       <c r="F13" t="n">
         <v>2267700</v>
@@ -692,16 +692,16 @@
         <v>44664</v>
       </c>
       <c r="B14" t="n">
-        <v>12.10381317138672</v>
+        <v>12.10381412506104</v>
       </c>
       <c r="C14" t="n">
-        <v>12.55498277187146</v>
+        <v>12.55498376109398</v>
       </c>
       <c r="D14" t="n">
-        <v>12.0882552152437</v>
+        <v>12.08825616769219</v>
       </c>
       <c r="E14" t="n">
-        <v>12.39162868343488</v>
+        <v>12.39162965978653</v>
       </c>
       <c r="F14" t="n">
         <v>4421300</v>
@@ -732,16 +732,16 @@
         <v>44669</v>
       </c>
       <c r="B16" t="n">
-        <v>12.45386123657227</v>
+        <v>12.45386028289795</v>
       </c>
       <c r="C16" t="n">
-        <v>12.45386123657227</v>
+        <v>12.45386028289795</v>
       </c>
       <c r="D16" t="n">
-        <v>11.92490250325453</v>
+        <v>11.92490159008608</v>
       </c>
       <c r="E16" t="n">
-        <v>12.10381532145966</v>
+        <v>12.10381439459067</v>
       </c>
       <c r="F16" t="n">
         <v>3931100</v>
@@ -752,16 +752,16 @@
         <v>44670</v>
       </c>
       <c r="B17" t="n">
-        <v>12.10381317138672</v>
+        <v>12.10381412506104</v>
       </c>
       <c r="C17" t="n">
-        <v>12.60165664030051</v>
+        <v>12.60165763320052</v>
       </c>
       <c r="D17" t="n">
-        <v>12.00268868198966</v>
+        <v>12.00268962769625</v>
       </c>
       <c r="E17" t="n">
-        <v>12.43830106817557</v>
+        <v>12.4383020482046</v>
       </c>
       <c r="F17" t="n">
         <v>3118100</v>
@@ -772,16 +772,16 @@
         <v>44671</v>
       </c>
       <c r="B18" t="n">
-        <v>12.0571403503418</v>
+        <v>12.05714130401611</v>
       </c>
       <c r="C18" t="n">
-        <v>12.2127162064935</v>
+        <v>12.21271717247328</v>
       </c>
       <c r="D18" t="n">
-        <v>11.95601585838214</v>
+        <v>11.95601680405789</v>
       </c>
       <c r="E18" t="n">
-        <v>12.07269830687907</v>
+        <v>12.07269926178396</v>
       </c>
       <c r="F18" t="n">
         <v>2798400</v>
@@ -832,16 +832,16 @@
         <v>44677</v>
       </c>
       <c r="B21" t="n">
-        <v>11.95601749420166</v>
+        <v>11.95601558685303</v>
       </c>
       <c r="C21" t="n">
-        <v>12.43830308518023</v>
+        <v>12.43830110089237</v>
       </c>
       <c r="D21" t="n">
-        <v>11.86267196773913</v>
+        <v>11.86267007528195</v>
       </c>
       <c r="E21" t="n">
-        <v>12.32940034189609</v>
+        <v>12.32939837498153</v>
       </c>
       <c r="F21" t="n">
         <v>2627000</v>
@@ -852,16 +852,16 @@
         <v>44678</v>
       </c>
       <c r="B22" t="n">
-        <v>12.0571403503418</v>
+        <v>12.05714130401611</v>
       </c>
       <c r="C22" t="n">
-        <v>12.06491932861043</v>
+        <v>12.06492028290003</v>
       </c>
       <c r="D22" t="n">
-        <v>11.83155517346078</v>
+        <v>11.83155610929216</v>
       </c>
       <c r="E22" t="n">
-        <v>12.04936137207316</v>
+        <v>12.04936232513219</v>
       </c>
       <c r="F22" t="n">
         <v>2401400</v>
@@ -932,16 +932,16 @@
         <v>44684</v>
       </c>
       <c r="B26" t="n">
-        <v>11.27148056030273</v>
+        <v>11.27148151397705</v>
       </c>
       <c r="C26" t="n">
-        <v>11.35704783157836</v>
+        <v>11.35704879249248</v>
       </c>
       <c r="D26" t="n">
-        <v>11.01478023016414</v>
+        <v>11.01478116211917</v>
       </c>
       <c r="E26" t="n">
-        <v>11.15479886181943</v>
+        <v>11.15479980562136</v>
       </c>
       <c r="F26" t="n">
         <v>1672900</v>
@@ -952,16 +952,16 @@
         <v>44685</v>
       </c>
       <c r="B27" t="n">
-        <v>11.69445705413818</v>
+        <v>11.69445610046387</v>
       </c>
       <c r="C27" t="n">
-        <v>11.69445705413818</v>
+        <v>11.69445610046387</v>
       </c>
       <c r="D27" t="n">
-        <v>11.03649687268372</v>
+        <v>11.03649597266557</v>
       </c>
       <c r="E27" t="n">
-        <v>11.2088199552074</v>
+        <v>11.20881904113643</v>
       </c>
       <c r="F27" t="n">
         <v>4400300</v>
@@ -992,16 +992,16 @@
         <v>44687</v>
       </c>
       <c r="B29" t="n">
-        <v>11.12265872955322</v>
+        <v>11.12265777587891</v>
       </c>
       <c r="C29" t="n">
-        <v>11.31064715104436</v>
+        <v>11.31064618125162</v>
       </c>
       <c r="D29" t="n">
-        <v>11.05216288474415</v>
+        <v>11.05216193711426</v>
       </c>
       <c r="E29" t="n">
-        <v>11.28714878510787</v>
+        <v>11.28714781732991</v>
       </c>
       <c r="F29" t="n">
         <v>2813300</v>
@@ -1012,16 +1012,16 @@
         <v>44690</v>
       </c>
       <c r="B30" t="n">
-        <v>11.07566070556641</v>
+        <v>11.07566165924072</v>
       </c>
       <c r="C30" t="n">
-        <v>11.13049046868818</v>
+        <v>11.13049142708364</v>
       </c>
       <c r="D30" t="n">
-        <v>10.80934343269006</v>
+        <v>10.80934436343302</v>
       </c>
       <c r="E30" t="n">
-        <v>10.99733183225001</v>
+        <v>10.99733277917979</v>
       </c>
       <c r="F30" t="n">
         <v>1545300</v>
@@ -1032,16 +1032,16 @@
         <v>44691</v>
       </c>
       <c r="B31" t="n">
-        <v>11.12265872955322</v>
+        <v>11.12265777587891</v>
       </c>
       <c r="C31" t="n">
-        <v>11.25581738152601</v>
+        <v>11.25581641643446</v>
       </c>
       <c r="D31" t="n">
-        <v>10.95033563635322</v>
+        <v>10.95033469745416</v>
       </c>
       <c r="E31" t="n">
-        <v>11.11482569190786</v>
+        <v>11.11482473890516</v>
       </c>
       <c r="F31" t="n">
         <v>2338900</v>
@@ -1072,16 +1072,16 @@
         <v>44693</v>
       </c>
       <c r="B33" t="n">
-        <v>11.15398979187012</v>
+        <v>11.1539888381958</v>
       </c>
       <c r="C33" t="n">
-        <v>11.27931540236311</v>
+        <v>11.27931443797336</v>
       </c>
       <c r="D33" t="n">
-        <v>10.85634109344948</v>
+        <v>10.85634016522435</v>
       </c>
       <c r="E33" t="n">
-        <v>10.99733277875388</v>
+        <v>10.99733183847385</v>
       </c>
       <c r="F33" t="n">
         <v>1884700</v>
@@ -1092,16 +1092,16 @@
         <v>44694</v>
       </c>
       <c r="B34" t="n">
-        <v>11.32631206512451</v>
+        <v>11.32631301879883</v>
       </c>
       <c r="C34" t="n">
-        <v>11.38114182902154</v>
+        <v>11.38114278731251</v>
       </c>
       <c r="D34" t="n">
-        <v>11.11482455237968</v>
+        <v>11.11482548824677</v>
       </c>
       <c r="E34" t="n">
-        <v>11.18532038996129</v>
+        <v>11.18532133176413</v>
       </c>
       <c r="F34" t="n">
         <v>1333500</v>
@@ -1112,16 +1112,16 @@
         <v>44697</v>
       </c>
       <c r="B35" t="n">
-        <v>11.27931594848633</v>
+        <v>11.27931499481201</v>
       </c>
       <c r="C35" t="n">
-        <v>11.41247460283231</v>
+        <v>11.41247363789934</v>
       </c>
       <c r="D35" t="n">
-        <v>11.11482589000009</v>
+        <v>11.11482495023352</v>
       </c>
       <c r="E35" t="n">
-        <v>11.1774894452802</v>
+        <v>11.17748850021538</v>
       </c>
       <c r="F35" t="n">
         <v>2419100</v>
@@ -1132,16 +1132,16 @@
         <v>44698</v>
       </c>
       <c r="B36" t="n">
-        <v>11.56129741668701</v>
+        <v>11.56129837036133</v>
       </c>
       <c r="C36" t="n">
-        <v>11.74928581037311</v>
+        <v>11.74928677955431</v>
       </c>
       <c r="D36" t="n">
-        <v>11.35764295002734</v>
+        <v>11.3576438869025</v>
       </c>
       <c r="E36" t="n">
-        <v>11.35764295002734</v>
+        <v>11.3576438869025</v>
       </c>
       <c r="F36" t="n">
         <v>1389700</v>
@@ -1152,16 +1152,16 @@
         <v>44699</v>
       </c>
       <c r="B37" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C37" t="n">
-        <v>11.5926298208571</v>
+        <v>11.59262882548476</v>
       </c>
       <c r="D37" t="n">
-        <v>11.03649688106261</v>
+        <v>11.03649593344125</v>
       </c>
       <c r="E37" t="n">
-        <v>11.51430094319608</v>
+        <v>11.51429995454926</v>
       </c>
       <c r="F37" t="n">
         <v>1959900</v>
@@ -1192,16 +1192,16 @@
         <v>44701</v>
       </c>
       <c r="B39" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C39" t="n">
-        <v>11.34197786054158</v>
+        <v>11.34197688669085</v>
       </c>
       <c r="D39" t="n">
-        <v>10.86417379840811</v>
+        <v>10.86417286558284</v>
       </c>
       <c r="E39" t="n">
-        <v>11.34197786054158</v>
+        <v>11.34197688669085</v>
       </c>
       <c r="F39" t="n">
         <v>1777400</v>
@@ -1252,16 +1252,16 @@
         <v>44706</v>
       </c>
       <c r="B42" t="n">
-        <v>11.32631206512451</v>
+        <v>11.32631301879883</v>
       </c>
       <c r="C42" t="n">
-        <v>11.39680790270612</v>
+        <v>11.39680886231618</v>
       </c>
       <c r="D42" t="n">
-        <v>11.13832366290656</v>
+        <v>11.13832460075227</v>
       </c>
       <c r="E42" t="n">
-        <v>11.17748810011851</v>
+        <v>11.17748904126186</v>
       </c>
       <c r="F42" t="n">
         <v>821700</v>
@@ -1272,16 +1272,16 @@
         <v>44707</v>
       </c>
       <c r="B43" t="n">
-        <v>11.25581550598145</v>
+        <v>11.25581645965576</v>
       </c>
       <c r="C43" t="n">
-        <v>11.44380389614828</v>
+        <v>11.44380486575034</v>
       </c>
       <c r="D43" t="n">
-        <v>11.20881878193947</v>
+        <v>11.20881973163188</v>
       </c>
       <c r="E43" t="n">
-        <v>11.33414437538402</v>
+        <v>11.33414533569493</v>
       </c>
       <c r="F43" t="n">
         <v>1248800</v>
@@ -1292,16 +1292,16 @@
         <v>44708</v>
       </c>
       <c r="B44" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C44" t="n">
-        <v>11.42030600182509</v>
+        <v>11.42030698171035</v>
       </c>
       <c r="D44" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="E44" t="n">
-        <v>11.26364900360379</v>
+        <v>11.26364997004757</v>
       </c>
       <c r="F44" t="n">
         <v>2224600</v>
@@ -1312,16 +1312,16 @@
         <v>44711</v>
       </c>
       <c r="B45" t="n">
-        <v>11.09916019439697</v>
+        <v>11.09915924072266</v>
       </c>
       <c r="C45" t="n">
-        <v>11.27148328496971</v>
+        <v>11.27148231648886</v>
       </c>
       <c r="D45" t="n">
-        <v>11.02866435066269</v>
+        <v>11.0286634030456</v>
       </c>
       <c r="E45" t="n">
-        <v>11.15398996307938</v>
+        <v>11.15398900469392</v>
       </c>
       <c r="F45" t="n">
         <v>1940200</v>
@@ -1332,16 +1332,16 @@
         <v>44712</v>
       </c>
       <c r="B46" t="n">
-        <v>10.93466854095459</v>
+        <v>10.93466949462891</v>
       </c>
       <c r="C46" t="n">
-        <v>11.2088188382412</v>
+        <v>11.20881981582572</v>
       </c>
       <c r="D46" t="n">
-        <v>10.82500827264005</v>
+        <v>10.82500921675028</v>
       </c>
       <c r="E46" t="n">
-        <v>11.16965440334319</v>
+        <v>11.16965537751195</v>
       </c>
       <c r="F46" t="n">
         <v>9431500</v>
@@ -1352,16 +1352,16 @@
         <v>44713</v>
       </c>
       <c r="B47" t="n">
-        <v>10.73101425170898</v>
+        <v>10.7310152053833</v>
       </c>
       <c r="C47" t="n">
-        <v>10.94250175540008</v>
+        <v>10.94250272786947</v>
       </c>
       <c r="D47" t="n">
-        <v>10.66051841714529</v>
+        <v>10.66051936455458</v>
       </c>
       <c r="E47" t="n">
-        <v>10.94250175540008</v>
+        <v>10.94250272786947</v>
       </c>
       <c r="F47" t="n">
         <v>6323900</v>
@@ -1372,16 +1372,16 @@
         <v>44714</v>
       </c>
       <c r="B48" t="n">
-        <v>10.86417388916016</v>
+        <v>10.86417293548584</v>
       </c>
       <c r="C48" t="n">
-        <v>10.98949949686503</v>
+        <v>10.98949853218943</v>
       </c>
       <c r="D48" t="n">
-        <v>10.68401851483428</v>
+        <v>10.68401757697429</v>
       </c>
       <c r="E48" t="n">
-        <v>10.75451360891862</v>
+        <v>10.75451266487045</v>
       </c>
       <c r="F48" t="n">
         <v>3275400</v>
@@ -1412,16 +1412,16 @@
         <v>44718</v>
       </c>
       <c r="B50" t="n">
-        <v>10.61352157592773</v>
+        <v>10.61352252960205</v>
       </c>
       <c r="C50" t="n">
-        <v>10.91117023693893</v>
+        <v>10.91117121735836</v>
       </c>
       <c r="D50" t="n">
-        <v>10.45686458250065</v>
+        <v>10.4568655220986</v>
       </c>
       <c r="E50" t="n">
-        <v>10.81717604088268</v>
+        <v>10.8171770128563</v>
       </c>
       <c r="F50" t="n">
         <v>3175000</v>
@@ -1452,16 +1452,16 @@
         <v>44720</v>
       </c>
       <c r="B52" t="n">
-        <v>11.12265872955322</v>
+        <v>11.12265777587891</v>
       </c>
       <c r="C52" t="n">
-        <v>11.19315457436229</v>
+        <v>11.19315361464355</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73884884892558</v>
+        <v>10.73884792815973</v>
       </c>
       <c r="E52" t="n">
-        <v>10.78584632779816</v>
+        <v>10.78584540300267</v>
       </c>
       <c r="F52" t="n">
         <v>2847500</v>
@@ -1532,16 +1532,16 @@
         <v>44726</v>
       </c>
       <c r="B56" t="n">
-        <v>10.39420223236084</v>
+        <v>10.39420318603516</v>
       </c>
       <c r="C56" t="n">
-        <v>10.47253035894487</v>
+        <v>10.47253131980584</v>
       </c>
       <c r="D56" t="n">
-        <v>10.01822468495919</v>
+        <v>10.01822560413734</v>
       </c>
       <c r="E56" t="n">
-        <v>10.01822468495919</v>
+        <v>10.01822560413734</v>
       </c>
       <c r="F56" t="n">
         <v>4085600</v>
@@ -1592,16 +1592,16 @@
         <v>44732</v>
       </c>
       <c r="B59" t="n">
-        <v>10.59785747528076</v>
+        <v>10.59785652160645</v>
       </c>
       <c r="C59" t="n">
-        <v>10.69968472670765</v>
+        <v>10.69968376387016</v>
       </c>
       <c r="D59" t="n">
-        <v>10.37070460578988</v>
+        <v>10.37070367255648</v>
       </c>
       <c r="E59" t="n">
-        <v>10.47253185721677</v>
+        <v>10.47253091482019</v>
       </c>
       <c r="F59" t="n">
         <v>1649800</v>
@@ -1712,16 +1712,16 @@
         <v>44740</v>
       </c>
       <c r="B65" t="n">
-        <v>10.61352157592773</v>
+        <v>10.61352252960205</v>
       </c>
       <c r="C65" t="n">
-        <v>10.86417276541107</v>
+        <v>10.86417374160756</v>
       </c>
       <c r="D65" t="n">
-        <v>10.47252990834362</v>
+        <v>10.47253084934918</v>
       </c>
       <c r="E65" t="n">
-        <v>10.52735966929324</v>
+        <v>10.5273606152255</v>
       </c>
       <c r="F65" t="n">
         <v>5362200</v>
@@ -1732,16 +1732,16 @@
         <v>44741</v>
       </c>
       <c r="B66" t="n">
-        <v>10.68401718139648</v>
+        <v>10.6840181350708</v>
       </c>
       <c r="C66" t="n">
-        <v>10.68401718139648</v>
+        <v>10.6840181350708</v>
       </c>
       <c r="D66" t="n">
-        <v>10.53519248057162</v>
+        <v>10.53519342096158</v>
       </c>
       <c r="E66" t="n">
-        <v>10.62918667461916</v>
+        <v>10.62918762339921</v>
       </c>
       <c r="F66" t="n">
         <v>1613700</v>
@@ -1772,16 +1772,16 @@
         <v>44743</v>
       </c>
       <c r="B68" t="n">
-        <v>10.68401718139648</v>
+        <v>10.6840181350708</v>
       </c>
       <c r="C68" t="n">
-        <v>10.84067417147572</v>
+        <v>10.84067513913352</v>
       </c>
       <c r="D68" t="n">
-        <v>10.54302551682544</v>
+        <v>10.54302645791459</v>
       </c>
       <c r="E68" t="n">
-        <v>10.72318086866671</v>
+        <v>10.72318182583684</v>
       </c>
       <c r="F68" t="n">
         <v>2696600</v>
@@ -1792,16 +1792,16 @@
         <v>44746</v>
       </c>
       <c r="B69" t="n">
-        <v>10.65268611907959</v>
+        <v>10.65268707275391</v>
       </c>
       <c r="C69" t="n">
-        <v>10.78584475159305</v>
+        <v>10.7858457171883</v>
       </c>
       <c r="D69" t="n">
-        <v>10.52735977606733</v>
+        <v>10.52736071852189</v>
       </c>
       <c r="E69" t="n">
-        <v>10.68401751808279</v>
+        <v>10.68401847456203</v>
       </c>
       <c r="F69" t="n">
         <v>1437100</v>
@@ -1872,16 +1872,16 @@
         <v>44750</v>
       </c>
       <c r="B73" t="n">
-        <v>11.15398979187012</v>
+        <v>11.1539888381958</v>
       </c>
       <c r="C73" t="n">
-        <v>11.31064680498636</v>
+        <v>11.31064583791775</v>
       </c>
       <c r="D73" t="n">
-        <v>11.00516581615958</v>
+        <v>11.00516487520982</v>
       </c>
       <c r="E73" t="n">
-        <v>11.00516581615958</v>
+        <v>11.00516487520982</v>
       </c>
       <c r="F73" t="n">
         <v>1922000</v>
@@ -1892,16 +1892,16 @@
         <v>44753</v>
       </c>
       <c r="B74" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C74" t="n">
-        <v>11.18532085221909</v>
+        <v>11.18531989181933</v>
       </c>
       <c r="D74" t="n">
-        <v>10.83284239674361</v>
+        <v>10.83284146660853</v>
       </c>
       <c r="E74" t="n">
-        <v>11.0599952455611</v>
+        <v>11.05999429592211</v>
       </c>
       <c r="F74" t="n">
         <v>1881000</v>
@@ -1912,16 +1912,16 @@
         <v>44754</v>
       </c>
       <c r="B75" t="n">
-        <v>11.14615535736084</v>
+        <v>11.14615631103516</v>
       </c>
       <c r="C75" t="n">
-        <v>11.22448422760069</v>
+        <v>11.22448518797689</v>
       </c>
       <c r="D75" t="n">
-        <v>10.99733140030449</v>
+        <v>10.99733234124531</v>
       </c>
       <c r="E75" t="n">
-        <v>11.10699166924038</v>
+        <v>11.10699261956382</v>
       </c>
       <c r="F75" t="n">
         <v>1673000</v>
@@ -1952,16 +1952,16 @@
         <v>44756</v>
       </c>
       <c r="B77" t="n">
-        <v>10.91117095947266</v>
+        <v>10.91117000579834</v>
       </c>
       <c r="C77" t="n">
-        <v>11.17748823943387</v>
+        <v>11.1774872624825</v>
       </c>
       <c r="D77" t="n">
-        <v>10.84850815795232</v>
+        <v>10.84850720975495</v>
       </c>
       <c r="E77" t="n">
-        <v>11.04432959945326</v>
+        <v>11.04432863414042</v>
       </c>
       <c r="F77" t="n">
         <v>1968500</v>
@@ -1972,16 +1972,16 @@
         <v>44757</v>
       </c>
       <c r="B78" t="n">
-        <v>10.80934238433838</v>
+        <v>10.80934429168701</v>
       </c>
       <c r="C78" t="n">
-        <v>10.98166544072187</v>
+        <v>10.98166737847755</v>
       </c>
       <c r="D78" t="n">
-        <v>10.60568793106692</v>
+        <v>10.60568980247997</v>
       </c>
       <c r="E78" t="n">
-        <v>10.97383240475003</v>
+        <v>10.97383434112354</v>
       </c>
       <c r="F78" t="n">
         <v>2342600</v>
@@ -1992,16 +1992,16 @@
         <v>44760</v>
       </c>
       <c r="B79" t="n">
-        <v>10.73101425170898</v>
+        <v>10.7310152053833</v>
       </c>
       <c r="C79" t="n">
-        <v>11.00516455345681</v>
+        <v>11.0051655314951</v>
       </c>
       <c r="D79" t="n">
-        <v>10.59002332958107</v>
+        <v>10.5900242707254</v>
       </c>
       <c r="E79" t="n">
-        <v>10.80934312277964</v>
+        <v>10.80934408341511</v>
       </c>
       <c r="F79" t="n">
         <v>1463400</v>
@@ -2012,16 +2012,16 @@
         <v>44761</v>
       </c>
       <c r="B80" t="n">
-        <v>11.09132671356201</v>
+        <v>11.0913257598877</v>
       </c>
       <c r="C80" t="n">
-        <v>11.09132671356201</v>
+        <v>11.0913257598877</v>
       </c>
       <c r="D80" t="n">
-        <v>10.78584573225599</v>
+        <v>10.78584480484809</v>
       </c>
       <c r="E80" t="n">
-        <v>10.87200690059879</v>
+        <v>10.87200596578243</v>
       </c>
       <c r="F80" t="n">
         <v>2890800</v>
@@ -2032,16 +2032,16 @@
         <v>44762</v>
       </c>
       <c r="B81" t="n">
-        <v>11.27931594848633</v>
+        <v>11.27931499481201</v>
       </c>
       <c r="C81" t="n">
-        <v>11.35764483233677</v>
+        <v>11.35764387203968</v>
       </c>
       <c r="D81" t="n">
-        <v>11.05216308171958</v>
+        <v>11.0521621472512</v>
       </c>
       <c r="E81" t="n">
-        <v>11.08349448585983</v>
+        <v>11.08349354874236</v>
       </c>
       <c r="F81" t="n">
         <v>2285400</v>
@@ -2112,16 +2112,16 @@
         <v>44768</v>
       </c>
       <c r="B85" t="n">
-        <v>11.27148151397705</v>
+        <v>11.27148342132568</v>
       </c>
       <c r="C85" t="n">
-        <v>11.38114103411199</v>
+        <v>11.3811429600171</v>
       </c>
       <c r="D85" t="n">
-        <v>11.16965428313785</v>
+        <v>11.16965617325538</v>
       </c>
       <c r="E85" t="n">
-        <v>11.19315264502399</v>
+        <v>11.19315453911789</v>
       </c>
       <c r="F85" t="n">
         <v>1661400</v>
@@ -2132,16 +2132,16 @@
         <v>44769</v>
       </c>
       <c r="B86" t="n">
-        <v>11.24015045166016</v>
+        <v>11.24015140533447</v>
       </c>
       <c r="C86" t="n">
-        <v>11.49080164460048</v>
+        <v>11.49080261954139</v>
       </c>
       <c r="D86" t="n">
-        <v>11.15398854383731</v>
+        <v>11.15398949020119</v>
       </c>
       <c r="E86" t="n">
-        <v>11.28714717683673</v>
+        <v>11.2871481344985</v>
       </c>
       <c r="F86" t="n">
         <v>3096400</v>
@@ -2172,16 +2172,16 @@
         <v>44771</v>
       </c>
       <c r="B88" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C88" t="n">
-        <v>11.33414483955325</v>
+        <v>11.33414581204571</v>
       </c>
       <c r="D88" t="n">
-        <v>10.51952770180302</v>
+        <v>10.51952860439969</v>
       </c>
       <c r="E88" t="n">
-        <v>10.96600033348359</v>
+        <v>10.96600127438851</v>
       </c>
       <c r="F88" t="n">
         <v>13059200</v>
@@ -2212,16 +2212,16 @@
         <v>44775</v>
       </c>
       <c r="B90" t="n">
-        <v>10.86417388916016</v>
+        <v>10.86417293548584</v>
       </c>
       <c r="C90" t="n">
-        <v>11.06782837518035</v>
+        <v>11.06782740362892</v>
       </c>
       <c r="D90" t="n">
-        <v>10.7231822069924</v>
+        <v>10.72318126569455</v>
       </c>
       <c r="E90" t="n">
-        <v>10.93466973024404</v>
+        <v>10.93466877038148</v>
       </c>
       <c r="F90" t="n">
         <v>2371400</v>
@@ -2292,16 +2292,16 @@
         <v>44781</v>
       </c>
       <c r="B94" t="n">
-        <v>10.97383403778076</v>
+        <v>10.97383308410645</v>
       </c>
       <c r="C94" t="n">
-        <v>11.10699268111997</v>
+        <v>11.10699171587358</v>
       </c>
       <c r="D94" t="n">
-        <v>10.87200679599199</v>
+        <v>10.8720058511669</v>
       </c>
       <c r="E94" t="n">
-        <v>11.02866380374413</v>
+        <v>11.02866284530486</v>
       </c>
       <c r="F94" t="n">
         <v>2949000</v>
@@ -2312,16 +2312,16 @@
         <v>44782</v>
       </c>
       <c r="B95" t="n">
-        <v>10.92683601379395</v>
+        <v>10.92683696746826</v>
       </c>
       <c r="C95" t="n">
-        <v>11.05999465045304</v>
+        <v>11.0599956157492</v>
       </c>
       <c r="D95" t="n">
-        <v>10.67618481396482</v>
+        <v>10.67618574576276</v>
       </c>
       <c r="E95" t="n">
-        <v>10.98166652400619</v>
+        <v>10.98166748246601</v>
       </c>
       <c r="F95" t="n">
         <v>1743500</v>
@@ -2332,16 +2332,16 @@
         <v>44783</v>
       </c>
       <c r="B96" t="n">
-        <v>11.05216121673584</v>
+        <v>11.05216217041016</v>
       </c>
       <c r="C96" t="n">
-        <v>11.16965452268523</v>
+        <v>11.16965548649786</v>
       </c>
       <c r="D96" t="n">
-        <v>10.88767118600627</v>
+        <v>10.88767212548699</v>
       </c>
       <c r="E96" t="n">
-        <v>10.92683562132274</v>
+        <v>10.9268365641829</v>
       </c>
       <c r="F96" t="n">
         <v>2933600</v>
@@ -2352,16 +2352,16 @@
         <v>44784</v>
       </c>
       <c r="B97" t="n">
-        <v>10.89550399780273</v>
+        <v>10.89550590515137</v>
       </c>
       <c r="C97" t="n">
-        <v>11.10699149595105</v>
+        <v>11.10699344032233</v>
       </c>
       <c r="D97" t="n">
-        <v>10.8328412013883</v>
+        <v>10.83284309776729</v>
       </c>
       <c r="E97" t="n">
-        <v>11.0599940251405</v>
+        <v>11.05999596128448</v>
       </c>
       <c r="F97" t="n">
         <v>1665400</v>
@@ -2432,16 +2432,16 @@
         <v>44790</v>
       </c>
       <c r="B101" t="n">
-        <v>11.24015045166016</v>
+        <v>11.24015140533447</v>
       </c>
       <c r="C101" t="n">
-        <v>11.25581577771919</v>
+        <v>11.25581673272263</v>
       </c>
       <c r="D101" t="n">
-        <v>10.91117038742624</v>
+        <v>10.91117131318813</v>
       </c>
       <c r="E101" t="n">
-        <v>10.98949851172035</v>
+        <v>10.98949944412802</v>
       </c>
       <c r="F101" t="n">
         <v>4396400</v>
@@ -2452,16 +2452,16 @@
         <v>44791</v>
       </c>
       <c r="B102" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="C102" t="n">
-        <v>11.37330994384684</v>
+        <v>11.37330897550059</v>
       </c>
       <c r="D102" t="n">
-        <v>11.09915962060828</v>
+        <v>11.09915867560374</v>
       </c>
       <c r="E102" t="n">
-        <v>11.27931499239396</v>
+        <v>11.27931403205064</v>
       </c>
       <c r="F102" t="n">
         <v>2180500</v>
@@ -2472,16 +2472,16 @@
         <v>44792</v>
       </c>
       <c r="B103" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C103" t="n">
-        <v>11.16182176801008</v>
+        <v>11.16182272571687</v>
       </c>
       <c r="D103" t="n">
-        <v>10.98166640680546</v>
+        <v>10.98166734905456</v>
       </c>
       <c r="E103" t="n">
-        <v>11.16182176801008</v>
+        <v>11.16182272571687</v>
       </c>
       <c r="F103" t="n">
         <v>1667800</v>
@@ -2492,16 +2492,16 @@
         <v>44795</v>
       </c>
       <c r="B104" t="n">
-        <v>11.05999565124512</v>
+        <v>11.0599946975708</v>
       </c>
       <c r="C104" t="n">
-        <v>11.22448570276716</v>
+        <v>11.2244847349093</v>
       </c>
       <c r="D104" t="n">
-        <v>10.98166751771054</v>
+        <v>10.98166657079026</v>
       </c>
       <c r="E104" t="n">
-        <v>11.05999565124512</v>
+        <v>11.0599946975708</v>
       </c>
       <c r="F104" t="n">
         <v>1703300</v>
@@ -2532,16 +2532,16 @@
         <v>44797</v>
       </c>
       <c r="B106" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C106" t="n">
-        <v>11.3968083737041</v>
+        <v>11.39680739514549</v>
       </c>
       <c r="D106" t="n">
-        <v>11.09915968439161</v>
+        <v>11.09915873138986</v>
       </c>
       <c r="E106" t="n">
-        <v>11.2244852910496</v>
+        <v>11.22448432728707</v>
       </c>
       <c r="F106" t="n">
         <v>2116800</v>
@@ -2572,16 +2572,16 @@
         <v>44799</v>
       </c>
       <c r="B108" t="n">
-        <v>11.05216121673584</v>
+        <v>11.05216217041016</v>
       </c>
       <c r="C108" t="n">
-        <v>11.17748755914842</v>
+        <v>11.17748852363695</v>
       </c>
       <c r="D108" t="n">
-        <v>10.95816702017601</v>
+        <v>10.95816796573971</v>
       </c>
       <c r="E108" t="n">
-        <v>11.05216121673584</v>
+        <v>11.05216217041016</v>
       </c>
       <c r="F108" t="n">
         <v>1356300</v>
@@ -2592,16 +2592,16 @@
         <v>44802</v>
       </c>
       <c r="B109" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C109" t="n">
-        <v>11.20881924097621</v>
+        <v>11.20882020271549</v>
       </c>
       <c r="D109" t="n">
-        <v>10.93466893383933</v>
+        <v>10.93466987205595</v>
       </c>
       <c r="E109" t="n">
-        <v>11.02083009611117</v>
+        <v>11.02083104172059</v>
       </c>
       <c r="F109" t="n">
         <v>3615600</v>
@@ -2692,16 +2692,16 @@
         <v>44809</v>
       </c>
       <c r="B114" t="n">
-        <v>11.85894584655762</v>
+        <v>11.85894680023193</v>
       </c>
       <c r="C114" t="n">
-        <v>11.92160864321847</v>
+        <v>11.92160960193201</v>
       </c>
       <c r="D114" t="n">
-        <v>11.60829391291476</v>
+        <v>11.60829484643211</v>
       </c>
       <c r="E114" t="n">
-        <v>11.76495165156634</v>
+        <v>11.76495259768182</v>
       </c>
       <c r="F114" t="n">
         <v>1899700</v>
@@ -2752,16 +2752,16 @@
         <v>44813</v>
       </c>
       <c r="B117" t="n">
-        <v>11.31847858428955</v>
+        <v>11.31847953796387</v>
       </c>
       <c r="C117" t="n">
-        <v>11.51430001566826</v>
+        <v>11.51430098584213</v>
       </c>
       <c r="D117" t="n">
-        <v>11.1696546251215</v>
+        <v>11.16965556625618</v>
       </c>
       <c r="E117" t="n">
-        <v>11.51430001566826</v>
+        <v>11.51430098584213</v>
       </c>
       <c r="F117" t="n">
         <v>2426300</v>
@@ -2772,16 +2772,16 @@
         <v>44816</v>
       </c>
       <c r="B118" t="n">
-        <v>11.41247272491455</v>
+        <v>11.41247367858887</v>
       </c>
       <c r="C118" t="n">
-        <v>11.64745859079944</v>
+        <v>11.64745956411016</v>
       </c>
       <c r="D118" t="n">
-        <v>11.35764296344122</v>
+        <v>11.35764391253373</v>
       </c>
       <c r="E118" t="n">
-        <v>11.39680739892195</v>
+        <v>11.3968083512872</v>
       </c>
       <c r="F118" t="n">
         <v>2097200</v>
@@ -2792,16 +2792,16 @@
         <v>44817</v>
       </c>
       <c r="B119" t="n">
-        <v>11.24015045166016</v>
+        <v>11.24015140533447</v>
       </c>
       <c r="C119" t="n">
-        <v>11.43597188289466</v>
+        <v>11.43597285318351</v>
       </c>
       <c r="D119" t="n">
-        <v>11.16965461689582</v>
+        <v>11.16965556458889</v>
       </c>
       <c r="E119" t="n">
-        <v>11.30281324989524</v>
+        <v>11.3028142088862</v>
       </c>
       <c r="F119" t="n">
         <v>1768400</v>
@@ -2852,16 +2852,16 @@
         <v>44820</v>
       </c>
       <c r="B122" t="n">
-        <v>11.16965579986572</v>
+        <v>11.16965484619141</v>
       </c>
       <c r="C122" t="n">
-        <v>11.35764421448068</v>
+        <v>11.35764324475576</v>
       </c>
       <c r="D122" t="n">
-        <v>11.02866411540472</v>
+        <v>11.02866317376839</v>
       </c>
       <c r="E122" t="n">
-        <v>11.22448556737853</v>
+        <v>11.2244846090228</v>
       </c>
       <c r="F122" t="n">
         <v>3523100</v>
@@ -2892,16 +2892,16 @@
         <v>44824</v>
       </c>
       <c r="B124" t="n">
-        <v>11.13049030303955</v>
+        <v>11.13049125671387</v>
       </c>
       <c r="C124" t="n">
-        <v>11.35764313587711</v>
+        <v>11.35764410901417</v>
       </c>
       <c r="D124" t="n">
-        <v>11.08349283034925</v>
+        <v>11.08349377999676</v>
       </c>
       <c r="E124" t="n">
-        <v>11.28714730034141</v>
+        <v>11.28714826743829</v>
       </c>
       <c r="F124" t="n">
         <v>1310600</v>
@@ -2912,16 +2912,16 @@
         <v>44825</v>
       </c>
       <c r="B125" t="n">
-        <v>11.09132671356201</v>
+        <v>11.0913257598877</v>
       </c>
       <c r="C125" t="n">
-        <v>11.23231839539528</v>
+        <v>11.23231742959796</v>
       </c>
       <c r="D125" t="n">
-        <v>10.93466970430257</v>
+        <v>10.93466876409822</v>
       </c>
       <c r="E125" t="n">
-        <v>11.13049115262676</v>
+        <v>11.13049019558493</v>
       </c>
       <c r="F125" t="n">
         <v>2825100</v>
@@ -2952,16 +2952,16 @@
         <v>44827</v>
       </c>
       <c r="B127" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="C127" t="n">
-        <v>11.30281410375695</v>
+        <v>11.30281314141286</v>
       </c>
       <c r="D127" t="n">
-        <v>11.07566125624483</v>
+        <v>11.07566031324099</v>
       </c>
       <c r="E127" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="F127" t="n">
         <v>2444100</v>
@@ -2992,16 +2992,16 @@
         <v>44831</v>
       </c>
       <c r="B129" t="n">
-        <v>10.90333843231201</v>
+        <v>10.9033374786377</v>
       </c>
       <c r="C129" t="n">
-        <v>11.04433011582452</v>
+        <v>11.04432914981819</v>
       </c>
       <c r="D129" t="n">
-        <v>10.77017978610565</v>
+        <v>10.77017884407822</v>
       </c>
       <c r="E129" t="n">
-        <v>11.04433011582452</v>
+        <v>11.04432914981819</v>
       </c>
       <c r="F129" t="n">
         <v>2130200</v>
@@ -3012,16 +3012,16 @@
         <v>44832</v>
       </c>
       <c r="B130" t="n">
-        <v>10.74668025970459</v>
+        <v>10.74668121337891</v>
       </c>
       <c r="C130" t="n">
-        <v>11.03649588571345</v>
+        <v>11.03649686510639</v>
       </c>
       <c r="D130" t="n">
-        <v>10.72318115032588</v>
+        <v>10.72318210191485</v>
       </c>
       <c r="E130" t="n">
-        <v>10.95816701511669</v>
+        <v>10.95816798755862</v>
       </c>
       <c r="F130" t="n">
         <v>4249200</v>
@@ -3032,16 +3032,16 @@
         <v>44833</v>
       </c>
       <c r="B131" t="n">
-        <v>10.70751667022705</v>
+        <v>10.70751571655273</v>
       </c>
       <c r="C131" t="n">
-        <v>10.83284227548216</v>
+        <v>10.83284131064561</v>
       </c>
       <c r="D131" t="n">
-        <v>10.6448538675995</v>
+        <v>10.6448529195063</v>
       </c>
       <c r="E131" t="n">
-        <v>10.6918505960704</v>
+        <v>10.69184964379139</v>
       </c>
       <c r="F131" t="n">
         <v>2222600</v>
@@ -3052,16 +3052,16 @@
         <v>44834</v>
       </c>
       <c r="B132" t="n">
-        <v>10.61352157592773</v>
+        <v>10.61352252960205</v>
       </c>
       <c r="C132" t="n">
-        <v>10.74668020709063</v>
+        <v>10.74668117272986</v>
       </c>
       <c r="D132" t="n">
-        <v>10.59785550308529</v>
+        <v>10.59785645535194</v>
       </c>
       <c r="E132" t="n">
-        <v>10.70751577198399</v>
+        <v>10.70751673410412</v>
       </c>
       <c r="F132" t="n">
         <v>4019300</v>
@@ -3072,16 +3072,16 @@
         <v>44837</v>
       </c>
       <c r="B133" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="C133" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="D133" t="n">
-        <v>10.62918785134206</v>
+        <v>10.62918694635185</v>
       </c>
       <c r="E133" t="n">
-        <v>10.74668116715839</v>
+        <v>10.74668025216456</v>
       </c>
       <c r="F133" t="n">
         <v>2250700</v>
@@ -3092,16 +3092,16 @@
         <v>44838</v>
       </c>
       <c r="B134" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C134" t="n">
-        <v>11.32631180289231</v>
+        <v>11.32631277471268</v>
       </c>
       <c r="D134" t="n">
-        <v>11.07566060573824</v>
+        <v>11.07566155605223</v>
       </c>
       <c r="E134" t="n">
-        <v>11.20881924097621</v>
+        <v>11.20882020271549</v>
       </c>
       <c r="F134" t="n">
         <v>2406500</v>
@@ -3112,16 +3112,16 @@
         <v>44839</v>
       </c>
       <c r="B135" t="n">
-        <v>10.97383403778076</v>
+        <v>10.97383308410645</v>
       </c>
       <c r="C135" t="n">
-        <v>11.20881992290874</v>
+        <v>11.20881894881312</v>
       </c>
       <c r="D135" t="n">
-        <v>10.85634072171701</v>
+        <v>10.85633977825337</v>
       </c>
       <c r="E135" t="n">
-        <v>11.20881992290874</v>
+        <v>11.20881894881312</v>
       </c>
       <c r="F135" t="n">
         <v>5244200</v>
@@ -3132,16 +3132,16 @@
         <v>44840</v>
       </c>
       <c r="B136" t="n">
-        <v>10.98949909210205</v>
+        <v>10.98950004577637</v>
       </c>
       <c r="C136" t="n">
-        <v>11.1226577321339</v>
+        <v>11.12265869736379</v>
       </c>
       <c r="D136" t="n">
-        <v>10.88767185284243</v>
+        <v>10.88767279768013</v>
       </c>
       <c r="E136" t="n">
-        <v>11.02866352981721</v>
+        <v>11.02866448689024</v>
       </c>
       <c r="F136" t="n">
         <v>3101100</v>
@@ -3152,16 +3152,16 @@
         <v>44841</v>
       </c>
       <c r="B137" t="n">
-        <v>11.02866458892822</v>
+        <v>11.02866363525391</v>
       </c>
       <c r="C137" t="n">
-        <v>11.15399020405247</v>
+        <v>11.15398923954096</v>
       </c>
       <c r="D137" t="n">
-        <v>10.9425034152802</v>
+        <v>10.94250246905644</v>
       </c>
       <c r="E137" t="n">
-        <v>10.98166785675642</v>
+        <v>10.98166690714602</v>
       </c>
       <c r="F137" t="n">
         <v>7588600</v>
@@ -3172,16 +3172,16 @@
         <v>44844</v>
       </c>
       <c r="B138" t="n">
-        <v>11.07566070556641</v>
+        <v>11.07566165924072</v>
       </c>
       <c r="C138" t="n">
-        <v>11.35764330490633</v>
+        <v>11.35764428286087</v>
       </c>
       <c r="D138" t="n">
-        <v>11.01299790571309</v>
+        <v>11.0129988539918</v>
       </c>
       <c r="E138" t="n">
-        <v>11.07566070556641</v>
+        <v>11.07566165924072</v>
       </c>
       <c r="F138" t="n">
         <v>2000500</v>
@@ -3212,16 +3212,16 @@
         <v>44847</v>
       </c>
       <c r="B140" t="n">
-        <v>10.91117095947266</v>
+        <v>10.91117000579834</v>
       </c>
       <c r="C140" t="n">
-        <v>11.20098660325412</v>
+        <v>11.20098562424891</v>
       </c>
       <c r="D140" t="n">
-        <v>10.87200652177256</v>
+        <v>10.87200557152136</v>
       </c>
       <c r="E140" t="n">
-        <v>11.12265772785393</v>
+        <v>11.12265675569494</v>
       </c>
       <c r="F140" t="n">
         <v>3739400</v>
@@ -3252,16 +3252,16 @@
         <v>44851</v>
       </c>
       <c r="B142" t="n">
-        <v>11.15398979187012</v>
+        <v>11.1539888381958</v>
       </c>
       <c r="C142" t="n">
-        <v>11.20098726930477</v>
+        <v>11.20098631161214</v>
       </c>
       <c r="D142" t="n">
-        <v>10.78584599779684</v>
+        <v>10.78584507559909</v>
       </c>
       <c r="E142" t="n">
-        <v>10.86417413085518</v>
+        <v>10.86417320196032</v>
       </c>
       <c r="F142" t="n">
         <v>6971700</v>
@@ -3272,16 +3272,16 @@
         <v>44852</v>
       </c>
       <c r="B143" t="n">
-        <v>11.27148151397705</v>
+        <v>11.27148342132568</v>
       </c>
       <c r="C143" t="n">
-        <v>11.37330874481625</v>
+        <v>11.37331066939599</v>
       </c>
       <c r="D143" t="n">
-        <v>11.06782705229865</v>
+        <v>11.06782892518508</v>
       </c>
       <c r="E143" t="n">
-        <v>11.20881871761438</v>
+        <v>11.20882061435928</v>
       </c>
       <c r="F143" t="n">
         <v>2646800</v>
@@ -3332,16 +3332,16 @@
         <v>44855</v>
       </c>
       <c r="B146" t="n">
-        <v>11.16965579986572</v>
+        <v>11.16965484619141</v>
       </c>
       <c r="C146" t="n">
-        <v>11.16965579986572</v>
+        <v>11.16965484619141</v>
       </c>
       <c r="D146" t="n">
-        <v>10.75451378384157</v>
+        <v>10.75451286561242</v>
       </c>
       <c r="E146" t="n">
-        <v>10.75451378384157</v>
+        <v>10.75451286561242</v>
       </c>
       <c r="F146" t="n">
         <v>9489900</v>
@@ -3372,16 +3372,16 @@
         <v>44859</v>
       </c>
       <c r="B148" t="n">
-        <v>11.38897514343262</v>
+        <v>11.38897609710693</v>
       </c>
       <c r="C148" t="n">
-        <v>11.50646771093245</v>
+        <v>11.5064686744452</v>
       </c>
       <c r="D148" t="n">
-        <v>11.18532066256667</v>
+        <v>11.18532159918765</v>
       </c>
       <c r="E148" t="n">
-        <v>11.24015117479952</v>
+        <v>11.24015211601182</v>
       </c>
       <c r="F148" t="n">
         <v>2935500</v>
@@ -3412,16 +3412,16 @@
         <v>44861</v>
       </c>
       <c r="B150" t="n">
-        <v>11.35764312744141</v>
+        <v>11.35764408111572</v>
       </c>
       <c r="C150" t="n">
-        <v>11.63179343276565</v>
+        <v>11.63179440945972</v>
       </c>
       <c r="D150" t="n">
-        <v>11.27148196573925</v>
+        <v>11.27148291217882</v>
       </c>
       <c r="E150" t="n">
-        <v>11.42813896292475</v>
+        <v>11.42813992251844</v>
       </c>
       <c r="F150" t="n">
         <v>4207900</v>
@@ -3472,16 +3472,16 @@
         <v>44866</v>
       </c>
       <c r="B153" t="n">
-        <v>11.56913185119629</v>
+        <v>11.56913089752197</v>
       </c>
       <c r="C153" t="n">
-        <v>11.80411699819995</v>
+        <v>11.80411602515518</v>
       </c>
       <c r="D153" t="n">
-        <v>11.34981128506018</v>
+        <v>11.34981034946504</v>
       </c>
       <c r="E153" t="n">
-        <v>11.67879138726478</v>
+        <v>11.67879042455094</v>
       </c>
       <c r="F153" t="n">
         <v>3576300</v>
@@ -3512,16 +3512,16 @@
         <v>44869</v>
       </c>
       <c r="B155" t="n">
-        <v>11.67095756530762</v>
+        <v>11.67095851898193</v>
       </c>
       <c r="C155" t="n">
-        <v>11.87461204288736</v>
+        <v>11.87461301320299</v>
       </c>
       <c r="D155" t="n">
-        <v>11.64745920158673</v>
+        <v>11.64746015334091</v>
       </c>
       <c r="E155" t="n">
-        <v>11.7492864403766</v>
+        <v>11.74928740045144</v>
       </c>
       <c r="F155" t="n">
         <v>2161500</v>
@@ -3532,16 +3532,16 @@
         <v>44872</v>
       </c>
       <c r="B156" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="C156" t="n">
-        <v>11.65529255720685</v>
+        <v>11.65529156485204</v>
       </c>
       <c r="D156" t="n">
-        <v>11.12265798497174</v>
+        <v>11.1226570379665</v>
       </c>
       <c r="E156" t="n">
-        <v>11.60829508148041</v>
+        <v>11.60829409312706</v>
       </c>
       <c r="F156" t="n">
         <v>3276500</v>
@@ -3552,16 +3552,16 @@
         <v>44873</v>
       </c>
       <c r="B157" t="n">
-        <v>11.12265872955322</v>
+        <v>11.12265777587891</v>
       </c>
       <c r="C157" t="n">
-        <v>11.27148345681673</v>
+        <v>11.27148249038195</v>
       </c>
       <c r="D157" t="n">
-        <v>11.02083148116229</v>
+        <v>11.02083053621881</v>
       </c>
       <c r="E157" t="n">
-        <v>11.11482569190786</v>
+        <v>11.11482473890516</v>
       </c>
       <c r="F157" t="n">
         <v>2450400</v>
@@ -3572,16 +3572,16 @@
         <v>44874</v>
       </c>
       <c r="B158" t="n">
-        <v>11.12265872955322</v>
+        <v>11.12265777587891</v>
       </c>
       <c r="C158" t="n">
-        <v>11.21665294029879</v>
+        <v>11.21665197856526</v>
       </c>
       <c r="D158" t="n">
-        <v>11.04433059409837</v>
+        <v>11.04432964714004</v>
       </c>
       <c r="E158" t="n">
-        <v>11.14615709548972</v>
+        <v>11.14615613980062</v>
       </c>
       <c r="F158" t="n">
         <v>1977800</v>
@@ -3592,16 +3592,16 @@
         <v>44875</v>
       </c>
       <c r="B159" t="n">
-        <v>10.70751667022705</v>
+        <v>10.70751571655273</v>
       </c>
       <c r="C159" t="n">
-        <v>11.10699259722736</v>
+        <v>11.10699160797338</v>
       </c>
       <c r="D159" t="n">
-        <v>10.4960291511094</v>
+        <v>10.49602821627141</v>
       </c>
       <c r="E159" t="n">
-        <v>11.04432979459981</v>
+        <v>11.04432881092694</v>
       </c>
       <c r="F159" t="n">
         <v>4341400</v>
@@ -3612,16 +3612,16 @@
         <v>44876</v>
       </c>
       <c r="B160" t="n">
-        <v>10.79367733001709</v>
+        <v>10.79367828369141</v>
       </c>
       <c r="C160" t="n">
-        <v>10.85634012970083</v>
+        <v>10.85634108891171</v>
       </c>
       <c r="D160" t="n">
-        <v>10.5351930945718</v>
+        <v>10.53519402540776</v>
       </c>
       <c r="E160" t="n">
-        <v>10.78584504030624</v>
+        <v>10.78584599328854</v>
       </c>
       <c r="F160" t="n">
         <v>3291200</v>
@@ -3652,16 +3652,16 @@
         <v>44881</v>
       </c>
       <c r="B162" t="n">
-        <v>10.90333843231201</v>
+        <v>10.9033374786377</v>
       </c>
       <c r="C162" t="n">
-        <v>10.90333843231201</v>
+        <v>10.9033374786377</v>
       </c>
       <c r="D162" t="n">
-        <v>10.59785670036809</v>
+        <v>10.59785577341312</v>
       </c>
       <c r="E162" t="n">
-        <v>10.86417399278081</v>
+        <v>10.86417304253206</v>
       </c>
       <c r="F162" t="n">
         <v>5270300</v>
@@ -3672,16 +3672,16 @@
         <v>44882</v>
       </c>
       <c r="B163" t="n">
-        <v>10.74668025970459</v>
+        <v>10.74668121337891</v>
       </c>
       <c r="C163" t="n">
-        <v>10.80151002092264</v>
+        <v>10.80151097946262</v>
       </c>
       <c r="D163" t="n">
-        <v>10.50386135845421</v>
+        <v>10.50386229058046</v>
       </c>
       <c r="E163" t="n">
-        <v>10.69184975148707</v>
+        <v>10.69185070029565</v>
       </c>
       <c r="F163" t="n">
         <v>5834900</v>
@@ -3692,16 +3692,16 @@
         <v>44883</v>
       </c>
       <c r="B164" t="n">
-        <v>10.78584575653076</v>
+        <v>10.78584671020508</v>
       </c>
       <c r="C164" t="n">
-        <v>10.98949949552661</v>
+        <v>10.9895004672078</v>
       </c>
       <c r="D164" t="n">
-        <v>10.57435823330488</v>
+        <v>10.57435916827967</v>
       </c>
       <c r="E164" t="n">
-        <v>10.80934412122268</v>
+        <v>10.8093450769747</v>
       </c>
       <c r="F164" t="n">
         <v>3568700</v>
@@ -3712,16 +3712,16 @@
         <v>44886</v>
       </c>
       <c r="B165" t="n">
-        <v>11.27931594848633</v>
+        <v>11.27931499481201</v>
       </c>
       <c r="C165" t="n">
-        <v>11.32631342819651</v>
+        <v>11.32631247054852</v>
       </c>
       <c r="D165" t="n">
-        <v>10.8093448863825</v>
+        <v>10.80934397244457</v>
       </c>
       <c r="E165" t="n">
-        <v>10.84067629052275</v>
+        <v>10.84067537393573</v>
       </c>
       <c r="F165" t="n">
         <v>4939800</v>
@@ -3752,16 +3752,16 @@
         <v>44888</v>
       </c>
       <c r="B167" t="n">
-        <v>10.56652545928955</v>
+        <v>10.56652450561523</v>
       </c>
       <c r="C167" t="n">
-        <v>10.81717742791213</v>
+        <v>10.8171764516154</v>
       </c>
       <c r="D167" t="n">
-        <v>10.51952872873502</v>
+        <v>10.51952777930236</v>
       </c>
       <c r="E167" t="n">
-        <v>10.80934439048652</v>
+        <v>10.80934341489675</v>
       </c>
       <c r="F167" t="n">
         <v>4669400</v>
@@ -3812,16 +3812,16 @@
         <v>44893</v>
       </c>
       <c r="B170" t="n">
-        <v>10.97383403778076</v>
+        <v>10.97383308410645</v>
       </c>
       <c r="C170" t="n">
-        <v>11.09915964398247</v>
+        <v>11.09915867941681</v>
       </c>
       <c r="D170" t="n">
-        <v>10.68401838668942</v>
+        <v>10.68401745820135</v>
       </c>
       <c r="E170" t="n">
-        <v>10.84067539444156</v>
+        <v>10.84067445233931</v>
       </c>
       <c r="F170" t="n">
         <v>4990000</v>
@@ -3832,16 +3832,16 @@
         <v>44894</v>
       </c>
       <c r="B171" t="n">
-        <v>11.16965579986572</v>
+        <v>11.16965484619141</v>
       </c>
       <c r="C171" t="n">
-        <v>11.2636500071732</v>
+        <v>11.26364904547358</v>
       </c>
       <c r="D171" t="n">
-        <v>10.9973327129689</v>
+        <v>10.99733177400767</v>
       </c>
       <c r="E171" t="n">
-        <v>11.01299878768659</v>
+        <v>11.01299784738778</v>
       </c>
       <c r="F171" t="n">
         <v>1705300</v>
@@ -3872,16 +3872,16 @@
         <v>44896</v>
       </c>
       <c r="B173" t="n">
-        <v>10.92683601379395</v>
+        <v>10.92683696746826</v>
       </c>
       <c r="C173" t="n">
-        <v>11.02083021372987</v>
+        <v>11.02083117560783</v>
       </c>
       <c r="D173" t="n">
-        <v>10.69185014045439</v>
+        <v>10.69185107361957</v>
       </c>
       <c r="E173" t="n">
-        <v>10.76234597715621</v>
+        <v>10.76234691647413</v>
       </c>
       <c r="F173" t="n">
         <v>1944500</v>
@@ -3912,16 +3912,16 @@
         <v>44900</v>
       </c>
       <c r="B175" t="n">
-        <v>10.51952838897705</v>
+        <v>10.51952743530273</v>
       </c>
       <c r="C175" t="n">
-        <v>10.80151100419552</v>
+        <v>10.80151002495736</v>
       </c>
       <c r="D175" t="n">
-        <v>10.50386231463181</v>
+        <v>10.50386136237774</v>
       </c>
       <c r="E175" t="n">
-        <v>10.7780126396772</v>
+        <v>10.77801166256934</v>
       </c>
       <c r="F175" t="n">
         <v>1355000</v>
@@ -3932,16 +3932,16 @@
         <v>44901</v>
       </c>
       <c r="B176" t="n">
-        <v>10.47253131866455</v>
+        <v>10.47253036499023</v>
       </c>
       <c r="C176" t="n">
-        <v>10.58219160233104</v>
+        <v>10.58219063867058</v>
       </c>
       <c r="D176" t="n">
-        <v>10.41770155033109</v>
+        <v>10.41770060164981</v>
       </c>
       <c r="E176" t="n">
-        <v>10.51952879652149</v>
+        <v>10.51952783856738</v>
       </c>
       <c r="F176" t="n">
         <v>1647500</v>
@@ -3952,16 +3952,16 @@
         <v>44902</v>
       </c>
       <c r="B177" t="n">
-        <v>10.65268611907959</v>
+        <v>10.65268707275391</v>
       </c>
       <c r="C177" t="n">
-        <v>10.80151007759491</v>
+        <v>10.80151104459258</v>
       </c>
       <c r="D177" t="n">
-        <v>10.42553328955654</v>
+        <v>10.42553422289516</v>
       </c>
       <c r="E177" t="n">
-        <v>10.42553328955654</v>
+        <v>10.42553422289516</v>
       </c>
       <c r="F177" t="n">
         <v>2865300</v>
@@ -3972,16 +3972,16 @@
         <v>44903</v>
       </c>
       <c r="B178" t="n">
-        <v>11.26364994049072</v>
+        <v>11.26364898681641</v>
       </c>
       <c r="C178" t="n">
-        <v>11.81194985337145</v>
+        <v>11.8119488532735</v>
       </c>
       <c r="D178" t="n">
-        <v>11.15398965911476</v>
+        <v>11.15398871472519</v>
       </c>
       <c r="E178" t="n">
-        <v>11.74928704887077</v>
+        <v>11.74928605407837</v>
       </c>
       <c r="F178" t="n">
         <v>12105700</v>
@@ -4052,16 +4052,16 @@
         <v>44909</v>
       </c>
       <c r="B182" t="n">
-        <v>10.99733352661133</v>
+        <v>10.99733257293701</v>
       </c>
       <c r="C182" t="n">
-        <v>11.13832522150366</v>
+        <v>11.13832425560273</v>
       </c>
       <c r="D182" t="n">
-        <v>10.7388492506418</v>
+        <v>10.7388483193829</v>
       </c>
       <c r="E182" t="n">
-        <v>11.01299960248808</v>
+        <v>11.01299864745522</v>
       </c>
       <c r="F182" t="n">
         <v>3892800</v>
@@ -4072,16 +4072,16 @@
         <v>44910</v>
       </c>
       <c r="B183" t="n">
-        <v>11.05216121673584</v>
+        <v>11.05216217041016</v>
       </c>
       <c r="C183" t="n">
-        <v>11.17748755914842</v>
+        <v>11.17748852363695</v>
       </c>
       <c r="D183" t="n">
-        <v>10.86417282361618</v>
+        <v>10.86417376106927</v>
       </c>
       <c r="E183" t="n">
-        <v>10.95033398371283</v>
+        <v>10.95033492860062</v>
       </c>
       <c r="F183" t="n">
         <v>3824700</v>
@@ -4112,16 +4112,16 @@
         <v>44914</v>
       </c>
       <c r="B185" t="n">
-        <v>11.37331008911133</v>
+        <v>11.37330913543701</v>
       </c>
       <c r="C185" t="n">
-        <v>11.5221340613134</v>
+        <v>11.5221330951599</v>
       </c>
       <c r="D185" t="n">
-        <v>11.18532093080405</v>
+        <v>11.18531999289299</v>
       </c>
       <c r="E185" t="n">
-        <v>11.23231840713075</v>
+        <v>11.23231746527886</v>
       </c>
       <c r="F185" t="n">
         <v>3838800</v>
@@ -4132,16 +4132,16 @@
         <v>44915</v>
       </c>
       <c r="B186" t="n">
-        <v>11.27931594848633</v>
+        <v>11.27931499481201</v>
       </c>
       <c r="C186" t="n">
-        <v>11.56129933274823</v>
+        <v>11.56129835523201</v>
       </c>
       <c r="D186" t="n">
-        <v>11.16965640749523</v>
+        <v>11.16965546309271</v>
       </c>
       <c r="E186" t="n">
-        <v>11.35764483233677</v>
+        <v>11.35764387203968</v>
       </c>
       <c r="F186" t="n">
         <v>4148100</v>
@@ -4212,16 +4212,16 @@
         <v>44921</v>
       </c>
       <c r="B190" t="n">
-        <v>11.5769624710083</v>
+        <v>11.57696342468262</v>
       </c>
       <c r="C190" t="n">
-        <v>11.8276144037077</v>
+        <v>11.82761537802995</v>
       </c>
       <c r="D190" t="n">
-        <v>11.51429967458331</v>
+        <v>11.51430062309566</v>
       </c>
       <c r="E190" t="n">
-        <v>11.77278389658625</v>
+        <v>11.77278486639172</v>
       </c>
       <c r="F190" t="n">
         <v>1646600</v>
@@ -4272,16 +4272,16 @@
         <v>44924</v>
       </c>
       <c r="B193" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="C193" t="n">
-        <v>11.73362032145083</v>
+        <v>11.73362129131107</v>
       </c>
       <c r="D193" t="n">
-        <v>11.4751360805163</v>
+        <v>11.47513702901113</v>
       </c>
       <c r="E193" t="n">
-        <v>11.62396079317528</v>
+        <v>11.62396175397144</v>
       </c>
       <c r="F193" t="n">
         <v>2424800</v>
@@ -4312,16 +4312,16 @@
         <v>44929</v>
       </c>
       <c r="B195" t="n">
-        <v>11.13832378387451</v>
+        <v>11.13832473754883</v>
       </c>
       <c r="C195" t="n">
-        <v>11.32631218813412</v>
+        <v>11.32631315790418</v>
       </c>
       <c r="D195" t="n">
-        <v>11.05999490859992</v>
+        <v>11.05999585556764</v>
       </c>
       <c r="E195" t="n">
-        <v>11.30281382435154</v>
+        <v>11.30281479210966</v>
       </c>
       <c r="F195" t="n">
         <v>1562800</v>
@@ -4332,16 +4332,16 @@
         <v>44930</v>
       </c>
       <c r="B196" t="n">
-        <v>11.35764312744141</v>
+        <v>11.35764408111572</v>
       </c>
       <c r="C196" t="n">
-        <v>11.35764312744141</v>
+        <v>11.35764408111572</v>
       </c>
       <c r="D196" t="n">
-        <v>10.96600026097791</v>
+        <v>10.9660011817669</v>
       </c>
       <c r="E196" t="n">
-        <v>11.1696547308188</v>
+        <v>11.16965566870818</v>
       </c>
       <c r="F196" t="n">
         <v>2937400</v>
@@ -4352,16 +4352,16 @@
         <v>44931</v>
       </c>
       <c r="B197" t="n">
-        <v>11.41247272491455</v>
+        <v>11.41247367858887</v>
       </c>
       <c r="C197" t="n">
-        <v>11.41247272491455</v>
+        <v>11.41247367858887</v>
       </c>
       <c r="D197" t="n">
-        <v>11.08349266207561</v>
+        <v>11.08349358825896</v>
       </c>
       <c r="E197" t="n">
-        <v>11.31064549146445</v>
+        <v>11.31064643662965</v>
       </c>
       <c r="F197" t="n">
         <v>4358300</v>
@@ -4412,16 +4412,16 @@
         <v>44936</v>
       </c>
       <c r="B200" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C200" t="n">
-        <v>11.1853201309934</v>
+        <v>11.1853210907164</v>
       </c>
       <c r="D200" t="n">
-        <v>10.6918500263467</v>
+        <v>10.69185094372897</v>
       </c>
       <c r="E200" t="n">
-        <v>11.08349289539969</v>
+        <v>11.08349384638571</v>
       </c>
       <c r="F200" t="n">
         <v>5832500</v>
@@ -4512,16 +4512,16 @@
         <v>44943</v>
       </c>
       <c r="B205" t="n">
-        <v>11.74928665161133</v>
+        <v>11.74928569793701</v>
       </c>
       <c r="C205" t="n">
-        <v>11.93727505875722</v>
+        <v>11.93727408982413</v>
       </c>
       <c r="D205" t="n">
-        <v>11.60829497275214</v>
+        <v>11.60829403052194</v>
       </c>
       <c r="E205" t="n">
-        <v>11.81194945399329</v>
+        <v>11.81194849523272</v>
       </c>
       <c r="F205" t="n">
         <v>2676600</v>
@@ -4532,16 +4532,16 @@
         <v>44944</v>
       </c>
       <c r="B206" t="n">
-        <v>11.41247272491455</v>
+        <v>11.41247367858887</v>
       </c>
       <c r="C206" t="n">
-        <v>11.89027749318036</v>
+        <v>11.89027848678206</v>
       </c>
       <c r="D206" t="n">
-        <v>11.41247272491455</v>
+        <v>11.41247367858887</v>
       </c>
       <c r="E206" t="n">
-        <v>11.87461142018828</v>
+        <v>11.87461241248085</v>
       </c>
       <c r="F206" t="n">
         <v>3532000</v>
@@ -4552,16 +4552,16 @@
         <v>44945</v>
       </c>
       <c r="B207" t="n">
-        <v>11.66312599182129</v>
+        <v>11.66312503814697</v>
       </c>
       <c r="C207" t="n">
-        <v>11.68662435698559</v>
+        <v>11.68662340138985</v>
       </c>
       <c r="D207" t="n">
-        <v>11.27931537680668</v>
+        <v>11.27931445451592</v>
       </c>
       <c r="E207" t="n">
-        <v>11.3419781819112</v>
+        <v>11.3419772544966</v>
       </c>
       <c r="F207" t="n">
         <v>1847800</v>
@@ -4592,16 +4592,16 @@
         <v>44949</v>
       </c>
       <c r="B209" t="n">
-        <v>11.52213478088379</v>
+        <v>11.52213382720947</v>
       </c>
       <c r="C209" t="n">
-        <v>11.64746039624901</v>
+        <v>11.64745943220163</v>
       </c>
       <c r="D209" t="n">
-        <v>11.34981168625682</v>
+        <v>11.34981074684549</v>
       </c>
       <c r="E209" t="n">
-        <v>11.59263062627662</v>
+        <v>11.59262966676744</v>
       </c>
       <c r="F209" t="n">
         <v>1770800</v>
@@ -4672,16 +4672,16 @@
         <v>44953</v>
       </c>
       <c r="B213" t="n">
-        <v>11.98427104949951</v>
+        <v>11.98427200317383</v>
       </c>
       <c r="C213" t="n">
-        <v>12.23492222797812</v>
+        <v>12.23492320159854</v>
       </c>
       <c r="D213" t="n">
-        <v>11.92160825487986</v>
+        <v>11.92160920356765</v>
       </c>
       <c r="E213" t="n">
-        <v>11.96860497734488</v>
+        <v>11.96860592977254</v>
       </c>
       <c r="F213" t="n">
         <v>4160800</v>
@@ -4692,16 +4692,16 @@
         <v>44956</v>
       </c>
       <c r="B214" t="n">
-        <v>11.84327983856201</v>
+        <v>11.84328079223633</v>
       </c>
       <c r="C214" t="n">
-        <v>11.97643846894329</v>
+        <v>11.97643943334014</v>
       </c>
       <c r="D214" t="n">
-        <v>11.74928564305749</v>
+        <v>11.74928658916297</v>
       </c>
       <c r="E214" t="n">
-        <v>11.86677820068828</v>
+        <v>11.86677915625479</v>
       </c>
       <c r="F214" t="n">
         <v>3859300</v>
@@ -4732,16 +4732,16 @@
         <v>44958</v>
       </c>
       <c r="B216" t="n">
-        <v>12.07826709747314</v>
+        <v>12.07826614379883</v>
       </c>
       <c r="C216" t="n">
-        <v>12.19575966868999</v>
+        <v>12.19575870573871</v>
       </c>
       <c r="D216" t="n">
-        <v>11.93727541441329</v>
+        <v>11.93727447187138</v>
       </c>
       <c r="E216" t="n">
-        <v>12.08610013475415</v>
+        <v>12.08609918046135</v>
       </c>
       <c r="F216" t="n">
         <v>3741600</v>
@@ -4772,16 +4772,16 @@
         <v>44960</v>
       </c>
       <c r="B218" t="n">
-        <v>11.92160892486572</v>
+        <v>11.92160987854004</v>
       </c>
       <c r="C218" t="n">
-        <v>12.17226011743074</v>
+        <v>12.17226109115601</v>
       </c>
       <c r="D218" t="n">
-        <v>11.80411561810126</v>
+        <v>11.80411656237665</v>
       </c>
       <c r="E218" t="n">
-        <v>11.99993704904255</v>
+        <v>11.99993800898276</v>
       </c>
       <c r="F218" t="n">
         <v>3073100</v>
@@ -4832,16 +4832,16 @@
         <v>44965</v>
       </c>
       <c r="B221" t="n">
-        <v>11.71012306213379</v>
+        <v>11.71012210845947</v>
       </c>
       <c r="C221" t="n">
-        <v>11.78845194428836</v>
+        <v>11.78845098423493</v>
       </c>
       <c r="D221" t="n">
-        <v>11.54563300720885</v>
+        <v>11.54563206693063</v>
       </c>
       <c r="E221" t="n">
-        <v>11.68662469628725</v>
+        <v>11.68662374452664</v>
       </c>
       <c r="F221" t="n">
         <v>3697100</v>
@@ -4852,16 +4852,16 @@
         <v>44966</v>
       </c>
       <c r="B222" t="n">
-        <v>11.66312599182129</v>
+        <v>11.66312503814697</v>
       </c>
       <c r="C222" t="n">
-        <v>11.78845160203032</v>
+        <v>11.78845063810834</v>
       </c>
       <c r="D222" t="n">
-        <v>11.55346570938861</v>
+        <v>11.55346476468103</v>
       </c>
       <c r="E222" t="n">
-        <v>11.7101227221499</v>
+        <v>11.71012176463273</v>
       </c>
       <c r="F222" t="n">
         <v>2260100</v>
@@ -4872,16 +4872,16 @@
         <v>44967</v>
       </c>
       <c r="B223" t="n">
-        <v>11.72578907012939</v>
+        <v>11.72578811645508</v>
       </c>
       <c r="C223" t="n">
-        <v>11.88244608654069</v>
+        <v>11.88244512012525</v>
       </c>
       <c r="D223" t="n">
-        <v>11.62396182271216</v>
+        <v>11.62396087731959</v>
       </c>
       <c r="E223" t="n">
-        <v>11.62396182271216</v>
+        <v>11.62396087731959</v>
       </c>
       <c r="F223" t="n">
         <v>6075300</v>
@@ -4912,16 +4912,16 @@
         <v>44971</v>
       </c>
       <c r="B225" t="n">
-        <v>11.71795463562012</v>
+        <v>11.71795558929443</v>
       </c>
       <c r="C225" t="n">
-        <v>11.88244466999244</v>
+        <v>11.8824456370539</v>
       </c>
       <c r="D225" t="n">
-        <v>11.51430016506401</v>
+        <v>11.51430110216375</v>
       </c>
       <c r="E225" t="n">
-        <v>11.78061743471438</v>
+        <v>11.78061839348856</v>
       </c>
       <c r="F225" t="n">
         <v>2141000</v>
@@ -4932,16 +4932,16 @@
         <v>44972</v>
       </c>
       <c r="B226" t="n">
-        <v>11.75711917877197</v>
+        <v>11.75712013244629</v>
       </c>
       <c r="C226" t="n">
-        <v>11.92944150434928</v>
+        <v>11.92944247200145</v>
       </c>
       <c r="D226" t="n">
-        <v>11.63179357944321</v>
+        <v>11.63179452295179</v>
       </c>
       <c r="E226" t="n">
-        <v>11.6631249792754</v>
+        <v>11.66312592532541</v>
       </c>
       <c r="F226" t="n">
         <v>3961900</v>
@@ -4972,16 +4972,16 @@
         <v>44974</v>
       </c>
       <c r="B228" t="n">
-        <v>11.72578907012939</v>
+        <v>11.72578811645508</v>
       </c>
       <c r="C228" t="n">
-        <v>12.13309731279878</v>
+        <v>12.13309632599753</v>
       </c>
       <c r="D228" t="n">
-        <v>11.55346597857718</v>
+        <v>11.55346503891813</v>
       </c>
       <c r="E228" t="n">
-        <v>11.94510889310522</v>
+        <v>11.94510792159332</v>
       </c>
       <c r="F228" t="n">
         <v>9428300</v>
@@ -4992,16 +4992,16 @@
         <v>44979</v>
       </c>
       <c r="B229" t="n">
-        <v>11.71795463562012</v>
+        <v>11.71795558929443</v>
       </c>
       <c r="C229" t="n">
-        <v>11.95294050572336</v>
+        <v>11.95294147852217</v>
       </c>
       <c r="D229" t="n">
-        <v>11.66312487316251</v>
+        <v>11.66312582237446</v>
       </c>
       <c r="E229" t="n">
-        <v>11.89810999626626</v>
+        <v>11.89811096460265</v>
       </c>
       <c r="F229" t="n">
         <v>6185800</v>
@@ -5112,16 +5112,16 @@
         <v>44987</v>
       </c>
       <c r="B235" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="C235" t="n">
-        <v>11.67879055731306</v>
+        <v>11.67879152264125</v>
       </c>
       <c r="D235" t="n">
-        <v>11.45947075376244</v>
+        <v>11.45947170096243</v>
       </c>
       <c r="E235" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="F235" t="n">
         <v>2250800</v>
@@ -5132,16 +5132,16 @@
         <v>44988</v>
       </c>
       <c r="B236" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="C236" t="n">
-        <v>11.64745915680582</v>
+        <v>11.64746011954428</v>
       </c>
       <c r="D236" t="n">
-        <v>11.45947075376244</v>
+        <v>11.45947170096243</v>
       </c>
       <c r="E236" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="F236" t="n">
         <v>1727100</v>
@@ -5212,16 +5212,16 @@
         <v>44994</v>
       </c>
       <c r="B240" t="n">
-        <v>11.5769624710083</v>
+        <v>11.57696342468262</v>
       </c>
       <c r="C240" t="n">
-        <v>11.70228806385827</v>
+        <v>11.70228902785652</v>
       </c>
       <c r="D240" t="n">
-        <v>11.51429967458331</v>
+        <v>11.51430062309566</v>
       </c>
       <c r="E240" t="n">
-        <v>11.62395994182677</v>
+        <v>11.62396089937259</v>
       </c>
       <c r="F240" t="n">
         <v>2514900</v>
@@ -5232,16 +5232,16 @@
         <v>44995</v>
       </c>
       <c r="B241" t="n">
-        <v>11.5769624710083</v>
+        <v>11.57696342468262</v>
       </c>
       <c r="C241" t="n">
-        <v>11.63179297812976</v>
+        <v>11.63179393632084</v>
       </c>
       <c r="D241" t="n">
-        <v>11.44380384185534</v>
+        <v>11.44380478456046</v>
       </c>
       <c r="E241" t="n">
-        <v>11.5769624710083</v>
+        <v>11.57696342468262</v>
       </c>
       <c r="F241" t="n">
         <v>3626000</v>
@@ -5252,16 +5252,16 @@
         <v>44998</v>
       </c>
       <c r="B242" t="n">
-        <v>11.66312599182129</v>
+        <v>11.66312503814697</v>
       </c>
       <c r="C242" t="n">
-        <v>11.74145412470215</v>
+        <v>11.74145316462308</v>
       </c>
       <c r="D242" t="n">
-        <v>11.45947150173183</v>
+        <v>11.45947056471</v>
       </c>
       <c r="E242" t="n">
-        <v>11.52213430683635</v>
+        <v>11.52213336469069</v>
       </c>
       <c r="F242" t="n">
         <v>3223500</v>
@@ -5272,16 +5272,16 @@
         <v>44999</v>
       </c>
       <c r="B243" t="n">
-        <v>11.75711917877197</v>
+        <v>11.75712013244629</v>
       </c>
       <c r="C243" t="n">
-        <v>11.82761501514428</v>
+        <v>11.82761597453684</v>
       </c>
       <c r="D243" t="n">
-        <v>11.63962586915163</v>
+        <v>11.63962681329553</v>
       </c>
       <c r="E243" t="n">
-        <v>11.69445637910759</v>
+        <v>11.69445732769904</v>
       </c>
       <c r="F243" t="n">
         <v>2520000</v>
@@ -5292,16 +5292,16 @@
         <v>45000</v>
       </c>
       <c r="B244" t="n">
-        <v>11.74928665161133</v>
+        <v>11.74928569793701</v>
       </c>
       <c r="C244" t="n">
-        <v>11.89027833047051</v>
+        <v>11.89027736535209</v>
       </c>
       <c r="D244" t="n">
-        <v>11.61612800979977</v>
+        <v>11.61612706693377</v>
       </c>
       <c r="E244" t="n">
-        <v>11.71795525042035</v>
+        <v>11.71795429928916</v>
       </c>
       <c r="F244" t="n">
         <v>4602600</v>
@@ -5312,16 +5312,16 @@
         <v>45001</v>
       </c>
       <c r="B245" t="n">
-        <v>11.67095756530762</v>
+        <v>11.67095851898193</v>
       </c>
       <c r="C245" t="n">
-        <v>11.81194924163198</v>
+        <v>11.81195020682722</v>
       </c>
       <c r="D245" t="n">
-        <v>11.63962616467993</v>
+        <v>11.63962711579405</v>
       </c>
       <c r="E245" t="n">
-        <v>11.81194924163198</v>
+        <v>11.81195020682722</v>
       </c>
       <c r="F245" t="n">
         <v>5495800</v>
@@ -5332,16 +5332,16 @@
         <v>45002</v>
       </c>
       <c r="B246" t="n">
-        <v>11.40464210510254</v>
+        <v>11.40464115142822</v>
       </c>
       <c r="C246" t="n">
-        <v>11.66312637131919</v>
+        <v>11.66312539603</v>
       </c>
       <c r="D246" t="n">
-        <v>11.37331070153081</v>
+        <v>11.37330975047648</v>
       </c>
       <c r="E246" t="n">
-        <v>11.66312637131919</v>
+        <v>11.66312539603</v>
       </c>
       <c r="F246" t="n">
         <v>6196900</v>
@@ -5352,16 +5352,16 @@
         <v>45005</v>
       </c>
       <c r="B247" t="n">
-        <v>11.31847858428955</v>
+        <v>11.31847953796387</v>
       </c>
       <c r="C247" t="n">
-        <v>11.51430001566826</v>
+        <v>11.51430098584213</v>
       </c>
       <c r="D247" t="n">
-        <v>11.2479827494733</v>
+        <v>11.24798369720776</v>
       </c>
       <c r="E247" t="n">
-        <v>11.45163721738703</v>
+        <v>11.45163818228105</v>
       </c>
       <c r="F247" t="n">
         <v>2892000</v>
@@ -5392,16 +5392,16 @@
         <v>45007</v>
       </c>
       <c r="B249" t="n">
-        <v>11.33414459228516</v>
+        <v>11.33414554595947</v>
       </c>
       <c r="C249" t="n">
-        <v>11.45947018812806</v>
+        <v>11.45947115234749</v>
       </c>
       <c r="D249" t="n">
-        <v>11.21665128593282</v>
+        <v>11.21665222972105</v>
       </c>
       <c r="E249" t="n">
-        <v>11.36547599124588</v>
+        <v>11.36547694755648</v>
       </c>
       <c r="F249" t="n">
         <v>3006300</v>
@@ -5412,16 +5412,16 @@
         <v>45008</v>
       </c>
       <c r="B250" t="n">
-        <v>11.18532085418701</v>
+        <v>11.18532180786133</v>
       </c>
       <c r="C250" t="n">
-        <v>11.47513650638449</v>
+        <v>11.47513748476884</v>
       </c>
       <c r="D250" t="n">
-        <v>11.05999524750697</v>
+        <v>11.05999619049587</v>
       </c>
       <c r="E250" t="n">
-        <v>11.39680837570923</v>
+        <v>11.39680934741524</v>
       </c>
       <c r="F250" t="n">
         <v>4422500</v>
@@ -5512,16 +5512,16 @@
         <v>45015</v>
       </c>
       <c r="B255" t="n">
-        <v>11.40464210510254</v>
+        <v>11.40464115142822</v>
       </c>
       <c r="C255" t="n">
-        <v>11.50646860646096</v>
+        <v>11.50646764427175</v>
       </c>
       <c r="D255" t="n">
-        <v>11.12265872595741</v>
+        <v>11.12265779586299</v>
       </c>
       <c r="E255" t="n">
-        <v>11.42030743338861</v>
+        <v>11.42030647840433</v>
       </c>
       <c r="F255" t="n">
         <v>3320400</v>
@@ -5612,16 +5612,16 @@
         <v>45022</v>
       </c>
       <c r="B260" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="C260" t="n">
-        <v>11.6631252305592</v>
+        <v>11.66312619459255</v>
       </c>
       <c r="D260" t="n">
-        <v>11.4751360805163</v>
+        <v>11.47513702901113</v>
       </c>
       <c r="E260" t="n">
-        <v>11.49080215426967</v>
+        <v>11.4908031040594</v>
       </c>
       <c r="F260" t="n">
         <v>4653400</v>
@@ -5632,16 +5632,16 @@
         <v>45026</v>
       </c>
       <c r="B261" t="n">
-        <v>11.71795463562012</v>
+        <v>11.71795558929443</v>
       </c>
       <c r="C261" t="n">
-        <v>11.85111327044531</v>
+        <v>11.85111423495683</v>
       </c>
       <c r="D261" t="n">
-        <v>11.4594704026064</v>
+        <v>11.45947133524378</v>
       </c>
       <c r="E261" t="n">
-        <v>11.53779852797449</v>
+        <v>11.53779946698666</v>
       </c>
       <c r="F261" t="n">
         <v>3430500</v>
@@ -5672,16 +5672,16 @@
         <v>45028</v>
       </c>
       <c r="B263" t="n">
-        <v>11.80411720275879</v>
+        <v>11.80411624908447</v>
       </c>
       <c r="C263" t="n">
-        <v>12.01560473512652</v>
+        <v>12.01560376436578</v>
       </c>
       <c r="D263" t="n">
-        <v>11.74928743377437</v>
+        <v>11.74928648452985</v>
       </c>
       <c r="E263" t="n">
-        <v>11.82761631546603</v>
+        <v>11.82761535989319</v>
       </c>
       <c r="F263" t="n">
         <v>2987000</v>
@@ -5792,16 +5792,16 @@
         <v>45036</v>
       </c>
       <c r="B269" t="n">
-        <v>12.09393215179443</v>
+        <v>12.09393119812012</v>
       </c>
       <c r="C269" t="n">
-        <v>12.14092962741908</v>
+        <v>12.14092867003875</v>
       </c>
       <c r="D269" t="n">
-        <v>12.00777098464871</v>
+        <v>12.00777003776868</v>
       </c>
       <c r="E269" t="n">
-        <v>12.06260075037785</v>
+        <v>12.06259979917419</v>
       </c>
       <c r="F269" t="n">
         <v>4813100</v>
@@ -5812,16 +5812,16 @@
         <v>45040</v>
       </c>
       <c r="B270" t="n">
-        <v>12.10959911346436</v>
+        <v>12.10959815979004</v>
       </c>
       <c r="C270" t="n">
-        <v>12.17226192088982</v>
+        <v>12.17226096228058</v>
       </c>
       <c r="D270" t="n">
-        <v>12.03127023068273</v>
+        <v>12.0312692831771</v>
       </c>
       <c r="E270" t="n">
-        <v>12.10176607578628</v>
+        <v>12.10176512272884</v>
       </c>
       <c r="F270" t="n">
         <v>2389300</v>
@@ -5832,16 +5832,16 @@
         <v>45041</v>
       </c>
       <c r="B271" t="n">
-        <v>12.06260013580322</v>
+        <v>12.06260108947754</v>
       </c>
       <c r="C271" t="n">
-        <v>12.14092900885369</v>
+        <v>12.14092996872072</v>
       </c>
       <c r="D271" t="n">
-        <v>11.96860593634236</v>
+        <v>11.96860688258545</v>
       </c>
       <c r="E271" t="n">
-        <v>12.11743064573835</v>
+        <v>12.11743160374759</v>
       </c>
       <c r="F271" t="n">
         <v>2381100</v>
@@ -5872,16 +5872,16 @@
         <v>45043</v>
       </c>
       <c r="B273" t="n">
-        <v>12.07826709747314</v>
+        <v>12.07826614379883</v>
       </c>
       <c r="C273" t="n">
-        <v>12.0939324250356</v>
+        <v>12.09393147012438</v>
       </c>
       <c r="D273" t="n">
-        <v>11.95294148897529</v>
+        <v>11.95294054519642</v>
       </c>
       <c r="E273" t="n">
-        <v>12.01560429322422</v>
+        <v>12.01560334449763</v>
       </c>
       <c r="F273" t="n">
         <v>2919600</v>
@@ -5972,16 +5972,16 @@
         <v>45051</v>
       </c>
       <c r="B278" t="n">
-        <v>12.50989723205566</v>
+        <v>12.50989818572998</v>
       </c>
       <c r="C278" t="n">
-        <v>12.59647124671763</v>
+        <v>12.59647220699179</v>
       </c>
       <c r="D278" t="n">
-        <v>12.15494525807742</v>
+        <v>12.15494618469247</v>
       </c>
       <c r="E278" t="n">
-        <v>12.34540759495513</v>
+        <v>12.34540853608981</v>
       </c>
       <c r="F278" t="n">
         <v>9400800</v>
@@ -6032,16 +6032,16 @@
         <v>45056</v>
       </c>
       <c r="B281" t="n">
-        <v>11.86925315856934</v>
+        <v>11.86925220489502</v>
       </c>
       <c r="C281" t="n">
-        <v>12.05105794406462</v>
+        <v>12.0510569757826</v>
       </c>
       <c r="D281" t="n">
-        <v>11.69610594039075</v>
+        <v>11.69610500062852</v>
       </c>
       <c r="E281" t="n">
-        <v>12.0164285004289</v>
+        <v>12.0164275349293</v>
       </c>
       <c r="F281" t="n">
         <v>5308900</v>
@@ -6112,16 +6112,16 @@
         <v>45062</v>
       </c>
       <c r="B285" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="C285" t="n">
-        <v>12.30212128603885</v>
+        <v>12.30212031805942</v>
       </c>
       <c r="D285" t="n">
-        <v>12.08568706272756</v>
+        <v>12.08568611177803</v>
       </c>
       <c r="E285" t="n">
-        <v>12.18091782375736</v>
+        <v>12.18091686531469</v>
       </c>
       <c r="F285" t="n">
         <v>2907500</v>
@@ -6132,16 +6132,16 @@
         <v>45063</v>
       </c>
       <c r="B286" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="C286" t="n">
-        <v>12.24152036724783</v>
+        <v>12.24151939290137</v>
       </c>
       <c r="D286" t="n">
-        <v>11.9471696818366</v>
+        <v>11.94716873091856</v>
       </c>
       <c r="E286" t="n">
-        <v>12.128974468377</v>
+        <v>12.12897350298847</v>
       </c>
       <c r="F286" t="n">
         <v>4330800</v>
@@ -6152,16 +6152,16 @@
         <v>45064</v>
       </c>
       <c r="B287" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="C287" t="n">
-        <v>12.05971558070743</v>
+        <v>12.05971462083146</v>
       </c>
       <c r="D287" t="n">
-        <v>11.82596621559931</v>
+        <v>11.82596527432829</v>
       </c>
       <c r="E287" t="n">
-        <v>12.01642856950617</v>
+        <v>12.01642761307558</v>
       </c>
       <c r="F287" t="n">
         <v>4680600</v>
@@ -6172,16 +6172,16 @@
         <v>45065</v>
       </c>
       <c r="B288" t="n">
-        <v>12.09434509277344</v>
+        <v>12.09434413909912</v>
       </c>
       <c r="C288" t="n">
-        <v>12.18091829003328</v>
+        <v>12.18091732953242</v>
       </c>
       <c r="D288" t="n">
-        <v>11.93851218182222</v>
+        <v>11.93851124043578</v>
       </c>
       <c r="E288" t="n">
-        <v>11.99911350246722</v>
+        <v>11.99911255630219</v>
       </c>
       <c r="F288" t="n">
         <v>2962700</v>
@@ -6252,16 +6252,16 @@
         <v>45071</v>
       </c>
       <c r="B292" t="n">
-        <v>12.29346466064453</v>
+        <v>12.29346370697021</v>
       </c>
       <c r="C292" t="n">
-        <v>12.39735299671616</v>
+        <v>12.39735203498263</v>
       </c>
       <c r="D292" t="n">
-        <v>12.20689146006706</v>
+        <v>12.20689051310872</v>
       </c>
       <c r="E292" t="n">
-        <v>12.28480709289745</v>
+        <v>12.28480613989475</v>
       </c>
       <c r="F292" t="n">
         <v>2204600</v>
@@ -6292,16 +6292,16 @@
         <v>45075</v>
       </c>
       <c r="B294" t="n">
-        <v>12.28480529785156</v>
+        <v>12.28480625152588</v>
       </c>
       <c r="C294" t="n">
-        <v>12.34540743759487</v>
+        <v>12.34540839597375</v>
       </c>
       <c r="D294" t="n">
-        <v>12.16360266962691</v>
+        <v>12.16360361389222</v>
       </c>
       <c r="E294" t="n">
-        <v>12.16360266962691</v>
+        <v>12.16360361389222</v>
       </c>
       <c r="F294" t="n">
         <v>1431900</v>
@@ -6312,16 +6312,16 @@
         <v>45076</v>
       </c>
       <c r="B295" t="n">
-        <v>12.26749229431152</v>
+        <v>12.26749134063721</v>
       </c>
       <c r="C295" t="n">
-        <v>12.38003819364653</v>
+        <v>12.3800372312229</v>
       </c>
       <c r="D295" t="n">
-        <v>12.25017715950718</v>
+        <v>12.25017620717894</v>
       </c>
       <c r="E295" t="n">
-        <v>12.37138062624436</v>
+        <v>12.37137966449377</v>
       </c>
       <c r="F295" t="n">
         <v>1829100</v>
@@ -6392,16 +6392,16 @@
         <v>45082</v>
       </c>
       <c r="B299" t="n">
-        <v>12.06837177276611</v>
+        <v>12.0683708190918</v>
       </c>
       <c r="C299" t="n">
-        <v>12.1982328004551</v>
+        <v>12.19823183651883</v>
       </c>
       <c r="D299" t="n">
-        <v>11.97314101296568</v>
+        <v>11.97314006681674</v>
       </c>
       <c r="E299" t="n">
-        <v>12.17226092516972</v>
+        <v>12.17225996328581</v>
       </c>
       <c r="F299" t="n">
         <v>3442900</v>
@@ -6432,16 +6432,16 @@
         <v>45084</v>
       </c>
       <c r="B301" t="n">
-        <v>12.22420597076416</v>
+        <v>12.22420501708984</v>
       </c>
       <c r="C301" t="n">
-        <v>12.46661209224716</v>
+        <v>12.46661111966148</v>
       </c>
       <c r="D301" t="n">
-        <v>12.21554840287484</v>
+        <v>12.21554744987595</v>
       </c>
       <c r="E301" t="n">
-        <v>12.38003889024736</v>
+        <v>12.3800379244157</v>
       </c>
       <c r="F301" t="n">
         <v>3154600</v>
@@ -6472,16 +6472,16 @@
         <v>45089</v>
       </c>
       <c r="B303" t="n">
-        <v>12.45795345306396</v>
+        <v>12.45795440673828</v>
       </c>
       <c r="C303" t="n">
-        <v>12.45795345306396</v>
+        <v>12.45795440673828</v>
       </c>
       <c r="D303" t="n">
-        <v>12.25883355008453</v>
+        <v>12.25883448851593</v>
       </c>
       <c r="E303" t="n">
-        <v>12.3800370051864</v>
+        <v>12.3800379528961</v>
       </c>
       <c r="F303" t="n">
         <v>2572800</v>
@@ -6492,16 +6492,16 @@
         <v>45090</v>
       </c>
       <c r="B304" t="n">
-        <v>12.31077861785889</v>
+        <v>12.3107795715332</v>
       </c>
       <c r="C304" t="n">
-        <v>12.50124013627868</v>
+        <v>12.5012411047074</v>
       </c>
       <c r="D304" t="n">
-        <v>12.29346348402198</v>
+        <v>12.29346443635495</v>
       </c>
       <c r="E304" t="n">
-        <v>12.46661069423589</v>
+        <v>12.46661165998199</v>
       </c>
       <c r="F304" t="n">
         <v>1312000</v>
@@ -6532,16 +6532,16 @@
         <v>45092</v>
       </c>
       <c r="B306" t="n">
-        <v>12.46661186218262</v>
+        <v>12.4666109085083</v>
       </c>
       <c r="C306" t="n">
-        <v>12.49258456537125</v>
+        <v>12.49258360971007</v>
       </c>
       <c r="D306" t="n">
-        <v>12.36272352632139</v>
+        <v>12.36272258059435</v>
       </c>
       <c r="E306" t="n">
-        <v>12.45795512008417</v>
+        <v>12.45795416707208</v>
       </c>
       <c r="F306" t="n">
         <v>1266000</v>
@@ -6552,16 +6552,16 @@
         <v>45093</v>
       </c>
       <c r="B307" t="n">
-        <v>12.62244319915771</v>
+        <v>12.62244415283203</v>
       </c>
       <c r="C307" t="n">
-        <v>12.83021984487801</v>
+        <v>12.83022081425066</v>
       </c>
       <c r="D307" t="n">
-        <v>12.4406384277447</v>
+        <v>12.44063936768297</v>
       </c>
       <c r="E307" t="n">
-        <v>12.46661030205199</v>
+        <v>12.46661124395253</v>
       </c>
       <c r="F307" t="n">
         <v>5319000</v>
@@ -6612,16 +6612,16 @@
         <v>45098</v>
       </c>
       <c r="B310" t="n">
-        <v>12.86484909057617</v>
+        <v>12.86485004425049</v>
       </c>
       <c r="C310" t="n">
-        <v>12.90813609751867</v>
+        <v>12.90813705440186</v>
       </c>
       <c r="D310" t="n">
-        <v>12.63975814061098</v>
+        <v>12.63975907759925</v>
       </c>
       <c r="E310" t="n">
-        <v>12.75230320277808</v>
+        <v>12.75230414810935</v>
       </c>
       <c r="F310" t="n">
         <v>5022600</v>
@@ -6692,16 +6692,16 @@
         <v>45104</v>
       </c>
       <c r="B314" t="n">
-        <v>12.50124073028564</v>
+        <v>12.50123977661133</v>
       </c>
       <c r="C314" t="n">
-        <v>12.83887842546918</v>
+        <v>12.83887744603771</v>
       </c>
       <c r="D314" t="n">
-        <v>12.39735239922096</v>
+        <v>12.3973514534719</v>
       </c>
       <c r="E314" t="n">
-        <v>12.76961953809272</v>
+        <v>12.76961856394476</v>
       </c>
       <c r="F314" t="n">
         <v>3014700</v>
@@ -6872,16 +6872,16 @@
         <v>45117</v>
       </c>
       <c r="B323" t="n">
-        <v>12.38869476318359</v>
+        <v>12.38869571685791</v>
       </c>
       <c r="C323" t="n">
-        <v>12.45795364556026</v>
+        <v>12.45795460456609</v>
       </c>
       <c r="D323" t="n">
-        <v>12.31077831410209</v>
+        <v>12.31077926177845</v>
       </c>
       <c r="E323" t="n">
-        <v>12.38003719647876</v>
+        <v>12.38003814948662</v>
       </c>
       <c r="F323" t="n">
         <v>1514600</v>
@@ -6912,16 +6912,16 @@
         <v>45119</v>
       </c>
       <c r="B325" t="n">
-        <v>12.38869476318359</v>
+        <v>12.38869571685791</v>
       </c>
       <c r="C325" t="n">
-        <v>12.45795364556026</v>
+        <v>12.45795460456609</v>
       </c>
       <c r="D325" t="n">
-        <v>12.28480561398759</v>
+        <v>12.28480655966458</v>
       </c>
       <c r="E325" t="n">
-        <v>12.37137962977392</v>
+        <v>12.37138058211533</v>
       </c>
       <c r="F325" t="n">
         <v>1842800</v>
@@ -7052,16 +7052,16 @@
         <v>45128</v>
       </c>
       <c r="B332" t="n">
-        <v>12.38869476318359</v>
+        <v>12.38869571685791</v>
       </c>
       <c r="C332" t="n">
-        <v>12.38869476318359</v>
+        <v>12.38869571685791</v>
       </c>
       <c r="D332" t="n">
-        <v>12.22420429831576</v>
+        <v>12.2242052393277</v>
       </c>
       <c r="E332" t="n">
-        <v>12.27614887291376</v>
+        <v>12.27614981792436</v>
       </c>
       <c r="F332" t="n">
         <v>2631400</v>
@@ -7152,16 +7152,16 @@
         <v>45135</v>
       </c>
       <c r="B337" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="C337" t="n">
-        <v>12.22420483354582</v>
+        <v>12.22420387169716</v>
       </c>
       <c r="D337" t="n">
-        <v>12.0597151871069</v>
+        <v>12.05971423820094</v>
       </c>
       <c r="E337" t="n">
-        <v>12.14628838105279</v>
+        <v>12.14628742533491</v>
       </c>
       <c r="F337" t="n">
         <v>1506100</v>
@@ -7172,16 +7172,16 @@
         <v>45138</v>
       </c>
       <c r="B338" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="C338" t="n">
-        <v>12.20689052500906</v>
+        <v>12.20688956452276</v>
       </c>
       <c r="D338" t="n">
-        <v>12.10300137126433</v>
+        <v>12.10300041895243</v>
       </c>
       <c r="E338" t="n">
-        <v>12.20689052500906</v>
+        <v>12.20688956452276</v>
       </c>
       <c r="F338" t="n">
         <v>1549400</v>
@@ -7212,16 +7212,16 @@
         <v>45140</v>
       </c>
       <c r="B340" t="n">
-        <v>12.22420597076416</v>
+        <v>12.22420501708984</v>
       </c>
       <c r="C340" t="n">
-        <v>12.23286353865348</v>
+        <v>12.23286258430374</v>
       </c>
       <c r="D340" t="n">
-        <v>12.12897520087505</v>
+        <v>12.12897425463018</v>
       </c>
       <c r="E340" t="n">
-        <v>12.13763276876436</v>
+        <v>12.13763182184407</v>
       </c>
       <c r="F340" t="n">
         <v>1697600</v>
@@ -7332,16 +7332,16 @@
         <v>45148</v>
       </c>
       <c r="B346" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C346" t="n">
-        <v>12.09434549372545</v>
+        <v>12.09434452900206</v>
       </c>
       <c r="D346" t="n">
-        <v>11.88656799702522</v>
+        <v>11.88656704887551</v>
       </c>
       <c r="E346" t="n">
-        <v>12.01642903566675</v>
+        <v>12.01642807715848</v>
       </c>
       <c r="F346" t="n">
         <v>2835300</v>
@@ -7412,16 +7412,16 @@
         <v>45154</v>
       </c>
       <c r="B350" t="n">
-        <v>11.68744850158691</v>
+        <v>11.6874475479126</v>
       </c>
       <c r="C350" t="n">
-        <v>11.91254030050967</v>
+        <v>11.91253932846828</v>
       </c>
       <c r="D350" t="n">
-        <v>11.64416149015853</v>
+        <v>11.64416054001635</v>
       </c>
       <c r="E350" t="n">
-        <v>11.886567598274</v>
+        <v>11.88656662835193</v>
       </c>
       <c r="F350" t="n">
         <v>3946200</v>
@@ -7432,16 +7432,16 @@
         <v>45155</v>
       </c>
       <c r="B351" t="n">
-        <v>11.71342086791992</v>
+        <v>11.71341991424561</v>
       </c>
       <c r="C351" t="n">
-        <v>11.78267975884857</v>
+        <v>11.78267879953539</v>
       </c>
       <c r="D351" t="n">
-        <v>11.66147711253899</v>
+        <v>11.66147616309379</v>
       </c>
       <c r="E351" t="n">
-        <v>11.73073600346764</v>
+        <v>11.73073504838357</v>
       </c>
       <c r="F351" t="n">
         <v>2345000</v>
@@ -7452,16 +7452,16 @@
         <v>45156</v>
       </c>
       <c r="B352" t="n">
-        <v>11.77402114868164</v>
+        <v>11.77402210235596</v>
       </c>
       <c r="C352" t="n">
-        <v>11.80865058865178</v>
+        <v>11.80865154513102</v>
       </c>
       <c r="D352" t="n">
-        <v>11.65281769597066</v>
+        <v>11.65281863982772</v>
       </c>
       <c r="E352" t="n">
-        <v>11.71341900951066</v>
+        <v>11.71341995827632</v>
       </c>
       <c r="F352" t="n">
         <v>3061800</v>
@@ -7512,16 +7512,16 @@
         <v>45161</v>
       </c>
       <c r="B355" t="n">
-        <v>11.87790966033936</v>
+        <v>11.87791061401367</v>
       </c>
       <c r="C355" t="n">
-        <v>11.89522396778845</v>
+        <v>11.89522492285292</v>
       </c>
       <c r="D355" t="n">
-        <v>11.79133564620093</v>
+        <v>11.79133659292425</v>
       </c>
       <c r="E355" t="n">
-        <v>11.86059452725928</v>
+        <v>11.86059547954337</v>
       </c>
       <c r="F355" t="n">
         <v>2615000</v>
@@ -7532,16 +7532,16 @@
         <v>45162</v>
       </c>
       <c r="B356" t="n">
-        <v>11.97314071655273</v>
+        <v>11.97314167022705</v>
       </c>
       <c r="C356" t="n">
-        <v>11.99911259119515</v>
+        <v>11.99911354693815</v>
       </c>
       <c r="D356" t="n">
-        <v>11.89522426699448</v>
+        <v>11.89522521446267</v>
       </c>
       <c r="E356" t="n">
-        <v>11.90388183375229</v>
+        <v>11.90388278191006</v>
       </c>
       <c r="F356" t="n">
         <v>2322800</v>
@@ -7592,16 +7592,16 @@
         <v>45167</v>
       </c>
       <c r="B359" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="C359" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="D359" t="n">
-        <v>11.97314116752997</v>
+        <v>11.97314022543599</v>
       </c>
       <c r="E359" t="n">
-        <v>11.98179873461387</v>
+        <v>11.98179779183868</v>
       </c>
       <c r="F359" t="n">
         <v>1776800</v>
@@ -7632,16 +7632,16 @@
         <v>45169</v>
       </c>
       <c r="B361" t="n">
-        <v>11.78267955780029</v>
+        <v>11.78267860412598</v>
       </c>
       <c r="C361" t="n">
-        <v>12.12031726453966</v>
+        <v>12.1203162835374</v>
       </c>
       <c r="D361" t="n">
-        <v>11.78267955780029</v>
+        <v>11.78267860412598</v>
       </c>
       <c r="E361" t="n">
-        <v>12.12031726453966</v>
+        <v>12.1203162835374</v>
       </c>
       <c r="F361" t="n">
         <v>3236500</v>
@@ -7712,16 +7712,16 @@
         <v>45175</v>
       </c>
       <c r="B365" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C365" t="n">
-        <v>12.02508660336907</v>
+        <v>12.02508564417022</v>
       </c>
       <c r="D365" t="n">
-        <v>11.81730910666884</v>
+        <v>11.81730816404367</v>
       </c>
       <c r="E365" t="n">
-        <v>11.93851257760805</v>
+        <v>11.9385116253149</v>
       </c>
       <c r="F365" t="n">
         <v>2473500</v>
@@ -7732,16 +7732,16 @@
         <v>45177</v>
       </c>
       <c r="B366" t="n">
-        <v>11.92985343933105</v>
+        <v>11.92985439300537</v>
       </c>
       <c r="C366" t="n">
-        <v>12.07702876837038</v>
+        <v>12.07702973380992</v>
       </c>
       <c r="D366" t="n">
-        <v>11.88656643214931</v>
+        <v>11.88656738236326</v>
       </c>
       <c r="E366" t="n">
-        <v>11.9385110058936</v>
+        <v>11.93851196026</v>
       </c>
       <c r="F366" t="n">
         <v>3462800</v>
@@ -7772,16 +7772,16 @@
         <v>45181</v>
       </c>
       <c r="B368" t="n">
-        <v>12.06837177276611</v>
+        <v>12.0683708190918</v>
       </c>
       <c r="C368" t="n">
-        <v>12.15494579122544</v>
+        <v>12.15494483070982</v>
       </c>
       <c r="D368" t="n">
-        <v>11.98179857993782</v>
+        <v>11.98179763310474</v>
       </c>
       <c r="E368" t="n">
-        <v>12.03374233050859</v>
+        <v>12.03374137957078</v>
       </c>
       <c r="F368" t="n">
         <v>2215400</v>
@@ -7792,16 +7792,16 @@
         <v>45182</v>
       </c>
       <c r="B369" t="n">
-        <v>12.06837177276611</v>
+        <v>12.0683708190918</v>
       </c>
       <c r="C369" t="n">
-        <v>12.1982328004551</v>
+        <v>12.19823183651883</v>
       </c>
       <c r="D369" t="n">
-        <v>12.03374233050859</v>
+        <v>12.03374137957078</v>
       </c>
       <c r="E369" t="n">
-        <v>12.07702933973825</v>
+        <v>12.07702838537979</v>
       </c>
       <c r="F369" t="n">
         <v>1684100</v>
@@ -7892,16 +7892,16 @@
         <v>45189</v>
       </c>
       <c r="B374" t="n">
-        <v>12.06837177276611</v>
+        <v>12.0683708190918</v>
       </c>
       <c r="C374" t="n">
-        <v>12.1462882242533</v>
+        <v>12.14628726442182</v>
       </c>
       <c r="D374" t="n">
-        <v>11.97314101296568</v>
+        <v>11.97314006681674</v>
       </c>
       <c r="E374" t="n">
-        <v>12.08568690671039</v>
+        <v>12.08568595166779</v>
       </c>
       <c r="F374" t="n">
         <v>2998000</v>
@@ -7912,16 +7912,16 @@
         <v>45190</v>
       </c>
       <c r="B375" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C375" t="n">
-        <v>12.0337433454403</v>
+        <v>12.03374238555092</v>
       </c>
       <c r="D375" t="n">
-        <v>11.877911254954</v>
+        <v>11.8779103074948</v>
       </c>
       <c r="E375" t="n">
-        <v>12.02508660336907</v>
+        <v>12.02508564417022</v>
       </c>
       <c r="F375" t="n">
         <v>4405700</v>
@@ -7932,16 +7932,16 @@
         <v>45191</v>
       </c>
       <c r="B376" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C376" t="n">
-        <v>12.10300223579667</v>
+        <v>12.10300127038276</v>
       </c>
       <c r="D376" t="n">
-        <v>11.92985500990573</v>
+        <v>11.92985405830317</v>
       </c>
       <c r="E376" t="n">
-        <v>12.02508660336907</v>
+        <v>12.02508564417022</v>
       </c>
       <c r="F376" t="n">
         <v>2812600</v>
@@ -8012,16 +8012,16 @@
         <v>45197</v>
       </c>
       <c r="B380" t="n">
-        <v>11.78267955780029</v>
+        <v>11.78267860412598</v>
       </c>
       <c r="C380" t="n">
-        <v>11.86059601517331</v>
+        <v>11.86059505519254</v>
       </c>
       <c r="D380" t="n">
-        <v>11.73073580330568</v>
+        <v>11.73073485383562</v>
       </c>
       <c r="E380" t="n">
-        <v>11.85193844754717</v>
+        <v>11.85193748826714</v>
       </c>
       <c r="F380" t="n">
         <v>2404900</v>
@@ -8092,16 +8092,16 @@
         <v>45203</v>
       </c>
       <c r="B384" t="n">
-        <v>11.77402114868164</v>
+        <v>11.77402210235596</v>
       </c>
       <c r="C384" t="n">
-        <v>11.86059433579151</v>
+        <v>11.86059529647809</v>
       </c>
       <c r="D384" t="n">
-        <v>11.7480484494808</v>
+        <v>11.74804940105138</v>
       </c>
       <c r="E384" t="n">
-        <v>11.80865058865178</v>
+        <v>11.80865154513102</v>
       </c>
       <c r="F384" t="n">
         <v>4367600</v>
@@ -8192,16 +8192,16 @@
         <v>45210</v>
       </c>
       <c r="B389" t="n">
-        <v>12.09434509277344</v>
+        <v>12.09434413909912</v>
       </c>
       <c r="C389" t="n">
-        <v>12.18957585744859</v>
+        <v>12.18957489626505</v>
       </c>
       <c r="D389" t="n">
-        <v>12.00777106988252</v>
+        <v>12.00777012303482</v>
       </c>
       <c r="E389" t="n">
-        <v>12.09434509277344</v>
+        <v>12.09434413909912</v>
       </c>
       <c r="F389" t="n">
         <v>3458500</v>
@@ -8232,16 +8232,16 @@
         <v>45215</v>
       </c>
       <c r="B391" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="C391" t="n">
-        <v>12.12031690101054</v>
+        <v>12.12031593631109</v>
       </c>
       <c r="D391" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="E391" t="n">
-        <v>12.05971558070743</v>
+        <v>12.05971462083146</v>
       </c>
       <c r="F391" t="n">
         <v>3983600</v>
@@ -8252,16 +8252,16 @@
         <v>45216</v>
       </c>
       <c r="B392" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C392" t="n">
-        <v>12.10300223579667</v>
+        <v>12.10300127038276</v>
       </c>
       <c r="D392" t="n">
-        <v>11.88656799702522</v>
+        <v>11.88656704887551</v>
       </c>
       <c r="E392" t="n">
-        <v>11.97314202278624</v>
+        <v>11.97314106773082</v>
       </c>
       <c r="F392" t="n">
         <v>5165000</v>
@@ -8292,16 +8292,16 @@
         <v>45218</v>
       </c>
       <c r="B394" t="n">
-        <v>11.67013263702393</v>
+        <v>11.67013359069824</v>
       </c>
       <c r="C394" t="n">
-        <v>11.75670665446719</v>
+        <v>11.75670761521626</v>
       </c>
       <c r="D394" t="n">
-        <v>11.62684645393332</v>
+        <v>11.62684740407032</v>
       </c>
       <c r="E394" t="n">
-        <v>11.66147589578441</v>
+        <v>11.66147684875131</v>
       </c>
       <c r="F394" t="n">
         <v>3066300</v>
@@ -8452,16 +8452,16 @@
         <v>45230</v>
       </c>
       <c r="B402" t="n">
-        <v>11.61818885803223</v>
+        <v>11.61818981170654</v>
       </c>
       <c r="C402" t="n">
-        <v>11.6614758666457</v>
+        <v>11.66147682387321</v>
       </c>
       <c r="D402" t="n">
-        <v>11.52295809958741</v>
+        <v>11.52295904544475</v>
       </c>
       <c r="E402" t="n">
-        <v>11.52295809958741</v>
+        <v>11.52295904544475</v>
       </c>
       <c r="F402" t="n">
         <v>3290000</v>
@@ -8592,16 +8592,16 @@
         <v>45240</v>
       </c>
       <c r="B409" t="n">
-        <v>11.78267955780029</v>
+        <v>11.78267860412598</v>
       </c>
       <c r="C409" t="n">
-        <v>11.86059601517331</v>
+        <v>11.86059505519254</v>
       </c>
       <c r="D409" t="n">
-        <v>11.69610635843224</v>
+        <v>11.69610541176504</v>
       </c>
       <c r="E409" t="n">
-        <v>11.69610635843224</v>
+        <v>11.69610541176504</v>
       </c>
       <c r="F409" t="n">
         <v>3430000</v>
@@ -8712,16 +8712,16 @@
         <v>45251</v>
       </c>
       <c r="B415" t="n">
-        <v>11.97314071655273</v>
+        <v>11.97314167022705</v>
       </c>
       <c r="C415" t="n">
-        <v>12.09434417426901</v>
+        <v>12.09434513759732</v>
       </c>
       <c r="D415" t="n">
-        <v>11.9125394005101</v>
+        <v>11.91254034935745</v>
       </c>
       <c r="E415" t="n">
-        <v>12.0856866075112</v>
+        <v>12.08568757014993</v>
       </c>
       <c r="F415" t="n">
         <v>2713400</v>
@@ -8732,16 +8732,16 @@
         <v>45252</v>
       </c>
       <c r="B416" t="n">
-        <v>12.46661186218262</v>
+        <v>12.4666109085083</v>
       </c>
       <c r="C416" t="n">
-        <v>12.94276735410323</v>
+        <v>12.94276636400384</v>
       </c>
       <c r="D416" t="n">
-        <v>12.44063998462508</v>
+        <v>12.44063903293757</v>
       </c>
       <c r="E416" t="n">
-        <v>12.81290714068447</v>
+        <v>12.81290616051917</v>
       </c>
       <c r="F416" t="n">
         <v>20875500</v>
@@ -8752,16 +8752,16 @@
         <v>45253</v>
       </c>
       <c r="B417" t="n">
-        <v>12.56184196472168</v>
+        <v>12.561842918396</v>
       </c>
       <c r="C417" t="n">
-        <v>12.76961861177884</v>
+        <v>12.76961958122722</v>
       </c>
       <c r="D417" t="n">
-        <v>12.46661038226389</v>
+        <v>12.46661132870839</v>
       </c>
       <c r="E417" t="n">
-        <v>12.76961861177884</v>
+        <v>12.76961958122722</v>
       </c>
       <c r="F417" t="n">
         <v>9122900</v>
@@ -8832,16 +8832,16 @@
         <v>45259</v>
       </c>
       <c r="B421" t="n">
-        <v>12.56184196472168</v>
+        <v>12.561842918396</v>
       </c>
       <c r="C421" t="n">
-        <v>12.75230347837524</v>
+        <v>12.75230444650908</v>
       </c>
       <c r="D421" t="n">
-        <v>12.56184196472168</v>
+        <v>12.561842918396</v>
       </c>
       <c r="E421" t="n">
-        <v>12.72633160390085</v>
+        <v>12.72633257006295</v>
       </c>
       <c r="F421" t="n">
         <v>5869600</v>
@@ -8872,16 +8872,16 @@
         <v>45261</v>
       </c>
       <c r="B423" t="n">
-        <v>12.86484909057617</v>
+        <v>12.86485004425049</v>
       </c>
       <c r="C423" t="n">
-        <v>12.96873741185957</v>
+        <v>12.96873837323515</v>
       </c>
       <c r="D423" t="n">
-        <v>12.70901702146657</v>
+        <v>12.70901796358902</v>
       </c>
       <c r="E423" t="n">
-        <v>12.72633132886498</v>
+        <v>12.72633227227094</v>
       </c>
       <c r="F423" t="n">
         <v>6458300</v>
@@ -8912,16 +8912,16 @@
         <v>45265</v>
       </c>
       <c r="B425" t="n">
-        <v>13.15920066833496</v>
+        <v>13.15919971466064</v>
       </c>
       <c r="C425" t="n">
-        <v>13.20248767830808</v>
+        <v>13.20248672149667</v>
       </c>
       <c r="D425" t="n">
-        <v>12.92545213548978</v>
+        <v>12.9254511987557</v>
       </c>
       <c r="E425" t="n">
-        <v>12.96008157834207</v>
+        <v>12.96008063909832</v>
       </c>
       <c r="F425" t="n">
         <v>6696500</v>
@@ -8952,16 +8952,16 @@
         <v>45267</v>
       </c>
       <c r="B427" t="n">
-        <v>13.1159143447876</v>
+        <v>13.11591339111328</v>
       </c>
       <c r="C427" t="n">
-        <v>13.15054378945223</v>
+        <v>13.15054283325996</v>
       </c>
       <c r="D427" t="n">
-        <v>12.97739656612907</v>
+        <v>12.97739562252655</v>
       </c>
       <c r="E427" t="n">
-        <v>13.10725760284475</v>
+        <v>13.10725664979988</v>
       </c>
       <c r="F427" t="n">
         <v>6196000</v>
@@ -9052,16 +9052,16 @@
         <v>45274</v>
       </c>
       <c r="B432" t="n">
-        <v>12.94470024108887</v>
+        <v>12.94470119476318</v>
       </c>
       <c r="C432" t="n">
-        <v>12.98319745470858</v>
+        <v>12.9831984112191</v>
       </c>
       <c r="D432" t="n">
-        <v>12.71371695937057</v>
+        <v>12.71371789602766</v>
       </c>
       <c r="E432" t="n">
-        <v>12.71371695937057</v>
+        <v>12.71371789602766</v>
       </c>
       <c r="F432" t="n">
         <v>5480800</v>
@@ -9092,16 +9092,16 @@
         <v>45278</v>
       </c>
       <c r="B434" t="n">
-        <v>12.84845733642578</v>
+        <v>12.8484582901001</v>
       </c>
       <c r="C434" t="n">
-        <v>13.0890651448394</v>
+        <v>13.08906611637279</v>
       </c>
       <c r="D434" t="n">
-        <v>12.84845733642578</v>
+        <v>12.8484582901001</v>
       </c>
       <c r="E434" t="n">
-        <v>12.983197121716</v>
+        <v>12.98319808539135</v>
       </c>
       <c r="F434" t="n">
         <v>3314300</v>
@@ -9112,16 +9112,16 @@
         <v>45279</v>
       </c>
       <c r="B435" t="n">
-        <v>12.86770629882812</v>
+        <v>12.86770534515381</v>
       </c>
       <c r="C435" t="n">
-        <v>12.94470072896945</v>
+        <v>12.94469976958878</v>
       </c>
       <c r="D435" t="n">
-        <v>12.7907118686868</v>
+        <v>12.79071092071883</v>
       </c>
       <c r="E435" t="n">
-        <v>12.87733083205729</v>
+        <v>12.87732987766966</v>
       </c>
       <c r="F435" t="n">
         <v>4780200</v>
@@ -9232,16 +9232,16 @@
         <v>45288</v>
       </c>
       <c r="B441" t="n">
-        <v>12.80996036529541</v>
+        <v>12.80996131896973</v>
       </c>
       <c r="C441" t="n">
-        <v>12.88695479201164</v>
+        <v>12.88695575141803</v>
       </c>
       <c r="D441" t="n">
-        <v>12.76183861913627</v>
+        <v>12.76183956922803</v>
       </c>
       <c r="E441" t="n">
-        <v>12.88695479201164</v>
+        <v>12.88695575141803</v>
       </c>
       <c r="F441" t="n">
         <v>3487000</v>
@@ -9332,16 +9332,16 @@
         <v>45299</v>
       </c>
       <c r="B446" t="n">
-        <v>13.01207065582275</v>
+        <v>13.01207160949707</v>
       </c>
       <c r="C446" t="n">
-        <v>13.09868869543668</v>
+        <v>13.09868965545936</v>
       </c>
       <c r="D446" t="n">
-        <v>12.88695448591916</v>
+        <v>12.88695543042352</v>
       </c>
       <c r="E446" t="n">
-        <v>12.95432437823419</v>
+        <v>12.9543253276762</v>
       </c>
       <c r="F446" t="n">
         <v>3738800</v>
@@ -9392,16 +9392,16 @@
         <v>45302</v>
       </c>
       <c r="B449" t="n">
-        <v>12.84845733642578</v>
+        <v>12.8484582901001</v>
       </c>
       <c r="C449" t="n">
-        <v>12.94469990908366</v>
+        <v>12.94470086990156</v>
       </c>
       <c r="D449" t="n">
-        <v>12.74258931330238</v>
+        <v>12.74259025911866</v>
       </c>
       <c r="E449" t="n">
-        <v>12.94469990908366</v>
+        <v>12.94470086990156</v>
       </c>
       <c r="F449" t="n">
         <v>4814200</v>
@@ -9412,16 +9412,16 @@
         <v>45303</v>
       </c>
       <c r="B450" t="n">
-        <v>12.77146434783936</v>
+        <v>12.77146339416504</v>
       </c>
       <c r="C450" t="n">
-        <v>12.88695599872818</v>
+        <v>12.88695503642984</v>
       </c>
       <c r="D450" t="n">
-        <v>12.74259074673261</v>
+        <v>12.74258979521435</v>
       </c>
       <c r="E450" t="n">
-        <v>12.84845878176524</v>
+        <v>12.84845782234157</v>
       </c>
       <c r="F450" t="n">
         <v>4041800</v>
@@ -9432,16 +9432,16 @@
         <v>45306</v>
       </c>
       <c r="B451" t="n">
-        <v>12.80996036529541</v>
+        <v>12.80996131896973</v>
       </c>
       <c r="C451" t="n">
-        <v>12.84845757865353</v>
+        <v>12.84845853519388</v>
       </c>
       <c r="D451" t="n">
-        <v>12.74258955353423</v>
+        <v>12.74259050219293</v>
       </c>
       <c r="E451" t="n">
-        <v>12.77146315193729</v>
+        <v>12.77146410274557</v>
       </c>
       <c r="F451" t="n">
         <v>1955800</v>
@@ -9492,16 +9492,16 @@
         <v>45309</v>
       </c>
       <c r="B454" t="n">
-        <v>12.55972766876221</v>
+        <v>12.55972862243652</v>
       </c>
       <c r="C454" t="n">
-        <v>12.77146279524125</v>
+        <v>12.77146376499286</v>
       </c>
       <c r="D454" t="n">
-        <v>12.51160592394707</v>
+        <v>12.51160687396745</v>
       </c>
       <c r="E454" t="n">
-        <v>12.76183826270904</v>
+        <v>12.76183923172984</v>
       </c>
       <c r="F454" t="n">
         <v>6534900</v>
@@ -9532,16 +9532,16 @@
         <v>45313</v>
       </c>
       <c r="B456" t="n">
-        <v>12.61747360229492</v>
+        <v>12.61747455596924</v>
       </c>
       <c r="C456" t="n">
-        <v>12.65597081632927</v>
+        <v>12.65597177291335</v>
       </c>
       <c r="D456" t="n">
-        <v>12.56935277313647</v>
+        <v>12.56935372317364</v>
       </c>
       <c r="E456" t="n">
-        <v>12.60784998717082</v>
+        <v>12.60785094011775</v>
       </c>
       <c r="F456" t="n">
         <v>4490300</v>
@@ -9572,16 +9572,16 @@
         <v>45315</v>
       </c>
       <c r="B458" t="n">
-        <v>12.79071235656738</v>
+        <v>12.79071140289307</v>
       </c>
       <c r="C458" t="n">
-        <v>12.82920957310646</v>
+        <v>12.82920861656179</v>
       </c>
       <c r="D458" t="n">
-        <v>12.64634802400737</v>
+        <v>12.64634708109684</v>
       </c>
       <c r="E458" t="n">
-        <v>12.6559716397576</v>
+        <v>12.65597069612954</v>
       </c>
       <c r="F458" t="n">
         <v>3333600</v>
@@ -9652,16 +9652,16 @@
         <v>45321</v>
       </c>
       <c r="B462" t="n">
-        <v>12.51160717010498</v>
+        <v>12.51160621643066</v>
       </c>
       <c r="C462" t="n">
-        <v>12.63672335194755</v>
+        <v>12.63672238873649</v>
       </c>
       <c r="D462" t="n">
-        <v>12.51160717010498</v>
+        <v>12.51160621643066</v>
       </c>
       <c r="E462" t="n">
-        <v>12.58860160233948</v>
+        <v>12.58860064279641</v>
       </c>
       <c r="F462" t="n">
         <v>3463200</v>
@@ -9672,16 +9672,16 @@
         <v>45322</v>
       </c>
       <c r="B463" t="n">
-        <v>12.68484401702881</v>
+        <v>12.68484497070312</v>
       </c>
       <c r="C463" t="n">
-        <v>12.79071112283833</v>
+        <v>12.79071208447197</v>
       </c>
       <c r="D463" t="n">
-        <v>12.53085516572552</v>
+        <v>12.53085610782262</v>
       </c>
       <c r="E463" t="n">
-        <v>12.57897599337333</v>
+        <v>12.57897693908826</v>
       </c>
       <c r="F463" t="n">
         <v>3755000</v>
@@ -9812,16 +9812,16 @@
         <v>45331</v>
       </c>
       <c r="B470" t="n">
-        <v>12.48273468017578</v>
+        <v>12.48273372650146</v>
       </c>
       <c r="C470" t="n">
-        <v>12.62709901338253</v>
+        <v>12.62709804867886</v>
       </c>
       <c r="D470" t="n">
-        <v>12.36724303004117</v>
+        <v>12.36724208519036</v>
       </c>
       <c r="E470" t="n">
-        <v>12.36724303004117</v>
+        <v>12.36724208519036</v>
       </c>
       <c r="F470" t="n">
         <v>4943200</v>
@@ -9852,16 +9852,16 @@
         <v>45337</v>
       </c>
       <c r="B472" t="n">
-        <v>12.50198268890381</v>
+        <v>12.50198173522949</v>
       </c>
       <c r="C472" t="n">
-        <v>12.58860165499141</v>
+        <v>12.58860069470964</v>
       </c>
       <c r="D472" t="n">
-        <v>12.4153637228162</v>
+        <v>12.41536277574934</v>
       </c>
       <c r="E472" t="n">
-        <v>12.46348547262554</v>
+        <v>12.46348452188787</v>
       </c>
       <c r="F472" t="n">
         <v>4740900</v>
@@ -9892,16 +9892,16 @@
         <v>45341</v>
       </c>
       <c r="B474" t="n">
-        <v>12.77146434783936</v>
+        <v>12.77146339416504</v>
       </c>
       <c r="C474" t="n">
-        <v>12.85808239762144</v>
+        <v>12.85808143747915</v>
       </c>
       <c r="D474" t="n">
-        <v>12.53085651235945</v>
+        <v>12.53085557665187</v>
       </c>
       <c r="E474" t="n">
-        <v>12.54048012821565</v>
+        <v>12.54047919178945</v>
       </c>
       <c r="F474" t="n">
         <v>4786000</v>
@@ -9972,16 +9972,16 @@
         <v>45345</v>
       </c>
       <c r="B478" t="n">
-        <v>12.41536331176758</v>
+        <v>12.41536235809326</v>
       </c>
       <c r="C478" t="n">
-        <v>12.55010402320352</v>
+        <v>12.55010305917923</v>
       </c>
       <c r="D478" t="n">
-        <v>12.41536331176758</v>
+        <v>12.41536235809326</v>
       </c>
       <c r="E478" t="n">
-        <v>12.52123134141225</v>
+        <v>12.52123037960578</v>
       </c>
       <c r="F478" t="n">
         <v>4574300</v>
@@ -9992,16 +9992,16 @@
         <v>45348</v>
       </c>
       <c r="B479" t="n">
-        <v>12.35761737823486</v>
+        <v>12.35761833190918</v>
       </c>
       <c r="C479" t="n">
-        <v>12.48273355068785</v>
+        <v>12.48273451401776</v>
       </c>
       <c r="D479" t="n">
-        <v>12.3383683126978</v>
+        <v>12.33836926488661</v>
       </c>
       <c r="E479" t="n">
-        <v>12.45385995238227</v>
+        <v>12.45386091348391</v>
       </c>
       <c r="F479" t="n">
         <v>6964500</v>
@@ -22212,19 +22212,39 @@
         <v>46239</v>
       </c>
       <c r="B1090" t="n">
-        <v>11.16</v>
+        <v>11.15999984741211</v>
       </c>
       <c r="C1090" t="n">
-        <v>11.55</v>
+        <v>11.55000019073486</v>
       </c>
       <c r="D1090" t="n">
-        <v>11.08</v>
+        <v>11.07999992370605</v>
       </c>
       <c r="E1090" t="n">
-        <v>11.32</v>
+        <v>11.31999969482422</v>
       </c>
       <c r="F1090" t="n">
         <v>5192700</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B1091" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="C1091" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="D1091" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="E1091" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>5195300</v>
       </c>
     </row>
   </sheetData>

--- a/database/AURE3.xlsx
+++ b/database/AURE3.xlsx
@@ -492,16 +492,16 @@
         <v>44650</v>
       </c>
       <c r="B4" t="n">
-        <v>12.38384914398193</v>
+        <v>12.38385009765625</v>
       </c>
       <c r="C4" t="n">
-        <v>13.04504741320321</v>
+        <v>13.04504841779609</v>
       </c>
       <c r="D4" t="n">
-        <v>12.3060608504815</v>
+        <v>12.30606179816537</v>
       </c>
       <c r="E4" t="n">
-        <v>12.9283657147967</v>
+        <v>12.92836671040398</v>
       </c>
       <c r="F4" t="n">
         <v>4408600</v>
@@ -512,16 +512,16 @@
         <v>44651</v>
       </c>
       <c r="B5" t="n">
-        <v>12.4383020401001</v>
+        <v>12.43830108642578</v>
       </c>
       <c r="C5" t="n">
-        <v>12.82724207193696</v>
+        <v>12.82724108844168</v>
       </c>
       <c r="D5" t="n">
-        <v>12.05714098694259</v>
+        <v>12.05714006249281</v>
       </c>
       <c r="E5" t="n">
-        <v>12.41496584590627</v>
+        <v>12.4149648940212</v>
       </c>
       <c r="F5" t="n">
         <v>3876100</v>
@@ -552,16 +552,16 @@
         <v>44655</v>
       </c>
       <c r="B7" t="n">
-        <v>12.42274570465088</v>
+        <v>12.42274475097656</v>
       </c>
       <c r="C7" t="n">
-        <v>12.7338981972699</v>
+        <v>12.7338972197089</v>
       </c>
       <c r="D7" t="n">
-        <v>12.33717841680461</v>
+        <v>12.33717746969916</v>
       </c>
       <c r="E7" t="n">
-        <v>12.54720566311648</v>
+        <v>12.54720469988757</v>
       </c>
       <c r="F7" t="n">
         <v>2842400</v>
@@ -572,16 +572,16 @@
         <v>44656</v>
       </c>
       <c r="B8" t="n">
-        <v>12.15826511383057</v>
+        <v>12.15826606750488</v>
       </c>
       <c r="C8" t="n">
-        <v>12.50053200500811</v>
+        <v>12.50053298552928</v>
       </c>
       <c r="D8" t="n">
-        <v>12.05714061961251</v>
+        <v>12.05714156535479</v>
       </c>
       <c r="E8" t="n">
-        <v>12.37607131730719</v>
+        <v>12.37607228806586</v>
       </c>
       <c r="F8" t="n">
         <v>3624900</v>
@@ -632,16 +632,16 @@
         <v>44659</v>
       </c>
       <c r="B11" t="n">
-        <v>12.60943508148193</v>
+        <v>12.60943603515625</v>
       </c>
       <c r="C11" t="n">
-        <v>12.75723270856147</v>
+        <v>12.75723367341398</v>
       </c>
       <c r="D11" t="n">
-        <v>12.33717750513392</v>
+        <v>12.3371784382169</v>
       </c>
       <c r="E11" t="n">
-        <v>12.33717750513392</v>
+        <v>12.3371784382169</v>
       </c>
       <c r="F11" t="n">
         <v>2049800</v>
@@ -692,16 +692,16 @@
         <v>44664</v>
       </c>
       <c r="B14" t="n">
-        <v>12.10381412506104</v>
+        <v>12.10381317138672</v>
       </c>
       <c r="C14" t="n">
-        <v>12.55498376109398</v>
+        <v>12.55498277187146</v>
       </c>
       <c r="D14" t="n">
-        <v>12.08825616769219</v>
+        <v>12.0882552152437</v>
       </c>
       <c r="E14" t="n">
-        <v>12.39162965978653</v>
+        <v>12.39162868343488</v>
       </c>
       <c r="F14" t="n">
         <v>4421300</v>
@@ -712,16 +712,16 @@
         <v>44665</v>
       </c>
       <c r="B15" t="n">
-        <v>12.11159229278564</v>
+        <v>12.11159324645996</v>
       </c>
       <c r="C15" t="n">
-        <v>12.36829265315281</v>
+        <v>12.36829362703988</v>
       </c>
       <c r="D15" t="n">
-        <v>12.04936194735386</v>
+        <v>12.04936289612812</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08047712006975</v>
+        <v>12.08047807129404</v>
       </c>
       <c r="F15" t="n">
         <v>2077400</v>
@@ -732,16 +732,16 @@
         <v>44669</v>
       </c>
       <c r="B16" t="n">
-        <v>12.45386028289795</v>
+        <v>12.45385932922363</v>
       </c>
       <c r="C16" t="n">
-        <v>12.45386028289795</v>
+        <v>12.45385932922363</v>
       </c>
       <c r="D16" t="n">
-        <v>11.92490159008608</v>
+        <v>11.92490067691762</v>
       </c>
       <c r="E16" t="n">
-        <v>12.10381439459067</v>
+        <v>12.10381346772168</v>
       </c>
       <c r="F16" t="n">
         <v>3931100</v>
@@ -752,16 +752,16 @@
         <v>44670</v>
       </c>
       <c r="B17" t="n">
-        <v>12.10381412506104</v>
+        <v>12.10381317138672</v>
       </c>
       <c r="C17" t="n">
-        <v>12.60165763320052</v>
+        <v>12.60165664030051</v>
       </c>
       <c r="D17" t="n">
-        <v>12.00268962769625</v>
+        <v>12.00268868198966</v>
       </c>
       <c r="E17" t="n">
-        <v>12.4383020482046</v>
+        <v>12.43830106817557</v>
       </c>
       <c r="F17" t="n">
         <v>3118100</v>
@@ -772,16 +772,16 @@
         <v>44671</v>
       </c>
       <c r="B18" t="n">
-        <v>12.05714130401611</v>
+        <v>12.0571403503418</v>
       </c>
       <c r="C18" t="n">
-        <v>12.21271717247328</v>
+        <v>12.2127162064935</v>
       </c>
       <c r="D18" t="n">
-        <v>11.95601680405789</v>
+        <v>11.95601585838214</v>
       </c>
       <c r="E18" t="n">
-        <v>12.07269926178396</v>
+        <v>12.07269830687907</v>
       </c>
       <c r="F18" t="n">
         <v>2798400</v>
@@ -832,16 +832,16 @@
         <v>44677</v>
       </c>
       <c r="B21" t="n">
-        <v>11.95601558685303</v>
+        <v>11.95601654052734</v>
       </c>
       <c r="C21" t="n">
-        <v>12.43830110089237</v>
+        <v>12.4383020930363</v>
       </c>
       <c r="D21" t="n">
-        <v>11.86267007528195</v>
+        <v>11.86267102151054</v>
       </c>
       <c r="E21" t="n">
-        <v>12.32939837498153</v>
+        <v>12.32939935843881</v>
       </c>
       <c r="F21" t="n">
         <v>2627000</v>
@@ -852,16 +852,16 @@
         <v>44678</v>
       </c>
       <c r="B22" t="n">
-        <v>12.05714130401611</v>
+        <v>12.0571403503418</v>
       </c>
       <c r="C22" t="n">
-        <v>12.06492028290003</v>
+        <v>12.06491932861043</v>
       </c>
       <c r="D22" t="n">
-        <v>11.83155610929216</v>
+        <v>11.83155517346078</v>
       </c>
       <c r="E22" t="n">
-        <v>12.04936232513219</v>
+        <v>12.04936137207316</v>
       </c>
       <c r="F22" t="n">
         <v>2401400</v>
@@ -872,16 +872,16 @@
         <v>44679</v>
       </c>
       <c r="B23" t="n">
-        <v>11.90934371948242</v>
+        <v>11.90934467315674</v>
       </c>
       <c r="C23" t="n">
-        <v>12.08825577230682</v>
+        <v>12.08825674030803</v>
       </c>
       <c r="D23" t="n">
-        <v>11.49706676482372</v>
+        <v>11.49706768548379</v>
       </c>
       <c r="E23" t="n">
-        <v>12.08825577230682</v>
+        <v>12.08825674030803</v>
       </c>
       <c r="F23" t="n">
         <v>3489600</v>
@@ -932,16 +932,16 @@
         <v>44684</v>
       </c>
       <c r="B26" t="n">
-        <v>11.27148151397705</v>
+        <v>11.27148246765137</v>
       </c>
       <c r="C26" t="n">
-        <v>11.35704879249248</v>
+        <v>11.3570497534066</v>
       </c>
       <c r="D26" t="n">
-        <v>11.01478116211917</v>
+        <v>11.0147820940742</v>
       </c>
       <c r="E26" t="n">
-        <v>11.15479980562136</v>
+        <v>11.1548007494233</v>
       </c>
       <c r="F26" t="n">
         <v>1672900</v>
@@ -952,16 +952,16 @@
         <v>44685</v>
       </c>
       <c r="B27" t="n">
-        <v>11.69445610046387</v>
+        <v>11.69445705413818</v>
       </c>
       <c r="C27" t="n">
-        <v>11.69445610046387</v>
+        <v>11.69445705413818</v>
       </c>
       <c r="D27" t="n">
-        <v>11.03649597266557</v>
+        <v>11.03649687268372</v>
       </c>
       <c r="E27" t="n">
-        <v>11.20881904113643</v>
+        <v>11.2088199552074</v>
       </c>
       <c r="F27" t="n">
         <v>4400300</v>
@@ -972,16 +972,16 @@
         <v>44686</v>
       </c>
       <c r="B28" t="n">
-        <v>11.28714752197266</v>
+        <v>11.28714847564697</v>
       </c>
       <c r="C28" t="n">
-        <v>11.62396063303483</v>
+        <v>11.62396161516718</v>
       </c>
       <c r="D28" t="n">
-        <v>11.14615584813277</v>
+        <v>11.14615678989441</v>
       </c>
       <c r="E28" t="n">
-        <v>11.61612759626606</v>
+        <v>11.61612857773658</v>
       </c>
       <c r="F28" t="n">
         <v>3065700</v>
@@ -1092,16 +1092,16 @@
         <v>44694</v>
       </c>
       <c r="B34" t="n">
-        <v>11.32631301879883</v>
+        <v>11.32631206512451</v>
       </c>
       <c r="C34" t="n">
-        <v>11.38114278731251</v>
+        <v>11.38114182902154</v>
       </c>
       <c r="D34" t="n">
-        <v>11.11482548824677</v>
+        <v>11.11482455237968</v>
       </c>
       <c r="E34" t="n">
-        <v>11.18532133176413</v>
+        <v>11.18532038996129</v>
       </c>
       <c r="F34" t="n">
         <v>1333500</v>
@@ -1132,16 +1132,16 @@
         <v>44698</v>
       </c>
       <c r="B36" t="n">
-        <v>11.56129837036133</v>
+        <v>11.56129741668701</v>
       </c>
       <c r="C36" t="n">
-        <v>11.74928677955431</v>
+        <v>11.74928581037311</v>
       </c>
       <c r="D36" t="n">
-        <v>11.3576438869025</v>
+        <v>11.35764295002734</v>
       </c>
       <c r="E36" t="n">
-        <v>11.3576438869025</v>
+        <v>11.35764295002734</v>
       </c>
       <c r="F36" t="n">
         <v>1389700</v>
@@ -1152,16 +1152,16 @@
         <v>44699</v>
       </c>
       <c r="B37" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C37" t="n">
-        <v>11.59262882548476</v>
+        <v>11.5926298208571</v>
       </c>
       <c r="D37" t="n">
-        <v>11.03649593344125</v>
+        <v>11.03649688106261</v>
       </c>
       <c r="E37" t="n">
-        <v>11.51429995454926</v>
+        <v>11.51430094319608</v>
       </c>
       <c r="F37" t="n">
         <v>1959900</v>
@@ -1172,16 +1172,16 @@
         <v>44700</v>
       </c>
       <c r="B38" t="n">
-        <v>11.22448539733887</v>
+        <v>11.22448444366455</v>
       </c>
       <c r="C38" t="n">
-        <v>11.25581679930005</v>
+        <v>11.25581584296371</v>
       </c>
       <c r="D38" t="n">
-        <v>10.97383418164937</v>
+        <v>10.97383324927132</v>
       </c>
       <c r="E38" t="n">
-        <v>11.11482511697494</v>
+        <v>11.11482417261777</v>
       </c>
       <c r="F38" t="n">
         <v>2127500</v>
@@ -1192,16 +1192,16 @@
         <v>44701</v>
       </c>
       <c r="B39" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C39" t="n">
-        <v>11.34197688669085</v>
+        <v>11.34197786054158</v>
       </c>
       <c r="D39" t="n">
-        <v>10.86417286558284</v>
+        <v>10.86417379840811</v>
       </c>
       <c r="E39" t="n">
-        <v>11.34197688669085</v>
+        <v>11.34197786054158</v>
       </c>
       <c r="F39" t="n">
         <v>1777400</v>
@@ -1232,16 +1232,16 @@
         <v>44705</v>
       </c>
       <c r="B41" t="n">
-        <v>11.21665191650391</v>
+        <v>11.21665096282959</v>
       </c>
       <c r="C41" t="n">
-        <v>11.22448495343431</v>
+        <v>11.22448399909401</v>
       </c>
       <c r="D41" t="n">
-        <v>11.00516514837963</v>
+        <v>11.00516421268657</v>
       </c>
       <c r="E41" t="n">
-        <v>11.09132631361552</v>
+        <v>11.09132537059677</v>
       </c>
       <c r="F41" t="n">
         <v>792900</v>
@@ -1252,16 +1252,16 @@
         <v>44706</v>
       </c>
       <c r="B42" t="n">
-        <v>11.32631301879883</v>
+        <v>11.32631206512451</v>
       </c>
       <c r="C42" t="n">
-        <v>11.39680886231618</v>
+        <v>11.39680790270612</v>
       </c>
       <c r="D42" t="n">
-        <v>11.13832460075227</v>
+        <v>11.13832366290656</v>
       </c>
       <c r="E42" t="n">
-        <v>11.17748904126186</v>
+        <v>11.17748810011851</v>
       </c>
       <c r="F42" t="n">
         <v>821700</v>
@@ -1272,16 +1272,16 @@
         <v>44707</v>
       </c>
       <c r="B43" t="n">
-        <v>11.25581645965576</v>
+        <v>11.25581741333008</v>
       </c>
       <c r="C43" t="n">
-        <v>11.44380486575034</v>
+        <v>11.44380583535239</v>
       </c>
       <c r="D43" t="n">
-        <v>11.20881973163188</v>
+        <v>11.20882068132429</v>
       </c>
       <c r="E43" t="n">
-        <v>11.33414533569493</v>
+        <v>11.33414629600583</v>
       </c>
       <c r="F43" t="n">
         <v>1248800</v>
@@ -1352,16 +1352,16 @@
         <v>44713</v>
       </c>
       <c r="B47" t="n">
-        <v>10.7310152053833</v>
+        <v>10.73101425170898</v>
       </c>
       <c r="C47" t="n">
-        <v>10.94250272786947</v>
+        <v>10.94250175540008</v>
       </c>
       <c r="D47" t="n">
-        <v>10.66051936455458</v>
+        <v>10.66051841714529</v>
       </c>
       <c r="E47" t="n">
-        <v>10.94250272786947</v>
+        <v>10.94250175540008</v>
       </c>
       <c r="F47" t="n">
         <v>6323900</v>
@@ -1372,16 +1372,16 @@
         <v>44714</v>
       </c>
       <c r="B48" t="n">
-        <v>10.86417293548584</v>
+        <v>10.86417388916016</v>
       </c>
       <c r="C48" t="n">
-        <v>10.98949853218943</v>
+        <v>10.98949949686503</v>
       </c>
       <c r="D48" t="n">
-        <v>10.68401757697429</v>
+        <v>10.68401851483428</v>
       </c>
       <c r="E48" t="n">
-        <v>10.75451266487045</v>
+        <v>10.75451360891862</v>
       </c>
       <c r="F48" t="n">
         <v>3275400</v>
@@ -1392,16 +1392,16 @@
         <v>44715</v>
       </c>
       <c r="B49" t="n">
-        <v>10.7780122756958</v>
+        <v>10.77801132202148</v>
       </c>
       <c r="C49" t="n">
-        <v>10.85634040377818</v>
+        <v>10.85633944317314</v>
       </c>
       <c r="D49" t="n">
-        <v>10.62135527253152</v>
+        <v>10.62135433271873</v>
       </c>
       <c r="E49" t="n">
-        <v>10.78584531260389</v>
+        <v>10.78584435823648</v>
       </c>
       <c r="F49" t="n">
         <v>2685000</v>
@@ -1432,16 +1432,16 @@
         <v>44719</v>
       </c>
       <c r="B51" t="n">
-        <v>10.8563404083252</v>
+        <v>10.85634136199951</v>
       </c>
       <c r="C51" t="n">
-        <v>10.87983951905932</v>
+        <v>10.87984047479791</v>
       </c>
       <c r="D51" t="n">
-        <v>10.53519336495403</v>
+        <v>10.53519429041721</v>
       </c>
       <c r="E51" t="n">
-        <v>10.59002387633413</v>
+        <v>10.59002480661389</v>
       </c>
       <c r="F51" t="n">
         <v>2760900</v>
@@ -1532,16 +1532,16 @@
         <v>44726</v>
       </c>
       <c r="B56" t="n">
-        <v>10.39420318603516</v>
+        <v>10.39420223236084</v>
       </c>
       <c r="C56" t="n">
-        <v>10.47253131980584</v>
+        <v>10.47253035894487</v>
       </c>
       <c r="D56" t="n">
-        <v>10.01822560413734</v>
+        <v>10.01822468495919</v>
       </c>
       <c r="E56" t="n">
-        <v>10.01822560413734</v>
+        <v>10.01822468495919</v>
       </c>
       <c r="F56" t="n">
         <v>4085600</v>
@@ -1792,16 +1792,16 @@
         <v>44746</v>
       </c>
       <c r="B69" t="n">
-        <v>10.65268707275391</v>
+        <v>10.65268611907959</v>
       </c>
       <c r="C69" t="n">
-        <v>10.7858457171883</v>
+        <v>10.78584475159305</v>
       </c>
       <c r="D69" t="n">
-        <v>10.52736071852189</v>
+        <v>10.52735977606733</v>
       </c>
       <c r="E69" t="n">
-        <v>10.68401847456203</v>
+        <v>10.68401751808279</v>
       </c>
       <c r="F69" t="n">
         <v>1437100</v>
@@ -1892,16 +1892,16 @@
         <v>44753</v>
       </c>
       <c r="B74" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C74" t="n">
-        <v>11.18531989181933</v>
+        <v>11.18532085221909</v>
       </c>
       <c r="D74" t="n">
-        <v>10.83284146660853</v>
+        <v>10.83284239674361</v>
       </c>
       <c r="E74" t="n">
-        <v>11.05999429592211</v>
+        <v>11.0599952455611</v>
       </c>
       <c r="F74" t="n">
         <v>1881000</v>
@@ -1912,16 +1912,16 @@
         <v>44754</v>
       </c>
       <c r="B75" t="n">
-        <v>11.14615631103516</v>
+        <v>11.14615535736084</v>
       </c>
       <c r="C75" t="n">
-        <v>11.22448518797689</v>
+        <v>11.22448422760069</v>
       </c>
       <c r="D75" t="n">
-        <v>10.99733234124531</v>
+        <v>10.99733140030449</v>
       </c>
       <c r="E75" t="n">
-        <v>11.10699261956382</v>
+        <v>11.10699166924038</v>
       </c>
       <c r="F75" t="n">
         <v>1673000</v>
@@ -1952,16 +1952,16 @@
         <v>44756</v>
       </c>
       <c r="B77" t="n">
-        <v>10.91117000579834</v>
+        <v>10.91117095947266</v>
       </c>
       <c r="C77" t="n">
-        <v>11.1774872624825</v>
+        <v>11.17748823943387</v>
       </c>
       <c r="D77" t="n">
-        <v>10.84850720975495</v>
+        <v>10.84850815795232</v>
       </c>
       <c r="E77" t="n">
-        <v>11.04432863414042</v>
+        <v>11.04432959945326</v>
       </c>
       <c r="F77" t="n">
         <v>1968500</v>
@@ -1972,16 +1972,16 @@
         <v>44757</v>
       </c>
       <c r="B78" t="n">
-        <v>10.80934429168701</v>
+        <v>10.8093433380127</v>
       </c>
       <c r="C78" t="n">
-        <v>10.98166737847755</v>
+        <v>10.98166640959971</v>
       </c>
       <c r="D78" t="n">
-        <v>10.60568980247997</v>
+        <v>10.60568886677345</v>
       </c>
       <c r="E78" t="n">
-        <v>10.97383434112354</v>
+        <v>10.97383337293678</v>
       </c>
       <c r="F78" t="n">
         <v>2342600</v>
@@ -1992,16 +1992,16 @@
         <v>44760</v>
       </c>
       <c r="B79" t="n">
-        <v>10.7310152053833</v>
+        <v>10.73101425170898</v>
       </c>
       <c r="C79" t="n">
-        <v>11.0051655314951</v>
+        <v>11.00516455345681</v>
       </c>
       <c r="D79" t="n">
-        <v>10.5900242707254</v>
+        <v>10.59002332958107</v>
       </c>
       <c r="E79" t="n">
-        <v>10.80934408341511</v>
+        <v>10.80934312277964</v>
       </c>
       <c r="F79" t="n">
         <v>1463400</v>
@@ -2012,16 +2012,16 @@
         <v>44761</v>
       </c>
       <c r="B80" t="n">
-        <v>11.0913257598877</v>
+        <v>11.09132671356201</v>
       </c>
       <c r="C80" t="n">
-        <v>11.0913257598877</v>
+        <v>11.09132671356201</v>
       </c>
       <c r="D80" t="n">
-        <v>10.78584480484809</v>
+        <v>10.78584573225599</v>
       </c>
       <c r="E80" t="n">
-        <v>10.87200596578243</v>
+        <v>10.87200690059879</v>
       </c>
       <c r="F80" t="n">
         <v>2890800</v>
@@ -2132,16 +2132,16 @@
         <v>44769</v>
       </c>
       <c r="B86" t="n">
-        <v>11.24015140533447</v>
+        <v>11.24015045166016</v>
       </c>
       <c r="C86" t="n">
-        <v>11.49080261954139</v>
+        <v>11.49080164460048</v>
       </c>
       <c r="D86" t="n">
-        <v>11.15398949020119</v>
+        <v>11.15398854383731</v>
       </c>
       <c r="E86" t="n">
-        <v>11.2871481344985</v>
+        <v>11.28714717683673</v>
       </c>
       <c r="F86" t="n">
         <v>3096400</v>
@@ -2152,16 +2152,16 @@
         <v>44770</v>
       </c>
       <c r="B87" t="n">
-        <v>10.9660005569458</v>
+        <v>10.96600151062012</v>
       </c>
       <c r="C87" t="n">
-        <v>11.33414507051741</v>
+        <v>11.33414605620796</v>
       </c>
       <c r="D87" t="n">
-        <v>10.8250088821738</v>
+        <v>10.82500982358657</v>
       </c>
       <c r="E87" t="n">
-        <v>11.31064596005574</v>
+        <v>11.31064694370265</v>
       </c>
       <c r="F87" t="n">
         <v>2911900</v>
@@ -2212,16 +2212,16 @@
         <v>44775</v>
       </c>
       <c r="B90" t="n">
-        <v>10.86417293548584</v>
+        <v>10.86417388916016</v>
       </c>
       <c r="C90" t="n">
-        <v>11.06782740362892</v>
+        <v>11.06782837518035</v>
       </c>
       <c r="D90" t="n">
-        <v>10.72318126569455</v>
+        <v>10.7231822069924</v>
       </c>
       <c r="E90" t="n">
-        <v>10.93466877038148</v>
+        <v>10.93466973024404</v>
       </c>
       <c r="F90" t="n">
         <v>2371400</v>
@@ -2232,16 +2232,16 @@
         <v>44776</v>
       </c>
       <c r="B91" t="n">
-        <v>10.88767147064209</v>
+        <v>10.88767242431641</v>
       </c>
       <c r="C91" t="n">
-        <v>11.02083010599954</v>
+        <v>11.02083107133751</v>
       </c>
       <c r="D91" t="n">
-        <v>10.70751610927583</v>
+        <v>10.70751704716995</v>
       </c>
       <c r="E91" t="n">
-        <v>10.83284170796531</v>
+        <v>10.83284265683698</v>
       </c>
       <c r="F91" t="n">
         <v>3133200</v>
@@ -2272,16 +2272,16 @@
         <v>44778</v>
       </c>
       <c r="B93" t="n">
-        <v>10.9660005569458</v>
+        <v>10.96600151062012</v>
       </c>
       <c r="C93" t="n">
-        <v>11.16965503228325</v>
+        <v>11.16965600366867</v>
       </c>
       <c r="D93" t="n">
-        <v>10.93466915666308</v>
+        <v>10.93467010761261</v>
       </c>
       <c r="E93" t="n">
-        <v>11.16965503228325</v>
+        <v>11.16965600366867</v>
       </c>
       <c r="F93" t="n">
         <v>1948700</v>
@@ -2312,16 +2312,16 @@
         <v>44782</v>
       </c>
       <c r="B95" t="n">
-        <v>10.92683696746826</v>
+        <v>10.92683601379395</v>
       </c>
       <c r="C95" t="n">
-        <v>11.0599956157492</v>
+        <v>11.05999465045304</v>
       </c>
       <c r="D95" t="n">
-        <v>10.67618574576276</v>
+        <v>10.67618481396482</v>
       </c>
       <c r="E95" t="n">
-        <v>10.98166748246601</v>
+        <v>10.98166652400619</v>
       </c>
       <c r="F95" t="n">
         <v>1743500</v>
@@ -2392,16 +2392,16 @@
         <v>44788</v>
       </c>
       <c r="B99" t="n">
-        <v>11.21665191650391</v>
+        <v>11.21665096282959</v>
       </c>
       <c r="C99" t="n">
-        <v>11.3106461186702</v>
+        <v>11.3106451570042</v>
       </c>
       <c r="D99" t="n">
-        <v>10.92683627307463</v>
+        <v>10.92683534404133</v>
       </c>
       <c r="E99" t="n">
-        <v>10.99733211144923</v>
+        <v>10.99733117642216</v>
       </c>
       <c r="F99" t="n">
         <v>3450900</v>
@@ -2432,16 +2432,16 @@
         <v>44790</v>
       </c>
       <c r="B101" t="n">
-        <v>11.24015140533447</v>
+        <v>11.24015045166016</v>
       </c>
       <c r="C101" t="n">
-        <v>11.25581673272263</v>
+        <v>11.25581577771919</v>
       </c>
       <c r="D101" t="n">
-        <v>10.91117131318813</v>
+        <v>10.91117038742624</v>
       </c>
       <c r="E101" t="n">
-        <v>10.98949944412802</v>
+        <v>10.98949851172035</v>
       </c>
       <c r="F101" t="n">
         <v>4396400</v>
@@ -2492,16 +2492,16 @@
         <v>44795</v>
       </c>
       <c r="B104" t="n">
-        <v>11.0599946975708</v>
+        <v>11.05999565124512</v>
       </c>
       <c r="C104" t="n">
-        <v>11.2244847349093</v>
+        <v>11.22448570276716</v>
       </c>
       <c r="D104" t="n">
-        <v>10.98166657079026</v>
+        <v>10.98166751771054</v>
       </c>
       <c r="E104" t="n">
-        <v>11.0599946975708</v>
+        <v>11.05999565124512</v>
       </c>
       <c r="F104" t="n">
         <v>1703300</v>
@@ -2512,16 +2512,16 @@
         <v>44796</v>
       </c>
       <c r="B105" t="n">
-        <v>11.22448539733887</v>
+        <v>11.22448444366455</v>
       </c>
       <c r="C105" t="n">
-        <v>11.27148287378042</v>
+        <v>11.27148191611302</v>
       </c>
       <c r="D105" t="n">
-        <v>10.98949950913019</v>
+        <v>10.98949857542116</v>
       </c>
       <c r="E105" t="n">
-        <v>10.98949950913019</v>
+        <v>10.98949857542116</v>
       </c>
       <c r="F105" t="n">
         <v>2361000</v>
@@ -2532,16 +2532,16 @@
         <v>44797</v>
       </c>
       <c r="B106" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C106" t="n">
-        <v>11.39680739514549</v>
+        <v>11.3968083737041</v>
       </c>
       <c r="D106" t="n">
-        <v>11.09915873138986</v>
+        <v>11.09915968439161</v>
       </c>
       <c r="E106" t="n">
-        <v>11.22448432728707</v>
+        <v>11.2244852910496</v>
       </c>
       <c r="F106" t="n">
         <v>2116800</v>
@@ -2632,16 +2632,16 @@
         <v>44804</v>
       </c>
       <c r="B111" t="n">
-        <v>12.03910160064697</v>
+        <v>12.03910255432129</v>
       </c>
       <c r="C111" t="n">
-        <v>12.07826603661254</v>
+        <v>12.07826699338926</v>
       </c>
       <c r="D111" t="n">
-        <v>10.96600023838756</v>
+        <v>10.96600110705643</v>
       </c>
       <c r="E111" t="n">
-        <v>11.02083000053966</v>
+        <v>11.02083087355185</v>
       </c>
       <c r="F111" t="n">
         <v>16560000</v>
@@ -2652,16 +2652,16 @@
         <v>44805</v>
       </c>
       <c r="B112" t="n">
-        <v>11.65529251098633</v>
+        <v>11.65529346466064</v>
       </c>
       <c r="C112" t="n">
-        <v>12.15659567974902</v>
+        <v>12.1565966744416</v>
       </c>
       <c r="D112" t="n">
-        <v>11.42030662728508</v>
+        <v>11.42030756173208</v>
       </c>
       <c r="E112" t="n">
-        <v>12.14092960556915</v>
+        <v>12.14093059897989</v>
       </c>
       <c r="F112" t="n">
         <v>4716400</v>
@@ -2712,16 +2712,16 @@
         <v>44810</v>
       </c>
       <c r="B115" t="n">
-        <v>11.58479785919189</v>
+        <v>11.58479595184326</v>
       </c>
       <c r="C115" t="n">
-        <v>11.90594494281729</v>
+        <v>11.90594298259424</v>
       </c>
       <c r="D115" t="n">
-        <v>11.49863668336545</v>
+        <v>11.49863479020259</v>
       </c>
       <c r="E115" t="n">
-        <v>11.89811190492408</v>
+        <v>11.89810994599068</v>
       </c>
       <c r="F115" t="n">
         <v>1316500</v>
@@ -2792,16 +2792,16 @@
         <v>44817</v>
       </c>
       <c r="B119" t="n">
-        <v>11.24015140533447</v>
+        <v>11.24015045166016</v>
       </c>
       <c r="C119" t="n">
-        <v>11.43597285318351</v>
+        <v>11.43597188289466</v>
       </c>
       <c r="D119" t="n">
-        <v>11.16965556458889</v>
+        <v>11.16965461689582</v>
       </c>
       <c r="E119" t="n">
-        <v>11.3028142088862</v>
+        <v>11.30281324989524</v>
       </c>
       <c r="F119" t="n">
         <v>1768400</v>
@@ -2832,16 +2832,16 @@
         <v>44819</v>
       </c>
       <c r="B121" t="n">
-        <v>11.22448539733887</v>
+        <v>11.22448444366455</v>
       </c>
       <c r="C121" t="n">
-        <v>11.27148287378042</v>
+        <v>11.27148191611302</v>
       </c>
       <c r="D121" t="n">
-        <v>11.11482511697494</v>
+        <v>11.11482417261777</v>
       </c>
       <c r="E121" t="n">
-        <v>11.16182259341649</v>
+        <v>11.16182164506624</v>
       </c>
       <c r="F121" t="n">
         <v>1523500</v>
@@ -2872,16 +2872,16 @@
         <v>44823</v>
       </c>
       <c r="B123" t="n">
-        <v>11.28714752197266</v>
+        <v>11.28714847564697</v>
       </c>
       <c r="C123" t="n">
-        <v>11.43597223258132</v>
+        <v>11.43597319883014</v>
       </c>
       <c r="D123" t="n">
-        <v>11.11482444805718</v>
+        <v>11.11482538717157</v>
       </c>
       <c r="E123" t="n">
-        <v>11.11482444805718</v>
+        <v>11.11482538717157</v>
       </c>
       <c r="F123" t="n">
         <v>1858600</v>
@@ -2892,16 +2892,16 @@
         <v>44824</v>
       </c>
       <c r="B124" t="n">
-        <v>11.13049125671387</v>
+        <v>11.13049030303955</v>
       </c>
       <c r="C124" t="n">
-        <v>11.35764410901417</v>
+        <v>11.35764313587711</v>
       </c>
       <c r="D124" t="n">
-        <v>11.08349377999676</v>
+        <v>11.08349283034925</v>
       </c>
       <c r="E124" t="n">
-        <v>11.28714826743829</v>
+        <v>11.28714730034141</v>
       </c>
       <c r="F124" t="n">
         <v>1310600</v>
@@ -2912,16 +2912,16 @@
         <v>44825</v>
       </c>
       <c r="B125" t="n">
-        <v>11.0913257598877</v>
+        <v>11.09132671356201</v>
       </c>
       <c r="C125" t="n">
-        <v>11.23231742959796</v>
+        <v>11.23231839539528</v>
       </c>
       <c r="D125" t="n">
-        <v>10.93466876409822</v>
+        <v>10.93466970430257</v>
       </c>
       <c r="E125" t="n">
-        <v>11.13049019558493</v>
+        <v>11.13049115262676</v>
       </c>
       <c r="F125" t="n">
         <v>2825100</v>
@@ -2992,16 +2992,16 @@
         <v>44831</v>
       </c>
       <c r="B129" t="n">
-        <v>10.9033374786377</v>
+        <v>10.90333843231201</v>
       </c>
       <c r="C129" t="n">
-        <v>11.04432914981819</v>
+        <v>11.04433011582452</v>
       </c>
       <c r="D129" t="n">
-        <v>10.77017884407822</v>
+        <v>10.77017978610565</v>
       </c>
       <c r="E129" t="n">
-        <v>11.04432914981819</v>
+        <v>11.04433011582452</v>
       </c>
       <c r="F129" t="n">
         <v>2130200</v>
@@ -3032,16 +3032,16 @@
         <v>44833</v>
       </c>
       <c r="B131" t="n">
-        <v>10.70751571655273</v>
+        <v>10.70751667022705</v>
       </c>
       <c r="C131" t="n">
-        <v>10.83284131064561</v>
+        <v>10.83284227548216</v>
       </c>
       <c r="D131" t="n">
-        <v>10.6448529195063</v>
+        <v>10.6448538675995</v>
       </c>
       <c r="E131" t="n">
-        <v>10.69184964379139</v>
+        <v>10.6918505960704</v>
       </c>
       <c r="F131" t="n">
         <v>2222600</v>
@@ -3132,16 +3132,16 @@
         <v>44840</v>
       </c>
       <c r="B136" t="n">
-        <v>10.98950004577637</v>
+        <v>10.98949909210205</v>
       </c>
       <c r="C136" t="n">
-        <v>11.12265869736379</v>
+        <v>11.1226577321339</v>
       </c>
       <c r="D136" t="n">
-        <v>10.88767279768013</v>
+        <v>10.88767185284243</v>
       </c>
       <c r="E136" t="n">
-        <v>11.02866448689024</v>
+        <v>11.02866352981721</v>
       </c>
       <c r="F136" t="n">
         <v>3101100</v>
@@ -3192,16 +3192,16 @@
         <v>44845</v>
       </c>
       <c r="B139" t="n">
-        <v>11.22448539733887</v>
+        <v>11.22448444366455</v>
       </c>
       <c r="C139" t="n">
-        <v>11.31847960322243</v>
+        <v>11.31847864156201</v>
       </c>
       <c r="D139" t="n">
-        <v>10.99733254637037</v>
+        <v>10.99733161199581</v>
       </c>
       <c r="E139" t="n">
-        <v>11.04433002281193</v>
+        <v>11.04432908444429</v>
       </c>
       <c r="F139" t="n">
         <v>1834300</v>
@@ -3212,16 +3212,16 @@
         <v>44847</v>
       </c>
       <c r="B140" t="n">
-        <v>10.91117000579834</v>
+        <v>10.91117095947266</v>
       </c>
       <c r="C140" t="n">
-        <v>11.20098562424891</v>
+        <v>11.20098660325412</v>
       </c>
       <c r="D140" t="n">
-        <v>10.87200557152136</v>
+        <v>10.87200652177256</v>
       </c>
       <c r="E140" t="n">
-        <v>11.12265675569494</v>
+        <v>11.12265772785393</v>
       </c>
       <c r="F140" t="n">
         <v>3739400</v>
@@ -3292,16 +3292,16 @@
         <v>44853</v>
       </c>
       <c r="B144" t="n">
-        <v>11.02083015441895</v>
+        <v>11.02082920074463</v>
       </c>
       <c r="C144" t="n">
-        <v>11.3263118628163</v>
+        <v>11.32631088270749</v>
       </c>
       <c r="D144" t="n">
-        <v>10.9973317913113</v>
+        <v>10.99733083967039</v>
       </c>
       <c r="E144" t="n">
-        <v>11.2871474263039</v>
+        <v>11.28714644958413</v>
       </c>
       <c r="F144" t="n">
         <v>2951600</v>
@@ -3372,16 +3372,16 @@
         <v>44859</v>
       </c>
       <c r="B148" t="n">
-        <v>11.38897609710693</v>
+        <v>11.3889741897583</v>
       </c>
       <c r="C148" t="n">
-        <v>11.5064686744452</v>
+        <v>11.50646674741971</v>
       </c>
       <c r="D148" t="n">
-        <v>11.18532159918765</v>
+        <v>11.18531972594569</v>
       </c>
       <c r="E148" t="n">
-        <v>11.24015211601182</v>
+        <v>11.24015023358722</v>
       </c>
       <c r="F148" t="n">
         <v>2935500</v>
@@ -3392,16 +3392,16 @@
         <v>44860</v>
       </c>
       <c r="B149" t="n">
-        <v>11.34197807312012</v>
+        <v>11.3419771194458</v>
       </c>
       <c r="C149" t="n">
-        <v>11.45163835450095</v>
+        <v>11.451637391606</v>
       </c>
       <c r="D149" t="n">
-        <v>11.20098713648711</v>
+        <v>11.20098619466782</v>
       </c>
       <c r="E149" t="n">
-        <v>11.43597302687486</v>
+        <v>11.43597206529711</v>
       </c>
       <c r="F149" t="n">
         <v>4386900</v>
@@ -3432,16 +3432,16 @@
         <v>44862</v>
       </c>
       <c r="B151" t="n">
-        <v>11.49080181121826</v>
+        <v>11.49080276489258</v>
       </c>
       <c r="C151" t="n">
-        <v>11.63962577243467</v>
+        <v>11.63962673846057</v>
       </c>
       <c r="D151" t="n">
-        <v>11.2244845413578</v>
+        <v>11.22448547292922</v>
       </c>
       <c r="E151" t="n">
-        <v>11.32631177671618</v>
+        <v>11.32631271673871</v>
       </c>
       <c r="F151" t="n">
         <v>2887600</v>
@@ -3452,16 +3452,16 @@
         <v>44865</v>
       </c>
       <c r="B152" t="n">
-        <v>11.68662357330322</v>
+        <v>11.68662452697754</v>
       </c>
       <c r="C152" t="n">
-        <v>11.72578801061714</v>
+        <v>11.72578896748743</v>
       </c>
       <c r="D152" t="n">
-        <v>11.16182205549541</v>
+        <v>11.16182296634386</v>
       </c>
       <c r="E152" t="n">
-        <v>11.23231789326056</v>
+        <v>11.23231880986175</v>
       </c>
       <c r="F152" t="n">
         <v>2644000</v>
@@ -3492,16 +3492,16 @@
         <v>44868</v>
       </c>
       <c r="B154" t="n">
-        <v>11.68662357330322</v>
+        <v>11.68662452697754</v>
       </c>
       <c r="C154" t="n">
-        <v>11.74928637420569</v>
+        <v>11.74928733299354</v>
       </c>
       <c r="D154" t="n">
-        <v>11.36547653192819</v>
+        <v>11.36547745939565</v>
       </c>
       <c r="E154" t="n">
-        <v>11.49863517059581</v>
+        <v>11.49863610892954</v>
       </c>
       <c r="F154" t="n">
         <v>2959500</v>
@@ -3592,16 +3592,16 @@
         <v>44875</v>
       </c>
       <c r="B159" t="n">
-        <v>10.70751571655273</v>
+        <v>10.70751667022705</v>
       </c>
       <c r="C159" t="n">
-        <v>11.10699160797338</v>
+        <v>11.10699259722736</v>
       </c>
       <c r="D159" t="n">
-        <v>10.49602821627141</v>
+        <v>10.4960291511094</v>
       </c>
       <c r="E159" t="n">
-        <v>11.04432881092694</v>
+        <v>11.04432979459981</v>
       </c>
       <c r="F159" t="n">
         <v>4341400</v>
@@ -3612,16 +3612,16 @@
         <v>44876</v>
       </c>
       <c r="B160" t="n">
-        <v>10.79367828369141</v>
+        <v>10.79367733001709</v>
       </c>
       <c r="C160" t="n">
-        <v>10.85634108891171</v>
+        <v>10.85634012970083</v>
       </c>
       <c r="D160" t="n">
-        <v>10.53519402540776</v>
+        <v>10.5351930945718</v>
       </c>
       <c r="E160" t="n">
-        <v>10.78584599328854</v>
+        <v>10.78584504030624</v>
       </c>
       <c r="F160" t="n">
         <v>3291200</v>
@@ -3652,16 +3652,16 @@
         <v>44881</v>
       </c>
       <c r="B162" t="n">
-        <v>10.9033374786377</v>
+        <v>10.90333843231201</v>
       </c>
       <c r="C162" t="n">
-        <v>10.9033374786377</v>
+        <v>10.90333843231201</v>
       </c>
       <c r="D162" t="n">
-        <v>10.59785577341312</v>
+        <v>10.59785670036809</v>
       </c>
       <c r="E162" t="n">
-        <v>10.86417304253206</v>
+        <v>10.86417399278081</v>
       </c>
       <c r="F162" t="n">
         <v>5270300</v>
@@ -3692,16 +3692,16 @@
         <v>44883</v>
       </c>
       <c r="B164" t="n">
-        <v>10.78584671020508</v>
+        <v>10.78584575653076</v>
       </c>
       <c r="C164" t="n">
-        <v>10.9895004672078</v>
+        <v>10.98949949552661</v>
       </c>
       <c r="D164" t="n">
-        <v>10.57435916827967</v>
+        <v>10.57435823330488</v>
       </c>
       <c r="E164" t="n">
-        <v>10.8093450769747</v>
+        <v>10.80934412122268</v>
       </c>
       <c r="F164" t="n">
         <v>3568700</v>
@@ -3732,16 +3732,16 @@
         <v>44887</v>
       </c>
       <c r="B166" t="n">
-        <v>10.84850883483887</v>
+        <v>10.84850788116455</v>
       </c>
       <c r="C166" t="n">
-        <v>11.4203071211389</v>
+        <v>11.42030611719874</v>
       </c>
       <c r="D166" t="n">
-        <v>10.80151135726647</v>
+        <v>10.80151040772362</v>
       </c>
       <c r="E166" t="n">
-        <v>11.29498151027859</v>
+        <v>11.29498051735561</v>
       </c>
       <c r="F166" t="n">
         <v>3523700</v>
@@ -3752,16 +3752,16 @@
         <v>44888</v>
       </c>
       <c r="B167" t="n">
-        <v>10.56652450561523</v>
+        <v>10.56652545928955</v>
       </c>
       <c r="C167" t="n">
-        <v>10.8171764516154</v>
+        <v>10.81717742791213</v>
       </c>
       <c r="D167" t="n">
-        <v>10.51952777930236</v>
+        <v>10.51952872873502</v>
       </c>
       <c r="E167" t="n">
-        <v>10.80934341489675</v>
+        <v>10.80934439048652</v>
       </c>
       <c r="F167" t="n">
         <v>4669400</v>
@@ -3872,16 +3872,16 @@
         <v>44896</v>
       </c>
       <c r="B173" t="n">
-        <v>10.92683696746826</v>
+        <v>10.92683601379395</v>
       </c>
       <c r="C173" t="n">
-        <v>11.02083117560783</v>
+        <v>11.02083021372987</v>
       </c>
       <c r="D173" t="n">
-        <v>10.69185107361957</v>
+        <v>10.69185014045439</v>
       </c>
       <c r="E173" t="n">
-        <v>10.76234691647413</v>
+        <v>10.76234597715621</v>
       </c>
       <c r="F173" t="n">
         <v>1944500</v>
@@ -3892,16 +3892,16 @@
         <v>44897</v>
       </c>
       <c r="B174" t="n">
-        <v>10.80151081085205</v>
+        <v>10.80150985717773</v>
       </c>
       <c r="C174" t="n">
-        <v>11.09132645805553</v>
+        <v>11.09132547879316</v>
       </c>
       <c r="D174" t="n">
-        <v>10.79367777381964</v>
+        <v>10.79367682083691</v>
       </c>
       <c r="E174" t="n">
-        <v>10.92683641537253</v>
+        <v>10.92683545063311</v>
       </c>
       <c r="F174" t="n">
         <v>1109200</v>
@@ -3912,16 +3912,16 @@
         <v>44900</v>
       </c>
       <c r="B175" t="n">
-        <v>10.51952743530273</v>
+        <v>10.51952838897705</v>
       </c>
       <c r="C175" t="n">
-        <v>10.80151002495736</v>
+        <v>10.80151100419552</v>
       </c>
       <c r="D175" t="n">
-        <v>10.50386136237774</v>
+        <v>10.50386231463181</v>
       </c>
       <c r="E175" t="n">
-        <v>10.77801166256934</v>
+        <v>10.7780126396772</v>
       </c>
       <c r="F175" t="n">
         <v>1355000</v>
@@ -3932,16 +3932,16 @@
         <v>44901</v>
       </c>
       <c r="B176" t="n">
-        <v>10.47253036499023</v>
+        <v>10.47253131866455</v>
       </c>
       <c r="C176" t="n">
-        <v>10.58219063867058</v>
+        <v>10.58219160233104</v>
       </c>
       <c r="D176" t="n">
-        <v>10.41770060164981</v>
+        <v>10.41770155033109</v>
       </c>
       <c r="E176" t="n">
-        <v>10.51952783856738</v>
+        <v>10.51952879652149</v>
       </c>
       <c r="F176" t="n">
         <v>1647500</v>
@@ -3952,16 +3952,16 @@
         <v>44902</v>
       </c>
       <c r="B177" t="n">
-        <v>10.65268707275391</v>
+        <v>10.65268611907959</v>
       </c>
       <c r="C177" t="n">
-        <v>10.80151104459258</v>
+        <v>10.80151007759491</v>
       </c>
       <c r="D177" t="n">
-        <v>10.42553422289516</v>
+        <v>10.42553328955654</v>
       </c>
       <c r="E177" t="n">
-        <v>10.42553422289516</v>
+        <v>10.42553328955654</v>
       </c>
       <c r="F177" t="n">
         <v>2865300</v>
@@ -3972,16 +3972,16 @@
         <v>44903</v>
       </c>
       <c r="B178" t="n">
-        <v>11.26364898681641</v>
+        <v>11.26364994049072</v>
       </c>
       <c r="C178" t="n">
-        <v>11.8119488532735</v>
+        <v>11.81194985337145</v>
       </c>
       <c r="D178" t="n">
-        <v>11.15398871472519</v>
+        <v>11.15398965911476</v>
       </c>
       <c r="E178" t="n">
-        <v>11.74928605407837</v>
+        <v>11.74928704887077</v>
       </c>
       <c r="F178" t="n">
         <v>12105700</v>
@@ -4052,16 +4052,16 @@
         <v>44909</v>
       </c>
       <c r="B182" t="n">
-        <v>10.99733257293701</v>
+        <v>10.9973316192627</v>
       </c>
       <c r="C182" t="n">
-        <v>11.13832425560273</v>
+        <v>11.13832328970179</v>
       </c>
       <c r="D182" t="n">
-        <v>10.7388483193829</v>
+        <v>10.738847388124</v>
       </c>
       <c r="E182" t="n">
-        <v>11.01299864745522</v>
+        <v>11.01299769242237</v>
       </c>
       <c r="F182" t="n">
         <v>3892800</v>
@@ -4152,16 +4152,16 @@
         <v>44916</v>
       </c>
       <c r="B187" t="n">
-        <v>11.58479785919189</v>
+        <v>11.58479595184326</v>
       </c>
       <c r="C187" t="n">
-        <v>11.7571209578444</v>
+        <v>11.75711902212409</v>
       </c>
       <c r="D187" t="n">
-        <v>11.15399048606043</v>
+        <v>11.15398864964095</v>
       </c>
       <c r="E187" t="n">
-        <v>11.4281408363258</v>
+        <v>11.42813895476955</v>
       </c>
       <c r="F187" t="n">
         <v>6348400</v>
@@ -4192,16 +4192,16 @@
         <v>44918</v>
       </c>
       <c r="B189" t="n">
-        <v>11.78845119476318</v>
+        <v>11.78845024108887</v>
       </c>
       <c r="C189" t="n">
-        <v>12.09393217234406</v>
+        <v>12.09393119395663</v>
       </c>
       <c r="D189" t="n">
-        <v>11.57696367459224</v>
+        <v>11.57696273802706</v>
       </c>
       <c r="E189" t="n">
-        <v>11.67879091611904</v>
+        <v>11.67878997131614</v>
       </c>
       <c r="F189" t="n">
         <v>5656000</v>
@@ -4232,16 +4232,16 @@
         <v>44922</v>
       </c>
       <c r="B191" t="n">
-        <v>11.52996730804443</v>
+        <v>11.52996635437012</v>
       </c>
       <c r="C191" t="n">
-        <v>11.60829544067951</v>
+        <v>11.60829448052647</v>
       </c>
       <c r="D191" t="n">
-        <v>11.34197814632122</v>
+        <v>11.34197720819598</v>
       </c>
       <c r="E191" t="n">
-        <v>11.60829544067951</v>
+        <v>11.60829448052647</v>
       </c>
       <c r="F191" t="n">
         <v>1633000</v>
@@ -4252,16 +4252,16 @@
         <v>44923</v>
       </c>
       <c r="B192" t="n">
-        <v>11.58479785919189</v>
+        <v>11.58479595184326</v>
       </c>
       <c r="C192" t="n">
-        <v>11.69445814869797</v>
+        <v>11.6944562232946</v>
       </c>
       <c r="D192" t="n">
-        <v>11.49863668336545</v>
+        <v>11.49863479020259</v>
       </c>
       <c r="E192" t="n">
-        <v>11.57696482129869</v>
+        <v>11.5769629152397</v>
       </c>
       <c r="F192" t="n">
         <v>2005900</v>
@@ -4272,16 +4272,16 @@
         <v>44924</v>
       </c>
       <c r="B193" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="C193" t="n">
-        <v>11.73362129131107</v>
+        <v>11.73362032145083</v>
       </c>
       <c r="D193" t="n">
-        <v>11.47513702901113</v>
+        <v>11.4751360805163</v>
       </c>
       <c r="E193" t="n">
-        <v>11.62396175397144</v>
+        <v>11.62396079317528</v>
       </c>
       <c r="F193" t="n">
         <v>2424800</v>
@@ -4292,16 +4292,16 @@
         <v>44928</v>
       </c>
       <c r="B194" t="n">
-        <v>11.34197807312012</v>
+        <v>11.3419771194458</v>
       </c>
       <c r="C194" t="n">
-        <v>11.46730442912659</v>
+        <v>11.46730346491438</v>
       </c>
       <c r="D194" t="n">
-        <v>11.1774887715482</v>
+        <v>11.17748783170473</v>
       </c>
       <c r="E194" t="n">
-        <v>11.38897554999749</v>
+        <v>11.38897459237146</v>
       </c>
       <c r="F194" t="n">
         <v>1018800</v>
@@ -4372,16 +4372,16 @@
         <v>44932</v>
       </c>
       <c r="B198" t="n">
-        <v>11.42030620574951</v>
+        <v>11.4203052520752</v>
       </c>
       <c r="C198" t="n">
-        <v>11.53779876976359</v>
+        <v>11.53779780627784</v>
       </c>
       <c r="D198" t="n">
-        <v>11.31847896833754</v>
+        <v>11.3184780231665</v>
       </c>
       <c r="E198" t="n">
-        <v>11.4124731689487</v>
+        <v>11.4124722159285</v>
       </c>
       <c r="F198" t="n">
         <v>2864500</v>
@@ -4472,16 +4472,16 @@
         <v>44939</v>
       </c>
       <c r="B203" t="n">
-        <v>11.58479785919189</v>
+        <v>11.58479595184326</v>
       </c>
       <c r="C203" t="n">
-        <v>11.78845236241762</v>
+        <v>11.78845042153883</v>
       </c>
       <c r="D203" t="n">
-        <v>11.4438061651126</v>
+        <v>11.44380428097718</v>
       </c>
       <c r="E203" t="n">
-        <v>11.7492879199512</v>
+        <v>11.74928598552053</v>
       </c>
       <c r="F203" t="n">
         <v>2269100</v>
@@ -4492,16 +4492,16 @@
         <v>44942</v>
       </c>
       <c r="B204" t="n">
-        <v>11.78845119476318</v>
+        <v>11.78845024108887</v>
       </c>
       <c r="C204" t="n">
-        <v>11.80411652199833</v>
+        <v>11.8041155670567</v>
       </c>
       <c r="D204" t="n">
-        <v>11.39680830289065</v>
+        <v>11.39680738089987</v>
       </c>
       <c r="E204" t="n">
-        <v>11.49080250730011</v>
+        <v>11.49080157770529</v>
       </c>
       <c r="F204" t="n">
         <v>3279700</v>
@@ -4512,16 +4512,16 @@
         <v>44943</v>
       </c>
       <c r="B205" t="n">
-        <v>11.74928569793701</v>
+        <v>11.74928665161133</v>
       </c>
       <c r="C205" t="n">
-        <v>11.93727408982413</v>
+        <v>11.93727505875722</v>
       </c>
       <c r="D205" t="n">
-        <v>11.60829403052194</v>
+        <v>11.60829497275214</v>
       </c>
       <c r="E205" t="n">
-        <v>11.81194849523272</v>
+        <v>11.81194945399329</v>
       </c>
       <c r="F205" t="n">
         <v>2676600</v>
@@ -4572,16 +4572,16 @@
         <v>44946</v>
       </c>
       <c r="B208" t="n">
-        <v>11.58479785919189</v>
+        <v>11.58479595184326</v>
       </c>
       <c r="C208" t="n">
-        <v>11.68662511080476</v>
+        <v>11.68662318669104</v>
       </c>
       <c r="D208" t="n">
-        <v>11.48297060757903</v>
+        <v>11.48296871699548</v>
       </c>
       <c r="E208" t="n">
-        <v>11.65529370623154</v>
+        <v>11.6552917872763</v>
       </c>
       <c r="F208" t="n">
         <v>2012100</v>
@@ -4612,16 +4612,16 @@
         <v>44950</v>
       </c>
       <c r="B210" t="n">
-        <v>11.68662357330322</v>
+        <v>11.68662452697754</v>
       </c>
       <c r="C210" t="n">
-        <v>11.80411613824548</v>
+        <v>11.80411710150764</v>
       </c>
       <c r="D210" t="n">
-        <v>11.32631209461427</v>
+        <v>11.32631301888575</v>
       </c>
       <c r="E210" t="n">
-        <v>11.52996657104705</v>
+        <v>11.52996751193754</v>
       </c>
       <c r="F210" t="n">
         <v>5839900</v>
@@ -4632,16 +4632,16 @@
         <v>44951</v>
       </c>
       <c r="B211" t="n">
-        <v>11.89027786254883</v>
+        <v>11.89027881622314</v>
       </c>
       <c r="C211" t="n">
-        <v>12.07043322555739</v>
+        <v>12.07043419368129</v>
       </c>
       <c r="D211" t="n">
-        <v>11.62396058940618</v>
+        <v>11.62396152172019</v>
       </c>
       <c r="E211" t="n">
-        <v>11.67879035258278</v>
+        <v>11.67879128929448</v>
       </c>
       <c r="F211" t="n">
         <v>10764800</v>
@@ -4712,16 +4712,16 @@
         <v>44957</v>
       </c>
       <c r="B215" t="n">
-        <v>12.07043361663818</v>
+        <v>12.0704345703125</v>
       </c>
       <c r="C215" t="n">
-        <v>12.14092945557759</v>
+        <v>12.14093041482172</v>
       </c>
       <c r="D215" t="n">
-        <v>11.82761544584636</v>
+        <v>11.82761638033583</v>
       </c>
       <c r="E215" t="n">
-        <v>11.84328077283316</v>
+        <v>11.84328170856034</v>
       </c>
       <c r="F215" t="n">
         <v>5446800</v>
@@ -4752,16 +4752,16 @@
         <v>44959</v>
       </c>
       <c r="B217" t="n">
-        <v>12.03910160064697</v>
+        <v>12.03910255432129</v>
       </c>
       <c r="C217" t="n">
-        <v>12.19575859750976</v>
+        <v>12.19575956359362</v>
       </c>
       <c r="D217" t="n">
-        <v>11.85111320441163</v>
+        <v>11.8511141431945</v>
       </c>
       <c r="E217" t="n">
-        <v>12.07043300001953</v>
+        <v>12.07043395617575</v>
       </c>
       <c r="F217" t="n">
         <v>3404900</v>
@@ -4932,16 +4932,16 @@
         <v>44972</v>
       </c>
       <c r="B226" t="n">
-        <v>11.75712013244629</v>
+        <v>11.75711917877197</v>
       </c>
       <c r="C226" t="n">
-        <v>11.92944247200145</v>
+        <v>11.92944150434928</v>
       </c>
       <c r="D226" t="n">
-        <v>11.63179452295179</v>
+        <v>11.63179357944321</v>
       </c>
       <c r="E226" t="n">
-        <v>11.66312592532541</v>
+        <v>11.6631249792754</v>
       </c>
       <c r="F226" t="n">
         <v>3961900</v>
@@ -4952,16 +4952,16 @@
         <v>44973</v>
       </c>
       <c r="B227" t="n">
-        <v>11.89027786254883</v>
+        <v>11.89027881622314</v>
       </c>
       <c r="C227" t="n">
-        <v>11.97643902568342</v>
+        <v>11.9764399862684</v>
       </c>
       <c r="D227" t="n">
-        <v>11.57696311596945</v>
+        <v>11.57696404451397</v>
       </c>
       <c r="E227" t="n">
-        <v>11.76495226271687</v>
+        <v>11.7649532063393</v>
       </c>
       <c r="F227" t="n">
         <v>4461000</v>
@@ -5052,16 +5052,16 @@
         <v>44984</v>
       </c>
       <c r="B232" t="n">
-        <v>11.64745998382568</v>
+        <v>11.64745903015137</v>
       </c>
       <c r="C232" t="n">
-        <v>11.85894751251565</v>
+        <v>11.85894654152509</v>
       </c>
       <c r="D232" t="n">
-        <v>11.56129881306286</v>
+        <v>11.56129786644328</v>
       </c>
       <c r="E232" t="n">
-        <v>11.7336211545885</v>
+        <v>11.73362019385946</v>
       </c>
       <c r="F232" t="n">
         <v>3412900</v>
@@ -5092,16 +5092,16 @@
         <v>44986</v>
       </c>
       <c r="B234" t="n">
-        <v>11.52996730804443</v>
+        <v>11.52996635437012</v>
       </c>
       <c r="C234" t="n">
-        <v>11.6552929178602</v>
+        <v>11.65529195381987</v>
       </c>
       <c r="D234" t="n">
-        <v>11.31847978123065</v>
+        <v>11.31847884504903</v>
       </c>
       <c r="E234" t="n">
-        <v>11.6004631503157</v>
+        <v>11.60046219081048</v>
       </c>
       <c r="F234" t="n">
         <v>8005300</v>
@@ -5112,16 +5112,16 @@
         <v>44987</v>
       </c>
       <c r="B235" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="C235" t="n">
-        <v>11.67879152264125</v>
+        <v>11.67879055731306</v>
       </c>
       <c r="D235" t="n">
-        <v>11.45947170096243</v>
+        <v>11.45947075376244</v>
       </c>
       <c r="E235" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="F235" t="n">
         <v>2250800</v>
@@ -5132,16 +5132,16 @@
         <v>44988</v>
       </c>
       <c r="B236" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="C236" t="n">
-        <v>11.64746011954428</v>
+        <v>11.64745915680582</v>
       </c>
       <c r="D236" t="n">
-        <v>11.45947170096243</v>
+        <v>11.45947075376244</v>
       </c>
       <c r="E236" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="F236" t="n">
         <v>1727100</v>
@@ -5172,16 +5172,16 @@
         <v>44992</v>
       </c>
       <c r="B238" t="n">
-        <v>11.61612796783447</v>
+        <v>11.61612701416016</v>
       </c>
       <c r="C238" t="n">
-        <v>11.6239610048538</v>
+        <v>11.6239600505364</v>
       </c>
       <c r="D238" t="n">
-        <v>11.3889751232706</v>
+        <v>11.38897418824534</v>
       </c>
       <c r="E238" t="n">
-        <v>11.52996680162043</v>
+        <v>11.52996585501987</v>
       </c>
       <c r="F238" t="n">
         <v>3776700</v>
@@ -5272,16 +5272,16 @@
         <v>44999</v>
       </c>
       <c r="B243" t="n">
-        <v>11.75712013244629</v>
+        <v>11.75711917877197</v>
       </c>
       <c r="C243" t="n">
-        <v>11.82761597453684</v>
+        <v>11.82761501514428</v>
       </c>
       <c r="D243" t="n">
-        <v>11.63962681329553</v>
+        <v>11.63962586915163</v>
       </c>
       <c r="E243" t="n">
-        <v>11.69445732769904</v>
+        <v>11.69445637910759</v>
       </c>
       <c r="F243" t="n">
         <v>2520000</v>
@@ -5292,16 +5292,16 @@
         <v>45000</v>
       </c>
       <c r="B244" t="n">
-        <v>11.74928569793701</v>
+        <v>11.74928665161133</v>
       </c>
       <c r="C244" t="n">
-        <v>11.89027736535209</v>
+        <v>11.89027833047051</v>
       </c>
       <c r="D244" t="n">
-        <v>11.61612706693377</v>
+        <v>11.61612800979977</v>
       </c>
       <c r="E244" t="n">
-        <v>11.71795429928916</v>
+        <v>11.71795525042035</v>
       </c>
       <c r="F244" t="n">
         <v>4602600</v>
@@ -5372,16 +5372,16 @@
         <v>45006</v>
       </c>
       <c r="B248" t="n">
-        <v>11.34197807312012</v>
+        <v>11.3419771194458</v>
       </c>
       <c r="C248" t="n">
-        <v>11.42030695224922</v>
+        <v>11.42030599198873</v>
       </c>
       <c r="D248" t="n">
-        <v>11.27931526861666</v>
+        <v>11.27931432021125</v>
       </c>
       <c r="E248" t="n">
-        <v>11.36547718505858</v>
+        <v>11.36547622940837</v>
       </c>
       <c r="F248" t="n">
         <v>2410300</v>
@@ -5412,16 +5412,16 @@
         <v>45008</v>
       </c>
       <c r="B250" t="n">
-        <v>11.18532180786133</v>
+        <v>11.18532085418701</v>
       </c>
       <c r="C250" t="n">
-        <v>11.47513748476884</v>
+        <v>11.47513650638449</v>
       </c>
       <c r="D250" t="n">
-        <v>11.05999619049587</v>
+        <v>11.05999524750697</v>
       </c>
       <c r="E250" t="n">
-        <v>11.39680934741524</v>
+        <v>11.39680837570923</v>
       </c>
       <c r="F250" t="n">
         <v>4422500</v>
@@ -5432,16 +5432,16 @@
         <v>45009</v>
       </c>
       <c r="B251" t="n">
-        <v>11.30281352996826</v>
+        <v>11.30281448364258</v>
       </c>
       <c r="C251" t="n">
-        <v>11.39680772964997</v>
+        <v>11.39680869125504</v>
       </c>
       <c r="D251" t="n">
-        <v>11.11482438360535</v>
+        <v>11.11482532141809</v>
       </c>
       <c r="E251" t="n">
-        <v>11.20881933028655</v>
+        <v>11.20882027603011</v>
       </c>
       <c r="F251" t="n">
         <v>3265300</v>
@@ -5452,16 +5452,16 @@
         <v>45012</v>
       </c>
       <c r="B252" t="n">
-        <v>11.28714752197266</v>
+        <v>11.28714847564697</v>
       </c>
       <c r="C252" t="n">
-        <v>11.42030615904377</v>
+        <v>11.42030712396893</v>
       </c>
       <c r="D252" t="n">
-        <v>11.1931533217459</v>
+        <v>11.19315426747845</v>
       </c>
       <c r="E252" t="n">
-        <v>11.39680779573696</v>
+        <v>11.39680875867669</v>
       </c>
       <c r="F252" t="n">
         <v>2288800</v>
@@ -5472,16 +5472,16 @@
         <v>45013</v>
       </c>
       <c r="B253" t="n">
-        <v>11.42030620574951</v>
+        <v>11.4203052520752</v>
       </c>
       <c r="C253" t="n">
-        <v>11.45163760595323</v>
+        <v>11.45163664966253</v>
       </c>
       <c r="D253" t="n">
-        <v>11.25581616793009</v>
+        <v>11.25581522799183</v>
       </c>
       <c r="E253" t="n">
-        <v>11.31064593153673</v>
+        <v>11.3106449870198</v>
       </c>
       <c r="F253" t="n">
         <v>3302900</v>
@@ -5532,16 +5532,16 @@
         <v>45016</v>
       </c>
       <c r="B256" t="n">
-        <v>11.49080181121826</v>
+        <v>11.49080276489258</v>
       </c>
       <c r="C256" t="n">
-        <v>11.61612740950566</v>
+        <v>11.61612837358132</v>
       </c>
       <c r="D256" t="n">
-        <v>11.30281341378716</v>
+        <v>11.30281435185946</v>
       </c>
       <c r="E256" t="n">
-        <v>11.42813901207456</v>
+        <v>11.42813996054821</v>
       </c>
       <c r="F256" t="n">
         <v>5155800</v>
@@ -5552,16 +5552,16 @@
         <v>45019</v>
       </c>
       <c r="B257" t="n">
-        <v>11.34197807312012</v>
+        <v>11.3419771194458</v>
       </c>
       <c r="C257" t="n">
-        <v>11.58479700082069</v>
+        <v>11.58479602672929</v>
       </c>
       <c r="D257" t="n">
-        <v>11.24798386636493</v>
+        <v>11.24798292059398</v>
       </c>
       <c r="E257" t="n">
-        <v>11.58479700082069</v>
+        <v>11.58479602672929</v>
       </c>
       <c r="F257" t="n">
         <v>6471200</v>
@@ -5592,16 +5592,16 @@
         <v>45021</v>
       </c>
       <c r="B259" t="n">
-        <v>11.49080181121826</v>
+        <v>11.49080276489258</v>
       </c>
       <c r="C259" t="n">
-        <v>11.56913068364763</v>
+        <v>11.56913164382282</v>
       </c>
       <c r="D259" t="n">
-        <v>11.27931430385866</v>
+        <v>11.27931523998066</v>
       </c>
       <c r="E259" t="n">
-        <v>11.55346461036196</v>
+        <v>11.55346556923695</v>
       </c>
       <c r="F259" t="n">
         <v>4689800</v>
@@ -5612,16 +5612,16 @@
         <v>45022</v>
       </c>
       <c r="B260" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="C260" t="n">
-        <v>11.66312619459255</v>
+        <v>11.6631252305592</v>
       </c>
       <c r="D260" t="n">
-        <v>11.47513702901113</v>
+        <v>11.4751360805163</v>
       </c>
       <c r="E260" t="n">
-        <v>11.4908031040594</v>
+        <v>11.49080215426967</v>
       </c>
       <c r="F260" t="n">
         <v>4653400</v>
@@ -5772,16 +5772,16 @@
         <v>45035</v>
       </c>
       <c r="B268" t="n">
-        <v>12.03910160064697</v>
+        <v>12.03910255432129</v>
       </c>
       <c r="C268" t="n">
-        <v>12.06259996342652</v>
+        <v>12.06260091896225</v>
       </c>
       <c r="D268" t="n">
-        <v>11.86677853059817</v>
+        <v>11.86677947062196</v>
       </c>
       <c r="E268" t="n">
-        <v>11.96860576530885</v>
+        <v>11.96860671339886</v>
       </c>
       <c r="F268" t="n">
         <v>3098200</v>
@@ -5792,16 +5792,16 @@
         <v>45036</v>
       </c>
       <c r="B269" t="n">
-        <v>12.09393119812012</v>
+        <v>12.09393215179443</v>
       </c>
       <c r="C269" t="n">
-        <v>12.14092867003875</v>
+        <v>12.14092962741908</v>
       </c>
       <c r="D269" t="n">
-        <v>12.00777003776868</v>
+        <v>12.00777098464871</v>
       </c>
       <c r="E269" t="n">
-        <v>12.06259979917419</v>
+        <v>12.06260075037785</v>
       </c>
       <c r="F269" t="n">
         <v>4813100</v>
@@ -5932,16 +5932,16 @@
         <v>45049</v>
       </c>
       <c r="B276" t="n">
-        <v>12.28975296020508</v>
+        <v>12.28975391387939</v>
       </c>
       <c r="C276" t="n">
-        <v>12.48557439565576</v>
+        <v>12.48557536452565</v>
       </c>
       <c r="D276" t="n">
-        <v>12.28192067050667</v>
+        <v>12.2819216235732</v>
       </c>
       <c r="E276" t="n">
-        <v>12.48557439565576</v>
+        <v>12.48557536452565</v>
       </c>
       <c r="F276" t="n">
         <v>6661600</v>
@@ -5992,16 +5992,16 @@
         <v>45054</v>
       </c>
       <c r="B279" t="n">
-        <v>12.11165904998779</v>
+        <v>12.11165809631348</v>
       </c>
       <c r="C279" t="n">
-        <v>12.58781451078781</v>
+        <v>12.58781351962092</v>
       </c>
       <c r="D279" t="n">
-        <v>12.05105773110397</v>
+        <v>12.05105678220141</v>
       </c>
       <c r="E279" t="n">
-        <v>12.54452750060035</v>
+        <v>12.54452651284189</v>
       </c>
       <c r="F279" t="n">
         <v>5826000</v>
@@ -6032,16 +6032,16 @@
         <v>45056</v>
       </c>
       <c r="B281" t="n">
-        <v>11.86925220489502</v>
+        <v>11.86925315856934</v>
       </c>
       <c r="C281" t="n">
-        <v>12.0510569757826</v>
+        <v>12.05105794406462</v>
       </c>
       <c r="D281" t="n">
-        <v>11.69610500062852</v>
+        <v>11.69610594039075</v>
       </c>
       <c r="E281" t="n">
-        <v>12.0164275349293</v>
+        <v>12.0164285004289</v>
       </c>
       <c r="F281" t="n">
         <v>5308900</v>
@@ -6072,16 +6072,16 @@
         <v>45058</v>
       </c>
       <c r="B283" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C283" t="n">
-        <v>12.25017632493442</v>
+        <v>12.25017729158851</v>
       </c>
       <c r="D283" t="n">
-        <v>11.99911266679329</v>
+        <v>11.9991136136361</v>
       </c>
       <c r="E283" t="n">
-        <v>12.04239967522403</v>
+        <v>12.0424006254826</v>
       </c>
       <c r="F283" t="n">
         <v>3087800</v>
@@ -6112,16 +6112,16 @@
         <v>45062</v>
       </c>
       <c r="B285" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="C285" t="n">
-        <v>12.30212031805942</v>
+        <v>12.30212128603885</v>
       </c>
       <c r="D285" t="n">
-        <v>12.08568611177803</v>
+        <v>12.08568706272756</v>
       </c>
       <c r="E285" t="n">
-        <v>12.18091686531469</v>
+        <v>12.18091782375736</v>
       </c>
       <c r="F285" t="n">
         <v>2907500</v>
@@ -6132,16 +6132,16 @@
         <v>45063</v>
       </c>
       <c r="B286" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="C286" t="n">
-        <v>12.24151939290137</v>
+        <v>12.24152036724783</v>
       </c>
       <c r="D286" t="n">
-        <v>11.94716873091856</v>
+        <v>11.9471696818366</v>
       </c>
       <c r="E286" t="n">
-        <v>12.12897350298847</v>
+        <v>12.128974468377</v>
       </c>
       <c r="F286" t="n">
         <v>4330800</v>
@@ -6152,16 +6152,16 @@
         <v>45064</v>
       </c>
       <c r="B287" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="C287" t="n">
-        <v>12.05971462083146</v>
+        <v>12.05971558070743</v>
       </c>
       <c r="D287" t="n">
-        <v>11.82596527432829</v>
+        <v>11.82596621559931</v>
       </c>
       <c r="E287" t="n">
-        <v>12.01642761307558</v>
+        <v>12.01642856950617</v>
       </c>
       <c r="F287" t="n">
         <v>4680600</v>
@@ -6172,16 +6172,16 @@
         <v>45065</v>
       </c>
       <c r="B288" t="n">
-        <v>12.09434413909912</v>
+        <v>12.09434509277344</v>
       </c>
       <c r="C288" t="n">
-        <v>12.18091732953242</v>
+        <v>12.18091829003328</v>
       </c>
       <c r="D288" t="n">
-        <v>11.93851124043578</v>
+        <v>11.93851218182222</v>
       </c>
       <c r="E288" t="n">
-        <v>11.99911255630219</v>
+        <v>11.99911350246722</v>
       </c>
       <c r="F288" t="n">
         <v>2962700</v>
@@ -6292,16 +6292,16 @@
         <v>45075</v>
       </c>
       <c r="B294" t="n">
-        <v>12.28480625152588</v>
+        <v>12.28480529785156</v>
       </c>
       <c r="C294" t="n">
-        <v>12.34540839597375</v>
+        <v>12.34540743759487</v>
       </c>
       <c r="D294" t="n">
-        <v>12.16360361389222</v>
+        <v>12.16360266962691</v>
       </c>
       <c r="E294" t="n">
-        <v>12.16360361389222</v>
+        <v>12.16360266962691</v>
       </c>
       <c r="F294" t="n">
         <v>1431900</v>
@@ -6312,16 +6312,16 @@
         <v>45076</v>
       </c>
       <c r="B295" t="n">
-        <v>12.26749134063721</v>
+        <v>12.26749229431152</v>
       </c>
       <c r="C295" t="n">
-        <v>12.3800372312229</v>
+        <v>12.38003819364653</v>
       </c>
       <c r="D295" t="n">
-        <v>12.25017620717894</v>
+        <v>12.25017715950718</v>
       </c>
       <c r="E295" t="n">
-        <v>12.37137966449377</v>
+        <v>12.37138062624436</v>
       </c>
       <c r="F295" t="n">
         <v>1829100</v>
@@ -6392,16 +6392,16 @@
         <v>45082</v>
       </c>
       <c r="B299" t="n">
-        <v>12.0683708190918</v>
+        <v>12.06837177276611</v>
       </c>
       <c r="C299" t="n">
-        <v>12.19823183651883</v>
+        <v>12.1982328004551</v>
       </c>
       <c r="D299" t="n">
-        <v>11.97314006681674</v>
+        <v>11.97314101296568</v>
       </c>
       <c r="E299" t="n">
-        <v>12.17225996328581</v>
+        <v>12.17226092516972</v>
       </c>
       <c r="F299" t="n">
         <v>3442900</v>
@@ -6472,16 +6472,16 @@
         <v>45089</v>
       </c>
       <c r="B303" t="n">
-        <v>12.45795440673828</v>
+        <v>12.45795345306396</v>
       </c>
       <c r="C303" t="n">
-        <v>12.45795440673828</v>
+        <v>12.45795345306396</v>
       </c>
       <c r="D303" t="n">
-        <v>12.25883448851593</v>
+        <v>12.25883355008453</v>
       </c>
       <c r="E303" t="n">
-        <v>12.3800379528961</v>
+        <v>12.3800370051864</v>
       </c>
       <c r="F303" t="n">
         <v>2572800</v>
@@ -6492,16 +6492,16 @@
         <v>45090</v>
       </c>
       <c r="B304" t="n">
-        <v>12.3107795715332</v>
+        <v>12.31077861785889</v>
       </c>
       <c r="C304" t="n">
-        <v>12.5012411047074</v>
+        <v>12.50124013627868</v>
       </c>
       <c r="D304" t="n">
-        <v>12.29346443635495</v>
+        <v>12.29346348402198</v>
       </c>
       <c r="E304" t="n">
-        <v>12.46661165998199</v>
+        <v>12.46661069423589</v>
       </c>
       <c r="F304" t="n">
         <v>1312000</v>
@@ -6532,16 +6532,16 @@
         <v>45092</v>
       </c>
       <c r="B306" t="n">
-        <v>12.4666109085083</v>
+        <v>12.46661186218262</v>
       </c>
       <c r="C306" t="n">
-        <v>12.49258360971007</v>
+        <v>12.49258456537125</v>
       </c>
       <c r="D306" t="n">
-        <v>12.36272258059435</v>
+        <v>12.36272352632139</v>
       </c>
       <c r="E306" t="n">
-        <v>12.45795416707208</v>
+        <v>12.45795512008417</v>
       </c>
       <c r="F306" t="n">
         <v>1266000</v>
@@ -6572,16 +6572,16 @@
         <v>45096</v>
       </c>
       <c r="B308" t="n">
-        <v>12.61378574371338</v>
+        <v>12.6137866973877</v>
       </c>
       <c r="C308" t="n">
-        <v>12.80424808345158</v>
+        <v>12.80424905152594</v>
       </c>
       <c r="D308" t="n">
-        <v>12.38869478834751</v>
+        <v>12.38869572500366</v>
       </c>
       <c r="E308" t="n">
-        <v>12.80424808345158</v>
+        <v>12.80424905152594</v>
       </c>
       <c r="F308" t="n">
         <v>3301400</v>
@@ -6592,16 +6592,16 @@
         <v>45097</v>
       </c>
       <c r="B309" t="n">
-        <v>12.72633171081543</v>
+        <v>12.72633266448975</v>
       </c>
       <c r="C309" t="n">
-        <v>12.89947891815102</v>
+        <v>12.89947988480048</v>
       </c>
       <c r="D309" t="n">
-        <v>12.64841526110666</v>
+        <v>12.64841620894215</v>
       </c>
       <c r="E309" t="n">
-        <v>12.69170226934831</v>
+        <v>12.6917032204276</v>
       </c>
       <c r="F309" t="n">
         <v>3568000</v>
@@ -6612,16 +6612,16 @@
         <v>45098</v>
       </c>
       <c r="B310" t="n">
-        <v>12.86485004425049</v>
+        <v>12.86484909057617</v>
       </c>
       <c r="C310" t="n">
-        <v>12.90813705440186</v>
+        <v>12.90813609751867</v>
       </c>
       <c r="D310" t="n">
-        <v>12.63975907759925</v>
+        <v>12.63975814061098</v>
       </c>
       <c r="E310" t="n">
-        <v>12.75230414810935</v>
+        <v>12.75230320277808</v>
       </c>
       <c r="F310" t="n">
         <v>5022600</v>
@@ -6672,16 +6672,16 @@
         <v>45103</v>
       </c>
       <c r="B313" t="n">
-        <v>12.71767520904541</v>
+        <v>12.71767425537109</v>
       </c>
       <c r="C313" t="n">
-        <v>13.01202589898095</v>
+        <v>13.01202492323384</v>
       </c>
       <c r="D313" t="n">
-        <v>12.66573145531036</v>
+        <v>12.66573050553121</v>
       </c>
       <c r="E313" t="n">
-        <v>12.94276701024684</v>
+        <v>12.94276603969331</v>
       </c>
       <c r="F313" t="n">
         <v>2677600</v>
@@ -6692,16 +6692,16 @@
         <v>45104</v>
       </c>
       <c r="B314" t="n">
-        <v>12.50123977661133</v>
+        <v>12.50124073028564</v>
       </c>
       <c r="C314" t="n">
-        <v>12.83887744603771</v>
+        <v>12.83887842546918</v>
       </c>
       <c r="D314" t="n">
-        <v>12.3973514534719</v>
+        <v>12.39735239922096</v>
       </c>
       <c r="E314" t="n">
-        <v>12.76961856394476</v>
+        <v>12.76961953809272</v>
       </c>
       <c r="F314" t="n">
         <v>3014700</v>
@@ -6792,16 +6792,16 @@
         <v>45111</v>
       </c>
       <c r="B319" t="n">
-        <v>12.34540843963623</v>
+        <v>12.34540748596191</v>
       </c>
       <c r="C319" t="n">
-        <v>12.40600975866739</v>
+        <v>12.40600880031166</v>
       </c>
       <c r="D319" t="n">
-        <v>12.23286254312761</v>
+        <v>12.23286159814739</v>
       </c>
       <c r="E319" t="n">
-        <v>12.38869544992894</v>
+        <v>12.38869449291073</v>
       </c>
       <c r="F319" t="n">
         <v>2230100</v>
@@ -6812,16 +6812,16 @@
         <v>45112</v>
       </c>
       <c r="B320" t="n">
-        <v>12.44063854217529</v>
+        <v>12.44063949584961</v>
       </c>
       <c r="C320" t="n">
-        <v>12.54452686599102</v>
+        <v>12.54452782762921</v>
       </c>
       <c r="D320" t="n">
-        <v>12.24151946126957</v>
+        <v>12.24152039967981</v>
       </c>
       <c r="E320" t="n">
-        <v>12.30212077708766</v>
+        <v>12.30212172014348</v>
       </c>
       <c r="F320" t="n">
         <v>5051100</v>
@@ -6852,16 +6852,16 @@
         <v>45114</v>
       </c>
       <c r="B322" t="n">
-        <v>12.34540843963623</v>
+        <v>12.34540748596191</v>
       </c>
       <c r="C322" t="n">
-        <v>12.48392621206805</v>
+        <v>12.48392524769333</v>
       </c>
       <c r="D322" t="n">
-        <v>12.25883441905082</v>
+        <v>12.25883347206429</v>
       </c>
       <c r="E322" t="n">
-        <v>12.42332489303689</v>
+        <v>12.42332393334358</v>
       </c>
       <c r="F322" t="n">
         <v>2149700</v>
@@ -6872,16 +6872,16 @@
         <v>45117</v>
       </c>
       <c r="B323" t="n">
-        <v>12.38869571685791</v>
+        <v>12.38869476318359</v>
       </c>
       <c r="C323" t="n">
-        <v>12.45795460456609</v>
+        <v>12.45795364556026</v>
       </c>
       <c r="D323" t="n">
-        <v>12.31077926177845</v>
+        <v>12.31077831410209</v>
       </c>
       <c r="E323" t="n">
-        <v>12.38003814948662</v>
+        <v>12.38003719647876</v>
       </c>
       <c r="F323" t="n">
         <v>1514600</v>
@@ -6892,16 +6892,16 @@
         <v>45118</v>
       </c>
       <c r="B324" t="n">
-        <v>12.34540843963623</v>
+        <v>12.34540748596191</v>
       </c>
       <c r="C324" t="n">
-        <v>12.39735219148264</v>
+        <v>12.3973512337957</v>
       </c>
       <c r="D324" t="n">
-        <v>12.23286254312761</v>
+        <v>12.23286159814739</v>
       </c>
       <c r="E324" t="n">
-        <v>12.38869544992894</v>
+        <v>12.38869449291073</v>
       </c>
       <c r="F324" t="n">
         <v>1919200</v>
@@ -6912,16 +6912,16 @@
         <v>45119</v>
       </c>
       <c r="B325" t="n">
-        <v>12.38869571685791</v>
+        <v>12.38869476318359</v>
       </c>
       <c r="C325" t="n">
-        <v>12.45795460456609</v>
+        <v>12.45795364556026</v>
       </c>
       <c r="D325" t="n">
-        <v>12.28480655966458</v>
+        <v>12.28480561398759</v>
       </c>
       <c r="E325" t="n">
-        <v>12.37138058211533</v>
+        <v>12.37137962977392</v>
       </c>
       <c r="F325" t="n">
         <v>1842800</v>
@@ -6932,16 +6932,16 @@
         <v>45120</v>
       </c>
       <c r="B326" t="n">
-        <v>12.44063854217529</v>
+        <v>12.44063949584961</v>
       </c>
       <c r="C326" t="n">
-        <v>12.51855499144484</v>
+        <v>12.51855595109208</v>
       </c>
       <c r="D326" t="n">
-        <v>12.34540778508529</v>
+        <v>12.34540873145941</v>
       </c>
       <c r="E326" t="n">
-        <v>12.4752679834472</v>
+        <v>12.47526893977614</v>
       </c>
       <c r="F326" t="n">
         <v>1737300</v>
@@ -6952,16 +6952,16 @@
         <v>45121</v>
       </c>
       <c r="B327" t="n">
-        <v>12.38003826141357</v>
+        <v>12.38003730773926</v>
       </c>
       <c r="C327" t="n">
-        <v>12.48392659391508</v>
+        <v>12.48392563223791</v>
       </c>
       <c r="D327" t="n">
-        <v>12.33675124979684</v>
+        <v>12.33675029945707</v>
       </c>
       <c r="E327" t="n">
-        <v>12.48392659391508</v>
+        <v>12.48392563223791</v>
       </c>
       <c r="F327" t="n">
         <v>1319400</v>
@@ -7052,16 +7052,16 @@
         <v>45128</v>
       </c>
       <c r="B332" t="n">
-        <v>12.38869571685791</v>
+        <v>12.38869476318359</v>
       </c>
       <c r="C332" t="n">
-        <v>12.38869571685791</v>
+        <v>12.38869476318359</v>
       </c>
       <c r="D332" t="n">
-        <v>12.2242052393277</v>
+        <v>12.22420429831576</v>
       </c>
       <c r="E332" t="n">
-        <v>12.27614981792436</v>
+        <v>12.27614887291376</v>
       </c>
       <c r="F332" t="n">
         <v>2631400</v>
@@ -7072,16 +7072,16 @@
         <v>45131</v>
       </c>
       <c r="B333" t="n">
-        <v>12.34540843963623</v>
+        <v>12.34540748596191</v>
       </c>
       <c r="C333" t="n">
-        <v>12.42332489303689</v>
+        <v>12.42332393334358</v>
       </c>
       <c r="D333" t="n">
-        <v>12.31943573808198</v>
+        <v>12.31943478641403</v>
       </c>
       <c r="E333" t="n">
-        <v>12.42332489303689</v>
+        <v>12.42332393334358</v>
       </c>
       <c r="F333" t="n">
         <v>1347200</v>
@@ -7132,16 +7132,16 @@
         <v>45134</v>
       </c>
       <c r="B336" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C336" t="n">
-        <v>12.22420445012837</v>
+        <v>12.22420541473304</v>
       </c>
       <c r="D336" t="n">
-        <v>12.03374210841168</v>
+        <v>12.03374305798708</v>
       </c>
       <c r="E336" t="n">
-        <v>12.18091744169762</v>
+        <v>12.18091840288654</v>
       </c>
       <c r="F336" t="n">
         <v>2852900</v>
@@ -7152,16 +7152,16 @@
         <v>45135</v>
       </c>
       <c r="B337" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="C337" t="n">
-        <v>12.22420387169716</v>
+        <v>12.22420483354582</v>
       </c>
       <c r="D337" t="n">
-        <v>12.05971423820094</v>
+        <v>12.0597151871069</v>
       </c>
       <c r="E337" t="n">
-        <v>12.14628742533491</v>
+        <v>12.14628838105279</v>
       </c>
       <c r="F337" t="n">
         <v>1506100</v>
@@ -7172,16 +7172,16 @@
         <v>45138</v>
       </c>
       <c r="B338" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="C338" t="n">
-        <v>12.20688956452276</v>
+        <v>12.20689052500906</v>
       </c>
       <c r="D338" t="n">
-        <v>12.10300041895243</v>
+        <v>12.10300137126433</v>
       </c>
       <c r="E338" t="n">
-        <v>12.20688956452276</v>
+        <v>12.20689052500906</v>
       </c>
       <c r="F338" t="n">
         <v>1549400</v>
@@ -7192,16 +7192,16 @@
         <v>45139</v>
       </c>
       <c r="B339" t="n">
-        <v>12.12897396087646</v>
+        <v>12.12897491455078</v>
       </c>
       <c r="C339" t="n">
-        <v>12.38003762458143</v>
+        <v>12.38003859799633</v>
       </c>
       <c r="D339" t="n">
-        <v>12.08568695148643</v>
+        <v>12.08568790175718</v>
       </c>
       <c r="E339" t="n">
-        <v>12.12031639387225</v>
+        <v>12.12031734686584</v>
       </c>
       <c r="F339" t="n">
         <v>5884200</v>
@@ -7292,16 +7292,16 @@
         <v>45146</v>
       </c>
       <c r="B344" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C344" t="n">
-        <v>12.15494556689158</v>
+        <v>12.15494652603107</v>
       </c>
       <c r="D344" t="n">
-        <v>11.92985378355649</v>
+        <v>11.92985472493413</v>
       </c>
       <c r="E344" t="n">
-        <v>11.99045592561195</v>
+        <v>11.99045687177166</v>
       </c>
       <c r="F344" t="n">
         <v>2176400</v>
@@ -7332,16 +7332,16 @@
         <v>45148</v>
       </c>
       <c r="B346" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C346" t="n">
-        <v>12.09434452900206</v>
+        <v>12.09434549372545</v>
       </c>
       <c r="D346" t="n">
-        <v>11.88656704887551</v>
+        <v>11.88656799702522</v>
       </c>
       <c r="E346" t="n">
-        <v>12.01642807715848</v>
+        <v>12.01642903566675</v>
       </c>
       <c r="F346" t="n">
         <v>2835300</v>
@@ -7452,16 +7452,16 @@
         <v>45156</v>
       </c>
       <c r="B352" t="n">
-        <v>11.77402210235596</v>
+        <v>11.77402114868164</v>
       </c>
       <c r="C352" t="n">
-        <v>11.80865154513102</v>
+        <v>11.80865058865178</v>
       </c>
       <c r="D352" t="n">
-        <v>11.65281863982772</v>
+        <v>11.65281769597066</v>
       </c>
       <c r="E352" t="n">
-        <v>11.71341995827632</v>
+        <v>11.71341900951066</v>
       </c>
       <c r="F352" t="n">
         <v>3061800</v>
@@ -7492,16 +7492,16 @@
         <v>45160</v>
       </c>
       <c r="B354" t="n">
-        <v>11.79999446868896</v>
+        <v>11.79999351501465</v>
       </c>
       <c r="C354" t="n">
-        <v>11.86925335711897</v>
+        <v>11.86925239784715</v>
       </c>
       <c r="D354" t="n">
-        <v>11.73073558025896</v>
+        <v>11.73073463218214</v>
       </c>
       <c r="E354" t="n">
-        <v>11.79133690122745</v>
+        <v>11.79133594825283</v>
       </c>
       <c r="F354" t="n">
         <v>2231700</v>
@@ -7512,16 +7512,16 @@
         <v>45161</v>
       </c>
       <c r="B355" t="n">
-        <v>11.87791061401367</v>
+        <v>11.87790966033936</v>
       </c>
       <c r="C355" t="n">
-        <v>11.89522492285292</v>
+        <v>11.89522396778845</v>
       </c>
       <c r="D355" t="n">
-        <v>11.79133659292425</v>
+        <v>11.79133564620093</v>
       </c>
       <c r="E355" t="n">
-        <v>11.86059547954337</v>
+        <v>11.86059452725928</v>
       </c>
       <c r="F355" t="n">
         <v>2615000</v>
@@ -7532,16 +7532,16 @@
         <v>45162</v>
       </c>
       <c r="B356" t="n">
-        <v>11.97314167022705</v>
+        <v>11.97314071655273</v>
       </c>
       <c r="C356" t="n">
-        <v>11.99911354693815</v>
+        <v>11.99911259119515</v>
       </c>
       <c r="D356" t="n">
-        <v>11.89522521446267</v>
+        <v>11.89522426699448</v>
       </c>
       <c r="E356" t="n">
-        <v>11.90388278191006</v>
+        <v>11.90388183375229</v>
       </c>
       <c r="F356" t="n">
         <v>2322800</v>
@@ -7592,16 +7592,16 @@
         <v>45167</v>
       </c>
       <c r="B359" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="C359" t="n">
-        <v>12.12031555175781</v>
+        <v>12.12031650543213</v>
       </c>
       <c r="D359" t="n">
-        <v>11.97314022543599</v>
+        <v>11.97314116752997</v>
       </c>
       <c r="E359" t="n">
-        <v>11.98179779183868</v>
+        <v>11.98179873461387</v>
       </c>
       <c r="F359" t="n">
         <v>1776800</v>
@@ -7612,16 +7612,16 @@
         <v>45168</v>
       </c>
       <c r="B360" t="n">
-        <v>12.11165904998779</v>
+        <v>12.11165809631348</v>
       </c>
       <c r="C360" t="n">
-        <v>12.19823307036272</v>
+        <v>12.19823210987155</v>
       </c>
       <c r="D360" t="n">
-        <v>12.05971529826767</v>
+        <v>12.05971434868342</v>
       </c>
       <c r="E360" t="n">
-        <v>12.17226119450266</v>
+        <v>12.17226023605652</v>
       </c>
       <c r="F360" t="n">
         <v>1998700</v>
@@ -7632,16 +7632,16 @@
         <v>45169</v>
       </c>
       <c r="B361" t="n">
-        <v>11.78267860412598</v>
+        <v>11.78267955780029</v>
       </c>
       <c r="C361" t="n">
-        <v>12.1203162835374</v>
+        <v>12.12031726453966</v>
       </c>
       <c r="D361" t="n">
-        <v>11.78267860412598</v>
+        <v>11.78267955780029</v>
       </c>
       <c r="E361" t="n">
-        <v>12.1203162835374</v>
+        <v>12.12031726453966</v>
       </c>
       <c r="F361" t="n">
         <v>3236500</v>
@@ -7652,16 +7652,16 @@
         <v>45170</v>
       </c>
       <c r="B362" t="n">
-        <v>12.04239940643311</v>
+        <v>12.04240036010742</v>
       </c>
       <c r="C362" t="n">
-        <v>12.04239940643311</v>
+        <v>12.04240036010742</v>
       </c>
       <c r="D362" t="n">
-        <v>11.89522407643217</v>
+        <v>11.89522501845123</v>
       </c>
       <c r="E362" t="n">
-        <v>11.90388164305129</v>
+        <v>11.90388258575596</v>
       </c>
       <c r="F362" t="n">
         <v>3740800</v>
@@ -7672,16 +7672,16 @@
         <v>45173</v>
       </c>
       <c r="B363" t="n">
-        <v>12.01642799377441</v>
+        <v>12.01642894744873</v>
       </c>
       <c r="C363" t="n">
-        <v>12.05105743595003</v>
+        <v>12.05105839237269</v>
       </c>
       <c r="D363" t="n">
-        <v>11.81730808204133</v>
+        <v>11.81730901991265</v>
       </c>
       <c r="E363" t="n">
-        <v>12.05105743595003</v>
+        <v>12.05105839237269</v>
       </c>
       <c r="F363" t="n">
         <v>2040600</v>
@@ -7712,16 +7712,16 @@
         <v>45175</v>
       </c>
       <c r="B365" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C365" t="n">
-        <v>12.02508564417022</v>
+        <v>12.02508660336907</v>
       </c>
       <c r="D365" t="n">
-        <v>11.81730816404367</v>
+        <v>11.81730910666884</v>
       </c>
       <c r="E365" t="n">
-        <v>11.9385116253149</v>
+        <v>11.93851257760805</v>
       </c>
       <c r="F365" t="n">
         <v>2473500</v>
@@ -7772,16 +7772,16 @@
         <v>45181</v>
       </c>
       <c r="B368" t="n">
-        <v>12.0683708190918</v>
+        <v>12.06837177276611</v>
       </c>
       <c r="C368" t="n">
-        <v>12.15494483070982</v>
+        <v>12.15494579122544</v>
       </c>
       <c r="D368" t="n">
-        <v>11.98179763310474</v>
+        <v>11.98179857993782</v>
       </c>
       <c r="E368" t="n">
-        <v>12.03374137957078</v>
+        <v>12.03374233050859</v>
       </c>
       <c r="F368" t="n">
         <v>2215400</v>
@@ -7792,16 +7792,16 @@
         <v>45182</v>
       </c>
       <c r="B369" t="n">
-        <v>12.0683708190918</v>
+        <v>12.06837177276611</v>
       </c>
       <c r="C369" t="n">
-        <v>12.19823183651883</v>
+        <v>12.1982328004551</v>
       </c>
       <c r="D369" t="n">
-        <v>12.03374137957078</v>
+        <v>12.03374233050859</v>
       </c>
       <c r="E369" t="n">
-        <v>12.07702838537979</v>
+        <v>12.07702933973825</v>
       </c>
       <c r="F369" t="n">
         <v>1684100</v>
@@ -7812,16 +7812,16 @@
         <v>45183</v>
       </c>
       <c r="B370" t="n">
-        <v>12.21554660797119</v>
+        <v>12.21554756164551</v>
       </c>
       <c r="C370" t="n">
-        <v>12.25017604880902</v>
+        <v>12.25017700518688</v>
       </c>
       <c r="D370" t="n">
-        <v>12.09434397785428</v>
+        <v>12.09434492206624</v>
       </c>
       <c r="E370" t="n">
-        <v>12.09434397785428</v>
+        <v>12.09434492206624</v>
       </c>
       <c r="F370" t="n">
         <v>2498700</v>
@@ -7892,16 +7892,16 @@
         <v>45189</v>
       </c>
       <c r="B374" t="n">
-        <v>12.0683708190918</v>
+        <v>12.06837177276611</v>
       </c>
       <c r="C374" t="n">
-        <v>12.14628726442182</v>
+        <v>12.1462882242533</v>
       </c>
       <c r="D374" t="n">
-        <v>11.97314006681674</v>
+        <v>11.97314101296568</v>
       </c>
       <c r="E374" t="n">
-        <v>12.08568595166779</v>
+        <v>12.08568690671039</v>
       </c>
       <c r="F374" t="n">
         <v>2998000</v>
@@ -7912,16 +7912,16 @@
         <v>45190</v>
       </c>
       <c r="B375" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C375" t="n">
-        <v>12.03374238555092</v>
+        <v>12.0337433454403</v>
       </c>
       <c r="D375" t="n">
-        <v>11.8779103074948</v>
+        <v>11.877911254954</v>
       </c>
       <c r="E375" t="n">
-        <v>12.02508564417022</v>
+        <v>12.02508660336907</v>
       </c>
       <c r="F375" t="n">
         <v>4405700</v>
@@ -7932,16 +7932,16 @@
         <v>45191</v>
       </c>
       <c r="B376" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C376" t="n">
-        <v>12.10300127038276</v>
+        <v>12.10300223579667</v>
       </c>
       <c r="D376" t="n">
-        <v>11.92985405830317</v>
+        <v>11.92985500990573</v>
       </c>
       <c r="E376" t="n">
-        <v>12.02508564417022</v>
+        <v>12.02508660336907</v>
       </c>
       <c r="F376" t="n">
         <v>2812600</v>
@@ -7952,16 +7952,16 @@
         <v>45194</v>
       </c>
       <c r="B377" t="n">
-        <v>11.80865097045898</v>
+        <v>11.8086519241333</v>
       </c>
       <c r="C377" t="n">
-        <v>11.97314060922783</v>
+        <v>11.97314157618643</v>
       </c>
       <c r="D377" t="n">
-        <v>11.80865097045898</v>
+        <v>11.8086519241333</v>
       </c>
       <c r="E377" t="n">
-        <v>11.95582630149842</v>
+        <v>11.95582726705872</v>
       </c>
       <c r="F377" t="n">
         <v>3691700</v>
@@ -8012,16 +8012,16 @@
         <v>45197</v>
       </c>
       <c r="B380" t="n">
-        <v>11.78267860412598</v>
+        <v>11.78267955780029</v>
       </c>
       <c r="C380" t="n">
-        <v>11.86059505519254</v>
+        <v>11.86059601517331</v>
       </c>
       <c r="D380" t="n">
-        <v>11.73073485383562</v>
+        <v>11.73073580330568</v>
       </c>
       <c r="E380" t="n">
-        <v>11.85193748826714</v>
+        <v>11.85193844754717</v>
       </c>
       <c r="F380" t="n">
         <v>2404900</v>
@@ -8072,16 +8072,16 @@
         <v>45202</v>
       </c>
       <c r="B383" t="n">
-        <v>11.80865097045898</v>
+        <v>11.8086519241333</v>
       </c>
       <c r="C383" t="n">
-        <v>11.91253929372841</v>
+        <v>11.91254025579282</v>
       </c>
       <c r="D383" t="n">
-        <v>11.75670639600877</v>
+        <v>11.75670734548801</v>
       </c>
       <c r="E383" t="n">
-        <v>11.8605947192782</v>
+        <v>11.86059567714752</v>
       </c>
       <c r="F383" t="n">
         <v>2809600</v>
@@ -8092,16 +8092,16 @@
         <v>45203</v>
       </c>
       <c r="B384" t="n">
-        <v>11.77402210235596</v>
+        <v>11.77402114868164</v>
       </c>
       <c r="C384" t="n">
-        <v>11.86059529647809</v>
+        <v>11.86059433579151</v>
       </c>
       <c r="D384" t="n">
-        <v>11.74804940105138</v>
+        <v>11.7480484494808</v>
       </c>
       <c r="E384" t="n">
-        <v>11.80865154513102</v>
+        <v>11.80865058865178</v>
       </c>
       <c r="F384" t="n">
         <v>4367600</v>
@@ -8172,16 +8172,16 @@
         <v>45209</v>
       </c>
       <c r="B388" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C388" t="n">
-        <v>12.16360313370393</v>
+        <v>12.16360409352659</v>
       </c>
       <c r="D388" t="n">
-        <v>11.9125394755628</v>
+        <v>11.91254041557417</v>
       </c>
       <c r="E388" t="n">
-        <v>11.92985378355649</v>
+        <v>11.92985472493413</v>
       </c>
       <c r="F388" t="n">
         <v>3643400</v>
@@ -8192,16 +8192,16 @@
         <v>45210</v>
       </c>
       <c r="B389" t="n">
-        <v>12.09434413909912</v>
+        <v>12.09434509277344</v>
       </c>
       <c r="C389" t="n">
-        <v>12.18957489626505</v>
+        <v>12.18957585744859</v>
       </c>
       <c r="D389" t="n">
-        <v>12.00777012303482</v>
+        <v>12.00777106988252</v>
       </c>
       <c r="E389" t="n">
-        <v>12.09434413909912</v>
+        <v>12.09434509277344</v>
       </c>
       <c r="F389" t="n">
         <v>3458500</v>
@@ -8212,16 +8212,16 @@
         <v>45212</v>
       </c>
       <c r="B390" t="n">
-        <v>12.02508640289307</v>
+        <v>12.02508544921875</v>
       </c>
       <c r="C390" t="n">
-        <v>12.19823362589739</v>
+        <v>12.19823265849127</v>
       </c>
       <c r="D390" t="n">
-        <v>12.02508640289307</v>
+        <v>12.02508544921875</v>
       </c>
       <c r="E390" t="n">
-        <v>12.0943452920948</v>
+        <v>12.09434433292776</v>
       </c>
       <c r="F390" t="n">
         <v>4555500</v>
@@ -8232,16 +8232,16 @@
         <v>45215</v>
       </c>
       <c r="B391" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="C391" t="n">
-        <v>12.12031593631109</v>
+        <v>12.12031690101054</v>
       </c>
       <c r="D391" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="E391" t="n">
-        <v>12.05971462083146</v>
+        <v>12.05971558070743</v>
       </c>
       <c r="F391" t="n">
         <v>3983600</v>
@@ -8252,16 +8252,16 @@
         <v>45216</v>
       </c>
       <c r="B392" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C392" t="n">
-        <v>12.10300127038276</v>
+        <v>12.10300223579667</v>
       </c>
       <c r="D392" t="n">
-        <v>11.88656704887551</v>
+        <v>11.88656799702522</v>
       </c>
       <c r="E392" t="n">
-        <v>11.97314106773082</v>
+        <v>11.97314202278624</v>
       </c>
       <c r="F392" t="n">
         <v>5165000</v>
@@ -8292,16 +8292,16 @@
         <v>45218</v>
       </c>
       <c r="B394" t="n">
-        <v>11.67013359069824</v>
+        <v>11.67013263702393</v>
       </c>
       <c r="C394" t="n">
-        <v>11.75670761521626</v>
+        <v>11.75670665446719</v>
       </c>
       <c r="D394" t="n">
-        <v>11.62684740407032</v>
+        <v>11.62684645393332</v>
       </c>
       <c r="E394" t="n">
-        <v>11.66147684875131</v>
+        <v>11.66147589578441</v>
       </c>
       <c r="F394" t="n">
         <v>3066300</v>
@@ -8332,16 +8332,16 @@
         <v>45222</v>
       </c>
       <c r="B396" t="n">
-        <v>11.72207736968994</v>
+        <v>11.72207832336426</v>
       </c>
       <c r="C396" t="n">
-        <v>11.90388214825212</v>
+        <v>11.90388311671755</v>
       </c>
       <c r="D396" t="n">
-        <v>11.72207736968994</v>
+        <v>11.72207832336426</v>
       </c>
       <c r="E396" t="n">
-        <v>11.77402194597815</v>
+        <v>11.77402290387853</v>
       </c>
       <c r="F396" t="n">
         <v>3068100</v>
@@ -8352,16 +8352,16 @@
         <v>45223</v>
       </c>
       <c r="B397" t="n">
-        <v>11.63550281524658</v>
+        <v>11.6355037689209</v>
       </c>
       <c r="C397" t="n">
-        <v>11.81730758543626</v>
+        <v>11.81730855401174</v>
       </c>
       <c r="D397" t="n">
-        <v>11.54892962626116</v>
+        <v>11.54893057283972</v>
       </c>
       <c r="E397" t="n">
-        <v>11.80865084447942</v>
+        <v>11.80865181234537</v>
       </c>
       <c r="F397" t="n">
         <v>3637500</v>
@@ -8452,16 +8452,16 @@
         <v>45230</v>
       </c>
       <c r="B402" t="n">
-        <v>11.61818981170654</v>
+        <v>11.61818885803223</v>
       </c>
       <c r="C402" t="n">
-        <v>11.66147682387321</v>
+        <v>11.6614758666457</v>
       </c>
       <c r="D402" t="n">
-        <v>11.52295904544475</v>
+        <v>11.52295809958741</v>
       </c>
       <c r="E402" t="n">
-        <v>11.52295904544475</v>
+        <v>11.52295809958741</v>
       </c>
       <c r="F402" t="n">
         <v>3290000</v>
@@ -8512,16 +8512,16 @@
         <v>45236</v>
       </c>
       <c r="B405" t="n">
-        <v>12.02508640289307</v>
+        <v>12.02508544921875</v>
       </c>
       <c r="C405" t="n">
-        <v>12.07703015697882</v>
+        <v>12.077029199185</v>
       </c>
       <c r="D405" t="n">
-        <v>11.81730890965679</v>
+        <v>11.8173079724607</v>
       </c>
       <c r="E405" t="n">
-        <v>11.94716994613335</v>
+        <v>11.94716899863836</v>
       </c>
       <c r="F405" t="n">
         <v>2982900</v>
@@ -8592,16 +8592,16 @@
         <v>45240</v>
       </c>
       <c r="B409" t="n">
-        <v>11.78267860412598</v>
+        <v>11.78267955780029</v>
       </c>
       <c r="C409" t="n">
-        <v>11.86059505519254</v>
+        <v>11.86059601517331</v>
       </c>
       <c r="D409" t="n">
-        <v>11.69610541176504</v>
+        <v>11.69610635843224</v>
       </c>
       <c r="E409" t="n">
-        <v>11.69610541176504</v>
+        <v>11.69610635843224</v>
       </c>
       <c r="F409" t="n">
         <v>3430000</v>
@@ -8692,16 +8692,16 @@
         <v>45250</v>
       </c>
       <c r="B414" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C414" t="n">
-        <v>12.23286201694073</v>
+        <v>12.23286298222856</v>
       </c>
       <c r="D414" t="n">
-        <v>11.99045592561195</v>
+        <v>11.99045687177166</v>
       </c>
       <c r="E414" t="n">
-        <v>12.20689014213468</v>
+        <v>12.20689110537309</v>
       </c>
       <c r="F414" t="n">
         <v>3248400</v>
@@ -8712,16 +8712,16 @@
         <v>45251</v>
       </c>
       <c r="B415" t="n">
-        <v>11.97314167022705</v>
+        <v>11.97314071655273</v>
       </c>
       <c r="C415" t="n">
-        <v>12.09434513759732</v>
+        <v>12.09434417426901</v>
       </c>
       <c r="D415" t="n">
-        <v>11.91254034935745</v>
+        <v>11.9125394005101</v>
       </c>
       <c r="E415" t="n">
-        <v>12.08568757014993</v>
+        <v>12.0856866075112</v>
       </c>
       <c r="F415" t="n">
         <v>2713400</v>
@@ -8732,16 +8732,16 @@
         <v>45252</v>
       </c>
       <c r="B416" t="n">
-        <v>12.4666109085083</v>
+        <v>12.46661186218262</v>
       </c>
       <c r="C416" t="n">
-        <v>12.94276636400384</v>
+        <v>12.94276735410323</v>
       </c>
       <c r="D416" t="n">
-        <v>12.44063903293757</v>
+        <v>12.44063998462508</v>
       </c>
       <c r="E416" t="n">
-        <v>12.81290616051917</v>
+        <v>12.81290714068447</v>
       </c>
       <c r="F416" t="n">
         <v>20875500</v>
@@ -8752,16 +8752,16 @@
         <v>45253</v>
       </c>
       <c r="B417" t="n">
-        <v>12.561842918396</v>
+        <v>12.56184196472168</v>
       </c>
       <c r="C417" t="n">
-        <v>12.76961958122722</v>
+        <v>12.76961861177884</v>
       </c>
       <c r="D417" t="n">
-        <v>12.46661132870839</v>
+        <v>12.46661038226389</v>
       </c>
       <c r="E417" t="n">
-        <v>12.76961958122722</v>
+        <v>12.76961861177884</v>
       </c>
       <c r="F417" t="n">
         <v>9122900</v>
@@ -8832,16 +8832,16 @@
         <v>45259</v>
       </c>
       <c r="B421" t="n">
-        <v>12.561842918396</v>
+        <v>12.56184196472168</v>
       </c>
       <c r="C421" t="n">
-        <v>12.75230444650908</v>
+        <v>12.75230347837524</v>
       </c>
       <c r="D421" t="n">
-        <v>12.561842918396</v>
+        <v>12.56184196472168</v>
       </c>
       <c r="E421" t="n">
-        <v>12.72633257006295</v>
+        <v>12.72633160390085</v>
       </c>
       <c r="F421" t="n">
         <v>5869600</v>
@@ -8852,16 +8852,16 @@
         <v>45260</v>
       </c>
       <c r="B422" t="n">
-        <v>12.71767520904541</v>
+        <v>12.71767425537109</v>
       </c>
       <c r="C422" t="n">
-        <v>12.71767520904541</v>
+        <v>12.71767425537109</v>
       </c>
       <c r="D422" t="n">
-        <v>12.58781499907671</v>
+        <v>12.58781405514036</v>
       </c>
       <c r="E422" t="n">
-        <v>12.6311020109433</v>
+        <v>12.63110106376094</v>
       </c>
       <c r="F422" t="n">
         <v>4162000</v>
@@ -8872,16 +8872,16 @@
         <v>45261</v>
       </c>
       <c r="B423" t="n">
-        <v>12.86485004425049</v>
+        <v>12.86484909057617</v>
       </c>
       <c r="C423" t="n">
-        <v>12.96873837323515</v>
+        <v>12.96873741185957</v>
       </c>
       <c r="D423" t="n">
-        <v>12.70901796358902</v>
+        <v>12.70901702146657</v>
       </c>
       <c r="E423" t="n">
-        <v>12.72633227227094</v>
+        <v>12.72633132886498</v>
       </c>
       <c r="F423" t="n">
         <v>6458300</v>
@@ -8892,16 +8892,16 @@
         <v>45264</v>
       </c>
       <c r="B424" t="n">
-        <v>12.89947891235352</v>
+        <v>12.89947986602783</v>
       </c>
       <c r="C424" t="n">
-        <v>12.98605292879791</v>
+        <v>12.98605388887275</v>
       </c>
       <c r="D424" t="n">
-        <v>12.86484947090196</v>
+        <v>12.86485042201608</v>
       </c>
       <c r="E424" t="n">
-        <v>12.94276592057571</v>
+        <v>12.94276687745029</v>
       </c>
       <c r="F424" t="n">
         <v>7048400</v>
@@ -8912,16 +8912,16 @@
         <v>45265</v>
       </c>
       <c r="B425" t="n">
-        <v>13.15919971466064</v>
+        <v>13.15920066833496</v>
       </c>
       <c r="C425" t="n">
-        <v>13.20248672149667</v>
+        <v>13.20248767830808</v>
       </c>
       <c r="D425" t="n">
-        <v>12.9254511987557</v>
+        <v>12.92545213548978</v>
       </c>
       <c r="E425" t="n">
-        <v>12.96008063909832</v>
+        <v>12.96008157834207</v>
       </c>
       <c r="F425" t="n">
         <v>6696500</v>
@@ -8972,16 +8972,16 @@
         <v>45268</v>
       </c>
       <c r="B428" t="n">
-        <v>12.92545223236084</v>
+        <v>12.92545127868652</v>
       </c>
       <c r="C428" t="n">
-        <v>13.15920076695787</v>
+        <v>13.15919979603697</v>
       </c>
       <c r="D428" t="n">
-        <v>12.86485008769187</v>
+        <v>12.86484913848894</v>
       </c>
       <c r="E428" t="n">
-        <v>13.15920076695787</v>
+        <v>13.15919979603697</v>
       </c>
       <c r="F428" t="n">
         <v>10990100</v>
@@ -9052,16 +9052,16 @@
         <v>45274</v>
       </c>
       <c r="B432" t="n">
-        <v>12.94470119476318</v>
+        <v>12.94470024108887</v>
       </c>
       <c r="C432" t="n">
-        <v>12.9831984112191</v>
+        <v>12.98319745470858</v>
       </c>
       <c r="D432" t="n">
-        <v>12.71371789602766</v>
+        <v>12.71371695937057</v>
       </c>
       <c r="E432" t="n">
-        <v>12.71371789602766</v>
+        <v>12.71371695937057</v>
       </c>
       <c r="F432" t="n">
         <v>5480800</v>
@@ -9092,16 +9092,16 @@
         <v>45278</v>
       </c>
       <c r="B434" t="n">
-        <v>12.8484582901001</v>
+        <v>12.84845733642578</v>
       </c>
       <c r="C434" t="n">
-        <v>13.08906611637279</v>
+        <v>13.0890651448394</v>
       </c>
       <c r="D434" t="n">
-        <v>12.8484582901001</v>
+        <v>12.84845733642578</v>
       </c>
       <c r="E434" t="n">
-        <v>12.98319808539135</v>
+        <v>12.983197121716</v>
       </c>
       <c r="F434" t="n">
         <v>3314300</v>
@@ -9112,16 +9112,16 @@
         <v>45279</v>
       </c>
       <c r="B435" t="n">
-        <v>12.86770534515381</v>
+        <v>12.86770629882812</v>
       </c>
       <c r="C435" t="n">
-        <v>12.94469976958878</v>
+        <v>12.94470072896945</v>
       </c>
       <c r="D435" t="n">
-        <v>12.79071092071883</v>
+        <v>12.7907118686868</v>
       </c>
       <c r="E435" t="n">
-        <v>12.87732987766966</v>
+        <v>12.87733083205729</v>
       </c>
       <c r="F435" t="n">
         <v>4780200</v>
@@ -9232,16 +9232,16 @@
         <v>45288</v>
       </c>
       <c r="B441" t="n">
-        <v>12.80996131896973</v>
+        <v>12.80996036529541</v>
       </c>
       <c r="C441" t="n">
-        <v>12.88695575141803</v>
+        <v>12.88695479201164</v>
       </c>
       <c r="D441" t="n">
-        <v>12.76183956922803</v>
+        <v>12.76183861913627</v>
       </c>
       <c r="E441" t="n">
-        <v>12.88695575141803</v>
+        <v>12.88695479201164</v>
       </c>
       <c r="F441" t="n">
         <v>3487000</v>
@@ -9332,16 +9332,16 @@
         <v>45299</v>
       </c>
       <c r="B446" t="n">
-        <v>13.01207160949707</v>
+        <v>13.01207065582275</v>
       </c>
       <c r="C446" t="n">
-        <v>13.09868965545936</v>
+        <v>13.09868869543668</v>
       </c>
       <c r="D446" t="n">
-        <v>12.88695543042352</v>
+        <v>12.88695448591916</v>
       </c>
       <c r="E446" t="n">
-        <v>12.9543253276762</v>
+        <v>12.95432437823419</v>
       </c>
       <c r="F446" t="n">
         <v>3738800</v>
@@ -9392,16 +9392,16 @@
         <v>45302</v>
       </c>
       <c r="B449" t="n">
-        <v>12.8484582901001</v>
+        <v>12.84845733642578</v>
       </c>
       <c r="C449" t="n">
-        <v>12.94470086990156</v>
+        <v>12.94469990908366</v>
       </c>
       <c r="D449" t="n">
-        <v>12.74259025911866</v>
+        <v>12.74258931330238</v>
       </c>
       <c r="E449" t="n">
-        <v>12.94470086990156</v>
+        <v>12.94469990908366</v>
       </c>
       <c r="F449" t="n">
         <v>4814200</v>
@@ -9412,16 +9412,16 @@
         <v>45303</v>
       </c>
       <c r="B450" t="n">
-        <v>12.77146339416504</v>
+        <v>12.77146434783936</v>
       </c>
       <c r="C450" t="n">
-        <v>12.88695503642984</v>
+        <v>12.88695599872818</v>
       </c>
       <c r="D450" t="n">
-        <v>12.74258979521435</v>
+        <v>12.74259074673261</v>
       </c>
       <c r="E450" t="n">
-        <v>12.84845782234157</v>
+        <v>12.84845878176524</v>
       </c>
       <c r="F450" t="n">
         <v>4041800</v>
@@ -9432,16 +9432,16 @@
         <v>45306</v>
       </c>
       <c r="B451" t="n">
-        <v>12.80996131896973</v>
+        <v>12.80996036529541</v>
       </c>
       <c r="C451" t="n">
-        <v>12.84845853519388</v>
+        <v>12.84845757865353</v>
       </c>
       <c r="D451" t="n">
-        <v>12.74259050219293</v>
+        <v>12.74258955353423</v>
       </c>
       <c r="E451" t="n">
-        <v>12.77146410274557</v>
+        <v>12.77146315193729</v>
       </c>
       <c r="F451" t="n">
         <v>1955800</v>
@@ -9492,16 +9492,16 @@
         <v>45309</v>
       </c>
       <c r="B454" t="n">
-        <v>12.55972862243652</v>
+        <v>12.55972766876221</v>
       </c>
       <c r="C454" t="n">
-        <v>12.77146376499286</v>
+        <v>12.77146279524125</v>
       </c>
       <c r="D454" t="n">
-        <v>12.51160687396745</v>
+        <v>12.51160592394707</v>
       </c>
       <c r="E454" t="n">
-        <v>12.76183923172984</v>
+        <v>12.76183826270904</v>
       </c>
       <c r="F454" t="n">
         <v>6534900</v>
@@ -9532,16 +9532,16 @@
         <v>45313</v>
       </c>
       <c r="B456" t="n">
-        <v>12.61747455596924</v>
+        <v>12.61747360229492</v>
       </c>
       <c r="C456" t="n">
-        <v>12.65597177291335</v>
+        <v>12.65597081632927</v>
       </c>
       <c r="D456" t="n">
-        <v>12.56935372317364</v>
+        <v>12.56935277313647</v>
       </c>
       <c r="E456" t="n">
-        <v>12.60785094011775</v>
+        <v>12.60784998717082</v>
       </c>
       <c r="F456" t="n">
         <v>4490300</v>
@@ -9572,16 +9572,16 @@
         <v>45315</v>
       </c>
       <c r="B458" t="n">
-        <v>12.79071140289307</v>
+        <v>12.79071235656738</v>
       </c>
       <c r="C458" t="n">
-        <v>12.82920861656179</v>
+        <v>12.82920957310646</v>
       </c>
       <c r="D458" t="n">
-        <v>12.64634708109684</v>
+        <v>12.64634802400737</v>
       </c>
       <c r="E458" t="n">
-        <v>12.65597069612954</v>
+        <v>12.6559716397576</v>
       </c>
       <c r="F458" t="n">
         <v>3333600</v>
@@ -9652,16 +9652,16 @@
         <v>45321</v>
       </c>
       <c r="B462" t="n">
-        <v>12.51160621643066</v>
+        <v>12.51160717010498</v>
       </c>
       <c r="C462" t="n">
-        <v>12.63672238873649</v>
+        <v>12.63672335194755</v>
       </c>
       <c r="D462" t="n">
-        <v>12.51160621643066</v>
+        <v>12.51160717010498</v>
       </c>
       <c r="E462" t="n">
-        <v>12.58860064279641</v>
+        <v>12.58860160233948</v>
       </c>
       <c r="F462" t="n">
         <v>3463200</v>
@@ -9672,16 +9672,16 @@
         <v>45322</v>
       </c>
       <c r="B463" t="n">
-        <v>12.68484497070312</v>
+        <v>12.68484401702881</v>
       </c>
       <c r="C463" t="n">
-        <v>12.79071208447197</v>
+        <v>12.79071112283833</v>
       </c>
       <c r="D463" t="n">
-        <v>12.53085610782262</v>
+        <v>12.53085516572552</v>
       </c>
       <c r="E463" t="n">
-        <v>12.57897693908826</v>
+        <v>12.57897599337333</v>
       </c>
       <c r="F463" t="n">
         <v>3755000</v>
@@ -9812,16 +9812,16 @@
         <v>45331</v>
       </c>
       <c r="B470" t="n">
-        <v>12.48273372650146</v>
+        <v>12.48273468017578</v>
       </c>
       <c r="C470" t="n">
-        <v>12.62709804867886</v>
+        <v>12.62709901338253</v>
       </c>
       <c r="D470" t="n">
-        <v>12.36724208519036</v>
+        <v>12.36724303004117</v>
       </c>
       <c r="E470" t="n">
-        <v>12.36724208519036</v>
+        <v>12.36724303004117</v>
       </c>
       <c r="F470" t="n">
         <v>4943200</v>
@@ -9852,16 +9852,16 @@
         <v>45337</v>
       </c>
       <c r="B472" t="n">
-        <v>12.50198173522949</v>
+        <v>12.50198268890381</v>
       </c>
       <c r="C472" t="n">
-        <v>12.58860069470964</v>
+        <v>12.58860165499141</v>
       </c>
       <c r="D472" t="n">
-        <v>12.41536277574934</v>
+        <v>12.4153637228162</v>
       </c>
       <c r="E472" t="n">
-        <v>12.46348452188787</v>
+        <v>12.46348547262554</v>
       </c>
       <c r="F472" t="n">
         <v>4740900</v>
@@ -9892,16 +9892,16 @@
         <v>45341</v>
       </c>
       <c r="B474" t="n">
-        <v>12.77146339416504</v>
+        <v>12.77146434783936</v>
       </c>
       <c r="C474" t="n">
-        <v>12.85808143747915</v>
+        <v>12.85808239762144</v>
       </c>
       <c r="D474" t="n">
-        <v>12.53085557665187</v>
+        <v>12.53085651235945</v>
       </c>
       <c r="E474" t="n">
-        <v>12.54047919178945</v>
+        <v>12.54048012821565</v>
       </c>
       <c r="F474" t="n">
         <v>4786000</v>
@@ -9972,16 +9972,16 @@
         <v>45345</v>
       </c>
       <c r="B478" t="n">
-        <v>12.41536235809326</v>
+        <v>12.41536331176758</v>
       </c>
       <c r="C478" t="n">
-        <v>12.55010305917923</v>
+        <v>12.55010402320352</v>
       </c>
       <c r="D478" t="n">
-        <v>12.41536235809326</v>
+        <v>12.41536331176758</v>
       </c>
       <c r="E478" t="n">
-        <v>12.52123037960578</v>
+        <v>12.52123134141225</v>
       </c>
       <c r="F478" t="n">
         <v>4574300</v>
@@ -9992,16 +9992,16 @@
         <v>45348</v>
       </c>
       <c r="B479" t="n">
-        <v>12.35761833190918</v>
+        <v>12.35761737823486</v>
       </c>
       <c r="C479" t="n">
-        <v>12.48273451401776</v>
+        <v>12.48273355068785</v>
       </c>
       <c r="D479" t="n">
-        <v>12.33836926488661</v>
+        <v>12.3383683126978</v>
       </c>
       <c r="E479" t="n">
-        <v>12.45386091348391</v>
+        <v>12.45385995238227</v>
       </c>
       <c r="F479" t="n">
         <v>6964500</v>

--- a/database/AURE3.xlsx
+++ b/database/AURE3.xlsx
@@ -472,16 +472,16 @@
         <v>44649</v>
       </c>
       <c r="B3" t="n">
-        <v>12.91280937194824</v>
+        <v>12.91281032562256</v>
       </c>
       <c r="C3" t="n">
-        <v>13.2161821224289</v>
+        <v>13.21618309850878</v>
       </c>
       <c r="D3" t="n">
-        <v>12.61721411646944</v>
+        <v>12.6172150483126</v>
       </c>
       <c r="E3" t="n">
-        <v>12.74945378682817</v>
+        <v>12.74945472843788</v>
       </c>
       <c r="F3" t="n">
         <v>4714100</v>
@@ -492,16 +492,16 @@
         <v>44650</v>
       </c>
       <c r="B4" t="n">
-        <v>12.38385009765625</v>
+        <v>12.38385105133057</v>
       </c>
       <c r="C4" t="n">
-        <v>13.04504841779609</v>
+        <v>13.04504942238897</v>
       </c>
       <c r="D4" t="n">
-        <v>12.30606179816537</v>
+        <v>12.30606274584925</v>
       </c>
       <c r="E4" t="n">
-        <v>12.92836671040398</v>
+        <v>12.92836770601126</v>
       </c>
       <c r="F4" t="n">
         <v>4408600</v>
@@ -552,16 +552,16 @@
         <v>44655</v>
       </c>
       <c r="B7" t="n">
-        <v>12.42274475097656</v>
+        <v>12.42274379730225</v>
       </c>
       <c r="C7" t="n">
-        <v>12.7338972197089</v>
+        <v>12.73389624214791</v>
       </c>
       <c r="D7" t="n">
-        <v>12.33717746969916</v>
+        <v>12.3371765225937</v>
       </c>
       <c r="E7" t="n">
-        <v>12.54720469988757</v>
+        <v>12.54720373665866</v>
       </c>
       <c r="F7" t="n">
         <v>2842400</v>
@@ -592,16 +592,16 @@
         <v>44657</v>
       </c>
       <c r="B9" t="n">
-        <v>12.43052291870117</v>
+        <v>12.43052387237549</v>
       </c>
       <c r="C9" t="n">
-        <v>12.44608087588125</v>
+        <v>12.44608183074918</v>
       </c>
       <c r="D9" t="n">
-        <v>12.01824669740399</v>
+        <v>12.01824761944832</v>
       </c>
       <c r="E9" t="n">
-        <v>12.06491982710001</v>
+        <v>12.06492075272512</v>
       </c>
       <c r="F9" t="n">
         <v>2914800</v>
@@ -612,16 +612,16 @@
         <v>44658</v>
       </c>
       <c r="B10" t="n">
-        <v>12.44608116149902</v>
+        <v>12.44608020782471</v>
       </c>
       <c r="C10" t="n">
-        <v>12.71833948364451</v>
+        <v>12.71833850910855</v>
       </c>
       <c r="D10" t="n">
-        <v>12.20493801258351</v>
+        <v>12.20493707738666</v>
       </c>
       <c r="E10" t="n">
-        <v>12.32162046857911</v>
+        <v>12.32161952444153</v>
       </c>
       <c r="F10" t="n">
         <v>3223900</v>
@@ -632,16 +632,16 @@
         <v>44659</v>
       </c>
       <c r="B11" t="n">
-        <v>12.60943603515625</v>
+        <v>12.60943508148193</v>
       </c>
       <c r="C11" t="n">
-        <v>12.75723367341398</v>
+        <v>12.75723270856147</v>
       </c>
       <c r="D11" t="n">
-        <v>12.3371784382169</v>
+        <v>12.33717750513392</v>
       </c>
       <c r="E11" t="n">
-        <v>12.3371784382169</v>
+        <v>12.33717750513392</v>
       </c>
       <c r="F11" t="n">
         <v>2049800</v>
@@ -652,16 +652,16 @@
         <v>44662</v>
       </c>
       <c r="B12" t="n">
-        <v>12.37607192993164</v>
+        <v>12.37607097625732</v>
       </c>
       <c r="C12" t="n">
-        <v>12.8972516418612</v>
+        <v>12.89725064802586</v>
       </c>
       <c r="D12" t="n">
-        <v>12.37607192993164</v>
+        <v>12.37607097625732</v>
       </c>
       <c r="E12" t="n">
-        <v>12.59387888603408</v>
+        <v>12.59387791557601</v>
       </c>
       <c r="F12" t="n">
         <v>2119500</v>
@@ -672,16 +672,16 @@
         <v>44663</v>
       </c>
       <c r="B13" t="n">
-        <v>12.24383163452148</v>
+        <v>12.2438325881958</v>
       </c>
       <c r="C13" t="n">
-        <v>12.64055063241211</v>
+        <v>12.64055161698694</v>
       </c>
       <c r="D13" t="n">
-        <v>12.21271646263855</v>
+        <v>12.2127174138893</v>
       </c>
       <c r="E13" t="n">
-        <v>12.4849740311532</v>
+        <v>12.48497500361014</v>
       </c>
       <c r="F13" t="n">
         <v>2267700</v>
@@ -692,16 +692,16 @@
         <v>44664</v>
       </c>
       <c r="B14" t="n">
-        <v>12.10381317138672</v>
+        <v>12.10381412506104</v>
       </c>
       <c r="C14" t="n">
-        <v>12.55498277187146</v>
+        <v>12.55498376109398</v>
       </c>
       <c r="D14" t="n">
-        <v>12.0882552152437</v>
+        <v>12.08825616769219</v>
       </c>
       <c r="E14" t="n">
-        <v>12.39162868343488</v>
+        <v>12.39162965978653</v>
       </c>
       <c r="F14" t="n">
         <v>4421300</v>
@@ -712,16 +712,16 @@
         <v>44665</v>
       </c>
       <c r="B15" t="n">
-        <v>12.11159324645996</v>
+        <v>12.11159133911133</v>
       </c>
       <c r="C15" t="n">
-        <v>12.36829362703988</v>
+        <v>12.36829167926575</v>
       </c>
       <c r="D15" t="n">
-        <v>12.04936289612812</v>
+        <v>12.0493609985796</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08047807129404</v>
+        <v>12.08047616884546</v>
       </c>
       <c r="F15" t="n">
         <v>2077400</v>
@@ -732,16 +732,16 @@
         <v>44669</v>
       </c>
       <c r="B16" t="n">
-        <v>12.45385932922363</v>
+        <v>12.45386028289795</v>
       </c>
       <c r="C16" t="n">
-        <v>12.45385932922363</v>
+        <v>12.45386028289795</v>
       </c>
       <c r="D16" t="n">
-        <v>11.92490067691762</v>
+        <v>11.92490159008608</v>
       </c>
       <c r="E16" t="n">
-        <v>12.10381346772168</v>
+        <v>12.10381439459067</v>
       </c>
       <c r="F16" t="n">
         <v>3931100</v>
@@ -752,16 +752,16 @@
         <v>44670</v>
       </c>
       <c r="B17" t="n">
-        <v>12.10381317138672</v>
+        <v>12.10381412506104</v>
       </c>
       <c r="C17" t="n">
-        <v>12.60165664030051</v>
+        <v>12.60165763320052</v>
       </c>
       <c r="D17" t="n">
-        <v>12.00268868198966</v>
+        <v>12.00268962769625</v>
       </c>
       <c r="E17" t="n">
-        <v>12.43830106817557</v>
+        <v>12.4383020482046</v>
       </c>
       <c r="F17" t="n">
         <v>3118100</v>
@@ -772,16 +772,16 @@
         <v>44671</v>
       </c>
       <c r="B18" t="n">
-        <v>12.0571403503418</v>
+        <v>12.05714130401611</v>
       </c>
       <c r="C18" t="n">
-        <v>12.2127162064935</v>
+        <v>12.21271717247328</v>
       </c>
       <c r="D18" t="n">
-        <v>11.95601585838214</v>
+        <v>11.95601680405789</v>
       </c>
       <c r="E18" t="n">
-        <v>12.07269830687907</v>
+        <v>12.07269926178396</v>
       </c>
       <c r="F18" t="n">
         <v>2798400</v>
@@ -792,16 +792,16 @@
         <v>44673</v>
       </c>
       <c r="B19" t="n">
-        <v>12.22049617767334</v>
+        <v>12.22049713134766</v>
       </c>
       <c r="C19" t="n">
-        <v>12.33717789380641</v>
+        <v>12.33717885658645</v>
       </c>
       <c r="D19" t="n">
-        <v>11.80044096101231</v>
+        <v>11.80044188190597</v>
       </c>
       <c r="E19" t="n">
-        <v>12.01824717732137</v>
+        <v>12.01824811521239</v>
       </c>
       <c r="F19" t="n">
         <v>11382300</v>
@@ -852,16 +852,16 @@
         <v>44678</v>
       </c>
       <c r="B22" t="n">
-        <v>12.0571403503418</v>
+        <v>12.05714130401611</v>
       </c>
       <c r="C22" t="n">
-        <v>12.06491932861043</v>
+        <v>12.06492028290003</v>
       </c>
       <c r="D22" t="n">
-        <v>11.83155517346078</v>
+        <v>11.83155610929216</v>
       </c>
       <c r="E22" t="n">
-        <v>12.04936137207316</v>
+        <v>12.04936232513219</v>
       </c>
       <c r="F22" t="n">
         <v>2401400</v>
@@ -872,16 +872,16 @@
         <v>44679</v>
       </c>
       <c r="B23" t="n">
-        <v>11.90934467315674</v>
+        <v>11.90934371948242</v>
       </c>
       <c r="C23" t="n">
-        <v>12.08825674030803</v>
+        <v>12.08825577230682</v>
       </c>
       <c r="D23" t="n">
-        <v>11.49706768548379</v>
+        <v>11.49706676482372</v>
       </c>
       <c r="E23" t="n">
-        <v>12.08825674030803</v>
+        <v>12.08825577230682</v>
       </c>
       <c r="F23" t="n">
         <v>3489600</v>
@@ -912,16 +912,16 @@
         <v>44683</v>
       </c>
       <c r="B25" t="n">
-        <v>11.1703577041626</v>
+        <v>11.17035675048828</v>
       </c>
       <c r="C25" t="n">
-        <v>11.47373120303561</v>
+        <v>11.47373022346064</v>
       </c>
       <c r="D25" t="n">
-        <v>10.96033046789994</v>
+        <v>10.96032953215679</v>
       </c>
       <c r="E25" t="n">
-        <v>11.42705807173043</v>
+        <v>11.4270570961402</v>
       </c>
       <c r="F25" t="n">
         <v>2883200</v>
@@ -932,16 +932,16 @@
         <v>44684</v>
       </c>
       <c r="B26" t="n">
-        <v>11.27148246765137</v>
+        <v>11.27148151397705</v>
       </c>
       <c r="C26" t="n">
-        <v>11.3570497534066</v>
+        <v>11.35704879249248</v>
       </c>
       <c r="D26" t="n">
-        <v>11.0147820940742</v>
+        <v>11.01478116211917</v>
       </c>
       <c r="E26" t="n">
-        <v>11.1548007494233</v>
+        <v>11.15479980562136</v>
       </c>
       <c r="F26" t="n">
         <v>1672900</v>
@@ -972,16 +972,16 @@
         <v>44686</v>
       </c>
       <c r="B28" t="n">
-        <v>11.28714847564697</v>
+        <v>11.28714656829834</v>
       </c>
       <c r="C28" t="n">
-        <v>11.62396161516718</v>
+        <v>11.62395965090248</v>
       </c>
       <c r="D28" t="n">
-        <v>11.14615678989441</v>
+        <v>11.14615490637113</v>
       </c>
       <c r="E28" t="n">
-        <v>11.61612857773658</v>
+        <v>11.61612661479554</v>
       </c>
       <c r="F28" t="n">
         <v>3065700</v>
@@ -1052,16 +1052,16 @@
         <v>44692</v>
       </c>
       <c r="B32" t="n">
-        <v>11.06782817840576</v>
+        <v>11.06782722473145</v>
       </c>
       <c r="C32" t="n">
-        <v>11.38897522918973</v>
+        <v>11.38897424784334</v>
       </c>
       <c r="D32" t="n">
-        <v>11.01299841275958</v>
+        <v>11.01299746380974</v>
       </c>
       <c r="E32" t="n">
-        <v>11.12265794405194</v>
+        <v>11.12265698565314</v>
       </c>
       <c r="F32" t="n">
         <v>1595100</v>
@@ -1072,16 +1072,16 @@
         <v>44693</v>
       </c>
       <c r="B33" t="n">
-        <v>11.1539888381958</v>
+        <v>11.15398788452148</v>
       </c>
       <c r="C33" t="n">
-        <v>11.27931443797336</v>
+        <v>11.27931347358361</v>
       </c>
       <c r="D33" t="n">
-        <v>10.85634016522435</v>
+        <v>10.85633923699921</v>
       </c>
       <c r="E33" t="n">
-        <v>10.99733183847385</v>
+        <v>10.99733089819382</v>
       </c>
       <c r="F33" t="n">
         <v>1884700</v>
@@ -1092,16 +1092,16 @@
         <v>44694</v>
       </c>
       <c r="B34" t="n">
-        <v>11.32631206512451</v>
+        <v>11.32631301879883</v>
       </c>
       <c r="C34" t="n">
-        <v>11.38114182902154</v>
+        <v>11.38114278731251</v>
       </c>
       <c r="D34" t="n">
-        <v>11.11482455237968</v>
+        <v>11.11482548824677</v>
       </c>
       <c r="E34" t="n">
-        <v>11.18532038996129</v>
+        <v>11.18532133176413</v>
       </c>
       <c r="F34" t="n">
         <v>1333500</v>
@@ -1132,16 +1132,16 @@
         <v>44698</v>
       </c>
       <c r="B36" t="n">
-        <v>11.56129741668701</v>
+        <v>11.56129837036133</v>
       </c>
       <c r="C36" t="n">
-        <v>11.74928581037311</v>
+        <v>11.74928677955431</v>
       </c>
       <c r="D36" t="n">
-        <v>11.35764295002734</v>
+        <v>11.3576438869025</v>
       </c>
       <c r="E36" t="n">
-        <v>11.35764295002734</v>
+        <v>11.3576438869025</v>
       </c>
       <c r="F36" t="n">
         <v>1389700</v>
@@ -1172,16 +1172,16 @@
         <v>44700</v>
       </c>
       <c r="B38" t="n">
-        <v>11.22448444366455</v>
+        <v>11.22448539733887</v>
       </c>
       <c r="C38" t="n">
-        <v>11.25581584296371</v>
+        <v>11.25581679930005</v>
       </c>
       <c r="D38" t="n">
-        <v>10.97383324927132</v>
+        <v>10.97383418164937</v>
       </c>
       <c r="E38" t="n">
-        <v>11.11482417261777</v>
+        <v>11.11482511697494</v>
       </c>
       <c r="F38" t="n">
         <v>2127500</v>
@@ -1212,16 +1212,16 @@
         <v>44704</v>
       </c>
       <c r="B40" t="n">
-        <v>11.20881938934326</v>
+        <v>11.20882034301758</v>
       </c>
       <c r="C40" t="n">
-        <v>11.43597222652075</v>
+        <v>11.4359731995218</v>
       </c>
       <c r="D40" t="n">
-        <v>11.16182191575504</v>
+        <v>11.16182286543069</v>
       </c>
       <c r="E40" t="n">
-        <v>11.1853202790494</v>
+        <v>11.18532123072435</v>
       </c>
       <c r="F40" t="n">
         <v>1184600</v>
@@ -1232,16 +1232,16 @@
         <v>44705</v>
       </c>
       <c r="B41" t="n">
-        <v>11.21665096282959</v>
+        <v>11.21665191650391</v>
       </c>
       <c r="C41" t="n">
-        <v>11.22448399909401</v>
+        <v>11.22448495343431</v>
       </c>
       <c r="D41" t="n">
-        <v>11.00516421268657</v>
+        <v>11.00516514837963</v>
       </c>
       <c r="E41" t="n">
-        <v>11.09132537059677</v>
+        <v>11.09132631361552</v>
       </c>
       <c r="F41" t="n">
         <v>792900</v>
@@ -1252,16 +1252,16 @@
         <v>44706</v>
       </c>
       <c r="B42" t="n">
-        <v>11.32631206512451</v>
+        <v>11.32631301879883</v>
       </c>
       <c r="C42" t="n">
-        <v>11.39680790270612</v>
+        <v>11.39680886231618</v>
       </c>
       <c r="D42" t="n">
-        <v>11.13832366290656</v>
+        <v>11.13832460075227</v>
       </c>
       <c r="E42" t="n">
-        <v>11.17748810011851</v>
+        <v>11.17748904126186</v>
       </c>
       <c r="F42" t="n">
         <v>821700</v>
@@ -1272,16 +1272,16 @@
         <v>44707</v>
       </c>
       <c r="B43" t="n">
-        <v>11.25581741333008</v>
+        <v>11.25581645965576</v>
       </c>
       <c r="C43" t="n">
-        <v>11.44380583535239</v>
+        <v>11.44380486575034</v>
       </c>
       <c r="D43" t="n">
-        <v>11.20882068132429</v>
+        <v>11.20881973163188</v>
       </c>
       <c r="E43" t="n">
-        <v>11.33414629600583</v>
+        <v>11.33414533569493</v>
       </c>
       <c r="F43" t="n">
         <v>1248800</v>
@@ -1312,16 +1312,16 @@
         <v>44711</v>
       </c>
       <c r="B45" t="n">
-        <v>11.09915924072266</v>
+        <v>11.09916019439697</v>
       </c>
       <c r="C45" t="n">
-        <v>11.27148231648886</v>
+        <v>11.27148328496971</v>
       </c>
       <c r="D45" t="n">
-        <v>11.0286634030456</v>
+        <v>11.02866435066269</v>
       </c>
       <c r="E45" t="n">
-        <v>11.15398900469392</v>
+        <v>11.15398996307938</v>
       </c>
       <c r="F45" t="n">
         <v>1940200</v>
@@ -1332,16 +1332,16 @@
         <v>44712</v>
       </c>
       <c r="B46" t="n">
-        <v>10.93466949462891</v>
+        <v>10.93466854095459</v>
       </c>
       <c r="C46" t="n">
-        <v>11.20881981582572</v>
+        <v>11.2088188382412</v>
       </c>
       <c r="D46" t="n">
-        <v>10.82500921675028</v>
+        <v>10.82500827264005</v>
       </c>
       <c r="E46" t="n">
-        <v>11.16965537751195</v>
+        <v>11.16965440334319</v>
       </c>
       <c r="F46" t="n">
         <v>9431500</v>
@@ -1352,16 +1352,16 @@
         <v>44713</v>
       </c>
       <c r="B47" t="n">
-        <v>10.73101425170898</v>
+        <v>10.7310152053833</v>
       </c>
       <c r="C47" t="n">
-        <v>10.94250175540008</v>
+        <v>10.94250272786947</v>
       </c>
       <c r="D47" t="n">
-        <v>10.66051841714529</v>
+        <v>10.66051936455458</v>
       </c>
       <c r="E47" t="n">
-        <v>10.94250175540008</v>
+        <v>10.94250272786947</v>
       </c>
       <c r="F47" t="n">
         <v>6323900</v>
@@ -1472,16 +1472,16 @@
         <v>44721</v>
       </c>
       <c r="B53" t="n">
-        <v>11.03649616241455</v>
+        <v>11.03649711608887</v>
       </c>
       <c r="C53" t="n">
-        <v>11.09915896166322</v>
+        <v>11.09915992075229</v>
       </c>
       <c r="D53" t="n">
-        <v>10.86417309098097</v>
+        <v>10.86417402976468</v>
       </c>
       <c r="E53" t="n">
-        <v>11.06782756203888</v>
+        <v>11.06782851842058</v>
       </c>
       <c r="F53" t="n">
         <v>1365200</v>
@@ -1672,16 +1672,16 @@
         <v>44736</v>
       </c>
       <c r="B63" t="n">
-        <v>10.48819637298584</v>
+        <v>10.48819732666016</v>
       </c>
       <c r="C63" t="n">
-        <v>10.70751617197673</v>
+        <v>10.70751714559343</v>
       </c>
       <c r="D63" t="n">
-        <v>10.42553357327416</v>
+        <v>10.42553452125065</v>
       </c>
       <c r="E63" t="n">
-        <v>10.70751617197673</v>
+        <v>10.70751714559343</v>
       </c>
       <c r="F63" t="n">
         <v>807500</v>
@@ -1752,16 +1752,16 @@
         <v>44742</v>
       </c>
       <c r="B67" t="n">
-        <v>10.6683521270752</v>
+        <v>10.66835117340088</v>
       </c>
       <c r="C67" t="n">
-        <v>10.84850824310999</v>
+        <v>10.84850727333101</v>
       </c>
       <c r="D67" t="n">
-        <v>10.48819675803992</v>
+        <v>10.48819582047021</v>
       </c>
       <c r="E67" t="n">
-        <v>10.53519348604933</v>
+        <v>10.53519254427845</v>
       </c>
       <c r="F67" t="n">
         <v>2634600</v>
@@ -1812,16 +1812,16 @@
         <v>44747</v>
       </c>
       <c r="B70" t="n">
-        <v>10.6213550567627</v>
+        <v>10.62135601043701</v>
       </c>
       <c r="C70" t="n">
-        <v>10.6213550567627</v>
+        <v>10.62135601043701</v>
       </c>
       <c r="D70" t="n">
-        <v>10.49602870977771</v>
+        <v>10.49602965219918</v>
       </c>
       <c r="E70" t="n">
-        <v>10.58219062001736</v>
+        <v>10.58219157017516</v>
       </c>
       <c r="F70" t="n">
         <v>1722600</v>
@@ -1852,16 +1852,16 @@
         <v>44749</v>
       </c>
       <c r="B72" t="n">
-        <v>11.04432964324951</v>
+        <v>11.0443286895752</v>
       </c>
       <c r="C72" t="n">
-        <v>11.16182220981619</v>
+        <v>11.16182124599643</v>
       </c>
       <c r="D72" t="n">
-        <v>10.62135535781014</v>
+        <v>10.62135444065952</v>
       </c>
       <c r="E72" t="n">
-        <v>10.7858453992032</v>
+        <v>10.78584446784892</v>
       </c>
       <c r="F72" t="n">
         <v>2931100</v>
@@ -1872,16 +1872,16 @@
         <v>44750</v>
       </c>
       <c r="B73" t="n">
-        <v>11.1539888381958</v>
+        <v>11.15398788452148</v>
       </c>
       <c r="C73" t="n">
-        <v>11.31064583791775</v>
+        <v>11.31064487084914</v>
       </c>
       <c r="D73" t="n">
-        <v>11.00516487520982</v>
+        <v>11.00516393426007</v>
       </c>
       <c r="E73" t="n">
-        <v>11.00516487520982</v>
+        <v>11.00516393426007</v>
       </c>
       <c r="F73" t="n">
         <v>1922000</v>
@@ -1912,16 +1912,16 @@
         <v>44754</v>
       </c>
       <c r="B75" t="n">
-        <v>11.14615535736084</v>
+        <v>11.14615631103516</v>
       </c>
       <c r="C75" t="n">
-        <v>11.22448422760069</v>
+        <v>11.22448518797689</v>
       </c>
       <c r="D75" t="n">
-        <v>10.99733140030449</v>
+        <v>10.99733234124531</v>
       </c>
       <c r="E75" t="n">
-        <v>11.10699166924038</v>
+        <v>11.10699261956382</v>
       </c>
       <c r="F75" t="n">
         <v>1673000</v>
@@ -1952,16 +1952,16 @@
         <v>44756</v>
       </c>
       <c r="B77" t="n">
-        <v>10.91117095947266</v>
+        <v>10.91117000579834</v>
       </c>
       <c r="C77" t="n">
-        <v>11.17748823943387</v>
+        <v>11.1774872624825</v>
       </c>
       <c r="D77" t="n">
-        <v>10.84850815795232</v>
+        <v>10.84850720975495</v>
       </c>
       <c r="E77" t="n">
-        <v>11.04432959945326</v>
+        <v>11.04432863414042</v>
       </c>
       <c r="F77" t="n">
         <v>1968500</v>
@@ -1972,16 +1972,16 @@
         <v>44757</v>
       </c>
       <c r="B78" t="n">
-        <v>10.8093433380127</v>
+        <v>10.80934429168701</v>
       </c>
       <c r="C78" t="n">
-        <v>10.98166640959971</v>
+        <v>10.98166737847755</v>
       </c>
       <c r="D78" t="n">
-        <v>10.60568886677345</v>
+        <v>10.60568980247997</v>
       </c>
       <c r="E78" t="n">
-        <v>10.97383337293678</v>
+        <v>10.97383434112354</v>
       </c>
       <c r="F78" t="n">
         <v>2342600</v>
@@ -1992,16 +1992,16 @@
         <v>44760</v>
       </c>
       <c r="B79" t="n">
-        <v>10.73101425170898</v>
+        <v>10.7310152053833</v>
       </c>
       <c r="C79" t="n">
-        <v>11.00516455345681</v>
+        <v>11.0051655314951</v>
       </c>
       <c r="D79" t="n">
-        <v>10.59002332958107</v>
+        <v>10.5900242707254</v>
       </c>
       <c r="E79" t="n">
-        <v>10.80934312277964</v>
+        <v>10.80934408341511</v>
       </c>
       <c r="F79" t="n">
         <v>1463400</v>
@@ -2012,16 +2012,16 @@
         <v>44761</v>
       </c>
       <c r="B80" t="n">
-        <v>11.09132671356201</v>
+        <v>11.0913257598877</v>
       </c>
       <c r="C80" t="n">
-        <v>11.09132671356201</v>
+        <v>11.0913257598877</v>
       </c>
       <c r="D80" t="n">
-        <v>10.78584573225599</v>
+        <v>10.78584480484809</v>
       </c>
       <c r="E80" t="n">
-        <v>10.87200690059879</v>
+        <v>10.87200596578243</v>
       </c>
       <c r="F80" t="n">
         <v>2890800</v>
@@ -2052,16 +2052,16 @@
         <v>44763</v>
       </c>
       <c r="B82" t="n">
-        <v>11.24798393249512</v>
+        <v>11.2479829788208</v>
       </c>
       <c r="C82" t="n">
-        <v>11.27931533493105</v>
+        <v>11.27931437860027</v>
       </c>
       <c r="D82" t="n">
-        <v>11.0599955178795</v>
+        <v>11.05999458014401</v>
       </c>
       <c r="E82" t="n">
-        <v>11.22448556741805</v>
+        <v>11.22448461573608</v>
       </c>
       <c r="F82" t="n">
         <v>1092700</v>
@@ -2072,16 +2072,16 @@
         <v>44764</v>
       </c>
       <c r="B83" t="n">
-        <v>11.36547660827637</v>
+        <v>11.36547756195068</v>
       </c>
       <c r="C83" t="n">
-        <v>11.37330964519167</v>
+        <v>11.37331059952326</v>
       </c>
       <c r="D83" t="n">
-        <v>11.13049072981382</v>
+        <v>11.13049166377053</v>
       </c>
       <c r="E83" t="n">
-        <v>11.27148240629125</v>
+        <v>11.27148335207854</v>
       </c>
       <c r="F83" t="n">
         <v>1975500</v>
@@ -2092,16 +2092,16 @@
         <v>44767</v>
       </c>
       <c r="B84" t="n">
-        <v>11.23231792449951</v>
+        <v>11.23231887817383</v>
       </c>
       <c r="C84" t="n">
-        <v>11.45163772826812</v>
+        <v>11.45163870056368</v>
       </c>
       <c r="D84" t="n">
-        <v>11.16965512342277</v>
+        <v>11.16965607177673</v>
       </c>
       <c r="E84" t="n">
-        <v>11.42030632772975</v>
+        <v>11.42030729736513</v>
       </c>
       <c r="F84" t="n">
         <v>1962700</v>
@@ -2112,16 +2112,16 @@
         <v>44768</v>
       </c>
       <c r="B85" t="n">
-        <v>11.27148342132568</v>
+        <v>11.27148246765137</v>
       </c>
       <c r="C85" t="n">
-        <v>11.3811429600171</v>
+        <v>11.38114199706455</v>
       </c>
       <c r="D85" t="n">
-        <v>11.16965617325538</v>
+        <v>11.16965522819662</v>
       </c>
       <c r="E85" t="n">
-        <v>11.19315453911789</v>
+        <v>11.19315359207094</v>
       </c>
       <c r="F85" t="n">
         <v>1661400</v>
@@ -2232,16 +2232,16 @@
         <v>44776</v>
       </c>
       <c r="B91" t="n">
-        <v>10.88767242431641</v>
+        <v>10.88767147064209</v>
       </c>
       <c r="C91" t="n">
-        <v>11.02083107133751</v>
+        <v>11.02083010599954</v>
       </c>
       <c r="D91" t="n">
-        <v>10.70751704716995</v>
+        <v>10.70751610927583</v>
       </c>
       <c r="E91" t="n">
-        <v>10.83284265683698</v>
+        <v>10.83284170796531</v>
       </c>
       <c r="F91" t="n">
         <v>3133200</v>
@@ -2252,16 +2252,16 @@
         <v>44777</v>
       </c>
       <c r="B92" t="n">
-        <v>11.06782817840576</v>
+        <v>11.06782722473145</v>
       </c>
       <c r="C92" t="n">
-        <v>11.25581658662083</v>
+        <v>11.25581561674824</v>
       </c>
       <c r="D92" t="n">
-        <v>10.89550509737551</v>
+        <v>10.89550415854965</v>
       </c>
       <c r="E92" t="n">
-        <v>10.93466953583687</v>
+        <v>10.93466859363635</v>
       </c>
       <c r="F92" t="n">
         <v>5742400</v>
@@ -2292,16 +2292,16 @@
         <v>44781</v>
       </c>
       <c r="B94" t="n">
-        <v>10.97383308410645</v>
+        <v>10.97383403778076</v>
       </c>
       <c r="C94" t="n">
-        <v>11.10699171587358</v>
+        <v>11.10699268111997</v>
       </c>
       <c r="D94" t="n">
-        <v>10.8720058511669</v>
+        <v>10.87200679599199</v>
       </c>
       <c r="E94" t="n">
-        <v>11.02866284530486</v>
+        <v>11.02866380374413</v>
       </c>
       <c r="F94" t="n">
         <v>2949000</v>
@@ -2312,16 +2312,16 @@
         <v>44782</v>
       </c>
       <c r="B95" t="n">
-        <v>10.92683601379395</v>
+        <v>10.92683696746826</v>
       </c>
       <c r="C95" t="n">
-        <v>11.05999465045304</v>
+        <v>11.0599956157492</v>
       </c>
       <c r="D95" t="n">
-        <v>10.67618481396482</v>
+        <v>10.67618574576276</v>
       </c>
       <c r="E95" t="n">
-        <v>10.98166652400619</v>
+        <v>10.98166748246601</v>
       </c>
       <c r="F95" t="n">
         <v>1743500</v>
@@ -2352,16 +2352,16 @@
         <v>44784</v>
       </c>
       <c r="B97" t="n">
-        <v>10.89550590515137</v>
+        <v>10.89550495147705</v>
       </c>
       <c r="C97" t="n">
-        <v>11.10699344032233</v>
+        <v>11.10699246813669</v>
       </c>
       <c r="D97" t="n">
-        <v>10.83284309776729</v>
+        <v>10.83284214957779</v>
       </c>
       <c r="E97" t="n">
-        <v>11.05999596128448</v>
+        <v>11.05999499321249</v>
       </c>
       <c r="F97" t="n">
         <v>1665400</v>
@@ -2392,16 +2392,16 @@
         <v>44788</v>
       </c>
       <c r="B99" t="n">
-        <v>11.21665096282959</v>
+        <v>11.21665191650391</v>
       </c>
       <c r="C99" t="n">
-        <v>11.3106451570042</v>
+        <v>11.3106461186702</v>
       </c>
       <c r="D99" t="n">
-        <v>10.92683534404133</v>
+        <v>10.92683627307463</v>
       </c>
       <c r="E99" t="n">
-        <v>10.99733117642216</v>
+        <v>10.99733211144923</v>
       </c>
       <c r="F99" t="n">
         <v>3450900</v>
@@ -2412,16 +2412,16 @@
         <v>44789</v>
       </c>
       <c r="B100" t="n">
-        <v>11.04432964324951</v>
+        <v>11.0443286895752</v>
       </c>
       <c r="C100" t="n">
-        <v>11.29498085032484</v>
+        <v>11.29497987500687</v>
       </c>
       <c r="D100" t="n">
-        <v>10.94250240362528</v>
+        <v>10.94250145874372</v>
       </c>
       <c r="E100" t="n">
-        <v>11.25581641246944</v>
+        <v>11.25581544053331</v>
       </c>
       <c r="F100" t="n">
         <v>1185300</v>
@@ -2512,16 +2512,16 @@
         <v>44796</v>
       </c>
       <c r="B105" t="n">
-        <v>11.22448444366455</v>
+        <v>11.22448539733887</v>
       </c>
       <c r="C105" t="n">
-        <v>11.27148191611302</v>
+        <v>11.27148287378042</v>
       </c>
       <c r="D105" t="n">
-        <v>10.98949857542116</v>
+        <v>10.98949950913019</v>
       </c>
       <c r="E105" t="n">
-        <v>10.98949857542116</v>
+        <v>10.98949950913019</v>
       </c>
       <c r="F105" t="n">
         <v>2361000</v>
@@ -2552,16 +2552,16 @@
         <v>44798</v>
       </c>
       <c r="B107" t="n">
-        <v>11.04432964324951</v>
+        <v>11.0443286895752</v>
       </c>
       <c r="C107" t="n">
-        <v>11.22448501158502</v>
+        <v>11.22448404235435</v>
       </c>
       <c r="D107" t="n">
-        <v>10.95033469359675</v>
+        <v>10.95033374803886</v>
       </c>
       <c r="E107" t="n">
-        <v>11.20881968464257</v>
+        <v>11.2088187167646</v>
       </c>
       <c r="F107" t="n">
         <v>2435800</v>
@@ -2652,16 +2652,16 @@
         <v>44805</v>
       </c>
       <c r="B112" t="n">
-        <v>11.65529346466064</v>
+        <v>11.65529251098633</v>
       </c>
       <c r="C112" t="n">
-        <v>12.1565966744416</v>
+        <v>12.15659567974902</v>
       </c>
       <c r="D112" t="n">
-        <v>11.42030756173208</v>
+        <v>11.42030662728508</v>
       </c>
       <c r="E112" t="n">
-        <v>12.14093059897989</v>
+        <v>12.14092960556915</v>
       </c>
       <c r="F112" t="n">
         <v>4716400</v>
@@ -2672,16 +2672,16 @@
         <v>44806</v>
       </c>
       <c r="B113" t="n">
-        <v>11.74145317077637</v>
+        <v>11.74145412445068</v>
       </c>
       <c r="C113" t="n">
-        <v>11.79628368103782</v>
+        <v>11.79628463916563</v>
       </c>
       <c r="D113" t="n">
-        <v>11.56129780748737</v>
+        <v>11.56129874652895</v>
       </c>
       <c r="E113" t="n">
-        <v>11.74145317077637</v>
+        <v>11.74145412445068</v>
       </c>
       <c r="F113" t="n">
         <v>3674700</v>
@@ -2712,16 +2712,16 @@
         <v>44810</v>
       </c>
       <c r="B115" t="n">
-        <v>11.58479595184326</v>
+        <v>11.58479690551758</v>
       </c>
       <c r="C115" t="n">
-        <v>11.90594298259424</v>
+        <v>11.90594396270576</v>
       </c>
       <c r="D115" t="n">
-        <v>11.49863479020259</v>
+        <v>11.49863573678402</v>
       </c>
       <c r="E115" t="n">
-        <v>11.89810994599068</v>
+        <v>11.89811092545738</v>
       </c>
       <c r="F115" t="n">
         <v>1316500</v>
@@ -2732,16 +2732,16 @@
         <v>44812</v>
       </c>
       <c r="B116" t="n">
-        <v>11.43597221374512</v>
+        <v>11.43597316741943</v>
       </c>
       <c r="C116" t="n">
-        <v>11.63962594040124</v>
+        <v>11.63962691105875</v>
       </c>
       <c r="D116" t="n">
-        <v>11.37330941369716</v>
+        <v>11.37331036214587</v>
       </c>
       <c r="E116" t="n">
-        <v>11.623960613889</v>
+        <v>11.62396158324014</v>
       </c>
       <c r="F116" t="n">
         <v>2598100</v>
@@ -2812,16 +2812,16 @@
         <v>44818</v>
       </c>
       <c r="B120" t="n">
-        <v>11.20881938934326</v>
+        <v>11.20882034301758</v>
       </c>
       <c r="C120" t="n">
-        <v>11.42030615299151</v>
+        <v>11.42030712465965</v>
       </c>
       <c r="D120" t="n">
-        <v>11.02866327875449</v>
+        <v>11.02866421710068</v>
       </c>
       <c r="E120" t="n">
-        <v>11.20098635257864</v>
+        <v>11.2009873055865</v>
       </c>
       <c r="F120" t="n">
         <v>1856400</v>
@@ -2832,16 +2832,16 @@
         <v>44819</v>
       </c>
       <c r="B121" t="n">
-        <v>11.22448444366455</v>
+        <v>11.22448539733887</v>
       </c>
       <c r="C121" t="n">
-        <v>11.27148191611302</v>
+        <v>11.27148287378042</v>
       </c>
       <c r="D121" t="n">
-        <v>11.11482417261777</v>
+        <v>11.11482511697494</v>
       </c>
       <c r="E121" t="n">
-        <v>11.16182164506624</v>
+        <v>11.16182259341649</v>
       </c>
       <c r="F121" t="n">
         <v>1523500</v>
@@ -2852,16 +2852,16 @@
         <v>44820</v>
       </c>
       <c r="B122" t="n">
-        <v>11.16965484619141</v>
+        <v>11.16965579986572</v>
       </c>
       <c r="C122" t="n">
-        <v>11.35764324475576</v>
+        <v>11.35764421448068</v>
       </c>
       <c r="D122" t="n">
-        <v>11.02866317376839</v>
+        <v>11.02866411540472</v>
       </c>
       <c r="E122" t="n">
-        <v>11.2244846090228</v>
+        <v>11.22448556737853</v>
       </c>
       <c r="F122" t="n">
         <v>3523100</v>
@@ -2872,16 +2872,16 @@
         <v>44823</v>
       </c>
       <c r="B123" t="n">
-        <v>11.28714847564697</v>
+        <v>11.28714656829834</v>
       </c>
       <c r="C123" t="n">
-        <v>11.43597319883014</v>
+        <v>11.43597126633249</v>
       </c>
       <c r="D123" t="n">
-        <v>11.11482538717157</v>
+        <v>11.1148235089428</v>
       </c>
       <c r="E123" t="n">
-        <v>11.11482538717157</v>
+        <v>11.1148235089428</v>
       </c>
       <c r="F123" t="n">
         <v>1858600</v>
@@ -2892,16 +2892,16 @@
         <v>44824</v>
       </c>
       <c r="B124" t="n">
-        <v>11.13049030303955</v>
+        <v>11.13048934936523</v>
       </c>
       <c r="C124" t="n">
-        <v>11.35764313587711</v>
+        <v>11.35764216274006</v>
       </c>
       <c r="D124" t="n">
-        <v>11.08349283034925</v>
+        <v>11.08349188070174</v>
       </c>
       <c r="E124" t="n">
-        <v>11.28714730034141</v>
+        <v>11.28714633324452</v>
       </c>
       <c r="F124" t="n">
         <v>1310600</v>
@@ -2912,16 +2912,16 @@
         <v>44825</v>
       </c>
       <c r="B125" t="n">
-        <v>11.09132671356201</v>
+        <v>11.0913257598877</v>
       </c>
       <c r="C125" t="n">
-        <v>11.23231839539528</v>
+        <v>11.23231742959796</v>
       </c>
       <c r="D125" t="n">
-        <v>10.93466970430257</v>
+        <v>10.93466876409822</v>
       </c>
       <c r="E125" t="n">
-        <v>11.13049115262676</v>
+        <v>11.13049019558493</v>
       </c>
       <c r="F125" t="n">
         <v>2825100</v>
@@ -2932,16 +2932,16 @@
         <v>44826</v>
       </c>
       <c r="B126" t="n">
-        <v>11.23231792449951</v>
+        <v>11.23231887817383</v>
       </c>
       <c r="C126" t="n">
-        <v>11.24015096138398</v>
+        <v>11.24015191572336</v>
       </c>
       <c r="D126" t="n">
-        <v>11.05999484803871</v>
+        <v>11.05999578708202</v>
       </c>
       <c r="E126" t="n">
-        <v>11.19315348707667</v>
+        <v>11.19315443742575</v>
       </c>
       <c r="F126" t="n">
         <v>1855600</v>
@@ -3112,16 +3112,16 @@
         <v>44839</v>
       </c>
       <c r="B135" t="n">
-        <v>10.97383308410645</v>
+        <v>10.97383403778076</v>
       </c>
       <c r="C135" t="n">
-        <v>11.20881894881312</v>
+        <v>11.20881992290874</v>
       </c>
       <c r="D135" t="n">
-        <v>10.85633977825337</v>
+        <v>10.85634072171701</v>
       </c>
       <c r="E135" t="n">
-        <v>11.20881894881312</v>
+        <v>11.20881992290874</v>
       </c>
       <c r="F135" t="n">
         <v>5244200</v>
@@ -3132,16 +3132,16 @@
         <v>44840</v>
       </c>
       <c r="B136" t="n">
-        <v>10.98949909210205</v>
+        <v>10.98950004577637</v>
       </c>
       <c r="C136" t="n">
-        <v>11.1226577321339</v>
+        <v>11.12265869736379</v>
       </c>
       <c r="D136" t="n">
-        <v>10.88767185284243</v>
+        <v>10.88767279768013</v>
       </c>
       <c r="E136" t="n">
-        <v>11.02866352981721</v>
+        <v>11.02866448689024</v>
       </c>
       <c r="F136" t="n">
         <v>3101100</v>
@@ -3192,16 +3192,16 @@
         <v>44845</v>
       </c>
       <c r="B139" t="n">
-        <v>11.22448444366455</v>
+        <v>11.22448539733887</v>
       </c>
       <c r="C139" t="n">
-        <v>11.31847864156201</v>
+        <v>11.31847960322243</v>
       </c>
       <c r="D139" t="n">
-        <v>10.99733161199581</v>
+        <v>10.99733254637037</v>
       </c>
       <c r="E139" t="n">
-        <v>11.04432908444429</v>
+        <v>11.04433002281193</v>
       </c>
       <c r="F139" t="n">
         <v>1834300</v>
@@ -3212,16 +3212,16 @@
         <v>44847</v>
       </c>
       <c r="B140" t="n">
-        <v>10.91117095947266</v>
+        <v>10.91117000579834</v>
       </c>
       <c r="C140" t="n">
-        <v>11.20098660325412</v>
+        <v>11.20098562424891</v>
       </c>
       <c r="D140" t="n">
-        <v>10.87200652177256</v>
+        <v>10.87200557152136</v>
       </c>
       <c r="E140" t="n">
-        <v>11.12265772785393</v>
+        <v>11.12265675569494</v>
       </c>
       <c r="F140" t="n">
         <v>3739400</v>
@@ -3252,16 +3252,16 @@
         <v>44851</v>
       </c>
       <c r="B142" t="n">
-        <v>11.1539888381958</v>
+        <v>11.15398788452148</v>
       </c>
       <c r="C142" t="n">
-        <v>11.20098631161214</v>
+        <v>11.2009853539195</v>
       </c>
       <c r="D142" t="n">
-        <v>10.78584507559909</v>
+        <v>10.78584415340134</v>
       </c>
       <c r="E142" t="n">
-        <v>10.86417320196032</v>
+        <v>10.86417227306545</v>
       </c>
       <c r="F142" t="n">
         <v>6971700</v>
@@ -3272,16 +3272,16 @@
         <v>44852</v>
       </c>
       <c r="B143" t="n">
-        <v>11.27148342132568</v>
+        <v>11.27148246765137</v>
       </c>
       <c r="C143" t="n">
-        <v>11.37331066939599</v>
+        <v>11.37330970710612</v>
       </c>
       <c r="D143" t="n">
-        <v>11.06782892518508</v>
+        <v>11.06782798874186</v>
       </c>
       <c r="E143" t="n">
-        <v>11.20882061435928</v>
+        <v>11.20881966598683</v>
       </c>
       <c r="F143" t="n">
         <v>2646800</v>
@@ -3312,16 +3312,16 @@
         <v>44854</v>
       </c>
       <c r="B145" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C145" t="n">
-        <v>10.98166658413194</v>
+        <v>10.98166755090811</v>
       </c>
       <c r="D145" t="n">
-        <v>10.39420227106638</v>
+        <v>10.39420318612486</v>
       </c>
       <c r="E145" t="n">
-        <v>10.57435763518006</v>
+        <v>10.5743585660986</v>
       </c>
       <c r="F145" t="n">
         <v>7194300</v>
@@ -3332,16 +3332,16 @@
         <v>44855</v>
       </c>
       <c r="B146" t="n">
-        <v>11.16965484619141</v>
+        <v>11.16965579986572</v>
       </c>
       <c r="C146" t="n">
-        <v>11.16965484619141</v>
+        <v>11.16965579986572</v>
       </c>
       <c r="D146" t="n">
-        <v>10.75451286561242</v>
+        <v>10.75451378384157</v>
       </c>
       <c r="E146" t="n">
-        <v>10.75451286561242</v>
+        <v>10.75451378384157</v>
       </c>
       <c r="F146" t="n">
         <v>9489900</v>
@@ -3352,16 +3352,16 @@
         <v>44858</v>
       </c>
       <c r="B147" t="n">
-        <v>11.24798393249512</v>
+        <v>11.2479829788208</v>
       </c>
       <c r="C147" t="n">
-        <v>11.45163842182848</v>
+        <v>11.45163745088707</v>
       </c>
       <c r="D147" t="n">
-        <v>11.10699299503318</v>
+        <v>11.10699205331296</v>
       </c>
       <c r="E147" t="n">
-        <v>11.10699299503318</v>
+        <v>11.10699205331296</v>
       </c>
       <c r="F147" t="n">
         <v>2219500</v>
@@ -3372,16 +3372,16 @@
         <v>44859</v>
       </c>
       <c r="B148" t="n">
-        <v>11.3889741897583</v>
+        <v>11.38897514343262</v>
       </c>
       <c r="C148" t="n">
-        <v>11.50646674741971</v>
+        <v>11.50646771093245</v>
       </c>
       <c r="D148" t="n">
-        <v>11.18531972594569</v>
+        <v>11.18532066256667</v>
       </c>
       <c r="E148" t="n">
-        <v>11.24015023358722</v>
+        <v>11.24015117479952</v>
       </c>
       <c r="F148" t="n">
         <v>2935500</v>
@@ -3392,16 +3392,16 @@
         <v>44860</v>
       </c>
       <c r="B149" t="n">
-        <v>11.3419771194458</v>
+        <v>11.34197807312012</v>
       </c>
       <c r="C149" t="n">
-        <v>11.451637391606</v>
+        <v>11.45163835450095</v>
       </c>
       <c r="D149" t="n">
-        <v>11.20098619466782</v>
+        <v>11.20098713648711</v>
       </c>
       <c r="E149" t="n">
-        <v>11.43597206529711</v>
+        <v>11.43597302687486</v>
       </c>
       <c r="F149" t="n">
         <v>4386900</v>
@@ -3452,16 +3452,16 @@
         <v>44865</v>
       </c>
       <c r="B152" t="n">
-        <v>11.68662452697754</v>
+        <v>11.68662357330322</v>
       </c>
       <c r="C152" t="n">
-        <v>11.72578896748743</v>
+        <v>11.72578801061714</v>
       </c>
       <c r="D152" t="n">
-        <v>11.16182296634386</v>
+        <v>11.16182205549541</v>
       </c>
       <c r="E152" t="n">
-        <v>11.23231880986175</v>
+        <v>11.23231789326056</v>
       </c>
       <c r="F152" t="n">
         <v>2644000</v>
@@ -3472,16 +3472,16 @@
         <v>44866</v>
       </c>
       <c r="B153" t="n">
-        <v>11.56913089752197</v>
+        <v>11.56913185119629</v>
       </c>
       <c r="C153" t="n">
-        <v>11.80411602515518</v>
+        <v>11.80411699819995</v>
       </c>
       <c r="D153" t="n">
-        <v>11.34981034946504</v>
+        <v>11.34981128506018</v>
       </c>
       <c r="E153" t="n">
-        <v>11.67879042455094</v>
+        <v>11.67879138726478</v>
       </c>
       <c r="F153" t="n">
         <v>3576300</v>
@@ -3492,16 +3492,16 @@
         <v>44868</v>
       </c>
       <c r="B154" t="n">
-        <v>11.68662452697754</v>
+        <v>11.68662357330322</v>
       </c>
       <c r="C154" t="n">
-        <v>11.74928733299354</v>
+        <v>11.74928637420569</v>
       </c>
       <c r="D154" t="n">
-        <v>11.36547745939565</v>
+        <v>11.36547653192819</v>
       </c>
       <c r="E154" t="n">
-        <v>11.49863610892954</v>
+        <v>11.49863517059581</v>
       </c>
       <c r="F154" t="n">
         <v>2959500</v>
@@ -3512,16 +3512,16 @@
         <v>44869</v>
       </c>
       <c r="B155" t="n">
-        <v>11.67095851898193</v>
+        <v>11.67095756530762</v>
       </c>
       <c r="C155" t="n">
-        <v>11.87461301320299</v>
+        <v>11.87461204288736</v>
       </c>
       <c r="D155" t="n">
-        <v>11.64746015334091</v>
+        <v>11.64745920158673</v>
       </c>
       <c r="E155" t="n">
-        <v>11.74928740045144</v>
+        <v>11.7492864403766</v>
       </c>
       <c r="F155" t="n">
         <v>2161500</v>
@@ -3632,16 +3632,16 @@
         <v>44879</v>
       </c>
       <c r="B161" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C161" t="n">
-        <v>10.9660005105571</v>
+        <v>10.9660014759541</v>
       </c>
       <c r="D161" t="n">
-        <v>10.71534930935563</v>
+        <v>10.71535025268644</v>
       </c>
       <c r="E161" t="n">
-        <v>10.94250214719434</v>
+        <v>10.94250311052265</v>
       </c>
       <c r="F161" t="n">
         <v>1203700</v>
@@ -3792,16 +3792,16 @@
         <v>44890</v>
       </c>
       <c r="B169" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C169" t="n">
-        <v>11.03649634764489</v>
+        <v>11.03649731924802</v>
       </c>
       <c r="D169" t="n">
-        <v>10.71534930935563</v>
+        <v>10.71535025268644</v>
       </c>
       <c r="E169" t="n">
-        <v>10.95033443698226</v>
+        <v>10.95033540100009</v>
       </c>
       <c r="F169" t="n">
         <v>1631500</v>
@@ -3812,16 +3812,16 @@
         <v>44893</v>
       </c>
       <c r="B170" t="n">
-        <v>10.97383308410645</v>
+        <v>10.97383403778076</v>
       </c>
       <c r="C170" t="n">
-        <v>11.09915867941681</v>
+        <v>11.09915964398247</v>
       </c>
       <c r="D170" t="n">
-        <v>10.68401745820135</v>
+        <v>10.68401838668942</v>
       </c>
       <c r="E170" t="n">
-        <v>10.84067445233931</v>
+        <v>10.84067539444156</v>
       </c>
       <c r="F170" t="n">
         <v>4990000</v>
@@ -3832,16 +3832,16 @@
         <v>44894</v>
       </c>
       <c r="B171" t="n">
-        <v>11.16965484619141</v>
+        <v>11.16965579986572</v>
       </c>
       <c r="C171" t="n">
-        <v>11.26364904547358</v>
+        <v>11.2636500071732</v>
       </c>
       <c r="D171" t="n">
-        <v>10.99733177400767</v>
+        <v>10.9973327129689</v>
       </c>
       <c r="E171" t="n">
-        <v>11.01299784738778</v>
+        <v>11.01299878768659</v>
       </c>
       <c r="F171" t="n">
         <v>1705300</v>
@@ -3852,16 +3852,16 @@
         <v>44895</v>
       </c>
       <c r="B172" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C172" t="n">
-        <v>11.20881942197064</v>
+        <v>11.20882040874432</v>
       </c>
       <c r="D172" t="n">
-        <v>10.69185019899337</v>
+        <v>10.69185114025542</v>
       </c>
       <c r="E172" t="n">
-        <v>11.20881942197064</v>
+        <v>11.20882040874432</v>
       </c>
       <c r="F172" t="n">
         <v>4586400</v>
@@ -3872,16 +3872,16 @@
         <v>44896</v>
       </c>
       <c r="B173" t="n">
-        <v>10.92683601379395</v>
+        <v>10.92683696746826</v>
       </c>
       <c r="C173" t="n">
-        <v>11.02083021372987</v>
+        <v>11.02083117560783</v>
       </c>
       <c r="D173" t="n">
-        <v>10.69185014045439</v>
+        <v>10.69185107361957</v>
       </c>
       <c r="E173" t="n">
-        <v>10.76234597715621</v>
+        <v>10.76234691647413</v>
       </c>
       <c r="F173" t="n">
         <v>1944500</v>
@@ -3912,16 +3912,16 @@
         <v>44900</v>
       </c>
       <c r="B175" t="n">
-        <v>10.51952838897705</v>
+        <v>10.51952743530273</v>
       </c>
       <c r="C175" t="n">
-        <v>10.80151100419552</v>
+        <v>10.80151002495736</v>
       </c>
       <c r="D175" t="n">
-        <v>10.50386231463181</v>
+        <v>10.50386136237774</v>
       </c>
       <c r="E175" t="n">
-        <v>10.7780126396772</v>
+        <v>10.77801166256934</v>
       </c>
       <c r="F175" t="n">
         <v>1355000</v>
@@ -3932,16 +3932,16 @@
         <v>44901</v>
       </c>
       <c r="B176" t="n">
-        <v>10.47253131866455</v>
+        <v>10.47253036499023</v>
       </c>
       <c r="C176" t="n">
-        <v>10.58219160233104</v>
+        <v>10.58219063867058</v>
       </c>
       <c r="D176" t="n">
-        <v>10.41770155033109</v>
+        <v>10.41770060164981</v>
       </c>
       <c r="E176" t="n">
-        <v>10.51952879652149</v>
+        <v>10.51952783856738</v>
       </c>
       <c r="F176" t="n">
         <v>1647500</v>
@@ -3972,16 +3972,16 @@
         <v>44903</v>
       </c>
       <c r="B178" t="n">
-        <v>11.26364994049072</v>
+        <v>11.26364898681641</v>
       </c>
       <c r="C178" t="n">
-        <v>11.81194985337145</v>
+        <v>11.8119488532735</v>
       </c>
       <c r="D178" t="n">
-        <v>11.15398965911476</v>
+        <v>11.15398871472519</v>
       </c>
       <c r="E178" t="n">
-        <v>11.74928704887077</v>
+        <v>11.74928605407837</v>
       </c>
       <c r="F178" t="n">
         <v>12105700</v>
@@ -4092,16 +4092,16 @@
         <v>44911</v>
       </c>
       <c r="B184" t="n">
-        <v>11.24798393249512</v>
+        <v>11.2479829788208</v>
       </c>
       <c r="C184" t="n">
-        <v>11.24798393249512</v>
+        <v>11.2479829788208</v>
       </c>
       <c r="D184" t="n">
-        <v>10.90333850569981</v>
+        <v>10.90333758124669</v>
       </c>
       <c r="E184" t="n">
-        <v>11.04433019016131</v>
+        <v>11.04432925375403</v>
       </c>
       <c r="F184" t="n">
         <v>3365900</v>
@@ -4152,16 +4152,16 @@
         <v>44916</v>
       </c>
       <c r="B187" t="n">
-        <v>11.58479595184326</v>
+        <v>11.58479690551758</v>
       </c>
       <c r="C187" t="n">
-        <v>11.75711902212409</v>
+        <v>11.75711998998425</v>
       </c>
       <c r="D187" t="n">
-        <v>11.15398864964095</v>
+        <v>11.15398956785069</v>
       </c>
       <c r="E187" t="n">
-        <v>11.42813895476955</v>
+        <v>11.42813989554768</v>
       </c>
       <c r="F187" t="n">
         <v>6348400</v>
@@ -4192,16 +4192,16 @@
         <v>44918</v>
       </c>
       <c r="B189" t="n">
-        <v>11.78845024108887</v>
+        <v>11.78845119476318</v>
       </c>
       <c r="C189" t="n">
-        <v>12.09393119395663</v>
+        <v>12.09393217234406</v>
       </c>
       <c r="D189" t="n">
-        <v>11.57696273802706</v>
+        <v>11.57696367459224</v>
       </c>
       <c r="E189" t="n">
-        <v>11.67878997131614</v>
+        <v>11.67879091611904</v>
       </c>
       <c r="F189" t="n">
         <v>5656000</v>
@@ -4252,16 +4252,16 @@
         <v>44923</v>
       </c>
       <c r="B192" t="n">
-        <v>11.58479595184326</v>
+        <v>11.58479690551758</v>
       </c>
       <c r="C192" t="n">
-        <v>11.6944562232946</v>
+        <v>11.69445718599628</v>
       </c>
       <c r="D192" t="n">
-        <v>11.49863479020259</v>
+        <v>11.49863573678402</v>
       </c>
       <c r="E192" t="n">
-        <v>11.5769629152397</v>
+        <v>11.5769638682692</v>
       </c>
       <c r="F192" t="n">
         <v>2005900</v>
@@ -4292,16 +4292,16 @@
         <v>44928</v>
       </c>
       <c r="B194" t="n">
-        <v>11.3419771194458</v>
+        <v>11.34197807312012</v>
       </c>
       <c r="C194" t="n">
-        <v>11.46730346491438</v>
+        <v>11.46730442912659</v>
       </c>
       <c r="D194" t="n">
-        <v>11.17748783170473</v>
+        <v>11.1774887715482</v>
       </c>
       <c r="E194" t="n">
-        <v>11.38897459237146</v>
+        <v>11.38897554999749</v>
       </c>
       <c r="F194" t="n">
         <v>1018800</v>
@@ -4312,16 +4312,16 @@
         <v>44929</v>
       </c>
       <c r="B195" t="n">
-        <v>11.13832473754883</v>
+        <v>11.13832378387451</v>
       </c>
       <c r="C195" t="n">
-        <v>11.32631315790418</v>
+        <v>11.32631218813412</v>
       </c>
       <c r="D195" t="n">
-        <v>11.05999585556764</v>
+        <v>11.05999490859992</v>
       </c>
       <c r="E195" t="n">
-        <v>11.30281479210966</v>
+        <v>11.30281382435154</v>
       </c>
       <c r="F195" t="n">
         <v>1562800</v>
@@ -4392,16 +4392,16 @@
         <v>44935</v>
       </c>
       <c r="B199" t="n">
-        <v>11.23231792449951</v>
+        <v>11.23231887817383</v>
       </c>
       <c r="C199" t="n">
-        <v>11.43597240149869</v>
+        <v>11.43597337246419</v>
       </c>
       <c r="D199" t="n">
-        <v>11.17748816030724</v>
+        <v>11.17748910932626</v>
       </c>
       <c r="E199" t="n">
-        <v>11.36547656353747</v>
+        <v>11.36547752851756</v>
       </c>
       <c r="F199" t="n">
         <v>1567200</v>
@@ -4472,16 +4472,16 @@
         <v>44939</v>
       </c>
       <c r="B203" t="n">
-        <v>11.58479595184326</v>
+        <v>11.58479690551758</v>
       </c>
       <c r="C203" t="n">
-        <v>11.78845042153883</v>
+        <v>11.78845139197822</v>
       </c>
       <c r="D203" t="n">
-        <v>11.44380428097718</v>
+        <v>11.44380522304489</v>
       </c>
       <c r="E203" t="n">
-        <v>11.74928598552053</v>
+        <v>11.74928695273586</v>
       </c>
       <c r="F203" t="n">
         <v>2269100</v>
@@ -4492,16 +4492,16 @@
         <v>44942</v>
       </c>
       <c r="B204" t="n">
-        <v>11.78845024108887</v>
+        <v>11.78845119476318</v>
       </c>
       <c r="C204" t="n">
-        <v>11.8041155670567</v>
+        <v>11.80411652199833</v>
       </c>
       <c r="D204" t="n">
-        <v>11.39680738089987</v>
+        <v>11.39680830289065</v>
       </c>
       <c r="E204" t="n">
-        <v>11.49080157770529</v>
+        <v>11.49080250730011</v>
       </c>
       <c r="F204" t="n">
         <v>3279700</v>
@@ -4512,16 +4512,16 @@
         <v>44943</v>
       </c>
       <c r="B205" t="n">
-        <v>11.74928665161133</v>
+        <v>11.74928569793701</v>
       </c>
       <c r="C205" t="n">
-        <v>11.93727505875722</v>
+        <v>11.93727408982413</v>
       </c>
       <c r="D205" t="n">
-        <v>11.60829497275214</v>
+        <v>11.60829403052194</v>
       </c>
       <c r="E205" t="n">
-        <v>11.81194945399329</v>
+        <v>11.81194849523272</v>
       </c>
       <c r="F205" t="n">
         <v>2676600</v>
@@ -4572,16 +4572,16 @@
         <v>44946</v>
       </c>
       <c r="B208" t="n">
-        <v>11.58479595184326</v>
+        <v>11.58479690551758</v>
       </c>
       <c r="C208" t="n">
-        <v>11.68662318669104</v>
+        <v>11.6866241487479</v>
       </c>
       <c r="D208" t="n">
-        <v>11.48296871699548</v>
+        <v>11.48296966228726</v>
       </c>
       <c r="E208" t="n">
-        <v>11.6552917872763</v>
+        <v>11.65529274675392</v>
       </c>
       <c r="F208" t="n">
         <v>2012100</v>
@@ -4612,16 +4612,16 @@
         <v>44950</v>
       </c>
       <c r="B210" t="n">
-        <v>11.68662452697754</v>
+        <v>11.68662357330322</v>
       </c>
       <c r="C210" t="n">
-        <v>11.80411710150764</v>
+        <v>11.80411613824548</v>
       </c>
       <c r="D210" t="n">
-        <v>11.32631301888575</v>
+        <v>11.32631209461427</v>
       </c>
       <c r="E210" t="n">
-        <v>11.52996751193754</v>
+        <v>11.52996657104705</v>
       </c>
       <c r="F210" t="n">
         <v>5839900</v>
@@ -4632,16 +4632,16 @@
         <v>44951</v>
       </c>
       <c r="B211" t="n">
-        <v>11.89027881622314</v>
+        <v>11.89027786254883</v>
       </c>
       <c r="C211" t="n">
-        <v>12.07043419368129</v>
+        <v>12.07043322555739</v>
       </c>
       <c r="D211" t="n">
-        <v>11.62396152172019</v>
+        <v>11.62396058940618</v>
       </c>
       <c r="E211" t="n">
-        <v>11.67879128929448</v>
+        <v>11.67879035258278</v>
       </c>
       <c r="F211" t="n">
         <v>10764800</v>
@@ -4672,16 +4672,16 @@
         <v>44953</v>
       </c>
       <c r="B213" t="n">
-        <v>11.98427200317383</v>
+        <v>11.98427295684814</v>
       </c>
       <c r="C213" t="n">
-        <v>12.23492320159854</v>
+        <v>12.23492417521897</v>
       </c>
       <c r="D213" t="n">
-        <v>11.92160920356765</v>
+        <v>11.92161015225544</v>
       </c>
       <c r="E213" t="n">
-        <v>11.96860592977254</v>
+        <v>11.96860688220019</v>
       </c>
       <c r="F213" t="n">
         <v>4160800</v>
@@ -4712,16 +4712,16 @@
         <v>44957</v>
       </c>
       <c r="B215" t="n">
-        <v>12.0704345703125</v>
+        <v>12.07043361663818</v>
       </c>
       <c r="C215" t="n">
-        <v>12.14093041482172</v>
+        <v>12.14092945557759</v>
       </c>
       <c r="D215" t="n">
-        <v>11.82761638033583</v>
+        <v>11.82761544584636</v>
       </c>
       <c r="E215" t="n">
-        <v>11.84328170856034</v>
+        <v>11.84328077283316</v>
       </c>
       <c r="F215" t="n">
         <v>5446800</v>
@@ -4952,16 +4952,16 @@
         <v>44973</v>
       </c>
       <c r="B227" t="n">
-        <v>11.89027881622314</v>
+        <v>11.89027786254883</v>
       </c>
       <c r="C227" t="n">
-        <v>11.9764399862684</v>
+        <v>11.97643902568342</v>
       </c>
       <c r="D227" t="n">
-        <v>11.57696404451397</v>
+        <v>11.57696311596945</v>
       </c>
       <c r="E227" t="n">
-        <v>11.7649532063393</v>
+        <v>11.76495226271687</v>
       </c>
       <c r="F227" t="n">
         <v>4461000</v>
@@ -5172,16 +5172,16 @@
         <v>44992</v>
       </c>
       <c r="B238" t="n">
-        <v>11.61612701416016</v>
+        <v>11.61612796783447</v>
       </c>
       <c r="C238" t="n">
-        <v>11.6239600505364</v>
+        <v>11.6239610048538</v>
       </c>
       <c r="D238" t="n">
-        <v>11.38897418824534</v>
+        <v>11.3889751232706</v>
       </c>
       <c r="E238" t="n">
-        <v>11.52996585501987</v>
+        <v>11.52996680162043</v>
       </c>
       <c r="F238" t="n">
         <v>3776700</v>
@@ -5292,16 +5292,16 @@
         <v>45000</v>
       </c>
       <c r="B244" t="n">
-        <v>11.74928665161133</v>
+        <v>11.74928569793701</v>
       </c>
       <c r="C244" t="n">
-        <v>11.89027833047051</v>
+        <v>11.89027736535209</v>
       </c>
       <c r="D244" t="n">
-        <v>11.61612800979977</v>
+        <v>11.61612706693377</v>
       </c>
       <c r="E244" t="n">
-        <v>11.71795525042035</v>
+        <v>11.71795429928916</v>
       </c>
       <c r="F244" t="n">
         <v>4602600</v>
@@ -5312,16 +5312,16 @@
         <v>45001</v>
       </c>
       <c r="B245" t="n">
-        <v>11.67095851898193</v>
+        <v>11.67095756530762</v>
       </c>
       <c r="C245" t="n">
-        <v>11.81195020682722</v>
+        <v>11.81194924163198</v>
       </c>
       <c r="D245" t="n">
-        <v>11.63962711579405</v>
+        <v>11.63962616467993</v>
       </c>
       <c r="E245" t="n">
-        <v>11.81195020682722</v>
+        <v>11.81194924163198</v>
       </c>
       <c r="F245" t="n">
         <v>5495800</v>
@@ -5372,16 +5372,16 @@
         <v>45006</v>
       </c>
       <c r="B248" t="n">
-        <v>11.3419771194458</v>
+        <v>11.34197807312012</v>
       </c>
       <c r="C248" t="n">
-        <v>11.42030599198873</v>
+        <v>11.42030695224922</v>
       </c>
       <c r="D248" t="n">
-        <v>11.27931432021125</v>
+        <v>11.27931526861666</v>
       </c>
       <c r="E248" t="n">
-        <v>11.36547622940837</v>
+        <v>11.36547718505858</v>
       </c>
       <c r="F248" t="n">
         <v>2410300</v>
@@ -5392,16 +5392,16 @@
         <v>45007</v>
       </c>
       <c r="B249" t="n">
-        <v>11.33414554595947</v>
+        <v>11.33414459228516</v>
       </c>
       <c r="C249" t="n">
-        <v>11.45947115234749</v>
+        <v>11.45947018812806</v>
       </c>
       <c r="D249" t="n">
-        <v>11.21665222972105</v>
+        <v>11.21665128593282</v>
       </c>
       <c r="E249" t="n">
-        <v>11.36547694755648</v>
+        <v>11.36547599124588</v>
       </c>
       <c r="F249" t="n">
         <v>3006300</v>
@@ -5452,16 +5452,16 @@
         <v>45012</v>
       </c>
       <c r="B252" t="n">
-        <v>11.28714847564697</v>
+        <v>11.28714656829834</v>
       </c>
       <c r="C252" t="n">
-        <v>11.42030712396893</v>
+        <v>11.42030519411861</v>
       </c>
       <c r="D252" t="n">
-        <v>11.19315426747845</v>
+        <v>11.19315237601335</v>
       </c>
       <c r="E252" t="n">
-        <v>11.39680875867669</v>
+        <v>11.39680683279722</v>
       </c>
       <c r="F252" t="n">
         <v>2288800</v>
@@ -5492,16 +5492,16 @@
         <v>45014</v>
       </c>
       <c r="B254" t="n">
-        <v>11.36547660827637</v>
+        <v>11.36547756195068</v>
       </c>
       <c r="C254" t="n">
-        <v>11.47513613709258</v>
+        <v>11.4751370999684</v>
       </c>
       <c r="D254" t="n">
-        <v>11.19315353113723</v>
+        <v>11.19315447035196</v>
       </c>
       <c r="E254" t="n">
-        <v>11.43597244651508</v>
+        <v>11.43597340610469</v>
       </c>
       <c r="F254" t="n">
         <v>2326000</v>
@@ -5552,16 +5552,16 @@
         <v>45019</v>
       </c>
       <c r="B257" t="n">
-        <v>11.3419771194458</v>
+        <v>11.34197807312012</v>
       </c>
       <c r="C257" t="n">
-        <v>11.58479602672929</v>
+        <v>11.58479700082069</v>
       </c>
       <c r="D257" t="n">
-        <v>11.24798292059398</v>
+        <v>11.24798386636493</v>
       </c>
       <c r="E257" t="n">
-        <v>11.58479602672929</v>
+        <v>11.58479700082069</v>
       </c>
       <c r="F257" t="n">
         <v>6471200</v>
@@ -5572,16 +5572,16 @@
         <v>45020</v>
       </c>
       <c r="B258" t="n">
-        <v>11.43597221374512</v>
+        <v>11.43597316741943</v>
       </c>
       <c r="C258" t="n">
-        <v>11.49863501379308</v>
+        <v>11.498635972693</v>
       </c>
       <c r="D258" t="n">
-        <v>11.24798306660174</v>
+        <v>11.24798400459917</v>
       </c>
       <c r="E258" t="n">
-        <v>11.35764334018542</v>
+        <v>11.35764428732769</v>
       </c>
       <c r="F258" t="n">
         <v>5230100</v>
@@ -5732,16 +5732,16 @@
         <v>45033</v>
       </c>
       <c r="B266" t="n">
-        <v>12.05476856231689</v>
+        <v>12.05476760864258</v>
       </c>
       <c r="C266" t="n">
-        <v>12.14092973019197</v>
+        <v>12.14092876970129</v>
       </c>
       <c r="D266" t="n">
-        <v>11.89027851673754</v>
+        <v>11.89027757607632</v>
       </c>
       <c r="E266" t="n">
-        <v>11.99210575895329</v>
+        <v>11.99210481023634</v>
       </c>
       <c r="F266" t="n">
         <v>4936300</v>
@@ -5852,16 +5852,16 @@
         <v>45042</v>
       </c>
       <c r="B272" t="n">
-        <v>11.99993801116943</v>
+        <v>11.99993705749512</v>
       </c>
       <c r="C272" t="n">
-        <v>12.12526361750026</v>
+        <v>12.12526265386591</v>
       </c>
       <c r="D272" t="n">
-        <v>11.95294128229514</v>
+        <v>11.95294033235581</v>
       </c>
       <c r="E272" t="n">
-        <v>12.10176525306311</v>
+        <v>12.10176429129625</v>
       </c>
       <c r="F272" t="n">
         <v>2471700</v>
@@ -5912,16 +5912,16 @@
         <v>45048</v>
       </c>
       <c r="B275" t="n">
-        <v>12.39158153533936</v>
+        <v>12.39158058166504</v>
       </c>
       <c r="C275" t="n">
-        <v>12.65006579830664</v>
+        <v>12.650064824739</v>
       </c>
       <c r="D275" t="n">
-        <v>12.25059059453875</v>
+        <v>12.2505896517153</v>
       </c>
       <c r="E275" t="n">
-        <v>12.53257322313954</v>
+        <v>12.5325722586143</v>
       </c>
       <c r="F275" t="n">
         <v>5999300</v>
@@ -5932,16 +5932,16 @@
         <v>45049</v>
       </c>
       <c r="B276" t="n">
-        <v>12.28975391387939</v>
+        <v>12.28975296020508</v>
       </c>
       <c r="C276" t="n">
-        <v>12.48557536452565</v>
+        <v>12.48557439565576</v>
       </c>
       <c r="D276" t="n">
-        <v>12.2819216235732</v>
+        <v>12.28192067050667</v>
       </c>
       <c r="E276" t="n">
-        <v>12.48557536452565</v>
+        <v>12.48557439565576</v>
       </c>
       <c r="F276" t="n">
         <v>6661600</v>
@@ -5992,16 +5992,16 @@
         <v>45054</v>
       </c>
       <c r="B279" t="n">
-        <v>12.11165809631348</v>
+        <v>12.11165904998779</v>
       </c>
       <c r="C279" t="n">
-        <v>12.58781351962092</v>
+        <v>12.58781451078781</v>
       </c>
       <c r="D279" t="n">
-        <v>12.05105678220141</v>
+        <v>12.05105773110397</v>
       </c>
       <c r="E279" t="n">
-        <v>12.54452651284189</v>
+        <v>12.54452750060035</v>
       </c>
       <c r="F279" t="n">
         <v>5826000</v>
@@ -6132,16 +6132,16 @@
         <v>45063</v>
       </c>
       <c r="B286" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="C286" t="n">
-        <v>12.24152036724783</v>
+        <v>12.24151939290137</v>
       </c>
       <c r="D286" t="n">
-        <v>11.9471696818366</v>
+        <v>11.94716873091856</v>
       </c>
       <c r="E286" t="n">
-        <v>12.128974468377</v>
+        <v>12.12897350298847</v>
       </c>
       <c r="F286" t="n">
         <v>4330800</v>
@@ -6152,16 +6152,16 @@
         <v>45064</v>
       </c>
       <c r="B287" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="C287" t="n">
-        <v>12.05971558070743</v>
+        <v>12.05971462083146</v>
       </c>
       <c r="D287" t="n">
-        <v>11.82596621559931</v>
+        <v>11.82596527432829</v>
       </c>
       <c r="E287" t="n">
-        <v>12.01642856950617</v>
+        <v>12.01642761307558</v>
       </c>
       <c r="F287" t="n">
         <v>4680600</v>
@@ -6172,16 +6172,16 @@
         <v>45065</v>
       </c>
       <c r="B288" t="n">
-        <v>12.09434509277344</v>
+        <v>12.09434413909912</v>
       </c>
       <c r="C288" t="n">
-        <v>12.18091829003328</v>
+        <v>12.18091732953242</v>
       </c>
       <c r="D288" t="n">
-        <v>11.93851218182222</v>
+        <v>11.93851124043578</v>
       </c>
       <c r="E288" t="n">
-        <v>11.99911350246722</v>
+        <v>11.99911255630219</v>
       </c>
       <c r="F288" t="n">
         <v>2962700</v>
@@ -6232,16 +6232,16 @@
         <v>45070</v>
       </c>
       <c r="B291" t="n">
-        <v>12.25017642974854</v>
+        <v>12.25017738342285</v>
       </c>
       <c r="C291" t="n">
-        <v>12.30212100543608</v>
+        <v>12.30212196315428</v>
       </c>
       <c r="D291" t="n">
-        <v>12.18091754591915</v>
+        <v>12.18091849420168</v>
       </c>
       <c r="E291" t="n">
-        <v>12.26749156352139</v>
+        <v>12.26749251854369</v>
       </c>
       <c r="F291" t="n">
         <v>1846000</v>
@@ -6292,16 +6292,16 @@
         <v>45075</v>
       </c>
       <c r="B294" t="n">
-        <v>12.28480529785156</v>
+        <v>12.28480625152588</v>
       </c>
       <c r="C294" t="n">
-        <v>12.34540743759487</v>
+        <v>12.34540839597375</v>
       </c>
       <c r="D294" t="n">
-        <v>12.16360266962691</v>
+        <v>12.16360361389222</v>
       </c>
       <c r="E294" t="n">
-        <v>12.16360266962691</v>
+        <v>12.16360361389222</v>
       </c>
       <c r="F294" t="n">
         <v>1431900</v>
@@ -6352,16 +6352,16 @@
         <v>45078</v>
       </c>
       <c r="B297" t="n">
-        <v>12.24151992797852</v>
+        <v>12.2415189743042</v>
       </c>
       <c r="C297" t="n">
-        <v>12.30212124610704</v>
+        <v>12.30212028771158</v>
       </c>
       <c r="D297" t="n">
-        <v>12.1636034757384</v>
+        <v>12.16360252813415</v>
       </c>
       <c r="E297" t="n">
-        <v>12.26749180351488</v>
+        <v>12.26749084781722</v>
       </c>
       <c r="F297" t="n">
         <v>2308800</v>
@@ -6412,16 +6412,16 @@
         <v>45083</v>
       </c>
       <c r="B300" t="n">
-        <v>12.32809352874756</v>
+        <v>12.32809257507324</v>
       </c>
       <c r="C300" t="n">
-        <v>12.41466755090237</v>
+        <v>12.41466659053087</v>
       </c>
       <c r="D300" t="n">
-        <v>12.0770298552559</v>
+        <v>12.07702892100332</v>
       </c>
       <c r="E300" t="n">
-        <v>12.08568742259759</v>
+        <v>12.08568648767528</v>
       </c>
       <c r="F300" t="n">
         <v>7376500</v>
@@ -6452,16 +6452,16 @@
         <v>45086</v>
       </c>
       <c r="B302" t="n">
-        <v>12.37137985229492</v>
+        <v>12.37138080596924</v>
       </c>
       <c r="C302" t="n">
-        <v>12.42332442782724</v>
+        <v>12.42332538550581</v>
       </c>
       <c r="D302" t="n">
-        <v>12.26749152686131</v>
+        <v>12.26749247252717</v>
       </c>
       <c r="E302" t="n">
-        <v>12.29346340181196</v>
+        <v>12.29346434947992</v>
       </c>
       <c r="F302" t="n">
         <v>4999400</v>
@@ -6472,16 +6472,16 @@
         <v>45089</v>
       </c>
       <c r="B303" t="n">
-        <v>12.45795345306396</v>
+        <v>12.45795440673828</v>
       </c>
       <c r="C303" t="n">
-        <v>12.45795345306396</v>
+        <v>12.45795440673828</v>
       </c>
       <c r="D303" t="n">
-        <v>12.25883355008453</v>
+        <v>12.25883448851593</v>
       </c>
       <c r="E303" t="n">
-        <v>12.3800370051864</v>
+        <v>12.3800379528961</v>
       </c>
       <c r="F303" t="n">
         <v>2572800</v>
@@ -6532,16 +6532,16 @@
         <v>45092</v>
       </c>
       <c r="B306" t="n">
-        <v>12.46661186218262</v>
+        <v>12.4666109085083</v>
       </c>
       <c r="C306" t="n">
-        <v>12.49258456537125</v>
+        <v>12.49258360971007</v>
       </c>
       <c r="D306" t="n">
-        <v>12.36272352632139</v>
+        <v>12.36272258059435</v>
       </c>
       <c r="E306" t="n">
-        <v>12.45795512008417</v>
+        <v>12.45795416707208</v>
       </c>
       <c r="F306" t="n">
         <v>1266000</v>
@@ -6572,16 +6572,16 @@
         <v>45096</v>
       </c>
       <c r="B308" t="n">
-        <v>12.6137866973877</v>
+        <v>12.61378574371338</v>
       </c>
       <c r="C308" t="n">
-        <v>12.80424905152594</v>
+        <v>12.80424808345158</v>
       </c>
       <c r="D308" t="n">
-        <v>12.38869572500366</v>
+        <v>12.38869478834751</v>
       </c>
       <c r="E308" t="n">
-        <v>12.80424905152594</v>
+        <v>12.80424808345158</v>
       </c>
       <c r="F308" t="n">
         <v>3301400</v>
@@ -6592,16 +6592,16 @@
         <v>45097</v>
       </c>
       <c r="B309" t="n">
-        <v>12.72633266448975</v>
+        <v>12.72633171081543</v>
       </c>
       <c r="C309" t="n">
-        <v>12.89947988480048</v>
+        <v>12.89947891815102</v>
       </c>
       <c r="D309" t="n">
-        <v>12.64841620894215</v>
+        <v>12.64841526110666</v>
       </c>
       <c r="E309" t="n">
-        <v>12.6917032204276</v>
+        <v>12.69170226934831</v>
       </c>
       <c r="F309" t="n">
         <v>3568000</v>
@@ -6612,16 +6612,16 @@
         <v>45098</v>
       </c>
       <c r="B310" t="n">
-        <v>12.86484909057617</v>
+        <v>12.86485004425049</v>
       </c>
       <c r="C310" t="n">
-        <v>12.90813609751867</v>
+        <v>12.90813705440186</v>
       </c>
       <c r="D310" t="n">
-        <v>12.63975814061098</v>
+        <v>12.63975907759925</v>
       </c>
       <c r="E310" t="n">
-        <v>12.75230320277808</v>
+        <v>12.75230414810935</v>
       </c>
       <c r="F310" t="n">
         <v>5022600</v>
@@ -6632,16 +6632,16 @@
         <v>45099</v>
       </c>
       <c r="B311" t="n">
-        <v>12.7869348526001</v>
+        <v>12.78693389892578</v>
       </c>
       <c r="C311" t="n">
-        <v>12.84753617349909</v>
+        <v>12.84753521530501</v>
       </c>
       <c r="D311" t="n">
-        <v>12.64841625026786</v>
+        <v>12.64841530692453</v>
       </c>
       <c r="E311" t="n">
-        <v>12.7869348526001</v>
+        <v>12.78693389892578</v>
       </c>
       <c r="F311" t="n">
         <v>2039700</v>
@@ -6652,16 +6652,16 @@
         <v>45100</v>
       </c>
       <c r="B312" t="n">
-        <v>12.94276714324951</v>
+        <v>12.9427661895752</v>
       </c>
       <c r="C312" t="n">
-        <v>13.07262818018377</v>
+        <v>13.07262721694078</v>
       </c>
       <c r="D312" t="n">
-        <v>12.76096235204642</v>
+        <v>12.7609614117682</v>
       </c>
       <c r="E312" t="n">
-        <v>12.81290693194634</v>
+        <v>12.81290598784064</v>
       </c>
       <c r="F312" t="n">
         <v>2959500</v>
@@ -6692,16 +6692,16 @@
         <v>45104</v>
       </c>
       <c r="B314" t="n">
-        <v>12.50124073028564</v>
+        <v>12.50123977661133</v>
       </c>
       <c r="C314" t="n">
-        <v>12.83887842546918</v>
+        <v>12.83887744603771</v>
       </c>
       <c r="D314" t="n">
-        <v>12.39735239922096</v>
+        <v>12.3973514534719</v>
       </c>
       <c r="E314" t="n">
-        <v>12.76961953809272</v>
+        <v>12.76961856394476</v>
       </c>
       <c r="F314" t="n">
         <v>3014700</v>
@@ -6812,16 +6812,16 @@
         <v>45112</v>
       </c>
       <c r="B320" t="n">
-        <v>12.44063949584961</v>
+        <v>12.44063854217529</v>
       </c>
       <c r="C320" t="n">
-        <v>12.54452782762921</v>
+        <v>12.54452686599102</v>
       </c>
       <c r="D320" t="n">
-        <v>12.24152039967981</v>
+        <v>12.24151946126957</v>
       </c>
       <c r="E320" t="n">
-        <v>12.30212172014348</v>
+        <v>12.30212077708766</v>
       </c>
       <c r="F320" t="n">
         <v>5051100</v>
@@ -6832,16 +6832,16 @@
         <v>45113</v>
       </c>
       <c r="B321" t="n">
-        <v>12.32809352874756</v>
+        <v>12.32809257507324</v>
       </c>
       <c r="C321" t="n">
-        <v>12.48392643837378</v>
+        <v>12.48392547264458</v>
       </c>
       <c r="D321" t="n">
-        <v>12.25017707393445</v>
+        <v>12.25017612628758</v>
       </c>
       <c r="E321" t="n">
-        <v>12.43198185995469</v>
+        <v>12.4319808982438</v>
       </c>
       <c r="F321" t="n">
         <v>2081000</v>
@@ -6872,16 +6872,16 @@
         <v>45117</v>
       </c>
       <c r="B323" t="n">
-        <v>12.38869476318359</v>
+        <v>12.38869571685791</v>
       </c>
       <c r="C323" t="n">
-        <v>12.45795364556026</v>
+        <v>12.45795460456609</v>
       </c>
       <c r="D323" t="n">
-        <v>12.31077831410209</v>
+        <v>12.31077926177845</v>
       </c>
       <c r="E323" t="n">
-        <v>12.38003719647876</v>
+        <v>12.38003814948662</v>
       </c>
       <c r="F323" t="n">
         <v>1514600</v>
@@ -6912,16 +6912,16 @@
         <v>45119</v>
       </c>
       <c r="B325" t="n">
-        <v>12.38869476318359</v>
+        <v>12.38869571685791</v>
       </c>
       <c r="C325" t="n">
-        <v>12.45795364556026</v>
+        <v>12.45795460456609</v>
       </c>
       <c r="D325" t="n">
-        <v>12.28480561398759</v>
+        <v>12.28480655966458</v>
       </c>
       <c r="E325" t="n">
-        <v>12.37137962977392</v>
+        <v>12.37138058211533</v>
       </c>
       <c r="F325" t="n">
         <v>1842800</v>
@@ -6932,16 +6932,16 @@
         <v>45120</v>
       </c>
       <c r="B326" t="n">
-        <v>12.44063949584961</v>
+        <v>12.44063854217529</v>
       </c>
       <c r="C326" t="n">
-        <v>12.51855595109208</v>
+        <v>12.51855499144484</v>
       </c>
       <c r="D326" t="n">
-        <v>12.34540873145941</v>
+        <v>12.34540778508529</v>
       </c>
       <c r="E326" t="n">
-        <v>12.47526893977614</v>
+        <v>12.4752679834472</v>
       </c>
       <c r="F326" t="n">
         <v>1737300</v>
@@ -6952,16 +6952,16 @@
         <v>45121</v>
       </c>
       <c r="B327" t="n">
-        <v>12.38003730773926</v>
+        <v>12.38003826141357</v>
       </c>
       <c r="C327" t="n">
-        <v>12.48392563223791</v>
+        <v>12.48392659391508</v>
       </c>
       <c r="D327" t="n">
-        <v>12.33675029945707</v>
+        <v>12.33675124979684</v>
       </c>
       <c r="E327" t="n">
-        <v>12.48392563223791</v>
+        <v>12.48392659391508</v>
       </c>
       <c r="F327" t="n">
         <v>1319400</v>
@@ -7052,16 +7052,16 @@
         <v>45128</v>
       </c>
       <c r="B332" t="n">
-        <v>12.38869476318359</v>
+        <v>12.38869571685791</v>
       </c>
       <c r="C332" t="n">
-        <v>12.38869476318359</v>
+        <v>12.38869571685791</v>
       </c>
       <c r="D332" t="n">
-        <v>12.22420429831576</v>
+        <v>12.2242052393277</v>
       </c>
       <c r="E332" t="n">
-        <v>12.27614887291376</v>
+        <v>12.27614981792436</v>
       </c>
       <c r="F332" t="n">
         <v>2631400</v>
@@ -7192,16 +7192,16 @@
         <v>45139</v>
       </c>
       <c r="B339" t="n">
-        <v>12.12897491455078</v>
+        <v>12.12897396087646</v>
       </c>
       <c r="C339" t="n">
-        <v>12.38003859799633</v>
+        <v>12.38003762458143</v>
       </c>
       <c r="D339" t="n">
-        <v>12.08568790175718</v>
+        <v>12.08568695148643</v>
       </c>
       <c r="E339" t="n">
-        <v>12.12031734686584</v>
+        <v>12.12031639387225</v>
       </c>
       <c r="F339" t="n">
         <v>5884200</v>
@@ -7332,16 +7332,16 @@
         <v>45148</v>
       </c>
       <c r="B346" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C346" t="n">
-        <v>12.09434549372545</v>
+        <v>12.09434452900206</v>
       </c>
       <c r="D346" t="n">
-        <v>11.88656799702522</v>
+        <v>11.88656704887551</v>
       </c>
       <c r="E346" t="n">
-        <v>12.01642903566675</v>
+        <v>12.01642807715848</v>
       </c>
       <c r="F346" t="n">
         <v>2835300</v>
@@ -7352,16 +7352,16 @@
         <v>45149</v>
       </c>
       <c r="B347" t="n">
-        <v>11.92119789123535</v>
+        <v>11.92119693756104</v>
       </c>
       <c r="C347" t="n">
-        <v>11.97314164454614</v>
+        <v>11.97314068671642</v>
       </c>
       <c r="D347" t="n">
-        <v>11.83462386820927</v>
+        <v>11.83462292146072</v>
       </c>
       <c r="E347" t="n">
-        <v>11.97314164454614</v>
+        <v>11.97314068671642</v>
       </c>
       <c r="F347" t="n">
         <v>2472600</v>
@@ -7392,16 +7392,16 @@
         <v>45153</v>
       </c>
       <c r="B349" t="n">
-        <v>11.86059474945068</v>
+        <v>11.860595703125</v>
       </c>
       <c r="C349" t="n">
-        <v>11.9991125141623</v>
+        <v>11.99911347897441</v>
       </c>
       <c r="D349" t="n">
-        <v>11.85193718274846</v>
+        <v>11.85193813572664</v>
       </c>
       <c r="E349" t="n">
-        <v>11.91253932403304</v>
+        <v>11.91254028188406</v>
       </c>
       <c r="F349" t="n">
         <v>2713800</v>
@@ -7452,16 +7452,16 @@
         <v>45156</v>
       </c>
       <c r="B352" t="n">
-        <v>11.77402114868164</v>
+        <v>11.77402210235596</v>
       </c>
       <c r="C352" t="n">
-        <v>11.80865058865178</v>
+        <v>11.80865154513102</v>
       </c>
       <c r="D352" t="n">
-        <v>11.65281769597066</v>
+        <v>11.65281863982772</v>
       </c>
       <c r="E352" t="n">
-        <v>11.71341900951066</v>
+        <v>11.71341995827632</v>
       </c>
       <c r="F352" t="n">
         <v>3061800</v>
@@ -7512,16 +7512,16 @@
         <v>45161</v>
       </c>
       <c r="B355" t="n">
-        <v>11.87790966033936</v>
+        <v>11.87791061401367</v>
       </c>
       <c r="C355" t="n">
-        <v>11.89522396778845</v>
+        <v>11.89522492285292</v>
       </c>
       <c r="D355" t="n">
-        <v>11.79133564620093</v>
+        <v>11.79133659292425</v>
       </c>
       <c r="E355" t="n">
-        <v>11.86059452725928</v>
+        <v>11.86059547954337</v>
       </c>
       <c r="F355" t="n">
         <v>2615000</v>
@@ -7532,16 +7532,16 @@
         <v>45162</v>
       </c>
       <c r="B356" t="n">
-        <v>11.97314071655273</v>
+        <v>11.97314167022705</v>
       </c>
       <c r="C356" t="n">
-        <v>11.99911259119515</v>
+        <v>11.99911354693815</v>
       </c>
       <c r="D356" t="n">
-        <v>11.89522426699448</v>
+        <v>11.89522521446267</v>
       </c>
       <c r="E356" t="n">
-        <v>11.90388183375229</v>
+        <v>11.90388278191006</v>
       </c>
       <c r="F356" t="n">
         <v>2322800</v>
@@ -7572,16 +7572,16 @@
         <v>45166</v>
       </c>
       <c r="B358" t="n">
-        <v>11.9644832611084</v>
+        <v>11.96448421478271</v>
       </c>
       <c r="C358" t="n">
-        <v>11.9991127028308</v>
+        <v>11.99911365926539</v>
       </c>
       <c r="D358" t="n">
-        <v>11.8432806278955</v>
+        <v>11.84328157190891</v>
       </c>
       <c r="E358" t="n">
-        <v>11.95582651990106</v>
+        <v>11.95582747288536</v>
       </c>
       <c r="F358" t="n">
         <v>2184700</v>
@@ -7612,16 +7612,16 @@
         <v>45168</v>
       </c>
       <c r="B360" t="n">
-        <v>12.11165809631348</v>
+        <v>12.11165904998779</v>
       </c>
       <c r="C360" t="n">
-        <v>12.19823210987155</v>
+        <v>12.19823307036272</v>
       </c>
       <c r="D360" t="n">
-        <v>12.05971434868342</v>
+        <v>12.05971529826767</v>
       </c>
       <c r="E360" t="n">
-        <v>12.17226023605652</v>
+        <v>12.17226119450266</v>
       </c>
       <c r="F360" t="n">
         <v>1998700</v>
@@ -7672,16 +7672,16 @@
         <v>45173</v>
       </c>
       <c r="B363" t="n">
-        <v>12.01642894744873</v>
+        <v>12.01642799377441</v>
       </c>
       <c r="C363" t="n">
-        <v>12.05105839237269</v>
+        <v>12.05105743595003</v>
       </c>
       <c r="D363" t="n">
-        <v>11.81730901991265</v>
+        <v>11.81730808204133</v>
       </c>
       <c r="E363" t="n">
-        <v>12.05105839237269</v>
+        <v>12.05105743595003</v>
       </c>
       <c r="F363" t="n">
         <v>2040600</v>
@@ -7692,16 +7692,16 @@
         <v>45174</v>
       </c>
       <c r="B364" t="n">
-        <v>11.92119789123535</v>
+        <v>11.92119693756104</v>
       </c>
       <c r="C364" t="n">
-        <v>12.06837240936998</v>
+        <v>12.06837144392197</v>
       </c>
       <c r="D364" t="n">
-        <v>11.91254032380653</v>
+        <v>11.9125393708248</v>
       </c>
       <c r="E364" t="n">
-        <v>12.04240053271458</v>
+        <v>12.04239956934427</v>
       </c>
       <c r="F364" t="n">
         <v>3869600</v>
@@ -7712,16 +7712,16 @@
         <v>45175</v>
       </c>
       <c r="B365" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C365" t="n">
-        <v>12.02508660336907</v>
+        <v>12.02508564417022</v>
       </c>
       <c r="D365" t="n">
-        <v>11.81730910666884</v>
+        <v>11.81730816404367</v>
       </c>
       <c r="E365" t="n">
-        <v>11.93851257760805</v>
+        <v>11.9385116253149</v>
       </c>
       <c r="F365" t="n">
         <v>2473500</v>
@@ -7912,16 +7912,16 @@
         <v>45190</v>
       </c>
       <c r="B375" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C375" t="n">
-        <v>12.0337433454403</v>
+        <v>12.03374238555092</v>
       </c>
       <c r="D375" t="n">
-        <v>11.877911254954</v>
+        <v>11.8779103074948</v>
       </c>
       <c r="E375" t="n">
-        <v>12.02508660336907</v>
+        <v>12.02508564417022</v>
       </c>
       <c r="F375" t="n">
         <v>4405700</v>
@@ -7932,16 +7932,16 @@
         <v>45191</v>
       </c>
       <c r="B376" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C376" t="n">
-        <v>12.10300223579667</v>
+        <v>12.10300127038276</v>
       </c>
       <c r="D376" t="n">
-        <v>11.92985500990573</v>
+        <v>11.92985405830317</v>
       </c>
       <c r="E376" t="n">
-        <v>12.02508660336907</v>
+        <v>12.02508564417022</v>
       </c>
       <c r="F376" t="n">
         <v>2812600</v>
@@ -7952,16 +7952,16 @@
         <v>45194</v>
       </c>
       <c r="B377" t="n">
-        <v>11.8086519241333</v>
+        <v>11.80865097045898</v>
       </c>
       <c r="C377" t="n">
-        <v>11.97314157618643</v>
+        <v>11.97314060922783</v>
       </c>
       <c r="D377" t="n">
-        <v>11.8086519241333</v>
+        <v>11.80865097045898</v>
       </c>
       <c r="E377" t="n">
-        <v>11.95582726705872</v>
+        <v>11.95582630149842</v>
       </c>
       <c r="F377" t="n">
         <v>3691700</v>
@@ -7972,16 +7972,16 @@
         <v>45195</v>
       </c>
       <c r="B378" t="n">
-        <v>11.83462333679199</v>
+        <v>11.83462238311768</v>
       </c>
       <c r="C378" t="n">
-        <v>12.06837186745655</v>
+        <v>12.06837089494598</v>
       </c>
       <c r="D378" t="n">
-        <v>11.78267876018263</v>
+        <v>11.78267781069418</v>
       </c>
       <c r="E378" t="n">
-        <v>11.80865146130283</v>
+        <v>11.80865050972141</v>
       </c>
       <c r="F378" t="n">
         <v>7795500</v>
@@ -8072,16 +8072,16 @@
         <v>45202</v>
       </c>
       <c r="B383" t="n">
-        <v>11.8086519241333</v>
+        <v>11.80865097045898</v>
       </c>
       <c r="C383" t="n">
-        <v>11.91254025579282</v>
+        <v>11.91253929372841</v>
       </c>
       <c r="D383" t="n">
-        <v>11.75670734548801</v>
+        <v>11.75670639600877</v>
       </c>
       <c r="E383" t="n">
-        <v>11.86059567714752</v>
+        <v>11.8605947192782</v>
       </c>
       <c r="F383" t="n">
         <v>2809600</v>
@@ -8092,16 +8092,16 @@
         <v>45203</v>
       </c>
       <c r="B384" t="n">
-        <v>11.77402114868164</v>
+        <v>11.77402210235596</v>
       </c>
       <c r="C384" t="n">
-        <v>11.86059433579151</v>
+        <v>11.86059529647809</v>
       </c>
       <c r="D384" t="n">
-        <v>11.7480484494808</v>
+        <v>11.74804940105138</v>
       </c>
       <c r="E384" t="n">
-        <v>11.80865058865178</v>
+        <v>11.80865154513102</v>
       </c>
       <c r="F384" t="n">
         <v>4367600</v>
@@ -8192,16 +8192,16 @@
         <v>45210</v>
       </c>
       <c r="B389" t="n">
-        <v>12.09434509277344</v>
+        <v>12.09434413909912</v>
       </c>
       <c r="C389" t="n">
-        <v>12.18957585744859</v>
+        <v>12.18957489626505</v>
       </c>
       <c r="D389" t="n">
-        <v>12.00777106988252</v>
+        <v>12.00777012303482</v>
       </c>
       <c r="E389" t="n">
-        <v>12.09434509277344</v>
+        <v>12.09434413909912</v>
       </c>
       <c r="F389" t="n">
         <v>3458500</v>
@@ -8232,16 +8232,16 @@
         <v>45215</v>
       </c>
       <c r="B391" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="C391" t="n">
-        <v>12.12031690101054</v>
+        <v>12.12031593631109</v>
       </c>
       <c r="D391" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="E391" t="n">
-        <v>12.05971558070743</v>
+        <v>12.05971462083146</v>
       </c>
       <c r="F391" t="n">
         <v>3983600</v>
@@ -8252,16 +8252,16 @@
         <v>45216</v>
       </c>
       <c r="B392" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C392" t="n">
-        <v>12.10300223579667</v>
+        <v>12.10300127038276</v>
       </c>
       <c r="D392" t="n">
-        <v>11.88656799702522</v>
+        <v>11.88656704887551</v>
       </c>
       <c r="E392" t="n">
-        <v>11.97314202278624</v>
+        <v>11.97314106773082</v>
       </c>
       <c r="F392" t="n">
         <v>5165000</v>
@@ -8292,16 +8292,16 @@
         <v>45218</v>
       </c>
       <c r="B394" t="n">
-        <v>11.67013263702393</v>
+        <v>11.67013359069824</v>
       </c>
       <c r="C394" t="n">
-        <v>11.75670665446719</v>
+        <v>11.75670761521626</v>
       </c>
       <c r="D394" t="n">
-        <v>11.62684645393332</v>
+        <v>11.62684740407032</v>
       </c>
       <c r="E394" t="n">
-        <v>11.66147589578441</v>
+        <v>11.66147684875131</v>
       </c>
       <c r="F394" t="n">
         <v>3066300</v>
@@ -8332,16 +8332,16 @@
         <v>45222</v>
       </c>
       <c r="B396" t="n">
-        <v>11.72207832336426</v>
+        <v>11.72207736968994</v>
       </c>
       <c r="C396" t="n">
-        <v>11.90388311671755</v>
+        <v>11.90388214825212</v>
       </c>
       <c r="D396" t="n">
-        <v>11.72207832336426</v>
+        <v>11.72207736968994</v>
       </c>
       <c r="E396" t="n">
-        <v>11.77402290387853</v>
+        <v>11.77402194597815</v>
       </c>
       <c r="F396" t="n">
         <v>3068100</v>
@@ -8432,16 +8432,16 @@
         <v>45229</v>
       </c>
       <c r="B401" t="n">
-        <v>11.49698543548584</v>
+        <v>11.49698638916016</v>
       </c>
       <c r="C401" t="n">
-        <v>11.64416076985956</v>
+        <v>11.64416173574207</v>
       </c>
       <c r="D401" t="n">
-        <v>11.47101356048784</v>
+        <v>11.47101451200779</v>
       </c>
       <c r="E401" t="n">
-        <v>11.57490188611087</v>
+        <v>11.57490284624835</v>
       </c>
       <c r="F401" t="n">
         <v>4549600</v>
@@ -8492,16 +8492,16 @@
         <v>45233</v>
       </c>
       <c r="B404" t="n">
-        <v>11.9644832611084</v>
+        <v>11.96448421478271</v>
       </c>
       <c r="C404" t="n">
-        <v>12.02508540334586</v>
+        <v>12.0250863618507</v>
       </c>
       <c r="D404" t="n">
-        <v>11.65281828560679</v>
+        <v>11.65281921443867</v>
       </c>
       <c r="E404" t="n">
-        <v>11.74804904393564</v>
+        <v>11.74804998035825</v>
       </c>
       <c r="F404" t="n">
         <v>4830800</v>
@@ -8672,16 +8672,16 @@
         <v>45247</v>
       </c>
       <c r="B413" t="n">
-        <v>12.25017642974854</v>
+        <v>12.25017738342285</v>
       </c>
       <c r="C413" t="n">
-        <v>12.48392578189597</v>
+        <v>12.48392675376763</v>
       </c>
       <c r="D413" t="n">
-        <v>12.14628810400446</v>
+        <v>12.14628904959109</v>
       </c>
       <c r="E413" t="n">
-        <v>12.48392578189597</v>
+        <v>12.48392675376763</v>
       </c>
       <c r="F413" t="n">
         <v>3124800</v>
@@ -8712,16 +8712,16 @@
         <v>45251</v>
       </c>
       <c r="B415" t="n">
-        <v>11.97314071655273</v>
+        <v>11.97314167022705</v>
       </c>
       <c r="C415" t="n">
-        <v>12.09434417426901</v>
+        <v>12.09434513759732</v>
       </c>
       <c r="D415" t="n">
-        <v>11.9125394005101</v>
+        <v>11.91254034935745</v>
       </c>
       <c r="E415" t="n">
-        <v>12.0856866075112</v>
+        <v>12.08568757014993</v>
       </c>
       <c r="F415" t="n">
         <v>2713400</v>
@@ -8732,16 +8732,16 @@
         <v>45252</v>
       </c>
       <c r="B416" t="n">
-        <v>12.46661186218262</v>
+        <v>12.4666109085083</v>
       </c>
       <c r="C416" t="n">
-        <v>12.94276735410323</v>
+        <v>12.94276636400384</v>
       </c>
       <c r="D416" t="n">
-        <v>12.44063998462508</v>
+        <v>12.44063903293757</v>
       </c>
       <c r="E416" t="n">
-        <v>12.81290714068447</v>
+        <v>12.81290616051917</v>
       </c>
       <c r="F416" t="n">
         <v>20875500</v>
@@ -8752,16 +8752,16 @@
         <v>45253</v>
       </c>
       <c r="B417" t="n">
-        <v>12.56184196472168</v>
+        <v>12.561842918396</v>
       </c>
       <c r="C417" t="n">
-        <v>12.76961861177884</v>
+        <v>12.76961958122722</v>
       </c>
       <c r="D417" t="n">
-        <v>12.46661038226389</v>
+        <v>12.46661132870839</v>
       </c>
       <c r="E417" t="n">
-        <v>12.76961861177884</v>
+        <v>12.76961958122722</v>
       </c>
       <c r="F417" t="n">
         <v>9122900</v>
@@ -8812,16 +8812,16 @@
         <v>45258</v>
       </c>
       <c r="B420" t="n">
-        <v>12.6397590637207</v>
+        <v>12.63975811004639</v>
       </c>
       <c r="C420" t="n">
-        <v>12.76961926840118</v>
+        <v>12.76961830492886</v>
       </c>
       <c r="D420" t="n">
-        <v>12.57050017780698</v>
+        <v>12.57049922935827</v>
       </c>
       <c r="E420" t="n">
-        <v>12.57915691932291</v>
+        <v>12.57915597022104</v>
       </c>
       <c r="F420" t="n">
         <v>5941200</v>
@@ -8832,16 +8832,16 @@
         <v>45259</v>
       </c>
       <c r="B421" t="n">
-        <v>12.56184196472168</v>
+        <v>12.561842918396</v>
       </c>
       <c r="C421" t="n">
-        <v>12.75230347837524</v>
+        <v>12.75230444650908</v>
       </c>
       <c r="D421" t="n">
-        <v>12.56184196472168</v>
+        <v>12.561842918396</v>
       </c>
       <c r="E421" t="n">
-        <v>12.72633160390085</v>
+        <v>12.72633257006295</v>
       </c>
       <c r="F421" t="n">
         <v>5869600</v>
@@ -8872,16 +8872,16 @@
         <v>45261</v>
       </c>
       <c r="B423" t="n">
-        <v>12.86484909057617</v>
+        <v>12.86485004425049</v>
       </c>
       <c r="C423" t="n">
-        <v>12.96873741185957</v>
+        <v>12.96873837323515</v>
       </c>
       <c r="D423" t="n">
-        <v>12.70901702146657</v>
+        <v>12.70901796358902</v>
       </c>
       <c r="E423" t="n">
-        <v>12.72633132886498</v>
+        <v>12.72633227227094</v>
       </c>
       <c r="F423" t="n">
         <v>6458300</v>
@@ -8892,16 +8892,16 @@
         <v>45264</v>
       </c>
       <c r="B424" t="n">
-        <v>12.89947986602783</v>
+        <v>12.89947891235352</v>
       </c>
       <c r="C424" t="n">
-        <v>12.98605388887275</v>
+        <v>12.98605292879791</v>
       </c>
       <c r="D424" t="n">
-        <v>12.86485042201608</v>
+        <v>12.86484947090196</v>
       </c>
       <c r="E424" t="n">
-        <v>12.94276687745029</v>
+        <v>12.94276592057571</v>
       </c>
       <c r="F424" t="n">
         <v>7048400</v>
@@ -8932,16 +8932,16 @@
         <v>45266</v>
       </c>
       <c r="B426" t="n">
-        <v>13.07262706756592</v>
+        <v>13.07262802124023</v>
       </c>
       <c r="C426" t="n">
-        <v>13.2717461513678</v>
+        <v>13.27174711956826</v>
       </c>
       <c r="D426" t="n">
-        <v>13.04665436701096</v>
+        <v>13.04665531879052</v>
       </c>
       <c r="E426" t="n">
-        <v>13.21114483466828</v>
+        <v>13.21114579844774</v>
       </c>
       <c r="F426" t="n">
         <v>5861300</v>
@@ -8952,16 +8952,16 @@
         <v>45267</v>
       </c>
       <c r="B427" t="n">
-        <v>13.11591339111328</v>
+        <v>13.1159143447876</v>
       </c>
       <c r="C427" t="n">
-        <v>13.15054283325996</v>
+        <v>13.15054378945223</v>
       </c>
       <c r="D427" t="n">
-        <v>12.97739562252655</v>
+        <v>12.97739656612907</v>
       </c>
       <c r="E427" t="n">
-        <v>13.10725664979988</v>
+        <v>13.10725760284475</v>
       </c>
       <c r="F427" t="n">
         <v>6196000</v>
@@ -8972,16 +8972,16 @@
         <v>45268</v>
       </c>
       <c r="B428" t="n">
-        <v>12.92545127868652</v>
+        <v>12.92545223236084</v>
       </c>
       <c r="C428" t="n">
-        <v>13.15919979603697</v>
+        <v>13.15920076695787</v>
       </c>
       <c r="D428" t="n">
-        <v>12.86484913848894</v>
+        <v>12.86485008769187</v>
       </c>
       <c r="E428" t="n">
-        <v>13.15919979603697</v>
+        <v>13.15920076695787</v>
       </c>
       <c r="F428" t="n">
         <v>10990100</v>
@@ -9052,16 +9052,16 @@
         <v>45274</v>
       </c>
       <c r="B432" t="n">
-        <v>12.94470024108887</v>
+        <v>12.94470119476318</v>
       </c>
       <c r="C432" t="n">
-        <v>12.98319745470858</v>
+        <v>12.9831984112191</v>
       </c>
       <c r="D432" t="n">
-        <v>12.71371695937057</v>
+        <v>12.71371789602766</v>
       </c>
       <c r="E432" t="n">
-        <v>12.71371695937057</v>
+        <v>12.71371789602766</v>
       </c>
       <c r="F432" t="n">
         <v>5480800</v>
@@ -9092,16 +9092,16 @@
         <v>45278</v>
       </c>
       <c r="B434" t="n">
-        <v>12.84845733642578</v>
+        <v>12.8484582901001</v>
       </c>
       <c r="C434" t="n">
-        <v>13.0890651448394</v>
+        <v>13.08906611637279</v>
       </c>
       <c r="D434" t="n">
-        <v>12.84845733642578</v>
+        <v>12.8484582901001</v>
       </c>
       <c r="E434" t="n">
-        <v>12.983197121716</v>
+        <v>12.98319808539135</v>
       </c>
       <c r="F434" t="n">
         <v>3314300</v>
@@ -9112,16 +9112,16 @@
         <v>45279</v>
       </c>
       <c r="B435" t="n">
-        <v>12.86770629882812</v>
+        <v>12.86770534515381</v>
       </c>
       <c r="C435" t="n">
-        <v>12.94470072896945</v>
+        <v>12.94469976958878</v>
       </c>
       <c r="D435" t="n">
-        <v>12.7907118686868</v>
+        <v>12.79071092071883</v>
       </c>
       <c r="E435" t="n">
-        <v>12.87733083205729</v>
+        <v>12.87732987766966</v>
       </c>
       <c r="F435" t="n">
         <v>4780200</v>
@@ -9232,16 +9232,16 @@
         <v>45288</v>
       </c>
       <c r="B441" t="n">
-        <v>12.80996036529541</v>
+        <v>12.80996131896973</v>
       </c>
       <c r="C441" t="n">
-        <v>12.88695479201164</v>
+        <v>12.88695575141803</v>
       </c>
       <c r="D441" t="n">
-        <v>12.76183861913627</v>
+        <v>12.76183956922803</v>
       </c>
       <c r="E441" t="n">
-        <v>12.88695479201164</v>
+        <v>12.88695575141803</v>
       </c>
       <c r="F441" t="n">
         <v>3487000</v>
@@ -9332,16 +9332,16 @@
         <v>45299</v>
       </c>
       <c r="B446" t="n">
-        <v>13.01207065582275</v>
+        <v>13.01207160949707</v>
       </c>
       <c r="C446" t="n">
-        <v>13.09868869543668</v>
+        <v>13.09868965545936</v>
       </c>
       <c r="D446" t="n">
-        <v>12.88695448591916</v>
+        <v>12.88695543042352</v>
       </c>
       <c r="E446" t="n">
-        <v>12.95432437823419</v>
+        <v>12.9543253276762</v>
       </c>
       <c r="F446" t="n">
         <v>3738800</v>
@@ -9392,16 +9392,16 @@
         <v>45302</v>
       </c>
       <c r="B449" t="n">
-        <v>12.84845733642578</v>
+        <v>12.8484582901001</v>
       </c>
       <c r="C449" t="n">
-        <v>12.94469990908366</v>
+        <v>12.94470086990156</v>
       </c>
       <c r="D449" t="n">
-        <v>12.74258931330238</v>
+        <v>12.74259025911866</v>
       </c>
       <c r="E449" t="n">
-        <v>12.94469990908366</v>
+        <v>12.94470086990156</v>
       </c>
       <c r="F449" t="n">
         <v>4814200</v>
@@ -9412,16 +9412,16 @@
         <v>45303</v>
       </c>
       <c r="B450" t="n">
-        <v>12.77146434783936</v>
+        <v>12.77146339416504</v>
       </c>
       <c r="C450" t="n">
-        <v>12.88695599872818</v>
+        <v>12.88695503642984</v>
       </c>
       <c r="D450" t="n">
-        <v>12.74259074673261</v>
+        <v>12.74258979521435</v>
       </c>
       <c r="E450" t="n">
-        <v>12.84845878176524</v>
+        <v>12.84845782234157</v>
       </c>
       <c r="F450" t="n">
         <v>4041800</v>
@@ -9432,16 +9432,16 @@
         <v>45306</v>
       </c>
       <c r="B451" t="n">
-        <v>12.80996036529541</v>
+        <v>12.80996131896973</v>
       </c>
       <c r="C451" t="n">
-        <v>12.84845757865353</v>
+        <v>12.84845853519388</v>
       </c>
       <c r="D451" t="n">
-        <v>12.74258955353423</v>
+        <v>12.74259050219293</v>
       </c>
       <c r="E451" t="n">
-        <v>12.77146315193729</v>
+        <v>12.77146410274557</v>
       </c>
       <c r="F451" t="n">
         <v>1955800</v>
@@ -9492,16 +9492,16 @@
         <v>45309</v>
       </c>
       <c r="B454" t="n">
-        <v>12.55972766876221</v>
+        <v>12.55972862243652</v>
       </c>
       <c r="C454" t="n">
-        <v>12.77146279524125</v>
+        <v>12.77146376499286</v>
       </c>
       <c r="D454" t="n">
-        <v>12.51160592394707</v>
+        <v>12.51160687396745</v>
       </c>
       <c r="E454" t="n">
-        <v>12.76183826270904</v>
+        <v>12.76183923172984</v>
       </c>
       <c r="F454" t="n">
         <v>6534900</v>
@@ -9532,16 +9532,16 @@
         <v>45313</v>
       </c>
       <c r="B456" t="n">
-        <v>12.61747360229492</v>
+        <v>12.61747455596924</v>
       </c>
       <c r="C456" t="n">
-        <v>12.65597081632927</v>
+        <v>12.65597177291335</v>
       </c>
       <c r="D456" t="n">
-        <v>12.56935277313647</v>
+        <v>12.56935372317364</v>
       </c>
       <c r="E456" t="n">
-        <v>12.60784998717082</v>
+        <v>12.60785094011775</v>
       </c>
       <c r="F456" t="n">
         <v>4490300</v>
@@ -9572,16 +9572,16 @@
         <v>45315</v>
       </c>
       <c r="B458" t="n">
-        <v>12.79071235656738</v>
+        <v>12.79071140289307</v>
       </c>
       <c r="C458" t="n">
-        <v>12.82920957310646</v>
+        <v>12.82920861656179</v>
       </c>
       <c r="D458" t="n">
-        <v>12.64634802400737</v>
+        <v>12.64634708109684</v>
       </c>
       <c r="E458" t="n">
-        <v>12.6559716397576</v>
+        <v>12.65597069612954</v>
       </c>
       <c r="F458" t="n">
         <v>3333600</v>
@@ -9652,16 +9652,16 @@
         <v>45321</v>
       </c>
       <c r="B462" t="n">
-        <v>12.51160717010498</v>
+        <v>12.51160621643066</v>
       </c>
       <c r="C462" t="n">
-        <v>12.63672335194755</v>
+        <v>12.63672238873649</v>
       </c>
       <c r="D462" t="n">
-        <v>12.51160717010498</v>
+        <v>12.51160621643066</v>
       </c>
       <c r="E462" t="n">
-        <v>12.58860160233948</v>
+        <v>12.58860064279641</v>
       </c>
       <c r="F462" t="n">
         <v>3463200</v>
@@ -9672,16 +9672,16 @@
         <v>45322</v>
       </c>
       <c r="B463" t="n">
-        <v>12.68484401702881</v>
+        <v>12.68484497070312</v>
       </c>
       <c r="C463" t="n">
-        <v>12.79071112283833</v>
+        <v>12.79071208447197</v>
       </c>
       <c r="D463" t="n">
-        <v>12.53085516572552</v>
+        <v>12.53085610782262</v>
       </c>
       <c r="E463" t="n">
-        <v>12.57897599337333</v>
+        <v>12.57897693908826</v>
       </c>
       <c r="F463" t="n">
         <v>3755000</v>
@@ -9812,16 +9812,16 @@
         <v>45331</v>
       </c>
       <c r="B470" t="n">
-        <v>12.48273468017578</v>
+        <v>12.48273372650146</v>
       </c>
       <c r="C470" t="n">
-        <v>12.62709901338253</v>
+        <v>12.62709804867886</v>
       </c>
       <c r="D470" t="n">
-        <v>12.36724303004117</v>
+        <v>12.36724208519036</v>
       </c>
       <c r="E470" t="n">
-        <v>12.36724303004117</v>
+        <v>12.36724208519036</v>
       </c>
       <c r="F470" t="n">
         <v>4943200</v>
@@ -9852,16 +9852,16 @@
         <v>45337</v>
       </c>
       <c r="B472" t="n">
-        <v>12.50198268890381</v>
+        <v>12.50198173522949</v>
       </c>
       <c r="C472" t="n">
-        <v>12.58860165499141</v>
+        <v>12.58860069470964</v>
       </c>
       <c r="D472" t="n">
-        <v>12.4153637228162</v>
+        <v>12.41536277574934</v>
       </c>
       <c r="E472" t="n">
-        <v>12.46348547262554</v>
+        <v>12.46348452188787</v>
       </c>
       <c r="F472" t="n">
         <v>4740900</v>
@@ -9892,16 +9892,16 @@
         <v>45341</v>
       </c>
       <c r="B474" t="n">
-        <v>12.77146434783936</v>
+        <v>12.77146339416504</v>
       </c>
       <c r="C474" t="n">
-        <v>12.85808239762144</v>
+        <v>12.85808143747915</v>
       </c>
       <c r="D474" t="n">
-        <v>12.53085651235945</v>
+        <v>12.53085557665187</v>
       </c>
       <c r="E474" t="n">
-        <v>12.54048012821565</v>
+        <v>12.54047919178945</v>
       </c>
       <c r="F474" t="n">
         <v>4786000</v>
@@ -9972,16 +9972,16 @@
         <v>45345</v>
       </c>
       <c r="B478" t="n">
-        <v>12.41536331176758</v>
+        <v>12.41536235809326</v>
       </c>
       <c r="C478" t="n">
-        <v>12.55010402320352</v>
+        <v>12.55010305917923</v>
       </c>
       <c r="D478" t="n">
-        <v>12.41536331176758</v>
+        <v>12.41536235809326</v>
       </c>
       <c r="E478" t="n">
-        <v>12.52123134141225</v>
+        <v>12.52123037960578</v>
       </c>
       <c r="F478" t="n">
         <v>4574300</v>
@@ -9992,16 +9992,16 @@
         <v>45348</v>
       </c>
       <c r="B479" t="n">
-        <v>12.35761737823486</v>
+        <v>12.35761833190918</v>
       </c>
       <c r="C479" t="n">
-        <v>12.48273355068785</v>
+        <v>12.48273451401776</v>
       </c>
       <c r="D479" t="n">
-        <v>12.3383683126978</v>
+        <v>12.33836926488661</v>
       </c>
       <c r="E479" t="n">
-        <v>12.45385995238227</v>
+        <v>12.45386091348391</v>
       </c>
       <c r="F479" t="n">
         <v>6964500</v>
@@ -22149,102 +22149,102 @@
     </row>
     <row r="1087">
       <c r="A1087" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B1087" t="n">
-        <v>10.97999954223633</v>
+        <v>11.19999980926514</v>
       </c>
       <c r="C1087" t="n">
-        <v>11.27999973297119</v>
+        <v>11.21000003814697</v>
       </c>
       <c r="D1087" t="n">
-        <v>10.90999984741211</v>
+        <v>10.84000015258789</v>
       </c>
       <c r="E1087" t="n">
-        <v>11.19999980926514</v>
+        <v>11.03999996185303</v>
       </c>
       <c r="F1087" t="n">
-        <v>5442500</v>
+        <v>4621900</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B1088" t="n">
-        <v>11.19999980926514</v>
+        <v>11.27999973297119</v>
       </c>
       <c r="C1088" t="n">
-        <v>11.21000003814697</v>
+        <v>11.56999969482422</v>
       </c>
       <c r="D1088" t="n">
-        <v>10.84000015258789</v>
+        <v>11.13000011444092</v>
       </c>
       <c r="E1088" t="n">
-        <v>11.03999996185303</v>
+        <v>11.32999992370605</v>
       </c>
       <c r="F1088" t="n">
-        <v>4621900</v>
+        <v>4289500</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B1089" t="n">
-        <v>11.27999973297119</v>
+        <v>11.15999984741211</v>
       </c>
       <c r="C1089" t="n">
-        <v>11.56999969482422</v>
+        <v>11.55000019073486</v>
       </c>
       <c r="D1089" t="n">
-        <v>11.13000011444092</v>
+        <v>11.07999992370605</v>
       </c>
       <c r="E1089" t="n">
-        <v>11.32999992370605</v>
+        <v>11.31999969482422</v>
       </c>
       <c r="F1089" t="n">
-        <v>4289500</v>
+        <v>5192700</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B1090" t="n">
-        <v>11.15999984741211</v>
+        <v>10.97999954223633</v>
       </c>
       <c r="C1090" t="n">
-        <v>11.55000019073486</v>
+        <v>11.14000034332275</v>
       </c>
       <c r="D1090" t="n">
-        <v>11.07999992370605</v>
+        <v>10.61999988555908</v>
       </c>
       <c r="E1090" t="n">
-        <v>11.31999969482422</v>
+        <v>11.14000034332275</v>
       </c>
       <c r="F1090" t="n">
-        <v>5192700</v>
+        <v>5195300</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B1091" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="C1091" t="n">
         <v>10.98</v>
       </c>
-      <c r="C1091" t="n">
-        <v>11.14</v>
-      </c>
       <c r="D1091" t="n">
-        <v>10.62</v>
+        <v>10.55</v>
       </c>
       <c r="E1091" t="n">
-        <v>11.14</v>
+        <v>10.98</v>
       </c>
       <c r="F1091" t="n">
-        <v>5195300</v>
+        <v>4285100</v>
       </c>
     </row>
   </sheetData>

--- a/database/AURE3.xlsx
+++ b/database/AURE3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1091"/>
+  <dimension ref="A1:F1093"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44648</v>
       </c>
       <c r="B2" t="n">
-        <v>12.75723171234131</v>
+        <v>12.75723266601562</v>
       </c>
       <c r="C2" t="n">
-        <v>13.06838341582507</v>
+        <v>13.06838439275972</v>
       </c>
       <c r="D2" t="n">
-        <v>12.02602483823237</v>
+        <v>12.02602573724489</v>
       </c>
       <c r="E2" t="n">
-        <v>13.06838341582507</v>
+        <v>13.06838439275972</v>
       </c>
       <c r="F2" t="n">
         <v>5237900</v>
@@ -472,16 +472,16 @@
         <v>44649</v>
       </c>
       <c r="B3" t="n">
-        <v>12.91281032562256</v>
+        <v>12.91280841827393</v>
       </c>
       <c r="C3" t="n">
-        <v>13.21618309850878</v>
+        <v>13.21618114634902</v>
       </c>
       <c r="D3" t="n">
-        <v>12.6172150483126</v>
+        <v>12.61721318462629</v>
       </c>
       <c r="E3" t="n">
-        <v>12.74945472843788</v>
+        <v>12.74945284521847</v>
       </c>
       <c r="F3" t="n">
         <v>4714100</v>
@@ -512,16 +512,16 @@
         <v>44651</v>
       </c>
       <c r="B5" t="n">
-        <v>12.43830108642578</v>
+        <v>12.4383020401001</v>
       </c>
       <c r="C5" t="n">
-        <v>12.82724108844168</v>
+        <v>12.82724207193696</v>
       </c>
       <c r="D5" t="n">
-        <v>12.05714006249281</v>
+        <v>12.05714098694259</v>
       </c>
       <c r="E5" t="n">
-        <v>12.4149648940212</v>
+        <v>12.41496584590627</v>
       </c>
       <c r="F5" t="n">
         <v>3876100</v>
@@ -532,16 +532,16 @@
         <v>44652</v>
       </c>
       <c r="B6" t="n">
-        <v>12.51609039306641</v>
+        <v>12.51608943939209</v>
       </c>
       <c r="C6" t="n">
-        <v>12.95170281502629</v>
+        <v>12.95170182816011</v>
       </c>
       <c r="D6" t="n">
-        <v>12.31384139766291</v>
+        <v>12.31384045939913</v>
       </c>
       <c r="E6" t="n">
-        <v>12.43830208965145</v>
+        <v>12.43830114190428</v>
       </c>
       <c r="F6" t="n">
         <v>4252000</v>
@@ -552,16 +552,16 @@
         <v>44655</v>
       </c>
       <c r="B7" t="n">
-        <v>12.42274379730225</v>
+        <v>12.42274475097656</v>
       </c>
       <c r="C7" t="n">
-        <v>12.73389624214791</v>
+        <v>12.7338972197089</v>
       </c>
       <c r="D7" t="n">
-        <v>12.3371765225937</v>
+        <v>12.33717746969916</v>
       </c>
       <c r="E7" t="n">
-        <v>12.54720373665866</v>
+        <v>12.54720469988757</v>
       </c>
       <c r="F7" t="n">
         <v>2842400</v>
@@ -612,16 +612,16 @@
         <v>44658</v>
       </c>
       <c r="B10" t="n">
-        <v>12.44608020782471</v>
+        <v>12.44608116149902</v>
       </c>
       <c r="C10" t="n">
-        <v>12.71833850910855</v>
+        <v>12.71833948364451</v>
       </c>
       <c r="D10" t="n">
-        <v>12.20493707738666</v>
+        <v>12.20493801258351</v>
       </c>
       <c r="E10" t="n">
-        <v>12.32161952444153</v>
+        <v>12.32162046857911</v>
       </c>
       <c r="F10" t="n">
         <v>3223900</v>
@@ -632,16 +632,16 @@
         <v>44659</v>
       </c>
       <c r="B11" t="n">
-        <v>12.60943508148193</v>
+        <v>12.60943603515625</v>
       </c>
       <c r="C11" t="n">
-        <v>12.75723270856147</v>
+        <v>12.75723367341398</v>
       </c>
       <c r="D11" t="n">
-        <v>12.33717750513392</v>
+        <v>12.3371784382169</v>
       </c>
       <c r="E11" t="n">
-        <v>12.33717750513392</v>
+        <v>12.3371784382169</v>
       </c>
       <c r="F11" t="n">
         <v>2049800</v>
@@ -652,16 +652,16 @@
         <v>44662</v>
       </c>
       <c r="B12" t="n">
-        <v>12.37607097625732</v>
+        <v>12.37607192993164</v>
       </c>
       <c r="C12" t="n">
-        <v>12.89725064802586</v>
+        <v>12.8972516418612</v>
       </c>
       <c r="D12" t="n">
-        <v>12.37607097625732</v>
+        <v>12.37607192993164</v>
       </c>
       <c r="E12" t="n">
-        <v>12.59387791557601</v>
+        <v>12.59387888603408</v>
       </c>
       <c r="F12" t="n">
         <v>2119500</v>
@@ -672,16 +672,16 @@
         <v>44663</v>
       </c>
       <c r="B13" t="n">
-        <v>12.2438325881958</v>
+        <v>12.24383163452148</v>
       </c>
       <c r="C13" t="n">
-        <v>12.64055161698694</v>
+        <v>12.64055063241211</v>
       </c>
       <c r="D13" t="n">
-        <v>12.2127174138893</v>
+        <v>12.21271646263855</v>
       </c>
       <c r="E13" t="n">
-        <v>12.48497500361014</v>
+        <v>12.4849740311532</v>
       </c>
       <c r="F13" t="n">
         <v>2267700</v>
@@ -692,16 +692,16 @@
         <v>44664</v>
       </c>
       <c r="B14" t="n">
-        <v>12.10381412506104</v>
+        <v>12.10381317138672</v>
       </c>
       <c r="C14" t="n">
-        <v>12.55498376109398</v>
+        <v>12.55498277187146</v>
       </c>
       <c r="D14" t="n">
-        <v>12.08825616769219</v>
+        <v>12.0882552152437</v>
       </c>
       <c r="E14" t="n">
-        <v>12.39162965978653</v>
+        <v>12.39162868343488</v>
       </c>
       <c r="F14" t="n">
         <v>4421300</v>
@@ -712,16 +712,16 @@
         <v>44665</v>
       </c>
       <c r="B15" t="n">
-        <v>12.11159133911133</v>
+        <v>12.11159229278564</v>
       </c>
       <c r="C15" t="n">
-        <v>12.36829167926575</v>
+        <v>12.36829265315281</v>
       </c>
       <c r="D15" t="n">
-        <v>12.0493609985796</v>
+        <v>12.04936194735386</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08047616884546</v>
+        <v>12.08047712006975</v>
       </c>
       <c r="F15" t="n">
         <v>2077400</v>
@@ -752,16 +752,16 @@
         <v>44670</v>
       </c>
       <c r="B17" t="n">
-        <v>12.10381412506104</v>
+        <v>12.10381317138672</v>
       </c>
       <c r="C17" t="n">
-        <v>12.60165763320052</v>
+        <v>12.60165664030051</v>
       </c>
       <c r="D17" t="n">
-        <v>12.00268962769625</v>
+        <v>12.00268868198966</v>
       </c>
       <c r="E17" t="n">
-        <v>12.4383020482046</v>
+        <v>12.43830106817557</v>
       </c>
       <c r="F17" t="n">
         <v>3118100</v>
@@ -772,16 +772,16 @@
         <v>44671</v>
       </c>
       <c r="B18" t="n">
-        <v>12.05714130401611</v>
+        <v>12.0571403503418</v>
       </c>
       <c r="C18" t="n">
-        <v>12.21271717247328</v>
+        <v>12.2127162064935</v>
       </c>
       <c r="D18" t="n">
-        <v>11.95601680405789</v>
+        <v>11.95601585838214</v>
       </c>
       <c r="E18" t="n">
-        <v>12.07269926178396</v>
+        <v>12.07269830687907</v>
       </c>
       <c r="F18" t="n">
         <v>2798400</v>
@@ -792,16 +792,16 @@
         <v>44673</v>
       </c>
       <c r="B19" t="n">
-        <v>12.22049713134766</v>
+        <v>12.22049617767334</v>
       </c>
       <c r="C19" t="n">
-        <v>12.33717885658645</v>
+        <v>12.33717789380641</v>
       </c>
       <c r="D19" t="n">
-        <v>11.80044188190597</v>
+        <v>11.80044096101231</v>
       </c>
       <c r="E19" t="n">
-        <v>12.01824811521239</v>
+        <v>12.01824717732137</v>
       </c>
       <c r="F19" t="n">
         <v>11382300</v>
@@ -812,16 +812,16 @@
         <v>44676</v>
       </c>
       <c r="B20" t="n">
-        <v>12.39162921905518</v>
+        <v>12.39163017272949</v>
       </c>
       <c r="C20" t="n">
-        <v>12.39162921905518</v>
+        <v>12.39163017272949</v>
       </c>
       <c r="D20" t="n">
-        <v>11.90156470703017</v>
+        <v>11.90156562298855</v>
       </c>
       <c r="E20" t="n">
-        <v>12.11937090953766</v>
+        <v>12.11937184225865</v>
       </c>
       <c r="F20" t="n">
         <v>2683100</v>
@@ -852,16 +852,16 @@
         <v>44678</v>
       </c>
       <c r="B22" t="n">
-        <v>12.05714130401611</v>
+        <v>12.0571403503418</v>
       </c>
       <c r="C22" t="n">
-        <v>12.06492028290003</v>
+        <v>12.06491932861043</v>
       </c>
       <c r="D22" t="n">
-        <v>11.83155610929216</v>
+        <v>11.83155517346078</v>
       </c>
       <c r="E22" t="n">
-        <v>12.04936232513219</v>
+        <v>12.04936137207316</v>
       </c>
       <c r="F22" t="n">
         <v>2401400</v>
@@ -972,16 +972,16 @@
         <v>44686</v>
       </c>
       <c r="B28" t="n">
-        <v>11.28714656829834</v>
+        <v>11.28714847564697</v>
       </c>
       <c r="C28" t="n">
-        <v>11.62395965090248</v>
+        <v>11.62396161516718</v>
       </c>
       <c r="D28" t="n">
-        <v>11.14615490637113</v>
+        <v>11.14615678989441</v>
       </c>
       <c r="E28" t="n">
-        <v>11.61612661479554</v>
+        <v>11.61612857773658</v>
       </c>
       <c r="F28" t="n">
         <v>3065700</v>
@@ -1052,16 +1052,16 @@
         <v>44692</v>
       </c>
       <c r="B32" t="n">
-        <v>11.06782722473145</v>
+        <v>11.06782817840576</v>
       </c>
       <c r="C32" t="n">
-        <v>11.38897424784334</v>
+        <v>11.38897522918973</v>
       </c>
       <c r="D32" t="n">
-        <v>11.01299746380974</v>
+        <v>11.01299841275958</v>
       </c>
       <c r="E32" t="n">
-        <v>11.12265698565314</v>
+        <v>11.12265794405194</v>
       </c>
       <c r="F32" t="n">
         <v>1595100</v>
@@ -1072,16 +1072,16 @@
         <v>44693</v>
       </c>
       <c r="B33" t="n">
-        <v>11.15398788452148</v>
+        <v>11.1539888381958</v>
       </c>
       <c r="C33" t="n">
-        <v>11.27931347358361</v>
+        <v>11.27931443797336</v>
       </c>
       <c r="D33" t="n">
-        <v>10.85633923699921</v>
+        <v>10.85634016522435</v>
       </c>
       <c r="E33" t="n">
-        <v>10.99733089819382</v>
+        <v>10.99733183847385</v>
       </c>
       <c r="F33" t="n">
         <v>1884700</v>
@@ -1092,16 +1092,16 @@
         <v>44694</v>
       </c>
       <c r="B34" t="n">
-        <v>11.32631301879883</v>
+        <v>11.32631206512451</v>
       </c>
       <c r="C34" t="n">
-        <v>11.38114278731251</v>
+        <v>11.38114182902154</v>
       </c>
       <c r="D34" t="n">
-        <v>11.11482548824677</v>
+        <v>11.11482455237968</v>
       </c>
       <c r="E34" t="n">
-        <v>11.18532133176413</v>
+        <v>11.18532038996129</v>
       </c>
       <c r="F34" t="n">
         <v>1333500</v>
@@ -1132,16 +1132,16 @@
         <v>44698</v>
       </c>
       <c r="B36" t="n">
-        <v>11.56129837036133</v>
+        <v>11.56129741668701</v>
       </c>
       <c r="C36" t="n">
-        <v>11.74928677955431</v>
+        <v>11.74928581037311</v>
       </c>
       <c r="D36" t="n">
-        <v>11.3576438869025</v>
+        <v>11.35764295002734</v>
       </c>
       <c r="E36" t="n">
-        <v>11.3576438869025</v>
+        <v>11.35764295002734</v>
       </c>
       <c r="F36" t="n">
         <v>1389700</v>
@@ -1172,16 +1172,16 @@
         <v>44700</v>
       </c>
       <c r="B38" t="n">
-        <v>11.22448539733887</v>
+        <v>11.22448444366455</v>
       </c>
       <c r="C38" t="n">
-        <v>11.25581679930005</v>
+        <v>11.25581584296371</v>
       </c>
       <c r="D38" t="n">
-        <v>10.97383418164937</v>
+        <v>10.97383324927132</v>
       </c>
       <c r="E38" t="n">
-        <v>11.11482511697494</v>
+        <v>11.11482417261777</v>
       </c>
       <c r="F38" t="n">
         <v>2127500</v>
@@ -1212,16 +1212,16 @@
         <v>44704</v>
       </c>
       <c r="B40" t="n">
-        <v>11.20882034301758</v>
+        <v>11.20881843566895</v>
       </c>
       <c r="C40" t="n">
-        <v>11.4359731995218</v>
+        <v>11.43597125351971</v>
       </c>
       <c r="D40" t="n">
-        <v>11.16182286543069</v>
+        <v>11.16182096607938</v>
       </c>
       <c r="E40" t="n">
-        <v>11.18532123072435</v>
+        <v>11.18531932737445</v>
       </c>
       <c r="F40" t="n">
         <v>1184600</v>
@@ -1252,16 +1252,16 @@
         <v>44706</v>
       </c>
       <c r="B42" t="n">
-        <v>11.32631301879883</v>
+        <v>11.32631206512451</v>
       </c>
       <c r="C42" t="n">
-        <v>11.39680886231618</v>
+        <v>11.39680790270612</v>
       </c>
       <c r="D42" t="n">
-        <v>11.13832460075227</v>
+        <v>11.13832366290656</v>
       </c>
       <c r="E42" t="n">
-        <v>11.17748904126186</v>
+        <v>11.17748810011851</v>
       </c>
       <c r="F42" t="n">
         <v>821700</v>
@@ -1272,16 +1272,16 @@
         <v>44707</v>
       </c>
       <c r="B43" t="n">
-        <v>11.25581645965576</v>
+        <v>11.25581741333008</v>
       </c>
       <c r="C43" t="n">
-        <v>11.44380486575034</v>
+        <v>11.44380583535239</v>
       </c>
       <c r="D43" t="n">
-        <v>11.20881973163188</v>
+        <v>11.20882068132429</v>
       </c>
       <c r="E43" t="n">
-        <v>11.33414533569493</v>
+        <v>11.33414629600583</v>
       </c>
       <c r="F43" t="n">
         <v>1248800</v>
@@ -1292,16 +1292,16 @@
         <v>44708</v>
       </c>
       <c r="B44" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C44" t="n">
-        <v>11.42030698171035</v>
+        <v>11.42030600182509</v>
       </c>
       <c r="D44" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="E44" t="n">
-        <v>11.26364997004757</v>
+        <v>11.26364900360379</v>
       </c>
       <c r="F44" t="n">
         <v>2224600</v>
@@ -1312,16 +1312,16 @@
         <v>44711</v>
       </c>
       <c r="B45" t="n">
-        <v>11.09916019439697</v>
+        <v>11.09915924072266</v>
       </c>
       <c r="C45" t="n">
-        <v>11.27148328496971</v>
+        <v>11.27148231648886</v>
       </c>
       <c r="D45" t="n">
-        <v>11.02866435066269</v>
+        <v>11.0286634030456</v>
       </c>
       <c r="E45" t="n">
-        <v>11.15398996307938</v>
+        <v>11.15398900469392</v>
       </c>
       <c r="F45" t="n">
         <v>1940200</v>
@@ -1332,16 +1332,16 @@
         <v>44712</v>
       </c>
       <c r="B46" t="n">
-        <v>10.93466854095459</v>
+        <v>10.93467044830322</v>
       </c>
       <c r="C46" t="n">
-        <v>11.2088188382412</v>
+        <v>11.20882079341023</v>
       </c>
       <c r="D46" t="n">
-        <v>10.82500827264005</v>
+        <v>10.8250101608605</v>
       </c>
       <c r="E46" t="n">
-        <v>11.16965440334319</v>
+        <v>11.16965635168072</v>
       </c>
       <c r="F46" t="n">
         <v>9431500</v>
@@ -1352,16 +1352,16 @@
         <v>44713</v>
       </c>
       <c r="B47" t="n">
-        <v>10.7310152053833</v>
+        <v>10.73101425170898</v>
       </c>
       <c r="C47" t="n">
-        <v>10.94250272786947</v>
+        <v>10.94250175540008</v>
       </c>
       <c r="D47" t="n">
-        <v>10.66051936455458</v>
+        <v>10.66051841714529</v>
       </c>
       <c r="E47" t="n">
-        <v>10.94250272786947</v>
+        <v>10.94250175540008</v>
       </c>
       <c r="F47" t="n">
         <v>6323900</v>
@@ -1392,16 +1392,16 @@
         <v>44715</v>
       </c>
       <c r="B49" t="n">
-        <v>10.77801132202148</v>
+        <v>10.7780122756958</v>
       </c>
       <c r="C49" t="n">
-        <v>10.85633944317314</v>
+        <v>10.85634040377818</v>
       </c>
       <c r="D49" t="n">
-        <v>10.62135433271873</v>
+        <v>10.62135527253152</v>
       </c>
       <c r="E49" t="n">
-        <v>10.78584435823648</v>
+        <v>10.78584531260389</v>
       </c>
       <c r="F49" t="n">
         <v>2685000</v>
@@ -1472,16 +1472,16 @@
         <v>44721</v>
       </c>
       <c r="B53" t="n">
-        <v>11.03649711608887</v>
+        <v>11.03649520874023</v>
       </c>
       <c r="C53" t="n">
-        <v>11.09915992075229</v>
+        <v>11.09915800257415</v>
       </c>
       <c r="D53" t="n">
-        <v>10.86417402976468</v>
+        <v>10.86417215219725</v>
       </c>
       <c r="E53" t="n">
-        <v>11.06782851842058</v>
+        <v>11.06782660565719</v>
       </c>
       <c r="F53" t="n">
         <v>1365200</v>
@@ -1632,16 +1632,16 @@
         <v>44734</v>
       </c>
       <c r="B61" t="n">
-        <v>10.73884773254395</v>
+        <v>10.73884868621826</v>
       </c>
       <c r="C61" t="n">
-        <v>10.83284193351813</v>
+        <v>10.8328428955397</v>
       </c>
       <c r="D61" t="n">
-        <v>10.43336601912821</v>
+        <v>10.43336694567391</v>
       </c>
       <c r="E61" t="n">
-        <v>10.53519325693346</v>
+        <v>10.53519419252203</v>
       </c>
       <c r="F61" t="n">
         <v>1196200</v>
@@ -1672,16 +1672,16 @@
         <v>44736</v>
       </c>
       <c r="B63" t="n">
-        <v>10.48819732666016</v>
+        <v>10.48819637298584</v>
       </c>
       <c r="C63" t="n">
-        <v>10.70751714559343</v>
+        <v>10.70751617197673</v>
       </c>
       <c r="D63" t="n">
-        <v>10.42553452125065</v>
+        <v>10.42553357327416</v>
       </c>
       <c r="E63" t="n">
-        <v>10.70751714559343</v>
+        <v>10.70751617197673</v>
       </c>
       <c r="F63" t="n">
         <v>807500</v>
@@ -1752,16 +1752,16 @@
         <v>44742</v>
       </c>
       <c r="B67" t="n">
-        <v>10.66835117340088</v>
+        <v>10.6683521270752</v>
       </c>
       <c r="C67" t="n">
-        <v>10.84850727333101</v>
+        <v>10.84850824310999</v>
       </c>
       <c r="D67" t="n">
-        <v>10.48819582047021</v>
+        <v>10.48819675803992</v>
       </c>
       <c r="E67" t="n">
-        <v>10.53519254427845</v>
+        <v>10.53519348604933</v>
       </c>
       <c r="F67" t="n">
         <v>2634600</v>
@@ -1792,16 +1792,16 @@
         <v>44746</v>
       </c>
       <c r="B69" t="n">
-        <v>10.65268611907959</v>
+        <v>10.65268707275391</v>
       </c>
       <c r="C69" t="n">
-        <v>10.78584475159305</v>
+        <v>10.7858457171883</v>
       </c>
       <c r="D69" t="n">
-        <v>10.52735977606733</v>
+        <v>10.52736071852189</v>
       </c>
       <c r="E69" t="n">
-        <v>10.68401751808279</v>
+        <v>10.68401847456203</v>
       </c>
       <c r="F69" t="n">
         <v>1437100</v>
@@ -1812,16 +1812,16 @@
         <v>44747</v>
       </c>
       <c r="B70" t="n">
-        <v>10.62135601043701</v>
+        <v>10.6213550567627</v>
       </c>
       <c r="C70" t="n">
-        <v>10.62135601043701</v>
+        <v>10.6213550567627</v>
       </c>
       <c r="D70" t="n">
-        <v>10.49602965219918</v>
+        <v>10.49602870977771</v>
       </c>
       <c r="E70" t="n">
-        <v>10.58219157017516</v>
+        <v>10.58219062001736</v>
       </c>
       <c r="F70" t="n">
         <v>1722600</v>
@@ -1852,16 +1852,16 @@
         <v>44749</v>
       </c>
       <c r="B72" t="n">
-        <v>11.0443286895752</v>
+        <v>11.04433059692383</v>
       </c>
       <c r="C72" t="n">
-        <v>11.16182124599643</v>
+        <v>11.16182317363595</v>
       </c>
       <c r="D72" t="n">
-        <v>10.62135444065952</v>
+        <v>10.62135627496076</v>
       </c>
       <c r="E72" t="n">
-        <v>10.78584446784892</v>
+        <v>10.78584633055749</v>
       </c>
       <c r="F72" t="n">
         <v>2931100</v>
@@ -1872,16 +1872,16 @@
         <v>44750</v>
       </c>
       <c r="B73" t="n">
-        <v>11.15398788452148</v>
+        <v>11.1539888381958</v>
       </c>
       <c r="C73" t="n">
-        <v>11.31064487084914</v>
+        <v>11.31064583791775</v>
       </c>
       <c r="D73" t="n">
-        <v>11.00516393426007</v>
+        <v>11.00516487520982</v>
       </c>
       <c r="E73" t="n">
-        <v>11.00516393426007</v>
+        <v>11.00516487520982</v>
       </c>
       <c r="F73" t="n">
         <v>1922000</v>
@@ -1952,16 +1952,16 @@
         <v>44756</v>
       </c>
       <c r="B77" t="n">
-        <v>10.91117000579834</v>
+        <v>10.91117095947266</v>
       </c>
       <c r="C77" t="n">
-        <v>11.1774872624825</v>
+        <v>11.17748823943387</v>
       </c>
       <c r="D77" t="n">
-        <v>10.84850720975495</v>
+        <v>10.84850815795232</v>
       </c>
       <c r="E77" t="n">
-        <v>11.04432863414042</v>
+        <v>11.04432959945326</v>
       </c>
       <c r="F77" t="n">
         <v>1968500</v>
@@ -1972,16 +1972,16 @@
         <v>44757</v>
       </c>
       <c r="B78" t="n">
-        <v>10.80934429168701</v>
+        <v>10.8093433380127</v>
       </c>
       <c r="C78" t="n">
-        <v>10.98166737847755</v>
+        <v>10.98166640959971</v>
       </c>
       <c r="D78" t="n">
-        <v>10.60568980247997</v>
+        <v>10.60568886677345</v>
       </c>
       <c r="E78" t="n">
-        <v>10.97383434112354</v>
+        <v>10.97383337293678</v>
       </c>
       <c r="F78" t="n">
         <v>2342600</v>
@@ -1992,16 +1992,16 @@
         <v>44760</v>
       </c>
       <c r="B79" t="n">
-        <v>10.7310152053833</v>
+        <v>10.73101425170898</v>
       </c>
       <c r="C79" t="n">
-        <v>11.0051655314951</v>
+        <v>11.00516455345681</v>
       </c>
       <c r="D79" t="n">
-        <v>10.5900242707254</v>
+        <v>10.59002332958107</v>
       </c>
       <c r="E79" t="n">
-        <v>10.80934408341511</v>
+        <v>10.80934312277964</v>
       </c>
       <c r="F79" t="n">
         <v>1463400</v>
@@ -2012,16 +2012,16 @@
         <v>44761</v>
       </c>
       <c r="B80" t="n">
-        <v>11.0913257598877</v>
+        <v>11.09132671356201</v>
       </c>
       <c r="C80" t="n">
-        <v>11.0913257598877</v>
+        <v>11.09132671356201</v>
       </c>
       <c r="D80" t="n">
-        <v>10.78584480484809</v>
+        <v>10.78584573225599</v>
       </c>
       <c r="E80" t="n">
-        <v>10.87200596578243</v>
+        <v>10.87200690059879</v>
       </c>
       <c r="F80" t="n">
         <v>2890800</v>
@@ -2072,16 +2072,16 @@
         <v>44764</v>
       </c>
       <c r="B83" t="n">
-        <v>11.36547756195068</v>
+        <v>11.36547660827637</v>
       </c>
       <c r="C83" t="n">
-        <v>11.37331059952326</v>
+        <v>11.37330964519167</v>
       </c>
       <c r="D83" t="n">
-        <v>11.13049166377053</v>
+        <v>11.13049072981382</v>
       </c>
       <c r="E83" t="n">
-        <v>11.27148335207854</v>
+        <v>11.27148240629125</v>
       </c>
       <c r="F83" t="n">
         <v>1975500</v>
@@ -2092,16 +2092,16 @@
         <v>44767</v>
       </c>
       <c r="B84" t="n">
-        <v>11.23231887817383</v>
+        <v>11.2323169708252</v>
       </c>
       <c r="C84" t="n">
-        <v>11.45163870056368</v>
+        <v>11.45163675597257</v>
       </c>
       <c r="D84" t="n">
-        <v>11.16965607177673</v>
+        <v>11.1696541750688</v>
       </c>
       <c r="E84" t="n">
-        <v>11.42030729736513</v>
+        <v>11.42030535809437</v>
       </c>
       <c r="F84" t="n">
         <v>1962700</v>
@@ -2112,16 +2112,16 @@
         <v>44768</v>
       </c>
       <c r="B85" t="n">
-        <v>11.27148246765137</v>
+        <v>11.27148342132568</v>
       </c>
       <c r="C85" t="n">
-        <v>11.38114199706455</v>
+        <v>11.3811429600171</v>
       </c>
       <c r="D85" t="n">
-        <v>11.16965522819662</v>
+        <v>11.16965617325538</v>
       </c>
       <c r="E85" t="n">
-        <v>11.19315359207094</v>
+        <v>11.19315453911789</v>
       </c>
       <c r="F85" t="n">
         <v>1661400</v>
@@ -2152,16 +2152,16 @@
         <v>44770</v>
       </c>
       <c r="B87" t="n">
-        <v>10.96600151062012</v>
+        <v>10.9660005569458</v>
       </c>
       <c r="C87" t="n">
-        <v>11.33414605620796</v>
+        <v>11.33414507051741</v>
       </c>
       <c r="D87" t="n">
-        <v>10.82500982358657</v>
+        <v>10.8250088821738</v>
       </c>
       <c r="E87" t="n">
-        <v>11.31064694370265</v>
+        <v>11.31064596005574</v>
       </c>
       <c r="F87" t="n">
         <v>2911900</v>
@@ -2172,16 +2172,16 @@
         <v>44771</v>
       </c>
       <c r="B88" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C88" t="n">
-        <v>11.33414581204571</v>
+        <v>11.33414483955325</v>
       </c>
       <c r="D88" t="n">
-        <v>10.51952860439969</v>
+        <v>10.51952770180302</v>
       </c>
       <c r="E88" t="n">
-        <v>10.96600127438851</v>
+        <v>10.96600033348359</v>
       </c>
       <c r="F88" t="n">
         <v>13059200</v>
@@ -2192,16 +2192,16 @@
         <v>44774</v>
       </c>
       <c r="B89" t="n">
-        <v>10.9503345489502</v>
+        <v>10.95033550262451</v>
       </c>
       <c r="C89" t="n">
-        <v>11.20881953658161</v>
+        <v>11.20882051276761</v>
       </c>
       <c r="D89" t="n">
-        <v>10.78584525672945</v>
+        <v>10.78584619607824</v>
       </c>
       <c r="E89" t="n">
-        <v>11.05999482409687</v>
+        <v>11.0599957873216</v>
       </c>
       <c r="F89" t="n">
         <v>3205600</v>
@@ -2232,16 +2232,16 @@
         <v>44776</v>
       </c>
       <c r="B91" t="n">
-        <v>10.88767147064209</v>
+        <v>10.88767242431641</v>
       </c>
       <c r="C91" t="n">
-        <v>11.02083010599954</v>
+        <v>11.02083107133751</v>
       </c>
       <c r="D91" t="n">
-        <v>10.70751610927583</v>
+        <v>10.70751704716995</v>
       </c>
       <c r="E91" t="n">
-        <v>10.83284170796531</v>
+        <v>10.83284265683698</v>
       </c>
       <c r="F91" t="n">
         <v>3133200</v>
@@ -2252,16 +2252,16 @@
         <v>44777</v>
       </c>
       <c r="B92" t="n">
-        <v>11.06782722473145</v>
+        <v>11.06782817840576</v>
       </c>
       <c r="C92" t="n">
-        <v>11.25581561674824</v>
+        <v>11.25581658662083</v>
       </c>
       <c r="D92" t="n">
-        <v>10.89550415854965</v>
+        <v>10.89550509737551</v>
       </c>
       <c r="E92" t="n">
-        <v>10.93466859363635</v>
+        <v>10.93466953583687</v>
       </c>
       <c r="F92" t="n">
         <v>5742400</v>
@@ -2272,16 +2272,16 @@
         <v>44778</v>
       </c>
       <c r="B93" t="n">
-        <v>10.96600151062012</v>
+        <v>10.9660005569458</v>
       </c>
       <c r="C93" t="n">
-        <v>11.16965600366867</v>
+        <v>11.16965503228325</v>
       </c>
       <c r="D93" t="n">
-        <v>10.93467010761261</v>
+        <v>10.93466915666308</v>
       </c>
       <c r="E93" t="n">
-        <v>11.16965600366867</v>
+        <v>11.16965503228325</v>
       </c>
       <c r="F93" t="n">
         <v>1948700</v>
@@ -2312,16 +2312,16 @@
         <v>44782</v>
       </c>
       <c r="B95" t="n">
-        <v>10.92683696746826</v>
+        <v>10.92683601379395</v>
       </c>
       <c r="C95" t="n">
-        <v>11.0599956157492</v>
+        <v>11.05999465045304</v>
       </c>
       <c r="D95" t="n">
-        <v>10.67618574576276</v>
+        <v>10.67618481396482</v>
       </c>
       <c r="E95" t="n">
-        <v>10.98166748246601</v>
+        <v>10.98166652400619</v>
       </c>
       <c r="F95" t="n">
         <v>1743500</v>
@@ -2412,16 +2412,16 @@
         <v>44789</v>
       </c>
       <c r="B100" t="n">
-        <v>11.0443286895752</v>
+        <v>11.04433059692383</v>
       </c>
       <c r="C100" t="n">
-        <v>11.29497987500687</v>
+        <v>11.2949818256428</v>
       </c>
       <c r="D100" t="n">
-        <v>10.94250145874372</v>
+        <v>10.94250334850685</v>
       </c>
       <c r="E100" t="n">
-        <v>11.25581544053331</v>
+        <v>11.25581738440557</v>
       </c>
       <c r="F100" t="n">
         <v>1185300</v>
@@ -2452,16 +2452,16 @@
         <v>44791</v>
       </c>
       <c r="B102" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="C102" t="n">
-        <v>11.37330897550059</v>
+        <v>11.37330994384684</v>
       </c>
       <c r="D102" t="n">
-        <v>11.09915867560374</v>
+        <v>11.09915962060828</v>
       </c>
       <c r="E102" t="n">
-        <v>11.27931403205064</v>
+        <v>11.27931499239396</v>
       </c>
       <c r="F102" t="n">
         <v>2180500</v>
@@ -2472,16 +2472,16 @@
         <v>44792</v>
       </c>
       <c r="B103" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C103" t="n">
-        <v>11.16182272571687</v>
+        <v>11.16182176801008</v>
       </c>
       <c r="D103" t="n">
-        <v>10.98166734905456</v>
+        <v>10.98166640680546</v>
       </c>
       <c r="E103" t="n">
-        <v>11.16182272571687</v>
+        <v>11.16182176801008</v>
       </c>
       <c r="F103" t="n">
         <v>1667800</v>
@@ -2512,16 +2512,16 @@
         <v>44796</v>
       </c>
       <c r="B105" t="n">
-        <v>11.22448539733887</v>
+        <v>11.22448444366455</v>
       </c>
       <c r="C105" t="n">
-        <v>11.27148287378042</v>
+        <v>11.27148191611302</v>
       </c>
       <c r="D105" t="n">
-        <v>10.98949950913019</v>
+        <v>10.98949857542116</v>
       </c>
       <c r="E105" t="n">
-        <v>10.98949950913019</v>
+        <v>10.98949857542116</v>
       </c>
       <c r="F105" t="n">
         <v>2361000</v>
@@ -2552,16 +2552,16 @@
         <v>44798</v>
       </c>
       <c r="B107" t="n">
-        <v>11.0443286895752</v>
+        <v>11.04433059692383</v>
       </c>
       <c r="C107" t="n">
-        <v>11.22448404235435</v>
+        <v>11.22448598081569</v>
       </c>
       <c r="D107" t="n">
-        <v>10.95033374803886</v>
+        <v>10.95033563915463</v>
       </c>
       <c r="E107" t="n">
-        <v>11.2088187167646</v>
+        <v>11.20882065252055</v>
       </c>
       <c r="F107" t="n">
         <v>2435800</v>
@@ -2592,16 +2592,16 @@
         <v>44802</v>
       </c>
       <c r="B109" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C109" t="n">
-        <v>11.20882020271549</v>
+        <v>11.20881924097621</v>
       </c>
       <c r="D109" t="n">
-        <v>10.93466987205595</v>
+        <v>10.93466893383933</v>
       </c>
       <c r="E109" t="n">
-        <v>11.02083104172059</v>
+        <v>11.02083009611117</v>
       </c>
       <c r="F109" t="n">
         <v>3615600</v>
@@ -2672,16 +2672,16 @@
         <v>44806</v>
       </c>
       <c r="B113" t="n">
-        <v>11.74145412445068</v>
+        <v>11.74145317077637</v>
       </c>
       <c r="C113" t="n">
-        <v>11.79628463916563</v>
+        <v>11.79628368103782</v>
       </c>
       <c r="D113" t="n">
-        <v>11.56129874652895</v>
+        <v>11.56129780748737</v>
       </c>
       <c r="E113" t="n">
-        <v>11.74145412445068</v>
+        <v>11.74145317077637</v>
       </c>
       <c r="F113" t="n">
         <v>3674700</v>
@@ -2692,16 +2692,16 @@
         <v>44809</v>
       </c>
       <c r="B114" t="n">
-        <v>11.85894680023193</v>
+        <v>11.85894775390625</v>
       </c>
       <c r="C114" t="n">
-        <v>11.92160960193201</v>
+        <v>11.92161056064555</v>
       </c>
       <c r="D114" t="n">
-        <v>11.60829484643211</v>
+        <v>11.60829577994947</v>
       </c>
       <c r="E114" t="n">
-        <v>11.76495259768182</v>
+        <v>11.7649535437973</v>
       </c>
       <c r="F114" t="n">
         <v>1899700</v>
@@ -2712,16 +2712,16 @@
         <v>44810</v>
       </c>
       <c r="B115" t="n">
-        <v>11.58479690551758</v>
+        <v>11.58479595184326</v>
       </c>
       <c r="C115" t="n">
-        <v>11.90594396270576</v>
+        <v>11.90594298259424</v>
       </c>
       <c r="D115" t="n">
-        <v>11.49863573678402</v>
+        <v>11.49863479020259</v>
       </c>
       <c r="E115" t="n">
-        <v>11.89811092545738</v>
+        <v>11.89810994599068</v>
       </c>
       <c r="F115" t="n">
         <v>1316500</v>
@@ -2732,16 +2732,16 @@
         <v>44812</v>
       </c>
       <c r="B116" t="n">
-        <v>11.43597316741943</v>
+        <v>11.43597221374512</v>
       </c>
       <c r="C116" t="n">
-        <v>11.63962691105875</v>
+        <v>11.63962594040124</v>
       </c>
       <c r="D116" t="n">
-        <v>11.37331036214587</v>
+        <v>11.37330941369716</v>
       </c>
       <c r="E116" t="n">
-        <v>11.62396158324014</v>
+        <v>11.623960613889</v>
       </c>
       <c r="F116" t="n">
         <v>2598100</v>
@@ -2812,16 +2812,16 @@
         <v>44818</v>
       </c>
       <c r="B120" t="n">
-        <v>11.20882034301758</v>
+        <v>11.20881843566895</v>
       </c>
       <c r="C120" t="n">
-        <v>11.42030712465965</v>
+        <v>11.42030518132337</v>
       </c>
       <c r="D120" t="n">
-        <v>11.02866421710068</v>
+        <v>11.02866234040831</v>
       </c>
       <c r="E120" t="n">
-        <v>11.2009873055865</v>
+        <v>11.20098539957078</v>
       </c>
       <c r="F120" t="n">
         <v>1856400</v>
@@ -2832,16 +2832,16 @@
         <v>44819</v>
       </c>
       <c r="B121" t="n">
-        <v>11.22448539733887</v>
+        <v>11.22448444366455</v>
       </c>
       <c r="C121" t="n">
-        <v>11.27148287378042</v>
+        <v>11.27148191611302</v>
       </c>
       <c r="D121" t="n">
-        <v>11.11482511697494</v>
+        <v>11.11482417261777</v>
       </c>
       <c r="E121" t="n">
-        <v>11.16182259341649</v>
+        <v>11.16182164506624</v>
       </c>
       <c r="F121" t="n">
         <v>1523500</v>
@@ -2852,16 +2852,16 @@
         <v>44820</v>
       </c>
       <c r="B122" t="n">
-        <v>11.16965579986572</v>
+        <v>11.16965484619141</v>
       </c>
       <c r="C122" t="n">
-        <v>11.35764421448068</v>
+        <v>11.35764324475576</v>
       </c>
       <c r="D122" t="n">
-        <v>11.02866411540472</v>
+        <v>11.02866317376839</v>
       </c>
       <c r="E122" t="n">
-        <v>11.22448556737853</v>
+        <v>11.2244846090228</v>
       </c>
       <c r="F122" t="n">
         <v>3523100</v>
@@ -2872,16 +2872,16 @@
         <v>44823</v>
       </c>
       <c r="B123" t="n">
-        <v>11.28714656829834</v>
+        <v>11.28714847564697</v>
       </c>
       <c r="C123" t="n">
-        <v>11.43597126633249</v>
+        <v>11.43597319883014</v>
       </c>
       <c r="D123" t="n">
-        <v>11.1148235089428</v>
+        <v>11.11482538717157</v>
       </c>
       <c r="E123" t="n">
-        <v>11.1148235089428</v>
+        <v>11.11482538717157</v>
       </c>
       <c r="F123" t="n">
         <v>1858600</v>
@@ -2892,16 +2892,16 @@
         <v>44824</v>
       </c>
       <c r="B124" t="n">
-        <v>11.13048934936523</v>
+        <v>11.13049030303955</v>
       </c>
       <c r="C124" t="n">
-        <v>11.35764216274006</v>
+        <v>11.35764313587711</v>
       </c>
       <c r="D124" t="n">
-        <v>11.08349188070174</v>
+        <v>11.08349283034925</v>
       </c>
       <c r="E124" t="n">
-        <v>11.28714633324452</v>
+        <v>11.28714730034141</v>
       </c>
       <c r="F124" t="n">
         <v>1310600</v>
@@ -2912,16 +2912,16 @@
         <v>44825</v>
       </c>
       <c r="B125" t="n">
-        <v>11.0913257598877</v>
+        <v>11.09132671356201</v>
       </c>
       <c r="C125" t="n">
-        <v>11.23231742959796</v>
+        <v>11.23231839539528</v>
       </c>
       <c r="D125" t="n">
-        <v>10.93466876409822</v>
+        <v>10.93466970430257</v>
       </c>
       <c r="E125" t="n">
-        <v>11.13049019558493</v>
+        <v>11.13049115262676</v>
       </c>
       <c r="F125" t="n">
         <v>2825100</v>
@@ -2932,16 +2932,16 @@
         <v>44826</v>
       </c>
       <c r="B126" t="n">
-        <v>11.23231887817383</v>
+        <v>11.2323169708252</v>
       </c>
       <c r="C126" t="n">
-        <v>11.24015191572336</v>
+        <v>11.24015000704461</v>
       </c>
       <c r="D126" t="n">
-        <v>11.05999578708202</v>
+        <v>11.05999390899539</v>
       </c>
       <c r="E126" t="n">
-        <v>11.19315443742575</v>
+        <v>11.19315253672759</v>
       </c>
       <c r="F126" t="n">
         <v>1855600</v>
@@ -2952,16 +2952,16 @@
         <v>44827</v>
       </c>
       <c r="B127" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="C127" t="n">
-        <v>11.30281314141286</v>
+        <v>11.30281410375695</v>
       </c>
       <c r="D127" t="n">
-        <v>11.07566031324099</v>
+        <v>11.07566125624483</v>
       </c>
       <c r="E127" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="F127" t="n">
         <v>2444100</v>
@@ -3012,16 +3012,16 @@
         <v>44832</v>
       </c>
       <c r="B130" t="n">
-        <v>10.74668121337891</v>
+        <v>10.74668025970459</v>
       </c>
       <c r="C130" t="n">
-        <v>11.03649686510639</v>
+        <v>11.03649588571345</v>
       </c>
       <c r="D130" t="n">
-        <v>10.72318210191485</v>
+        <v>10.72318115032588</v>
       </c>
       <c r="E130" t="n">
-        <v>10.95816798755862</v>
+        <v>10.95816701511669</v>
       </c>
       <c r="F130" t="n">
         <v>4249200</v>
@@ -3072,16 +3072,16 @@
         <v>44837</v>
       </c>
       <c r="B133" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="C133" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="D133" t="n">
-        <v>10.62918694635185</v>
+        <v>10.62918785134206</v>
       </c>
       <c r="E133" t="n">
-        <v>10.74668025216456</v>
+        <v>10.74668116715839</v>
       </c>
       <c r="F133" t="n">
         <v>2250700</v>
@@ -3092,16 +3092,16 @@
         <v>44838</v>
       </c>
       <c r="B134" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C134" t="n">
-        <v>11.32631277471268</v>
+        <v>11.32631180289231</v>
       </c>
       <c r="D134" t="n">
-        <v>11.07566155605223</v>
+        <v>11.07566060573824</v>
       </c>
       <c r="E134" t="n">
-        <v>11.20882020271549</v>
+        <v>11.20881924097621</v>
       </c>
       <c r="F134" t="n">
         <v>2406500</v>
@@ -3132,16 +3132,16 @@
         <v>44840</v>
       </c>
       <c r="B136" t="n">
-        <v>10.98950004577637</v>
+        <v>10.98949909210205</v>
       </c>
       <c r="C136" t="n">
-        <v>11.12265869736379</v>
+        <v>11.1226577321339</v>
       </c>
       <c r="D136" t="n">
-        <v>10.88767279768013</v>
+        <v>10.88767185284243</v>
       </c>
       <c r="E136" t="n">
-        <v>11.02866448689024</v>
+        <v>11.02866352981721</v>
       </c>
       <c r="F136" t="n">
         <v>3101100</v>
@@ -3192,16 +3192,16 @@
         <v>44845</v>
       </c>
       <c r="B139" t="n">
-        <v>11.22448539733887</v>
+        <v>11.22448444366455</v>
       </c>
       <c r="C139" t="n">
-        <v>11.31847960322243</v>
+        <v>11.31847864156201</v>
       </c>
       <c r="D139" t="n">
-        <v>10.99733254637037</v>
+        <v>10.99733161199581</v>
       </c>
       <c r="E139" t="n">
-        <v>11.04433002281193</v>
+        <v>11.04432908444429</v>
       </c>
       <c r="F139" t="n">
         <v>1834300</v>
@@ -3212,16 +3212,16 @@
         <v>44847</v>
       </c>
       <c r="B140" t="n">
-        <v>10.91117000579834</v>
+        <v>10.91117095947266</v>
       </c>
       <c r="C140" t="n">
-        <v>11.20098562424891</v>
+        <v>11.20098660325412</v>
       </c>
       <c r="D140" t="n">
-        <v>10.87200557152136</v>
+        <v>10.87200652177256</v>
       </c>
       <c r="E140" t="n">
-        <v>11.12265675569494</v>
+        <v>11.12265772785393</v>
       </c>
       <c r="F140" t="n">
         <v>3739400</v>
@@ -3252,16 +3252,16 @@
         <v>44851</v>
       </c>
       <c r="B142" t="n">
-        <v>11.15398788452148</v>
+        <v>11.1539888381958</v>
       </c>
       <c r="C142" t="n">
-        <v>11.2009853539195</v>
+        <v>11.20098631161214</v>
       </c>
       <c r="D142" t="n">
-        <v>10.78584415340134</v>
+        <v>10.78584507559909</v>
       </c>
       <c r="E142" t="n">
-        <v>10.86417227306545</v>
+        <v>10.86417320196032</v>
       </c>
       <c r="F142" t="n">
         <v>6971700</v>
@@ -3272,16 +3272,16 @@
         <v>44852</v>
       </c>
       <c r="B143" t="n">
-        <v>11.27148246765137</v>
+        <v>11.27148342132568</v>
       </c>
       <c r="C143" t="n">
-        <v>11.37330970710612</v>
+        <v>11.37331066939599</v>
       </c>
       <c r="D143" t="n">
-        <v>11.06782798874186</v>
+        <v>11.06782892518508</v>
       </c>
       <c r="E143" t="n">
-        <v>11.20881966598683</v>
+        <v>11.20882061435928</v>
       </c>
       <c r="F143" t="n">
         <v>2646800</v>
@@ -3292,16 +3292,16 @@
         <v>44853</v>
       </c>
       <c r="B144" t="n">
-        <v>11.02082920074463</v>
+        <v>11.02083015441895</v>
       </c>
       <c r="C144" t="n">
-        <v>11.32631088270749</v>
+        <v>11.3263118628163</v>
       </c>
       <c r="D144" t="n">
-        <v>10.99733083967039</v>
+        <v>10.9973317913113</v>
       </c>
       <c r="E144" t="n">
-        <v>11.28714644958413</v>
+        <v>11.2871474263039</v>
       </c>
       <c r="F144" t="n">
         <v>2951600</v>
@@ -3312,16 +3312,16 @@
         <v>44854</v>
       </c>
       <c r="B145" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C145" t="n">
-        <v>10.98166755090811</v>
+        <v>10.98166658413194</v>
       </c>
       <c r="D145" t="n">
-        <v>10.39420318612486</v>
+        <v>10.39420227106638</v>
       </c>
       <c r="E145" t="n">
-        <v>10.5743585660986</v>
+        <v>10.57435763518006</v>
       </c>
       <c r="F145" t="n">
         <v>7194300</v>
@@ -3332,16 +3332,16 @@
         <v>44855</v>
       </c>
       <c r="B146" t="n">
-        <v>11.16965579986572</v>
+        <v>11.16965484619141</v>
       </c>
       <c r="C146" t="n">
-        <v>11.16965579986572</v>
+        <v>11.16965484619141</v>
       </c>
       <c r="D146" t="n">
-        <v>10.75451378384157</v>
+        <v>10.75451286561242</v>
       </c>
       <c r="E146" t="n">
-        <v>10.75451378384157</v>
+        <v>10.75451286561242</v>
       </c>
       <c r="F146" t="n">
         <v>9489900</v>
@@ -3372,16 +3372,16 @@
         <v>44859</v>
       </c>
       <c r="B148" t="n">
-        <v>11.38897514343262</v>
+        <v>11.3889741897583</v>
       </c>
       <c r="C148" t="n">
-        <v>11.50646771093245</v>
+        <v>11.50646674741971</v>
       </c>
       <c r="D148" t="n">
-        <v>11.18532066256667</v>
+        <v>11.18531972594569</v>
       </c>
       <c r="E148" t="n">
-        <v>11.24015117479952</v>
+        <v>11.24015023358722</v>
       </c>
       <c r="F148" t="n">
         <v>2935500</v>
@@ -3452,16 +3452,16 @@
         <v>44865</v>
       </c>
       <c r="B152" t="n">
-        <v>11.68662357330322</v>
+        <v>11.68662452697754</v>
       </c>
       <c r="C152" t="n">
-        <v>11.72578801061714</v>
+        <v>11.72578896748743</v>
       </c>
       <c r="D152" t="n">
-        <v>11.16182205549541</v>
+        <v>11.16182296634386</v>
       </c>
       <c r="E152" t="n">
-        <v>11.23231789326056</v>
+        <v>11.23231880986175</v>
       </c>
       <c r="F152" t="n">
         <v>2644000</v>
@@ -3472,16 +3472,16 @@
         <v>44866</v>
       </c>
       <c r="B153" t="n">
-        <v>11.56913185119629</v>
+        <v>11.56913089752197</v>
       </c>
       <c r="C153" t="n">
-        <v>11.80411699819995</v>
+        <v>11.80411602515518</v>
       </c>
       <c r="D153" t="n">
-        <v>11.34981128506018</v>
+        <v>11.34981034946504</v>
       </c>
       <c r="E153" t="n">
-        <v>11.67879138726478</v>
+        <v>11.67879042455094</v>
       </c>
       <c r="F153" t="n">
         <v>3576300</v>
@@ -3492,16 +3492,16 @@
         <v>44868</v>
       </c>
       <c r="B154" t="n">
-        <v>11.68662357330322</v>
+        <v>11.68662452697754</v>
       </c>
       <c r="C154" t="n">
-        <v>11.74928637420569</v>
+        <v>11.74928733299354</v>
       </c>
       <c r="D154" t="n">
-        <v>11.36547653192819</v>
+        <v>11.36547745939565</v>
       </c>
       <c r="E154" t="n">
-        <v>11.49863517059581</v>
+        <v>11.49863610892954</v>
       </c>
       <c r="F154" t="n">
         <v>2959500</v>
@@ -3512,16 +3512,16 @@
         <v>44869</v>
       </c>
       <c r="B155" t="n">
-        <v>11.67095756530762</v>
+        <v>11.67095851898193</v>
       </c>
       <c r="C155" t="n">
-        <v>11.87461204288736</v>
+        <v>11.87461301320299</v>
       </c>
       <c r="D155" t="n">
-        <v>11.64745920158673</v>
+        <v>11.64746015334091</v>
       </c>
       <c r="E155" t="n">
-        <v>11.7492864403766</v>
+        <v>11.74928740045144</v>
       </c>
       <c r="F155" t="n">
         <v>2161500</v>
@@ -3532,16 +3532,16 @@
         <v>44872</v>
       </c>
       <c r="B156" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="C156" t="n">
-        <v>11.65529156485204</v>
+        <v>11.65529255720685</v>
       </c>
       <c r="D156" t="n">
-        <v>11.1226570379665</v>
+        <v>11.12265798497174</v>
       </c>
       <c r="E156" t="n">
-        <v>11.60829409312706</v>
+        <v>11.60829508148041</v>
       </c>
       <c r="F156" t="n">
         <v>3276500</v>
@@ -3632,16 +3632,16 @@
         <v>44879</v>
       </c>
       <c r="B161" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C161" t="n">
-        <v>10.9660014759541</v>
+        <v>10.9660005105571</v>
       </c>
       <c r="D161" t="n">
-        <v>10.71535025268644</v>
+        <v>10.71534930935563</v>
       </c>
       <c r="E161" t="n">
-        <v>10.94250311052265</v>
+        <v>10.94250214719434</v>
       </c>
       <c r="F161" t="n">
         <v>1203700</v>
@@ -3672,16 +3672,16 @@
         <v>44882</v>
       </c>
       <c r="B163" t="n">
-        <v>10.74668121337891</v>
+        <v>10.74668025970459</v>
       </c>
       <c r="C163" t="n">
-        <v>10.80151097946262</v>
+        <v>10.80151002092264</v>
       </c>
       <c r="D163" t="n">
-        <v>10.50386229058046</v>
+        <v>10.50386135845421</v>
       </c>
       <c r="E163" t="n">
-        <v>10.69185070029565</v>
+        <v>10.69184975148707</v>
       </c>
       <c r="F163" t="n">
         <v>5834900</v>
@@ -3692,16 +3692,16 @@
         <v>44883</v>
       </c>
       <c r="B164" t="n">
-        <v>10.78584575653076</v>
+        <v>10.78584480285645</v>
       </c>
       <c r="C164" t="n">
-        <v>10.98949949552661</v>
+        <v>10.98949852384542</v>
       </c>
       <c r="D164" t="n">
-        <v>10.57435823330488</v>
+        <v>10.57435729833009</v>
       </c>
       <c r="E164" t="n">
-        <v>10.80934412122268</v>
+        <v>10.80934316547066</v>
       </c>
       <c r="F164" t="n">
         <v>3568700</v>
@@ -3732,16 +3732,16 @@
         <v>44887</v>
       </c>
       <c r="B166" t="n">
-        <v>10.84850788116455</v>
+        <v>10.84850883483887</v>
       </c>
       <c r="C166" t="n">
-        <v>11.42030611719874</v>
+        <v>11.4203071211389</v>
       </c>
       <c r="D166" t="n">
-        <v>10.80151040772362</v>
+        <v>10.80151135726647</v>
       </c>
       <c r="E166" t="n">
-        <v>11.29498051735561</v>
+        <v>11.29498151027859</v>
       </c>
       <c r="F166" t="n">
         <v>3523700</v>
@@ -3772,16 +3772,16 @@
         <v>44889</v>
       </c>
       <c r="B168" t="n">
-        <v>10.9503345489502</v>
+        <v>10.95033550262451</v>
       </c>
       <c r="C168" t="n">
-        <v>11.09132622456742</v>
+        <v>11.09132719052083</v>
       </c>
       <c r="D168" t="n">
-        <v>10.56652470643609</v>
+        <v>10.56652562668407</v>
       </c>
       <c r="E168" t="n">
-        <v>10.56652470643609</v>
+        <v>10.56652562668407</v>
       </c>
       <c r="F168" t="n">
         <v>1852400</v>
@@ -3792,16 +3792,16 @@
         <v>44890</v>
       </c>
       <c r="B169" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C169" t="n">
-        <v>11.03649731924802</v>
+        <v>11.03649634764489</v>
       </c>
       <c r="D169" t="n">
-        <v>10.71535025268644</v>
+        <v>10.71534930935563</v>
       </c>
       <c r="E169" t="n">
-        <v>10.95033540100009</v>
+        <v>10.95033443698226</v>
       </c>
       <c r="F169" t="n">
         <v>1631500</v>
@@ -3832,16 +3832,16 @@
         <v>44894</v>
       </c>
       <c r="B171" t="n">
-        <v>11.16965579986572</v>
+        <v>11.16965484619141</v>
       </c>
       <c r="C171" t="n">
-        <v>11.2636500071732</v>
+        <v>11.26364904547358</v>
       </c>
       <c r="D171" t="n">
-        <v>10.9973327129689</v>
+        <v>10.99733177400767</v>
       </c>
       <c r="E171" t="n">
-        <v>11.01299878768659</v>
+        <v>11.01299784738778</v>
       </c>
       <c r="F171" t="n">
         <v>1705300</v>
@@ -3852,16 +3852,16 @@
         <v>44895</v>
       </c>
       <c r="B172" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C172" t="n">
-        <v>11.20882040874432</v>
+        <v>11.20881942197064</v>
       </c>
       <c r="D172" t="n">
-        <v>10.69185114025542</v>
+        <v>10.69185019899337</v>
       </c>
       <c r="E172" t="n">
-        <v>11.20882040874432</v>
+        <v>11.20881942197064</v>
       </c>
       <c r="F172" t="n">
         <v>4586400</v>
@@ -3872,16 +3872,16 @@
         <v>44896</v>
       </c>
       <c r="B173" t="n">
-        <v>10.92683696746826</v>
+        <v>10.92683601379395</v>
       </c>
       <c r="C173" t="n">
-        <v>11.02083117560783</v>
+        <v>11.02083021372987</v>
       </c>
       <c r="D173" t="n">
-        <v>10.69185107361957</v>
+        <v>10.69185014045439</v>
       </c>
       <c r="E173" t="n">
-        <v>10.76234691647413</v>
+        <v>10.76234597715621</v>
       </c>
       <c r="F173" t="n">
         <v>1944500</v>
@@ -3892,16 +3892,16 @@
         <v>44897</v>
       </c>
       <c r="B174" t="n">
-        <v>10.80150985717773</v>
+        <v>10.80151081085205</v>
       </c>
       <c r="C174" t="n">
-        <v>11.09132547879316</v>
+        <v>11.09132645805553</v>
       </c>
       <c r="D174" t="n">
-        <v>10.79367682083691</v>
+        <v>10.79367777381964</v>
       </c>
       <c r="E174" t="n">
-        <v>10.92683545063311</v>
+        <v>10.92683641537253</v>
       </c>
       <c r="F174" t="n">
         <v>1109200</v>
@@ -3912,16 +3912,16 @@
         <v>44900</v>
       </c>
       <c r="B175" t="n">
-        <v>10.51952743530273</v>
+        <v>10.51952838897705</v>
       </c>
       <c r="C175" t="n">
-        <v>10.80151002495736</v>
+        <v>10.80151100419552</v>
       </c>
       <c r="D175" t="n">
-        <v>10.50386136237774</v>
+        <v>10.50386231463181</v>
       </c>
       <c r="E175" t="n">
-        <v>10.77801166256934</v>
+        <v>10.7780126396772</v>
       </c>
       <c r="F175" t="n">
         <v>1355000</v>
@@ -3932,16 +3932,16 @@
         <v>44901</v>
       </c>
       <c r="B176" t="n">
-        <v>10.47253036499023</v>
+        <v>10.47253131866455</v>
       </c>
       <c r="C176" t="n">
-        <v>10.58219063867058</v>
+        <v>10.58219160233104</v>
       </c>
       <c r="D176" t="n">
-        <v>10.41770060164981</v>
+        <v>10.41770155033109</v>
       </c>
       <c r="E176" t="n">
-        <v>10.51952783856738</v>
+        <v>10.51952879652149</v>
       </c>
       <c r="F176" t="n">
         <v>1647500</v>
@@ -3952,16 +3952,16 @@
         <v>44902</v>
       </c>
       <c r="B177" t="n">
-        <v>10.65268611907959</v>
+        <v>10.65268707275391</v>
       </c>
       <c r="C177" t="n">
-        <v>10.80151007759491</v>
+        <v>10.80151104459258</v>
       </c>
       <c r="D177" t="n">
-        <v>10.42553328955654</v>
+        <v>10.42553422289516</v>
       </c>
       <c r="E177" t="n">
-        <v>10.42553328955654</v>
+        <v>10.42553422289516</v>
       </c>
       <c r="F177" t="n">
         <v>2865300</v>
@@ -3972,16 +3972,16 @@
         <v>44903</v>
       </c>
       <c r="B178" t="n">
-        <v>11.26364898681641</v>
+        <v>11.26364994049072</v>
       </c>
       <c r="C178" t="n">
-        <v>11.8119488532735</v>
+        <v>11.81194985337145</v>
       </c>
       <c r="D178" t="n">
-        <v>11.15398871472519</v>
+        <v>11.15398965911476</v>
       </c>
       <c r="E178" t="n">
-        <v>11.74928605407837</v>
+        <v>11.74928704887077</v>
       </c>
       <c r="F178" t="n">
         <v>12105700</v>
@@ -4152,16 +4152,16 @@
         <v>44916</v>
       </c>
       <c r="B187" t="n">
-        <v>11.58479690551758</v>
+        <v>11.58479595184326</v>
       </c>
       <c r="C187" t="n">
-        <v>11.75711998998425</v>
+        <v>11.75711902212409</v>
       </c>
       <c r="D187" t="n">
-        <v>11.15398956785069</v>
+        <v>11.15398864964095</v>
       </c>
       <c r="E187" t="n">
-        <v>11.42813989554768</v>
+        <v>11.42813895476955</v>
       </c>
       <c r="F187" t="n">
         <v>6348400</v>
@@ -4192,16 +4192,16 @@
         <v>44918</v>
       </c>
       <c r="B189" t="n">
-        <v>11.78845119476318</v>
+        <v>11.78845024108887</v>
       </c>
       <c r="C189" t="n">
-        <v>12.09393217234406</v>
+        <v>12.09393119395663</v>
       </c>
       <c r="D189" t="n">
-        <v>11.57696367459224</v>
+        <v>11.57696273802706</v>
       </c>
       <c r="E189" t="n">
-        <v>11.67879091611904</v>
+        <v>11.67878997131614</v>
       </c>
       <c r="F189" t="n">
         <v>5656000</v>
@@ -4252,16 +4252,16 @@
         <v>44923</v>
       </c>
       <c r="B192" t="n">
-        <v>11.58479690551758</v>
+        <v>11.58479595184326</v>
       </c>
       <c r="C192" t="n">
-        <v>11.69445718599628</v>
+        <v>11.6944562232946</v>
       </c>
       <c r="D192" t="n">
-        <v>11.49863573678402</v>
+        <v>11.49863479020259</v>
       </c>
       <c r="E192" t="n">
-        <v>11.5769638682692</v>
+        <v>11.5769629152397</v>
       </c>
       <c r="F192" t="n">
         <v>2005900</v>
@@ -4372,16 +4372,16 @@
         <v>44932</v>
       </c>
       <c r="B198" t="n">
-        <v>11.4203052520752</v>
+        <v>11.42030620574951</v>
       </c>
       <c r="C198" t="n">
-        <v>11.53779780627784</v>
+        <v>11.53779876976359</v>
       </c>
       <c r="D198" t="n">
-        <v>11.3184780231665</v>
+        <v>11.31847896833754</v>
       </c>
       <c r="E198" t="n">
-        <v>11.4124722159285</v>
+        <v>11.4124731689487</v>
       </c>
       <c r="F198" t="n">
         <v>2864500</v>
@@ -4392,16 +4392,16 @@
         <v>44935</v>
       </c>
       <c r="B199" t="n">
-        <v>11.23231887817383</v>
+        <v>11.2323169708252</v>
       </c>
       <c r="C199" t="n">
-        <v>11.43597337246419</v>
+        <v>11.43597143053319</v>
       </c>
       <c r="D199" t="n">
-        <v>11.17748910932626</v>
+        <v>11.17748721128821</v>
       </c>
       <c r="E199" t="n">
-        <v>11.36547752851756</v>
+        <v>11.36547559855739</v>
       </c>
       <c r="F199" t="n">
         <v>1567200</v>
@@ -4412,16 +4412,16 @@
         <v>44936</v>
       </c>
       <c r="B200" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C200" t="n">
-        <v>11.1853210907164</v>
+        <v>11.1853201309934</v>
       </c>
       <c r="D200" t="n">
-        <v>10.69185094372897</v>
+        <v>10.6918500263467</v>
       </c>
       <c r="E200" t="n">
-        <v>11.08349384638571</v>
+        <v>11.08349289539969</v>
       </c>
       <c r="F200" t="n">
         <v>5832500</v>
@@ -4472,16 +4472,16 @@
         <v>44939</v>
       </c>
       <c r="B203" t="n">
-        <v>11.58479690551758</v>
+        <v>11.58479595184326</v>
       </c>
       <c r="C203" t="n">
-        <v>11.78845139197822</v>
+        <v>11.78845042153883</v>
       </c>
       <c r="D203" t="n">
-        <v>11.44380522304489</v>
+        <v>11.44380428097718</v>
       </c>
       <c r="E203" t="n">
-        <v>11.74928695273586</v>
+        <v>11.74928598552053</v>
       </c>
       <c r="F203" t="n">
         <v>2269100</v>
@@ -4492,16 +4492,16 @@
         <v>44942</v>
       </c>
       <c r="B204" t="n">
-        <v>11.78845119476318</v>
+        <v>11.78845024108887</v>
       </c>
       <c r="C204" t="n">
-        <v>11.80411652199833</v>
+        <v>11.8041155670567</v>
       </c>
       <c r="D204" t="n">
-        <v>11.39680830289065</v>
+        <v>11.39680738089987</v>
       </c>
       <c r="E204" t="n">
-        <v>11.49080250730011</v>
+        <v>11.49080157770529</v>
       </c>
       <c r="F204" t="n">
         <v>3279700</v>
@@ -4512,16 +4512,16 @@
         <v>44943</v>
       </c>
       <c r="B205" t="n">
-        <v>11.74928569793701</v>
+        <v>11.74928665161133</v>
       </c>
       <c r="C205" t="n">
-        <v>11.93727408982413</v>
+        <v>11.93727505875722</v>
       </c>
       <c r="D205" t="n">
-        <v>11.60829403052194</v>
+        <v>11.60829497275214</v>
       </c>
       <c r="E205" t="n">
-        <v>11.81194849523272</v>
+        <v>11.81194945399329</v>
       </c>
       <c r="F205" t="n">
         <v>2676600</v>
@@ -4552,16 +4552,16 @@
         <v>44945</v>
       </c>
       <c r="B207" t="n">
-        <v>11.66312503814697</v>
+        <v>11.66312599182129</v>
       </c>
       <c r="C207" t="n">
-        <v>11.68662340138985</v>
+        <v>11.68662435698559</v>
       </c>
       <c r="D207" t="n">
-        <v>11.27931445451592</v>
+        <v>11.27931537680668</v>
       </c>
       <c r="E207" t="n">
-        <v>11.3419772544966</v>
+        <v>11.3419781819112</v>
       </c>
       <c r="F207" t="n">
         <v>1847800</v>
@@ -4572,16 +4572,16 @@
         <v>44946</v>
       </c>
       <c r="B208" t="n">
-        <v>11.58479690551758</v>
+        <v>11.58479595184326</v>
       </c>
       <c r="C208" t="n">
-        <v>11.6866241487479</v>
+        <v>11.68662318669104</v>
       </c>
       <c r="D208" t="n">
-        <v>11.48296966228726</v>
+        <v>11.48296871699548</v>
       </c>
       <c r="E208" t="n">
-        <v>11.65529274675392</v>
+        <v>11.6552917872763</v>
       </c>
       <c r="F208" t="n">
         <v>2012100</v>
@@ -4612,16 +4612,16 @@
         <v>44950</v>
       </c>
       <c r="B210" t="n">
-        <v>11.68662357330322</v>
+        <v>11.68662452697754</v>
       </c>
       <c r="C210" t="n">
-        <v>11.80411613824548</v>
+        <v>11.80411710150764</v>
       </c>
       <c r="D210" t="n">
-        <v>11.32631209461427</v>
+        <v>11.32631301888575</v>
       </c>
       <c r="E210" t="n">
-        <v>11.52996657104705</v>
+        <v>11.52996751193754</v>
       </c>
       <c r="F210" t="n">
         <v>5839900</v>
@@ -4632,16 +4632,16 @@
         <v>44951</v>
       </c>
       <c r="B211" t="n">
-        <v>11.89027786254883</v>
+        <v>11.89027881622314</v>
       </c>
       <c r="C211" t="n">
-        <v>12.07043322555739</v>
+        <v>12.07043419368129</v>
       </c>
       <c r="D211" t="n">
-        <v>11.62396058940618</v>
+        <v>11.62396152172019</v>
       </c>
       <c r="E211" t="n">
-        <v>11.67879035258278</v>
+        <v>11.67879128929448</v>
       </c>
       <c r="F211" t="n">
         <v>10764800</v>
@@ -4672,16 +4672,16 @@
         <v>44953</v>
       </c>
       <c r="B213" t="n">
-        <v>11.98427295684814</v>
+        <v>11.98427200317383</v>
       </c>
       <c r="C213" t="n">
-        <v>12.23492417521897</v>
+        <v>12.23492320159854</v>
       </c>
       <c r="D213" t="n">
-        <v>11.92161015225544</v>
+        <v>11.92160920356765</v>
       </c>
       <c r="E213" t="n">
-        <v>11.96860688220019</v>
+        <v>11.96860592977254</v>
       </c>
       <c r="F213" t="n">
         <v>4160800</v>
@@ -4712,16 +4712,16 @@
         <v>44957</v>
       </c>
       <c r="B215" t="n">
-        <v>12.07043361663818</v>
+        <v>12.0704345703125</v>
       </c>
       <c r="C215" t="n">
-        <v>12.14092945557759</v>
+        <v>12.14093041482172</v>
       </c>
       <c r="D215" t="n">
-        <v>11.82761544584636</v>
+        <v>11.82761638033583</v>
       </c>
       <c r="E215" t="n">
-        <v>11.84328077283316</v>
+        <v>11.84328170856034</v>
       </c>
       <c r="F215" t="n">
         <v>5446800</v>
@@ -4812,16 +4812,16 @@
         <v>44964</v>
       </c>
       <c r="B220" t="n">
-        <v>11.60046291351318</v>
+        <v>11.60046195983887</v>
       </c>
       <c r="C220" t="n">
-        <v>12.02343721150694</v>
+        <v>12.02343622305989</v>
       </c>
       <c r="D220" t="n">
-        <v>11.49080263366312</v>
+        <v>11.49080168900398</v>
       </c>
       <c r="E220" t="n">
-        <v>12.02343721150694</v>
+        <v>12.02343622305989</v>
       </c>
       <c r="F220" t="n">
         <v>5199600</v>
@@ -4852,16 +4852,16 @@
         <v>44966</v>
       </c>
       <c r="B222" t="n">
-        <v>11.66312503814697</v>
+        <v>11.66312599182129</v>
       </c>
       <c r="C222" t="n">
-        <v>11.78845063810834</v>
+        <v>11.78845160203032</v>
       </c>
       <c r="D222" t="n">
-        <v>11.55346476468103</v>
+        <v>11.55346570938861</v>
       </c>
       <c r="E222" t="n">
-        <v>11.71012176463273</v>
+        <v>11.7101227221499</v>
       </c>
       <c r="F222" t="n">
         <v>2260100</v>
@@ -4952,16 +4952,16 @@
         <v>44973</v>
       </c>
       <c r="B227" t="n">
-        <v>11.89027786254883</v>
+        <v>11.89027881622314</v>
       </c>
       <c r="C227" t="n">
-        <v>11.97643902568342</v>
+        <v>11.9764399862684</v>
       </c>
       <c r="D227" t="n">
-        <v>11.57696311596945</v>
+        <v>11.57696404451397</v>
       </c>
       <c r="E227" t="n">
-        <v>11.76495226271687</v>
+        <v>11.7649532063393</v>
       </c>
       <c r="F227" t="n">
         <v>4461000</v>
@@ -5172,16 +5172,16 @@
         <v>44992</v>
       </c>
       <c r="B238" t="n">
-        <v>11.61612796783447</v>
+        <v>11.61612701416016</v>
       </c>
       <c r="C238" t="n">
-        <v>11.6239610048538</v>
+        <v>11.6239600505364</v>
       </c>
       <c r="D238" t="n">
-        <v>11.3889751232706</v>
+        <v>11.38897418824534</v>
       </c>
       <c r="E238" t="n">
-        <v>11.52996680162043</v>
+        <v>11.52996585501987</v>
       </c>
       <c r="F238" t="n">
         <v>3776700</v>
@@ -5252,16 +5252,16 @@
         <v>44998</v>
       </c>
       <c r="B242" t="n">
-        <v>11.66312503814697</v>
+        <v>11.66312599182129</v>
       </c>
       <c r="C242" t="n">
-        <v>11.74145316462308</v>
+        <v>11.74145412470215</v>
       </c>
       <c r="D242" t="n">
-        <v>11.45947056471</v>
+        <v>11.45947150173183</v>
       </c>
       <c r="E242" t="n">
-        <v>11.52213336469069</v>
+        <v>11.52213430683635</v>
       </c>
       <c r="F242" t="n">
         <v>3223500</v>
@@ -5292,16 +5292,16 @@
         <v>45000</v>
       </c>
       <c r="B244" t="n">
-        <v>11.74928569793701</v>
+        <v>11.74928665161133</v>
       </c>
       <c r="C244" t="n">
-        <v>11.89027736535209</v>
+        <v>11.89027833047051</v>
       </c>
       <c r="D244" t="n">
-        <v>11.61612706693377</v>
+        <v>11.61612800979977</v>
       </c>
       <c r="E244" t="n">
-        <v>11.71795429928916</v>
+        <v>11.71795525042035</v>
       </c>
       <c r="F244" t="n">
         <v>4602600</v>
@@ -5312,16 +5312,16 @@
         <v>45001</v>
       </c>
       <c r="B245" t="n">
-        <v>11.67095756530762</v>
+        <v>11.67095851898193</v>
       </c>
       <c r="C245" t="n">
-        <v>11.81194924163198</v>
+        <v>11.81195020682722</v>
       </c>
       <c r="D245" t="n">
-        <v>11.63962616467993</v>
+        <v>11.63962711579405</v>
       </c>
       <c r="E245" t="n">
-        <v>11.81194924163198</v>
+        <v>11.81195020682722</v>
       </c>
       <c r="F245" t="n">
         <v>5495800</v>
@@ -5332,16 +5332,16 @@
         <v>45002</v>
       </c>
       <c r="B246" t="n">
-        <v>11.40464115142822</v>
+        <v>11.40464019775391</v>
       </c>
       <c r="C246" t="n">
-        <v>11.66312539603</v>
+        <v>11.66312442074082</v>
       </c>
       <c r="D246" t="n">
-        <v>11.37330975047648</v>
+        <v>11.37330879942214</v>
       </c>
       <c r="E246" t="n">
-        <v>11.66312539603</v>
+        <v>11.66312442074082</v>
       </c>
       <c r="F246" t="n">
         <v>6196900</v>
@@ -5392,16 +5392,16 @@
         <v>45007</v>
       </c>
       <c r="B249" t="n">
-        <v>11.33414459228516</v>
+        <v>11.33414554595947</v>
       </c>
       <c r="C249" t="n">
-        <v>11.45947018812806</v>
+        <v>11.45947115234749</v>
       </c>
       <c r="D249" t="n">
-        <v>11.21665128593282</v>
+        <v>11.21665222972105</v>
       </c>
       <c r="E249" t="n">
-        <v>11.36547599124588</v>
+        <v>11.36547694755648</v>
       </c>
       <c r="F249" t="n">
         <v>3006300</v>
@@ -5452,16 +5452,16 @@
         <v>45012</v>
       </c>
       <c r="B252" t="n">
-        <v>11.28714656829834</v>
+        <v>11.28714847564697</v>
       </c>
       <c r="C252" t="n">
-        <v>11.42030519411861</v>
+        <v>11.42030712396893</v>
       </c>
       <c r="D252" t="n">
-        <v>11.19315237601335</v>
+        <v>11.19315426747845</v>
       </c>
       <c r="E252" t="n">
-        <v>11.39680683279722</v>
+        <v>11.39680875867669</v>
       </c>
       <c r="F252" t="n">
         <v>2288800</v>
@@ -5472,16 +5472,16 @@
         <v>45013</v>
       </c>
       <c r="B253" t="n">
-        <v>11.4203052520752</v>
+        <v>11.42030620574951</v>
       </c>
       <c r="C253" t="n">
-        <v>11.45163664966253</v>
+        <v>11.45163760595323</v>
       </c>
       <c r="D253" t="n">
-        <v>11.25581522799183</v>
+        <v>11.25581616793009</v>
       </c>
       <c r="E253" t="n">
-        <v>11.3106449870198</v>
+        <v>11.31064593153673</v>
       </c>
       <c r="F253" t="n">
         <v>3302900</v>
@@ -5492,16 +5492,16 @@
         <v>45014</v>
       </c>
       <c r="B254" t="n">
-        <v>11.36547756195068</v>
+        <v>11.36547660827637</v>
       </c>
       <c r="C254" t="n">
-        <v>11.4751370999684</v>
+        <v>11.47513613709258</v>
       </c>
       <c r="D254" t="n">
-        <v>11.19315447035196</v>
+        <v>11.19315353113723</v>
       </c>
       <c r="E254" t="n">
-        <v>11.43597340610469</v>
+        <v>11.43597244651508</v>
       </c>
       <c r="F254" t="n">
         <v>2326000</v>
@@ -5512,16 +5512,16 @@
         <v>45015</v>
       </c>
       <c r="B255" t="n">
-        <v>11.40464115142822</v>
+        <v>11.40464019775391</v>
       </c>
       <c r="C255" t="n">
-        <v>11.50646764427175</v>
+        <v>11.50646668208254</v>
       </c>
       <c r="D255" t="n">
-        <v>11.12265779586299</v>
+        <v>11.12265686576857</v>
       </c>
       <c r="E255" t="n">
-        <v>11.42030647840433</v>
+        <v>11.42030552342006</v>
       </c>
       <c r="F255" t="n">
         <v>3320400</v>
@@ -5572,16 +5572,16 @@
         <v>45020</v>
       </c>
       <c r="B258" t="n">
-        <v>11.43597316741943</v>
+        <v>11.43597221374512</v>
       </c>
       <c r="C258" t="n">
-        <v>11.498635972693</v>
+        <v>11.49863501379308</v>
       </c>
       <c r="D258" t="n">
-        <v>11.24798400459917</v>
+        <v>11.24798306660174</v>
       </c>
       <c r="E258" t="n">
-        <v>11.35764428732769</v>
+        <v>11.35764334018542</v>
       </c>
       <c r="F258" t="n">
         <v>5230100</v>
@@ -5732,16 +5732,16 @@
         <v>45033</v>
       </c>
       <c r="B266" t="n">
-        <v>12.05476760864258</v>
+        <v>12.05476856231689</v>
       </c>
       <c r="C266" t="n">
-        <v>12.14092876970129</v>
+        <v>12.14092973019197</v>
       </c>
       <c r="D266" t="n">
-        <v>11.89027757607632</v>
+        <v>11.89027851673754</v>
       </c>
       <c r="E266" t="n">
-        <v>11.99210481023634</v>
+        <v>11.99210575895329</v>
       </c>
       <c r="F266" t="n">
         <v>4936300</v>
@@ -5832,16 +5832,16 @@
         <v>45041</v>
       </c>
       <c r="B271" t="n">
-        <v>12.06260108947754</v>
+        <v>12.06260013580322</v>
       </c>
       <c r="C271" t="n">
-        <v>12.14092996872072</v>
+        <v>12.14092900885369</v>
       </c>
       <c r="D271" t="n">
-        <v>11.96860688258545</v>
+        <v>11.96860593634236</v>
       </c>
       <c r="E271" t="n">
-        <v>12.11743160374759</v>
+        <v>12.11743064573835</v>
       </c>
       <c r="F271" t="n">
         <v>2381100</v>
@@ -5852,16 +5852,16 @@
         <v>45042</v>
       </c>
       <c r="B272" t="n">
-        <v>11.99993705749512</v>
+        <v>11.99993801116943</v>
       </c>
       <c r="C272" t="n">
-        <v>12.12526265386591</v>
+        <v>12.12526361750026</v>
       </c>
       <c r="D272" t="n">
-        <v>11.95294033235581</v>
+        <v>11.95294128229514</v>
       </c>
       <c r="E272" t="n">
-        <v>12.10176429129625</v>
+        <v>12.10176525306311</v>
       </c>
       <c r="F272" t="n">
         <v>2471700</v>
@@ -5932,16 +5932,16 @@
         <v>45049</v>
       </c>
       <c r="B276" t="n">
-        <v>12.28975296020508</v>
+        <v>12.28975391387939</v>
       </c>
       <c r="C276" t="n">
-        <v>12.48557439565576</v>
+        <v>12.48557536452565</v>
       </c>
       <c r="D276" t="n">
-        <v>12.28192067050667</v>
+        <v>12.2819216235732</v>
       </c>
       <c r="E276" t="n">
-        <v>12.48557439565576</v>
+        <v>12.48557536452565</v>
       </c>
       <c r="F276" t="n">
         <v>6661600</v>
@@ -5992,16 +5992,16 @@
         <v>45054</v>
       </c>
       <c r="B279" t="n">
-        <v>12.11165904998779</v>
+        <v>12.11165809631348</v>
       </c>
       <c r="C279" t="n">
-        <v>12.58781451078781</v>
+        <v>12.58781351962092</v>
       </c>
       <c r="D279" t="n">
-        <v>12.05105773110397</v>
+        <v>12.05105678220141</v>
       </c>
       <c r="E279" t="n">
-        <v>12.54452750060035</v>
+        <v>12.54452651284189</v>
       </c>
       <c r="F279" t="n">
         <v>5826000</v>
@@ -6132,16 +6132,16 @@
         <v>45063</v>
       </c>
       <c r="B286" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="C286" t="n">
-        <v>12.24151939290137</v>
+        <v>12.24152036724783</v>
       </c>
       <c r="D286" t="n">
-        <v>11.94716873091856</v>
+        <v>11.9471696818366</v>
       </c>
       <c r="E286" t="n">
-        <v>12.12897350298847</v>
+        <v>12.128974468377</v>
       </c>
       <c r="F286" t="n">
         <v>4330800</v>
@@ -6152,16 +6152,16 @@
         <v>45064</v>
       </c>
       <c r="B287" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="C287" t="n">
-        <v>12.05971462083146</v>
+        <v>12.05971558070743</v>
       </c>
       <c r="D287" t="n">
-        <v>11.82596527432829</v>
+        <v>11.82596621559931</v>
       </c>
       <c r="E287" t="n">
-        <v>12.01642761307558</v>
+        <v>12.01642856950617</v>
       </c>
       <c r="F287" t="n">
         <v>4680600</v>
@@ -6172,16 +6172,16 @@
         <v>45065</v>
       </c>
       <c r="B288" t="n">
-        <v>12.09434413909912</v>
+        <v>12.09434509277344</v>
       </c>
       <c r="C288" t="n">
-        <v>12.18091732953242</v>
+        <v>12.18091829003328</v>
       </c>
       <c r="D288" t="n">
-        <v>11.93851124043578</v>
+        <v>11.93851218182222</v>
       </c>
       <c r="E288" t="n">
-        <v>11.99911255630219</v>
+        <v>11.99911350246722</v>
       </c>
       <c r="F288" t="n">
         <v>2962700</v>
@@ -6232,16 +6232,16 @@
         <v>45070</v>
       </c>
       <c r="B291" t="n">
-        <v>12.25017738342285</v>
+        <v>12.25017642974854</v>
       </c>
       <c r="C291" t="n">
-        <v>12.30212196315428</v>
+        <v>12.30212100543608</v>
       </c>
       <c r="D291" t="n">
-        <v>12.18091849420168</v>
+        <v>12.18091754591915</v>
       </c>
       <c r="E291" t="n">
-        <v>12.26749251854369</v>
+        <v>12.26749156352139</v>
       </c>
       <c r="F291" t="n">
         <v>1846000</v>
@@ -6292,16 +6292,16 @@
         <v>45075</v>
       </c>
       <c r="B294" t="n">
-        <v>12.28480625152588</v>
+        <v>12.28480529785156</v>
       </c>
       <c r="C294" t="n">
-        <v>12.34540839597375</v>
+        <v>12.34540743759487</v>
       </c>
       <c r="D294" t="n">
-        <v>12.16360361389222</v>
+        <v>12.16360266962691</v>
       </c>
       <c r="E294" t="n">
-        <v>12.16360361389222</v>
+        <v>12.16360266962691</v>
       </c>
       <c r="F294" t="n">
         <v>1431900</v>
@@ -6352,16 +6352,16 @@
         <v>45078</v>
       </c>
       <c r="B297" t="n">
-        <v>12.2415189743042</v>
+        <v>12.24151992797852</v>
       </c>
       <c r="C297" t="n">
-        <v>12.30212028771158</v>
+        <v>12.30212124610704</v>
       </c>
       <c r="D297" t="n">
-        <v>12.16360252813415</v>
+        <v>12.1636034757384</v>
       </c>
       <c r="E297" t="n">
-        <v>12.26749084781722</v>
+        <v>12.26749180351488</v>
       </c>
       <c r="F297" t="n">
         <v>2308800</v>
@@ -6412,16 +6412,16 @@
         <v>45083</v>
       </c>
       <c r="B300" t="n">
-        <v>12.32809257507324</v>
+        <v>12.32809352874756</v>
       </c>
       <c r="C300" t="n">
-        <v>12.41466659053087</v>
+        <v>12.41466755090237</v>
       </c>
       <c r="D300" t="n">
-        <v>12.07702892100332</v>
+        <v>12.0770298552559</v>
       </c>
       <c r="E300" t="n">
-        <v>12.08568648767528</v>
+        <v>12.08568742259759</v>
       </c>
       <c r="F300" t="n">
         <v>7376500</v>
@@ -6452,16 +6452,16 @@
         <v>45086</v>
       </c>
       <c r="B302" t="n">
-        <v>12.37138080596924</v>
+        <v>12.37137985229492</v>
       </c>
       <c r="C302" t="n">
-        <v>12.42332538550581</v>
+        <v>12.42332442782724</v>
       </c>
       <c r="D302" t="n">
-        <v>12.26749247252717</v>
+        <v>12.26749152686131</v>
       </c>
       <c r="E302" t="n">
-        <v>12.29346434947992</v>
+        <v>12.29346340181196</v>
       </c>
       <c r="F302" t="n">
         <v>4999400</v>
@@ -6472,16 +6472,16 @@
         <v>45089</v>
       </c>
       <c r="B303" t="n">
-        <v>12.45795440673828</v>
+        <v>12.45795345306396</v>
       </c>
       <c r="C303" t="n">
-        <v>12.45795440673828</v>
+        <v>12.45795345306396</v>
       </c>
       <c r="D303" t="n">
-        <v>12.25883448851593</v>
+        <v>12.25883355008453</v>
       </c>
       <c r="E303" t="n">
-        <v>12.3800379528961</v>
+        <v>12.3800370051864</v>
       </c>
       <c r="F303" t="n">
         <v>2572800</v>
@@ -6532,16 +6532,16 @@
         <v>45092</v>
       </c>
       <c r="B306" t="n">
-        <v>12.4666109085083</v>
+        <v>12.46661186218262</v>
       </c>
       <c r="C306" t="n">
-        <v>12.49258360971007</v>
+        <v>12.49258456537125</v>
       </c>
       <c r="D306" t="n">
-        <v>12.36272258059435</v>
+        <v>12.36272352632139</v>
       </c>
       <c r="E306" t="n">
-        <v>12.45795416707208</v>
+        <v>12.45795512008417</v>
       </c>
       <c r="F306" t="n">
         <v>1266000</v>
@@ -6572,16 +6572,16 @@
         <v>45096</v>
       </c>
       <c r="B308" t="n">
-        <v>12.61378574371338</v>
+        <v>12.6137866973877</v>
       </c>
       <c r="C308" t="n">
-        <v>12.80424808345158</v>
+        <v>12.80424905152594</v>
       </c>
       <c r="D308" t="n">
-        <v>12.38869478834751</v>
+        <v>12.38869572500366</v>
       </c>
       <c r="E308" t="n">
-        <v>12.80424808345158</v>
+        <v>12.80424905152594</v>
       </c>
       <c r="F308" t="n">
         <v>3301400</v>
@@ -6592,16 +6592,16 @@
         <v>45097</v>
       </c>
       <c r="B309" t="n">
-        <v>12.72633171081543</v>
+        <v>12.72633266448975</v>
       </c>
       <c r="C309" t="n">
-        <v>12.89947891815102</v>
+        <v>12.89947988480048</v>
       </c>
       <c r="D309" t="n">
-        <v>12.64841526110666</v>
+        <v>12.64841620894215</v>
       </c>
       <c r="E309" t="n">
-        <v>12.69170226934831</v>
+        <v>12.6917032204276</v>
       </c>
       <c r="F309" t="n">
         <v>3568000</v>
@@ -6612,16 +6612,16 @@
         <v>45098</v>
       </c>
       <c r="B310" t="n">
-        <v>12.86485004425049</v>
+        <v>12.86484909057617</v>
       </c>
       <c r="C310" t="n">
-        <v>12.90813705440186</v>
+        <v>12.90813609751867</v>
       </c>
       <c r="D310" t="n">
-        <v>12.63975907759925</v>
+        <v>12.63975814061098</v>
       </c>
       <c r="E310" t="n">
-        <v>12.75230414810935</v>
+        <v>12.75230320277808</v>
       </c>
       <c r="F310" t="n">
         <v>5022600</v>
@@ -6632,16 +6632,16 @@
         <v>45099</v>
       </c>
       <c r="B311" t="n">
-        <v>12.78693389892578</v>
+        <v>12.7869348526001</v>
       </c>
       <c r="C311" t="n">
-        <v>12.84753521530501</v>
+        <v>12.84753617349909</v>
       </c>
       <c r="D311" t="n">
-        <v>12.64841530692453</v>
+        <v>12.64841625026786</v>
       </c>
       <c r="E311" t="n">
-        <v>12.78693389892578</v>
+        <v>12.7869348526001</v>
       </c>
       <c r="F311" t="n">
         <v>2039700</v>
@@ -6652,16 +6652,16 @@
         <v>45100</v>
       </c>
       <c r="B312" t="n">
-        <v>12.9427661895752</v>
+        <v>12.94276714324951</v>
       </c>
       <c r="C312" t="n">
-        <v>13.07262721694078</v>
+        <v>13.07262818018377</v>
       </c>
       <c r="D312" t="n">
-        <v>12.7609614117682</v>
+        <v>12.76096235204642</v>
       </c>
       <c r="E312" t="n">
-        <v>12.81290598784064</v>
+        <v>12.81290693194634</v>
       </c>
       <c r="F312" t="n">
         <v>2959500</v>
@@ -6692,16 +6692,16 @@
         <v>45104</v>
       </c>
       <c r="B314" t="n">
-        <v>12.50123977661133</v>
+        <v>12.50124073028564</v>
       </c>
       <c r="C314" t="n">
-        <v>12.83887744603771</v>
+        <v>12.83887842546918</v>
       </c>
       <c r="D314" t="n">
-        <v>12.3973514534719</v>
+        <v>12.39735239922096</v>
       </c>
       <c r="E314" t="n">
-        <v>12.76961856394476</v>
+        <v>12.76961953809272</v>
       </c>
       <c r="F314" t="n">
         <v>3014700</v>
@@ -6812,16 +6812,16 @@
         <v>45112</v>
       </c>
       <c r="B320" t="n">
-        <v>12.44063854217529</v>
+        <v>12.44063949584961</v>
       </c>
       <c r="C320" t="n">
-        <v>12.54452686599102</v>
+        <v>12.54452782762921</v>
       </c>
       <c r="D320" t="n">
-        <v>12.24151946126957</v>
+        <v>12.24152039967981</v>
       </c>
       <c r="E320" t="n">
-        <v>12.30212077708766</v>
+        <v>12.30212172014348</v>
       </c>
       <c r="F320" t="n">
         <v>5051100</v>
@@ -6832,16 +6832,16 @@
         <v>45113</v>
       </c>
       <c r="B321" t="n">
-        <v>12.32809257507324</v>
+        <v>12.32809352874756</v>
       </c>
       <c r="C321" t="n">
-        <v>12.48392547264458</v>
+        <v>12.48392643837378</v>
       </c>
       <c r="D321" t="n">
-        <v>12.25017612628758</v>
+        <v>12.25017707393445</v>
       </c>
       <c r="E321" t="n">
-        <v>12.4319808982438</v>
+        <v>12.43198185995469</v>
       </c>
       <c r="F321" t="n">
         <v>2081000</v>
@@ -6872,16 +6872,16 @@
         <v>45117</v>
       </c>
       <c r="B323" t="n">
-        <v>12.38869571685791</v>
+        <v>12.38869476318359</v>
       </c>
       <c r="C323" t="n">
-        <v>12.45795460456609</v>
+        <v>12.45795364556026</v>
       </c>
       <c r="D323" t="n">
-        <v>12.31077926177845</v>
+        <v>12.31077831410209</v>
       </c>
       <c r="E323" t="n">
-        <v>12.38003814948662</v>
+        <v>12.38003719647876</v>
       </c>
       <c r="F323" t="n">
         <v>1514600</v>
@@ -6912,16 +6912,16 @@
         <v>45119</v>
       </c>
       <c r="B325" t="n">
-        <v>12.38869571685791</v>
+        <v>12.38869476318359</v>
       </c>
       <c r="C325" t="n">
-        <v>12.45795460456609</v>
+        <v>12.45795364556026</v>
       </c>
       <c r="D325" t="n">
-        <v>12.28480655966458</v>
+        <v>12.28480561398759</v>
       </c>
       <c r="E325" t="n">
-        <v>12.37138058211533</v>
+        <v>12.37137962977392</v>
       </c>
       <c r="F325" t="n">
         <v>1842800</v>
@@ -6932,16 +6932,16 @@
         <v>45120</v>
       </c>
       <c r="B326" t="n">
-        <v>12.44063854217529</v>
+        <v>12.44063949584961</v>
       </c>
       <c r="C326" t="n">
-        <v>12.51855499144484</v>
+        <v>12.51855595109208</v>
       </c>
       <c r="D326" t="n">
-        <v>12.34540778508529</v>
+        <v>12.34540873145941</v>
       </c>
       <c r="E326" t="n">
-        <v>12.4752679834472</v>
+        <v>12.47526893977614</v>
       </c>
       <c r="F326" t="n">
         <v>1737300</v>
@@ -6952,16 +6952,16 @@
         <v>45121</v>
       </c>
       <c r="B327" t="n">
-        <v>12.38003826141357</v>
+        <v>12.38003730773926</v>
       </c>
       <c r="C327" t="n">
-        <v>12.48392659391508</v>
+        <v>12.48392563223791</v>
       </c>
       <c r="D327" t="n">
-        <v>12.33675124979684</v>
+        <v>12.33675029945707</v>
       </c>
       <c r="E327" t="n">
-        <v>12.48392659391508</v>
+        <v>12.48392563223791</v>
       </c>
       <c r="F327" t="n">
         <v>1319400</v>
@@ -7052,16 +7052,16 @@
         <v>45128</v>
       </c>
       <c r="B332" t="n">
-        <v>12.38869571685791</v>
+        <v>12.38869476318359</v>
       </c>
       <c r="C332" t="n">
-        <v>12.38869571685791</v>
+        <v>12.38869476318359</v>
       </c>
       <c r="D332" t="n">
-        <v>12.2242052393277</v>
+        <v>12.22420429831576</v>
       </c>
       <c r="E332" t="n">
-        <v>12.27614981792436</v>
+        <v>12.27614887291376</v>
       </c>
       <c r="F332" t="n">
         <v>2631400</v>
@@ -7192,16 +7192,16 @@
         <v>45139</v>
       </c>
       <c r="B339" t="n">
-        <v>12.12897396087646</v>
+        <v>12.12897491455078</v>
       </c>
       <c r="C339" t="n">
-        <v>12.38003762458143</v>
+        <v>12.38003859799633</v>
       </c>
       <c r="D339" t="n">
-        <v>12.08568695148643</v>
+        <v>12.08568790175718</v>
       </c>
       <c r="E339" t="n">
-        <v>12.12031639387225</v>
+        <v>12.12031734686584</v>
       </c>
       <c r="F339" t="n">
         <v>5884200</v>
@@ -7332,16 +7332,16 @@
         <v>45148</v>
       </c>
       <c r="B346" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C346" t="n">
-        <v>12.09434452900206</v>
+        <v>12.09434549372545</v>
       </c>
       <c r="D346" t="n">
-        <v>11.88656704887551</v>
+        <v>11.88656799702522</v>
       </c>
       <c r="E346" t="n">
-        <v>12.01642807715848</v>
+        <v>12.01642903566675</v>
       </c>
       <c r="F346" t="n">
         <v>2835300</v>
@@ -7352,16 +7352,16 @@
         <v>45149</v>
       </c>
       <c r="B347" t="n">
-        <v>11.92119693756104</v>
+        <v>11.92119789123535</v>
       </c>
       <c r="C347" t="n">
-        <v>11.97314068671642</v>
+        <v>11.97314164454614</v>
       </c>
       <c r="D347" t="n">
-        <v>11.83462292146072</v>
+        <v>11.83462386820927</v>
       </c>
       <c r="E347" t="n">
-        <v>11.97314068671642</v>
+        <v>11.97314164454614</v>
       </c>
       <c r="F347" t="n">
         <v>2472600</v>
@@ -7392,16 +7392,16 @@
         <v>45153</v>
       </c>
       <c r="B349" t="n">
-        <v>11.860595703125</v>
+        <v>11.86059474945068</v>
       </c>
       <c r="C349" t="n">
-        <v>11.99911347897441</v>
+        <v>11.9991125141623</v>
       </c>
       <c r="D349" t="n">
-        <v>11.85193813572664</v>
+        <v>11.85193718274846</v>
       </c>
       <c r="E349" t="n">
-        <v>11.91254028188406</v>
+        <v>11.91253932403304</v>
       </c>
       <c r="F349" t="n">
         <v>2713800</v>
@@ -7452,16 +7452,16 @@
         <v>45156</v>
       </c>
       <c r="B352" t="n">
-        <v>11.77402210235596</v>
+        <v>11.77402114868164</v>
       </c>
       <c r="C352" t="n">
-        <v>11.80865154513102</v>
+        <v>11.80865058865178</v>
       </c>
       <c r="D352" t="n">
-        <v>11.65281863982772</v>
+        <v>11.65281769597066</v>
       </c>
       <c r="E352" t="n">
-        <v>11.71341995827632</v>
+        <v>11.71341900951066</v>
       </c>
       <c r="F352" t="n">
         <v>3061800</v>
@@ -7512,16 +7512,16 @@
         <v>45161</v>
       </c>
       <c r="B355" t="n">
-        <v>11.87791061401367</v>
+        <v>11.87790966033936</v>
       </c>
       <c r="C355" t="n">
-        <v>11.89522492285292</v>
+        <v>11.89522396778845</v>
       </c>
       <c r="D355" t="n">
-        <v>11.79133659292425</v>
+        <v>11.79133564620093</v>
       </c>
       <c r="E355" t="n">
-        <v>11.86059547954337</v>
+        <v>11.86059452725928</v>
       </c>
       <c r="F355" t="n">
         <v>2615000</v>
@@ -7532,16 +7532,16 @@
         <v>45162</v>
       </c>
       <c r="B356" t="n">
-        <v>11.97314167022705</v>
+        <v>11.97314071655273</v>
       </c>
       <c r="C356" t="n">
-        <v>11.99911354693815</v>
+        <v>11.99911259119515</v>
       </c>
       <c r="D356" t="n">
-        <v>11.89522521446267</v>
+        <v>11.89522426699448</v>
       </c>
       <c r="E356" t="n">
-        <v>11.90388278191006</v>
+        <v>11.90388183375229</v>
       </c>
       <c r="F356" t="n">
         <v>2322800</v>
@@ -7572,16 +7572,16 @@
         <v>45166</v>
       </c>
       <c r="B358" t="n">
-        <v>11.96448421478271</v>
+        <v>11.9644832611084</v>
       </c>
       <c r="C358" t="n">
-        <v>11.99911365926539</v>
+        <v>11.9991127028308</v>
       </c>
       <c r="D358" t="n">
-        <v>11.84328157190891</v>
+        <v>11.8432806278955</v>
       </c>
       <c r="E358" t="n">
-        <v>11.95582747288536</v>
+        <v>11.95582651990106</v>
       </c>
       <c r="F358" t="n">
         <v>2184700</v>
@@ -7612,16 +7612,16 @@
         <v>45168</v>
       </c>
       <c r="B360" t="n">
-        <v>12.11165904998779</v>
+        <v>12.11165809631348</v>
       </c>
       <c r="C360" t="n">
-        <v>12.19823307036272</v>
+        <v>12.19823210987155</v>
       </c>
       <c r="D360" t="n">
-        <v>12.05971529826767</v>
+        <v>12.05971434868342</v>
       </c>
       <c r="E360" t="n">
-        <v>12.17226119450266</v>
+        <v>12.17226023605652</v>
       </c>
       <c r="F360" t="n">
         <v>1998700</v>
@@ -7672,16 +7672,16 @@
         <v>45173</v>
       </c>
       <c r="B363" t="n">
-        <v>12.01642799377441</v>
+        <v>12.01642894744873</v>
       </c>
       <c r="C363" t="n">
-        <v>12.05105743595003</v>
+        <v>12.05105839237269</v>
       </c>
       <c r="D363" t="n">
-        <v>11.81730808204133</v>
+        <v>11.81730901991265</v>
       </c>
       <c r="E363" t="n">
-        <v>12.05105743595003</v>
+        <v>12.05105839237269</v>
       </c>
       <c r="F363" t="n">
         <v>2040600</v>
@@ -7692,16 +7692,16 @@
         <v>45174</v>
       </c>
       <c r="B364" t="n">
-        <v>11.92119693756104</v>
+        <v>11.92119789123535</v>
       </c>
       <c r="C364" t="n">
-        <v>12.06837144392197</v>
+        <v>12.06837240936998</v>
       </c>
       <c r="D364" t="n">
-        <v>11.9125393708248</v>
+        <v>11.91254032380653</v>
       </c>
       <c r="E364" t="n">
-        <v>12.04239956934427</v>
+        <v>12.04240053271458</v>
       </c>
       <c r="F364" t="n">
         <v>3869600</v>
@@ -7712,16 +7712,16 @@
         <v>45175</v>
       </c>
       <c r="B365" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C365" t="n">
-        <v>12.02508564417022</v>
+        <v>12.02508660336907</v>
       </c>
       <c r="D365" t="n">
-        <v>11.81730816404367</v>
+        <v>11.81730910666884</v>
       </c>
       <c r="E365" t="n">
-        <v>11.9385116253149</v>
+        <v>11.93851257760805</v>
       </c>
       <c r="F365" t="n">
         <v>2473500</v>
@@ -7912,16 +7912,16 @@
         <v>45190</v>
       </c>
       <c r="B375" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C375" t="n">
-        <v>12.03374238555092</v>
+        <v>12.0337433454403</v>
       </c>
       <c r="D375" t="n">
-        <v>11.8779103074948</v>
+        <v>11.877911254954</v>
       </c>
       <c r="E375" t="n">
-        <v>12.02508564417022</v>
+        <v>12.02508660336907</v>
       </c>
       <c r="F375" t="n">
         <v>4405700</v>
@@ -7932,16 +7932,16 @@
         <v>45191</v>
       </c>
       <c r="B376" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C376" t="n">
-        <v>12.10300127038276</v>
+        <v>12.10300223579667</v>
       </c>
       <c r="D376" t="n">
-        <v>11.92985405830317</v>
+        <v>11.92985500990573</v>
       </c>
       <c r="E376" t="n">
-        <v>12.02508564417022</v>
+        <v>12.02508660336907</v>
       </c>
       <c r="F376" t="n">
         <v>2812600</v>
@@ -7952,16 +7952,16 @@
         <v>45194</v>
       </c>
       <c r="B377" t="n">
-        <v>11.80865097045898</v>
+        <v>11.8086519241333</v>
       </c>
       <c r="C377" t="n">
-        <v>11.97314060922783</v>
+        <v>11.97314157618643</v>
       </c>
       <c r="D377" t="n">
-        <v>11.80865097045898</v>
+        <v>11.8086519241333</v>
       </c>
       <c r="E377" t="n">
-        <v>11.95582630149842</v>
+        <v>11.95582726705872</v>
       </c>
       <c r="F377" t="n">
         <v>3691700</v>
@@ -7972,16 +7972,16 @@
         <v>45195</v>
       </c>
       <c r="B378" t="n">
-        <v>11.83462238311768</v>
+        <v>11.83462333679199</v>
       </c>
       <c r="C378" t="n">
-        <v>12.06837089494598</v>
+        <v>12.06837186745655</v>
       </c>
       <c r="D378" t="n">
-        <v>11.78267781069418</v>
+        <v>11.78267876018263</v>
       </c>
       <c r="E378" t="n">
-        <v>11.80865050972141</v>
+        <v>11.80865146130283</v>
       </c>
       <c r="F378" t="n">
         <v>7795500</v>
@@ -8072,16 +8072,16 @@
         <v>45202</v>
       </c>
       <c r="B383" t="n">
-        <v>11.80865097045898</v>
+        <v>11.8086519241333</v>
       </c>
       <c r="C383" t="n">
-        <v>11.91253929372841</v>
+        <v>11.91254025579282</v>
       </c>
       <c r="D383" t="n">
-        <v>11.75670639600877</v>
+        <v>11.75670734548801</v>
       </c>
       <c r="E383" t="n">
-        <v>11.8605947192782</v>
+        <v>11.86059567714752</v>
       </c>
       <c r="F383" t="n">
         <v>2809600</v>
@@ -8092,16 +8092,16 @@
         <v>45203</v>
       </c>
       <c r="B384" t="n">
-        <v>11.77402210235596</v>
+        <v>11.77402114868164</v>
       </c>
       <c r="C384" t="n">
-        <v>11.86059529647809</v>
+        <v>11.86059433579151</v>
       </c>
       <c r="D384" t="n">
-        <v>11.74804940105138</v>
+        <v>11.7480484494808</v>
       </c>
       <c r="E384" t="n">
-        <v>11.80865154513102</v>
+        <v>11.80865058865178</v>
       </c>
       <c r="F384" t="n">
         <v>4367600</v>
@@ -8192,16 +8192,16 @@
         <v>45210</v>
       </c>
       <c r="B389" t="n">
-        <v>12.09434413909912</v>
+        <v>12.09434509277344</v>
       </c>
       <c r="C389" t="n">
-        <v>12.18957489626505</v>
+        <v>12.18957585744859</v>
       </c>
       <c r="D389" t="n">
-        <v>12.00777012303482</v>
+        <v>12.00777106988252</v>
       </c>
       <c r="E389" t="n">
-        <v>12.09434413909912</v>
+        <v>12.09434509277344</v>
       </c>
       <c r="F389" t="n">
         <v>3458500</v>
@@ -8232,16 +8232,16 @@
         <v>45215</v>
       </c>
       <c r="B391" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="C391" t="n">
-        <v>12.12031593631109</v>
+        <v>12.12031690101054</v>
       </c>
       <c r="D391" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="E391" t="n">
-        <v>12.05971462083146</v>
+        <v>12.05971558070743</v>
       </c>
       <c r="F391" t="n">
         <v>3983600</v>
@@ -8252,16 +8252,16 @@
         <v>45216</v>
       </c>
       <c r="B392" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C392" t="n">
-        <v>12.10300127038276</v>
+        <v>12.10300223579667</v>
       </c>
       <c r="D392" t="n">
-        <v>11.88656704887551</v>
+        <v>11.88656799702522</v>
       </c>
       <c r="E392" t="n">
-        <v>11.97314106773082</v>
+        <v>11.97314202278624</v>
       </c>
       <c r="F392" t="n">
         <v>5165000</v>
@@ -8292,16 +8292,16 @@
         <v>45218</v>
       </c>
       <c r="B394" t="n">
-        <v>11.67013359069824</v>
+        <v>11.67013263702393</v>
       </c>
       <c r="C394" t="n">
-        <v>11.75670761521626</v>
+        <v>11.75670665446719</v>
       </c>
       <c r="D394" t="n">
-        <v>11.62684740407032</v>
+        <v>11.62684645393332</v>
       </c>
       <c r="E394" t="n">
-        <v>11.66147684875131</v>
+        <v>11.66147589578441</v>
       </c>
       <c r="F394" t="n">
         <v>3066300</v>
@@ -8332,16 +8332,16 @@
         <v>45222</v>
       </c>
       <c r="B396" t="n">
-        <v>11.72207736968994</v>
+        <v>11.72207832336426</v>
       </c>
       <c r="C396" t="n">
-        <v>11.90388214825212</v>
+        <v>11.90388311671755</v>
       </c>
       <c r="D396" t="n">
-        <v>11.72207736968994</v>
+        <v>11.72207832336426</v>
       </c>
       <c r="E396" t="n">
-        <v>11.77402194597815</v>
+        <v>11.77402290387853</v>
       </c>
       <c r="F396" t="n">
         <v>3068100</v>
@@ -8432,16 +8432,16 @@
         <v>45229</v>
       </c>
       <c r="B401" t="n">
-        <v>11.49698638916016</v>
+        <v>11.49698543548584</v>
       </c>
       <c r="C401" t="n">
-        <v>11.64416173574207</v>
+        <v>11.64416076985956</v>
       </c>
       <c r="D401" t="n">
-        <v>11.47101451200779</v>
+        <v>11.47101356048784</v>
       </c>
       <c r="E401" t="n">
-        <v>11.57490284624835</v>
+        <v>11.57490188611087</v>
       </c>
       <c r="F401" t="n">
         <v>4549600</v>
@@ -8492,16 +8492,16 @@
         <v>45233</v>
       </c>
       <c r="B404" t="n">
-        <v>11.96448421478271</v>
+        <v>11.9644832611084</v>
       </c>
       <c r="C404" t="n">
-        <v>12.0250863618507</v>
+        <v>12.02508540334586</v>
       </c>
       <c r="D404" t="n">
-        <v>11.65281921443867</v>
+        <v>11.65281828560679</v>
       </c>
       <c r="E404" t="n">
-        <v>11.74804998035825</v>
+        <v>11.74804904393564</v>
       </c>
       <c r="F404" t="n">
         <v>4830800</v>
@@ -8672,16 +8672,16 @@
         <v>45247</v>
       </c>
       <c r="B413" t="n">
-        <v>12.25017738342285</v>
+        <v>12.25017642974854</v>
       </c>
       <c r="C413" t="n">
-        <v>12.48392675376763</v>
+        <v>12.48392578189597</v>
       </c>
       <c r="D413" t="n">
-        <v>12.14628904959109</v>
+        <v>12.14628810400446</v>
       </c>
       <c r="E413" t="n">
-        <v>12.48392675376763</v>
+        <v>12.48392578189597</v>
       </c>
       <c r="F413" t="n">
         <v>3124800</v>
@@ -8712,16 +8712,16 @@
         <v>45251</v>
       </c>
       <c r="B415" t="n">
-        <v>11.97314167022705</v>
+        <v>11.97314071655273</v>
       </c>
       <c r="C415" t="n">
-        <v>12.09434513759732</v>
+        <v>12.09434417426901</v>
       </c>
       <c r="D415" t="n">
-        <v>11.91254034935745</v>
+        <v>11.9125394005101</v>
       </c>
       <c r="E415" t="n">
-        <v>12.08568757014993</v>
+        <v>12.0856866075112</v>
       </c>
       <c r="F415" t="n">
         <v>2713400</v>
@@ -8732,16 +8732,16 @@
         <v>45252</v>
       </c>
       <c r="B416" t="n">
-        <v>12.4666109085083</v>
+        <v>12.46661186218262</v>
       </c>
       <c r="C416" t="n">
-        <v>12.94276636400384</v>
+        <v>12.94276735410323</v>
       </c>
       <c r="D416" t="n">
-        <v>12.44063903293757</v>
+        <v>12.44063998462508</v>
       </c>
       <c r="E416" t="n">
-        <v>12.81290616051917</v>
+        <v>12.81290714068447</v>
       </c>
       <c r="F416" t="n">
         <v>20875500</v>
@@ -8752,16 +8752,16 @@
         <v>45253</v>
       </c>
       <c r="B417" t="n">
-        <v>12.561842918396</v>
+        <v>12.56184196472168</v>
       </c>
       <c r="C417" t="n">
-        <v>12.76961958122722</v>
+        <v>12.76961861177884</v>
       </c>
       <c r="D417" t="n">
-        <v>12.46661132870839</v>
+        <v>12.46661038226389</v>
       </c>
       <c r="E417" t="n">
-        <v>12.76961958122722</v>
+        <v>12.76961861177884</v>
       </c>
       <c r="F417" t="n">
         <v>9122900</v>
@@ -8812,16 +8812,16 @@
         <v>45258</v>
       </c>
       <c r="B420" t="n">
-        <v>12.63975811004639</v>
+        <v>12.6397590637207</v>
       </c>
       <c r="C420" t="n">
-        <v>12.76961830492886</v>
+        <v>12.76961926840118</v>
       </c>
       <c r="D420" t="n">
-        <v>12.57049922935827</v>
+        <v>12.57050017780698</v>
       </c>
       <c r="E420" t="n">
-        <v>12.57915597022104</v>
+        <v>12.57915691932291</v>
       </c>
       <c r="F420" t="n">
         <v>5941200</v>
@@ -8832,16 +8832,16 @@
         <v>45259</v>
       </c>
       <c r="B421" t="n">
-        <v>12.561842918396</v>
+        <v>12.56184196472168</v>
       </c>
       <c r="C421" t="n">
-        <v>12.75230444650908</v>
+        <v>12.75230347837524</v>
       </c>
       <c r="D421" t="n">
-        <v>12.561842918396</v>
+        <v>12.56184196472168</v>
       </c>
       <c r="E421" t="n">
-        <v>12.72633257006295</v>
+        <v>12.72633160390085</v>
       </c>
       <c r="F421" t="n">
         <v>5869600</v>
@@ -8872,16 +8872,16 @@
         <v>45261</v>
       </c>
       <c r="B423" t="n">
-        <v>12.86485004425049</v>
+        <v>12.86484909057617</v>
       </c>
       <c r="C423" t="n">
-        <v>12.96873837323515</v>
+        <v>12.96873741185957</v>
       </c>
       <c r="D423" t="n">
-        <v>12.70901796358902</v>
+        <v>12.70901702146657</v>
       </c>
       <c r="E423" t="n">
-        <v>12.72633227227094</v>
+        <v>12.72633132886498</v>
       </c>
       <c r="F423" t="n">
         <v>6458300</v>
@@ -8892,16 +8892,16 @@
         <v>45264</v>
       </c>
       <c r="B424" t="n">
-        <v>12.89947891235352</v>
+        <v>12.89947986602783</v>
       </c>
       <c r="C424" t="n">
-        <v>12.98605292879791</v>
+        <v>12.98605388887275</v>
       </c>
       <c r="D424" t="n">
-        <v>12.86484947090196</v>
+        <v>12.86485042201608</v>
       </c>
       <c r="E424" t="n">
-        <v>12.94276592057571</v>
+        <v>12.94276687745029</v>
       </c>
       <c r="F424" t="n">
         <v>7048400</v>
@@ -8932,16 +8932,16 @@
         <v>45266</v>
       </c>
       <c r="B426" t="n">
-        <v>13.07262802124023</v>
+        <v>13.07262706756592</v>
       </c>
       <c r="C426" t="n">
-        <v>13.27174711956826</v>
+        <v>13.2717461513678</v>
       </c>
       <c r="D426" t="n">
-        <v>13.04665531879052</v>
+        <v>13.04665436701096</v>
       </c>
       <c r="E426" t="n">
-        <v>13.21114579844774</v>
+        <v>13.21114483466828</v>
       </c>
       <c r="F426" t="n">
         <v>5861300</v>
@@ -8952,16 +8952,16 @@
         <v>45267</v>
       </c>
       <c r="B427" t="n">
-        <v>13.1159143447876</v>
+        <v>13.11591339111328</v>
       </c>
       <c r="C427" t="n">
-        <v>13.15054378945223</v>
+        <v>13.15054283325996</v>
       </c>
       <c r="D427" t="n">
-        <v>12.97739656612907</v>
+        <v>12.97739562252655</v>
       </c>
       <c r="E427" t="n">
-        <v>13.10725760284475</v>
+        <v>13.10725664979988</v>
       </c>
       <c r="F427" t="n">
         <v>6196000</v>
@@ -8972,16 +8972,16 @@
         <v>45268</v>
       </c>
       <c r="B428" t="n">
-        <v>12.92545223236084</v>
+        <v>12.92545127868652</v>
       </c>
       <c r="C428" t="n">
-        <v>13.15920076695787</v>
+        <v>13.15919979603697</v>
       </c>
       <c r="D428" t="n">
-        <v>12.86485008769187</v>
+        <v>12.86484913848894</v>
       </c>
       <c r="E428" t="n">
-        <v>13.15920076695787</v>
+        <v>13.15919979603697</v>
       </c>
       <c r="F428" t="n">
         <v>10990100</v>
@@ -9052,16 +9052,16 @@
         <v>45274</v>
       </c>
       <c r="B432" t="n">
-        <v>12.94470119476318</v>
+        <v>12.94470024108887</v>
       </c>
       <c r="C432" t="n">
-        <v>12.9831984112191</v>
+        <v>12.98319745470858</v>
       </c>
       <c r="D432" t="n">
-        <v>12.71371789602766</v>
+        <v>12.71371695937057</v>
       </c>
       <c r="E432" t="n">
-        <v>12.71371789602766</v>
+        <v>12.71371695937057</v>
       </c>
       <c r="F432" t="n">
         <v>5480800</v>
@@ -9092,16 +9092,16 @@
         <v>45278</v>
       </c>
       <c r="B434" t="n">
-        <v>12.8484582901001</v>
+        <v>12.84845733642578</v>
       </c>
       <c r="C434" t="n">
-        <v>13.08906611637279</v>
+        <v>13.0890651448394</v>
       </c>
       <c r="D434" t="n">
-        <v>12.8484582901001</v>
+        <v>12.84845733642578</v>
       </c>
       <c r="E434" t="n">
-        <v>12.98319808539135</v>
+        <v>12.983197121716</v>
       </c>
       <c r="F434" t="n">
         <v>3314300</v>
@@ -9112,16 +9112,16 @@
         <v>45279</v>
       </c>
       <c r="B435" t="n">
-        <v>12.86770534515381</v>
+        <v>12.86770629882812</v>
       </c>
       <c r="C435" t="n">
-        <v>12.94469976958878</v>
+        <v>12.94470072896945</v>
       </c>
       <c r="D435" t="n">
-        <v>12.79071092071883</v>
+        <v>12.7907118686868</v>
       </c>
       <c r="E435" t="n">
-        <v>12.87732987766966</v>
+        <v>12.87733083205729</v>
       </c>
       <c r="F435" t="n">
         <v>4780200</v>
@@ -9232,16 +9232,16 @@
         <v>45288</v>
       </c>
       <c r="B441" t="n">
-        <v>12.80996131896973</v>
+        <v>12.80996036529541</v>
       </c>
       <c r="C441" t="n">
-        <v>12.88695575141803</v>
+        <v>12.88695479201164</v>
       </c>
       <c r="D441" t="n">
-        <v>12.76183956922803</v>
+        <v>12.76183861913627</v>
       </c>
       <c r="E441" t="n">
-        <v>12.88695575141803</v>
+        <v>12.88695479201164</v>
       </c>
       <c r="F441" t="n">
         <v>3487000</v>
@@ -9332,16 +9332,16 @@
         <v>45299</v>
       </c>
       <c r="B446" t="n">
-        <v>13.01207160949707</v>
+        <v>13.01207065582275</v>
       </c>
       <c r="C446" t="n">
-        <v>13.09868965545936</v>
+        <v>13.09868869543668</v>
       </c>
       <c r="D446" t="n">
-        <v>12.88695543042352</v>
+        <v>12.88695448591916</v>
       </c>
       <c r="E446" t="n">
-        <v>12.9543253276762</v>
+        <v>12.95432437823419</v>
       </c>
       <c r="F446" t="n">
         <v>3738800</v>
@@ -9392,16 +9392,16 @@
         <v>45302</v>
       </c>
       <c r="B449" t="n">
-        <v>12.8484582901001</v>
+        <v>12.84845733642578</v>
       </c>
       <c r="C449" t="n">
-        <v>12.94470086990156</v>
+        <v>12.94469990908366</v>
       </c>
       <c r="D449" t="n">
-        <v>12.74259025911866</v>
+        <v>12.74258931330238</v>
       </c>
       <c r="E449" t="n">
-        <v>12.94470086990156</v>
+        <v>12.94469990908366</v>
       </c>
       <c r="F449" t="n">
         <v>4814200</v>
@@ -9412,16 +9412,16 @@
         <v>45303</v>
       </c>
       <c r="B450" t="n">
-        <v>12.77146339416504</v>
+        <v>12.77146434783936</v>
       </c>
       <c r="C450" t="n">
-        <v>12.88695503642984</v>
+        <v>12.88695599872818</v>
       </c>
       <c r="D450" t="n">
-        <v>12.74258979521435</v>
+        <v>12.74259074673261</v>
       </c>
       <c r="E450" t="n">
-        <v>12.84845782234157</v>
+        <v>12.84845878176524</v>
       </c>
       <c r="F450" t="n">
         <v>4041800</v>
@@ -9432,16 +9432,16 @@
         <v>45306</v>
       </c>
       <c r="B451" t="n">
-        <v>12.80996131896973</v>
+        <v>12.80996036529541</v>
       </c>
       <c r="C451" t="n">
-        <v>12.84845853519388</v>
+        <v>12.84845757865353</v>
       </c>
       <c r="D451" t="n">
-        <v>12.74259050219293</v>
+        <v>12.74258955353423</v>
       </c>
       <c r="E451" t="n">
-        <v>12.77146410274557</v>
+        <v>12.77146315193729</v>
       </c>
       <c r="F451" t="n">
         <v>1955800</v>
@@ -9492,16 +9492,16 @@
         <v>45309</v>
       </c>
       <c r="B454" t="n">
-        <v>12.55972862243652</v>
+        <v>12.55972766876221</v>
       </c>
       <c r="C454" t="n">
-        <v>12.77146376499286</v>
+        <v>12.77146279524125</v>
       </c>
       <c r="D454" t="n">
-        <v>12.51160687396745</v>
+        <v>12.51160592394707</v>
       </c>
       <c r="E454" t="n">
-        <v>12.76183923172984</v>
+        <v>12.76183826270904</v>
       </c>
       <c r="F454" t="n">
         <v>6534900</v>
@@ -9532,16 +9532,16 @@
         <v>45313</v>
       </c>
       <c r="B456" t="n">
-        <v>12.61747455596924</v>
+        <v>12.61747360229492</v>
       </c>
       <c r="C456" t="n">
-        <v>12.65597177291335</v>
+        <v>12.65597081632927</v>
       </c>
       <c r="D456" t="n">
-        <v>12.56935372317364</v>
+        <v>12.56935277313647</v>
       </c>
       <c r="E456" t="n">
-        <v>12.60785094011775</v>
+        <v>12.60784998717082</v>
       </c>
       <c r="F456" t="n">
         <v>4490300</v>
@@ -9572,16 +9572,16 @@
         <v>45315</v>
       </c>
       <c r="B458" t="n">
-        <v>12.79071140289307</v>
+        <v>12.79071235656738</v>
       </c>
       <c r="C458" t="n">
-        <v>12.82920861656179</v>
+        <v>12.82920957310646</v>
       </c>
       <c r="D458" t="n">
-        <v>12.64634708109684</v>
+        <v>12.64634802400737</v>
       </c>
       <c r="E458" t="n">
-        <v>12.65597069612954</v>
+        <v>12.6559716397576</v>
       </c>
       <c r="F458" t="n">
         <v>3333600</v>
@@ -9652,16 +9652,16 @@
         <v>45321</v>
       </c>
       <c r="B462" t="n">
-        <v>12.51160621643066</v>
+        <v>12.51160717010498</v>
       </c>
       <c r="C462" t="n">
-        <v>12.63672238873649</v>
+        <v>12.63672335194755</v>
       </c>
       <c r="D462" t="n">
-        <v>12.51160621643066</v>
+        <v>12.51160717010498</v>
       </c>
       <c r="E462" t="n">
-        <v>12.58860064279641</v>
+        <v>12.58860160233948</v>
       </c>
       <c r="F462" t="n">
         <v>3463200</v>
@@ -9672,16 +9672,16 @@
         <v>45322</v>
       </c>
       <c r="B463" t="n">
-        <v>12.68484497070312</v>
+        <v>12.68484401702881</v>
       </c>
       <c r="C463" t="n">
-        <v>12.79071208447197</v>
+        <v>12.79071112283833</v>
       </c>
       <c r="D463" t="n">
-        <v>12.53085610782262</v>
+        <v>12.53085516572552</v>
       </c>
       <c r="E463" t="n">
-        <v>12.57897693908826</v>
+        <v>12.57897599337333</v>
       </c>
       <c r="F463" t="n">
         <v>3755000</v>
@@ -9812,16 +9812,16 @@
         <v>45331</v>
       </c>
       <c r="B470" t="n">
-        <v>12.48273372650146</v>
+        <v>12.48273468017578</v>
       </c>
       <c r="C470" t="n">
-        <v>12.62709804867886</v>
+        <v>12.62709901338253</v>
       </c>
       <c r="D470" t="n">
-        <v>12.36724208519036</v>
+        <v>12.36724303004117</v>
       </c>
       <c r="E470" t="n">
-        <v>12.36724208519036</v>
+        <v>12.36724303004117</v>
       </c>
       <c r="F470" t="n">
         <v>4943200</v>
@@ -9852,16 +9852,16 @@
         <v>45337</v>
       </c>
       <c r="B472" t="n">
-        <v>12.50198173522949</v>
+        <v>12.50198268890381</v>
       </c>
       <c r="C472" t="n">
-        <v>12.58860069470964</v>
+        <v>12.58860165499141</v>
       </c>
       <c r="D472" t="n">
-        <v>12.41536277574934</v>
+        <v>12.4153637228162</v>
       </c>
       <c r="E472" t="n">
-        <v>12.46348452188787</v>
+        <v>12.46348547262554</v>
       </c>
       <c r="F472" t="n">
         <v>4740900</v>
@@ -9892,16 +9892,16 @@
         <v>45341</v>
       </c>
       <c r="B474" t="n">
-        <v>12.77146339416504</v>
+        <v>12.77146434783936</v>
       </c>
       <c r="C474" t="n">
-        <v>12.85808143747915</v>
+        <v>12.85808239762144</v>
       </c>
       <c r="D474" t="n">
-        <v>12.53085557665187</v>
+        <v>12.53085651235945</v>
       </c>
       <c r="E474" t="n">
-        <v>12.54047919178945</v>
+        <v>12.54048012821565</v>
       </c>
       <c r="F474" t="n">
         <v>4786000</v>
@@ -9972,16 +9972,16 @@
         <v>45345</v>
       </c>
       <c r="B478" t="n">
-        <v>12.41536235809326</v>
+        <v>12.41536331176758</v>
       </c>
       <c r="C478" t="n">
-        <v>12.55010305917923</v>
+        <v>12.55010402320352</v>
       </c>
       <c r="D478" t="n">
-        <v>12.41536235809326</v>
+        <v>12.41536331176758</v>
       </c>
       <c r="E478" t="n">
-        <v>12.52123037960578</v>
+        <v>12.52123134141225</v>
       </c>
       <c r="F478" t="n">
         <v>4574300</v>
@@ -9992,16 +9992,16 @@
         <v>45348</v>
       </c>
       <c r="B479" t="n">
-        <v>12.35761833190918</v>
+        <v>12.35761737823486</v>
       </c>
       <c r="C479" t="n">
-        <v>12.48273451401776</v>
+        <v>12.48273355068785</v>
       </c>
       <c r="D479" t="n">
-        <v>12.33836926488661</v>
+        <v>12.3383683126978</v>
       </c>
       <c r="E479" t="n">
-        <v>12.45386091348391</v>
+        <v>12.45385995238227</v>
       </c>
       <c r="F479" t="n">
         <v>6964500</v>
@@ -22149,102 +22149,142 @@
     </row>
     <row r="1087">
       <c r="A1087" s="1" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B1087" t="n">
+        <v>10.97999954223633</v>
+      </c>
+      <c r="C1087" t="n">
+        <v>11.27999973297119</v>
+      </c>
+      <c r="D1087" t="n">
+        <v>10.90999984741211</v>
+      </c>
+      <c r="E1087" t="n">
         <v>11.19999980926514</v>
       </c>
-      <c r="C1087" t="n">
-        <v>11.21000003814697</v>
-      </c>
-      <c r="D1087" t="n">
-        <v>10.84000015258789</v>
-      </c>
-      <c r="E1087" t="n">
-        <v>11.03999996185303</v>
-      </c>
       <c r="F1087" t="n">
-        <v>4621900</v>
+        <v>5442500</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" s="1" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B1088" t="n">
-        <v>11.27999973297119</v>
+        <v>11.19999980926514</v>
       </c>
       <c r="C1088" t="n">
-        <v>11.56999969482422</v>
+        <v>11.21000003814697</v>
       </c>
       <c r="D1088" t="n">
-        <v>11.13000011444092</v>
+        <v>10.84000015258789</v>
       </c>
       <c r="E1088" t="n">
-        <v>11.32999992370605</v>
+        <v>11.03999996185303</v>
       </c>
       <c r="F1088" t="n">
-        <v>4289500</v>
+        <v>4621900</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" s="1" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B1089" t="n">
-        <v>11.15999984741211</v>
+        <v>11.27999973297119</v>
       </c>
       <c r="C1089" t="n">
-        <v>11.55000019073486</v>
+        <v>11.56999969482422</v>
       </c>
       <c r="D1089" t="n">
-        <v>11.07999992370605</v>
+        <v>11.13000011444092</v>
       </c>
       <c r="E1089" t="n">
-        <v>11.31999969482422</v>
+        <v>11.32999992370605</v>
       </c>
       <c r="F1089" t="n">
-        <v>5192700</v>
+        <v>4289500</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" s="1" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B1090" t="n">
-        <v>10.97999954223633</v>
+        <v>11.15999984741211</v>
       </c>
       <c r="C1090" t="n">
-        <v>11.14000034332275</v>
+        <v>11.55000019073486</v>
       </c>
       <c r="D1090" t="n">
-        <v>10.61999988555908</v>
+        <v>11.07999992370605</v>
       </c>
       <c r="E1090" t="n">
-        <v>11.14000034332275</v>
+        <v>11.31999969482422</v>
       </c>
       <c r="F1090" t="n">
-        <v>5195300</v>
+        <v>5192700</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B1091" t="n">
+        <v>10.97999954223633</v>
+      </c>
+      <c r="C1091" t="n">
+        <v>11.14000034332275</v>
+      </c>
+      <c r="D1091" t="n">
+        <v>10.61999988555908</v>
+      </c>
+      <c r="E1091" t="n">
+        <v>11.14000034332275</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>5195300</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="1" t="n">
         <v>46241</v>
       </c>
-      <c r="B1091" t="n">
-        <v>10.81</v>
-      </c>
-      <c r="C1091" t="n">
-        <v>10.98</v>
-      </c>
-      <c r="D1091" t="n">
-        <v>10.55</v>
-      </c>
-      <c r="E1091" t="n">
-        <v>10.98</v>
-      </c>
-      <c r="F1091" t="n">
+      <c r="B1092" t="n">
+        <v>10.8100004196167</v>
+      </c>
+      <c r="C1092" t="n">
+        <v>10.97999954223633</v>
+      </c>
+      <c r="D1092" t="n">
+        <v>10.55000019073486</v>
+      </c>
+      <c r="E1092" t="n">
+        <v>10.97999954223633</v>
+      </c>
+      <c r="F1092" t="n">
         <v>4285100</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B1093" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="C1093" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="D1093" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="E1093" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F1093" t="n">
+        <v>3624700</v>
       </c>
     </row>
   </sheetData>

--- a/database/AURE3.xlsx
+++ b/database/AURE3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1093"/>
+  <dimension ref="A1:F1094"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>44649</v>
       </c>
       <c r="B3" t="n">
-        <v>12.91280841827393</v>
+        <v>12.91280937194824</v>
       </c>
       <c r="C3" t="n">
-        <v>13.21618114634902</v>
+        <v>13.2161821224289</v>
       </c>
       <c r="D3" t="n">
-        <v>12.61721318462629</v>
+        <v>12.61721411646944</v>
       </c>
       <c r="E3" t="n">
-        <v>12.74945284521847</v>
+        <v>12.74945378682817</v>
       </c>
       <c r="F3" t="n">
         <v>4714100</v>
@@ -492,16 +492,16 @@
         <v>44650</v>
       </c>
       <c r="B4" t="n">
-        <v>12.38385105133057</v>
+        <v>12.38385009765625</v>
       </c>
       <c r="C4" t="n">
-        <v>13.04504942238897</v>
+        <v>13.04504841779609</v>
       </c>
       <c r="D4" t="n">
-        <v>12.30606274584925</v>
+        <v>12.30606179816537</v>
       </c>
       <c r="E4" t="n">
-        <v>12.92836770601126</v>
+        <v>12.92836671040398</v>
       </c>
       <c r="F4" t="n">
         <v>4408600</v>
@@ -532,16 +532,16 @@
         <v>44652</v>
       </c>
       <c r="B6" t="n">
-        <v>12.51608943939209</v>
+        <v>12.51609039306641</v>
       </c>
       <c r="C6" t="n">
-        <v>12.95170182816011</v>
+        <v>12.95170281502629</v>
       </c>
       <c r="D6" t="n">
-        <v>12.31384045939913</v>
+        <v>12.31384139766291</v>
       </c>
       <c r="E6" t="n">
-        <v>12.43830114190428</v>
+        <v>12.43830208965145</v>
       </c>
       <c r="F6" t="n">
         <v>4252000</v>
@@ -592,16 +592,16 @@
         <v>44657</v>
       </c>
       <c r="B9" t="n">
-        <v>12.43052387237549</v>
+        <v>12.43052291870117</v>
       </c>
       <c r="C9" t="n">
-        <v>12.44608183074918</v>
+        <v>12.44608087588125</v>
       </c>
       <c r="D9" t="n">
-        <v>12.01824761944832</v>
+        <v>12.01824669740399</v>
       </c>
       <c r="E9" t="n">
-        <v>12.06492075272512</v>
+        <v>12.06491982710001</v>
       </c>
       <c r="F9" t="n">
         <v>2914800</v>
@@ -632,16 +632,16 @@
         <v>44659</v>
       </c>
       <c r="B11" t="n">
-        <v>12.60943603515625</v>
+        <v>12.60943508148193</v>
       </c>
       <c r="C11" t="n">
-        <v>12.75723367341398</v>
+        <v>12.75723270856147</v>
       </c>
       <c r="D11" t="n">
-        <v>12.3371784382169</v>
+        <v>12.33717750513392</v>
       </c>
       <c r="E11" t="n">
-        <v>12.3371784382169</v>
+        <v>12.33717750513392</v>
       </c>
       <c r="F11" t="n">
         <v>2049800</v>
@@ -672,16 +672,16 @@
         <v>44663</v>
       </c>
       <c r="B13" t="n">
-        <v>12.24383163452148</v>
+        <v>12.2438325881958</v>
       </c>
       <c r="C13" t="n">
-        <v>12.64055063241211</v>
+        <v>12.64055161698694</v>
       </c>
       <c r="D13" t="n">
-        <v>12.21271646263855</v>
+        <v>12.2127174138893</v>
       </c>
       <c r="E13" t="n">
-        <v>12.4849740311532</v>
+        <v>12.48497500361014</v>
       </c>
       <c r="F13" t="n">
         <v>2267700</v>
@@ -712,16 +712,16 @@
         <v>44665</v>
       </c>
       <c r="B15" t="n">
-        <v>12.11159229278564</v>
+        <v>12.11159133911133</v>
       </c>
       <c r="C15" t="n">
-        <v>12.36829265315281</v>
+        <v>12.36829167926575</v>
       </c>
       <c r="D15" t="n">
-        <v>12.04936194735386</v>
+        <v>12.0493609985796</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08047712006975</v>
+        <v>12.08047616884546</v>
       </c>
       <c r="F15" t="n">
         <v>2077400</v>
@@ -972,16 +972,16 @@
         <v>44686</v>
       </c>
       <c r="B28" t="n">
-        <v>11.28714847564697</v>
+        <v>11.28714752197266</v>
       </c>
       <c r="C28" t="n">
-        <v>11.62396161516718</v>
+        <v>11.62396063303483</v>
       </c>
       <c r="D28" t="n">
-        <v>11.14615678989441</v>
+        <v>11.14615584813277</v>
       </c>
       <c r="E28" t="n">
-        <v>11.61612857773658</v>
+        <v>11.61612759626606</v>
       </c>
       <c r="F28" t="n">
         <v>3065700</v>
@@ -1152,16 +1152,16 @@
         <v>44699</v>
       </c>
       <c r="B37" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C37" t="n">
-        <v>11.5926298208571</v>
+        <v>11.59262882548476</v>
       </c>
       <c r="D37" t="n">
-        <v>11.03649688106261</v>
+        <v>11.03649593344125</v>
       </c>
       <c r="E37" t="n">
-        <v>11.51430094319608</v>
+        <v>11.51429995454926</v>
       </c>
       <c r="F37" t="n">
         <v>1959900</v>
@@ -1172,16 +1172,16 @@
         <v>44700</v>
       </c>
       <c r="B38" t="n">
-        <v>11.22448444366455</v>
+        <v>11.22448539733887</v>
       </c>
       <c r="C38" t="n">
-        <v>11.25581584296371</v>
+        <v>11.25581679930005</v>
       </c>
       <c r="D38" t="n">
-        <v>10.97383324927132</v>
+        <v>10.97383418164937</v>
       </c>
       <c r="E38" t="n">
-        <v>11.11482417261777</v>
+        <v>11.11482511697494</v>
       </c>
       <c r="F38" t="n">
         <v>2127500</v>
@@ -1192,16 +1192,16 @@
         <v>44701</v>
       </c>
       <c r="B39" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C39" t="n">
-        <v>11.34197786054158</v>
+        <v>11.34197688669085</v>
       </c>
       <c r="D39" t="n">
-        <v>10.86417379840811</v>
+        <v>10.86417286558284</v>
       </c>
       <c r="E39" t="n">
-        <v>11.34197786054158</v>
+        <v>11.34197688669085</v>
       </c>
       <c r="F39" t="n">
         <v>1777400</v>
@@ -1212,16 +1212,16 @@
         <v>44704</v>
       </c>
       <c r="B40" t="n">
-        <v>11.20881843566895</v>
+        <v>11.20881938934326</v>
       </c>
       <c r="C40" t="n">
-        <v>11.43597125351971</v>
+        <v>11.43597222652075</v>
       </c>
       <c r="D40" t="n">
-        <v>11.16182096607938</v>
+        <v>11.16182191575504</v>
       </c>
       <c r="E40" t="n">
-        <v>11.18531932737445</v>
+        <v>11.1853202790494</v>
       </c>
       <c r="F40" t="n">
         <v>1184600</v>
@@ -1272,16 +1272,16 @@
         <v>44707</v>
       </c>
       <c r="B43" t="n">
-        <v>11.25581741333008</v>
+        <v>11.25581645965576</v>
       </c>
       <c r="C43" t="n">
-        <v>11.44380583535239</v>
+        <v>11.44380486575034</v>
       </c>
       <c r="D43" t="n">
-        <v>11.20882068132429</v>
+        <v>11.20881973163188</v>
       </c>
       <c r="E43" t="n">
-        <v>11.33414629600583</v>
+        <v>11.33414533569493</v>
       </c>
       <c r="F43" t="n">
         <v>1248800</v>
@@ -1332,16 +1332,16 @@
         <v>44712</v>
       </c>
       <c r="B46" t="n">
-        <v>10.93467044830322</v>
+        <v>10.93466949462891</v>
       </c>
       <c r="C46" t="n">
-        <v>11.20882079341023</v>
+        <v>11.20881981582572</v>
       </c>
       <c r="D46" t="n">
-        <v>10.8250101608605</v>
+        <v>10.82500921675028</v>
       </c>
       <c r="E46" t="n">
-        <v>11.16965635168072</v>
+        <v>11.16965537751195</v>
       </c>
       <c r="F46" t="n">
         <v>9431500</v>
@@ -1372,16 +1372,16 @@
         <v>44714</v>
       </c>
       <c r="B48" t="n">
-        <v>10.86417388916016</v>
+        <v>10.86417293548584</v>
       </c>
       <c r="C48" t="n">
-        <v>10.98949949686503</v>
+        <v>10.98949853218943</v>
       </c>
       <c r="D48" t="n">
-        <v>10.68401851483428</v>
+        <v>10.68401757697429</v>
       </c>
       <c r="E48" t="n">
-        <v>10.75451360891862</v>
+        <v>10.75451266487045</v>
       </c>
       <c r="F48" t="n">
         <v>3275400</v>
@@ -1432,16 +1432,16 @@
         <v>44719</v>
       </c>
       <c r="B51" t="n">
-        <v>10.85634136199951</v>
+        <v>10.8563404083252</v>
       </c>
       <c r="C51" t="n">
-        <v>10.87984047479791</v>
+        <v>10.87983951905932</v>
       </c>
       <c r="D51" t="n">
-        <v>10.53519429041721</v>
+        <v>10.53519336495403</v>
       </c>
       <c r="E51" t="n">
-        <v>10.59002480661389</v>
+        <v>10.59002387633413</v>
       </c>
       <c r="F51" t="n">
         <v>2760900</v>
@@ -1472,16 +1472,16 @@
         <v>44721</v>
       </c>
       <c r="B53" t="n">
-        <v>11.03649520874023</v>
+        <v>11.03649616241455</v>
       </c>
       <c r="C53" t="n">
-        <v>11.09915800257415</v>
+        <v>11.09915896166322</v>
       </c>
       <c r="D53" t="n">
-        <v>10.86417215219725</v>
+        <v>10.86417309098097</v>
       </c>
       <c r="E53" t="n">
-        <v>11.06782660565719</v>
+        <v>11.06782756203888</v>
       </c>
       <c r="F53" t="n">
         <v>1365200</v>
@@ -1552,16 +1552,16 @@
         <v>44727</v>
       </c>
       <c r="B57" t="n">
-        <v>10.84067535400391</v>
+        <v>10.84067440032959</v>
       </c>
       <c r="C57" t="n">
-        <v>10.84850839111218</v>
+        <v>10.84850743674878</v>
       </c>
       <c r="D57" t="n">
-        <v>10.44119942547642</v>
+        <v>10.44119850694474</v>
       </c>
       <c r="E57" t="n">
-        <v>10.55085970399363</v>
+        <v>10.55085877581493</v>
       </c>
       <c r="F57" t="n">
         <v>3153700</v>
@@ -1852,16 +1852,16 @@
         <v>44749</v>
       </c>
       <c r="B72" t="n">
-        <v>11.04433059692383</v>
+        <v>11.04432964324951</v>
       </c>
       <c r="C72" t="n">
-        <v>11.16182317363595</v>
+        <v>11.16182220981619</v>
       </c>
       <c r="D72" t="n">
-        <v>10.62135627496076</v>
+        <v>10.62135535781014</v>
       </c>
       <c r="E72" t="n">
-        <v>10.78584633055749</v>
+        <v>10.7858453992032</v>
       </c>
       <c r="F72" t="n">
         <v>2931100</v>
@@ -1892,16 +1892,16 @@
         <v>44753</v>
       </c>
       <c r="B74" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C74" t="n">
-        <v>11.18532085221909</v>
+        <v>11.18531989181933</v>
       </c>
       <c r="D74" t="n">
-        <v>10.83284239674361</v>
+        <v>10.83284146660853</v>
       </c>
       <c r="E74" t="n">
-        <v>11.0599952455611</v>
+        <v>11.05999429592211</v>
       </c>
       <c r="F74" t="n">
         <v>1881000</v>
@@ -1912,16 +1912,16 @@
         <v>44754</v>
       </c>
       <c r="B75" t="n">
-        <v>11.14615631103516</v>
+        <v>11.14615726470947</v>
       </c>
       <c r="C75" t="n">
-        <v>11.22448518797689</v>
+        <v>11.22448614835309</v>
       </c>
       <c r="D75" t="n">
-        <v>10.99733234124531</v>
+        <v>10.99733328218612</v>
       </c>
       <c r="E75" t="n">
-        <v>11.10699261956382</v>
+        <v>11.10699356988726</v>
       </c>
       <c r="F75" t="n">
         <v>1673000</v>
@@ -1972,16 +1972,16 @@
         <v>44757</v>
       </c>
       <c r="B78" t="n">
-        <v>10.8093433380127</v>
+        <v>10.80934429168701</v>
       </c>
       <c r="C78" t="n">
-        <v>10.98166640959971</v>
+        <v>10.98166737847755</v>
       </c>
       <c r="D78" t="n">
-        <v>10.60568886677345</v>
+        <v>10.60568980247997</v>
       </c>
       <c r="E78" t="n">
-        <v>10.97383337293678</v>
+        <v>10.97383434112354</v>
       </c>
       <c r="F78" t="n">
         <v>2342600</v>
@@ -2012,16 +2012,16 @@
         <v>44761</v>
       </c>
       <c r="B80" t="n">
-        <v>11.09132671356201</v>
+        <v>11.0913257598877</v>
       </c>
       <c r="C80" t="n">
-        <v>11.09132671356201</v>
+        <v>11.0913257598877</v>
       </c>
       <c r="D80" t="n">
-        <v>10.78584573225599</v>
+        <v>10.78584480484809</v>
       </c>
       <c r="E80" t="n">
-        <v>10.87200690059879</v>
+        <v>10.87200596578243</v>
       </c>
       <c r="F80" t="n">
         <v>2890800</v>
@@ -2052,16 +2052,16 @@
         <v>44763</v>
       </c>
       <c r="B82" t="n">
-        <v>11.2479829788208</v>
+        <v>11.24798202514648</v>
       </c>
       <c r="C82" t="n">
-        <v>11.27931437860027</v>
+        <v>11.27931342226948</v>
       </c>
       <c r="D82" t="n">
-        <v>11.05999458014401</v>
+        <v>11.05999364240853</v>
       </c>
       <c r="E82" t="n">
-        <v>11.22448461573608</v>
+        <v>11.2244836640541</v>
       </c>
       <c r="F82" t="n">
         <v>1092700</v>
@@ -2092,16 +2092,16 @@
         <v>44767</v>
       </c>
       <c r="B84" t="n">
-        <v>11.2323169708252</v>
+        <v>11.23231792449951</v>
       </c>
       <c r="C84" t="n">
-        <v>11.45163675597257</v>
+        <v>11.45163772826812</v>
       </c>
       <c r="D84" t="n">
-        <v>11.1696541750688</v>
+        <v>11.16965512342277</v>
       </c>
       <c r="E84" t="n">
-        <v>11.42030535809437</v>
+        <v>11.42030632772975</v>
       </c>
       <c r="F84" t="n">
         <v>1962700</v>
@@ -2112,16 +2112,16 @@
         <v>44768</v>
       </c>
       <c r="B85" t="n">
-        <v>11.27148342132568</v>
+        <v>11.27148246765137</v>
       </c>
       <c r="C85" t="n">
-        <v>11.3811429600171</v>
+        <v>11.38114199706455</v>
       </c>
       <c r="D85" t="n">
-        <v>11.16965617325538</v>
+        <v>11.16965522819662</v>
       </c>
       <c r="E85" t="n">
-        <v>11.19315453911789</v>
+        <v>11.19315359207094</v>
       </c>
       <c r="F85" t="n">
         <v>1661400</v>
@@ -2132,16 +2132,16 @@
         <v>44769</v>
       </c>
       <c r="B86" t="n">
-        <v>11.24015045166016</v>
+        <v>11.24015140533447</v>
       </c>
       <c r="C86" t="n">
-        <v>11.49080164460048</v>
+        <v>11.49080261954139</v>
       </c>
       <c r="D86" t="n">
-        <v>11.15398854383731</v>
+        <v>11.15398949020119</v>
       </c>
       <c r="E86" t="n">
-        <v>11.28714717683673</v>
+        <v>11.2871481344985</v>
       </c>
       <c r="F86" t="n">
         <v>3096400</v>
@@ -2192,16 +2192,16 @@
         <v>44774</v>
       </c>
       <c r="B89" t="n">
-        <v>10.95033550262451</v>
+        <v>10.9503345489502</v>
       </c>
       <c r="C89" t="n">
-        <v>11.20882051276761</v>
+        <v>11.20881953658161</v>
       </c>
       <c r="D89" t="n">
-        <v>10.78584619607824</v>
+        <v>10.78584525672945</v>
       </c>
       <c r="E89" t="n">
-        <v>11.0599957873216</v>
+        <v>11.05999482409687</v>
       </c>
       <c r="F89" t="n">
         <v>3205600</v>
@@ -2212,16 +2212,16 @@
         <v>44775</v>
       </c>
       <c r="B90" t="n">
-        <v>10.86417388916016</v>
+        <v>10.86417293548584</v>
       </c>
       <c r="C90" t="n">
-        <v>11.06782837518035</v>
+        <v>11.06782740362892</v>
       </c>
       <c r="D90" t="n">
-        <v>10.7231822069924</v>
+        <v>10.72318126569455</v>
       </c>
       <c r="E90" t="n">
-        <v>10.93466973024404</v>
+        <v>10.93466877038148</v>
       </c>
       <c r="F90" t="n">
         <v>2371400</v>
@@ -2232,16 +2232,16 @@
         <v>44776</v>
       </c>
       <c r="B91" t="n">
-        <v>10.88767242431641</v>
+        <v>10.88767147064209</v>
       </c>
       <c r="C91" t="n">
-        <v>11.02083107133751</v>
+        <v>11.02083010599954</v>
       </c>
       <c r="D91" t="n">
-        <v>10.70751704716995</v>
+        <v>10.70751610927583</v>
       </c>
       <c r="E91" t="n">
-        <v>10.83284265683698</v>
+        <v>10.83284170796531</v>
       </c>
       <c r="F91" t="n">
         <v>3133200</v>
@@ -2312,16 +2312,16 @@
         <v>44782</v>
       </c>
       <c r="B95" t="n">
-        <v>10.92683601379395</v>
+        <v>10.92683696746826</v>
       </c>
       <c r="C95" t="n">
-        <v>11.05999465045304</v>
+        <v>11.0599956157492</v>
       </c>
       <c r="D95" t="n">
-        <v>10.67618481396482</v>
+        <v>10.67618574576276</v>
       </c>
       <c r="E95" t="n">
-        <v>10.98166652400619</v>
+        <v>10.98166748246601</v>
       </c>
       <c r="F95" t="n">
         <v>1743500</v>
@@ -2412,16 +2412,16 @@
         <v>44789</v>
       </c>
       <c r="B100" t="n">
-        <v>11.04433059692383</v>
+        <v>11.04432964324951</v>
       </c>
       <c r="C100" t="n">
-        <v>11.2949818256428</v>
+        <v>11.29498085032484</v>
       </c>
       <c r="D100" t="n">
-        <v>10.94250334850685</v>
+        <v>10.94250240362528</v>
       </c>
       <c r="E100" t="n">
-        <v>11.25581738440557</v>
+        <v>11.25581641246944</v>
       </c>
       <c r="F100" t="n">
         <v>1185300</v>
@@ -2432,16 +2432,16 @@
         <v>44790</v>
       </c>
       <c r="B101" t="n">
-        <v>11.24015045166016</v>
+        <v>11.24015140533447</v>
       </c>
       <c r="C101" t="n">
-        <v>11.25581577771919</v>
+        <v>11.25581673272263</v>
       </c>
       <c r="D101" t="n">
-        <v>10.91117038742624</v>
+        <v>10.91117131318813</v>
       </c>
       <c r="E101" t="n">
-        <v>10.98949851172035</v>
+        <v>10.98949944412802</v>
       </c>
       <c r="F101" t="n">
         <v>4396400</v>
@@ -2512,16 +2512,16 @@
         <v>44796</v>
       </c>
       <c r="B105" t="n">
-        <v>11.22448444366455</v>
+        <v>11.22448539733887</v>
       </c>
       <c r="C105" t="n">
-        <v>11.27148191611302</v>
+        <v>11.27148287378042</v>
       </c>
       <c r="D105" t="n">
-        <v>10.98949857542116</v>
+        <v>10.98949950913019</v>
       </c>
       <c r="E105" t="n">
-        <v>10.98949857542116</v>
+        <v>10.98949950913019</v>
       </c>
       <c r="F105" t="n">
         <v>2361000</v>
@@ -2532,16 +2532,16 @@
         <v>44797</v>
       </c>
       <c r="B106" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C106" t="n">
-        <v>11.3968083737041</v>
+        <v>11.39680739514549</v>
       </c>
       <c r="D106" t="n">
-        <v>11.09915968439161</v>
+        <v>11.09915873138986</v>
       </c>
       <c r="E106" t="n">
-        <v>11.2244852910496</v>
+        <v>11.22448432728707</v>
       </c>
       <c r="F106" t="n">
         <v>2116800</v>
@@ -2552,16 +2552,16 @@
         <v>44798</v>
       </c>
       <c r="B107" t="n">
-        <v>11.04433059692383</v>
+        <v>11.04432964324951</v>
       </c>
       <c r="C107" t="n">
-        <v>11.22448598081569</v>
+        <v>11.22448501158502</v>
       </c>
       <c r="D107" t="n">
-        <v>10.95033563915463</v>
+        <v>10.95033469359675</v>
       </c>
       <c r="E107" t="n">
-        <v>11.20882065252055</v>
+        <v>11.20881968464257</v>
       </c>
       <c r="F107" t="n">
         <v>2435800</v>
@@ -2652,16 +2652,16 @@
         <v>44805</v>
       </c>
       <c r="B112" t="n">
-        <v>11.65529251098633</v>
+        <v>11.65529155731201</v>
       </c>
       <c r="C112" t="n">
-        <v>12.15659567974902</v>
+        <v>12.15659468505643</v>
       </c>
       <c r="D112" t="n">
-        <v>11.42030662728508</v>
+        <v>11.42030569283808</v>
       </c>
       <c r="E112" t="n">
-        <v>12.14092960556915</v>
+        <v>12.14092861215841</v>
       </c>
       <c r="F112" t="n">
         <v>4716400</v>
@@ -2732,16 +2732,16 @@
         <v>44812</v>
       </c>
       <c r="B116" t="n">
-        <v>11.43597221374512</v>
+        <v>11.43597316741943</v>
       </c>
       <c r="C116" t="n">
-        <v>11.63962594040124</v>
+        <v>11.63962691105875</v>
       </c>
       <c r="D116" t="n">
-        <v>11.37330941369716</v>
+        <v>11.37331036214587</v>
       </c>
       <c r="E116" t="n">
-        <v>11.623960613889</v>
+        <v>11.62396158324014</v>
       </c>
       <c r="F116" t="n">
         <v>2598100</v>
@@ -2792,16 +2792,16 @@
         <v>44817</v>
       </c>
       <c r="B119" t="n">
-        <v>11.24015045166016</v>
+        <v>11.24015140533447</v>
       </c>
       <c r="C119" t="n">
-        <v>11.43597188289466</v>
+        <v>11.43597285318351</v>
       </c>
       <c r="D119" t="n">
-        <v>11.16965461689582</v>
+        <v>11.16965556458889</v>
       </c>
       <c r="E119" t="n">
-        <v>11.30281324989524</v>
+        <v>11.3028142088862</v>
       </c>
       <c r="F119" t="n">
         <v>1768400</v>
@@ -2812,16 +2812,16 @@
         <v>44818</v>
       </c>
       <c r="B120" t="n">
-        <v>11.20881843566895</v>
+        <v>11.20881938934326</v>
       </c>
       <c r="C120" t="n">
-        <v>11.42030518132337</v>
+        <v>11.42030615299151</v>
       </c>
       <c r="D120" t="n">
-        <v>11.02866234040831</v>
+        <v>11.02866327875449</v>
       </c>
       <c r="E120" t="n">
-        <v>11.20098539957078</v>
+        <v>11.20098635257864</v>
       </c>
       <c r="F120" t="n">
         <v>1856400</v>
@@ -2832,16 +2832,16 @@
         <v>44819</v>
       </c>
       <c r="B121" t="n">
-        <v>11.22448444366455</v>
+        <v>11.22448539733887</v>
       </c>
       <c r="C121" t="n">
-        <v>11.27148191611302</v>
+        <v>11.27148287378042</v>
       </c>
       <c r="D121" t="n">
-        <v>11.11482417261777</v>
+        <v>11.11482511697494</v>
       </c>
       <c r="E121" t="n">
-        <v>11.16182164506624</v>
+        <v>11.16182259341649</v>
       </c>
       <c r="F121" t="n">
         <v>1523500</v>
@@ -2872,16 +2872,16 @@
         <v>44823</v>
       </c>
       <c r="B123" t="n">
-        <v>11.28714847564697</v>
+        <v>11.28714752197266</v>
       </c>
       <c r="C123" t="n">
-        <v>11.43597319883014</v>
+        <v>11.43597223258132</v>
       </c>
       <c r="D123" t="n">
-        <v>11.11482538717157</v>
+        <v>11.11482444805718</v>
       </c>
       <c r="E123" t="n">
-        <v>11.11482538717157</v>
+        <v>11.11482444805718</v>
       </c>
       <c r="F123" t="n">
         <v>1858600</v>
@@ -2912,16 +2912,16 @@
         <v>44825</v>
       </c>
       <c r="B125" t="n">
-        <v>11.09132671356201</v>
+        <v>11.0913257598877</v>
       </c>
       <c r="C125" t="n">
-        <v>11.23231839539528</v>
+        <v>11.23231742959796</v>
       </c>
       <c r="D125" t="n">
-        <v>10.93466970430257</v>
+        <v>10.93466876409822</v>
       </c>
       <c r="E125" t="n">
-        <v>11.13049115262676</v>
+        <v>11.13049019558493</v>
       </c>
       <c r="F125" t="n">
         <v>2825100</v>
@@ -2932,16 +2932,16 @@
         <v>44826</v>
       </c>
       <c r="B126" t="n">
-        <v>11.2323169708252</v>
+        <v>11.23231792449951</v>
       </c>
       <c r="C126" t="n">
-        <v>11.24015000704461</v>
+        <v>11.24015096138398</v>
       </c>
       <c r="D126" t="n">
-        <v>11.05999390899539</v>
+        <v>11.05999484803871</v>
       </c>
       <c r="E126" t="n">
-        <v>11.19315253672759</v>
+        <v>11.19315348707667</v>
       </c>
       <c r="F126" t="n">
         <v>1855600</v>
@@ -2972,16 +2972,16 @@
         <v>44830</v>
       </c>
       <c r="B128" t="n">
-        <v>11.00516510009766</v>
+        <v>11.00516605377197</v>
       </c>
       <c r="C128" t="n">
-        <v>11.20881957739757</v>
+        <v>11.20882054871997</v>
       </c>
       <c r="D128" t="n">
-        <v>10.88767178765562</v>
+        <v>10.88767273114832</v>
       </c>
       <c r="E128" t="n">
-        <v>11.20098654050153</v>
+        <v>11.20098751114514</v>
       </c>
       <c r="F128" t="n">
         <v>1884300</v>
@@ -3012,16 +3012,16 @@
         <v>44832</v>
       </c>
       <c r="B130" t="n">
-        <v>10.74668025970459</v>
+        <v>10.74668121337891</v>
       </c>
       <c r="C130" t="n">
-        <v>11.03649588571345</v>
+        <v>11.03649686510639</v>
       </c>
       <c r="D130" t="n">
-        <v>10.72318115032588</v>
+        <v>10.72318210191485</v>
       </c>
       <c r="E130" t="n">
-        <v>10.95816701511669</v>
+        <v>10.95816798755862</v>
       </c>
       <c r="F130" t="n">
         <v>4249200</v>
@@ -3032,16 +3032,16 @@
         <v>44833</v>
       </c>
       <c r="B131" t="n">
-        <v>10.70751667022705</v>
+        <v>10.70751571655273</v>
       </c>
       <c r="C131" t="n">
-        <v>10.83284227548216</v>
+        <v>10.83284131064561</v>
       </c>
       <c r="D131" t="n">
-        <v>10.6448538675995</v>
+        <v>10.6448529195063</v>
       </c>
       <c r="E131" t="n">
-        <v>10.6918505960704</v>
+        <v>10.69184964379139</v>
       </c>
       <c r="F131" t="n">
         <v>2222600</v>
@@ -3132,16 +3132,16 @@
         <v>44840</v>
       </c>
       <c r="B136" t="n">
-        <v>10.98949909210205</v>
+        <v>10.98950004577637</v>
       </c>
       <c r="C136" t="n">
-        <v>11.1226577321339</v>
+        <v>11.12265869736379</v>
       </c>
       <c r="D136" t="n">
-        <v>10.88767185284243</v>
+        <v>10.88767279768013</v>
       </c>
       <c r="E136" t="n">
-        <v>11.02866352981721</v>
+        <v>11.02866448689024</v>
       </c>
       <c r="F136" t="n">
         <v>3101100</v>
@@ -3192,16 +3192,16 @@
         <v>44845</v>
       </c>
       <c r="B139" t="n">
-        <v>11.22448444366455</v>
+        <v>11.22448539733887</v>
       </c>
       <c r="C139" t="n">
-        <v>11.31847864156201</v>
+        <v>11.31847960322243</v>
       </c>
       <c r="D139" t="n">
-        <v>10.99733161199581</v>
+        <v>10.99733254637037</v>
       </c>
       <c r="E139" t="n">
-        <v>11.04432908444429</v>
+        <v>11.04433002281193</v>
       </c>
       <c r="F139" t="n">
         <v>1834300</v>
@@ -3232,16 +3232,16 @@
         <v>44848</v>
       </c>
       <c r="B141" t="n">
-        <v>10.82500839233398</v>
+        <v>10.8250093460083</v>
       </c>
       <c r="C141" t="n">
-        <v>11.16182149038183</v>
+        <v>11.1618224737291</v>
       </c>
       <c r="D141" t="n">
-        <v>10.82500839233398</v>
+        <v>10.8250093460083</v>
       </c>
       <c r="E141" t="n">
-        <v>10.97383309719211</v>
+        <v>10.97383406397776</v>
       </c>
       <c r="F141" t="n">
         <v>3601200</v>
@@ -3272,16 +3272,16 @@
         <v>44852</v>
       </c>
       <c r="B143" t="n">
-        <v>11.27148342132568</v>
+        <v>11.27148246765137</v>
       </c>
       <c r="C143" t="n">
-        <v>11.37331066939599</v>
+        <v>11.37330970710612</v>
       </c>
       <c r="D143" t="n">
-        <v>11.06782892518508</v>
+        <v>11.06782798874186</v>
       </c>
       <c r="E143" t="n">
-        <v>11.20882061435928</v>
+        <v>11.20881966598683</v>
       </c>
       <c r="F143" t="n">
         <v>2646800</v>
@@ -3312,16 +3312,16 @@
         <v>44854</v>
       </c>
       <c r="B145" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C145" t="n">
-        <v>10.98166658413194</v>
+        <v>10.98166755090811</v>
       </c>
       <c r="D145" t="n">
-        <v>10.39420227106638</v>
+        <v>10.39420318612486</v>
       </c>
       <c r="E145" t="n">
-        <v>10.57435763518006</v>
+        <v>10.5743585660986</v>
       </c>
       <c r="F145" t="n">
         <v>7194300</v>
@@ -3352,16 +3352,16 @@
         <v>44858</v>
       </c>
       <c r="B147" t="n">
-        <v>11.2479829788208</v>
+        <v>11.24798202514648</v>
       </c>
       <c r="C147" t="n">
-        <v>11.45163745088707</v>
+        <v>11.45163647994565</v>
       </c>
       <c r="D147" t="n">
-        <v>11.10699205331296</v>
+        <v>11.10699111159273</v>
       </c>
       <c r="E147" t="n">
-        <v>11.10699205331296</v>
+        <v>11.10699111159273</v>
       </c>
       <c r="F147" t="n">
         <v>2219500</v>
@@ -3372,16 +3372,16 @@
         <v>44859</v>
       </c>
       <c r="B148" t="n">
-        <v>11.3889741897583</v>
+        <v>11.38897514343262</v>
       </c>
       <c r="C148" t="n">
-        <v>11.50646674741971</v>
+        <v>11.50646771093245</v>
       </c>
       <c r="D148" t="n">
-        <v>11.18531972594569</v>
+        <v>11.18532066256667</v>
       </c>
       <c r="E148" t="n">
-        <v>11.24015023358722</v>
+        <v>11.24015117479952</v>
       </c>
       <c r="F148" t="n">
         <v>2935500</v>
@@ -3432,16 +3432,16 @@
         <v>44862</v>
       </c>
       <c r="B151" t="n">
-        <v>11.49080276489258</v>
+        <v>11.49080181121826</v>
       </c>
       <c r="C151" t="n">
-        <v>11.63962673846057</v>
+        <v>11.63962577243467</v>
       </c>
       <c r="D151" t="n">
-        <v>11.22448547292922</v>
+        <v>11.2244845413578</v>
       </c>
       <c r="E151" t="n">
-        <v>11.32631271673871</v>
+        <v>11.32631177671618</v>
       </c>
       <c r="F151" t="n">
         <v>2887600</v>
@@ -3452,16 +3452,16 @@
         <v>44865</v>
       </c>
       <c r="B152" t="n">
-        <v>11.68662452697754</v>
+        <v>11.68662357330322</v>
       </c>
       <c r="C152" t="n">
-        <v>11.72578896748743</v>
+        <v>11.72578801061714</v>
       </c>
       <c r="D152" t="n">
-        <v>11.16182296634386</v>
+        <v>11.16182205549541</v>
       </c>
       <c r="E152" t="n">
-        <v>11.23231880986175</v>
+        <v>11.23231789326056</v>
       </c>
       <c r="F152" t="n">
         <v>2644000</v>
@@ -3492,16 +3492,16 @@
         <v>44868</v>
       </c>
       <c r="B154" t="n">
-        <v>11.68662452697754</v>
+        <v>11.68662357330322</v>
       </c>
       <c r="C154" t="n">
-        <v>11.74928733299354</v>
+        <v>11.74928637420569</v>
       </c>
       <c r="D154" t="n">
-        <v>11.36547745939565</v>
+        <v>11.36547653192819</v>
       </c>
       <c r="E154" t="n">
-        <v>11.49863610892954</v>
+        <v>11.49863517059581</v>
       </c>
       <c r="F154" t="n">
         <v>2959500</v>
@@ -3512,16 +3512,16 @@
         <v>44869</v>
       </c>
       <c r="B155" t="n">
-        <v>11.67095851898193</v>
+        <v>11.67095756530762</v>
       </c>
       <c r="C155" t="n">
-        <v>11.87461301320299</v>
+        <v>11.87461204288736</v>
       </c>
       <c r="D155" t="n">
-        <v>11.64746015334091</v>
+        <v>11.64745920158673</v>
       </c>
       <c r="E155" t="n">
-        <v>11.74928740045144</v>
+        <v>11.7492864403766</v>
       </c>
       <c r="F155" t="n">
         <v>2161500</v>
@@ -3592,16 +3592,16 @@
         <v>44875</v>
       </c>
       <c r="B159" t="n">
-        <v>10.70751667022705</v>
+        <v>10.70751571655273</v>
       </c>
       <c r="C159" t="n">
-        <v>11.10699259722736</v>
+        <v>11.10699160797338</v>
       </c>
       <c r="D159" t="n">
-        <v>10.4960291511094</v>
+        <v>10.49602821627141</v>
       </c>
       <c r="E159" t="n">
-        <v>11.04432979459981</v>
+        <v>11.04432881092694</v>
       </c>
       <c r="F159" t="n">
         <v>4341400</v>
@@ -3632,16 +3632,16 @@
         <v>44879</v>
       </c>
       <c r="B161" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C161" t="n">
-        <v>10.9660005105571</v>
+        <v>10.9660014759541</v>
       </c>
       <c r="D161" t="n">
-        <v>10.71534930935563</v>
+        <v>10.71535025268644</v>
       </c>
       <c r="E161" t="n">
-        <v>10.94250214719434</v>
+        <v>10.94250311052265</v>
       </c>
       <c r="F161" t="n">
         <v>1203700</v>
@@ -3672,16 +3672,16 @@
         <v>44882</v>
       </c>
       <c r="B163" t="n">
-        <v>10.74668025970459</v>
+        <v>10.74668121337891</v>
       </c>
       <c r="C163" t="n">
-        <v>10.80151002092264</v>
+        <v>10.80151097946262</v>
       </c>
       <c r="D163" t="n">
-        <v>10.50386135845421</v>
+        <v>10.50386229058046</v>
       </c>
       <c r="E163" t="n">
-        <v>10.69184975148707</v>
+        <v>10.69185070029565</v>
       </c>
       <c r="F163" t="n">
         <v>5834900</v>
@@ -3772,16 +3772,16 @@
         <v>44889</v>
       </c>
       <c r="B168" t="n">
-        <v>10.95033550262451</v>
+        <v>10.9503345489502</v>
       </c>
       <c r="C168" t="n">
-        <v>11.09132719052083</v>
+        <v>11.09132622456742</v>
       </c>
       <c r="D168" t="n">
-        <v>10.56652562668407</v>
+        <v>10.56652470643609</v>
       </c>
       <c r="E168" t="n">
-        <v>10.56652562668407</v>
+        <v>10.56652470643609</v>
       </c>
       <c r="F168" t="n">
         <v>1852400</v>
@@ -3792,16 +3792,16 @@
         <v>44890</v>
       </c>
       <c r="B169" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C169" t="n">
-        <v>11.03649634764489</v>
+        <v>11.03649731924802</v>
       </c>
       <c r="D169" t="n">
-        <v>10.71534930935563</v>
+        <v>10.71535025268644</v>
       </c>
       <c r="E169" t="n">
-        <v>10.95033443698226</v>
+        <v>10.95033540100009</v>
       </c>
       <c r="F169" t="n">
         <v>1631500</v>
@@ -3852,16 +3852,16 @@
         <v>44895</v>
       </c>
       <c r="B172" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C172" t="n">
-        <v>11.20881942197064</v>
+        <v>11.20882040874432</v>
       </c>
       <c r="D172" t="n">
-        <v>10.69185019899337</v>
+        <v>10.69185114025542</v>
       </c>
       <c r="E172" t="n">
-        <v>11.20881942197064</v>
+        <v>11.20882040874432</v>
       </c>
       <c r="F172" t="n">
         <v>4586400</v>
@@ -3872,16 +3872,16 @@
         <v>44896</v>
       </c>
       <c r="B173" t="n">
-        <v>10.92683601379395</v>
+        <v>10.92683696746826</v>
       </c>
       <c r="C173" t="n">
-        <v>11.02083021372987</v>
+        <v>11.02083117560783</v>
       </c>
       <c r="D173" t="n">
-        <v>10.69185014045439</v>
+        <v>10.69185107361957</v>
       </c>
       <c r="E173" t="n">
-        <v>10.76234597715621</v>
+        <v>10.76234691647413</v>
       </c>
       <c r="F173" t="n">
         <v>1944500</v>
@@ -3972,16 +3972,16 @@
         <v>44903</v>
       </c>
       <c r="B178" t="n">
-        <v>11.26364994049072</v>
+        <v>11.26364898681641</v>
       </c>
       <c r="C178" t="n">
-        <v>11.81194985337145</v>
+        <v>11.8119488532735</v>
       </c>
       <c r="D178" t="n">
-        <v>11.15398965911476</v>
+        <v>11.15398871472519</v>
       </c>
       <c r="E178" t="n">
-        <v>11.74928704887077</v>
+        <v>11.74928605407837</v>
       </c>
       <c r="F178" t="n">
         <v>12105700</v>
@@ -4012,16 +4012,16 @@
         <v>44907</v>
       </c>
       <c r="B180" t="n">
-        <v>11.00516510009766</v>
+        <v>11.00516605377197</v>
       </c>
       <c r="C180" t="n">
-        <v>11.26364934167081</v>
+        <v>11.26365031774459</v>
       </c>
       <c r="D180" t="n">
-        <v>10.7466808585245</v>
+        <v>10.74668178979936</v>
       </c>
       <c r="E180" t="n">
-        <v>11.17748817681293</v>
+        <v>11.17748914542024</v>
       </c>
       <c r="F180" t="n">
         <v>4004300</v>
@@ -4092,16 +4092,16 @@
         <v>44911</v>
       </c>
       <c r="B184" t="n">
-        <v>11.2479829788208</v>
+        <v>11.24798202514648</v>
       </c>
       <c r="C184" t="n">
-        <v>11.2479829788208</v>
+        <v>11.24798202514648</v>
       </c>
       <c r="D184" t="n">
-        <v>10.90333758124669</v>
+        <v>10.90333665679356</v>
       </c>
       <c r="E184" t="n">
-        <v>11.04432925375403</v>
+        <v>11.04432831734674</v>
       </c>
       <c r="F184" t="n">
         <v>3365900</v>
@@ -4172,16 +4172,16 @@
         <v>44917</v>
       </c>
       <c r="B188" t="n">
-        <v>11.63179397583008</v>
+        <v>11.63179492950439</v>
       </c>
       <c r="C188" t="n">
-        <v>11.74928654245482</v>
+        <v>11.74928750576218</v>
       </c>
       <c r="D188" t="n">
-        <v>11.50646762523096</v>
+        <v>11.50646856862995</v>
       </c>
       <c r="E188" t="n">
-        <v>11.60046257493018</v>
+        <v>11.60046352603568</v>
       </c>
       <c r="F188" t="n">
         <v>2577900</v>
@@ -4192,16 +4192,16 @@
         <v>44918</v>
       </c>
       <c r="B189" t="n">
-        <v>11.78845024108887</v>
+        <v>11.78845119476318</v>
       </c>
       <c r="C189" t="n">
-        <v>12.09393119395663</v>
+        <v>12.09393217234406</v>
       </c>
       <c r="D189" t="n">
-        <v>11.57696273802706</v>
+        <v>11.57696367459224</v>
       </c>
       <c r="E189" t="n">
-        <v>11.67878997131614</v>
+        <v>11.67879091611904</v>
       </c>
       <c r="F189" t="n">
         <v>5656000</v>
@@ -4212,16 +4212,16 @@
         <v>44921</v>
       </c>
       <c r="B190" t="n">
-        <v>11.57696342468262</v>
+        <v>11.5769624710083</v>
       </c>
       <c r="C190" t="n">
-        <v>11.82761537802995</v>
+        <v>11.8276144037077</v>
       </c>
       <c r="D190" t="n">
-        <v>11.51430062309566</v>
+        <v>11.51429967458331</v>
       </c>
       <c r="E190" t="n">
-        <v>11.77278486639172</v>
+        <v>11.77278389658625</v>
       </c>
       <c r="F190" t="n">
         <v>1646600</v>
@@ -4392,16 +4392,16 @@
         <v>44935</v>
       </c>
       <c r="B199" t="n">
-        <v>11.2323169708252</v>
+        <v>11.23231792449951</v>
       </c>
       <c r="C199" t="n">
-        <v>11.43597143053319</v>
+        <v>11.43597240149869</v>
       </c>
       <c r="D199" t="n">
-        <v>11.17748721128821</v>
+        <v>11.17748816030724</v>
       </c>
       <c r="E199" t="n">
-        <v>11.36547559855739</v>
+        <v>11.36547656353747</v>
       </c>
       <c r="F199" t="n">
         <v>1567200</v>
@@ -4492,16 +4492,16 @@
         <v>44942</v>
       </c>
       <c r="B204" t="n">
-        <v>11.78845024108887</v>
+        <v>11.78845119476318</v>
       </c>
       <c r="C204" t="n">
-        <v>11.8041155670567</v>
+        <v>11.80411652199833</v>
       </c>
       <c r="D204" t="n">
-        <v>11.39680738089987</v>
+        <v>11.39680830289065</v>
       </c>
       <c r="E204" t="n">
-        <v>11.49080157770529</v>
+        <v>11.49080250730011</v>
       </c>
       <c r="F204" t="n">
         <v>3279700</v>
@@ -4552,16 +4552,16 @@
         <v>44945</v>
       </c>
       <c r="B207" t="n">
-        <v>11.66312599182129</v>
+        <v>11.66312503814697</v>
       </c>
       <c r="C207" t="n">
-        <v>11.68662435698559</v>
+        <v>11.68662340138985</v>
       </c>
       <c r="D207" t="n">
-        <v>11.27931537680668</v>
+        <v>11.27931445451592</v>
       </c>
       <c r="E207" t="n">
-        <v>11.3419781819112</v>
+        <v>11.3419772544966</v>
       </c>
       <c r="F207" t="n">
         <v>1847800</v>
@@ -4612,16 +4612,16 @@
         <v>44950</v>
       </c>
       <c r="B210" t="n">
-        <v>11.68662452697754</v>
+        <v>11.68662357330322</v>
       </c>
       <c r="C210" t="n">
-        <v>11.80411710150764</v>
+        <v>11.80411613824548</v>
       </c>
       <c r="D210" t="n">
-        <v>11.32631301888575</v>
+        <v>11.32631209461427</v>
       </c>
       <c r="E210" t="n">
-        <v>11.52996751193754</v>
+        <v>11.52996657104705</v>
       </c>
       <c r="F210" t="n">
         <v>5839900</v>
@@ -4632,16 +4632,16 @@
         <v>44951</v>
       </c>
       <c r="B211" t="n">
-        <v>11.89027881622314</v>
+        <v>11.89027786254883</v>
       </c>
       <c r="C211" t="n">
-        <v>12.07043419368129</v>
+        <v>12.07043322555739</v>
       </c>
       <c r="D211" t="n">
-        <v>11.62396152172019</v>
+        <v>11.62396058940618</v>
       </c>
       <c r="E211" t="n">
-        <v>11.67879128929448</v>
+        <v>11.67879035258278</v>
       </c>
       <c r="F211" t="n">
         <v>10764800</v>
@@ -4712,16 +4712,16 @@
         <v>44957</v>
       </c>
       <c r="B215" t="n">
-        <v>12.0704345703125</v>
+        <v>12.07043361663818</v>
       </c>
       <c r="C215" t="n">
-        <v>12.14093041482172</v>
+        <v>12.14092945557759</v>
       </c>
       <c r="D215" t="n">
-        <v>11.82761638033583</v>
+        <v>11.82761544584636</v>
       </c>
       <c r="E215" t="n">
-        <v>11.84328170856034</v>
+        <v>11.84328077283316</v>
       </c>
       <c r="F215" t="n">
         <v>5446800</v>
@@ -4852,16 +4852,16 @@
         <v>44966</v>
       </c>
       <c r="B222" t="n">
-        <v>11.66312599182129</v>
+        <v>11.66312503814697</v>
       </c>
       <c r="C222" t="n">
-        <v>11.78845160203032</v>
+        <v>11.78845063810834</v>
       </c>
       <c r="D222" t="n">
-        <v>11.55346570938861</v>
+        <v>11.55346476468103</v>
       </c>
       <c r="E222" t="n">
-        <v>11.7101227221499</v>
+        <v>11.71012176463273</v>
       </c>
       <c r="F222" t="n">
         <v>2260100</v>
@@ -4912,16 +4912,16 @@
         <v>44971</v>
       </c>
       <c r="B225" t="n">
-        <v>11.71795558929443</v>
+        <v>11.71795463562012</v>
       </c>
       <c r="C225" t="n">
-        <v>11.8824456370539</v>
+        <v>11.88244466999244</v>
       </c>
       <c r="D225" t="n">
-        <v>11.51430110216375</v>
+        <v>11.51430016506401</v>
       </c>
       <c r="E225" t="n">
-        <v>11.78061839348856</v>
+        <v>11.78061743471438</v>
       </c>
       <c r="F225" t="n">
         <v>2141000</v>
@@ -4952,16 +4952,16 @@
         <v>44973</v>
       </c>
       <c r="B227" t="n">
-        <v>11.89027881622314</v>
+        <v>11.89027786254883</v>
       </c>
       <c r="C227" t="n">
-        <v>11.9764399862684</v>
+        <v>11.97643902568342</v>
       </c>
       <c r="D227" t="n">
-        <v>11.57696404451397</v>
+        <v>11.57696311596945</v>
       </c>
       <c r="E227" t="n">
-        <v>11.7649532063393</v>
+        <v>11.76495226271687</v>
       </c>
       <c r="F227" t="n">
         <v>4461000</v>
@@ -4992,16 +4992,16 @@
         <v>44979</v>
       </c>
       <c r="B229" t="n">
-        <v>11.71795558929443</v>
+        <v>11.71795463562012</v>
       </c>
       <c r="C229" t="n">
-        <v>11.95294147852217</v>
+        <v>11.95294050572336</v>
       </c>
       <c r="D229" t="n">
-        <v>11.66312582237446</v>
+        <v>11.66312487316251</v>
       </c>
       <c r="E229" t="n">
-        <v>11.89811096460265</v>
+        <v>11.89810999626626</v>
       </c>
       <c r="F229" t="n">
         <v>6185800</v>
@@ -5072,16 +5072,16 @@
         <v>44985</v>
       </c>
       <c r="B233" t="n">
-        <v>11.59262943267822</v>
+        <v>11.59263038635254</v>
       </c>
       <c r="C233" t="n">
-        <v>11.82761531079323</v>
+        <v>11.82761628379879</v>
       </c>
       <c r="D233" t="n">
-        <v>11.54563195825542</v>
+        <v>11.54563290806346</v>
       </c>
       <c r="E233" t="n">
-        <v>11.67095756071688</v>
+        <v>11.67095852083491</v>
       </c>
       <c r="F233" t="n">
         <v>7018700</v>
@@ -5172,16 +5172,16 @@
         <v>44992</v>
       </c>
       <c r="B238" t="n">
-        <v>11.61612701416016</v>
+        <v>11.61612796783447</v>
       </c>
       <c r="C238" t="n">
-        <v>11.6239600505364</v>
+        <v>11.6239610048538</v>
       </c>
       <c r="D238" t="n">
-        <v>11.38897418824534</v>
+        <v>11.3889751232706</v>
       </c>
       <c r="E238" t="n">
-        <v>11.52996585501987</v>
+        <v>11.52996680162043</v>
       </c>
       <c r="F238" t="n">
         <v>3776700</v>
@@ -5192,16 +5192,16 @@
         <v>44993</v>
       </c>
       <c r="B239" t="n">
-        <v>11.63179397583008</v>
+        <v>11.63179492950439</v>
       </c>
       <c r="C239" t="n">
-        <v>11.63962626580541</v>
+        <v>11.63962722012189</v>
       </c>
       <c r="D239" t="n">
-        <v>11.48296926130592</v>
+        <v>11.48297020277831</v>
       </c>
       <c r="E239" t="n">
-        <v>11.62396093885522</v>
+        <v>11.62396189188732</v>
       </c>
       <c r="F239" t="n">
         <v>2946500</v>
@@ -5212,16 +5212,16 @@
         <v>44994</v>
       </c>
       <c r="B240" t="n">
-        <v>11.57696342468262</v>
+        <v>11.5769624710083</v>
       </c>
       <c r="C240" t="n">
-        <v>11.70228902785652</v>
+        <v>11.70228806385827</v>
       </c>
       <c r="D240" t="n">
-        <v>11.51430062309566</v>
+        <v>11.51429967458331</v>
       </c>
       <c r="E240" t="n">
-        <v>11.62396089937259</v>
+        <v>11.62395994182677</v>
       </c>
       <c r="F240" t="n">
         <v>2514900</v>
@@ -5232,16 +5232,16 @@
         <v>44995</v>
       </c>
       <c r="B241" t="n">
-        <v>11.57696342468262</v>
+        <v>11.5769624710083</v>
       </c>
       <c r="C241" t="n">
-        <v>11.63179393632084</v>
+        <v>11.63179297812976</v>
       </c>
       <c r="D241" t="n">
-        <v>11.44380478456046</v>
+        <v>11.44380384185534</v>
       </c>
       <c r="E241" t="n">
-        <v>11.57696342468262</v>
+        <v>11.5769624710083</v>
       </c>
       <c r="F241" t="n">
         <v>3626000</v>
@@ -5252,16 +5252,16 @@
         <v>44998</v>
       </c>
       <c r="B242" t="n">
-        <v>11.66312599182129</v>
+        <v>11.66312503814697</v>
       </c>
       <c r="C242" t="n">
-        <v>11.74145412470215</v>
+        <v>11.74145316462308</v>
       </c>
       <c r="D242" t="n">
-        <v>11.45947150173183</v>
+        <v>11.45947056471</v>
       </c>
       <c r="E242" t="n">
-        <v>11.52213430683635</v>
+        <v>11.52213336469069</v>
       </c>
       <c r="F242" t="n">
         <v>3223500</v>
@@ -5312,16 +5312,16 @@
         <v>45001</v>
       </c>
       <c r="B245" t="n">
-        <v>11.67095851898193</v>
+        <v>11.67095756530762</v>
       </c>
       <c r="C245" t="n">
-        <v>11.81195020682722</v>
+        <v>11.81194924163198</v>
       </c>
       <c r="D245" t="n">
-        <v>11.63962711579405</v>
+        <v>11.63962616467993</v>
       </c>
       <c r="E245" t="n">
-        <v>11.81195020682722</v>
+        <v>11.81194924163198</v>
       </c>
       <c r="F245" t="n">
         <v>5495800</v>
@@ -5392,16 +5392,16 @@
         <v>45007</v>
       </c>
       <c r="B249" t="n">
-        <v>11.33414554595947</v>
+        <v>11.33414459228516</v>
       </c>
       <c r="C249" t="n">
-        <v>11.45947115234749</v>
+        <v>11.45947018812806</v>
       </c>
       <c r="D249" t="n">
-        <v>11.21665222972105</v>
+        <v>11.21665128593282</v>
       </c>
       <c r="E249" t="n">
-        <v>11.36547694755648</v>
+        <v>11.36547599124588</v>
       </c>
       <c r="F249" t="n">
         <v>3006300</v>
@@ -5452,16 +5452,16 @@
         <v>45012</v>
       </c>
       <c r="B252" t="n">
-        <v>11.28714847564697</v>
+        <v>11.28714752197266</v>
       </c>
       <c r="C252" t="n">
-        <v>11.42030712396893</v>
+        <v>11.42030615904377</v>
       </c>
       <c r="D252" t="n">
-        <v>11.19315426747845</v>
+        <v>11.1931533217459</v>
       </c>
       <c r="E252" t="n">
-        <v>11.39680875867669</v>
+        <v>11.39680779573696</v>
       </c>
       <c r="F252" t="n">
         <v>2288800</v>
@@ -5532,16 +5532,16 @@
         <v>45016</v>
       </c>
       <c r="B256" t="n">
-        <v>11.49080276489258</v>
+        <v>11.49080181121826</v>
       </c>
       <c r="C256" t="n">
-        <v>11.61612837358132</v>
+        <v>11.61612740950566</v>
       </c>
       <c r="D256" t="n">
-        <v>11.30281435185946</v>
+        <v>11.30281341378716</v>
       </c>
       <c r="E256" t="n">
-        <v>11.42813996054821</v>
+        <v>11.42813901207456</v>
       </c>
       <c r="F256" t="n">
         <v>5155800</v>
@@ -5572,16 +5572,16 @@
         <v>45020</v>
       </c>
       <c r="B258" t="n">
-        <v>11.43597221374512</v>
+        <v>11.43597316741943</v>
       </c>
       <c r="C258" t="n">
-        <v>11.49863501379308</v>
+        <v>11.498635972693</v>
       </c>
       <c r="D258" t="n">
-        <v>11.24798306660174</v>
+        <v>11.24798400459917</v>
       </c>
       <c r="E258" t="n">
-        <v>11.35764334018542</v>
+        <v>11.35764428732769</v>
       </c>
       <c r="F258" t="n">
         <v>5230100</v>
@@ -5592,16 +5592,16 @@
         <v>45021</v>
       </c>
       <c r="B259" t="n">
-        <v>11.49080276489258</v>
+        <v>11.49080181121826</v>
       </c>
       <c r="C259" t="n">
-        <v>11.56913164382282</v>
+        <v>11.56913068364763</v>
       </c>
       <c r="D259" t="n">
-        <v>11.27931523998066</v>
+        <v>11.27931430385866</v>
       </c>
       <c r="E259" t="n">
-        <v>11.55346556923695</v>
+        <v>11.55346461036196</v>
       </c>
       <c r="F259" t="n">
         <v>4689800</v>
@@ -5632,16 +5632,16 @@
         <v>45026</v>
       </c>
       <c r="B261" t="n">
-        <v>11.71795558929443</v>
+        <v>11.71795463562012</v>
       </c>
       <c r="C261" t="n">
-        <v>11.85111423495683</v>
+        <v>11.85111327044531</v>
       </c>
       <c r="D261" t="n">
-        <v>11.45947133524378</v>
+        <v>11.4594704026064</v>
       </c>
       <c r="E261" t="n">
-        <v>11.53779946698666</v>
+        <v>11.53779852797449</v>
       </c>
       <c r="F261" t="n">
         <v>3430500</v>
@@ -5892,16 +5892,16 @@
         <v>45044</v>
       </c>
       <c r="B274" t="n">
-        <v>12.36024951934814</v>
+        <v>12.36024856567383</v>
       </c>
       <c r="C274" t="n">
-        <v>12.45424372422157</v>
+        <v>12.45424276329498</v>
       </c>
       <c r="D274" t="n">
-        <v>12.01560410147892</v>
+        <v>12.01560317439626</v>
       </c>
       <c r="E274" t="n">
-        <v>12.11743134350835</v>
+        <v>12.11743040856905</v>
       </c>
       <c r="F274" t="n">
         <v>8419400</v>
@@ -5932,16 +5932,16 @@
         <v>45049</v>
       </c>
       <c r="B276" t="n">
-        <v>12.28975391387939</v>
+        <v>12.28975296020508</v>
       </c>
       <c r="C276" t="n">
-        <v>12.48557536452565</v>
+        <v>12.48557439565576</v>
       </c>
       <c r="D276" t="n">
-        <v>12.2819216235732</v>
+        <v>12.28192067050667</v>
       </c>
       <c r="E276" t="n">
-        <v>12.48557536452565</v>
+        <v>12.48557439565576</v>
       </c>
       <c r="F276" t="n">
         <v>6661600</v>
@@ -6052,16 +6052,16 @@
         <v>45057</v>
       </c>
       <c r="B282" t="n">
-        <v>12.05971527099609</v>
+        <v>12.05971622467041</v>
       </c>
       <c r="C282" t="n">
-        <v>12.11165902259875</v>
+        <v>12.11165998038074</v>
       </c>
       <c r="D282" t="n">
-        <v>11.7393927173429</v>
+        <v>11.73939364568632</v>
       </c>
       <c r="E282" t="n">
-        <v>11.79133646894556</v>
+        <v>11.79133740139665</v>
       </c>
       <c r="F282" t="n">
         <v>3678200</v>
@@ -6132,16 +6132,16 @@
         <v>45063</v>
       </c>
       <c r="B286" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="C286" t="n">
-        <v>12.24152036724783</v>
+        <v>12.24151939290137</v>
       </c>
       <c r="D286" t="n">
-        <v>11.9471696818366</v>
+        <v>11.94716873091856</v>
       </c>
       <c r="E286" t="n">
-        <v>12.128974468377</v>
+        <v>12.12897350298847</v>
       </c>
       <c r="F286" t="n">
         <v>4330800</v>
@@ -6152,16 +6152,16 @@
         <v>45064</v>
       </c>
       <c r="B287" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="C287" t="n">
-        <v>12.05971558070743</v>
+        <v>12.05971462083146</v>
       </c>
       <c r="D287" t="n">
-        <v>11.82596621559931</v>
+        <v>11.82596527432829</v>
       </c>
       <c r="E287" t="n">
-        <v>12.01642856950617</v>
+        <v>12.01642761307558</v>
       </c>
       <c r="F287" t="n">
         <v>4680600</v>
@@ -6172,16 +6172,16 @@
         <v>45065</v>
       </c>
       <c r="B288" t="n">
-        <v>12.09434509277344</v>
+        <v>12.09434413909912</v>
       </c>
       <c r="C288" t="n">
-        <v>12.18091829003328</v>
+        <v>12.18091732953242</v>
       </c>
       <c r="D288" t="n">
-        <v>11.93851218182222</v>
+        <v>11.93851124043578</v>
       </c>
       <c r="E288" t="n">
-        <v>11.99911350246722</v>
+        <v>11.99911255630219</v>
       </c>
       <c r="F288" t="n">
         <v>2962700</v>
@@ -6232,16 +6232,16 @@
         <v>45070</v>
       </c>
       <c r="B291" t="n">
-        <v>12.25017642974854</v>
+        <v>12.25017738342285</v>
       </c>
       <c r="C291" t="n">
-        <v>12.30212100543608</v>
+        <v>12.30212196315428</v>
       </c>
       <c r="D291" t="n">
-        <v>12.18091754591915</v>
+        <v>12.18091849420168</v>
       </c>
       <c r="E291" t="n">
-        <v>12.26749156352139</v>
+        <v>12.26749251854369</v>
       </c>
       <c r="F291" t="n">
         <v>1846000</v>
@@ -6292,16 +6292,16 @@
         <v>45075</v>
       </c>
       <c r="B294" t="n">
-        <v>12.28480529785156</v>
+        <v>12.28480625152588</v>
       </c>
       <c r="C294" t="n">
-        <v>12.34540743759487</v>
+        <v>12.34540839597375</v>
       </c>
       <c r="D294" t="n">
-        <v>12.16360266962691</v>
+        <v>12.16360361389222</v>
       </c>
       <c r="E294" t="n">
-        <v>12.16360266962691</v>
+        <v>12.16360361389222</v>
       </c>
       <c r="F294" t="n">
         <v>1431900</v>
@@ -6352,16 +6352,16 @@
         <v>45078</v>
       </c>
       <c r="B297" t="n">
-        <v>12.24151992797852</v>
+        <v>12.2415189743042</v>
       </c>
       <c r="C297" t="n">
-        <v>12.30212124610704</v>
+        <v>12.30212028771158</v>
       </c>
       <c r="D297" t="n">
-        <v>12.1636034757384</v>
+        <v>12.16360252813415</v>
       </c>
       <c r="E297" t="n">
-        <v>12.26749180351488</v>
+        <v>12.26749084781722</v>
       </c>
       <c r="F297" t="n">
         <v>2308800</v>
@@ -6372,16 +6372,16 @@
         <v>45079</v>
       </c>
       <c r="B298" t="n">
-        <v>12.17226123809814</v>
+        <v>12.17226219177246</v>
       </c>
       <c r="C298" t="n">
-        <v>12.33675088664238</v>
+        <v>12.33675185320416</v>
       </c>
       <c r="D298" t="n">
-        <v>12.07702965021844</v>
+        <v>12.07703059643153</v>
       </c>
       <c r="E298" t="n">
-        <v>12.3107790106893</v>
+        <v>12.31077997521623</v>
       </c>
       <c r="F298" t="n">
         <v>5725100</v>
@@ -6412,16 +6412,16 @@
         <v>45083</v>
       </c>
       <c r="B300" t="n">
-        <v>12.32809352874756</v>
+        <v>12.32809257507324</v>
       </c>
       <c r="C300" t="n">
-        <v>12.41466755090237</v>
+        <v>12.41466659053087</v>
       </c>
       <c r="D300" t="n">
-        <v>12.0770298552559</v>
+        <v>12.07702892100332</v>
       </c>
       <c r="E300" t="n">
-        <v>12.08568742259759</v>
+        <v>12.08568648767528</v>
       </c>
       <c r="F300" t="n">
         <v>7376500</v>
@@ -6432,16 +6432,16 @@
         <v>45084</v>
       </c>
       <c r="B301" t="n">
-        <v>12.22420501708984</v>
+        <v>12.22420406341553</v>
       </c>
       <c r="C301" t="n">
-        <v>12.46661111966148</v>
+        <v>12.46661014707579</v>
       </c>
       <c r="D301" t="n">
-        <v>12.21554744987595</v>
+        <v>12.21554649687706</v>
       </c>
       <c r="E301" t="n">
-        <v>12.3800379244157</v>
+        <v>12.38003695858405</v>
       </c>
       <c r="F301" t="n">
         <v>3154600</v>
@@ -6472,16 +6472,16 @@
         <v>45089</v>
       </c>
       <c r="B303" t="n">
-        <v>12.45795345306396</v>
+        <v>12.45795440673828</v>
       </c>
       <c r="C303" t="n">
-        <v>12.45795345306396</v>
+        <v>12.45795440673828</v>
       </c>
       <c r="D303" t="n">
-        <v>12.25883355008453</v>
+        <v>12.25883448851593</v>
       </c>
       <c r="E303" t="n">
-        <v>12.3800370051864</v>
+        <v>12.3800379528961</v>
       </c>
       <c r="F303" t="n">
         <v>2572800</v>
@@ -6612,16 +6612,16 @@
         <v>45098</v>
       </c>
       <c r="B310" t="n">
-        <v>12.86484909057617</v>
+        <v>12.86485004425049</v>
       </c>
       <c r="C310" t="n">
-        <v>12.90813609751867</v>
+        <v>12.90813705440186</v>
       </c>
       <c r="D310" t="n">
-        <v>12.63975814061098</v>
+        <v>12.63975907759925</v>
       </c>
       <c r="E310" t="n">
-        <v>12.75230320277808</v>
+        <v>12.75230414810935</v>
       </c>
       <c r="F310" t="n">
         <v>5022600</v>
@@ -6652,16 +6652,16 @@
         <v>45100</v>
       </c>
       <c r="B312" t="n">
-        <v>12.94276714324951</v>
+        <v>12.9427661895752</v>
       </c>
       <c r="C312" t="n">
-        <v>13.07262818018377</v>
+        <v>13.07262721694078</v>
       </c>
       <c r="D312" t="n">
-        <v>12.76096235204642</v>
+        <v>12.7609614117682</v>
       </c>
       <c r="E312" t="n">
-        <v>12.81290693194634</v>
+        <v>12.81290598784064</v>
       </c>
       <c r="F312" t="n">
         <v>2959500</v>
@@ -6692,16 +6692,16 @@
         <v>45104</v>
       </c>
       <c r="B314" t="n">
-        <v>12.50124073028564</v>
+        <v>12.50123977661133</v>
       </c>
       <c r="C314" t="n">
-        <v>12.83887842546918</v>
+        <v>12.83887744603771</v>
       </c>
       <c r="D314" t="n">
-        <v>12.39735239922096</v>
+        <v>12.3973514534719</v>
       </c>
       <c r="E314" t="n">
-        <v>12.76961953809272</v>
+        <v>12.76961856394476</v>
       </c>
       <c r="F314" t="n">
         <v>3014700</v>
@@ -6812,16 +6812,16 @@
         <v>45112</v>
       </c>
       <c r="B320" t="n">
-        <v>12.44063949584961</v>
+        <v>12.44063854217529</v>
       </c>
       <c r="C320" t="n">
-        <v>12.54452782762921</v>
+        <v>12.54452686599102</v>
       </c>
       <c r="D320" t="n">
-        <v>12.24152039967981</v>
+        <v>12.24151946126957</v>
       </c>
       <c r="E320" t="n">
-        <v>12.30212172014348</v>
+        <v>12.30212077708766</v>
       </c>
       <c r="F320" t="n">
         <v>5051100</v>
@@ -6832,16 +6832,16 @@
         <v>45113</v>
       </c>
       <c r="B321" t="n">
-        <v>12.32809352874756</v>
+        <v>12.32809257507324</v>
       </c>
       <c r="C321" t="n">
-        <v>12.48392643837378</v>
+        <v>12.48392547264458</v>
       </c>
       <c r="D321" t="n">
-        <v>12.25017707393445</v>
+        <v>12.25017612628758</v>
       </c>
       <c r="E321" t="n">
-        <v>12.43198185995469</v>
+        <v>12.4319808982438</v>
       </c>
       <c r="F321" t="n">
         <v>2081000</v>
@@ -6932,16 +6932,16 @@
         <v>45120</v>
       </c>
       <c r="B326" t="n">
-        <v>12.44063949584961</v>
+        <v>12.44063854217529</v>
       </c>
       <c r="C326" t="n">
-        <v>12.51855595109208</v>
+        <v>12.51855499144484</v>
       </c>
       <c r="D326" t="n">
-        <v>12.34540873145941</v>
+        <v>12.34540778508529</v>
       </c>
       <c r="E326" t="n">
-        <v>12.47526893977614</v>
+        <v>12.4752679834472</v>
       </c>
       <c r="F326" t="n">
         <v>1737300</v>
@@ -6952,16 +6952,16 @@
         <v>45121</v>
       </c>
       <c r="B327" t="n">
-        <v>12.38003730773926</v>
+        <v>12.38003826141357</v>
       </c>
       <c r="C327" t="n">
-        <v>12.48392563223791</v>
+        <v>12.48392659391508</v>
       </c>
       <c r="D327" t="n">
-        <v>12.33675029945707</v>
+        <v>12.33675124979684</v>
       </c>
       <c r="E327" t="n">
-        <v>12.48392563223791</v>
+        <v>12.48392659391508</v>
       </c>
       <c r="F327" t="n">
         <v>1319400</v>
@@ -7092,16 +7092,16 @@
         <v>45132</v>
       </c>
       <c r="B334" t="n">
-        <v>12.17226123809814</v>
+        <v>12.17226219177246</v>
       </c>
       <c r="C334" t="n">
-        <v>12.47526865923354</v>
+        <v>12.47526963664793</v>
       </c>
       <c r="D334" t="n">
-        <v>12.16360367090343</v>
+        <v>12.16360462389945</v>
       </c>
       <c r="E334" t="n">
-        <v>12.41466734013267</v>
+        <v>12.41466831279906</v>
       </c>
       <c r="F334" t="n">
         <v>2710400</v>
@@ -7192,16 +7192,16 @@
         <v>45139</v>
       </c>
       <c r="B339" t="n">
-        <v>12.12897491455078</v>
+        <v>12.12897396087646</v>
       </c>
       <c r="C339" t="n">
-        <v>12.38003859799633</v>
+        <v>12.38003762458143</v>
       </c>
       <c r="D339" t="n">
-        <v>12.08568790175718</v>
+        <v>12.08568695148643</v>
       </c>
       <c r="E339" t="n">
-        <v>12.12031734686584</v>
+        <v>12.12031639387225</v>
       </c>
       <c r="F339" t="n">
         <v>5884200</v>
@@ -7212,16 +7212,16 @@
         <v>45140</v>
       </c>
       <c r="B340" t="n">
-        <v>12.22420501708984</v>
+        <v>12.22420406341553</v>
       </c>
       <c r="C340" t="n">
-        <v>12.23286258430374</v>
+        <v>12.232861629954</v>
       </c>
       <c r="D340" t="n">
-        <v>12.12897425463018</v>
+        <v>12.12897330838532</v>
       </c>
       <c r="E340" t="n">
-        <v>12.13763182184407</v>
+        <v>12.13763087492379</v>
       </c>
       <c r="F340" t="n">
         <v>1697600</v>
@@ -7332,16 +7332,16 @@
         <v>45148</v>
       </c>
       <c r="B346" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C346" t="n">
-        <v>12.09434549372545</v>
+        <v>12.09434452900206</v>
       </c>
       <c r="D346" t="n">
-        <v>11.88656799702522</v>
+        <v>11.88656704887551</v>
       </c>
       <c r="E346" t="n">
-        <v>12.01642903566675</v>
+        <v>12.01642807715848</v>
       </c>
       <c r="F346" t="n">
         <v>2835300</v>
@@ -7352,16 +7352,16 @@
         <v>45149</v>
       </c>
       <c r="B347" t="n">
-        <v>11.92119789123535</v>
+        <v>11.92119693756104</v>
       </c>
       <c r="C347" t="n">
-        <v>11.97314164454614</v>
+        <v>11.97314068671642</v>
       </c>
       <c r="D347" t="n">
-        <v>11.83462386820927</v>
+        <v>11.83462292146072</v>
       </c>
       <c r="E347" t="n">
-        <v>11.97314164454614</v>
+        <v>11.97314068671642</v>
       </c>
       <c r="F347" t="n">
         <v>2472600</v>
@@ -7372,16 +7372,16 @@
         <v>45152</v>
       </c>
       <c r="B348" t="n">
-        <v>11.9125394821167</v>
+        <v>11.91254043579102</v>
       </c>
       <c r="C348" t="n">
-        <v>11.96448323175737</v>
+        <v>11.96448418959011</v>
       </c>
       <c r="D348" t="n">
-        <v>11.82596546520757</v>
+        <v>11.82596641195109</v>
       </c>
       <c r="E348" t="n">
-        <v>11.92119704893382</v>
+        <v>11.92119800330122</v>
       </c>
       <c r="F348" t="n">
         <v>1369900</v>
@@ -7392,16 +7392,16 @@
         <v>45153</v>
       </c>
       <c r="B349" t="n">
-        <v>11.86059474945068</v>
+        <v>11.860595703125</v>
       </c>
       <c r="C349" t="n">
-        <v>11.9991125141623</v>
+        <v>11.99911347897441</v>
       </c>
       <c r="D349" t="n">
-        <v>11.85193718274846</v>
+        <v>11.85193813572664</v>
       </c>
       <c r="E349" t="n">
-        <v>11.91253932403304</v>
+        <v>11.91254028188406</v>
       </c>
       <c r="F349" t="n">
         <v>2713800</v>
@@ -7452,16 +7452,16 @@
         <v>45156</v>
       </c>
       <c r="B352" t="n">
-        <v>11.77402114868164</v>
+        <v>11.77402210235596</v>
       </c>
       <c r="C352" t="n">
-        <v>11.80865058865178</v>
+        <v>11.80865154513102</v>
       </c>
       <c r="D352" t="n">
-        <v>11.65281769597066</v>
+        <v>11.65281863982772</v>
       </c>
       <c r="E352" t="n">
-        <v>11.71341900951066</v>
+        <v>11.71341995827632</v>
       </c>
       <c r="F352" t="n">
         <v>3061800</v>
@@ -7512,16 +7512,16 @@
         <v>45161</v>
       </c>
       <c r="B355" t="n">
-        <v>11.87790966033936</v>
+        <v>11.87791061401367</v>
       </c>
       <c r="C355" t="n">
-        <v>11.89522396778845</v>
+        <v>11.89522492285292</v>
       </c>
       <c r="D355" t="n">
-        <v>11.79133564620093</v>
+        <v>11.79133659292425</v>
       </c>
       <c r="E355" t="n">
-        <v>11.86059452725928</v>
+        <v>11.86059547954337</v>
       </c>
       <c r="F355" t="n">
         <v>2615000</v>
@@ -7532,16 +7532,16 @@
         <v>45162</v>
       </c>
       <c r="B356" t="n">
-        <v>11.97314071655273</v>
+        <v>11.97314167022705</v>
       </c>
       <c r="C356" t="n">
-        <v>11.99911259119515</v>
+        <v>11.99911354693815</v>
       </c>
       <c r="D356" t="n">
-        <v>11.89522426699448</v>
+        <v>11.89522521446267</v>
       </c>
       <c r="E356" t="n">
-        <v>11.90388183375229</v>
+        <v>11.90388278191006</v>
       </c>
       <c r="F356" t="n">
         <v>2322800</v>
@@ -7672,16 +7672,16 @@
         <v>45173</v>
       </c>
       <c r="B363" t="n">
-        <v>12.01642894744873</v>
+        <v>12.01642799377441</v>
       </c>
       <c r="C363" t="n">
-        <v>12.05105839237269</v>
+        <v>12.05105743595003</v>
       </c>
       <c r="D363" t="n">
-        <v>11.81730901991265</v>
+        <v>11.81730808204133</v>
       </c>
       <c r="E363" t="n">
-        <v>12.05105839237269</v>
+        <v>12.05105743595003</v>
       </c>
       <c r="F363" t="n">
         <v>2040600</v>
@@ -7692,16 +7692,16 @@
         <v>45174</v>
       </c>
       <c r="B364" t="n">
-        <v>11.92119789123535</v>
+        <v>11.92119693756104</v>
       </c>
       <c r="C364" t="n">
-        <v>12.06837240936998</v>
+        <v>12.06837144392197</v>
       </c>
       <c r="D364" t="n">
-        <v>11.91254032380653</v>
+        <v>11.9125393708248</v>
       </c>
       <c r="E364" t="n">
-        <v>12.04240053271458</v>
+        <v>12.04239956934427</v>
       </c>
       <c r="F364" t="n">
         <v>3869600</v>
@@ -7712,16 +7712,16 @@
         <v>45175</v>
       </c>
       <c r="B365" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C365" t="n">
-        <v>12.02508660336907</v>
+        <v>12.02508564417022</v>
       </c>
       <c r="D365" t="n">
-        <v>11.81730910666884</v>
+        <v>11.81730816404367</v>
       </c>
       <c r="E365" t="n">
-        <v>11.93851257760805</v>
+        <v>11.9385116253149</v>
       </c>
       <c r="F365" t="n">
         <v>2473500</v>
@@ -7852,16 +7852,16 @@
         <v>45187</v>
       </c>
       <c r="B372" t="n">
-        <v>12.05971527099609</v>
+        <v>12.05971622467041</v>
       </c>
       <c r="C372" t="n">
-        <v>12.24152005286748</v>
+        <v>12.2415210209188</v>
       </c>
       <c r="D372" t="n">
-        <v>11.99911312661827</v>
+        <v>11.99911407550021</v>
       </c>
       <c r="E372" t="n">
-        <v>12.21554735143511</v>
+        <v>12.21554831743252</v>
       </c>
       <c r="F372" t="n">
         <v>3188500</v>
@@ -7912,16 +7912,16 @@
         <v>45190</v>
       </c>
       <c r="B375" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C375" t="n">
-        <v>12.0337433454403</v>
+        <v>12.03374238555092</v>
       </c>
       <c r="D375" t="n">
-        <v>11.877911254954</v>
+        <v>11.8779103074948</v>
       </c>
       <c r="E375" t="n">
-        <v>12.02508660336907</v>
+        <v>12.02508564417022</v>
       </c>
       <c r="F375" t="n">
         <v>4405700</v>
@@ -7932,16 +7932,16 @@
         <v>45191</v>
       </c>
       <c r="B376" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C376" t="n">
-        <v>12.10300223579667</v>
+        <v>12.10300127038276</v>
       </c>
       <c r="D376" t="n">
-        <v>11.92985500990573</v>
+        <v>11.92985405830317</v>
       </c>
       <c r="E376" t="n">
-        <v>12.02508660336907</v>
+        <v>12.02508564417022</v>
       </c>
       <c r="F376" t="n">
         <v>2812600</v>
@@ -7972,16 +7972,16 @@
         <v>45195</v>
       </c>
       <c r="B378" t="n">
-        <v>11.83462333679199</v>
+        <v>11.83462238311768</v>
       </c>
       <c r="C378" t="n">
-        <v>12.06837186745655</v>
+        <v>12.06837089494598</v>
       </c>
       <c r="D378" t="n">
-        <v>11.78267876018263</v>
+        <v>11.78267781069418</v>
       </c>
       <c r="E378" t="n">
-        <v>11.80865146130283</v>
+        <v>11.80865050972141</v>
       </c>
       <c r="F378" t="n">
         <v>7795500</v>
@@ -8092,16 +8092,16 @@
         <v>45203</v>
       </c>
       <c r="B384" t="n">
-        <v>11.77402114868164</v>
+        <v>11.77402210235596</v>
       </c>
       <c r="C384" t="n">
-        <v>11.86059433579151</v>
+        <v>11.86059529647809</v>
       </c>
       <c r="D384" t="n">
-        <v>11.7480484494808</v>
+        <v>11.74804940105138</v>
       </c>
       <c r="E384" t="n">
-        <v>11.80865058865178</v>
+        <v>11.80865154513102</v>
       </c>
       <c r="F384" t="n">
         <v>4367600</v>
@@ -8152,16 +8152,16 @@
         <v>45208</v>
       </c>
       <c r="B387" t="n">
-        <v>11.9125394821167</v>
+        <v>11.91254043579102</v>
       </c>
       <c r="C387" t="n">
-        <v>11.92985379011992</v>
+        <v>11.92985474518035</v>
       </c>
       <c r="D387" t="n">
-        <v>11.61818881538288</v>
+        <v>11.61818974549255</v>
       </c>
       <c r="E387" t="n">
-        <v>11.61818881538288</v>
+        <v>11.61818974549255</v>
       </c>
       <c r="F387" t="n">
         <v>4118900</v>
@@ -8192,16 +8192,16 @@
         <v>45210</v>
       </c>
       <c r="B389" t="n">
-        <v>12.09434509277344</v>
+        <v>12.09434413909912</v>
       </c>
       <c r="C389" t="n">
-        <v>12.18957585744859</v>
+        <v>12.18957489626505</v>
       </c>
       <c r="D389" t="n">
-        <v>12.00777106988252</v>
+        <v>12.00777012303482</v>
       </c>
       <c r="E389" t="n">
-        <v>12.09434509277344</v>
+        <v>12.09434413909912</v>
       </c>
       <c r="F389" t="n">
         <v>3458500</v>
@@ -8232,16 +8232,16 @@
         <v>45215</v>
       </c>
       <c r="B391" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="C391" t="n">
-        <v>12.12031690101054</v>
+        <v>12.12031593631109</v>
       </c>
       <c r="D391" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="E391" t="n">
-        <v>12.05971558070743</v>
+        <v>12.05971462083146</v>
       </c>
       <c r="F391" t="n">
         <v>3983600</v>
@@ -8252,16 +8252,16 @@
         <v>45216</v>
       </c>
       <c r="B392" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C392" t="n">
-        <v>12.10300223579667</v>
+        <v>12.10300127038276</v>
       </c>
       <c r="D392" t="n">
-        <v>11.88656799702522</v>
+        <v>11.88656704887551</v>
       </c>
       <c r="E392" t="n">
-        <v>11.97314202278624</v>
+        <v>11.97314106773082</v>
       </c>
       <c r="F392" t="n">
         <v>5165000</v>
@@ -8312,16 +8312,16 @@
         <v>45219</v>
       </c>
       <c r="B395" t="n">
-        <v>11.76536464691162</v>
+        <v>11.76536560058594</v>
       </c>
       <c r="C395" t="n">
-        <v>11.91253998651014</v>
+        <v>11.91254095211416</v>
       </c>
       <c r="D395" t="n">
-        <v>11.67013305915314</v>
+        <v>11.67013400510819</v>
       </c>
       <c r="E395" t="n">
-        <v>11.67013305915314</v>
+        <v>11.67013400510819</v>
       </c>
       <c r="F395" t="n">
         <v>6261200</v>
@@ -8332,16 +8332,16 @@
         <v>45222</v>
       </c>
       <c r="B396" t="n">
-        <v>11.72207832336426</v>
+        <v>11.72207736968994</v>
       </c>
       <c r="C396" t="n">
-        <v>11.90388311671755</v>
+        <v>11.90388214825212</v>
       </c>
       <c r="D396" t="n">
-        <v>11.72207832336426</v>
+        <v>11.72207736968994</v>
       </c>
       <c r="E396" t="n">
-        <v>11.77402290387853</v>
+        <v>11.77402194597815</v>
       </c>
       <c r="F396" t="n">
         <v>3068100</v>
@@ -8552,16 +8552,16 @@
         <v>45238</v>
       </c>
       <c r="B407" t="n">
-        <v>11.81730842590332</v>
+        <v>11.817307472229</v>
       </c>
       <c r="C407" t="n">
-        <v>11.96448376583999</v>
+        <v>11.96448280028841</v>
       </c>
       <c r="D407" t="n">
-        <v>11.73073523076066</v>
+        <v>11.73073428407293</v>
       </c>
       <c r="E407" t="n">
-        <v>11.9385118898603</v>
+        <v>11.93851092640469</v>
       </c>
       <c r="F407" t="n">
         <v>5488500</v>
@@ -8652,16 +8652,16 @@
         <v>45246</v>
       </c>
       <c r="B412" t="n">
-        <v>12.49258327484131</v>
+        <v>12.49258422851562</v>
       </c>
       <c r="C412" t="n">
-        <v>12.49258327484131</v>
+        <v>12.49258422851562</v>
       </c>
       <c r="D412" t="n">
-        <v>12.12897372407367</v>
+        <v>12.12897464999031</v>
       </c>
       <c r="E412" t="n">
-        <v>12.12897372407367</v>
+        <v>12.12897464999031</v>
       </c>
       <c r="F412" t="n">
         <v>6741500</v>
@@ -8672,16 +8672,16 @@
         <v>45247</v>
       </c>
       <c r="B413" t="n">
-        <v>12.25017642974854</v>
+        <v>12.25017738342285</v>
       </c>
       <c r="C413" t="n">
-        <v>12.48392578189597</v>
+        <v>12.48392675376763</v>
       </c>
       <c r="D413" t="n">
-        <v>12.14628810400446</v>
+        <v>12.14628904959109</v>
       </c>
       <c r="E413" t="n">
-        <v>12.48392578189597</v>
+        <v>12.48392675376763</v>
       </c>
       <c r="F413" t="n">
         <v>3124800</v>
@@ -8712,16 +8712,16 @@
         <v>45251</v>
       </c>
       <c r="B415" t="n">
-        <v>11.97314071655273</v>
+        <v>11.97314167022705</v>
       </c>
       <c r="C415" t="n">
-        <v>12.09434417426901</v>
+        <v>12.09434513759732</v>
       </c>
       <c r="D415" t="n">
-        <v>11.9125394005101</v>
+        <v>11.91254034935745</v>
       </c>
       <c r="E415" t="n">
-        <v>12.0856866075112</v>
+        <v>12.08568757014993</v>
       </c>
       <c r="F415" t="n">
         <v>2713400</v>
@@ -8752,16 +8752,16 @@
         <v>45253</v>
       </c>
       <c r="B417" t="n">
-        <v>12.56184196472168</v>
+        <v>12.561842918396</v>
       </c>
       <c r="C417" t="n">
-        <v>12.76961861177884</v>
+        <v>12.76961958122722</v>
       </c>
       <c r="D417" t="n">
-        <v>12.46661038226389</v>
+        <v>12.46661132870839</v>
       </c>
       <c r="E417" t="n">
-        <v>12.76961861177884</v>
+        <v>12.76961958122722</v>
       </c>
       <c r="F417" t="n">
         <v>9122900</v>
@@ -8832,16 +8832,16 @@
         <v>45259</v>
       </c>
       <c r="B421" t="n">
-        <v>12.56184196472168</v>
+        <v>12.561842918396</v>
       </c>
       <c r="C421" t="n">
-        <v>12.75230347837524</v>
+        <v>12.75230444650908</v>
       </c>
       <c r="D421" t="n">
-        <v>12.56184196472168</v>
+        <v>12.561842918396</v>
       </c>
       <c r="E421" t="n">
-        <v>12.72633160390085</v>
+        <v>12.72633257006295</v>
       </c>
       <c r="F421" t="n">
         <v>5869600</v>
@@ -8872,16 +8872,16 @@
         <v>45261</v>
       </c>
       <c r="B423" t="n">
-        <v>12.86484909057617</v>
+        <v>12.86485004425049</v>
       </c>
       <c r="C423" t="n">
-        <v>12.96873741185957</v>
+        <v>12.96873837323515</v>
       </c>
       <c r="D423" t="n">
-        <v>12.70901702146657</v>
+        <v>12.70901796358902</v>
       </c>
       <c r="E423" t="n">
-        <v>12.72633132886498</v>
+        <v>12.72633227227094</v>
       </c>
       <c r="F423" t="n">
         <v>6458300</v>
@@ -22272,19 +22272,39 @@
         <v>46244</v>
       </c>
       <c r="B1093" t="n">
-        <v>10.7</v>
+        <v>10.69999980926514</v>
       </c>
       <c r="C1093" t="n">
-        <v>10.83</v>
+        <v>10.82999992370605</v>
       </c>
       <c r="D1093" t="n">
-        <v>10.56</v>
+        <v>10.5600004196167</v>
       </c>
       <c r="E1093" t="n">
-        <v>10.8</v>
+        <v>10.80000019073486</v>
       </c>
       <c r="F1093" t="n">
         <v>3624700</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B1094" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="C1094" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="D1094" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E1094" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>3147300</v>
       </c>
     </row>
   </sheetData>

--- a/database/AURE3.xlsx
+++ b/database/AURE3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1094"/>
+  <dimension ref="A1:F1093"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>44649</v>
       </c>
       <c r="B3" t="n">
-        <v>12.91280937194824</v>
+        <v>12.91281032562256</v>
       </c>
       <c r="C3" t="n">
-        <v>13.2161821224289</v>
+        <v>13.21618309850878</v>
       </c>
       <c r="D3" t="n">
-        <v>12.61721411646944</v>
+        <v>12.6172150483126</v>
       </c>
       <c r="E3" t="n">
-        <v>12.74945378682817</v>
+        <v>12.74945472843788</v>
       </c>
       <c r="F3" t="n">
         <v>4714100</v>
@@ -492,16 +492,16 @@
         <v>44650</v>
       </c>
       <c r="B4" t="n">
-        <v>12.38385009765625</v>
+        <v>12.38385105133057</v>
       </c>
       <c r="C4" t="n">
-        <v>13.04504841779609</v>
+        <v>13.04504942238897</v>
       </c>
       <c r="D4" t="n">
-        <v>12.30606179816537</v>
+        <v>12.30606274584925</v>
       </c>
       <c r="E4" t="n">
-        <v>12.92836671040398</v>
+        <v>12.92836770601126</v>
       </c>
       <c r="F4" t="n">
         <v>4408600</v>
@@ -512,16 +512,16 @@
         <v>44651</v>
       </c>
       <c r="B5" t="n">
-        <v>12.4383020401001</v>
+        <v>12.43830108642578</v>
       </c>
       <c r="C5" t="n">
-        <v>12.82724207193696</v>
+        <v>12.82724108844168</v>
       </c>
       <c r="D5" t="n">
-        <v>12.05714098694259</v>
+        <v>12.05714006249281</v>
       </c>
       <c r="E5" t="n">
-        <v>12.41496584590627</v>
+        <v>12.4149648940212</v>
       </c>
       <c r="F5" t="n">
         <v>3876100</v>
@@ -532,16 +532,16 @@
         <v>44652</v>
       </c>
       <c r="B6" t="n">
-        <v>12.51609039306641</v>
+        <v>12.51609134674072</v>
       </c>
       <c r="C6" t="n">
-        <v>12.95170281502629</v>
+        <v>12.95170380189247</v>
       </c>
       <c r="D6" t="n">
-        <v>12.31384139766291</v>
+        <v>12.31384233592669</v>
       </c>
       <c r="E6" t="n">
-        <v>12.43830208965145</v>
+        <v>12.43830303739862</v>
       </c>
       <c r="F6" t="n">
         <v>4252000</v>
@@ -552,16 +552,16 @@
         <v>44655</v>
       </c>
       <c r="B7" t="n">
-        <v>12.42274475097656</v>
+        <v>12.42274379730225</v>
       </c>
       <c r="C7" t="n">
-        <v>12.7338972197089</v>
+        <v>12.73389624214791</v>
       </c>
       <c r="D7" t="n">
-        <v>12.33717746969916</v>
+        <v>12.3371765225937</v>
       </c>
       <c r="E7" t="n">
-        <v>12.54720469988757</v>
+        <v>12.54720373665866</v>
       </c>
       <c r="F7" t="n">
         <v>2842400</v>
@@ -572,16 +572,16 @@
         <v>44656</v>
       </c>
       <c r="B8" t="n">
-        <v>12.15826606750488</v>
+        <v>12.15826511383057</v>
       </c>
       <c r="C8" t="n">
-        <v>12.50053298552928</v>
+        <v>12.50053200500811</v>
       </c>
       <c r="D8" t="n">
-        <v>12.05714156535479</v>
+        <v>12.05714061961251</v>
       </c>
       <c r="E8" t="n">
-        <v>12.37607228806586</v>
+        <v>12.37607131730719</v>
       </c>
       <c r="F8" t="n">
         <v>3624900</v>
@@ -612,16 +612,16 @@
         <v>44658</v>
       </c>
       <c r="B10" t="n">
-        <v>12.44608116149902</v>
+        <v>12.44608020782471</v>
       </c>
       <c r="C10" t="n">
-        <v>12.71833948364451</v>
+        <v>12.71833850910855</v>
       </c>
       <c r="D10" t="n">
-        <v>12.20493801258351</v>
+        <v>12.20493707738666</v>
       </c>
       <c r="E10" t="n">
-        <v>12.32162046857911</v>
+        <v>12.32161952444153</v>
       </c>
       <c r="F10" t="n">
         <v>3223900</v>
@@ -632,16 +632,16 @@
         <v>44659</v>
       </c>
       <c r="B11" t="n">
-        <v>12.60943508148193</v>
+        <v>12.60943603515625</v>
       </c>
       <c r="C11" t="n">
-        <v>12.75723270856147</v>
+        <v>12.75723367341398</v>
       </c>
       <c r="D11" t="n">
-        <v>12.33717750513392</v>
+        <v>12.3371784382169</v>
       </c>
       <c r="E11" t="n">
-        <v>12.33717750513392</v>
+        <v>12.3371784382169</v>
       </c>
       <c r="F11" t="n">
         <v>2049800</v>
@@ -652,16 +652,16 @@
         <v>44662</v>
       </c>
       <c r="B12" t="n">
-        <v>12.37607192993164</v>
+        <v>12.37607097625732</v>
       </c>
       <c r="C12" t="n">
-        <v>12.8972516418612</v>
+        <v>12.89725064802586</v>
       </c>
       <c r="D12" t="n">
-        <v>12.37607192993164</v>
+        <v>12.37607097625732</v>
       </c>
       <c r="E12" t="n">
-        <v>12.59387888603408</v>
+        <v>12.59387791557601</v>
       </c>
       <c r="F12" t="n">
         <v>2119500</v>
@@ -672,16 +672,16 @@
         <v>44663</v>
       </c>
       <c r="B13" t="n">
-        <v>12.2438325881958</v>
+        <v>12.24383163452148</v>
       </c>
       <c r="C13" t="n">
-        <v>12.64055161698694</v>
+        <v>12.64055063241211</v>
       </c>
       <c r="D13" t="n">
-        <v>12.2127174138893</v>
+        <v>12.21271646263855</v>
       </c>
       <c r="E13" t="n">
-        <v>12.48497500361014</v>
+        <v>12.4849740311532</v>
       </c>
       <c r="F13" t="n">
         <v>2267700</v>
@@ -692,16 +692,16 @@
         <v>44664</v>
       </c>
       <c r="B14" t="n">
-        <v>12.10381317138672</v>
+        <v>12.10381412506104</v>
       </c>
       <c r="C14" t="n">
-        <v>12.55498277187146</v>
+        <v>12.55498376109398</v>
       </c>
       <c r="D14" t="n">
-        <v>12.0882552152437</v>
+        <v>12.08825616769219</v>
       </c>
       <c r="E14" t="n">
-        <v>12.39162868343488</v>
+        <v>12.39162965978653</v>
       </c>
       <c r="F14" t="n">
         <v>4421300</v>
@@ -712,16 +712,16 @@
         <v>44665</v>
       </c>
       <c r="B15" t="n">
-        <v>12.11159133911133</v>
+        <v>12.11159229278564</v>
       </c>
       <c r="C15" t="n">
-        <v>12.36829167926575</v>
+        <v>12.36829265315281</v>
       </c>
       <c r="D15" t="n">
-        <v>12.0493609985796</v>
+        <v>12.04936194735386</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08047616884546</v>
+        <v>12.08047712006975</v>
       </c>
       <c r="F15" t="n">
         <v>2077400</v>
@@ -732,16 +732,16 @@
         <v>44669</v>
       </c>
       <c r="B16" t="n">
-        <v>12.45386028289795</v>
+        <v>12.45385932922363</v>
       </c>
       <c r="C16" t="n">
-        <v>12.45386028289795</v>
+        <v>12.45385932922363</v>
       </c>
       <c r="D16" t="n">
-        <v>11.92490159008608</v>
+        <v>11.92490067691762</v>
       </c>
       <c r="E16" t="n">
-        <v>12.10381439459067</v>
+        <v>12.10381346772168</v>
       </c>
       <c r="F16" t="n">
         <v>3931100</v>
@@ -752,16 +752,16 @@
         <v>44670</v>
       </c>
       <c r="B17" t="n">
-        <v>12.10381317138672</v>
+        <v>12.10381412506104</v>
       </c>
       <c r="C17" t="n">
-        <v>12.60165664030051</v>
+        <v>12.60165763320052</v>
       </c>
       <c r="D17" t="n">
-        <v>12.00268868198966</v>
+        <v>12.00268962769625</v>
       </c>
       <c r="E17" t="n">
-        <v>12.43830106817557</v>
+        <v>12.4383020482046</v>
       </c>
       <c r="F17" t="n">
         <v>3118100</v>
@@ -772,16 +772,16 @@
         <v>44671</v>
       </c>
       <c r="B18" t="n">
-        <v>12.0571403503418</v>
+        <v>12.05714130401611</v>
       </c>
       <c r="C18" t="n">
-        <v>12.2127162064935</v>
+        <v>12.21271717247328</v>
       </c>
       <c r="D18" t="n">
-        <v>11.95601585838214</v>
+        <v>11.95601680405789</v>
       </c>
       <c r="E18" t="n">
-        <v>12.07269830687907</v>
+        <v>12.07269926178396</v>
       </c>
       <c r="F18" t="n">
         <v>2798400</v>
@@ -792,16 +792,16 @@
         <v>44673</v>
       </c>
       <c r="B19" t="n">
-        <v>12.22049617767334</v>
+        <v>12.22049522399902</v>
       </c>
       <c r="C19" t="n">
-        <v>12.33717789380641</v>
+        <v>12.33717693102638</v>
       </c>
       <c r="D19" t="n">
-        <v>11.80044096101231</v>
+        <v>11.80044004011864</v>
       </c>
       <c r="E19" t="n">
-        <v>12.01824717732137</v>
+        <v>12.01824623943035</v>
       </c>
       <c r="F19" t="n">
         <v>11382300</v>
@@ -812,16 +812,16 @@
         <v>44676</v>
       </c>
       <c r="B20" t="n">
-        <v>12.39163017272949</v>
+        <v>12.39162921905518</v>
       </c>
       <c r="C20" t="n">
-        <v>12.39163017272949</v>
+        <v>12.39162921905518</v>
       </c>
       <c r="D20" t="n">
-        <v>11.90156562298855</v>
+        <v>11.90156470703017</v>
       </c>
       <c r="E20" t="n">
-        <v>12.11937184225865</v>
+        <v>12.11937090953766</v>
       </c>
       <c r="F20" t="n">
         <v>2683100</v>
@@ -832,16 +832,16 @@
         <v>44677</v>
       </c>
       <c r="B21" t="n">
-        <v>11.95601654052734</v>
+        <v>11.95601558685303</v>
       </c>
       <c r="C21" t="n">
-        <v>12.4383020930363</v>
+        <v>12.43830110089237</v>
       </c>
       <c r="D21" t="n">
-        <v>11.86267102151054</v>
+        <v>11.86267007528195</v>
       </c>
       <c r="E21" t="n">
-        <v>12.32939935843881</v>
+        <v>12.32939837498153</v>
       </c>
       <c r="F21" t="n">
         <v>2627000</v>
@@ -852,16 +852,16 @@
         <v>44678</v>
       </c>
       <c r="B22" t="n">
-        <v>12.0571403503418</v>
+        <v>12.05714130401611</v>
       </c>
       <c r="C22" t="n">
-        <v>12.06491932861043</v>
+        <v>12.06492028290003</v>
       </c>
       <c r="D22" t="n">
-        <v>11.83155517346078</v>
+        <v>11.83155610929216</v>
       </c>
       <c r="E22" t="n">
-        <v>12.04936137207316</v>
+        <v>12.04936232513219</v>
       </c>
       <c r="F22" t="n">
         <v>2401400</v>
@@ -872,16 +872,16 @@
         <v>44679</v>
       </c>
       <c r="B23" t="n">
-        <v>11.90934371948242</v>
+        <v>11.90934467315674</v>
       </c>
       <c r="C23" t="n">
-        <v>12.08825577230682</v>
+        <v>12.08825674030803</v>
       </c>
       <c r="D23" t="n">
-        <v>11.49706676482372</v>
+        <v>11.49706768548379</v>
       </c>
       <c r="E23" t="n">
-        <v>12.08825577230682</v>
+        <v>12.08825674030803</v>
       </c>
       <c r="F23" t="n">
         <v>3489600</v>
@@ -912,16 +912,16 @@
         <v>44683</v>
       </c>
       <c r="B25" t="n">
-        <v>11.17035675048828</v>
+        <v>11.1703577041626</v>
       </c>
       <c r="C25" t="n">
-        <v>11.47373022346064</v>
+        <v>11.47373120303561</v>
       </c>
       <c r="D25" t="n">
-        <v>10.96032953215679</v>
+        <v>10.96033046789994</v>
       </c>
       <c r="E25" t="n">
-        <v>11.4270570961402</v>
+        <v>11.42705807173043</v>
       </c>
       <c r="F25" t="n">
         <v>2883200</v>
@@ -972,16 +972,16 @@
         <v>44686</v>
       </c>
       <c r="B28" t="n">
-        <v>11.28714752197266</v>
+        <v>11.28714847564697</v>
       </c>
       <c r="C28" t="n">
-        <v>11.62396063303483</v>
+        <v>11.62396161516718</v>
       </c>
       <c r="D28" t="n">
-        <v>11.14615584813277</v>
+        <v>11.14615678989441</v>
       </c>
       <c r="E28" t="n">
-        <v>11.61612759626606</v>
+        <v>11.61612857773658</v>
       </c>
       <c r="F28" t="n">
         <v>3065700</v>
@@ -1072,16 +1072,16 @@
         <v>44693</v>
       </c>
       <c r="B33" t="n">
-        <v>11.1539888381958</v>
+        <v>11.15398979187012</v>
       </c>
       <c r="C33" t="n">
-        <v>11.27931443797336</v>
+        <v>11.27931540236311</v>
       </c>
       <c r="D33" t="n">
-        <v>10.85634016522435</v>
+        <v>10.85634109344948</v>
       </c>
       <c r="E33" t="n">
-        <v>10.99733183847385</v>
+        <v>10.99733277875388</v>
       </c>
       <c r="F33" t="n">
         <v>1884700</v>
@@ -1132,16 +1132,16 @@
         <v>44698</v>
       </c>
       <c r="B36" t="n">
-        <v>11.56129741668701</v>
+        <v>11.56129837036133</v>
       </c>
       <c r="C36" t="n">
-        <v>11.74928581037311</v>
+        <v>11.74928677955431</v>
       </c>
       <c r="D36" t="n">
-        <v>11.35764295002734</v>
+        <v>11.3576438869025</v>
       </c>
       <c r="E36" t="n">
-        <v>11.35764295002734</v>
+        <v>11.3576438869025</v>
       </c>
       <c r="F36" t="n">
         <v>1389700</v>
@@ -1152,16 +1152,16 @@
         <v>44699</v>
       </c>
       <c r="B37" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C37" t="n">
-        <v>11.59262882548476</v>
+        <v>11.5926298208571</v>
       </c>
       <c r="D37" t="n">
-        <v>11.03649593344125</v>
+        <v>11.03649688106261</v>
       </c>
       <c r="E37" t="n">
-        <v>11.51429995454926</v>
+        <v>11.51430094319608</v>
       </c>
       <c r="F37" t="n">
         <v>1959900</v>
@@ -1172,16 +1172,16 @@
         <v>44700</v>
       </c>
       <c r="B38" t="n">
-        <v>11.22448539733887</v>
+        <v>11.22448444366455</v>
       </c>
       <c r="C38" t="n">
-        <v>11.25581679930005</v>
+        <v>11.25581584296371</v>
       </c>
       <c r="D38" t="n">
-        <v>10.97383418164937</v>
+        <v>10.97383324927132</v>
       </c>
       <c r="E38" t="n">
-        <v>11.11482511697494</v>
+        <v>11.11482417261777</v>
       </c>
       <c r="F38" t="n">
         <v>2127500</v>
@@ -1192,16 +1192,16 @@
         <v>44701</v>
       </c>
       <c r="B39" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C39" t="n">
-        <v>11.34197688669085</v>
+        <v>11.34197786054158</v>
       </c>
       <c r="D39" t="n">
-        <v>10.86417286558284</v>
+        <v>10.86417379840811</v>
       </c>
       <c r="E39" t="n">
-        <v>11.34197688669085</v>
+        <v>11.34197786054158</v>
       </c>
       <c r="F39" t="n">
         <v>1777400</v>
@@ -1232,16 +1232,16 @@
         <v>44705</v>
       </c>
       <c r="B41" t="n">
-        <v>11.21665191650391</v>
+        <v>11.21665096282959</v>
       </c>
       <c r="C41" t="n">
-        <v>11.22448495343431</v>
+        <v>11.22448399909401</v>
       </c>
       <c r="D41" t="n">
-        <v>11.00516514837963</v>
+        <v>11.00516421268657</v>
       </c>
       <c r="E41" t="n">
-        <v>11.09132631361552</v>
+        <v>11.09132537059677</v>
       </c>
       <c r="F41" t="n">
         <v>792900</v>
@@ -1292,16 +1292,16 @@
         <v>44708</v>
       </c>
       <c r="B44" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C44" t="n">
-        <v>11.42030600182509</v>
+        <v>11.42030698171035</v>
       </c>
       <c r="D44" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="E44" t="n">
-        <v>11.26364900360379</v>
+        <v>11.26364997004757</v>
       </c>
       <c r="F44" t="n">
         <v>2224600</v>
@@ -1352,16 +1352,16 @@
         <v>44713</v>
       </c>
       <c r="B47" t="n">
-        <v>10.73101425170898</v>
+        <v>10.7310152053833</v>
       </c>
       <c r="C47" t="n">
-        <v>10.94250175540008</v>
+        <v>10.94250272786947</v>
       </c>
       <c r="D47" t="n">
-        <v>10.66051841714529</v>
+        <v>10.66051936455458</v>
       </c>
       <c r="E47" t="n">
-        <v>10.94250175540008</v>
+        <v>10.94250272786947</v>
       </c>
       <c r="F47" t="n">
         <v>6323900</v>
@@ -1372,16 +1372,16 @@
         <v>44714</v>
       </c>
       <c r="B48" t="n">
-        <v>10.86417293548584</v>
+        <v>10.86417388916016</v>
       </c>
       <c r="C48" t="n">
-        <v>10.98949853218943</v>
+        <v>10.98949949686503</v>
       </c>
       <c r="D48" t="n">
-        <v>10.68401757697429</v>
+        <v>10.68401851483428</v>
       </c>
       <c r="E48" t="n">
-        <v>10.75451266487045</v>
+        <v>10.75451360891862</v>
       </c>
       <c r="F48" t="n">
         <v>3275400</v>
@@ -1412,16 +1412,16 @@
         <v>44718</v>
       </c>
       <c r="B50" t="n">
-        <v>10.61352252960205</v>
+        <v>10.61352157592773</v>
       </c>
       <c r="C50" t="n">
-        <v>10.91117121735836</v>
+        <v>10.91117023693893</v>
       </c>
       <c r="D50" t="n">
-        <v>10.4568655220986</v>
+        <v>10.45686458250065</v>
       </c>
       <c r="E50" t="n">
-        <v>10.8171770128563</v>
+        <v>10.81717604088268</v>
       </c>
       <c r="F50" t="n">
         <v>3175000</v>
@@ -1532,16 +1532,16 @@
         <v>44726</v>
       </c>
       <c r="B56" t="n">
-        <v>10.39420223236084</v>
+        <v>10.39420127868652</v>
       </c>
       <c r="C56" t="n">
-        <v>10.47253035894487</v>
+        <v>10.4725293980839</v>
       </c>
       <c r="D56" t="n">
-        <v>10.01822468495919</v>
+        <v>10.01822376578104</v>
       </c>
       <c r="E56" t="n">
-        <v>10.01822468495919</v>
+        <v>10.01822376578104</v>
       </c>
       <c r="F56" t="n">
         <v>4085600</v>
@@ -1552,16 +1552,16 @@
         <v>44727</v>
       </c>
       <c r="B57" t="n">
-        <v>10.84067440032959</v>
+        <v>10.84067535400391</v>
       </c>
       <c r="C57" t="n">
-        <v>10.84850743674878</v>
+        <v>10.84850839111218</v>
       </c>
       <c r="D57" t="n">
-        <v>10.44119850694474</v>
+        <v>10.44119942547642</v>
       </c>
       <c r="E57" t="n">
-        <v>10.55085877581493</v>
+        <v>10.55085970399363</v>
       </c>
       <c r="F57" t="n">
         <v>3153700</v>
@@ -1632,16 +1632,16 @@
         <v>44734</v>
       </c>
       <c r="B61" t="n">
-        <v>10.73884868621826</v>
+        <v>10.73884773254395</v>
       </c>
       <c r="C61" t="n">
-        <v>10.8328428955397</v>
+        <v>10.83284193351813</v>
       </c>
       <c r="D61" t="n">
-        <v>10.43336694567391</v>
+        <v>10.43336601912821</v>
       </c>
       <c r="E61" t="n">
-        <v>10.53519419252203</v>
+        <v>10.53519325693346</v>
       </c>
       <c r="F61" t="n">
         <v>1196200</v>
@@ -1672,16 +1672,16 @@
         <v>44736</v>
       </c>
       <c r="B63" t="n">
-        <v>10.48819637298584</v>
+        <v>10.48819732666016</v>
       </c>
       <c r="C63" t="n">
-        <v>10.70751617197673</v>
+        <v>10.70751714559343</v>
       </c>
       <c r="D63" t="n">
-        <v>10.42553357327416</v>
+        <v>10.42553452125065</v>
       </c>
       <c r="E63" t="n">
-        <v>10.70751617197673</v>
+        <v>10.70751714559343</v>
       </c>
       <c r="F63" t="n">
         <v>807500</v>
@@ -1712,16 +1712,16 @@
         <v>44740</v>
       </c>
       <c r="B65" t="n">
-        <v>10.61352252960205</v>
+        <v>10.61352157592773</v>
       </c>
       <c r="C65" t="n">
-        <v>10.86417374160756</v>
+        <v>10.86417276541107</v>
       </c>
       <c r="D65" t="n">
-        <v>10.47253084934918</v>
+        <v>10.47252990834362</v>
       </c>
       <c r="E65" t="n">
-        <v>10.5273606152255</v>
+        <v>10.52735966929324</v>
       </c>
       <c r="F65" t="n">
         <v>5362200</v>
@@ -1852,16 +1852,16 @@
         <v>44749</v>
       </c>
       <c r="B72" t="n">
-        <v>11.04432964324951</v>
+        <v>11.04433059692383</v>
       </c>
       <c r="C72" t="n">
-        <v>11.16182220981619</v>
+        <v>11.16182317363595</v>
       </c>
       <c r="D72" t="n">
-        <v>10.62135535781014</v>
+        <v>10.62135627496076</v>
       </c>
       <c r="E72" t="n">
-        <v>10.7858453992032</v>
+        <v>10.78584633055749</v>
       </c>
       <c r="F72" t="n">
         <v>2931100</v>
@@ -1872,16 +1872,16 @@
         <v>44750</v>
       </c>
       <c r="B73" t="n">
-        <v>11.1539888381958</v>
+        <v>11.15398979187012</v>
       </c>
       <c r="C73" t="n">
-        <v>11.31064583791775</v>
+        <v>11.31064680498636</v>
       </c>
       <c r="D73" t="n">
-        <v>11.00516487520982</v>
+        <v>11.00516581615958</v>
       </c>
       <c r="E73" t="n">
-        <v>11.00516487520982</v>
+        <v>11.00516581615958</v>
       </c>
       <c r="F73" t="n">
         <v>1922000</v>
@@ -1892,16 +1892,16 @@
         <v>44753</v>
       </c>
       <c r="B74" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C74" t="n">
-        <v>11.18531989181933</v>
+        <v>11.18532085221909</v>
       </c>
       <c r="D74" t="n">
-        <v>10.83284146660853</v>
+        <v>10.83284239674361</v>
       </c>
       <c r="E74" t="n">
-        <v>11.05999429592211</v>
+        <v>11.0599952455611</v>
       </c>
       <c r="F74" t="n">
         <v>1881000</v>
@@ -1912,16 +1912,16 @@
         <v>44754</v>
       </c>
       <c r="B75" t="n">
-        <v>11.14615726470947</v>
+        <v>11.14615535736084</v>
       </c>
       <c r="C75" t="n">
-        <v>11.22448614835309</v>
+        <v>11.22448422760069</v>
       </c>
       <c r="D75" t="n">
-        <v>10.99733328218612</v>
+        <v>10.99733140030449</v>
       </c>
       <c r="E75" t="n">
-        <v>11.10699356988726</v>
+        <v>11.10699166924038</v>
       </c>
       <c r="F75" t="n">
         <v>1673000</v>
@@ -1932,16 +1932,16 @@
         <v>44755</v>
       </c>
       <c r="B76" t="n">
-        <v>11.17748737335205</v>
+        <v>11.17748832702637</v>
       </c>
       <c r="C76" t="n">
-        <v>11.23231713368402</v>
+        <v>11.23231809203646</v>
       </c>
       <c r="D76" t="n">
-        <v>11.0129973453567</v>
+        <v>11.01299828499656</v>
       </c>
       <c r="E76" t="n">
-        <v>11.18531966268557</v>
+        <v>11.18532061702815</v>
       </c>
       <c r="F76" t="n">
         <v>2559400</v>
@@ -1952,16 +1952,16 @@
         <v>44756</v>
       </c>
       <c r="B77" t="n">
-        <v>10.91117095947266</v>
+        <v>10.91117191314697</v>
       </c>
       <c r="C77" t="n">
-        <v>11.17748823943387</v>
+        <v>11.17748921638524</v>
       </c>
       <c r="D77" t="n">
-        <v>10.84850815795232</v>
+        <v>10.84850910614968</v>
       </c>
       <c r="E77" t="n">
-        <v>11.04432959945326</v>
+        <v>11.04433056476611</v>
       </c>
       <c r="F77" t="n">
         <v>1968500</v>
@@ -1972,16 +1972,16 @@
         <v>44757</v>
       </c>
       <c r="B78" t="n">
-        <v>10.80934429168701</v>
+        <v>10.8093433380127</v>
       </c>
       <c r="C78" t="n">
-        <v>10.98166737847755</v>
+        <v>10.98166640959971</v>
       </c>
       <c r="D78" t="n">
-        <v>10.60568980247997</v>
+        <v>10.60568886677345</v>
       </c>
       <c r="E78" t="n">
-        <v>10.97383434112354</v>
+        <v>10.97383337293678</v>
       </c>
       <c r="F78" t="n">
         <v>2342600</v>
@@ -1992,16 +1992,16 @@
         <v>44760</v>
       </c>
       <c r="B79" t="n">
-        <v>10.73101425170898</v>
+        <v>10.7310152053833</v>
       </c>
       <c r="C79" t="n">
-        <v>11.00516455345681</v>
+        <v>11.0051655314951</v>
       </c>
       <c r="D79" t="n">
-        <v>10.59002332958107</v>
+        <v>10.5900242707254</v>
       </c>
       <c r="E79" t="n">
-        <v>10.80934312277964</v>
+        <v>10.80934408341511</v>
       </c>
       <c r="F79" t="n">
         <v>1463400</v>
@@ -2012,16 +2012,16 @@
         <v>44761</v>
       </c>
       <c r="B80" t="n">
-        <v>11.0913257598877</v>
+        <v>11.09132671356201</v>
       </c>
       <c r="C80" t="n">
-        <v>11.0913257598877</v>
+        <v>11.09132671356201</v>
       </c>
       <c r="D80" t="n">
-        <v>10.78584480484809</v>
+        <v>10.78584573225599</v>
       </c>
       <c r="E80" t="n">
-        <v>10.87200596578243</v>
+        <v>10.87200690059879</v>
       </c>
       <c r="F80" t="n">
         <v>2890800</v>
@@ -2052,16 +2052,16 @@
         <v>44763</v>
       </c>
       <c r="B82" t="n">
-        <v>11.24798202514648</v>
+        <v>11.24798393249512</v>
       </c>
       <c r="C82" t="n">
-        <v>11.27931342226948</v>
+        <v>11.27931533493105</v>
       </c>
       <c r="D82" t="n">
-        <v>11.05999364240853</v>
+        <v>11.0599955178795</v>
       </c>
       <c r="E82" t="n">
-        <v>11.2244836640541</v>
+        <v>11.22448556741805</v>
       </c>
       <c r="F82" t="n">
         <v>1092700</v>
@@ -2132,16 +2132,16 @@
         <v>44769</v>
       </c>
       <c r="B86" t="n">
-        <v>11.24015140533447</v>
+        <v>11.24015045166016</v>
       </c>
       <c r="C86" t="n">
-        <v>11.49080261954139</v>
+        <v>11.49080164460048</v>
       </c>
       <c r="D86" t="n">
-        <v>11.15398949020119</v>
+        <v>11.15398854383731</v>
       </c>
       <c r="E86" t="n">
-        <v>11.2871481344985</v>
+        <v>11.28714717683673</v>
       </c>
       <c r="F86" t="n">
         <v>3096400</v>
@@ -2152,16 +2152,16 @@
         <v>44770</v>
       </c>
       <c r="B87" t="n">
-        <v>10.9660005569458</v>
+        <v>10.96599960327148</v>
       </c>
       <c r="C87" t="n">
-        <v>11.33414507051741</v>
+        <v>11.33414408482687</v>
       </c>
       <c r="D87" t="n">
-        <v>10.8250088821738</v>
+        <v>10.82500794076103</v>
       </c>
       <c r="E87" t="n">
-        <v>11.31064596005574</v>
+        <v>11.31064497640883</v>
       </c>
       <c r="F87" t="n">
         <v>2911900</v>
@@ -2172,16 +2172,16 @@
         <v>44771</v>
       </c>
       <c r="B88" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C88" t="n">
-        <v>11.33414483955325</v>
+        <v>11.33414581204571</v>
       </c>
       <c r="D88" t="n">
-        <v>10.51952770180302</v>
+        <v>10.51952860439969</v>
       </c>
       <c r="E88" t="n">
-        <v>10.96600033348359</v>
+        <v>10.96600127438851</v>
       </c>
       <c r="F88" t="n">
         <v>13059200</v>
@@ -2212,16 +2212,16 @@
         <v>44775</v>
       </c>
       <c r="B90" t="n">
-        <v>10.86417293548584</v>
+        <v>10.86417388916016</v>
       </c>
       <c r="C90" t="n">
-        <v>11.06782740362892</v>
+        <v>11.06782837518035</v>
       </c>
       <c r="D90" t="n">
-        <v>10.72318126569455</v>
+        <v>10.7231822069924</v>
       </c>
       <c r="E90" t="n">
-        <v>10.93466877038148</v>
+        <v>10.93466973024404</v>
       </c>
       <c r="F90" t="n">
         <v>2371400</v>
@@ -2232,16 +2232,16 @@
         <v>44776</v>
       </c>
       <c r="B91" t="n">
-        <v>10.88767147064209</v>
+        <v>10.88767242431641</v>
       </c>
       <c r="C91" t="n">
-        <v>11.02083010599954</v>
+        <v>11.02083107133751</v>
       </c>
       <c r="D91" t="n">
-        <v>10.70751610927583</v>
+        <v>10.70751704716995</v>
       </c>
       <c r="E91" t="n">
-        <v>10.83284170796531</v>
+        <v>10.83284265683698</v>
       </c>
       <c r="F91" t="n">
         <v>3133200</v>
@@ -2272,16 +2272,16 @@
         <v>44778</v>
       </c>
       <c r="B93" t="n">
-        <v>10.9660005569458</v>
+        <v>10.96599960327148</v>
       </c>
       <c r="C93" t="n">
-        <v>11.16965503228325</v>
+        <v>11.16965406089782</v>
       </c>
       <c r="D93" t="n">
-        <v>10.93466915666308</v>
+        <v>10.93466820571354</v>
       </c>
       <c r="E93" t="n">
-        <v>11.16965503228325</v>
+        <v>11.16965406089782</v>
       </c>
       <c r="F93" t="n">
         <v>1948700</v>
@@ -2292,16 +2292,16 @@
         <v>44781</v>
       </c>
       <c r="B94" t="n">
-        <v>10.97383403778076</v>
+        <v>10.97383308410645</v>
       </c>
       <c r="C94" t="n">
-        <v>11.10699268111997</v>
+        <v>11.10699171587358</v>
       </c>
       <c r="D94" t="n">
-        <v>10.87200679599199</v>
+        <v>10.8720058511669</v>
       </c>
       <c r="E94" t="n">
-        <v>11.02866380374413</v>
+        <v>11.02866284530486</v>
       </c>
       <c r="F94" t="n">
         <v>2949000</v>
@@ -2312,16 +2312,16 @@
         <v>44782</v>
       </c>
       <c r="B95" t="n">
-        <v>10.92683696746826</v>
+        <v>10.92683601379395</v>
       </c>
       <c r="C95" t="n">
-        <v>11.0599956157492</v>
+        <v>11.05999465045304</v>
       </c>
       <c r="D95" t="n">
-        <v>10.67618574576276</v>
+        <v>10.67618481396482</v>
       </c>
       <c r="E95" t="n">
-        <v>10.98166748246601</v>
+        <v>10.98166652400619</v>
       </c>
       <c r="F95" t="n">
         <v>1743500</v>
@@ -2392,16 +2392,16 @@
         <v>44788</v>
       </c>
       <c r="B99" t="n">
-        <v>11.21665191650391</v>
+        <v>11.21665096282959</v>
       </c>
       <c r="C99" t="n">
-        <v>11.3106461186702</v>
+        <v>11.3106451570042</v>
       </c>
       <c r="D99" t="n">
-        <v>10.92683627307463</v>
+        <v>10.92683534404133</v>
       </c>
       <c r="E99" t="n">
-        <v>10.99733211144923</v>
+        <v>10.99733117642216</v>
       </c>
       <c r="F99" t="n">
         <v>3450900</v>
@@ -2412,16 +2412,16 @@
         <v>44789</v>
       </c>
       <c r="B100" t="n">
-        <v>11.04432964324951</v>
+        <v>11.04433059692383</v>
       </c>
       <c r="C100" t="n">
-        <v>11.29498085032484</v>
+        <v>11.2949818256428</v>
       </c>
       <c r="D100" t="n">
-        <v>10.94250240362528</v>
+        <v>10.94250334850685</v>
       </c>
       <c r="E100" t="n">
-        <v>11.25581641246944</v>
+        <v>11.25581738440557</v>
       </c>
       <c r="F100" t="n">
         <v>1185300</v>
@@ -2432,16 +2432,16 @@
         <v>44790</v>
       </c>
       <c r="B101" t="n">
-        <v>11.24015140533447</v>
+        <v>11.24015045166016</v>
       </c>
       <c r="C101" t="n">
-        <v>11.25581673272263</v>
+        <v>11.25581577771919</v>
       </c>
       <c r="D101" t="n">
-        <v>10.91117131318813</v>
+        <v>10.91117038742624</v>
       </c>
       <c r="E101" t="n">
-        <v>10.98949944412802</v>
+        <v>10.98949851172035</v>
       </c>
       <c r="F101" t="n">
         <v>4396400</v>
@@ -2472,16 +2472,16 @@
         <v>44792</v>
       </c>
       <c r="B103" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C103" t="n">
-        <v>11.16182176801008</v>
+        <v>11.16182272571687</v>
       </c>
       <c r="D103" t="n">
-        <v>10.98166640680546</v>
+        <v>10.98166734905456</v>
       </c>
       <c r="E103" t="n">
-        <v>11.16182176801008</v>
+        <v>11.16182272571687</v>
       </c>
       <c r="F103" t="n">
         <v>1667800</v>
@@ -2512,16 +2512,16 @@
         <v>44796</v>
       </c>
       <c r="B105" t="n">
-        <v>11.22448539733887</v>
+        <v>11.22448444366455</v>
       </c>
       <c r="C105" t="n">
-        <v>11.27148287378042</v>
+        <v>11.27148191611302</v>
       </c>
       <c r="D105" t="n">
-        <v>10.98949950913019</v>
+        <v>10.98949857542116</v>
       </c>
       <c r="E105" t="n">
-        <v>10.98949950913019</v>
+        <v>10.98949857542116</v>
       </c>
       <c r="F105" t="n">
         <v>2361000</v>
@@ -2532,16 +2532,16 @@
         <v>44797</v>
       </c>
       <c r="B106" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C106" t="n">
-        <v>11.39680739514549</v>
+        <v>11.3968083737041</v>
       </c>
       <c r="D106" t="n">
-        <v>11.09915873138986</v>
+        <v>11.09915968439161</v>
       </c>
       <c r="E106" t="n">
-        <v>11.22448432728707</v>
+        <v>11.2244852910496</v>
       </c>
       <c r="F106" t="n">
         <v>2116800</v>
@@ -2552,16 +2552,16 @@
         <v>44798</v>
       </c>
       <c r="B107" t="n">
-        <v>11.04432964324951</v>
+        <v>11.04433059692383</v>
       </c>
       <c r="C107" t="n">
-        <v>11.22448501158502</v>
+        <v>11.22448598081569</v>
       </c>
       <c r="D107" t="n">
-        <v>10.95033469359675</v>
+        <v>10.95033563915463</v>
       </c>
       <c r="E107" t="n">
-        <v>11.20881968464257</v>
+        <v>11.20882065252055</v>
       </c>
       <c r="F107" t="n">
         <v>2435800</v>
@@ -2592,16 +2592,16 @@
         <v>44802</v>
       </c>
       <c r="B109" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C109" t="n">
-        <v>11.20881924097621</v>
+        <v>11.20882020271549</v>
       </c>
       <c r="D109" t="n">
-        <v>10.93466893383933</v>
+        <v>10.93466987205595</v>
       </c>
       <c r="E109" t="n">
-        <v>11.02083009611117</v>
+        <v>11.02083104172059</v>
       </c>
       <c r="F109" t="n">
         <v>3615600</v>
@@ -2612,16 +2612,16 @@
         <v>44803</v>
       </c>
       <c r="B110" t="n">
-        <v>11.01299858093262</v>
+        <v>11.0129976272583</v>
       </c>
       <c r="C110" t="n">
-        <v>11.16182255295894</v>
+        <v>11.16182158639716</v>
       </c>
       <c r="D110" t="n">
-        <v>10.93466970281379</v>
+        <v>10.93466875592239</v>
       </c>
       <c r="E110" t="n">
-        <v>11.11482507668773</v>
+        <v>11.11482411419572</v>
       </c>
       <c r="F110" t="n">
         <v>1284900</v>
@@ -2632,16 +2632,16 @@
         <v>44804</v>
       </c>
       <c r="B111" t="n">
-        <v>12.03910255432129</v>
+        <v>12.03910160064697</v>
       </c>
       <c r="C111" t="n">
-        <v>12.07826699338926</v>
+        <v>12.07826603661254</v>
       </c>
       <c r="D111" t="n">
-        <v>10.96600110705643</v>
+        <v>10.96600023838756</v>
       </c>
       <c r="E111" t="n">
-        <v>11.02083087355185</v>
+        <v>11.02083000053966</v>
       </c>
       <c r="F111" t="n">
         <v>16560000</v>
@@ -2652,16 +2652,16 @@
         <v>44805</v>
       </c>
       <c r="B112" t="n">
-        <v>11.65529155731201</v>
+        <v>11.65529251098633</v>
       </c>
       <c r="C112" t="n">
-        <v>12.15659468505643</v>
+        <v>12.15659567974902</v>
       </c>
       <c r="D112" t="n">
-        <v>11.42030569283808</v>
+        <v>11.42030662728508</v>
       </c>
       <c r="E112" t="n">
-        <v>12.14092861215841</v>
+        <v>12.14092960556915</v>
       </c>
       <c r="F112" t="n">
         <v>4716400</v>
@@ -2672,16 +2672,16 @@
         <v>44806</v>
       </c>
       <c r="B113" t="n">
-        <v>11.74145317077637</v>
+        <v>11.74145412445068</v>
       </c>
       <c r="C113" t="n">
-        <v>11.79628368103782</v>
+        <v>11.79628463916563</v>
       </c>
       <c r="D113" t="n">
-        <v>11.56129780748737</v>
+        <v>11.56129874652895</v>
       </c>
       <c r="E113" t="n">
-        <v>11.74145317077637</v>
+        <v>11.74145412445068</v>
       </c>
       <c r="F113" t="n">
         <v>3674700</v>
@@ -2692,16 +2692,16 @@
         <v>44809</v>
       </c>
       <c r="B114" t="n">
-        <v>11.85894775390625</v>
+        <v>11.85894680023193</v>
       </c>
       <c r="C114" t="n">
-        <v>11.92161056064555</v>
+        <v>11.92160960193201</v>
       </c>
       <c r="D114" t="n">
-        <v>11.60829577994947</v>
+        <v>11.60829484643211</v>
       </c>
       <c r="E114" t="n">
-        <v>11.7649535437973</v>
+        <v>11.76495259768182</v>
       </c>
       <c r="F114" t="n">
         <v>1899700</v>
@@ -2712,16 +2712,16 @@
         <v>44810</v>
       </c>
       <c r="B115" t="n">
-        <v>11.58479595184326</v>
+        <v>11.58479690551758</v>
       </c>
       <c r="C115" t="n">
-        <v>11.90594298259424</v>
+        <v>11.90594396270576</v>
       </c>
       <c r="D115" t="n">
-        <v>11.49863479020259</v>
+        <v>11.49863573678402</v>
       </c>
       <c r="E115" t="n">
-        <v>11.89810994599068</v>
+        <v>11.89811092545738</v>
       </c>
       <c r="F115" t="n">
         <v>1316500</v>
@@ -2732,16 +2732,16 @@
         <v>44812</v>
       </c>
       <c r="B116" t="n">
-        <v>11.43597316741943</v>
+        <v>11.43597221374512</v>
       </c>
       <c r="C116" t="n">
-        <v>11.63962691105875</v>
+        <v>11.63962594040124</v>
       </c>
       <c r="D116" t="n">
-        <v>11.37331036214587</v>
+        <v>11.37330941369716</v>
       </c>
       <c r="E116" t="n">
-        <v>11.62396158324014</v>
+        <v>11.623960613889</v>
       </c>
       <c r="F116" t="n">
         <v>2598100</v>
@@ -2752,16 +2752,16 @@
         <v>44813</v>
       </c>
       <c r="B117" t="n">
-        <v>11.31847953796387</v>
+        <v>11.31847858428955</v>
       </c>
       <c r="C117" t="n">
-        <v>11.51430098584213</v>
+        <v>11.51430001566826</v>
       </c>
       <c r="D117" t="n">
-        <v>11.16965556625618</v>
+        <v>11.1696546251215</v>
       </c>
       <c r="E117" t="n">
-        <v>11.51430098584213</v>
+        <v>11.51430001566826</v>
       </c>
       <c r="F117" t="n">
         <v>2426300</v>
@@ -2772,16 +2772,16 @@
         <v>44816</v>
       </c>
       <c r="B118" t="n">
-        <v>11.41247367858887</v>
+        <v>11.41247272491455</v>
       </c>
       <c r="C118" t="n">
-        <v>11.64745956411016</v>
+        <v>11.64745859079944</v>
       </c>
       <c r="D118" t="n">
-        <v>11.35764391253373</v>
+        <v>11.35764296344122</v>
       </c>
       <c r="E118" t="n">
-        <v>11.3968083512872</v>
+        <v>11.39680739892195</v>
       </c>
       <c r="F118" t="n">
         <v>2097200</v>
@@ -2792,16 +2792,16 @@
         <v>44817</v>
       </c>
       <c r="B119" t="n">
-        <v>11.24015140533447</v>
+        <v>11.24015045166016</v>
       </c>
       <c r="C119" t="n">
-        <v>11.43597285318351</v>
+        <v>11.43597188289466</v>
       </c>
       <c r="D119" t="n">
-        <v>11.16965556458889</v>
+        <v>11.16965461689582</v>
       </c>
       <c r="E119" t="n">
-        <v>11.3028142088862</v>
+        <v>11.30281324989524</v>
       </c>
       <c r="F119" t="n">
         <v>1768400</v>
@@ -2832,16 +2832,16 @@
         <v>44819</v>
       </c>
       <c r="B121" t="n">
-        <v>11.22448539733887</v>
+        <v>11.22448444366455</v>
       </c>
       <c r="C121" t="n">
-        <v>11.27148287378042</v>
+        <v>11.27148191611302</v>
       </c>
       <c r="D121" t="n">
-        <v>11.11482511697494</v>
+        <v>11.11482417261777</v>
       </c>
       <c r="E121" t="n">
-        <v>11.16182259341649</v>
+        <v>11.16182164506624</v>
       </c>
       <c r="F121" t="n">
         <v>1523500</v>
@@ -2872,16 +2872,16 @@
         <v>44823</v>
       </c>
       <c r="B123" t="n">
-        <v>11.28714752197266</v>
+        <v>11.28714847564697</v>
       </c>
       <c r="C123" t="n">
-        <v>11.43597223258132</v>
+        <v>11.43597319883014</v>
       </c>
       <c r="D123" t="n">
-        <v>11.11482444805718</v>
+        <v>11.11482538717157</v>
       </c>
       <c r="E123" t="n">
-        <v>11.11482444805718</v>
+        <v>11.11482538717157</v>
       </c>
       <c r="F123" t="n">
         <v>1858600</v>
@@ -2892,16 +2892,16 @@
         <v>44824</v>
       </c>
       <c r="B124" t="n">
-        <v>11.13049030303955</v>
+        <v>11.13049125671387</v>
       </c>
       <c r="C124" t="n">
-        <v>11.35764313587711</v>
+        <v>11.35764410901417</v>
       </c>
       <c r="D124" t="n">
-        <v>11.08349283034925</v>
+        <v>11.08349377999676</v>
       </c>
       <c r="E124" t="n">
-        <v>11.28714730034141</v>
+        <v>11.28714826743829</v>
       </c>
       <c r="F124" t="n">
         <v>1310600</v>
@@ -2912,16 +2912,16 @@
         <v>44825</v>
       </c>
       <c r="B125" t="n">
-        <v>11.0913257598877</v>
+        <v>11.09132671356201</v>
       </c>
       <c r="C125" t="n">
-        <v>11.23231742959796</v>
+        <v>11.23231839539528</v>
       </c>
       <c r="D125" t="n">
-        <v>10.93466876409822</v>
+        <v>10.93466970430257</v>
       </c>
       <c r="E125" t="n">
-        <v>11.13049019558493</v>
+        <v>11.13049115262676</v>
       </c>
       <c r="F125" t="n">
         <v>2825100</v>
@@ -2972,16 +2972,16 @@
         <v>44830</v>
       </c>
       <c r="B128" t="n">
-        <v>11.00516605377197</v>
+        <v>11.00516510009766</v>
       </c>
       <c r="C128" t="n">
-        <v>11.20882054871997</v>
+        <v>11.20881957739757</v>
       </c>
       <c r="D128" t="n">
-        <v>10.88767273114832</v>
+        <v>10.88767178765562</v>
       </c>
       <c r="E128" t="n">
-        <v>11.20098751114514</v>
+        <v>11.20098654050153</v>
       </c>
       <c r="F128" t="n">
         <v>1884300</v>
@@ -2992,16 +2992,16 @@
         <v>44831</v>
       </c>
       <c r="B129" t="n">
-        <v>10.90333843231201</v>
+        <v>10.9033374786377</v>
       </c>
       <c r="C129" t="n">
-        <v>11.04433011582452</v>
+        <v>11.04432914981819</v>
       </c>
       <c r="D129" t="n">
-        <v>10.77017978610565</v>
+        <v>10.77017884407822</v>
       </c>
       <c r="E129" t="n">
-        <v>11.04433011582452</v>
+        <v>11.04432914981819</v>
       </c>
       <c r="F129" t="n">
         <v>2130200</v>
@@ -3012,16 +3012,16 @@
         <v>44832</v>
       </c>
       <c r="B130" t="n">
-        <v>10.74668121337891</v>
+        <v>10.74668025970459</v>
       </c>
       <c r="C130" t="n">
-        <v>11.03649686510639</v>
+        <v>11.03649588571345</v>
       </c>
       <c r="D130" t="n">
-        <v>10.72318210191485</v>
+        <v>10.72318115032588</v>
       </c>
       <c r="E130" t="n">
-        <v>10.95816798755862</v>
+        <v>10.95816701511669</v>
       </c>
       <c r="F130" t="n">
         <v>4249200</v>
@@ -3032,16 +3032,16 @@
         <v>44833</v>
       </c>
       <c r="B131" t="n">
-        <v>10.70751571655273</v>
+        <v>10.70751762390137</v>
       </c>
       <c r="C131" t="n">
-        <v>10.83284131064561</v>
+        <v>10.83284324031871</v>
       </c>
       <c r="D131" t="n">
-        <v>10.6448529195063</v>
+        <v>10.64485481569269</v>
       </c>
       <c r="E131" t="n">
-        <v>10.69184964379139</v>
+        <v>10.6918515483494</v>
       </c>
       <c r="F131" t="n">
         <v>2222600</v>
@@ -3052,16 +3052,16 @@
         <v>44834</v>
       </c>
       <c r="B132" t="n">
-        <v>10.61352252960205</v>
+        <v>10.61352157592773</v>
       </c>
       <c r="C132" t="n">
-        <v>10.74668117272986</v>
+        <v>10.74668020709063</v>
       </c>
       <c r="D132" t="n">
-        <v>10.59785645535194</v>
+        <v>10.59785550308529</v>
       </c>
       <c r="E132" t="n">
-        <v>10.70751673410412</v>
+        <v>10.70751577198399</v>
       </c>
       <c r="F132" t="n">
         <v>4019300</v>
@@ -3092,16 +3092,16 @@
         <v>44838</v>
       </c>
       <c r="B134" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C134" t="n">
-        <v>11.32631180289231</v>
+        <v>11.32631277471268</v>
       </c>
       <c r="D134" t="n">
-        <v>11.07566060573824</v>
+        <v>11.07566155605223</v>
       </c>
       <c r="E134" t="n">
-        <v>11.20881924097621</v>
+        <v>11.20882020271549</v>
       </c>
       <c r="F134" t="n">
         <v>2406500</v>
@@ -3112,16 +3112,16 @@
         <v>44839</v>
       </c>
       <c r="B135" t="n">
-        <v>10.97383403778076</v>
+        <v>10.97383308410645</v>
       </c>
       <c r="C135" t="n">
-        <v>11.20881992290874</v>
+        <v>11.20881894881312</v>
       </c>
       <c r="D135" t="n">
-        <v>10.85634072171701</v>
+        <v>10.85633977825337</v>
       </c>
       <c r="E135" t="n">
-        <v>11.20881992290874</v>
+        <v>11.20881894881312</v>
       </c>
       <c r="F135" t="n">
         <v>5244200</v>
@@ -3132,16 +3132,16 @@
         <v>44840</v>
       </c>
       <c r="B136" t="n">
-        <v>10.98950004577637</v>
+        <v>10.98949909210205</v>
       </c>
       <c r="C136" t="n">
-        <v>11.12265869736379</v>
+        <v>11.1226577321339</v>
       </c>
       <c r="D136" t="n">
-        <v>10.88767279768013</v>
+        <v>10.88767185284243</v>
       </c>
       <c r="E136" t="n">
-        <v>11.02866448689024</v>
+        <v>11.02866352981721</v>
       </c>
       <c r="F136" t="n">
         <v>3101100</v>
@@ -3192,16 +3192,16 @@
         <v>44845</v>
       </c>
       <c r="B139" t="n">
-        <v>11.22448539733887</v>
+        <v>11.22448444366455</v>
       </c>
       <c r="C139" t="n">
-        <v>11.31847960322243</v>
+        <v>11.31847864156201</v>
       </c>
       <c r="D139" t="n">
-        <v>10.99733254637037</v>
+        <v>10.99733161199581</v>
       </c>
       <c r="E139" t="n">
-        <v>11.04433002281193</v>
+        <v>11.04432908444429</v>
       </c>
       <c r="F139" t="n">
         <v>1834300</v>
@@ -3212,16 +3212,16 @@
         <v>44847</v>
       </c>
       <c r="B140" t="n">
-        <v>10.91117095947266</v>
+        <v>10.91117191314697</v>
       </c>
       <c r="C140" t="n">
-        <v>11.20098660325412</v>
+        <v>11.20098758225933</v>
       </c>
       <c r="D140" t="n">
-        <v>10.87200652177256</v>
+        <v>10.87200747202377</v>
       </c>
       <c r="E140" t="n">
-        <v>11.12265772785393</v>
+        <v>11.12265870001293</v>
       </c>
       <c r="F140" t="n">
         <v>3739400</v>
@@ -3232,16 +3232,16 @@
         <v>44848</v>
       </c>
       <c r="B141" t="n">
-        <v>10.8250093460083</v>
+        <v>10.82500839233398</v>
       </c>
       <c r="C141" t="n">
-        <v>11.1618224737291</v>
+        <v>11.16182149038183</v>
       </c>
       <c r="D141" t="n">
-        <v>10.8250093460083</v>
+        <v>10.82500839233398</v>
       </c>
       <c r="E141" t="n">
-        <v>10.97383406397776</v>
+        <v>10.97383309719211</v>
       </c>
       <c r="F141" t="n">
         <v>3601200</v>
@@ -3252,16 +3252,16 @@
         <v>44851</v>
       </c>
       <c r="B142" t="n">
-        <v>11.1539888381958</v>
+        <v>11.15398979187012</v>
       </c>
       <c r="C142" t="n">
-        <v>11.20098631161214</v>
+        <v>11.20098726930477</v>
       </c>
       <c r="D142" t="n">
-        <v>10.78584507559909</v>
+        <v>10.78584599779684</v>
       </c>
       <c r="E142" t="n">
-        <v>10.86417320196032</v>
+        <v>10.86417413085518</v>
       </c>
       <c r="F142" t="n">
         <v>6971700</v>
@@ -3312,16 +3312,16 @@
         <v>44854</v>
       </c>
       <c r="B145" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C145" t="n">
-        <v>10.98166755090811</v>
+        <v>10.98166658413194</v>
       </c>
       <c r="D145" t="n">
-        <v>10.39420318612486</v>
+        <v>10.39420227106638</v>
       </c>
       <c r="E145" t="n">
-        <v>10.5743585660986</v>
+        <v>10.57435763518006</v>
       </c>
       <c r="F145" t="n">
         <v>7194300</v>
@@ -3352,16 +3352,16 @@
         <v>44858</v>
       </c>
       <c r="B147" t="n">
-        <v>11.24798202514648</v>
+        <v>11.24798393249512</v>
       </c>
       <c r="C147" t="n">
-        <v>11.45163647994565</v>
+        <v>11.45163842182848</v>
       </c>
       <c r="D147" t="n">
-        <v>11.10699111159273</v>
+        <v>11.10699299503318</v>
       </c>
       <c r="E147" t="n">
-        <v>11.10699111159273</v>
+        <v>11.10699299503318</v>
       </c>
       <c r="F147" t="n">
         <v>2219500</v>
@@ -3432,16 +3432,16 @@
         <v>44862</v>
       </c>
       <c r="B151" t="n">
-        <v>11.49080181121826</v>
+        <v>11.49080276489258</v>
       </c>
       <c r="C151" t="n">
-        <v>11.63962577243467</v>
+        <v>11.63962673846057</v>
       </c>
       <c r="D151" t="n">
-        <v>11.2244845413578</v>
+        <v>11.22448547292922</v>
       </c>
       <c r="E151" t="n">
-        <v>11.32631177671618</v>
+        <v>11.32631271673871</v>
       </c>
       <c r="F151" t="n">
         <v>2887600</v>
@@ -3592,16 +3592,16 @@
         <v>44875</v>
       </c>
       <c r="B159" t="n">
-        <v>10.70751571655273</v>
+        <v>10.70751762390137</v>
       </c>
       <c r="C159" t="n">
-        <v>11.10699160797338</v>
+        <v>11.10699358648135</v>
       </c>
       <c r="D159" t="n">
-        <v>10.49602821627141</v>
+        <v>10.4960300859474</v>
       </c>
       <c r="E159" t="n">
-        <v>11.04432881092694</v>
+        <v>11.04433077827268</v>
       </c>
       <c r="F159" t="n">
         <v>4341400</v>
@@ -3612,16 +3612,16 @@
         <v>44876</v>
       </c>
       <c r="B160" t="n">
-        <v>10.79367733001709</v>
+        <v>10.79367637634277</v>
       </c>
       <c r="C160" t="n">
-        <v>10.85634012970083</v>
+        <v>10.85633917048995</v>
       </c>
       <c r="D160" t="n">
-        <v>10.5351930945718</v>
+        <v>10.53519216373583</v>
       </c>
       <c r="E160" t="n">
-        <v>10.78584504030624</v>
+        <v>10.78584408732395</v>
       </c>
       <c r="F160" t="n">
         <v>3291200</v>
@@ -3632,16 +3632,16 @@
         <v>44879</v>
       </c>
       <c r="B161" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C161" t="n">
-        <v>10.9660014759541</v>
+        <v>10.9660005105571</v>
       </c>
       <c r="D161" t="n">
-        <v>10.71535025268644</v>
+        <v>10.71534930935563</v>
       </c>
       <c r="E161" t="n">
-        <v>10.94250311052265</v>
+        <v>10.94250214719434</v>
       </c>
       <c r="F161" t="n">
         <v>1203700</v>
@@ -3652,16 +3652,16 @@
         <v>44881</v>
       </c>
       <c r="B162" t="n">
-        <v>10.90333843231201</v>
+        <v>10.9033374786377</v>
       </c>
       <c r="C162" t="n">
-        <v>10.90333843231201</v>
+        <v>10.9033374786377</v>
       </c>
       <c r="D162" t="n">
-        <v>10.59785670036809</v>
+        <v>10.59785577341312</v>
       </c>
       <c r="E162" t="n">
-        <v>10.86417399278081</v>
+        <v>10.86417304253206</v>
       </c>
       <c r="F162" t="n">
         <v>5270300</v>
@@ -3672,16 +3672,16 @@
         <v>44882</v>
       </c>
       <c r="B163" t="n">
-        <v>10.74668121337891</v>
+        <v>10.74668025970459</v>
       </c>
       <c r="C163" t="n">
-        <v>10.80151097946262</v>
+        <v>10.80151002092264</v>
       </c>
       <c r="D163" t="n">
-        <v>10.50386229058046</v>
+        <v>10.50386135845421</v>
       </c>
       <c r="E163" t="n">
-        <v>10.69185070029565</v>
+        <v>10.69184975148707</v>
       </c>
       <c r="F163" t="n">
         <v>5834900</v>
@@ -3692,16 +3692,16 @@
         <v>44883</v>
       </c>
       <c r="B164" t="n">
-        <v>10.78584480285645</v>
+        <v>10.78584575653076</v>
       </c>
       <c r="C164" t="n">
-        <v>10.98949852384542</v>
+        <v>10.98949949552661</v>
       </c>
       <c r="D164" t="n">
-        <v>10.57435729833009</v>
+        <v>10.57435823330488</v>
       </c>
       <c r="E164" t="n">
-        <v>10.80934316547066</v>
+        <v>10.80934412122268</v>
       </c>
       <c r="F164" t="n">
         <v>3568700</v>
@@ -3752,16 +3752,16 @@
         <v>44888</v>
       </c>
       <c r="B167" t="n">
-        <v>10.56652545928955</v>
+        <v>10.56652450561523</v>
       </c>
       <c r="C167" t="n">
-        <v>10.81717742791213</v>
+        <v>10.8171764516154</v>
       </c>
       <c r="D167" t="n">
-        <v>10.51952872873502</v>
+        <v>10.51952777930236</v>
       </c>
       <c r="E167" t="n">
-        <v>10.80934439048652</v>
+        <v>10.80934341489675</v>
       </c>
       <c r="F167" t="n">
         <v>4669400</v>
@@ -3792,16 +3792,16 @@
         <v>44890</v>
       </c>
       <c r="B169" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C169" t="n">
-        <v>11.03649731924802</v>
+        <v>11.03649634764489</v>
       </c>
       <c r="D169" t="n">
-        <v>10.71535025268644</v>
+        <v>10.71534930935563</v>
       </c>
       <c r="E169" t="n">
-        <v>10.95033540100009</v>
+        <v>10.95033443698226</v>
       </c>
       <c r="F169" t="n">
         <v>1631500</v>
@@ -3812,16 +3812,16 @@
         <v>44893</v>
       </c>
       <c r="B170" t="n">
-        <v>10.97383403778076</v>
+        <v>10.97383308410645</v>
       </c>
       <c r="C170" t="n">
-        <v>11.09915964398247</v>
+        <v>11.09915867941681</v>
       </c>
       <c r="D170" t="n">
-        <v>10.68401838668942</v>
+        <v>10.68401745820135</v>
       </c>
       <c r="E170" t="n">
-        <v>10.84067539444156</v>
+        <v>10.84067445233931</v>
       </c>
       <c r="F170" t="n">
         <v>4990000</v>
@@ -3852,16 +3852,16 @@
         <v>44895</v>
       </c>
       <c r="B172" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C172" t="n">
-        <v>11.20882040874432</v>
+        <v>11.20881942197064</v>
       </c>
       <c r="D172" t="n">
-        <v>10.69185114025542</v>
+        <v>10.69185019899337</v>
       </c>
       <c r="E172" t="n">
-        <v>11.20882040874432</v>
+        <v>11.20881942197064</v>
       </c>
       <c r="F172" t="n">
         <v>4586400</v>
@@ -3872,16 +3872,16 @@
         <v>44896</v>
       </c>
       <c r="B173" t="n">
-        <v>10.92683696746826</v>
+        <v>10.92683601379395</v>
       </c>
       <c r="C173" t="n">
-        <v>11.02083117560783</v>
+        <v>11.02083021372987</v>
       </c>
       <c r="D173" t="n">
-        <v>10.69185107361957</v>
+        <v>10.69185014045439</v>
       </c>
       <c r="E173" t="n">
-        <v>10.76234691647413</v>
+        <v>10.76234597715621</v>
       </c>
       <c r="F173" t="n">
         <v>1944500</v>
@@ -3972,16 +3972,16 @@
         <v>44903</v>
       </c>
       <c r="B178" t="n">
-        <v>11.26364898681641</v>
+        <v>11.26364994049072</v>
       </c>
       <c r="C178" t="n">
-        <v>11.8119488532735</v>
+        <v>11.81194985337145</v>
       </c>
       <c r="D178" t="n">
-        <v>11.15398871472519</v>
+        <v>11.15398965911476</v>
       </c>
       <c r="E178" t="n">
-        <v>11.74928605407837</v>
+        <v>11.74928704887077</v>
       </c>
       <c r="F178" t="n">
         <v>12105700</v>
@@ -3992,16 +3992,16 @@
         <v>44904</v>
       </c>
       <c r="B179" t="n">
-        <v>11.17748737335205</v>
+        <v>11.17748832702637</v>
       </c>
       <c r="C179" t="n">
-        <v>11.5691302260077</v>
+        <v>11.56913121309737</v>
       </c>
       <c r="D179" t="n">
-        <v>11.04432874368917</v>
+        <v>11.04432968600226</v>
       </c>
       <c r="E179" t="n">
-        <v>11.29497993034896</v>
+        <v>11.29498089404786</v>
       </c>
       <c r="F179" t="n">
         <v>7204400</v>
@@ -4012,16 +4012,16 @@
         <v>44907</v>
       </c>
       <c r="B180" t="n">
-        <v>11.00516605377197</v>
+        <v>11.00516510009766</v>
       </c>
       <c r="C180" t="n">
-        <v>11.26365031774459</v>
+        <v>11.26364934167081</v>
       </c>
       <c r="D180" t="n">
-        <v>10.74668178979936</v>
+        <v>10.7466808585245</v>
       </c>
       <c r="E180" t="n">
-        <v>11.17748914542024</v>
+        <v>11.17748817681293</v>
       </c>
       <c r="F180" t="n">
         <v>4004300</v>
@@ -4052,16 +4052,16 @@
         <v>44909</v>
       </c>
       <c r="B182" t="n">
-        <v>10.9973316192627</v>
+        <v>10.99733257293701</v>
       </c>
       <c r="C182" t="n">
-        <v>11.13832328970179</v>
+        <v>11.13832425560273</v>
       </c>
       <c r="D182" t="n">
-        <v>10.738847388124</v>
+        <v>10.7388483193829</v>
       </c>
       <c r="E182" t="n">
-        <v>11.01299769242237</v>
+        <v>11.01299864745522</v>
       </c>
       <c r="F182" t="n">
         <v>3892800</v>
@@ -4092,16 +4092,16 @@
         <v>44911</v>
       </c>
       <c r="B184" t="n">
-        <v>11.24798202514648</v>
+        <v>11.24798393249512</v>
       </c>
       <c r="C184" t="n">
-        <v>11.24798202514648</v>
+        <v>11.24798393249512</v>
       </c>
       <c r="D184" t="n">
-        <v>10.90333665679356</v>
+        <v>10.90333850569981</v>
       </c>
       <c r="E184" t="n">
-        <v>11.04432831734674</v>
+        <v>11.04433019016131</v>
       </c>
       <c r="F184" t="n">
         <v>3365900</v>
@@ -4152,16 +4152,16 @@
         <v>44916</v>
       </c>
       <c r="B187" t="n">
-        <v>11.58479595184326</v>
+        <v>11.58479690551758</v>
       </c>
       <c r="C187" t="n">
-        <v>11.75711902212409</v>
+        <v>11.75711998998425</v>
       </c>
       <c r="D187" t="n">
-        <v>11.15398864964095</v>
+        <v>11.15398956785069</v>
       </c>
       <c r="E187" t="n">
-        <v>11.42813895476955</v>
+        <v>11.42813989554768</v>
       </c>
       <c r="F187" t="n">
         <v>6348400</v>
@@ -4172,16 +4172,16 @@
         <v>44917</v>
       </c>
       <c r="B188" t="n">
-        <v>11.63179492950439</v>
+        <v>11.63179397583008</v>
       </c>
       <c r="C188" t="n">
-        <v>11.74928750576218</v>
+        <v>11.74928654245482</v>
       </c>
       <c r="D188" t="n">
-        <v>11.50646856862995</v>
+        <v>11.50646762523096</v>
       </c>
       <c r="E188" t="n">
-        <v>11.60046352603568</v>
+        <v>11.60046257493018</v>
       </c>
       <c r="F188" t="n">
         <v>2577900</v>
@@ -4212,16 +4212,16 @@
         <v>44921</v>
       </c>
       <c r="B190" t="n">
-        <v>11.5769624710083</v>
+        <v>11.57696342468262</v>
       </c>
       <c r="C190" t="n">
-        <v>11.8276144037077</v>
+        <v>11.82761537802995</v>
       </c>
       <c r="D190" t="n">
-        <v>11.51429967458331</v>
+        <v>11.51430062309566</v>
       </c>
       <c r="E190" t="n">
-        <v>11.77278389658625</v>
+        <v>11.77278486639172</v>
       </c>
       <c r="F190" t="n">
         <v>1646600</v>
@@ -4252,16 +4252,16 @@
         <v>44923</v>
       </c>
       <c r="B192" t="n">
-        <v>11.58479595184326</v>
+        <v>11.58479690551758</v>
       </c>
       <c r="C192" t="n">
-        <v>11.6944562232946</v>
+        <v>11.69445718599628</v>
       </c>
       <c r="D192" t="n">
-        <v>11.49863479020259</v>
+        <v>11.49863573678402</v>
       </c>
       <c r="E192" t="n">
-        <v>11.5769629152397</v>
+        <v>11.5769638682692</v>
       </c>
       <c r="F192" t="n">
         <v>2005900</v>
@@ -4272,16 +4272,16 @@
         <v>44924</v>
       </c>
       <c r="B193" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="C193" t="n">
-        <v>11.73362032145083</v>
+        <v>11.73362129131107</v>
       </c>
       <c r="D193" t="n">
-        <v>11.4751360805163</v>
+        <v>11.47513702901113</v>
       </c>
       <c r="E193" t="n">
-        <v>11.62396079317528</v>
+        <v>11.62396175397144</v>
       </c>
       <c r="F193" t="n">
         <v>2424800</v>
@@ -4312,16 +4312,16 @@
         <v>44929</v>
       </c>
       <c r="B195" t="n">
-        <v>11.13832378387451</v>
+        <v>11.13832473754883</v>
       </c>
       <c r="C195" t="n">
-        <v>11.32631218813412</v>
+        <v>11.32631315790418</v>
       </c>
       <c r="D195" t="n">
-        <v>11.05999490859992</v>
+        <v>11.05999585556764</v>
       </c>
       <c r="E195" t="n">
-        <v>11.30281382435154</v>
+        <v>11.30281479210966</v>
       </c>
       <c r="F195" t="n">
         <v>1562800</v>
@@ -4352,16 +4352,16 @@
         <v>44931</v>
       </c>
       <c r="B197" t="n">
-        <v>11.41247367858887</v>
+        <v>11.41247272491455</v>
       </c>
       <c r="C197" t="n">
-        <v>11.41247367858887</v>
+        <v>11.41247272491455</v>
       </c>
       <c r="D197" t="n">
-        <v>11.08349358825896</v>
+        <v>11.08349266207561</v>
       </c>
       <c r="E197" t="n">
-        <v>11.31064643662965</v>
+        <v>11.31064549146445</v>
       </c>
       <c r="F197" t="n">
         <v>4358300</v>
@@ -4412,16 +4412,16 @@
         <v>44936</v>
       </c>
       <c r="B200" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C200" t="n">
-        <v>11.1853201309934</v>
+        <v>11.1853210907164</v>
       </c>
       <c r="D200" t="n">
-        <v>10.6918500263467</v>
+        <v>10.69185094372897</v>
       </c>
       <c r="E200" t="n">
-        <v>11.08349289539969</v>
+        <v>11.08349384638571</v>
       </c>
       <c r="F200" t="n">
         <v>5832500</v>
@@ -4452,16 +4452,16 @@
         <v>44938</v>
       </c>
       <c r="B202" t="n">
-        <v>11.79628372192383</v>
+        <v>11.79628276824951</v>
       </c>
       <c r="C202" t="n">
-        <v>11.97643908583725</v>
+        <v>11.97643811759822</v>
       </c>
       <c r="D202" t="n">
-        <v>11.49863504732819</v>
+        <v>11.49863411771738</v>
       </c>
       <c r="E202" t="n">
-        <v>11.49863504732819</v>
+        <v>11.49863411771738</v>
       </c>
       <c r="F202" t="n">
         <v>5662900</v>
@@ -4472,16 +4472,16 @@
         <v>44939</v>
       </c>
       <c r="B203" t="n">
-        <v>11.58479595184326</v>
+        <v>11.58479690551758</v>
       </c>
       <c r="C203" t="n">
-        <v>11.78845042153883</v>
+        <v>11.78845139197822</v>
       </c>
       <c r="D203" t="n">
-        <v>11.44380428097718</v>
+        <v>11.44380522304489</v>
       </c>
       <c r="E203" t="n">
-        <v>11.74928598552053</v>
+        <v>11.74928695273586</v>
       </c>
       <c r="F203" t="n">
         <v>2269100</v>
@@ -4512,16 +4512,16 @@
         <v>44943</v>
       </c>
       <c r="B205" t="n">
-        <v>11.74928665161133</v>
+        <v>11.74928569793701</v>
       </c>
       <c r="C205" t="n">
-        <v>11.93727505875722</v>
+        <v>11.93727408982413</v>
       </c>
       <c r="D205" t="n">
-        <v>11.60829497275214</v>
+        <v>11.60829403052194</v>
       </c>
       <c r="E205" t="n">
-        <v>11.81194945399329</v>
+        <v>11.81194849523272</v>
       </c>
       <c r="F205" t="n">
         <v>2676600</v>
@@ -4532,16 +4532,16 @@
         <v>44944</v>
       </c>
       <c r="B206" t="n">
-        <v>11.41247367858887</v>
+        <v>11.41247272491455</v>
       </c>
       <c r="C206" t="n">
-        <v>11.89027848678206</v>
+        <v>11.89027749318036</v>
       </c>
       <c r="D206" t="n">
-        <v>11.41247367858887</v>
+        <v>11.41247272491455</v>
       </c>
       <c r="E206" t="n">
-        <v>11.87461241248085</v>
+        <v>11.87461142018828</v>
       </c>
       <c r="F206" t="n">
         <v>3532000</v>
@@ -4552,16 +4552,16 @@
         <v>44945</v>
       </c>
       <c r="B207" t="n">
-        <v>11.66312503814697</v>
+        <v>11.66312599182129</v>
       </c>
       <c r="C207" t="n">
-        <v>11.68662340138985</v>
+        <v>11.68662435698559</v>
       </c>
       <c r="D207" t="n">
-        <v>11.27931445451592</v>
+        <v>11.27931537680668</v>
       </c>
       <c r="E207" t="n">
-        <v>11.3419772544966</v>
+        <v>11.3419781819112</v>
       </c>
       <c r="F207" t="n">
         <v>1847800</v>
@@ -4572,16 +4572,16 @@
         <v>44946</v>
       </c>
       <c r="B208" t="n">
-        <v>11.58479595184326</v>
+        <v>11.58479690551758</v>
       </c>
       <c r="C208" t="n">
-        <v>11.68662318669104</v>
+        <v>11.6866241487479</v>
       </c>
       <c r="D208" t="n">
-        <v>11.48296871699548</v>
+        <v>11.48296966228726</v>
       </c>
       <c r="E208" t="n">
-        <v>11.6552917872763</v>
+        <v>11.65529274675392</v>
       </c>
       <c r="F208" t="n">
         <v>2012100</v>
@@ -4632,16 +4632,16 @@
         <v>44951</v>
       </c>
       <c r="B211" t="n">
-        <v>11.89027786254883</v>
+        <v>11.89027881622314</v>
       </c>
       <c r="C211" t="n">
-        <v>12.07043322555739</v>
+        <v>12.07043419368129</v>
       </c>
       <c r="D211" t="n">
-        <v>11.62396058940618</v>
+        <v>11.62396152172019</v>
       </c>
       <c r="E211" t="n">
-        <v>11.67879035258278</v>
+        <v>11.67879128929448</v>
       </c>
       <c r="F211" t="n">
         <v>10764800</v>
@@ -4712,16 +4712,16 @@
         <v>44957</v>
       </c>
       <c r="B215" t="n">
-        <v>12.07043361663818</v>
+        <v>12.0704345703125</v>
       </c>
       <c r="C215" t="n">
-        <v>12.14092945557759</v>
+        <v>12.14093041482172</v>
       </c>
       <c r="D215" t="n">
-        <v>11.82761544584636</v>
+        <v>11.82761638033583</v>
       </c>
       <c r="E215" t="n">
-        <v>11.84328077283316</v>
+        <v>11.84328170856034</v>
       </c>
       <c r="F215" t="n">
         <v>5446800</v>
@@ -4732,16 +4732,16 @@
         <v>44958</v>
       </c>
       <c r="B216" t="n">
-        <v>12.07826614379883</v>
+        <v>12.07826709747314</v>
       </c>
       <c r="C216" t="n">
-        <v>12.19575870573871</v>
+        <v>12.19575966868999</v>
       </c>
       <c r="D216" t="n">
-        <v>11.93727447187138</v>
+        <v>11.93727541441329</v>
       </c>
       <c r="E216" t="n">
-        <v>12.08609918046135</v>
+        <v>12.08610013475415</v>
       </c>
       <c r="F216" t="n">
         <v>3741600</v>
@@ -4752,16 +4752,16 @@
         <v>44959</v>
       </c>
       <c r="B217" t="n">
-        <v>12.03910255432129</v>
+        <v>12.03910160064697</v>
       </c>
       <c r="C217" t="n">
-        <v>12.19575956359362</v>
+        <v>12.19575859750976</v>
       </c>
       <c r="D217" t="n">
-        <v>11.8511141431945</v>
+        <v>11.85111320441163</v>
       </c>
       <c r="E217" t="n">
-        <v>12.07043395617575</v>
+        <v>12.07043300001953</v>
       </c>
       <c r="F217" t="n">
         <v>3404900</v>
@@ -4772,16 +4772,16 @@
         <v>44960</v>
       </c>
       <c r="B218" t="n">
-        <v>11.92160987854004</v>
+        <v>11.92160892486572</v>
       </c>
       <c r="C218" t="n">
-        <v>12.17226109115601</v>
+        <v>12.17226011743074</v>
       </c>
       <c r="D218" t="n">
-        <v>11.80411656237665</v>
+        <v>11.80411561810126</v>
       </c>
       <c r="E218" t="n">
-        <v>11.99993800898276</v>
+        <v>11.99993704904255</v>
       </c>
       <c r="F218" t="n">
         <v>3073100</v>
@@ -4792,16 +4792,16 @@
         <v>44963</v>
       </c>
       <c r="B219" t="n">
-        <v>11.91377639770508</v>
+        <v>11.91377735137939</v>
       </c>
       <c r="C219" t="n">
-        <v>11.96077387182007</v>
+        <v>11.96077482925644</v>
       </c>
       <c r="D219" t="n">
-        <v>11.75711939565429</v>
+        <v>11.75712033678852</v>
       </c>
       <c r="E219" t="n">
-        <v>11.92160943455749</v>
+        <v>11.92161038885883</v>
       </c>
       <c r="F219" t="n">
         <v>3421200</v>
@@ -4812,16 +4812,16 @@
         <v>44964</v>
       </c>
       <c r="B220" t="n">
-        <v>11.60046195983887</v>
+        <v>11.60046291351318</v>
       </c>
       <c r="C220" t="n">
-        <v>12.02343622305989</v>
+        <v>12.02343721150694</v>
       </c>
       <c r="D220" t="n">
-        <v>11.49080168900398</v>
+        <v>11.49080263366312</v>
       </c>
       <c r="E220" t="n">
-        <v>12.02343622305989</v>
+        <v>12.02343721150694</v>
       </c>
       <c r="F220" t="n">
         <v>5199600</v>
@@ -4832,16 +4832,16 @@
         <v>44965</v>
       </c>
       <c r="B221" t="n">
-        <v>11.71012210845947</v>
+        <v>11.71012306213379</v>
       </c>
       <c r="C221" t="n">
-        <v>11.78845098423493</v>
+        <v>11.78845194428836</v>
       </c>
       <c r="D221" t="n">
-        <v>11.54563206693063</v>
+        <v>11.54563300720885</v>
       </c>
       <c r="E221" t="n">
-        <v>11.68662374452664</v>
+        <v>11.68662469628725</v>
       </c>
       <c r="F221" t="n">
         <v>3697100</v>
@@ -4852,16 +4852,16 @@
         <v>44966</v>
       </c>
       <c r="B222" t="n">
-        <v>11.66312503814697</v>
+        <v>11.66312599182129</v>
       </c>
       <c r="C222" t="n">
-        <v>11.78845063810834</v>
+        <v>11.78845160203032</v>
       </c>
       <c r="D222" t="n">
-        <v>11.55346476468103</v>
+        <v>11.55346570938861</v>
       </c>
       <c r="E222" t="n">
-        <v>11.71012176463273</v>
+        <v>11.7101227221499</v>
       </c>
       <c r="F222" t="n">
         <v>2260100</v>
@@ -4892,16 +4892,16 @@
         <v>44970</v>
       </c>
       <c r="B224" t="n">
-        <v>11.79628372192383</v>
+        <v>11.79628276824951</v>
       </c>
       <c r="C224" t="n">
-        <v>11.87461184871247</v>
+        <v>11.87461088870569</v>
       </c>
       <c r="D224" t="n">
-        <v>11.63179368456833</v>
+        <v>11.63179274419227</v>
       </c>
       <c r="E224" t="n">
-        <v>11.74145321147233</v>
+        <v>11.7414522622308</v>
       </c>
       <c r="F224" t="n">
         <v>2704300</v>
@@ -4912,16 +4912,16 @@
         <v>44971</v>
       </c>
       <c r="B225" t="n">
-        <v>11.71795463562012</v>
+        <v>11.71795558929443</v>
       </c>
       <c r="C225" t="n">
-        <v>11.88244466999244</v>
+        <v>11.8824456370539</v>
       </c>
       <c r="D225" t="n">
-        <v>11.51430016506401</v>
+        <v>11.51430110216375</v>
       </c>
       <c r="E225" t="n">
-        <v>11.78061743471438</v>
+        <v>11.78061839348856</v>
       </c>
       <c r="F225" t="n">
         <v>2141000</v>
@@ -4932,16 +4932,16 @@
         <v>44972</v>
       </c>
       <c r="B226" t="n">
-        <v>11.75711917877197</v>
+        <v>11.75712013244629</v>
       </c>
       <c r="C226" t="n">
-        <v>11.92944150434928</v>
+        <v>11.92944247200145</v>
       </c>
       <c r="D226" t="n">
-        <v>11.63179357944321</v>
+        <v>11.63179452295179</v>
       </c>
       <c r="E226" t="n">
-        <v>11.6631249792754</v>
+        <v>11.66312592532541</v>
       </c>
       <c r="F226" t="n">
         <v>3961900</v>
@@ -4952,16 +4952,16 @@
         <v>44973</v>
       </c>
       <c r="B227" t="n">
-        <v>11.89027786254883</v>
+        <v>11.89027881622314</v>
       </c>
       <c r="C227" t="n">
-        <v>11.97643902568342</v>
+        <v>11.9764399862684</v>
       </c>
       <c r="D227" t="n">
-        <v>11.57696311596945</v>
+        <v>11.57696404451397</v>
       </c>
       <c r="E227" t="n">
-        <v>11.76495226271687</v>
+        <v>11.7649532063393</v>
       </c>
       <c r="F227" t="n">
         <v>4461000</v>
@@ -4992,16 +4992,16 @@
         <v>44979</v>
       </c>
       <c r="B229" t="n">
-        <v>11.71795463562012</v>
+        <v>11.71795558929443</v>
       </c>
       <c r="C229" t="n">
-        <v>11.95294050572336</v>
+        <v>11.95294147852217</v>
       </c>
       <c r="D229" t="n">
-        <v>11.66312487316251</v>
+        <v>11.66312582237446</v>
       </c>
       <c r="E229" t="n">
-        <v>11.89810999626626</v>
+        <v>11.89811096460265</v>
       </c>
       <c r="F229" t="n">
         <v>6185800</v>
@@ -5072,16 +5072,16 @@
         <v>44985</v>
       </c>
       <c r="B233" t="n">
-        <v>11.59263038635254</v>
+        <v>11.59262943267822</v>
       </c>
       <c r="C233" t="n">
-        <v>11.82761628379879</v>
+        <v>11.82761531079323</v>
       </c>
       <c r="D233" t="n">
-        <v>11.54563290806346</v>
+        <v>11.54563195825542</v>
       </c>
       <c r="E233" t="n">
-        <v>11.67095852083491</v>
+        <v>11.67095756071688</v>
       </c>
       <c r="F233" t="n">
         <v>7018700</v>
@@ -5112,16 +5112,16 @@
         <v>44987</v>
       </c>
       <c r="B235" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="C235" t="n">
-        <v>11.67879055731306</v>
+        <v>11.67879152264125</v>
       </c>
       <c r="D235" t="n">
-        <v>11.45947075376244</v>
+        <v>11.45947170096243</v>
       </c>
       <c r="E235" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="F235" t="n">
         <v>2250800</v>
@@ -5132,16 +5132,16 @@
         <v>44988</v>
       </c>
       <c r="B236" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="C236" t="n">
-        <v>11.64745915680582</v>
+        <v>11.64746011954428</v>
       </c>
       <c r="D236" t="n">
-        <v>11.45947075376244</v>
+        <v>11.45947170096243</v>
       </c>
       <c r="E236" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="F236" t="n">
         <v>1727100</v>
@@ -5192,16 +5192,16 @@
         <v>44993</v>
       </c>
       <c r="B239" t="n">
-        <v>11.63179492950439</v>
+        <v>11.63179397583008</v>
       </c>
       <c r="C239" t="n">
-        <v>11.63962722012189</v>
+        <v>11.63962626580541</v>
       </c>
       <c r="D239" t="n">
-        <v>11.48297020277831</v>
+        <v>11.48296926130592</v>
       </c>
       <c r="E239" t="n">
-        <v>11.62396189188732</v>
+        <v>11.62396093885522</v>
       </c>
       <c r="F239" t="n">
         <v>2946500</v>
@@ -5212,16 +5212,16 @@
         <v>44994</v>
       </c>
       <c r="B240" t="n">
-        <v>11.5769624710083</v>
+        <v>11.57696342468262</v>
       </c>
       <c r="C240" t="n">
-        <v>11.70228806385827</v>
+        <v>11.70228902785652</v>
       </c>
       <c r="D240" t="n">
-        <v>11.51429967458331</v>
+        <v>11.51430062309566</v>
       </c>
       <c r="E240" t="n">
-        <v>11.62395994182677</v>
+        <v>11.62396089937259</v>
       </c>
       <c r="F240" t="n">
         <v>2514900</v>
@@ -5232,16 +5232,16 @@
         <v>44995</v>
       </c>
       <c r="B241" t="n">
-        <v>11.5769624710083</v>
+        <v>11.57696342468262</v>
       </c>
       <c r="C241" t="n">
-        <v>11.63179297812976</v>
+        <v>11.63179393632084</v>
       </c>
       <c r="D241" t="n">
-        <v>11.44380384185534</v>
+        <v>11.44380478456046</v>
       </c>
       <c r="E241" t="n">
-        <v>11.5769624710083</v>
+        <v>11.57696342468262</v>
       </c>
       <c r="F241" t="n">
         <v>3626000</v>
@@ -5252,16 +5252,16 @@
         <v>44998</v>
       </c>
       <c r="B242" t="n">
-        <v>11.66312503814697</v>
+        <v>11.66312599182129</v>
       </c>
       <c r="C242" t="n">
-        <v>11.74145316462308</v>
+        <v>11.74145412470215</v>
       </c>
       <c r="D242" t="n">
-        <v>11.45947056471</v>
+        <v>11.45947150173183</v>
       </c>
       <c r="E242" t="n">
-        <v>11.52213336469069</v>
+        <v>11.52213430683635</v>
       </c>
       <c r="F242" t="n">
         <v>3223500</v>
@@ -5272,16 +5272,16 @@
         <v>44999</v>
       </c>
       <c r="B243" t="n">
-        <v>11.75711917877197</v>
+        <v>11.75712013244629</v>
       </c>
       <c r="C243" t="n">
-        <v>11.82761501514428</v>
+        <v>11.82761597453684</v>
       </c>
       <c r="D243" t="n">
-        <v>11.63962586915163</v>
+        <v>11.63962681329553</v>
       </c>
       <c r="E243" t="n">
-        <v>11.69445637910759</v>
+        <v>11.69445732769904</v>
       </c>
       <c r="F243" t="n">
         <v>2520000</v>
@@ -5292,16 +5292,16 @@
         <v>45000</v>
       </c>
       <c r="B244" t="n">
-        <v>11.74928665161133</v>
+        <v>11.74928569793701</v>
       </c>
       <c r="C244" t="n">
-        <v>11.89027833047051</v>
+        <v>11.89027736535209</v>
       </c>
       <c r="D244" t="n">
-        <v>11.61612800979977</v>
+        <v>11.61612706693377</v>
       </c>
       <c r="E244" t="n">
-        <v>11.71795525042035</v>
+        <v>11.71795429928916</v>
       </c>
       <c r="F244" t="n">
         <v>4602600</v>
@@ -5332,16 +5332,16 @@
         <v>45002</v>
       </c>
       <c r="B246" t="n">
-        <v>11.40464019775391</v>
+        <v>11.40464115142822</v>
       </c>
       <c r="C246" t="n">
-        <v>11.66312442074082</v>
+        <v>11.66312539603</v>
       </c>
       <c r="D246" t="n">
-        <v>11.37330879942214</v>
+        <v>11.37330975047648</v>
       </c>
       <c r="E246" t="n">
-        <v>11.66312442074082</v>
+        <v>11.66312539603</v>
       </c>
       <c r="F246" t="n">
         <v>6196900</v>
@@ -5352,16 +5352,16 @@
         <v>45005</v>
       </c>
       <c r="B247" t="n">
-        <v>11.31847953796387</v>
+        <v>11.31847858428955</v>
       </c>
       <c r="C247" t="n">
-        <v>11.51430098584213</v>
+        <v>11.51430001566826</v>
       </c>
       <c r="D247" t="n">
-        <v>11.24798369720776</v>
+        <v>11.2479827494733</v>
       </c>
       <c r="E247" t="n">
-        <v>11.45163818228105</v>
+        <v>11.45163721738703</v>
       </c>
       <c r="F247" t="n">
         <v>2892000</v>
@@ -5392,16 +5392,16 @@
         <v>45007</v>
       </c>
       <c r="B249" t="n">
-        <v>11.33414459228516</v>
+        <v>11.33414554595947</v>
       </c>
       <c r="C249" t="n">
-        <v>11.45947018812806</v>
+        <v>11.45947115234749</v>
       </c>
       <c r="D249" t="n">
-        <v>11.21665128593282</v>
+        <v>11.21665222972105</v>
       </c>
       <c r="E249" t="n">
-        <v>11.36547599124588</v>
+        <v>11.36547694755648</v>
       </c>
       <c r="F249" t="n">
         <v>3006300</v>
@@ -5432,16 +5432,16 @@
         <v>45009</v>
       </c>
       <c r="B251" t="n">
-        <v>11.30281448364258</v>
+        <v>11.30281352996826</v>
       </c>
       <c r="C251" t="n">
-        <v>11.39680869125504</v>
+        <v>11.39680772964997</v>
       </c>
       <c r="D251" t="n">
-        <v>11.11482532141809</v>
+        <v>11.11482438360535</v>
       </c>
       <c r="E251" t="n">
-        <v>11.20882027603011</v>
+        <v>11.20881933028655</v>
       </c>
       <c r="F251" t="n">
         <v>3265300</v>
@@ -5452,16 +5452,16 @@
         <v>45012</v>
       </c>
       <c r="B252" t="n">
-        <v>11.28714752197266</v>
+        <v>11.28714847564697</v>
       </c>
       <c r="C252" t="n">
-        <v>11.42030615904377</v>
+        <v>11.42030712396893</v>
       </c>
       <c r="D252" t="n">
-        <v>11.1931533217459</v>
+        <v>11.19315426747845</v>
       </c>
       <c r="E252" t="n">
-        <v>11.39680779573696</v>
+        <v>11.39680875867669</v>
       </c>
       <c r="F252" t="n">
         <v>2288800</v>
@@ -5512,16 +5512,16 @@
         <v>45015</v>
       </c>
       <c r="B255" t="n">
-        <v>11.40464019775391</v>
+        <v>11.40464115142822</v>
       </c>
       <c r="C255" t="n">
-        <v>11.50646668208254</v>
+        <v>11.50646764427175</v>
       </c>
       <c r="D255" t="n">
-        <v>11.12265686576857</v>
+        <v>11.12265779586299</v>
       </c>
       <c r="E255" t="n">
-        <v>11.42030552342006</v>
+        <v>11.42030647840433</v>
       </c>
       <c r="F255" t="n">
         <v>3320400</v>
@@ -5532,16 +5532,16 @@
         <v>45016</v>
       </c>
       <c r="B256" t="n">
-        <v>11.49080181121826</v>
+        <v>11.49080276489258</v>
       </c>
       <c r="C256" t="n">
-        <v>11.61612740950566</v>
+        <v>11.61612837358132</v>
       </c>
       <c r="D256" t="n">
-        <v>11.30281341378716</v>
+        <v>11.30281435185946</v>
       </c>
       <c r="E256" t="n">
-        <v>11.42813901207456</v>
+        <v>11.42813996054821</v>
       </c>
       <c r="F256" t="n">
         <v>5155800</v>
@@ -5572,16 +5572,16 @@
         <v>45020</v>
       </c>
       <c r="B258" t="n">
-        <v>11.43597316741943</v>
+        <v>11.43597221374512</v>
       </c>
       <c r="C258" t="n">
-        <v>11.498635972693</v>
+        <v>11.49863501379308</v>
       </c>
       <c r="D258" t="n">
-        <v>11.24798400459917</v>
+        <v>11.24798306660174</v>
       </c>
       <c r="E258" t="n">
-        <v>11.35764428732769</v>
+        <v>11.35764334018542</v>
       </c>
       <c r="F258" t="n">
         <v>5230100</v>
@@ -5592,16 +5592,16 @@
         <v>45021</v>
       </c>
       <c r="B259" t="n">
-        <v>11.49080181121826</v>
+        <v>11.49080276489258</v>
       </c>
       <c r="C259" t="n">
-        <v>11.56913068364763</v>
+        <v>11.56913164382282</v>
       </c>
       <c r="D259" t="n">
-        <v>11.27931430385866</v>
+        <v>11.27931523998066</v>
       </c>
       <c r="E259" t="n">
-        <v>11.55346461036196</v>
+        <v>11.55346556923695</v>
       </c>
       <c r="F259" t="n">
         <v>4689800</v>
@@ -5612,16 +5612,16 @@
         <v>45022</v>
       </c>
       <c r="B260" t="n">
-        <v>11.53779888153076</v>
+        <v>11.53779983520508</v>
       </c>
       <c r="C260" t="n">
-        <v>11.6631252305592</v>
+        <v>11.66312619459255</v>
       </c>
       <c r="D260" t="n">
-        <v>11.4751360805163</v>
+        <v>11.47513702901113</v>
       </c>
       <c r="E260" t="n">
-        <v>11.49080215426967</v>
+        <v>11.4908031040594</v>
       </c>
       <c r="F260" t="n">
         <v>4653400</v>
@@ -5632,16 +5632,16 @@
         <v>45026</v>
       </c>
       <c r="B261" t="n">
-        <v>11.71795463562012</v>
+        <v>11.71795558929443</v>
       </c>
       <c r="C261" t="n">
-        <v>11.85111327044531</v>
+        <v>11.85111423495683</v>
       </c>
       <c r="D261" t="n">
-        <v>11.4594704026064</v>
+        <v>11.45947133524378</v>
       </c>
       <c r="E261" t="n">
-        <v>11.53779852797449</v>
+        <v>11.53779946698666</v>
       </c>
       <c r="F261" t="n">
         <v>3430500</v>
@@ -5692,16 +5692,16 @@
         <v>45029</v>
       </c>
       <c r="B264" t="n">
-        <v>11.91377639770508</v>
+        <v>11.91377735137939</v>
       </c>
       <c r="C264" t="n">
-        <v>11.99993756208313</v>
+        <v>11.99993852265448</v>
       </c>
       <c r="D264" t="n">
-        <v>11.77278472235961</v>
+        <v>11.77278566474782</v>
       </c>
       <c r="E264" t="n">
-        <v>11.82761523332702</v>
+        <v>11.82761618010431</v>
       </c>
       <c r="F264" t="n">
         <v>3337400</v>
@@ -5772,16 +5772,16 @@
         <v>45035</v>
       </c>
       <c r="B268" t="n">
-        <v>12.03910255432129</v>
+        <v>12.03910160064697</v>
       </c>
       <c r="C268" t="n">
-        <v>12.06260091896225</v>
+        <v>12.06259996342652</v>
       </c>
       <c r="D268" t="n">
-        <v>11.86677947062196</v>
+        <v>11.86677853059817</v>
       </c>
       <c r="E268" t="n">
-        <v>11.96860671339886</v>
+        <v>11.96860576530885</v>
       </c>
       <c r="F268" t="n">
         <v>3098200</v>
@@ -5792,16 +5792,16 @@
         <v>45036</v>
       </c>
       <c r="B269" t="n">
-        <v>12.09393215179443</v>
+        <v>12.09393310546875</v>
       </c>
       <c r="C269" t="n">
-        <v>12.14092962741908</v>
+        <v>12.14093058479941</v>
       </c>
       <c r="D269" t="n">
-        <v>12.00777098464871</v>
+        <v>12.00777193152874</v>
       </c>
       <c r="E269" t="n">
-        <v>12.06260075037785</v>
+        <v>12.06260170158151</v>
       </c>
       <c r="F269" t="n">
         <v>4813100</v>
@@ -5832,16 +5832,16 @@
         <v>45041</v>
       </c>
       <c r="B271" t="n">
-        <v>12.06260013580322</v>
+        <v>12.06260108947754</v>
       </c>
       <c r="C271" t="n">
-        <v>12.14092900885369</v>
+        <v>12.14092996872072</v>
       </c>
       <c r="D271" t="n">
-        <v>11.96860593634236</v>
+        <v>11.96860688258545</v>
       </c>
       <c r="E271" t="n">
-        <v>12.11743064573835</v>
+        <v>12.11743160374759</v>
       </c>
       <c r="F271" t="n">
         <v>2381100</v>
@@ -5872,16 +5872,16 @@
         <v>45043</v>
       </c>
       <c r="B273" t="n">
-        <v>12.07826614379883</v>
+        <v>12.07826709747314</v>
       </c>
       <c r="C273" t="n">
-        <v>12.09393147012438</v>
+        <v>12.0939324250356</v>
       </c>
       <c r="D273" t="n">
-        <v>11.95294054519642</v>
+        <v>11.95294148897529</v>
       </c>
       <c r="E273" t="n">
-        <v>12.01560334449763</v>
+        <v>12.01560429322422</v>
       </c>
       <c r="F273" t="n">
         <v>2919600</v>
@@ -5892,16 +5892,16 @@
         <v>45044</v>
       </c>
       <c r="B274" t="n">
-        <v>12.36024856567383</v>
+        <v>12.36024951934814</v>
       </c>
       <c r="C274" t="n">
-        <v>12.45424276329498</v>
+        <v>12.45424372422157</v>
       </c>
       <c r="D274" t="n">
-        <v>12.01560317439626</v>
+        <v>12.01560410147892</v>
       </c>
       <c r="E274" t="n">
-        <v>12.11743040856905</v>
+        <v>12.11743134350835</v>
       </c>
       <c r="F274" t="n">
         <v>8419400</v>
@@ -5932,16 +5932,16 @@
         <v>45049</v>
       </c>
       <c r="B276" t="n">
-        <v>12.28975296020508</v>
+        <v>12.28975391387939</v>
       </c>
       <c r="C276" t="n">
-        <v>12.48557439565576</v>
+        <v>12.48557536452565</v>
       </c>
       <c r="D276" t="n">
-        <v>12.28192067050667</v>
+        <v>12.2819216235732</v>
       </c>
       <c r="E276" t="n">
-        <v>12.48557439565576</v>
+        <v>12.48557536452565</v>
       </c>
       <c r="F276" t="n">
         <v>6661600</v>
@@ -5972,16 +5972,16 @@
         <v>45051</v>
       </c>
       <c r="B278" t="n">
-        <v>12.50989818572998</v>
+        <v>12.50989723205566</v>
       </c>
       <c r="C278" t="n">
-        <v>12.59647220699179</v>
+        <v>12.59647124671763</v>
       </c>
       <c r="D278" t="n">
-        <v>12.15494618469247</v>
+        <v>12.15494525807742</v>
       </c>
       <c r="E278" t="n">
-        <v>12.34540853608981</v>
+        <v>12.34540759495513</v>
       </c>
       <c r="F278" t="n">
         <v>9400800</v>
@@ -5992,16 +5992,16 @@
         <v>45054</v>
       </c>
       <c r="B279" t="n">
-        <v>12.11165809631348</v>
+        <v>12.11165904998779</v>
       </c>
       <c r="C279" t="n">
-        <v>12.58781351962092</v>
+        <v>12.58781451078781</v>
       </c>
       <c r="D279" t="n">
-        <v>12.05105678220141</v>
+        <v>12.05105773110397</v>
       </c>
       <c r="E279" t="n">
-        <v>12.54452651284189</v>
+        <v>12.54452750060035</v>
       </c>
       <c r="F279" t="n">
         <v>5826000</v>
@@ -6052,16 +6052,16 @@
         <v>45057</v>
       </c>
       <c r="B282" t="n">
-        <v>12.05971622467041</v>
+        <v>12.05971527099609</v>
       </c>
       <c r="C282" t="n">
-        <v>12.11165998038074</v>
+        <v>12.11165902259875</v>
       </c>
       <c r="D282" t="n">
-        <v>11.73939364568632</v>
+        <v>11.7393927173429</v>
       </c>
       <c r="E282" t="n">
-        <v>11.79133740139665</v>
+        <v>11.79133646894556</v>
       </c>
       <c r="F282" t="n">
         <v>3678200</v>
@@ -6072,16 +6072,16 @@
         <v>45058</v>
       </c>
       <c r="B283" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C283" t="n">
-        <v>12.25017729158851</v>
+        <v>12.25017632493442</v>
       </c>
       <c r="D283" t="n">
-        <v>11.9991136136361</v>
+        <v>11.99911266679329</v>
       </c>
       <c r="E283" t="n">
-        <v>12.0424006254826</v>
+        <v>12.04239967522403</v>
       </c>
       <c r="F283" t="n">
         <v>3087800</v>
@@ -6132,16 +6132,16 @@
         <v>45063</v>
       </c>
       <c r="B286" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="C286" t="n">
-        <v>12.24151939290137</v>
+        <v>12.24152036724783</v>
       </c>
       <c r="D286" t="n">
-        <v>11.94716873091856</v>
+        <v>11.9471696818366</v>
       </c>
       <c r="E286" t="n">
-        <v>12.12897350298847</v>
+        <v>12.128974468377</v>
       </c>
       <c r="F286" t="n">
         <v>4330800</v>
@@ -6152,16 +6152,16 @@
         <v>45064</v>
       </c>
       <c r="B287" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="C287" t="n">
-        <v>12.05971462083146</v>
+        <v>12.05971558070743</v>
       </c>
       <c r="D287" t="n">
-        <v>11.82596527432829</v>
+        <v>11.82596621559931</v>
       </c>
       <c r="E287" t="n">
-        <v>12.01642761307558</v>
+        <v>12.01642856950617</v>
       </c>
       <c r="F287" t="n">
         <v>4680600</v>
@@ -6172,16 +6172,16 @@
         <v>45065</v>
       </c>
       <c r="B288" t="n">
-        <v>12.09434413909912</v>
+        <v>12.09434509277344</v>
       </c>
       <c r="C288" t="n">
-        <v>12.18091732953242</v>
+        <v>12.18091829003328</v>
       </c>
       <c r="D288" t="n">
-        <v>11.93851124043578</v>
+        <v>11.93851218182222</v>
       </c>
       <c r="E288" t="n">
-        <v>11.99911255630219</v>
+        <v>11.99911350246722</v>
       </c>
       <c r="F288" t="n">
         <v>2962700</v>
@@ -6232,16 +6232,16 @@
         <v>45070</v>
       </c>
       <c r="B291" t="n">
-        <v>12.25017738342285</v>
+        <v>12.25017642974854</v>
       </c>
       <c r="C291" t="n">
-        <v>12.30212196315428</v>
+        <v>12.30212100543608</v>
       </c>
       <c r="D291" t="n">
-        <v>12.18091849420168</v>
+        <v>12.18091754591915</v>
       </c>
       <c r="E291" t="n">
-        <v>12.26749251854369</v>
+        <v>12.26749156352139</v>
       </c>
       <c r="F291" t="n">
         <v>1846000</v>
@@ -6252,16 +6252,16 @@
         <v>45071</v>
       </c>
       <c r="B292" t="n">
-        <v>12.29346370697021</v>
+        <v>12.29346466064453</v>
       </c>
       <c r="C292" t="n">
-        <v>12.39735203498263</v>
+        <v>12.39735299671616</v>
       </c>
       <c r="D292" t="n">
-        <v>12.20689051310872</v>
+        <v>12.20689146006706</v>
       </c>
       <c r="E292" t="n">
-        <v>12.28480613989475</v>
+        <v>12.28480709289745</v>
       </c>
       <c r="F292" t="n">
         <v>2204600</v>
@@ -6292,16 +6292,16 @@
         <v>45075</v>
       </c>
       <c r="B294" t="n">
-        <v>12.28480625152588</v>
+        <v>12.28480529785156</v>
       </c>
       <c r="C294" t="n">
-        <v>12.34540839597375</v>
+        <v>12.34540743759487</v>
       </c>
       <c r="D294" t="n">
-        <v>12.16360361389222</v>
+        <v>12.16360266962691</v>
       </c>
       <c r="E294" t="n">
-        <v>12.16360361389222</v>
+        <v>12.16360266962691</v>
       </c>
       <c r="F294" t="n">
         <v>1431900</v>
@@ -6352,16 +6352,16 @@
         <v>45078</v>
       </c>
       <c r="B297" t="n">
-        <v>12.2415189743042</v>
+        <v>12.24151992797852</v>
       </c>
       <c r="C297" t="n">
-        <v>12.30212028771158</v>
+        <v>12.30212124610704</v>
       </c>
       <c r="D297" t="n">
-        <v>12.16360252813415</v>
+        <v>12.1636034757384</v>
       </c>
       <c r="E297" t="n">
-        <v>12.26749084781722</v>
+        <v>12.26749180351488</v>
       </c>
       <c r="F297" t="n">
         <v>2308800</v>
@@ -6372,16 +6372,16 @@
         <v>45079</v>
       </c>
       <c r="B298" t="n">
-        <v>12.17226219177246</v>
+        <v>12.17226123809814</v>
       </c>
       <c r="C298" t="n">
-        <v>12.33675185320416</v>
+        <v>12.33675088664238</v>
       </c>
       <c r="D298" t="n">
-        <v>12.07703059643153</v>
+        <v>12.07702965021844</v>
       </c>
       <c r="E298" t="n">
-        <v>12.31077997521623</v>
+        <v>12.3107790106893</v>
       </c>
       <c r="F298" t="n">
         <v>5725100</v>
@@ -6412,16 +6412,16 @@
         <v>45083</v>
       </c>
       <c r="B300" t="n">
-        <v>12.32809257507324</v>
+        <v>12.32809352874756</v>
       </c>
       <c r="C300" t="n">
-        <v>12.41466659053087</v>
+        <v>12.41466755090237</v>
       </c>
       <c r="D300" t="n">
-        <v>12.07702892100332</v>
+        <v>12.0770298552559</v>
       </c>
       <c r="E300" t="n">
-        <v>12.08568648767528</v>
+        <v>12.08568742259759</v>
       </c>
       <c r="F300" t="n">
         <v>7376500</v>
@@ -6432,16 +6432,16 @@
         <v>45084</v>
       </c>
       <c r="B301" t="n">
-        <v>12.22420406341553</v>
+        <v>12.22420597076416</v>
       </c>
       <c r="C301" t="n">
-        <v>12.46661014707579</v>
+        <v>12.46661209224716</v>
       </c>
       <c r="D301" t="n">
-        <v>12.21554649687706</v>
+        <v>12.21554840287484</v>
       </c>
       <c r="E301" t="n">
-        <v>12.38003695858405</v>
+        <v>12.38003889024736</v>
       </c>
       <c r="F301" t="n">
         <v>3154600</v>
@@ -6472,16 +6472,16 @@
         <v>45089</v>
       </c>
       <c r="B303" t="n">
-        <v>12.45795440673828</v>
+        <v>12.45795345306396</v>
       </c>
       <c r="C303" t="n">
-        <v>12.45795440673828</v>
+        <v>12.45795345306396</v>
       </c>
       <c r="D303" t="n">
-        <v>12.25883448851593</v>
+        <v>12.25883355008453</v>
       </c>
       <c r="E303" t="n">
-        <v>12.3800379528961</v>
+        <v>12.3800370051864</v>
       </c>
       <c r="F303" t="n">
         <v>2572800</v>
@@ -6552,16 +6552,16 @@
         <v>45093</v>
       </c>
       <c r="B307" t="n">
-        <v>12.62244415283203</v>
+        <v>12.62244319915771</v>
       </c>
       <c r="C307" t="n">
-        <v>12.83022081425066</v>
+        <v>12.83021984487801</v>
       </c>
       <c r="D307" t="n">
-        <v>12.44063936768297</v>
+        <v>12.4406384277447</v>
       </c>
       <c r="E307" t="n">
-        <v>12.46661124395253</v>
+        <v>12.46661030205199</v>
       </c>
       <c r="F307" t="n">
         <v>5319000</v>
@@ -6572,16 +6572,16 @@
         <v>45096</v>
       </c>
       <c r="B308" t="n">
-        <v>12.6137866973877</v>
+        <v>12.61378574371338</v>
       </c>
       <c r="C308" t="n">
-        <v>12.80424905152594</v>
+        <v>12.80424808345158</v>
       </c>
       <c r="D308" t="n">
-        <v>12.38869572500366</v>
+        <v>12.38869478834751</v>
       </c>
       <c r="E308" t="n">
-        <v>12.80424905152594</v>
+        <v>12.80424808345158</v>
       </c>
       <c r="F308" t="n">
         <v>3301400</v>
@@ -6592,16 +6592,16 @@
         <v>45097</v>
       </c>
       <c r="B309" t="n">
-        <v>12.72633266448975</v>
+        <v>12.72633171081543</v>
       </c>
       <c r="C309" t="n">
-        <v>12.89947988480048</v>
+        <v>12.89947891815102</v>
       </c>
       <c r="D309" t="n">
-        <v>12.64841620894215</v>
+        <v>12.64841526110666</v>
       </c>
       <c r="E309" t="n">
-        <v>12.6917032204276</v>
+        <v>12.69170226934831</v>
       </c>
       <c r="F309" t="n">
         <v>3568000</v>
@@ -6612,16 +6612,16 @@
         <v>45098</v>
       </c>
       <c r="B310" t="n">
-        <v>12.86485004425049</v>
+        <v>12.86484909057617</v>
       </c>
       <c r="C310" t="n">
-        <v>12.90813705440186</v>
+        <v>12.90813609751867</v>
       </c>
       <c r="D310" t="n">
-        <v>12.63975907759925</v>
+        <v>12.63975814061098</v>
       </c>
       <c r="E310" t="n">
-        <v>12.75230414810935</v>
+        <v>12.75230320277808</v>
       </c>
       <c r="F310" t="n">
         <v>5022600</v>
@@ -6652,16 +6652,16 @@
         <v>45100</v>
       </c>
       <c r="B312" t="n">
-        <v>12.9427661895752</v>
+        <v>12.94276714324951</v>
       </c>
       <c r="C312" t="n">
-        <v>13.07262721694078</v>
+        <v>13.07262818018377</v>
       </c>
       <c r="D312" t="n">
-        <v>12.7609614117682</v>
+        <v>12.76096235204642</v>
       </c>
       <c r="E312" t="n">
-        <v>12.81290598784064</v>
+        <v>12.81290693194634</v>
       </c>
       <c r="F312" t="n">
         <v>2959500</v>
@@ -6672,16 +6672,16 @@
         <v>45103</v>
       </c>
       <c r="B313" t="n">
-        <v>12.71767425537109</v>
+        <v>12.71767520904541</v>
       </c>
       <c r="C313" t="n">
-        <v>13.01202492323384</v>
+        <v>13.01202589898095</v>
       </c>
       <c r="D313" t="n">
-        <v>12.66573050553121</v>
+        <v>12.66573145531036</v>
       </c>
       <c r="E313" t="n">
-        <v>12.94276603969331</v>
+        <v>12.94276701024684</v>
       </c>
       <c r="F313" t="n">
         <v>2677600</v>
@@ -6692,16 +6692,16 @@
         <v>45104</v>
       </c>
       <c r="B314" t="n">
-        <v>12.50123977661133</v>
+        <v>12.50124073028564</v>
       </c>
       <c r="C314" t="n">
-        <v>12.83887744603771</v>
+        <v>12.83887842546918</v>
       </c>
       <c r="D314" t="n">
-        <v>12.3973514534719</v>
+        <v>12.39735239922096</v>
       </c>
       <c r="E314" t="n">
-        <v>12.76961856394476</v>
+        <v>12.76961953809272</v>
       </c>
       <c r="F314" t="n">
         <v>3014700</v>
@@ -6792,16 +6792,16 @@
         <v>45111</v>
       </c>
       <c r="B319" t="n">
-        <v>12.34540748596191</v>
+        <v>12.34540843963623</v>
       </c>
       <c r="C319" t="n">
-        <v>12.40600880031166</v>
+        <v>12.40600975866739</v>
       </c>
       <c r="D319" t="n">
-        <v>12.23286159814739</v>
+        <v>12.23286254312761</v>
       </c>
       <c r="E319" t="n">
-        <v>12.38869449291073</v>
+        <v>12.38869544992894</v>
       </c>
       <c r="F319" t="n">
         <v>2230100</v>
@@ -6832,16 +6832,16 @@
         <v>45113</v>
       </c>
       <c r="B321" t="n">
-        <v>12.32809257507324</v>
+        <v>12.32809352874756</v>
       </c>
       <c r="C321" t="n">
-        <v>12.48392547264458</v>
+        <v>12.48392643837378</v>
       </c>
       <c r="D321" t="n">
-        <v>12.25017612628758</v>
+        <v>12.25017707393445</v>
       </c>
       <c r="E321" t="n">
-        <v>12.4319808982438</v>
+        <v>12.43198185995469</v>
       </c>
       <c r="F321" t="n">
         <v>2081000</v>
@@ -6852,16 +6852,16 @@
         <v>45114</v>
       </c>
       <c r="B322" t="n">
-        <v>12.34540748596191</v>
+        <v>12.34540843963623</v>
       </c>
       <c r="C322" t="n">
-        <v>12.48392524769333</v>
+        <v>12.48392621206805</v>
       </c>
       <c r="D322" t="n">
-        <v>12.25883347206429</v>
+        <v>12.25883441905082</v>
       </c>
       <c r="E322" t="n">
-        <v>12.42332393334358</v>
+        <v>12.42332489303689</v>
       </c>
       <c r="F322" t="n">
         <v>2149700</v>
@@ -6892,16 +6892,16 @@
         <v>45118</v>
       </c>
       <c r="B324" t="n">
-        <v>12.34540748596191</v>
+        <v>12.34540843963623</v>
       </c>
       <c r="C324" t="n">
-        <v>12.3973512337957</v>
+        <v>12.39735219148264</v>
       </c>
       <c r="D324" t="n">
-        <v>12.23286159814739</v>
+        <v>12.23286254312761</v>
       </c>
       <c r="E324" t="n">
-        <v>12.38869449291073</v>
+        <v>12.38869544992894</v>
       </c>
       <c r="F324" t="n">
         <v>1919200</v>
@@ -7072,16 +7072,16 @@
         <v>45131</v>
       </c>
       <c r="B333" t="n">
-        <v>12.34540748596191</v>
+        <v>12.34540843963623</v>
       </c>
       <c r="C333" t="n">
-        <v>12.42332393334358</v>
+        <v>12.42332489303689</v>
       </c>
       <c r="D333" t="n">
-        <v>12.31943478641403</v>
+        <v>12.31943573808198</v>
       </c>
       <c r="E333" t="n">
-        <v>12.42332393334358</v>
+        <v>12.42332489303689</v>
       </c>
       <c r="F333" t="n">
         <v>1347200</v>
@@ -7092,16 +7092,16 @@
         <v>45132</v>
       </c>
       <c r="B334" t="n">
-        <v>12.17226219177246</v>
+        <v>12.17226123809814</v>
       </c>
       <c r="C334" t="n">
-        <v>12.47526963664793</v>
+        <v>12.47526865923354</v>
       </c>
       <c r="D334" t="n">
-        <v>12.16360462389945</v>
+        <v>12.16360367090343</v>
       </c>
       <c r="E334" t="n">
-        <v>12.41466831279906</v>
+        <v>12.41466734013267</v>
       </c>
       <c r="F334" t="n">
         <v>2710400</v>
@@ -7132,16 +7132,16 @@
         <v>45134</v>
       </c>
       <c r="B336" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C336" t="n">
-        <v>12.22420541473304</v>
+        <v>12.22420445012837</v>
       </c>
       <c r="D336" t="n">
-        <v>12.03374305798708</v>
+        <v>12.03374210841168</v>
       </c>
       <c r="E336" t="n">
-        <v>12.18091840288654</v>
+        <v>12.18091744169762</v>
       </c>
       <c r="F336" t="n">
         <v>2852900</v>
@@ -7212,16 +7212,16 @@
         <v>45140</v>
       </c>
       <c r="B340" t="n">
-        <v>12.22420406341553</v>
+        <v>12.22420597076416</v>
       </c>
       <c r="C340" t="n">
-        <v>12.232861629954</v>
+        <v>12.23286353865348</v>
       </c>
       <c r="D340" t="n">
-        <v>12.12897330838532</v>
+        <v>12.12897520087505</v>
       </c>
       <c r="E340" t="n">
-        <v>12.13763087492379</v>
+        <v>12.13763276876436</v>
       </c>
       <c r="F340" t="n">
         <v>1697600</v>
@@ -7292,16 +7292,16 @@
         <v>45146</v>
       </c>
       <c r="B344" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C344" t="n">
-        <v>12.15494652603107</v>
+        <v>12.15494556689158</v>
       </c>
       <c r="D344" t="n">
-        <v>11.92985472493413</v>
+        <v>11.92985378355649</v>
       </c>
       <c r="E344" t="n">
-        <v>11.99045687177166</v>
+        <v>11.99045592561195</v>
       </c>
       <c r="F344" t="n">
         <v>2176400</v>
@@ -7332,16 +7332,16 @@
         <v>45148</v>
       </c>
       <c r="B346" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C346" t="n">
-        <v>12.09434452900206</v>
+        <v>12.09434549372545</v>
       </c>
       <c r="D346" t="n">
-        <v>11.88656704887551</v>
+        <v>11.88656799702522</v>
       </c>
       <c r="E346" t="n">
-        <v>12.01642807715848</v>
+        <v>12.01642903566675</v>
       </c>
       <c r="F346" t="n">
         <v>2835300</v>
@@ -7352,16 +7352,16 @@
         <v>45149</v>
       </c>
       <c r="B347" t="n">
-        <v>11.92119693756104</v>
+        <v>11.92119789123535</v>
       </c>
       <c r="C347" t="n">
-        <v>11.97314068671642</v>
+        <v>11.97314164454614</v>
       </c>
       <c r="D347" t="n">
-        <v>11.83462292146072</v>
+        <v>11.83462386820927</v>
       </c>
       <c r="E347" t="n">
-        <v>11.97314068671642</v>
+        <v>11.97314164454614</v>
       </c>
       <c r="F347" t="n">
         <v>2472600</v>
@@ -7372,16 +7372,16 @@
         <v>45152</v>
       </c>
       <c r="B348" t="n">
-        <v>11.91254043579102</v>
+        <v>11.9125394821167</v>
       </c>
       <c r="C348" t="n">
-        <v>11.96448418959011</v>
+        <v>11.96448323175737</v>
       </c>
       <c r="D348" t="n">
-        <v>11.82596641195109</v>
+        <v>11.82596546520757</v>
       </c>
       <c r="E348" t="n">
-        <v>11.92119800330122</v>
+        <v>11.92119704893382</v>
       </c>
       <c r="F348" t="n">
         <v>1369900</v>
@@ -7392,16 +7392,16 @@
         <v>45153</v>
       </c>
       <c r="B349" t="n">
-        <v>11.860595703125</v>
+        <v>11.86059474945068</v>
       </c>
       <c r="C349" t="n">
-        <v>11.99911347897441</v>
+        <v>11.9991125141623</v>
       </c>
       <c r="D349" t="n">
-        <v>11.85193813572664</v>
+        <v>11.85193718274846</v>
       </c>
       <c r="E349" t="n">
-        <v>11.91254028188406</v>
+        <v>11.91253932403304</v>
       </c>
       <c r="F349" t="n">
         <v>2713800</v>
@@ -7412,16 +7412,16 @@
         <v>45154</v>
       </c>
       <c r="B350" t="n">
-        <v>11.6874475479126</v>
+        <v>11.68744850158691</v>
       </c>
       <c r="C350" t="n">
-        <v>11.91253932846828</v>
+        <v>11.91254030050967</v>
       </c>
       <c r="D350" t="n">
-        <v>11.64416054001635</v>
+        <v>11.64416149015853</v>
       </c>
       <c r="E350" t="n">
-        <v>11.88656662835193</v>
+        <v>11.886567598274</v>
       </c>
       <c r="F350" t="n">
         <v>3946200</v>
@@ -7432,16 +7432,16 @@
         <v>45155</v>
       </c>
       <c r="B351" t="n">
-        <v>11.71341991424561</v>
+        <v>11.71342086791992</v>
       </c>
       <c r="C351" t="n">
-        <v>11.78267879953539</v>
+        <v>11.78267975884857</v>
       </c>
       <c r="D351" t="n">
-        <v>11.66147616309379</v>
+        <v>11.66147711253899</v>
       </c>
       <c r="E351" t="n">
-        <v>11.73073504838357</v>
+        <v>11.73073600346764</v>
       </c>
       <c r="F351" t="n">
         <v>2345000</v>
@@ -7452,16 +7452,16 @@
         <v>45156</v>
       </c>
       <c r="B352" t="n">
-        <v>11.77402210235596</v>
+        <v>11.77402114868164</v>
       </c>
       <c r="C352" t="n">
-        <v>11.80865154513102</v>
+        <v>11.80865058865178</v>
       </c>
       <c r="D352" t="n">
-        <v>11.65281863982772</v>
+        <v>11.65281769597066</v>
       </c>
       <c r="E352" t="n">
-        <v>11.71341995827632</v>
+        <v>11.71341900951066</v>
       </c>
       <c r="F352" t="n">
         <v>3061800</v>
@@ -7492,16 +7492,16 @@
         <v>45160</v>
       </c>
       <c r="B354" t="n">
-        <v>11.79999351501465</v>
+        <v>11.79999446868896</v>
       </c>
       <c r="C354" t="n">
-        <v>11.86925239784715</v>
+        <v>11.86925335711897</v>
       </c>
       <c r="D354" t="n">
-        <v>11.73073463218214</v>
+        <v>11.73073558025896</v>
       </c>
       <c r="E354" t="n">
-        <v>11.79133594825283</v>
+        <v>11.79133690122745</v>
       </c>
       <c r="F354" t="n">
         <v>2231700</v>
@@ -7512,16 +7512,16 @@
         <v>45161</v>
       </c>
       <c r="B355" t="n">
-        <v>11.87791061401367</v>
+        <v>11.87790966033936</v>
       </c>
       <c r="C355" t="n">
-        <v>11.89522492285292</v>
+        <v>11.89522396778845</v>
       </c>
       <c r="D355" t="n">
-        <v>11.79133659292425</v>
+        <v>11.79133564620093</v>
       </c>
       <c r="E355" t="n">
-        <v>11.86059547954337</v>
+        <v>11.86059452725928</v>
       </c>
       <c r="F355" t="n">
         <v>2615000</v>
@@ -7532,16 +7532,16 @@
         <v>45162</v>
       </c>
       <c r="B356" t="n">
-        <v>11.97314167022705</v>
+        <v>11.97314071655273</v>
       </c>
       <c r="C356" t="n">
-        <v>11.99911354693815</v>
+        <v>11.99911259119515</v>
       </c>
       <c r="D356" t="n">
-        <v>11.89522521446267</v>
+        <v>11.89522426699448</v>
       </c>
       <c r="E356" t="n">
-        <v>11.90388278191006</v>
+        <v>11.90388183375229</v>
       </c>
       <c r="F356" t="n">
         <v>2322800</v>
@@ -7612,16 +7612,16 @@
         <v>45168</v>
       </c>
       <c r="B360" t="n">
-        <v>12.11165809631348</v>
+        <v>12.11165904998779</v>
       </c>
       <c r="C360" t="n">
-        <v>12.19823210987155</v>
+        <v>12.19823307036272</v>
       </c>
       <c r="D360" t="n">
-        <v>12.05971434868342</v>
+        <v>12.05971529826767</v>
       </c>
       <c r="E360" t="n">
-        <v>12.17226023605652</v>
+        <v>12.17226119450266</v>
       </c>
       <c r="F360" t="n">
         <v>1998700</v>
@@ -7652,16 +7652,16 @@
         <v>45170</v>
       </c>
       <c r="B362" t="n">
-        <v>12.04240036010742</v>
+        <v>12.04239940643311</v>
       </c>
       <c r="C362" t="n">
-        <v>12.04240036010742</v>
+        <v>12.04239940643311</v>
       </c>
       <c r="D362" t="n">
-        <v>11.89522501845123</v>
+        <v>11.89522407643217</v>
       </c>
       <c r="E362" t="n">
-        <v>11.90388258575596</v>
+        <v>11.90388164305129</v>
       </c>
       <c r="F362" t="n">
         <v>3740800</v>
@@ -7692,16 +7692,16 @@
         <v>45174</v>
       </c>
       <c r="B364" t="n">
-        <v>11.92119693756104</v>
+        <v>11.92119789123535</v>
       </c>
       <c r="C364" t="n">
-        <v>12.06837144392197</v>
+        <v>12.06837240936998</v>
       </c>
       <c r="D364" t="n">
-        <v>11.9125393708248</v>
+        <v>11.91254032380653</v>
       </c>
       <c r="E364" t="n">
-        <v>12.04239956934427</v>
+        <v>12.04240053271458</v>
       </c>
       <c r="F364" t="n">
         <v>3869600</v>
@@ -7712,16 +7712,16 @@
         <v>45175</v>
       </c>
       <c r="B365" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C365" t="n">
-        <v>12.02508564417022</v>
+        <v>12.02508660336907</v>
       </c>
       <c r="D365" t="n">
-        <v>11.81730816404367</v>
+        <v>11.81730910666884</v>
       </c>
       <c r="E365" t="n">
-        <v>11.9385116253149</v>
+        <v>11.93851257760805</v>
       </c>
       <c r="F365" t="n">
         <v>2473500</v>
@@ -7732,16 +7732,16 @@
         <v>45177</v>
       </c>
       <c r="B366" t="n">
-        <v>11.92985439300537</v>
+        <v>11.92985343933105</v>
       </c>
       <c r="C366" t="n">
-        <v>12.07702973380992</v>
+        <v>12.07702876837038</v>
       </c>
       <c r="D366" t="n">
-        <v>11.88656738236326</v>
+        <v>11.88656643214931</v>
       </c>
       <c r="E366" t="n">
-        <v>11.93851196026</v>
+        <v>11.9385110058936</v>
       </c>
       <c r="F366" t="n">
         <v>3462800</v>
@@ -7812,16 +7812,16 @@
         <v>45183</v>
       </c>
       <c r="B370" t="n">
-        <v>12.21554756164551</v>
+        <v>12.21554660797119</v>
       </c>
       <c r="C370" t="n">
-        <v>12.25017700518688</v>
+        <v>12.25017604880902</v>
       </c>
       <c r="D370" t="n">
-        <v>12.09434492206624</v>
+        <v>12.09434397785428</v>
       </c>
       <c r="E370" t="n">
-        <v>12.09434492206624</v>
+        <v>12.09434397785428</v>
       </c>
       <c r="F370" t="n">
         <v>2498700</v>
@@ -7852,16 +7852,16 @@
         <v>45187</v>
       </c>
       <c r="B372" t="n">
-        <v>12.05971622467041</v>
+        <v>12.05971527099609</v>
       </c>
       <c r="C372" t="n">
-        <v>12.2415210209188</v>
+        <v>12.24152005286748</v>
       </c>
       <c r="D372" t="n">
-        <v>11.99911407550021</v>
+        <v>11.99911312661827</v>
       </c>
       <c r="E372" t="n">
-        <v>12.21554831743252</v>
+        <v>12.21554735143511</v>
       </c>
       <c r="F372" t="n">
         <v>3188500</v>
@@ -7912,16 +7912,16 @@
         <v>45190</v>
       </c>
       <c r="B375" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C375" t="n">
-        <v>12.03374238555092</v>
+        <v>12.0337433454403</v>
       </c>
       <c r="D375" t="n">
-        <v>11.8779103074948</v>
+        <v>11.877911254954</v>
       </c>
       <c r="E375" t="n">
-        <v>12.02508564417022</v>
+        <v>12.02508660336907</v>
       </c>
       <c r="F375" t="n">
         <v>4405700</v>
@@ -7932,16 +7932,16 @@
         <v>45191</v>
       </c>
       <c r="B376" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C376" t="n">
-        <v>12.10300127038276</v>
+        <v>12.10300223579667</v>
       </c>
       <c r="D376" t="n">
-        <v>11.92985405830317</v>
+        <v>11.92985500990573</v>
       </c>
       <c r="E376" t="n">
-        <v>12.02508564417022</v>
+        <v>12.02508660336907</v>
       </c>
       <c r="F376" t="n">
         <v>2812600</v>
@@ -7952,16 +7952,16 @@
         <v>45194</v>
       </c>
       <c r="B377" t="n">
-        <v>11.8086519241333</v>
+        <v>11.80865097045898</v>
       </c>
       <c r="C377" t="n">
-        <v>11.97314157618643</v>
+        <v>11.97314060922783</v>
       </c>
       <c r="D377" t="n">
-        <v>11.8086519241333</v>
+        <v>11.80865097045898</v>
       </c>
       <c r="E377" t="n">
-        <v>11.95582726705872</v>
+        <v>11.95582630149842</v>
       </c>
       <c r="F377" t="n">
         <v>3691700</v>
@@ -7972,16 +7972,16 @@
         <v>45195</v>
       </c>
       <c r="B378" t="n">
-        <v>11.83462238311768</v>
+        <v>11.83462333679199</v>
       </c>
       <c r="C378" t="n">
-        <v>12.06837089494598</v>
+        <v>12.06837186745655</v>
       </c>
       <c r="D378" t="n">
-        <v>11.78267781069418</v>
+        <v>11.78267876018263</v>
       </c>
       <c r="E378" t="n">
-        <v>11.80865050972141</v>
+        <v>11.80865146130283</v>
       </c>
       <c r="F378" t="n">
         <v>7795500</v>
@@ -8072,16 +8072,16 @@
         <v>45202</v>
       </c>
       <c r="B383" t="n">
-        <v>11.8086519241333</v>
+        <v>11.80865097045898</v>
       </c>
       <c r="C383" t="n">
-        <v>11.91254025579282</v>
+        <v>11.91253929372841</v>
       </c>
       <c r="D383" t="n">
-        <v>11.75670734548801</v>
+        <v>11.75670639600877</v>
       </c>
       <c r="E383" t="n">
-        <v>11.86059567714752</v>
+        <v>11.8605947192782</v>
       </c>
       <c r="F383" t="n">
         <v>2809600</v>
@@ -8092,16 +8092,16 @@
         <v>45203</v>
       </c>
       <c r="B384" t="n">
-        <v>11.77402210235596</v>
+        <v>11.77402114868164</v>
       </c>
       <c r="C384" t="n">
-        <v>11.86059529647809</v>
+        <v>11.86059433579151</v>
       </c>
       <c r="D384" t="n">
-        <v>11.74804940105138</v>
+        <v>11.7480484494808</v>
       </c>
       <c r="E384" t="n">
-        <v>11.80865154513102</v>
+        <v>11.80865058865178</v>
       </c>
       <c r="F384" t="n">
         <v>4367600</v>
@@ -8152,16 +8152,16 @@
         <v>45208</v>
       </c>
       <c r="B387" t="n">
-        <v>11.91254043579102</v>
+        <v>11.9125394821167</v>
       </c>
       <c r="C387" t="n">
-        <v>11.92985474518035</v>
+        <v>11.92985379011992</v>
       </c>
       <c r="D387" t="n">
-        <v>11.61818974549255</v>
+        <v>11.61818881538288</v>
       </c>
       <c r="E387" t="n">
-        <v>11.61818974549255</v>
+        <v>11.61818881538288</v>
       </c>
       <c r="F387" t="n">
         <v>4118900</v>
@@ -8172,16 +8172,16 @@
         <v>45209</v>
       </c>
       <c r="B388" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C388" t="n">
-        <v>12.16360409352659</v>
+        <v>12.16360313370393</v>
       </c>
       <c r="D388" t="n">
-        <v>11.91254041557417</v>
+        <v>11.9125394755628</v>
       </c>
       <c r="E388" t="n">
-        <v>11.92985472493413</v>
+        <v>11.92985378355649</v>
       </c>
       <c r="F388" t="n">
         <v>3643400</v>
@@ -8192,16 +8192,16 @@
         <v>45210</v>
       </c>
       <c r="B389" t="n">
-        <v>12.09434413909912</v>
+        <v>12.09434509277344</v>
       </c>
       <c r="C389" t="n">
-        <v>12.18957489626505</v>
+        <v>12.18957585744859</v>
       </c>
       <c r="D389" t="n">
-        <v>12.00777012303482</v>
+        <v>12.00777106988252</v>
       </c>
       <c r="E389" t="n">
-        <v>12.09434413909912</v>
+        <v>12.09434509277344</v>
       </c>
       <c r="F389" t="n">
         <v>3458500</v>
@@ -8212,16 +8212,16 @@
         <v>45212</v>
       </c>
       <c r="B390" t="n">
-        <v>12.02508544921875</v>
+        <v>12.02508640289307</v>
       </c>
       <c r="C390" t="n">
-        <v>12.19823265849127</v>
+        <v>12.19823362589739</v>
       </c>
       <c r="D390" t="n">
-        <v>12.02508544921875</v>
+        <v>12.02508640289307</v>
       </c>
       <c r="E390" t="n">
-        <v>12.09434433292776</v>
+        <v>12.0943452920948</v>
       </c>
       <c r="F390" t="n">
         <v>4555500</v>
@@ -8232,16 +8232,16 @@
         <v>45215</v>
       </c>
       <c r="B391" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="C391" t="n">
-        <v>12.12031593631109</v>
+        <v>12.12031690101054</v>
       </c>
       <c r="D391" t="n">
-        <v>11.98179817199707</v>
+        <v>11.98179912567139</v>
       </c>
       <c r="E391" t="n">
-        <v>12.05971462083146</v>
+        <v>12.05971558070743</v>
       </c>
       <c r="F391" t="n">
         <v>3983600</v>
@@ -8252,16 +8252,16 @@
         <v>45216</v>
       </c>
       <c r="B392" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C392" t="n">
-        <v>12.10300127038276</v>
+        <v>12.10300223579667</v>
       </c>
       <c r="D392" t="n">
-        <v>11.88656704887551</v>
+        <v>11.88656799702522</v>
       </c>
       <c r="E392" t="n">
-        <v>11.97314106773082</v>
+        <v>11.97314202278624</v>
       </c>
       <c r="F392" t="n">
         <v>5165000</v>
@@ -8312,16 +8312,16 @@
         <v>45219</v>
       </c>
       <c r="B395" t="n">
-        <v>11.76536560058594</v>
+        <v>11.76536464691162</v>
       </c>
       <c r="C395" t="n">
-        <v>11.91254095211416</v>
+        <v>11.91253998651014</v>
       </c>
       <c r="D395" t="n">
-        <v>11.67013400510819</v>
+        <v>11.67013305915314</v>
       </c>
       <c r="E395" t="n">
-        <v>11.67013400510819</v>
+        <v>11.67013305915314</v>
       </c>
       <c r="F395" t="n">
         <v>6261200</v>
@@ -8352,16 +8352,16 @@
         <v>45223</v>
       </c>
       <c r="B397" t="n">
-        <v>11.6355037689209</v>
+        <v>11.63550281524658</v>
       </c>
       <c r="C397" t="n">
-        <v>11.81730855401174</v>
+        <v>11.81730758543626</v>
       </c>
       <c r="D397" t="n">
-        <v>11.54893057283972</v>
+        <v>11.54892962626116</v>
       </c>
       <c r="E397" t="n">
-        <v>11.80865181234537</v>
+        <v>11.80865084447942</v>
       </c>
       <c r="F397" t="n">
         <v>3637500</v>
@@ -8512,16 +8512,16 @@
         <v>45236</v>
       </c>
       <c r="B405" t="n">
-        <v>12.02508544921875</v>
+        <v>12.02508640289307</v>
       </c>
       <c r="C405" t="n">
-        <v>12.077029199185</v>
+        <v>12.07703015697882</v>
       </c>
       <c r="D405" t="n">
-        <v>11.8173079724607</v>
+        <v>11.81730890965679</v>
       </c>
       <c r="E405" t="n">
-        <v>11.94716899863836</v>
+        <v>11.94716994613335</v>
       </c>
       <c r="F405" t="n">
         <v>2982900</v>
@@ -8552,16 +8552,16 @@
         <v>45238</v>
       </c>
       <c r="B407" t="n">
-        <v>11.817307472229</v>
+        <v>11.81730842590332</v>
       </c>
       <c r="C407" t="n">
-        <v>11.96448280028841</v>
+        <v>11.96448376583999</v>
       </c>
       <c r="D407" t="n">
-        <v>11.73073428407293</v>
+        <v>11.73073523076066</v>
       </c>
       <c r="E407" t="n">
-        <v>11.93851092640469</v>
+        <v>11.9385118898603</v>
       </c>
       <c r="F407" t="n">
         <v>5488500</v>
@@ -8652,16 +8652,16 @@
         <v>45246</v>
       </c>
       <c r="B412" t="n">
-        <v>12.49258422851562</v>
+        <v>12.49258327484131</v>
       </c>
       <c r="C412" t="n">
-        <v>12.49258422851562</v>
+        <v>12.49258327484131</v>
       </c>
       <c r="D412" t="n">
-        <v>12.12897464999031</v>
+        <v>12.12897372407367</v>
       </c>
       <c r="E412" t="n">
-        <v>12.12897464999031</v>
+        <v>12.12897372407367</v>
       </c>
       <c r="F412" t="n">
         <v>6741500</v>
@@ -8672,16 +8672,16 @@
         <v>45247</v>
       </c>
       <c r="B413" t="n">
-        <v>12.25017738342285</v>
+        <v>12.25017642974854</v>
       </c>
       <c r="C413" t="n">
-        <v>12.48392675376763</v>
+        <v>12.48392578189597</v>
       </c>
       <c r="D413" t="n">
-        <v>12.14628904959109</v>
+        <v>12.14628810400446</v>
       </c>
       <c r="E413" t="n">
-        <v>12.48392675376763</v>
+        <v>12.48392578189597</v>
       </c>
       <c r="F413" t="n">
         <v>3124800</v>
@@ -8692,16 +8692,16 @@
         <v>45250</v>
       </c>
       <c r="B414" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C414" t="n">
-        <v>12.23286298222856</v>
+        <v>12.23286201694073</v>
       </c>
       <c r="D414" t="n">
-        <v>11.99045687177166</v>
+        <v>11.99045592561195</v>
       </c>
       <c r="E414" t="n">
-        <v>12.20689110537309</v>
+        <v>12.20689014213468</v>
       </c>
       <c r="F414" t="n">
         <v>3248400</v>
@@ -8712,16 +8712,16 @@
         <v>45251</v>
       </c>
       <c r="B415" t="n">
-        <v>11.97314167022705</v>
+        <v>11.97314071655273</v>
       </c>
       <c r="C415" t="n">
-        <v>12.09434513759732</v>
+        <v>12.09434417426901</v>
       </c>
       <c r="D415" t="n">
-        <v>11.91254034935745</v>
+        <v>11.9125394005101</v>
       </c>
       <c r="E415" t="n">
-        <v>12.08568757014993</v>
+        <v>12.0856866075112</v>
       </c>
       <c r="F415" t="n">
         <v>2713400</v>
@@ -8752,16 +8752,16 @@
         <v>45253</v>
       </c>
       <c r="B417" t="n">
-        <v>12.561842918396</v>
+        <v>12.56184196472168</v>
       </c>
       <c r="C417" t="n">
-        <v>12.76961958122722</v>
+        <v>12.76961861177884</v>
       </c>
       <c r="D417" t="n">
-        <v>12.46661132870839</v>
+        <v>12.46661038226389</v>
       </c>
       <c r="E417" t="n">
-        <v>12.76961958122722</v>
+        <v>12.76961861177884</v>
       </c>
       <c r="F417" t="n">
         <v>9122900</v>
@@ -8832,16 +8832,16 @@
         <v>45259</v>
       </c>
       <c r="B421" t="n">
-        <v>12.561842918396</v>
+        <v>12.56184196472168</v>
       </c>
       <c r="C421" t="n">
-        <v>12.75230444650908</v>
+        <v>12.75230347837524</v>
       </c>
       <c r="D421" t="n">
-        <v>12.561842918396</v>
+        <v>12.56184196472168</v>
       </c>
       <c r="E421" t="n">
-        <v>12.72633257006295</v>
+        <v>12.72633160390085</v>
       </c>
       <c r="F421" t="n">
         <v>5869600</v>
@@ -8852,16 +8852,16 @@
         <v>45260</v>
       </c>
       <c r="B422" t="n">
-        <v>12.71767425537109</v>
+        <v>12.71767520904541</v>
       </c>
       <c r="C422" t="n">
-        <v>12.71767425537109</v>
+        <v>12.71767520904541</v>
       </c>
       <c r="D422" t="n">
-        <v>12.58781405514036</v>
+        <v>12.58781499907671</v>
       </c>
       <c r="E422" t="n">
-        <v>12.63110106376094</v>
+        <v>12.6311020109433</v>
       </c>
       <c r="F422" t="n">
         <v>4162000</v>
@@ -8872,16 +8872,16 @@
         <v>45261</v>
       </c>
       <c r="B423" t="n">
-        <v>12.86485004425049</v>
+        <v>12.86484909057617</v>
       </c>
       <c r="C423" t="n">
-        <v>12.96873837323515</v>
+        <v>12.96873741185957</v>
       </c>
       <c r="D423" t="n">
-        <v>12.70901796358902</v>
+        <v>12.70901702146657</v>
       </c>
       <c r="E423" t="n">
-        <v>12.72633227227094</v>
+        <v>12.72633132886498</v>
       </c>
       <c r="F423" t="n">
         <v>6458300</v>
@@ -8892,16 +8892,16 @@
         <v>45264</v>
       </c>
       <c r="B424" t="n">
-        <v>12.89947986602783</v>
+        <v>12.89947891235352</v>
       </c>
       <c r="C424" t="n">
-        <v>12.98605388887275</v>
+        <v>12.98605292879791</v>
       </c>
       <c r="D424" t="n">
-        <v>12.86485042201608</v>
+        <v>12.86484947090196</v>
       </c>
       <c r="E424" t="n">
-        <v>12.94276687745029</v>
+        <v>12.94276592057571</v>
       </c>
       <c r="F424" t="n">
         <v>7048400</v>
@@ -8952,16 +8952,16 @@
         <v>45267</v>
       </c>
       <c r="B427" t="n">
-        <v>13.11591339111328</v>
+        <v>13.1159143447876</v>
       </c>
       <c r="C427" t="n">
-        <v>13.15054283325996</v>
+        <v>13.15054378945223</v>
       </c>
       <c r="D427" t="n">
-        <v>12.97739562252655</v>
+        <v>12.97739656612907</v>
       </c>
       <c r="E427" t="n">
-        <v>13.10725664979988</v>
+        <v>13.10725760284475</v>
       </c>
       <c r="F427" t="n">
         <v>6196000</v>
@@ -8972,16 +8972,16 @@
         <v>45268</v>
       </c>
       <c r="B428" t="n">
-        <v>12.92545127868652</v>
+        <v>12.92545223236084</v>
       </c>
       <c r="C428" t="n">
-        <v>13.15919979603697</v>
+        <v>13.15920076695787</v>
       </c>
       <c r="D428" t="n">
-        <v>12.86484913848894</v>
+        <v>12.86485008769187</v>
       </c>
       <c r="E428" t="n">
-        <v>13.15919979603697</v>
+        <v>13.15920076695787</v>
       </c>
       <c r="F428" t="n">
         <v>10990100</v>
@@ -22149,162 +22149,142 @@
     </row>
     <row r="1087">
       <c r="A1087" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B1087" t="n">
-        <v>10.97999954223633</v>
+        <v>11.19999980926514</v>
       </c>
       <c r="C1087" t="n">
-        <v>11.27999973297119</v>
+        <v>11.21000003814697</v>
       </c>
       <c r="D1087" t="n">
-        <v>10.90999984741211</v>
+        <v>10.84000015258789</v>
       </c>
       <c r="E1087" t="n">
-        <v>11.19999980926514</v>
+        <v>11.03999996185303</v>
       </c>
       <c r="F1087" t="n">
-        <v>5442500</v>
+        <v>4621900</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B1088" t="n">
-        <v>11.19999980926514</v>
+        <v>11.27999973297119</v>
       </c>
       <c r="C1088" t="n">
-        <v>11.21000003814697</v>
+        <v>11.56999969482422</v>
       </c>
       <c r="D1088" t="n">
-        <v>10.84000015258789</v>
+        <v>11.13000011444092</v>
       </c>
       <c r="E1088" t="n">
-        <v>11.03999996185303</v>
+        <v>11.32999992370605</v>
       </c>
       <c r="F1088" t="n">
-        <v>4621900</v>
+        <v>4289500</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B1089" t="n">
-        <v>11.27999973297119</v>
+        <v>11.15999984741211</v>
       </c>
       <c r="C1089" t="n">
-        <v>11.56999969482422</v>
+        <v>11.55000019073486</v>
       </c>
       <c r="D1089" t="n">
-        <v>11.13000011444092</v>
+        <v>11.07999992370605</v>
       </c>
       <c r="E1089" t="n">
-        <v>11.32999992370605</v>
+        <v>11.31999969482422</v>
       </c>
       <c r="F1089" t="n">
-        <v>4289500</v>
+        <v>5192700</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B1090" t="n">
-        <v>11.15999984741211</v>
+        <v>10.97999954223633</v>
       </c>
       <c r="C1090" t="n">
-        <v>11.55000019073486</v>
+        <v>11.14000034332275</v>
       </c>
       <c r="D1090" t="n">
-        <v>11.07999992370605</v>
+        <v>10.61999988555908</v>
       </c>
       <c r="E1090" t="n">
-        <v>11.31999969482422</v>
+        <v>11.14000034332275</v>
       </c>
       <c r="F1090" t="n">
-        <v>5192700</v>
+        <v>5195300</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B1091" t="n">
+        <v>10.8100004196167</v>
+      </c>
+      <c r="C1091" t="n">
         <v>10.97999954223633</v>
       </c>
-      <c r="C1091" t="n">
-        <v>11.14000034332275</v>
-      </c>
       <c r="D1091" t="n">
-        <v>10.61999988555908</v>
+        <v>10.55000019073486</v>
       </c>
       <c r="E1091" t="n">
-        <v>11.14000034332275</v>
+        <v>10.97999954223633</v>
       </c>
       <c r="F1091" t="n">
-        <v>5195300</v>
+        <v>4285100</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B1092" t="n">
-        <v>10.8100004196167</v>
+        <v>10.53999996185303</v>
       </c>
       <c r="C1092" t="n">
-        <v>10.97999954223633</v>
+        <v>10.88000011444092</v>
       </c>
       <c r="D1092" t="n">
-        <v>10.55000019073486</v>
+        <v>10.5</v>
       </c>
       <c r="E1092" t="n">
-        <v>10.97999954223633</v>
+        <v>10.65999984741211</v>
       </c>
       <c r="F1092" t="n">
-        <v>4285100</v>
+        <v>3147300</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B1093" t="n">
-        <v>10.69999980926514</v>
+        <v>10.38</v>
       </c>
       <c r="C1093" t="n">
-        <v>10.82999992370605</v>
+        <v>10.61</v>
       </c>
       <c r="D1093" t="n">
-        <v>10.5600004196167</v>
+        <v>10.22</v>
       </c>
       <c r="E1093" t="n">
-        <v>10.80000019073486</v>
+        <v>10.59</v>
       </c>
       <c r="F1093" t="n">
-        <v>3624700</v>
-      </c>
-    </row>
-    <row r="1094">
-      <c r="A1094" s="1" t="n">
-        <v>46245</v>
-      </c>
-      <c r="B1094" t="n">
-        <v>10.54</v>
-      </c>
-      <c r="C1094" t="n">
-        <v>10.88</v>
-      </c>
-      <c r="D1094" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="E1094" t="n">
-        <v>10.66</v>
-      </c>
-      <c r="F1094" t="n">
-        <v>3147300</v>
+        <v>6023200</v>
       </c>
     </row>
   </sheetData>

--- a/database/AURE3.xlsx
+++ b/database/AURE3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1093"/>
+  <dimension ref="A1:F1094"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44648</v>
       </c>
       <c r="B2" t="n">
-        <v>12.75723266601562</v>
+        <v>12.75723171234131</v>
       </c>
       <c r="C2" t="n">
-        <v>13.06838439275972</v>
+        <v>13.06838341582507</v>
       </c>
       <c r="D2" t="n">
-        <v>12.02602573724489</v>
+        <v>12.02602483823237</v>
       </c>
       <c r="E2" t="n">
-        <v>13.06838439275972</v>
+        <v>13.06838341582507</v>
       </c>
       <c r="F2" t="n">
         <v>5237900</v>
@@ -472,16 +472,16 @@
         <v>44649</v>
       </c>
       <c r="B3" t="n">
-        <v>12.91281032562256</v>
+        <v>12.91280937194824</v>
       </c>
       <c r="C3" t="n">
-        <v>13.21618309850878</v>
+        <v>13.2161821224289</v>
       </c>
       <c r="D3" t="n">
-        <v>12.6172150483126</v>
+        <v>12.61721411646944</v>
       </c>
       <c r="E3" t="n">
-        <v>12.74945472843788</v>
+        <v>12.74945378682817</v>
       </c>
       <c r="F3" t="n">
         <v>4714100</v>
@@ -492,16 +492,16 @@
         <v>44650</v>
       </c>
       <c r="B4" t="n">
-        <v>12.38385105133057</v>
+        <v>12.38384914398193</v>
       </c>
       <c r="C4" t="n">
-        <v>13.04504942238897</v>
+        <v>13.04504741320321</v>
       </c>
       <c r="D4" t="n">
-        <v>12.30606274584925</v>
+        <v>12.3060608504815</v>
       </c>
       <c r="E4" t="n">
-        <v>12.92836770601126</v>
+        <v>12.9283657147967</v>
       </c>
       <c r="F4" t="n">
         <v>4408600</v>
@@ -512,16 +512,16 @@
         <v>44651</v>
       </c>
       <c r="B5" t="n">
-        <v>12.43830108642578</v>
+        <v>12.4383020401001</v>
       </c>
       <c r="C5" t="n">
-        <v>12.82724108844168</v>
+        <v>12.82724207193696</v>
       </c>
       <c r="D5" t="n">
-        <v>12.05714006249281</v>
+        <v>12.05714098694259</v>
       </c>
       <c r="E5" t="n">
-        <v>12.4149648940212</v>
+        <v>12.41496584590627</v>
       </c>
       <c r="F5" t="n">
         <v>3876100</v>
@@ -532,16 +532,16 @@
         <v>44652</v>
       </c>
       <c r="B6" t="n">
-        <v>12.51609134674072</v>
+        <v>12.51609039306641</v>
       </c>
       <c r="C6" t="n">
-        <v>12.95170380189247</v>
+        <v>12.95170281502629</v>
       </c>
       <c r="D6" t="n">
-        <v>12.31384233592669</v>
+        <v>12.31384139766291</v>
       </c>
       <c r="E6" t="n">
-        <v>12.43830303739862</v>
+        <v>12.43830208965145</v>
       </c>
       <c r="F6" t="n">
         <v>4252000</v>
@@ -552,16 +552,16 @@
         <v>44655</v>
       </c>
       <c r="B7" t="n">
-        <v>12.42274379730225</v>
+        <v>12.42274475097656</v>
       </c>
       <c r="C7" t="n">
-        <v>12.73389624214791</v>
+        <v>12.7338972197089</v>
       </c>
       <c r="D7" t="n">
-        <v>12.3371765225937</v>
+        <v>12.33717746969916</v>
       </c>
       <c r="E7" t="n">
-        <v>12.54720373665866</v>
+        <v>12.54720469988757</v>
       </c>
       <c r="F7" t="n">
         <v>2842400</v>
@@ -612,16 +612,16 @@
         <v>44658</v>
       </c>
       <c r="B10" t="n">
-        <v>12.44608020782471</v>
+        <v>12.44608116149902</v>
       </c>
       <c r="C10" t="n">
-        <v>12.71833850910855</v>
+        <v>12.71833948364451</v>
       </c>
       <c r="D10" t="n">
-        <v>12.20493707738666</v>
+        <v>12.20493801258351</v>
       </c>
       <c r="E10" t="n">
-        <v>12.32161952444153</v>
+        <v>12.32162046857911</v>
       </c>
       <c r="F10" t="n">
         <v>3223900</v>
@@ -652,16 +652,16 @@
         <v>44662</v>
       </c>
       <c r="B12" t="n">
-        <v>12.37607097625732</v>
+        <v>12.37607192993164</v>
       </c>
       <c r="C12" t="n">
-        <v>12.89725064802586</v>
+        <v>12.8972516418612</v>
       </c>
       <c r="D12" t="n">
-        <v>12.37607097625732</v>
+        <v>12.37607192993164</v>
       </c>
       <c r="E12" t="n">
-        <v>12.59387791557601</v>
+        <v>12.59387888603408</v>
       </c>
       <c r="F12" t="n">
         <v>2119500</v>
@@ -692,16 +692,16 @@
         <v>44664</v>
       </c>
       <c r="B14" t="n">
-        <v>12.10381412506104</v>
+        <v>12.10381317138672</v>
       </c>
       <c r="C14" t="n">
-        <v>12.55498376109398</v>
+        <v>12.55498277187146</v>
       </c>
       <c r="D14" t="n">
-        <v>12.08825616769219</v>
+        <v>12.0882552152437</v>
       </c>
       <c r="E14" t="n">
-        <v>12.39162965978653</v>
+        <v>12.39162868343488</v>
       </c>
       <c r="F14" t="n">
         <v>4421300</v>
@@ -712,16 +712,16 @@
         <v>44665</v>
       </c>
       <c r="B15" t="n">
-        <v>12.11159229278564</v>
+        <v>12.11159324645996</v>
       </c>
       <c r="C15" t="n">
-        <v>12.36829265315281</v>
+        <v>12.36829362703988</v>
       </c>
       <c r="D15" t="n">
-        <v>12.04936194735386</v>
+        <v>12.04936289612812</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08047712006975</v>
+        <v>12.08047807129404</v>
       </c>
       <c r="F15" t="n">
         <v>2077400</v>
@@ -752,16 +752,16 @@
         <v>44670</v>
       </c>
       <c r="B17" t="n">
-        <v>12.10381412506104</v>
+        <v>12.10381317138672</v>
       </c>
       <c r="C17" t="n">
-        <v>12.60165763320052</v>
+        <v>12.60165664030051</v>
       </c>
       <c r="D17" t="n">
-        <v>12.00268962769625</v>
+        <v>12.00268868198966</v>
       </c>
       <c r="E17" t="n">
-        <v>12.4383020482046</v>
+        <v>12.43830106817557</v>
       </c>
       <c r="F17" t="n">
         <v>3118100</v>
@@ -792,16 +792,16 @@
         <v>44673</v>
       </c>
       <c r="B19" t="n">
-        <v>12.22049522399902</v>
+        <v>12.22049617767334</v>
       </c>
       <c r="C19" t="n">
-        <v>12.33717693102638</v>
+        <v>12.33717789380641</v>
       </c>
       <c r="D19" t="n">
-        <v>11.80044004011864</v>
+        <v>11.80044096101231</v>
       </c>
       <c r="E19" t="n">
-        <v>12.01824623943035</v>
+        <v>12.01824717732137</v>
       </c>
       <c r="F19" t="n">
         <v>11382300</v>
@@ -872,16 +872,16 @@
         <v>44679</v>
       </c>
       <c r="B23" t="n">
-        <v>11.90934467315674</v>
+        <v>11.90934371948242</v>
       </c>
       <c r="C23" t="n">
-        <v>12.08825674030803</v>
+        <v>12.08825577230682</v>
       </c>
       <c r="D23" t="n">
-        <v>11.49706768548379</v>
+        <v>11.49706676482372</v>
       </c>
       <c r="E23" t="n">
-        <v>12.08825674030803</v>
+        <v>12.08825577230682</v>
       </c>
       <c r="F23" t="n">
         <v>3489600</v>
@@ -912,16 +912,16 @@
         <v>44683</v>
       </c>
       <c r="B25" t="n">
-        <v>11.1703577041626</v>
+        <v>11.17035675048828</v>
       </c>
       <c r="C25" t="n">
-        <v>11.47373120303561</v>
+        <v>11.47373022346064</v>
       </c>
       <c r="D25" t="n">
-        <v>10.96033046789994</v>
+        <v>10.96032953215679</v>
       </c>
       <c r="E25" t="n">
-        <v>11.42705807173043</v>
+        <v>11.4270570961402</v>
       </c>
       <c r="F25" t="n">
         <v>2883200</v>
@@ -1072,16 +1072,16 @@
         <v>44693</v>
       </c>
       <c r="B33" t="n">
-        <v>11.15398979187012</v>
+        <v>11.1539888381958</v>
       </c>
       <c r="C33" t="n">
-        <v>11.27931540236311</v>
+        <v>11.27931443797336</v>
       </c>
       <c r="D33" t="n">
-        <v>10.85634109344948</v>
+        <v>10.85634016522435</v>
       </c>
       <c r="E33" t="n">
-        <v>10.99733277875388</v>
+        <v>10.99733183847385</v>
       </c>
       <c r="F33" t="n">
         <v>1884700</v>
@@ -1152,16 +1152,16 @@
         <v>44699</v>
       </c>
       <c r="B37" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C37" t="n">
-        <v>11.5926298208571</v>
+        <v>11.59262882548476</v>
       </c>
       <c r="D37" t="n">
-        <v>11.03649688106261</v>
+        <v>11.03649593344125</v>
       </c>
       <c r="E37" t="n">
-        <v>11.51430094319608</v>
+        <v>11.51429995454926</v>
       </c>
       <c r="F37" t="n">
         <v>1959900</v>
@@ -1172,16 +1172,16 @@
         <v>44700</v>
       </c>
       <c r="B38" t="n">
-        <v>11.22448444366455</v>
+        <v>11.22448539733887</v>
       </c>
       <c r="C38" t="n">
-        <v>11.25581584296371</v>
+        <v>11.25581679930005</v>
       </c>
       <c r="D38" t="n">
-        <v>10.97383324927132</v>
+        <v>10.97383418164937</v>
       </c>
       <c r="E38" t="n">
-        <v>11.11482417261777</v>
+        <v>11.11482511697494</v>
       </c>
       <c r="F38" t="n">
         <v>2127500</v>
@@ -1192,16 +1192,16 @@
         <v>44701</v>
       </c>
       <c r="B39" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C39" t="n">
-        <v>11.34197786054158</v>
+        <v>11.34197688669085</v>
       </c>
       <c r="D39" t="n">
-        <v>10.86417379840811</v>
+        <v>10.86417286558284</v>
       </c>
       <c r="E39" t="n">
-        <v>11.34197786054158</v>
+        <v>11.34197688669085</v>
       </c>
       <c r="F39" t="n">
         <v>1777400</v>
@@ -1532,16 +1532,16 @@
         <v>44726</v>
       </c>
       <c r="B56" t="n">
-        <v>10.39420127868652</v>
+        <v>10.39420223236084</v>
       </c>
       <c r="C56" t="n">
-        <v>10.4725293980839</v>
+        <v>10.47253035894487</v>
       </c>
       <c r="D56" t="n">
-        <v>10.01822376578104</v>
+        <v>10.01822468495919</v>
       </c>
       <c r="E56" t="n">
-        <v>10.01822376578104</v>
+        <v>10.01822468495919</v>
       </c>
       <c r="F56" t="n">
         <v>4085600</v>
@@ -1552,16 +1552,16 @@
         <v>44727</v>
       </c>
       <c r="B57" t="n">
-        <v>10.84067535400391</v>
+        <v>10.84067630767822</v>
       </c>
       <c r="C57" t="n">
-        <v>10.84850839111218</v>
+        <v>10.84850934547558</v>
       </c>
       <c r="D57" t="n">
-        <v>10.44119942547642</v>
+        <v>10.44120034400809</v>
       </c>
       <c r="E57" t="n">
-        <v>10.55085970399363</v>
+        <v>10.55086063217233</v>
       </c>
       <c r="F57" t="n">
         <v>3153700</v>
@@ -1872,16 +1872,16 @@
         <v>44750</v>
       </c>
       <c r="B73" t="n">
-        <v>11.15398979187012</v>
+        <v>11.1539888381958</v>
       </c>
       <c r="C73" t="n">
-        <v>11.31064680498636</v>
+        <v>11.31064583791775</v>
       </c>
       <c r="D73" t="n">
-        <v>11.00516581615958</v>
+        <v>11.00516487520982</v>
       </c>
       <c r="E73" t="n">
-        <v>11.00516581615958</v>
+        <v>11.00516487520982</v>
       </c>
       <c r="F73" t="n">
         <v>1922000</v>
@@ -1892,16 +1892,16 @@
         <v>44753</v>
       </c>
       <c r="B74" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C74" t="n">
-        <v>11.18532085221909</v>
+        <v>11.18531989181933</v>
       </c>
       <c r="D74" t="n">
-        <v>10.83284239674361</v>
+        <v>10.83284146660853</v>
       </c>
       <c r="E74" t="n">
-        <v>11.0599952455611</v>
+        <v>11.05999429592211</v>
       </c>
       <c r="F74" t="n">
         <v>1881000</v>
@@ -1912,16 +1912,16 @@
         <v>44754</v>
       </c>
       <c r="B75" t="n">
-        <v>11.14615535736084</v>
+        <v>11.14615631103516</v>
       </c>
       <c r="C75" t="n">
-        <v>11.22448422760069</v>
+        <v>11.22448518797689</v>
       </c>
       <c r="D75" t="n">
-        <v>10.99733140030449</v>
+        <v>10.99733234124531</v>
       </c>
       <c r="E75" t="n">
-        <v>11.10699166924038</v>
+        <v>11.10699261956382</v>
       </c>
       <c r="F75" t="n">
         <v>1673000</v>
@@ -1952,16 +1952,16 @@
         <v>44756</v>
       </c>
       <c r="B77" t="n">
-        <v>10.91117191314697</v>
+        <v>10.91117095947266</v>
       </c>
       <c r="C77" t="n">
-        <v>11.17748921638524</v>
+        <v>11.17748823943387</v>
       </c>
       <c r="D77" t="n">
-        <v>10.84850910614968</v>
+        <v>10.84850815795232</v>
       </c>
       <c r="E77" t="n">
-        <v>11.04433056476611</v>
+        <v>11.04432959945326</v>
       </c>
       <c r="F77" t="n">
         <v>1968500</v>
@@ -2112,16 +2112,16 @@
         <v>44768</v>
       </c>
       <c r="B85" t="n">
-        <v>11.27148246765137</v>
+        <v>11.27148342132568</v>
       </c>
       <c r="C85" t="n">
-        <v>11.38114199706455</v>
+        <v>11.3811429600171</v>
       </c>
       <c r="D85" t="n">
-        <v>11.16965522819662</v>
+        <v>11.16965617325538</v>
       </c>
       <c r="E85" t="n">
-        <v>11.19315359207094</v>
+        <v>11.19315453911789</v>
       </c>
       <c r="F85" t="n">
         <v>1661400</v>
@@ -2152,16 +2152,16 @@
         <v>44770</v>
       </c>
       <c r="B87" t="n">
-        <v>10.96599960327148</v>
+        <v>10.9660005569458</v>
       </c>
       <c r="C87" t="n">
-        <v>11.33414408482687</v>
+        <v>11.33414507051741</v>
       </c>
       <c r="D87" t="n">
-        <v>10.82500794076103</v>
+        <v>10.8250088821738</v>
       </c>
       <c r="E87" t="n">
-        <v>11.31064497640883</v>
+        <v>11.31064596005574</v>
       </c>
       <c r="F87" t="n">
         <v>2911900</v>
@@ -2272,16 +2272,16 @@
         <v>44778</v>
       </c>
       <c r="B93" t="n">
-        <v>10.96599960327148</v>
+        <v>10.9660005569458</v>
       </c>
       <c r="C93" t="n">
-        <v>11.16965406089782</v>
+        <v>11.16965503228325</v>
       </c>
       <c r="D93" t="n">
-        <v>10.93466820571354</v>
+        <v>10.93466915666308</v>
       </c>
       <c r="E93" t="n">
-        <v>11.16965406089782</v>
+        <v>11.16965503228325</v>
       </c>
       <c r="F93" t="n">
         <v>1948700</v>
@@ -2352,16 +2352,16 @@
         <v>44784</v>
       </c>
       <c r="B97" t="n">
-        <v>10.89550495147705</v>
+        <v>10.89550590515137</v>
       </c>
       <c r="C97" t="n">
-        <v>11.10699246813669</v>
+        <v>11.10699344032233</v>
       </c>
       <c r="D97" t="n">
-        <v>10.83284214957779</v>
+        <v>10.83284309776729</v>
       </c>
       <c r="E97" t="n">
-        <v>11.05999499321249</v>
+        <v>11.05999596128448</v>
       </c>
       <c r="F97" t="n">
         <v>1665400</v>
@@ -2452,16 +2452,16 @@
         <v>44791</v>
       </c>
       <c r="B102" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="C102" t="n">
-        <v>11.37330994384684</v>
+        <v>11.37330897550059</v>
       </c>
       <c r="D102" t="n">
-        <v>11.09915962060828</v>
+        <v>11.09915867560374</v>
       </c>
       <c r="E102" t="n">
-        <v>11.27931499239396</v>
+        <v>11.27931403205064</v>
       </c>
       <c r="F102" t="n">
         <v>2180500</v>
@@ -2492,16 +2492,16 @@
         <v>44795</v>
       </c>
       <c r="B104" t="n">
-        <v>11.05999565124512</v>
+        <v>11.0599946975708</v>
       </c>
       <c r="C104" t="n">
-        <v>11.22448570276716</v>
+        <v>11.2244847349093</v>
       </c>
       <c r="D104" t="n">
-        <v>10.98166751771054</v>
+        <v>10.98166657079026</v>
       </c>
       <c r="E104" t="n">
-        <v>11.05999565124512</v>
+        <v>11.0599946975708</v>
       </c>
       <c r="F104" t="n">
         <v>1703300</v>
@@ -2512,16 +2512,16 @@
         <v>44796</v>
       </c>
       <c r="B105" t="n">
-        <v>11.22448444366455</v>
+        <v>11.22448539733887</v>
       </c>
       <c r="C105" t="n">
-        <v>11.27148191611302</v>
+        <v>11.27148287378042</v>
       </c>
       <c r="D105" t="n">
-        <v>10.98949857542116</v>
+        <v>10.98949950913019</v>
       </c>
       <c r="E105" t="n">
-        <v>10.98949857542116</v>
+        <v>10.98949950913019</v>
       </c>
       <c r="F105" t="n">
         <v>2361000</v>
@@ -2532,16 +2532,16 @@
         <v>44797</v>
       </c>
       <c r="B106" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C106" t="n">
-        <v>11.3968083737041</v>
+        <v>11.39680739514549</v>
       </c>
       <c r="D106" t="n">
-        <v>11.09915968439161</v>
+        <v>11.09915873138986</v>
       </c>
       <c r="E106" t="n">
-        <v>11.2244852910496</v>
+        <v>11.22448432728707</v>
       </c>
       <c r="F106" t="n">
         <v>2116800</v>
@@ -2672,16 +2672,16 @@
         <v>44806</v>
       </c>
       <c r="B113" t="n">
-        <v>11.74145412445068</v>
+        <v>11.74145317077637</v>
       </c>
       <c r="C113" t="n">
-        <v>11.79628463916563</v>
+        <v>11.79628368103782</v>
       </c>
       <c r="D113" t="n">
-        <v>11.56129874652895</v>
+        <v>11.56129780748737</v>
       </c>
       <c r="E113" t="n">
-        <v>11.74145412445068</v>
+        <v>11.74145317077637</v>
       </c>
       <c r="F113" t="n">
         <v>3674700</v>
@@ -2752,16 +2752,16 @@
         <v>44813</v>
       </c>
       <c r="B117" t="n">
-        <v>11.31847858428955</v>
+        <v>11.31847953796387</v>
       </c>
       <c r="C117" t="n">
-        <v>11.51430001566826</v>
+        <v>11.51430098584213</v>
       </c>
       <c r="D117" t="n">
-        <v>11.1696546251215</v>
+        <v>11.16965556625618</v>
       </c>
       <c r="E117" t="n">
-        <v>11.51430001566826</v>
+        <v>11.51430098584213</v>
       </c>
       <c r="F117" t="n">
         <v>2426300</v>
@@ -2832,16 +2832,16 @@
         <v>44819</v>
       </c>
       <c r="B121" t="n">
-        <v>11.22448444366455</v>
+        <v>11.22448539733887</v>
       </c>
       <c r="C121" t="n">
-        <v>11.27148191611302</v>
+        <v>11.27148287378042</v>
       </c>
       <c r="D121" t="n">
-        <v>11.11482417261777</v>
+        <v>11.11482511697494</v>
       </c>
       <c r="E121" t="n">
-        <v>11.16182164506624</v>
+        <v>11.16182259341649</v>
       </c>
       <c r="F121" t="n">
         <v>1523500</v>
@@ -2952,16 +2952,16 @@
         <v>44827</v>
       </c>
       <c r="B127" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="C127" t="n">
-        <v>11.30281410375695</v>
+        <v>11.30281314141286</v>
       </c>
       <c r="D127" t="n">
-        <v>11.07566125624483</v>
+        <v>11.07566031324099</v>
       </c>
       <c r="E127" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="F127" t="n">
         <v>2444100</v>
@@ -3012,16 +3012,16 @@
         <v>44832</v>
       </c>
       <c r="B130" t="n">
-        <v>10.74668025970459</v>
+        <v>10.74668121337891</v>
       </c>
       <c r="C130" t="n">
-        <v>11.03649588571345</v>
+        <v>11.03649686510639</v>
       </c>
       <c r="D130" t="n">
-        <v>10.72318115032588</v>
+        <v>10.72318210191485</v>
       </c>
       <c r="E130" t="n">
-        <v>10.95816701511669</v>
+        <v>10.95816798755862</v>
       </c>
       <c r="F130" t="n">
         <v>4249200</v>
@@ -3032,16 +3032,16 @@
         <v>44833</v>
       </c>
       <c r="B131" t="n">
-        <v>10.70751762390137</v>
+        <v>10.70751667022705</v>
       </c>
       <c r="C131" t="n">
-        <v>10.83284324031871</v>
+        <v>10.83284227548216</v>
       </c>
       <c r="D131" t="n">
-        <v>10.64485481569269</v>
+        <v>10.6448538675995</v>
       </c>
       <c r="E131" t="n">
-        <v>10.6918515483494</v>
+        <v>10.6918505960704</v>
       </c>
       <c r="F131" t="n">
         <v>2222600</v>
@@ -3072,16 +3072,16 @@
         <v>44837</v>
       </c>
       <c r="B133" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="C133" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="D133" t="n">
-        <v>10.62918785134206</v>
+        <v>10.62918694635185</v>
       </c>
       <c r="E133" t="n">
-        <v>10.74668116715839</v>
+        <v>10.74668025216456</v>
       </c>
       <c r="F133" t="n">
         <v>2250700</v>
@@ -3192,16 +3192,16 @@
         <v>44845</v>
       </c>
       <c r="B139" t="n">
-        <v>11.22448444366455</v>
+        <v>11.22448539733887</v>
       </c>
       <c r="C139" t="n">
-        <v>11.31847864156201</v>
+        <v>11.31847960322243</v>
       </c>
       <c r="D139" t="n">
-        <v>10.99733161199581</v>
+        <v>10.99733254637037</v>
       </c>
       <c r="E139" t="n">
-        <v>11.04432908444429</v>
+        <v>11.04433002281193</v>
       </c>
       <c r="F139" t="n">
         <v>1834300</v>
@@ -3212,16 +3212,16 @@
         <v>44847</v>
       </c>
       <c r="B140" t="n">
-        <v>10.91117191314697</v>
+        <v>10.91117095947266</v>
       </c>
       <c r="C140" t="n">
-        <v>11.20098758225933</v>
+        <v>11.20098660325412</v>
       </c>
       <c r="D140" t="n">
-        <v>10.87200747202377</v>
+        <v>10.87200652177256</v>
       </c>
       <c r="E140" t="n">
-        <v>11.12265870001293</v>
+        <v>11.12265772785393</v>
       </c>
       <c r="F140" t="n">
         <v>3739400</v>
@@ -3252,16 +3252,16 @@
         <v>44851</v>
       </c>
       <c r="B142" t="n">
-        <v>11.15398979187012</v>
+        <v>11.1539888381958</v>
       </c>
       <c r="C142" t="n">
-        <v>11.20098726930477</v>
+        <v>11.20098631161214</v>
       </c>
       <c r="D142" t="n">
-        <v>10.78584599779684</v>
+        <v>10.78584507559909</v>
       </c>
       <c r="E142" t="n">
-        <v>10.86417413085518</v>
+        <v>10.86417320196032</v>
       </c>
       <c r="F142" t="n">
         <v>6971700</v>
@@ -3272,16 +3272,16 @@
         <v>44852</v>
       </c>
       <c r="B143" t="n">
-        <v>11.27148246765137</v>
+        <v>11.27148342132568</v>
       </c>
       <c r="C143" t="n">
-        <v>11.37330970710612</v>
+        <v>11.37331066939599</v>
       </c>
       <c r="D143" t="n">
-        <v>11.06782798874186</v>
+        <v>11.06782892518508</v>
       </c>
       <c r="E143" t="n">
-        <v>11.20881966598683</v>
+        <v>11.20882061435928</v>
       </c>
       <c r="F143" t="n">
         <v>2646800</v>
@@ -3512,16 +3512,16 @@
         <v>44869</v>
       </c>
       <c r="B155" t="n">
-        <v>11.67095756530762</v>
+        <v>11.67095851898193</v>
       </c>
       <c r="C155" t="n">
-        <v>11.87461204288736</v>
+        <v>11.87461301320299</v>
       </c>
       <c r="D155" t="n">
-        <v>11.64745920158673</v>
+        <v>11.64746015334091</v>
       </c>
       <c r="E155" t="n">
-        <v>11.7492864403766</v>
+        <v>11.74928740045144</v>
       </c>
       <c r="F155" t="n">
         <v>2161500</v>
@@ -3532,16 +3532,16 @@
         <v>44872</v>
       </c>
       <c r="B156" t="n">
-        <v>11.20098686218262</v>
+        <v>11.2009859085083</v>
       </c>
       <c r="C156" t="n">
-        <v>11.65529255720685</v>
+        <v>11.65529156485204</v>
       </c>
       <c r="D156" t="n">
-        <v>11.12265798497174</v>
+        <v>11.1226570379665</v>
       </c>
       <c r="E156" t="n">
-        <v>11.60829508148041</v>
+        <v>11.60829409312706</v>
       </c>
       <c r="F156" t="n">
         <v>3276500</v>
@@ -3592,16 +3592,16 @@
         <v>44875</v>
       </c>
       <c r="B159" t="n">
-        <v>10.70751762390137</v>
+        <v>10.70751667022705</v>
       </c>
       <c r="C159" t="n">
-        <v>11.10699358648135</v>
+        <v>11.10699259722736</v>
       </c>
       <c r="D159" t="n">
-        <v>10.4960300859474</v>
+        <v>10.4960291511094</v>
       </c>
       <c r="E159" t="n">
-        <v>11.04433077827268</v>
+        <v>11.04432979459981</v>
       </c>
       <c r="F159" t="n">
         <v>4341400</v>
@@ -3612,16 +3612,16 @@
         <v>44876</v>
       </c>
       <c r="B160" t="n">
-        <v>10.79367637634277</v>
+        <v>10.79367733001709</v>
       </c>
       <c r="C160" t="n">
-        <v>10.85633917048995</v>
+        <v>10.85634012970083</v>
       </c>
       <c r="D160" t="n">
-        <v>10.53519216373583</v>
+        <v>10.5351930945718</v>
       </c>
       <c r="E160" t="n">
-        <v>10.78584408732395</v>
+        <v>10.78584504030624</v>
       </c>
       <c r="F160" t="n">
         <v>3291200</v>
@@ -3672,16 +3672,16 @@
         <v>44882</v>
       </c>
       <c r="B163" t="n">
-        <v>10.74668025970459</v>
+        <v>10.74668121337891</v>
       </c>
       <c r="C163" t="n">
-        <v>10.80151002092264</v>
+        <v>10.80151097946262</v>
       </c>
       <c r="D163" t="n">
-        <v>10.50386135845421</v>
+        <v>10.50386229058046</v>
       </c>
       <c r="E163" t="n">
-        <v>10.69184975148707</v>
+        <v>10.69185070029565</v>
       </c>
       <c r="F163" t="n">
         <v>5834900</v>
@@ -3912,16 +3912,16 @@
         <v>44900</v>
       </c>
       <c r="B175" t="n">
-        <v>10.51952838897705</v>
+        <v>10.51952743530273</v>
       </c>
       <c r="C175" t="n">
-        <v>10.80151100419552</v>
+        <v>10.80151002495736</v>
       </c>
       <c r="D175" t="n">
-        <v>10.50386231463181</v>
+        <v>10.50386136237774</v>
       </c>
       <c r="E175" t="n">
-        <v>10.7780126396772</v>
+        <v>10.77801166256934</v>
       </c>
       <c r="F175" t="n">
         <v>1355000</v>
@@ -3932,16 +3932,16 @@
         <v>44901</v>
       </c>
       <c r="B176" t="n">
-        <v>10.47253131866455</v>
+        <v>10.47253036499023</v>
       </c>
       <c r="C176" t="n">
-        <v>10.58219160233104</v>
+        <v>10.58219063867058</v>
       </c>
       <c r="D176" t="n">
-        <v>10.41770155033109</v>
+        <v>10.41770060164981</v>
       </c>
       <c r="E176" t="n">
-        <v>10.51952879652149</v>
+        <v>10.51952783856738</v>
       </c>
       <c r="F176" t="n">
         <v>1647500</v>
@@ -4192,16 +4192,16 @@
         <v>44918</v>
       </c>
       <c r="B189" t="n">
-        <v>11.78845119476318</v>
+        <v>11.78845024108887</v>
       </c>
       <c r="C189" t="n">
-        <v>12.09393217234406</v>
+        <v>12.09393119395663</v>
       </c>
       <c r="D189" t="n">
-        <v>11.57696367459224</v>
+        <v>11.57696273802706</v>
       </c>
       <c r="E189" t="n">
-        <v>11.67879091611904</v>
+        <v>11.67878997131614</v>
       </c>
       <c r="F189" t="n">
         <v>5656000</v>
@@ -4212,16 +4212,16 @@
         <v>44921</v>
       </c>
       <c r="B190" t="n">
-        <v>11.57696342468262</v>
+        <v>11.57696437835693</v>
       </c>
       <c r="C190" t="n">
-        <v>11.82761537802995</v>
+        <v>11.82761635235219</v>
       </c>
       <c r="D190" t="n">
-        <v>11.51430062309566</v>
+        <v>11.51430157160801</v>
       </c>
       <c r="E190" t="n">
-        <v>11.77278486639172</v>
+        <v>11.7727858361972</v>
       </c>
       <c r="F190" t="n">
         <v>1646600</v>
@@ -4492,16 +4492,16 @@
         <v>44942</v>
       </c>
       <c r="B204" t="n">
-        <v>11.78845119476318</v>
+        <v>11.78845024108887</v>
       </c>
       <c r="C204" t="n">
-        <v>11.80411652199833</v>
+        <v>11.8041155670567</v>
       </c>
       <c r="D204" t="n">
-        <v>11.39680830289065</v>
+        <v>11.39680738089987</v>
       </c>
       <c r="E204" t="n">
-        <v>11.49080250730011</v>
+        <v>11.49080157770529</v>
       </c>
       <c r="F204" t="n">
         <v>3279700</v>
@@ -4552,16 +4552,16 @@
         <v>44945</v>
       </c>
       <c r="B207" t="n">
-        <v>11.66312599182129</v>
+        <v>11.66312503814697</v>
       </c>
       <c r="C207" t="n">
-        <v>11.68662435698559</v>
+        <v>11.68662340138985</v>
       </c>
       <c r="D207" t="n">
-        <v>11.27931537680668</v>
+        <v>11.27931445451592</v>
       </c>
       <c r="E207" t="n">
-        <v>11.3419781819112</v>
+        <v>11.3419772544966</v>
       </c>
       <c r="F207" t="n">
         <v>1847800</v>
@@ -4732,16 +4732,16 @@
         <v>44958</v>
       </c>
       <c r="B216" t="n">
-        <v>12.07826709747314</v>
+        <v>12.07826614379883</v>
       </c>
       <c r="C216" t="n">
-        <v>12.19575966868999</v>
+        <v>12.19575870573871</v>
       </c>
       <c r="D216" t="n">
-        <v>11.93727541441329</v>
+        <v>11.93727447187138</v>
       </c>
       <c r="E216" t="n">
-        <v>12.08610013475415</v>
+        <v>12.08609918046135</v>
       </c>
       <c r="F216" t="n">
         <v>3741600</v>
@@ -4772,16 +4772,16 @@
         <v>44960</v>
       </c>
       <c r="B218" t="n">
-        <v>11.92160892486572</v>
+        <v>11.92160987854004</v>
       </c>
       <c r="C218" t="n">
-        <v>12.17226011743074</v>
+        <v>12.17226109115601</v>
       </c>
       <c r="D218" t="n">
-        <v>11.80411561810126</v>
+        <v>11.80411656237665</v>
       </c>
       <c r="E218" t="n">
-        <v>11.99993704904255</v>
+        <v>11.99993800898276</v>
       </c>
       <c r="F218" t="n">
         <v>3073100</v>
@@ -4852,16 +4852,16 @@
         <v>44966</v>
       </c>
       <c r="B222" t="n">
-        <v>11.66312599182129</v>
+        <v>11.66312503814697</v>
       </c>
       <c r="C222" t="n">
-        <v>11.78845160203032</v>
+        <v>11.78845063810834</v>
       </c>
       <c r="D222" t="n">
-        <v>11.55346570938861</v>
+        <v>11.55346476468103</v>
       </c>
       <c r="E222" t="n">
-        <v>11.7101227221499</v>
+        <v>11.71012176463273</v>
       </c>
       <c r="F222" t="n">
         <v>2260100</v>
@@ -5072,16 +5072,16 @@
         <v>44985</v>
       </c>
       <c r="B233" t="n">
-        <v>11.59262943267822</v>
+        <v>11.59262847900391</v>
       </c>
       <c r="C233" t="n">
-        <v>11.82761531079323</v>
+        <v>11.82761433778766</v>
       </c>
       <c r="D233" t="n">
-        <v>11.54563195825542</v>
+        <v>11.54563100844737</v>
       </c>
       <c r="E233" t="n">
-        <v>11.67095756071688</v>
+        <v>11.67095660059886</v>
       </c>
       <c r="F233" t="n">
         <v>7018700</v>
@@ -5172,16 +5172,16 @@
         <v>44992</v>
       </c>
       <c r="B238" t="n">
-        <v>11.61612796783447</v>
+        <v>11.61612701416016</v>
       </c>
       <c r="C238" t="n">
-        <v>11.6239610048538</v>
+        <v>11.6239600505364</v>
       </c>
       <c r="D238" t="n">
-        <v>11.3889751232706</v>
+        <v>11.38897418824534</v>
       </c>
       <c r="E238" t="n">
-        <v>11.52996680162043</v>
+        <v>11.52996585501987</v>
       </c>
       <c r="F238" t="n">
         <v>3776700</v>
@@ -5212,16 +5212,16 @@
         <v>44994</v>
       </c>
       <c r="B240" t="n">
-        <v>11.57696342468262</v>
+        <v>11.57696437835693</v>
       </c>
       <c r="C240" t="n">
-        <v>11.70228902785652</v>
+        <v>11.70228999185477</v>
       </c>
       <c r="D240" t="n">
-        <v>11.51430062309566</v>
+        <v>11.51430157160801</v>
       </c>
       <c r="E240" t="n">
-        <v>11.62396089937259</v>
+        <v>11.62396185691841</v>
       </c>
       <c r="F240" t="n">
         <v>2514900</v>
@@ -5232,16 +5232,16 @@
         <v>44995</v>
       </c>
       <c r="B241" t="n">
-        <v>11.57696342468262</v>
+        <v>11.57696437835693</v>
       </c>
       <c r="C241" t="n">
-        <v>11.63179393632084</v>
+        <v>11.63179489451192</v>
       </c>
       <c r="D241" t="n">
-        <v>11.44380478456046</v>
+        <v>11.44380572726558</v>
       </c>
       <c r="E241" t="n">
-        <v>11.57696342468262</v>
+        <v>11.57696437835693</v>
       </c>
       <c r="F241" t="n">
         <v>3626000</v>
@@ -5252,16 +5252,16 @@
         <v>44998</v>
       </c>
       <c r="B242" t="n">
-        <v>11.66312599182129</v>
+        <v>11.66312503814697</v>
       </c>
       <c r="C242" t="n">
-        <v>11.74145412470215</v>
+        <v>11.74145316462308</v>
       </c>
       <c r="D242" t="n">
-        <v>11.45947150173183</v>
+        <v>11.45947056471</v>
       </c>
       <c r="E242" t="n">
-        <v>11.52213430683635</v>
+        <v>11.52213336469069</v>
       </c>
       <c r="F242" t="n">
         <v>3223500</v>
@@ -5312,16 +5312,16 @@
         <v>45001</v>
       </c>
       <c r="B245" t="n">
-        <v>11.67095756530762</v>
+        <v>11.67095851898193</v>
       </c>
       <c r="C245" t="n">
-        <v>11.81194924163198</v>
+        <v>11.81195020682722</v>
       </c>
       <c r="D245" t="n">
-        <v>11.63962616467993</v>
+        <v>11.63962711579405</v>
       </c>
       <c r="E245" t="n">
-        <v>11.81194924163198</v>
+        <v>11.81195020682722</v>
       </c>
       <c r="F245" t="n">
         <v>5495800</v>
@@ -5352,16 +5352,16 @@
         <v>45005</v>
       </c>
       <c r="B247" t="n">
-        <v>11.31847858428955</v>
+        <v>11.31847953796387</v>
       </c>
       <c r="C247" t="n">
-        <v>11.51430001566826</v>
+        <v>11.51430098584213</v>
       </c>
       <c r="D247" t="n">
-        <v>11.2479827494733</v>
+        <v>11.24798369720776</v>
       </c>
       <c r="E247" t="n">
-        <v>11.45163721738703</v>
+        <v>11.45163818228105</v>
       </c>
       <c r="F247" t="n">
         <v>2892000</v>
@@ -5792,16 +5792,16 @@
         <v>45036</v>
       </c>
       <c r="B269" t="n">
-        <v>12.09393310546875</v>
+        <v>12.09393215179443</v>
       </c>
       <c r="C269" t="n">
-        <v>12.14093058479941</v>
+        <v>12.14092962741908</v>
       </c>
       <c r="D269" t="n">
-        <v>12.00777193152874</v>
+        <v>12.00777098464871</v>
       </c>
       <c r="E269" t="n">
-        <v>12.06260170158151</v>
+        <v>12.06260075037785</v>
       </c>
       <c r="F269" t="n">
         <v>4813100</v>
@@ -5872,16 +5872,16 @@
         <v>45043</v>
       </c>
       <c r="B273" t="n">
-        <v>12.07826709747314</v>
+        <v>12.07826614379883</v>
       </c>
       <c r="C273" t="n">
-        <v>12.0939324250356</v>
+        <v>12.09393147012438</v>
       </c>
       <c r="D273" t="n">
-        <v>11.95294148897529</v>
+        <v>11.95294054519642</v>
       </c>
       <c r="E273" t="n">
-        <v>12.01560429322422</v>
+        <v>12.01560334449763</v>
       </c>
       <c r="F273" t="n">
         <v>2919600</v>
@@ -22272,19 +22272,39 @@
         <v>46246</v>
       </c>
       <c r="B1093" t="n">
-        <v>10.38</v>
+        <v>10.38000011444092</v>
       </c>
       <c r="C1093" t="n">
-        <v>10.61</v>
+        <v>10.60999965667725</v>
       </c>
       <c r="D1093" t="n">
-        <v>10.22</v>
+        <v>10.22000026702881</v>
       </c>
       <c r="E1093" t="n">
-        <v>10.59</v>
+        <v>10.59000015258789</v>
       </c>
       <c r="F1093" t="n">
         <v>6023200</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B1094" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="C1094" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="D1094" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="E1094" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>3162000</v>
       </c>
     </row>
   </sheetData>

--- a/database/AURE3.xlsx
+++ b/database/AURE3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1094"/>
+  <dimension ref="A1:F1095"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44648</v>
       </c>
       <c r="B2" t="n">
-        <v>12.75723171234131</v>
+        <v>12.75723361968994</v>
       </c>
       <c r="C2" t="n">
-        <v>13.06838341582507</v>
+        <v>13.06838536969437</v>
       </c>
       <c r="D2" t="n">
-        <v>12.02602483823237</v>
+        <v>12.0260266362574</v>
       </c>
       <c r="E2" t="n">
-        <v>13.06838341582507</v>
+        <v>13.06838536969437</v>
       </c>
       <c r="F2" t="n">
         <v>5237900</v>
@@ -492,16 +492,16 @@
         <v>44650</v>
       </c>
       <c r="B4" t="n">
-        <v>12.38384914398193</v>
+        <v>12.38385009765625</v>
       </c>
       <c r="C4" t="n">
-        <v>13.04504741320321</v>
+        <v>13.04504841779609</v>
       </c>
       <c r="D4" t="n">
-        <v>12.3060608504815</v>
+        <v>12.30606179816537</v>
       </c>
       <c r="E4" t="n">
-        <v>12.9283657147967</v>
+        <v>12.92836671040398</v>
       </c>
       <c r="F4" t="n">
         <v>4408600</v>
@@ -512,16 +512,16 @@
         <v>44651</v>
       </c>
       <c r="B5" t="n">
-        <v>12.4383020401001</v>
+        <v>12.43830108642578</v>
       </c>
       <c r="C5" t="n">
-        <v>12.82724207193696</v>
+        <v>12.82724108844168</v>
       </c>
       <c r="D5" t="n">
-        <v>12.05714098694259</v>
+        <v>12.05714006249281</v>
       </c>
       <c r="E5" t="n">
-        <v>12.41496584590627</v>
+        <v>12.4149648940212</v>
       </c>
       <c r="F5" t="n">
         <v>3876100</v>
@@ -572,16 +572,16 @@
         <v>44656</v>
       </c>
       <c r="B8" t="n">
-        <v>12.15826511383057</v>
+        <v>12.15826606750488</v>
       </c>
       <c r="C8" t="n">
-        <v>12.50053200500811</v>
+        <v>12.50053298552928</v>
       </c>
       <c r="D8" t="n">
-        <v>12.05714061961251</v>
+        <v>12.05714156535479</v>
       </c>
       <c r="E8" t="n">
-        <v>12.37607131730719</v>
+        <v>12.37607228806586</v>
       </c>
       <c r="F8" t="n">
         <v>3624900</v>
@@ -592,16 +592,16 @@
         <v>44657</v>
       </c>
       <c r="B9" t="n">
-        <v>12.43052291870117</v>
+        <v>12.43052196502686</v>
       </c>
       <c r="C9" t="n">
-        <v>12.44608087588125</v>
+        <v>12.44607992101333</v>
       </c>
       <c r="D9" t="n">
-        <v>12.01824669740399</v>
+        <v>12.01824577535966</v>
       </c>
       <c r="E9" t="n">
-        <v>12.06491982710001</v>
+        <v>12.06491890147489</v>
       </c>
       <c r="F9" t="n">
         <v>2914800</v>
@@ -612,16 +612,16 @@
         <v>44658</v>
       </c>
       <c r="B10" t="n">
-        <v>12.44608116149902</v>
+        <v>12.44608020782471</v>
       </c>
       <c r="C10" t="n">
-        <v>12.71833948364451</v>
+        <v>12.71833850910855</v>
       </c>
       <c r="D10" t="n">
-        <v>12.20493801258351</v>
+        <v>12.20493707738666</v>
       </c>
       <c r="E10" t="n">
-        <v>12.32162046857911</v>
+        <v>12.32161952444153</v>
       </c>
       <c r="F10" t="n">
         <v>3223900</v>
@@ -672,16 +672,16 @@
         <v>44663</v>
       </c>
       <c r="B13" t="n">
-        <v>12.24383163452148</v>
+        <v>12.2438325881958</v>
       </c>
       <c r="C13" t="n">
-        <v>12.64055063241211</v>
+        <v>12.64055161698694</v>
       </c>
       <c r="D13" t="n">
-        <v>12.21271646263855</v>
+        <v>12.2127174138893</v>
       </c>
       <c r="E13" t="n">
-        <v>12.4849740311532</v>
+        <v>12.48497500361014</v>
       </c>
       <c r="F13" t="n">
         <v>2267700</v>
@@ -692,16 +692,16 @@
         <v>44664</v>
       </c>
       <c r="B14" t="n">
-        <v>12.10381317138672</v>
+        <v>12.10381412506104</v>
       </c>
       <c r="C14" t="n">
-        <v>12.55498277187146</v>
+        <v>12.55498376109398</v>
       </c>
       <c r="D14" t="n">
-        <v>12.0882552152437</v>
+        <v>12.08825616769219</v>
       </c>
       <c r="E14" t="n">
-        <v>12.39162868343488</v>
+        <v>12.39162965978653</v>
       </c>
       <c r="F14" t="n">
         <v>4421300</v>
@@ -712,16 +712,16 @@
         <v>44665</v>
       </c>
       <c r="B15" t="n">
-        <v>12.11159324645996</v>
+        <v>12.11159229278564</v>
       </c>
       <c r="C15" t="n">
-        <v>12.36829362703988</v>
+        <v>12.36829265315281</v>
       </c>
       <c r="D15" t="n">
-        <v>12.04936289612812</v>
+        <v>12.04936194735386</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08047807129404</v>
+        <v>12.08047712006975</v>
       </c>
       <c r="F15" t="n">
         <v>2077400</v>
@@ -732,16 +732,16 @@
         <v>44669</v>
       </c>
       <c r="B16" t="n">
-        <v>12.45385932922363</v>
+        <v>12.45386028289795</v>
       </c>
       <c r="C16" t="n">
-        <v>12.45385932922363</v>
+        <v>12.45386028289795</v>
       </c>
       <c r="D16" t="n">
-        <v>11.92490067691762</v>
+        <v>11.92490159008608</v>
       </c>
       <c r="E16" t="n">
-        <v>12.10381346772168</v>
+        <v>12.10381439459067</v>
       </c>
       <c r="F16" t="n">
         <v>3931100</v>
@@ -752,16 +752,16 @@
         <v>44670</v>
       </c>
       <c r="B17" t="n">
-        <v>12.10381317138672</v>
+        <v>12.10381412506104</v>
       </c>
       <c r="C17" t="n">
-        <v>12.60165664030051</v>
+        <v>12.60165763320052</v>
       </c>
       <c r="D17" t="n">
-        <v>12.00268868198966</v>
+        <v>12.00268962769625</v>
       </c>
       <c r="E17" t="n">
-        <v>12.43830106817557</v>
+        <v>12.4383020482046</v>
       </c>
       <c r="F17" t="n">
         <v>3118100</v>
@@ -772,16 +772,16 @@
         <v>44671</v>
       </c>
       <c r="B18" t="n">
-        <v>12.05714130401611</v>
+        <v>12.0571403503418</v>
       </c>
       <c r="C18" t="n">
-        <v>12.21271717247328</v>
+        <v>12.2127162064935</v>
       </c>
       <c r="D18" t="n">
-        <v>11.95601680405789</v>
+        <v>11.95601585838214</v>
       </c>
       <c r="E18" t="n">
-        <v>12.07269926178396</v>
+        <v>12.07269830687907</v>
       </c>
       <c r="F18" t="n">
         <v>2798400</v>
@@ -812,16 +812,16 @@
         <v>44676</v>
       </c>
       <c r="B20" t="n">
-        <v>12.39162921905518</v>
+        <v>12.39163017272949</v>
       </c>
       <c r="C20" t="n">
-        <v>12.39162921905518</v>
+        <v>12.39163017272949</v>
       </c>
       <c r="D20" t="n">
-        <v>11.90156470703017</v>
+        <v>11.90156562298855</v>
       </c>
       <c r="E20" t="n">
-        <v>12.11937090953766</v>
+        <v>12.11937184225865</v>
       </c>
       <c r="F20" t="n">
         <v>2683100</v>
@@ -852,16 +852,16 @@
         <v>44678</v>
       </c>
       <c r="B22" t="n">
-        <v>12.05714130401611</v>
+        <v>12.0571403503418</v>
       </c>
       <c r="C22" t="n">
-        <v>12.06492028290003</v>
+        <v>12.06491932861043</v>
       </c>
       <c r="D22" t="n">
-        <v>11.83155610929216</v>
+        <v>11.83155517346078</v>
       </c>
       <c r="E22" t="n">
-        <v>12.04936232513219</v>
+        <v>12.04936137207316</v>
       </c>
       <c r="F22" t="n">
         <v>2401400</v>
@@ -892,16 +892,16 @@
         <v>44680</v>
       </c>
       <c r="B24" t="n">
-        <v>11.40372180938721</v>
+        <v>11.40372085571289</v>
       </c>
       <c r="C24" t="n">
-        <v>11.96379567250737</v>
+        <v>11.963794671995</v>
       </c>
       <c r="D24" t="n">
-        <v>11.40372180938721</v>
+        <v>11.40372085571289</v>
       </c>
       <c r="E24" t="n">
-        <v>11.96379567250737</v>
+        <v>11.963794671995</v>
       </c>
       <c r="F24" t="n">
         <v>10427400</v>
@@ -952,16 +952,16 @@
         <v>44685</v>
       </c>
       <c r="B27" t="n">
-        <v>11.69445705413818</v>
+        <v>11.69445610046387</v>
       </c>
       <c r="C27" t="n">
-        <v>11.69445705413818</v>
+        <v>11.69445610046387</v>
       </c>
       <c r="D27" t="n">
-        <v>11.03649687268372</v>
+        <v>11.03649597266557</v>
       </c>
       <c r="E27" t="n">
-        <v>11.2088199552074</v>
+        <v>11.20881904113643</v>
       </c>
       <c r="F27" t="n">
         <v>4400300</v>
@@ -972,16 +972,16 @@
         <v>44686</v>
       </c>
       <c r="B28" t="n">
-        <v>11.28714847564697</v>
+        <v>11.28714752197266</v>
       </c>
       <c r="C28" t="n">
-        <v>11.62396161516718</v>
+        <v>11.62396063303483</v>
       </c>
       <c r="D28" t="n">
-        <v>11.14615678989441</v>
+        <v>11.14615584813277</v>
       </c>
       <c r="E28" t="n">
-        <v>11.61612857773658</v>
+        <v>11.61612759626606</v>
       </c>
       <c r="F28" t="n">
         <v>3065700</v>
@@ -1012,16 +1012,16 @@
         <v>44690</v>
       </c>
       <c r="B30" t="n">
-        <v>11.07566165924072</v>
+        <v>11.07566070556641</v>
       </c>
       <c r="C30" t="n">
-        <v>11.13049142708364</v>
+        <v>11.13049046868818</v>
       </c>
       <c r="D30" t="n">
-        <v>10.80934436343302</v>
+        <v>10.80934343269006</v>
       </c>
       <c r="E30" t="n">
-        <v>10.99733277917979</v>
+        <v>10.99733183225001</v>
       </c>
       <c r="F30" t="n">
         <v>1545300</v>
@@ -1112,16 +1112,16 @@
         <v>44697</v>
       </c>
       <c r="B35" t="n">
-        <v>11.27931499481201</v>
+        <v>11.27931594848633</v>
       </c>
       <c r="C35" t="n">
-        <v>11.41247363789934</v>
+        <v>11.41247460283231</v>
       </c>
       <c r="D35" t="n">
-        <v>11.11482495023352</v>
+        <v>11.11482589000009</v>
       </c>
       <c r="E35" t="n">
-        <v>11.17748850021538</v>
+        <v>11.1774894452802</v>
       </c>
       <c r="F35" t="n">
         <v>2419100</v>
@@ -1132,16 +1132,16 @@
         <v>44698</v>
       </c>
       <c r="B36" t="n">
-        <v>11.56129837036133</v>
+        <v>11.56129741668701</v>
       </c>
       <c r="C36" t="n">
-        <v>11.74928677955431</v>
+        <v>11.74928581037311</v>
       </c>
       <c r="D36" t="n">
-        <v>11.3576438869025</v>
+        <v>11.35764295002734</v>
       </c>
       <c r="E36" t="n">
-        <v>11.3576438869025</v>
+        <v>11.35764295002734</v>
       </c>
       <c r="F36" t="n">
         <v>1389700</v>
@@ -1172,16 +1172,16 @@
         <v>44700</v>
       </c>
       <c r="B38" t="n">
-        <v>11.22448539733887</v>
+        <v>11.22448444366455</v>
       </c>
       <c r="C38" t="n">
-        <v>11.25581679930005</v>
+        <v>11.25581584296371</v>
       </c>
       <c r="D38" t="n">
-        <v>10.97383418164937</v>
+        <v>10.97383324927132</v>
       </c>
       <c r="E38" t="n">
-        <v>11.11482511697494</v>
+        <v>11.11482417261777</v>
       </c>
       <c r="F38" t="n">
         <v>2127500</v>
@@ -1232,16 +1232,16 @@
         <v>44705</v>
       </c>
       <c r="B41" t="n">
-        <v>11.21665096282959</v>
+        <v>11.21665191650391</v>
       </c>
       <c r="C41" t="n">
-        <v>11.22448399909401</v>
+        <v>11.22448495343431</v>
       </c>
       <c r="D41" t="n">
-        <v>11.00516421268657</v>
+        <v>11.00516514837963</v>
       </c>
       <c r="E41" t="n">
-        <v>11.09132537059677</v>
+        <v>11.09132631361552</v>
       </c>
       <c r="F41" t="n">
         <v>792900</v>
@@ -1292,16 +1292,16 @@
         <v>44708</v>
       </c>
       <c r="B44" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C44" t="n">
-        <v>11.42030698171035</v>
+        <v>11.42030600182509</v>
       </c>
       <c r="D44" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="E44" t="n">
-        <v>11.26364997004757</v>
+        <v>11.26364900360379</v>
       </c>
       <c r="F44" t="n">
         <v>2224600</v>
@@ -1352,16 +1352,16 @@
         <v>44713</v>
       </c>
       <c r="B47" t="n">
-        <v>10.7310152053833</v>
+        <v>10.73101425170898</v>
       </c>
       <c r="C47" t="n">
-        <v>10.94250272786947</v>
+        <v>10.94250175540008</v>
       </c>
       <c r="D47" t="n">
-        <v>10.66051936455458</v>
+        <v>10.66051841714529</v>
       </c>
       <c r="E47" t="n">
-        <v>10.94250272786947</v>
+        <v>10.94250175540008</v>
       </c>
       <c r="F47" t="n">
         <v>6323900</v>
@@ -1372,16 +1372,16 @@
         <v>44714</v>
       </c>
       <c r="B48" t="n">
-        <v>10.86417388916016</v>
+        <v>10.86417293548584</v>
       </c>
       <c r="C48" t="n">
-        <v>10.98949949686503</v>
+        <v>10.98949853218943</v>
       </c>
       <c r="D48" t="n">
-        <v>10.68401851483428</v>
+        <v>10.68401757697429</v>
       </c>
       <c r="E48" t="n">
-        <v>10.75451360891862</v>
+        <v>10.75451266487045</v>
       </c>
       <c r="F48" t="n">
         <v>3275400</v>
@@ -1392,16 +1392,16 @@
         <v>44715</v>
       </c>
       <c r="B49" t="n">
-        <v>10.7780122756958</v>
+        <v>10.77801322937012</v>
       </c>
       <c r="C49" t="n">
-        <v>10.85634040377818</v>
+        <v>10.85634136438323</v>
       </c>
       <c r="D49" t="n">
-        <v>10.62135527253152</v>
+        <v>10.6213562123443</v>
       </c>
       <c r="E49" t="n">
-        <v>10.78584531260389</v>
+        <v>10.7858462669713</v>
       </c>
       <c r="F49" t="n">
         <v>2685000</v>
@@ -1412,16 +1412,16 @@
         <v>44718</v>
       </c>
       <c r="B50" t="n">
-        <v>10.61352157592773</v>
+        <v>10.61352252960205</v>
       </c>
       <c r="C50" t="n">
-        <v>10.91117023693893</v>
+        <v>10.91117121735836</v>
       </c>
       <c r="D50" t="n">
-        <v>10.45686458250065</v>
+        <v>10.4568655220986</v>
       </c>
       <c r="E50" t="n">
-        <v>10.81717604088268</v>
+        <v>10.8171770128563</v>
       </c>
       <c r="F50" t="n">
         <v>3175000</v>
@@ -1472,16 +1472,16 @@
         <v>44721</v>
       </c>
       <c r="B53" t="n">
-        <v>11.03649616241455</v>
+        <v>11.03649711608887</v>
       </c>
       <c r="C53" t="n">
-        <v>11.09915896166322</v>
+        <v>11.09915992075229</v>
       </c>
       <c r="D53" t="n">
-        <v>10.86417309098097</v>
+        <v>10.86417402976468</v>
       </c>
       <c r="E53" t="n">
-        <v>11.06782756203888</v>
+        <v>11.06782851842058</v>
       </c>
       <c r="F53" t="n">
         <v>1365200</v>
@@ -1532,16 +1532,16 @@
         <v>44726</v>
       </c>
       <c r="B56" t="n">
-        <v>10.39420223236084</v>
+        <v>10.39420318603516</v>
       </c>
       <c r="C56" t="n">
-        <v>10.47253035894487</v>
+        <v>10.47253131980584</v>
       </c>
       <c r="D56" t="n">
-        <v>10.01822468495919</v>
+        <v>10.01822560413734</v>
       </c>
       <c r="E56" t="n">
-        <v>10.01822468495919</v>
+        <v>10.01822560413734</v>
       </c>
       <c r="F56" t="n">
         <v>4085600</v>
@@ -1552,16 +1552,16 @@
         <v>44727</v>
       </c>
       <c r="B57" t="n">
-        <v>10.84067630767822</v>
+        <v>10.84067440032959</v>
       </c>
       <c r="C57" t="n">
-        <v>10.84850934547558</v>
+        <v>10.84850743674878</v>
       </c>
       <c r="D57" t="n">
-        <v>10.44120034400809</v>
+        <v>10.44119850694474</v>
       </c>
       <c r="E57" t="n">
-        <v>10.55086063217233</v>
+        <v>10.55085877581493</v>
       </c>
       <c r="F57" t="n">
         <v>3153700</v>
@@ -1672,16 +1672,16 @@
         <v>44736</v>
       </c>
       <c r="B63" t="n">
-        <v>10.48819732666016</v>
+        <v>10.48819637298584</v>
       </c>
       <c r="C63" t="n">
-        <v>10.70751714559343</v>
+        <v>10.70751617197673</v>
       </c>
       <c r="D63" t="n">
-        <v>10.42553452125065</v>
+        <v>10.42553357327416</v>
       </c>
       <c r="E63" t="n">
-        <v>10.70751714559343</v>
+        <v>10.70751617197673</v>
       </c>
       <c r="F63" t="n">
         <v>807500</v>
@@ -1712,16 +1712,16 @@
         <v>44740</v>
       </c>
       <c r="B65" t="n">
-        <v>10.61352157592773</v>
+        <v>10.61352252960205</v>
       </c>
       <c r="C65" t="n">
-        <v>10.86417276541107</v>
+        <v>10.86417374160756</v>
       </c>
       <c r="D65" t="n">
-        <v>10.47252990834362</v>
+        <v>10.47253084934918</v>
       </c>
       <c r="E65" t="n">
-        <v>10.52735966929324</v>
+        <v>10.5273606152255</v>
       </c>
       <c r="F65" t="n">
         <v>5362200</v>
@@ -1752,16 +1752,16 @@
         <v>44742</v>
       </c>
       <c r="B67" t="n">
-        <v>10.6683521270752</v>
+        <v>10.66835117340088</v>
       </c>
       <c r="C67" t="n">
-        <v>10.84850824310999</v>
+        <v>10.84850727333101</v>
       </c>
       <c r="D67" t="n">
-        <v>10.48819675803992</v>
+        <v>10.48819582047021</v>
       </c>
       <c r="E67" t="n">
-        <v>10.53519348604933</v>
+        <v>10.53519254427845</v>
       </c>
       <c r="F67" t="n">
         <v>2634600</v>
@@ -1832,16 +1832,16 @@
         <v>44748</v>
       </c>
       <c r="B71" t="n">
-        <v>10.67618560791016</v>
+        <v>10.67618465423584</v>
       </c>
       <c r="C71" t="n">
-        <v>10.71535004754583</v>
+        <v>10.71534909037307</v>
       </c>
       <c r="D71" t="n">
-        <v>10.49602948438586</v>
+        <v>10.49602854680439</v>
       </c>
       <c r="E71" t="n">
-        <v>10.57435836365721</v>
+        <v>10.57435741907885</v>
       </c>
       <c r="F71" t="n">
         <v>1826800</v>
@@ -1852,16 +1852,16 @@
         <v>44749</v>
       </c>
       <c r="B72" t="n">
-        <v>11.04433059692383</v>
+        <v>11.0443286895752</v>
       </c>
       <c r="C72" t="n">
-        <v>11.16182317363595</v>
+        <v>11.16182124599643</v>
       </c>
       <c r="D72" t="n">
-        <v>10.62135627496076</v>
+        <v>10.62135444065952</v>
       </c>
       <c r="E72" t="n">
-        <v>10.78584633055749</v>
+        <v>10.78584446784892</v>
       </c>
       <c r="F72" t="n">
         <v>2931100</v>
@@ -1912,16 +1912,16 @@
         <v>44754</v>
       </c>
       <c r="B75" t="n">
-        <v>11.14615631103516</v>
+        <v>11.14615726470947</v>
       </c>
       <c r="C75" t="n">
-        <v>11.22448518797689</v>
+        <v>11.22448614835309</v>
       </c>
       <c r="D75" t="n">
-        <v>10.99733234124531</v>
+        <v>10.99733328218612</v>
       </c>
       <c r="E75" t="n">
-        <v>11.10699261956382</v>
+        <v>11.10699356988726</v>
       </c>
       <c r="F75" t="n">
         <v>1673000</v>
@@ -1932,16 +1932,16 @@
         <v>44755</v>
       </c>
       <c r="B76" t="n">
-        <v>11.17748832702637</v>
+        <v>11.17748737335205</v>
       </c>
       <c r="C76" t="n">
-        <v>11.23231809203646</v>
+        <v>11.23231713368402</v>
       </c>
       <c r="D76" t="n">
-        <v>11.01299828499656</v>
+        <v>11.0129973453567</v>
       </c>
       <c r="E76" t="n">
-        <v>11.18532061702815</v>
+        <v>11.18531966268557</v>
       </c>
       <c r="F76" t="n">
         <v>2559400</v>
@@ -1992,16 +1992,16 @@
         <v>44760</v>
       </c>
       <c r="B79" t="n">
-        <v>10.7310152053833</v>
+        <v>10.73101425170898</v>
       </c>
       <c r="C79" t="n">
-        <v>11.0051655314951</v>
+        <v>11.00516455345681</v>
       </c>
       <c r="D79" t="n">
-        <v>10.5900242707254</v>
+        <v>10.59002332958107</v>
       </c>
       <c r="E79" t="n">
-        <v>10.80934408341511</v>
+        <v>10.80934312277964</v>
       </c>
       <c r="F79" t="n">
         <v>1463400</v>
@@ -2032,16 +2032,16 @@
         <v>44762</v>
       </c>
       <c r="B81" t="n">
-        <v>11.27931499481201</v>
+        <v>11.27931594848633</v>
       </c>
       <c r="C81" t="n">
-        <v>11.35764387203968</v>
+        <v>11.35764483233677</v>
       </c>
       <c r="D81" t="n">
-        <v>11.0521621472512</v>
+        <v>11.05216308171958</v>
       </c>
       <c r="E81" t="n">
-        <v>11.08349354874236</v>
+        <v>11.08349448585983</v>
       </c>
       <c r="F81" t="n">
         <v>2285400</v>
@@ -2052,16 +2052,16 @@
         <v>44763</v>
       </c>
       <c r="B82" t="n">
-        <v>11.24798393249512</v>
+        <v>11.2479829788208</v>
       </c>
       <c r="C82" t="n">
-        <v>11.27931533493105</v>
+        <v>11.27931437860027</v>
       </c>
       <c r="D82" t="n">
-        <v>11.0599955178795</v>
+        <v>11.05999458014401</v>
       </c>
       <c r="E82" t="n">
-        <v>11.22448556741805</v>
+        <v>11.22448461573608</v>
       </c>
       <c r="F82" t="n">
         <v>1092700</v>
@@ -2112,16 +2112,16 @@
         <v>44768</v>
       </c>
       <c r="B85" t="n">
-        <v>11.27148342132568</v>
+        <v>11.27148246765137</v>
       </c>
       <c r="C85" t="n">
-        <v>11.3811429600171</v>
+        <v>11.38114199706455</v>
       </c>
       <c r="D85" t="n">
-        <v>11.16965617325538</v>
+        <v>11.16965522819662</v>
       </c>
       <c r="E85" t="n">
-        <v>11.19315453911789</v>
+        <v>11.19315359207094</v>
       </c>
       <c r="F85" t="n">
         <v>1661400</v>
@@ -2152,16 +2152,16 @@
         <v>44770</v>
       </c>
       <c r="B87" t="n">
-        <v>10.9660005569458</v>
+        <v>10.96600151062012</v>
       </c>
       <c r="C87" t="n">
-        <v>11.33414507051741</v>
+        <v>11.33414605620796</v>
       </c>
       <c r="D87" t="n">
-        <v>10.8250088821738</v>
+        <v>10.82500982358657</v>
       </c>
       <c r="E87" t="n">
-        <v>11.31064596005574</v>
+        <v>11.31064694370265</v>
       </c>
       <c r="F87" t="n">
         <v>2911900</v>
@@ -2172,16 +2172,16 @@
         <v>44771</v>
       </c>
       <c r="B88" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C88" t="n">
-        <v>11.33414581204571</v>
+        <v>11.33414483955325</v>
       </c>
       <c r="D88" t="n">
-        <v>10.51952860439969</v>
+        <v>10.51952770180302</v>
       </c>
       <c r="E88" t="n">
-        <v>10.96600127438851</v>
+        <v>10.96600033348359</v>
       </c>
       <c r="F88" t="n">
         <v>13059200</v>
@@ -2212,16 +2212,16 @@
         <v>44775</v>
       </c>
       <c r="B90" t="n">
-        <v>10.86417388916016</v>
+        <v>10.86417293548584</v>
       </c>
       <c r="C90" t="n">
-        <v>11.06782837518035</v>
+        <v>11.06782740362892</v>
       </c>
       <c r="D90" t="n">
-        <v>10.7231822069924</v>
+        <v>10.72318126569455</v>
       </c>
       <c r="E90" t="n">
-        <v>10.93466973024404</v>
+        <v>10.93466877038148</v>
       </c>
       <c r="F90" t="n">
         <v>2371400</v>
@@ -2232,16 +2232,16 @@
         <v>44776</v>
       </c>
       <c r="B91" t="n">
-        <v>10.88767242431641</v>
+        <v>10.88767147064209</v>
       </c>
       <c r="C91" t="n">
-        <v>11.02083107133751</v>
+        <v>11.02083010599954</v>
       </c>
       <c r="D91" t="n">
-        <v>10.70751704716995</v>
+        <v>10.70751610927583</v>
       </c>
       <c r="E91" t="n">
-        <v>10.83284265683698</v>
+        <v>10.83284170796531</v>
       </c>
       <c r="F91" t="n">
         <v>3133200</v>
@@ -2272,16 +2272,16 @@
         <v>44778</v>
       </c>
       <c r="B93" t="n">
-        <v>10.9660005569458</v>
+        <v>10.96600151062012</v>
       </c>
       <c r="C93" t="n">
-        <v>11.16965503228325</v>
+        <v>11.16965600366867</v>
       </c>
       <c r="D93" t="n">
-        <v>10.93466915666308</v>
+        <v>10.93467010761261</v>
       </c>
       <c r="E93" t="n">
-        <v>11.16965503228325</v>
+        <v>11.16965600366867</v>
       </c>
       <c r="F93" t="n">
         <v>1948700</v>
@@ -2392,16 +2392,16 @@
         <v>44788</v>
       </c>
       <c r="B99" t="n">
-        <v>11.21665096282959</v>
+        <v>11.21665191650391</v>
       </c>
       <c r="C99" t="n">
-        <v>11.3106451570042</v>
+        <v>11.3106461186702</v>
       </c>
       <c r="D99" t="n">
-        <v>10.92683534404133</v>
+        <v>10.92683627307463</v>
       </c>
       <c r="E99" t="n">
-        <v>10.99733117642216</v>
+        <v>10.99733211144923</v>
       </c>
       <c r="F99" t="n">
         <v>3450900</v>
@@ -2412,16 +2412,16 @@
         <v>44789</v>
       </c>
       <c r="B100" t="n">
-        <v>11.04433059692383</v>
+        <v>11.0443286895752</v>
       </c>
       <c r="C100" t="n">
-        <v>11.2949818256428</v>
+        <v>11.29497987500687</v>
       </c>
       <c r="D100" t="n">
-        <v>10.94250334850685</v>
+        <v>10.94250145874372</v>
       </c>
       <c r="E100" t="n">
-        <v>11.25581738440557</v>
+        <v>11.25581544053331</v>
       </c>
       <c r="F100" t="n">
         <v>1185300</v>
@@ -2452,16 +2452,16 @@
         <v>44791</v>
       </c>
       <c r="B102" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="C102" t="n">
-        <v>11.37330897550059</v>
+        <v>11.37330994384684</v>
       </c>
       <c r="D102" t="n">
-        <v>11.09915867560374</v>
+        <v>11.09915962060828</v>
       </c>
       <c r="E102" t="n">
-        <v>11.27931403205064</v>
+        <v>11.27931499239396</v>
       </c>
       <c r="F102" t="n">
         <v>2180500</v>
@@ -2472,16 +2472,16 @@
         <v>44792</v>
       </c>
       <c r="B103" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C103" t="n">
-        <v>11.16182272571687</v>
+        <v>11.16182176801008</v>
       </c>
       <c r="D103" t="n">
-        <v>10.98166734905456</v>
+        <v>10.98166640680546</v>
       </c>
       <c r="E103" t="n">
-        <v>11.16182272571687</v>
+        <v>11.16182176801008</v>
       </c>
       <c r="F103" t="n">
         <v>1667800</v>
@@ -2512,16 +2512,16 @@
         <v>44796</v>
       </c>
       <c r="B105" t="n">
-        <v>11.22448539733887</v>
+        <v>11.22448444366455</v>
       </c>
       <c r="C105" t="n">
-        <v>11.27148287378042</v>
+        <v>11.27148191611302</v>
       </c>
       <c r="D105" t="n">
-        <v>10.98949950913019</v>
+        <v>10.98949857542116</v>
       </c>
       <c r="E105" t="n">
-        <v>10.98949950913019</v>
+        <v>10.98949857542116</v>
       </c>
       <c r="F105" t="n">
         <v>2361000</v>
@@ -2552,16 +2552,16 @@
         <v>44798</v>
       </c>
       <c r="B107" t="n">
-        <v>11.04433059692383</v>
+        <v>11.0443286895752</v>
       </c>
       <c r="C107" t="n">
-        <v>11.22448598081569</v>
+        <v>11.22448404235435</v>
       </c>
       <c r="D107" t="n">
-        <v>10.95033563915463</v>
+        <v>10.95033374803886</v>
       </c>
       <c r="E107" t="n">
-        <v>11.20882065252055</v>
+        <v>11.2088187167646</v>
       </c>
       <c r="F107" t="n">
         <v>2435800</v>
@@ -2592,16 +2592,16 @@
         <v>44802</v>
       </c>
       <c r="B109" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C109" t="n">
-        <v>11.20882020271549</v>
+        <v>11.20881924097621</v>
       </c>
       <c r="D109" t="n">
-        <v>10.93466987205595</v>
+        <v>10.93466893383933</v>
       </c>
       <c r="E109" t="n">
-        <v>11.02083104172059</v>
+        <v>11.02083009611117</v>
       </c>
       <c r="F109" t="n">
         <v>3615600</v>
@@ -2612,16 +2612,16 @@
         <v>44803</v>
       </c>
       <c r="B110" t="n">
-        <v>11.0129976272583</v>
+        <v>11.01299953460693</v>
       </c>
       <c r="C110" t="n">
-        <v>11.16182158639716</v>
+        <v>11.16182351952071</v>
       </c>
       <c r="D110" t="n">
-        <v>10.93466875592239</v>
+        <v>10.93467064970519</v>
       </c>
       <c r="E110" t="n">
-        <v>11.11482411419572</v>
+        <v>11.11482603917975</v>
       </c>
       <c r="F110" t="n">
         <v>1284900</v>
@@ -2632,16 +2632,16 @@
         <v>44804</v>
       </c>
       <c r="B111" t="n">
-        <v>12.03910160064697</v>
+        <v>12.03910255432129</v>
       </c>
       <c r="C111" t="n">
-        <v>12.07826603661254</v>
+        <v>12.07826699338926</v>
       </c>
       <c r="D111" t="n">
-        <v>10.96600023838756</v>
+        <v>10.96600110705643</v>
       </c>
       <c r="E111" t="n">
-        <v>11.02083000053966</v>
+        <v>11.02083087355185</v>
       </c>
       <c r="F111" t="n">
         <v>16560000</v>
@@ -2732,16 +2732,16 @@
         <v>44812</v>
       </c>
       <c r="B116" t="n">
-        <v>11.43597221374512</v>
+        <v>11.43597316741943</v>
       </c>
       <c r="C116" t="n">
-        <v>11.63962594040124</v>
+        <v>11.63962691105875</v>
       </c>
       <c r="D116" t="n">
-        <v>11.37330941369716</v>
+        <v>11.37331036214587</v>
       </c>
       <c r="E116" t="n">
-        <v>11.623960613889</v>
+        <v>11.62396158324014</v>
       </c>
       <c r="F116" t="n">
         <v>2598100</v>
@@ -2772,16 +2772,16 @@
         <v>44816</v>
       </c>
       <c r="B118" t="n">
-        <v>11.41247272491455</v>
+        <v>11.41247367858887</v>
       </c>
       <c r="C118" t="n">
-        <v>11.64745859079944</v>
+        <v>11.64745956411016</v>
       </c>
       <c r="D118" t="n">
-        <v>11.35764296344122</v>
+        <v>11.35764391253373</v>
       </c>
       <c r="E118" t="n">
-        <v>11.39680739892195</v>
+        <v>11.3968083512872</v>
       </c>
       <c r="F118" t="n">
         <v>2097200</v>
@@ -2832,16 +2832,16 @@
         <v>44819</v>
       </c>
       <c r="B121" t="n">
-        <v>11.22448539733887</v>
+        <v>11.22448444366455</v>
       </c>
       <c r="C121" t="n">
-        <v>11.27148287378042</v>
+        <v>11.27148191611302</v>
       </c>
       <c r="D121" t="n">
-        <v>11.11482511697494</v>
+        <v>11.11482417261777</v>
       </c>
       <c r="E121" t="n">
-        <v>11.16182259341649</v>
+        <v>11.16182164506624</v>
       </c>
       <c r="F121" t="n">
         <v>1523500</v>
@@ -2872,16 +2872,16 @@
         <v>44823</v>
       </c>
       <c r="B123" t="n">
-        <v>11.28714847564697</v>
+        <v>11.28714752197266</v>
       </c>
       <c r="C123" t="n">
-        <v>11.43597319883014</v>
+        <v>11.43597223258132</v>
       </c>
       <c r="D123" t="n">
-        <v>11.11482538717157</v>
+        <v>11.11482444805718</v>
       </c>
       <c r="E123" t="n">
-        <v>11.11482538717157</v>
+        <v>11.11482444805718</v>
       </c>
       <c r="F123" t="n">
         <v>1858600</v>
@@ -2892,16 +2892,16 @@
         <v>44824</v>
       </c>
       <c r="B124" t="n">
-        <v>11.13049125671387</v>
+        <v>11.13049030303955</v>
       </c>
       <c r="C124" t="n">
-        <v>11.35764410901417</v>
+        <v>11.35764313587711</v>
       </c>
       <c r="D124" t="n">
-        <v>11.08349377999676</v>
+        <v>11.08349283034925</v>
       </c>
       <c r="E124" t="n">
-        <v>11.28714826743829</v>
+        <v>11.28714730034141</v>
       </c>
       <c r="F124" t="n">
         <v>1310600</v>
@@ -2952,16 +2952,16 @@
         <v>44827</v>
       </c>
       <c r="B127" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="C127" t="n">
-        <v>11.30281314141286</v>
+        <v>11.30281410375695</v>
       </c>
       <c r="D127" t="n">
-        <v>11.07566031324099</v>
+        <v>11.07566125624483</v>
       </c>
       <c r="E127" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="F127" t="n">
         <v>2444100</v>
@@ -2992,16 +2992,16 @@
         <v>44831</v>
       </c>
       <c r="B129" t="n">
-        <v>10.9033374786377</v>
+        <v>10.90333843231201</v>
       </c>
       <c r="C129" t="n">
-        <v>11.04432914981819</v>
+        <v>11.04433011582452</v>
       </c>
       <c r="D129" t="n">
-        <v>10.77017884407822</v>
+        <v>10.77017978610565</v>
       </c>
       <c r="E129" t="n">
-        <v>11.04432914981819</v>
+        <v>11.04433011582452</v>
       </c>
       <c r="F129" t="n">
         <v>2130200</v>
@@ -3032,16 +3032,16 @@
         <v>44833</v>
       </c>
       <c r="B131" t="n">
-        <v>10.70751667022705</v>
+        <v>10.70751571655273</v>
       </c>
       <c r="C131" t="n">
-        <v>10.83284227548216</v>
+        <v>10.83284131064561</v>
       </c>
       <c r="D131" t="n">
-        <v>10.6448538675995</v>
+        <v>10.6448529195063</v>
       </c>
       <c r="E131" t="n">
-        <v>10.6918505960704</v>
+        <v>10.69184964379139</v>
       </c>
       <c r="F131" t="n">
         <v>2222600</v>
@@ -3052,16 +3052,16 @@
         <v>44834</v>
       </c>
       <c r="B132" t="n">
-        <v>10.61352157592773</v>
+        <v>10.61352252960205</v>
       </c>
       <c r="C132" t="n">
-        <v>10.74668020709063</v>
+        <v>10.74668117272986</v>
       </c>
       <c r="D132" t="n">
-        <v>10.59785550308529</v>
+        <v>10.59785645535194</v>
       </c>
       <c r="E132" t="n">
-        <v>10.70751577198399</v>
+        <v>10.70751673410412</v>
       </c>
       <c r="F132" t="n">
         <v>4019300</v>
@@ -3072,16 +3072,16 @@
         <v>44837</v>
       </c>
       <c r="B133" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="C133" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="D133" t="n">
-        <v>10.62918694635185</v>
+        <v>10.62918785134206</v>
       </c>
       <c r="E133" t="n">
-        <v>10.74668025216456</v>
+        <v>10.74668116715839</v>
       </c>
       <c r="F133" t="n">
         <v>2250700</v>
@@ -3092,16 +3092,16 @@
         <v>44838</v>
       </c>
       <c r="B134" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C134" t="n">
-        <v>11.32631277471268</v>
+        <v>11.32631180289231</v>
       </c>
       <c r="D134" t="n">
-        <v>11.07566155605223</v>
+        <v>11.07566060573824</v>
       </c>
       <c r="E134" t="n">
-        <v>11.20882020271549</v>
+        <v>11.20881924097621</v>
       </c>
       <c r="F134" t="n">
         <v>2406500</v>
@@ -3152,16 +3152,16 @@
         <v>44841</v>
       </c>
       <c r="B137" t="n">
-        <v>11.02866363525391</v>
+        <v>11.02866458892822</v>
       </c>
       <c r="C137" t="n">
-        <v>11.15398923954096</v>
+        <v>11.15399020405247</v>
       </c>
       <c r="D137" t="n">
-        <v>10.94250246905644</v>
+        <v>10.9425034152802</v>
       </c>
       <c r="E137" t="n">
-        <v>10.98166690714602</v>
+        <v>10.98166785675642</v>
       </c>
       <c r="F137" t="n">
         <v>7588600</v>
@@ -3172,16 +3172,16 @@
         <v>44844</v>
       </c>
       <c r="B138" t="n">
-        <v>11.07566165924072</v>
+        <v>11.07566070556641</v>
       </c>
       <c r="C138" t="n">
-        <v>11.35764428286087</v>
+        <v>11.35764330490633</v>
       </c>
       <c r="D138" t="n">
-        <v>11.0129988539918</v>
+        <v>11.01299790571309</v>
       </c>
       <c r="E138" t="n">
-        <v>11.07566165924072</v>
+        <v>11.07566070556641</v>
       </c>
       <c r="F138" t="n">
         <v>2000500</v>
@@ -3192,16 +3192,16 @@
         <v>44845</v>
       </c>
       <c r="B139" t="n">
-        <v>11.22448539733887</v>
+        <v>11.22448444366455</v>
       </c>
       <c r="C139" t="n">
-        <v>11.31847960322243</v>
+        <v>11.31847864156201</v>
       </c>
       <c r="D139" t="n">
-        <v>10.99733254637037</v>
+        <v>10.99733161199581</v>
       </c>
       <c r="E139" t="n">
-        <v>11.04433002281193</v>
+        <v>11.04432908444429</v>
       </c>
       <c r="F139" t="n">
         <v>1834300</v>
@@ -3272,16 +3272,16 @@
         <v>44852</v>
       </c>
       <c r="B143" t="n">
-        <v>11.27148342132568</v>
+        <v>11.27148246765137</v>
       </c>
       <c r="C143" t="n">
-        <v>11.37331066939599</v>
+        <v>11.37330970710612</v>
       </c>
       <c r="D143" t="n">
-        <v>11.06782892518508</v>
+        <v>11.06782798874186</v>
       </c>
       <c r="E143" t="n">
-        <v>11.20882061435928</v>
+        <v>11.20881966598683</v>
       </c>
       <c r="F143" t="n">
         <v>2646800</v>
@@ -3312,16 +3312,16 @@
         <v>44854</v>
       </c>
       <c r="B145" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C145" t="n">
-        <v>10.98166658413194</v>
+        <v>10.98166755090811</v>
       </c>
       <c r="D145" t="n">
-        <v>10.39420227106638</v>
+        <v>10.39420318612486</v>
       </c>
       <c r="E145" t="n">
-        <v>10.57435763518006</v>
+        <v>10.5743585660986</v>
       </c>
       <c r="F145" t="n">
         <v>7194300</v>
@@ -3352,16 +3352,16 @@
         <v>44858</v>
       </c>
       <c r="B147" t="n">
-        <v>11.24798393249512</v>
+        <v>11.2479829788208</v>
       </c>
       <c r="C147" t="n">
-        <v>11.45163842182848</v>
+        <v>11.45163745088707</v>
       </c>
       <c r="D147" t="n">
-        <v>11.10699299503318</v>
+        <v>11.10699205331296</v>
       </c>
       <c r="E147" t="n">
-        <v>11.10699299503318</v>
+        <v>11.10699205331296</v>
       </c>
       <c r="F147" t="n">
         <v>2219500</v>
@@ -3412,16 +3412,16 @@
         <v>44861</v>
       </c>
       <c r="B150" t="n">
-        <v>11.35764408111572</v>
+        <v>11.35764312744141</v>
       </c>
       <c r="C150" t="n">
-        <v>11.63179440945972</v>
+        <v>11.63179343276565</v>
       </c>
       <c r="D150" t="n">
-        <v>11.27148291217882</v>
+        <v>11.27148196573925</v>
       </c>
       <c r="E150" t="n">
-        <v>11.42813992251844</v>
+        <v>11.42813896292475</v>
       </c>
       <c r="F150" t="n">
         <v>4207900</v>
@@ -3432,16 +3432,16 @@
         <v>44862</v>
       </c>
       <c r="B151" t="n">
-        <v>11.49080276489258</v>
+        <v>11.49080181121826</v>
       </c>
       <c r="C151" t="n">
-        <v>11.63962673846057</v>
+        <v>11.63962577243467</v>
       </c>
       <c r="D151" t="n">
-        <v>11.22448547292922</v>
+        <v>11.2244845413578</v>
       </c>
       <c r="E151" t="n">
-        <v>11.32631271673871</v>
+        <v>11.32631177671618</v>
       </c>
       <c r="F151" t="n">
         <v>2887600</v>
@@ -3472,16 +3472,16 @@
         <v>44866</v>
       </c>
       <c r="B153" t="n">
-        <v>11.56913089752197</v>
+        <v>11.56913185119629</v>
       </c>
       <c r="C153" t="n">
-        <v>11.80411602515518</v>
+        <v>11.80411699819995</v>
       </c>
       <c r="D153" t="n">
-        <v>11.34981034946504</v>
+        <v>11.34981128506018</v>
       </c>
       <c r="E153" t="n">
-        <v>11.67879042455094</v>
+        <v>11.67879138726478</v>
       </c>
       <c r="F153" t="n">
         <v>3576300</v>
@@ -3512,16 +3512,16 @@
         <v>44869</v>
       </c>
       <c r="B155" t="n">
-        <v>11.67095851898193</v>
+        <v>11.67095756530762</v>
       </c>
       <c r="C155" t="n">
-        <v>11.87461301320299</v>
+        <v>11.87461204288736</v>
       </c>
       <c r="D155" t="n">
-        <v>11.64746015334091</v>
+        <v>11.64745920158673</v>
       </c>
       <c r="E155" t="n">
-        <v>11.74928740045144</v>
+        <v>11.7492864403766</v>
       </c>
       <c r="F155" t="n">
         <v>2161500</v>
@@ -3532,16 +3532,16 @@
         <v>44872</v>
       </c>
       <c r="B156" t="n">
-        <v>11.2009859085083</v>
+        <v>11.20098686218262</v>
       </c>
       <c r="C156" t="n">
-        <v>11.65529156485204</v>
+        <v>11.65529255720685</v>
       </c>
       <c r="D156" t="n">
-        <v>11.1226570379665</v>
+        <v>11.12265798497174</v>
       </c>
       <c r="E156" t="n">
-        <v>11.60829409312706</v>
+        <v>11.60829508148041</v>
       </c>
       <c r="F156" t="n">
         <v>3276500</v>
@@ -3592,16 +3592,16 @@
         <v>44875</v>
       </c>
       <c r="B159" t="n">
-        <v>10.70751667022705</v>
+        <v>10.70751571655273</v>
       </c>
       <c r="C159" t="n">
-        <v>11.10699259722736</v>
+        <v>11.10699160797338</v>
       </c>
       <c r="D159" t="n">
-        <v>10.4960291511094</v>
+        <v>10.49602821627141</v>
       </c>
       <c r="E159" t="n">
-        <v>11.04432979459981</v>
+        <v>11.04432881092694</v>
       </c>
       <c r="F159" t="n">
         <v>4341400</v>
@@ -3632,16 +3632,16 @@
         <v>44879</v>
       </c>
       <c r="B161" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C161" t="n">
-        <v>10.9660005105571</v>
+        <v>10.9660014759541</v>
       </c>
       <c r="D161" t="n">
-        <v>10.71534930935563</v>
+        <v>10.71535025268644</v>
       </c>
       <c r="E161" t="n">
-        <v>10.94250214719434</v>
+        <v>10.94250311052265</v>
       </c>
       <c r="F161" t="n">
         <v>1203700</v>
@@ -3652,16 +3652,16 @@
         <v>44881</v>
       </c>
       <c r="B162" t="n">
-        <v>10.9033374786377</v>
+        <v>10.90333843231201</v>
       </c>
       <c r="C162" t="n">
-        <v>10.9033374786377</v>
+        <v>10.90333843231201</v>
       </c>
       <c r="D162" t="n">
-        <v>10.59785577341312</v>
+        <v>10.59785670036809</v>
       </c>
       <c r="E162" t="n">
-        <v>10.86417304253206</v>
+        <v>10.86417399278081</v>
       </c>
       <c r="F162" t="n">
         <v>5270300</v>
@@ -3712,16 +3712,16 @@
         <v>44886</v>
       </c>
       <c r="B165" t="n">
-        <v>11.27931499481201</v>
+        <v>11.27931594848633</v>
       </c>
       <c r="C165" t="n">
-        <v>11.32631247054852</v>
+        <v>11.32631342819651</v>
       </c>
       <c r="D165" t="n">
-        <v>10.80934397244457</v>
+        <v>10.8093448863825</v>
       </c>
       <c r="E165" t="n">
-        <v>10.84067537393573</v>
+        <v>10.84067629052275</v>
       </c>
       <c r="F165" t="n">
         <v>4939800</v>
@@ -3732,16 +3732,16 @@
         <v>44887</v>
       </c>
       <c r="B166" t="n">
-        <v>10.84850883483887</v>
+        <v>10.84850788116455</v>
       </c>
       <c r="C166" t="n">
-        <v>11.4203071211389</v>
+        <v>11.42030611719874</v>
       </c>
       <c r="D166" t="n">
-        <v>10.80151135726647</v>
+        <v>10.80151040772362</v>
       </c>
       <c r="E166" t="n">
-        <v>11.29498151027859</v>
+        <v>11.29498051735561</v>
       </c>
       <c r="F166" t="n">
         <v>3523700</v>
@@ -3752,16 +3752,16 @@
         <v>44888</v>
       </c>
       <c r="B167" t="n">
-        <v>10.56652450561523</v>
+        <v>10.56652545928955</v>
       </c>
       <c r="C167" t="n">
-        <v>10.8171764516154</v>
+        <v>10.81717742791213</v>
       </c>
       <c r="D167" t="n">
-        <v>10.51952777930236</v>
+        <v>10.51952872873502</v>
       </c>
       <c r="E167" t="n">
-        <v>10.80934341489675</v>
+        <v>10.80934439048652</v>
       </c>
       <c r="F167" t="n">
         <v>4669400</v>
@@ -3792,16 +3792,16 @@
         <v>44890</v>
       </c>
       <c r="B169" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C169" t="n">
-        <v>11.03649634764489</v>
+        <v>11.03649731924802</v>
       </c>
       <c r="D169" t="n">
-        <v>10.71534930935563</v>
+        <v>10.71535025268644</v>
       </c>
       <c r="E169" t="n">
-        <v>10.95033443698226</v>
+        <v>10.95033540100009</v>
       </c>
       <c r="F169" t="n">
         <v>1631500</v>
@@ -3852,16 +3852,16 @@
         <v>44895</v>
       </c>
       <c r="B172" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C172" t="n">
-        <v>11.20881942197064</v>
+        <v>11.20882040874432</v>
       </c>
       <c r="D172" t="n">
-        <v>10.69185019899337</v>
+        <v>10.69185114025542</v>
       </c>
       <c r="E172" t="n">
-        <v>11.20881942197064</v>
+        <v>11.20882040874432</v>
       </c>
       <c r="F172" t="n">
         <v>4586400</v>
@@ -3912,16 +3912,16 @@
         <v>44900</v>
       </c>
       <c r="B175" t="n">
-        <v>10.51952743530273</v>
+        <v>10.51952838897705</v>
       </c>
       <c r="C175" t="n">
-        <v>10.80151002495736</v>
+        <v>10.80151100419552</v>
       </c>
       <c r="D175" t="n">
-        <v>10.50386136237774</v>
+        <v>10.50386231463181</v>
       </c>
       <c r="E175" t="n">
-        <v>10.77801166256934</v>
+        <v>10.7780126396772</v>
       </c>
       <c r="F175" t="n">
         <v>1355000</v>
@@ -3932,16 +3932,16 @@
         <v>44901</v>
       </c>
       <c r="B176" t="n">
-        <v>10.47253036499023</v>
+        <v>10.47253131866455</v>
       </c>
       <c r="C176" t="n">
-        <v>10.58219063867058</v>
+        <v>10.58219160233104</v>
       </c>
       <c r="D176" t="n">
-        <v>10.41770060164981</v>
+        <v>10.41770155033109</v>
       </c>
       <c r="E176" t="n">
-        <v>10.51952783856738</v>
+        <v>10.51952879652149</v>
       </c>
       <c r="F176" t="n">
         <v>1647500</v>
@@ -3992,16 +3992,16 @@
         <v>44904</v>
       </c>
       <c r="B179" t="n">
-        <v>11.17748832702637</v>
+        <v>11.17748737335205</v>
       </c>
       <c r="C179" t="n">
-        <v>11.56913121309737</v>
+        <v>11.5691302260077</v>
       </c>
       <c r="D179" t="n">
-        <v>11.04432968600226</v>
+        <v>11.04432874368917</v>
       </c>
       <c r="E179" t="n">
-        <v>11.29498089404786</v>
+        <v>11.29497993034896</v>
       </c>
       <c r="F179" t="n">
         <v>7204400</v>
@@ -4052,16 +4052,16 @@
         <v>44909</v>
       </c>
       <c r="B182" t="n">
-        <v>10.99733257293701</v>
+        <v>10.9973316192627</v>
       </c>
       <c r="C182" t="n">
-        <v>11.13832425560273</v>
+        <v>11.13832328970179</v>
       </c>
       <c r="D182" t="n">
-        <v>10.7388483193829</v>
+        <v>10.738847388124</v>
       </c>
       <c r="E182" t="n">
-        <v>11.01299864745522</v>
+        <v>11.01299769242237</v>
       </c>
       <c r="F182" t="n">
         <v>3892800</v>
@@ -4092,16 +4092,16 @@
         <v>44911</v>
       </c>
       <c r="B184" t="n">
-        <v>11.24798393249512</v>
+        <v>11.2479829788208</v>
       </c>
       <c r="C184" t="n">
-        <v>11.24798393249512</v>
+        <v>11.2479829788208</v>
       </c>
       <c r="D184" t="n">
-        <v>10.90333850569981</v>
+        <v>10.90333758124669</v>
       </c>
       <c r="E184" t="n">
-        <v>11.04433019016131</v>
+        <v>11.04432925375403</v>
       </c>
       <c r="F184" t="n">
         <v>3365900</v>
@@ -4132,16 +4132,16 @@
         <v>44915</v>
       </c>
       <c r="B186" t="n">
-        <v>11.27931499481201</v>
+        <v>11.27931594848633</v>
       </c>
       <c r="C186" t="n">
-        <v>11.56129835523201</v>
+        <v>11.56129933274823</v>
       </c>
       <c r="D186" t="n">
-        <v>11.16965546309271</v>
+        <v>11.16965640749523</v>
       </c>
       <c r="E186" t="n">
-        <v>11.35764387203968</v>
+        <v>11.35764483233677</v>
       </c>
       <c r="F186" t="n">
         <v>4148100</v>
@@ -4172,16 +4172,16 @@
         <v>44917</v>
       </c>
       <c r="B188" t="n">
-        <v>11.63179397583008</v>
+        <v>11.63179492950439</v>
       </c>
       <c r="C188" t="n">
-        <v>11.74928654245482</v>
+        <v>11.74928750576218</v>
       </c>
       <c r="D188" t="n">
-        <v>11.50646762523096</v>
+        <v>11.50646856862995</v>
       </c>
       <c r="E188" t="n">
-        <v>11.60046257493018</v>
+        <v>11.60046352603568</v>
       </c>
       <c r="F188" t="n">
         <v>2577900</v>
@@ -4212,16 +4212,16 @@
         <v>44921</v>
       </c>
       <c r="B190" t="n">
-        <v>11.57696437835693</v>
+        <v>11.5769624710083</v>
       </c>
       <c r="C190" t="n">
-        <v>11.82761635235219</v>
+        <v>11.8276144037077</v>
       </c>
       <c r="D190" t="n">
-        <v>11.51430157160801</v>
+        <v>11.51429967458331</v>
       </c>
       <c r="E190" t="n">
-        <v>11.7727858361972</v>
+        <v>11.77278389658625</v>
       </c>
       <c r="F190" t="n">
         <v>1646600</v>
@@ -4272,16 +4272,16 @@
         <v>44924</v>
       </c>
       <c r="B193" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="C193" t="n">
-        <v>11.73362129131107</v>
+        <v>11.73362032145083</v>
       </c>
       <c r="D193" t="n">
-        <v>11.47513702901113</v>
+        <v>11.4751360805163</v>
       </c>
       <c r="E193" t="n">
-        <v>11.62396175397144</v>
+        <v>11.62396079317528</v>
       </c>
       <c r="F193" t="n">
         <v>2424800</v>
@@ -4312,16 +4312,16 @@
         <v>44929</v>
       </c>
       <c r="B195" t="n">
-        <v>11.13832473754883</v>
+        <v>11.13832378387451</v>
       </c>
       <c r="C195" t="n">
-        <v>11.32631315790418</v>
+        <v>11.32631218813412</v>
       </c>
       <c r="D195" t="n">
-        <v>11.05999585556764</v>
+        <v>11.05999490859992</v>
       </c>
       <c r="E195" t="n">
-        <v>11.30281479210966</v>
+        <v>11.30281382435154</v>
       </c>
       <c r="F195" t="n">
         <v>1562800</v>
@@ -4332,16 +4332,16 @@
         <v>44930</v>
       </c>
       <c r="B196" t="n">
-        <v>11.35764408111572</v>
+        <v>11.35764312744141</v>
       </c>
       <c r="C196" t="n">
-        <v>11.35764408111572</v>
+        <v>11.35764312744141</v>
       </c>
       <c r="D196" t="n">
-        <v>10.9660011817669</v>
+        <v>10.96600026097791</v>
       </c>
       <c r="E196" t="n">
-        <v>11.16965566870818</v>
+        <v>11.1696547308188</v>
       </c>
       <c r="F196" t="n">
         <v>2937400</v>
@@ -4352,16 +4352,16 @@
         <v>44931</v>
       </c>
       <c r="B197" t="n">
-        <v>11.41247272491455</v>
+        <v>11.41247367858887</v>
       </c>
       <c r="C197" t="n">
-        <v>11.41247272491455</v>
+        <v>11.41247367858887</v>
       </c>
       <c r="D197" t="n">
-        <v>11.08349266207561</v>
+        <v>11.08349358825896</v>
       </c>
       <c r="E197" t="n">
-        <v>11.31064549146445</v>
+        <v>11.31064643662965</v>
       </c>
       <c r="F197" t="n">
         <v>4358300</v>
@@ -4412,16 +4412,16 @@
         <v>44936</v>
       </c>
       <c r="B200" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C200" t="n">
-        <v>11.1853210907164</v>
+        <v>11.1853201309934</v>
       </c>
       <c r="D200" t="n">
-        <v>10.69185094372897</v>
+        <v>10.6918500263467</v>
       </c>
       <c r="E200" t="n">
-        <v>11.08349384638571</v>
+        <v>11.08349289539969</v>
       </c>
       <c r="F200" t="n">
         <v>5832500</v>
@@ -4452,16 +4452,16 @@
         <v>44938</v>
       </c>
       <c r="B202" t="n">
-        <v>11.79628276824951</v>
+        <v>11.79628372192383</v>
       </c>
       <c r="C202" t="n">
-        <v>11.97643811759822</v>
+        <v>11.97643908583725</v>
       </c>
       <c r="D202" t="n">
-        <v>11.49863411771738</v>
+        <v>11.49863504732819</v>
       </c>
       <c r="E202" t="n">
-        <v>11.49863411771738</v>
+        <v>11.49863504732819</v>
       </c>
       <c r="F202" t="n">
         <v>5662900</v>
@@ -4512,16 +4512,16 @@
         <v>44943</v>
       </c>
       <c r="B205" t="n">
-        <v>11.74928569793701</v>
+        <v>11.74928665161133</v>
       </c>
       <c r="C205" t="n">
-        <v>11.93727408982413</v>
+        <v>11.93727505875722</v>
       </c>
       <c r="D205" t="n">
-        <v>11.60829403052194</v>
+        <v>11.60829497275214</v>
       </c>
       <c r="E205" t="n">
-        <v>11.81194849523272</v>
+        <v>11.81194945399329</v>
       </c>
       <c r="F205" t="n">
         <v>2676600</v>
@@ -4532,16 +4532,16 @@
         <v>44944</v>
       </c>
       <c r="B206" t="n">
-        <v>11.41247272491455</v>
+        <v>11.41247367858887</v>
       </c>
       <c r="C206" t="n">
-        <v>11.89027749318036</v>
+        <v>11.89027848678206</v>
       </c>
       <c r="D206" t="n">
-        <v>11.41247272491455</v>
+        <v>11.41247367858887</v>
       </c>
       <c r="E206" t="n">
-        <v>11.87461142018828</v>
+        <v>11.87461241248085</v>
       </c>
       <c r="F206" t="n">
         <v>3532000</v>
@@ -4632,16 +4632,16 @@
         <v>44951</v>
       </c>
       <c r="B211" t="n">
-        <v>11.89027881622314</v>
+        <v>11.89027786254883</v>
       </c>
       <c r="C211" t="n">
-        <v>12.07043419368129</v>
+        <v>12.07043322555739</v>
       </c>
       <c r="D211" t="n">
-        <v>11.62396152172019</v>
+        <v>11.62396058940618</v>
       </c>
       <c r="E211" t="n">
-        <v>11.67879128929448</v>
+        <v>11.67879035258278</v>
       </c>
       <c r="F211" t="n">
         <v>10764800</v>
@@ -4652,16 +4652,16 @@
         <v>44952</v>
       </c>
       <c r="B212" t="n">
-        <v>11.96860599517822</v>
+        <v>11.96860694885254</v>
       </c>
       <c r="C212" t="n">
-        <v>12.09393159507546</v>
+        <v>12.09393255873588</v>
       </c>
       <c r="D212" t="n">
-        <v>11.79628366881928</v>
+        <v>11.79628460876272</v>
       </c>
       <c r="E212" t="n">
-        <v>11.91377623197306</v>
+        <v>11.91377718127847</v>
       </c>
       <c r="F212" t="n">
         <v>8143300</v>
@@ -4712,16 +4712,16 @@
         <v>44957</v>
       </c>
       <c r="B215" t="n">
-        <v>12.0704345703125</v>
+        <v>12.07043361663818</v>
       </c>
       <c r="C215" t="n">
-        <v>12.14093041482172</v>
+        <v>12.14092945557759</v>
       </c>
       <c r="D215" t="n">
-        <v>11.82761638033583</v>
+        <v>11.82761544584636</v>
       </c>
       <c r="E215" t="n">
-        <v>11.84328170856034</v>
+        <v>11.84328077283316</v>
       </c>
       <c r="F215" t="n">
         <v>5446800</v>
@@ -4752,16 +4752,16 @@
         <v>44959</v>
       </c>
       <c r="B217" t="n">
-        <v>12.03910160064697</v>
+        <v>12.03910255432129</v>
       </c>
       <c r="C217" t="n">
-        <v>12.19575859750976</v>
+        <v>12.19575956359362</v>
       </c>
       <c r="D217" t="n">
-        <v>11.85111320441163</v>
+        <v>11.8511141431945</v>
       </c>
       <c r="E217" t="n">
-        <v>12.07043300001953</v>
+        <v>12.07043395617575</v>
       </c>
       <c r="F217" t="n">
         <v>3404900</v>
@@ -4792,16 +4792,16 @@
         <v>44963</v>
       </c>
       <c r="B219" t="n">
-        <v>11.91377735137939</v>
+        <v>11.91377544403076</v>
       </c>
       <c r="C219" t="n">
-        <v>11.96077482925644</v>
+        <v>11.9607729143837</v>
       </c>
       <c r="D219" t="n">
-        <v>11.75712033678852</v>
+        <v>11.75711845452006</v>
       </c>
       <c r="E219" t="n">
-        <v>11.92161038885883</v>
+        <v>11.92160848025616</v>
       </c>
       <c r="F219" t="n">
         <v>3421200</v>
@@ -4812,16 +4812,16 @@
         <v>44964</v>
       </c>
       <c r="B220" t="n">
-        <v>11.60046291351318</v>
+        <v>11.60046195983887</v>
       </c>
       <c r="C220" t="n">
-        <v>12.02343721150694</v>
+        <v>12.02343622305989</v>
       </c>
       <c r="D220" t="n">
-        <v>11.49080263366312</v>
+        <v>11.49080168900398</v>
       </c>
       <c r="E220" t="n">
-        <v>12.02343721150694</v>
+        <v>12.02343622305989</v>
       </c>
       <c r="F220" t="n">
         <v>5199600</v>
@@ -4832,16 +4832,16 @@
         <v>44965</v>
       </c>
       <c r="B221" t="n">
-        <v>11.71012306213379</v>
+        <v>11.71012210845947</v>
       </c>
       <c r="C221" t="n">
-        <v>11.78845194428836</v>
+        <v>11.78845098423493</v>
       </c>
       <c r="D221" t="n">
-        <v>11.54563300720885</v>
+        <v>11.54563206693063</v>
       </c>
       <c r="E221" t="n">
-        <v>11.68662469628725</v>
+        <v>11.68662374452664</v>
       </c>
       <c r="F221" t="n">
         <v>3697100</v>
@@ -4892,16 +4892,16 @@
         <v>44970</v>
       </c>
       <c r="B224" t="n">
-        <v>11.79628276824951</v>
+        <v>11.79628372192383</v>
       </c>
       <c r="C224" t="n">
-        <v>11.87461088870569</v>
+        <v>11.87461184871247</v>
       </c>
       <c r="D224" t="n">
-        <v>11.63179274419227</v>
+        <v>11.63179368456833</v>
       </c>
       <c r="E224" t="n">
-        <v>11.7414522622308</v>
+        <v>11.74145321147233</v>
       </c>
       <c r="F224" t="n">
         <v>2704300</v>
@@ -4932,16 +4932,16 @@
         <v>44972</v>
       </c>
       <c r="B226" t="n">
-        <v>11.75712013244629</v>
+        <v>11.75711917877197</v>
       </c>
       <c r="C226" t="n">
-        <v>11.92944247200145</v>
+        <v>11.92944150434928</v>
       </c>
       <c r="D226" t="n">
-        <v>11.63179452295179</v>
+        <v>11.63179357944321</v>
       </c>
       <c r="E226" t="n">
-        <v>11.66312592532541</v>
+        <v>11.6631249792754</v>
       </c>
       <c r="F226" t="n">
         <v>3961900</v>
@@ -4952,16 +4952,16 @@
         <v>44973</v>
       </c>
       <c r="B227" t="n">
-        <v>11.89027881622314</v>
+        <v>11.89027786254883</v>
       </c>
       <c r="C227" t="n">
-        <v>11.9764399862684</v>
+        <v>11.97643902568342</v>
       </c>
       <c r="D227" t="n">
-        <v>11.57696404451397</v>
+        <v>11.57696311596945</v>
       </c>
       <c r="E227" t="n">
-        <v>11.7649532063393</v>
+        <v>11.76495226271687</v>
       </c>
       <c r="F227" t="n">
         <v>4461000</v>
@@ -5012,16 +5012,16 @@
         <v>44980</v>
       </c>
       <c r="B230" t="n">
-        <v>11.67879104614258</v>
+        <v>11.67879009246826</v>
       </c>
       <c r="C230" t="n">
-        <v>11.85111412964489</v>
+        <v>11.8511131618989</v>
       </c>
       <c r="D230" t="n">
-        <v>11.61612824250529</v>
+        <v>11.61612729394793</v>
       </c>
       <c r="E230" t="n">
-        <v>11.79628436321215</v>
+        <v>11.79628339994349</v>
       </c>
       <c r="F230" t="n">
         <v>3218000</v>
@@ -5032,16 +5032,16 @@
         <v>44981</v>
       </c>
       <c r="B231" t="n">
-        <v>11.67879104614258</v>
+        <v>11.67879009246826</v>
       </c>
       <c r="C231" t="n">
-        <v>11.89811085887308</v>
+        <v>11.89810988728941</v>
       </c>
       <c r="D231" t="n">
-        <v>11.51430099984482</v>
+        <v>11.51430005960253</v>
       </c>
       <c r="E231" t="n">
-        <v>11.72578852237032</v>
+        <v>11.72578756485825</v>
       </c>
       <c r="F231" t="n">
         <v>4705500</v>
@@ -5052,16 +5052,16 @@
         <v>44984</v>
       </c>
       <c r="B232" t="n">
-        <v>11.64745903015137</v>
+        <v>11.64745998382568</v>
       </c>
       <c r="C232" t="n">
-        <v>11.85894654152509</v>
+        <v>11.85894751251565</v>
       </c>
       <c r="D232" t="n">
-        <v>11.56129786644328</v>
+        <v>11.56129881306286</v>
       </c>
       <c r="E232" t="n">
-        <v>11.73362019385946</v>
+        <v>11.7336211545885</v>
       </c>
       <c r="F232" t="n">
         <v>3412900</v>
@@ -5072,16 +5072,16 @@
         <v>44985</v>
       </c>
       <c r="B233" t="n">
-        <v>11.59262847900391</v>
+        <v>11.59263038635254</v>
       </c>
       <c r="C233" t="n">
-        <v>11.82761433778766</v>
+        <v>11.82761628379879</v>
       </c>
       <c r="D233" t="n">
-        <v>11.54563100844737</v>
+        <v>11.54563290806346</v>
       </c>
       <c r="E233" t="n">
-        <v>11.67095660059886</v>
+        <v>11.67095852083491</v>
       </c>
       <c r="F233" t="n">
         <v>7018700</v>
@@ -5112,16 +5112,16 @@
         <v>44987</v>
       </c>
       <c r="B235" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="C235" t="n">
-        <v>11.67879152264125</v>
+        <v>11.67879055731306</v>
       </c>
       <c r="D235" t="n">
-        <v>11.45947170096243</v>
+        <v>11.45947075376244</v>
       </c>
       <c r="E235" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="F235" t="n">
         <v>2250800</v>
@@ -5132,16 +5132,16 @@
         <v>44988</v>
       </c>
       <c r="B236" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="C236" t="n">
-        <v>11.64746011954428</v>
+        <v>11.64745915680582</v>
       </c>
       <c r="D236" t="n">
-        <v>11.45947170096243</v>
+        <v>11.45947075376244</v>
       </c>
       <c r="E236" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="F236" t="n">
         <v>1727100</v>
@@ -5152,16 +5152,16 @@
         <v>44991</v>
       </c>
       <c r="B237" t="n">
-        <v>11.47513675689697</v>
+        <v>11.47513580322266</v>
       </c>
       <c r="C237" t="n">
-        <v>11.60046311331254</v>
+        <v>11.60046214922261</v>
       </c>
       <c r="D237" t="n">
-        <v>11.27931530543457</v>
+        <v>11.27931436803456</v>
       </c>
       <c r="E237" t="n">
-        <v>11.53779956160498</v>
+        <v>11.53779860272289</v>
       </c>
       <c r="F237" t="n">
         <v>5313400</v>
@@ -5172,16 +5172,16 @@
         <v>44992</v>
       </c>
       <c r="B238" t="n">
-        <v>11.61612701416016</v>
+        <v>11.61612796783447</v>
       </c>
       <c r="C238" t="n">
-        <v>11.6239600505364</v>
+        <v>11.6239610048538</v>
       </c>
       <c r="D238" t="n">
-        <v>11.38897418824534</v>
+        <v>11.3889751232706</v>
       </c>
       <c r="E238" t="n">
-        <v>11.52996585501987</v>
+        <v>11.52996680162043</v>
       </c>
       <c r="F238" t="n">
         <v>3776700</v>
@@ -5192,16 +5192,16 @@
         <v>44993</v>
       </c>
       <c r="B239" t="n">
-        <v>11.63179397583008</v>
+        <v>11.63179492950439</v>
       </c>
       <c r="C239" t="n">
-        <v>11.63962626580541</v>
+        <v>11.63962722012189</v>
       </c>
       <c r="D239" t="n">
-        <v>11.48296926130592</v>
+        <v>11.48297020277831</v>
       </c>
       <c r="E239" t="n">
-        <v>11.62396093885522</v>
+        <v>11.62396189188732</v>
       </c>
       <c r="F239" t="n">
         <v>2946500</v>
@@ -5212,16 +5212,16 @@
         <v>44994</v>
       </c>
       <c r="B240" t="n">
-        <v>11.57696437835693</v>
+        <v>11.5769624710083</v>
       </c>
       <c r="C240" t="n">
-        <v>11.70228999185477</v>
+        <v>11.70228806385827</v>
       </c>
       <c r="D240" t="n">
-        <v>11.51430157160801</v>
+        <v>11.51429967458331</v>
       </c>
       <c r="E240" t="n">
-        <v>11.62396185691841</v>
+        <v>11.62395994182677</v>
       </c>
       <c r="F240" t="n">
         <v>2514900</v>
@@ -5232,16 +5232,16 @@
         <v>44995</v>
       </c>
       <c r="B241" t="n">
-        <v>11.57696437835693</v>
+        <v>11.5769624710083</v>
       </c>
       <c r="C241" t="n">
-        <v>11.63179489451192</v>
+        <v>11.63179297812976</v>
       </c>
       <c r="D241" t="n">
-        <v>11.44380572726558</v>
+        <v>11.44380384185534</v>
       </c>
       <c r="E241" t="n">
-        <v>11.57696437835693</v>
+        <v>11.5769624710083</v>
       </c>
       <c r="F241" t="n">
         <v>3626000</v>
@@ -5272,16 +5272,16 @@
         <v>44999</v>
       </c>
       <c r="B243" t="n">
-        <v>11.75712013244629</v>
+        <v>11.75711917877197</v>
       </c>
       <c r="C243" t="n">
-        <v>11.82761597453684</v>
+        <v>11.82761501514428</v>
       </c>
       <c r="D243" t="n">
-        <v>11.63962681329553</v>
+        <v>11.63962586915163</v>
       </c>
       <c r="E243" t="n">
-        <v>11.69445732769904</v>
+        <v>11.69445637910759</v>
       </c>
       <c r="F243" t="n">
         <v>2520000</v>
@@ -5292,16 +5292,16 @@
         <v>45000</v>
       </c>
       <c r="B244" t="n">
-        <v>11.74928569793701</v>
+        <v>11.74928665161133</v>
       </c>
       <c r="C244" t="n">
-        <v>11.89027736535209</v>
+        <v>11.89027833047051</v>
       </c>
       <c r="D244" t="n">
-        <v>11.61612706693377</v>
+        <v>11.61612800979977</v>
       </c>
       <c r="E244" t="n">
-        <v>11.71795429928916</v>
+        <v>11.71795525042035</v>
       </c>
       <c r="F244" t="n">
         <v>4602600</v>
@@ -5312,16 +5312,16 @@
         <v>45001</v>
       </c>
       <c r="B245" t="n">
-        <v>11.67095851898193</v>
+        <v>11.67095756530762</v>
       </c>
       <c r="C245" t="n">
-        <v>11.81195020682722</v>
+        <v>11.81194924163198</v>
       </c>
       <c r="D245" t="n">
-        <v>11.63962711579405</v>
+        <v>11.63962616467993</v>
       </c>
       <c r="E245" t="n">
-        <v>11.81195020682722</v>
+        <v>11.81194924163198</v>
       </c>
       <c r="F245" t="n">
         <v>5495800</v>
@@ -5432,16 +5432,16 @@
         <v>45009</v>
       </c>
       <c r="B251" t="n">
-        <v>11.30281352996826</v>
+        <v>11.30281448364258</v>
       </c>
       <c r="C251" t="n">
-        <v>11.39680772964997</v>
+        <v>11.39680869125504</v>
       </c>
       <c r="D251" t="n">
-        <v>11.11482438360535</v>
+        <v>11.11482532141809</v>
       </c>
       <c r="E251" t="n">
-        <v>11.20881933028655</v>
+        <v>11.20882027603011</v>
       </c>
       <c r="F251" t="n">
         <v>3265300</v>
@@ -5452,16 +5452,16 @@
         <v>45012</v>
       </c>
       <c r="B252" t="n">
-        <v>11.28714847564697</v>
+        <v>11.28714752197266</v>
       </c>
       <c r="C252" t="n">
-        <v>11.42030712396893</v>
+        <v>11.42030615904377</v>
       </c>
       <c r="D252" t="n">
-        <v>11.19315426747845</v>
+        <v>11.1931533217459</v>
       </c>
       <c r="E252" t="n">
-        <v>11.39680875867669</v>
+        <v>11.39680779573696</v>
       </c>
       <c r="F252" t="n">
         <v>2288800</v>
@@ -5532,16 +5532,16 @@
         <v>45016</v>
       </c>
       <c r="B256" t="n">
-        <v>11.49080276489258</v>
+        <v>11.49080181121826</v>
       </c>
       <c r="C256" t="n">
-        <v>11.61612837358132</v>
+        <v>11.61612740950566</v>
       </c>
       <c r="D256" t="n">
-        <v>11.30281435185946</v>
+        <v>11.30281341378716</v>
       </c>
       <c r="E256" t="n">
-        <v>11.42813996054821</v>
+        <v>11.42813901207456</v>
       </c>
       <c r="F256" t="n">
         <v>5155800</v>
@@ -5572,16 +5572,16 @@
         <v>45020</v>
       </c>
       <c r="B258" t="n">
-        <v>11.43597221374512</v>
+        <v>11.43597316741943</v>
       </c>
       <c r="C258" t="n">
-        <v>11.49863501379308</v>
+        <v>11.498635972693</v>
       </c>
       <c r="D258" t="n">
-        <v>11.24798306660174</v>
+        <v>11.24798400459917</v>
       </c>
       <c r="E258" t="n">
-        <v>11.35764334018542</v>
+        <v>11.35764428732769</v>
       </c>
       <c r="F258" t="n">
         <v>5230100</v>
@@ -5592,16 +5592,16 @@
         <v>45021</v>
       </c>
       <c r="B259" t="n">
-        <v>11.49080276489258</v>
+        <v>11.49080181121826</v>
       </c>
       <c r="C259" t="n">
-        <v>11.56913164382282</v>
+        <v>11.56913068364763</v>
       </c>
       <c r="D259" t="n">
-        <v>11.27931523998066</v>
+        <v>11.27931430385866</v>
       </c>
       <c r="E259" t="n">
-        <v>11.55346556923695</v>
+        <v>11.55346461036196</v>
       </c>
       <c r="F259" t="n">
         <v>4689800</v>
@@ -5612,16 +5612,16 @@
         <v>45022</v>
       </c>
       <c r="B260" t="n">
-        <v>11.53779983520508</v>
+        <v>11.53779888153076</v>
       </c>
       <c r="C260" t="n">
-        <v>11.66312619459255</v>
+        <v>11.6631252305592</v>
       </c>
       <c r="D260" t="n">
-        <v>11.47513702901113</v>
+        <v>11.4751360805163</v>
       </c>
       <c r="E260" t="n">
-        <v>11.4908031040594</v>
+        <v>11.49080215426967</v>
       </c>
       <c r="F260" t="n">
         <v>4653400</v>
@@ -5652,16 +5652,16 @@
         <v>45027</v>
       </c>
       <c r="B262" t="n">
-        <v>11.76495265960693</v>
+        <v>11.76495361328125</v>
       </c>
       <c r="C262" t="n">
-        <v>12.01560386772655</v>
+        <v>12.0156048417188</v>
       </c>
       <c r="D262" t="n">
-        <v>11.71012214758113</v>
+        <v>11.71012309681085</v>
       </c>
       <c r="E262" t="n">
-        <v>11.82761546163684</v>
+        <v>11.82761642039064</v>
       </c>
       <c r="F262" t="n">
         <v>2622300</v>
@@ -5692,16 +5692,16 @@
         <v>45029</v>
       </c>
       <c r="B264" t="n">
-        <v>11.91377735137939</v>
+        <v>11.91377544403076</v>
       </c>
       <c r="C264" t="n">
-        <v>11.99993852265448</v>
+        <v>11.99993660151179</v>
       </c>
       <c r="D264" t="n">
-        <v>11.77278566474782</v>
+        <v>11.7727837799714</v>
       </c>
       <c r="E264" t="n">
-        <v>11.82761618010431</v>
+        <v>11.82761428654974</v>
       </c>
       <c r="F264" t="n">
         <v>3337400</v>
@@ -5752,16 +5752,16 @@
         <v>45034</v>
       </c>
       <c r="B267" t="n">
-        <v>11.96860599517822</v>
+        <v>11.96860694885254</v>
       </c>
       <c r="C267" t="n">
-        <v>12.16442743176752</v>
+        <v>12.16442840104515</v>
       </c>
       <c r="D267" t="n">
-        <v>11.94510763194737</v>
+        <v>11.9451085837493</v>
       </c>
       <c r="E267" t="n">
-        <v>12.14092906853667</v>
+        <v>12.14093003594191</v>
       </c>
       <c r="F267" t="n">
         <v>3259600</v>
@@ -5772,16 +5772,16 @@
         <v>45035</v>
       </c>
       <c r="B268" t="n">
-        <v>12.03910160064697</v>
+        <v>12.03910255432129</v>
       </c>
       <c r="C268" t="n">
-        <v>12.06259996342652</v>
+        <v>12.06260091896225</v>
       </c>
       <c r="D268" t="n">
-        <v>11.86677853059817</v>
+        <v>11.86677947062196</v>
       </c>
       <c r="E268" t="n">
-        <v>11.96860576530885</v>
+        <v>11.96860671339886</v>
       </c>
       <c r="F268" t="n">
         <v>3098200</v>
@@ -5832,16 +5832,16 @@
         <v>45041</v>
       </c>
       <c r="B271" t="n">
-        <v>12.06260108947754</v>
+        <v>12.06260013580322</v>
       </c>
       <c r="C271" t="n">
-        <v>12.14092996872072</v>
+        <v>12.14092900885369</v>
       </c>
       <c r="D271" t="n">
-        <v>11.96860688258545</v>
+        <v>11.96860593634236</v>
       </c>
       <c r="E271" t="n">
-        <v>12.11743160374759</v>
+        <v>12.11743064573835</v>
       </c>
       <c r="F271" t="n">
         <v>2381100</v>
@@ -5892,16 +5892,16 @@
         <v>45044</v>
       </c>
       <c r="B274" t="n">
-        <v>12.36024951934814</v>
+        <v>12.36024856567383</v>
       </c>
       <c r="C274" t="n">
-        <v>12.45424372422157</v>
+        <v>12.45424276329498</v>
       </c>
       <c r="D274" t="n">
-        <v>12.01560410147892</v>
+        <v>12.01560317439626</v>
       </c>
       <c r="E274" t="n">
-        <v>12.11743134350835</v>
+        <v>12.11743040856905</v>
       </c>
       <c r="F274" t="n">
         <v>8419400</v>
@@ -5932,16 +5932,16 @@
         <v>45049</v>
       </c>
       <c r="B276" t="n">
-        <v>12.28975391387939</v>
+        <v>12.28975296020508</v>
       </c>
       <c r="C276" t="n">
-        <v>12.48557536452565</v>
+        <v>12.48557439565576</v>
       </c>
       <c r="D276" t="n">
-        <v>12.2819216235732</v>
+        <v>12.28192067050667</v>
       </c>
       <c r="E276" t="n">
-        <v>12.48557536452565</v>
+        <v>12.48557439565576</v>
       </c>
       <c r="F276" t="n">
         <v>6661600</v>
@@ -5972,16 +5972,16 @@
         <v>45051</v>
       </c>
       <c r="B278" t="n">
-        <v>12.50989723205566</v>
+        <v>12.50989818572998</v>
       </c>
       <c r="C278" t="n">
-        <v>12.59647124671763</v>
+        <v>12.59647220699179</v>
       </c>
       <c r="D278" t="n">
-        <v>12.15494525807742</v>
+        <v>12.15494618469247</v>
       </c>
       <c r="E278" t="n">
-        <v>12.34540759495513</v>
+        <v>12.34540853608981</v>
       </c>
       <c r="F278" t="n">
         <v>9400800</v>
@@ -5992,16 +5992,16 @@
         <v>45054</v>
       </c>
       <c r="B279" t="n">
-        <v>12.11165904998779</v>
+        <v>12.11165809631348</v>
       </c>
       <c r="C279" t="n">
-        <v>12.58781451078781</v>
+        <v>12.58781351962092</v>
       </c>
       <c r="D279" t="n">
-        <v>12.05105773110397</v>
+        <v>12.05105678220141</v>
       </c>
       <c r="E279" t="n">
-        <v>12.54452750060035</v>
+        <v>12.54452651284189</v>
       </c>
       <c r="F279" t="n">
         <v>5826000</v>
@@ -6052,16 +6052,16 @@
         <v>45057</v>
       </c>
       <c r="B282" t="n">
-        <v>12.05971527099609</v>
+        <v>12.05971622467041</v>
       </c>
       <c r="C282" t="n">
-        <v>12.11165902259875</v>
+        <v>12.11165998038074</v>
       </c>
       <c r="D282" t="n">
-        <v>11.7393927173429</v>
+        <v>11.73939364568632</v>
       </c>
       <c r="E282" t="n">
-        <v>11.79133646894556</v>
+        <v>11.79133740139665</v>
       </c>
       <c r="F282" t="n">
         <v>3678200</v>
@@ -6072,16 +6072,16 @@
         <v>45058</v>
       </c>
       <c r="B283" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C283" t="n">
-        <v>12.25017632493442</v>
+        <v>12.25017729158851</v>
       </c>
       <c r="D283" t="n">
-        <v>11.99911266679329</v>
+        <v>11.9991136136361</v>
       </c>
       <c r="E283" t="n">
-        <v>12.04239967522403</v>
+        <v>12.0424006254826</v>
       </c>
       <c r="F283" t="n">
         <v>3087800</v>
@@ -6132,16 +6132,16 @@
         <v>45063</v>
       </c>
       <c r="B286" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="C286" t="n">
-        <v>12.24152036724783</v>
+        <v>12.24151939290137</v>
       </c>
       <c r="D286" t="n">
-        <v>11.9471696818366</v>
+        <v>11.94716873091856</v>
       </c>
       <c r="E286" t="n">
-        <v>12.128974468377</v>
+        <v>12.12897350298847</v>
       </c>
       <c r="F286" t="n">
         <v>4330800</v>
@@ -6152,16 +6152,16 @@
         <v>45064</v>
       </c>
       <c r="B287" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="C287" t="n">
-        <v>12.05971558070743</v>
+        <v>12.05971462083146</v>
       </c>
       <c r="D287" t="n">
-        <v>11.82596621559931</v>
+        <v>11.82596527432829</v>
       </c>
       <c r="E287" t="n">
-        <v>12.01642856950617</v>
+        <v>12.01642761307558</v>
       </c>
       <c r="F287" t="n">
         <v>4680600</v>
@@ -6172,16 +6172,16 @@
         <v>45065</v>
       </c>
       <c r="B288" t="n">
-        <v>12.09434509277344</v>
+        <v>12.09434413909912</v>
       </c>
       <c r="C288" t="n">
-        <v>12.18091829003328</v>
+        <v>12.18091732953242</v>
       </c>
       <c r="D288" t="n">
-        <v>11.93851218182222</v>
+        <v>11.93851124043578</v>
       </c>
       <c r="E288" t="n">
-        <v>11.99911350246722</v>
+        <v>11.99911255630219</v>
       </c>
       <c r="F288" t="n">
         <v>2962700</v>
@@ -6232,16 +6232,16 @@
         <v>45070</v>
       </c>
       <c r="B291" t="n">
-        <v>12.25017642974854</v>
+        <v>12.25017738342285</v>
       </c>
       <c r="C291" t="n">
-        <v>12.30212100543608</v>
+        <v>12.30212196315428</v>
       </c>
       <c r="D291" t="n">
-        <v>12.18091754591915</v>
+        <v>12.18091849420168</v>
       </c>
       <c r="E291" t="n">
-        <v>12.26749156352139</v>
+        <v>12.26749251854369</v>
       </c>
       <c r="F291" t="n">
         <v>1846000</v>
@@ -6252,16 +6252,16 @@
         <v>45071</v>
       </c>
       <c r="B292" t="n">
-        <v>12.29346466064453</v>
+        <v>12.29346370697021</v>
       </c>
       <c r="C292" t="n">
-        <v>12.39735299671616</v>
+        <v>12.39735203498263</v>
       </c>
       <c r="D292" t="n">
-        <v>12.20689146006706</v>
+        <v>12.20689051310872</v>
       </c>
       <c r="E292" t="n">
-        <v>12.28480709289745</v>
+        <v>12.28480613989475</v>
       </c>
       <c r="F292" t="n">
         <v>2204600</v>
@@ -6292,16 +6292,16 @@
         <v>45075</v>
       </c>
       <c r="B294" t="n">
-        <v>12.28480529785156</v>
+        <v>12.28480625152588</v>
       </c>
       <c r="C294" t="n">
-        <v>12.34540743759487</v>
+        <v>12.34540839597375</v>
       </c>
       <c r="D294" t="n">
-        <v>12.16360266962691</v>
+        <v>12.16360361389222</v>
       </c>
       <c r="E294" t="n">
-        <v>12.16360266962691</v>
+        <v>12.16360361389222</v>
       </c>
       <c r="F294" t="n">
         <v>1431900</v>
@@ -6352,16 +6352,16 @@
         <v>45078</v>
       </c>
       <c r="B297" t="n">
-        <v>12.24151992797852</v>
+        <v>12.2415189743042</v>
       </c>
       <c r="C297" t="n">
-        <v>12.30212124610704</v>
+        <v>12.30212028771158</v>
       </c>
       <c r="D297" t="n">
-        <v>12.1636034757384</v>
+        <v>12.16360252813415</v>
       </c>
       <c r="E297" t="n">
-        <v>12.26749180351488</v>
+        <v>12.26749084781722</v>
       </c>
       <c r="F297" t="n">
         <v>2308800</v>
@@ -6372,16 +6372,16 @@
         <v>45079</v>
       </c>
       <c r="B298" t="n">
-        <v>12.17226123809814</v>
+        <v>12.17226219177246</v>
       </c>
       <c r="C298" t="n">
-        <v>12.33675088664238</v>
+        <v>12.33675185320416</v>
       </c>
       <c r="D298" t="n">
-        <v>12.07702965021844</v>
+        <v>12.07703059643153</v>
       </c>
       <c r="E298" t="n">
-        <v>12.3107790106893</v>
+        <v>12.31077997521623</v>
       </c>
       <c r="F298" t="n">
         <v>5725100</v>
@@ -6412,16 +6412,16 @@
         <v>45083</v>
       </c>
       <c r="B300" t="n">
-        <v>12.32809352874756</v>
+        <v>12.32809257507324</v>
       </c>
       <c r="C300" t="n">
-        <v>12.41466755090237</v>
+        <v>12.41466659053087</v>
       </c>
       <c r="D300" t="n">
-        <v>12.0770298552559</v>
+        <v>12.07702892100332</v>
       </c>
       <c r="E300" t="n">
-        <v>12.08568742259759</v>
+        <v>12.08568648767528</v>
       </c>
       <c r="F300" t="n">
         <v>7376500</v>
@@ -6432,16 +6432,16 @@
         <v>45084</v>
       </c>
       <c r="B301" t="n">
-        <v>12.22420597076416</v>
+        <v>12.22420406341553</v>
       </c>
       <c r="C301" t="n">
-        <v>12.46661209224716</v>
+        <v>12.46661014707579</v>
       </c>
       <c r="D301" t="n">
-        <v>12.21554840287484</v>
+        <v>12.21554649687706</v>
       </c>
       <c r="E301" t="n">
-        <v>12.38003889024736</v>
+        <v>12.38003695858405</v>
       </c>
       <c r="F301" t="n">
         <v>3154600</v>
@@ -6472,16 +6472,16 @@
         <v>45089</v>
       </c>
       <c r="B303" t="n">
-        <v>12.45795345306396</v>
+        <v>12.45795440673828</v>
       </c>
       <c r="C303" t="n">
-        <v>12.45795345306396</v>
+        <v>12.45795440673828</v>
       </c>
       <c r="D303" t="n">
-        <v>12.25883355008453</v>
+        <v>12.25883448851593</v>
       </c>
       <c r="E303" t="n">
-        <v>12.3800370051864</v>
+        <v>12.3800379528961</v>
       </c>
       <c r="F303" t="n">
         <v>2572800</v>
@@ -6552,16 +6552,16 @@
         <v>45093</v>
       </c>
       <c r="B307" t="n">
-        <v>12.62244319915771</v>
+        <v>12.62244415283203</v>
       </c>
       <c r="C307" t="n">
-        <v>12.83021984487801</v>
+        <v>12.83022081425066</v>
       </c>
       <c r="D307" t="n">
-        <v>12.4406384277447</v>
+        <v>12.44063936768297</v>
       </c>
       <c r="E307" t="n">
-        <v>12.46661030205199</v>
+        <v>12.46661124395253</v>
       </c>
       <c r="F307" t="n">
         <v>5319000</v>
@@ -6572,16 +6572,16 @@
         <v>45096</v>
       </c>
       <c r="B308" t="n">
-        <v>12.61378574371338</v>
+        <v>12.6137866973877</v>
       </c>
       <c r="C308" t="n">
-        <v>12.80424808345158</v>
+        <v>12.80424905152594</v>
       </c>
       <c r="D308" t="n">
-        <v>12.38869478834751</v>
+        <v>12.38869572500366</v>
       </c>
       <c r="E308" t="n">
-        <v>12.80424808345158</v>
+        <v>12.80424905152594</v>
       </c>
       <c r="F308" t="n">
         <v>3301400</v>
@@ -6592,16 +6592,16 @@
         <v>45097</v>
       </c>
       <c r="B309" t="n">
-        <v>12.72633171081543</v>
+        <v>12.72633266448975</v>
       </c>
       <c r="C309" t="n">
-        <v>12.89947891815102</v>
+        <v>12.89947988480048</v>
       </c>
       <c r="D309" t="n">
-        <v>12.64841526110666</v>
+        <v>12.64841620894215</v>
       </c>
       <c r="E309" t="n">
-        <v>12.69170226934831</v>
+        <v>12.6917032204276</v>
       </c>
       <c r="F309" t="n">
         <v>3568000</v>
@@ -6612,16 +6612,16 @@
         <v>45098</v>
       </c>
       <c r="B310" t="n">
-        <v>12.86484909057617</v>
+        <v>12.86485004425049</v>
       </c>
       <c r="C310" t="n">
-        <v>12.90813609751867</v>
+        <v>12.90813705440186</v>
       </c>
       <c r="D310" t="n">
-        <v>12.63975814061098</v>
+        <v>12.63975907759925</v>
       </c>
       <c r="E310" t="n">
-        <v>12.75230320277808</v>
+        <v>12.75230414810935</v>
       </c>
       <c r="F310" t="n">
         <v>5022600</v>
@@ -6652,16 +6652,16 @@
         <v>45100</v>
       </c>
       <c r="B312" t="n">
-        <v>12.94276714324951</v>
+        <v>12.9427661895752</v>
       </c>
       <c r="C312" t="n">
-        <v>13.07262818018377</v>
+        <v>13.07262721694078</v>
       </c>
       <c r="D312" t="n">
-        <v>12.76096235204642</v>
+        <v>12.7609614117682</v>
       </c>
       <c r="E312" t="n">
-        <v>12.81290693194634</v>
+        <v>12.81290598784064</v>
       </c>
       <c r="F312" t="n">
         <v>2959500</v>
@@ -6672,16 +6672,16 @@
         <v>45103</v>
       </c>
       <c r="B313" t="n">
-        <v>12.71767520904541</v>
+        <v>12.71767425537109</v>
       </c>
       <c r="C313" t="n">
-        <v>13.01202589898095</v>
+        <v>13.01202492323384</v>
       </c>
       <c r="D313" t="n">
-        <v>12.66573145531036</v>
+        <v>12.66573050553121</v>
       </c>
       <c r="E313" t="n">
-        <v>12.94276701024684</v>
+        <v>12.94276603969331</v>
       </c>
       <c r="F313" t="n">
         <v>2677600</v>
@@ -6692,16 +6692,16 @@
         <v>45104</v>
       </c>
       <c r="B314" t="n">
-        <v>12.50124073028564</v>
+        <v>12.50123977661133</v>
       </c>
       <c r="C314" t="n">
-        <v>12.83887842546918</v>
+        <v>12.83887744603771</v>
       </c>
       <c r="D314" t="n">
-        <v>12.39735239922096</v>
+        <v>12.3973514534719</v>
       </c>
       <c r="E314" t="n">
-        <v>12.76961953809272</v>
+        <v>12.76961856394476</v>
       </c>
       <c r="F314" t="n">
         <v>3014700</v>
@@ -6792,16 +6792,16 @@
         <v>45111</v>
       </c>
       <c r="B319" t="n">
-        <v>12.34540843963623</v>
+        <v>12.34540748596191</v>
       </c>
       <c r="C319" t="n">
-        <v>12.40600975866739</v>
+        <v>12.40600880031166</v>
       </c>
       <c r="D319" t="n">
-        <v>12.23286254312761</v>
+        <v>12.23286159814739</v>
       </c>
       <c r="E319" t="n">
-        <v>12.38869544992894</v>
+        <v>12.38869449291073</v>
       </c>
       <c r="F319" t="n">
         <v>2230100</v>
@@ -6832,16 +6832,16 @@
         <v>45113</v>
       </c>
       <c r="B321" t="n">
-        <v>12.32809352874756</v>
+        <v>12.32809257507324</v>
       </c>
       <c r="C321" t="n">
-        <v>12.48392643837378</v>
+        <v>12.48392547264458</v>
       </c>
       <c r="D321" t="n">
-        <v>12.25017707393445</v>
+        <v>12.25017612628758</v>
       </c>
       <c r="E321" t="n">
-        <v>12.43198185995469</v>
+        <v>12.4319808982438</v>
       </c>
       <c r="F321" t="n">
         <v>2081000</v>
@@ -6852,16 +6852,16 @@
         <v>45114</v>
       </c>
       <c r="B322" t="n">
-        <v>12.34540843963623</v>
+        <v>12.34540748596191</v>
       </c>
       <c r="C322" t="n">
-        <v>12.48392621206805</v>
+        <v>12.48392524769333</v>
       </c>
       <c r="D322" t="n">
-        <v>12.25883441905082</v>
+        <v>12.25883347206429</v>
       </c>
       <c r="E322" t="n">
-        <v>12.42332489303689</v>
+        <v>12.42332393334358</v>
       </c>
       <c r="F322" t="n">
         <v>2149700</v>
@@ -6892,16 +6892,16 @@
         <v>45118</v>
       </c>
       <c r="B324" t="n">
-        <v>12.34540843963623</v>
+        <v>12.34540748596191</v>
       </c>
       <c r="C324" t="n">
-        <v>12.39735219148264</v>
+        <v>12.3973512337957</v>
       </c>
       <c r="D324" t="n">
-        <v>12.23286254312761</v>
+        <v>12.23286159814739</v>
       </c>
       <c r="E324" t="n">
-        <v>12.38869544992894</v>
+        <v>12.38869449291073</v>
       </c>
       <c r="F324" t="n">
         <v>1919200</v>
@@ -7072,16 +7072,16 @@
         <v>45131</v>
       </c>
       <c r="B333" t="n">
-        <v>12.34540843963623</v>
+        <v>12.34540748596191</v>
       </c>
       <c r="C333" t="n">
-        <v>12.42332489303689</v>
+        <v>12.42332393334358</v>
       </c>
       <c r="D333" t="n">
-        <v>12.31943573808198</v>
+        <v>12.31943478641403</v>
       </c>
       <c r="E333" t="n">
-        <v>12.42332489303689</v>
+        <v>12.42332393334358</v>
       </c>
       <c r="F333" t="n">
         <v>1347200</v>
@@ -7092,16 +7092,16 @@
         <v>45132</v>
       </c>
       <c r="B334" t="n">
-        <v>12.17226123809814</v>
+        <v>12.17226219177246</v>
       </c>
       <c r="C334" t="n">
-        <v>12.47526865923354</v>
+        <v>12.47526963664793</v>
       </c>
       <c r="D334" t="n">
-        <v>12.16360367090343</v>
+        <v>12.16360462389945</v>
       </c>
       <c r="E334" t="n">
-        <v>12.41466734013267</v>
+        <v>12.41466831279906</v>
       </c>
       <c r="F334" t="n">
         <v>2710400</v>
@@ -7132,16 +7132,16 @@
         <v>45134</v>
       </c>
       <c r="B336" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C336" t="n">
-        <v>12.22420445012837</v>
+        <v>12.22420541473304</v>
       </c>
       <c r="D336" t="n">
-        <v>12.03374210841168</v>
+        <v>12.03374305798708</v>
       </c>
       <c r="E336" t="n">
-        <v>12.18091744169762</v>
+        <v>12.18091840288654</v>
       </c>
       <c r="F336" t="n">
         <v>2852900</v>
@@ -7212,16 +7212,16 @@
         <v>45140</v>
       </c>
       <c r="B340" t="n">
-        <v>12.22420597076416</v>
+        <v>12.22420406341553</v>
       </c>
       <c r="C340" t="n">
-        <v>12.23286353865348</v>
+        <v>12.232861629954</v>
       </c>
       <c r="D340" t="n">
-        <v>12.12897520087505</v>
+        <v>12.12897330838532</v>
       </c>
       <c r="E340" t="n">
-        <v>12.13763276876436</v>
+        <v>12.13763087492379</v>
       </c>
       <c r="F340" t="n">
         <v>1697600</v>
@@ -7292,16 +7292,16 @@
         <v>45146</v>
       </c>
       <c r="B344" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C344" t="n">
-        <v>12.15494556689158</v>
+        <v>12.15494652603107</v>
       </c>
       <c r="D344" t="n">
-        <v>11.92985378355649</v>
+        <v>11.92985472493413</v>
       </c>
       <c r="E344" t="n">
-        <v>11.99045592561195</v>
+        <v>11.99045687177166</v>
       </c>
       <c r="F344" t="n">
         <v>2176400</v>
@@ -7332,16 +7332,16 @@
         <v>45148</v>
       </c>
       <c r="B346" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C346" t="n">
-        <v>12.09434549372545</v>
+        <v>12.09434452900206</v>
       </c>
       <c r="D346" t="n">
-        <v>11.88656799702522</v>
+        <v>11.88656704887551</v>
       </c>
       <c r="E346" t="n">
-        <v>12.01642903566675</v>
+        <v>12.01642807715848</v>
       </c>
       <c r="F346" t="n">
         <v>2835300</v>
@@ -7352,16 +7352,16 @@
         <v>45149</v>
       </c>
       <c r="B347" t="n">
-        <v>11.92119789123535</v>
+        <v>11.92119693756104</v>
       </c>
       <c r="C347" t="n">
-        <v>11.97314164454614</v>
+        <v>11.97314068671642</v>
       </c>
       <c r="D347" t="n">
-        <v>11.83462386820927</v>
+        <v>11.83462292146072</v>
       </c>
       <c r="E347" t="n">
-        <v>11.97314164454614</v>
+        <v>11.97314068671642</v>
       </c>
       <c r="F347" t="n">
         <v>2472600</v>
@@ -7372,16 +7372,16 @@
         <v>45152</v>
       </c>
       <c r="B348" t="n">
-        <v>11.9125394821167</v>
+        <v>11.91254043579102</v>
       </c>
       <c r="C348" t="n">
-        <v>11.96448323175737</v>
+        <v>11.96448418959011</v>
       </c>
       <c r="D348" t="n">
-        <v>11.82596546520757</v>
+        <v>11.82596641195109</v>
       </c>
       <c r="E348" t="n">
-        <v>11.92119704893382</v>
+        <v>11.92119800330122</v>
       </c>
       <c r="F348" t="n">
         <v>1369900</v>
@@ -7392,16 +7392,16 @@
         <v>45153</v>
       </c>
       <c r="B349" t="n">
-        <v>11.86059474945068</v>
+        <v>11.860595703125</v>
       </c>
       <c r="C349" t="n">
-        <v>11.9991125141623</v>
+        <v>11.99911347897441</v>
       </c>
       <c r="D349" t="n">
-        <v>11.85193718274846</v>
+        <v>11.85193813572664</v>
       </c>
       <c r="E349" t="n">
-        <v>11.91253932403304</v>
+        <v>11.91254028188406</v>
       </c>
       <c r="F349" t="n">
         <v>2713800</v>
@@ -7412,16 +7412,16 @@
         <v>45154</v>
       </c>
       <c r="B350" t="n">
-        <v>11.68744850158691</v>
+        <v>11.6874475479126</v>
       </c>
       <c r="C350" t="n">
-        <v>11.91254030050967</v>
+        <v>11.91253932846828</v>
       </c>
       <c r="D350" t="n">
-        <v>11.64416149015853</v>
+        <v>11.64416054001635</v>
       </c>
       <c r="E350" t="n">
-        <v>11.886567598274</v>
+        <v>11.88656662835193</v>
       </c>
       <c r="F350" t="n">
         <v>3946200</v>
@@ -7432,16 +7432,16 @@
         <v>45155</v>
       </c>
       <c r="B351" t="n">
-        <v>11.71342086791992</v>
+        <v>11.71341991424561</v>
       </c>
       <c r="C351" t="n">
-        <v>11.78267975884857</v>
+        <v>11.78267879953539</v>
       </c>
       <c r="D351" t="n">
-        <v>11.66147711253899</v>
+        <v>11.66147616309379</v>
       </c>
       <c r="E351" t="n">
-        <v>11.73073600346764</v>
+        <v>11.73073504838357</v>
       </c>
       <c r="F351" t="n">
         <v>2345000</v>
@@ -7452,16 +7452,16 @@
         <v>45156</v>
       </c>
       <c r="B352" t="n">
-        <v>11.77402114868164</v>
+        <v>11.77402210235596</v>
       </c>
       <c r="C352" t="n">
-        <v>11.80865058865178</v>
+        <v>11.80865154513102</v>
       </c>
       <c r="D352" t="n">
-        <v>11.65281769597066</v>
+        <v>11.65281863982772</v>
       </c>
       <c r="E352" t="n">
-        <v>11.71341900951066</v>
+        <v>11.71341995827632</v>
       </c>
       <c r="F352" t="n">
         <v>3061800</v>
@@ -7492,16 +7492,16 @@
         <v>45160</v>
       </c>
       <c r="B354" t="n">
-        <v>11.79999446868896</v>
+        <v>11.79999351501465</v>
       </c>
       <c r="C354" t="n">
-        <v>11.86925335711897</v>
+        <v>11.86925239784715</v>
       </c>
       <c r="D354" t="n">
-        <v>11.73073558025896</v>
+        <v>11.73073463218214</v>
       </c>
       <c r="E354" t="n">
-        <v>11.79133690122745</v>
+        <v>11.79133594825283</v>
       </c>
       <c r="F354" t="n">
         <v>2231700</v>
@@ -7512,16 +7512,16 @@
         <v>45161</v>
       </c>
       <c r="B355" t="n">
-        <v>11.87790966033936</v>
+        <v>11.87791061401367</v>
       </c>
       <c r="C355" t="n">
-        <v>11.89522396778845</v>
+        <v>11.89522492285292</v>
       </c>
       <c r="D355" t="n">
-        <v>11.79133564620093</v>
+        <v>11.79133659292425</v>
       </c>
       <c r="E355" t="n">
-        <v>11.86059452725928</v>
+        <v>11.86059547954337</v>
       </c>
       <c r="F355" t="n">
         <v>2615000</v>
@@ -7532,16 +7532,16 @@
         <v>45162</v>
       </c>
       <c r="B356" t="n">
-        <v>11.97314071655273</v>
+        <v>11.97314167022705</v>
       </c>
       <c r="C356" t="n">
-        <v>11.99911259119515</v>
+        <v>11.99911354693815</v>
       </c>
       <c r="D356" t="n">
-        <v>11.89522426699448</v>
+        <v>11.89522521446267</v>
       </c>
       <c r="E356" t="n">
-        <v>11.90388183375229</v>
+        <v>11.90388278191006</v>
       </c>
       <c r="F356" t="n">
         <v>2322800</v>
@@ -7612,16 +7612,16 @@
         <v>45168</v>
       </c>
       <c r="B360" t="n">
-        <v>12.11165904998779</v>
+        <v>12.11165809631348</v>
       </c>
       <c r="C360" t="n">
-        <v>12.19823307036272</v>
+        <v>12.19823210987155</v>
       </c>
       <c r="D360" t="n">
-        <v>12.05971529826767</v>
+        <v>12.05971434868342</v>
       </c>
       <c r="E360" t="n">
-        <v>12.17226119450266</v>
+        <v>12.17226023605652</v>
       </c>
       <c r="F360" t="n">
         <v>1998700</v>
@@ -7652,16 +7652,16 @@
         <v>45170</v>
       </c>
       <c r="B362" t="n">
-        <v>12.04239940643311</v>
+        <v>12.04240036010742</v>
       </c>
       <c r="C362" t="n">
-        <v>12.04239940643311</v>
+        <v>12.04240036010742</v>
       </c>
       <c r="D362" t="n">
-        <v>11.89522407643217</v>
+        <v>11.89522501845123</v>
       </c>
       <c r="E362" t="n">
-        <v>11.90388164305129</v>
+        <v>11.90388258575596</v>
       </c>
       <c r="F362" t="n">
         <v>3740800</v>
@@ -7692,16 +7692,16 @@
         <v>45174</v>
       </c>
       <c r="B364" t="n">
-        <v>11.92119789123535</v>
+        <v>11.92119693756104</v>
       </c>
       <c r="C364" t="n">
-        <v>12.06837240936998</v>
+        <v>12.06837144392197</v>
       </c>
       <c r="D364" t="n">
-        <v>11.91254032380653</v>
+        <v>11.9125393708248</v>
       </c>
       <c r="E364" t="n">
-        <v>12.04240053271458</v>
+        <v>12.04239956934427</v>
       </c>
       <c r="F364" t="n">
         <v>3869600</v>
@@ -7712,16 +7712,16 @@
         <v>45175</v>
       </c>
       <c r="B365" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C365" t="n">
-        <v>12.02508660336907</v>
+        <v>12.02508564417022</v>
       </c>
       <c r="D365" t="n">
-        <v>11.81730910666884</v>
+        <v>11.81730816404367</v>
       </c>
       <c r="E365" t="n">
-        <v>11.93851257760805</v>
+        <v>11.9385116253149</v>
       </c>
       <c r="F365" t="n">
         <v>2473500</v>
@@ -7732,16 +7732,16 @@
         <v>45177</v>
       </c>
       <c r="B366" t="n">
-        <v>11.92985343933105</v>
+        <v>11.92985439300537</v>
       </c>
       <c r="C366" t="n">
-        <v>12.07702876837038</v>
+        <v>12.07702973380992</v>
       </c>
       <c r="D366" t="n">
-        <v>11.88656643214931</v>
+        <v>11.88656738236326</v>
       </c>
       <c r="E366" t="n">
-        <v>11.9385110058936</v>
+        <v>11.93851196026</v>
       </c>
       <c r="F366" t="n">
         <v>3462800</v>
@@ -7812,16 +7812,16 @@
         <v>45183</v>
       </c>
       <c r="B370" t="n">
-        <v>12.21554660797119</v>
+        <v>12.21554756164551</v>
       </c>
       <c r="C370" t="n">
-        <v>12.25017604880902</v>
+        <v>12.25017700518688</v>
       </c>
       <c r="D370" t="n">
-        <v>12.09434397785428</v>
+        <v>12.09434492206624</v>
       </c>
       <c r="E370" t="n">
-        <v>12.09434397785428</v>
+        <v>12.09434492206624</v>
       </c>
       <c r="F370" t="n">
         <v>2498700</v>
@@ -7852,16 +7852,16 @@
         <v>45187</v>
       </c>
       <c r="B372" t="n">
-        <v>12.05971527099609</v>
+        <v>12.05971622467041</v>
       </c>
       <c r="C372" t="n">
-        <v>12.24152005286748</v>
+        <v>12.2415210209188</v>
       </c>
       <c r="D372" t="n">
-        <v>11.99911312661827</v>
+        <v>11.99911407550021</v>
       </c>
       <c r="E372" t="n">
-        <v>12.21554735143511</v>
+        <v>12.21554831743252</v>
       </c>
       <c r="F372" t="n">
         <v>3188500</v>
@@ -7912,16 +7912,16 @@
         <v>45190</v>
       </c>
       <c r="B375" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C375" t="n">
-        <v>12.0337433454403</v>
+        <v>12.03374238555092</v>
       </c>
       <c r="D375" t="n">
-        <v>11.877911254954</v>
+        <v>11.8779103074948</v>
       </c>
       <c r="E375" t="n">
-        <v>12.02508660336907</v>
+        <v>12.02508564417022</v>
       </c>
       <c r="F375" t="n">
         <v>4405700</v>
@@ -7932,16 +7932,16 @@
         <v>45191</v>
       </c>
       <c r="B376" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C376" t="n">
-        <v>12.10300223579667</v>
+        <v>12.10300127038276</v>
       </c>
       <c r="D376" t="n">
-        <v>11.92985500990573</v>
+        <v>11.92985405830317</v>
       </c>
       <c r="E376" t="n">
-        <v>12.02508660336907</v>
+        <v>12.02508564417022</v>
       </c>
       <c r="F376" t="n">
         <v>2812600</v>
@@ -7952,16 +7952,16 @@
         <v>45194</v>
       </c>
       <c r="B377" t="n">
-        <v>11.80865097045898</v>
+        <v>11.8086519241333</v>
       </c>
       <c r="C377" t="n">
-        <v>11.97314060922783</v>
+        <v>11.97314157618643</v>
       </c>
       <c r="D377" t="n">
-        <v>11.80865097045898</v>
+        <v>11.8086519241333</v>
       </c>
       <c r="E377" t="n">
-        <v>11.95582630149842</v>
+        <v>11.95582726705872</v>
       </c>
       <c r="F377" t="n">
         <v>3691700</v>
@@ -7972,16 +7972,16 @@
         <v>45195</v>
       </c>
       <c r="B378" t="n">
-        <v>11.83462333679199</v>
+        <v>11.83462238311768</v>
       </c>
       <c r="C378" t="n">
-        <v>12.06837186745655</v>
+        <v>12.06837089494598</v>
       </c>
       <c r="D378" t="n">
-        <v>11.78267876018263</v>
+        <v>11.78267781069418</v>
       </c>
       <c r="E378" t="n">
-        <v>11.80865146130283</v>
+        <v>11.80865050972141</v>
       </c>
       <c r="F378" t="n">
         <v>7795500</v>
@@ -8072,16 +8072,16 @@
         <v>45202</v>
       </c>
       <c r="B383" t="n">
-        <v>11.80865097045898</v>
+        <v>11.8086519241333</v>
       </c>
       <c r="C383" t="n">
-        <v>11.91253929372841</v>
+        <v>11.91254025579282</v>
       </c>
       <c r="D383" t="n">
-        <v>11.75670639600877</v>
+        <v>11.75670734548801</v>
       </c>
       <c r="E383" t="n">
-        <v>11.8605947192782</v>
+        <v>11.86059567714752</v>
       </c>
       <c r="F383" t="n">
         <v>2809600</v>
@@ -8092,16 +8092,16 @@
         <v>45203</v>
       </c>
       <c r="B384" t="n">
-        <v>11.77402114868164</v>
+        <v>11.77402210235596</v>
       </c>
       <c r="C384" t="n">
-        <v>11.86059433579151</v>
+        <v>11.86059529647809</v>
       </c>
       <c r="D384" t="n">
-        <v>11.7480484494808</v>
+        <v>11.74804940105138</v>
       </c>
       <c r="E384" t="n">
-        <v>11.80865058865178</v>
+        <v>11.80865154513102</v>
       </c>
       <c r="F384" t="n">
         <v>4367600</v>
@@ -8152,16 +8152,16 @@
         <v>45208</v>
       </c>
       <c r="B387" t="n">
-        <v>11.9125394821167</v>
+        <v>11.91254043579102</v>
       </c>
       <c r="C387" t="n">
-        <v>11.92985379011992</v>
+        <v>11.92985474518035</v>
       </c>
       <c r="D387" t="n">
-        <v>11.61818881538288</v>
+        <v>11.61818974549255</v>
       </c>
       <c r="E387" t="n">
-        <v>11.61818881538288</v>
+        <v>11.61818974549255</v>
       </c>
       <c r="F387" t="n">
         <v>4118900</v>
@@ -8172,16 +8172,16 @@
         <v>45209</v>
       </c>
       <c r="B388" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C388" t="n">
-        <v>12.16360313370393</v>
+        <v>12.16360409352659</v>
       </c>
       <c r="D388" t="n">
-        <v>11.9125394755628</v>
+        <v>11.91254041557417</v>
       </c>
       <c r="E388" t="n">
-        <v>11.92985378355649</v>
+        <v>11.92985472493413</v>
       </c>
       <c r="F388" t="n">
         <v>3643400</v>
@@ -8192,16 +8192,16 @@
         <v>45210</v>
       </c>
       <c r="B389" t="n">
-        <v>12.09434509277344</v>
+        <v>12.09434413909912</v>
       </c>
       <c r="C389" t="n">
-        <v>12.18957585744859</v>
+        <v>12.18957489626505</v>
       </c>
       <c r="D389" t="n">
-        <v>12.00777106988252</v>
+        <v>12.00777012303482</v>
       </c>
       <c r="E389" t="n">
-        <v>12.09434509277344</v>
+        <v>12.09434413909912</v>
       </c>
       <c r="F389" t="n">
         <v>3458500</v>
@@ -8212,16 +8212,16 @@
         <v>45212</v>
       </c>
       <c r="B390" t="n">
-        <v>12.02508640289307</v>
+        <v>12.02508544921875</v>
       </c>
       <c r="C390" t="n">
-        <v>12.19823362589739</v>
+        <v>12.19823265849127</v>
       </c>
       <c r="D390" t="n">
-        <v>12.02508640289307</v>
+        <v>12.02508544921875</v>
       </c>
       <c r="E390" t="n">
-        <v>12.0943452920948</v>
+        <v>12.09434433292776</v>
       </c>
       <c r="F390" t="n">
         <v>4555500</v>
@@ -8232,16 +8232,16 @@
         <v>45215</v>
       </c>
       <c r="B391" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="C391" t="n">
-        <v>12.12031690101054</v>
+        <v>12.12031593631109</v>
       </c>
       <c r="D391" t="n">
-        <v>11.98179912567139</v>
+        <v>11.98179817199707</v>
       </c>
       <c r="E391" t="n">
-        <v>12.05971558070743</v>
+        <v>12.05971462083146</v>
       </c>
       <c r="F391" t="n">
         <v>3983600</v>
@@ -8252,16 +8252,16 @@
         <v>45216</v>
       </c>
       <c r="B392" t="n">
-        <v>11.9558277130127</v>
+        <v>11.95582675933838</v>
       </c>
       <c r="C392" t="n">
-        <v>12.10300223579667</v>
+        <v>12.10300127038276</v>
       </c>
       <c r="D392" t="n">
-        <v>11.88656799702522</v>
+        <v>11.88656704887551</v>
       </c>
       <c r="E392" t="n">
-        <v>11.97314202278624</v>
+        <v>11.97314106773082</v>
       </c>
       <c r="F392" t="n">
         <v>5165000</v>
@@ -8312,16 +8312,16 @@
         <v>45219</v>
       </c>
       <c r="B395" t="n">
-        <v>11.76536464691162</v>
+        <v>11.76536560058594</v>
       </c>
       <c r="C395" t="n">
-        <v>11.91253998651014</v>
+        <v>11.91254095211416</v>
       </c>
       <c r="D395" t="n">
-        <v>11.67013305915314</v>
+        <v>11.67013400510819</v>
       </c>
       <c r="E395" t="n">
-        <v>11.67013305915314</v>
+        <v>11.67013400510819</v>
       </c>
       <c r="F395" t="n">
         <v>6261200</v>
@@ -8352,16 +8352,16 @@
         <v>45223</v>
       </c>
       <c r="B397" t="n">
-        <v>11.63550281524658</v>
+        <v>11.6355037689209</v>
       </c>
       <c r="C397" t="n">
-        <v>11.81730758543626</v>
+        <v>11.81730855401174</v>
       </c>
       <c r="D397" t="n">
-        <v>11.54892962626116</v>
+        <v>11.54893057283972</v>
       </c>
       <c r="E397" t="n">
-        <v>11.80865084447942</v>
+        <v>11.80865181234537</v>
       </c>
       <c r="F397" t="n">
         <v>3637500</v>
@@ -8512,16 +8512,16 @@
         <v>45236</v>
       </c>
       <c r="B405" t="n">
-        <v>12.02508640289307</v>
+        <v>12.02508544921875</v>
       </c>
       <c r="C405" t="n">
-        <v>12.07703015697882</v>
+        <v>12.077029199185</v>
       </c>
       <c r="D405" t="n">
-        <v>11.81730890965679</v>
+        <v>11.8173079724607</v>
       </c>
       <c r="E405" t="n">
-        <v>11.94716994613335</v>
+        <v>11.94716899863836</v>
       </c>
       <c r="F405" t="n">
         <v>2982900</v>
@@ -8552,16 +8552,16 @@
         <v>45238</v>
       </c>
       <c r="B407" t="n">
-        <v>11.81730842590332</v>
+        <v>11.817307472229</v>
       </c>
       <c r="C407" t="n">
-        <v>11.96448376583999</v>
+        <v>11.96448280028841</v>
       </c>
       <c r="D407" t="n">
-        <v>11.73073523076066</v>
+        <v>11.73073428407293</v>
       </c>
       <c r="E407" t="n">
-        <v>11.9385118898603</v>
+        <v>11.93851092640469</v>
       </c>
       <c r="F407" t="n">
         <v>5488500</v>
@@ -8652,16 +8652,16 @@
         <v>45246</v>
       </c>
       <c r="B412" t="n">
-        <v>12.49258327484131</v>
+        <v>12.49258422851562</v>
       </c>
       <c r="C412" t="n">
-        <v>12.49258327484131</v>
+        <v>12.49258422851562</v>
       </c>
       <c r="D412" t="n">
-        <v>12.12897372407367</v>
+        <v>12.12897464999031</v>
       </c>
       <c r="E412" t="n">
-        <v>12.12897372407367</v>
+        <v>12.12897464999031</v>
       </c>
       <c r="F412" t="n">
         <v>6741500</v>
@@ -8672,16 +8672,16 @@
         <v>45247</v>
       </c>
       <c r="B413" t="n">
-        <v>12.25017642974854</v>
+        <v>12.25017738342285</v>
       </c>
       <c r="C413" t="n">
-        <v>12.48392578189597</v>
+        <v>12.48392675376763</v>
       </c>
       <c r="D413" t="n">
-        <v>12.14628810400446</v>
+        <v>12.14628904959109</v>
       </c>
       <c r="E413" t="n">
-        <v>12.48392578189597</v>
+        <v>12.48392675376763</v>
       </c>
       <c r="F413" t="n">
         <v>3124800</v>
@@ -8692,16 +8692,16 @@
         <v>45250</v>
       </c>
       <c r="B414" t="n">
-        <v>12.08568668365479</v>
+        <v>12.0856876373291</v>
       </c>
       <c r="C414" t="n">
-        <v>12.23286201694073</v>
+        <v>12.23286298222856</v>
       </c>
       <c r="D414" t="n">
-        <v>11.99045592561195</v>
+        <v>11.99045687177166</v>
       </c>
       <c r="E414" t="n">
-        <v>12.20689014213468</v>
+        <v>12.20689110537309</v>
       </c>
       <c r="F414" t="n">
         <v>3248400</v>
@@ -8712,16 +8712,16 @@
         <v>45251</v>
       </c>
       <c r="B415" t="n">
-        <v>11.97314071655273</v>
+        <v>11.97314167022705</v>
       </c>
       <c r="C415" t="n">
-        <v>12.09434417426901</v>
+        <v>12.09434513759732</v>
       </c>
       <c r="D415" t="n">
-        <v>11.9125394005101</v>
+        <v>11.91254034935745</v>
       </c>
       <c r="E415" t="n">
-        <v>12.0856866075112</v>
+        <v>12.08568757014993</v>
       </c>
       <c r="F415" t="n">
         <v>2713400</v>
@@ -8752,16 +8752,16 @@
         <v>45253</v>
       </c>
       <c r="B417" t="n">
-        <v>12.56184196472168</v>
+        <v>12.561842918396</v>
       </c>
       <c r="C417" t="n">
-        <v>12.76961861177884</v>
+        <v>12.76961958122722</v>
       </c>
       <c r="D417" t="n">
-        <v>12.46661038226389</v>
+        <v>12.46661132870839</v>
       </c>
       <c r="E417" t="n">
-        <v>12.76961861177884</v>
+        <v>12.76961958122722</v>
       </c>
       <c r="F417" t="n">
         <v>9122900</v>
@@ -8832,16 +8832,16 @@
         <v>45259</v>
       </c>
       <c r="B421" t="n">
-        <v>12.56184196472168</v>
+        <v>12.561842918396</v>
       </c>
       <c r="C421" t="n">
-        <v>12.75230347837524</v>
+        <v>12.75230444650908</v>
       </c>
       <c r="D421" t="n">
-        <v>12.56184196472168</v>
+        <v>12.561842918396</v>
       </c>
       <c r="E421" t="n">
-        <v>12.72633160390085</v>
+        <v>12.72633257006295</v>
       </c>
       <c r="F421" t="n">
         <v>5869600</v>
@@ -8852,16 +8852,16 @@
         <v>45260</v>
       </c>
       <c r="B422" t="n">
-        <v>12.71767520904541</v>
+        <v>12.71767425537109</v>
       </c>
       <c r="C422" t="n">
-        <v>12.71767520904541</v>
+        <v>12.71767425537109</v>
       </c>
       <c r="D422" t="n">
-        <v>12.58781499907671</v>
+        <v>12.58781405514036</v>
       </c>
       <c r="E422" t="n">
-        <v>12.6311020109433</v>
+        <v>12.63110106376094</v>
       </c>
       <c r="F422" t="n">
         <v>4162000</v>
@@ -8872,16 +8872,16 @@
         <v>45261</v>
       </c>
       <c r="B423" t="n">
-        <v>12.86484909057617</v>
+        <v>12.86485004425049</v>
       </c>
       <c r="C423" t="n">
-        <v>12.96873741185957</v>
+        <v>12.96873837323515</v>
       </c>
       <c r="D423" t="n">
-        <v>12.70901702146657</v>
+        <v>12.70901796358902</v>
       </c>
       <c r="E423" t="n">
-        <v>12.72633132886498</v>
+        <v>12.72633227227094</v>
       </c>
       <c r="F423" t="n">
         <v>6458300</v>
@@ -8892,16 +8892,16 @@
         <v>45264</v>
       </c>
       <c r="B424" t="n">
-        <v>12.89947891235352</v>
+        <v>12.89947986602783</v>
       </c>
       <c r="C424" t="n">
-        <v>12.98605292879791</v>
+        <v>12.98605388887275</v>
       </c>
       <c r="D424" t="n">
-        <v>12.86484947090196</v>
+        <v>12.86485042201608</v>
       </c>
       <c r="E424" t="n">
-        <v>12.94276592057571</v>
+        <v>12.94276687745029</v>
       </c>
       <c r="F424" t="n">
         <v>7048400</v>
@@ -8952,16 +8952,16 @@
         <v>45267</v>
       </c>
       <c r="B427" t="n">
-        <v>13.1159143447876</v>
+        <v>13.11591339111328</v>
       </c>
       <c r="C427" t="n">
-        <v>13.15054378945223</v>
+        <v>13.15054283325996</v>
       </c>
       <c r="D427" t="n">
-        <v>12.97739656612907</v>
+        <v>12.97739562252655</v>
       </c>
       <c r="E427" t="n">
-        <v>13.10725760284475</v>
+        <v>13.10725664979988</v>
       </c>
       <c r="F427" t="n">
         <v>6196000</v>
@@ -8972,16 +8972,16 @@
         <v>45268</v>
       </c>
       <c r="B428" t="n">
-        <v>12.92545223236084</v>
+        <v>12.92545127868652</v>
       </c>
       <c r="C428" t="n">
-        <v>13.15920076695787</v>
+        <v>13.15919979603697</v>
       </c>
       <c r="D428" t="n">
-        <v>12.86485008769187</v>
+        <v>12.86484913848894</v>
       </c>
       <c r="E428" t="n">
-        <v>13.15920076695787</v>
+        <v>13.15919979603697</v>
       </c>
       <c r="F428" t="n">
         <v>10990100</v>
@@ -21969,282 +21969,282 @@
     </row>
     <row r="1078">
       <c r="A1078" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B1078" t="n">
-        <v>11.3100004196167</v>
+        <v>11.21000003814697</v>
       </c>
       <c r="C1078" t="n">
-        <v>11.68000030517578</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="D1078" t="n">
-        <v>11.3100004196167</v>
+        <v>11.19999980926514</v>
       </c>
       <c r="E1078" t="n">
-        <v>11.61999988555908</v>
+        <v>11.27999973297119</v>
       </c>
       <c r="F1078" t="n">
-        <v>1721500</v>
+        <v>2651800</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B1079" t="n">
-        <v>11.21000003814697</v>
+        <v>11.55000019073486</v>
       </c>
       <c r="C1079" t="n">
-        <v>11.35999965667725</v>
+        <v>11.64000034332275</v>
       </c>
       <c r="D1079" t="n">
-        <v>11.19999980926514</v>
+        <v>11.1899995803833</v>
       </c>
       <c r="E1079" t="n">
-        <v>11.27999973297119</v>
+        <v>11.26000022888184</v>
       </c>
       <c r="F1079" t="n">
-        <v>2651800</v>
+        <v>2065500</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B1080" t="n">
-        <v>11.55000019073486</v>
+        <v>11.39000034332275</v>
       </c>
       <c r="C1080" t="n">
-        <v>11.64000034332275</v>
+        <v>11.5</v>
       </c>
       <c r="D1080" t="n">
-        <v>11.1899995803833</v>
+        <v>11.30000019073486</v>
       </c>
       <c r="E1080" t="n">
-        <v>11.26000022888184</v>
+        <v>11.5</v>
       </c>
       <c r="F1080" t="n">
-        <v>2065500</v>
+        <v>1499900</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B1081" t="n">
-        <v>11.39000034332275</v>
+        <v>11.1899995803833</v>
       </c>
       <c r="C1081" t="n">
-        <v>11.5</v>
+        <v>11.38000011444092</v>
       </c>
       <c r="D1081" t="n">
-        <v>11.30000019073486</v>
+        <v>11.18000030517578</v>
       </c>
       <c r="E1081" t="n">
-        <v>11.5</v>
+        <v>11.34000015258789</v>
       </c>
       <c r="F1081" t="n">
-        <v>1499900</v>
+        <v>1240200</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B1082" t="n">
-        <v>11.1899995803833</v>
+        <v>11.31999969482422</v>
       </c>
       <c r="C1082" t="n">
-        <v>11.38000011444092</v>
+        <v>11.36999988555908</v>
       </c>
       <c r="D1082" t="n">
-        <v>11.18000030517578</v>
+        <v>11.15999984741211</v>
       </c>
       <c r="E1082" t="n">
-        <v>11.34000015258789</v>
+        <v>11.25</v>
       </c>
       <c r="F1082" t="n">
-        <v>1240200</v>
+        <v>1323600</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B1083" t="n">
-        <v>11.31999969482422</v>
+        <v>11.44999980926514</v>
       </c>
       <c r="C1083" t="n">
-        <v>11.36999988555908</v>
+        <v>11.72000026702881</v>
       </c>
       <c r="D1083" t="n">
-        <v>11.15999984741211</v>
+        <v>11.38000011444092</v>
       </c>
       <c r="E1083" t="n">
-        <v>11.25</v>
+        <v>11.52999973297119</v>
       </c>
       <c r="F1083" t="n">
-        <v>1323600</v>
+        <v>1564600</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B1084" t="n">
+        <v>11.10999965667725</v>
+      </c>
+      <c r="C1084" t="n">
+        <v>11.47000026702881</v>
+      </c>
+      <c r="D1084" t="n">
+        <v>11.07999992370605</v>
+      </c>
+      <c r="E1084" t="n">
         <v>11.44999980926514</v>
       </c>
-      <c r="C1084" t="n">
-        <v>11.72000026702881</v>
-      </c>
-      <c r="D1084" t="n">
-        <v>11.38000011444092</v>
-      </c>
-      <c r="E1084" t="n">
-        <v>11.52999973297119</v>
-      </c>
       <c r="F1084" t="n">
-        <v>1564600</v>
+        <v>2114700</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B1085" t="n">
-        <v>11.10999965667725</v>
+        <v>11.19999980926514</v>
       </c>
       <c r="C1085" t="n">
-        <v>11.47000026702881</v>
+        <v>11.3100004196167</v>
       </c>
       <c r="D1085" t="n">
-        <v>11.07999992370605</v>
+        <v>11.09000015258789</v>
       </c>
       <c r="E1085" t="n">
-        <v>11.44999980926514</v>
+        <v>11.18000030517578</v>
       </c>
       <c r="F1085" t="n">
-        <v>2114700</v>
+        <v>2543000</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B1086" t="n">
         <v>11.19999980926514</v>
       </c>
       <c r="C1086" t="n">
-        <v>11.3100004196167</v>
+        <v>11.21000003814697</v>
       </c>
       <c r="D1086" t="n">
-        <v>11.09000015258789</v>
+        <v>10.84000015258789</v>
       </c>
       <c r="E1086" t="n">
-        <v>11.18000030517578</v>
+        <v>11.03999996185303</v>
       </c>
       <c r="F1086" t="n">
-        <v>2543000</v>
+        <v>4621900</v>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B1087" t="n">
-        <v>11.19999980926514</v>
+        <v>11.27999973297119</v>
       </c>
       <c r="C1087" t="n">
-        <v>11.21000003814697</v>
+        <v>11.56999969482422</v>
       </c>
       <c r="D1087" t="n">
-        <v>10.84000015258789</v>
+        <v>11.13000011444092</v>
       </c>
       <c r="E1087" t="n">
-        <v>11.03999996185303</v>
+        <v>11.32999992370605</v>
       </c>
       <c r="F1087" t="n">
-        <v>4621900</v>
+        <v>4289500</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B1088" t="n">
-        <v>11.27999973297119</v>
+        <v>11.15999984741211</v>
       </c>
       <c r="C1088" t="n">
-        <v>11.56999969482422</v>
+        <v>11.55000019073486</v>
       </c>
       <c r="D1088" t="n">
-        <v>11.13000011444092</v>
+        <v>11.07999992370605</v>
       </c>
       <c r="E1088" t="n">
-        <v>11.32999992370605</v>
+        <v>11.31999969482422</v>
       </c>
       <c r="F1088" t="n">
-        <v>4289500</v>
+        <v>5192700</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B1089" t="n">
-        <v>11.15999984741211</v>
+        <v>10.97999954223633</v>
       </c>
       <c r="C1089" t="n">
-        <v>11.55000019073486</v>
+        <v>11.14000034332275</v>
       </c>
       <c r="D1089" t="n">
-        <v>11.07999992370605</v>
+        <v>10.61999988555908</v>
       </c>
       <c r="E1089" t="n">
-        <v>11.31999969482422</v>
+        <v>11.14000034332275</v>
       </c>
       <c r="F1089" t="n">
-        <v>5192700</v>
+        <v>5195300</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B1090" t="n">
+        <v>10.8100004196167</v>
+      </c>
+      <c r="C1090" t="n">
         <v>10.97999954223633</v>
       </c>
-      <c r="C1090" t="n">
-        <v>11.14000034332275</v>
-      </c>
       <c r="D1090" t="n">
-        <v>10.61999988555908</v>
+        <v>10.55000019073486</v>
       </c>
       <c r="E1090" t="n">
-        <v>11.14000034332275</v>
+        <v>10.97999954223633</v>
       </c>
       <c r="F1090" t="n">
-        <v>5195300</v>
+        <v>4285100</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B1091" t="n">
-        <v>10.8100004196167</v>
+        <v>10.69999980926514</v>
       </c>
       <c r="C1091" t="n">
-        <v>10.97999954223633</v>
+        <v>10.82999992370605</v>
       </c>
       <c r="D1091" t="n">
-        <v>10.55000019073486</v>
+        <v>10.5600004196167</v>
       </c>
       <c r="E1091" t="n">
-        <v>10.97999954223633</v>
+        <v>10.80000019073486</v>
       </c>
       <c r="F1091" t="n">
-        <v>4285100</v>
+        <v>3624700</v>
       </c>
     </row>
     <row r="1092">
@@ -22292,19 +22292,39 @@
         <v>46247</v>
       </c>
       <c r="B1094" t="n">
-        <v>10.29</v>
+        <v>10.28999996185303</v>
       </c>
       <c r="C1094" t="n">
-        <v>10.48</v>
+        <v>10.47999954223633</v>
       </c>
       <c r="D1094" t="n">
-        <v>10.23</v>
+        <v>10.22999954223633</v>
       </c>
       <c r="E1094" t="n">
-        <v>10.35</v>
+        <v>10.35000038146973</v>
       </c>
       <c r="F1094" t="n">
         <v>3162000</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B1095" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="C1095" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="D1095" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="E1095" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="F1095" t="n">
+        <v>3773500</v>
       </c>
     </row>
   </sheetData>

--- a/database/AURE3.xlsx
+++ b/database/AURE3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1095"/>
+  <dimension ref="A1:F1096"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44648</v>
       </c>
       <c r="B2" t="n">
-        <v>12.75723361968994</v>
+        <v>12.75723075866699</v>
       </c>
       <c r="C2" t="n">
-        <v>13.06838536969437</v>
+        <v>13.06838243889043</v>
       </c>
       <c r="D2" t="n">
-        <v>12.0260266362574</v>
+        <v>12.02602393921985</v>
       </c>
       <c r="E2" t="n">
-        <v>13.06838536969437</v>
+        <v>13.06838243889043</v>
       </c>
       <c r="F2" t="n">
         <v>5237900</v>
@@ -472,16 +472,16 @@
         <v>44649</v>
       </c>
       <c r="B3" t="n">
-        <v>12.91280937194824</v>
+        <v>12.91281032562256</v>
       </c>
       <c r="C3" t="n">
-        <v>13.2161821224289</v>
+        <v>13.21618309850878</v>
       </c>
       <c r="D3" t="n">
-        <v>12.61721411646944</v>
+        <v>12.6172150483126</v>
       </c>
       <c r="E3" t="n">
-        <v>12.74945378682817</v>
+        <v>12.74945472843788</v>
       </c>
       <c r="F3" t="n">
         <v>4714100</v>
@@ -512,16 +512,16 @@
         <v>44651</v>
       </c>
       <c r="B5" t="n">
-        <v>12.43830108642578</v>
+        <v>12.4383020401001</v>
       </c>
       <c r="C5" t="n">
-        <v>12.82724108844168</v>
+        <v>12.82724207193696</v>
       </c>
       <c r="D5" t="n">
-        <v>12.05714006249281</v>
+        <v>12.05714098694259</v>
       </c>
       <c r="E5" t="n">
-        <v>12.4149648940212</v>
+        <v>12.41496584590627</v>
       </c>
       <c r="F5" t="n">
         <v>3876100</v>
@@ -592,16 +592,16 @@
         <v>44657</v>
       </c>
       <c r="B9" t="n">
-        <v>12.43052196502686</v>
+        <v>12.43052387237549</v>
       </c>
       <c r="C9" t="n">
-        <v>12.44607992101333</v>
+        <v>12.44608183074918</v>
       </c>
       <c r="D9" t="n">
-        <v>12.01824577535966</v>
+        <v>12.01824761944832</v>
       </c>
       <c r="E9" t="n">
-        <v>12.06491890147489</v>
+        <v>12.06492075272512</v>
       </c>
       <c r="F9" t="n">
         <v>2914800</v>
@@ -612,16 +612,16 @@
         <v>44658</v>
       </c>
       <c r="B10" t="n">
-        <v>12.44608020782471</v>
+        <v>12.44608211517334</v>
       </c>
       <c r="C10" t="n">
-        <v>12.71833850910855</v>
+        <v>12.71834045818048</v>
       </c>
       <c r="D10" t="n">
-        <v>12.20493707738666</v>
+        <v>12.20493894778036</v>
       </c>
       <c r="E10" t="n">
-        <v>12.32161952444153</v>
+        <v>12.32162141271669</v>
       </c>
       <c r="F10" t="n">
         <v>3223900</v>
@@ -632,16 +632,16 @@
         <v>44659</v>
       </c>
       <c r="B11" t="n">
-        <v>12.60943603515625</v>
+        <v>12.60943508148193</v>
       </c>
       <c r="C11" t="n">
-        <v>12.75723367341398</v>
+        <v>12.75723270856147</v>
       </c>
       <c r="D11" t="n">
-        <v>12.3371784382169</v>
+        <v>12.33717750513392</v>
       </c>
       <c r="E11" t="n">
-        <v>12.3371784382169</v>
+        <v>12.33717750513392</v>
       </c>
       <c r="F11" t="n">
         <v>2049800</v>
@@ -652,16 +652,16 @@
         <v>44662</v>
       </c>
       <c r="B12" t="n">
-        <v>12.37607192993164</v>
+        <v>12.37607097625732</v>
       </c>
       <c r="C12" t="n">
-        <v>12.8972516418612</v>
+        <v>12.89725064802586</v>
       </c>
       <c r="D12" t="n">
-        <v>12.37607192993164</v>
+        <v>12.37607097625732</v>
       </c>
       <c r="E12" t="n">
-        <v>12.59387888603408</v>
+        <v>12.59387791557601</v>
       </c>
       <c r="F12" t="n">
         <v>2119500</v>
@@ -672,16 +672,16 @@
         <v>44663</v>
       </c>
       <c r="B13" t="n">
-        <v>12.2438325881958</v>
+        <v>12.24383163452148</v>
       </c>
       <c r="C13" t="n">
-        <v>12.64055161698694</v>
+        <v>12.64055063241211</v>
       </c>
       <c r="D13" t="n">
-        <v>12.2127174138893</v>
+        <v>12.21271646263855</v>
       </c>
       <c r="E13" t="n">
-        <v>12.48497500361014</v>
+        <v>12.4849740311532</v>
       </c>
       <c r="F13" t="n">
         <v>2267700</v>
@@ -712,16 +712,16 @@
         <v>44665</v>
       </c>
       <c r="B15" t="n">
-        <v>12.11159229278564</v>
+        <v>12.11159133911133</v>
       </c>
       <c r="C15" t="n">
-        <v>12.36829265315281</v>
+        <v>12.36829167926575</v>
       </c>
       <c r="D15" t="n">
-        <v>12.04936194735386</v>
+        <v>12.0493609985796</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08047712006975</v>
+        <v>12.08047616884546</v>
       </c>
       <c r="F15" t="n">
         <v>2077400</v>
@@ -772,16 +772,16 @@
         <v>44671</v>
       </c>
       <c r="B18" t="n">
-        <v>12.0571403503418</v>
+        <v>12.05714130401611</v>
       </c>
       <c r="C18" t="n">
-        <v>12.2127162064935</v>
+        <v>12.21271717247328</v>
       </c>
       <c r="D18" t="n">
-        <v>11.95601585838214</v>
+        <v>11.95601680405789</v>
       </c>
       <c r="E18" t="n">
-        <v>12.07269830687907</v>
+        <v>12.07269926178396</v>
       </c>
       <c r="F18" t="n">
         <v>2798400</v>
@@ -832,16 +832,16 @@
         <v>44677</v>
       </c>
       <c r="B21" t="n">
-        <v>11.95601558685303</v>
+        <v>11.95601654052734</v>
       </c>
       <c r="C21" t="n">
-        <v>12.43830110089237</v>
+        <v>12.4383020930363</v>
       </c>
       <c r="D21" t="n">
-        <v>11.86267007528195</v>
+        <v>11.86267102151054</v>
       </c>
       <c r="E21" t="n">
-        <v>12.32939837498153</v>
+        <v>12.32939935843881</v>
       </c>
       <c r="F21" t="n">
         <v>2627000</v>
@@ -852,16 +852,16 @@
         <v>44678</v>
       </c>
       <c r="B22" t="n">
-        <v>12.0571403503418</v>
+        <v>12.05714130401611</v>
       </c>
       <c r="C22" t="n">
-        <v>12.06491932861043</v>
+        <v>12.06492028290003</v>
       </c>
       <c r="D22" t="n">
-        <v>11.83155517346078</v>
+        <v>11.83155610929216</v>
       </c>
       <c r="E22" t="n">
-        <v>12.04936137207316</v>
+        <v>12.04936232513219</v>
       </c>
       <c r="F22" t="n">
         <v>2401400</v>
@@ -892,16 +892,16 @@
         <v>44680</v>
       </c>
       <c r="B24" t="n">
-        <v>11.40372085571289</v>
+        <v>11.40372180938721</v>
       </c>
       <c r="C24" t="n">
-        <v>11.963794671995</v>
+        <v>11.96379567250737</v>
       </c>
       <c r="D24" t="n">
-        <v>11.40372085571289</v>
+        <v>11.40372180938721</v>
       </c>
       <c r="E24" t="n">
-        <v>11.963794671995</v>
+        <v>11.96379567250737</v>
       </c>
       <c r="F24" t="n">
         <v>10427400</v>
@@ -912,16 +912,16 @@
         <v>44683</v>
       </c>
       <c r="B25" t="n">
-        <v>11.17035675048828</v>
+        <v>11.1703577041626</v>
       </c>
       <c r="C25" t="n">
-        <v>11.47373022346064</v>
+        <v>11.47373120303561</v>
       </c>
       <c r="D25" t="n">
-        <v>10.96032953215679</v>
+        <v>10.96033046789994</v>
       </c>
       <c r="E25" t="n">
-        <v>11.4270570961402</v>
+        <v>11.42705807173043</v>
       </c>
       <c r="F25" t="n">
         <v>2883200</v>
@@ -952,16 +952,16 @@
         <v>44685</v>
       </c>
       <c r="B27" t="n">
-        <v>11.69445610046387</v>
+        <v>11.69445705413818</v>
       </c>
       <c r="C27" t="n">
-        <v>11.69445610046387</v>
+        <v>11.69445705413818</v>
       </c>
       <c r="D27" t="n">
-        <v>11.03649597266557</v>
+        <v>11.03649687268372</v>
       </c>
       <c r="E27" t="n">
-        <v>11.20881904113643</v>
+        <v>11.2088199552074</v>
       </c>
       <c r="F27" t="n">
         <v>4400300</v>
@@ -972,16 +972,16 @@
         <v>44686</v>
       </c>
       <c r="B28" t="n">
-        <v>11.28714752197266</v>
+        <v>11.28714656829834</v>
       </c>
       <c r="C28" t="n">
-        <v>11.62396063303483</v>
+        <v>11.62395965090248</v>
       </c>
       <c r="D28" t="n">
-        <v>11.14615584813277</v>
+        <v>11.14615490637113</v>
       </c>
       <c r="E28" t="n">
-        <v>11.61612759626606</v>
+        <v>11.61612661479554</v>
       </c>
       <c r="F28" t="n">
         <v>3065700</v>
@@ -1092,16 +1092,16 @@
         <v>44694</v>
       </c>
       <c r="B34" t="n">
-        <v>11.32631206512451</v>
+        <v>11.32631301879883</v>
       </c>
       <c r="C34" t="n">
-        <v>11.38114182902154</v>
+        <v>11.38114278731251</v>
       </c>
       <c r="D34" t="n">
-        <v>11.11482455237968</v>
+        <v>11.11482548824677</v>
       </c>
       <c r="E34" t="n">
-        <v>11.18532038996129</v>
+        <v>11.18532133176413</v>
       </c>
       <c r="F34" t="n">
         <v>1333500</v>
@@ -1112,16 +1112,16 @@
         <v>44697</v>
       </c>
       <c r="B35" t="n">
-        <v>11.27931594848633</v>
+        <v>11.27931499481201</v>
       </c>
       <c r="C35" t="n">
-        <v>11.41247460283231</v>
+        <v>11.41247363789934</v>
       </c>
       <c r="D35" t="n">
-        <v>11.11482589000009</v>
+        <v>11.11482495023352</v>
       </c>
       <c r="E35" t="n">
-        <v>11.1774894452802</v>
+        <v>11.17748850021538</v>
       </c>
       <c r="F35" t="n">
         <v>2419100</v>
@@ -1152,16 +1152,16 @@
         <v>44699</v>
       </c>
       <c r="B37" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C37" t="n">
-        <v>11.59262882548476</v>
+        <v>11.5926298208571</v>
       </c>
       <c r="D37" t="n">
-        <v>11.03649593344125</v>
+        <v>11.03649688106261</v>
       </c>
       <c r="E37" t="n">
-        <v>11.51429995454926</v>
+        <v>11.51430094319608</v>
       </c>
       <c r="F37" t="n">
         <v>1959900</v>
@@ -1192,16 +1192,16 @@
         <v>44701</v>
       </c>
       <c r="B39" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C39" t="n">
-        <v>11.34197688669085</v>
+        <v>11.34197786054158</v>
       </c>
       <c r="D39" t="n">
-        <v>10.86417286558284</v>
+        <v>10.86417379840811</v>
       </c>
       <c r="E39" t="n">
-        <v>11.34197688669085</v>
+        <v>11.34197786054158</v>
       </c>
       <c r="F39" t="n">
         <v>1777400</v>
@@ -1212,16 +1212,16 @@
         <v>44704</v>
       </c>
       <c r="B40" t="n">
-        <v>11.20881938934326</v>
+        <v>11.20882034301758</v>
       </c>
       <c r="C40" t="n">
-        <v>11.43597222652075</v>
+        <v>11.4359731995218</v>
       </c>
       <c r="D40" t="n">
-        <v>11.16182191575504</v>
+        <v>11.16182286543069</v>
       </c>
       <c r="E40" t="n">
-        <v>11.1853202790494</v>
+        <v>11.18532123072435</v>
       </c>
       <c r="F40" t="n">
         <v>1184600</v>
@@ -1252,16 +1252,16 @@
         <v>44706</v>
       </c>
       <c r="B42" t="n">
-        <v>11.32631206512451</v>
+        <v>11.32631301879883</v>
       </c>
       <c r="C42" t="n">
-        <v>11.39680790270612</v>
+        <v>11.39680886231618</v>
       </c>
       <c r="D42" t="n">
-        <v>11.13832366290656</v>
+        <v>11.13832460075227</v>
       </c>
       <c r="E42" t="n">
-        <v>11.17748810011851</v>
+        <v>11.17748904126186</v>
       </c>
       <c r="F42" t="n">
         <v>821700</v>
@@ -1292,16 +1292,16 @@
         <v>44708</v>
       </c>
       <c r="B44" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C44" t="n">
-        <v>11.42030600182509</v>
+        <v>11.42030698171035</v>
       </c>
       <c r="D44" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="E44" t="n">
-        <v>11.26364900360379</v>
+        <v>11.26364997004757</v>
       </c>
       <c r="F44" t="n">
         <v>2224600</v>
@@ -1312,16 +1312,16 @@
         <v>44711</v>
       </c>
       <c r="B45" t="n">
-        <v>11.09915924072266</v>
+        <v>11.09915828704834</v>
       </c>
       <c r="C45" t="n">
-        <v>11.27148231648886</v>
+        <v>11.271481348008</v>
       </c>
       <c r="D45" t="n">
-        <v>11.0286634030456</v>
+        <v>11.0286624554285</v>
       </c>
       <c r="E45" t="n">
-        <v>11.15398900469392</v>
+        <v>11.15398804630846</v>
       </c>
       <c r="F45" t="n">
         <v>1940200</v>
@@ -1372,16 +1372,16 @@
         <v>44714</v>
       </c>
       <c r="B48" t="n">
-        <v>10.86417293548584</v>
+        <v>10.86417388916016</v>
       </c>
       <c r="C48" t="n">
-        <v>10.98949853218943</v>
+        <v>10.98949949686503</v>
       </c>
       <c r="D48" t="n">
-        <v>10.68401757697429</v>
+        <v>10.68401851483428</v>
       </c>
       <c r="E48" t="n">
-        <v>10.75451266487045</v>
+        <v>10.75451360891862</v>
       </c>
       <c r="F48" t="n">
         <v>3275400</v>
@@ -1392,16 +1392,16 @@
         <v>44715</v>
       </c>
       <c r="B49" t="n">
-        <v>10.77801322937012</v>
+        <v>10.7780122756958</v>
       </c>
       <c r="C49" t="n">
-        <v>10.85634136438323</v>
+        <v>10.85634040377818</v>
       </c>
       <c r="D49" t="n">
-        <v>10.6213562123443</v>
+        <v>10.62135527253152</v>
       </c>
       <c r="E49" t="n">
-        <v>10.7858462669713</v>
+        <v>10.78584531260389</v>
       </c>
       <c r="F49" t="n">
         <v>2685000</v>
@@ -1472,16 +1472,16 @@
         <v>44721</v>
       </c>
       <c r="B53" t="n">
-        <v>11.03649711608887</v>
+        <v>11.03649616241455</v>
       </c>
       <c r="C53" t="n">
-        <v>11.09915992075229</v>
+        <v>11.09915896166322</v>
       </c>
       <c r="D53" t="n">
-        <v>10.86417402976468</v>
+        <v>10.86417309098097</v>
       </c>
       <c r="E53" t="n">
-        <v>11.06782851842058</v>
+        <v>11.06782756203888</v>
       </c>
       <c r="F53" t="n">
         <v>1365200</v>
@@ -1532,16 +1532,16 @@
         <v>44726</v>
       </c>
       <c r="B56" t="n">
-        <v>10.39420318603516</v>
+        <v>10.39420223236084</v>
       </c>
       <c r="C56" t="n">
-        <v>10.47253131980584</v>
+        <v>10.47253035894487</v>
       </c>
       <c r="D56" t="n">
-        <v>10.01822560413734</v>
+        <v>10.01822468495919</v>
       </c>
       <c r="E56" t="n">
-        <v>10.01822560413734</v>
+        <v>10.01822468495919</v>
       </c>
       <c r="F56" t="n">
         <v>4085600</v>
@@ -1592,16 +1592,16 @@
         <v>44732</v>
       </c>
       <c r="B59" t="n">
-        <v>10.59785652160645</v>
+        <v>10.59785556793213</v>
       </c>
       <c r="C59" t="n">
-        <v>10.69968376387016</v>
+        <v>10.69968280103267</v>
       </c>
       <c r="D59" t="n">
-        <v>10.37070367255648</v>
+        <v>10.37070273932307</v>
       </c>
       <c r="E59" t="n">
-        <v>10.47253091482019</v>
+        <v>10.47252997242361</v>
       </c>
       <c r="F59" t="n">
         <v>1649800</v>
@@ -1612,16 +1612,16 @@
         <v>44733</v>
       </c>
       <c r="B60" t="n">
-        <v>10.6370210647583</v>
+        <v>10.63702011108398</v>
       </c>
       <c r="C60" t="n">
-        <v>10.71534994326738</v>
+        <v>10.7153489825704</v>
       </c>
       <c r="D60" t="n">
-        <v>10.51952849399422</v>
+        <v>10.51952755085384</v>
       </c>
       <c r="E60" t="n">
-        <v>10.69185083151493</v>
+        <v>10.69184987292479</v>
       </c>
       <c r="F60" t="n">
         <v>1455700</v>
@@ -1632,16 +1632,16 @@
         <v>44734</v>
       </c>
       <c r="B61" t="n">
-        <v>10.73884773254395</v>
+        <v>10.73884868621826</v>
       </c>
       <c r="C61" t="n">
-        <v>10.83284193351813</v>
+        <v>10.8328428955397</v>
       </c>
       <c r="D61" t="n">
-        <v>10.43336601912821</v>
+        <v>10.43336694567391</v>
       </c>
       <c r="E61" t="n">
-        <v>10.53519325693346</v>
+        <v>10.53519419252203</v>
       </c>
       <c r="F61" t="n">
         <v>1196200</v>
@@ -1652,16 +1652,16 @@
         <v>44735</v>
       </c>
       <c r="B62" t="n">
-        <v>10.6370210647583</v>
+        <v>10.63702011108398</v>
       </c>
       <c r="C62" t="n">
-        <v>10.89550531803891</v>
+        <v>10.89550434118989</v>
       </c>
       <c r="D62" t="n">
-        <v>10.55085989599795</v>
+        <v>10.55085895004851</v>
       </c>
       <c r="E62" t="n">
-        <v>10.87983999053682</v>
+        <v>10.8798390150923</v>
       </c>
       <c r="F62" t="n">
         <v>3444100</v>
@@ -1732,16 +1732,16 @@
         <v>44741</v>
       </c>
       <c r="B66" t="n">
-        <v>10.6840181350708</v>
+        <v>10.68401718139648</v>
       </c>
       <c r="C66" t="n">
-        <v>10.6840181350708</v>
+        <v>10.68401718139648</v>
       </c>
       <c r="D66" t="n">
-        <v>10.53519342096158</v>
+        <v>10.53519248057162</v>
       </c>
       <c r="E66" t="n">
-        <v>10.62918762339921</v>
+        <v>10.62918667461916</v>
       </c>
       <c r="F66" t="n">
         <v>1613700</v>
@@ -1752,16 +1752,16 @@
         <v>44742</v>
       </c>
       <c r="B67" t="n">
-        <v>10.66835117340088</v>
+        <v>10.6683521270752</v>
       </c>
       <c r="C67" t="n">
-        <v>10.84850727333101</v>
+        <v>10.84850824310999</v>
       </c>
       <c r="D67" t="n">
-        <v>10.48819582047021</v>
+        <v>10.48819675803992</v>
       </c>
       <c r="E67" t="n">
-        <v>10.53519254427845</v>
+        <v>10.53519348604933</v>
       </c>
       <c r="F67" t="n">
         <v>2634600</v>
@@ -1772,16 +1772,16 @@
         <v>44743</v>
       </c>
       <c r="B68" t="n">
-        <v>10.6840181350708</v>
+        <v>10.68401718139648</v>
       </c>
       <c r="C68" t="n">
-        <v>10.84067513913352</v>
+        <v>10.84067417147572</v>
       </c>
       <c r="D68" t="n">
-        <v>10.54302645791459</v>
+        <v>10.54302551682544</v>
       </c>
       <c r="E68" t="n">
-        <v>10.72318182583684</v>
+        <v>10.72318086866671</v>
       </c>
       <c r="F68" t="n">
         <v>2696600</v>
@@ -1832,16 +1832,16 @@
         <v>44748</v>
       </c>
       <c r="B71" t="n">
-        <v>10.67618465423584</v>
+        <v>10.67618560791016</v>
       </c>
       <c r="C71" t="n">
-        <v>10.71534909037307</v>
+        <v>10.71535004754583</v>
       </c>
       <c r="D71" t="n">
-        <v>10.49602854680439</v>
+        <v>10.49602948438586</v>
       </c>
       <c r="E71" t="n">
-        <v>10.57435741907885</v>
+        <v>10.57435836365721</v>
       </c>
       <c r="F71" t="n">
         <v>1826800</v>
@@ -1852,16 +1852,16 @@
         <v>44749</v>
       </c>
       <c r="B72" t="n">
-        <v>11.0443286895752</v>
+        <v>11.04432964324951</v>
       </c>
       <c r="C72" t="n">
-        <v>11.16182124599643</v>
+        <v>11.16182220981619</v>
       </c>
       <c r="D72" t="n">
-        <v>10.62135444065952</v>
+        <v>10.62135535781014</v>
       </c>
       <c r="E72" t="n">
-        <v>10.78584446784892</v>
+        <v>10.7858453992032</v>
       </c>
       <c r="F72" t="n">
         <v>2931100</v>
@@ -1892,16 +1892,16 @@
         <v>44753</v>
       </c>
       <c r="B74" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C74" t="n">
-        <v>11.18531989181933</v>
+        <v>11.18532085221909</v>
       </c>
       <c r="D74" t="n">
-        <v>10.83284146660853</v>
+        <v>10.83284239674361</v>
       </c>
       <c r="E74" t="n">
-        <v>11.05999429592211</v>
+        <v>11.0599952455611</v>
       </c>
       <c r="F74" t="n">
         <v>1881000</v>
@@ -1912,16 +1912,16 @@
         <v>44754</v>
       </c>
       <c r="B75" t="n">
-        <v>11.14615726470947</v>
+        <v>11.14615535736084</v>
       </c>
       <c r="C75" t="n">
-        <v>11.22448614835309</v>
+        <v>11.22448422760069</v>
       </c>
       <c r="D75" t="n">
-        <v>10.99733328218612</v>
+        <v>10.99733140030449</v>
       </c>
       <c r="E75" t="n">
-        <v>11.10699356988726</v>
+        <v>11.10699166924038</v>
       </c>
       <c r="F75" t="n">
         <v>1673000</v>
@@ -2032,16 +2032,16 @@
         <v>44762</v>
       </c>
       <c r="B81" t="n">
-        <v>11.27931594848633</v>
+        <v>11.27931499481201</v>
       </c>
       <c r="C81" t="n">
-        <v>11.35764483233677</v>
+        <v>11.35764387203968</v>
       </c>
       <c r="D81" t="n">
-        <v>11.05216308171958</v>
+        <v>11.0521621472512</v>
       </c>
       <c r="E81" t="n">
-        <v>11.08349448585983</v>
+        <v>11.08349354874236</v>
       </c>
       <c r="F81" t="n">
         <v>2285400</v>
@@ -2052,16 +2052,16 @@
         <v>44763</v>
       </c>
       <c r="B82" t="n">
-        <v>11.2479829788208</v>
+        <v>11.24798393249512</v>
       </c>
       <c r="C82" t="n">
-        <v>11.27931437860027</v>
+        <v>11.27931533493105</v>
       </c>
       <c r="D82" t="n">
-        <v>11.05999458014401</v>
+        <v>11.0599955178795</v>
       </c>
       <c r="E82" t="n">
-        <v>11.22448461573608</v>
+        <v>11.22448556741805</v>
       </c>
       <c r="F82" t="n">
         <v>1092700</v>
@@ -2072,16 +2072,16 @@
         <v>44764</v>
       </c>
       <c r="B83" t="n">
-        <v>11.36547660827637</v>
+        <v>11.36547565460205</v>
       </c>
       <c r="C83" t="n">
-        <v>11.37330964519167</v>
+        <v>11.37330869086009</v>
       </c>
       <c r="D83" t="n">
-        <v>11.13049072981382</v>
+        <v>11.13048979585711</v>
       </c>
       <c r="E83" t="n">
-        <v>11.27148240629125</v>
+        <v>11.27148146050397</v>
       </c>
       <c r="F83" t="n">
         <v>1975500</v>
@@ -2152,16 +2152,16 @@
         <v>44770</v>
       </c>
       <c r="B87" t="n">
-        <v>10.96600151062012</v>
+        <v>10.96599960327148</v>
       </c>
       <c r="C87" t="n">
-        <v>11.33414605620796</v>
+        <v>11.33414408482687</v>
       </c>
       <c r="D87" t="n">
-        <v>10.82500982358657</v>
+        <v>10.82500794076103</v>
       </c>
       <c r="E87" t="n">
-        <v>11.31064694370265</v>
+        <v>11.31064497640883</v>
       </c>
       <c r="F87" t="n">
         <v>2911900</v>
@@ -2172,16 +2172,16 @@
         <v>44771</v>
       </c>
       <c r="B88" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C88" t="n">
-        <v>11.33414483955325</v>
+        <v>11.33414581204571</v>
       </c>
       <c r="D88" t="n">
-        <v>10.51952770180302</v>
+        <v>10.51952860439969</v>
       </c>
       <c r="E88" t="n">
-        <v>10.96600033348359</v>
+        <v>10.96600127438851</v>
       </c>
       <c r="F88" t="n">
         <v>13059200</v>
@@ -2212,16 +2212,16 @@
         <v>44775</v>
       </c>
       <c r="B90" t="n">
-        <v>10.86417293548584</v>
+        <v>10.86417388916016</v>
       </c>
       <c r="C90" t="n">
-        <v>11.06782740362892</v>
+        <v>11.06782837518035</v>
       </c>
       <c r="D90" t="n">
-        <v>10.72318126569455</v>
+        <v>10.7231822069924</v>
       </c>
       <c r="E90" t="n">
-        <v>10.93466877038148</v>
+        <v>10.93466973024404</v>
       </c>
       <c r="F90" t="n">
         <v>2371400</v>
@@ -2272,16 +2272,16 @@
         <v>44778</v>
       </c>
       <c r="B93" t="n">
-        <v>10.96600151062012</v>
+        <v>10.96599960327148</v>
       </c>
       <c r="C93" t="n">
-        <v>11.16965600366867</v>
+        <v>11.16965406089782</v>
       </c>
       <c r="D93" t="n">
-        <v>10.93467010761261</v>
+        <v>10.93466820571354</v>
       </c>
       <c r="E93" t="n">
-        <v>11.16965600366867</v>
+        <v>11.16965406089782</v>
       </c>
       <c r="F93" t="n">
         <v>1948700</v>
@@ -2292,16 +2292,16 @@
         <v>44781</v>
       </c>
       <c r="B94" t="n">
-        <v>10.97383308410645</v>
+        <v>10.97383403778076</v>
       </c>
       <c r="C94" t="n">
-        <v>11.10699171587358</v>
+        <v>11.10699268111997</v>
       </c>
       <c r="D94" t="n">
-        <v>10.8720058511669</v>
+        <v>10.87200679599199</v>
       </c>
       <c r="E94" t="n">
-        <v>11.02866284530486</v>
+        <v>11.02866380374413</v>
       </c>
       <c r="F94" t="n">
         <v>2949000</v>
@@ -2312,16 +2312,16 @@
         <v>44782</v>
       </c>
       <c r="B95" t="n">
-        <v>10.92683601379395</v>
+        <v>10.92683696746826</v>
       </c>
       <c r="C95" t="n">
-        <v>11.05999465045304</v>
+        <v>11.0599956157492</v>
       </c>
       <c r="D95" t="n">
-        <v>10.67618481396482</v>
+        <v>10.67618574576276</v>
       </c>
       <c r="E95" t="n">
-        <v>10.98166652400619</v>
+        <v>10.98166748246601</v>
       </c>
       <c r="F95" t="n">
         <v>1743500</v>
@@ -2352,16 +2352,16 @@
         <v>44784</v>
       </c>
       <c r="B97" t="n">
-        <v>10.89550590515137</v>
+        <v>10.89550495147705</v>
       </c>
       <c r="C97" t="n">
-        <v>11.10699344032233</v>
+        <v>11.10699246813669</v>
       </c>
       <c r="D97" t="n">
-        <v>10.83284309776729</v>
+        <v>10.83284214957779</v>
       </c>
       <c r="E97" t="n">
-        <v>11.05999596128448</v>
+        <v>11.05999499321249</v>
       </c>
       <c r="F97" t="n">
         <v>1665400</v>
@@ -2412,16 +2412,16 @@
         <v>44789</v>
       </c>
       <c r="B100" t="n">
-        <v>11.0443286895752</v>
+        <v>11.04432964324951</v>
       </c>
       <c r="C100" t="n">
-        <v>11.29497987500687</v>
+        <v>11.29498085032484</v>
       </c>
       <c r="D100" t="n">
-        <v>10.94250145874372</v>
+        <v>10.94250240362528</v>
       </c>
       <c r="E100" t="n">
-        <v>11.25581544053331</v>
+        <v>11.25581641246944</v>
       </c>
       <c r="F100" t="n">
         <v>1185300</v>
@@ -2472,16 +2472,16 @@
         <v>44792</v>
       </c>
       <c r="B103" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C103" t="n">
-        <v>11.16182176801008</v>
+        <v>11.16182272571687</v>
       </c>
       <c r="D103" t="n">
-        <v>10.98166640680546</v>
+        <v>10.98166734905456</v>
       </c>
       <c r="E103" t="n">
-        <v>11.16182176801008</v>
+        <v>11.16182272571687</v>
       </c>
       <c r="F103" t="n">
         <v>1667800</v>
@@ -2492,16 +2492,16 @@
         <v>44795</v>
       </c>
       <c r="B104" t="n">
-        <v>11.0599946975708</v>
+        <v>11.05999565124512</v>
       </c>
       <c r="C104" t="n">
-        <v>11.2244847349093</v>
+        <v>11.22448570276716</v>
       </c>
       <c r="D104" t="n">
-        <v>10.98166657079026</v>
+        <v>10.98166751771054</v>
       </c>
       <c r="E104" t="n">
-        <v>11.0599946975708</v>
+        <v>11.05999565124512</v>
       </c>
       <c r="F104" t="n">
         <v>1703300</v>
@@ -2532,16 +2532,16 @@
         <v>44797</v>
       </c>
       <c r="B106" t="n">
-        <v>11.1069917678833</v>
+        <v>11.10699272155762</v>
       </c>
       <c r="C106" t="n">
-        <v>11.39680739514549</v>
+        <v>11.3968083737041</v>
       </c>
       <c r="D106" t="n">
-        <v>11.09915873138986</v>
+        <v>11.09915968439161</v>
       </c>
       <c r="E106" t="n">
-        <v>11.22448432728707</v>
+        <v>11.2244852910496</v>
       </c>
       <c r="F106" t="n">
         <v>2116800</v>
@@ -2552,16 +2552,16 @@
         <v>44798</v>
       </c>
       <c r="B107" t="n">
-        <v>11.0443286895752</v>
+        <v>11.04432964324951</v>
       </c>
       <c r="C107" t="n">
-        <v>11.22448404235435</v>
+        <v>11.22448501158502</v>
       </c>
       <c r="D107" t="n">
-        <v>10.95033374803886</v>
+        <v>10.95033469359675</v>
       </c>
       <c r="E107" t="n">
-        <v>11.2088187167646</v>
+        <v>11.20881968464257</v>
       </c>
       <c r="F107" t="n">
         <v>2435800</v>
@@ -2592,16 +2592,16 @@
         <v>44802</v>
       </c>
       <c r="B109" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C109" t="n">
-        <v>11.20881924097621</v>
+        <v>11.20882020271549</v>
       </c>
       <c r="D109" t="n">
-        <v>10.93466893383933</v>
+        <v>10.93466987205595</v>
       </c>
       <c r="E109" t="n">
-        <v>11.02083009611117</v>
+        <v>11.02083104172059</v>
       </c>
       <c r="F109" t="n">
         <v>3615600</v>
@@ -2612,16 +2612,16 @@
         <v>44803</v>
       </c>
       <c r="B110" t="n">
-        <v>11.01299953460693</v>
+        <v>11.0129976272583</v>
       </c>
       <c r="C110" t="n">
-        <v>11.16182351952071</v>
+        <v>11.16182158639716</v>
       </c>
       <c r="D110" t="n">
-        <v>10.93467064970519</v>
+        <v>10.93466875592239</v>
       </c>
       <c r="E110" t="n">
-        <v>11.11482603917975</v>
+        <v>11.11482411419572</v>
       </c>
       <c r="F110" t="n">
         <v>1284900</v>
@@ -2632,16 +2632,16 @@
         <v>44804</v>
       </c>
       <c r="B111" t="n">
-        <v>12.03910255432129</v>
+        <v>12.03910160064697</v>
       </c>
       <c r="C111" t="n">
-        <v>12.07826699338926</v>
+        <v>12.07826603661254</v>
       </c>
       <c r="D111" t="n">
-        <v>10.96600110705643</v>
+        <v>10.96600023838756</v>
       </c>
       <c r="E111" t="n">
-        <v>11.02083087355185</v>
+        <v>11.02083000053966</v>
       </c>
       <c r="F111" t="n">
         <v>16560000</v>
@@ -2672,16 +2672,16 @@
         <v>44806</v>
       </c>
       <c r="B113" t="n">
-        <v>11.74145317077637</v>
+        <v>11.74145412445068</v>
       </c>
       <c r="C113" t="n">
-        <v>11.79628368103782</v>
+        <v>11.79628463916563</v>
       </c>
       <c r="D113" t="n">
-        <v>11.56129780748737</v>
+        <v>11.56129874652895</v>
       </c>
       <c r="E113" t="n">
-        <v>11.74145317077637</v>
+        <v>11.74145412445068</v>
       </c>
       <c r="F113" t="n">
         <v>3674700</v>
@@ -2732,16 +2732,16 @@
         <v>44812</v>
       </c>
       <c r="B116" t="n">
-        <v>11.43597316741943</v>
+        <v>11.43597221374512</v>
       </c>
       <c r="C116" t="n">
-        <v>11.63962691105875</v>
+        <v>11.63962594040124</v>
       </c>
       <c r="D116" t="n">
-        <v>11.37331036214587</v>
+        <v>11.37330941369716</v>
       </c>
       <c r="E116" t="n">
-        <v>11.62396158324014</v>
+        <v>11.623960613889</v>
       </c>
       <c r="F116" t="n">
         <v>2598100</v>
@@ -2812,16 +2812,16 @@
         <v>44818</v>
       </c>
       <c r="B120" t="n">
-        <v>11.20881938934326</v>
+        <v>11.20882034301758</v>
       </c>
       <c r="C120" t="n">
-        <v>11.42030615299151</v>
+        <v>11.42030712465965</v>
       </c>
       <c r="D120" t="n">
-        <v>11.02866327875449</v>
+        <v>11.02866421710068</v>
       </c>
       <c r="E120" t="n">
-        <v>11.20098635257864</v>
+        <v>11.2009873055865</v>
       </c>
       <c r="F120" t="n">
         <v>1856400</v>
@@ -2872,16 +2872,16 @@
         <v>44823</v>
       </c>
       <c r="B123" t="n">
-        <v>11.28714752197266</v>
+        <v>11.28714656829834</v>
       </c>
       <c r="C123" t="n">
-        <v>11.43597223258132</v>
+        <v>11.43597126633249</v>
       </c>
       <c r="D123" t="n">
-        <v>11.11482444805718</v>
+        <v>11.1148235089428</v>
       </c>
       <c r="E123" t="n">
-        <v>11.11482444805718</v>
+        <v>11.1148235089428</v>
       </c>
       <c r="F123" t="n">
         <v>1858600</v>
@@ -2892,16 +2892,16 @@
         <v>44824</v>
       </c>
       <c r="B124" t="n">
-        <v>11.13049030303955</v>
+        <v>11.13049125671387</v>
       </c>
       <c r="C124" t="n">
-        <v>11.35764313587711</v>
+        <v>11.35764410901417</v>
       </c>
       <c r="D124" t="n">
-        <v>11.08349283034925</v>
+        <v>11.08349377999676</v>
       </c>
       <c r="E124" t="n">
-        <v>11.28714730034141</v>
+        <v>11.28714826743829</v>
       </c>
       <c r="F124" t="n">
         <v>1310600</v>
@@ -2992,16 +2992,16 @@
         <v>44831</v>
       </c>
       <c r="B129" t="n">
-        <v>10.90333843231201</v>
+        <v>10.9033374786377</v>
       </c>
       <c r="C129" t="n">
-        <v>11.04433011582452</v>
+        <v>11.04432914981819</v>
       </c>
       <c r="D129" t="n">
-        <v>10.77017978610565</v>
+        <v>10.77017884407822</v>
       </c>
       <c r="E129" t="n">
-        <v>11.04433011582452</v>
+        <v>11.04432914981819</v>
       </c>
       <c r="F129" t="n">
         <v>2130200</v>
@@ -3092,16 +3092,16 @@
         <v>44838</v>
       </c>
       <c r="B134" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C134" t="n">
-        <v>11.32631180289231</v>
+        <v>11.32631277471268</v>
       </c>
       <c r="D134" t="n">
-        <v>11.07566060573824</v>
+        <v>11.07566155605223</v>
       </c>
       <c r="E134" t="n">
-        <v>11.20881924097621</v>
+        <v>11.20882020271549</v>
       </c>
       <c r="F134" t="n">
         <v>2406500</v>
@@ -3112,16 +3112,16 @@
         <v>44839</v>
       </c>
       <c r="B135" t="n">
-        <v>10.97383308410645</v>
+        <v>10.97383403778076</v>
       </c>
       <c r="C135" t="n">
-        <v>11.20881894881312</v>
+        <v>11.20881992290874</v>
       </c>
       <c r="D135" t="n">
-        <v>10.85633977825337</v>
+        <v>10.85634072171701</v>
       </c>
       <c r="E135" t="n">
-        <v>11.20881894881312</v>
+        <v>11.20881992290874</v>
       </c>
       <c r="F135" t="n">
         <v>5244200</v>
@@ -3152,16 +3152,16 @@
         <v>44841</v>
       </c>
       <c r="B137" t="n">
-        <v>11.02866458892822</v>
+        <v>11.02866363525391</v>
       </c>
       <c r="C137" t="n">
-        <v>11.15399020405247</v>
+        <v>11.15398923954096</v>
       </c>
       <c r="D137" t="n">
-        <v>10.9425034152802</v>
+        <v>10.94250246905644</v>
       </c>
       <c r="E137" t="n">
-        <v>10.98166785675642</v>
+        <v>10.98166690714602</v>
       </c>
       <c r="F137" t="n">
         <v>7588600</v>
@@ -3312,16 +3312,16 @@
         <v>44854</v>
       </c>
       <c r="B145" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C145" t="n">
-        <v>10.98166755090811</v>
+        <v>10.98166658413194</v>
       </c>
       <c r="D145" t="n">
-        <v>10.39420318612486</v>
+        <v>10.39420227106638</v>
       </c>
       <c r="E145" t="n">
-        <v>10.5743585660986</v>
+        <v>10.57435763518006</v>
       </c>
       <c r="F145" t="n">
         <v>7194300</v>
@@ -3352,16 +3352,16 @@
         <v>44858</v>
       </c>
       <c r="B147" t="n">
-        <v>11.2479829788208</v>
+        <v>11.24798393249512</v>
       </c>
       <c r="C147" t="n">
-        <v>11.45163745088707</v>
+        <v>11.45163842182848</v>
       </c>
       <c r="D147" t="n">
-        <v>11.10699205331296</v>
+        <v>11.10699299503318</v>
       </c>
       <c r="E147" t="n">
-        <v>11.10699205331296</v>
+        <v>11.10699299503318</v>
       </c>
       <c r="F147" t="n">
         <v>2219500</v>
@@ -3472,16 +3472,16 @@
         <v>44866</v>
       </c>
       <c r="B153" t="n">
-        <v>11.56913185119629</v>
+        <v>11.56913089752197</v>
       </c>
       <c r="C153" t="n">
-        <v>11.80411699819995</v>
+        <v>11.80411602515518</v>
       </c>
       <c r="D153" t="n">
-        <v>11.34981128506018</v>
+        <v>11.34981034946504</v>
       </c>
       <c r="E153" t="n">
-        <v>11.67879138726478</v>
+        <v>11.67879042455094</v>
       </c>
       <c r="F153" t="n">
         <v>3576300</v>
@@ -3612,16 +3612,16 @@
         <v>44876</v>
       </c>
       <c r="B160" t="n">
-        <v>10.79367733001709</v>
+        <v>10.79367828369141</v>
       </c>
       <c r="C160" t="n">
-        <v>10.85634012970083</v>
+        <v>10.85634108891171</v>
       </c>
       <c r="D160" t="n">
-        <v>10.5351930945718</v>
+        <v>10.53519402540776</v>
       </c>
       <c r="E160" t="n">
-        <v>10.78584504030624</v>
+        <v>10.78584599328854</v>
       </c>
       <c r="F160" t="n">
         <v>3291200</v>
@@ -3632,16 +3632,16 @@
         <v>44879</v>
       </c>
       <c r="B161" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C161" t="n">
-        <v>10.9660014759541</v>
+        <v>10.9660005105571</v>
       </c>
       <c r="D161" t="n">
-        <v>10.71535025268644</v>
+        <v>10.71534930935563</v>
       </c>
       <c r="E161" t="n">
-        <v>10.94250311052265</v>
+        <v>10.94250214719434</v>
       </c>
       <c r="F161" t="n">
         <v>1203700</v>
@@ -3652,16 +3652,16 @@
         <v>44881</v>
       </c>
       <c r="B162" t="n">
-        <v>10.90333843231201</v>
+        <v>10.9033374786377</v>
       </c>
       <c r="C162" t="n">
-        <v>10.90333843231201</v>
+        <v>10.9033374786377</v>
       </c>
       <c r="D162" t="n">
-        <v>10.59785670036809</v>
+        <v>10.59785577341312</v>
       </c>
       <c r="E162" t="n">
-        <v>10.86417399278081</v>
+        <v>10.86417304253206</v>
       </c>
       <c r="F162" t="n">
         <v>5270300</v>
@@ -3712,16 +3712,16 @@
         <v>44886</v>
       </c>
       <c r="B165" t="n">
-        <v>11.27931594848633</v>
+        <v>11.27931499481201</v>
       </c>
       <c r="C165" t="n">
-        <v>11.32631342819651</v>
+        <v>11.32631247054852</v>
       </c>
       <c r="D165" t="n">
-        <v>10.8093448863825</v>
+        <v>10.80934397244457</v>
       </c>
       <c r="E165" t="n">
-        <v>10.84067629052275</v>
+        <v>10.84067537393573</v>
       </c>
       <c r="F165" t="n">
         <v>4939800</v>
@@ -3732,16 +3732,16 @@
         <v>44887</v>
       </c>
       <c r="B166" t="n">
-        <v>10.84850788116455</v>
+        <v>10.84850883483887</v>
       </c>
       <c r="C166" t="n">
-        <v>11.42030611719874</v>
+        <v>11.4203071211389</v>
       </c>
       <c r="D166" t="n">
-        <v>10.80151040772362</v>
+        <v>10.80151135726647</v>
       </c>
       <c r="E166" t="n">
-        <v>11.29498051735561</v>
+        <v>11.29498151027859</v>
       </c>
       <c r="F166" t="n">
         <v>3523700</v>
@@ -3752,16 +3752,16 @@
         <v>44888</v>
       </c>
       <c r="B167" t="n">
-        <v>10.56652545928955</v>
+        <v>10.56652450561523</v>
       </c>
       <c r="C167" t="n">
-        <v>10.81717742791213</v>
+        <v>10.8171764516154</v>
       </c>
       <c r="D167" t="n">
-        <v>10.51952872873502</v>
+        <v>10.51952777930236</v>
       </c>
       <c r="E167" t="n">
-        <v>10.80934439048652</v>
+        <v>10.80934341489675</v>
       </c>
       <c r="F167" t="n">
         <v>4669400</v>
@@ -3792,16 +3792,16 @@
         <v>44890</v>
       </c>
       <c r="B169" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C169" t="n">
-        <v>11.03649731924802</v>
+        <v>11.03649634764489</v>
       </c>
       <c r="D169" t="n">
-        <v>10.71535025268644</v>
+        <v>10.71534930935563</v>
       </c>
       <c r="E169" t="n">
-        <v>10.95033540100009</v>
+        <v>10.95033443698226</v>
       </c>
       <c r="F169" t="n">
         <v>1631500</v>
@@ -3812,16 +3812,16 @@
         <v>44893</v>
       </c>
       <c r="B170" t="n">
-        <v>10.97383308410645</v>
+        <v>10.97383403778076</v>
       </c>
       <c r="C170" t="n">
-        <v>11.09915867941681</v>
+        <v>11.09915964398247</v>
       </c>
       <c r="D170" t="n">
-        <v>10.68401745820135</v>
+        <v>10.68401838668942</v>
       </c>
       <c r="E170" t="n">
-        <v>10.84067445233931</v>
+        <v>10.84067539444156</v>
       </c>
       <c r="F170" t="n">
         <v>4990000</v>
@@ -3852,16 +3852,16 @@
         <v>44895</v>
       </c>
       <c r="B172" t="n">
-        <v>10.83284282684326</v>
+        <v>10.83284187316895</v>
       </c>
       <c r="C172" t="n">
-        <v>11.20882040874432</v>
+        <v>11.20881942197064</v>
       </c>
       <c r="D172" t="n">
-        <v>10.69185114025542</v>
+        <v>10.69185019899337</v>
       </c>
       <c r="E172" t="n">
-        <v>11.20882040874432</v>
+        <v>11.20881942197064</v>
       </c>
       <c r="F172" t="n">
         <v>4586400</v>
@@ -3872,16 +3872,16 @@
         <v>44896</v>
       </c>
       <c r="B173" t="n">
-        <v>10.92683601379395</v>
+        <v>10.92683696746826</v>
       </c>
       <c r="C173" t="n">
-        <v>11.02083021372987</v>
+        <v>11.02083117560783</v>
       </c>
       <c r="D173" t="n">
-        <v>10.69185014045439</v>
+        <v>10.69185107361957</v>
       </c>
       <c r="E173" t="n">
-        <v>10.76234597715621</v>
+        <v>10.76234691647413</v>
       </c>
       <c r="F173" t="n">
         <v>1944500</v>
@@ -3932,16 +3932,16 @@
         <v>44901</v>
       </c>
       <c r="B176" t="n">
-        <v>10.47253131866455</v>
+        <v>10.47253036499023</v>
       </c>
       <c r="C176" t="n">
-        <v>10.58219160233104</v>
+        <v>10.58219063867058</v>
       </c>
       <c r="D176" t="n">
-        <v>10.41770155033109</v>
+        <v>10.41770060164981</v>
       </c>
       <c r="E176" t="n">
-        <v>10.51952879652149</v>
+        <v>10.51952783856738</v>
       </c>
       <c r="F176" t="n">
         <v>1647500</v>
@@ -4052,16 +4052,16 @@
         <v>44909</v>
       </c>
       <c r="B182" t="n">
-        <v>10.9973316192627</v>
+        <v>10.99733257293701</v>
       </c>
       <c r="C182" t="n">
-        <v>11.13832328970179</v>
+        <v>11.13832425560273</v>
       </c>
       <c r="D182" t="n">
-        <v>10.738847388124</v>
+        <v>10.7388483193829</v>
       </c>
       <c r="E182" t="n">
-        <v>11.01299769242237</v>
+        <v>11.01299864745522</v>
       </c>
       <c r="F182" t="n">
         <v>3892800</v>
@@ -4092,16 +4092,16 @@
         <v>44911</v>
       </c>
       <c r="B184" t="n">
-        <v>11.2479829788208</v>
+        <v>11.24798393249512</v>
       </c>
       <c r="C184" t="n">
-        <v>11.2479829788208</v>
+        <v>11.24798393249512</v>
       </c>
       <c r="D184" t="n">
-        <v>10.90333758124669</v>
+        <v>10.90333850569981</v>
       </c>
       <c r="E184" t="n">
-        <v>11.04432925375403</v>
+        <v>11.04433019016131</v>
       </c>
       <c r="F184" t="n">
         <v>3365900</v>
@@ -4132,16 +4132,16 @@
         <v>44915</v>
       </c>
       <c r="B186" t="n">
-        <v>11.27931594848633</v>
+        <v>11.27931499481201</v>
       </c>
       <c r="C186" t="n">
-        <v>11.56129933274823</v>
+        <v>11.56129835523201</v>
       </c>
       <c r="D186" t="n">
-        <v>11.16965640749523</v>
+        <v>11.16965546309271</v>
       </c>
       <c r="E186" t="n">
-        <v>11.35764483233677</v>
+        <v>11.35764387203968</v>
       </c>
       <c r="F186" t="n">
         <v>4148100</v>
@@ -4172,16 +4172,16 @@
         <v>44917</v>
       </c>
       <c r="B188" t="n">
-        <v>11.63179492950439</v>
+        <v>11.63179397583008</v>
       </c>
       <c r="C188" t="n">
-        <v>11.74928750576218</v>
+        <v>11.74928654245482</v>
       </c>
       <c r="D188" t="n">
-        <v>11.50646856862995</v>
+        <v>11.50646762523096</v>
       </c>
       <c r="E188" t="n">
-        <v>11.60046352603568</v>
+        <v>11.60046257493018</v>
       </c>
       <c r="F188" t="n">
         <v>2577900</v>
@@ -4192,16 +4192,16 @@
         <v>44918</v>
       </c>
       <c r="B189" t="n">
-        <v>11.78845024108887</v>
+        <v>11.78845119476318</v>
       </c>
       <c r="C189" t="n">
-        <v>12.09393119395663</v>
+        <v>12.09393217234406</v>
       </c>
       <c r="D189" t="n">
-        <v>11.57696273802706</v>
+        <v>11.57696367459224</v>
       </c>
       <c r="E189" t="n">
-        <v>11.67878997131614</v>
+        <v>11.67879091611904</v>
       </c>
       <c r="F189" t="n">
         <v>5656000</v>
@@ -4212,16 +4212,16 @@
         <v>44921</v>
       </c>
       <c r="B190" t="n">
-        <v>11.5769624710083</v>
+        <v>11.57696342468262</v>
       </c>
       <c r="C190" t="n">
-        <v>11.8276144037077</v>
+        <v>11.82761537802995</v>
       </c>
       <c r="D190" t="n">
-        <v>11.51429967458331</v>
+        <v>11.51430062309566</v>
       </c>
       <c r="E190" t="n">
-        <v>11.77278389658625</v>
+        <v>11.77278486639172</v>
       </c>
       <c r="F190" t="n">
         <v>1646600</v>
@@ -4232,16 +4232,16 @@
         <v>44922</v>
       </c>
       <c r="B191" t="n">
-        <v>11.52996635437012</v>
+        <v>11.52996730804443</v>
       </c>
       <c r="C191" t="n">
-        <v>11.60829448052647</v>
+        <v>11.60829544067951</v>
       </c>
       <c r="D191" t="n">
-        <v>11.34197720819598</v>
+        <v>11.34197814632122</v>
       </c>
       <c r="E191" t="n">
-        <v>11.60829448052647</v>
+        <v>11.60829544067951</v>
       </c>
       <c r="F191" t="n">
         <v>1633000</v>
@@ -4312,16 +4312,16 @@
         <v>44929</v>
       </c>
       <c r="B195" t="n">
-        <v>11.13832378387451</v>
+        <v>11.13832473754883</v>
       </c>
       <c r="C195" t="n">
-        <v>11.32631218813412</v>
+        <v>11.32631315790418</v>
       </c>
       <c r="D195" t="n">
-        <v>11.05999490859992</v>
+        <v>11.05999585556764</v>
       </c>
       <c r="E195" t="n">
-        <v>11.30281382435154</v>
+        <v>11.30281479210966</v>
       </c>
       <c r="F195" t="n">
         <v>1562800</v>
@@ -4412,16 +4412,16 @@
         <v>44936</v>
       </c>
       <c r="B200" t="n">
-        <v>11.11482429504395</v>
+        <v>11.11482524871826</v>
       </c>
       <c r="C200" t="n">
-        <v>11.1853201309934</v>
+        <v>11.1853210907164</v>
       </c>
       <c r="D200" t="n">
-        <v>10.6918500263467</v>
+        <v>10.69185094372897</v>
       </c>
       <c r="E200" t="n">
-        <v>11.08349289539969</v>
+        <v>11.08349384638571</v>
       </c>
       <c r="F200" t="n">
         <v>5832500</v>
@@ -4492,16 +4492,16 @@
         <v>44942</v>
       </c>
       <c r="B204" t="n">
-        <v>11.78845024108887</v>
+        <v>11.78845119476318</v>
       </c>
       <c r="C204" t="n">
-        <v>11.8041155670567</v>
+        <v>11.80411652199833</v>
       </c>
       <c r="D204" t="n">
-        <v>11.39680738089987</v>
+        <v>11.39680830289065</v>
       </c>
       <c r="E204" t="n">
-        <v>11.49080157770529</v>
+        <v>11.49080250730011</v>
       </c>
       <c r="F204" t="n">
         <v>3279700</v>
@@ -4512,16 +4512,16 @@
         <v>44943</v>
       </c>
       <c r="B205" t="n">
-        <v>11.74928665161133</v>
+        <v>11.74928569793701</v>
       </c>
       <c r="C205" t="n">
-        <v>11.93727505875722</v>
+        <v>11.93727408982413</v>
       </c>
       <c r="D205" t="n">
-        <v>11.60829497275214</v>
+        <v>11.60829403052194</v>
       </c>
       <c r="E205" t="n">
-        <v>11.81194945399329</v>
+        <v>11.81194849523272</v>
       </c>
       <c r="F205" t="n">
         <v>2676600</v>
@@ -4552,16 +4552,16 @@
         <v>44945</v>
       </c>
       <c r="B207" t="n">
-        <v>11.66312503814697</v>
+        <v>11.66312599182129</v>
       </c>
       <c r="C207" t="n">
-        <v>11.68662340138985</v>
+        <v>11.68662435698559</v>
       </c>
       <c r="D207" t="n">
-        <v>11.27931445451592</v>
+        <v>11.27931537680668</v>
       </c>
       <c r="E207" t="n">
-        <v>11.3419772544966</v>
+        <v>11.3419781819112</v>
       </c>
       <c r="F207" t="n">
         <v>1847800</v>
@@ -4632,16 +4632,16 @@
         <v>44951</v>
       </c>
       <c r="B211" t="n">
-        <v>11.89027786254883</v>
+        <v>11.89027881622314</v>
       </c>
       <c r="C211" t="n">
-        <v>12.07043322555739</v>
+        <v>12.07043419368129</v>
       </c>
       <c r="D211" t="n">
-        <v>11.62396058940618</v>
+        <v>11.62396152172019</v>
       </c>
       <c r="E211" t="n">
-        <v>11.67879035258278</v>
+        <v>11.67879128929448</v>
       </c>
       <c r="F211" t="n">
         <v>10764800</v>
@@ -4652,16 +4652,16 @@
         <v>44952</v>
       </c>
       <c r="B212" t="n">
-        <v>11.96860694885254</v>
+        <v>11.96860599517822</v>
       </c>
       <c r="C212" t="n">
-        <v>12.09393255873588</v>
+        <v>12.09393159507546</v>
       </c>
       <c r="D212" t="n">
-        <v>11.79628460876272</v>
+        <v>11.79628366881928</v>
       </c>
       <c r="E212" t="n">
-        <v>11.91377718127847</v>
+        <v>11.91377623197306</v>
       </c>
       <c r="F212" t="n">
         <v>8143300</v>
@@ -4672,16 +4672,16 @@
         <v>44953</v>
       </c>
       <c r="B213" t="n">
-        <v>11.98427200317383</v>
+        <v>11.98427295684814</v>
       </c>
       <c r="C213" t="n">
-        <v>12.23492320159854</v>
+        <v>12.23492417521897</v>
       </c>
       <c r="D213" t="n">
-        <v>11.92160920356765</v>
+        <v>11.92161015225544</v>
       </c>
       <c r="E213" t="n">
-        <v>11.96860592977254</v>
+        <v>11.96860688220019</v>
       </c>
       <c r="F213" t="n">
         <v>4160800</v>
@@ -4712,16 +4712,16 @@
         <v>44957</v>
       </c>
       <c r="B215" t="n">
-        <v>12.07043361663818</v>
+        <v>12.07043266296387</v>
       </c>
       <c r="C215" t="n">
-        <v>12.14092945557759</v>
+        <v>12.14092849633346</v>
       </c>
       <c r="D215" t="n">
-        <v>11.82761544584636</v>
+        <v>11.8276145113569</v>
       </c>
       <c r="E215" t="n">
-        <v>11.84328077283316</v>
+        <v>11.84327983710599</v>
       </c>
       <c r="F215" t="n">
         <v>5446800</v>
@@ -4732,16 +4732,16 @@
         <v>44958</v>
       </c>
       <c r="B216" t="n">
-        <v>12.07826614379883</v>
+        <v>12.07826709747314</v>
       </c>
       <c r="C216" t="n">
-        <v>12.19575870573871</v>
+        <v>12.19575966868999</v>
       </c>
       <c r="D216" t="n">
-        <v>11.93727447187138</v>
+        <v>11.93727541441329</v>
       </c>
       <c r="E216" t="n">
-        <v>12.08609918046135</v>
+        <v>12.08610013475415</v>
       </c>
       <c r="F216" t="n">
         <v>3741600</v>
@@ -4752,16 +4752,16 @@
         <v>44959</v>
       </c>
       <c r="B217" t="n">
-        <v>12.03910255432129</v>
+        <v>12.03910160064697</v>
       </c>
       <c r="C217" t="n">
-        <v>12.19575956359362</v>
+        <v>12.19575859750976</v>
       </c>
       <c r="D217" t="n">
-        <v>11.8511141431945</v>
+        <v>11.85111320441163</v>
       </c>
       <c r="E217" t="n">
-        <v>12.07043395617575</v>
+        <v>12.07043300001953</v>
       </c>
       <c r="F217" t="n">
         <v>3404900</v>
@@ -4772,16 +4772,16 @@
         <v>44960</v>
       </c>
       <c r="B218" t="n">
-        <v>11.92160987854004</v>
+        <v>11.92161083221436</v>
       </c>
       <c r="C218" t="n">
-        <v>12.17226109115601</v>
+        <v>12.17226206488128</v>
       </c>
       <c r="D218" t="n">
-        <v>11.80411656237665</v>
+        <v>11.80411750665204</v>
       </c>
       <c r="E218" t="n">
-        <v>11.99993800898276</v>
+        <v>11.99993896892297</v>
       </c>
       <c r="F218" t="n">
         <v>3073100</v>
@@ -4792,16 +4792,16 @@
         <v>44963</v>
       </c>
       <c r="B219" t="n">
-        <v>11.91377544403076</v>
+        <v>11.91377639770508</v>
       </c>
       <c r="C219" t="n">
-        <v>11.9607729143837</v>
+        <v>11.96077387182007</v>
       </c>
       <c r="D219" t="n">
-        <v>11.75711845452006</v>
+        <v>11.75711939565429</v>
       </c>
       <c r="E219" t="n">
-        <v>11.92160848025616</v>
+        <v>11.92160943455749</v>
       </c>
       <c r="F219" t="n">
         <v>3421200</v>
@@ -4812,16 +4812,16 @@
         <v>44964</v>
       </c>
       <c r="B220" t="n">
-        <v>11.60046195983887</v>
+        <v>11.60046291351318</v>
       </c>
       <c r="C220" t="n">
-        <v>12.02343622305989</v>
+        <v>12.02343721150694</v>
       </c>
       <c r="D220" t="n">
-        <v>11.49080168900398</v>
+        <v>11.49080263366312</v>
       </c>
       <c r="E220" t="n">
-        <v>12.02343622305989</v>
+        <v>12.02343721150694</v>
       </c>
       <c r="F220" t="n">
         <v>5199600</v>
@@ -4852,16 +4852,16 @@
         <v>44966</v>
       </c>
       <c r="B222" t="n">
-        <v>11.66312503814697</v>
+        <v>11.66312599182129</v>
       </c>
       <c r="C222" t="n">
-        <v>11.78845063810834</v>
+        <v>11.78845160203032</v>
       </c>
       <c r="D222" t="n">
-        <v>11.55346476468103</v>
+        <v>11.55346570938861</v>
       </c>
       <c r="E222" t="n">
-        <v>11.71012176463273</v>
+        <v>11.7101227221499</v>
       </c>
       <c r="F222" t="n">
         <v>2260100</v>
@@ -4952,16 +4952,16 @@
         <v>44973</v>
       </c>
       <c r="B227" t="n">
-        <v>11.89027786254883</v>
+        <v>11.89027881622314</v>
       </c>
       <c r="C227" t="n">
-        <v>11.97643902568342</v>
+        <v>11.9764399862684</v>
       </c>
       <c r="D227" t="n">
-        <v>11.57696311596945</v>
+        <v>11.57696404451397</v>
       </c>
       <c r="E227" t="n">
-        <v>11.76495226271687</v>
+        <v>11.7649532063393</v>
       </c>
       <c r="F227" t="n">
         <v>4461000</v>
@@ -5072,16 +5072,16 @@
         <v>44985</v>
       </c>
       <c r="B233" t="n">
-        <v>11.59263038635254</v>
+        <v>11.59262943267822</v>
       </c>
       <c r="C233" t="n">
-        <v>11.82761628379879</v>
+        <v>11.82761531079323</v>
       </c>
       <c r="D233" t="n">
-        <v>11.54563290806346</v>
+        <v>11.54563195825542</v>
       </c>
       <c r="E233" t="n">
-        <v>11.67095852083491</v>
+        <v>11.67095756071688</v>
       </c>
       <c r="F233" t="n">
         <v>7018700</v>
@@ -5092,16 +5092,16 @@
         <v>44986</v>
       </c>
       <c r="B234" t="n">
-        <v>11.52996635437012</v>
+        <v>11.52996730804443</v>
       </c>
       <c r="C234" t="n">
-        <v>11.65529195381987</v>
+        <v>11.6552929178602</v>
       </c>
       <c r="D234" t="n">
-        <v>11.31847884504903</v>
+        <v>11.31847978123065</v>
       </c>
       <c r="E234" t="n">
-        <v>11.60046219081048</v>
+        <v>11.6004631503157</v>
       </c>
       <c r="F234" t="n">
         <v>8005300</v>
@@ -5152,16 +5152,16 @@
         <v>44991</v>
       </c>
       <c r="B237" t="n">
-        <v>11.47513580322266</v>
+        <v>11.47513675689697</v>
       </c>
       <c r="C237" t="n">
-        <v>11.60046214922261</v>
+        <v>11.60046311331254</v>
       </c>
       <c r="D237" t="n">
-        <v>11.27931436803456</v>
+        <v>11.27931530543457</v>
       </c>
       <c r="E237" t="n">
-        <v>11.53779860272289</v>
+        <v>11.53779956160498</v>
       </c>
       <c r="F237" t="n">
         <v>5313400</v>
@@ -5192,16 +5192,16 @@
         <v>44993</v>
       </c>
       <c r="B239" t="n">
-        <v>11.63179492950439</v>
+        <v>11.63179397583008</v>
       </c>
       <c r="C239" t="n">
-        <v>11.63962722012189</v>
+        <v>11.63962626580541</v>
       </c>
       <c r="D239" t="n">
-        <v>11.48297020277831</v>
+        <v>11.48296926130592</v>
       </c>
       <c r="E239" t="n">
-        <v>11.62396189188732</v>
+        <v>11.62396093885522</v>
       </c>
       <c r="F239" t="n">
         <v>2946500</v>
@@ -5212,16 +5212,16 @@
         <v>44994</v>
       </c>
       <c r="B240" t="n">
-        <v>11.5769624710083</v>
+        <v>11.57696342468262</v>
       </c>
       <c r="C240" t="n">
-        <v>11.70228806385827</v>
+        <v>11.70228902785652</v>
       </c>
       <c r="D240" t="n">
-        <v>11.51429967458331</v>
+        <v>11.51430062309566</v>
       </c>
       <c r="E240" t="n">
-        <v>11.62395994182677</v>
+        <v>11.62396089937259</v>
       </c>
       <c r="F240" t="n">
         <v>2514900</v>
@@ -5232,16 +5232,16 @@
         <v>44995</v>
       </c>
       <c r="B241" t="n">
-        <v>11.5769624710083</v>
+        <v>11.57696342468262</v>
       </c>
       <c r="C241" t="n">
-        <v>11.63179297812976</v>
+        <v>11.63179393632084</v>
       </c>
       <c r="D241" t="n">
-        <v>11.44380384185534</v>
+        <v>11.44380478456046</v>
       </c>
       <c r="E241" t="n">
-        <v>11.5769624710083</v>
+        <v>11.57696342468262</v>
       </c>
       <c r="F241" t="n">
         <v>3626000</v>
@@ -5252,16 +5252,16 @@
         <v>44998</v>
       </c>
       <c r="B242" t="n">
-        <v>11.66312503814697</v>
+        <v>11.66312599182129</v>
       </c>
       <c r="C242" t="n">
-        <v>11.74145316462308</v>
+        <v>11.74145412470215</v>
       </c>
       <c r="D242" t="n">
-        <v>11.45947056471</v>
+        <v>11.45947150173183</v>
       </c>
       <c r="E242" t="n">
-        <v>11.52213336469069</v>
+        <v>11.52213430683635</v>
       </c>
       <c r="F242" t="n">
         <v>3223500</v>
@@ -5292,16 +5292,16 @@
         <v>45000</v>
       </c>
       <c r="B244" t="n">
-        <v>11.74928665161133</v>
+        <v>11.74928569793701</v>
       </c>
       <c r="C244" t="n">
-        <v>11.89027833047051</v>
+        <v>11.89027736535209</v>
       </c>
       <c r="D244" t="n">
-        <v>11.61612800979977</v>
+        <v>11.61612706693377</v>
       </c>
       <c r="E244" t="n">
-        <v>11.71795525042035</v>
+        <v>11.71795429928916</v>
       </c>
       <c r="F244" t="n">
         <v>4602600</v>
@@ -5392,16 +5392,16 @@
         <v>45007</v>
       </c>
       <c r="B249" t="n">
-        <v>11.33414554595947</v>
+        <v>11.33414459228516</v>
       </c>
       <c r="C249" t="n">
-        <v>11.45947115234749</v>
+        <v>11.45947018812806</v>
       </c>
       <c r="D249" t="n">
-        <v>11.21665222972105</v>
+        <v>11.21665128593282</v>
       </c>
       <c r="E249" t="n">
-        <v>11.36547694755648</v>
+        <v>11.36547599124588</v>
       </c>
       <c r="F249" t="n">
         <v>3006300</v>
@@ -5412,16 +5412,16 @@
         <v>45008</v>
       </c>
       <c r="B250" t="n">
-        <v>11.18532085418701</v>
+        <v>11.18532180786133</v>
       </c>
       <c r="C250" t="n">
-        <v>11.47513650638449</v>
+        <v>11.47513748476884</v>
       </c>
       <c r="D250" t="n">
-        <v>11.05999524750697</v>
+        <v>11.05999619049587</v>
       </c>
       <c r="E250" t="n">
-        <v>11.39680837570923</v>
+        <v>11.39680934741524</v>
       </c>
       <c r="F250" t="n">
         <v>4422500</v>
@@ -5432,16 +5432,16 @@
         <v>45009</v>
       </c>
       <c r="B251" t="n">
-        <v>11.30281448364258</v>
+        <v>11.30281352996826</v>
       </c>
       <c r="C251" t="n">
-        <v>11.39680869125504</v>
+        <v>11.39680772964997</v>
       </c>
       <c r="D251" t="n">
-        <v>11.11482532141809</v>
+        <v>11.11482438360535</v>
       </c>
       <c r="E251" t="n">
-        <v>11.20882027603011</v>
+        <v>11.20881933028655</v>
       </c>
       <c r="F251" t="n">
         <v>3265300</v>
@@ -5452,16 +5452,16 @@
         <v>45012</v>
       </c>
       <c r="B252" t="n">
-        <v>11.28714752197266</v>
+        <v>11.28714656829834</v>
       </c>
       <c r="C252" t="n">
-        <v>11.42030615904377</v>
+        <v>11.42030519411861</v>
       </c>
       <c r="D252" t="n">
-        <v>11.1931533217459</v>
+        <v>11.19315237601335</v>
       </c>
       <c r="E252" t="n">
-        <v>11.39680779573696</v>
+        <v>11.39680683279722</v>
       </c>
       <c r="F252" t="n">
         <v>2288800</v>
@@ -5492,16 +5492,16 @@
         <v>45014</v>
       </c>
       <c r="B254" t="n">
-        <v>11.36547660827637</v>
+        <v>11.36547565460205</v>
       </c>
       <c r="C254" t="n">
-        <v>11.47513613709258</v>
+        <v>11.47513517421676</v>
       </c>
       <c r="D254" t="n">
-        <v>11.19315353113723</v>
+        <v>11.1931525919225</v>
       </c>
       <c r="E254" t="n">
-        <v>11.43597244651508</v>
+        <v>11.43597148692548</v>
       </c>
       <c r="F254" t="n">
         <v>2326000</v>
@@ -5572,16 +5572,16 @@
         <v>45020</v>
       </c>
       <c r="B258" t="n">
-        <v>11.43597316741943</v>
+        <v>11.43597221374512</v>
       </c>
       <c r="C258" t="n">
-        <v>11.498635972693</v>
+        <v>11.49863501379308</v>
       </c>
       <c r="D258" t="n">
-        <v>11.24798400459917</v>
+        <v>11.24798306660174</v>
       </c>
       <c r="E258" t="n">
-        <v>11.35764428732769</v>
+        <v>11.35764334018542</v>
       </c>
       <c r="F258" t="n">
         <v>5230100</v>
@@ -5652,16 +5652,16 @@
         <v>45027</v>
       </c>
       <c r="B262" t="n">
-        <v>11.76495361328125</v>
+        <v>11.76495265960693</v>
       </c>
       <c r="C262" t="n">
-        <v>12.0156048417188</v>
+        <v>12.01560386772655</v>
       </c>
       <c r="D262" t="n">
-        <v>11.71012309681085</v>
+        <v>11.71012214758113</v>
       </c>
       <c r="E262" t="n">
-        <v>11.82761642039064</v>
+        <v>11.82761546163684</v>
       </c>
       <c r="F262" t="n">
         <v>2622300</v>
@@ -5692,16 +5692,16 @@
         <v>45029</v>
       </c>
       <c r="B264" t="n">
-        <v>11.91377544403076</v>
+        <v>11.91377639770508</v>
       </c>
       <c r="C264" t="n">
-        <v>11.99993660151179</v>
+        <v>11.99993756208313</v>
       </c>
       <c r="D264" t="n">
-        <v>11.7727837799714</v>
+        <v>11.77278472235961</v>
       </c>
       <c r="E264" t="n">
-        <v>11.82761428654974</v>
+        <v>11.82761523332702</v>
       </c>
       <c r="F264" t="n">
         <v>3337400</v>
@@ -5712,16 +5712,16 @@
         <v>45030</v>
       </c>
       <c r="B265" t="n">
-        <v>11.97643947601318</v>
+        <v>11.97643852233887</v>
       </c>
       <c r="C265" t="n">
-        <v>12.10176508055754</v>
+        <v>12.10176411690365</v>
       </c>
       <c r="D265" t="n">
-        <v>11.83544779740101</v>
+        <v>11.83544685495376</v>
       </c>
       <c r="E265" t="n">
-        <v>12.01560391418318</v>
+        <v>12.01560295739023</v>
       </c>
       <c r="F265" t="n">
         <v>3392800</v>
@@ -5752,16 +5752,16 @@
         <v>45034</v>
       </c>
       <c r="B267" t="n">
-        <v>11.96860694885254</v>
+        <v>11.96860599517822</v>
       </c>
       <c r="C267" t="n">
-        <v>12.16442840104515</v>
+        <v>12.16442743176752</v>
       </c>
       <c r="D267" t="n">
-        <v>11.9451085837493</v>
+        <v>11.94510763194737</v>
       </c>
       <c r="E267" t="n">
-        <v>12.14093003594191</v>
+        <v>12.14092906853667</v>
       </c>
       <c r="F267" t="n">
         <v>3259600</v>
@@ -5772,16 +5772,16 @@
         <v>45035</v>
       </c>
       <c r="B268" t="n">
-        <v>12.03910255432129</v>
+        <v>12.03910160064697</v>
       </c>
       <c r="C268" t="n">
-        <v>12.06260091896225</v>
+        <v>12.06259996342652</v>
       </c>
       <c r="D268" t="n">
-        <v>11.86677947062196</v>
+        <v>11.86677853059817</v>
       </c>
       <c r="E268" t="n">
-        <v>11.96860671339886</v>
+        <v>11.96860576530885</v>
       </c>
       <c r="F268" t="n">
         <v>3098200</v>
@@ -5792,16 +5792,16 @@
         <v>45036</v>
       </c>
       <c r="B269" t="n">
-        <v>12.09393215179443</v>
+        <v>12.09393119812012</v>
       </c>
       <c r="C269" t="n">
-        <v>12.14092962741908</v>
+        <v>12.14092867003875</v>
       </c>
       <c r="D269" t="n">
-        <v>12.00777098464871</v>
+        <v>12.00777003776868</v>
       </c>
       <c r="E269" t="n">
-        <v>12.06260075037785</v>
+        <v>12.06259979917419</v>
       </c>
       <c r="F269" t="n">
         <v>4813100</v>
@@ -5832,16 +5832,16 @@
         <v>45041</v>
       </c>
       <c r="B271" t="n">
-        <v>12.06260013580322</v>
+        <v>12.06260108947754</v>
       </c>
       <c r="C271" t="n">
-        <v>12.14092900885369</v>
+        <v>12.14092996872072</v>
       </c>
       <c r="D271" t="n">
-        <v>11.96860593634236</v>
+        <v>11.96860688258545</v>
       </c>
       <c r="E271" t="n">
-        <v>12.11743064573835</v>
+        <v>12.11743160374759</v>
       </c>
       <c r="F271" t="n">
         <v>2381100</v>
@@ -5872,16 +5872,16 @@
         <v>45043</v>
       </c>
       <c r="B273" t="n">
-        <v>12.07826614379883</v>
+        <v>12.07826709747314</v>
       </c>
       <c r="C273" t="n">
-        <v>12.09393147012438</v>
+        <v>12.0939324250356</v>
       </c>
       <c r="D273" t="n">
-        <v>11.95294054519642</v>
+        <v>11.95294148897529</v>
       </c>
       <c r="E273" t="n">
-        <v>12.01560334449763</v>
+        <v>12.01560429322422</v>
       </c>
       <c r="F273" t="n">
         <v>2919600</v>
@@ -5932,16 +5932,16 @@
         <v>45049</v>
       </c>
       <c r="B276" t="n">
-        <v>12.28975296020508</v>
+        <v>12.28975391387939</v>
       </c>
       <c r="C276" t="n">
-        <v>12.48557439565576</v>
+        <v>12.48557536452565</v>
       </c>
       <c r="D276" t="n">
-        <v>12.28192067050667</v>
+        <v>12.2819216235732</v>
       </c>
       <c r="E276" t="n">
-        <v>12.48557439565576</v>
+        <v>12.48557536452565</v>
       </c>
       <c r="F276" t="n">
         <v>6661600</v>
@@ -5952,16 +5952,16 @@
         <v>45050</v>
       </c>
       <c r="B277" t="n">
-        <v>12.33675098419189</v>
+        <v>12.33675193786621</v>
       </c>
       <c r="C277" t="n">
-        <v>12.43857822481247</v>
+        <v>12.43857918635839</v>
       </c>
       <c r="D277" t="n">
-        <v>12.25842210771467</v>
+        <v>12.25842305533389</v>
       </c>
       <c r="E277" t="n">
-        <v>12.43074518776484</v>
+        <v>12.43074614870524</v>
       </c>
       <c r="F277" t="n">
         <v>8184400</v>
@@ -5992,16 +5992,16 @@
         <v>45054</v>
       </c>
       <c r="B279" t="n">
-        <v>12.11165809631348</v>
+        <v>12.11165904998779</v>
       </c>
       <c r="C279" t="n">
-        <v>12.58781351962092</v>
+        <v>12.58781451078781</v>
       </c>
       <c r="D279" t="n">
-        <v>12.05105678220141</v>
+        <v>12.05105773110397</v>
       </c>
       <c r="E279" t="n">
-        <v>12.54452651284189</v>
+        <v>12.54452750060035</v>
       </c>
       <c r="F279" t="n">
         <v>5826000</v>
@@ -6052,16 +6052,16 @@
         <v>45057</v>
       </c>
       <c r="B282" t="n">
-        <v>12.05971622467041</v>
+        <v>12.05971527099609</v>
       </c>
       <c r="C282" t="n">
-        <v>12.11165998038074</v>
+        <v>12.11165902259875</v>
       </c>
       <c r="D282" t="n">
-        <v>11.73939364568632</v>
+        <v>11.7393927173429</v>
       </c>
       <c r="E282" t="n">
-        <v>11.79133740139665</v>
+        <v>11.79133646894556</v>
       </c>
       <c r="F282" t="n">
         <v>3678200</v>
@@ -6072,16 +6072,16 @@
         <v>45058</v>
       </c>
       <c r="B283" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C283" t="n">
-        <v>12.25017729158851</v>
+        <v>12.25017632493442</v>
       </c>
       <c r="D283" t="n">
-        <v>11.9991136136361</v>
+        <v>11.99911266679329</v>
       </c>
       <c r="E283" t="n">
-        <v>12.0424006254826</v>
+        <v>12.04239967522403</v>
       </c>
       <c r="F283" t="n">
         <v>3087800</v>
@@ -6112,16 +6112,16 @@
         <v>45062</v>
       </c>
       <c r="B285" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="C285" t="n">
-        <v>12.30212128603885</v>
+        <v>12.30212031805942</v>
       </c>
       <c r="D285" t="n">
-        <v>12.08568706272756</v>
+        <v>12.08568611177803</v>
       </c>
       <c r="E285" t="n">
-        <v>12.18091782375736</v>
+        <v>12.18091686531469</v>
       </c>
       <c r="F285" t="n">
         <v>2907500</v>
@@ -6232,16 +6232,16 @@
         <v>45070</v>
       </c>
       <c r="B291" t="n">
-        <v>12.25017738342285</v>
+        <v>12.25017642974854</v>
       </c>
       <c r="C291" t="n">
-        <v>12.30212196315428</v>
+        <v>12.30212100543608</v>
       </c>
       <c r="D291" t="n">
-        <v>12.18091849420168</v>
+        <v>12.18091754591915</v>
       </c>
       <c r="E291" t="n">
-        <v>12.26749251854369</v>
+        <v>12.26749156352139</v>
       </c>
       <c r="F291" t="n">
         <v>1846000</v>
@@ -6312,16 +6312,16 @@
         <v>45076</v>
       </c>
       <c r="B295" t="n">
-        <v>12.26749229431152</v>
+        <v>12.26749134063721</v>
       </c>
       <c r="C295" t="n">
-        <v>12.38003819364653</v>
+        <v>12.3800372312229</v>
       </c>
       <c r="D295" t="n">
-        <v>12.25017715950718</v>
+        <v>12.25017620717894</v>
       </c>
       <c r="E295" t="n">
-        <v>12.37138062624436</v>
+        <v>12.37137966449377</v>
       </c>
       <c r="F295" t="n">
         <v>1829100</v>
@@ -6332,16 +6332,16 @@
         <v>45077</v>
       </c>
       <c r="B296" t="n">
-        <v>12.18957614898682</v>
+        <v>12.1895751953125</v>
       </c>
       <c r="C296" t="n">
-        <v>12.31077961880671</v>
+        <v>12.31077865564981</v>
       </c>
       <c r="D296" t="n">
-        <v>12.1636042717508</v>
+        <v>12.16360332010844</v>
       </c>
       <c r="E296" t="n">
-        <v>12.27615017394832</v>
+        <v>12.27614921350073</v>
       </c>
       <c r="F296" t="n">
         <v>3816500</v>
@@ -6352,16 +6352,16 @@
         <v>45078</v>
       </c>
       <c r="B297" t="n">
-        <v>12.2415189743042</v>
+        <v>12.24151992797852</v>
       </c>
       <c r="C297" t="n">
-        <v>12.30212028771158</v>
+        <v>12.30212124610704</v>
       </c>
       <c r="D297" t="n">
-        <v>12.16360252813415</v>
+        <v>12.1636034757384</v>
       </c>
       <c r="E297" t="n">
-        <v>12.26749084781722</v>
+        <v>12.26749180351488</v>
       </c>
       <c r="F297" t="n">
         <v>2308800</v>
@@ -6372,16 +6372,16 @@
         <v>45079</v>
       </c>
       <c r="B298" t="n">
-        <v>12.17226219177246</v>
+        <v>12.17226028442383</v>
       </c>
       <c r="C298" t="n">
-        <v>12.33675185320416</v>
+        <v>12.3367499200806</v>
       </c>
       <c r="D298" t="n">
-        <v>12.07703059643153</v>
+        <v>12.07702870400534</v>
       </c>
       <c r="E298" t="n">
-        <v>12.31077997521623</v>
+        <v>12.31077804616237</v>
       </c>
       <c r="F298" t="n">
         <v>5725100</v>
@@ -6392,16 +6392,16 @@
         <v>45082</v>
       </c>
       <c r="B299" t="n">
-        <v>12.06837177276611</v>
+        <v>12.0683708190918</v>
       </c>
       <c r="C299" t="n">
-        <v>12.1982328004551</v>
+        <v>12.19823183651883</v>
       </c>
       <c r="D299" t="n">
-        <v>11.97314101296568</v>
+        <v>11.97314006681674</v>
       </c>
       <c r="E299" t="n">
-        <v>12.17226092516972</v>
+        <v>12.17225996328581</v>
       </c>
       <c r="F299" t="n">
         <v>3442900</v>
@@ -6412,16 +6412,16 @@
         <v>45083</v>
       </c>
       <c r="B300" t="n">
-        <v>12.32809257507324</v>
+        <v>12.32809352874756</v>
       </c>
       <c r="C300" t="n">
-        <v>12.41466659053087</v>
+        <v>12.41466755090237</v>
       </c>
       <c r="D300" t="n">
-        <v>12.07702892100332</v>
+        <v>12.0770298552559</v>
       </c>
       <c r="E300" t="n">
-        <v>12.08568648767528</v>
+        <v>12.08568742259759</v>
       </c>
       <c r="F300" t="n">
         <v>7376500</v>
@@ -6432,16 +6432,16 @@
         <v>45084</v>
       </c>
       <c r="B301" t="n">
-        <v>12.22420406341553</v>
+        <v>12.22420501708984</v>
       </c>
       <c r="C301" t="n">
-        <v>12.46661014707579</v>
+        <v>12.46661111966148</v>
       </c>
       <c r="D301" t="n">
-        <v>12.21554649687706</v>
+        <v>12.21554744987595</v>
       </c>
       <c r="E301" t="n">
-        <v>12.38003695858405</v>
+        <v>12.3800379244157</v>
       </c>
       <c r="F301" t="n">
         <v>3154600</v>
@@ -6492,16 +6492,16 @@
         <v>45090</v>
       </c>
       <c r="B304" t="n">
-        <v>12.31077861785889</v>
+        <v>12.3107795715332</v>
       </c>
       <c r="C304" t="n">
-        <v>12.50124013627868</v>
+        <v>12.5012411047074</v>
       </c>
       <c r="D304" t="n">
-        <v>12.29346348402198</v>
+        <v>12.29346443635495</v>
       </c>
       <c r="E304" t="n">
-        <v>12.46661069423589</v>
+        <v>12.46661165998199</v>
       </c>
       <c r="F304" t="n">
         <v>1312000</v>
@@ -6532,16 +6532,16 @@
         <v>45092</v>
       </c>
       <c r="B306" t="n">
-        <v>12.46661186218262</v>
+        <v>12.4666109085083</v>
       </c>
       <c r="C306" t="n">
-        <v>12.49258456537125</v>
+        <v>12.49258360971007</v>
       </c>
       <c r="D306" t="n">
-        <v>12.36272352632139</v>
+        <v>12.36272258059435</v>
       </c>
       <c r="E306" t="n">
-        <v>12.45795512008417</v>
+        <v>12.45795416707208</v>
       </c>
       <c r="F306" t="n">
         <v>1266000</v>
@@ -6592,16 +6592,16 @@
         <v>45097</v>
       </c>
       <c r="B309" t="n">
-        <v>12.72633266448975</v>
+        <v>12.72633171081543</v>
       </c>
       <c r="C309" t="n">
-        <v>12.89947988480048</v>
+        <v>12.89947891815102</v>
       </c>
       <c r="D309" t="n">
-        <v>12.64841620894215</v>
+        <v>12.64841526110666</v>
       </c>
       <c r="E309" t="n">
-        <v>12.6917032204276</v>
+        <v>12.69170226934831</v>
       </c>
       <c r="F309" t="n">
         <v>3568000</v>
@@ -6652,16 +6652,16 @@
         <v>45100</v>
       </c>
       <c r="B312" t="n">
-        <v>12.9427661895752</v>
+        <v>12.94276714324951</v>
       </c>
       <c r="C312" t="n">
-        <v>13.07262721694078</v>
+        <v>13.07262818018377</v>
       </c>
       <c r="D312" t="n">
-        <v>12.7609614117682</v>
+        <v>12.76096235204642</v>
       </c>
       <c r="E312" t="n">
-        <v>12.81290598784064</v>
+        <v>12.81290693194634</v>
       </c>
       <c r="F312" t="n">
         <v>2959500</v>
@@ -6672,16 +6672,16 @@
         <v>45103</v>
       </c>
       <c r="B313" t="n">
-        <v>12.71767425537109</v>
+        <v>12.71767520904541</v>
       </c>
       <c r="C313" t="n">
-        <v>13.01202492323384</v>
+        <v>13.01202589898095</v>
       </c>
       <c r="D313" t="n">
-        <v>12.66573050553121</v>
+        <v>12.66573145531036</v>
       </c>
       <c r="E313" t="n">
-        <v>12.94276603969331</v>
+        <v>12.94276701024684</v>
       </c>
       <c r="F313" t="n">
         <v>2677600</v>
@@ -6792,16 +6792,16 @@
         <v>45111</v>
       </c>
       <c r="B319" t="n">
-        <v>12.34540748596191</v>
+        <v>12.34540843963623</v>
       </c>
       <c r="C319" t="n">
-        <v>12.40600880031166</v>
+        <v>12.40600975866739</v>
       </c>
       <c r="D319" t="n">
-        <v>12.23286159814739</v>
+        <v>12.23286254312761</v>
       </c>
       <c r="E319" t="n">
-        <v>12.38869449291073</v>
+        <v>12.38869544992894</v>
       </c>
       <c r="F319" t="n">
         <v>2230100</v>
@@ -6832,16 +6832,16 @@
         <v>45113</v>
       </c>
       <c r="B321" t="n">
-        <v>12.32809257507324</v>
+        <v>12.32809352874756</v>
       </c>
       <c r="C321" t="n">
-        <v>12.48392547264458</v>
+        <v>12.48392643837378</v>
       </c>
       <c r="D321" t="n">
-        <v>12.25017612628758</v>
+        <v>12.25017707393445</v>
       </c>
       <c r="E321" t="n">
-        <v>12.4319808982438</v>
+        <v>12.43198185995469</v>
       </c>
       <c r="F321" t="n">
         <v>2081000</v>
@@ -6852,16 +6852,16 @@
         <v>45114</v>
       </c>
       <c r="B322" t="n">
-        <v>12.34540748596191</v>
+        <v>12.34540843963623</v>
       </c>
       <c r="C322" t="n">
-        <v>12.48392524769333</v>
+        <v>12.48392621206805</v>
       </c>
       <c r="D322" t="n">
-        <v>12.25883347206429</v>
+        <v>12.25883441905082</v>
       </c>
       <c r="E322" t="n">
-        <v>12.42332393334358</v>
+        <v>12.42332489303689</v>
       </c>
       <c r="F322" t="n">
         <v>2149700</v>
@@ -6872,16 +6872,16 @@
         <v>45117</v>
       </c>
       <c r="B323" t="n">
-        <v>12.38869476318359</v>
+        <v>12.38869571685791</v>
       </c>
       <c r="C323" t="n">
-        <v>12.45795364556026</v>
+        <v>12.45795460456609</v>
       </c>
       <c r="D323" t="n">
-        <v>12.31077831410209</v>
+        <v>12.31077926177845</v>
       </c>
       <c r="E323" t="n">
-        <v>12.38003719647876</v>
+        <v>12.38003814948662</v>
       </c>
       <c r="F323" t="n">
         <v>1514600</v>
@@ -6892,16 +6892,16 @@
         <v>45118</v>
       </c>
       <c r="B324" t="n">
-        <v>12.34540748596191</v>
+        <v>12.34540843963623</v>
       </c>
       <c r="C324" t="n">
-        <v>12.3973512337957</v>
+        <v>12.39735219148264</v>
       </c>
       <c r="D324" t="n">
-        <v>12.23286159814739</v>
+        <v>12.23286254312761</v>
       </c>
       <c r="E324" t="n">
-        <v>12.38869449291073</v>
+        <v>12.38869544992894</v>
       </c>
       <c r="F324" t="n">
         <v>1919200</v>
@@ -6912,16 +6912,16 @@
         <v>45119</v>
       </c>
       <c r="B325" t="n">
-        <v>12.38869476318359</v>
+        <v>12.38869571685791</v>
       </c>
       <c r="C325" t="n">
-        <v>12.45795364556026</v>
+        <v>12.45795460456609</v>
       </c>
       <c r="D325" t="n">
-        <v>12.28480561398759</v>
+        <v>12.28480655966458</v>
       </c>
       <c r="E325" t="n">
-        <v>12.37137962977392</v>
+        <v>12.37138058211533</v>
       </c>
       <c r="F325" t="n">
         <v>1842800</v>
@@ -7052,16 +7052,16 @@
         <v>45128</v>
       </c>
       <c r="B332" t="n">
-        <v>12.38869476318359</v>
+        <v>12.38869571685791</v>
       </c>
       <c r="C332" t="n">
-        <v>12.38869476318359</v>
+        <v>12.38869571685791</v>
       </c>
       <c r="D332" t="n">
-        <v>12.22420429831576</v>
+        <v>12.2242052393277</v>
       </c>
       <c r="E332" t="n">
-        <v>12.27614887291376</v>
+        <v>12.27614981792436</v>
       </c>
       <c r="F332" t="n">
         <v>2631400</v>
@@ -7072,16 +7072,16 @@
         <v>45131</v>
       </c>
       <c r="B333" t="n">
-        <v>12.34540748596191</v>
+        <v>12.34540843963623</v>
       </c>
       <c r="C333" t="n">
-        <v>12.42332393334358</v>
+        <v>12.42332489303689</v>
       </c>
       <c r="D333" t="n">
-        <v>12.31943478641403</v>
+        <v>12.31943573808198</v>
       </c>
       <c r="E333" t="n">
-        <v>12.42332393334358</v>
+        <v>12.42332489303689</v>
       </c>
       <c r="F333" t="n">
         <v>1347200</v>
@@ -7092,16 +7092,16 @@
         <v>45132</v>
       </c>
       <c r="B334" t="n">
-        <v>12.17226219177246</v>
+        <v>12.17226028442383</v>
       </c>
       <c r="C334" t="n">
-        <v>12.47526963664793</v>
+        <v>12.47526768181915</v>
       </c>
       <c r="D334" t="n">
-        <v>12.16360462389945</v>
+        <v>12.16360271790742</v>
       </c>
       <c r="E334" t="n">
-        <v>12.41466831279906</v>
+        <v>12.41466636746628</v>
       </c>
       <c r="F334" t="n">
         <v>2710400</v>
@@ -7132,16 +7132,16 @@
         <v>45134</v>
       </c>
       <c r="B336" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C336" t="n">
-        <v>12.22420541473304</v>
+        <v>12.22420445012837</v>
       </c>
       <c r="D336" t="n">
-        <v>12.03374305798708</v>
+        <v>12.03374210841168</v>
       </c>
       <c r="E336" t="n">
-        <v>12.18091840288654</v>
+        <v>12.18091744169762</v>
       </c>
       <c r="F336" t="n">
         <v>2852900</v>
@@ -7152,16 +7152,16 @@
         <v>45135</v>
       </c>
       <c r="B337" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="C337" t="n">
-        <v>12.22420483354582</v>
+        <v>12.22420387169716</v>
       </c>
       <c r="D337" t="n">
-        <v>12.0597151871069</v>
+        <v>12.05971423820094</v>
       </c>
       <c r="E337" t="n">
-        <v>12.14628838105279</v>
+        <v>12.14628742533491</v>
       </c>
       <c r="F337" t="n">
         <v>1506100</v>
@@ -7172,16 +7172,16 @@
         <v>45138</v>
       </c>
       <c r="B338" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="C338" t="n">
-        <v>12.20689052500906</v>
+        <v>12.20688956452276</v>
       </c>
       <c r="D338" t="n">
-        <v>12.10300137126433</v>
+        <v>12.10300041895243</v>
       </c>
       <c r="E338" t="n">
-        <v>12.20689052500906</v>
+        <v>12.20688956452276</v>
       </c>
       <c r="F338" t="n">
         <v>1549400</v>
@@ -7192,16 +7192,16 @@
         <v>45139</v>
       </c>
       <c r="B339" t="n">
-        <v>12.12897396087646</v>
+        <v>12.12897491455078</v>
       </c>
       <c r="C339" t="n">
-        <v>12.38003762458143</v>
+        <v>12.38003859799633</v>
       </c>
       <c r="D339" t="n">
-        <v>12.08568695148643</v>
+        <v>12.08568790175718</v>
       </c>
       <c r="E339" t="n">
-        <v>12.12031639387225</v>
+        <v>12.12031734686584</v>
       </c>
       <c r="F339" t="n">
         <v>5884200</v>
@@ -7212,16 +7212,16 @@
         <v>45140</v>
       </c>
       <c r="B340" t="n">
-        <v>12.22420406341553</v>
+        <v>12.22420501708984</v>
       </c>
       <c r="C340" t="n">
-        <v>12.232861629954</v>
+        <v>12.23286258430374</v>
       </c>
       <c r="D340" t="n">
-        <v>12.12897330838532</v>
+        <v>12.12897425463018</v>
       </c>
       <c r="E340" t="n">
-        <v>12.13763087492379</v>
+        <v>12.13763182184407</v>
       </c>
       <c r="F340" t="n">
         <v>1697600</v>
@@ -7292,16 +7292,16 @@
         <v>45146</v>
       </c>
       <c r="B344" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C344" t="n">
-        <v>12.15494652603107</v>
+        <v>12.15494556689158</v>
       </c>
       <c r="D344" t="n">
-        <v>11.92985472493413</v>
+        <v>11.92985378355649</v>
       </c>
       <c r="E344" t="n">
-        <v>11.99045687177166</v>
+        <v>11.99045592561195</v>
       </c>
       <c r="F344" t="n">
         <v>2176400</v>
@@ -7332,16 +7332,16 @@
         <v>45148</v>
       </c>
       <c r="B346" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C346" t="n">
-        <v>12.09434452900206</v>
+        <v>12.09434549372545</v>
       </c>
       <c r="D346" t="n">
-        <v>11.88656704887551</v>
+        <v>11.88656799702522</v>
       </c>
       <c r="E346" t="n">
-        <v>12.01642807715848</v>
+        <v>12.01642903566675</v>
       </c>
       <c r="F346" t="n">
         <v>2835300</v>
@@ -7352,16 +7352,16 @@
         <v>45149</v>
       </c>
       <c r="B347" t="n">
-        <v>11.92119693756104</v>
+        <v>11.92119789123535</v>
       </c>
       <c r="C347" t="n">
-        <v>11.97314068671642</v>
+        <v>11.97314164454614</v>
       </c>
       <c r="D347" t="n">
-        <v>11.83462292146072</v>
+        <v>11.83462386820927</v>
       </c>
       <c r="E347" t="n">
-        <v>11.97314068671642</v>
+        <v>11.97314164454614</v>
       </c>
       <c r="F347" t="n">
         <v>2472600</v>
@@ -7372,16 +7372,16 @@
         <v>45152</v>
       </c>
       <c r="B348" t="n">
-        <v>11.91254043579102</v>
+        <v>11.9125394821167</v>
       </c>
       <c r="C348" t="n">
-        <v>11.96448418959011</v>
+        <v>11.96448323175737</v>
       </c>
       <c r="D348" t="n">
-        <v>11.82596641195109</v>
+        <v>11.82596546520757</v>
       </c>
       <c r="E348" t="n">
-        <v>11.92119800330122</v>
+        <v>11.92119704893382</v>
       </c>
       <c r="F348" t="n">
         <v>1369900</v>
@@ -7392,16 +7392,16 @@
         <v>45153</v>
       </c>
       <c r="B349" t="n">
-        <v>11.860595703125</v>
+        <v>11.86059474945068</v>
       </c>
       <c r="C349" t="n">
-        <v>11.99911347897441</v>
+        <v>11.9991125141623</v>
       </c>
       <c r="D349" t="n">
-        <v>11.85193813572664</v>
+        <v>11.85193718274846</v>
       </c>
       <c r="E349" t="n">
-        <v>11.91254028188406</v>
+        <v>11.91253932403304</v>
       </c>
       <c r="F349" t="n">
         <v>2713800</v>
@@ -7432,16 +7432,16 @@
         <v>45155</v>
       </c>
       <c r="B351" t="n">
-        <v>11.71341991424561</v>
+        <v>11.71341896057129</v>
       </c>
       <c r="C351" t="n">
-        <v>11.78267879953539</v>
+        <v>11.7826778402222</v>
       </c>
       <c r="D351" t="n">
-        <v>11.66147616309379</v>
+        <v>11.66147521364859</v>
       </c>
       <c r="E351" t="n">
-        <v>11.73073504838357</v>
+        <v>11.7307340932995</v>
       </c>
       <c r="F351" t="n">
         <v>2345000</v>
@@ -7492,16 +7492,16 @@
         <v>45160</v>
       </c>
       <c r="B354" t="n">
-        <v>11.79999351501465</v>
+        <v>11.79999446868896</v>
       </c>
       <c r="C354" t="n">
-        <v>11.86925239784715</v>
+        <v>11.86925335711897</v>
       </c>
       <c r="D354" t="n">
-        <v>11.73073463218214</v>
+        <v>11.73073558025896</v>
       </c>
       <c r="E354" t="n">
-        <v>11.79133594825283</v>
+        <v>11.79133690122745</v>
       </c>
       <c r="F354" t="n">
         <v>2231700</v>
@@ -7592,16 +7592,16 @@
         <v>45167</v>
       </c>
       <c r="B359" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="C359" t="n">
-        <v>12.12031650543213</v>
+        <v>12.12031555175781</v>
       </c>
       <c r="D359" t="n">
-        <v>11.97314116752997</v>
+        <v>11.97314022543599</v>
       </c>
       <c r="E359" t="n">
-        <v>11.98179873461387</v>
+        <v>11.98179779183868</v>
       </c>
       <c r="F359" t="n">
         <v>1776800</v>
@@ -7612,16 +7612,16 @@
         <v>45168</v>
       </c>
       <c r="B360" t="n">
-        <v>12.11165809631348</v>
+        <v>12.11165904998779</v>
       </c>
       <c r="C360" t="n">
-        <v>12.19823210987155</v>
+        <v>12.19823307036272</v>
       </c>
       <c r="D360" t="n">
-        <v>12.05971434868342</v>
+        <v>12.05971529826767</v>
       </c>
       <c r="E360" t="n">
-        <v>12.17226023605652</v>
+        <v>12.17226119450266</v>
       </c>
       <c r="F360" t="n">
         <v>1998700</v>
@@ -7692,16 +7692,16 @@
         <v>45174</v>
       </c>
       <c r="B364" t="n">
-        <v>11.92119693756104</v>
+        <v>11.92119789123535</v>
       </c>
       <c r="C364" t="n">
-        <v>12.06837144392197</v>
+        <v>12.06837240936998</v>
       </c>
       <c r="D364" t="n">
-        <v>11.9125393708248</v>
+        <v>11.91254032380653</v>
       </c>
       <c r="E364" t="n">
-        <v>12.04239956934427</v>
+        <v>12.04240053271458</v>
       </c>
       <c r="F364" t="n">
         <v>3869600</v>
@@ -7712,16 +7712,16 @@
         <v>45175</v>
       </c>
       <c r="B365" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C365" t="n">
-        <v>12.02508564417022</v>
+        <v>12.02508660336907</v>
       </c>
       <c r="D365" t="n">
-        <v>11.81730816404367</v>
+        <v>11.81730910666884</v>
       </c>
       <c r="E365" t="n">
-        <v>11.9385116253149</v>
+        <v>11.93851257760805</v>
       </c>
       <c r="F365" t="n">
         <v>2473500</v>
@@ -7772,16 +7772,16 @@
         <v>45181</v>
       </c>
       <c r="B368" t="n">
-        <v>12.06837177276611</v>
+        <v>12.0683708190918</v>
       </c>
       <c r="C368" t="n">
-        <v>12.15494579122544</v>
+        <v>12.15494483070982</v>
       </c>
       <c r="D368" t="n">
-        <v>11.98179857993782</v>
+        <v>11.98179763310474</v>
       </c>
       <c r="E368" t="n">
-        <v>12.03374233050859</v>
+        <v>12.03374137957078</v>
       </c>
       <c r="F368" t="n">
         <v>2215400</v>
@@ -7792,16 +7792,16 @@
         <v>45182</v>
       </c>
       <c r="B369" t="n">
-        <v>12.06837177276611</v>
+        <v>12.0683708190918</v>
       </c>
       <c r="C369" t="n">
-        <v>12.1982328004551</v>
+        <v>12.19823183651883</v>
       </c>
       <c r="D369" t="n">
-        <v>12.03374233050859</v>
+        <v>12.03374137957078</v>
       </c>
       <c r="E369" t="n">
-        <v>12.07702933973825</v>
+        <v>12.07702838537979</v>
       </c>
       <c r="F369" t="n">
         <v>1684100</v>
@@ -7852,16 +7852,16 @@
         <v>45187</v>
       </c>
       <c r="B372" t="n">
-        <v>12.05971622467041</v>
+        <v>12.05971527099609</v>
       </c>
       <c r="C372" t="n">
-        <v>12.2415210209188</v>
+        <v>12.24152005286748</v>
       </c>
       <c r="D372" t="n">
-        <v>11.99911407550021</v>
+        <v>11.99911312661827</v>
       </c>
       <c r="E372" t="n">
-        <v>12.21554831743252</v>
+        <v>12.21554735143511</v>
       </c>
       <c r="F372" t="n">
         <v>3188500</v>
@@ -7892,16 +7892,16 @@
         <v>45189</v>
       </c>
       <c r="B374" t="n">
-        <v>12.06837177276611</v>
+        <v>12.0683708190918</v>
       </c>
       <c r="C374" t="n">
-        <v>12.1462882242533</v>
+        <v>12.14628726442182</v>
       </c>
       <c r="D374" t="n">
-        <v>11.97314101296568</v>
+        <v>11.97314006681674</v>
       </c>
       <c r="E374" t="n">
-        <v>12.08568690671039</v>
+        <v>12.08568595166779</v>
       </c>
       <c r="F374" t="n">
         <v>2998000</v>
@@ -7912,16 +7912,16 @@
         <v>45190</v>
       </c>
       <c r="B375" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C375" t="n">
-        <v>12.03374238555092</v>
+        <v>12.0337433454403</v>
       </c>
       <c r="D375" t="n">
-        <v>11.8779103074948</v>
+        <v>11.877911254954</v>
       </c>
       <c r="E375" t="n">
-        <v>12.02508564417022</v>
+        <v>12.02508660336907</v>
       </c>
       <c r="F375" t="n">
         <v>4405700</v>
@@ -7932,16 +7932,16 @@
         <v>45191</v>
       </c>
       <c r="B376" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C376" t="n">
-        <v>12.10300127038276</v>
+        <v>12.10300223579667</v>
       </c>
       <c r="D376" t="n">
-        <v>11.92985405830317</v>
+        <v>11.92985500990573</v>
       </c>
       <c r="E376" t="n">
-        <v>12.02508564417022</v>
+        <v>12.02508660336907</v>
       </c>
       <c r="F376" t="n">
         <v>2812600</v>
@@ -7952,16 +7952,16 @@
         <v>45194</v>
       </c>
       <c r="B377" t="n">
-        <v>11.8086519241333</v>
+        <v>11.80865097045898</v>
       </c>
       <c r="C377" t="n">
-        <v>11.97314157618643</v>
+        <v>11.97314060922783</v>
       </c>
       <c r="D377" t="n">
-        <v>11.8086519241333</v>
+        <v>11.80865097045898</v>
       </c>
       <c r="E377" t="n">
-        <v>11.95582726705872</v>
+        <v>11.95582630149842</v>
       </c>
       <c r="F377" t="n">
         <v>3691700</v>
@@ -7972,16 +7972,16 @@
         <v>45195</v>
       </c>
       <c r="B378" t="n">
-        <v>11.83462238311768</v>
+        <v>11.83462333679199</v>
       </c>
       <c r="C378" t="n">
-        <v>12.06837089494598</v>
+        <v>12.06837186745655</v>
       </c>
       <c r="D378" t="n">
-        <v>11.78267781069418</v>
+        <v>11.78267876018263</v>
       </c>
       <c r="E378" t="n">
-        <v>11.80865050972141</v>
+        <v>11.80865146130283</v>
       </c>
       <c r="F378" t="n">
         <v>7795500</v>
@@ -8072,16 +8072,16 @@
         <v>45202</v>
       </c>
       <c r="B383" t="n">
-        <v>11.8086519241333</v>
+        <v>11.80865097045898</v>
       </c>
       <c r="C383" t="n">
-        <v>11.91254025579282</v>
+        <v>11.91253929372841</v>
       </c>
       <c r="D383" t="n">
-        <v>11.75670734548801</v>
+        <v>11.75670639600877</v>
       </c>
       <c r="E383" t="n">
-        <v>11.86059567714752</v>
+        <v>11.8605947192782</v>
       </c>
       <c r="F383" t="n">
         <v>2809600</v>
@@ -8132,16 +8132,16 @@
         <v>45205</v>
       </c>
       <c r="B386" t="n">
-        <v>11.67879104614258</v>
+        <v>11.67879009246826</v>
       </c>
       <c r="C386" t="n">
-        <v>11.70476374862726</v>
+        <v>11.70476279283205</v>
       </c>
       <c r="D386" t="n">
-        <v>11.61818972494048</v>
+        <v>11.61818877621478</v>
       </c>
       <c r="E386" t="n">
-        <v>11.68744861363747</v>
+        <v>11.68744765925619</v>
       </c>
       <c r="F386" t="n">
         <v>3573900</v>
@@ -8152,16 +8152,16 @@
         <v>45208</v>
       </c>
       <c r="B387" t="n">
-        <v>11.91254043579102</v>
+        <v>11.9125394821167</v>
       </c>
       <c r="C387" t="n">
-        <v>11.92985474518035</v>
+        <v>11.92985379011992</v>
       </c>
       <c r="D387" t="n">
-        <v>11.61818974549255</v>
+        <v>11.61818881538288</v>
       </c>
       <c r="E387" t="n">
-        <v>11.61818974549255</v>
+        <v>11.61818881538288</v>
       </c>
       <c r="F387" t="n">
         <v>4118900</v>
@@ -8172,16 +8172,16 @@
         <v>45209</v>
       </c>
       <c r="B388" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C388" t="n">
-        <v>12.16360409352659</v>
+        <v>12.16360313370393</v>
       </c>
       <c r="D388" t="n">
-        <v>11.91254041557417</v>
+        <v>11.9125394755628</v>
       </c>
       <c r="E388" t="n">
-        <v>11.92985472493413</v>
+        <v>11.92985378355649</v>
       </c>
       <c r="F388" t="n">
         <v>3643400</v>
@@ -8212,16 +8212,16 @@
         <v>45212</v>
       </c>
       <c r="B390" t="n">
-        <v>12.02508544921875</v>
+        <v>12.02508640289307</v>
       </c>
       <c r="C390" t="n">
-        <v>12.19823265849127</v>
+        <v>12.19823362589739</v>
       </c>
       <c r="D390" t="n">
-        <v>12.02508544921875</v>
+        <v>12.02508640289307</v>
       </c>
       <c r="E390" t="n">
-        <v>12.09434433292776</v>
+        <v>12.0943452920948</v>
       </c>
       <c r="F390" t="n">
         <v>4555500</v>
@@ -8252,16 +8252,16 @@
         <v>45216</v>
       </c>
       <c r="B392" t="n">
-        <v>11.95582675933838</v>
+        <v>11.9558277130127</v>
       </c>
       <c r="C392" t="n">
-        <v>12.10300127038276</v>
+        <v>12.10300223579667</v>
       </c>
       <c r="D392" t="n">
-        <v>11.88656704887551</v>
+        <v>11.88656799702522</v>
       </c>
       <c r="E392" t="n">
-        <v>11.97314106773082</v>
+        <v>11.97314202278624</v>
       </c>
       <c r="F392" t="n">
         <v>5165000</v>
@@ -8272,16 +8272,16 @@
         <v>45217</v>
       </c>
       <c r="B393" t="n">
-        <v>11.66147613525391</v>
+        <v>11.66147518157959</v>
       </c>
       <c r="C393" t="n">
-        <v>11.95582680984828</v>
+        <v>11.955825832102</v>
       </c>
       <c r="D393" t="n">
-        <v>11.66147613525391</v>
+        <v>11.66147518157959</v>
       </c>
       <c r="E393" t="n">
-        <v>11.95582680984828</v>
+        <v>11.955825832102</v>
       </c>
       <c r="F393" t="n">
         <v>13737300</v>
@@ -8292,16 +8292,16 @@
         <v>45218</v>
       </c>
       <c r="B394" t="n">
-        <v>11.67013263702393</v>
+        <v>11.67013359069824</v>
       </c>
       <c r="C394" t="n">
-        <v>11.75670665446719</v>
+        <v>11.75670761521626</v>
       </c>
       <c r="D394" t="n">
-        <v>11.62684645393332</v>
+        <v>11.62684740407032</v>
       </c>
       <c r="E394" t="n">
-        <v>11.66147589578441</v>
+        <v>11.66147684875131</v>
       </c>
       <c r="F394" t="n">
         <v>3066300</v>
@@ -8312,16 +8312,16 @@
         <v>45219</v>
       </c>
       <c r="B395" t="n">
-        <v>11.76536560058594</v>
+        <v>11.7653636932373</v>
       </c>
       <c r="C395" t="n">
-        <v>11.91254095211416</v>
+        <v>11.91253902090612</v>
       </c>
       <c r="D395" t="n">
-        <v>11.67013400510819</v>
+        <v>11.67013211319808</v>
       </c>
       <c r="E395" t="n">
-        <v>11.67013400510819</v>
+        <v>11.67013211319808</v>
       </c>
       <c r="F395" t="n">
         <v>6261200</v>
@@ -8332,16 +8332,16 @@
         <v>45222</v>
       </c>
       <c r="B396" t="n">
-        <v>11.72207736968994</v>
+        <v>11.72207832336426</v>
       </c>
       <c r="C396" t="n">
-        <v>11.90388214825212</v>
+        <v>11.90388311671755</v>
       </c>
       <c r="D396" t="n">
-        <v>11.72207736968994</v>
+        <v>11.72207832336426</v>
       </c>
       <c r="E396" t="n">
-        <v>11.77402194597815</v>
+        <v>11.77402290387853</v>
       </c>
       <c r="F396" t="n">
         <v>3068100</v>
@@ -8392,16 +8392,16 @@
         <v>45225</v>
       </c>
       <c r="B399" t="n">
-        <v>11.67879104614258</v>
+        <v>11.67879009246826</v>
       </c>
       <c r="C399" t="n">
-        <v>11.73073562548086</v>
+        <v>11.73073466756482</v>
       </c>
       <c r="D399" t="n">
-        <v>11.54893083624348</v>
+        <v>11.54892989317337</v>
       </c>
       <c r="E399" t="n">
-        <v>11.54893083624348</v>
+        <v>11.54892989317337</v>
       </c>
       <c r="F399" t="n">
         <v>2627000</v>
@@ -8432,16 +8432,16 @@
         <v>45229</v>
       </c>
       <c r="B401" t="n">
-        <v>11.49698543548584</v>
+        <v>11.49698638916016</v>
       </c>
       <c r="C401" t="n">
-        <v>11.64416076985956</v>
+        <v>11.64416173574207</v>
       </c>
       <c r="D401" t="n">
-        <v>11.47101356048784</v>
+        <v>11.47101451200779</v>
       </c>
       <c r="E401" t="n">
-        <v>11.57490188611087</v>
+        <v>11.57490284624835</v>
       </c>
       <c r="F401" t="n">
         <v>4549600</v>
@@ -8452,16 +8452,16 @@
         <v>45230</v>
       </c>
       <c r="B402" t="n">
-        <v>11.61818885803223</v>
+        <v>11.61818981170654</v>
       </c>
       <c r="C402" t="n">
-        <v>11.6614758666457</v>
+        <v>11.66147682387321</v>
       </c>
       <c r="D402" t="n">
-        <v>11.52295809958741</v>
+        <v>11.52295904544475</v>
       </c>
       <c r="E402" t="n">
-        <v>11.52295809958741</v>
+        <v>11.52295904544475</v>
       </c>
       <c r="F402" t="n">
         <v>3290000</v>
@@ -8472,16 +8472,16 @@
         <v>45231</v>
       </c>
       <c r="B403" t="n">
-        <v>11.66147613525391</v>
+        <v>11.66147518157959</v>
       </c>
       <c r="C403" t="n">
-        <v>11.74804932884394</v>
+        <v>11.74804836808967</v>
       </c>
       <c r="D403" t="n">
-        <v>11.28055144143846</v>
+        <v>11.28055051891613</v>
       </c>
       <c r="E403" t="n">
-        <v>11.55758780756725</v>
+        <v>11.55758686238891</v>
       </c>
       <c r="F403" t="n">
         <v>7182500</v>
@@ -8512,16 +8512,16 @@
         <v>45236</v>
       </c>
       <c r="B405" t="n">
-        <v>12.02508544921875</v>
+        <v>12.02508640289307</v>
       </c>
       <c r="C405" t="n">
-        <v>12.077029199185</v>
+        <v>12.07703015697882</v>
       </c>
       <c r="D405" t="n">
-        <v>11.8173079724607</v>
+        <v>11.81730890965679</v>
       </c>
       <c r="E405" t="n">
-        <v>11.94716899863836</v>
+        <v>11.94716994613335</v>
       </c>
       <c r="F405" t="n">
         <v>2982900</v>
@@ -8552,16 +8552,16 @@
         <v>45238</v>
       </c>
       <c r="B407" t="n">
-        <v>11.817307472229</v>
+        <v>11.81730842590332</v>
       </c>
       <c r="C407" t="n">
-        <v>11.96448280028841</v>
+        <v>11.96448376583999</v>
       </c>
       <c r="D407" t="n">
-        <v>11.73073428407293</v>
+        <v>11.73073523076066</v>
       </c>
       <c r="E407" t="n">
-        <v>11.93851092640469</v>
+        <v>11.9385118898603</v>
       </c>
       <c r="F407" t="n">
         <v>5488500</v>
@@ -8632,16 +8632,16 @@
         <v>45244</v>
       </c>
       <c r="B411" t="n">
-        <v>12.18957614898682</v>
+        <v>12.1895751953125</v>
       </c>
       <c r="C411" t="n">
-        <v>12.25017747108122</v>
+        <v>12.25017651266564</v>
       </c>
       <c r="D411" t="n">
-        <v>11.86059601001661</v>
+        <v>11.86059508208067</v>
       </c>
       <c r="E411" t="n">
-        <v>11.86059601001661</v>
+        <v>11.86059508208067</v>
       </c>
       <c r="F411" t="n">
         <v>3963500</v>
@@ -8652,16 +8652,16 @@
         <v>45246</v>
       </c>
       <c r="B412" t="n">
-        <v>12.49258422851562</v>
+        <v>12.49258327484131</v>
       </c>
       <c r="C412" t="n">
-        <v>12.49258422851562</v>
+        <v>12.49258327484131</v>
       </c>
       <c r="D412" t="n">
-        <v>12.12897464999031</v>
+        <v>12.12897372407367</v>
       </c>
       <c r="E412" t="n">
-        <v>12.12897464999031</v>
+        <v>12.12897372407367</v>
       </c>
       <c r="F412" t="n">
         <v>6741500</v>
@@ -8672,16 +8672,16 @@
         <v>45247</v>
       </c>
       <c r="B413" t="n">
-        <v>12.25017738342285</v>
+        <v>12.25017642974854</v>
       </c>
       <c r="C413" t="n">
-        <v>12.48392675376763</v>
+        <v>12.48392578189597</v>
       </c>
       <c r="D413" t="n">
-        <v>12.14628904959109</v>
+        <v>12.14628810400446</v>
       </c>
       <c r="E413" t="n">
-        <v>12.48392675376763</v>
+        <v>12.48392578189597</v>
       </c>
       <c r="F413" t="n">
         <v>3124800</v>
@@ -8692,16 +8692,16 @@
         <v>45250</v>
       </c>
       <c r="B414" t="n">
-        <v>12.0856876373291</v>
+        <v>12.08568668365479</v>
       </c>
       <c r="C414" t="n">
-        <v>12.23286298222856</v>
+        <v>12.23286201694073</v>
       </c>
       <c r="D414" t="n">
-        <v>11.99045687177166</v>
+        <v>11.99045592561195</v>
       </c>
       <c r="E414" t="n">
-        <v>12.20689110537309</v>
+        <v>12.20689014213468</v>
       </c>
       <c r="F414" t="n">
         <v>3248400</v>
@@ -8732,16 +8732,16 @@
         <v>45252</v>
       </c>
       <c r="B416" t="n">
-        <v>12.46661186218262</v>
+        <v>12.4666109085083</v>
       </c>
       <c r="C416" t="n">
-        <v>12.94276735410323</v>
+        <v>12.94276636400384</v>
       </c>
       <c r="D416" t="n">
-        <v>12.44063998462508</v>
+        <v>12.44063903293757</v>
       </c>
       <c r="E416" t="n">
-        <v>12.81290714068447</v>
+        <v>12.81290616051917</v>
       </c>
       <c r="F416" t="n">
         <v>20875500</v>
@@ -8752,16 +8752,16 @@
         <v>45253</v>
       </c>
       <c r="B417" t="n">
-        <v>12.561842918396</v>
+        <v>12.56184196472168</v>
       </c>
       <c r="C417" t="n">
-        <v>12.76961958122722</v>
+        <v>12.76961861177884</v>
       </c>
       <c r="D417" t="n">
-        <v>12.46661132870839</v>
+        <v>12.46661038226389</v>
       </c>
       <c r="E417" t="n">
-        <v>12.76961958122722</v>
+        <v>12.76961861177884</v>
       </c>
       <c r="F417" t="n">
         <v>9122900</v>
@@ -8832,16 +8832,16 @@
         <v>45259</v>
       </c>
       <c r="B421" t="n">
-        <v>12.561842918396</v>
+        <v>12.56184196472168</v>
       </c>
       <c r="C421" t="n">
-        <v>12.75230444650908</v>
+        <v>12.75230347837524</v>
       </c>
       <c r="D421" t="n">
-        <v>12.561842918396</v>
+        <v>12.56184196472168</v>
       </c>
       <c r="E421" t="n">
-        <v>12.72633257006295</v>
+        <v>12.72633160390085</v>
       </c>
       <c r="F421" t="n">
         <v>5869600</v>
@@ -8852,16 +8852,16 @@
         <v>45260</v>
       </c>
       <c r="B422" t="n">
-        <v>12.71767425537109</v>
+        <v>12.71767520904541</v>
       </c>
       <c r="C422" t="n">
-        <v>12.71767425537109</v>
+        <v>12.71767520904541</v>
       </c>
       <c r="D422" t="n">
-        <v>12.58781405514036</v>
+        <v>12.58781499907671</v>
       </c>
       <c r="E422" t="n">
-        <v>12.63110106376094</v>
+        <v>12.6311020109433</v>
       </c>
       <c r="F422" t="n">
         <v>4162000</v>
@@ -8892,16 +8892,16 @@
         <v>45264</v>
       </c>
       <c r="B424" t="n">
-        <v>12.89947986602783</v>
+        <v>12.89947891235352</v>
       </c>
       <c r="C424" t="n">
-        <v>12.98605388887275</v>
+        <v>12.98605292879791</v>
       </c>
       <c r="D424" t="n">
-        <v>12.86485042201608</v>
+        <v>12.86484947090196</v>
       </c>
       <c r="E424" t="n">
-        <v>12.94276687745029</v>
+        <v>12.94276592057571</v>
       </c>
       <c r="F424" t="n">
         <v>7048400</v>
@@ -8932,16 +8932,16 @@
         <v>45266</v>
       </c>
       <c r="B426" t="n">
-        <v>13.07262706756592</v>
+        <v>13.07262802124023</v>
       </c>
       <c r="C426" t="n">
-        <v>13.2717461513678</v>
+        <v>13.27174711956826</v>
       </c>
       <c r="D426" t="n">
-        <v>13.04665436701096</v>
+        <v>13.04665531879052</v>
       </c>
       <c r="E426" t="n">
-        <v>13.21114483466828</v>
+        <v>13.21114579844774</v>
       </c>
       <c r="F426" t="n">
         <v>5861300</v>
@@ -8972,16 +8972,16 @@
         <v>45268</v>
       </c>
       <c r="B428" t="n">
-        <v>12.92545127868652</v>
+        <v>12.92545223236084</v>
       </c>
       <c r="C428" t="n">
-        <v>13.15919979603697</v>
+        <v>13.15920076695787</v>
       </c>
       <c r="D428" t="n">
-        <v>12.86484913848894</v>
+        <v>12.86485008769187</v>
       </c>
       <c r="E428" t="n">
-        <v>13.15919979603697</v>
+        <v>13.15920076695787</v>
       </c>
       <c r="F428" t="n">
         <v>10990100</v>
@@ -9052,16 +9052,16 @@
         <v>45274</v>
       </c>
       <c r="B432" t="n">
-        <v>12.94470024108887</v>
+        <v>12.94470119476318</v>
       </c>
       <c r="C432" t="n">
-        <v>12.98319745470858</v>
+        <v>12.9831984112191</v>
       </c>
       <c r="D432" t="n">
-        <v>12.71371695937057</v>
+        <v>12.71371789602766</v>
       </c>
       <c r="E432" t="n">
-        <v>12.71371695937057</v>
+        <v>12.71371789602766</v>
       </c>
       <c r="F432" t="n">
         <v>5480800</v>
@@ -9092,16 +9092,16 @@
         <v>45278</v>
       </c>
       <c r="B434" t="n">
-        <v>12.84845733642578</v>
+        <v>12.8484582901001</v>
       </c>
       <c r="C434" t="n">
-        <v>13.0890651448394</v>
+        <v>13.08906611637279</v>
       </c>
       <c r="D434" t="n">
-        <v>12.84845733642578</v>
+        <v>12.8484582901001</v>
       </c>
       <c r="E434" t="n">
-        <v>12.983197121716</v>
+        <v>12.98319808539135</v>
       </c>
       <c r="F434" t="n">
         <v>3314300</v>
@@ -9112,16 +9112,16 @@
         <v>45279</v>
       </c>
       <c r="B435" t="n">
-        <v>12.86770629882812</v>
+        <v>12.86770534515381</v>
       </c>
       <c r="C435" t="n">
-        <v>12.94470072896945</v>
+        <v>12.94469976958878</v>
       </c>
       <c r="D435" t="n">
-        <v>12.7907118686868</v>
+        <v>12.79071092071883</v>
       </c>
       <c r="E435" t="n">
-        <v>12.87733083205729</v>
+        <v>12.87732987766966</v>
       </c>
       <c r="F435" t="n">
         <v>4780200</v>
@@ -9232,16 +9232,16 @@
         <v>45288</v>
       </c>
       <c r="B441" t="n">
-        <v>12.80996036529541</v>
+        <v>12.80996131896973</v>
       </c>
       <c r="C441" t="n">
-        <v>12.88695479201164</v>
+        <v>12.88695575141803</v>
       </c>
       <c r="D441" t="n">
-        <v>12.76183861913627</v>
+        <v>12.76183956922803</v>
       </c>
       <c r="E441" t="n">
-        <v>12.88695479201164</v>
+        <v>12.88695575141803</v>
       </c>
       <c r="F441" t="n">
         <v>3487000</v>
@@ -9332,16 +9332,16 @@
         <v>45299</v>
       </c>
       <c r="B446" t="n">
-        <v>13.01207065582275</v>
+        <v>13.01207160949707</v>
       </c>
       <c r="C446" t="n">
-        <v>13.09868869543668</v>
+        <v>13.09868965545936</v>
       </c>
       <c r="D446" t="n">
-        <v>12.88695448591916</v>
+        <v>12.88695543042352</v>
       </c>
       <c r="E446" t="n">
-        <v>12.95432437823419</v>
+        <v>12.9543253276762</v>
       </c>
       <c r="F446" t="n">
         <v>3738800</v>
@@ -9392,16 +9392,16 @@
         <v>45302</v>
       </c>
       <c r="B449" t="n">
-        <v>12.84845733642578</v>
+        <v>12.8484582901001</v>
       </c>
       <c r="C449" t="n">
-        <v>12.94469990908366</v>
+        <v>12.94470086990156</v>
       </c>
       <c r="D449" t="n">
-        <v>12.74258931330238</v>
+        <v>12.74259025911866</v>
       </c>
       <c r="E449" t="n">
-        <v>12.94469990908366</v>
+        <v>12.94470086990156</v>
       </c>
       <c r="F449" t="n">
         <v>4814200</v>
@@ -9412,16 +9412,16 @@
         <v>45303</v>
       </c>
       <c r="B450" t="n">
-        <v>12.77146434783936</v>
+        <v>12.77146339416504</v>
       </c>
       <c r="C450" t="n">
-        <v>12.88695599872818</v>
+        <v>12.88695503642984</v>
       </c>
       <c r="D450" t="n">
-        <v>12.74259074673261</v>
+        <v>12.74258979521435</v>
       </c>
       <c r="E450" t="n">
-        <v>12.84845878176524</v>
+        <v>12.84845782234157</v>
       </c>
       <c r="F450" t="n">
         <v>4041800</v>
@@ -9432,16 +9432,16 @@
         <v>45306</v>
       </c>
       <c r="B451" t="n">
-        <v>12.80996036529541</v>
+        <v>12.80996131896973</v>
       </c>
       <c r="C451" t="n">
-        <v>12.84845757865353</v>
+        <v>12.84845853519388</v>
       </c>
       <c r="D451" t="n">
-        <v>12.74258955353423</v>
+        <v>12.74259050219293</v>
       </c>
       <c r="E451" t="n">
-        <v>12.77146315193729</v>
+        <v>12.77146410274557</v>
       </c>
       <c r="F451" t="n">
         <v>1955800</v>
@@ -9492,16 +9492,16 @@
         <v>45309</v>
       </c>
       <c r="B454" t="n">
-        <v>12.55972766876221</v>
+        <v>12.55972862243652</v>
       </c>
       <c r="C454" t="n">
-        <v>12.77146279524125</v>
+        <v>12.77146376499286</v>
       </c>
       <c r="D454" t="n">
-        <v>12.51160592394707</v>
+        <v>12.51160687396745</v>
       </c>
       <c r="E454" t="n">
-        <v>12.76183826270904</v>
+        <v>12.76183923172984</v>
       </c>
       <c r="F454" t="n">
         <v>6534900</v>
@@ -9532,16 +9532,16 @@
         <v>45313</v>
       </c>
       <c r="B456" t="n">
-        <v>12.61747360229492</v>
+        <v>12.61747455596924</v>
       </c>
       <c r="C456" t="n">
-        <v>12.65597081632927</v>
+        <v>12.65597177291335</v>
       </c>
       <c r="D456" t="n">
-        <v>12.56935277313647</v>
+        <v>12.56935372317364</v>
       </c>
       <c r="E456" t="n">
-        <v>12.60784998717082</v>
+        <v>12.60785094011775</v>
       </c>
       <c r="F456" t="n">
         <v>4490300</v>
@@ -9572,16 +9572,16 @@
         <v>45315</v>
       </c>
       <c r="B458" t="n">
-        <v>12.79071235656738</v>
+        <v>12.79071140289307</v>
       </c>
       <c r="C458" t="n">
-        <v>12.82920957310646</v>
+        <v>12.82920861656179</v>
       </c>
       <c r="D458" t="n">
-        <v>12.64634802400737</v>
+        <v>12.64634708109684</v>
       </c>
       <c r="E458" t="n">
-        <v>12.6559716397576</v>
+        <v>12.65597069612954</v>
       </c>
       <c r="F458" t="n">
         <v>3333600</v>
@@ -9652,16 +9652,16 @@
         <v>45321</v>
       </c>
       <c r="B462" t="n">
-        <v>12.51160717010498</v>
+        <v>12.51160621643066</v>
       </c>
       <c r="C462" t="n">
-        <v>12.63672335194755</v>
+        <v>12.63672238873649</v>
       </c>
       <c r="D462" t="n">
-        <v>12.51160717010498</v>
+        <v>12.51160621643066</v>
       </c>
       <c r="E462" t="n">
-        <v>12.58860160233948</v>
+        <v>12.58860064279641</v>
       </c>
       <c r="F462" t="n">
         <v>3463200</v>
@@ -9672,16 +9672,16 @@
         <v>45322</v>
       </c>
       <c r="B463" t="n">
-        <v>12.68484401702881</v>
+        <v>12.68484497070312</v>
       </c>
       <c r="C463" t="n">
-        <v>12.79071112283833</v>
+        <v>12.79071208447197</v>
       </c>
       <c r="D463" t="n">
-        <v>12.53085516572552</v>
+        <v>12.53085610782262</v>
       </c>
       <c r="E463" t="n">
-        <v>12.57897599337333</v>
+        <v>12.57897693908826</v>
       </c>
       <c r="F463" t="n">
         <v>3755000</v>
@@ -9812,16 +9812,16 @@
         <v>45331</v>
       </c>
       <c r="B470" t="n">
-        <v>12.48273468017578</v>
+        <v>12.48273372650146</v>
       </c>
       <c r="C470" t="n">
-        <v>12.62709901338253</v>
+        <v>12.62709804867886</v>
       </c>
       <c r="D470" t="n">
-        <v>12.36724303004117</v>
+        <v>12.36724208519036</v>
       </c>
       <c r="E470" t="n">
-        <v>12.36724303004117</v>
+        <v>12.36724208519036</v>
       </c>
       <c r="F470" t="n">
         <v>4943200</v>
@@ -9852,16 +9852,16 @@
         <v>45337</v>
       </c>
       <c r="B472" t="n">
-        <v>12.50198268890381</v>
+        <v>12.50198173522949</v>
       </c>
       <c r="C472" t="n">
-        <v>12.58860165499141</v>
+        <v>12.58860069470964</v>
       </c>
       <c r="D472" t="n">
-        <v>12.4153637228162</v>
+        <v>12.41536277574934</v>
       </c>
       <c r="E472" t="n">
-        <v>12.46348547262554</v>
+        <v>12.46348452188787</v>
       </c>
       <c r="F472" t="n">
         <v>4740900</v>
@@ -9892,16 +9892,16 @@
         <v>45341</v>
       </c>
       <c r="B474" t="n">
-        <v>12.77146434783936</v>
+        <v>12.77146339416504</v>
       </c>
       <c r="C474" t="n">
-        <v>12.85808239762144</v>
+        <v>12.85808143747915</v>
       </c>
       <c r="D474" t="n">
-        <v>12.53085651235945</v>
+        <v>12.53085557665187</v>
       </c>
       <c r="E474" t="n">
-        <v>12.54048012821565</v>
+        <v>12.54047919178945</v>
       </c>
       <c r="F474" t="n">
         <v>4786000</v>
@@ -9972,16 +9972,16 @@
         <v>45345</v>
       </c>
       <c r="B478" t="n">
-        <v>12.41536331176758</v>
+        <v>12.41536235809326</v>
       </c>
       <c r="C478" t="n">
-        <v>12.55010402320352</v>
+        <v>12.55010305917923</v>
       </c>
       <c r="D478" t="n">
-        <v>12.41536331176758</v>
+        <v>12.41536235809326</v>
       </c>
       <c r="E478" t="n">
-        <v>12.52123134141225</v>
+        <v>12.52123037960578</v>
       </c>
       <c r="F478" t="n">
         <v>4574300</v>
@@ -9992,16 +9992,16 @@
         <v>45348</v>
       </c>
       <c r="B479" t="n">
-        <v>12.35761737823486</v>
+        <v>12.35761833190918</v>
       </c>
       <c r="C479" t="n">
-        <v>12.48273355068785</v>
+        <v>12.48273451401776</v>
       </c>
       <c r="D479" t="n">
-        <v>12.3383683126978</v>
+        <v>12.33836926488661</v>
       </c>
       <c r="E479" t="n">
-        <v>12.45385995238227</v>
+        <v>12.45386091348391</v>
       </c>
       <c r="F479" t="n">
         <v>6964500</v>
@@ -21969,282 +21969,282 @@
     </row>
     <row r="1078">
       <c r="A1078" s="1" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B1078" t="n">
-        <v>11.21000003814697</v>
+        <v>11.3100004196167</v>
       </c>
       <c r="C1078" t="n">
-        <v>11.35999965667725</v>
+        <v>11.68000030517578</v>
       </c>
       <c r="D1078" t="n">
-        <v>11.19999980926514</v>
+        <v>11.3100004196167</v>
       </c>
       <c r="E1078" t="n">
-        <v>11.27999973297119</v>
+        <v>11.61999988555908</v>
       </c>
       <c r="F1078" t="n">
-        <v>2651800</v>
+        <v>1721500</v>
       </c>
     </row>
     <row r="1079">
       <c r="A1079" s="1" t="n">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="B1079" t="n">
-        <v>11.55000019073486</v>
+        <v>11.21000003814697</v>
       </c>
       <c r="C1079" t="n">
-        <v>11.64000034332275</v>
+        <v>11.35999965667725</v>
       </c>
       <c r="D1079" t="n">
-        <v>11.1899995803833</v>
+        <v>11.19999980926514</v>
       </c>
       <c r="E1079" t="n">
-        <v>11.26000022888184</v>
+        <v>11.27999973297119</v>
       </c>
       <c r="F1079" t="n">
-        <v>2065500</v>
+        <v>2651800</v>
       </c>
     </row>
     <row r="1080">
       <c r="A1080" s="1" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="B1080" t="n">
-        <v>11.39000034332275</v>
+        <v>11.55000019073486</v>
       </c>
       <c r="C1080" t="n">
-        <v>11.5</v>
+        <v>11.64000034332275</v>
       </c>
       <c r="D1080" t="n">
-        <v>11.30000019073486</v>
+        <v>11.1899995803833</v>
       </c>
       <c r="E1080" t="n">
-        <v>11.5</v>
+        <v>11.26000022888184</v>
       </c>
       <c r="F1080" t="n">
-        <v>1499900</v>
+        <v>2065500</v>
       </c>
     </row>
     <row r="1081">
       <c r="A1081" s="1" t="n">
-        <v>46227</v>
+        <v>46226</v>
       </c>
       <c r="B1081" t="n">
-        <v>11.1899995803833</v>
+        <v>11.39000034332275</v>
       </c>
       <c r="C1081" t="n">
-        <v>11.38000011444092</v>
+        <v>11.5</v>
       </c>
       <c r="D1081" t="n">
-        <v>11.18000030517578</v>
+        <v>11.30000019073486</v>
       </c>
       <c r="E1081" t="n">
-        <v>11.34000015258789</v>
+        <v>11.5</v>
       </c>
       <c r="F1081" t="n">
-        <v>1240200</v>
+        <v>1499900</v>
       </c>
     </row>
     <row r="1082">
       <c r="A1082" s="1" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B1082" t="n">
-        <v>11.31999969482422</v>
+        <v>11.1899995803833</v>
       </c>
       <c r="C1082" t="n">
-        <v>11.36999988555908</v>
+        <v>11.38000011444092</v>
       </c>
       <c r="D1082" t="n">
-        <v>11.15999984741211</v>
+        <v>11.18000030517578</v>
       </c>
       <c r="E1082" t="n">
-        <v>11.25</v>
+        <v>11.34000015258789</v>
       </c>
       <c r="F1082" t="n">
-        <v>1323600</v>
+        <v>1240200</v>
       </c>
     </row>
     <row r="1083">
       <c r="A1083" s="1" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="B1083" t="n">
-        <v>11.44999980926514</v>
+        <v>11.31999969482422</v>
       </c>
       <c r="C1083" t="n">
-        <v>11.72000026702881</v>
+        <v>11.36999988555908</v>
       </c>
       <c r="D1083" t="n">
-        <v>11.38000011444092</v>
+        <v>11.15999984741211</v>
       </c>
       <c r="E1083" t="n">
-        <v>11.52999973297119</v>
+        <v>11.25</v>
       </c>
       <c r="F1083" t="n">
-        <v>1564600</v>
+        <v>1323600</v>
       </c>
     </row>
     <row r="1084">
       <c r="A1084" s="1" t="n">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="B1084" t="n">
-        <v>11.10999965667725</v>
+        <v>11.44999980926514</v>
       </c>
       <c r="C1084" t="n">
-        <v>11.47000026702881</v>
+        <v>11.72000026702881</v>
       </c>
       <c r="D1084" t="n">
-        <v>11.07999992370605</v>
+        <v>11.38000011444092</v>
       </c>
       <c r="E1084" t="n">
-        <v>11.44999980926514</v>
+        <v>11.52999973297119</v>
       </c>
       <c r="F1084" t="n">
-        <v>2114700</v>
+        <v>1564600</v>
       </c>
     </row>
     <row r="1085">
       <c r="A1085" s="1" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="B1085" t="n">
-        <v>11.19999980926514</v>
+        <v>11.10999965667725</v>
       </c>
       <c r="C1085" t="n">
-        <v>11.3100004196167</v>
+        <v>11.47000026702881</v>
       </c>
       <c r="D1085" t="n">
-        <v>11.09000015258789</v>
+        <v>11.07999992370605</v>
       </c>
       <c r="E1085" t="n">
-        <v>11.18000030517578</v>
+        <v>11.44999980926514</v>
       </c>
       <c r="F1085" t="n">
-        <v>2543000</v>
+        <v>2114700</v>
       </c>
     </row>
     <row r="1086">
       <c r="A1086" s="1" t="n">
-        <v>46237</v>
+        <v>46233</v>
       </c>
       <c r="B1086" t="n">
         <v>11.19999980926514</v>
       </c>
       <c r="C1086" t="n">
-        <v>11.21000003814697</v>
+        <v>11.3100004196167</v>
       </c>
       <c r="D1086" t="n">
-        <v>10.84000015258789</v>
+        <v>11.09000015258789</v>
       </c>
       <c r="E1086" t="n">
-        <v>11.03999996185303</v>
+        <v>11.18000030517578</v>
       </c>
       <c r="F1086" t="n">
-        <v>4621900</v>
+        <v>2543000</v>
       </c>
     </row>
     <row r="1087">
       <c r="A1087" s="1" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B1087" t="n">
-        <v>11.27999973297119</v>
+        <v>11.19999980926514</v>
       </c>
       <c r="C1087" t="n">
-        <v>11.56999969482422</v>
+        <v>11.21000003814697</v>
       </c>
       <c r="D1087" t="n">
-        <v>11.13000011444092</v>
+        <v>10.84000015258789</v>
       </c>
       <c r="E1087" t="n">
-        <v>11.32999992370605</v>
+        <v>11.03999996185303</v>
       </c>
       <c r="F1087" t="n">
-        <v>4289500</v>
+        <v>4621900</v>
       </c>
     </row>
     <row r="1088">
       <c r="A1088" s="1" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B1088" t="n">
-        <v>11.15999984741211</v>
+        <v>11.27999973297119</v>
       </c>
       <c r="C1088" t="n">
-        <v>11.55000019073486</v>
+        <v>11.56999969482422</v>
       </c>
       <c r="D1088" t="n">
-        <v>11.07999992370605</v>
+        <v>11.13000011444092</v>
       </c>
       <c r="E1088" t="n">
-        <v>11.31999969482422</v>
+        <v>11.32999992370605</v>
       </c>
       <c r="F1088" t="n">
-        <v>5192700</v>
+        <v>4289500</v>
       </c>
     </row>
     <row r="1089">
       <c r="A1089" s="1" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B1089" t="n">
-        <v>10.97999954223633</v>
+        <v>11.15999984741211</v>
       </c>
       <c r="C1089" t="n">
-        <v>11.14000034332275</v>
+        <v>11.55000019073486</v>
       </c>
       <c r="D1089" t="n">
-        <v>10.61999988555908</v>
+        <v>11.07999992370605</v>
       </c>
       <c r="E1089" t="n">
-        <v>11.14000034332275</v>
+        <v>11.31999969482422</v>
       </c>
       <c r="F1089" t="n">
-        <v>5195300</v>
+        <v>5192700</v>
       </c>
     </row>
     <row r="1090">
       <c r="A1090" s="1" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="B1090" t="n">
-        <v>10.8100004196167</v>
+        <v>10.97999954223633</v>
       </c>
       <c r="C1090" t="n">
-        <v>10.97999954223633</v>
+        <v>11.14000034332275</v>
       </c>
       <c r="D1090" t="n">
-        <v>10.55000019073486</v>
+        <v>10.61999988555908</v>
       </c>
       <c r="E1090" t="n">
-        <v>10.97999954223633</v>
+        <v>11.14000034332275</v>
       </c>
       <c r="F1090" t="n">
-        <v>4285100</v>
+        <v>5195300</v>
       </c>
     </row>
     <row r="1091">
       <c r="A1091" s="1" t="n">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="B1091" t="n">
-        <v>10.69999980926514</v>
+        <v>10.8100004196167</v>
       </c>
       <c r="C1091" t="n">
-        <v>10.82999992370605</v>
+        <v>10.97999954223633</v>
       </c>
       <c r="D1091" t="n">
-        <v>10.5600004196167</v>
+        <v>10.55000019073486</v>
       </c>
       <c r="E1091" t="n">
-        <v>10.80000019073486</v>
+        <v>10.97999954223633</v>
       </c>
       <c r="F1091" t="n">
-        <v>3624700</v>
+        <v>4285100</v>
       </c>
     </row>
     <row r="1092">
@@ -22312,19 +22312,39 @@
         <v>46248</v>
       </c>
       <c r="B1095" t="n">
-        <v>10.05</v>
+        <v>10.05000019073486</v>
       </c>
       <c r="C1095" t="n">
-        <v>10.26</v>
+        <v>10.26000022888184</v>
       </c>
       <c r="D1095" t="n">
-        <v>9.99</v>
+        <v>9.989999771118164</v>
       </c>
       <c r="E1095" t="n">
-        <v>10.26</v>
+        <v>10.26000022888184</v>
       </c>
       <c r="F1095" t="n">
         <v>3773500</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B1096" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="C1096" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D1096" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="E1096" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="F1096" t="n">
+        <v>3187700</v>
       </c>
     </row>
   </sheetData>

--- a/database/AURE3.xlsx
+++ b/database/AURE3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1096"/>
+  <dimension ref="A1:F1097"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44648</v>
       </c>
       <c r="B2" t="n">
-        <v>12.75723075866699</v>
+        <v>12.75723171234131</v>
       </c>
       <c r="C2" t="n">
-        <v>13.06838243889043</v>
+        <v>13.06838341582507</v>
       </c>
       <c r="D2" t="n">
-        <v>12.02602393921985</v>
+        <v>12.02602483823237</v>
       </c>
       <c r="E2" t="n">
-        <v>13.06838243889043</v>
+        <v>13.06838341582507</v>
       </c>
       <c r="F2" t="n">
         <v>5237900</v>
@@ -532,16 +532,16 @@
         <v>44652</v>
       </c>
       <c r="B6" t="n">
-        <v>12.51609039306641</v>
+        <v>12.51609134674072</v>
       </c>
       <c r="C6" t="n">
-        <v>12.95170281502629</v>
+        <v>12.95170380189247</v>
       </c>
       <c r="D6" t="n">
-        <v>12.31384139766291</v>
+        <v>12.31384233592669</v>
       </c>
       <c r="E6" t="n">
-        <v>12.43830208965145</v>
+        <v>12.43830303739862</v>
       </c>
       <c r="F6" t="n">
         <v>4252000</v>
@@ -592,16 +592,16 @@
         <v>44657</v>
       </c>
       <c r="B9" t="n">
-        <v>12.43052387237549</v>
+        <v>12.43052291870117</v>
       </c>
       <c r="C9" t="n">
-        <v>12.44608183074918</v>
+        <v>12.44608087588125</v>
       </c>
       <c r="D9" t="n">
-        <v>12.01824761944832</v>
+        <v>12.01824669740399</v>
       </c>
       <c r="E9" t="n">
-        <v>12.06492075272512</v>
+        <v>12.06491982710001</v>
       </c>
       <c r="F9" t="n">
         <v>2914800</v>
@@ -612,16 +612,16 @@
         <v>44658</v>
       </c>
       <c r="B10" t="n">
-        <v>12.44608211517334</v>
+        <v>12.44608116149902</v>
       </c>
       <c r="C10" t="n">
-        <v>12.71834045818048</v>
+        <v>12.71833948364451</v>
       </c>
       <c r="D10" t="n">
-        <v>12.20493894778036</v>
+        <v>12.20493801258351</v>
       </c>
       <c r="E10" t="n">
-        <v>12.32162141271669</v>
+        <v>12.32162046857911</v>
       </c>
       <c r="F10" t="n">
         <v>3223900</v>
@@ -632,16 +632,16 @@
         <v>44659</v>
       </c>
       <c r="B11" t="n">
-        <v>12.60943508148193</v>
+        <v>12.60943603515625</v>
       </c>
       <c r="C11" t="n">
-        <v>12.75723270856147</v>
+        <v>12.75723367341398</v>
       </c>
       <c r="D11" t="n">
-        <v>12.33717750513392</v>
+        <v>12.3371784382169</v>
       </c>
       <c r="E11" t="n">
-        <v>12.33717750513392</v>
+        <v>12.3371784382169</v>
       </c>
       <c r="F11" t="n">
         <v>2049800</v>
@@ -652,16 +652,16 @@
         <v>44662</v>
       </c>
       <c r="B12" t="n">
-        <v>12.37607097625732</v>
+        <v>12.37607192993164</v>
       </c>
       <c r="C12" t="n">
-        <v>12.89725064802586</v>
+        <v>12.8972516418612</v>
       </c>
       <c r="D12" t="n">
-        <v>12.37607097625732</v>
+        <v>12.37607192993164</v>
       </c>
       <c r="E12" t="n">
-        <v>12.59387791557601</v>
+        <v>12.59387888603408</v>
       </c>
       <c r="F12" t="n">
         <v>2119500</v>
@@ -672,16 +672,16 @@
         <v>44663</v>
       </c>
       <c r="B13" t="n">
-        <v>12.24383163452148</v>
+        <v>12.2438325881958</v>
       </c>
       <c r="C13" t="n">
-        <v>12.64055063241211</v>
+        <v>12.64055161698694</v>
       </c>
       <c r="D13" t="n">
-        <v>12.21271646263855</v>
+        <v>12.2127174138893</v>
       </c>
       <c r="E13" t="n">
-        <v>12.4849740311532</v>
+        <v>12.48497500361014</v>
       </c>
       <c r="F13" t="n">
         <v>2267700</v>
@@ -712,16 +712,16 @@
         <v>44665</v>
       </c>
       <c r="B15" t="n">
-        <v>12.11159133911133</v>
+        <v>12.11159229278564</v>
       </c>
       <c r="C15" t="n">
-        <v>12.36829167926575</v>
+        <v>12.36829265315281</v>
       </c>
       <c r="D15" t="n">
-        <v>12.0493609985796</v>
+        <v>12.04936194735386</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08047616884546</v>
+        <v>12.08047712006975</v>
       </c>
       <c r="F15" t="n">
         <v>2077400</v>
@@ -792,16 +792,16 @@
         <v>44673</v>
       </c>
       <c r="B19" t="n">
-        <v>12.22049617767334</v>
+        <v>12.22049713134766</v>
       </c>
       <c r="C19" t="n">
-        <v>12.33717789380641</v>
+        <v>12.33717885658645</v>
       </c>
       <c r="D19" t="n">
-        <v>11.80044096101231</v>
+        <v>11.80044188190597</v>
       </c>
       <c r="E19" t="n">
-        <v>12.01824717732137</v>
+        <v>12.01824811521239</v>
       </c>
       <c r="F19" t="n">
         <v>11382300</v>
@@ -892,16 +892,16 @@
         <v>44680</v>
       </c>
       <c r="B24" t="n">
-        <v>11.40372180938721</v>
+        <v>11.40372085571289</v>
       </c>
       <c r="C24" t="n">
-        <v>11.96379567250737</v>
+        <v>11.963794671995</v>
       </c>
       <c r="D24" t="n">
-        <v>11.40372180938721</v>
+        <v>11.40372085571289</v>
       </c>
       <c r="E24" t="n">
-        <v>11.96379567250737</v>
+        <v>11.963794671995</v>
       </c>
       <c r="F24" t="n">
         <v>10427400</v>
@@ -912,16 +912,16 @@
         <v>44683</v>
       </c>
       <c r="B25" t="n">
-        <v>11.1703577041626</v>
+        <v>11.17035675048828</v>
       </c>
       <c r="C25" t="n">
-        <v>11.47373120303561</v>
+        <v>11.47373022346064</v>
       </c>
       <c r="D25" t="n">
-        <v>10.96033046789994</v>
+        <v>10.96032953215679</v>
       </c>
       <c r="E25" t="n">
-        <v>11.42705807173043</v>
+        <v>11.4270570961402</v>
       </c>
       <c r="F25" t="n">
         <v>2883200</v>
@@ -972,16 +972,16 @@
         <v>44686</v>
       </c>
       <c r="B28" t="n">
-        <v>11.28714656829834</v>
+        <v>11.28714752197266</v>
       </c>
       <c r="C28" t="n">
-        <v>11.62395965090248</v>
+        <v>11.62396063303483</v>
       </c>
       <c r="D28" t="n">
-        <v>11.14615490637113</v>
+        <v>11.14615584813277</v>
       </c>
       <c r="E28" t="n">
-        <v>11.61612661479554</v>
+        <v>11.61612759626606</v>
       </c>
       <c r="F28" t="n">
         <v>3065700</v>
@@ -1132,16 +1132,16 @@
         <v>44698</v>
       </c>
       <c r="B36" t="n">
-        <v>11.56129741668701</v>
+        <v>11.56129837036133</v>
       </c>
       <c r="C36" t="n">
-        <v>11.74928581037311</v>
+        <v>11.74928677955431</v>
       </c>
       <c r="D36" t="n">
-        <v>11.35764295002734</v>
+        <v>11.3576438869025</v>
       </c>
       <c r="E36" t="n">
-        <v>11.35764295002734</v>
+        <v>11.3576438869025</v>
       </c>
       <c r="F36" t="n">
         <v>1389700</v>
@@ -1152,16 +1152,16 @@
         <v>44699</v>
       </c>
       <c r="B37" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C37" t="n">
-        <v>11.5926298208571</v>
+        <v>11.59262882548476</v>
       </c>
       <c r="D37" t="n">
-        <v>11.03649688106261</v>
+        <v>11.03649593344125</v>
       </c>
       <c r="E37" t="n">
-        <v>11.51430094319608</v>
+        <v>11.51429995454926</v>
       </c>
       <c r="F37" t="n">
         <v>1959900</v>
@@ -1192,16 +1192,16 @@
         <v>44701</v>
       </c>
       <c r="B39" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C39" t="n">
-        <v>11.34197786054158</v>
+        <v>11.34197688669085</v>
       </c>
       <c r="D39" t="n">
-        <v>10.86417379840811</v>
+        <v>10.86417286558284</v>
       </c>
       <c r="E39" t="n">
-        <v>11.34197786054158</v>
+        <v>11.34197688669085</v>
       </c>
       <c r="F39" t="n">
         <v>1777400</v>
@@ -1292,16 +1292,16 @@
         <v>44708</v>
       </c>
       <c r="B44" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C44" t="n">
-        <v>11.42030698171035</v>
+        <v>11.42030600182509</v>
       </c>
       <c r="D44" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="E44" t="n">
-        <v>11.26364997004757</v>
+        <v>11.26364900360379</v>
       </c>
       <c r="F44" t="n">
         <v>2224600</v>
@@ -1312,16 +1312,16 @@
         <v>44711</v>
       </c>
       <c r="B45" t="n">
-        <v>11.09915828704834</v>
+        <v>11.09915924072266</v>
       </c>
       <c r="C45" t="n">
-        <v>11.271481348008</v>
+        <v>11.27148231648886</v>
       </c>
       <c r="D45" t="n">
-        <v>11.0286624554285</v>
+        <v>11.0286634030456</v>
       </c>
       <c r="E45" t="n">
-        <v>11.15398804630846</v>
+        <v>11.15398900469392</v>
       </c>
       <c r="F45" t="n">
         <v>1940200</v>
@@ -1372,16 +1372,16 @@
         <v>44714</v>
       </c>
       <c r="B48" t="n">
-        <v>10.86417388916016</v>
+        <v>10.86417293548584</v>
       </c>
       <c r="C48" t="n">
-        <v>10.98949949686503</v>
+        <v>10.98949853218943</v>
       </c>
       <c r="D48" t="n">
-        <v>10.68401851483428</v>
+        <v>10.68401757697429</v>
       </c>
       <c r="E48" t="n">
-        <v>10.75451360891862</v>
+        <v>10.75451266487045</v>
       </c>
       <c r="F48" t="n">
         <v>3275400</v>
@@ -1472,16 +1472,16 @@
         <v>44721</v>
       </c>
       <c r="B53" t="n">
-        <v>11.03649616241455</v>
+        <v>11.03649711608887</v>
       </c>
       <c r="C53" t="n">
-        <v>11.09915896166322</v>
+        <v>11.09915992075229</v>
       </c>
       <c r="D53" t="n">
-        <v>10.86417309098097</v>
+        <v>10.86417402976468</v>
       </c>
       <c r="E53" t="n">
-        <v>11.06782756203888</v>
+        <v>11.06782851842058</v>
       </c>
       <c r="F53" t="n">
         <v>1365200</v>
@@ -1592,16 +1592,16 @@
         <v>44732</v>
       </c>
       <c r="B59" t="n">
-        <v>10.59785556793213</v>
+        <v>10.59785652160645</v>
       </c>
       <c r="C59" t="n">
-        <v>10.69968280103267</v>
+        <v>10.69968376387016</v>
       </c>
       <c r="D59" t="n">
-        <v>10.37070273932307</v>
+        <v>10.37070367255648</v>
       </c>
       <c r="E59" t="n">
-        <v>10.47252997242361</v>
+        <v>10.47253091482019</v>
       </c>
       <c r="F59" t="n">
         <v>1649800</v>
@@ -1612,16 +1612,16 @@
         <v>44733</v>
       </c>
       <c r="B60" t="n">
-        <v>10.63702011108398</v>
+        <v>10.6370210647583</v>
       </c>
       <c r="C60" t="n">
-        <v>10.7153489825704</v>
+        <v>10.71534994326738</v>
       </c>
       <c r="D60" t="n">
-        <v>10.51952755085384</v>
+        <v>10.51952849399422</v>
       </c>
       <c r="E60" t="n">
-        <v>10.69184987292479</v>
+        <v>10.69185083151493</v>
       </c>
       <c r="F60" t="n">
         <v>1455700</v>
@@ -1632,16 +1632,16 @@
         <v>44734</v>
       </c>
       <c r="B61" t="n">
-        <v>10.73884868621826</v>
+        <v>10.73884773254395</v>
       </c>
       <c r="C61" t="n">
-        <v>10.8328428955397</v>
+        <v>10.83284193351813</v>
       </c>
       <c r="D61" t="n">
-        <v>10.43336694567391</v>
+        <v>10.43336601912821</v>
       </c>
       <c r="E61" t="n">
-        <v>10.53519419252203</v>
+        <v>10.53519325693346</v>
       </c>
       <c r="F61" t="n">
         <v>1196200</v>
@@ -1652,16 +1652,16 @@
         <v>44735</v>
       </c>
       <c r="B62" t="n">
-        <v>10.63702011108398</v>
+        <v>10.6370210647583</v>
       </c>
       <c r="C62" t="n">
-        <v>10.89550434118989</v>
+        <v>10.89550531803891</v>
       </c>
       <c r="D62" t="n">
-        <v>10.55085895004851</v>
+        <v>10.55085989599795</v>
       </c>
       <c r="E62" t="n">
-        <v>10.8798390150923</v>
+        <v>10.87983999053682</v>
       </c>
       <c r="F62" t="n">
         <v>3444100</v>
@@ -1832,16 +1832,16 @@
         <v>44748</v>
       </c>
       <c r="B71" t="n">
-        <v>10.67618560791016</v>
+        <v>10.67618465423584</v>
       </c>
       <c r="C71" t="n">
-        <v>10.71535004754583</v>
+        <v>10.71534909037307</v>
       </c>
       <c r="D71" t="n">
-        <v>10.49602948438586</v>
+        <v>10.49602854680439</v>
       </c>
       <c r="E71" t="n">
-        <v>10.57435836365721</v>
+        <v>10.57435741907885</v>
       </c>
       <c r="F71" t="n">
         <v>1826800</v>
@@ -1852,16 +1852,16 @@
         <v>44749</v>
       </c>
       <c r="B72" t="n">
-        <v>11.04432964324951</v>
+        <v>11.0443286895752</v>
       </c>
       <c r="C72" t="n">
-        <v>11.16182220981619</v>
+        <v>11.16182124599643</v>
       </c>
       <c r="D72" t="n">
-        <v>10.62135535781014</v>
+        <v>10.62135444065952</v>
       </c>
       <c r="E72" t="n">
-        <v>10.7858453992032</v>
+        <v>10.78584446784892</v>
       </c>
       <c r="F72" t="n">
         <v>2931100</v>
@@ -1892,16 +1892,16 @@
         <v>44753</v>
       </c>
       <c r="B74" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C74" t="n">
-        <v>11.18532085221909</v>
+        <v>11.18531989181933</v>
       </c>
       <c r="D74" t="n">
-        <v>10.83284239674361</v>
+        <v>10.83284146660853</v>
       </c>
       <c r="E74" t="n">
-        <v>11.0599952455611</v>
+        <v>11.05999429592211</v>
       </c>
       <c r="F74" t="n">
         <v>1881000</v>
@@ -1912,16 +1912,16 @@
         <v>44754</v>
       </c>
       <c r="B75" t="n">
-        <v>11.14615535736084</v>
+        <v>11.14615631103516</v>
       </c>
       <c r="C75" t="n">
-        <v>11.22448422760069</v>
+        <v>11.22448518797689</v>
       </c>
       <c r="D75" t="n">
-        <v>10.99733140030449</v>
+        <v>10.99733234124531</v>
       </c>
       <c r="E75" t="n">
-        <v>11.10699166924038</v>
+        <v>11.10699261956382</v>
       </c>
       <c r="F75" t="n">
         <v>1673000</v>
@@ -2052,16 +2052,16 @@
         <v>44763</v>
       </c>
       <c r="B82" t="n">
-        <v>11.24798393249512</v>
+        <v>11.2479829788208</v>
       </c>
       <c r="C82" t="n">
-        <v>11.27931533493105</v>
+        <v>11.27931437860027</v>
       </c>
       <c r="D82" t="n">
-        <v>11.0599955178795</v>
+        <v>11.05999458014401</v>
       </c>
       <c r="E82" t="n">
-        <v>11.22448556741805</v>
+        <v>11.22448461573608</v>
       </c>
       <c r="F82" t="n">
         <v>1092700</v>
@@ -2072,16 +2072,16 @@
         <v>44764</v>
       </c>
       <c r="B83" t="n">
-        <v>11.36547565460205</v>
+        <v>11.36547660827637</v>
       </c>
       <c r="C83" t="n">
-        <v>11.37330869086009</v>
+        <v>11.37330964519167</v>
       </c>
       <c r="D83" t="n">
-        <v>11.13048979585711</v>
+        <v>11.13049072981382</v>
       </c>
       <c r="E83" t="n">
-        <v>11.27148146050397</v>
+        <v>11.27148240629125</v>
       </c>
       <c r="F83" t="n">
         <v>1975500</v>
@@ -2152,16 +2152,16 @@
         <v>44770</v>
       </c>
       <c r="B87" t="n">
-        <v>10.96599960327148</v>
+        <v>10.96600151062012</v>
       </c>
       <c r="C87" t="n">
-        <v>11.33414408482687</v>
+        <v>11.33414605620796</v>
       </c>
       <c r="D87" t="n">
-        <v>10.82500794076103</v>
+        <v>10.82500982358657</v>
       </c>
       <c r="E87" t="n">
-        <v>11.31064497640883</v>
+        <v>11.31064694370265</v>
       </c>
       <c r="F87" t="n">
         <v>2911900</v>
@@ -2172,16 +2172,16 @@
         <v>44771</v>
       </c>
       <c r="B88" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C88" t="n">
-        <v>11.33414581204571</v>
+        <v>11.33414483955325</v>
       </c>
       <c r="D88" t="n">
-        <v>10.51952860439969</v>
+        <v>10.51952770180302</v>
       </c>
       <c r="E88" t="n">
-        <v>10.96600127438851</v>
+        <v>10.96600033348359</v>
       </c>
       <c r="F88" t="n">
         <v>13059200</v>
@@ -2212,16 +2212,16 @@
         <v>44775</v>
       </c>
       <c r="B90" t="n">
-        <v>10.86417388916016</v>
+        <v>10.86417293548584</v>
       </c>
       <c r="C90" t="n">
-        <v>11.06782837518035</v>
+        <v>11.06782740362892</v>
       </c>
       <c r="D90" t="n">
-        <v>10.7231822069924</v>
+        <v>10.72318126569455</v>
       </c>
       <c r="E90" t="n">
-        <v>10.93466973024404</v>
+        <v>10.93466877038148</v>
       </c>
       <c r="F90" t="n">
         <v>2371400</v>
@@ -2272,16 +2272,16 @@
         <v>44778</v>
       </c>
       <c r="B93" t="n">
-        <v>10.96599960327148</v>
+        <v>10.96600151062012</v>
       </c>
       <c r="C93" t="n">
-        <v>11.16965406089782</v>
+        <v>11.16965600366867</v>
       </c>
       <c r="D93" t="n">
-        <v>10.93466820571354</v>
+        <v>10.93467010761261</v>
       </c>
       <c r="E93" t="n">
-        <v>11.16965406089782</v>
+        <v>11.16965600366867</v>
       </c>
       <c r="F93" t="n">
         <v>1948700</v>
@@ -2292,16 +2292,16 @@
         <v>44781</v>
       </c>
       <c r="B94" t="n">
-        <v>10.97383403778076</v>
+        <v>10.97383308410645</v>
       </c>
       <c r="C94" t="n">
-        <v>11.10699268111997</v>
+        <v>11.10699171587358</v>
       </c>
       <c r="D94" t="n">
-        <v>10.87200679599199</v>
+        <v>10.8720058511669</v>
       </c>
       <c r="E94" t="n">
-        <v>11.02866380374413</v>
+        <v>11.02866284530486</v>
       </c>
       <c r="F94" t="n">
         <v>2949000</v>
@@ -2352,16 +2352,16 @@
         <v>44784</v>
       </c>
       <c r="B97" t="n">
-        <v>10.89550495147705</v>
+        <v>10.89550590515137</v>
       </c>
       <c r="C97" t="n">
-        <v>11.10699246813669</v>
+        <v>11.10699344032233</v>
       </c>
       <c r="D97" t="n">
-        <v>10.83284214957779</v>
+        <v>10.83284309776729</v>
       </c>
       <c r="E97" t="n">
-        <v>11.05999499321249</v>
+        <v>11.05999596128448</v>
       </c>
       <c r="F97" t="n">
         <v>1665400</v>
@@ -2412,16 +2412,16 @@
         <v>44789</v>
       </c>
       <c r="B100" t="n">
-        <v>11.04432964324951</v>
+        <v>11.0443286895752</v>
       </c>
       <c r="C100" t="n">
-        <v>11.29498085032484</v>
+        <v>11.29497987500687</v>
       </c>
       <c r="D100" t="n">
-        <v>10.94250240362528</v>
+        <v>10.94250145874372</v>
       </c>
       <c r="E100" t="n">
-        <v>11.25581641246944</v>
+        <v>11.25581544053331</v>
       </c>
       <c r="F100" t="n">
         <v>1185300</v>
@@ -2472,16 +2472,16 @@
         <v>44792</v>
       </c>
       <c r="B103" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C103" t="n">
-        <v>11.16182272571687</v>
+        <v>11.16182176801008</v>
       </c>
       <c r="D103" t="n">
-        <v>10.98166734905456</v>
+        <v>10.98166640680546</v>
       </c>
       <c r="E103" t="n">
-        <v>11.16182272571687</v>
+        <v>11.16182176801008</v>
       </c>
       <c r="F103" t="n">
         <v>1667800</v>
@@ -2532,16 +2532,16 @@
         <v>44797</v>
       </c>
       <c r="B106" t="n">
-        <v>11.10699272155762</v>
+        <v>11.1069917678833</v>
       </c>
       <c r="C106" t="n">
-        <v>11.3968083737041</v>
+        <v>11.39680739514549</v>
       </c>
       <c r="D106" t="n">
-        <v>11.09915968439161</v>
+        <v>11.09915873138986</v>
       </c>
       <c r="E106" t="n">
-        <v>11.2244852910496</v>
+        <v>11.22448432728707</v>
       </c>
       <c r="F106" t="n">
         <v>2116800</v>
@@ -2552,16 +2552,16 @@
         <v>44798</v>
       </c>
       <c r="B107" t="n">
-        <v>11.04432964324951</v>
+        <v>11.0443286895752</v>
       </c>
       <c r="C107" t="n">
-        <v>11.22448501158502</v>
+        <v>11.22448404235435</v>
       </c>
       <c r="D107" t="n">
-        <v>10.95033469359675</v>
+        <v>10.95033374803886</v>
       </c>
       <c r="E107" t="n">
-        <v>11.20881968464257</v>
+        <v>11.2088187167646</v>
       </c>
       <c r="F107" t="n">
         <v>2435800</v>
@@ -2592,16 +2592,16 @@
         <v>44802</v>
       </c>
       <c r="B109" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C109" t="n">
-        <v>11.20882020271549</v>
+        <v>11.20881924097621</v>
       </c>
       <c r="D109" t="n">
-        <v>10.93466987205595</v>
+        <v>10.93466893383933</v>
       </c>
       <c r="E109" t="n">
-        <v>11.02083104172059</v>
+        <v>11.02083009611117</v>
       </c>
       <c r="F109" t="n">
         <v>3615600</v>
@@ -2612,16 +2612,16 @@
         <v>44803</v>
       </c>
       <c r="B110" t="n">
-        <v>11.0129976272583</v>
+        <v>11.01299858093262</v>
       </c>
       <c r="C110" t="n">
-        <v>11.16182158639716</v>
+        <v>11.16182255295894</v>
       </c>
       <c r="D110" t="n">
-        <v>10.93466875592239</v>
+        <v>10.93466970281379</v>
       </c>
       <c r="E110" t="n">
-        <v>11.11482411419572</v>
+        <v>11.11482507668773</v>
       </c>
       <c r="F110" t="n">
         <v>1284900</v>
@@ -2672,16 +2672,16 @@
         <v>44806</v>
       </c>
       <c r="B113" t="n">
-        <v>11.74145412445068</v>
+        <v>11.74145317077637</v>
       </c>
       <c r="C113" t="n">
-        <v>11.79628463916563</v>
+        <v>11.79628368103782</v>
       </c>
       <c r="D113" t="n">
-        <v>11.56129874652895</v>
+        <v>11.56129780748737</v>
       </c>
       <c r="E113" t="n">
-        <v>11.74145412445068</v>
+        <v>11.74145317077637</v>
       </c>
       <c r="F113" t="n">
         <v>3674700</v>
@@ -2872,16 +2872,16 @@
         <v>44823</v>
       </c>
       <c r="B123" t="n">
-        <v>11.28714656829834</v>
+        <v>11.28714752197266</v>
       </c>
       <c r="C123" t="n">
-        <v>11.43597126633249</v>
+        <v>11.43597223258132</v>
       </c>
       <c r="D123" t="n">
-        <v>11.1148235089428</v>
+        <v>11.11482444805718</v>
       </c>
       <c r="E123" t="n">
-        <v>11.1148235089428</v>
+        <v>11.11482444805718</v>
       </c>
       <c r="F123" t="n">
         <v>1858600</v>
@@ -2992,16 +2992,16 @@
         <v>44831</v>
       </c>
       <c r="B129" t="n">
-        <v>10.9033374786377</v>
+        <v>10.90333843231201</v>
       </c>
       <c r="C129" t="n">
-        <v>11.04432914981819</v>
+        <v>11.04433011582452</v>
       </c>
       <c r="D129" t="n">
-        <v>10.77017884407822</v>
+        <v>10.77017978610565</v>
       </c>
       <c r="E129" t="n">
-        <v>11.04432914981819</v>
+        <v>11.04433011582452</v>
       </c>
       <c r="F129" t="n">
         <v>2130200</v>
@@ -3092,16 +3092,16 @@
         <v>44838</v>
       </c>
       <c r="B134" t="n">
-        <v>11.11482524871826</v>
+        <v>11.11482429504395</v>
       </c>
       <c r="C134" t="n">
-        <v>11.32631277471268</v>
+        <v>11.32631180289231</v>
       </c>
       <c r="D134" t="n">
-        <v>11.07566155605223</v>
+        <v>11.07566060573824</v>
       </c>
       <c r="E134" t="n">
-        <v>11.20882020271549</v>
+        <v>11.20881924097621</v>
       </c>
       <c r="F134" t="n">
         <v>2406500</v>
@@ -3112,16 +3112,16 @@
         <v>44839</v>
       </c>
       <c r="B135" t="n">
-        <v>10.97383403778076</v>
+        <v>10.97383308410645</v>
       </c>
       <c r="C135" t="n">
-        <v>11.20881992290874</v>
+        <v>11.20881894881312</v>
       </c>
       <c r="D135" t="n">
-        <v>10.85634072171701</v>
+        <v>10.85633977825337</v>
       </c>
       <c r="E135" t="n">
-        <v>11.20881992290874</v>
+        <v>11.20881894881312</v>
       </c>
       <c r="F135" t="n">
         <v>5244200</v>
@@ -3152,16 +3152,16 @@
         <v>44841</v>
       </c>
       <c r="B137" t="n">
-        <v>11.02866363525391</v>
+        <v>11.02866458892822</v>
       </c>
       <c r="C137" t="n">
-        <v>11.15398923954096</v>
+        <v>11.15399020405247</v>
       </c>
       <c r="D137" t="n">
-        <v>10.94250246905644</v>
+        <v>10.9425034152802</v>
       </c>
       <c r="E137" t="n">
-        <v>10.98166690714602</v>
+        <v>10.98166785675642</v>
       </c>
       <c r="F137" t="n">
         <v>7588600</v>
@@ -3232,16 +3232,16 @@
         <v>44848</v>
       </c>
       <c r="B141" t="n">
-        <v>10.82500839233398</v>
+        <v>10.8250093460083</v>
       </c>
       <c r="C141" t="n">
-        <v>11.16182149038183</v>
+        <v>11.1618224737291</v>
       </c>
       <c r="D141" t="n">
-        <v>10.82500839233398</v>
+        <v>10.8250093460083</v>
       </c>
       <c r="E141" t="n">
-        <v>10.97383309719211</v>
+        <v>10.97383406397776</v>
       </c>
       <c r="F141" t="n">
         <v>3601200</v>
@@ -3312,16 +3312,16 @@
         <v>44854</v>
       </c>
       <c r="B145" t="n">
-        <v>10.83284187316895</v>
+        <v>10.83284282684326</v>
       </c>
       <c r="C145" t="n">
-        <v>10.98166658413194</v>
+        <v>10.98166755090811</v>
       </c>
       <c r="D145" t="n">
-        <v>10.39420227106638</v>
+       